--- a/dashboards/Reliance Group.xlsx
+++ b/dashboards/Reliance Group.xlsx
@@ -493,7 +493,7 @@
         <v>91.84999847412109</v>
       </c>
       <c r="G2" t="n">
-        <v>1088.746704101562</v>
+        <v>1088.74658203125</v>
       </c>
       <c r="H2" t="n">
         <v>100.8000030517578</v>
@@ -551,7 +551,7 @@
         <v>89.94999694824219</v>
       </c>
       <c r="G4" t="n">
-        <v>1118.526000976562</v>
+        <v>1118.526123046875</v>
       </c>
       <c r="H4" t="n">
         <v>97.05000305175781</v>
@@ -580,7 +580,7 @@
         <v>89.90000152587891</v>
       </c>
       <c r="G5" t="n">
-        <v>1094.476196289062</v>
+        <v>1094.47607421875</v>
       </c>
       <c r="H5" t="n">
         <v>100.1500015258789</v>
@@ -609,7 +609,7 @@
         <v>91</v>
       </c>
       <c r="G6" t="n">
-        <v>1103.30810546875</v>
+        <v>1103.307983398438</v>
       </c>
       <c r="H6" t="n">
         <v>98.55000305175781</v>
@@ -673,7 +673,7 @@
         <v>98.40000152587891</v>
       </c>
       <c r="I8" t="n">
-        <v>968.8118286132812</v>
+        <v>968.8118896484375</v>
       </c>
       <c r="J8" t="n">
         <v>14.30000019073486</v>
@@ -702,7 +702,7 @@
         <v>96.40000152587891</v>
       </c>
       <c r="I9" t="n">
-        <v>941.8934936523438</v>
+        <v>941.8935546875</v>
       </c>
       <c r="J9" t="n">
         <v>14.35000038146973</v>
@@ -754,7 +754,7 @@
         <v>89.59999847412109</v>
       </c>
       <c r="G11" t="n">
-        <v>1149.958618164062</v>
+        <v>1149.95849609375</v>
       </c>
       <c r="H11" t="n">
         <v>102.75</v>
@@ -783,7 +783,7 @@
         <v>91.40000152587891</v>
       </c>
       <c r="G12" t="n">
-        <v>1155.959594726562</v>
+        <v>1155.959716796875</v>
       </c>
       <c r="H12" t="n">
         <v>105.5500030517578</v>
@@ -812,7 +812,7 @@
         <v>89.80000305175781</v>
       </c>
       <c r="G13" t="n">
-        <v>1142.168334960938</v>
+        <v>1142.16845703125</v>
       </c>
       <c r="H13" t="n">
         <v>101.9499969482422</v>
@@ -841,13 +841,13 @@
         <v>90.69999694824219</v>
       </c>
       <c r="G14" t="n">
-        <v>1142.077758789062</v>
+        <v>1142.077880859375</v>
       </c>
       <c r="H14" t="n">
         <v>99.75</v>
       </c>
       <c r="I14" t="n">
-        <v>957.7103881835938</v>
+        <v>957.71044921875</v>
       </c>
       <c r="J14" t="n">
         <v>15.85000038146973</v>
@@ -870,13 +870,13 @@
         <v>88.75</v>
       </c>
       <c r="G15" t="n">
-        <v>1122.081665039062</v>
+        <v>1122.08154296875</v>
       </c>
       <c r="H15" t="n">
         <v>101.5500030517578</v>
       </c>
       <c r="I15" t="n">
-        <v>936.3428955078125</v>
+        <v>936.3428344726562</v>
       </c>
       <c r="J15" t="n">
         <v>16.54999923706055</v>
@@ -934,7 +934,7 @@
         <v>93.55000305175781</v>
       </c>
       <c r="I17" t="n">
-        <v>835.7432861328125</v>
+        <v>835.7432250976562</v>
       </c>
       <c r="J17" t="n">
         <v>15.25</v>
@@ -963,7 +963,7 @@
         <v>98.05000305175781</v>
       </c>
       <c r="I18" t="n">
-        <v>835.7432861328125</v>
+        <v>835.7432250976562</v>
       </c>
       <c r="J18" t="n">
         <v>14.75</v>
@@ -992,7 +992,7 @@
         <v>97.80000305175781</v>
       </c>
       <c r="I19" t="n">
-        <v>855.3916015625</v>
+        <v>855.3916625976562</v>
       </c>
       <c r="J19" t="n">
         <v>14.80000019073486</v>
@@ -1021,7 +1021,7 @@
         <v>102.3000030517578</v>
       </c>
       <c r="I20" t="n">
-        <v>885.7974853515625</v>
+        <v>885.7974243164062</v>
       </c>
       <c r="J20" t="n">
         <v>15.19999980926514</v>
@@ -1044,7 +1044,7 @@
         <v>82</v>
       </c>
       <c r="G21" t="n">
-        <v>1080.93408203125</v>
+        <v>1080.933959960938</v>
       </c>
       <c r="H21" t="n">
         <v>101.0500030517578</v>
@@ -1166,7 +1166,7 @@
         <v>121.3499984741211</v>
       </c>
       <c r="I25" t="n">
-        <v>898.3724975585938</v>
+        <v>898.3724365234375</v>
       </c>
       <c r="J25" t="n">
         <v>17.64999961853027</v>
@@ -1189,7 +1189,7 @@
         <v>83.25</v>
       </c>
       <c r="G26" t="n">
-        <v>1049.456176757812</v>
+        <v>1049.4560546875</v>
       </c>
       <c r="H26" t="n">
         <v>133.4499969482422</v>
@@ -1224,7 +1224,7 @@
         <v>134.4499969482422</v>
       </c>
       <c r="I27" t="n">
-        <v>865.2158813476562</v>
+        <v>865.2157592773438</v>
       </c>
       <c r="J27" t="n">
         <v>17.60000038146973</v>
@@ -1247,13 +1247,13 @@
         <v>87.75</v>
       </c>
       <c r="G28" t="n">
-        <v>1079.52978515625</v>
+        <v>1079.529907226562</v>
       </c>
       <c r="H28" t="n">
         <v>147.8500061035156</v>
       </c>
       <c r="I28" t="n">
-        <v>866.5419921875</v>
+        <v>866.5420532226562</v>
       </c>
       <c r="J28" t="n">
         <v>17</v>
@@ -1282,7 +1282,7 @@
         <v>133.1000061035156</v>
       </c>
       <c r="I29" t="n">
-        <v>879.5099487304688</v>
+        <v>879.510009765625</v>
       </c>
       <c r="J29" t="n">
         <v>16.14999961853027</v>
@@ -1334,7 +1334,7 @@
         <v>86.90000152587891</v>
       </c>
       <c r="G31" t="n">
-        <v>1059.171142578125</v>
+        <v>1059.171020507812</v>
       </c>
       <c r="H31" t="n">
         <v>120.5999984741211</v>
@@ -1363,13 +1363,13 @@
         <v>87.05000305175781</v>
       </c>
       <c r="G32" t="n">
-        <v>1095.132690429688</v>
+        <v>1095.1328125</v>
       </c>
       <c r="H32" t="n">
         <v>111.8499984741211</v>
       </c>
       <c r="I32" t="n">
-        <v>784.4610595703125</v>
+        <v>784.4609985351562</v>
       </c>
       <c r="J32" t="n">
         <v>14.55000019073486</v>
@@ -1427,7 +1427,7 @@
         <v>113.3499984741211</v>
       </c>
       <c r="I34" t="n">
-        <v>801.113037109375</v>
+        <v>801.1129760742188</v>
       </c>
       <c r="J34" t="n">
         <v>14.14999961853027</v>
@@ -1485,7 +1485,7 @@
         <v>112.6999969482422</v>
       </c>
       <c r="I36" t="n">
-        <v>750.4694213867188</v>
+        <v>750.4693603515625</v>
       </c>
       <c r="J36" t="n">
         <v>13.60000038146973</v>
@@ -1514,7 +1514,7 @@
         <v>114.3499984741211</v>
       </c>
       <c r="I37" t="n">
-        <v>725.5650634765625</v>
+        <v>725.5650024414062</v>
       </c>
       <c r="J37" t="n">
         <v>12.94999980926514</v>
@@ -1601,7 +1601,7 @@
         <v>104.5999984741211</v>
       </c>
       <c r="I40" t="n">
-        <v>681.9456176757812</v>
+        <v>681.9456787109375</v>
       </c>
       <c r="J40" t="n">
         <v>13</v>
@@ -1624,13 +1624,13 @@
         <v>76.94999694824219</v>
       </c>
       <c r="G41" t="n">
-        <v>1068.682495117188</v>
+        <v>1068.682373046875</v>
       </c>
       <c r="H41" t="n">
         <v>104.5999984741211</v>
       </c>
       <c r="I41" t="n">
-        <v>686.1209106445312</v>
+        <v>686.1209716796875</v>
       </c>
       <c r="J41" t="n">
         <v>13.05000019073486</v>
@@ -1653,13 +1653,13 @@
         <v>76.25</v>
       </c>
       <c r="G42" t="n">
-        <v>1086.346313476562</v>
+        <v>1086.34619140625</v>
       </c>
       <c r="H42" t="n">
         <v>107.5999984741211</v>
       </c>
       <c r="I42" t="n">
-        <v>692.8504638671875</v>
+        <v>692.8505249023438</v>
       </c>
       <c r="J42" t="n">
         <v>13.14999961853027</v>
@@ -1711,13 +1711,13 @@
         <v>77.5</v>
       </c>
       <c r="G44" t="n">
-        <v>1053.283203125</v>
+        <v>1053.283325195312</v>
       </c>
       <c r="H44" t="n">
         <v>103.5</v>
       </c>
       <c r="I44" t="n">
-        <v>674.7249755859375</v>
+        <v>674.7249145507812</v>
       </c>
       <c r="J44" t="n">
         <v>12.85000038146973</v>
@@ -1740,7 +1740,7 @@
         <v>73.65000152587891</v>
       </c>
       <c r="G45" t="n">
-        <v>1014.332458496094</v>
+        <v>1014.332397460938</v>
       </c>
       <c r="H45" t="n">
         <v>99.59999847412109</v>
@@ -1775,7 +1775,7 @@
         <v>101.75</v>
       </c>
       <c r="I46" t="n">
-        <v>667.504150390625</v>
+        <v>667.5040893554688</v>
       </c>
       <c r="J46" t="n">
         <v>12.80000019073486</v>
@@ -1798,13 +1798,13 @@
         <v>77.80000305175781</v>
       </c>
       <c r="G47" t="n">
-        <v>1066.214111328125</v>
+        <v>1066.213989257812</v>
       </c>
       <c r="H47" t="n">
         <v>107.5</v>
       </c>
       <c r="I47" t="n">
-        <v>693.8820190429688</v>
+        <v>693.882080078125</v>
       </c>
       <c r="J47" t="n">
         <v>13.35000038146973</v>
@@ -1856,7 +1856,7 @@
         <v>77.84999847412109</v>
       </c>
       <c r="G49" t="n">
-        <v>1086.618041992188</v>
+        <v>1086.617797851562</v>
       </c>
       <c r="H49" t="n">
         <v>122.5</v>
@@ -1920,7 +1920,7 @@
         <v>115.5500030517578</v>
       </c>
       <c r="I51" t="n">
-        <v>747.32568359375</v>
+        <v>747.3255615234375</v>
       </c>
       <c r="J51" t="n">
         <v>13.44999980926514</v>
@@ -1943,7 +1943,7 @@
         <v>77.75</v>
       </c>
       <c r="G52" t="n">
-        <v>1088.520263671875</v>
+        <v>1088.520385742188</v>
       </c>
       <c r="H52" t="n">
         <v>118.9499969482422</v>
@@ -1978,7 +1978,7 @@
         <v>116.8000030517578</v>
       </c>
       <c r="I53" t="n">
-        <v>758.7706909179688</v>
+        <v>758.770751953125</v>
       </c>
       <c r="J53" t="n">
         <v>13.75</v>
@@ -2001,7 +2001,7 @@
         <v>79.15000152587891</v>
       </c>
       <c r="G54" t="n">
-        <v>1117.529663085938</v>
+        <v>1117.52978515625</v>
       </c>
       <c r="H54" t="n">
         <v>115.4000015258789</v>
@@ -2036,7 +2036,7 @@
         <v>113.1500015258789</v>
       </c>
       <c r="I55" t="n">
-        <v>751.10791015625</v>
+        <v>751.1078491210938</v>
       </c>
       <c r="J55" t="n">
         <v>13</v>
@@ -2059,13 +2059,13 @@
         <v>81.65000152587891</v>
       </c>
       <c r="G56" t="n">
-        <v>1150.049072265625</v>
+        <v>1150.049194335938</v>
       </c>
       <c r="H56" t="n">
         <v>111.8000030517578</v>
       </c>
       <c r="I56" t="n">
-        <v>756.5111694335938</v>
+        <v>756.51123046875</v>
       </c>
       <c r="J56" t="n">
         <v>12.85000038146973</v>
@@ -2088,7 +2088,7 @@
         <v>85.55000305175781</v>
       </c>
       <c r="G57" t="n">
-        <v>1167.916748046875</v>
+        <v>1167.916625976562</v>
       </c>
       <c r="H57" t="n">
         <v>109.6999969482422</v>
@@ -2117,13 +2117,13 @@
         <v>85.59999847412109</v>
       </c>
       <c r="G58" t="n">
-        <v>1175.706909179688</v>
+        <v>1175.70703125</v>
       </c>
       <c r="H58" t="n">
         <v>109.1999969482422</v>
       </c>
       <c r="I58" t="n">
-        <v>755.5779418945312</v>
+        <v>755.577880859375</v>
       </c>
       <c r="J58" t="n">
         <v>13</v>
@@ -2146,13 +2146,13 @@
         <v>87.59999847412109</v>
       </c>
       <c r="G59" t="n">
-        <v>1187.528198242188</v>
+        <v>1187.5283203125</v>
       </c>
       <c r="H59" t="n">
         <v>100.6999969482422</v>
       </c>
       <c r="I59" t="n">
-        <v>731.4595336914062</v>
+        <v>731.4595947265625</v>
       </c>
       <c r="J59" t="n">
         <v>12.35000038146973</v>
@@ -2181,7 +2181,7 @@
         <v>110.75</v>
       </c>
       <c r="I60" t="n">
-        <v>735.4383544921875</v>
+        <v>735.4382934570312</v>
       </c>
       <c r="J60" t="n">
         <v>12.94999980926514</v>
@@ -2204,7 +2204,7 @@
         <v>85.80000305175781</v>
       </c>
       <c r="G61" t="n">
-        <v>1210.627075195312</v>
+        <v>1210.626953125</v>
       </c>
       <c r="H61" t="n">
         <v>114.8000030517578</v>
@@ -2239,7 +2239,7 @@
         <v>112.3000030517578</v>
       </c>
       <c r="I62" t="n">
-        <v>764.6162109375</v>
+        <v>764.6161499023438</v>
       </c>
       <c r="J62" t="n">
         <v>13.5</v>
@@ -2262,13 +2262,13 @@
         <v>87.84999847412109</v>
       </c>
       <c r="G63" t="n">
-        <v>1202.882080078125</v>
+        <v>1202.881958007812</v>
       </c>
       <c r="H63" t="n">
         <v>122.6500015258789</v>
       </c>
       <c r="I63" t="n">
-        <v>790.2572631835938</v>
+        <v>790.2572021484375</v>
       </c>
       <c r="J63" t="n">
         <v>14.14999961853027</v>
@@ -2297,7 +2297,7 @@
         <v>124.6999969482422</v>
       </c>
       <c r="I64" t="n">
-        <v>794.3343505859375</v>
+        <v>794.3342895507812</v>
       </c>
       <c r="J64" t="n">
         <v>14.85000038146973</v>
@@ -2320,13 +2320,13 @@
         <v>93.05000305175781</v>
       </c>
       <c r="G65" t="n">
-        <v>1189.385009765625</v>
+        <v>1189.385131835938</v>
       </c>
       <c r="H65" t="n">
         <v>132.1499938964844</v>
       </c>
       <c r="I65" t="n">
-        <v>804.305908203125</v>
+        <v>804.3058471679688</v>
       </c>
       <c r="J65" t="n">
         <v>15.55000019073486</v>
@@ -2349,13 +2349,13 @@
         <v>94.5</v>
       </c>
       <c r="G66" t="n">
-        <v>1186.214721679688</v>
+        <v>1186.21484375</v>
       </c>
       <c r="H66" t="n">
         <v>136.1499938964844</v>
       </c>
       <c r="I66" t="n">
-        <v>822.1367797851562</v>
+        <v>822.13671875</v>
       </c>
       <c r="J66" t="n">
         <v>16.29999923706055</v>
@@ -2413,7 +2413,7 @@
         <v>126.75</v>
       </c>
       <c r="I68" t="n">
-        <v>815.8491821289062</v>
+        <v>815.8493041992188</v>
       </c>
       <c r="J68" t="n">
         <v>15.60000038146973</v>
@@ -2436,13 +2436,13 @@
         <v>98.40000152587891</v>
       </c>
       <c r="G69" t="n">
-        <v>1182.206298828125</v>
+        <v>1182.206420898438</v>
       </c>
       <c r="H69" t="n">
         <v>125.8499984741211</v>
       </c>
       <c r="I69" t="n">
-        <v>816.3896484375</v>
+        <v>816.3895874023438</v>
       </c>
       <c r="J69" t="n">
         <v>15.69999980926514</v>
@@ -2471,7 +2471,7 @@
         <v>122.9499969482422</v>
       </c>
       <c r="I70" t="n">
-        <v>794.8746337890625</v>
+        <v>794.8745727539062</v>
       </c>
       <c r="J70" t="n">
         <v>15.14999961853027</v>
@@ -2494,7 +2494,7 @@
         <v>93.80000305175781</v>
       </c>
       <c r="G71" t="n">
-        <v>1155.68798828125</v>
+        <v>1155.688110351562</v>
       </c>
       <c r="H71" t="n">
         <v>123.4000015258789</v>
@@ -2552,7 +2552,7 @@
         <v>99.09999847412109</v>
       </c>
       <c r="G73" t="n">
-        <v>1196.065673828125</v>
+        <v>1196.065551757812</v>
       </c>
       <c r="H73" t="n">
         <v>123.5999984741211</v>
@@ -2610,7 +2610,7 @@
         <v>103.4499969482422</v>
       </c>
       <c r="G75" t="n">
-        <v>1260.062866210938</v>
+        <v>1260.06298828125</v>
       </c>
       <c r="H75" t="n">
         <v>130.3000030517578</v>
@@ -2639,13 +2639,13 @@
         <v>98.90000152587891</v>
       </c>
       <c r="G76" t="n">
-        <v>1249.509887695312</v>
+        <v>1249.510009765625</v>
       </c>
       <c r="H76" t="n">
         <v>128.8999938964844</v>
       </c>
       <c r="I76" t="n">
-        <v>962.5242919921875</v>
+        <v>962.5243530273438</v>
       </c>
       <c r="J76" t="n">
         <v>14.94999980926514</v>
@@ -2674,7 +2674,7 @@
         <v>123.25</v>
       </c>
       <c r="I77" t="n">
-        <v>902.3511962890625</v>
+        <v>902.3511352539062</v>
       </c>
       <c r="J77" t="n">
         <v>14.55000019073486</v>
@@ -2697,7 +2697,7 @@
         <v>114.1999969482422</v>
       </c>
       <c r="G78" t="n">
-        <v>1257.1416015625</v>
+        <v>1257.141479492188</v>
       </c>
       <c r="H78" t="n">
         <v>121.1999969482422</v>
@@ -2726,7 +2726,7 @@
         <v>113.6999969482422</v>
       </c>
       <c r="G79" t="n">
-        <v>1258.364501953125</v>
+        <v>1258.364624023438</v>
       </c>
       <c r="H79" t="n">
         <v>123</v>
@@ -2755,13 +2755,13 @@
         <v>91.34999847412109</v>
       </c>
       <c r="G80" t="n">
-        <v>1277.160766601562</v>
+        <v>1277.16064453125</v>
       </c>
       <c r="H80" t="n">
         <v>120.5999984741211</v>
       </c>
       <c r="I80" t="n">
-        <v>1080.660034179688</v>
+        <v>1080.66015625</v>
       </c>
       <c r="J80" t="n">
         <v>13.94999980926514</v>
@@ -2813,13 +2813,13 @@
         <v>85</v>
       </c>
       <c r="G82" t="n">
-        <v>1259.315673828125</v>
+        <v>1259.315795898438</v>
       </c>
       <c r="H82" t="n">
         <v>124.25</v>
       </c>
       <c r="I82" t="n">
-        <v>1096.47705078125</v>
+        <v>1096.476928710938</v>
       </c>
       <c r="J82" t="n">
         <v>14.19999980926514</v>
@@ -2848,7 +2848,7 @@
         <v>116.0999984741211</v>
       </c>
       <c r="I83" t="n">
-        <v>1001.13330078125</v>
+        <v>1001.133361816406</v>
       </c>
       <c r="J83" t="n">
         <v>13.55000019073486</v>
@@ -2871,7 +2871,7 @@
         <v>80.30000305175781</v>
       </c>
       <c r="G84" t="n">
-        <v>1196.11083984375</v>
+        <v>1196.110961914062</v>
       </c>
       <c r="H84" t="n">
         <v>115.0999984741211</v>
@@ -2935,7 +2935,7 @@
         <v>112.3000030517578</v>
       </c>
       <c r="I86" t="n">
-        <v>1002.950866699219</v>
+        <v>1002.950927734375</v>
       </c>
       <c r="J86" t="n">
         <v>13.69999980926514</v>
@@ -2958,13 +2958,13 @@
         <v>72.80000305175781</v>
       </c>
       <c r="G87" t="n">
-        <v>1120.813354492188</v>
+        <v>1120.813232421875</v>
       </c>
       <c r="H87" t="n">
         <v>108.1999969482422</v>
       </c>
       <c r="I87" t="n">
-        <v>953.9772338867188</v>
+        <v>953.977294921875</v>
       </c>
       <c r="J87" t="n">
         <v>13.10000038146973</v>
@@ -2987,13 +2987,13 @@
         <v>68.44999694824219</v>
       </c>
       <c r="G88" t="n">
-        <v>1109.331787109375</v>
+        <v>1109.331909179688</v>
       </c>
       <c r="H88" t="n">
         <v>101</v>
       </c>
       <c r="I88" t="n">
-        <v>964.9312744140625</v>
+        <v>964.9312133789062</v>
       </c>
       <c r="J88" t="n">
         <v>13</v>
@@ -3016,7 +3016,7 @@
         <v>72.75</v>
       </c>
       <c r="G89" t="n">
-        <v>1086.731201171875</v>
+        <v>1086.731323242188</v>
       </c>
       <c r="H89" t="n">
         <v>100.9000015258789</v>
@@ -3045,13 +3045,13 @@
         <v>76.65000152587891</v>
       </c>
       <c r="G90" t="n">
-        <v>1099.050537109375</v>
+        <v>1099.050659179688</v>
       </c>
       <c r="H90" t="n">
         <v>102.0500030517578</v>
       </c>
       <c r="I90" t="n">
-        <v>955.74560546875</v>
+        <v>955.7456665039062</v>
       </c>
       <c r="J90" t="n">
         <v>12.5</v>
@@ -3074,13 +3074,13 @@
         <v>74.59999847412109</v>
       </c>
       <c r="G91" t="n">
-        <v>1099.322387695312</v>
+        <v>1099.322265625</v>
       </c>
       <c r="H91" t="n">
         <v>98.30000305175781</v>
       </c>
       <c r="I91" t="n">
-        <v>964.9312744140625</v>
+        <v>964.9312133789062</v>
       </c>
       <c r="J91" t="n">
         <v>11.89999961853027</v>
@@ -3103,7 +3103,7 @@
         <v>77.90000152587891</v>
       </c>
       <c r="G92" t="n">
-        <v>1145.497314453125</v>
+        <v>1145.497192382812</v>
       </c>
       <c r="H92" t="n">
         <v>107.0500030517578</v>
@@ -3161,7 +3161,7 @@
         <v>75.65000152587891</v>
       </c>
       <c r="G94" t="n">
-        <v>1123.168579101562</v>
+        <v>1123.168334960938</v>
       </c>
       <c r="H94" t="n">
         <v>102.0999984741211</v>
@@ -3225,7 +3225,7 @@
         <v>101.6999969482422</v>
       </c>
       <c r="I96" t="n">
-        <v>979.0288696289062</v>
+        <v>979.0289916992188</v>
       </c>
       <c r="J96" t="n">
         <v>12.39999961853027</v>
@@ -3248,7 +3248,7 @@
         <v>78.94999694824219</v>
       </c>
       <c r="G97" t="n">
-        <v>1184.765380859375</v>
+        <v>1184.765258789062</v>
       </c>
       <c r="H97" t="n">
         <v>100.9000015258789</v>
@@ -3312,7 +3312,7 @@
         <v>100.3499984741211</v>
       </c>
       <c r="I99" t="n">
-        <v>832.8450927734375</v>
+        <v>832.8451538085938</v>
       </c>
       <c r="J99" t="n">
         <v>11.89999961853027</v>
@@ -3335,13 +3335,13 @@
         <v>71.65000152587891</v>
       </c>
       <c r="G100" t="n">
-        <v>1166.308837890625</v>
+        <v>1166.308959960938</v>
       </c>
       <c r="H100" t="n">
         <v>99.84999847412109</v>
       </c>
       <c r="I100" t="n">
-        <v>871.9945068359375</v>
+        <v>871.9944458007812</v>
       </c>
       <c r="J100" t="n">
         <v>11.85000038146973</v>
@@ -3399,7 +3399,7 @@
         <v>107.9499969482422</v>
       </c>
       <c r="I102" t="n">
-        <v>909.1299438476562</v>
+        <v>909.1298217773438</v>
       </c>
       <c r="J102" t="n">
         <v>12.60000038146973</v>
@@ -3428,7 +3428,7 @@
         <v>108.0500030517578</v>
       </c>
       <c r="I103" t="n">
-        <v>929.4660034179688</v>
+        <v>929.4659423828125</v>
       </c>
       <c r="J103" t="n">
         <v>13.19999980926514</v>
@@ -3451,13 +3451,13 @@
         <v>76.5</v>
       </c>
       <c r="G104" t="n">
-        <v>1233.884521484375</v>
+        <v>1233.884399414062</v>
       </c>
       <c r="H104" t="n">
         <v>109.3000030517578</v>
       </c>
       <c r="I104" t="n">
-        <v>936.24462890625</v>
+        <v>936.2446899414062</v>
       </c>
       <c r="J104" t="n">
         <v>13.85000038146973</v>
@@ -3480,13 +3480,13 @@
         <v>76.59999847412109</v>
       </c>
       <c r="G105" t="n">
-        <v>1258.88525390625</v>
+        <v>1258.885375976562</v>
       </c>
       <c r="H105" t="n">
         <v>106.5999984741211</v>
       </c>
       <c r="I105" t="n">
-        <v>965.9136962890625</v>
+        <v>965.9136352539062</v>
       </c>
       <c r="J105" t="n">
         <v>13.25</v>
@@ -3538,13 +3538,13 @@
         <v>75.90000152587891</v>
       </c>
       <c r="G107" t="n">
-        <v>1255.828125</v>
+        <v>1255.828247070312</v>
       </c>
       <c r="H107" t="n">
         <v>105.5</v>
       </c>
       <c r="I107" t="n">
-        <v>978.390380859375</v>
+        <v>978.3903198242188</v>
       </c>
       <c r="J107" t="n">
         <v>14.30000019073486</v>
@@ -3596,13 +3596,13 @@
         <v>80.94999694824219</v>
       </c>
       <c r="G109" t="n">
-        <v>1267.604125976562</v>
+        <v>1267.60400390625</v>
       </c>
       <c r="H109" t="n">
         <v>104.4499969482422</v>
       </c>
       <c r="I109" t="n">
-        <v>974.75537109375</v>
+        <v>974.7554321289062</v>
       </c>
       <c r="J109" t="n">
         <v>13.94999980926514</v>
@@ -3683,7 +3683,7 @@
         <v>72.84999847412109</v>
       </c>
       <c r="G112" t="n">
-        <v>1190.313598632812</v>
+        <v>1190.3134765625</v>
       </c>
       <c r="H112" t="n">
         <v>95.75</v>
@@ -3712,7 +3712,7 @@
         <v>74.59999847412109</v>
       </c>
       <c r="G113" t="n">
-        <v>1175.910888671875</v>
+        <v>1175.910766601562</v>
       </c>
       <c r="H113" t="n">
         <v>95.5</v>
@@ -3741,7 +3741,7 @@
         <v>67.25</v>
       </c>
       <c r="G114" t="n">
-        <v>1159.469848632812</v>
+        <v>1159.469970703125</v>
       </c>
       <c r="H114" t="n">
         <v>95.40000152587891</v>
@@ -3776,7 +3776,7 @@
         <v>95.59999847412109</v>
       </c>
       <c r="I115" t="n">
-        <v>833.4837646484375</v>
+        <v>833.4837036132812</v>
       </c>
       <c r="J115" t="n">
         <v>12.14999961853027</v>
@@ -3805,7 +3805,7 @@
         <v>90.65000152587891</v>
       </c>
       <c r="I116" t="n">
-        <v>730.1824340820312</v>
+        <v>730.182373046875</v>
       </c>
       <c r="J116" t="n">
         <v>11.10000038146973</v>
@@ -3828,7 +3828,7 @@
         <v>62.29999923706055</v>
       </c>
       <c r="G117" t="n">
-        <v>1170.38525390625</v>
+        <v>1170.385131835938</v>
       </c>
       <c r="H117" t="n">
         <v>94.5</v>
@@ -3886,13 +3886,13 @@
         <v>61.40000152587891</v>
       </c>
       <c r="G119" t="n">
-        <v>1116.419921875</v>
+        <v>1116.420043945312</v>
       </c>
       <c r="H119" t="n">
         <v>90.30000305175781</v>
       </c>
       <c r="I119" t="n">
-        <v>755.8726196289062</v>
+        <v>755.8726806640625</v>
       </c>
       <c r="J119" t="n">
         <v>11.60000038146973</v>
@@ -3921,7 +3921,7 @@
         <v>90.69999694824219</v>
       </c>
       <c r="I120" t="n">
-        <v>775.570068359375</v>
+        <v>775.5701293945312</v>
       </c>
       <c r="J120" t="n">
         <v>11.85000038146973</v>
@@ -3950,7 +3950,7 @@
         <v>93.09999847412109</v>
       </c>
       <c r="I121" t="n">
-        <v>801.5060424804688</v>
+        <v>801.5059814453125</v>
       </c>
       <c r="J121" t="n">
         <v>11.80000019073486</v>
@@ -4037,7 +4037,7 @@
         <v>90.59999847412109</v>
       </c>
       <c r="I124" t="n">
-        <v>935.9990844726562</v>
+        <v>935.9990234375</v>
       </c>
       <c r="J124" t="n">
         <v>11.5</v>
@@ -4066,7 +4066,7 @@
         <v>91.09999847412109</v>
       </c>
       <c r="I125" t="n">
-        <v>920.820556640625</v>
+        <v>920.8206787109375</v>
       </c>
       <c r="J125" t="n">
         <v>11.39999961853027</v>
@@ -4095,7 +4095,7 @@
         <v>94.5</v>
       </c>
       <c r="I126" t="n">
-        <v>935.704345703125</v>
+        <v>935.7042846679688</v>
       </c>
       <c r="J126" t="n">
         <v>11.35000038146973</v>
@@ -4147,7 +4147,7 @@
         <v>65.30000305175781</v>
       </c>
       <c r="G128" t="n">
-        <v>1092.3701171875</v>
+        <v>1092.369995117188</v>
       </c>
       <c r="H128" t="n">
         <v>91.75</v>
@@ -4182,7 +4182,7 @@
         <v>94.90000152587891</v>
       </c>
       <c r="I129" t="n">
-        <v>936.4902954101562</v>
+        <v>936.490234375</v>
       </c>
       <c r="J129" t="n">
         <v>11.44999980926514</v>
@@ -4234,13 +4234,13 @@
         <v>68.30000305175781</v>
       </c>
       <c r="G131" t="n">
-        <v>1097.82763671875</v>
+        <v>1097.827758789062</v>
       </c>
       <c r="H131" t="n">
         <v>101.3499984741211</v>
       </c>
       <c r="I131" t="n">
-        <v>940.5673217773438</v>
+        <v>940.5672607421875</v>
       </c>
       <c r="J131" t="n">
         <v>11.64999961853027</v>
@@ -4263,13 +4263,13 @@
         <v>69.19999694824219</v>
       </c>
       <c r="G132" t="n">
-        <v>1096.265014648438</v>
+        <v>1096.26513671875</v>
       </c>
       <c r="H132" t="n">
         <v>102.5999984741211</v>
       </c>
       <c r="I132" t="n">
-        <v>951.2264404296875</v>
+        <v>951.2265625</v>
       </c>
       <c r="J132" t="n">
         <v>11.5</v>
@@ -4292,13 +4292,13 @@
         <v>70.59999847412109</v>
       </c>
       <c r="G133" t="n">
-        <v>1076.8349609375</v>
+        <v>1076.834838867188</v>
       </c>
       <c r="H133" t="n">
         <v>101.6500015258789</v>
       </c>
       <c r="I133" t="n">
-        <v>945.1846313476562</v>
+        <v>945.1845703125</v>
       </c>
       <c r="J133" t="n">
         <v>11.5</v>
@@ -4321,7 +4321,7 @@
         <v>69.75</v>
       </c>
       <c r="G134" t="n">
-        <v>1085.712036132812</v>
+        <v>1085.712158203125</v>
       </c>
       <c r="H134" t="n">
         <v>100.4000015258789</v>
@@ -4350,13 +4350,13 @@
         <v>68.34999847412109</v>
       </c>
       <c r="G135" t="n">
-        <v>1087.818115234375</v>
+        <v>1087.818237304688</v>
       </c>
       <c r="H135" t="n">
         <v>99.44999694824219</v>
       </c>
       <c r="I135" t="n">
-        <v>945.33203125</v>
+        <v>945.3319702148438</v>
       </c>
       <c r="J135" t="n">
         <v>11.30000019073486</v>
@@ -4414,7 +4414,7 @@
         <v>102.3000030517578</v>
       </c>
       <c r="I137" t="n">
-        <v>978.8324584960938</v>
+        <v>978.8323974609375</v>
       </c>
       <c r="J137" t="n">
         <v>11.80000019073486</v>
@@ -4437,13 +4437,13 @@
         <v>67</v>
       </c>
       <c r="G138" t="n">
-        <v>1133.653564453125</v>
+        <v>1133.6533203125</v>
       </c>
       <c r="H138" t="n">
         <v>104.4000015258789</v>
       </c>
       <c r="I138" t="n">
-        <v>959.67529296875</v>
+        <v>959.6753540039062</v>
       </c>
       <c r="J138" t="n">
         <v>11.85000038146973</v>
@@ -4466,7 +4466,7 @@
         <v>65</v>
       </c>
       <c r="G139" t="n">
-        <v>1126.089721679688</v>
+        <v>1126.08984375</v>
       </c>
       <c r="H139" t="n">
         <v>105.8000030517578</v>
@@ -4495,7 +4495,7 @@
         <v>63.75</v>
       </c>
       <c r="G140" t="n">
-        <v>1133.698852539062</v>
+        <v>1133.698974609375</v>
       </c>
       <c r="H140" t="n">
         <v>104.5</v>
@@ -4553,7 +4553,7 @@
         <v>62.90000152587891</v>
       </c>
       <c r="G142" t="n">
-        <v>1096.740600585938</v>
+        <v>1096.74072265625</v>
       </c>
       <c r="H142" t="n">
         <v>113.9000015258789</v>
@@ -4582,7 +4582,7 @@
         <v>64.90000152587891</v>
       </c>
       <c r="G143" t="n">
-        <v>1095.699096679688</v>
+        <v>1095.69921875</v>
       </c>
       <c r="H143" t="n">
         <v>115.8499984741211</v>
@@ -4611,7 +4611,7 @@
         <v>65.15000152587891</v>
       </c>
       <c r="G144" t="n">
-        <v>1112.864624023438</v>
+        <v>1112.86474609375</v>
       </c>
       <c r="H144" t="n">
         <v>114.25</v>
@@ -4640,13 +4640,13 @@
         <v>64.90000152587891</v>
       </c>
       <c r="G145" t="n">
-        <v>1136.574951171875</v>
+        <v>1136.57470703125</v>
       </c>
       <c r="H145" t="n">
         <v>117.0999984741211</v>
       </c>
       <c r="I145" t="n">
-        <v>964.6856079101562</v>
+        <v>964.6856689453125</v>
       </c>
       <c r="J145" t="n">
         <v>12.39999961853027</v>
@@ -4669,13 +4669,13 @@
         <v>66.94999694824219</v>
       </c>
       <c r="G146" t="n">
-        <v>1166.195678710938</v>
+        <v>1166.19580078125</v>
       </c>
       <c r="H146" t="n">
         <v>123.25</v>
       </c>
       <c r="I146" t="n">
-        <v>1014.592529296875</v>
+        <v>1014.592407226562</v>
       </c>
       <c r="J146" t="n">
         <v>13</v>
@@ -4698,7 +4698,7 @@
         <v>68.05000305175781</v>
       </c>
       <c r="G147" t="n">
-        <v>1170.634399414062</v>
+        <v>1170.634155273438</v>
       </c>
       <c r="H147" t="n">
         <v>128.6999969482422</v>
@@ -4733,7 +4733,7 @@
         <v>125.0500030517578</v>
       </c>
       <c r="I148" t="n">
-        <v>966.06103515625</v>
+        <v>966.0609741210938</v>
       </c>
       <c r="J148" t="n">
         <v>13</v>
@@ -4762,7 +4762,7 @@
         <v>121.3499984741211</v>
       </c>
       <c r="I149" t="n">
-        <v>952.7492065429688</v>
+        <v>952.7493286132812</v>
       </c>
       <c r="J149" t="n">
         <v>13.19999980926514</v>
@@ -4785,13 +4785,13 @@
         <v>68.09999847412109</v>
       </c>
       <c r="G150" t="n">
-        <v>1147.69384765625</v>
+        <v>1147.693969726562</v>
       </c>
       <c r="H150" t="n">
         <v>120</v>
       </c>
       <c r="I150" t="n">
-        <v>942.0408325195312</v>
+        <v>942.0409545898438</v>
       </c>
       <c r="J150" t="n">
         <v>13.14999961853027</v>
@@ -4843,13 +4843,13 @@
         <v>66.65000152587891</v>
       </c>
       <c r="G152" t="n">
-        <v>1169.660522460938</v>
+        <v>1169.660400390625</v>
       </c>
       <c r="H152" t="n">
         <v>117.5500030517578</v>
       </c>
       <c r="I152" t="n">
-        <v>944.4968872070312</v>
+        <v>944.4969482421875</v>
       </c>
       <c r="J152" t="n">
         <v>14.14999961853027</v>
@@ -4872,7 +4872,7 @@
         <v>67.19999694824219</v>
       </c>
       <c r="G153" t="n">
-        <v>1173.5556640625</v>
+        <v>1173.555541992188</v>
       </c>
       <c r="H153" t="n">
         <v>115.3499984741211</v>
@@ -4907,7 +4907,7 @@
         <v>115.1500015258789</v>
       </c>
       <c r="I154" t="n">
-        <v>954.0263671875</v>
+        <v>954.0264282226562</v>
       </c>
       <c r="J154" t="n">
         <v>13.39999961853027</v>
@@ -4994,7 +4994,7 @@
         <v>129.8999938964844</v>
       </c>
       <c r="I157" t="n">
-        <v>1020.880004882812</v>
+        <v>1020.8798828125</v>
       </c>
       <c r="J157" t="n">
         <v>14.19999980926514</v>
@@ -5075,7 +5075,7 @@
         <v>72.25</v>
       </c>
       <c r="G160" t="n">
-        <v>1202.694458007812</v>
+        <v>1202.694580078125</v>
       </c>
       <c r="H160" t="n">
         <v>138.6999969482422</v>
@@ -5104,13 +5104,13 @@
         <v>74.15000152587891</v>
       </c>
       <c r="G161" t="n">
-        <v>1199.491088867188</v>
+        <v>1199.490966796875</v>
       </c>
       <c r="H161" t="n">
         <v>139.6999969482422</v>
       </c>
       <c r="I161" t="n">
-        <v>1007.224426269531</v>
+        <v>1007.224365234375</v>
       </c>
       <c r="J161" t="n">
         <v>15.30000019073486</v>
@@ -5168,7 +5168,7 @@
         <v>157.3500061035156</v>
       </c>
       <c r="I163" t="n">
-        <v>997.10546875</v>
+        <v>997.1054077148438</v>
       </c>
       <c r="J163" t="n">
         <v>16.25</v>
@@ -5191,7 +5191,7 @@
         <v>69.65000152587891</v>
       </c>
       <c r="G164" t="n">
-        <v>1180.36083984375</v>
+        <v>1180.360961914062</v>
       </c>
       <c r="H164" t="n">
         <v>158.75</v>
@@ -5220,7 +5220,7 @@
         <v>70.59999847412109</v>
       </c>
       <c r="G165" t="n">
-        <v>1198.672973632812</v>
+        <v>1198.673095703125</v>
       </c>
       <c r="H165" t="n">
         <v>162</v>
@@ -5284,7 +5284,7 @@
         <v>179.1499938964844</v>
       </c>
       <c r="I167" t="n">
-        <v>1082.084594726562</v>
+        <v>1082.084716796875</v>
       </c>
       <c r="J167" t="n">
         <v>21.20000076293945</v>
@@ -5307,7 +5307,7 @@
         <v>75.59999847412109</v>
       </c>
       <c r="G168" t="n">
-        <v>1167.705932617188</v>
+        <v>1167.7060546875</v>
       </c>
       <c r="H168" t="n">
         <v>182.6999969482422</v>
@@ -5394,7 +5394,7 @@
         <v>73.65000152587891</v>
       </c>
       <c r="G171" t="n">
-        <v>1174.79443359375</v>
+        <v>1174.794677734375</v>
       </c>
       <c r="H171" t="n">
         <v>180.3000030517578</v>
@@ -5429,7 +5429,7 @@
         <v>162.4499969482422</v>
       </c>
       <c r="I172" t="n">
-        <v>1153.801147460938</v>
+        <v>1153.801025390625</v>
       </c>
       <c r="J172" t="n">
         <v>19.20000076293945</v>
@@ -5452,7 +5452,7 @@
         <v>73.90000152587891</v>
       </c>
       <c r="G173" t="n">
-        <v>1180.542602539062</v>
+        <v>1180.542724609375</v>
       </c>
       <c r="H173" t="n">
         <v>174.1999969482422</v>
@@ -5539,7 +5539,7 @@
         <v>71.75</v>
       </c>
       <c r="G176" t="n">
-        <v>1164.479858398438</v>
+        <v>1164.479736328125</v>
       </c>
       <c r="H176" t="n">
         <v>154.4499969482422</v>
@@ -5568,13 +5568,13 @@
         <v>68.65000152587891</v>
       </c>
       <c r="G177" t="n">
-        <v>1135.625732421875</v>
+        <v>1135.625610351562</v>
       </c>
       <c r="H177" t="n">
         <v>156.3500061035156</v>
       </c>
       <c r="I177" t="n">
-        <v>1119.121826171875</v>
+        <v>1119.121704101562</v>
       </c>
       <c r="J177" t="n">
         <v>18.45000076293945</v>
@@ -5742,7 +5742,7 @@
         <v>64</v>
       </c>
       <c r="G183" t="n">
-        <v>1080.257690429688</v>
+        <v>1080.257568359375</v>
       </c>
       <c r="H183" t="n">
         <v>137.1999969482422</v>
@@ -5829,7 +5829,7 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G186" t="n">
-        <v>1056.606201171875</v>
+        <v>1056.606323242188</v>
       </c>
       <c r="H186" t="n">
         <v>137.6499938964844</v>
@@ -5858,7 +5858,7 @@
         <v>64.59999847412109</v>
       </c>
       <c r="G187" t="n">
-        <v>1080.439453125</v>
+        <v>1080.439331054688</v>
       </c>
       <c r="H187" t="n">
         <v>136.6999969482422</v>
@@ -5887,7 +5887,7 @@
         <v>63.95000076293945</v>
       </c>
       <c r="G188" t="n">
-        <v>1076.690673828125</v>
+        <v>1076.690551757812</v>
       </c>
       <c r="H188" t="n">
         <v>135.4499969482422</v>
@@ -5916,7 +5916,7 @@
         <v>66</v>
       </c>
       <c r="G189" t="n">
-        <v>1096.547729492188</v>
+        <v>1096.547607421875</v>
       </c>
       <c r="H189" t="n">
         <v>137.5500030517578</v>
@@ -5945,7 +5945,7 @@
         <v>67.30000305175781</v>
       </c>
       <c r="G190" t="n">
-        <v>1100.591552734375</v>
+        <v>1100.591796875</v>
       </c>
       <c r="H190" t="n">
         <v>144.3999938964844</v>
@@ -6003,7 +6003,7 @@
         <v>67.25</v>
       </c>
       <c r="G192" t="n">
-        <v>1093.185180664062</v>
+        <v>1093.185302734375</v>
       </c>
       <c r="H192" t="n">
         <v>157.6999969482422</v>
@@ -6148,7 +6148,7 @@
         <v>66.40000152587891</v>
       </c>
       <c r="G197" t="n">
-        <v>1094.525634765625</v>
+        <v>1094.525512695312</v>
       </c>
       <c r="H197" t="n">
         <v>138.6999969482422</v>
@@ -6206,7 +6206,7 @@
         <v>65.59999847412109</v>
       </c>
       <c r="G199" t="n">
-        <v>1133.217407226562</v>
+        <v>1133.217529296875</v>
       </c>
       <c r="H199" t="n">
         <v>141.3500061035156</v>
@@ -6235,7 +6235,7 @@
         <v>65.09999847412109</v>
       </c>
       <c r="G200" t="n">
-        <v>1136.261840820312</v>
+        <v>1136.261962890625</v>
       </c>
       <c r="H200" t="n">
         <v>139.1000061035156</v>
@@ -6264,7 +6264,7 @@
         <v>63.70000076293945</v>
       </c>
       <c r="G201" t="n">
-        <v>1123.084350585938</v>
+        <v>1123.084228515625</v>
       </c>
       <c r="H201" t="n">
         <v>139.1499938964844</v>
@@ -6293,7 +6293,7 @@
         <v>64.15000152587891</v>
       </c>
       <c r="G202" t="n">
-        <v>1126.833251953125</v>
+        <v>1126.833129882812</v>
       </c>
       <c r="H202" t="n">
         <v>139.1499938964844</v>
@@ -6322,7 +6322,7 @@
         <v>65.05000305175781</v>
       </c>
       <c r="G203" t="n">
-        <v>1109.429809570312</v>
+        <v>1109.4296875</v>
       </c>
       <c r="H203" t="n">
         <v>141.6000061035156</v>
@@ -6351,7 +6351,7 @@
         <v>64.30000305175781</v>
       </c>
       <c r="G204" t="n">
-        <v>1113.791870117188</v>
+        <v>1113.7919921875</v>
       </c>
       <c r="H204" t="n">
         <v>141.8500061035156</v>
@@ -6380,7 +6380,7 @@
         <v>63.25</v>
       </c>
       <c r="G205" t="n">
-        <v>1147.871826171875</v>
+        <v>1147.871704101562</v>
       </c>
       <c r="H205" t="n">
         <v>141.8999938964844</v>
@@ -6467,7 +6467,7 @@
         <v>63.20000076293945</v>
       </c>
       <c r="G208" t="n">
-        <v>1156.732299804688</v>
+        <v>1156.732421875</v>
       </c>
       <c r="H208" t="n">
         <v>140.5500030517578</v>
@@ -6583,7 +6583,7 @@
         <v>65.25</v>
       </c>
       <c r="G212" t="n">
-        <v>1183.246337890625</v>
+        <v>1183.246459960938</v>
       </c>
       <c r="H212" t="n">
         <v>146.6499938964844</v>
@@ -6670,7 +6670,7 @@
         <v>64.05000305175781</v>
       </c>
       <c r="G215" t="n">
-        <v>1190.085083007812</v>
+        <v>1190.0849609375</v>
       </c>
       <c r="H215" t="n">
         <v>153.3999938964844</v>
@@ -6699,7 +6699,7 @@
         <v>63.04999923706055</v>
       </c>
       <c r="G216" t="n">
-        <v>1184.745849609375</v>
+        <v>1184.745971679688</v>
       </c>
       <c r="H216" t="n">
         <v>151.3500061035156</v>
@@ -6728,7 +6728,7 @@
         <v>62.54999923706055</v>
       </c>
       <c r="G217" t="n">
-        <v>1177.95263671875</v>
+        <v>1177.952758789062</v>
       </c>
       <c r="H217" t="n">
         <v>148.6499938964844</v>
@@ -6786,7 +6786,7 @@
         <v>61.59999847412109</v>
       </c>
       <c r="G219" t="n">
-        <v>1180.36083984375</v>
+        <v>1180.360961914062</v>
       </c>
       <c r="H219" t="n">
         <v>147.6499938964844</v>
@@ -6815,7 +6815,7 @@
         <v>60.75</v>
       </c>
       <c r="G220" t="n">
-        <v>1159.118041992188</v>
+        <v>1159.117919921875</v>
       </c>
       <c r="H220" t="n">
         <v>145.25</v>
@@ -6873,7 +6873,7 @@
         <v>60.54999923706055</v>
       </c>
       <c r="G222" t="n">
-        <v>1161.912475585938</v>
+        <v>1161.912353515625</v>
       </c>
       <c r="H222" t="n">
         <v>146.1499938964844</v>
@@ -6902,7 +6902,7 @@
         <v>60.40000152587891</v>
       </c>
       <c r="G223" t="n">
-        <v>1171.931884765625</v>
+        <v>1171.932006835938</v>
       </c>
       <c r="H223" t="n">
         <v>147.0500030517578</v>
@@ -6960,7 +6960,7 @@
         <v>63.75</v>
       </c>
       <c r="G225" t="n">
-        <v>1230.299194335938</v>
+        <v>1230.299072265625</v>
       </c>
       <c r="H225" t="n">
         <v>153.6499938964844</v>
@@ -7047,7 +7047,7 @@
         <v>73.40000152587891</v>
       </c>
       <c r="G228" t="n">
-        <v>1237.455810546875</v>
+        <v>1237.455688476562</v>
       </c>
       <c r="H228" t="n">
         <v>156.1000061035156</v>
@@ -7076,7 +7076,7 @@
         <v>74.19999694824219</v>
       </c>
       <c r="G229" t="n">
-        <v>1236.93310546875</v>
+        <v>1236.933227539062</v>
       </c>
       <c r="H229" t="n">
         <v>162.8999938964844</v>
@@ -7105,7 +7105,7 @@
         <v>75.94999694824219</v>
       </c>
       <c r="G230" t="n">
-        <v>1218.893798828125</v>
+        <v>1218.893676757812</v>
       </c>
       <c r="H230" t="n">
         <v>157.8999938964844</v>
@@ -7134,7 +7134,7 @@
         <v>73.5</v>
       </c>
       <c r="G231" t="n">
-        <v>1222.415161132812</v>
+        <v>1222.415283203125</v>
       </c>
       <c r="H231" t="n">
         <v>156.3999938964844</v>
@@ -7221,7 +7221,7 @@
         <v>72.90000152587891</v>
       </c>
       <c r="G234" t="n">
-        <v>1185.563720703125</v>
+        <v>1185.563842773438</v>
       </c>
       <c r="H234" t="n">
         <v>154.75</v>
@@ -7250,7 +7250,7 @@
         <v>72.40000152587891</v>
       </c>
       <c r="G235" t="n">
-        <v>1187.38134765625</v>
+        <v>1187.381225585938</v>
       </c>
       <c r="H235" t="n">
         <v>161.8000030517578</v>
@@ -7337,7 +7337,7 @@
         <v>73.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1171.591064453125</v>
+        <v>1171.591186523438</v>
       </c>
       <c r="H238" t="n">
         <v>148.8999938964844</v>
@@ -7569,7 +7569,7 @@
         <v>65.80000305175781</v>
       </c>
       <c r="G246" t="n">
-        <v>1156.300659179688</v>
+        <v>1156.30078125</v>
       </c>
       <c r="H246" t="n">
         <v>134.6000061035156</v>
@@ -7714,7 +7714,7 @@
         <v>66.84999847412109</v>
       </c>
       <c r="G251" t="n">
-        <v>1161.912475585938</v>
+        <v>1161.912353515625</v>
       </c>
       <c r="H251" t="n">
         <v>138.6000061035156</v>
@@ -7743,7 +7743,7 @@
         <v>65.75</v>
       </c>
       <c r="G252" t="n">
-        <v>1144.418212890625</v>
+        <v>1144.418334960938</v>
       </c>
       <c r="H252" t="n">
         <v>136.4499969482422</v>
@@ -7801,7 +7801,7 @@
         <v>65.40000152587891</v>
       </c>
       <c r="G254" t="n">
-        <v>1152.756469726562</v>
+        <v>1152.756225585938</v>
       </c>
       <c r="H254" t="n">
         <v>130.1999969482422</v>
@@ -7830,7 +7830,7 @@
         <v>64.75</v>
       </c>
       <c r="G255" t="n">
-        <v>1179.974609375</v>
+        <v>1179.974731445312</v>
       </c>
       <c r="H255" t="n">
         <v>135.0500030517578</v>
@@ -7859,7 +7859,7 @@
         <v>63.75</v>
       </c>
       <c r="G256" t="n">
-        <v>1162.526000976562</v>
+        <v>1162.52587890625</v>
       </c>
       <c r="H256" t="n">
         <v>133</v>
@@ -7888,7 +7888,7 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G257" t="n">
-        <v>1147.871826171875</v>
+        <v>1147.871704101562</v>
       </c>
       <c r="H257" t="n">
         <v>134.3000030517578</v>
@@ -7917,7 +7917,7 @@
         <v>63.59999847412109</v>
       </c>
       <c r="G258" t="n">
-        <v>1123.084350585938</v>
+        <v>1123.084228515625</v>
       </c>
       <c r="H258" t="n">
         <v>132.3000030517578</v>
@@ -7975,7 +7975,7 @@
         <v>65.44999694824219</v>
       </c>
       <c r="G260" t="n">
-        <v>1110.588500976562</v>
+        <v>1110.58837890625</v>
       </c>
       <c r="H260" t="n">
         <v>139.25</v>
@@ -8178,7 +8178,7 @@
         <v>60.90000152587891</v>
       </c>
       <c r="G267" t="n">
-        <v>1082.620361328125</v>
+        <v>1082.620483398438</v>
       </c>
       <c r="H267" t="n">
         <v>128.1499938964844</v>
@@ -8236,7 +8236,7 @@
         <v>58.45000076293945</v>
       </c>
       <c r="G269" t="n">
-        <v>1072.260375976562</v>
+        <v>1072.26025390625</v>
       </c>
       <c r="H269" t="n">
         <v>119.1500015258789</v>
@@ -8323,7 +8323,7 @@
         <v>59.20000076293945</v>
       </c>
       <c r="G272" t="n">
-        <v>1057.35595703125</v>
+        <v>1057.356079101562</v>
       </c>
       <c r="H272" t="n">
         <v>121.3000030517578</v>
@@ -8352,7 +8352,7 @@
         <v>59.34999847412109</v>
       </c>
       <c r="G273" t="n">
-        <v>1058.28759765625</v>
+        <v>1058.287475585938</v>
       </c>
       <c r="H273" t="n">
         <v>121.4000015258789</v>
@@ -8410,7 +8410,7 @@
         <v>59.54999923706055</v>
       </c>
       <c r="G275" t="n">
-        <v>1047.791015625</v>
+        <v>1047.791137695312</v>
       </c>
       <c r="H275" t="n">
         <v>123.25</v>
@@ -8497,7 +8497,7 @@
         <v>60.84999847412109</v>
       </c>
       <c r="G278" t="n">
-        <v>1061.763671875</v>
+        <v>1061.763549804688</v>
       </c>
       <c r="H278" t="n">
         <v>130.9499969482422</v>
@@ -8555,7 +8555,7 @@
         <v>60.04999923706055</v>
       </c>
       <c r="G280" t="n">
-        <v>1080.598388671875</v>
+        <v>1080.598510742188</v>
       </c>
       <c r="H280" t="n">
         <v>123.3000030517578</v>
@@ -8613,7 +8613,7 @@
         <v>60.40000152587891</v>
       </c>
       <c r="G282" t="n">
-        <v>1104.204223632812</v>
+        <v>1104.2041015625</v>
       </c>
       <c r="H282" t="n">
         <v>129.5500030517578</v>
@@ -8671,7 +8671,7 @@
         <v>60.45000076293945</v>
       </c>
       <c r="G284" t="n">
-        <v>1097.093017578125</v>
+        <v>1097.092895507812</v>
       </c>
       <c r="H284" t="n">
         <v>123.6500015258789</v>
@@ -8700,7 +8700,7 @@
         <v>60.40000152587891</v>
       </c>
       <c r="G285" t="n">
-        <v>1106.044555664062</v>
+        <v>1106.044677734375</v>
       </c>
       <c r="H285" t="n">
         <v>120.8000030517578</v>
@@ -8729,7 +8729,7 @@
         <v>59.34999847412109</v>
       </c>
       <c r="G286" t="n">
-        <v>1080.9619140625</v>
+        <v>1080.961791992188</v>
       </c>
       <c r="H286" t="n">
         <v>118.5500030517578</v>
@@ -8874,7 +8874,7 @@
         <v>58.90000152587891</v>
       </c>
       <c r="G291" t="n">
-        <v>1065.057983398438</v>
+        <v>1065.05810546875</v>
       </c>
       <c r="H291" t="n">
         <v>135.6999969482422</v>
@@ -8903,7 +8903,7 @@
         <v>58.54999923706055</v>
       </c>
       <c r="G292" t="n">
-        <v>1056.947021484375</v>
+        <v>1056.946899414062</v>
       </c>
       <c r="H292" t="n">
         <v>135.8000030517578</v>
@@ -9019,7 +9019,7 @@
         <v>58.95000076293945</v>
       </c>
       <c r="G296" t="n">
-        <v>1072.032958984375</v>
+        <v>1072.033081054688</v>
       </c>
       <c r="H296" t="n">
         <v>146.3500061035156</v>
@@ -9048,7 +9048,7 @@
         <v>58.25</v>
       </c>
       <c r="G297" t="n">
-        <v>1055.4248046875</v>
+        <v>1055.424682617188</v>
       </c>
       <c r="H297" t="n">
         <v>147.25</v>
@@ -9193,7 +9193,7 @@
         <v>52.54999923706055</v>
       </c>
       <c r="G302" t="n">
-        <v>1010.167114257812</v>
+        <v>1010.167053222656</v>
       </c>
       <c r="H302" t="n">
         <v>148.6499938964844</v>
@@ -9251,7 +9251,7 @@
         <v>59.59999847412109</v>
       </c>
       <c r="G304" t="n">
-        <v>1031.341674804688</v>
+        <v>1031.341796875</v>
       </c>
       <c r="H304" t="n">
         <v>146.8500061035156</v>
@@ -9338,7 +9338,7 @@
         <v>52.25</v>
       </c>
       <c r="G307" t="n">
-        <v>1001.169921875</v>
+        <v>1001.169982910156</v>
       </c>
       <c r="H307" t="n">
         <v>143.1000061035156</v>
@@ -9367,7 +9367,7 @@
         <v>53.59999847412109</v>
       </c>
       <c r="G308" t="n">
-        <v>1016.73291015625</v>
+        <v>1016.732971191406</v>
       </c>
       <c r="H308" t="n">
         <v>142.1999969482422</v>
@@ -9425,7 +9425,7 @@
         <v>53.79999923706055</v>
       </c>
       <c r="G310" t="n">
-        <v>1015.43798828125</v>
+        <v>1015.438049316406</v>
       </c>
       <c r="H310" t="n">
         <v>141.5500030517578</v>
@@ -9570,7 +9570,7 @@
         <v>56.29999923706055</v>
       </c>
       <c r="G315" t="n">
-        <v>1056.401733398438</v>
+        <v>1056.401611328125</v>
       </c>
       <c r="H315" t="n">
         <v>146.8000030517578</v>
@@ -9599,7 +9599,7 @@
         <v>55.59999847412109</v>
       </c>
       <c r="G316" t="n">
-        <v>1061.627197265625</v>
+        <v>1061.627319335938</v>
       </c>
       <c r="H316" t="n">
         <v>157.3500061035156</v>
@@ -9686,7 +9686,7 @@
         <v>57.34999847412109</v>
       </c>
       <c r="G319" t="n">
-        <v>1075.759033203125</v>
+        <v>1075.758911132812</v>
       </c>
       <c r="H319" t="n">
         <v>162</v>
@@ -9744,7 +9744,7 @@
         <v>55</v>
       </c>
       <c r="G321" t="n">
-        <v>1068.738647460938</v>
+        <v>1068.738525390625</v>
       </c>
       <c r="H321" t="n">
         <v>159.1999969482422</v>
@@ -9802,7 +9802,7 @@
         <v>54.20000076293945</v>
       </c>
       <c r="G323" t="n">
-        <v>1067.37548828125</v>
+        <v>1067.375366210938</v>
       </c>
       <c r="H323" t="n">
         <v>159.3500061035156</v>
@@ -9889,7 +9889,7 @@
         <v>55</v>
       </c>
       <c r="G326" t="n">
-        <v>1073.328002929688</v>
+        <v>1073.328125</v>
       </c>
       <c r="H326" t="n">
         <v>153.6000061035156</v>
@@ -9918,7 +9918,7 @@
         <v>58.90000152587891</v>
       </c>
       <c r="G327" t="n">
-        <v>1080.121215820312</v>
+        <v>1080.121337890625</v>
       </c>
       <c r="H327" t="n">
         <v>160.6999969482422</v>
@@ -10063,7 +10063,7 @@
         <v>57.5</v>
       </c>
       <c r="G332" t="n">
-        <v>1109.520629882812</v>
+        <v>1109.5205078125</v>
       </c>
       <c r="H332" t="n">
         <v>153.6000061035156</v>
@@ -10121,7 +10121,7 @@
         <v>56.25</v>
       </c>
       <c r="G334" t="n">
-        <v>1126.69677734375</v>
+        <v>1126.696899414062</v>
       </c>
       <c r="H334" t="n">
         <v>150.3000030517578</v>
@@ -10150,7 +10150,7 @@
         <v>59.25</v>
       </c>
       <c r="G335" t="n">
-        <v>1134.4443359375</v>
+        <v>1134.444213867188</v>
       </c>
       <c r="H335" t="n">
         <v>148.8000030517578</v>
@@ -10179,7 +10179,7 @@
         <v>58.59999847412109</v>
       </c>
       <c r="G336" t="n">
-        <v>1127.037719726562</v>
+        <v>1127.03759765625</v>
       </c>
       <c r="H336" t="n">
         <v>147.8500061035156</v>
@@ -10295,7 +10295,7 @@
         <v>59.25</v>
       </c>
       <c r="G340" t="n">
-        <v>1108.4072265625</v>
+        <v>1108.407348632812</v>
       </c>
       <c r="H340" t="n">
         <v>137.1000061035156</v>
@@ -10382,7 +10382,7 @@
         <v>58.29999923706055</v>
       </c>
       <c r="G343" t="n">
-        <v>1115.541259765625</v>
+        <v>1115.541381835938</v>
       </c>
       <c r="H343" t="n">
         <v>134.6499938964844</v>
@@ -10469,7 +10469,7 @@
         <v>60.34999847412109</v>
       </c>
       <c r="G346" t="n">
-        <v>1108.702758789062</v>
+        <v>1108.70263671875</v>
       </c>
       <c r="H346" t="n">
         <v>138.8999938964844</v>
@@ -10556,7 +10556,7 @@
         <v>61.25</v>
       </c>
       <c r="G349" t="n">
-        <v>1145.054443359375</v>
+        <v>1145.054321289062</v>
       </c>
       <c r="H349" t="n">
         <v>138.6000061035156</v>
@@ -10585,7 +10585,7 @@
         <v>61.29999923706055</v>
       </c>
       <c r="G350" t="n">
-        <v>1122.311767578125</v>
+        <v>1122.311889648438</v>
       </c>
       <c r="H350" t="n">
         <v>134.6999969482422</v>
@@ -10643,7 +10643,7 @@
         <v>66.19999694824219</v>
       </c>
       <c r="G352" t="n">
-        <v>1115.63232421875</v>
+        <v>1115.632202148438</v>
       </c>
       <c r="H352" t="n">
         <v>134.6000061035156</v>
@@ -10788,7 +10788,7 @@
         <v>63.75</v>
       </c>
       <c r="G357" t="n">
-        <v>1127.787353515625</v>
+        <v>1127.787475585938</v>
       </c>
       <c r="H357" t="n">
         <v>137.1999969482422</v>
@@ -10817,7 +10817,7 @@
         <v>63.54999923706055</v>
       </c>
       <c r="G358" t="n">
-        <v>1128.787109375</v>
+        <v>1128.786987304688</v>
       </c>
       <c r="H358" t="n">
         <v>139.3999938964844</v>
@@ -10904,7 +10904,7 @@
         <v>62.95000076293945</v>
       </c>
       <c r="G361" t="n">
-        <v>1159.86767578125</v>
+        <v>1159.867797851562</v>
       </c>
       <c r="H361" t="n">
         <v>149.4499969482422</v>
@@ -11078,7 +11078,7 @@
         <v>63.15000152587891</v>
       </c>
       <c r="G367" t="n">
-        <v>1142.691650390625</v>
+        <v>1142.691528320312</v>
       </c>
       <c r="H367" t="n">
         <v>143.25</v>
@@ -11107,7 +11107,7 @@
         <v>63.29999923706055</v>
       </c>
       <c r="G368" t="n">
-        <v>1133.967041015625</v>
+        <v>1133.967163085938</v>
       </c>
       <c r="H368" t="n">
         <v>140.1999969482422</v>
@@ -11136,7 +11136,7 @@
         <v>63.29999923706055</v>
       </c>
       <c r="G369" t="n">
-        <v>1134.376220703125</v>
+        <v>1134.376098632812</v>
       </c>
       <c r="H369" t="n">
         <v>141.25</v>
@@ -11194,7 +11194,7 @@
         <v>62.79999923706055</v>
       </c>
       <c r="G371" t="n">
-        <v>1158.822509765625</v>
+        <v>1158.822631835938</v>
       </c>
       <c r="H371" t="n">
         <v>138.25</v>
@@ -11223,7 +11223,7 @@
         <v>62</v>
       </c>
       <c r="G372" t="n">
-        <v>1188.562744140625</v>
+        <v>1188.562866210938</v>
       </c>
       <c r="H372" t="n">
         <v>139.6499938964844</v>
@@ -11252,7 +11252,7 @@
         <v>62.45000076293945</v>
       </c>
       <c r="G373" t="n">
-        <v>1176.316772460938</v>
+        <v>1176.31689453125</v>
       </c>
       <c r="H373" t="n">
         <v>137.1000061035156</v>
@@ -11310,7 +11310,7 @@
         <v>63.54999923706055</v>
       </c>
       <c r="G375" t="n">
-        <v>1199.03662109375</v>
+        <v>1199.036743164062</v>
       </c>
       <c r="H375" t="n">
         <v>138.75</v>
@@ -11339,7 +11339,7 @@
         <v>64.15000152587891</v>
       </c>
       <c r="G376" t="n">
-        <v>1196.696411132812</v>
+        <v>1196.696655273438</v>
       </c>
       <c r="H376" t="n">
         <v>138.6000061035156</v>
@@ -11426,7 +11426,7 @@
         <v>63.45000076293945</v>
       </c>
       <c r="G379" t="n">
-        <v>1257.653686523438</v>
+        <v>1257.653564453125</v>
       </c>
       <c r="H379" t="n">
         <v>137.5500030517578</v>
@@ -11455,7 +11455,7 @@
         <v>62.79999923706055</v>
       </c>
       <c r="G380" t="n">
-        <v>1246.4072265625</v>
+        <v>1246.407348632812</v>
       </c>
       <c r="H380" t="n">
         <v>136.4499969482422</v>
@@ -11513,7 +11513,7 @@
         <v>65</v>
       </c>
       <c r="G382" t="n">
-        <v>1270.808349609375</v>
+        <v>1270.808471679688</v>
       </c>
       <c r="H382" t="n">
         <v>135</v>
@@ -11542,7 +11542,7 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G383" t="n">
-        <v>1281.600341796875</v>
+        <v>1281.600219726562</v>
       </c>
       <c r="H383" t="n">
         <v>141.6999969482422</v>
@@ -11600,7 +11600,7 @@
         <v>59.70000076293945</v>
       </c>
       <c r="G385" t="n">
-        <v>1289.760375976562</v>
+        <v>1289.760498046875</v>
       </c>
       <c r="H385" t="n">
         <v>162.3999938964844</v>
@@ -11629,7 +11629,7 @@
         <v>58.79999923706055</v>
       </c>
       <c r="G386" t="n">
-        <v>1249.834716796875</v>
+        <v>1249.834594726562</v>
       </c>
       <c r="H386" t="n">
         <v>163.0500030517578</v>
@@ -11774,7 +11774,7 @@
         <v>58.45000076293945</v>
       </c>
       <c r="G391" t="n">
-        <v>1244.46875</v>
+        <v>1244.468627929688</v>
       </c>
       <c r="H391" t="n">
         <v>184.8500061035156</v>
@@ -11803,7 +11803,7 @@
         <v>58.25</v>
       </c>
       <c r="G392" t="n">
-        <v>1255.00390625</v>
+        <v>1255.003784179688</v>
       </c>
       <c r="H392" t="n">
         <v>188.8500061035156</v>
@@ -11861,7 +11861,7 @@
         <v>58.15000152587891</v>
       </c>
       <c r="G394" t="n">
-        <v>1224.038208007812</v>
+        <v>1224.0380859375</v>
       </c>
       <c r="H394" t="n">
         <v>181.1999969482422</v>
@@ -11890,7 +11890,7 @@
         <v>58.54999923706055</v>
       </c>
       <c r="G395" t="n">
-        <v>1218.8935546875</v>
+        <v>1218.893432617188</v>
       </c>
       <c r="H395" t="n">
         <v>187.0500030517578</v>
@@ -11919,7 +11919,7 @@
         <v>58.15000152587891</v>
       </c>
       <c r="G396" t="n">
-        <v>1235.459350585938</v>
+        <v>1235.45947265625</v>
       </c>
       <c r="H396" t="n">
         <v>199.1499938964844</v>
@@ -11948,7 +11948,7 @@
         <v>59.04999923706055</v>
       </c>
       <c r="G397" t="n">
-        <v>1242.49951171875</v>
+        <v>1242.499389648438</v>
       </c>
       <c r="H397" t="n">
         <v>210.0500030517578</v>
@@ -12006,7 +12006,7 @@
         <v>60.04999923706055</v>
       </c>
       <c r="G399" t="n">
-        <v>1243.163940429688</v>
+        <v>1243.1640625</v>
       </c>
       <c r="H399" t="n">
         <v>191.4499969482422</v>
@@ -12093,7 +12093,7 @@
         <v>61.25</v>
       </c>
       <c r="G402" t="n">
-        <v>1268.788452148438</v>
+        <v>1268.788330078125</v>
       </c>
       <c r="H402" t="n">
         <v>166.9499969482422</v>
@@ -12151,7 +12151,7 @@
         <v>60.95000076293945</v>
       </c>
       <c r="G404" t="n">
-        <v>1249.465454101562</v>
+        <v>1249.46533203125</v>
       </c>
       <c r="H404" t="n">
         <v>158.0500030517578</v>
@@ -12180,7 +12180,7 @@
         <v>63.5</v>
       </c>
       <c r="G405" t="n">
-        <v>1258.720825195312</v>
+        <v>1258.720703125</v>
       </c>
       <c r="H405" t="n">
         <v>160.6000061035156</v>
@@ -12206,7 +12206,7 @@
         <v>16.75</v>
       </c>
       <c r="E406" t="n">
-        <v>247.9318389892578</v>
+        <v>247.9318237304688</v>
       </c>
       <c r="F406" t="n">
         <v>63.70000076293945</v>
@@ -12270,13 +12270,13 @@
         <v>16.89999961853027</v>
       </c>
       <c r="E408" t="n">
-        <v>223.7761535644531</v>
+        <v>223.7761688232422</v>
       </c>
       <c r="F408" t="n">
         <v>67.84999847412109</v>
       </c>
       <c r="G408" t="n">
-        <v>1246.0732421875</v>
+        <v>1246.073364257812</v>
       </c>
       <c r="H408" t="n">
         <v>178.9499969482422</v>
@@ -12302,13 +12302,13 @@
         <v>16.70000076293945</v>
       </c>
       <c r="E409" t="n">
-        <v>212.6197204589844</v>
+        <v>212.6197357177734</v>
       </c>
       <c r="F409" t="n">
         <v>66.94999694824219</v>
       </c>
       <c r="G409" t="n">
-        <v>1225.1259765625</v>
+        <v>1225.125854492188</v>
       </c>
       <c r="H409" t="n">
         <v>177.3000030517578</v>
@@ -12334,13 +12334,13 @@
         <v>16.64999961853027</v>
       </c>
       <c r="E410" t="n">
-        <v>213.6656646728516</v>
+        <v>213.6656494140625</v>
       </c>
       <c r="F410" t="n">
         <v>67.5</v>
       </c>
       <c r="G410" t="n">
-        <v>1219.46923828125</v>
+        <v>1219.469116210938</v>
       </c>
       <c r="H410" t="n">
         <v>177.25</v>
@@ -12372,7 +12372,7 @@
         <v>68.65000152587891</v>
       </c>
       <c r="G411" t="n">
-        <v>1207.315551757812</v>
+        <v>1207.315673828125</v>
       </c>
       <c r="H411" t="n">
         <v>177.8999938964844</v>
@@ -12398,7 +12398,7 @@
         <v>16.64999961853027</v>
       </c>
       <c r="E412" t="n">
-        <v>219.3932800292969</v>
+        <v>219.3932952880859</v>
       </c>
       <c r="F412" t="n">
         <v>69.40000152587891</v>
@@ -12436,7 +12436,7 @@
         <v>68.75</v>
       </c>
       <c r="G413" t="n">
-        <v>1194.618896484375</v>
+        <v>1194.618774414062</v>
       </c>
       <c r="H413" t="n">
         <v>188.0500030517578</v>
@@ -12462,13 +12462,13 @@
         <v>16.5</v>
       </c>
       <c r="E414" t="n">
-        <v>232.5917358398438</v>
+        <v>232.5917510986328</v>
       </c>
       <c r="F414" t="n">
         <v>68.34999847412109</v>
       </c>
       <c r="G414" t="n">
-        <v>1189.15966796875</v>
+        <v>1189.159545898438</v>
       </c>
       <c r="H414" t="n">
         <v>186.75</v>
@@ -12500,7 +12500,7 @@
         <v>69.15000152587891</v>
       </c>
       <c r="G415" t="n">
-        <v>1191.950805664062</v>
+        <v>1191.950927734375</v>
       </c>
       <c r="H415" t="n">
         <v>186.8999938964844</v>
@@ -12596,7 +12596,7 @@
         <v>72.15000152587891</v>
       </c>
       <c r="G418" t="n">
-        <v>1199.88037109375</v>
+        <v>1199.880249023438</v>
       </c>
       <c r="H418" t="n">
         <v>190.3999938964844</v>
@@ -12628,7 +12628,7 @@
         <v>70.75</v>
       </c>
       <c r="G419" t="n">
-        <v>1201.510620117188</v>
+        <v>1201.5107421875</v>
       </c>
       <c r="H419" t="n">
         <v>189.8000030517578</v>
@@ -12686,13 +12686,13 @@
         <v>18.60000038146973</v>
       </c>
       <c r="E421" t="n">
-        <v>249.1769866943359</v>
+        <v>249.1769714355469</v>
       </c>
       <c r="F421" t="n">
         <v>70.94999694824219</v>
       </c>
       <c r="G421" t="n">
-        <v>1222.556884765625</v>
+        <v>1222.557006835938</v>
       </c>
       <c r="H421" t="n">
         <v>182.8500061035156</v>
@@ -12750,7 +12750,7 @@
         <v>17.35000038146973</v>
       </c>
       <c r="E423" t="n">
-        <v>239.2656707763672</v>
+        <v>239.2656860351562</v>
       </c>
       <c r="F423" t="n">
         <v>68.55000305175781</v>
@@ -12788,7 +12788,7 @@
         <v>68.55000305175781</v>
       </c>
       <c r="G424" t="n">
-        <v>1212.03369140625</v>
+        <v>1212.033813476562</v>
       </c>
       <c r="H424" t="n">
         <v>175.3000030517578</v>
@@ -12820,7 +12820,7 @@
         <v>66.15000152587891</v>
       </c>
       <c r="G425" t="n">
-        <v>1214.281616210938</v>
+        <v>1214.28173828125</v>
       </c>
       <c r="H425" t="n">
         <v>183.75</v>
@@ -12852,7 +12852,7 @@
         <v>66.15000152587891</v>
       </c>
       <c r="G426" t="n">
-        <v>1203.709228515625</v>
+        <v>1203.709106445312</v>
       </c>
       <c r="H426" t="n">
         <v>177.8500061035156</v>
@@ -12942,7 +12942,7 @@
         <v>19.14999961853027</v>
       </c>
       <c r="E429" t="n">
-        <v>226.9139251708984</v>
+        <v>226.9139099121094</v>
       </c>
       <c r="F429" t="n">
         <v>68.05000305175781</v>
@@ -12980,7 +12980,7 @@
         <v>65.94999694824219</v>
       </c>
       <c r="G430" t="n">
-        <v>1156.281127929688</v>
+        <v>1156.281005859375</v>
       </c>
       <c r="H430" t="n">
         <v>173.5500030517578</v>
@@ -13012,7 +13012,7 @@
         <v>64.5</v>
       </c>
       <c r="G431" t="n">
-        <v>1157.2939453125</v>
+        <v>1157.293823242188</v>
       </c>
       <c r="H431" t="n">
         <v>171</v>
@@ -13038,7 +13038,7 @@
         <v>19.79999923706055</v>
       </c>
       <c r="E432" t="n">
-        <v>226.4656829833984</v>
+        <v>226.4656677246094</v>
       </c>
       <c r="F432" t="n">
         <v>63.95000076293945</v>
@@ -13166,13 +13166,13 @@
         <v>20.89999961853027</v>
       </c>
       <c r="E436" t="n">
-        <v>223.7761535644531</v>
+        <v>223.7761688232422</v>
       </c>
       <c r="F436" t="n">
         <v>68.05000305175781</v>
       </c>
       <c r="G436" t="n">
-        <v>1143.287719726562</v>
+        <v>1143.287841796875</v>
       </c>
       <c r="H436" t="n">
         <v>170.3999938964844</v>
@@ -13198,7 +13198,7 @@
         <v>21.04999923706055</v>
       </c>
       <c r="E437" t="n">
-        <v>224.5232543945312</v>
+        <v>224.5232391357422</v>
       </c>
       <c r="F437" t="n">
         <v>72.84999847412109</v>
@@ -13268,7 +13268,7 @@
         <v>70.94999694824219</v>
       </c>
       <c r="G439" t="n">
-        <v>1135.432495117188</v>
+        <v>1135.4326171875</v>
       </c>
       <c r="H439" t="n">
         <v>171.25</v>
@@ -13294,7 +13294,7 @@
         <v>19.5</v>
       </c>
       <c r="E440" t="n">
-        <v>219.2936553955078</v>
+        <v>219.2936706542969</v>
       </c>
       <c r="F440" t="n">
         <v>71.65000152587891</v>
@@ -13364,7 +13364,7 @@
         <v>80.55000305175781</v>
       </c>
       <c r="G442" t="n">
-        <v>1160.702758789062</v>
+        <v>1160.70263671875</v>
       </c>
       <c r="H442" t="n">
         <v>169.3500061035156</v>
@@ -13390,7 +13390,7 @@
         <v>20.29999923706055</v>
       </c>
       <c r="E443" t="n">
-        <v>223.6765747070312</v>
+        <v>223.6765594482422</v>
       </c>
       <c r="F443" t="n">
         <v>78.75</v>
@@ -13486,13 +13486,13 @@
         <v>19.70000076293945</v>
       </c>
       <c r="E446" t="n">
-        <v>215.1598205566406</v>
+        <v>215.1598052978516</v>
       </c>
       <c r="F446" t="n">
         <v>77.94999694824219</v>
       </c>
       <c r="G446" t="n">
-        <v>1148.154174804688</v>
+        <v>1148.154052734375</v>
       </c>
       <c r="H446" t="n">
         <v>169.1999969482422</v>
@@ -13518,7 +13518,7 @@
         <v>19.89999961853027</v>
       </c>
       <c r="E447" t="n">
-        <v>213.3668060302734</v>
+        <v>213.3668212890625</v>
       </c>
       <c r="F447" t="n">
         <v>77.84999847412109</v>
@@ -13550,13 +13550,13 @@
         <v>19.39999961853027</v>
       </c>
       <c r="E448" t="n">
-        <v>213.3668060302734</v>
+        <v>213.3668212890625</v>
       </c>
       <c r="F448" t="n">
         <v>76.80000305175781</v>
       </c>
       <c r="G448" t="n">
-        <v>1135.8525390625</v>
+        <v>1135.852416992188</v>
       </c>
       <c r="H448" t="n">
         <v>178.6499938964844</v>
@@ -13588,7 +13588,7 @@
         <v>70</v>
       </c>
       <c r="G449" t="n">
-        <v>1118.116333007812</v>
+        <v>1118.1162109375</v>
       </c>
       <c r="H449" t="n">
         <v>169.75</v>
@@ -13620,7 +13620,7 @@
         <v>68.59999847412109</v>
       </c>
       <c r="G450" t="n">
-        <v>1115.522705078125</v>
+        <v>1115.522583007812</v>
       </c>
       <c r="H450" t="n">
         <v>162.3000030517578</v>
@@ -13652,7 +13652,7 @@
         <v>68.19999694824219</v>
       </c>
       <c r="G451" t="n">
-        <v>1099.98486328125</v>
+        <v>1099.984985351562</v>
       </c>
       <c r="H451" t="n">
         <v>159.0500030517578</v>
@@ -13678,7 +13678,7 @@
         <v>18.39999961853027</v>
       </c>
       <c r="E452" t="n">
-        <v>222.0329742431641</v>
+        <v>222.032958984375</v>
       </c>
       <c r="F452" t="n">
         <v>68.75</v>
@@ -13780,7 +13780,7 @@
         <v>67.05000305175781</v>
       </c>
       <c r="G455" t="n">
-        <v>1135.012573242188</v>
+        <v>1135.0126953125</v>
       </c>
       <c r="H455" t="n">
         <v>172.25</v>
@@ -13806,7 +13806,7 @@
         <v>18.04999923706055</v>
       </c>
       <c r="E456" t="n">
-        <v>216.5045623779297</v>
+        <v>216.5045776367188</v>
       </c>
       <c r="F456" t="n">
         <v>67.59999847412109</v>
@@ -14030,13 +14030,13 @@
         <v>19.10000038146973</v>
       </c>
       <c r="E463" t="n">
-        <v>223.8757781982422</v>
+        <v>223.8757934570312</v>
       </c>
       <c r="F463" t="n">
         <v>76</v>
       </c>
       <c r="G463" t="n">
-        <v>1143.51025390625</v>
+        <v>1143.510131835938</v>
       </c>
       <c r="H463" t="n">
         <v>181.1499938964844</v>
@@ -14132,7 +14132,7 @@
         <v>85.15000152587891</v>
       </c>
       <c r="G466" t="n">
-        <v>1163.7412109375</v>
+        <v>1163.741088867188</v>
       </c>
       <c r="H466" t="n">
         <v>186</v>
@@ -14254,13 +14254,13 @@
         <v>20.14999961853027</v>
       </c>
       <c r="E470" t="n">
-        <v>220.3893890380859</v>
+        <v>220.389404296875</v>
       </c>
       <c r="F470" t="n">
         <v>82.40000152587891</v>
       </c>
       <c r="G470" t="n">
-        <v>1183.478149414062</v>
+        <v>1183.47802734375</v>
       </c>
       <c r="H470" t="n">
         <v>174.25</v>
@@ -14292,7 +14292,7 @@
         <v>83.44999694824219</v>
       </c>
       <c r="G471" t="n">
-        <v>1182.687622070312</v>
+        <v>1182.6875</v>
       </c>
       <c r="H471" t="n">
         <v>173.4499969482422</v>
@@ -14324,7 +14324,7 @@
         <v>82.90000152587891</v>
       </c>
       <c r="G472" t="n">
-        <v>1182.934692382812</v>
+        <v>1182.9345703125</v>
       </c>
       <c r="H472" t="n">
         <v>177.8999938964844</v>
@@ -14420,7 +14420,7 @@
         <v>87.69999694824219</v>
       </c>
       <c r="G475" t="n">
-        <v>1182.88525390625</v>
+        <v>1182.885375976562</v>
       </c>
       <c r="H475" t="n">
         <v>194.0500030517578</v>
@@ -14516,7 +14516,7 @@
         <v>98.44999694824219</v>
       </c>
       <c r="G478" t="n">
-        <v>1215.887329101562</v>
+        <v>1215.887451171875</v>
       </c>
       <c r="H478" t="n">
         <v>212.3999938964844</v>
@@ -14548,7 +14548,7 @@
         <v>90.65000152587891</v>
       </c>
       <c r="G479" t="n">
-        <v>1213.886352539062</v>
+        <v>1213.886474609375</v>
       </c>
       <c r="H479" t="n">
         <v>220.5</v>
@@ -14612,7 +14612,7 @@
         <v>84.55000305175781</v>
       </c>
       <c r="G481" t="n">
-        <v>1215.022705078125</v>
+        <v>1215.022827148438</v>
       </c>
       <c r="H481" t="n">
         <v>218.6999969482422</v>
@@ -14638,7 +14638,7 @@
         <v>20.54999923706055</v>
       </c>
       <c r="E482" t="n">
-        <v>239.6143341064453</v>
+        <v>239.6143188476562</v>
       </c>
       <c r="F482" t="n">
         <v>86.65000152587891</v>
@@ -14734,7 +14734,7 @@
         <v>20.35000038146973</v>
       </c>
       <c r="E485" t="n">
-        <v>236.7256011962891</v>
+        <v>236.7255859375</v>
       </c>
       <c r="F485" t="n">
         <v>85.90000152587891</v>
@@ -14766,13 +14766,13 @@
         <v>21.5</v>
       </c>
       <c r="E486" t="n">
-        <v>239.2158813476562</v>
+        <v>239.2158660888672</v>
       </c>
       <c r="F486" t="n">
         <v>86.19999694824219</v>
       </c>
       <c r="G486" t="n">
-        <v>1245.48046875</v>
+        <v>1245.480346679688</v>
       </c>
       <c r="H486" t="n">
         <v>213.4499969482422</v>
@@ -14804,7 +14804,7 @@
         <v>87.65000152587891</v>
       </c>
       <c r="G487" t="n">
-        <v>1263.809326171875</v>
+        <v>1263.809448242188</v>
       </c>
       <c r="H487" t="n">
         <v>209.6499938964844</v>
@@ -14862,7 +14862,7 @@
         <v>21.64999961853027</v>
       </c>
       <c r="E489" t="n">
-        <v>237.0742340087891</v>
+        <v>237.0742492675781</v>
       </c>
       <c r="F489" t="n">
         <v>85.90000152587891</v>
@@ -14894,7 +14894,7 @@
         <v>22.04999923706055</v>
       </c>
       <c r="E490" t="n">
-        <v>235.8291168212891</v>
+        <v>235.8291015625</v>
       </c>
       <c r="F490" t="n">
         <v>86.09999847412109</v>
@@ -14932,7 +14932,7 @@
         <v>88.84999847412109</v>
       </c>
       <c r="G491" t="n">
-        <v>1273.66552734375</v>
+        <v>1273.665649414062</v>
       </c>
       <c r="H491" t="n">
         <v>196.75</v>
@@ -14958,7 +14958,7 @@
         <v>21.64999961853027</v>
       </c>
       <c r="E492" t="n">
-        <v>233.0898132324219</v>
+        <v>233.0897979736328</v>
       </c>
       <c r="F492" t="n">
         <v>88.90000152587891</v>
@@ -14996,7 +14996,7 @@
         <v>88.05000305175781</v>
       </c>
       <c r="G493" t="n">
-        <v>1287.251708984375</v>
+        <v>1287.251831054688</v>
       </c>
       <c r="H493" t="n">
         <v>190.8000030517578</v>
@@ -15022,13 +15022,13 @@
         <v>21.20000076293945</v>
       </c>
       <c r="E494" t="n">
-        <v>232.0438690185547</v>
+        <v>232.0438842773438</v>
       </c>
       <c r="F494" t="n">
         <v>87.34999847412109</v>
       </c>
       <c r="G494" t="n">
-        <v>1277.074340820312</v>
+        <v>1277.074462890625</v>
       </c>
       <c r="H494" t="n">
         <v>209.8000030517578</v>
@@ -15124,7 +15124,7 @@
         <v>89.69999694824219</v>
       </c>
       <c r="G497" t="n">
-        <v>1276.25927734375</v>
+        <v>1276.259399414062</v>
       </c>
       <c r="H497" t="n">
         <v>215.1499938964844</v>
@@ -15214,13 +15214,13 @@
         <v>24.79999923706055</v>
       </c>
       <c r="E500" t="n">
-        <v>241.4571075439453</v>
+        <v>241.4571228027344</v>
       </c>
       <c r="F500" t="n">
         <v>100.5500030517578</v>
       </c>
       <c r="G500" t="n">
-        <v>1278.260131835938</v>
+        <v>1278.26025390625</v>
       </c>
       <c r="H500" t="n">
         <v>241</v>
@@ -15246,7 +15246,7 @@
         <v>24.10000038146973</v>
       </c>
       <c r="E501" t="n">
-        <v>241.2080993652344</v>
+        <v>241.2080841064453</v>
       </c>
       <c r="F501" t="n">
         <v>99.5</v>
@@ -15278,7 +15278,7 @@
         <v>24.89999961853027</v>
       </c>
       <c r="E502" t="n">
-        <v>240.0127563476562</v>
+        <v>240.0127716064453</v>
       </c>
       <c r="F502" t="n">
         <v>119.4000015258789</v>
@@ -15348,7 +15348,7 @@
         <v>124.1999969482422</v>
       </c>
       <c r="G504" t="n">
-        <v>1354.391967773438</v>
+        <v>1354.39208984375</v>
       </c>
       <c r="H504" t="n">
         <v>238.4499969482422</v>
@@ -15380,7 +15380,7 @@
         <v>122.8499984741211</v>
       </c>
       <c r="G505" t="n">
-        <v>1377.513305664062</v>
+        <v>1377.513061523438</v>
       </c>
       <c r="H505" t="n">
         <v>232.6499938964844</v>
@@ -15412,7 +15412,7 @@
         <v>118.5500030517578</v>
       </c>
       <c r="G506" t="n">
-        <v>1358.245483398438</v>
+        <v>1358.24560546875</v>
       </c>
       <c r="H506" t="n">
         <v>221.8999938964844</v>
@@ -15444,7 +15444,7 @@
         <v>129.6999969482422</v>
       </c>
       <c r="G507" t="n">
-        <v>1345.350952148438</v>
+        <v>1345.35107421875</v>
       </c>
       <c r="H507" t="n">
         <v>217.3000030517578</v>
@@ -15572,7 +15572,7 @@
         <v>120.4000015258789</v>
       </c>
       <c r="G511" t="n">
-        <v>1327.861938476562</v>
+        <v>1327.862060546875</v>
       </c>
       <c r="H511" t="n">
         <v>213.3999938964844</v>
@@ -15630,13 +15630,13 @@
         <v>23.85000038146973</v>
       </c>
       <c r="E513" t="n">
-        <v>250.023681640625</v>
+        <v>250.0236663818359</v>
       </c>
       <c r="F513" t="n">
         <v>117</v>
       </c>
       <c r="G513" t="n">
-        <v>1430.795776367188</v>
+        <v>1430.795654296875</v>
       </c>
       <c r="H513" t="n">
         <v>227.9499969482422</v>
@@ -15668,7 +15668,7 @@
         <v>115.5500030517578</v>
       </c>
       <c r="G514" t="n">
-        <v>1390.852294921875</v>
+        <v>1390.852416992188</v>
       </c>
       <c r="H514" t="n">
         <v>231.5500030517578</v>
@@ -15700,7 +15700,7 @@
         <v>117</v>
       </c>
       <c r="G515" t="n">
-        <v>1409.6259765625</v>
+        <v>1409.625854492188</v>
       </c>
       <c r="H515" t="n">
         <v>231.0500030517578</v>
@@ -15758,13 +15758,13 @@
         <v>24</v>
       </c>
       <c r="E517" t="n">
-        <v>252.8127899169922</v>
+        <v>252.8127746582031</v>
       </c>
       <c r="F517" t="n">
         <v>113.1500015258789</v>
       </c>
       <c r="G517" t="n">
-        <v>1440.33056640625</v>
+        <v>1440.330688476562</v>
       </c>
       <c r="H517" t="n">
         <v>221.9499969482422</v>
@@ -15790,13 +15790,13 @@
         <v>26</v>
       </c>
       <c r="E518" t="n">
-        <v>287.9754638671875</v>
+        <v>287.9754943847656</v>
       </c>
       <c r="F518" t="n">
         <v>114.4000015258789</v>
       </c>
       <c r="G518" t="n">
-        <v>1421.878173828125</v>
+        <v>1421.878295898438</v>
       </c>
       <c r="H518" t="n">
         <v>214.5</v>
@@ -15828,7 +15828,7 @@
         <v>113.6999969482422</v>
       </c>
       <c r="G519" t="n">
-        <v>1410.786865234375</v>
+        <v>1410.786987304688</v>
       </c>
       <c r="H519" t="n">
         <v>214.9499969482422</v>
@@ -15860,7 +15860,7 @@
         <v>110.3000030517578</v>
       </c>
       <c r="G520" t="n">
-        <v>1424.965942382812</v>
+        <v>1424.966064453125</v>
       </c>
       <c r="H520" t="n">
         <v>216.4499969482422</v>
@@ -15924,7 +15924,7 @@
         <v>108.3499984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>1443.34423828125</v>
+        <v>1443.344360351562</v>
       </c>
       <c r="H522" t="n">
         <v>213</v>
@@ -15950,7 +15950,7 @@
         <v>23.45000076293945</v>
       </c>
       <c r="E523" t="n">
-        <v>270.3941650390625</v>
+        <v>270.3941345214844</v>
       </c>
       <c r="F523" t="n">
         <v>106.25</v>
@@ -15982,7 +15982,7 @@
         <v>23.64999961853027</v>
       </c>
       <c r="E524" t="n">
-        <v>271.6890563964844</v>
+        <v>271.6890869140625</v>
       </c>
       <c r="F524" t="n">
         <v>105.4000015258789</v>
@@ -16116,7 +16116,7 @@
         <v>117.9000015258789</v>
       </c>
       <c r="G528" t="n">
-        <v>1456.436401367188</v>
+        <v>1456.4365234375</v>
       </c>
       <c r="H528" t="n">
         <v>242.8500061035156</v>
@@ -16142,13 +16142,13 @@
         <v>24.85000038146973</v>
       </c>
       <c r="E529" t="n">
-        <v>280.6042785644531</v>
+        <v>280.604248046875</v>
       </c>
       <c r="F529" t="n">
         <v>119</v>
       </c>
       <c r="G529" t="n">
-        <v>1453.4970703125</v>
+        <v>1453.496948242188</v>
       </c>
       <c r="H529" t="n">
         <v>241.1999969482422</v>
@@ -16212,7 +16212,7 @@
         <v>116.3499984741211</v>
       </c>
       <c r="G531" t="n">
-        <v>1464.093994140625</v>
+        <v>1464.094116210938</v>
       </c>
       <c r="H531" t="n">
         <v>229.4499969482422</v>
@@ -16308,7 +16308,7 @@
         <v>116.5999984741211</v>
       </c>
       <c r="G534" t="n">
-        <v>1467.947631835938</v>
+        <v>1467.94775390625</v>
       </c>
       <c r="H534" t="n">
         <v>220.5500030517578</v>
@@ -16340,7 +16340,7 @@
         <v>112.5999984741211</v>
       </c>
       <c r="G535" t="n">
-        <v>1438.280395507812</v>
+        <v>1438.280517578125</v>
       </c>
       <c r="H535" t="n">
         <v>212.1000061035156</v>
@@ -16372,7 +16372,7 @@
         <v>107</v>
       </c>
       <c r="G536" t="n">
-        <v>1443.393798828125</v>
+        <v>1443.393920898438</v>
       </c>
       <c r="H536" t="n">
         <v>220.8999938964844</v>
@@ -16398,13 +16398,13 @@
         <v>22.64999961853027</v>
       </c>
       <c r="E537" t="n">
-        <v>316.6634216308594</v>
+        <v>316.6634521484375</v>
       </c>
       <c r="F537" t="n">
         <v>102.4499969482422</v>
       </c>
       <c r="G537" t="n">
-        <v>1474.345458984375</v>
+        <v>1474.345581054688</v>
       </c>
       <c r="H537" t="n">
         <v>223.25</v>
@@ -16462,7 +16462,7 @@
         <v>22</v>
       </c>
       <c r="E539" t="n">
-        <v>320.4486694335938</v>
+        <v>320.4486999511719</v>
       </c>
       <c r="F539" t="n">
         <v>95.25</v>
@@ -16558,13 +16558,13 @@
         <v>21.25</v>
       </c>
       <c r="E542" t="n">
-        <v>354.2666015625</v>
+        <v>354.2666320800781</v>
       </c>
       <c r="F542" t="n">
         <v>92.05000305175781</v>
       </c>
       <c r="G542" t="n">
-        <v>1449.12451171875</v>
+        <v>1449.124633789062</v>
       </c>
       <c r="H542" t="n">
         <v>223.6499938964844</v>
@@ -16596,7 +16596,7 @@
         <v>87.5</v>
       </c>
       <c r="G543" t="n">
-        <v>1457.844604492188</v>
+        <v>1457.844482421875</v>
       </c>
       <c r="H543" t="n">
         <v>217.5500030517578</v>
@@ -16654,13 +16654,13 @@
         <v>20.20000076293945</v>
       </c>
       <c r="E545" t="n">
-        <v>337.033935546875</v>
+        <v>337.0339050292969</v>
       </c>
       <c r="F545" t="n">
         <v>84.65000152587891</v>
       </c>
       <c r="G545" t="n">
-        <v>1414.418212890625</v>
+        <v>1414.418090820312</v>
       </c>
       <c r="H545" t="n">
         <v>214.25</v>
@@ -16750,7 +16750,7 @@
         <v>19.70000076293945</v>
       </c>
       <c r="E548" t="n">
-        <v>351.9257507324219</v>
+        <v>351.9257202148438</v>
       </c>
       <c r="F548" t="n">
         <v>88.15000152587891</v>
@@ -16788,7 +16788,7 @@
         <v>86</v>
       </c>
       <c r="G549" t="n">
-        <v>1426.546752929688</v>
+        <v>1426.546997070312</v>
       </c>
       <c r="H549" t="n">
         <v>249.3000030517578</v>
@@ -16814,13 +16814,13 @@
         <v>19.39999961853027</v>
       </c>
       <c r="E550" t="n">
-        <v>337.382568359375</v>
+        <v>337.3825378417969</v>
       </c>
       <c r="F550" t="n">
         <v>87.05000305175781</v>
       </c>
       <c r="G550" t="n">
-        <v>1433.685791015625</v>
+        <v>1433.685668945312</v>
       </c>
       <c r="H550" t="n">
         <v>271.2000122070312</v>
@@ -16878,7 +16878,7 @@
         <v>19.85000038146973</v>
       </c>
       <c r="E552" t="n">
-        <v>344.8035888671875</v>
+        <v>344.8035583496094</v>
       </c>
       <c r="F552" t="n">
         <v>90.94999694824219</v>
@@ -16916,7 +16916,7 @@
         <v>87.5</v>
       </c>
       <c r="G553" t="n">
-        <v>1475.061889648438</v>
+        <v>1475.061767578125</v>
       </c>
       <c r="H553" t="n">
         <v>266.9500122070312</v>
@@ -16948,7 +16948,7 @@
         <v>86.19999694824219</v>
       </c>
       <c r="G554" t="n">
-        <v>1468.145263671875</v>
+        <v>1468.145141601562</v>
       </c>
       <c r="H554" t="n">
         <v>270.9500122070312</v>
@@ -16974,7 +16974,7 @@
         <v>21.5</v>
       </c>
       <c r="E555" t="n">
-        <v>355.5615844726562</v>
+        <v>355.5615539550781</v>
       </c>
       <c r="F555" t="n">
         <v>90.40000152587891</v>
@@ -17006,7 +17006,7 @@
         <v>21.5</v>
       </c>
       <c r="E556" t="n">
-        <v>355.7109680175781</v>
+        <v>355.7109985351562</v>
       </c>
       <c r="F556" t="n">
         <v>89.90000152587891</v>
@@ -17038,7 +17038,7 @@
         <v>21.95000076293945</v>
       </c>
       <c r="E557" t="n">
-        <v>355.7109680175781</v>
+        <v>355.7109985351562</v>
       </c>
       <c r="F557" t="n">
         <v>92.40000152587891</v>
@@ -17102,7 +17102,7 @@
         <v>22.10000038146973</v>
       </c>
       <c r="E559" t="n">
-        <v>371.7483825683594</v>
+        <v>371.7483520507812</v>
       </c>
       <c r="F559" t="n">
         <v>90.84999847412109</v>
@@ -17140,7 +17140,7 @@
         <v>91.75</v>
       </c>
       <c r="G560" t="n">
-        <v>1468.268676757812</v>
+        <v>1468.268798828125</v>
       </c>
       <c r="H560" t="n">
         <v>287.6000061035156</v>
@@ -17172,7 +17172,7 @@
         <v>89.44999694824219</v>
       </c>
       <c r="G561" t="n">
-        <v>1446.209838867188</v>
+        <v>1446.209716796875</v>
       </c>
       <c r="H561" t="n">
         <v>284.5</v>
@@ -17262,7 +17262,7 @@
         <v>20.75</v>
       </c>
       <c r="E564" t="n">
-        <v>352.921875</v>
+        <v>352.9218444824219</v>
       </c>
       <c r="F564" t="n">
         <v>85.90000152587891</v>
@@ -17326,13 +17326,13 @@
         <v>22</v>
       </c>
       <c r="E566" t="n">
-        <v>376.9281005859375</v>
+        <v>376.9281311035156</v>
       </c>
       <c r="F566" t="n">
         <v>89.5</v>
       </c>
       <c r="G566" t="n">
-        <v>1446.876586914062</v>
+        <v>1446.876708984375</v>
       </c>
       <c r="H566" t="n">
         <v>194.6999969482422</v>
@@ -17358,13 +17358,13 @@
         <v>22.10000038146973</v>
       </c>
       <c r="E567" t="n">
-        <v>368.6604309082031</v>
+        <v>368.660400390625</v>
       </c>
       <c r="F567" t="n">
         <v>87.59999847412109</v>
       </c>
       <c r="G567" t="n">
-        <v>1452.607666015625</v>
+        <v>1452.607543945312</v>
       </c>
       <c r="H567" t="n">
         <v>188.75</v>
@@ -17390,7 +17390,7 @@
         <v>22.25</v>
       </c>
       <c r="E568" t="n">
-        <v>381.2113952636719</v>
+        <v>381.21142578125</v>
       </c>
       <c r="F568" t="n">
         <v>87.19999694824219</v>
@@ -17422,13 +17422,13 @@
         <v>22.64999961853027</v>
       </c>
       <c r="E569" t="n">
-        <v>386.4409790039062</v>
+        <v>386.4410095214844</v>
       </c>
       <c r="F569" t="n">
         <v>88.05000305175781</v>
       </c>
       <c r="G569" t="n">
-        <v>1441.936401367188</v>
+        <v>1441.936279296875</v>
       </c>
       <c r="H569" t="n">
         <v>192.9499969482422</v>
@@ -17454,13 +17454,13 @@
         <v>22.75</v>
       </c>
       <c r="E570" t="n">
-        <v>380.3646850585938</v>
+        <v>380.3647155761719</v>
       </c>
       <c r="F570" t="n">
         <v>92.44999694824219</v>
       </c>
       <c r="G570" t="n">
-        <v>1432.895385742188</v>
+        <v>1432.895263671875</v>
       </c>
       <c r="H570" t="n">
         <v>191.6999969482422</v>
@@ -17486,7 +17486,7 @@
         <v>22.35000038146973</v>
       </c>
       <c r="E571" t="n">
-        <v>380.8129577636719</v>
+        <v>380.8129272460938</v>
       </c>
       <c r="F571" t="n">
         <v>92.75</v>
@@ -17524,7 +17524,7 @@
         <v>90.59999847412109</v>
       </c>
       <c r="G572" t="n">
-        <v>1435.2421875</v>
+        <v>1435.242065429688</v>
       </c>
       <c r="H572" t="n">
         <v>190.8999938964844</v>
@@ -17556,7 +17556,7 @@
         <v>88.75</v>
       </c>
       <c r="G573" t="n">
-        <v>1447.568359375</v>
+        <v>1447.568481445312</v>
       </c>
       <c r="H573" t="n">
         <v>185.8000030517578</v>
@@ -17588,7 +17588,7 @@
         <v>88.90000152587891</v>
       </c>
       <c r="G574" t="n">
-        <v>1449.519775390625</v>
+        <v>1449.519897460938</v>
       </c>
       <c r="H574" t="n">
         <v>177.8999938964844</v>
@@ -17678,7 +17678,7 @@
         <v>21.45000076293945</v>
       </c>
       <c r="E577" t="n">
-        <v>368.809814453125</v>
+        <v>368.8098449707031</v>
       </c>
       <c r="F577" t="n">
         <v>80.65000152587891</v>
@@ -17710,13 +17710,13 @@
         <v>21.04999923706055</v>
       </c>
       <c r="E578" t="n">
-        <v>354.8642578125</v>
+        <v>354.8642883300781</v>
       </c>
       <c r="F578" t="n">
         <v>80</v>
       </c>
       <c r="G578" t="n">
-        <v>1384.775634765625</v>
+        <v>1384.775512695312</v>
       </c>
       <c r="H578" t="n">
         <v>170.75</v>
@@ -17748,7 +17748,7 @@
         <v>80.59999847412109</v>
       </c>
       <c r="G579" t="n">
-        <v>1401.647338867188</v>
+        <v>1401.647216796875</v>
       </c>
       <c r="H579" t="n">
         <v>166.8000030517578</v>
@@ -17780,7 +17780,7 @@
         <v>77.55000305175781</v>
       </c>
       <c r="G580" t="n">
-        <v>1377.513305664062</v>
+        <v>1377.513061523438</v>
       </c>
       <c r="H580" t="n">
         <v>161.1999969482422</v>
@@ -17806,7 +17806,7 @@
         <v>20.79999923706055</v>
       </c>
       <c r="E581" t="n">
-        <v>346.4969482421875</v>
+        <v>346.4969787597656</v>
       </c>
       <c r="F581" t="n">
         <v>78</v>
@@ -17844,7 +17844,7 @@
         <v>76.44999694824219</v>
       </c>
       <c r="G582" t="n">
-        <v>1385.986083984375</v>
+        <v>1385.985961914062</v>
       </c>
       <c r="H582" t="n">
         <v>164.6999969482422</v>
@@ -17876,7 +17876,7 @@
         <v>80.25</v>
       </c>
       <c r="G583" t="n">
-        <v>1403.15380859375</v>
+        <v>1403.153930664062</v>
       </c>
       <c r="H583" t="n">
         <v>171.4499969482422</v>
@@ -17902,13 +17902,13 @@
         <v>20.85000038146973</v>
       </c>
       <c r="E584" t="n">
-        <v>352.4736328125</v>
+        <v>352.4736022949219</v>
       </c>
       <c r="F584" t="n">
         <v>80.5</v>
       </c>
       <c r="G584" t="n">
-        <v>1399.3994140625</v>
+        <v>1399.399291992188</v>
       </c>
       <c r="H584" t="n">
         <v>171.6000061035156</v>
@@ -17972,7 +17972,7 @@
         <v>81.69999694824219</v>
       </c>
       <c r="G586" t="n">
-        <v>1418.592895507812</v>
+        <v>1418.5927734375</v>
       </c>
       <c r="H586" t="n">
         <v>170.1000061035156</v>
@@ -18004,7 +18004,7 @@
         <v>80.5</v>
       </c>
       <c r="G587" t="n">
-        <v>1419.012817382812</v>
+        <v>1419.0126953125</v>
       </c>
       <c r="H587" t="n">
         <v>167.8500061035156</v>
@@ -18030,7 +18030,7 @@
         <v>21.20000076293945</v>
       </c>
       <c r="E588" t="n">
-        <v>356.2588195800781</v>
+        <v>356.2588500976562</v>
       </c>
       <c r="F588" t="n">
         <v>82.25</v>
@@ -18068,7 +18068,7 @@
         <v>81.59999847412109</v>
       </c>
       <c r="G589" t="n">
-        <v>1468.342895507812</v>
+        <v>1468.343017578125</v>
       </c>
       <c r="H589" t="n">
         <v>166.0500030517578</v>
@@ -18094,7 +18094,7 @@
         <v>21.39999961853027</v>
       </c>
       <c r="E590" t="n">
-        <v>363.9786987304688</v>
+        <v>363.9786682128906</v>
       </c>
       <c r="F590" t="n">
         <v>82.19999694824219</v>
@@ -18190,7 +18190,7 @@
         <v>20.79999923706055</v>
       </c>
       <c r="E593" t="n">
-        <v>347.8417053222656</v>
+        <v>347.8417358398438</v>
       </c>
       <c r="F593" t="n">
         <v>77.80000305175781</v>
@@ -18222,7 +18222,7 @@
         <v>20.54999923706055</v>
       </c>
       <c r="E594" t="n">
-        <v>346.3973388671875</v>
+        <v>346.3973693847656</v>
       </c>
       <c r="F594" t="n">
         <v>80.94999694824219</v>
@@ -18260,7 +18260,7 @@
         <v>79.90000152587891</v>
       </c>
       <c r="G595" t="n">
-        <v>1413.35595703125</v>
+        <v>1413.356079101562</v>
       </c>
       <c r="H595" t="n">
         <v>166.3500061035156</v>
@@ -18318,7 +18318,7 @@
         <v>19.39999961853027</v>
       </c>
       <c r="E597" t="n">
-        <v>331.6549072265625</v>
+        <v>331.6549377441406</v>
       </c>
       <c r="F597" t="n">
         <v>75.59999847412109</v>
@@ -18350,13 +18350,13 @@
         <v>19.95000076293945</v>
       </c>
       <c r="E598" t="n">
-        <v>344.2557373046875</v>
+        <v>344.2557067871094</v>
       </c>
       <c r="F598" t="n">
         <v>76.09999847412109</v>
       </c>
       <c r="G598" t="n">
-        <v>1403.820922851562</v>
+        <v>1403.821044921875</v>
       </c>
       <c r="H598" t="n">
         <v>149.9499969482422</v>
@@ -18382,13 +18382,13 @@
         <v>20.29999923706055</v>
       </c>
       <c r="E599" t="n">
-        <v>348.0409240722656</v>
+        <v>348.0408935546875</v>
       </c>
       <c r="F599" t="n">
         <v>79.84999847412109</v>
       </c>
       <c r="G599" t="n">
-        <v>1414.541625976562</v>
+        <v>1414.541748046875</v>
       </c>
       <c r="H599" t="n">
         <v>157.6499938964844</v>
@@ -18420,7 +18420,7 @@
         <v>80.90000152587891</v>
       </c>
       <c r="G600" t="n">
-        <v>1452.4345703125</v>
+        <v>1452.434692382812</v>
       </c>
       <c r="H600" t="n">
         <v>167.8000030517578</v>
@@ -18478,7 +18478,7 @@
         <v>21.68000030517578</v>
       </c>
       <c r="E602" t="n">
-        <v>348.8876342773438</v>
+        <v>348.8876037597656</v>
       </c>
       <c r="F602" t="n">
         <v>79.94000244140625</v>
@@ -18548,7 +18548,7 @@
         <v>84.11000061035156</v>
       </c>
       <c r="G604" t="n">
-        <v>1447.790771484375</v>
+        <v>1447.790649414062</v>
       </c>
       <c r="H604" t="n">
         <v>203.1499938964844</v>
@@ -18580,7 +18580,7 @@
         <v>85.09999847412109</v>
       </c>
       <c r="G605" t="n">
-        <v>1459.944213867188</v>
+        <v>1459.944091796875</v>
       </c>
       <c r="H605" t="n">
         <v>208.9799957275391</v>
@@ -18670,13 +18670,13 @@
         <v>22.73999977111816</v>
       </c>
       <c r="E608" t="n">
-        <v>364.1280822753906</v>
+        <v>364.1281127929688</v>
       </c>
       <c r="F608" t="n">
         <v>84.08999633789062</v>
       </c>
       <c r="G608" t="n">
-        <v>1456.14013671875</v>
+        <v>1456.139892578125</v>
       </c>
       <c r="H608" t="n">
         <v>213.25</v>
@@ -18708,7 +18708,7 @@
         <v>83.44999694824219</v>
       </c>
       <c r="G609" t="n">
-        <v>1436.872314453125</v>
+        <v>1436.872436523438</v>
       </c>
       <c r="H609" t="n">
         <v>214.8000030517578</v>
@@ -18734,7 +18734,7 @@
         <v>22.72999954223633</v>
       </c>
       <c r="E610" t="n">
-        <v>353.9677734375</v>
+        <v>353.9678039550781</v>
       </c>
       <c r="F610" t="n">
         <v>82.69999694824219</v>
@@ -18772,7 +18772,7 @@
         <v>80.86000061035156</v>
       </c>
       <c r="G611" t="n">
-        <v>1436.822998046875</v>
+        <v>1436.822875976562</v>
       </c>
       <c r="H611" t="n">
         <v>208.3999938964844</v>
@@ -18798,7 +18798,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="E612" t="n">
-        <v>354.8642578125</v>
+        <v>354.8642883300781</v>
       </c>
       <c r="F612" t="n">
         <v>81.08999633789062</v>
@@ -18958,7 +18958,7 @@
         <v>23.46999931335449</v>
       </c>
       <c r="E617" t="n">
-        <v>349.9335021972656</v>
+        <v>349.9335327148438</v>
       </c>
       <c r="F617" t="n">
         <v>88.41000366210938</v>
@@ -19118,7 +19118,7 @@
         <v>23.09000015258789</v>
       </c>
       <c r="E622" t="n">
-        <v>346.5965881347656</v>
+        <v>346.5965576171875</v>
       </c>
       <c r="F622" t="n">
         <v>82.37999725341797</v>
@@ -19220,7 +19220,7 @@
         <v>84.87000274658203</v>
       </c>
       <c r="G625" t="n">
-        <v>1578.193237304688</v>
+        <v>1578.193115234375</v>
       </c>
       <c r="H625" t="n">
         <v>194.3899993896484</v>
@@ -19284,7 +19284,7 @@
         <v>80.31999969482422</v>
       </c>
       <c r="G627" t="n">
-        <v>1567.768920898438</v>
+        <v>1567.76904296875</v>
       </c>
       <c r="H627" t="n">
         <v>188</v>
@@ -19316,7 +19316,7 @@
         <v>78.91999816894531</v>
       </c>
       <c r="G628" t="n">
-        <v>1536.619506835938</v>
+        <v>1536.61962890625</v>
       </c>
       <c r="H628" t="n">
         <v>181.7400054931641</v>
@@ -19348,7 +19348,7 @@
         <v>78.16999816894531</v>
       </c>
       <c r="G629" t="n">
-        <v>1482.793701171875</v>
+        <v>1482.793579101562</v>
       </c>
       <c r="H629" t="n">
         <v>177.7599945068359</v>
@@ -19380,7 +19380,7 @@
         <v>85.40000152587891</v>
       </c>
       <c r="G630" t="n">
-        <v>1470.170776367188</v>
+        <v>1470.1708984375</v>
       </c>
       <c r="H630" t="n">
         <v>175.1699981689453</v>
@@ -19412,7 +19412,7 @@
         <v>83.40000152587891</v>
       </c>
       <c r="G631" t="n">
-        <v>1477.877807617188</v>
+        <v>1477.8779296875</v>
       </c>
       <c r="H631" t="n">
         <v>184.3899993896484</v>
@@ -19438,7 +19438,7 @@
         <v>23.82999992370605</v>
       </c>
       <c r="E632" t="n">
-        <v>327.9194946289062</v>
+        <v>327.9195251464844</v>
       </c>
       <c r="F632" t="n">
         <v>84.30999755859375</v>
@@ -19470,7 +19470,7 @@
         <v>23.92000007629395</v>
       </c>
       <c r="E633" t="n">
-        <v>330.6090087890625</v>
+        <v>330.6089782714844</v>
       </c>
       <c r="F633" t="n">
         <v>91.58999633789062</v>
@@ -19508,7 +19508,7 @@
         <v>93.55999755859375</v>
       </c>
       <c r="G634" t="n">
-        <v>1501.987182617188</v>
+        <v>1501.987060546875</v>
       </c>
       <c r="H634" t="n">
         <v>199.3699951171875</v>
@@ -19534,13 +19534,13 @@
         <v>24.17000007629395</v>
       </c>
       <c r="E635" t="n">
-        <v>328.0689392089844</v>
+        <v>328.0689086914062</v>
       </c>
       <c r="F635" t="n">
         <v>90.97000122070312</v>
       </c>
       <c r="G635" t="n">
-        <v>1495.119873046875</v>
+        <v>1495.119995117188</v>
       </c>
       <c r="H635" t="n">
         <v>201.2599945068359</v>
@@ -19572,7 +19572,7 @@
         <v>98.19999694824219</v>
       </c>
       <c r="G636" t="n">
-        <v>1487.486938476562</v>
+        <v>1487.487060546875</v>
       </c>
       <c r="H636" t="n">
         <v>207.1699981689453</v>
@@ -19604,7 +19604,7 @@
         <v>93.66000366210938</v>
       </c>
       <c r="G637" t="n">
-        <v>1497.244506835938</v>
+        <v>1497.244384765625</v>
       </c>
       <c r="H637" t="n">
         <v>214.4400024414062</v>
@@ -19630,7 +19630,7 @@
         <v>23.06999969482422</v>
       </c>
       <c r="E638" t="n">
-        <v>324.98095703125</v>
+        <v>324.9809875488281</v>
       </c>
       <c r="F638" t="n">
         <v>93.27999877929688</v>
@@ -19668,7 +19668,7 @@
         <v>87.73999786376953</v>
       </c>
       <c r="G639" t="n">
-        <v>1430.079223632812</v>
+        <v>1430.079345703125</v>
       </c>
       <c r="H639" t="n">
         <v>195.3300018310547</v>
@@ -19764,7 +19764,7 @@
         <v>96.30999755859375</v>
       </c>
       <c r="G642" t="n">
-        <v>1431.85791015625</v>
+        <v>1431.857788085938</v>
       </c>
       <c r="H642" t="n">
         <v>208.1999969482422</v>
@@ -19790,13 +19790,13 @@
         <v>21.71999931335449</v>
       </c>
       <c r="E643" t="n">
-        <v>324.33349609375</v>
+        <v>324.3335266113281</v>
       </c>
       <c r="F643" t="n">
         <v>99.91999816894531</v>
       </c>
       <c r="G643" t="n">
-        <v>1456.73291015625</v>
+        <v>1456.733032226562</v>
       </c>
       <c r="H643" t="n">
         <v>230.0200042724609</v>
@@ -19828,7 +19828,7 @@
         <v>96.81999969482422</v>
       </c>
       <c r="G644" t="n">
-        <v>1443.220825195312</v>
+        <v>1443.220703125</v>
       </c>
       <c r="H644" t="n">
         <v>226.0599975585938</v>
@@ -19860,7 +19860,7 @@
         <v>93.66999816894531</v>
       </c>
       <c r="G645" t="n">
-        <v>1446.185180664062</v>
+        <v>1446.18505859375</v>
       </c>
       <c r="H645" t="n">
         <v>222.8699951171875</v>
@@ -20014,7 +20014,7 @@
         <v>21.45999908447266</v>
       </c>
       <c r="E650" t="n">
-        <v>329.8121337890625</v>
+        <v>329.8121032714844</v>
       </c>
       <c r="F650" t="n">
         <v>98.65000152587891</v>
@@ -20116,7 +20116,7 @@
         <v>95.69999694824219</v>
       </c>
       <c r="G653" t="n">
-        <v>1499.649169921875</v>
+        <v>1499.649047851562</v>
       </c>
       <c r="H653" t="n">
         <v>206.75</v>
@@ -20142,7 +20142,7 @@
         <v>21.40999984741211</v>
       </c>
       <c r="E654" t="n">
-        <v>322.3412780761719</v>
+        <v>322.34130859375</v>
       </c>
       <c r="F654" t="n">
         <v>97.77999877929688</v>
@@ -20174,13 +20174,13 @@
         <v>21.23999977111816</v>
       </c>
       <c r="E655" t="n">
-        <v>320.9965209960938</v>
+        <v>320.9965515136719</v>
       </c>
       <c r="F655" t="n">
         <v>96.19000244140625</v>
       </c>
       <c r="G655" t="n">
-        <v>1485.4716796875</v>
+        <v>1485.471557617188</v>
       </c>
       <c r="H655" t="n">
         <v>213.5</v>
@@ -20238,7 +20238,7 @@
         <v>21.11000061035156</v>
       </c>
       <c r="E657" t="n">
-        <v>320.4486694335938</v>
+        <v>320.4486999511719</v>
       </c>
       <c r="F657" t="n">
         <v>95.16000366210938</v>
@@ -20276,7 +20276,7 @@
         <v>94.29000091552734</v>
       </c>
       <c r="G658" t="n">
-        <v>1503.267944335938</v>
+        <v>1503.267822265625</v>
       </c>
       <c r="H658" t="n">
         <v>204.75</v>
@@ -20302,7 +20302,7 @@
         <v>20.65999984741211</v>
       </c>
       <c r="E659" t="n">
-        <v>348.8377990722656</v>
+        <v>348.8378295898438</v>
       </c>
       <c r="F659" t="n">
         <v>93.05999755859375</v>
@@ -20334,7 +20334,7 @@
         <v>20.5</v>
       </c>
       <c r="E660" t="n">
-        <v>345.8494873046875</v>
+        <v>345.8495178222656</v>
       </c>
       <c r="F660" t="n">
         <v>91.76000213623047</v>
@@ -20436,7 +20436,7 @@
         <v>89.33999633789062</v>
       </c>
       <c r="G663" t="n">
-        <v>1449.928466796875</v>
+        <v>1449.928344726562</v>
       </c>
       <c r="H663" t="n">
         <v>211.75</v>
@@ -20468,7 +20468,7 @@
         <v>90.38999938964844</v>
       </c>
       <c r="G664" t="n">
-        <v>1449.011474609375</v>
+        <v>1449.011352539062</v>
       </c>
       <c r="H664" t="n">
         <v>216.9700012207031</v>
@@ -20500,7 +20500,7 @@
         <v>88.48999786376953</v>
       </c>
       <c r="G665" t="n">
-        <v>1439.072265625</v>
+        <v>1439.072143554688</v>
       </c>
       <c r="H665" t="n">
         <v>210.9799957275391</v>
@@ -20590,13 +20590,13 @@
         <v>21.73999977111816</v>
       </c>
       <c r="E668" t="n">
-        <v>347.4432678222656</v>
+        <v>347.4432373046875</v>
       </c>
       <c r="F668" t="n">
         <v>91.58000183105469</v>
       </c>
       <c r="G668" t="n">
-        <v>1458.752319335938</v>
+        <v>1458.752197265625</v>
       </c>
       <c r="H668" t="n">
         <v>216.0500030517578</v>
@@ -20660,7 +20660,7 @@
         <v>90.40000152587891</v>
       </c>
       <c r="G670" t="n">
-        <v>1450.919799804688</v>
+        <v>1450.919921875</v>
       </c>
       <c r="H670" t="n">
         <v>282.7300109863281</v>
@@ -20686,7 +20686,7 @@
         <v>20.45000076293945</v>
       </c>
       <c r="E671" t="n">
-        <v>345.3016052246094</v>
+        <v>345.3016357421875</v>
       </c>
       <c r="F671" t="n">
         <v>83.73999786376953</v>
@@ -20750,7 +20750,7 @@
         <v>20.71999931335449</v>
       </c>
       <c r="E673" t="n">
-        <v>352.8720397949219</v>
+        <v>352.8720703125</v>
       </c>
       <c r="F673" t="n">
         <v>83.36000061035156</v>
@@ -20974,7 +20974,7 @@
         <v>20.25</v>
       </c>
       <c r="E680" t="n">
-        <v>344.2557373046875</v>
+        <v>344.2557067871094</v>
       </c>
       <c r="F680" t="n">
         <v>80.34999847412109</v>
@@ -21044,7 +21044,7 @@
         <v>74</v>
       </c>
       <c r="G682" t="n">
-        <v>1358.98876953125</v>
+        <v>1358.988891601562</v>
       </c>
       <c r="H682" t="n">
         <v>288.25</v>
@@ -21070,13 +21070,13 @@
         <v>19.6200008392334</v>
       </c>
       <c r="E683" t="n">
-        <v>344.2557373046875</v>
+        <v>344.2557067871094</v>
       </c>
       <c r="F683" t="n">
         <v>75.75</v>
       </c>
       <c r="G683" t="n">
-        <v>1385.3857421875</v>
+        <v>1385.385864257812</v>
       </c>
       <c r="H683" t="n">
         <v>299.5</v>
@@ -21166,7 +21166,7 @@
         <v>20.09000015258789</v>
       </c>
       <c r="E686" t="n">
-        <v>340.1716613769531</v>
+        <v>340.171630859375</v>
       </c>
       <c r="F686" t="n">
         <v>81.36000061035156</v>
@@ -21198,7 +21198,7 @@
         <v>20.72999954223633</v>
       </c>
       <c r="E687" t="n">
-        <v>338.727294921875</v>
+        <v>338.7272644042969</v>
       </c>
       <c r="F687" t="n">
         <v>79.09999847412109</v>
@@ -21262,13 +21262,13 @@
         <v>20.48999977111816</v>
       </c>
       <c r="E689" t="n">
-        <v>332.3522033691406</v>
+        <v>332.3521728515625</v>
       </c>
       <c r="F689" t="n">
         <v>85.95999908447266</v>
       </c>
       <c r="G689" t="n">
-        <v>1342.4814453125</v>
+        <v>1342.481323242188</v>
       </c>
       <c r="H689" t="n">
         <v>291.4500122070312</v>
@@ -21364,7 +21364,7 @@
         <v>80</v>
       </c>
       <c r="G692" t="n">
-        <v>1357.476928710938</v>
+        <v>1357.476806640625</v>
       </c>
       <c r="H692" t="n">
         <v>267.9500122070312</v>
@@ -21390,13 +21390,13 @@
         <v>18.84000015258789</v>
       </c>
       <c r="E693" t="n">
-        <v>312.8283996582031</v>
+        <v>312.8284301757812</v>
       </c>
       <c r="F693" t="n">
         <v>76.08000183105469</v>
       </c>
       <c r="G693" t="n">
-        <v>1331.84814453125</v>
+        <v>1331.848266601562</v>
       </c>
       <c r="H693" t="n">
         <v>254.5500030517578</v>
@@ -21422,13 +21422,13 @@
         <v>18.93000030517578</v>
       </c>
       <c r="E694" t="n">
-        <v>313.4758911132812</v>
+        <v>313.4759216308594</v>
       </c>
       <c r="F694" t="n">
         <v>79.12999725341797</v>
       </c>
       <c r="G694" t="n">
-        <v>1327.064453125</v>
+        <v>1327.064575195312</v>
       </c>
       <c r="H694" t="n">
         <v>267.25</v>
@@ -21582,7 +21582,7 @@
         <v>19.28000068664551</v>
       </c>
       <c r="E699" t="n">
-        <v>318.7054748535156</v>
+        <v>318.7055053710938</v>
       </c>
       <c r="F699" t="n">
         <v>81.11000061035156</v>
@@ -21748,7 +21748,7 @@
         <v>86.12000274658203</v>
       </c>
       <c r="G704" t="n">
-        <v>1314.002319335938</v>
+        <v>1314.002197265625</v>
       </c>
       <c r="H704" t="n">
         <v>303.3500061035156</v>
@@ -21774,13 +21774,13 @@
         <v>19.6299991607666</v>
       </c>
       <c r="E705" t="n">
-        <v>320.2992553710938</v>
+        <v>320.2992248535156</v>
       </c>
       <c r="F705" t="n">
         <v>83.80999755859375</v>
       </c>
       <c r="G705" t="n">
-        <v>1294.471069335938</v>
+        <v>1294.470947265625</v>
       </c>
       <c r="H705" t="n">
         <v>288.25</v>
@@ -21812,7 +21812,7 @@
         <v>82.36000061035156</v>
       </c>
       <c r="G706" t="n">
-        <v>1272.758422851562</v>
+        <v>1272.758544921875</v>
       </c>
       <c r="H706" t="n">
         <v>274.2999877929688</v>
@@ -21902,7 +21902,7 @@
         <v>18.28000068664551</v>
       </c>
       <c r="E709" t="n">
-        <v>298.2354125976562</v>
+        <v>298.2353820800781</v>
       </c>
       <c r="F709" t="n">
         <v>77.97000122070312</v>
@@ -22030,13 +22030,13 @@
         <v>18.11000061035156</v>
       </c>
       <c r="E713" t="n">
-        <v>312.9778747558594</v>
+        <v>312.9778442382812</v>
       </c>
       <c r="F713" t="n">
         <v>84.30000305175781</v>
       </c>
       <c r="G713" t="n">
-        <v>1212.528686523438</v>
+        <v>1212.528564453125</v>
       </c>
       <c r="H713" t="n">
         <v>248.6000061035156</v>
@@ -22062,13 +22062,13 @@
         <v>18.17000007629395</v>
       </c>
       <c r="E714" t="n">
-        <v>312.5793762207031</v>
+        <v>312.5794067382812</v>
       </c>
       <c r="F714" t="n">
         <v>79.55999755859375</v>
       </c>
       <c r="G714" t="n">
-        <v>1254.565551757812</v>
+        <v>1254.565673828125</v>
       </c>
       <c r="H714" t="n">
         <v>257.6499938964844</v>
@@ -22132,7 +22132,7 @@
         <v>79.15000152587891</v>
       </c>
       <c r="G716" t="n">
-        <v>1284.606201171875</v>
+        <v>1284.606079101562</v>
       </c>
       <c r="H716" t="n">
         <v>271.75</v>
@@ -22158,7 +22158,7 @@
         <v>17.02000045776367</v>
       </c>
       <c r="E717" t="n">
-        <v>327.6206665039062</v>
+        <v>327.6206359863281</v>
       </c>
       <c r="F717" t="n">
         <v>79.70999908447266</v>
@@ -22222,7 +22222,7 @@
         <v>17.28000068664551</v>
       </c>
       <c r="E719" t="n">
-        <v>327.0728149414062</v>
+        <v>327.0727844238281</v>
       </c>
       <c r="F719" t="n">
         <v>78.83999633789062</v>
@@ -22260,7 +22260,7 @@
         <v>79.05000305175781</v>
       </c>
       <c r="G720" t="n">
-        <v>1297.941162109375</v>
+        <v>1297.941040039062</v>
       </c>
       <c r="H720" t="n">
         <v>274.0499877929688</v>
@@ -22286,13 +22286,13 @@
         <v>17.86000061035156</v>
       </c>
       <c r="E721" t="n">
-        <v>339.0261535644531</v>
+        <v>339.026123046875</v>
       </c>
       <c r="F721" t="n">
         <v>79.80999755859375</v>
       </c>
       <c r="G721" t="n">
-        <v>1311.969848632812</v>
+        <v>1311.969970703125</v>
       </c>
       <c r="H721" t="n">
         <v>281.3999938964844</v>
@@ -22350,7 +22350,7 @@
         <v>17.93000030517578</v>
       </c>
       <c r="E723" t="n">
-        <v>340.1716613769531</v>
+        <v>340.171630859375</v>
       </c>
       <c r="F723" t="n">
         <v>79.20999908447266</v>
@@ -22382,13 +22382,13 @@
         <v>18.06999969482422</v>
       </c>
       <c r="E724" t="n">
-        <v>337.581787109375</v>
+        <v>337.5817565917969</v>
       </c>
       <c r="F724" t="n">
         <v>79.58999633789062</v>
       </c>
       <c r="G724" t="n">
-        <v>1300.320434570312</v>
+        <v>1300.320556640625</v>
       </c>
       <c r="H724" t="n">
         <v>303.25</v>
@@ -22548,7 +22548,7 @@
         <v>74.69000244140625</v>
       </c>
       <c r="G729" t="n">
-        <v>1261.951904296875</v>
+        <v>1261.951782226562</v>
       </c>
       <c r="H729" t="n">
         <v>294.7000122070312</v>
@@ -22574,13 +22574,13 @@
         <v>17.80999946594238</v>
       </c>
       <c r="E730" t="n">
-        <v>339.0261535644531</v>
+        <v>339.026123046875</v>
       </c>
       <c r="F730" t="n">
         <v>74.36000061035156</v>
       </c>
       <c r="G730" t="n">
-        <v>1257.44091796875</v>
+        <v>1257.440795898438</v>
       </c>
       <c r="H730" t="n">
         <v>291.9500122070312</v>
@@ -22606,13 +22606,13 @@
         <v>17.55999946594238</v>
       </c>
       <c r="E731" t="n">
-        <v>335.7887573242188</v>
+        <v>335.7887878417969</v>
       </c>
       <c r="F731" t="n">
         <v>73.54000091552734</v>
       </c>
       <c r="G731" t="n">
-        <v>1234.6376953125</v>
+        <v>1234.637817382812</v>
       </c>
       <c r="H731" t="n">
         <v>286.7000122070312</v>
@@ -22638,7 +22638,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="E732" t="n">
-        <v>323.3373718261719</v>
+        <v>323.33740234375</v>
       </c>
       <c r="F732" t="n">
         <v>72.55999755859375</v>
@@ -22670,7 +22670,7 @@
         <v>17.13999938964844</v>
       </c>
       <c r="E733" t="n">
-        <v>311.7825317382812</v>
+        <v>311.7825012207031</v>
       </c>
       <c r="F733" t="n">
         <v>70.18000030517578</v>
@@ -22702,13 +22702,13 @@
         <v>16.61000061035156</v>
       </c>
       <c r="E734" t="n">
-        <v>303.1163635253906</v>
+        <v>303.1163330078125</v>
       </c>
       <c r="F734" t="n">
         <v>74.33999633789062</v>
       </c>
       <c r="G734" t="n">
-        <v>1194.980224609375</v>
+        <v>1194.980346679688</v>
       </c>
       <c r="H734" t="n">
         <v>290.2999877929688</v>
@@ -22772,7 +22772,7 @@
         <v>73.47000122070312</v>
       </c>
       <c r="G736" t="n">
-        <v>1212.28076171875</v>
+        <v>1212.280883789062</v>
       </c>
       <c r="H736" t="n">
         <v>302.2999877929688</v>
@@ -22830,7 +22830,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="E738" t="n">
-        <v>303.7638549804688</v>
+        <v>303.7638244628906</v>
       </c>
       <c r="F738" t="n">
         <v>73.19000244140625</v>
@@ -22862,13 +22862,13 @@
         <v>15.19999980926514</v>
       </c>
       <c r="E739" t="n">
-        <v>305.0587463378906</v>
+        <v>305.0587768554688</v>
       </c>
       <c r="F739" t="n">
         <v>70.33999633789062</v>
       </c>
       <c r="G739" t="n">
-        <v>1200.333984375</v>
+        <v>1200.333862304688</v>
       </c>
       <c r="H739" t="n">
         <v>297.0499877929688</v>
@@ -22990,13 +22990,13 @@
         <v>16.32999992370605</v>
       </c>
       <c r="E743" t="n">
-        <v>306.2540893554688</v>
+        <v>306.2541198730469</v>
       </c>
       <c r="F743" t="n">
         <v>72.80000305175781</v>
       </c>
       <c r="G743" t="n">
-        <v>1240.437744140625</v>
+        <v>1240.437622070312</v>
       </c>
       <c r="H743" t="n">
         <v>319.2000122070312</v>
@@ -23022,13 +23022,13 @@
         <v>15.73999977111816</v>
       </c>
       <c r="E744" t="n">
-        <v>295.5458984375</v>
+        <v>295.5459289550781</v>
       </c>
       <c r="F744" t="n">
         <v>68.94999694824219</v>
       </c>
       <c r="G744" t="n">
-        <v>1207.571411132812</v>
+        <v>1207.571533203125</v>
       </c>
       <c r="H744" t="n">
         <v>303.25</v>
@@ -23118,13 +23118,13 @@
         <v>15.77999973297119</v>
       </c>
       <c r="E747" t="n">
-        <v>288.1249084472656</v>
+        <v>288.1248779296875</v>
       </c>
       <c r="F747" t="n">
         <v>66.61000061035156</v>
       </c>
       <c r="G747" t="n">
-        <v>1244.006713867188</v>
+        <v>1244.0068359375</v>
       </c>
       <c r="H747" t="n">
         <v>287.0499877929688</v>
@@ -23182,7 +23182,7 @@
         <v>14.53999996185303</v>
       </c>
       <c r="E749" t="n">
-        <v>265.1147155761719</v>
+        <v>265.11474609375</v>
       </c>
       <c r="F749" t="n">
         <v>59.84000015258789</v>
@@ -23214,7 +23214,7 @@
         <v>15.23999977111816</v>
       </c>
       <c r="E750" t="n">
-        <v>271.7886657714844</v>
+        <v>271.7886962890625</v>
       </c>
       <c r="F750" t="n">
         <v>61.43999862670898</v>
@@ -23412,7 +23412,7 @@
         <v>54.09999847412109</v>
       </c>
       <c r="G756" t="n">
-        <v>1266.165405273438</v>
+        <v>1266.16552734375</v>
       </c>
       <c r="H756" t="n">
         <v>274.3999938964844</v>
@@ -23444,7 +23444,7 @@
         <v>53.88999938964844</v>
       </c>
       <c r="G757" t="n">
-        <v>1252.83056640625</v>
+        <v>1252.830688476562</v>
       </c>
       <c r="H757" t="n">
         <v>274.3999938964844</v>
@@ -23502,7 +23502,7 @@
         <v>14.88000011444092</v>
       </c>
       <c r="E759" t="n">
-        <v>232.3925323486328</v>
+        <v>232.3925170898438</v>
       </c>
       <c r="F759" t="n">
         <v>50.02999877929688</v>
@@ -23534,13 +23534,13 @@
         <v>14.77999973297119</v>
       </c>
       <c r="E760" t="n">
-        <v>232.4921417236328</v>
+        <v>232.4921264648438</v>
       </c>
       <c r="F760" t="n">
         <v>49.66999816894531</v>
       </c>
       <c r="G760" t="n">
-        <v>1223.831176757812</v>
+        <v>1223.8310546875</v>
       </c>
       <c r="H760" t="n">
         <v>240.6000061035156</v>
@@ -23662,7 +23662,7 @@
         <v>15.10999965667725</v>
       </c>
       <c r="E764" t="n">
-        <v>240.5705871582031</v>
+        <v>240.5705718994141</v>
       </c>
       <c r="F764" t="n">
         <v>52.81999969482422</v>
@@ -23726,7 +23726,7 @@
         <v>14.75</v>
       </c>
       <c r="E766" t="n">
-        <v>244.1466369628906</v>
+        <v>244.1466217041016</v>
       </c>
       <c r="F766" t="n">
         <v>51.83000183105469</v>
@@ -23758,7 +23758,7 @@
         <v>14.84000015258789</v>
       </c>
       <c r="E767" t="n">
-        <v>248.8482666015625</v>
+        <v>248.8482818603516</v>
       </c>
       <c r="F767" t="n">
         <v>53.2599983215332</v>
@@ -23822,7 +23822,7 @@
         <v>14.69999980926514</v>
       </c>
       <c r="E769" t="n">
-        <v>248.4797058105469</v>
+        <v>248.4796905517578</v>
       </c>
       <c r="F769" t="n">
         <v>51.79000091552734</v>
@@ -23854,7 +23854,7 @@
         <v>14.82999992370605</v>
       </c>
       <c r="E770" t="n">
-        <v>242.0149536132812</v>
+        <v>242.0149688720703</v>
       </c>
       <c r="F770" t="n">
         <v>50.41999816894531</v>
@@ -23950,13 +23950,13 @@
         <v>14.34000015258789</v>
       </c>
       <c r="E773" t="n">
-        <v>227.1728973388672</v>
+        <v>227.1729125976562</v>
       </c>
       <c r="F773" t="n">
         <v>49.22999954223633</v>
       </c>
       <c r="G773" t="n">
-        <v>1205.687744140625</v>
+        <v>1205.687622070312</v>
       </c>
       <c r="H773" t="n">
         <v>266.7000122070312</v>
@@ -24020,7 +24020,7 @@
         <v>46.41999816894531</v>
       </c>
       <c r="G775" t="n">
-        <v>1214.412353515625</v>
+        <v>1214.412475585938</v>
       </c>
       <c r="H775" t="n">
         <v>244.3500061035156</v>
@@ -24078,13 +24078,13 @@
         <v>14.14000034332275</v>
       </c>
       <c r="E777" t="n">
-        <v>228.0295715332031</v>
+        <v>228.0295562744141</v>
       </c>
       <c r="F777" t="n">
         <v>46.93000030517578</v>
       </c>
       <c r="G777" t="n">
-        <v>1216.940551757812</v>
+        <v>1216.9404296875</v>
       </c>
       <c r="H777" t="n">
         <v>256.25</v>
@@ -24180,7 +24180,7 @@
         <v>45.2599983215332</v>
       </c>
       <c r="G780" t="n">
-        <v>1204.151000976562</v>
+        <v>1204.151123046875</v>
       </c>
       <c r="H780" t="n">
         <v>240.8000030517578</v>
@@ -24212,7 +24212,7 @@
         <v>45.16999816894531</v>
       </c>
       <c r="G781" t="n">
-        <v>1193.691284179688</v>
+        <v>1193.69140625</v>
       </c>
       <c r="H781" t="n">
         <v>238.8000030517578</v>
@@ -24270,7 +24270,7 @@
         <v>13.22000026702881</v>
       </c>
       <c r="E783" t="n">
-        <v>206.8024597167969</v>
+        <v>206.8024444580078</v>
       </c>
       <c r="F783" t="n">
         <v>41.31999969482422</v>
@@ -24372,7 +24372,7 @@
         <v>43</v>
       </c>
       <c r="G786" t="n">
-        <v>1165.534545898438</v>
+        <v>1165.534423828125</v>
       </c>
       <c r="H786" t="n">
         <v>219.6000061035156</v>
@@ -24398,13 +24398,13 @@
         <v>13.89999961853027</v>
       </c>
       <c r="E787" t="n">
-        <v>219.0845031738281</v>
+        <v>219.0844879150391</v>
       </c>
       <c r="F787" t="n">
         <v>44.04999923706055</v>
       </c>
       <c r="G787" t="n">
-        <v>1199.243408203125</v>
+        <v>1199.243286132812</v>
       </c>
       <c r="H787" t="n">
         <v>235.8600006103516</v>
@@ -24430,7 +24430,7 @@
         <v>14.17000007629395</v>
       </c>
       <c r="E788" t="n">
-        <v>220.9472045898438</v>
+        <v>220.9472198486328</v>
       </c>
       <c r="F788" t="n">
         <v>45.45000076293945</v>
@@ -24468,7 +24468,7 @@
         <v>44.18999862670898</v>
       </c>
       <c r="G789" t="n">
-        <v>1227.796752929688</v>
+        <v>1227.796875</v>
       </c>
       <c r="H789" t="n">
         <v>229.7200012207031</v>
@@ -24526,13 +24526,13 @@
         <v>13.38000011444092</v>
       </c>
       <c r="E791" t="n">
-        <v>224.6527557373047</v>
+        <v>224.6527404785156</v>
       </c>
       <c r="F791" t="n">
         <v>41.93000030517578</v>
       </c>
       <c r="G791" t="n">
-        <v>1246.287109375</v>
+        <v>1246.287231445312</v>
       </c>
       <c r="H791" t="n">
         <v>220.3300018310547</v>
@@ -24564,7 +24564,7 @@
         <v>41.4900016784668</v>
       </c>
       <c r="G792" t="n">
-        <v>1237.215576171875</v>
+        <v>1237.215454101562</v>
       </c>
       <c r="H792" t="n">
         <v>218.4400024414062</v>
@@ -24590,13 +24590,13 @@
         <v>13.01000022888184</v>
       </c>
       <c r="E793" t="n">
-        <v>218.6661376953125</v>
+        <v>218.6661224365234</v>
       </c>
       <c r="F793" t="n">
         <v>40.52999877929688</v>
       </c>
       <c r="G793" t="n">
-        <v>1228.242797851562</v>
+        <v>1228.242919921875</v>
       </c>
       <c r="H793" t="n">
         <v>219.3800048828125</v>
@@ -24622,13 +24622,13 @@
         <v>13.01000022888184</v>
       </c>
       <c r="E794" t="n">
-        <v>218.6661376953125</v>
+        <v>218.6661224365234</v>
       </c>
       <c r="F794" t="n">
         <v>40.52999877929688</v>
       </c>
       <c r="G794" t="n">
-        <v>1228.242797851562</v>
+        <v>1228.242919921875</v>
       </c>
       <c r="H794" t="n">
         <v>219.3800048828125</v>
@@ -24654,7 +24654,7 @@
         <v>13.55000019073486</v>
       </c>
       <c r="E795" t="n">
-        <v>227.9498748779297</v>
+        <v>227.9498596191406</v>
       </c>
       <c r="F795" t="n">
         <v>43.86999893188477</v>
@@ -24692,7 +24692,7 @@
         <v>44.0099983215332</v>
       </c>
       <c r="G796" t="n">
-        <v>1258.283569335938</v>
+        <v>1258.283447265625</v>
       </c>
       <c r="H796" t="n">
         <v>237.2799987792969</v>
@@ -24718,13 +24718,13 @@
         <v>13.71000003814697</v>
       </c>
       <c r="E797" t="n">
-        <v>228.2287750244141</v>
+        <v>228.2287902832031</v>
       </c>
       <c r="F797" t="n">
         <v>47.43999862670898</v>
       </c>
       <c r="G797" t="n">
-        <v>1265.421752929688</v>
+        <v>1265.421875</v>
       </c>
       <c r="H797" t="n">
         <v>239.5</v>
@@ -24750,13 +24750,13 @@
         <v>13.9399995803833</v>
       </c>
       <c r="E798" t="n">
-        <v>231.7749328613281</v>
+        <v>231.7749176025391</v>
       </c>
       <c r="F798" t="n">
         <v>47.4900016784668</v>
       </c>
       <c r="G798" t="n">
-        <v>1290.951293945312</v>
+        <v>1290.951416015625</v>
       </c>
       <c r="H798" t="n">
         <v>243.6399993896484</v>
@@ -24782,7 +24782,7 @@
         <v>13.32999992370605</v>
       </c>
       <c r="E799" t="n">
-        <v>226.6449584960938</v>
+        <v>226.6449737548828</v>
       </c>
       <c r="F799" t="n">
         <v>45.36000061035156</v>
@@ -24846,7 +24846,7 @@
         <v>13.07999992370605</v>
       </c>
       <c r="E801" t="n">
-        <v>224.9017639160156</v>
+        <v>224.9017791748047</v>
       </c>
       <c r="F801" t="n">
         <v>44.95999908447266</v>
@@ -24878,7 +24878,7 @@
         <v>13</v>
       </c>
       <c r="E802" t="n">
-        <v>226.6250305175781</v>
+        <v>226.6250457763672</v>
       </c>
       <c r="F802" t="n">
         <v>43.40999984741211</v>
@@ -24948,7 +24948,7 @@
         <v>44.70000076293945</v>
       </c>
       <c r="G804" t="n">
-        <v>1240.437744140625</v>
+        <v>1240.437622070312</v>
       </c>
       <c r="H804" t="n">
         <v>257.2000122070312</v>
@@ -24980,7 +24980,7 @@
         <v>45.41999816894531</v>
       </c>
       <c r="G805" t="n">
-        <v>1238.008666992188</v>
+        <v>1238.008544921875</v>
       </c>
       <c r="H805" t="n">
         <v>262.25</v>
@@ -25038,13 +25038,13 @@
         <v>12.46000003814697</v>
       </c>
       <c r="E807" t="n">
-        <v>212.6894683837891</v>
+        <v>212.689453125</v>
       </c>
       <c r="F807" t="n">
         <v>41.22999954223633</v>
       </c>
       <c r="G807" t="n">
-        <v>1155.719116210938</v>
+        <v>1155.71923828125</v>
       </c>
       <c r="H807" t="n">
         <v>241.5</v>
@@ -25070,7 +25070,7 @@
         <v>12.98999977111816</v>
       </c>
       <c r="E808" t="n">
-        <v>223.935546875</v>
+        <v>223.9355316162109</v>
       </c>
       <c r="F808" t="n">
         <v>41.70999908447266</v>
@@ -25262,13 +25262,13 @@
         <v>14.10999965667725</v>
       </c>
       <c r="E814" t="n">
-        <v>245.4216461181641</v>
+        <v>245.4216613769531</v>
       </c>
       <c r="F814" t="n">
         <v>45.11000061035156</v>
       </c>
       <c r="G814" t="n">
-        <v>1284.407836914062</v>
+        <v>1284.407958984375</v>
       </c>
       <c r="H814" t="n">
         <v>271.25</v>
@@ -25300,7 +25300,7 @@
         <v>45.79000091552734</v>
       </c>
       <c r="G815" t="n">
-        <v>1280.144775390625</v>
+        <v>1280.144653320312</v>
       </c>
       <c r="H815" t="n">
         <v>266.5499877929688</v>
@@ -25326,7 +25326,7 @@
         <v>14.72999954223633</v>
       </c>
       <c r="E816" t="n">
-        <v>257.1359252929688</v>
+        <v>257.1358947753906</v>
       </c>
       <c r="F816" t="n">
         <v>45.86999893188477</v>
@@ -25422,13 +25422,13 @@
         <v>14.02000045776367</v>
       </c>
       <c r="E819" t="n">
-        <v>256.8968200683594</v>
+        <v>256.8968505859375</v>
       </c>
       <c r="F819" t="n">
         <v>43.45000076293945</v>
       </c>
       <c r="G819" t="n">
-        <v>1357.080444335938</v>
+        <v>1357.080322265625</v>
       </c>
       <c r="H819" t="n">
         <v>255.3000030517578</v>
@@ -25454,7 +25454,7 @@
         <v>13.90999984741211</v>
       </c>
       <c r="E820" t="n">
-        <v>256.6278991699219</v>
+        <v>256.6278686523438</v>
       </c>
       <c r="F820" t="n">
         <v>45.27000045776367</v>
@@ -25678,13 +25678,13 @@
         <v>13.15999984741211</v>
       </c>
       <c r="E827" t="n">
-        <v>247.3839874267578</v>
+        <v>247.3840026855469</v>
       </c>
       <c r="F827" t="n">
         <v>42.4900016784668</v>
       </c>
       <c r="G827" t="n">
-        <v>1365.408325195312</v>
+        <v>1365.408447265625</v>
       </c>
       <c r="H827" t="n">
         <v>234.6000061035156</v>
@@ -25716,7 +25716,7 @@
         <v>45.20000076293945</v>
       </c>
       <c r="G828" t="n">
-        <v>1424.200561523438</v>
+        <v>1424.20068359375</v>
       </c>
       <c r="H828" t="n">
         <v>255.3500061035156</v>
@@ -25748,7 +25748,7 @@
         <v>45.61000061035156</v>
       </c>
       <c r="G829" t="n">
-        <v>1403.57861328125</v>
+        <v>1403.578735351562</v>
       </c>
       <c r="H829" t="n">
         <v>265.0499877929688</v>
@@ -25780,7 +25780,7 @@
         <v>46.59000015258789</v>
       </c>
       <c r="G830" t="n">
-        <v>1412.204345703125</v>
+        <v>1412.204223632812</v>
       </c>
       <c r="H830" t="n">
         <v>271.6499938964844</v>
@@ -25902,13 +25902,13 @@
         <v>15.01000022888184</v>
       </c>
       <c r="E834" t="n">
-        <v>270.3941650390625</v>
+        <v>270.3941345214844</v>
       </c>
       <c r="F834" t="n">
         <v>46.61999893188477</v>
       </c>
       <c r="G834" t="n">
-        <v>1412.402465820312</v>
+        <v>1412.402587890625</v>
       </c>
       <c r="H834" t="n">
         <v>274.6499938964844</v>
@@ -25934,13 +25934,13 @@
         <v>15.14999961853027</v>
       </c>
       <c r="E835" t="n">
-        <v>273.2828674316406</v>
+        <v>273.2828369140625</v>
       </c>
       <c r="F835" t="n">
         <v>46.68999862670898</v>
       </c>
       <c r="G835" t="n">
-        <v>1416.963012695312</v>
+        <v>1416.963134765625</v>
       </c>
       <c r="H835" t="n">
         <v>276.1499938964844</v>
@@ -25998,7 +25998,7 @@
         <v>15.3100004196167</v>
       </c>
       <c r="E837" t="n">
-        <v>280.654052734375</v>
+        <v>280.6540832519531</v>
       </c>
       <c r="F837" t="n">
         <v>48.81999969482422</v>
@@ -26030,7 +26030,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="E838" t="n">
-        <v>280.654052734375</v>
+        <v>280.6540832519531</v>
       </c>
       <c r="F838" t="n">
         <v>50.0099983215332</v>
@@ -26094,13 +26094,13 @@
         <v>15.52000045776367</v>
       </c>
       <c r="E840" t="n">
-        <v>289.2206420898438</v>
+        <v>289.2206115722656</v>
       </c>
       <c r="F840" t="n">
         <v>52.68999862670898</v>
       </c>
       <c r="G840" t="n">
-        <v>1400.802856445312</v>
+        <v>1400.802734375</v>
       </c>
       <c r="H840" t="n">
         <v>308.2999877929688</v>
@@ -26228,7 +26228,7 @@
         <v>55.09000015258789</v>
       </c>
       <c r="G844" t="n">
-        <v>1393.466064453125</v>
+        <v>1393.466186523438</v>
       </c>
       <c r="H844" t="n">
         <v>342.0499877929688</v>
@@ -26254,13 +26254,13 @@
         <v>15.72999954223633</v>
       </c>
       <c r="E845" t="n">
-        <v>289.2206420898438</v>
+        <v>289.2206115722656</v>
       </c>
       <c r="F845" t="n">
         <v>55.31999969482422</v>
       </c>
       <c r="G845" t="n">
-        <v>1411.311889648438</v>
+        <v>1411.31201171875</v>
       </c>
       <c r="H845" t="n">
         <v>380.6000061035156</v>
@@ -26286,7 +26286,7 @@
         <v>15.75</v>
       </c>
       <c r="E846" t="n">
-        <v>290.3661499023438</v>
+        <v>290.3661193847656</v>
       </c>
       <c r="F846" t="n">
         <v>54.68999862670898</v>
@@ -26324,7 +26324,7 @@
         <v>54.13999938964844</v>
       </c>
       <c r="G847" t="n">
-        <v>1431.140625</v>
+        <v>1431.140747070312</v>
       </c>
       <c r="H847" t="n">
         <v>371.7999877929688</v>
@@ -26350,7 +26350,7 @@
         <v>15.80000019073486</v>
       </c>
       <c r="E848" t="n">
-        <v>303.0665283203125</v>
+        <v>303.0665588378906</v>
       </c>
       <c r="F848" t="n">
         <v>54.47999954223633</v>
@@ -26382,7 +26382,7 @@
         <v>15.98999977111816</v>
       </c>
       <c r="E849" t="n">
-        <v>301.6221618652344</v>
+        <v>301.6221923828125</v>
       </c>
       <c r="F849" t="n">
         <v>57.08000183105469</v>
@@ -26452,7 +26452,7 @@
         <v>55.16999816894531</v>
       </c>
       <c r="G851" t="n">
-        <v>1429.256958007812</v>
+        <v>1429.257080078125</v>
       </c>
       <c r="H851" t="n">
         <v>395.4500122070312</v>
@@ -26516,7 +26516,7 @@
         <v>54.61999893188477</v>
       </c>
       <c r="G853" t="n">
-        <v>1425.489501953125</v>
+        <v>1425.489624023438</v>
       </c>
       <c r="H853" t="n">
         <v>380.8999938964844</v>
@@ -26542,13 +26542,13 @@
         <v>15.03999996185303</v>
       </c>
       <c r="E854" t="n">
-        <v>288.6727600097656</v>
+        <v>288.6727294921875</v>
       </c>
       <c r="F854" t="n">
         <v>53.13999938964844</v>
       </c>
       <c r="G854" t="n">
-        <v>1418.945922851562</v>
+        <v>1418.946044921875</v>
       </c>
       <c r="H854" t="n">
         <v>368.1000061035156</v>
@@ -26574,7 +26574,7 @@
         <v>14.89000034332275</v>
       </c>
       <c r="E855" t="n">
-        <v>287.0291748046875</v>
+        <v>287.0291442871094</v>
       </c>
       <c r="F855" t="n">
         <v>52.86999893188477</v>
@@ -26612,7 +26612,7 @@
         <v>52.4900016784668</v>
       </c>
       <c r="G856" t="n">
-        <v>1421.028076171875</v>
+        <v>1421.028198242188</v>
       </c>
       <c r="H856" t="n">
         <v>382.7999877929688</v>
@@ -26702,13 +26702,13 @@
         <v>15.15999984741211</v>
       </c>
       <c r="E859" t="n">
-        <v>299.6299743652344</v>
+        <v>299.6299438476562</v>
       </c>
       <c r="F859" t="n">
         <v>53.65999984741211</v>
       </c>
       <c r="G859" t="n">
-        <v>1438.378173828125</v>
+        <v>1438.378295898438</v>
       </c>
       <c r="H859" t="n">
         <v>385.3999938964844</v>
@@ -26734,7 +26734,7 @@
         <v>16.04999923706055</v>
       </c>
       <c r="E860" t="n">
-        <v>302.1202392578125</v>
+        <v>302.1202087402344</v>
       </c>
       <c r="F860" t="n">
         <v>61.81999969482422</v>
@@ -26772,7 +26772,7 @@
         <v>59.54000091552734</v>
       </c>
       <c r="G861" t="n">
-        <v>1482.497192382812</v>
+        <v>1482.497314453125</v>
       </c>
       <c r="H861" t="n">
         <v>417.3999938964844</v>
@@ -26804,7 +26804,7 @@
         <v>58.88000106811523</v>
       </c>
       <c r="G862" t="n">
-        <v>1502.425048828125</v>
+        <v>1502.425170898438</v>
       </c>
       <c r="H862" t="n">
         <v>413.0499877929688</v>
@@ -26894,13 +26894,13 @@
         <v>15.85999965667725</v>
       </c>
       <c r="E865" t="n">
-        <v>325.4292297363281</v>
+        <v>325.4292602539062</v>
       </c>
       <c r="F865" t="n">
         <v>57.02000045776367</v>
       </c>
       <c r="G865" t="n">
-        <v>1505.796142578125</v>
+        <v>1505.796020507812</v>
       </c>
       <c r="H865" t="n">
         <v>396.75</v>
@@ -26926,13 +26926,13 @@
         <v>15.96000003814697</v>
       </c>
       <c r="E866" t="n">
-        <v>323.7856140136719</v>
+        <v>323.78564453125</v>
       </c>
       <c r="F866" t="n">
         <v>58.11000061035156</v>
       </c>
       <c r="G866" t="n">
-        <v>1504.804565429688</v>
+        <v>1504.8046875</v>
       </c>
       <c r="H866" t="n">
         <v>376.9500122070312</v>
@@ -26958,7 +26958,7 @@
         <v>15.98999977111816</v>
       </c>
       <c r="E867" t="n">
-        <v>323.6860656738281</v>
+        <v>323.68603515625</v>
       </c>
       <c r="F867" t="n">
         <v>56.41999816894531</v>
@@ -27028,7 +27028,7 @@
         <v>55.86000061035156</v>
       </c>
       <c r="G869" t="n">
-        <v>1524.43505859375</v>
+        <v>1524.434936523438</v>
       </c>
       <c r="H869" t="n">
         <v>373.4500122070312</v>
@@ -27086,13 +27086,13 @@
         <v>15.57999992370605</v>
       </c>
       <c r="E871" t="n">
-        <v>330.3599853515625</v>
+        <v>330.3599548339844</v>
       </c>
       <c r="F871" t="n">
         <v>55.68000030517578</v>
       </c>
       <c r="G871" t="n">
-        <v>1504.209716796875</v>
+        <v>1504.209594726562</v>
       </c>
       <c r="H871" t="n">
         <v>372.1499938964844</v>
@@ -27118,7 +27118,7 @@
         <v>15.35999965667725</v>
       </c>
       <c r="E872" t="n">
-        <v>324.53271484375</v>
+        <v>324.5326843261719</v>
       </c>
       <c r="F872" t="n">
         <v>54.81000137329102</v>
@@ -27252,7 +27252,7 @@
         <v>60.77999877929688</v>
       </c>
       <c r="G876" t="n">
-        <v>1463.759033203125</v>
+        <v>1463.759155273438</v>
       </c>
       <c r="H876" t="n">
         <v>396.3500061035156</v>
@@ -27284,7 +27284,7 @@
         <v>61.22999954223633</v>
       </c>
       <c r="G877" t="n">
-        <v>1463.362426757812</v>
+        <v>1463.362548828125</v>
       </c>
       <c r="H877" t="n">
         <v>390.2999877929688</v>
@@ -27310,7 +27310,7 @@
         <v>15.86999988555908</v>
       </c>
       <c r="E878" t="n">
-        <v>316.0159606933594</v>
+        <v>316.0159912109375</v>
       </c>
       <c r="F878" t="n">
         <v>59.61000061035156</v>
@@ -27380,7 +27380,7 @@
         <v>60.09999847412109</v>
       </c>
       <c r="G880" t="n">
-        <v>1412.402465820312</v>
+        <v>1412.402587890625</v>
       </c>
       <c r="H880" t="n">
         <v>378.75</v>
@@ -27412,7 +27412,7 @@
         <v>59.95000076293945</v>
       </c>
       <c r="G881" t="n">
-        <v>1390.888305664062</v>
+        <v>1390.888427734375</v>
       </c>
       <c r="H881" t="n">
         <v>359.8500061035156</v>
@@ -27470,13 +27470,13 @@
         <v>14.85999965667725</v>
       </c>
       <c r="E883" t="n">
-        <v>306.1544799804688</v>
+        <v>306.1545104980469</v>
       </c>
       <c r="F883" t="n">
         <v>56.25</v>
       </c>
       <c r="G883" t="n">
-        <v>1375.719360351562</v>
+        <v>1375.71923828125</v>
       </c>
       <c r="H883" t="n">
         <v>326.3999938964844</v>
@@ -27508,7 +27508,7 @@
         <v>56.45999908447266</v>
       </c>
       <c r="G884" t="n">
-        <v>1404.966796875</v>
+        <v>1404.966674804688</v>
       </c>
       <c r="H884" t="n">
         <v>340.25</v>
@@ -27540,7 +27540,7 @@
         <v>56.16999816894531</v>
       </c>
       <c r="G885" t="n">
-        <v>1398.026733398438</v>
+        <v>1398.026611328125</v>
       </c>
       <c r="H885" t="n">
         <v>327.4500122070312</v>
@@ -27598,7 +27598,7 @@
         <v>15.10000038146973</v>
       </c>
       <c r="E887" t="n">
-        <v>328.2183227539062</v>
+        <v>328.2183532714844</v>
       </c>
       <c r="F887" t="n">
         <v>57.47000122070312</v>
@@ -27700,7 +27700,7 @@
         <v>57.2400016784668</v>
       </c>
       <c r="G890" t="n">
-        <v>1380.874877929688</v>
+        <v>1380.874755859375</v>
       </c>
       <c r="H890" t="n">
         <v>295.0499877929688</v>
@@ -27726,13 +27726,13 @@
         <v>14.31999969482422</v>
       </c>
       <c r="E891" t="n">
-        <v>324.2339172363281</v>
+        <v>324.23388671875</v>
       </c>
       <c r="F891" t="n">
         <v>56.29000091552734</v>
       </c>
       <c r="G891" t="n">
-        <v>1377.50390625</v>
+        <v>1377.504028320312</v>
       </c>
       <c r="H891" t="n">
         <v>281.2999877929688</v>
@@ -37136,7 +37136,7 @@
         <v>3.846153846153855</v>
       </c>
       <c r="E19" t="n">
-        <v>14.46530988416585</v>
+        <v>14.46530217715354</v>
       </c>
       <c r="F19" t="n">
         <v>0.2994726297447459</v>
@@ -37168,7 +37168,7 @@
         <v>-1.664147220764423</v>
       </c>
       <c r="E20" t="n">
-        <v>9.585268389905522</v>
+        <v>9.585283854023508</v>
       </c>
       <c r="F20" t="n">
         <v>5.058083659302848</v>
@@ -37200,7 +37200,7 @@
         <v>-12.04257816433491</v>
       </c>
       <c r="E21" t="n">
-        <v>-14.08648260149032</v>
+        <v>-14.08648894056502</v>
       </c>
       <c r="F21" t="n">
         <v>-21.56416200558649</v>
@@ -37264,7 +37264,7 @@
         <v>-8.96991367371337</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.029997792400145</v>
+        <v>-9.02998930442963</v>
       </c>
       <c r="F23" t="n">
         <v>-9.284627137033763</v>
@@ -37296,7 +37296,7 @@
         <v>-10.92782976067592</v>
       </c>
       <c r="E24" t="n">
-        <v>1.877140080946416</v>
+        <v>1.877130575284558</v>
       </c>
       <c r="F24" t="n">
         <v>-8.750005850085408</v>
@@ -37360,7 +37360,7 @@
         <v>-2.652777627189706</v>
       </c>
       <c r="E26" t="n">
-        <v>8.983528534268292</v>
+        <v>8.983518155342285</v>
       </c>
       <c r="F26" t="n">
         <v>-13.86086794220902</v>
@@ -37392,13 +37392,13 @@
         <v>-12.37027614512571</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.070018161948173</v>
+        <v>-2.070008835693593</v>
       </c>
       <c r="F27" t="n">
         <v>-3.095716273530114</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6193430171434144</v>
+        <v>0.6193347598382193</v>
       </c>
       <c r="H27" t="n">
         <v>0.9847026900382971</v>
@@ -37430,7 +37430,7 @@
         <v>23.30486903670943</v>
       </c>
       <c r="G28" t="n">
-        <v>-3.831297640943399</v>
+        <v>-3.831289748878441</v>
       </c>
       <c r="H28" t="n">
         <v>3.621270323810255</v>
@@ -37462,7 +37462,7 @@
         <v>-0.3254094258637208</v>
       </c>
       <c r="G29" t="n">
-        <v>9.437925303146976</v>
+        <v>9.437915851090327</v>
       </c>
       <c r="H29" t="n">
         <v>20.18634526010754</v>
@@ -37494,7 +37494,7 @@
         <v>-10.12373435941966</v>
       </c>
       <c r="G30" t="n">
-        <v>-2.4948827172523</v>
+        <v>-2.494882507147478</v>
       </c>
       <c r="H30" t="n">
         <v>-6.49240482812462</v>
@@ -37526,7 +37526,7 @@
         <v>3.132256001421796</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.268640695312884</v>
+        <v>-1.26862417160658</v>
       </c>
       <c r="H31" t="n">
         <v>-34.34213475489638</v>
@@ -37558,7 +37558,7 @@
         <v>-19.4392551885587</v>
       </c>
       <c r="G32" t="n">
-        <v>1.714810252326515</v>
+        <v>1.714793192957242</v>
       </c>
       <c r="H32" t="n">
         <v>22.65731991554547</v>
@@ -37590,7 +37590,7 @@
         <v>-8.54700854700855</v>
       </c>
       <c r="G33" t="n">
-        <v>2.395516458058666</v>
+        <v>2.395533985038512</v>
       </c>
       <c r="H33" t="n">
         <v>-4.392992435061648</v>
@@ -37616,13 +37616,13 @@
         <v>12.97169764638586</v>
       </c>
       <c r="E34" t="n">
-        <v>6.56794299184198</v>
+        <v>6.567935984125439</v>
       </c>
       <c r="F34" t="n">
         <v>33.94390617495342</v>
       </c>
       <c r="G34" t="n">
-        <v>10.3793202560976</v>
+        <v>10.37930014680082</v>
       </c>
       <c r="H34" t="n">
         <v>10.12869384694794</v>
@@ -37648,13 +37648,13 @@
         <v>5.735668676501682</v>
       </c>
       <c r="E35" t="n">
-        <v>1.547509662461577</v>
+        <v>1.547516340043864</v>
       </c>
       <c r="F35" t="n">
         <v>0.9243158800178009</v>
       </c>
       <c r="G35" t="n">
-        <v>8.72783114447817</v>
+        <v>8.727841537326796</v>
       </c>
       <c r="H35" t="n">
         <v>10.5665365226655</v>
@@ -37744,13 +37744,13 @@
         <v>21.21212121212121</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9850075430692273</v>
+        <v>-0.9850140387806072</v>
       </c>
       <c r="F38" t="n">
         <v>-6.583760205501399</v>
       </c>
       <c r="G38" t="n">
-        <v>-2.57582022494055</v>
+        <v>-2.575810224095743</v>
       </c>
       <c r="H38" t="n">
         <v>-7.202140266796353</v>
@@ -37779,7 +37779,7 @@
         <v>17.33905317445681</v>
       </c>
       <c r="G39" t="n">
-        <v>-5.246536520989409</v>
+        <v>-5.246537031303699</v>
       </c>
       <c r="H39" t="n">
         <v>-1.111996841749918</v>
@@ -37808,7 +37808,7 @@
         <v>-7.245221803084723</v>
       </c>
       <c r="G40" t="n">
-        <v>8.299924766203226</v>
+        <v>8.299902823900585</v>
       </c>
       <c r="H40" t="n">
         <v>36.60036607849231</v>
@@ -37837,7 +37837,7 @@
         <v>2.446982085920046</v>
       </c>
       <c r="G41" t="n">
-        <v>3.253172892082179</v>
+        <v>3.253172538244864</v>
       </c>
       <c r="H41" t="n">
         <v>2.635488591081314</v>
@@ -37866,7 +37866,7 @@
         <v>5.598621951273208</v>
       </c>
       <c r="G42" t="n">
-        <v>2.040889260620204</v>
+        <v>2.040900359286013</v>
       </c>
       <c r="H42" t="n">
         <v>-14.50333586855534</v>
@@ -38069,7 +38069,7 @@
         <v>-0.696589719615015</v>
       </c>
       <c r="G49" t="n">
-        <v>7.227408100364263</v>
+        <v>7.227420215142799</v>
       </c>
       <c r="H49" t="n">
         <v>3.474762330681291</v>
@@ -38098,7 +38098,7 @@
         <v>-8.498583753085121</v>
       </c>
       <c r="G50" t="n">
-        <v>-9.863701201961927</v>
+        <v>-9.863720565037227</v>
       </c>
       <c r="H50" t="n">
         <v>-15.6172858344184</v>
@@ -38127,13 +38127,13 @@
         <v>8.782737772308536</v>
       </c>
       <c r="G51" t="n">
-        <v>5.463609979870743</v>
+        <v>5.463643374052984</v>
       </c>
       <c r="H51" t="n">
         <v>38.34329813061588</v>
       </c>
       <c r="I51" t="n">
-        <v>4.312858971254707</v>
+        <v>4.312852371434839</v>
       </c>
       <c r="J51" t="n">
         <v>35.48386898298783</v>
@@ -38156,13 +38156,13 @@
         <v>-5.942026774088538</v>
       </c>
       <c r="G52" t="n">
-        <v>-3.320938877438184</v>
+        <v>-3.320959644468446</v>
       </c>
       <c r="H52" t="n">
         <v>29.24944861623748</v>
       </c>
       <c r="I52" t="n">
-        <v>3.064802510321041</v>
+        <v>3.064815751886085</v>
       </c>
       <c r="J52" t="n">
         <v>7.826083639393677</v>
@@ -38191,7 +38191,7 @@
         <v>-16.0722547147822</v>
       </c>
       <c r="I53" t="n">
-        <v>2.955478565724423</v>
+        <v>2.955485676141079</v>
       </c>
       <c r="J53" t="n">
         <v>-8.730161493387333</v>
@@ -38220,7 +38220,7 @@
         <v>-12.62647164563844</v>
       </c>
       <c r="I54" t="n">
-        <v>-16.35936109340738</v>
+        <v>-16.35937232396798</v>
       </c>
       <c r="J54" t="n">
         <v>-11.57894469144052</v>
@@ -38249,7 +38249,7 @@
         <v>10.01780916676824</v>
       </c>
       <c r="I55" t="n">
-        <v>42.15597528376036</v>
+        <v>42.15598663130014</v>
       </c>
       <c r="J55" t="n">
         <v>5.555555555555558</v>
@@ -38272,13 +38272,13 @@
         <v>10.65627667685571</v>
       </c>
       <c r="G56" t="n">
-        <v>11.66323439425943</v>
+        <v>11.66324714899951</v>
       </c>
       <c r="H56" t="n">
         <v>7.361381156751889</v>
       </c>
       <c r="I56" t="n">
-        <v>11.44044716830326</v>
+        <v>11.44042835922838</v>
       </c>
       <c r="J56" t="n">
         <v>3.4482743501002</v>
@@ -38301,13 +38301,13 @@
         <v>-6.15854030702172</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.133425906142194</v>
+        <v>-1.133426034140439</v>
       </c>
       <c r="H57" t="n">
         <v>3.513107684464867</v>
       </c>
       <c r="I57" t="n">
-        <v>-20.63636456057385</v>
+        <v>-20.63635750063468</v>
       </c>
       <c r="J57" t="n">
         <v>-11.82432417193846</v>
@@ -38570,7 +38570,7 @@
         <v>22.99999823937049</v>
       </c>
       <c r="E7" t="n">
-        <v>43.62007306981142</v>
+        <v>43.62006339979285</v>
       </c>
       <c r="F7" t="n">
         <v>35.63695294881548</v>
@@ -38602,7 +38602,7 @@
         <v>-17.35536949575909</v>
       </c>
       <c r="E8" t="n">
-        <v>-23.83328563970489</v>
+        <v>-23.83328051135775</v>
       </c>
       <c r="F8" t="n">
         <v>-39.30368863961553</v>
@@ -38704,7 +38704,7 @@
         <v>-7.610206253873331</v>
       </c>
       <c r="G11" t="n">
-        <v>5.353841666523929</v>
+        <v>5.353850426268458</v>
       </c>
       <c r="H11" t="n">
         <v>-26.21148416003172</v>
@@ -38730,13 +38730,13 @@
         <v>-7.547171339100844</v>
       </c>
       <c r="E12" t="n">
-        <v>51.8566402671572</v>
+        <v>51.85663028133727</v>
       </c>
       <c r="F12" t="n">
         <v>-1.316544414387844</v>
       </c>
       <c r="G12" t="n">
-        <v>14.96161317663234</v>
+        <v>14.96159262933299</v>
       </c>
       <c r="H12" t="n">
         <v>29.14681042220371</v>
@@ -38762,13 +38762,13 @@
         <v>6.000003814697275</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7569145032003677</v>
+        <v>0.7569211287945299</v>
       </c>
       <c r="F13" t="n">
         <v>36.80501262584171</v>
       </c>
       <c r="G13" t="n">
-        <v>10.23239665903461</v>
+        <v>10.23240719569851</v>
       </c>
       <c r="H13" t="n">
         <v>21.06174227192534</v>
@@ -38797,7 +38797,7 @@
         <v>1.671973327733589</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.02532372548660344</v>
+        <v>-0.02533425681351398</v>
       </c>
       <c r="H14" t="n">
         <v>25.35262426890257</v>
@@ -38826,7 +38826,7 @@
         <v>15.76036725725447</v>
       </c>
       <c r="G15" t="n">
-        <v>9.403473939461261</v>
+        <v>9.403485464018434</v>
       </c>
       <c r="H15" t="n">
         <v>-4.159445407279028</v>
@@ -38884,7 +38884,7 @@
         <v>2.321981478994783</v>
       </c>
       <c r="G17" t="n">
-        <v>7.126458598841245</v>
+        <v>7.126470702214305</v>
       </c>
       <c r="H17" t="n">
         <v>0.7315289117223678</v>
@@ -38913,13 +38913,13 @@
         <v>-6.376813805621606</v>
       </c>
       <c r="G18" t="n">
-        <v>-8.09592291278366</v>
+        <v>-8.095933296298796</v>
       </c>
       <c r="H18" t="n">
         <v>50.88300138028043</v>
       </c>
       <c r="I18" t="n">
-        <v>13.2924593012159</v>
+        <v>13.29246668885498</v>
       </c>
       <c r="J18" t="n">
         <v>42.60869233504585</v>
@@ -38948,7 +38948,7 @@
         <v>-19.32324486904549</v>
       </c>
       <c r="I19" t="n">
-        <v>22.41423489112568</v>
+        <v>22.41423668033238</v>
       </c>
       <c r="J19" t="n">
         <v>-14.81481481481481</v>
@@ -39051,13 +39051,13 @@
         <v>24.71641426655784</v>
       </c>
       <c r="E2" t="n">
-        <v>38.56970207824606</v>
+        <v>38.56971060642054</v>
       </c>
       <c r="F2" t="n">
         <v>48.02197768635678</v>
       </c>
       <c r="G2" t="n">
-        <v>20.74573916003721</v>
+        <v>20.74572935508516</v>
       </c>
       <c r="H2" t="n">
         <v>26.11641041112731</v>
@@ -39083,7 +39083,7 @@
         <v>21.52941086713005</v>
       </c>
       <c r="E3" t="n">
-        <v>48.10741480535528</v>
+        <v>48.10742776232155</v>
       </c>
       <c r="F3" t="n">
         <v>37.25662738916504</v>
@@ -39115,13 +39115,13 @@
         <v>21.30177788597374</v>
       </c>
       <c r="E4" t="n">
-        <v>54.55153813119511</v>
+        <v>54.55154123022257</v>
       </c>
       <c r="F4" t="n">
         <v>35.23950508448274</v>
       </c>
       <c r="G4" t="n">
-        <v>20.50514742013778</v>
+        <v>20.50513561497333</v>
       </c>
       <c r="H4" t="n">
         <v>18.55826056452661</v>
@@ -39147,13 +39147,13 @@
         <v>25.38921902642992</v>
       </c>
       <c r="E5" t="n">
-        <v>61.79434466708855</v>
+        <v>61.79433305581566</v>
       </c>
       <c r="F5" t="n">
         <v>37.43092805121666</v>
       </c>
       <c r="G5" t="n">
-        <v>20.81958647428637</v>
+        <v>20.81959851262889</v>
       </c>
       <c r="H5" t="n">
         <v>18.42639458918014</v>
@@ -39179,13 +39179,13 @@
         <v>23.483483105072</v>
       </c>
       <c r="E6" t="n">
-        <v>57.03962773712359</v>
+        <v>57.03963895200328</v>
       </c>
       <c r="F6" t="n">
         <v>32.87407769097221</v>
       </c>
       <c r="G6" t="n">
-        <v>19.09140759479682</v>
+        <v>19.09141951598872</v>
       </c>
       <c r="H6" t="n">
         <v>20.42312944893776</v>
@@ -39217,7 +39217,7 @@
         <v>30.13837487565421</v>
       </c>
       <c r="G7" t="n">
-        <v>20.09523646786675</v>
+        <v>20.09521421428811</v>
       </c>
       <c r="H7" t="n">
         <v>19.02754764747889</v>
@@ -39243,13 +39243,13 @@
         <v>28.34835632939052</v>
       </c>
       <c r="E8" t="n">
-        <v>59.59137463922708</v>
+        <v>59.59136353965761</v>
       </c>
       <c r="F8" t="n">
         <v>30.24495302920487</v>
       </c>
       <c r="G8" t="n">
-        <v>21.17961628996452</v>
+        <v>21.1796060813265</v>
       </c>
       <c r="H8" t="n">
         <v>17.59891665078761</v>
@@ -39281,7 +39281,7 @@
         <v>28.71272416548296</v>
       </c>
       <c r="G9" t="n">
-        <v>20.46287480132978</v>
+        <v>20.46287689229769</v>
       </c>
       <c r="H9" t="n">
         <v>12.19356144837187</v>
@@ -39307,13 +39307,13 @@
         <v>27.15151237718987</v>
       </c>
       <c r="E10" t="n">
-        <v>49.80728369996403</v>
+        <v>49.80727387211014</v>
       </c>
       <c r="F10" t="n">
         <v>30.0219527879438</v>
       </c>
       <c r="G10" t="n">
-        <v>23.37534835154322</v>
+        <v>23.37536101634281</v>
       </c>
       <c r="H10" t="n">
         <v>14.29718712087935</v>
@@ -39345,7 +39345,7 @@
         <v>28.25741212487847</v>
       </c>
       <c r="G11" t="n">
-        <v>22.48964894222016</v>
+        <v>22.48963639778619</v>
       </c>
       <c r="H11" t="n">
         <v>13.73462507545713</v>
@@ -39371,13 +39371,13 @@
         <v>17.83197220667512</v>
       </c>
       <c r="E12" t="n">
-        <v>37.62083806523711</v>
+        <v>37.62082597735093</v>
       </c>
       <c r="F12" t="n">
         <v>29.44169870113738</v>
       </c>
       <c r="G12" t="n">
-        <v>22.48258353089252</v>
+        <v>22.48257328138885</v>
       </c>
       <c r="H12" t="n">
         <v>12.00104193248259</v>
@@ -39441,7 +39441,7 @@
         <v>25.29452475957892</v>
       </c>
       <c r="G14" t="n">
-        <v>20.92203812635944</v>
+        <v>20.92206060195419</v>
       </c>
       <c r="H14" t="n">
         <v>48.492657589076</v>
@@ -39467,13 +39467,13 @@
         <v>10.24259624810628</v>
       </c>
       <c r="E15" t="n">
-        <v>37.66877358173188</v>
+        <v>37.66878574882724</v>
       </c>
       <c r="F15" t="n">
         <v>18.36042100886153</v>
       </c>
       <c r="G15" t="n">
-        <v>21.27164341356986</v>
+        <v>21.27163109269175</v>
       </c>
       <c r="H15" t="n">
         <v>50.10011067847504</v>
@@ -39531,13 +39531,13 @@
         <v>11.39784348605077</v>
       </c>
       <c r="E17" t="n">
-        <v>41.61502010126967</v>
+        <v>41.61504102066482</v>
       </c>
       <c r="F17" t="n">
         <v>17.49119689344376</v>
       </c>
       <c r="G17" t="n">
-        <v>21.10591855208681</v>
+        <v>21.10590645985941</v>
       </c>
       <c r="H17" t="n">
         <v>80.21875186197276</v>
@@ -39595,7 +39595,7 @@
         <v>18.21325520423087</v>
       </c>
       <c r="E19" t="n">
-        <v>46.87759936456168</v>
+        <v>46.8775899976761</v>
       </c>
       <c r="F19" t="n">
         <v>18.99342970595615</v>
@@ -39633,7 +39633,7 @@
         <v>19.92705386519244</v>
       </c>
       <c r="G20" t="n">
-        <v>22.53161956213026</v>
+        <v>22.53160722132512</v>
       </c>
       <c r="H20" t="n">
         <v>87.55847280153539</v>
@@ -39665,7 +39665,7 @@
         <v>23.86999327483017</v>
       </c>
       <c r="G21" t="n">
-        <v>24.60930726084567</v>
+        <v>24.60929473401883</v>
       </c>
       <c r="H21" t="n">
         <v>75.75510868409864</v>
@@ -39697,7 +39697,7 @@
         <v>23.91534290235078</v>
       </c>
       <c r="G22" t="n">
-        <v>21.61844907698027</v>
+        <v>21.61846141052666</v>
       </c>
       <c r="H22" t="n">
         <v>88.99634149417557</v>
@@ -39755,7 +39755,7 @@
         <v>1.75879592049748</v>
       </c>
       <c r="E24" t="n">
-        <v>51.81200920138686</v>
+        <v>51.81199574355784</v>
       </c>
       <c r="F24" t="n">
         <v>19.30215336975127</v>
@@ -39787,7 +39787,7 @@
         <v>4.647526447655226</v>
       </c>
       <c r="E25" t="n">
-        <v>48.72694435241242</v>
+        <v>48.72695435353167</v>
       </c>
       <c r="F25" t="n">
         <v>15.13592205797443</v>
@@ -39825,7 +39825,7 @@
         <v>12.20622202314199</v>
       </c>
       <c r="G26" t="n">
-        <v>17.53099974610059</v>
+        <v>17.53102271117308</v>
       </c>
       <c r="H26" t="n">
         <v>66.09046092268591</v>
@@ -39851,13 +39851,13 @@
         <v>-2.630266944568471</v>
       </c>
       <c r="E27" t="n">
-        <v>50.0000166214994</v>
+        <v>50.00000332429988</v>
       </c>
       <c r="F27" t="n">
         <v>17.44186046511629</v>
       </c>
       <c r="G27" t="n">
-        <v>19.70906335411693</v>
+        <v>19.7090865288315</v>
       </c>
       <c r="H27" t="n">
         <v>75.14619883040936</v>
@@ -39883,7 +39883,7 @@
         <v>0.101012416840085</v>
       </c>
       <c r="E28" t="n">
-        <v>50.86870028982617</v>
+        <v>50.86871045504766</v>
       </c>
       <c r="F28" t="n">
         <v>21.00077612236952</v>
@@ -39947,7 +39947,7 @@
         <v>0.450000762939462</v>
       </c>
       <c r="E30" t="n">
-        <v>47.7076172998504</v>
+        <v>47.70760404866208</v>
       </c>
       <c r="F30" t="n">
         <v>27.42365317882882</v>
@@ -39979,7 +39979,7 @@
         <v>0.1449216337739756</v>
       </c>
       <c r="E31" t="n">
-        <v>46.95333165365223</v>
+        <v>46.95331841391677</v>
       </c>
       <c r="F31" t="n">
         <v>15.39021874936699</v>
@@ -40011,13 +40011,13 @@
         <v>-1.052628312774884</v>
       </c>
       <c r="E32" t="n">
-        <v>49.89985267357972</v>
+        <v>49.89984245224899</v>
       </c>
       <c r="F32" t="n">
         <v>27.97941577115182</v>
       </c>
       <c r="G32" t="n">
-        <v>16.55136612272741</v>
+        <v>16.55135367838822</v>
       </c>
       <c r="H32" t="n">
         <v>68.60328526038532</v>
@@ -40043,13 +40043,13 @@
         <v>-2.660330100898289</v>
       </c>
       <c r="E33" t="n">
-        <v>48.02573758579716</v>
+        <v>48.02573405358237</v>
       </c>
       <c r="F33" t="n">
         <v>17.99588316396285</v>
       </c>
       <c r="G33" t="n">
-        <v>17.4254069034677</v>
+        <v>17.42539622610888</v>
       </c>
       <c r="H33" t="n">
         <v>69.25088116850071</v>
@@ -40113,7 +40113,7 @@
         <v>15.1233316680212</v>
       </c>
       <c r="G35" t="n">
-        <v>18.69147896411565</v>
+        <v>18.69146620359978</v>
       </c>
       <c r="H35" t="n">
         <v>64.23357664233578</v>
@@ -40139,13 +40139,13 @@
         <v>-0.4102560190054061</v>
       </c>
       <c r="E36" t="n">
-        <v>48.62594908343376</v>
+        <v>48.62593874181287</v>
       </c>
       <c r="F36" t="n">
         <v>11.65387061590668</v>
       </c>
       <c r="G36" t="n">
-        <v>19.03024894081289</v>
+        <v>19.03023823708794</v>
       </c>
       <c r="H36" t="n">
         <v>56.8334812026194</v>
@@ -40171,13 +40171,13 @@
         <v>-5.088162264342754</v>
       </c>
       <c r="E37" t="n">
-        <v>39.51575431044456</v>
+        <v>39.51576792072717</v>
       </c>
       <c r="F37" t="n">
         <v>5.373968208882274</v>
       </c>
       <c r="G37" t="n">
-        <v>14.95782473939171</v>
+        <v>14.95783527583134</v>
       </c>
       <c r="H37" t="n">
         <v>49.29618947317174</v>
@@ -40203,13 +40203,13 @@
         <v>-9.425834207230599</v>
       </c>
       <c r="E38" t="n">
-        <v>39.77348672798779</v>
+        <v>39.77350033524889</v>
       </c>
       <c r="F38" t="n">
         <v>-1.762887330280316</v>
       </c>
       <c r="G38" t="n">
-        <v>14.33284215758213</v>
+        <v>14.3328646988224</v>
       </c>
       <c r="H38" t="n">
         <v>57.80926505349091</v>
@@ -40235,7 +40235,7 @@
         <v>-7.586202295846512</v>
       </c>
       <c r="E39" t="n">
-        <v>40.77041965314101</v>
+        <v>40.77042925623107</v>
       </c>
       <c r="F39" t="n">
         <v>-0.3809562562003932</v>
@@ -40331,13 +40331,13 @@
         <v>-4.7715761302202</v>
       </c>
       <c r="E42" t="n">
-        <v>51.01852289181952</v>
+        <v>51.01853360181148</v>
       </c>
       <c r="F42" t="n">
         <v>0.8595328089425314</v>
       </c>
       <c r="G42" t="n">
-        <v>15.70979617739452</v>
+        <v>15.70980847951631</v>
       </c>
       <c r="H42" t="n">
         <v>61.70213418337656</v>
@@ -40363,7 +40363,7 @@
         <v>-3.115572581757442</v>
       </c>
       <c r="E43" t="n">
-        <v>49.36975473509047</v>
+        <v>49.36975835587943</v>
       </c>
       <c r="F43" t="n">
         <v>4.18754296740822</v>
@@ -40395,13 +40395,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>50.46685642285065</v>
+        <v>50.46684566231154</v>
       </c>
       <c r="F44" t="n">
         <v>12.49999751647324</v>
       </c>
       <c r="G44" t="n">
-        <v>16.26905554318454</v>
+        <v>16.26906803864587</v>
       </c>
       <c r="H44" t="n">
         <v>57.01092056153711</v>
@@ -40433,7 +40433,7 @@
         <v>23.09999738420758</v>
       </c>
       <c r="G45" t="n">
-        <v>18.6986038377839</v>
+        <v>18.69861679670135</v>
       </c>
       <c r="H45" t="n">
         <v>71.45801931839102</v>
@@ -40465,7 +40465,7 @@
         <v>23.51312717433578</v>
       </c>
       <c r="G46" t="n">
-        <v>15.73058716649658</v>
+        <v>15.7305998307574</v>
       </c>
       <c r="H46" t="n">
         <v>82.7479978598209</v>
@@ -40497,7 +40497,7 @@
         <v>22.59531429862704</v>
       </c>
       <c r="G47" t="n">
-        <v>17.64925742497345</v>
+        <v>17.64924436890285</v>
       </c>
       <c r="H47" t="n">
         <v>85.00471194850942</v>
@@ -40523,13 +40523,13 @@
         <v>6.467394340917232</v>
       </c>
       <c r="E48" t="n">
-        <v>46.27635349583639</v>
+        <v>46.2763635483981</v>
       </c>
       <c r="F48" t="n">
         <v>25.26545854048294</v>
       </c>
       <c r="G48" t="n">
-        <v>17.38442805403455</v>
+        <v>17.38441714906611</v>
       </c>
       <c r="H48" t="n">
         <v>86.16140643431169</v>
@@ -40555,13 +40555,13 @@
         <v>8.154267621721157</v>
       </c>
       <c r="E49" t="n">
-        <v>46.82648416678226</v>
+        <v>46.82647017740005</v>
       </c>
       <c r="F49" t="n">
         <v>21.11271857609913</v>
       </c>
       <c r="G49" t="n">
-        <v>13.30433706701131</v>
+        <v>13.30432638226435</v>
       </c>
       <c r="H49" t="n">
         <v>71.57738095238095</v>
@@ -40593,7 +40593,7 @@
         <v>20.76246964183235</v>
       </c>
       <c r="G50" t="n">
-        <v>12.60167988271601</v>
+        <v>12.60169068234773</v>
       </c>
       <c r="H50" t="n">
         <v>62.06793961179837</v>
@@ -40625,7 +40625,7 @@
         <v>20.35793180493602</v>
       </c>
       <c r="G51" t="n">
-        <v>11.17083706934259</v>
+        <v>11.17082511294873</v>
       </c>
       <c r="H51" t="n">
         <v>51.29173068418904</v>
@@ -40651,7 +40651,7 @@
         <v>3.767314869352423</v>
       </c>
       <c r="E52" t="n">
-        <v>42.74212492167262</v>
+        <v>42.7421148615067</v>
       </c>
       <c r="F52" t="n">
         <v>20.88757849896625</v>
@@ -40683,7 +40683,7 @@
         <v>-0.6521681215901576</v>
       </c>
       <c r="E53" t="n">
-        <v>36.68112349098636</v>
+        <v>36.68110950479731</v>
       </c>
       <c r="F53" t="n">
         <v>9.971790610249332</v>
@@ -40811,13 +40811,13 @@
         <v>-2.895437100396392</v>
       </c>
       <c r="E57" t="n">
-        <v>46.03767088371107</v>
+        <v>46.03765664399515</v>
       </c>
       <c r="F57" t="n">
         <v>17.16470691777749</v>
       </c>
       <c r="G57" t="n">
-        <v>6.221535872660366</v>
+        <v>6.221525178895981</v>
       </c>
       <c r="H57" t="n">
         <v>39.5845017315855</v>
@@ -40843,13 +40843,13 @@
         <v>-4.116098444549698</v>
       </c>
       <c r="E58" t="n">
-        <v>41.38318530518315</v>
+        <v>41.38319910862871</v>
       </c>
       <c r="F58" t="n">
         <v>2.990288101739491</v>
       </c>
       <c r="G58" t="n">
-        <v>9.697583982835024</v>
+        <v>9.697594656504771</v>
       </c>
       <c r="H58" t="n">
         <v>45.31866297896825</v>
@@ -40875,13 +40875,13 @@
         <v>-4.293192033753879</v>
       </c>
       <c r="E59" t="n">
-        <v>43.82647727908604</v>
+        <v>43.82646747624919</v>
       </c>
       <c r="F59" t="n">
         <v>5.94736400403475</v>
       </c>
       <c r="G59" t="n">
-        <v>11.58453424108281</v>
+        <v>11.58454615279096</v>
       </c>
       <c r="H59" t="n">
         <v>42.8926386006018</v>
@@ -40913,7 +40913,7 @@
         <v>-5.322962953904497</v>
       </c>
       <c r="G60" t="n">
-        <v>10.34374505217044</v>
+        <v>10.34373456670381</v>
       </c>
       <c r="H60" t="n">
         <v>49.51856946354882</v>
@@ -40939,7 +40939,7 @@
         <v>-16.15763006192025</v>
       </c>
       <c r="E61" t="n">
-        <v>44.92179529589908</v>
+        <v>44.92178179656079</v>
       </c>
       <c r="F61" t="n">
         <v>-6.880840531123522</v>
@@ -40977,7 +40977,7 @@
         <v>-6.987674070479477</v>
       </c>
       <c r="G62" t="n">
-        <v>8.264571345614691</v>
+        <v>8.264582701998147</v>
       </c>
       <c r="H62" t="n">
         <v>50.16128375966063</v>
@@ -41003,7 +41003,7 @@
         <v>-13.16582403069547</v>
       </c>
       <c r="E63" t="n">
-        <v>52.36659633483563</v>
+        <v>52.36658211824747</v>
       </c>
       <c r="F63" t="n">
         <v>-4.954792961494691</v>
@@ -41041,7 +41041,7 @@
         <v>-7.543856079815425</v>
       </c>
       <c r="G64" t="n">
-        <v>10.43704479153176</v>
+        <v>10.43703440501735</v>
       </c>
       <c r="H64" t="n">
         <v>52.6315695544544</v>
@@ -41067,13 +41067,13 @@
         <v>-9.5696171627769</v>
       </c>
       <c r="E65" t="n">
-        <v>53.37992447951525</v>
+        <v>53.37991067295851</v>
       </c>
       <c r="F65" t="n">
         <v>-2.789282531167381</v>
       </c>
       <c r="G65" t="n">
-        <v>11.19598680172837</v>
+        <v>11.19599714779607</v>
       </c>
       <c r="H65" t="n">
         <v>60.93793770295235</v>
@@ -41099,13 +41099,13 @@
         <v>-11.31513063255917</v>
       </c>
       <c r="E66" t="n">
-        <v>56.02260652743436</v>
+        <v>56.02259572511812</v>
       </c>
       <c r="F66" t="n">
         <v>-3.191753439454137</v>
       </c>
       <c r="G66" t="n">
-        <v>9.654975583939551</v>
+        <v>9.654986894345697</v>
       </c>
       <c r="H66" t="n">
         <v>69.55524373430775</v>
@@ -41131,13 +41131,13 @@
         <v>-11.01736652795241</v>
       </c>
       <c r="E67" t="n">
-        <v>50.77263103718916</v>
+        <v>50.77261751103143</v>
       </c>
       <c r="F67" t="n">
         <v>-5.080884384452744</v>
       </c>
       <c r="G67" t="n">
-        <v>10.82644025020392</v>
+        <v>10.82645168908207</v>
       </c>
       <c r="H67" t="n">
         <v>74.20005719956657</v>
@@ -41163,13 +41163,13 @@
         <v>-9.423563890822795</v>
       </c>
       <c r="E68" t="n">
-        <v>49.72388691054292</v>
+        <v>49.7238733754217</v>
       </c>
       <c r="F68" t="n">
         <v>-3.992768548930603</v>
       </c>
       <c r="G68" t="n">
-        <v>9.923264821242771</v>
+        <v>9.923286483809047</v>
       </c>
       <c r="H68" t="n">
         <v>70.46093895677912</v>
@@ -41265,7 +41265,7 @@
         <v>-11.76738888704267</v>
       </c>
       <c r="G71" t="n">
-        <v>7.132621466067346</v>
+        <v>7.132610410294027</v>
       </c>
       <c r="H71" t="n">
         <v>51.19813928486645</v>
@@ -41329,7 +41329,7 @@
         <v>-17.74229082477954</v>
       </c>
       <c r="G73" t="n">
-        <v>4.782695642945956</v>
+        <v>4.782685507174245</v>
       </c>
       <c r="H73" t="n">
         <v>45.67474432100389</v>
@@ -41355,13 +41355,13 @@
         <v>-10.50251353091357</v>
       </c>
       <c r="E74" t="n">
-        <v>37.76564791574937</v>
+        <v>37.76563551471814</v>
       </c>
       <c r="F74" t="n">
         <v>-24.46927078175064</v>
       </c>
       <c r="G74" t="n">
-        <v>3.417552586709838</v>
+        <v>3.417532164388515</v>
       </c>
       <c r="H74" t="n">
         <v>37.45292871774588</v>
@@ -41387,13 +41387,13 @@
         <v>-11.97995591778075</v>
       </c>
       <c r="E75" t="n">
-        <v>35.300020332275</v>
+        <v>35.3000326287824</v>
       </c>
       <c r="F75" t="n">
         <v>-18.87479351610046</v>
       </c>
       <c r="G75" t="n">
-        <v>1.709496340413774</v>
+        <v>1.709496168504154</v>
       </c>
       <c r="H75" t="n">
         <v>30.02268127303005</v>
@@ -41419,7 +41419,7 @@
         <v>-11.60304744813735</v>
       </c>
       <c r="E76" t="n">
-        <v>32.8966170006417</v>
+        <v>32.89662954383419</v>
       </c>
       <c r="F76" t="n">
         <v>-17.12165045191634</v>
@@ -41451,13 +41451,13 @@
         <v>-16.59367383947344</v>
       </c>
       <c r="E77" t="n">
-        <v>27.44300298995188</v>
+        <v>27.44299051570651</v>
       </c>
       <c r="F77" t="n">
         <v>-16.99586307263094</v>
       </c>
       <c r="G77" t="n">
-        <v>0.4026336152652688</v>
+        <v>0.4026235280631285</v>
       </c>
       <c r="H77" t="n">
         <v>33.76771462059234</v>
@@ -41483,13 +41483,13 @@
         <v>-19.17274342085357</v>
       </c>
       <c r="E78" t="n">
-        <v>26.50176570435701</v>
+        <v>26.50176102394366</v>
       </c>
       <c r="F78" t="n">
         <v>-14.20658392523141</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.217336350478059</v>
+        <v>-0.2173261574215601</v>
       </c>
       <c r="H78" t="n">
         <v>37.16040451905292</v>
@@ -41553,7 +41553,7 @@
         <v>-14.96527786669417</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.4200185863839745</v>
+        <v>-0.4200085592022895</v>
       </c>
       <c r="H80" t="n">
         <v>40.86671910305058</v>
@@ -41579,7 +41579,7 @@
         <v>-24.76658411486981</v>
       </c>
       <c r="E81" t="n">
-        <v>28.57142580895549</v>
+        <v>28.5714340963751</v>
       </c>
       <c r="F81" t="n">
         <v>-16.15832902940159</v>
@@ -41611,13 +41611,13 @@
         <v>-27.62790502503861</v>
       </c>
       <c r="E82" t="n">
-        <v>26.98314730158067</v>
+        <v>26.98314264407708</v>
       </c>
       <c r="F82" t="n">
         <v>-15.09280158634767</v>
       </c>
       <c r="G82" t="n">
-        <v>-2.800927886138316</v>
+        <v>-2.800918359596094</v>
       </c>
       <c r="H82" t="n">
         <v>40.05622697643856</v>
@@ -41643,13 +41643,13 @@
         <v>-34.48276159737812</v>
       </c>
       <c r="E83" t="n">
-        <v>28.51446747407287</v>
+        <v>28.51448033045003</v>
       </c>
       <c r="F83" t="n">
         <v>-19.74900728652863</v>
       </c>
       <c r="G83" t="n">
-        <v>-5.022541018046145</v>
+        <v>-5.022559850758135</v>
       </c>
       <c r="H83" t="n">
         <v>41.68852680226573</v>
@@ -41707,7 +41707,7 @@
         <v>-24.665128160175</v>
       </c>
       <c r="E85" t="n">
-        <v>27.92017608149169</v>
+        <v>27.92016784817664</v>
       </c>
       <c r="F85" t="n">
         <v>-16.67054649645153</v>
@@ -41739,7 +41739,7 @@
         <v>-26.6666637832975</v>
       </c>
       <c r="E86" t="n">
-        <v>28.70115663257717</v>
+        <v>28.70116495989465</v>
       </c>
       <c r="F86" t="n">
         <v>-17.14285992776975</v>
@@ -41771,13 +41771,13 @@
         <v>-26.10859890573426</v>
       </c>
       <c r="E87" t="n">
-        <v>30.99702123862926</v>
+        <v>30.99703429220788</v>
       </c>
       <c r="F87" t="n">
         <v>-18.06414822509883</v>
       </c>
       <c r="G87" t="n">
-        <v>-2.608831164051528</v>
+        <v>-2.608850082361591</v>
       </c>
       <c r="H87" t="n">
         <v>62.23634673800827</v>
@@ -41803,13 +41803,13 @@
         <v>-27.29792125425134</v>
       </c>
       <c r="E88" t="n">
-        <v>26.79485831618089</v>
+        <v>26.79487970919705</v>
       </c>
       <c r="F88" t="n">
         <v>-22.44094964591114</v>
       </c>
       <c r="G88" t="n">
-        <v>-5.51181892058864</v>
+        <v>-5.511809369019527</v>
       </c>
       <c r="H88" t="n">
         <v>55.75244209203252</v>
@@ -41841,7 +41841,7 @@
         <v>-21.64679673751331</v>
       </c>
       <c r="G89" t="n">
-        <v>-4.430058284525817</v>
+        <v>-4.430067347439826</v>
       </c>
       <c r="H89" t="n">
         <v>62.23793649992655</v>
@@ -41867,13 +41867,13 @@
         <v>-25.66037895417199</v>
       </c>
       <c r="E90" t="n">
-        <v>28.18202818962325</v>
+        <v>28.1820197606033</v>
       </c>
       <c r="F90" t="n">
         <v>-21.60274235468711</v>
       </c>
       <c r="G90" t="n">
-        <v>-1.754756569930216</v>
+        <v>-1.754765960790283</v>
       </c>
       <c r="H90" t="n">
         <v>44.01810748398501</v>
@@ -41899,13 +41899,13 @@
         <v>-27.11316392142076</v>
       </c>
       <c r="E91" t="n">
-        <v>23.32125845384157</v>
+        <v>23.32124539191589</v>
       </c>
       <c r="F91" t="n">
         <v>-24.73446258717338</v>
       </c>
       <c r="G91" t="n">
-        <v>-2.788650154475081</v>
+        <v>-2.788640615443083</v>
       </c>
       <c r="H91" t="n">
         <v>35.52879303916819</v>
@@ -41963,13 +41963,13 @@
         <v>-33.75854461744496</v>
       </c>
       <c r="E93" t="n">
-        <v>13.49678679972988</v>
+        <v>13.49679986444057</v>
       </c>
       <c r="F93" t="n">
         <v>-33.28873780551388</v>
       </c>
       <c r="G93" t="n">
-        <v>-3.684588482805928</v>
+        <v>-3.684597695080793</v>
       </c>
       <c r="H93" t="n">
         <v>29.00301913394756</v>
@@ -41995,7 +41995,7 @@
         <v>-32.86343938807552</v>
       </c>
       <c r="E94" t="n">
-        <v>13.0281626461012</v>
+        <v>13.02817533738021</v>
       </c>
       <c r="F94" t="n">
         <v>-31.92243919478229</v>
@@ -42059,13 +42059,13 @@
         <v>-39.19354682410292</v>
       </c>
       <c r="E96" t="n">
-        <v>14.19141889163848</v>
+        <v>14.19141167535614</v>
       </c>
       <c r="F96" t="n">
         <v>-43.65987090351605</v>
       </c>
       <c r="G96" t="n">
-        <v>-1.77221865009497</v>
+        <v>-1.772228030575917</v>
       </c>
       <c r="H96" t="n">
         <v>15.89211111741442</v>
@@ -42091,7 +42091,7 @@
         <v>-37.38589247413267</v>
       </c>
       <c r="E97" t="n">
-        <v>15.21784099939436</v>
+        <v>15.21784828805857</v>
       </c>
       <c r="F97" t="n">
         <v>-43.28643185409469</v>
@@ -42123,7 +42123,7 @@
         <v>-36.22489816175252</v>
       </c>
       <c r="E98" t="n">
-        <v>14.42208246479413</v>
+        <v>14.42207519042114</v>
       </c>
       <c r="F98" t="n">
         <v>-52.13567772568902</v>
@@ -42193,7 +42193,7 @@
         <v>-56.44122399079755</v>
       </c>
       <c r="G100" t="n">
-        <v>-6.514108515058659</v>
+        <v>-6.514107927947088</v>
       </c>
       <c r="H100" t="n">
         <v>15.07653487454037</v>
@@ -42225,7 +42225,7 @@
         <v>-56.13349608547158</v>
       </c>
       <c r="G101" t="n">
-        <v>-9.051291101519077</v>
+        <v>-9.051266120771629</v>
       </c>
       <c r="H101" t="n">
         <v>17.94541203322633</v>
@@ -42257,7 +42257,7 @@
         <v>-55.91733700865703</v>
       </c>
       <c r="G102" t="n">
-        <v>-9.027544169019031</v>
+        <v>-9.027552345033785</v>
       </c>
       <c r="H102" t="n">
         <v>18.40919658725724</v>
@@ -42283,13 +42283,13 @@
         <v>-37.47898911160345</v>
       </c>
       <c r="E103" t="n">
-        <v>-3.813640407312757</v>
+        <v>-3.813646722865827</v>
       </c>
       <c r="F103" t="n">
         <v>-61.42636857635259</v>
       </c>
       <c r="G103" t="n">
-        <v>-9.404738086845111</v>
+        <v>-9.404746306998312</v>
       </c>
       <c r="H103" t="n">
         <v>14.88724822383976</v>
@@ -42315,13 +42315,13 @@
         <v>-38.02935221563132</v>
       </c>
       <c r="E104" t="n">
-        <v>-4.049327871322895</v>
+        <v>-4.049334168701613</v>
       </c>
       <c r="F104" t="n">
         <v>-60.6574271929146</v>
       </c>
       <c r="G104" t="n">
-        <v>-9.456504668185772</v>
+        <v>-9.456513699392843</v>
       </c>
       <c r="H104" t="n">
         <v>9.913208228453851</v>
@@ -42417,7 +42417,7 @@
         <v>-56.24584747712591</v>
       </c>
       <c r="G107" t="n">
-        <v>-5.542274228029543</v>
+        <v>-5.542282911524943</v>
       </c>
       <c r="H107" t="n">
         <v>17.43205870243658</v>
@@ -42443,7 +42443,7 @@
         <v>-34.87069327681005</v>
       </c>
       <c r="E108" t="n">
-        <v>0.6920954001579327</v>
+        <v>0.6920890135108326</v>
       </c>
       <c r="F108" t="n">
         <v>-56.18415731425067</v>
@@ -42475,13 +42475,13 @@
         <v>-38.2809222994163</v>
       </c>
       <c r="E109" t="n">
-        <v>-6.784861443789014</v>
+        <v>-6.78485575492701</v>
       </c>
       <c r="F109" t="n">
         <v>-56.1025635808961</v>
       </c>
       <c r="G109" t="n">
-        <v>-13.66813584312502</v>
+        <v>-13.66812847760248</v>
       </c>
       <c r="H109" t="n">
         <v>2.676028157570309</v>
@@ -42507,13 +42507,13 @@
         <v>-38.41336313097599</v>
       </c>
       <c r="E110" t="n">
-        <v>-1.049651814667596</v>
+        <v>-1.049657998912068</v>
       </c>
       <c r="F110" t="n">
         <v>-55.1449584922653</v>
       </c>
       <c r="G110" t="n">
-        <v>-8.387393142026822</v>
+        <v>-8.387401182548881</v>
       </c>
       <c r="H110" t="n">
         <v>6.024615316080983</v>
@@ -42539,13 +42539,13 @@
         <v>-38.03757962483449</v>
       </c>
       <c r="E111" t="n">
-        <v>0.6324251301784045</v>
+        <v>0.632431300721481</v>
       </c>
       <c r="F111" t="n">
         <v>-54.47863391321948</v>
       </c>
       <c r="G111" t="n">
-        <v>-10.09984190731003</v>
+        <v>-10.09983412216593</v>
       </c>
       <c r="H111" t="n">
         <v>10.12767521636539</v>
@@ -42603,13 +42603,13 @@
         <v>-38.7500007947286</v>
       </c>
       <c r="E113" t="n">
-        <v>-1.713949720608687</v>
+        <v>-1.713949824055983</v>
       </c>
       <c r="F113" t="n">
         <v>-54.22889949879295</v>
       </c>
       <c r="G113" t="n">
-        <v>-12.80789830622243</v>
+        <v>-12.80790569589147</v>
       </c>
       <c r="H113" t="n">
         <v>29.08312860522841</v>
@@ -42635,13 +42635,13 @@
         <v>-42.96153875497671</v>
       </c>
       <c r="E114" t="n">
-        <v>-15.959870204464</v>
+        <v>-15.95987381179289</v>
       </c>
       <c r="F114" t="n">
         <v>-55.92657561500155</v>
       </c>
       <c r="G114" t="n">
-        <v>-12.58630432315313</v>
+        <v>-12.58631182774559</v>
       </c>
       <c r="H114" t="n">
         <v>32.61072830164626</v>
@@ -42673,7 +42673,7 @@
         <v>-56.60509984441939</v>
       </c>
       <c r="G115" t="n">
-        <v>-13.22025659231684</v>
+        <v>-13.22026410105521</v>
       </c>
       <c r="H115" t="n">
         <v>24.44754770776356</v>
@@ -42705,7 +42705,7 @@
         <v>-55.79329376930953</v>
       </c>
       <c r="G116" t="n">
-        <v>-15.35700080551199</v>
+        <v>-15.35700805648983</v>
       </c>
       <c r="H116" t="n">
         <v>23.26171935995283</v>
@@ -42731,13 +42731,13 @@
         <v>-44.84615325927734</v>
       </c>
       <c r="E117" t="n">
-        <v>-13.21917958333557</v>
+        <v>-13.21917375442618</v>
       </c>
       <c r="F117" t="n">
         <v>-55.92658828357197</v>
       </c>
       <c r="G117" t="n">
-        <v>-15.85363754969596</v>
+        <v>-15.85364606912631</v>
       </c>
       <c r="H117" t="n">
         <v>24.94730195367547</v>
@@ -42769,7 +42769,7 @@
         <v>-56.78818610596754</v>
       </c>
       <c r="G118" t="n">
-        <v>-16.38669079411861</v>
+        <v>-16.38669786568314</v>
       </c>
       <c r="H118" t="n">
         <v>17.44131168849032</v>
@@ -42795,13 +42795,13 @@
         <v>-41.87633402561816</v>
       </c>
       <c r="E119" t="n">
-        <v>-18.05122097776638</v>
+        <v>-18.0512117287556</v>
       </c>
       <c r="F119" t="n">
         <v>-56.31058995863971</v>
       </c>
       <c r="G119" t="n">
-        <v>-15.37458178389647</v>
+        <v>-15.37457327751788</v>
       </c>
       <c r="H119" t="n">
         <v>20.81582502027968</v>
@@ -42827,7 +42827,7 @@
         <v>-42.79069788072998</v>
       </c>
       <c r="E120" t="n">
-        <v>-18.96607964296703</v>
+        <v>-18.96608874513238</v>
       </c>
       <c r="F120" t="n">
         <v>-56.69829342607511</v>
@@ -42859,13 +42859,13 @@
         <v>-41.32780033399969</v>
       </c>
       <c r="E121" t="n">
-        <v>-16.14651905964717</v>
+        <v>-16.14652467077281</v>
       </c>
       <c r="F121" t="n">
         <v>-57.14155223271617</v>
       </c>
       <c r="G121" t="n">
-        <v>-16.85994364190014</v>
+        <v>-16.85995198161126</v>
       </c>
       <c r="H121" t="n">
         <v>11.82631761961019</v>
@@ -42961,7 +42961,7 @@
         <v>-61.61153711978648</v>
       </c>
       <c r="G124" t="n">
-        <v>-17.32210209479792</v>
+        <v>-17.3221006429568</v>
       </c>
       <c r="H124" t="n">
         <v>-0.8441437102060356</v>
@@ -42987,13 +42987,13 @@
         <v>-44.06438871165855</v>
       </c>
       <c r="E125" t="n">
-        <v>-19.65921433551706</v>
+        <v>-19.65920559792231</v>
       </c>
       <c r="F125" t="n">
         <v>-62.04201834542411</v>
       </c>
       <c r="G125" t="n">
-        <v>-17.87453111804034</v>
+        <v>-17.87451582243691</v>
       </c>
       <c r="H125" t="n">
         <v>-0.9950223577321893</v>
@@ -43051,13 +43051,13 @@
         <v>-45.25879720144958</v>
       </c>
       <c r="E127" t="n">
-        <v>-31.44790974132207</v>
+        <v>-31.44791479939482</v>
       </c>
       <c r="F127" t="n">
         <v>-64.48646305395978</v>
       </c>
       <c r="G127" t="n">
-        <v>-18.73303819338198</v>
+        <v>-18.73304496909627</v>
       </c>
       <c r="H127" t="n">
         <v>-7.626934073983682</v>
@@ -43153,7 +43153,7 @@
         <v>-63.12178339389629</v>
       </c>
       <c r="G130" t="n">
-        <v>-20.60108135869104</v>
+        <v>-20.60109627698906</v>
       </c>
       <c r="H130" t="n">
         <v>-0.430739938833391</v>
@@ -43179,13 +43179,13 @@
         <v>-38.22222391764323</v>
       </c>
       <c r="E131" t="n">
-        <v>-28.66038601708145</v>
+        <v>-28.66039098574015</v>
       </c>
       <c r="F131" t="n">
         <v>-60.87921861989671</v>
       </c>
       <c r="G131" t="n">
-        <v>-16.61963745395354</v>
+        <v>-16.61965301788414</v>
       </c>
       <c r="H131" t="n">
         <v>11.20226017119483</v>
@@ -43211,13 +43211,13 @@
         <v>-37.71428537892771</v>
       </c>
       <c r="E132" t="n">
-        <v>-28.44839309277756</v>
+        <v>-28.44838815136688</v>
       </c>
       <c r="F132" t="n">
         <v>-57.52336377295379</v>
       </c>
       <c r="G132" t="n">
-        <v>-14.15376426238819</v>
+        <v>-14.15377152255236</v>
       </c>
       <c r="H132" t="n">
         <v>8.352201320420626</v>
@@ -43243,13 +43243,13 @@
         <v>-39.29359721158256</v>
       </c>
       <c r="E133" t="n">
-        <v>-31.89681766180208</v>
+        <v>-31.89682422506088</v>
       </c>
       <c r="F133" t="n">
         <v>-56.86676433086298</v>
       </c>
       <c r="G133" t="n">
-        <v>-16.72258727099999</v>
+        <v>-16.72258588643216</v>
       </c>
       <c r="H133" t="n">
         <v>2.898096851378784</v>
@@ -43307,13 +43307,13 @@
         <v>-39.18181766163219</v>
       </c>
       <c r="E135" t="n">
-        <v>-29.89430845995157</v>
+        <v>-29.8943198980845</v>
       </c>
       <c r="F135" t="n">
         <v>-55.97900230427739</v>
       </c>
       <c r="G135" t="n">
-        <v>-15.92344686738257</v>
+        <v>-15.92343863232097</v>
       </c>
       <c r="H135" t="n">
         <v>-2.809878783828057</v>
@@ -43345,7 +43345,7 @@
         <v>-54.15469427793725</v>
       </c>
       <c r="G136" t="n">
-        <v>-16.69092168949762</v>
+        <v>-16.69092990921731</v>
       </c>
       <c r="H136" t="n">
         <v>0.04121654929012397</v>
@@ -43371,13 +43371,13 @@
         <v>-41.2641063072619</v>
       </c>
       <c r="E137" t="n">
-        <v>-34.25575730483226</v>
+        <v>-34.25576189254548</v>
       </c>
       <c r="F137" t="n">
         <v>-56.62921337306769</v>
       </c>
       <c r="G137" t="n">
-        <v>-15.94878553516822</v>
+        <v>-15.94877718164233</v>
       </c>
       <c r="H137" t="n">
         <v>-0.8227812344208774</v>
@@ -43403,13 +43403,13 @@
         <v>-38.77646951114431</v>
       </c>
       <c r="E138" t="n">
-        <v>-38.27638938277526</v>
+        <v>-38.27639900697836</v>
       </c>
       <c r="F138" t="n">
         <v>-55.96958453493185</v>
       </c>
       <c r="G138" t="n">
-        <v>-15.24242479379555</v>
+        <v>-15.24242350981521</v>
       </c>
       <c r="H138" t="n">
         <v>-1.909228316656353</v>
@@ -43435,13 +43435,13 @@
         <v>-33.90243809397627</v>
       </c>
       <c r="E139" t="n">
-        <v>-36.75832572741635</v>
+        <v>-36.75832996076532</v>
       </c>
       <c r="F139" t="n">
         <v>-49.86285836356027</v>
       </c>
       <c r="G139" t="n">
-        <v>-15.18492986028326</v>
+        <v>-15.18492275842689</v>
       </c>
       <c r="H139" t="n">
         <v>11.39967947776015</v>
@@ -43473,7 +43473,7 @@
         <v>-47.07156041622452</v>
       </c>
       <c r="G140" t="n">
-        <v>-11.08226986572446</v>
+        <v>-11.08227849193191</v>
       </c>
       <c r="H140" t="n">
         <v>26.95559471805855</v>
@@ -43499,13 +43499,13 @@
         <v>-32.12871524589028</v>
       </c>
       <c r="E141" t="n">
-        <v>-32.2831469020805</v>
+        <v>-32.28313624311352</v>
       </c>
       <c r="F141" t="n">
         <v>-43.95747457582054</v>
       </c>
       <c r="G141" t="n">
-        <v>-10.53411633157888</v>
+        <v>-10.53409997986522</v>
       </c>
       <c r="H141" t="n">
         <v>11.78529754959159</v>
@@ -43531,13 +43531,13 @@
         <v>-31.4987748448557</v>
       </c>
       <c r="E142" t="n">
-        <v>-32.50761786349332</v>
+        <v>-32.50762230682122</v>
       </c>
       <c r="F142" t="n">
         <v>-46.5503629780039</v>
       </c>
       <c r="G142" t="n">
-        <v>-7.876450728562324</v>
+        <v>-7.876442017505214</v>
       </c>
       <c r="H142" t="n">
         <v>2.585262900904595</v>
@@ -43563,7 +43563,7 @@
         <v>-33.84615297239228</v>
       </c>
       <c r="E143" t="n">
-        <v>-35.46164071660527</v>
+        <v>-35.46163637158381</v>
       </c>
       <c r="F143" t="n">
         <v>-51.06795889575086</v>
@@ -43595,7 +43595,7 @@
         <v>-33.90862967753029</v>
       </c>
       <c r="E144" t="n">
-        <v>-36.97424007121808</v>
+        <v>-36.97423460587854</v>
       </c>
       <c r="F144" t="n">
         <v>-49.50652575035288</v>
@@ -43627,13 +43627,13 @@
         <v>-32.57731865513828</v>
       </c>
       <c r="E145" t="n">
-        <v>-33.10222787693342</v>
+        <v>-33.10222333815624</v>
       </c>
       <c r="F145" t="n">
         <v>-47.72093129712481</v>
       </c>
       <c r="G145" t="n">
-        <v>-11.16617952809754</v>
+        <v>-11.166194731203</v>
       </c>
       <c r="H145" t="n">
         <v>2.334533491450208</v>
@@ -43659,13 +43659,13 @@
         <v>-32.98968940399975</v>
       </c>
       <c r="E146" t="n">
-        <v>-32.82847077144174</v>
+        <v>-32.82846017281587</v>
       </c>
       <c r="F146" t="n">
         <v>-50.13210990744989</v>
       </c>
       <c r="G146" t="n">
-        <v>-11.82290408126045</v>
+        <v>-11.82289657347413</v>
       </c>
       <c r="H146" t="n">
         <v>-4.631267327895838</v>
@@ -43723,13 +43723,13 @@
         <v>-32.69521712881676</v>
       </c>
       <c r="E148" t="n">
-        <v>-33.61837794033982</v>
+        <v>-33.61837206509205</v>
       </c>
       <c r="F148" t="n">
         <v>-50.8521140595779</v>
       </c>
       <c r="G148" t="n">
-        <v>-12.91493707036117</v>
+        <v>-12.91494564032035</v>
       </c>
       <c r="H148" t="n">
         <v>-6.028498086992817</v>
@@ -43761,7 +43761,7 @@
         <v>-48.09143066406249</v>
       </c>
       <c r="G149" t="n">
-        <v>-16.07073061271678</v>
+        <v>-16.07073194266726</v>
       </c>
       <c r="H149" t="n">
         <v>-1.760633823603719</v>
@@ -43793,7 +43793,7 @@
         <v>-49.79118293323855</v>
       </c>
       <c r="G150" t="n">
-        <v>-18.64665687650983</v>
+        <v>-18.64665011230938</v>
       </c>
       <c r="H150" t="n">
         <v>-7.602880670023849</v>
@@ -43819,13 +43819,13 @@
         <v>-42.04651145047919</v>
       </c>
       <c r="E151" t="n">
-        <v>-40.1821013090503</v>
+        <v>-40.1821004663875</v>
       </c>
       <c r="F151" t="n">
         <v>-54.39159419656274</v>
       </c>
       <c r="G151" t="n">
-        <v>-21.22333815512868</v>
+        <v>-21.22332983451548</v>
       </c>
       <c r="H151" t="n">
         <v>-10.10608394316426</v>
@@ -43851,7 +43851,7 @@
         <v>-39.58139641340389</v>
       </c>
       <c r="E152" t="n">
-        <v>-37.04564463586239</v>
+        <v>-37.04565432657586</v>
       </c>
       <c r="F152" t="n">
         <v>-53.60400625525475</v>
@@ -43883,7 +43883,7 @@
         <v>-41.59453644999592</v>
       </c>
       <c r="E153" t="n">
-        <v>-38.13497790868293</v>
+        <v>-38.13498321627997</v>
       </c>
       <c r="F153" t="n">
         <v>-55.56276981035423</v>
@@ -43947,7 +43947,7 @@
         <v>-39.45701410186536</v>
       </c>
       <c r="E155" t="n">
-        <v>-36.07449555886241</v>
+        <v>-36.07449031108776</v>
       </c>
       <c r="F155" t="n">
         <v>-51.83269228782829</v>
@@ -43985,7 +43985,7 @@
         <v>-50.83378680070674</v>
       </c>
       <c r="G156" t="n">
-        <v>-16.31714083164055</v>
+        <v>-16.31714778894482</v>
       </c>
       <c r="H156" t="n">
         <v>-11.96105995313918</v>
@@ -44017,7 +44017,7 @@
         <v>-49.81553837768958</v>
       </c>
       <c r="G157" t="n">
-        <v>-12.62763296200138</v>
+        <v>-12.62762558715662</v>
       </c>
       <c r="H157" t="n">
         <v>-7.803167735336114</v>
@@ -44043,13 +44043,13 @@
         <v>-34.9769623935906</v>
       </c>
       <c r="E158" t="n">
-        <v>-33.49170244123877</v>
+        <v>-33.49169830616715</v>
       </c>
       <c r="F158" t="n">
         <v>-49.31460605578476</v>
       </c>
       <c r="G158" t="n">
-        <v>-12.14390576552569</v>
+        <v>-12.14389741566937</v>
       </c>
       <c r="H158" t="n">
         <v>19.17837993230622</v>
@@ -44081,7 +44081,7 @@
         <v>-48.69467684534752</v>
       </c>
       <c r="G159" t="n">
-        <v>-11.6939399096355</v>
+        <v>-11.69394833020523</v>
       </c>
       <c r="H159" t="n">
         <v>34.79139711401707</v>
@@ -44107,7 +44107,7 @@
         <v>-29.01205039886107</v>
       </c>
       <c r="E160" t="n">
-        <v>-27.1408366814982</v>
+        <v>-27.14083902839913</v>
       </c>
       <c r="F160" t="n">
         <v>-46.60070067860755</v>
@@ -44171,13 +44171,13 @@
         <v>-36.22727394104004</v>
       </c>
       <c r="E162" t="n">
-        <v>-33.12631667581559</v>
+        <v>-33.12632209017097</v>
       </c>
       <c r="F162" t="n">
         <v>-51.18435907630281</v>
       </c>
       <c r="G162" t="n">
-        <v>-10.89316097368617</v>
+        <v>-10.8931684914654</v>
       </c>
       <c r="H162" t="n">
         <v>31.94658342227763</v>
@@ -44203,13 +44203,13 @@
         <v>-36.56108499654562</v>
       </c>
       <c r="E163" t="n">
-        <v>-30.31613958799745</v>
+        <v>-30.31612554162724</v>
       </c>
       <c r="F163" t="n">
         <v>-50.39954164408403</v>
       </c>
       <c r="G163" t="n">
-        <v>-6.576257575571676</v>
+        <v>-6.576258128209467</v>
       </c>
       <c r="H163" t="n">
         <v>35.25827976252069</v>
@@ -44235,7 +44235,7 @@
         <v>-37.483146753204</v>
       </c>
       <c r="E164" t="n">
-        <v>-32.68094753767251</v>
+        <v>-32.68096093226646</v>
       </c>
       <c r="F164" t="n">
         <v>-48.08486004347705</v>
@@ -44267,13 +44267,13 @@
         <v>-40.39734998955379</v>
       </c>
       <c r="E165" t="n">
-        <v>-32.87279104672564</v>
+        <v>-32.87279634781893</v>
       </c>
       <c r="F165" t="n">
         <v>-50.55082406989408</v>
       </c>
       <c r="G165" t="n">
-        <v>-3.395854658131747</v>
+        <v>-3.395846479893661</v>
       </c>
       <c r="H165" t="n">
         <v>31.92537293485394</v>
@@ -44299,13 +44299,13 @@
         <v>-40.43955960116543</v>
       </c>
       <c r="E166" t="n">
-        <v>-32.08065123048447</v>
+        <v>-32.08065667981757</v>
       </c>
       <c r="F166" t="n">
         <v>-53.59653548729015</v>
       </c>
       <c r="G166" t="n">
-        <v>-1.762285595699331</v>
+        <v>-1.762277226693731</v>
       </c>
       <c r="H166" t="n">
         <v>31.32498904941086</v>
@@ -44331,7 +44331,7 @@
         <v>-38.52349200624654</v>
       </c>
       <c r="E167" t="n">
-        <v>-31.8336393401792</v>
+        <v>-31.83363387746486</v>
       </c>
       <c r="F167" t="n">
         <v>-53.46630744214328</v>
@@ -44369,7 +44369,7 @@
         <v>-53.21192041547695</v>
       </c>
       <c r="G168" t="n">
-        <v>-1.846931117352801</v>
+        <v>-1.846922769230852</v>
       </c>
       <c r="H168" t="n">
         <v>23.80828374026902</v>
@@ -44401,7 +44401,7 @@
         <v>-52.13521178339568</v>
       </c>
       <c r="G169" t="n">
-        <v>-3.703214914559028</v>
+        <v>-3.703223035058201</v>
       </c>
       <c r="H169" t="n">
         <v>29.44025621625235</v>
@@ -44433,7 +44433,7 @@
         <v>-52.14848123130358</v>
       </c>
       <c r="G170" t="n">
-        <v>-3.764455597413807</v>
+        <v>-3.764463701823417</v>
       </c>
       <c r="H170" t="n">
         <v>31.30973250029547</v>
@@ -44459,13 +44459,13 @@
         <v>-40.04556086562169</v>
       </c>
       <c r="E171" t="n">
-        <v>-34.58448249718911</v>
+        <v>-34.58447846232172</v>
       </c>
       <c r="F171" t="n">
         <v>-51.04838688412199</v>
       </c>
       <c r="G171" t="n">
-        <v>-5.77381942704066</v>
+        <v>-5.77381100302633</v>
       </c>
       <c r="H171" t="n">
         <v>33.71331443951104</v>
@@ -44497,7 +44497,7 @@
         <v>-45.99760763325964</v>
       </c>
       <c r="G172" t="n">
-        <v>0.5143205788882721</v>
+        <v>0.5143291941176686</v>
       </c>
       <c r="H172" t="n">
         <v>44.92055080938697</v>
@@ -44523,13 +44523,13 @@
         <v>-32.91375369932255</v>
       </c>
       <c r="E173" t="n">
-        <v>-27.77852341218486</v>
+        <v>-27.77852938823074</v>
       </c>
       <c r="F173" t="n">
         <v>-43.44699349358814</v>
       </c>
       <c r="G173" t="n">
-        <v>0.06901541889747786</v>
+        <v>0.06902412197677954</v>
       </c>
       <c r="H173" t="n">
         <v>59.14138873392913</v>
@@ -44555,13 +44555,13 @@
         <v>-30.59382334344727</v>
       </c>
       <c r="E174" t="n">
-        <v>-24.91227355035074</v>
+        <v>-24.91228000773636</v>
       </c>
       <c r="F174" t="n">
         <v>-41.76249980926514</v>
       </c>
       <c r="G174" t="n">
-        <v>1.980733214022967</v>
+        <v>1.980733388627964</v>
       </c>
       <c r="H174" t="n">
         <v>59.09223654259699</v>
@@ -44593,7 +44593,7 @@
         <v>-42.28287675129394</v>
       </c>
       <c r="G175" t="n">
-        <v>2.861048248629738</v>
+        <v>2.861057206861273</v>
       </c>
       <c r="H175" t="n">
         <v>63.09951008127501</v>
@@ -44625,7 +44625,7 @@
         <v>-38.62024938625434</v>
       </c>
       <c r="G176" t="n">
-        <v>4.821513659026477</v>
+        <v>4.821532236846604</v>
       </c>
       <c r="H176" t="n">
         <v>73.38710005667144</v>
@@ -44651,7 +44651,7 @@
         <v>-26.87499713439198</v>
       </c>
       <c r="E177" t="n">
-        <v>-20.35359835800773</v>
+        <v>-20.35360537283162</v>
       </c>
       <c r="F177" t="n">
         <v>-38.99999765249399</v>
@@ -44683,13 +44683,13 @@
         <v>-27.66264949936464</v>
       </c>
       <c r="E178" t="n">
-        <v>-20.47750781759832</v>
+        <v>-20.47751679276931</v>
       </c>
       <c r="F178" t="n">
         <v>-39.01896560774591</v>
       </c>
       <c r="G178" t="n">
-        <v>1.905962992066756</v>
+        <v>1.905980774876026</v>
       </c>
       <c r="H178" t="n">
         <v>66.75774073195311</v>
@@ -44715,13 +44715,13 @@
         <v>-28.19905523871372</v>
       </c>
       <c r="E179" t="n">
-        <v>-22.15916869716422</v>
+        <v>-22.15917738967272</v>
       </c>
       <c r="F179" t="n">
         <v>-41.81931635301061</v>
       </c>
       <c r="G179" t="n">
-        <v>0.9841546961556702</v>
+        <v>0.9841546105370691</v>
       </c>
       <c r="H179" t="n">
         <v>61.06736588618858</v>
@@ -44747,13 +44747,13 @@
         <v>-27.29016992783636</v>
       </c>
       <c r="E180" t="n">
-        <v>-22.41063438366677</v>
+        <v>-22.41062766588845</v>
       </c>
       <c r="F180" t="n">
         <v>-39.6770169275888</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.1476812388126914</v>
+        <v>-0.147672528644105</v>
       </c>
       <c r="H180" t="n">
         <v>65.15150572053405</v>
@@ -44779,7 +44779,7 @@
         <v>-26.03864804185331</v>
       </c>
       <c r="E181" t="n">
-        <v>-20.64498270087283</v>
+        <v>-20.64497407201848</v>
       </c>
       <c r="F181" t="n">
         <v>-39.39168486008041</v>
@@ -44811,13 +44811,13 @@
         <v>-27.65957226150498</v>
       </c>
       <c r="E182" t="n">
-        <v>-21.12262914734645</v>
+        <v>-21.12262057043012</v>
       </c>
       <c r="F182" t="n">
         <v>-38.78824946197358</v>
       </c>
       <c r="G182" t="n">
-        <v>0.2764967520753059</v>
+        <v>0.2765053808964302</v>
       </c>
       <c r="H182" t="n">
         <v>72.57494253958269</v>
@@ -44849,7 +44849,7 @@
         <v>-37.81366289032172</v>
       </c>
       <c r="G183" t="n">
-        <v>-0.6405063489323015</v>
+        <v>-0.6404978015496887</v>
       </c>
       <c r="H183" t="n">
         <v>82.78223213394497</v>
@@ -44875,13 +44875,13 @@
         <v>-26.79245330549804</v>
       </c>
       <c r="E184" t="n">
-        <v>-18.81726817858214</v>
+        <v>-18.81728369892127</v>
       </c>
       <c r="F184" t="n">
         <v>-35.9392113960985</v>
       </c>
       <c r="G184" t="n">
-        <v>-2.94078491301919</v>
+        <v>-2.940793371060713</v>
       </c>
       <c r="H184" t="n">
         <v>84.22466480357787</v>
@@ -44913,7 +44913,7 @@
         <v>-32.85538977932256</v>
       </c>
       <c r="G185" t="n">
-        <v>-4.268894345299334</v>
+        <v>-4.268902303879751</v>
       </c>
       <c r="H185" t="n">
         <v>88.55766356470485</v>
@@ -44939,7 +44939,7 @@
         <v>-25.23364352705133</v>
       </c>
       <c r="E186" t="n">
-        <v>-21.55172688455815</v>
+        <v>-21.55172030710867</v>
       </c>
       <c r="F186" t="n">
         <v>-33.64963145939185</v>
@@ -45009,7 +45009,7 @@
         <v>-30.48580422386386</v>
       </c>
       <c r="G188" t="n">
-        <v>-3.154080916110713</v>
+        <v>-3.154072432221577</v>
       </c>
       <c r="H188" t="n">
         <v>102.5162819144948</v>
@@ -45035,13 +45035,13 @@
         <v>-24.3749994268784</v>
       </c>
       <c r="E189" t="n">
-        <v>-16.85279894143548</v>
+        <v>-16.85281500968847</v>
       </c>
       <c r="F189" t="n">
         <v>-28.89460472383064</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.86368840437544</v>
+        <v>-0.8636798296580928</v>
       </c>
       <c r="H189" t="n">
         <v>123.2258100313875</v>
@@ -45067,7 +45067,7 @@
         <v>-23.35766138815261</v>
       </c>
       <c r="E190" t="n">
-        <v>-16.1754097615417</v>
+        <v>-16.17542595647212</v>
       </c>
       <c r="F190" t="n">
         <v>-32.43977679001436</v>
@@ -45105,7 +45105,7 @@
         <v>-32.24030243339486</v>
       </c>
       <c r="G191" t="n">
-        <v>1.258329006240344</v>
+        <v>1.258328897559591</v>
       </c>
       <c r="H191" t="n">
         <v>123.5046433130916</v>
@@ -45131,7 +45131,7 @@
         <v>-24.58234073821581</v>
       </c>
       <c r="E192" t="n">
-        <v>-14.560524436397</v>
+        <v>-14.56051583298611</v>
       </c>
       <c r="F192" t="n">
         <v>-31.51477378726198</v>
@@ -45163,7 +45163,7 @@
         <v>-17.57731914672299</v>
       </c>
       <c r="E193" t="n">
-        <v>-9.055420169258021</v>
+        <v>-9.055419336014003</v>
       </c>
       <c r="F193" t="n">
         <v>-24.49735055141047</v>
@@ -45195,13 +45195,13 @@
         <v>-19.49875262272378</v>
       </c>
       <c r="E194" t="n">
-        <v>-12.42766767500797</v>
+        <v>-12.4276599118963</v>
       </c>
       <c r="F194" t="n">
         <v>-25.51905198204355</v>
       </c>
       <c r="G194" t="n">
-        <v>2.327475210869889</v>
+        <v>2.327466312907478</v>
       </c>
       <c r="H194" t="n">
         <v>167.3891432924977</v>
@@ -45227,13 +45227,13 @@
         <v>-22.51231461369236</v>
       </c>
       <c r="E195" t="n">
-        <v>-15.28334387731973</v>
+        <v>-15.28333644903409</v>
       </c>
       <c r="F195" t="n">
         <v>-30.90795338358637</v>
       </c>
       <c r="G195" t="n">
-        <v>1.040289784409199</v>
+        <v>1.04028969463561</v>
       </c>
       <c r="H195" t="n">
         <v>150.8404868487914</v>
@@ -45265,7 +45265,7 @@
         <v>-34.04202768366776</v>
       </c>
       <c r="G196" t="n">
-        <v>-2.530940440115026</v>
+        <v>-2.530948631931584</v>
       </c>
       <c r="H196" t="n">
         <v>129.1716214536388</v>
@@ -45297,7 +45297,7 @@
         <v>-31.52814186982629</v>
       </c>
       <c r="G197" t="n">
-        <v>-1.951892522654342</v>
+        <v>-1.951884126406522</v>
       </c>
       <c r="H197" t="n">
         <v>105.2926634038812</v>
@@ -45323,13 +45323,13 @@
         <v>-30.62730742553335</v>
       </c>
       <c r="E198" t="n">
-        <v>-17.25910245924941</v>
+        <v>-17.25910396892187</v>
       </c>
       <c r="F198" t="n">
         <v>-33.52514665157967</v>
       </c>
       <c r="G198" t="n">
-        <v>-1.415397459717427</v>
+        <v>-1.4153889785956</v>
       </c>
       <c r="H198" t="n">
         <v>94.45324890083117</v>
@@ -45355,7 +45355,7 @@
         <v>-33.10871432964622</v>
       </c>
       <c r="E199" t="n">
-        <v>-20.1689956791109</v>
+        <v>-20.16900416692024</v>
       </c>
       <c r="F199" t="n">
         <v>-36.51537018870842</v>
@@ -45393,7 +45393,7 @@
         <v>-37.59362584999582</v>
       </c>
       <c r="G200" t="n">
-        <v>-1.848519540227556</v>
+        <v>-1.848502833106846</v>
       </c>
       <c r="H200" t="n">
         <v>88.43219261331876</v>
@@ -45425,7 +45425,7 @@
         <v>-38.58989511330547</v>
       </c>
       <c r="G201" t="n">
-        <v>-0.4313761788073966</v>
+        <v>-0.4313678535755705</v>
       </c>
       <c r="H201" t="n">
         <v>77.8160655089662</v>
@@ -45483,13 +45483,13 @@
         <v>-33.21586194762303</v>
       </c>
       <c r="E203" t="n">
-        <v>-16.04799614881611</v>
+        <v>-16.04800469940202</v>
       </c>
       <c r="F203" t="n">
         <v>-36.18741564478685</v>
       </c>
       <c r="G203" t="n">
-        <v>-0.2006033940044616</v>
+        <v>-0.2005949243657046</v>
       </c>
       <c r="H203" t="n">
         <v>83.68124127503025</v>
@@ -45515,13 +45515,13 @@
         <v>-29.41952771061378</v>
       </c>
       <c r="E204" t="n">
-        <v>-17.02912959365807</v>
+        <v>-17.02914492844722</v>
       </c>
       <c r="F204" t="n">
         <v>-26.48352671295293</v>
       </c>
       <c r="G204" t="n">
-        <v>-0.09635584766152228</v>
+        <v>-0.09633909752766456</v>
       </c>
       <c r="H204" t="n">
         <v>89.75380721992235</v>
@@ -45553,7 +45553,7 @@
         <v>-28.65188365140916</v>
       </c>
       <c r="G205" t="n">
-        <v>3.175291045053807</v>
+        <v>3.17529077529517</v>
       </c>
       <c r="H205" t="n">
         <v>94.32029234930152</v>
@@ -45579,13 +45579,13 @@
         <v>-29.47645838329669</v>
       </c>
       <c r="E206" t="n">
-        <v>-8.977062831240701</v>
+        <v>-8.977070678845955</v>
       </c>
       <c r="F206" t="n">
         <v>-28.80289813678555</v>
       </c>
       <c r="G206" t="n">
-        <v>5.485231778209143</v>
+        <v>5.485240348763276</v>
       </c>
       <c r="H206" t="n">
         <v>93.58391397352406</v>
@@ -45617,7 +45617,7 @@
         <v>-27.18278428929728</v>
       </c>
       <c r="G207" t="n">
-        <v>3.544544670919225</v>
+        <v>3.544553467908163</v>
       </c>
       <c r="H207" t="n">
         <v>96.56910071694344</v>
@@ -45643,7 +45643,7 @@
         <v>-27.65476350642918</v>
       </c>
       <c r="E208" t="n">
-        <v>-7.480690033325899</v>
+        <v>-7.480697989790852</v>
       </c>
       <c r="F208" t="n">
         <v>-28.56085470297766</v>
@@ -45675,13 +45675,13 @@
         <v>-26.7097961922128</v>
       </c>
       <c r="E209" t="n">
-        <v>-7.60746146904766</v>
+        <v>-7.607452804809</v>
       </c>
       <c r="F209" t="n">
         <v>-28.01413821889418</v>
       </c>
       <c r="G209" t="n">
-        <v>-0.4308950012773538</v>
+        <v>-0.4309030730417995</v>
       </c>
       <c r="H209" t="n">
         <v>100.6930017200002</v>
@@ -45707,13 +45707,13 @@
         <v>-26.72176522045333</v>
       </c>
       <c r="E210" t="n">
-        <v>-9.241946894024998</v>
+        <v>-9.241938339858734</v>
       </c>
       <c r="F210" t="n">
         <v>-27.03415236602241</v>
       </c>
       <c r="G210" t="n">
-        <v>-2.711681952938827</v>
+        <v>-2.71167406087387</v>
       </c>
       <c r="H210" t="n">
         <v>88.54100235891897</v>
@@ -45739,7 +45739,7 @@
         <v>-27.28512988836156</v>
       </c>
       <c r="E211" t="n">
-        <v>-7.893973574240542</v>
+        <v>-7.893982258126419</v>
       </c>
       <c r="F211" t="n">
         <v>-31.35418360746799</v>
@@ -45803,13 +45803,13 @@
         <v>-32.08351066583373</v>
       </c>
       <c r="E213" t="n">
-        <v>-6.390539985580757</v>
+        <v>-6.390548149228259</v>
       </c>
       <c r="F213" t="n">
         <v>-36.81710406455739</v>
       </c>
       <c r="G213" t="n">
-        <v>-0.6188002002239346</v>
+        <v>-0.6188081582501281</v>
       </c>
       <c r="H213" t="n">
         <v>101.0606230012067</v>
@@ -45867,13 +45867,13 @@
         <v>-31.69662302286084</v>
       </c>
       <c r="E215" t="n">
-        <v>-5.981569662750863</v>
+        <v>-5.981578347866867</v>
       </c>
       <c r="F215" t="n">
         <v>-35.00641823830535</v>
       </c>
       <c r="G215" t="n">
-        <v>-4.171881583451709</v>
+        <v>-4.171889360138847</v>
       </c>
       <c r="H215" t="n">
         <v>86.87857539273911</v>
@@ -45899,7 +45899,7 @@
         <v>-33.33333747254461</v>
       </c>
       <c r="E216" t="n">
-        <v>-6.459947047595593</v>
+        <v>-6.459955843676058</v>
       </c>
       <c r="F216" t="n">
         <v>-35.39603519665386</v>
@@ -45963,7 +45963,7 @@
         <v>-31.83196333000435</v>
       </c>
       <c r="E218" t="n">
-        <v>-7.687890327936886</v>
+        <v>-7.68788219992188</v>
       </c>
       <c r="F218" t="n">
         <v>-32.37436156607637</v>
@@ -46033,7 +46033,7 @@
         <v>-26.70043400693196</v>
       </c>
       <c r="G220" t="n">
-        <v>-7.221913463495833</v>
+        <v>-7.221905726259203</v>
       </c>
       <c r="H220" t="n">
         <v>107.9485799639777</v>
@@ -46065,7 +46065,7 @@
         <v>-27.85436837434032</v>
       </c>
       <c r="G221" t="n">
-        <v>-7.27609318254262</v>
+        <v>-7.276078275705611</v>
       </c>
       <c r="H221" t="n">
         <v>100.7819275777789</v>
@@ -46091,7 +46091,7 @@
         <v>-36.29064639593801</v>
       </c>
       <c r="E222" t="n">
-        <v>-7.84314091942816</v>
+        <v>-7.843132019864541</v>
       </c>
       <c r="F222" t="n">
         <v>-28.89180566823137</v>
@@ -46129,7 +46129,7 @@
         <v>-26.85507940336083</v>
       </c>
       <c r="G223" t="n">
-        <v>-10.6562456616022</v>
+        <v>-10.65625261812432</v>
       </c>
       <c r="H223" t="n">
         <v>100.0265892515791</v>
@@ -46161,7 +46161,7 @@
         <v>-23.84693377024153</v>
       </c>
       <c r="G224" t="n">
-        <v>-8.083786549827233</v>
+        <v>-8.083785907644659</v>
       </c>
       <c r="H224" t="n">
         <v>108.4021066095138</v>
@@ -46193,7 +46193,7 @@
         <v>-23.3081717190626</v>
       </c>
       <c r="G225" t="n">
-        <v>-6.198124218843004</v>
+        <v>-6.198108264191005</v>
       </c>
       <c r="H225" t="n">
         <v>102.435878276131</v>
@@ -46225,7 +46225,7 @@
         <v>-32.43559750352636</v>
       </c>
       <c r="G226" t="n">
-        <v>-6.148033829310229</v>
+        <v>-6.148041621968114</v>
       </c>
       <c r="H226" t="n">
         <v>95.15328519545527</v>
@@ -46251,13 +46251,13 @@
         <v>-34.85313456992967</v>
       </c>
       <c r="E227" t="n">
-        <v>-8.171498781349463</v>
+        <v>-8.1714896278546</v>
       </c>
       <c r="F227" t="n">
         <v>-32.55395806851909</v>
       </c>
       <c r="G227" t="n">
-        <v>-6.912509731121618</v>
+        <v>-6.91252567983417</v>
       </c>
       <c r="H227" t="n">
         <v>77.01610443999401</v>
@@ -46283,13 +46283,13 @@
         <v>-36.55056678989862</v>
       </c>
       <c r="E228" t="n">
-        <v>-2.460506794340878</v>
+        <v>-2.460515871778712</v>
       </c>
       <c r="F228" t="n">
         <v>-33.03285408680733</v>
       </c>
       <c r="G228" t="n">
-        <v>-4.723286234245117</v>
+        <v>-4.723294512346953</v>
       </c>
       <c r="H228" t="n">
         <v>77.41683291570176</v>
@@ -46315,13 +46315,13 @@
         <v>-37.24916312288149</v>
       </c>
       <c r="E229" t="n">
-        <v>-3.495035167181182</v>
+        <v>-3.495026259081291</v>
       </c>
       <c r="F229" t="n">
         <v>-38.67234368945173</v>
       </c>
       <c r="G229" t="n">
-        <v>-6.23841041819182</v>
+        <v>-6.238418605092876</v>
       </c>
       <c r="H229" t="n">
         <v>72.01618573078785</v>
@@ -46353,7 +46353,7 @@
         <v>-40.67977613483576</v>
       </c>
       <c r="G230" t="n">
-        <v>-8.235102601298294</v>
+        <v>-8.235095143331449</v>
       </c>
       <c r="H230" t="n">
         <v>64.56839752173443</v>
@@ -46379,13 +46379,13 @@
         <v>-37.52585712120092</v>
       </c>
       <c r="E231" t="n">
-        <v>0.04553419329549335</v>
+        <v>0.04555280190197131</v>
       </c>
       <c r="F231" t="n">
         <v>-36.82532653673968</v>
       </c>
       <c r="G231" t="n">
-        <v>-7.581518060630521</v>
+        <v>-7.581525606214157</v>
       </c>
       <c r="H231" t="n">
         <v>54.87430225307104</v>
@@ -46417,7 +46417,7 @@
         <v>-39.58248098284007</v>
       </c>
       <c r="G232" t="n">
-        <v>-5.920876570197042</v>
+        <v>-5.920884290780492</v>
       </c>
       <c r="H232" t="n">
         <v>42.95023242456983</v>
@@ -46449,7 +46449,7 @@
         <v>-37.74290081852664</v>
       </c>
       <c r="G233" t="n">
-        <v>-7.84509988930675</v>
+        <v>-7.845092375919105</v>
       </c>
       <c r="H233" t="n">
         <v>31.20220243440443</v>
@@ -46475,13 +46475,13 @@
         <v>-37.23450483839871</v>
       </c>
       <c r="E234" t="n">
-        <v>0.09195250322659998</v>
+        <v>0.09194310401834382</v>
       </c>
       <c r="F234" t="n">
         <v>-38.63636103394656</v>
       </c>
       <c r="G234" t="n">
-        <v>-6.78956868988656</v>
+        <v>-6.789576929754382</v>
       </c>
       <c r="H234" t="n">
         <v>36.77451609649452</v>
@@ -46507,13 +46507,13 @@
         <v>-34.25161045286568</v>
       </c>
       <c r="E235" t="n">
-        <v>2.665208703368349</v>
+        <v>2.665199040303001</v>
       </c>
       <c r="F235" t="n">
         <v>-35.84453808293154</v>
       </c>
       <c r="G235" t="n">
-        <v>-3.676391944864155</v>
+        <v>-3.67639163105058</v>
       </c>
       <c r="H235" t="n">
         <v>44.01268886295892</v>
@@ -46609,7 +46609,7 @@
         <v>-41.6571487373118</v>
       </c>
       <c r="G238" t="n">
-        <v>-4.419213318578863</v>
+        <v>-4.419205170020679</v>
       </c>
       <c r="H238" t="n">
         <v>30.13929691573842</v>
@@ -46635,13 +46635,13 @@
         <v>-33.56353240626703</v>
       </c>
       <c r="E239" t="n">
-        <v>1.693959968986869</v>
+        <v>1.693950400277155</v>
       </c>
       <c r="F239" t="n">
         <v>-43.07445745551136</v>
       </c>
       <c r="G239" t="n">
-        <v>-5.901618930685871</v>
+        <v>-5.901626815877281</v>
       </c>
       <c r="H239" t="n">
         <v>11.90330802341504</v>
@@ -46673,7 +46673,7 @@
         <v>-41.94381402432754</v>
       </c>
       <c r="G240" t="n">
-        <v>-5.248220291782069</v>
+        <v>-5.24821227749892</v>
       </c>
       <c r="H240" t="n">
         <v>14.92523692770091</v>
@@ -46705,7 +46705,7 @@
         <v>-39.35091012724563</v>
       </c>
       <c r="G241" t="n">
-        <v>-4.898697568503607</v>
+        <v>-4.898689541145263</v>
       </c>
       <c r="H241" t="n">
         <v>17.4900219142698</v>
@@ -46859,7 +46859,7 @@
         <v>-31.36067022065163</v>
       </c>
       <c r="E246" t="n">
-        <v>-3.292501612801146</v>
+        <v>-3.292492664437496</v>
       </c>
       <c r="F246" t="n">
         <v>-44.01419291641084</v>
@@ -46961,7 +46961,7 @@
         <v>-44.79623457080469</v>
       </c>
       <c r="G249" t="n">
-        <v>-9.915348039572402</v>
+        <v>-9.915340706749021</v>
       </c>
       <c r="H249" t="n">
         <v>28.24667177580864</v>
@@ -46987,7 +46987,7 @@
         <v>-32.32134575251007</v>
       </c>
       <c r="E250" t="n">
-        <v>-2.799844619809422</v>
+        <v>-2.79985382220842</v>
       </c>
       <c r="F250" t="n">
         <v>-45.22397009414632</v>
@@ -47019,13 +47019,13 @@
         <v>-31.40301388027185</v>
       </c>
       <c r="E251" t="n">
-        <v>-3.107483694785163</v>
+        <v>-3.107492906488285</v>
       </c>
       <c r="F251" t="n">
         <v>-44.10021926081409</v>
       </c>
       <c r="G251" t="n">
-        <v>-8.432388439330673</v>
+        <v>-8.432380914658189</v>
       </c>
       <c r="H251" t="n">
         <v>30.84309419368414</v>
@@ -47083,7 +47083,7 @@
         <v>-30.50687043040482</v>
       </c>
       <c r="E253" t="n">
-        <v>-3.657896195424548</v>
+        <v>-3.657905370458425</v>
       </c>
       <c r="F253" t="n">
         <v>-43.2534700274485</v>
@@ -47121,7 +47121,7 @@
         <v>-42.68745318611167</v>
       </c>
       <c r="G254" t="n">
-        <v>-8.953564788171864</v>
+        <v>-8.95355739490059</v>
       </c>
       <c r="H254" t="n">
         <v>38.11965215773809</v>
@@ -47147,7 +47147,7 @@
         <v>-28.36398693106126</v>
       </c>
       <c r="E255" t="n">
-        <v>-11.0265174091879</v>
+        <v>-11.02652519290564</v>
       </c>
       <c r="F255" t="n">
         <v>-40.86610764775907</v>
@@ -47179,7 +47179,7 @@
         <v>-28.43902401807832</v>
       </c>
       <c r="E256" t="n">
-        <v>-11.16641471354466</v>
+        <v>-11.16642255217313</v>
       </c>
       <c r="F256" t="n">
         <v>-40.68221552091195</v>
@@ -47281,7 +47281,7 @@
         <v>-39.33288226479107</v>
       </c>
       <c r="G259" t="n">
-        <v>-4.231148930266126</v>
+        <v>-4.231140867430727</v>
       </c>
       <c r="H259" t="n">
         <v>17.21369395430563</v>
@@ -47313,7 +47313,7 @@
         <v>-40.19249724712132</v>
       </c>
       <c r="G260" t="n">
-        <v>-3.875158357386355</v>
+        <v>-3.87515025945846</v>
       </c>
       <c r="H260" t="n">
         <v>14.30151569558824</v>
@@ -47345,7 +47345,7 @@
         <v>-38.08339672481785</v>
       </c>
       <c r="G261" t="n">
-        <v>-2.796236792638485</v>
+        <v>-2.796228547260515</v>
       </c>
       <c r="H261" t="n">
         <v>23.4240208407088</v>
@@ -47435,13 +47435,13 @@
         <v>-30.63477422966672</v>
       </c>
       <c r="E264" t="n">
-        <v>-8.975257928817172</v>
+        <v>-8.975249933684793</v>
       </c>
       <c r="F264" t="n">
         <v>-39.47368508745812</v>
       </c>
       <c r="G264" t="n">
-        <v>-3.964318621962881</v>
+        <v>-3.964310585570097</v>
       </c>
       <c r="H264" t="n">
         <v>19.41679997949015</v>
@@ -47505,7 +47505,7 @@
         <v>-39.77876359755991</v>
       </c>
       <c r="G266" t="n">
-        <v>-4.653323444895163</v>
+        <v>-4.653331466701482</v>
       </c>
       <c r="H266" t="n">
         <v>-6.341747425683231</v>
@@ -47531,7 +47531,7 @@
         <v>-29.24205512377247</v>
       </c>
       <c r="E267" t="n">
-        <v>-11.37217723657323</v>
+        <v>-11.3721850694539</v>
       </c>
       <c r="F267" t="n">
         <v>-35.66993037243454</v>
@@ -47595,7 +47595,7 @@
         <v>-31.51544377109349</v>
       </c>
       <c r="E269" t="n">
-        <v>-16.3552932302255</v>
+        <v>-16.35530046410454</v>
       </c>
       <c r="F269" t="n">
         <v>-38.0038388594275</v>
@@ -47819,7 +47819,7 @@
         <v>-30.96296522352431</v>
       </c>
       <c r="E276" t="n">
-        <v>-11.7115071824372</v>
+        <v>-11.71149935583935</v>
       </c>
       <c r="F276" t="n">
         <v>-34.97199627598184</v>
@@ -47889,7 +47889,7 @@
         <v>-29.18918712719066</v>
       </c>
       <c r="G278" t="n">
-        <v>1.203260337258172</v>
+        <v>1.203251246739723</v>
       </c>
       <c r="H278" t="n">
         <v>-16.10060838234497</v>
@@ -47915,13 +47915,13 @@
         <v>-28.54230449507224</v>
       </c>
       <c r="E279" t="n">
-        <v>-10.61025096954303</v>
+        <v>-10.61024304532102</v>
       </c>
       <c r="F279" t="n">
         <v>-31.85478688860097</v>
       </c>
       <c r="G279" t="n">
-        <v>-1.206441403179814</v>
+        <v>-1.206450108162938</v>
       </c>
       <c r="H279" t="n">
         <v>-20.91819495708994</v>
@@ -48011,7 +48011,7 @@
         <v>-31.95619725003812</v>
       </c>
       <c r="E282" t="n">
-        <v>-8.466570285765041</v>
+        <v>-8.466562074090877</v>
       </c>
       <c r="F282" t="n">
         <v>-36.50442544264273</v>
@@ -48043,7 +48043,7 @@
         <v>-34.78050768782048</v>
       </c>
       <c r="E283" t="n">
-        <v>-8.900954788972681</v>
+        <v>-8.900946581418934</v>
       </c>
       <c r="F283" t="n">
         <v>-36.51074312329671</v>
@@ -48107,13 +48107,13 @@
         <v>-33.6261564988414</v>
       </c>
       <c r="E285" t="n">
-        <v>-6.403066080333931</v>
+        <v>-6.403057485981378</v>
       </c>
       <c r="F285" t="n">
         <v>-43.19450633885003</v>
       </c>
       <c r="G285" t="n">
-        <v>8.638869470524856</v>
+        <v>8.638879348934726</v>
       </c>
       <c r="H285" t="n">
         <v>-22.43266500066909</v>
@@ -48209,7 +48209,7 @@
         <v>-40.31249999999999</v>
       </c>
       <c r="G288" t="n">
-        <v>8.824660078984214</v>
+        <v>8.824669864978496</v>
       </c>
       <c r="H288" t="n">
         <v>-15.80145910348596</v>
@@ -48235,13 +48235,13 @@
         <v>-27.07006549980937</v>
       </c>
       <c r="E289" t="n">
-        <v>-1.789447632229446</v>
+        <v>-1.789457213034507</v>
       </c>
       <c r="F289" t="n">
         <v>-36.1724497836834</v>
       </c>
       <c r="G289" t="n">
-        <v>11.12805096008431</v>
+        <v>11.12804077466287</v>
       </c>
       <c r="H289" t="n">
         <v>-15.80435876850455</v>
@@ -48267,13 +48267,13 @@
         <v>-26.88853708679655</v>
       </c>
       <c r="E290" t="n">
-        <v>-1.419444239463907</v>
+        <v>-1.419453836500251</v>
       </c>
       <c r="F290" t="n">
         <v>-38.08921600038258</v>
       </c>
       <c r="G290" t="n">
-        <v>12.82625316981061</v>
+        <v>12.82624279146409</v>
       </c>
       <c r="H290" t="n">
         <v>-18.49578771778532</v>
@@ -48427,7 +48427,7 @@
         <v>-30.8609987086815</v>
       </c>
       <c r="E295" t="n">
-        <v>-6.683905083631759</v>
+        <v>-6.68391401909465</v>
       </c>
       <c r="F295" t="n">
         <v>-41.6964609053498</v>
@@ -48593,7 +48593,7 @@
         <v>-45.71528273452657</v>
       </c>
       <c r="G300" t="n">
-        <v>14.45538481947792</v>
+        <v>14.45539545234036</v>
       </c>
       <c r="H300" t="n">
         <v>-39.12642164276215</v>
@@ -48619,13 +48619,13 @@
         <v>-32.60315788154286</v>
       </c>
       <c r="E301" t="n">
-        <v>-1.915399321961297</v>
+        <v>-1.915389976623461</v>
       </c>
       <c r="F301" t="n">
         <v>-44.79178880131202</v>
       </c>
       <c r="G301" t="n">
-        <v>16.79747672337286</v>
+        <v>16.79748773752852</v>
       </c>
       <c r="H301" t="n">
         <v>-35.27146510631234</v>
@@ -48657,7 +48657,7 @@
         <v>-43.0791637679723</v>
       </c>
       <c r="G302" t="n">
-        <v>18.74306630347453</v>
+        <v>18.74305491482327</v>
       </c>
       <c r="H302" t="n">
         <v>-31.04994046679992</v>
@@ -48747,7 +48747,7 @@
         <v>-27.57111994645234</v>
       </c>
       <c r="E305" t="n">
-        <v>3.149916020112609</v>
+        <v>3.14992657515003</v>
       </c>
       <c r="F305" t="n">
         <v>-41.52879384528914</v>
@@ -48875,13 +48875,13 @@
         <v>-27.55384073228704</v>
       </c>
       <c r="E309" t="n">
-        <v>-1.820419341165691</v>
+        <v>-1.820409767954434</v>
       </c>
       <c r="F309" t="n">
         <v>-46.45314619747551</v>
       </c>
       <c r="G309" t="n">
-        <v>28.87734715522496</v>
+        <v>28.87736012984552</v>
       </c>
       <c r="H309" t="n">
         <v>-36.46017585048106</v>
@@ -48907,13 +48907,13 @@
         <v>-28.12327812449581</v>
       </c>
       <c r="E310" t="n">
-        <v>-2.189961319395339</v>
+        <v>-2.189970868730429</v>
       </c>
       <c r="F310" t="n">
         <v>-43.11211700553351</v>
       </c>
       <c r="G310" t="n">
-        <v>24.04331600956311</v>
+        <v>24.04330394004244</v>
       </c>
       <c r="H310" t="n">
         <v>-35.62972636042486</v>
@@ -48977,7 +48977,7 @@
         <v>-42.96904798556517</v>
       </c>
       <c r="G312" t="n">
-        <v>21.35176776838568</v>
+        <v>21.35177929989596</v>
       </c>
       <c r="H312" t="n">
         <v>-39.16467071785878</v>
@@ -49003,7 +49003,7 @@
         <v>-23.67802924944825</v>
       </c>
       <c r="E313" t="n">
-        <v>-7.167713321274871</v>
+        <v>-7.167704674027875</v>
       </c>
       <c r="F313" t="n">
         <v>-43.89662309077295</v>
@@ -49067,7 +49067,7 @@
         <v>-25.69444651405009</v>
       </c>
       <c r="E315" t="n">
-        <v>-7.8052930518827</v>
+        <v>-7.805284449640915</v>
       </c>
       <c r="F315" t="n">
         <v>-44.86300958919328</v>
@@ -49105,7 +49105,7 @@
         <v>-45.28779464855661</v>
       </c>
       <c r="G316" t="n">
-        <v>18.14939600670908</v>
+        <v>18.1494071185649</v>
       </c>
       <c r="H316" t="n">
         <v>-43.54679306508746</v>
@@ -49131,13 +49131,13 @@
         <v>-30.79507707567796</v>
       </c>
       <c r="E317" t="n">
-        <v>-12.54196405882723</v>
+        <v>-12.54195618625559</v>
       </c>
       <c r="F317" t="n">
         <v>-47.19959819731769</v>
       </c>
       <c r="G317" t="n">
-        <v>17.06813866501322</v>
+        <v>17.06812777258078</v>
       </c>
       <c r="H317" t="n">
         <v>-47.77185344404541</v>
@@ -49195,7 +49195,7 @@
         <v>-28.38817660877887</v>
       </c>
       <c r="E319" t="n">
-        <v>-14.69882014884166</v>
+        <v>-14.69881249627694</v>
       </c>
       <c r="F319" t="n">
         <v>-46.19366314291567</v>
@@ -49227,13 +49227,13 @@
         <v>-30.04980322748305</v>
       </c>
       <c r="E320" t="n">
-        <v>-11.79834711640336</v>
+        <v>-11.798339142925</v>
       </c>
       <c r="F320" t="n">
         <v>-45.88515934593683</v>
       </c>
       <c r="G320" t="n">
-        <v>18.27003278657746</v>
+        <v>18.27002168373071</v>
       </c>
       <c r="H320" t="n">
         <v>-57.36521243655967</v>
@@ -49393,7 +49393,7 @@
         <v>-44.55750636787307</v>
       </c>
       <c r="G325" t="n">
-        <v>21.81860743612587</v>
+        <v>21.81861921980548</v>
       </c>
       <c r="H325" t="n">
         <v>-44.02443166579163</v>
@@ -49419,13 +49419,13 @@
         <v>-30.20774464959777</v>
       </c>
       <c r="E326" t="n">
-        <v>-12.61553365320609</v>
+        <v>-12.61552578725684</v>
       </c>
       <c r="F326" t="n">
         <v>-43.7062933475497</v>
       </c>
       <c r="G326" t="n">
-        <v>23.89423855416915</v>
+        <v>23.89425058162082</v>
       </c>
       <c r="H326" t="n">
         <v>-40.67477660339317</v>
@@ -49451,13 +49451,13 @@
         <v>-28.4168560528505</v>
       </c>
       <c r="E327" t="n">
-        <v>-11.23824265940424</v>
+        <v>-11.2382507263617</v>
       </c>
       <c r="F327" t="n">
         <v>-42.01795096708333</v>
       </c>
       <c r="G327" t="n">
-        <v>27.01293197887475</v>
+        <v>27.0129194209342</v>
       </c>
       <c r="H327" t="n">
         <v>-39.58842358779834</v>
@@ -49483,7 +49483,7 @@
         <v>-26.30973188082025</v>
       </c>
       <c r="E328" t="n">
-        <v>-7.835551445906363</v>
+        <v>-7.835560144670373</v>
       </c>
       <c r="F328" t="n">
         <v>-39.07111277288545</v>
@@ -49515,7 +49515,7 @@
         <v>-26.77945952370142</v>
       </c>
       <c r="E329" t="n">
-        <v>-4.355889351430875</v>
+        <v>-4.35587998969117</v>
       </c>
       <c r="F329" t="n">
         <v>-37.83128971446084</v>
@@ -49547,13 +49547,13 @@
         <v>-24.20228964506092</v>
       </c>
       <c r="E330" t="n">
-        <v>-2.263212839202788</v>
+        <v>-2.263202999119251</v>
       </c>
       <c r="F330" t="n">
         <v>-40.89319237117981</v>
       </c>
       <c r="G330" t="n">
-        <v>29.87863864934677</v>
+        <v>29.87862538191015</v>
       </c>
       <c r="H330" t="n">
         <v>-40.33758035437396</v>
@@ -49617,7 +49617,7 @@
         <v>-41.81298585856907</v>
       </c>
       <c r="G332" t="n">
-        <v>26.43221168776087</v>
+        <v>26.43219895670177</v>
       </c>
       <c r="H332" t="n">
         <v>-45.57062522979041</v>
@@ -49675,7 +49675,7 @@
         <v>-19.98714991312431</v>
       </c>
       <c r="E334" t="n">
-        <v>-2.882084250995653</v>
+        <v>-2.88207449406167</v>
       </c>
       <c r="F334" t="n">
         <v>-41.09851185636433</v>
@@ -49707,13 +49707,13 @@
         <v>-16.57894431388936</v>
       </c>
       <c r="E335" t="n">
-        <v>-1.332080853007134</v>
+        <v>-1.332090723583423</v>
       </c>
       <c r="F335" t="n">
         <v>-37.75945257518652</v>
       </c>
       <c r="G335" t="n">
-        <v>32.04423288765659</v>
+        <v>32.04424631615452</v>
       </c>
       <c r="H335" t="n">
         <v>-44.60865172604881</v>
@@ -49835,13 +49835,13 @@
         <v>-25.53582422398183</v>
       </c>
       <c r="E339" t="n">
-        <v>-4.372171369682365</v>
+        <v>-4.37218089879411</v>
       </c>
       <c r="F339" t="n">
         <v>-41.2774749891061</v>
       </c>
       <c r="G339" t="n">
-        <v>18.00929099618114</v>
+        <v>18.00930260936568</v>
       </c>
       <c r="H339" t="n">
         <v>-51.0275685005831</v>
@@ -49867,13 +49867,13 @@
         <v>-23.0622628159228</v>
       </c>
       <c r="E340" t="n">
-        <v>-3.0340603821715</v>
+        <v>-3.034070394712185</v>
       </c>
       <c r="F340" t="n">
         <v>-39.3328445504433</v>
       </c>
       <c r="G340" t="n">
-        <v>21.60856412861356</v>
+        <v>21.60855183551538</v>
       </c>
       <c r="H340" t="n">
         <v>-48.45177004972177</v>
@@ -49963,13 +49963,13 @@
         <v>-23.89099852905706</v>
       </c>
       <c r="E343" t="n">
-        <v>-0.6231572275657182</v>
+        <v>-0.6231467017805636</v>
       </c>
       <c r="F343" t="n">
         <v>-38.56778592704874</v>
       </c>
       <c r="G343" t="n">
-        <v>16.72655504620151</v>
+        <v>16.72654359220733</v>
       </c>
       <c r="H343" t="n">
         <v>-48.263368464608</v>
@@ -50027,7 +50027,7 @@
         <v>-17.2627251407637</v>
       </c>
       <c r="E345" t="n">
-        <v>4.916314993451909</v>
+        <v>4.916302916447957</v>
       </c>
       <c r="F345" t="n">
         <v>-32.87099253590478</v>
@@ -50059,7 +50059,7 @@
         <v>-21.78477522759588</v>
       </c>
       <c r="E346" t="n">
-        <v>1.183745152549909</v>
+        <v>1.183733791213348</v>
       </c>
       <c r="F346" t="n">
         <v>-35.87239191644272</v>
@@ -50257,7 +50257,7 @@
         <v>-30.979665054058</v>
       </c>
       <c r="G352" t="n">
-        <v>9.801756136726736</v>
+        <v>9.801745550800645</v>
       </c>
       <c r="H352" t="n">
         <v>-51.15160485874554</v>
@@ -50289,7 +50289,7 @@
         <v>-31.89830918797701</v>
       </c>
       <c r="G353" t="n">
-        <v>10.51758966122418</v>
+        <v>10.51757889287628</v>
       </c>
       <c r="H353" t="n">
         <v>-51.15160485874554</v>
@@ -50347,7 +50347,7 @@
         <v>-27.28494884671743</v>
       </c>
       <c r="E355" t="n">
-        <v>4.792385488267725</v>
+        <v>4.792392368889042</v>
       </c>
       <c r="F355" t="n">
         <v>-27.42354135671774</v>
@@ -50379,13 +50379,13 @@
         <v>-25.3721249509532</v>
       </c>
       <c r="E356" t="n">
-        <v>13.24400678497606</v>
+        <v>13.24401421734134</v>
       </c>
       <c r="F356" t="n">
         <v>-24.46144183427424</v>
       </c>
       <c r="G356" t="n">
-        <v>16.88588990711302</v>
+        <v>16.88590156582772</v>
       </c>
       <c r="H356" t="n">
         <v>-47.48545500046233</v>
@@ -50507,7 +50507,7 @@
         <v>-21.90601946492874</v>
       </c>
       <c r="E360" t="n">
-        <v>11.65991396441235</v>
+        <v>11.65992104672113</v>
       </c>
       <c r="F360" t="n">
         <v>-25.74782005433018</v>
@@ -50571,7 +50571,7 @@
         <v>-20.94915357686705</v>
       </c>
       <c r="E362" t="n">
-        <v>10.45348008305296</v>
+        <v>10.4534869862259</v>
       </c>
       <c r="F362" t="n">
         <v>-24.44530491228184</v>
@@ -50603,7 +50603,7 @@
         <v>-22.84366784680649</v>
       </c>
       <c r="E363" t="n">
-        <v>7.26410489731748</v>
+        <v>7.264098320135837</v>
       </c>
       <c r="F363" t="n">
         <v>-29.10251687659797</v>
@@ -50667,7 +50667,7 @@
         <v>-24.28571252479959</v>
       </c>
       <c r="E365" t="n">
-        <v>5.415672922114378</v>
+        <v>5.415679395542905</v>
       </c>
       <c r="F365" t="n">
         <v>-28.71211138002472</v>
@@ -50699,7 +50699,7 @@
         <v>-23.19622116035478</v>
       </c>
       <c r="E366" t="n">
-        <v>8.128497798204526</v>
+        <v>8.128490980816538</v>
       </c>
       <c r="F366" t="n">
         <v>-26.12058438561582</v>
@@ -50795,13 +50795,13 @@
         <v>-22.73361362756691</v>
       </c>
       <c r="E369" t="n">
-        <v>13.56803192476519</v>
+        <v>13.56802429660819</v>
       </c>
       <c r="F369" t="n">
         <v>-26.71135046405951</v>
       </c>
       <c r="G369" t="n">
-        <v>17.18353782537481</v>
+        <v>17.18354968966769</v>
       </c>
       <c r="H369" t="n">
         <v>-61.07611818254843</v>
@@ -50865,7 +50865,7 @@
         <v>-25.2692804931725</v>
       </c>
       <c r="G371" t="n">
-        <v>17.11213568001337</v>
+        <v>17.11212390813579</v>
       </c>
       <c r="H371" t="n">
         <v>-60.87988788615164</v>
@@ -50923,13 +50923,13 @@
         <v>-24.32815028665871</v>
       </c>
       <c r="E373" t="n">
-        <v>12.06946184813773</v>
+        <v>12.0694693473598</v>
       </c>
       <c r="F373" t="n">
         <v>-28.85148269226424</v>
       </c>
       <c r="G373" t="n">
-        <v>15.0693482521175</v>
+        <v>15.06935979463098</v>
       </c>
       <c r="H373" t="n">
         <v>-63.36000023818598</v>
@@ -51025,7 +51025,7 @@
         <v>-28.413604225734</v>
       </c>
       <c r="G376" t="n">
-        <v>11.18289445739504</v>
+        <v>11.18288318627598</v>
       </c>
       <c r="H376" t="n">
         <v>-64.01993426427576</v>
@@ -51057,7 +51057,7 @@
         <v>-26.25635881430726</v>
       </c>
       <c r="G377" t="n">
-        <v>15.85957219958973</v>
+        <v>15.85956035145704</v>
       </c>
       <c r="H377" t="n">
         <v>-62.27387136240345</v>
@@ -51115,7 +51115,7 @@
         <v>-24.13010945252098</v>
       </c>
       <c r="E379" t="n">
-        <v>12.04284864922218</v>
+        <v>12.0428569162337</v>
       </c>
       <c r="F379" t="n">
         <v>-21.73281609041534</v>
@@ -51217,7 +51217,7 @@
         <v>-23.55814201887264</v>
       </c>
       <c r="G382" t="n">
-        <v>18.89760002530356</v>
+        <v>18.89761247784627</v>
       </c>
       <c r="H382" t="n">
         <v>-59.06648593293944</v>
@@ -51243,13 +51243,13 @@
         <v>-29.13668595833225</v>
       </c>
       <c r="E383" t="n">
-        <v>7.127772389347142</v>
+        <v>7.127779850578642</v>
       </c>
       <c r="F383" t="n">
         <v>-29.39840880790665</v>
       </c>
       <c r="G383" t="n">
-        <v>14.60105360211445</v>
+        <v>14.60106526729248</v>
       </c>
       <c r="H383" t="n">
         <v>-63.74968210856202</v>
@@ -51275,7 +51275,7 @@
         <v>-31.12208767584927</v>
       </c>
       <c r="E384" t="n">
-        <v>5.818247463604265</v>
+        <v>5.818240155712728</v>
       </c>
       <c r="F384" t="n">
         <v>-32.58526100040748</v>
@@ -51313,7 +51313,7 @@
         <v>-30.70830099386722</v>
       </c>
       <c r="G385" t="n">
-        <v>13.30602734449839</v>
+        <v>13.30601607935962</v>
       </c>
       <c r="H385" t="n">
         <v>-66.09785963800563</v>
@@ -51371,13 +51371,13 @@
         <v>-26.75635196626188</v>
       </c>
       <c r="E387" t="n">
-        <v>6.337682199015493</v>
+        <v>6.33768942164834</v>
       </c>
       <c r="F387" t="n">
         <v>-27.73670637603035</v>
       </c>
       <c r="G387" t="n">
-        <v>10.60266510369081</v>
+        <v>10.60265427047231</v>
       </c>
       <c r="H387" t="n">
         <v>-65.63790747729136</v>
@@ -51409,7 +51409,7 @@
         <v>-25.50012389260924</v>
       </c>
       <c r="G388" t="n">
-        <v>13.79508390008357</v>
+        <v>13.79509512771688</v>
       </c>
       <c r="H388" t="n">
         <v>-64.53946245251012</v>
@@ -51435,13 +51435,13 @@
         <v>-28.43965983222077</v>
       </c>
       <c r="E389" t="n">
-        <v>3.158053617653644</v>
+        <v>3.1580608161486</v>
       </c>
       <c r="F389" t="n">
         <v>-27.92992853630824</v>
       </c>
       <c r="G389" t="n">
-        <v>14.09152370384321</v>
+        <v>14.09151236472803</v>
       </c>
       <c r="H389" t="n">
         <v>-66.45546781840915</v>
@@ -51467,13 +51467,13 @@
         <v>-27.36356923125641</v>
       </c>
       <c r="E390" t="n">
-        <v>6.169301512354353</v>
+        <v>6.169308920977867</v>
       </c>
       <c r="F390" t="n">
         <v>-25.73402100163619</v>
       </c>
       <c r="G390" t="n">
-        <v>14.41569148156412</v>
+        <v>14.41568011023115</v>
       </c>
       <c r="H390" t="n">
         <v>-66.94776163626966</v>
@@ -51499,7 +51499,7 @@
         <v>-27.97047902954666</v>
       </c>
       <c r="E391" t="n">
-        <v>3.880493928511441</v>
+        <v>3.880500882192162</v>
       </c>
       <c r="F391" t="n">
         <v>-30.45361073235145</v>
@@ -51537,7 +51537,7 @@
         <v>-34.6966578795431</v>
       </c>
       <c r="G392" t="n">
-        <v>6.644929854007509</v>
+        <v>6.644940199991112</v>
       </c>
       <c r="H392" t="n">
         <v>-70.29248220397415</v>
@@ -51563,13 +51563,13 @@
         <v>-35.30269977477008</v>
       </c>
       <c r="E393" t="n">
-        <v>-2.038462945038977</v>
+        <v>-2.038469494495021</v>
       </c>
       <c r="F393" t="n">
         <v>-41.98987931194888</v>
       </c>
       <c r="G393" t="n">
-        <v>5.712973775205987</v>
+        <v>5.71296357748774</v>
       </c>
       <c r="H393" t="n">
         <v>-72.03757777841206</v>
@@ -51595,13 +51595,13 @@
         <v>-30.55953661004619</v>
       </c>
       <c r="E394" t="n">
-        <v>-0.1668970655057334</v>
+        <v>-0.1668904930419157</v>
       </c>
       <c r="F394" t="n">
         <v>-36.04969516561641</v>
       </c>
       <c r="G394" t="n">
-        <v>5.573188073951862</v>
+        <v>5.573178091119124</v>
       </c>
       <c r="H394" t="n">
         <v>-71.34296508383973</v>
@@ -51627,7 +51627,7 @@
         <v>-26.6316594977735</v>
       </c>
       <c r="E395" t="n">
-        <v>1.014306215598793</v>
+        <v>1.014299414847986</v>
       </c>
       <c r="F395" t="n">
         <v>-34.01675506515429</v>
@@ -51691,7 +51691,7 @@
         <v>-22.62996984260145</v>
       </c>
       <c r="E397" t="n">
-        <v>4.392318912024984</v>
+        <v>4.392311829375939</v>
       </c>
       <c r="F397" t="n">
         <v>-32.47330687594106</v>
@@ -51723,7 +51723,7 @@
         <v>-18.38461802555964</v>
       </c>
       <c r="E398" t="n">
-        <v>8.674330050879009</v>
+        <v>8.674322733776552</v>
       </c>
       <c r="F398" t="n">
         <v>-26.03086679746717</v>
@@ -51793,7 +51793,7 @@
         <v>-25.63758140687569</v>
       </c>
       <c r="G400" t="n">
-        <v>8.347715817465362</v>
+        <v>8.347726479863283</v>
       </c>
       <c r="H400" t="n">
         <v>-65.36158938197161</v>
@@ -51825,7 +51825,7 @@
         <v>-25.91368806155924</v>
       </c>
       <c r="G401" t="n">
-        <v>5.738151941372749</v>
+        <v>5.73816236738256</v>
       </c>
       <c r="H401" t="n">
         <v>-66.77216419841814</v>
@@ -51883,13 +51883,13 @@
         <v>-7.945423499897474</v>
       </c>
       <c r="E403" t="n">
-        <v>13.17263868232146</v>
+        <v>13.17264680156478</v>
       </c>
       <c r="F403" t="n">
         <v>-13.55808929093354</v>
       </c>
       <c r="G403" t="n">
-        <v>15.69574121395054</v>
+        <v>15.69572899384135</v>
       </c>
       <c r="H403" t="n">
         <v>-63.91718451774392</v>
@@ -51915,7 +51915,7 @@
         <v>-10.77751842338764</v>
       </c>
       <c r="E404" t="n">
-        <v>8.642973758231221</v>
+        <v>8.642981161077067</v>
       </c>
       <c r="F404" t="n">
         <v>-12.82665689655393</v>
@@ -52107,13 +52107,13 @@
         <v>-21.33238375936532</v>
       </c>
       <c r="E410" t="n">
-        <v>3.107196346569774</v>
+        <v>3.107189936007027</v>
       </c>
       <c r="F410" t="n">
         <v>-21.59166824801976</v>
       </c>
       <c r="G410" t="n">
-        <v>5.847544766048696</v>
+        <v>5.847534706283208</v>
       </c>
       <c r="H410" t="n">
         <v>-71.00092030889978</v>
@@ -52145,7 +52145,7 @@
         <v>-23.4112273561191</v>
       </c>
       <c r="G411" t="n">
-        <v>7.99620785689179</v>
+        <v>7.996218155048962</v>
       </c>
       <c r="H411" t="n">
         <v>-70.48958646991004</v>
@@ -52171,7 +52171,7 @@
         <v>-24.71146980834059</v>
       </c>
       <c r="E412" t="n">
-        <v>-2.726841153927861</v>
+        <v>-2.726829609288295</v>
       </c>
       <c r="F412" t="n">
         <v>-24.11161503408237</v>
@@ -52267,13 +52267,13 @@
         <v>-22.53923464985733</v>
       </c>
       <c r="E415" t="n">
-        <v>-1.847951917291468</v>
+        <v>-1.847963577079392</v>
       </c>
       <c r="F415" t="n">
         <v>-20.80552533209156</v>
       </c>
       <c r="G415" t="n">
-        <v>7.316138780590764</v>
+        <v>7.31614843375159</v>
       </c>
       <c r="H415" t="n">
         <v>-70.72855367660009</v>
@@ -52299,7 +52299,7 @@
         <v>-21.78288832645033</v>
       </c>
       <c r="E416" t="n">
-        <v>-3.412876137907805</v>
+        <v>-3.412864651995873</v>
       </c>
       <c r="F416" t="n">
         <v>-24.29865228356438</v>
@@ -52523,13 +52523,13 @@
         <v>-20.82066719519743</v>
       </c>
       <c r="E423" t="n">
-        <v>-5.578780694495011</v>
+        <v>-5.578786518450696</v>
       </c>
       <c r="F423" t="n">
         <v>-22.82890181163548</v>
       </c>
       <c r="G423" t="n">
-        <v>-0.7232805190683367</v>
+        <v>-0.7232893946104491</v>
       </c>
       <c r="H423" t="n">
         <v>-69.73572116248295</v>
@@ -52561,7 +52561,7 @@
         <v>-28.71681266182397</v>
       </c>
       <c r="G424" t="n">
-        <v>-6.59675696969183</v>
+        <v>-6.596764975419667</v>
       </c>
       <c r="H424" t="n">
         <v>-72.19502709891556</v>
@@ -52593,7 +52593,7 @@
         <v>-31.15545012423484</v>
       </c>
       <c r="G425" t="n">
-        <v>-5.259896490868588</v>
+        <v>-5.259904730487608</v>
       </c>
       <c r="H425" t="n">
         <v>-74.55197130553066</v>
@@ -52625,7 +52625,7 @@
         <v>-30.92938355917067</v>
       </c>
       <c r="G426" t="n">
-        <v>-6.768986318174663</v>
+        <v>-6.768978259326808</v>
       </c>
       <c r="H426" t="n">
         <v>-75.17025640944985</v>
@@ -52747,13 +52747,13 @@
         <v>-30.24650161641759</v>
       </c>
       <c r="E430" t="n">
-        <v>-10.80606292625648</v>
+        <v>-10.80605285953314</v>
       </c>
       <c r="F430" t="n">
         <v>-32.41098037149195</v>
       </c>
       <c r="G430" t="n">
-        <v>-3.659994152320223</v>
+        <v>-3.660002478738422</v>
       </c>
       <c r="H430" t="n">
         <v>-76.66848598030319</v>
@@ -52779,13 +52779,13 @@
         <v>-30.16501524682917</v>
       </c>
       <c r="E431" t="n">
-        <v>-12.13950456134066</v>
+        <v>-12.13949474993221</v>
       </c>
       <c r="F431" t="n">
         <v>-32.61940456242382</v>
       </c>
       <c r="G431" t="n">
-        <v>-4.721720235280513</v>
+        <v>-4.721728443432937</v>
       </c>
       <c r="H431" t="n">
         <v>-76.79521881319495</v>
@@ -52843,7 +52843,7 @@
         <v>-28.28217347291736</v>
       </c>
       <c r="E433" t="n">
-        <v>-13.65793860950155</v>
+        <v>-13.65794799810753</v>
       </c>
       <c r="F433" t="n">
         <v>-35.94838047268804</v>
@@ -52875,7 +52875,7 @@
         <v>-29.41176433922557</v>
       </c>
       <c r="E434" t="n">
-        <v>-15.05851917996379</v>
+        <v>-15.05852841627437</v>
       </c>
       <c r="F434" t="n">
         <v>-37.55248832154153</v>
@@ -52939,13 +52939,13 @@
         <v>-31.18556707365781</v>
       </c>
       <c r="E436" t="n">
-        <v>-18.02633419934322</v>
+        <v>-18.02632554975999</v>
       </c>
       <c r="F436" t="n">
         <v>-42.55076628068165</v>
       </c>
       <c r="G436" t="n">
-        <v>-6.585726987444507</v>
+        <v>-6.585718847033862</v>
       </c>
       <c r="H436" t="n">
         <v>-77.08725196671594</v>
@@ -53073,7 +53073,7 @@
         <v>-42.14920901985823</v>
       </c>
       <c r="G440" t="n">
-        <v>-9.341168683292222</v>
+        <v>-9.341176625179859</v>
       </c>
       <c r="H440" t="n">
         <v>-74.90425393909189</v>
@@ -53099,13 +53099,13 @@
         <v>-31.21424024348101</v>
       </c>
       <c r="E441" t="n">
-        <v>-19.20950236051181</v>
+        <v>-19.20949383577247</v>
       </c>
       <c r="F441" t="n">
         <v>-42.29934878455828</v>
       </c>
       <c r="G441" t="n">
-        <v>-10.06949204629482</v>
+        <v>-10.06949982476274</v>
       </c>
       <c r="H441" t="n">
         <v>-77.44613900123169</v>
@@ -53131,7 +53131,7 @@
         <v>-32.31746128627232</v>
       </c>
       <c r="E442" t="n">
-        <v>-20.9163266846164</v>
+        <v>-20.91631837289538</v>
       </c>
       <c r="F442" t="n">
         <v>-44.41396894882384</v>
@@ -53169,7 +53169,7 @@
         <v>-45.10528325008265</v>
       </c>
       <c r="G443" t="n">
-        <v>-11.74871442140775</v>
+        <v>-11.74872194887284</v>
       </c>
       <c r="H443" t="n">
         <v>-76.91231867772697</v>
@@ -53195,7 +53195,7 @@
         <v>-32.40506217564133</v>
       </c>
       <c r="E444" t="n">
-        <v>-22.34746171639906</v>
+        <v>-22.34746953569596</v>
       </c>
       <c r="F444" t="n">
         <v>-42.16226047422541</v>
@@ -53227,7 +53227,7 @@
         <v>-29.89368231014634</v>
       </c>
       <c r="E445" t="n">
-        <v>-20.77492865674345</v>
+        <v>-20.7749366725903</v>
       </c>
       <c r="F445" t="n">
         <v>-42.99229174547121</v>
@@ -53297,7 +53297,7 @@
         <v>-38.00978448792061</v>
       </c>
       <c r="G447" t="n">
-        <v>-6.755748593347743</v>
+        <v>-6.755756557173886</v>
       </c>
       <c r="H447" t="n">
         <v>-79.37792374904173</v>
@@ -53361,7 +53361,7 @@
         <v>-37.7883555351</v>
       </c>
       <c r="G449" t="n">
-        <v>-8.136819092262881</v>
+        <v>-8.13682695887027</v>
       </c>
       <c r="H449" t="n">
         <v>-78.59018000564203</v>
@@ -53387,13 +53387,13 @@
         <v>-18.88297978584559</v>
       </c>
       <c r="E450" t="n">
-        <v>-15.88698719525661</v>
+        <v>-15.88697830309197</v>
       </c>
       <c r="F450" t="n">
         <v>-35.79224816752393</v>
       </c>
       <c r="G450" t="n">
-        <v>-6.515112476293671</v>
+        <v>-6.515120518692097</v>
       </c>
       <c r="H450" t="n">
         <v>-78.95137134685486</v>
@@ -53419,7 +53419,7 @@
         <v>-21.15514103139139</v>
       </c>
       <c r="E451" t="n">
-        <v>-17.34137682167169</v>
+        <v>-17.34136803322271</v>
       </c>
       <c r="F451" t="n">
         <v>-37.43143086937941</v>
@@ -53457,7 +53457,7 @@
         <v>-36.80701636831384</v>
       </c>
       <c r="G452" t="n">
-        <v>-7.559885859211124</v>
+        <v>-7.5598938000765</v>
       </c>
       <c r="H452" t="n">
         <v>-79.75966409935273</v>
@@ -53547,13 +53547,13 @@
         <v>-26.51714739149942</v>
       </c>
       <c r="E455" t="n">
-        <v>-21.18380265372481</v>
+        <v>-21.18379462622453</v>
       </c>
       <c r="F455" t="n">
         <v>-41.48341463321004</v>
       </c>
       <c r="G455" t="n">
-        <v>-9.550907843832491</v>
+        <v>-9.55091551994175</v>
       </c>
       <c r="H455" t="n">
         <v>-80.90036279810563</v>
@@ -53579,7 +53579,7 @@
         <v>-30.5295940900473</v>
       </c>
       <c r="E456" t="n">
-        <v>-21.92261802067016</v>
+        <v>-21.92261013396634</v>
       </c>
       <c r="F456" t="n">
         <v>-48.90003185290745</v>
@@ -53617,7 +53617,7 @@
         <v>-45.07893809183386</v>
       </c>
       <c r="G457" t="n">
-        <v>-11.77049058031225</v>
+        <v>-11.77049784521835</v>
       </c>
       <c r="H457" t="n">
         <v>-82.36463783259975</v>
@@ -53649,7 +53649,7 @@
         <v>-43.76698367914717</v>
       </c>
       <c r="G458" t="n">
-        <v>-13.2402643967687</v>
+        <v>-13.24027144589717</v>
       </c>
       <c r="H458" t="n">
         <v>-82.17891229009145</v>
@@ -53739,13 +53739,13 @@
         <v>-30.07565956712446</v>
       </c>
       <c r="E461" t="n">
-        <v>-25.48238809077367</v>
+        <v>-25.4823950787656</v>
       </c>
       <c r="F461" t="n">
         <v>-44.03718065374491</v>
       </c>
       <c r="G461" t="n">
-        <v>-13.10908645483005</v>
+        <v>-13.10907941084746</v>
       </c>
       <c r="H461" t="n">
         <v>-82.374291038393</v>
@@ -53771,13 +53771,13 @@
         <v>-32.39348410987978</v>
       </c>
       <c r="E462" t="n">
-        <v>-29.13438953225068</v>
+        <v>-29.13439621150543</v>
       </c>
       <c r="F462" t="n">
         <v>-46.7217367763071</v>
       </c>
       <c r="G462" t="n">
-        <v>-15.21157938208825</v>
+        <v>-15.21158626015627</v>
       </c>
       <c r="H462" t="n">
         <v>-81.44846848638161</v>
@@ -53803,7 +53803,7 @@
         <v>-31.89493121198945</v>
       </c>
       <c r="E463" t="n">
-        <v>-28.07081853704482</v>
+        <v>-28.07081175545964</v>
       </c>
       <c r="F463" t="n">
         <v>-45.49804856795367</v>
@@ -53873,7 +53873,7 @@
         <v>-43.08986650881587</v>
       </c>
       <c r="G465" t="n">
-        <v>-14.92585944524146</v>
+        <v>-14.92585263286353</v>
       </c>
       <c r="H465" t="n">
         <v>-82.20913100290016</v>
@@ -53931,13 +53931,13 @@
         <v>-28.04877989062005</v>
       </c>
       <c r="E467" t="n">
-        <v>-28.55151148667798</v>
+        <v>-28.551504886499</v>
       </c>
       <c r="F467" t="n">
         <v>-42.95977001650706</v>
       </c>
       <c r="G467" t="n">
-        <v>-13.87504112400696</v>
+        <v>-13.87503413475447</v>
       </c>
       <c r="H467" t="n">
         <v>-82.14698279428512</v>
@@ -53963,7 +53963,7 @@
         <v>-27.86458221768647</v>
       </c>
       <c r="E468" t="n">
-        <v>-27.55756191669814</v>
+        <v>-27.55755510454062</v>
       </c>
       <c r="F468" t="n">
         <v>-44.69987464603042</v>
@@ -54097,7 +54097,7 @@
         <v>-52.68180189783389</v>
       </c>
       <c r="G472" t="n">
-        <v>-11.96638610891365</v>
+        <v>-11.96639345048396</v>
       </c>
       <c r="H472" t="n">
         <v>-84.05702090232704</v>
@@ -54129,7 +54129,7 @@
         <v>-54.05846909836642</v>
       </c>
       <c r="G473" t="n">
-        <v>-13.06323519659256</v>
+        <v>-13.063242448656</v>
       </c>
       <c r="H473" t="n">
         <v>-83.80988967383018</v>
@@ -54155,7 +54155,7 @@
         <v>-32.19911590123635</v>
       </c>
       <c r="E474" t="n">
-        <v>-25.90196375525328</v>
+        <v>-25.90197091088043</v>
       </c>
       <c r="F474" t="n">
         <v>-51.98792057340895</v>
@@ -54225,7 +54225,7 @@
         <v>-51.98003104313121</v>
       </c>
       <c r="G476" t="n">
-        <v>-10.24513324991935</v>
+        <v>-10.24514100720096</v>
       </c>
       <c r="H476" t="n">
         <v>-84.14785454375516</v>
@@ -54257,7 +54257,7 @@
         <v>-51.22602268723562</v>
       </c>
       <c r="G477" t="n">
-        <v>-8.267254874581775</v>
+        <v>-8.26726292543951</v>
       </c>
       <c r="H477" t="n">
         <v>-83.31527028006884</v>
@@ -54315,13 +54315,13 @@
         <v>-27.52354840786123</v>
       </c>
       <c r="E479" t="n">
-        <v>-16.42755184124513</v>
+        <v>-16.4275601717731</v>
       </c>
       <c r="F479" t="n">
         <v>-47.64444308810764</v>
       </c>
       <c r="G479" t="n">
-        <v>-4.93700339479709</v>
+        <v>-4.936994959667762</v>
       </c>
       <c r="H479" t="n">
         <v>-81.60539153240039</v>
@@ -54353,7 +54353,7 @@
         <v>-47.96316040173912</v>
       </c>
       <c r="G480" t="n">
-        <v>-6.118777829213606</v>
+        <v>-6.118769672358115</v>
       </c>
       <c r="H480" t="n">
         <v>-81.47244646127044</v>
@@ -54385,7 +54385,7 @@
         <v>-46.50169090859205</v>
       </c>
       <c r="G481" t="n">
-        <v>-7.66270818898882</v>
+        <v>-7.662700126451261</v>
       </c>
       <c r="H481" t="n">
         <v>-79.78622691284023</v>
@@ -54443,7 +54443,7 @@
         <v>-28.27814801252383</v>
       </c>
       <c r="E483" t="n">
-        <v>-20.02722811908593</v>
+        <v>-20.0272355549142</v>
       </c>
       <c r="F483" t="n">
         <v>-47.95545639098183</v>
@@ -54545,7 +54545,7 @@
         <v>-49.09154693367059</v>
       </c>
       <c r="G486" t="n">
-        <v>-4.125996817397826</v>
+        <v>-4.125988342067622</v>
       </c>
       <c r="H486" t="n">
         <v>-75.83799225046901</v>
@@ -54571,13 +54571,13 @@
         <v>-25.48882469494409</v>
       </c>
       <c r="E487" t="n">
-        <v>-21.0292402548563</v>
+        <v>-21.02923282196163</v>
       </c>
       <c r="F487" t="n">
         <v>-48.99627177559144</v>
       </c>
       <c r="G487" t="n">
-        <v>-3.521144733595927</v>
+        <v>-3.521153283265299</v>
       </c>
       <c r="H487" t="n">
         <v>-75.16174696814954</v>

--- a/dashboards/Reliance Group.xlsx
+++ b/dashboards/Reliance Group.xlsx
@@ -499,7 +499,7 @@
         <v>100.8000030517578</v>
       </c>
       <c r="I2" t="n">
-        <v>850.6760864257812</v>
+        <v>850.676025390625</v>
       </c>
       <c r="J2" t="n">
         <v>14.25</v>
@@ -551,13 +551,13 @@
         <v>89.94999694824219</v>
       </c>
       <c r="G4" t="n">
-        <v>1118.526000976562</v>
+        <v>1118.526123046875</v>
       </c>
       <c r="H4" t="n">
         <v>97.05000305175781</v>
       </c>
       <c r="I4" t="n">
-        <v>844.1919555664062</v>
+        <v>844.1920776367188</v>
       </c>
       <c r="J4" t="n">
         <v>13.85000038146973</v>
@@ -580,7 +580,7 @@
         <v>89.90000152587891</v>
       </c>
       <c r="G5" t="n">
-        <v>1094.476196289062</v>
+        <v>1094.47607421875</v>
       </c>
       <c r="H5" t="n">
         <v>100.1500015258789</v>
@@ -615,7 +615,7 @@
         <v>98.55000305175781</v>
       </c>
       <c r="I6" t="n">
-        <v>844.0446166992188</v>
+        <v>844.0447387695312</v>
       </c>
       <c r="J6" t="n">
         <v>14.14999961853027</v>
@@ -638,13 +638,13 @@
         <v>91.5</v>
       </c>
       <c r="G7" t="n">
-        <v>1104.213745117188</v>
+        <v>1104.2138671875</v>
       </c>
       <c r="H7" t="n">
         <v>103.4499969482422</v>
       </c>
       <c r="I7" t="n">
-        <v>939.3392944335938</v>
+        <v>939.3392333984375</v>
       </c>
       <c r="J7" t="n">
         <v>14.85000038146973</v>
@@ -667,13 +667,13 @@
         <v>89.34999847412109</v>
       </c>
       <c r="G8" t="n">
-        <v>1112.16259765625</v>
+        <v>1112.162719726562</v>
       </c>
       <c r="H8" t="n">
         <v>98.40000152587891</v>
       </c>
       <c r="I8" t="n">
-        <v>968.8118286132812</v>
+        <v>968.8118896484375</v>
       </c>
       <c r="J8" t="n">
         <v>14.30000019073486</v>
@@ -696,7 +696,7 @@
         <v>88.09999847412109</v>
       </c>
       <c r="G9" t="n">
-        <v>1141.851196289062</v>
+        <v>1141.851440429688</v>
       </c>
       <c r="H9" t="n">
         <v>96.40000152587891</v>
@@ -731,7 +731,7 @@
         <v>99.05000305175781</v>
       </c>
       <c r="I10" t="n">
-        <v>931.4308471679688</v>
+        <v>931.4307861328125</v>
       </c>
       <c r="J10" t="n">
         <v>14.25</v>
@@ -754,13 +754,13 @@
         <v>89.59999847412109</v>
       </c>
       <c r="G11" t="n">
-        <v>1149.958618164062</v>
+        <v>1149.95849609375</v>
       </c>
       <c r="H11" t="n">
         <v>102.75</v>
       </c>
       <c r="I11" t="n">
-        <v>931.529052734375</v>
+        <v>931.5291137695312</v>
       </c>
       <c r="J11" t="n">
         <v>14.94999980926514</v>
@@ -812,13 +812,13 @@
         <v>89.80000305175781</v>
       </c>
       <c r="G13" t="n">
-        <v>1142.168212890625</v>
+        <v>1142.168334960938</v>
       </c>
       <c r="H13" t="n">
         <v>101.9499969482422</v>
       </c>
       <c r="I13" t="n">
-        <v>930.4976196289062</v>
+        <v>930.49755859375</v>
       </c>
       <c r="J13" t="n">
         <v>16.10000038146973</v>
@@ -841,7 +841,7 @@
         <v>90.69999694824219</v>
       </c>
       <c r="G14" t="n">
-        <v>1142.077880859375</v>
+        <v>1142.077758789062</v>
       </c>
       <c r="H14" t="n">
         <v>99.75</v>
@@ -876,7 +876,7 @@
         <v>101.5500030517578</v>
       </c>
       <c r="I15" t="n">
-        <v>936.3428344726562</v>
+        <v>936.3428955078125</v>
       </c>
       <c r="J15" t="n">
         <v>16.54999923706055</v>
@@ -899,7 +899,7 @@
         <v>86.40000152587891</v>
       </c>
       <c r="G16" t="n">
-        <v>1122.262451171875</v>
+        <v>1122.262573242188</v>
       </c>
       <c r="H16" t="n">
         <v>98.25</v>
@@ -928,13 +928,13 @@
         <v>82.09999847412109</v>
       </c>
       <c r="G17" t="n">
-        <v>1076.99365234375</v>
+        <v>1076.993530273438</v>
       </c>
       <c r="H17" t="n">
         <v>93.55000305175781</v>
       </c>
       <c r="I17" t="n">
-        <v>835.7432250976562</v>
+        <v>835.7432861328125</v>
       </c>
       <c r="J17" t="n">
         <v>15.25</v>
@@ -963,7 +963,7 @@
         <v>98.05000305175781</v>
       </c>
       <c r="I18" t="n">
-        <v>835.7432250976562</v>
+        <v>835.7432861328125</v>
       </c>
       <c r="J18" t="n">
         <v>14.75</v>
@@ -992,7 +992,7 @@
         <v>97.80000305175781</v>
       </c>
       <c r="I19" t="n">
-        <v>855.3916625976562</v>
+        <v>855.3916015625</v>
       </c>
       <c r="J19" t="n">
         <v>14.80000019073486</v>
@@ -1015,7 +1015,7 @@
         <v>84.25</v>
       </c>
       <c r="G20" t="n">
-        <v>1057.9482421875</v>
+        <v>1057.948364257812</v>
       </c>
       <c r="H20" t="n">
         <v>102.3000030517578</v>
@@ -1044,13 +1044,13 @@
         <v>82</v>
       </c>
       <c r="G21" t="n">
-        <v>1080.933837890625</v>
+        <v>1080.933959960938</v>
       </c>
       <c r="H21" t="n">
         <v>101.0500030517578</v>
       </c>
       <c r="I21" t="n">
-        <v>864.5281372070312</v>
+        <v>864.5280151367188</v>
       </c>
       <c r="J21" t="n">
         <v>14.80000019073486</v>
@@ -1073,7 +1073,7 @@
         <v>82.55000305175781</v>
       </c>
       <c r="G22" t="n">
-        <v>1077.355834960938</v>
+        <v>1077.35595703125</v>
       </c>
       <c r="H22" t="n">
         <v>106.0999984741211</v>
@@ -1102,13 +1102,13 @@
         <v>85.90000152587891</v>
       </c>
       <c r="G23" t="n">
-        <v>1079.552490234375</v>
+        <v>1079.552368164062</v>
       </c>
       <c r="H23" t="n">
         <v>110.0999984741211</v>
       </c>
       <c r="I23" t="n">
-        <v>921.5574951171875</v>
+        <v>921.5574340820312</v>
       </c>
       <c r="J23" t="n">
         <v>16.04999923706055</v>
@@ -1131,13 +1131,13 @@
         <v>87.75</v>
       </c>
       <c r="G24" t="n">
-        <v>1065.602661132812</v>
+        <v>1065.6025390625</v>
       </c>
       <c r="H24" t="n">
         <v>115.5999984741211</v>
       </c>
       <c r="I24" t="n">
-        <v>910.0139770507812</v>
+        <v>910.0140380859375</v>
       </c>
       <c r="J24" t="n">
         <v>16.85000038146973</v>
@@ -1166,7 +1166,7 @@
         <v>121.3499984741211</v>
       </c>
       <c r="I25" t="n">
-        <v>898.3723754882812</v>
+        <v>898.3724365234375</v>
       </c>
       <c r="J25" t="n">
         <v>17.64999961853027</v>
@@ -1189,7 +1189,7 @@
         <v>83.25</v>
       </c>
       <c r="G26" t="n">
-        <v>1049.456176757812</v>
+        <v>1049.4560546875</v>
       </c>
       <c r="H26" t="n">
         <v>133.4499969482422</v>
@@ -1224,7 +1224,7 @@
         <v>134.4499969482422</v>
       </c>
       <c r="I27" t="n">
-        <v>865.2157592773438</v>
+        <v>865.2158203125</v>
       </c>
       <c r="J27" t="n">
         <v>17.60000038146973</v>
@@ -1253,7 +1253,7 @@
         <v>147.8500061035156</v>
       </c>
       <c r="I28" t="n">
-        <v>866.5420532226562</v>
+        <v>866.5419921875</v>
       </c>
       <c r="J28" t="n">
         <v>17</v>
@@ -1276,7 +1276,7 @@
         <v>92.09999847412109</v>
       </c>
       <c r="G29" t="n">
-        <v>1078.420166015625</v>
+        <v>1078.420288085938</v>
       </c>
       <c r="H29" t="n">
         <v>133.1000061035156</v>
@@ -1311,7 +1311,7 @@
         <v>134</v>
       </c>
       <c r="I30" t="n">
-        <v>853.67236328125</v>
+        <v>853.6724243164062</v>
       </c>
       <c r="J30" t="n">
         <v>15.94999980926514</v>
@@ -1369,7 +1369,7 @@
         <v>111.8499984741211</v>
       </c>
       <c r="I32" t="n">
-        <v>784.4609985351562</v>
+        <v>784.4610595703125</v>
       </c>
       <c r="J32" t="n">
         <v>14.55000019073486</v>
@@ -1392,7 +1392,7 @@
         <v>86.69999694824219</v>
       </c>
       <c r="G33" t="n">
-        <v>1092.8681640625</v>
+        <v>1092.868408203125</v>
       </c>
       <c r="H33" t="n">
         <v>122.5999984741211</v>
@@ -1421,13 +1421,13 @@
         <v>85.30000305175781</v>
       </c>
       <c r="G34" t="n">
-        <v>1106.704833984375</v>
+        <v>1106.704956054688</v>
       </c>
       <c r="H34" t="n">
         <v>113.3499984741211</v>
       </c>
       <c r="I34" t="n">
-        <v>801.1129760742188</v>
+        <v>801.113037109375</v>
       </c>
       <c r="J34" t="n">
         <v>14.14999961853027</v>
@@ -1450,13 +1450,13 @@
         <v>83.09999847412109</v>
       </c>
       <c r="G35" t="n">
-        <v>1098.05419921875</v>
+        <v>1098.054321289062</v>
       </c>
       <c r="H35" t="n">
         <v>120.0999984741211</v>
       </c>
       <c r="I35" t="n">
-        <v>790.3064575195312</v>
+        <v>790.306396484375</v>
       </c>
       <c r="J35" t="n">
         <v>14.14999961853027</v>
@@ -1485,7 +1485,7 @@
         <v>112.6999969482422</v>
       </c>
       <c r="I36" t="n">
-        <v>750.4692993164062</v>
+        <v>750.4694213867188</v>
       </c>
       <c r="J36" t="n">
         <v>13.60000038146973</v>
@@ -1508,13 +1508,13 @@
         <v>78.05000305175781</v>
       </c>
       <c r="G37" t="n">
-        <v>1082.020874023438</v>
+        <v>1082.02099609375</v>
       </c>
       <c r="H37" t="n">
         <v>114.3499984741211</v>
       </c>
       <c r="I37" t="n">
-        <v>725.5650024414062</v>
+        <v>725.5650634765625</v>
       </c>
       <c r="J37" t="n">
         <v>12.94999980926514</v>
@@ -1537,7 +1537,7 @@
         <v>78.65000152587891</v>
       </c>
       <c r="G38" t="n">
-        <v>1075.249633789062</v>
+        <v>1075.249755859375</v>
       </c>
       <c r="H38" t="n">
         <v>113.25</v>
@@ -1572,7 +1572,7 @@
         <v>101.9499969482422</v>
       </c>
       <c r="I39" t="n">
-        <v>655.5676879882812</v>
+        <v>655.567626953125</v>
       </c>
       <c r="J39" t="n">
         <v>12.89999961853027</v>
@@ -1601,7 +1601,7 @@
         <v>104.5999984741211</v>
       </c>
       <c r="I40" t="n">
-        <v>681.9457397460938</v>
+        <v>681.9456787109375</v>
       </c>
       <c r="J40" t="n">
         <v>13</v>
@@ -1630,7 +1630,7 @@
         <v>104.5999984741211</v>
       </c>
       <c r="I41" t="n">
-        <v>686.1209716796875</v>
+        <v>686.1209106445312</v>
       </c>
       <c r="J41" t="n">
         <v>13.05000019073486</v>
@@ -1653,7 +1653,7 @@
         <v>76.25</v>
       </c>
       <c r="G42" t="n">
-        <v>1086.346435546875</v>
+        <v>1086.34619140625</v>
       </c>
       <c r="H42" t="n">
         <v>107.5999984741211</v>
@@ -1682,13 +1682,13 @@
         <v>76.75</v>
       </c>
       <c r="G43" t="n">
-        <v>1077.174682617188</v>
+        <v>1077.174560546875</v>
       </c>
       <c r="H43" t="n">
         <v>106.4000015258789</v>
       </c>
       <c r="I43" t="n">
-        <v>688.6752319335938</v>
+        <v>688.6751708984375</v>
       </c>
       <c r="J43" t="n">
         <v>13.05000019073486</v>
@@ -1711,13 +1711,13 @@
         <v>77.5</v>
       </c>
       <c r="G44" t="n">
-        <v>1053.283325195312</v>
+        <v>1053.283203125</v>
       </c>
       <c r="H44" t="n">
         <v>103.5</v>
       </c>
       <c r="I44" t="n">
-        <v>674.724853515625</v>
+        <v>674.7249145507812</v>
       </c>
       <c r="J44" t="n">
         <v>12.85000038146973</v>
@@ -1769,7 +1769,7 @@
         <v>74.09999847412109</v>
       </c>
       <c r="G46" t="n">
-        <v>1012.498046875</v>
+        <v>1012.497985839844</v>
       </c>
       <c r="H46" t="n">
         <v>101.75</v>
@@ -1804,7 +1804,7 @@
         <v>107.5</v>
       </c>
       <c r="I47" t="n">
-        <v>693.882080078125</v>
+        <v>693.8820190429688</v>
       </c>
       <c r="J47" t="n">
         <v>13.35000038146973</v>
@@ -1885,7 +1885,7 @@
         <v>76.5</v>
       </c>
       <c r="G50" t="n">
-        <v>1095.540405273438</v>
+        <v>1095.54052734375</v>
       </c>
       <c r="H50" t="n">
         <v>117.25</v>
@@ -1920,7 +1920,7 @@
         <v>115.5500030517578</v>
       </c>
       <c r="I51" t="n">
-        <v>747.3255615234375</v>
+        <v>747.3256225585938</v>
       </c>
       <c r="J51" t="n">
         <v>13.44999980926514</v>
@@ -1943,13 +1943,13 @@
         <v>77.75</v>
       </c>
       <c r="G52" t="n">
-        <v>1088.520263671875</v>
+        <v>1088.520385742188</v>
       </c>
       <c r="H52" t="n">
         <v>118.9499969482422</v>
       </c>
       <c r="I52" t="n">
-        <v>750.5184326171875</v>
+        <v>750.5184936523438</v>
       </c>
       <c r="J52" t="n">
         <v>14.10000038146973</v>
@@ -1972,13 +1972,13 @@
         <v>78.75</v>
       </c>
       <c r="G53" t="n">
-        <v>1124.006469726562</v>
+        <v>1124.00634765625</v>
       </c>
       <c r="H53" t="n">
         <v>116.8000030517578</v>
       </c>
       <c r="I53" t="n">
-        <v>758.770751953125</v>
+        <v>758.7706909179688</v>
       </c>
       <c r="J53" t="n">
         <v>13.75</v>
@@ -2059,13 +2059,13 @@
         <v>81.65000152587891</v>
       </c>
       <c r="G56" t="n">
-        <v>1150.049194335938</v>
+        <v>1150.049072265625</v>
       </c>
       <c r="H56" t="n">
         <v>111.8000030517578</v>
       </c>
       <c r="I56" t="n">
-        <v>756.51123046875</v>
+        <v>756.5111694335938</v>
       </c>
       <c r="J56" t="n">
         <v>12.85000038146973</v>
@@ -2094,7 +2094,7 @@
         <v>109.6999969482422</v>
       </c>
       <c r="I57" t="n">
-        <v>756.3638916015625</v>
+        <v>756.3638305664062</v>
       </c>
       <c r="J57" t="n">
         <v>13</v>
@@ -2117,7 +2117,7 @@
         <v>85.59999847412109</v>
       </c>
       <c r="G58" t="n">
-        <v>1175.706909179688</v>
+        <v>1175.706787109375</v>
       </c>
       <c r="H58" t="n">
         <v>109.1999969482422</v>
@@ -2146,13 +2146,13 @@
         <v>87.59999847412109</v>
       </c>
       <c r="G59" t="n">
-        <v>1187.528198242188</v>
+        <v>1187.5283203125</v>
       </c>
       <c r="H59" t="n">
         <v>100.6999969482422</v>
       </c>
       <c r="I59" t="n">
-        <v>731.4595336914062</v>
+        <v>731.45947265625</v>
       </c>
       <c r="J59" t="n">
         <v>12.35000038146973</v>
@@ -2181,7 +2181,7 @@
         <v>110.75</v>
       </c>
       <c r="I60" t="n">
-        <v>735.4383544921875</v>
+        <v>735.4382934570312</v>
       </c>
       <c r="J60" t="n">
         <v>12.94999980926514</v>
@@ -2210,7 +2210,7 @@
         <v>114.8000030517578</v>
       </c>
       <c r="I61" t="n">
-        <v>769.7738037109375</v>
+        <v>769.7738647460938</v>
       </c>
       <c r="J61" t="n">
         <v>13.55000019073486</v>
@@ -2233,7 +2233,7 @@
         <v>85.15000152587891</v>
       </c>
       <c r="G62" t="n">
-        <v>1193.325561523438</v>
+        <v>1193.325439453125</v>
       </c>
       <c r="H62" t="n">
         <v>112.3000030517578</v>
@@ -2268,7 +2268,7 @@
         <v>122.6500015258789</v>
       </c>
       <c r="I63" t="n">
-        <v>790.25732421875</v>
+        <v>790.2572631835938</v>
       </c>
       <c r="J63" t="n">
         <v>14.14999961853027</v>
@@ -2291,13 +2291,13 @@
         <v>92.19999694824219</v>
       </c>
       <c r="G64" t="n">
-        <v>1206.437622070312</v>
+        <v>1206.437377929688</v>
       </c>
       <c r="H64" t="n">
         <v>124.6999969482422</v>
       </c>
       <c r="I64" t="n">
-        <v>794.3342895507812</v>
+        <v>794.3343505859375</v>
       </c>
       <c r="J64" t="n">
         <v>14.85000038146973</v>
@@ -2326,7 +2326,7 @@
         <v>132.1499938964844</v>
       </c>
       <c r="I65" t="n">
-        <v>804.305908203125</v>
+        <v>804.3058471679688</v>
       </c>
       <c r="J65" t="n">
         <v>15.55000019073486</v>
@@ -2349,13 +2349,13 @@
         <v>94.5</v>
       </c>
       <c r="G66" t="n">
-        <v>1186.214599609375</v>
+        <v>1186.214721679688</v>
       </c>
       <c r="H66" t="n">
         <v>136.1499938964844</v>
       </c>
       <c r="I66" t="n">
-        <v>822.13671875</v>
+        <v>822.1367797851562</v>
       </c>
       <c r="J66" t="n">
         <v>16.29999923706055</v>
@@ -2413,7 +2413,7 @@
         <v>126.75</v>
       </c>
       <c r="I68" t="n">
-        <v>815.8493041992188</v>
+        <v>815.8491821289062</v>
       </c>
       <c r="J68" t="n">
         <v>15.60000038146973</v>
@@ -2436,13 +2436,13 @@
         <v>98.40000152587891</v>
       </c>
       <c r="G69" t="n">
-        <v>1182.206420898438</v>
+        <v>1182.206298828125</v>
       </c>
       <c r="H69" t="n">
         <v>125.8499984741211</v>
       </c>
       <c r="I69" t="n">
-        <v>816.3895874023438</v>
+        <v>816.3896484375</v>
       </c>
       <c r="J69" t="n">
         <v>15.69999980926514</v>
@@ -2465,7 +2465,7 @@
         <v>94.84999847412109</v>
       </c>
       <c r="G70" t="n">
-        <v>1159.945678710938</v>
+        <v>1159.945556640625</v>
       </c>
       <c r="H70" t="n">
         <v>122.9499969482422</v>
@@ -2494,7 +2494,7 @@
         <v>93.80000305175781</v>
       </c>
       <c r="G71" t="n">
-        <v>1155.68798828125</v>
+        <v>1155.688110351562</v>
       </c>
       <c r="H71" t="n">
         <v>123.4000015258789</v>
@@ -2581,13 +2581,13 @@
         <v>101.5500030517578</v>
       </c>
       <c r="G74" t="n">
-        <v>1231.234619140625</v>
+        <v>1231.234741210938</v>
       </c>
       <c r="H74" t="n">
         <v>125.75</v>
       </c>
       <c r="I74" t="n">
-        <v>945.7249755859375</v>
+        <v>945.7249145507812</v>
       </c>
       <c r="J74" t="n">
         <v>14.75</v>
@@ -2610,13 +2610,13 @@
         <v>103.4499969482422</v>
       </c>
       <c r="G75" t="n">
-        <v>1260.062866210938</v>
+        <v>1260.06298828125</v>
       </c>
       <c r="H75" t="n">
         <v>130.3000030517578</v>
       </c>
       <c r="I75" t="n">
-        <v>987.2321166992188</v>
+        <v>987.232177734375</v>
       </c>
       <c r="J75" t="n">
         <v>15.14999961853027</v>
@@ -2668,7 +2668,7 @@
         <v>105.6999969482422</v>
       </c>
       <c r="G77" t="n">
-        <v>1220.613891601562</v>
+        <v>1220.61376953125</v>
       </c>
       <c r="H77" t="n">
         <v>123.25</v>
@@ -2703,7 +2703,7 @@
         <v>121.1999969482422</v>
       </c>
       <c r="I78" t="n">
-        <v>926.469482421875</v>
+        <v>926.4695434570312</v>
       </c>
       <c r="J78" t="n">
         <v>14.5</v>
@@ -2784,13 +2784,13 @@
         <v>86.19999694824219</v>
       </c>
       <c r="G81" t="n">
-        <v>1263.754272460938</v>
+        <v>1263.75439453125</v>
       </c>
       <c r="H81" t="n">
         <v>123.5500030517578</v>
       </c>
       <c r="I81" t="n">
-        <v>1086.94775390625</v>
+        <v>1086.947631835938</v>
       </c>
       <c r="J81" t="n">
         <v>14.25</v>
@@ -2813,13 +2813,13 @@
         <v>85</v>
       </c>
       <c r="G82" t="n">
-        <v>1259.315795898438</v>
+        <v>1259.315673828125</v>
       </c>
       <c r="H82" t="n">
         <v>124.25</v>
       </c>
       <c r="I82" t="n">
-        <v>1096.477172851562</v>
+        <v>1096.47705078125</v>
       </c>
       <c r="J82" t="n">
         <v>14.19999980926514</v>
@@ -2842,7 +2842,7 @@
         <v>76.94999694824219</v>
       </c>
       <c r="G83" t="n">
-        <v>1220.002319335938</v>
+        <v>1220.00244140625</v>
       </c>
       <c r="H83" t="n">
         <v>116.0999984741211</v>
@@ -2871,7 +2871,7 @@
         <v>80.30000305175781</v>
       </c>
       <c r="G84" t="n">
-        <v>1196.110961914062</v>
+        <v>1196.11083984375</v>
       </c>
       <c r="H84" t="n">
         <v>115.0999984741211</v>
@@ -2900,13 +2900,13 @@
         <v>78.34999847412109</v>
       </c>
       <c r="G85" t="n">
-        <v>1186.939331054688</v>
+        <v>1186.939453125</v>
       </c>
       <c r="H85" t="n">
         <v>111.3000030517578</v>
       </c>
       <c r="I85" t="n">
-        <v>1049.320922851562</v>
+        <v>1049.321044921875</v>
       </c>
       <c r="J85" t="n">
         <v>13.10000038146973</v>
@@ -2929,13 +2929,13 @@
         <v>74.19999694824219</v>
       </c>
       <c r="G86" t="n">
-        <v>1140.583129882812</v>
+        <v>1140.583251953125</v>
       </c>
       <c r="H86" t="n">
         <v>112.3000030517578</v>
       </c>
       <c r="I86" t="n">
-        <v>1002.950927734375</v>
+        <v>1002.950866699219</v>
       </c>
       <c r="J86" t="n">
         <v>13.69999980926514</v>
@@ -2993,7 +2993,7 @@
         <v>101</v>
       </c>
       <c r="I88" t="n">
-        <v>964.9312133789062</v>
+        <v>964.9312744140625</v>
       </c>
       <c r="J88" t="n">
         <v>13</v>
@@ -3022,7 +3022,7 @@
         <v>100.9000015258789</v>
       </c>
       <c r="I89" t="n">
-        <v>943.9074096679688</v>
+        <v>943.907470703125</v>
       </c>
       <c r="J89" t="n">
         <v>12.39999961853027</v>
@@ -3045,7 +3045,7 @@
         <v>76.65000152587891</v>
       </c>
       <c r="G90" t="n">
-        <v>1099.050537109375</v>
+        <v>1099.050659179688</v>
       </c>
       <c r="H90" t="n">
         <v>102.0500030517578</v>
@@ -3074,13 +3074,13 @@
         <v>74.59999847412109</v>
       </c>
       <c r="G91" t="n">
-        <v>1099.322387695312</v>
+        <v>1099.322509765625</v>
       </c>
       <c r="H91" t="n">
         <v>98.30000305175781</v>
       </c>
       <c r="I91" t="n">
-        <v>964.9312133789062</v>
+        <v>964.9312744140625</v>
       </c>
       <c r="J91" t="n">
         <v>11.89999961853027</v>
@@ -3109,7 +3109,7 @@
         <v>107.0500030517578</v>
       </c>
       <c r="I92" t="n">
-        <v>1028.100708007812</v>
+        <v>1028.100830078125</v>
       </c>
       <c r="J92" t="n">
         <v>12.44999980926514</v>
@@ -3132,13 +3132,13 @@
         <v>78.30000305175781</v>
       </c>
       <c r="G93" t="n">
-        <v>1149.6640625</v>
+        <v>1149.664184570312</v>
       </c>
       <c r="H93" t="n">
         <v>104.0999984741211</v>
       </c>
       <c r="I93" t="n">
-        <v>1021.714965820312</v>
+        <v>1021.715026855469</v>
       </c>
       <c r="J93" t="n">
         <v>12.44999980926514</v>
@@ -3167,7 +3167,7 @@
         <v>102.0999984741211</v>
       </c>
       <c r="I94" t="n">
-        <v>977.5062866210938</v>
+        <v>977.5061645507812</v>
       </c>
       <c r="J94" t="n">
         <v>12.30000019073486</v>
@@ -3190,13 +3190,13 @@
         <v>80.75</v>
       </c>
       <c r="G95" t="n">
-        <v>1188.660278320312</v>
+        <v>1188.660522460938</v>
       </c>
       <c r="H95" t="n">
         <v>104</v>
       </c>
       <c r="I95" t="n">
-        <v>1021.665954589844</v>
+        <v>1021.665893554688</v>
       </c>
       <c r="J95" t="n">
         <v>12.85000038146973</v>
@@ -3219,7 +3219,7 @@
         <v>80.05000305175781</v>
       </c>
       <c r="G96" t="n">
-        <v>1180.711669921875</v>
+        <v>1180.711791992188</v>
       </c>
       <c r="H96" t="n">
         <v>101.6999969482422</v>
@@ -3248,13 +3248,13 @@
         <v>78.94999694824219</v>
       </c>
       <c r="G97" t="n">
-        <v>1184.765380859375</v>
+        <v>1184.765258789062</v>
       </c>
       <c r="H97" t="n">
         <v>100.9000015258789</v>
       </c>
       <c r="I97" t="n">
-        <v>945.7249755859375</v>
+        <v>945.7249145507812</v>
       </c>
       <c r="J97" t="n">
         <v>12.55000019073486</v>
@@ -3283,7 +3283,7 @@
         <v>100.6500015258789</v>
       </c>
       <c r="I98" t="n">
-        <v>869.9805297851562</v>
+        <v>869.98046875</v>
       </c>
       <c r="J98" t="n">
         <v>12.10000038146973</v>
@@ -3306,7 +3306,7 @@
         <v>71.59999847412109</v>
       </c>
       <c r="G99" t="n">
-        <v>1171.744018554688</v>
+        <v>1171.743896484375</v>
       </c>
       <c r="H99" t="n">
         <v>100.3499984741211</v>
@@ -3341,7 +3341,7 @@
         <v>99.84999847412109</v>
       </c>
       <c r="I100" t="n">
-        <v>871.9944458007812</v>
+        <v>871.9945068359375</v>
       </c>
       <c r="J100" t="n">
         <v>11.85000038146973</v>
@@ -3364,7 +3364,7 @@
         <v>73.15000152587891</v>
       </c>
       <c r="G101" t="n">
-        <v>1206.935668945312</v>
+        <v>1206.935791015625</v>
       </c>
       <c r="H101" t="n">
         <v>102.5500030517578</v>
@@ -3399,7 +3399,7 @@
         <v>107.9499969482422</v>
       </c>
       <c r="I102" t="n">
-        <v>909.1298828125</v>
+        <v>909.1299438476562</v>
       </c>
       <c r="J102" t="n">
         <v>12.60000038146973</v>
@@ -3422,13 +3422,13 @@
         <v>76.05000305175781</v>
       </c>
       <c r="G103" t="n">
-        <v>1192.75927734375</v>
+        <v>1192.759399414062</v>
       </c>
       <c r="H103" t="n">
         <v>108.0500030517578</v>
       </c>
       <c r="I103" t="n">
-        <v>929.4658813476562</v>
+        <v>929.4659423828125</v>
       </c>
       <c r="J103" t="n">
         <v>13.19999980926514</v>
@@ -3451,13 +3451,13 @@
         <v>76.5</v>
       </c>
       <c r="G104" t="n">
-        <v>1233.88427734375</v>
+        <v>1233.884399414062</v>
       </c>
       <c r="H104" t="n">
         <v>109.3000030517578</v>
       </c>
       <c r="I104" t="n">
-        <v>936.24462890625</v>
+        <v>936.2446899414062</v>
       </c>
       <c r="J104" t="n">
         <v>13.85000038146973</v>
@@ -3509,13 +3509,13 @@
         <v>74.65000152587891</v>
       </c>
       <c r="G106" t="n">
-        <v>1253.473022460938</v>
+        <v>1253.47314453125</v>
       </c>
       <c r="H106" t="n">
         <v>105.1500015258789</v>
       </c>
       <c r="I106" t="n">
-        <v>990.7197265625</v>
+        <v>990.7197875976562</v>
       </c>
       <c r="J106" t="n">
         <v>13.80000019073486</v>
@@ -3567,7 +3567,7 @@
         <v>80.05000305175781</v>
       </c>
       <c r="G108" t="n">
-        <v>1233.77099609375</v>
+        <v>1233.771118164062</v>
       </c>
       <c r="H108" t="n">
         <v>104.8499984741211</v>
@@ -3596,13 +3596,13 @@
         <v>80.94999694824219</v>
       </c>
       <c r="G109" t="n">
-        <v>1267.60400390625</v>
+        <v>1267.604125976562</v>
       </c>
       <c r="H109" t="n">
         <v>104.4499969482422</v>
       </c>
       <c r="I109" t="n">
-        <v>974.7554321289062</v>
+        <v>974.75537109375</v>
       </c>
       <c r="J109" t="n">
         <v>13.94999980926514</v>
@@ -3625,7 +3625,7 @@
         <v>78.59999847412109</v>
       </c>
       <c r="G110" t="n">
-        <v>1229.33251953125</v>
+        <v>1229.332397460938</v>
       </c>
       <c r="H110" t="n">
         <v>103.5999984741211</v>
@@ -3654,7 +3654,7 @@
         <v>73.55000305175781</v>
       </c>
       <c r="G111" t="n">
-        <v>1206.075073242188</v>
+        <v>1206.074951171875</v>
       </c>
       <c r="H111" t="n">
         <v>96.94999694824219</v>
@@ -3683,7 +3683,7 @@
         <v>72.84999847412109</v>
       </c>
       <c r="G112" t="n">
-        <v>1190.3134765625</v>
+        <v>1190.313598632812</v>
       </c>
       <c r="H112" t="n">
         <v>95.75</v>
@@ -3712,13 +3712,13 @@
         <v>74.59999847412109</v>
       </c>
       <c r="G113" t="n">
-        <v>1175.910766601562</v>
+        <v>1175.910888671875</v>
       </c>
       <c r="H113" t="n">
         <v>95.5</v>
       </c>
       <c r="I113" t="n">
-        <v>876.513671875</v>
+        <v>876.5136108398438</v>
       </c>
       <c r="J113" t="n">
         <v>12.64999961853027</v>
@@ -3741,13 +3741,13 @@
         <v>67.25</v>
       </c>
       <c r="G114" t="n">
-        <v>1159.4697265625</v>
+        <v>1159.469848632812</v>
       </c>
       <c r="H114" t="n">
         <v>95.40000152587891</v>
       </c>
       <c r="I114" t="n">
-        <v>825.7225341796875</v>
+        <v>825.7225952148438</v>
       </c>
       <c r="J114" t="n">
         <v>12.05000019073486</v>
@@ -3828,7 +3828,7 @@
         <v>62.29999923706055</v>
       </c>
       <c r="G117" t="n">
-        <v>1170.385131835938</v>
+        <v>1170.38525390625</v>
       </c>
       <c r="H117" t="n">
         <v>94.5</v>
@@ -3857,7 +3857,7 @@
         <v>59.15000152587891</v>
       </c>
       <c r="G118" t="n">
-        <v>1134.831176757812</v>
+        <v>1134.831298828125</v>
       </c>
       <c r="H118" t="n">
         <v>91.19999694824219</v>
@@ -3921,7 +3921,7 @@
         <v>90.69999694824219</v>
       </c>
       <c r="I120" t="n">
-        <v>775.5701293945312</v>
+        <v>775.570068359375</v>
       </c>
       <c r="J120" t="n">
         <v>11.85000038146973</v>
@@ -4002,13 +4002,13 @@
         <v>68.19999694824219</v>
       </c>
       <c r="G123" t="n">
-        <v>1168.596069335938</v>
+        <v>1168.59619140625</v>
       </c>
       <c r="H123" t="n">
         <v>92.09999847412109</v>
       </c>
       <c r="I123" t="n">
-        <v>938.1112060546875</v>
+        <v>938.111328125</v>
       </c>
       <c r="J123" t="n">
         <v>11.75</v>
@@ -4037,7 +4037,7 @@
         <v>90.59999847412109</v>
       </c>
       <c r="I124" t="n">
-        <v>935.9990844726562</v>
+        <v>935.9990234375</v>
       </c>
       <c r="J124" t="n">
         <v>11.5</v>
@@ -4089,7 +4089,7 @@
         <v>65.55000305175781</v>
       </c>
       <c r="G126" t="n">
-        <v>1093.2080078125</v>
+        <v>1093.207885742188</v>
       </c>
       <c r="H126" t="n">
         <v>94.5</v>
@@ -4124,7 +4124,7 @@
         <v>93.15000152587891</v>
       </c>
       <c r="I127" t="n">
-        <v>927.0099487304688</v>
+        <v>927.0098876953125</v>
       </c>
       <c r="J127" t="n">
         <v>11.35000038146973</v>
@@ -4153,7 +4153,7 @@
         <v>91.75</v>
       </c>
       <c r="I128" t="n">
-        <v>925.6345825195312</v>
+        <v>925.634521484375</v>
       </c>
       <c r="J128" t="n">
         <v>11.19999980926514</v>
@@ -4205,13 +4205,13 @@
         <v>67.40000152587891</v>
       </c>
       <c r="G130" t="n">
-        <v>1083.10791015625</v>
+        <v>1083.108032226562</v>
       </c>
       <c r="H130" t="n">
         <v>94.80000305175781</v>
       </c>
       <c r="I130" t="n">
-        <v>933.3465576171875</v>
+        <v>933.3464965820312</v>
       </c>
       <c r="J130" t="n">
         <v>11.39999961853027</v>
@@ -4234,13 +4234,13 @@
         <v>68.30000305175781</v>
       </c>
       <c r="G131" t="n">
-        <v>1097.82763671875</v>
+        <v>1097.827758789062</v>
       </c>
       <c r="H131" t="n">
         <v>101.3499984741211</v>
       </c>
       <c r="I131" t="n">
-        <v>940.5673217773438</v>
+        <v>940.5672607421875</v>
       </c>
       <c r="J131" t="n">
         <v>11.64999961853027</v>
@@ -4263,7 +4263,7 @@
         <v>69.19999694824219</v>
       </c>
       <c r="G132" t="n">
-        <v>1096.26513671875</v>
+        <v>1096.265014648438</v>
       </c>
       <c r="H132" t="n">
         <v>102.5999984741211</v>
@@ -4321,13 +4321,13 @@
         <v>69.75</v>
       </c>
       <c r="G134" t="n">
-        <v>1085.712158203125</v>
+        <v>1085.712036132812</v>
       </c>
       <c r="H134" t="n">
         <v>100.4000015258789</v>
       </c>
       <c r="I134" t="n">
-        <v>937.9638671875</v>
+        <v>937.9639282226562</v>
       </c>
       <c r="J134" t="n">
         <v>11.39999961853027</v>
@@ -4379,13 +4379,13 @@
         <v>68.15000152587891</v>
       </c>
       <c r="G136" t="n">
-        <v>1097.08056640625</v>
+        <v>1097.080322265625</v>
       </c>
       <c r="H136" t="n">
         <v>102.25</v>
       </c>
       <c r="I136" t="n">
-        <v>964.4400634765625</v>
+        <v>964.4400024414062</v>
       </c>
       <c r="J136" t="n">
         <v>11.5</v>
@@ -4408,7 +4408,7 @@
         <v>67.09999847412109</v>
       </c>
       <c r="G137" t="n">
-        <v>1103.806396484375</v>
+        <v>1103.806518554688</v>
       </c>
       <c r="H137" t="n">
         <v>102.3000030517578</v>
@@ -4437,7 +4437,7 @@
         <v>67</v>
       </c>
       <c r="G138" t="n">
-        <v>1133.653564453125</v>
+        <v>1133.653442382812</v>
       </c>
       <c r="H138" t="n">
         <v>104.4000015258789</v>
@@ -4495,13 +4495,13 @@
         <v>63.75</v>
       </c>
       <c r="G140" t="n">
-        <v>1133.698974609375</v>
+        <v>1133.698852539062</v>
       </c>
       <c r="H140" t="n">
         <v>104.5</v>
       </c>
       <c r="I140" t="n">
-        <v>971.4151611328125</v>
+        <v>971.4152221679688</v>
       </c>
       <c r="J140" t="n">
         <v>11.75</v>
@@ -4553,7 +4553,7 @@
         <v>62.90000152587891</v>
       </c>
       <c r="G142" t="n">
-        <v>1096.740844726562</v>
+        <v>1096.74072265625</v>
       </c>
       <c r="H142" t="n">
         <v>113.9000015258789</v>
@@ -4588,7 +4588,7 @@
         <v>115.8499984741211</v>
       </c>
       <c r="I143" t="n">
-        <v>945.8232421875</v>
+        <v>945.8231811523438</v>
       </c>
       <c r="J143" t="n">
         <v>11.89999961853027</v>
@@ -4611,13 +4611,13 @@
         <v>65.15000152587891</v>
       </c>
       <c r="G144" t="n">
-        <v>1112.864624023438</v>
+        <v>1112.86474609375</v>
       </c>
       <c r="H144" t="n">
         <v>114.25</v>
       </c>
       <c r="I144" t="n">
-        <v>955.1070556640625</v>
+        <v>955.1071166992188</v>
       </c>
       <c r="J144" t="n">
         <v>11.75</v>
@@ -4640,7 +4640,7 @@
         <v>64.90000152587891</v>
       </c>
       <c r="G145" t="n">
-        <v>1136.57470703125</v>
+        <v>1136.574829101562</v>
       </c>
       <c r="H145" t="n">
         <v>117.0999984741211</v>
@@ -4669,13 +4669,13 @@
         <v>66.94999694824219</v>
       </c>
       <c r="G146" t="n">
-        <v>1166.195556640625</v>
+        <v>1166.19580078125</v>
       </c>
       <c r="H146" t="n">
         <v>123.25</v>
       </c>
       <c r="I146" t="n">
-        <v>1014.592346191406</v>
+        <v>1014.592407226562</v>
       </c>
       <c r="J146" t="n">
         <v>13</v>
@@ -4698,13 +4698,13 @@
         <v>68.05000305175781</v>
       </c>
       <c r="G147" t="n">
-        <v>1170.63427734375</v>
+        <v>1170.634399414062</v>
       </c>
       <c r="H147" t="n">
         <v>128.6999969482422</v>
       </c>
       <c r="I147" t="n">
-        <v>994.7968139648438</v>
+        <v>994.7967529296875</v>
       </c>
       <c r="J147" t="n">
         <v>13.30000019073486</v>
@@ -4727,7 +4727,7 @@
         <v>69.19999694824219</v>
       </c>
       <c r="G148" t="n">
-        <v>1180.462646484375</v>
+        <v>1180.462524414062</v>
       </c>
       <c r="H148" t="n">
         <v>125.0500030517578</v>
@@ -4762,7 +4762,7 @@
         <v>121.3499984741211</v>
       </c>
       <c r="I149" t="n">
-        <v>952.749267578125</v>
+        <v>952.7492065429688</v>
       </c>
       <c r="J149" t="n">
         <v>13.19999980926514</v>
@@ -4785,7 +4785,7 @@
         <v>68.09999847412109</v>
       </c>
       <c r="G150" t="n">
-        <v>1147.694091796875</v>
+        <v>1147.69384765625</v>
       </c>
       <c r="H150" t="n">
         <v>120</v>
@@ -4814,13 +4814,13 @@
         <v>67.5</v>
       </c>
       <c r="G151" t="n">
-        <v>1162.7080078125</v>
+        <v>1162.708129882812</v>
       </c>
       <c r="H151" t="n">
         <v>115.8499984741211</v>
       </c>
       <c r="I151" t="n">
-        <v>944.7916259765625</v>
+        <v>944.7916870117188</v>
       </c>
       <c r="J151" t="n">
         <v>13.30000019073486</v>
@@ -4843,13 +4843,13 @@
         <v>66.65000152587891</v>
       </c>
       <c r="G152" t="n">
-        <v>1169.660522460938</v>
+        <v>1169.660400390625</v>
       </c>
       <c r="H152" t="n">
         <v>117.5500030517578</v>
       </c>
       <c r="I152" t="n">
-        <v>944.4969482421875</v>
+        <v>944.4968872070312</v>
       </c>
       <c r="J152" t="n">
         <v>14.14999961853027</v>
@@ -4872,13 +4872,13 @@
         <v>67.19999694824219</v>
       </c>
       <c r="G153" t="n">
-        <v>1173.5556640625</v>
+        <v>1173.555541992188</v>
       </c>
       <c r="H153" t="n">
         <v>115.3499984741211</v>
       </c>
       <c r="I153" t="n">
-        <v>953.8790283203125</v>
+        <v>953.8790893554688</v>
       </c>
       <c r="J153" t="n">
         <v>13.60000038146973</v>
@@ -4901,7 +4901,7 @@
         <v>68.34999847412109</v>
       </c>
       <c r="G154" t="n">
-        <v>1192.532836914062</v>
+        <v>1192.53271484375</v>
       </c>
       <c r="H154" t="n">
         <v>115.1500015258789</v>
@@ -4936,7 +4936,7 @@
         <v>116.5500030517578</v>
       </c>
       <c r="I155" t="n">
-        <v>979.5202026367188</v>
+        <v>979.5201416015625</v>
       </c>
       <c r="J155" t="n">
         <v>13.39999961853027</v>
@@ -4959,13 +4959,13 @@
         <v>72.55000305175781</v>
       </c>
       <c r="G156" t="n">
-        <v>1207.094116210938</v>
+        <v>1207.09423828125</v>
       </c>
       <c r="H156" t="n">
         <v>121.8000030517578</v>
       </c>
       <c r="I156" t="n">
-        <v>975.4922485351562</v>
+        <v>975.4921875</v>
       </c>
       <c r="J156" t="n">
         <v>13.64999961853027</v>
@@ -4994,7 +4994,7 @@
         <v>129.8999938964844</v>
       </c>
       <c r="I157" t="n">
-        <v>1020.8798828125</v>
+        <v>1020.880004882812</v>
       </c>
       <c r="J157" t="n">
         <v>14.19999980926514</v>
@@ -5017,7 +5017,7 @@
         <v>73.75</v>
       </c>
       <c r="G158" t="n">
-        <v>1187.72216796875</v>
+        <v>1187.722045898438</v>
       </c>
       <c r="H158" t="n">
         <v>135.6000061035156</v>
@@ -5133,13 +5133,13 @@
         <v>74.05000305175781</v>
       </c>
       <c r="G162" t="n">
-        <v>1195.992065429688</v>
+        <v>1195.992309570312</v>
       </c>
       <c r="H162" t="n">
         <v>139.75</v>
       </c>
       <c r="I162" t="n">
-        <v>1002.852600097656</v>
+        <v>1002.8525390625</v>
       </c>
       <c r="J162" t="n">
         <v>15.05000019073486</v>
@@ -5191,13 +5191,13 @@
         <v>69.65000152587891</v>
       </c>
       <c r="G164" t="n">
-        <v>1180.360961914062</v>
+        <v>1180.36083984375</v>
       </c>
       <c r="H164" t="n">
         <v>158.75</v>
       </c>
       <c r="I164" t="n">
-        <v>992.1442260742188</v>
+        <v>992.144287109375</v>
       </c>
       <c r="J164" t="n">
         <v>16.29999923706055</v>
@@ -5220,13 +5220,13 @@
         <v>70.59999847412109</v>
       </c>
       <c r="G165" t="n">
-        <v>1198.673095703125</v>
+        <v>1198.672973632812</v>
       </c>
       <c r="H165" t="n">
         <v>162</v>
       </c>
       <c r="I165" t="n">
-        <v>1006.291076660156</v>
+        <v>1006.291137695312</v>
       </c>
       <c r="J165" t="n">
         <v>16.79999923706055</v>
@@ -5255,7 +5255,7 @@
         <v>193.8500061035156</v>
       </c>
       <c r="I166" t="n">
-        <v>1039.64404296875</v>
+        <v>1039.644165039062</v>
       </c>
       <c r="J166" t="n">
         <v>20.14999961853027</v>
@@ -5278,7 +5278,7 @@
         <v>71.69999694824219</v>
       </c>
       <c r="G167" t="n">
-        <v>1149.84814453125</v>
+        <v>1149.848266601562</v>
       </c>
       <c r="H167" t="n">
         <v>179.1499938964844</v>
@@ -5365,7 +5365,7 @@
         <v>75.09999847412109</v>
       </c>
       <c r="G170" t="n">
-        <v>1173.135986328125</v>
+        <v>1173.136108398438</v>
       </c>
       <c r="H170" t="n">
         <v>180.6999969482422</v>
@@ -5394,13 +5394,13 @@
         <v>73.65000152587891</v>
       </c>
       <c r="G171" t="n">
-        <v>1174.79443359375</v>
+        <v>1174.794555664062</v>
       </c>
       <c r="H171" t="n">
         <v>180.3000030517578</v>
       </c>
       <c r="I171" t="n">
-        <v>1188.775268554688</v>
+        <v>1188.775390625</v>
       </c>
       <c r="J171" t="n">
         <v>21.29999923706055</v>
@@ -5429,7 +5429,7 @@
         <v>162.4499969482422</v>
       </c>
       <c r="I172" t="n">
-        <v>1153.80126953125</v>
+        <v>1153.801147460938</v>
       </c>
       <c r="J172" t="n">
         <v>19.20000076293945</v>
@@ -5487,7 +5487,7 @@
         <v>165.5</v>
       </c>
       <c r="I174" t="n">
-        <v>1137.443969726562</v>
+        <v>1137.44384765625</v>
       </c>
       <c r="J174" t="n">
         <v>20.04999923706055</v>
@@ -5510,7 +5510,7 @@
         <v>73.25</v>
       </c>
       <c r="G175" t="n">
-        <v>1176.134887695312</v>
+        <v>1176.135009765625</v>
       </c>
       <c r="H175" t="n">
         <v>157.4499969482422</v>
@@ -5539,7 +5539,7 @@
         <v>71.75</v>
       </c>
       <c r="G176" t="n">
-        <v>1164.479736328125</v>
+        <v>1164.479858398438</v>
       </c>
       <c r="H176" t="n">
         <v>154.4499969482422</v>
@@ -5568,13 +5568,13 @@
         <v>68.65000152587891</v>
       </c>
       <c r="G177" t="n">
-        <v>1135.625610351562</v>
+        <v>1135.625732421875</v>
       </c>
       <c r="H177" t="n">
         <v>156.3500061035156</v>
       </c>
       <c r="I177" t="n">
-        <v>1119.121826171875</v>
+        <v>1119.121704101562</v>
       </c>
       <c r="J177" t="n">
         <v>18.45000076293945</v>
@@ -5597,7 +5597,7 @@
         <v>67.05000305175781</v>
       </c>
       <c r="G178" t="n">
-        <v>1137.102416992188</v>
+        <v>1137.1025390625</v>
       </c>
       <c r="H178" t="n">
         <v>151.8000030517578</v>
@@ -5684,7 +5684,7 @@
         <v>70</v>
       </c>
       <c r="G181" t="n">
-        <v>1129.672973632812</v>
+        <v>1129.673095703125</v>
       </c>
       <c r="H181" t="n">
         <v>146.1499938964844</v>
@@ -5713,7 +5713,7 @@
         <v>67.69999694824219</v>
       </c>
       <c r="G182" t="n">
-        <v>1108.498168945312</v>
+        <v>1108.498291015625</v>
       </c>
       <c r="H182" t="n">
         <v>144.1499938964844</v>
@@ -5748,7 +5748,7 @@
         <v>137.1999969482422</v>
       </c>
       <c r="I183" t="n">
-        <v>1051.699829101562</v>
+        <v>1051.699951171875</v>
       </c>
       <c r="J183" t="n">
         <v>16.35000038146973</v>
@@ -5771,13 +5771,13 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G184" t="n">
-        <v>1088.845581054688</v>
+        <v>1088.845703125</v>
       </c>
       <c r="H184" t="n">
         <v>138.3500061035156</v>
       </c>
       <c r="I184" t="n">
-        <v>1044.903930664062</v>
+        <v>1044.90380859375</v>
       </c>
       <c r="J184" t="n">
         <v>16.20000076293945</v>
@@ -5800,13 +5800,13 @@
         <v>61.70000076293945</v>
       </c>
       <c r="G185" t="n">
-        <v>1059.855346679688</v>
+        <v>1059.855102539062</v>
       </c>
       <c r="H185" t="n">
         <v>136.3500061035156</v>
       </c>
       <c r="I185" t="n">
-        <v>1021.610473632812</v>
+        <v>1021.610412597656</v>
       </c>
       <c r="J185" t="n">
         <v>16.10000038146973</v>
@@ -5829,7 +5829,7 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G186" t="n">
-        <v>1056.606323242188</v>
+        <v>1056.606201171875</v>
       </c>
       <c r="H186" t="n">
         <v>137.6499938964844</v>
@@ -5916,7 +5916,7 @@
         <v>66</v>
       </c>
       <c r="G189" t="n">
-        <v>1096.547607421875</v>
+        <v>1096.547729492188</v>
       </c>
       <c r="H189" t="n">
         <v>137.5500030517578</v>
@@ -5951,7 +5951,7 @@
         <v>144.3999938964844</v>
       </c>
       <c r="I190" t="n">
-        <v>1120.151977539062</v>
+        <v>1120.152099609375</v>
       </c>
       <c r="J190" t="n">
         <v>16.75</v>
@@ -5974,13 +5974,13 @@
         <v>68.19999694824219</v>
       </c>
       <c r="G191" t="n">
-        <v>1105.249267578125</v>
+        <v>1105.249389648438</v>
       </c>
       <c r="H191" t="n">
         <v>151.6000061035156</v>
       </c>
       <c r="I191" t="n">
-        <v>1158.268432617188</v>
+        <v>1158.268310546875</v>
       </c>
       <c r="J191" t="n">
         <v>17.54999923706055</v>
@@ -6009,7 +6009,7 @@
         <v>157.6999969482422</v>
       </c>
       <c r="I192" t="n">
-        <v>1173.879272460938</v>
+        <v>1173.87939453125</v>
       </c>
       <c r="J192" t="n">
         <v>17.75</v>
@@ -6038,7 +6038,7 @@
         <v>149.8500061035156</v>
       </c>
       <c r="I193" t="n">
-        <v>1184.81201171875</v>
+        <v>1184.811889648438</v>
       </c>
       <c r="J193" t="n">
         <v>16.89999961853027</v>
@@ -6096,7 +6096,7 @@
         <v>142.3500061035156</v>
       </c>
       <c r="I195" t="n">
-        <v>1122.663330078125</v>
+        <v>1122.663452148438</v>
       </c>
       <c r="J195" t="n">
         <v>16.5</v>
@@ -6125,7 +6125,7 @@
         <v>138.8500061035156</v>
       </c>
       <c r="I196" t="n">
-        <v>1100.404296875</v>
+        <v>1100.404174804688</v>
       </c>
       <c r="J196" t="n">
         <v>16.20000076293945</v>
@@ -6177,7 +6177,7 @@
         <v>70</v>
       </c>
       <c r="G198" t="n">
-        <v>1113.83740234375</v>
+        <v>1113.837524414062</v>
       </c>
       <c r="H198" t="n">
         <v>143.6999969482422</v>
@@ -6206,13 +6206,13 @@
         <v>65.59999847412109</v>
       </c>
       <c r="G199" t="n">
-        <v>1133.21728515625</v>
+        <v>1133.217407226562</v>
       </c>
       <c r="H199" t="n">
         <v>141.3500061035156</v>
       </c>
       <c r="I199" t="n">
-        <v>1121.087524414062</v>
+        <v>1121.087646484375</v>
       </c>
       <c r="J199" t="n">
         <v>16.35000038146973</v>
@@ -6235,7 +6235,7 @@
         <v>65.09999847412109</v>
       </c>
       <c r="G200" t="n">
-        <v>1136.261962890625</v>
+        <v>1136.261840820312</v>
       </c>
       <c r="H200" t="n">
         <v>139.1000061035156</v>
@@ -6270,7 +6270,7 @@
         <v>139.1499938964844</v>
       </c>
       <c r="I201" t="n">
-        <v>1088.585083007812</v>
+        <v>1088.585205078125</v>
       </c>
       <c r="J201" t="n">
         <v>16.35000038146973</v>
@@ -6351,13 +6351,13 @@
         <v>64.30000305175781</v>
       </c>
       <c r="G204" t="n">
-        <v>1113.7919921875</v>
+        <v>1113.791870117188</v>
       </c>
       <c r="H204" t="n">
         <v>141.8500061035156</v>
       </c>
       <c r="I204" t="n">
-        <v>1086.566040039062</v>
+        <v>1086.56591796875</v>
       </c>
       <c r="J204" t="n">
         <v>16.14999961853027</v>
@@ -6380,13 +6380,13 @@
         <v>63.25</v>
       </c>
       <c r="G205" t="n">
-        <v>1147.871704101562</v>
+        <v>1147.871826171875</v>
       </c>
       <c r="H205" t="n">
         <v>141.8999938964844</v>
       </c>
       <c r="I205" t="n">
-        <v>1081.690551757812</v>
+        <v>1081.690673828125</v>
       </c>
       <c r="J205" t="n">
         <v>16</v>
@@ -6415,7 +6415,7 @@
         <v>141.4499969482422</v>
       </c>
       <c r="I206" t="n">
-        <v>1081.54296875</v>
+        <v>1081.542846679688</v>
       </c>
       <c r="J206" t="n">
         <v>16.10000038146973</v>
@@ -6496,7 +6496,7 @@
         <v>62.75</v>
       </c>
       <c r="G209" t="n">
-        <v>1161.049194335938</v>
+        <v>1161.049072265625</v>
       </c>
       <c r="H209" t="n">
         <v>140.1499938964844</v>
@@ -6531,7 +6531,7 @@
         <v>147.1499938964844</v>
       </c>
       <c r="I210" t="n">
-        <v>1074.057495117188</v>
+        <v>1074.0576171875</v>
       </c>
       <c r="J210" t="n">
         <v>16.79999923706055</v>
@@ -6560,7 +6560,7 @@
         <v>152.9499969482422</v>
       </c>
       <c r="I211" t="n">
-        <v>1081.93701171875</v>
+        <v>1081.936889648438</v>
       </c>
       <c r="J211" t="n">
         <v>16.85000038146973</v>
@@ -6589,7 +6589,7 @@
         <v>146.6499938964844</v>
       </c>
       <c r="I212" t="n">
-        <v>1074.057495117188</v>
+        <v>1074.0576171875</v>
       </c>
       <c r="J212" t="n">
         <v>16.45000076293945</v>
@@ -6612,13 +6612,13 @@
         <v>64.5</v>
       </c>
       <c r="G213" t="n">
-        <v>1168.932983398438</v>
+        <v>1168.932861328125</v>
       </c>
       <c r="H213" t="n">
         <v>142.8500061035156</v>
       </c>
       <c r="I213" t="n">
-        <v>1053.669799804688</v>
+        <v>1053.669677734375</v>
       </c>
       <c r="J213" t="n">
         <v>16.10000038146973</v>
@@ -6641,7 +6641,7 @@
         <v>63.95000076293945</v>
       </c>
       <c r="G214" t="n">
-        <v>1195.878662109375</v>
+        <v>1195.878540039062</v>
       </c>
       <c r="H214" t="n">
         <v>146.1999969482422</v>
@@ -6699,13 +6699,13 @@
         <v>63.04999923706055</v>
       </c>
       <c r="G216" t="n">
-        <v>1184.745849609375</v>
+        <v>1184.745971679688</v>
       </c>
       <c r="H216" t="n">
         <v>151.3500061035156</v>
       </c>
       <c r="I216" t="n">
-        <v>1058.93896484375</v>
+        <v>1058.939086914062</v>
       </c>
       <c r="J216" t="n">
         <v>16.10000038146973</v>
@@ -6728,7 +6728,7 @@
         <v>62.54999923706055</v>
       </c>
       <c r="G217" t="n">
-        <v>1177.952758789062</v>
+        <v>1177.95263671875</v>
       </c>
       <c r="H217" t="n">
         <v>148.6499938964844</v>
@@ -6763,7 +6763,7 @@
         <v>146.0500030517578</v>
       </c>
       <c r="I218" t="n">
-        <v>1011.120971679688</v>
+        <v>1011.121032714844</v>
       </c>
       <c r="J218" t="n">
         <v>15.64999961853027</v>
@@ -6786,13 +6786,13 @@
         <v>61.59999847412109</v>
       </c>
       <c r="G219" t="n">
-        <v>1180.360961914062</v>
+        <v>1180.36083984375</v>
       </c>
       <c r="H219" t="n">
         <v>147.6499938964844</v>
       </c>
       <c r="I219" t="n">
-        <v>990.683837890625</v>
+        <v>990.6838989257812</v>
       </c>
       <c r="J219" t="n">
         <v>15.5</v>
@@ -6850,7 +6850,7 @@
         <v>141.3000030517578</v>
       </c>
       <c r="I221" t="n">
-        <v>985.06982421875</v>
+        <v>985.0698852539062</v>
       </c>
       <c r="J221" t="n">
         <v>15.05000019073486</v>
@@ -6902,13 +6902,13 @@
         <v>60.40000152587891</v>
       </c>
       <c r="G223" t="n">
-        <v>1171.932006835938</v>
+        <v>1171.931884765625</v>
       </c>
       <c r="H223" t="n">
         <v>147.0500030517578</v>
       </c>
       <c r="I223" t="n">
-        <v>990.5853271484375</v>
+        <v>990.5853881835938</v>
       </c>
       <c r="J223" t="n">
         <v>15.25</v>
@@ -6966,7 +6966,7 @@
         <v>153.6499938964844</v>
       </c>
       <c r="I225" t="n">
-        <v>1027.520141601562</v>
+        <v>1027.52001953125</v>
       </c>
       <c r="J225" t="n">
         <v>16</v>
@@ -7024,7 +7024,7 @@
         <v>157.6999969482422</v>
       </c>
       <c r="I227" t="n">
-        <v>1039.289794921875</v>
+        <v>1039.289672851562</v>
       </c>
       <c r="J227" t="n">
         <v>16.04999923706055</v>
@@ -7076,13 +7076,13 @@
         <v>74.19999694824219</v>
       </c>
       <c r="G229" t="n">
-        <v>1236.93310546875</v>
+        <v>1236.932983398438</v>
       </c>
       <c r="H229" t="n">
         <v>162.8999938964844</v>
       </c>
       <c r="I229" t="n">
-        <v>1033.675659179688</v>
+        <v>1033.67578125</v>
       </c>
       <c r="J229" t="n">
         <v>16.79999923706055</v>
@@ -7105,13 +7105,13 @@
         <v>75.94999694824219</v>
       </c>
       <c r="G230" t="n">
-        <v>1218.8935546875</v>
+        <v>1218.893676757812</v>
       </c>
       <c r="H230" t="n">
         <v>157.8999938964844</v>
       </c>
       <c r="I230" t="n">
-        <v>1054.162231445312</v>
+        <v>1054.162109375</v>
       </c>
       <c r="J230" t="n">
         <v>16.04999923706055</v>
@@ -7134,13 +7134,13 @@
         <v>73.5</v>
       </c>
       <c r="G231" t="n">
-        <v>1222.415283203125</v>
+        <v>1222.415161132812</v>
       </c>
       <c r="H231" t="n">
         <v>156.3999938964844</v>
       </c>
       <c r="I231" t="n">
-        <v>1050.41943359375</v>
+        <v>1050.419555664062</v>
       </c>
       <c r="J231" t="n">
         <v>15.85000038146973</v>
@@ -7163,7 +7163,7 @@
         <v>71.19999694824219</v>
       </c>
       <c r="G232" t="n">
-        <v>1204.375854492188</v>
+        <v>1204.375732421875</v>
       </c>
       <c r="H232" t="n">
         <v>154.1999969482422</v>
@@ -7198,7 +7198,7 @@
         <v>154.0500030517578</v>
       </c>
       <c r="I233" t="n">
-        <v>1031.31201171875</v>
+        <v>1031.311889648438</v>
       </c>
       <c r="J233" t="n">
         <v>15.85000038146973</v>
@@ -7221,7 +7221,7 @@
         <v>72.90000152587891</v>
       </c>
       <c r="G234" t="n">
-        <v>1185.563720703125</v>
+        <v>1185.563842773438</v>
       </c>
       <c r="H234" t="n">
         <v>154.75</v>
@@ -7285,7 +7285,7 @@
         <v>157.25</v>
       </c>
       <c r="I236" t="n">
-        <v>1016.48876953125</v>
+        <v>1016.488891601562</v>
       </c>
       <c r="J236" t="n">
         <v>15.75</v>
@@ -7343,7 +7343,7 @@
         <v>148.8999938964844</v>
       </c>
       <c r="I238" t="n">
-        <v>1001.271789550781</v>
+        <v>1001.271850585938</v>
       </c>
       <c r="J238" t="n">
         <v>15.89999961853027</v>
@@ -7372,7 +7372,7 @@
         <v>151.1000061035156</v>
       </c>
       <c r="I239" t="n">
-        <v>982.7552490234375</v>
+        <v>982.7553100585938</v>
       </c>
       <c r="J239" t="n">
         <v>15.75</v>
@@ -7395,13 +7395,13 @@
         <v>70.94999694824219</v>
       </c>
       <c r="G240" t="n">
-        <v>1181.110595703125</v>
+        <v>1181.110717773438</v>
       </c>
       <c r="H240" t="n">
         <v>150.6499938964844</v>
       </c>
       <c r="I240" t="n">
-        <v>989.0095825195312</v>
+        <v>989.009521484375</v>
       </c>
       <c r="J240" t="n">
         <v>15.80000019073486</v>
@@ -7424,13 +7424,13 @@
         <v>71.34999847412109</v>
       </c>
       <c r="G241" t="n">
-        <v>1191.334716796875</v>
+        <v>1191.334594726562</v>
       </c>
       <c r="H241" t="n">
         <v>149.8000030517578</v>
       </c>
       <c r="I241" t="n">
-        <v>982.2135009765625</v>
+        <v>982.2135620117188</v>
       </c>
       <c r="J241" t="n">
         <v>15.75</v>
@@ -7517,7 +7517,7 @@
         <v>128.6999969482422</v>
       </c>
       <c r="I244" t="n">
-        <v>796.0140380859375</v>
+        <v>796.0140991210938</v>
       </c>
       <c r="J244" t="n">
         <v>13.55000019073486</v>
@@ -7546,7 +7546,7 @@
         <v>128.1999969482422</v>
       </c>
       <c r="I245" t="n">
-        <v>858.014892578125</v>
+        <v>858.0149536132812</v>
       </c>
       <c r="J245" t="n">
         <v>14.14999961853027</v>
@@ -7569,13 +7569,13 @@
         <v>65.80000305175781</v>
       </c>
       <c r="G246" t="n">
-        <v>1156.30078125</v>
+        <v>1156.300659179688</v>
       </c>
       <c r="H246" t="n">
         <v>134.6000061035156</v>
       </c>
       <c r="I246" t="n">
-        <v>890.71435546875</v>
+        <v>890.7142944335938</v>
       </c>
       <c r="J246" t="n">
         <v>14.80000019073486</v>
@@ -7627,13 +7627,13 @@
         <v>66.15000152587891</v>
       </c>
       <c r="G248" t="n">
-        <v>1155.664428710938</v>
+        <v>1155.66455078125</v>
       </c>
       <c r="H248" t="n">
         <v>135.8000030517578</v>
       </c>
       <c r="I248" t="n">
-        <v>928.781494140625</v>
+        <v>928.7815551757812</v>
       </c>
       <c r="J248" t="n">
         <v>14.30000019073486</v>
@@ -7656,7 +7656,7 @@
         <v>66.09999847412109</v>
       </c>
       <c r="G249" t="n">
-        <v>1157.436767578125</v>
+        <v>1157.4365234375</v>
       </c>
       <c r="H249" t="n">
         <v>137.6999969482422</v>
@@ -7685,13 +7685,13 @@
         <v>67.55000305175781</v>
       </c>
       <c r="G250" t="n">
-        <v>1170.477905273438</v>
+        <v>1170.477783203125</v>
       </c>
       <c r="H250" t="n">
         <v>137.8500061035156</v>
       </c>
       <c r="I250" t="n">
-        <v>937.2025756835938</v>
+        <v>937.20263671875</v>
       </c>
       <c r="J250" t="n">
         <v>14.69999980926514</v>
@@ -7743,13 +7743,13 @@
         <v>65.75</v>
       </c>
       <c r="G252" t="n">
-        <v>1144.418334960938</v>
+        <v>1144.418212890625</v>
       </c>
       <c r="H252" t="n">
         <v>136.4499969482422</v>
       </c>
       <c r="I252" t="n">
-        <v>901.9916381835938</v>
+        <v>901.9915771484375</v>
       </c>
       <c r="J252" t="n">
         <v>14.44999980926514</v>
@@ -7772,13 +7772,13 @@
         <v>65.75</v>
       </c>
       <c r="G253" t="n">
-        <v>1142.37353515625</v>
+        <v>1142.373413085938</v>
       </c>
       <c r="H253" t="n">
         <v>133.75</v>
       </c>
       <c r="I253" t="n">
-        <v>905.3403930664062</v>
+        <v>905.3404541015625</v>
       </c>
       <c r="J253" t="n">
         <v>14.60000038146973</v>
@@ -7801,13 +7801,13 @@
         <v>65.40000152587891</v>
       </c>
       <c r="G254" t="n">
-        <v>1152.75634765625</v>
+        <v>1152.756469726562</v>
       </c>
       <c r="H254" t="n">
         <v>130.1999969482422</v>
       </c>
       <c r="I254" t="n">
-        <v>892.9303588867188</v>
+        <v>892.9302978515625</v>
       </c>
       <c r="J254" t="n">
         <v>14.44999980926514</v>
@@ -7830,7 +7830,7 @@
         <v>64.75</v>
       </c>
       <c r="G255" t="n">
-        <v>1179.974731445312</v>
+        <v>1179.974609375</v>
       </c>
       <c r="H255" t="n">
         <v>135.0500030517578</v>
@@ -7859,7 +7859,7 @@
         <v>63.75</v>
       </c>
       <c r="G256" t="n">
-        <v>1162.52587890625</v>
+        <v>1162.526000976562</v>
       </c>
       <c r="H256" t="n">
         <v>133</v>
@@ -7888,7 +7888,7 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G257" t="n">
-        <v>1147.871704101562</v>
+        <v>1147.871826171875</v>
       </c>
       <c r="H257" t="n">
         <v>134.3000030517578</v>
@@ -7946,13 +7946,13 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G259" t="n">
-        <v>1121.266723632812</v>
+        <v>1121.266845703125</v>
       </c>
       <c r="H259" t="n">
         <v>132.6499938964844</v>
       </c>
       <c r="I259" t="n">
-        <v>899.332275390625</v>
+        <v>899.3323364257812</v>
       </c>
       <c r="J259" t="n">
         <v>14.14999961853027</v>
@@ -7975,7 +7975,7 @@
         <v>65.44999694824219</v>
       </c>
       <c r="G260" t="n">
-        <v>1110.588623046875</v>
+        <v>1110.588500976562</v>
       </c>
       <c r="H260" t="n">
         <v>139.25</v>
@@ -8010,7 +8010,7 @@
         <v>141.3000030517578</v>
       </c>
       <c r="I261" t="n">
-        <v>883.5243530273438</v>
+        <v>883.5242919921875</v>
       </c>
       <c r="J261" t="n">
         <v>14.14999961853027</v>
@@ -8033,13 +8033,13 @@
         <v>62.84999847412109</v>
       </c>
       <c r="G262" t="n">
-        <v>1124.493041992188</v>
+        <v>1124.492919921875</v>
       </c>
       <c r="H262" t="n">
         <v>139.5</v>
       </c>
       <c r="I262" t="n">
-        <v>899.6770629882812</v>
+        <v>899.6771240234375</v>
       </c>
       <c r="J262" t="n">
         <v>14</v>
@@ -8097,7 +8097,7 @@
         <v>136.25</v>
       </c>
       <c r="I264" t="n">
-        <v>895.392578125</v>
+        <v>895.3926391601562</v>
       </c>
       <c r="J264" t="n">
         <v>13.85000038146973</v>
@@ -8126,7 +8126,7 @@
         <v>133.6999969482422</v>
       </c>
       <c r="I265" t="n">
-        <v>892.0439453125</v>
+        <v>892.0438842773438</v>
       </c>
       <c r="J265" t="n">
         <v>13.19999980926514</v>
@@ -8155,7 +8155,7 @@
         <v>132.1000061035156</v>
       </c>
       <c r="I266" t="n">
-        <v>882.8842163085938</v>
+        <v>882.8841552734375</v>
       </c>
       <c r="J266" t="n">
         <v>13.19999980926514</v>
@@ -8178,7 +8178,7 @@
         <v>60.90000152587891</v>
       </c>
       <c r="G267" t="n">
-        <v>1082.620361328125</v>
+        <v>1082.620239257812</v>
       </c>
       <c r="H267" t="n">
         <v>128.1499938964844</v>
@@ -8236,7 +8236,7 @@
         <v>58.45000076293945</v>
       </c>
       <c r="G269" t="n">
-        <v>1072.26025390625</v>
+        <v>1072.260375976562</v>
       </c>
       <c r="H269" t="n">
         <v>119.1500015258789</v>
@@ -8271,7 +8271,7 @@
         <v>125.0999984741211</v>
       </c>
       <c r="I270" t="n">
-        <v>856.8822021484375</v>
+        <v>856.8822631835938</v>
       </c>
       <c r="J270" t="n">
         <v>12.75</v>
@@ -8323,7 +8323,7 @@
         <v>59.20000076293945</v>
       </c>
       <c r="G272" t="n">
-        <v>1057.35595703125</v>
+        <v>1057.356079101562</v>
       </c>
       <c r="H272" t="n">
         <v>121.3000030517578</v>
@@ -8474,7 +8474,7 @@
         <v>127.3000030517578</v>
       </c>
       <c r="I277" t="n">
-        <v>831.4220581054688</v>
+        <v>831.4219970703125</v>
       </c>
       <c r="J277" t="n">
         <v>11.69999980926514</v>
@@ -8532,7 +8532,7 @@
         <v>127.5500030517578</v>
       </c>
       <c r="I279" t="n">
-        <v>823.788818359375</v>
+        <v>823.7888793945312</v>
       </c>
       <c r="J279" t="n">
         <v>11.35000038146973</v>
@@ -8584,7 +8584,7 @@
         <v>60.25</v>
       </c>
       <c r="G281" t="n">
-        <v>1105.0673828125</v>
+        <v>1105.067504882812</v>
       </c>
       <c r="H281" t="n">
         <v>128.4499969482422</v>
@@ -8700,7 +8700,7 @@
         <v>60.40000152587891</v>
       </c>
       <c r="G285" t="n">
-        <v>1106.044555664062</v>
+        <v>1106.044677734375</v>
       </c>
       <c r="H285" t="n">
         <v>120.8000030517578</v>
@@ -8729,13 +8729,13 @@
         <v>59.34999847412109</v>
       </c>
       <c r="G286" t="n">
-        <v>1080.961791992188</v>
+        <v>1080.9619140625</v>
       </c>
       <c r="H286" t="n">
         <v>118.5500030517578</v>
       </c>
       <c r="I286" t="n">
-        <v>818.1255493164062</v>
+        <v>818.1256103515625</v>
       </c>
       <c r="J286" t="n">
         <v>10.39999961853027</v>
@@ -8758,7 +8758,7 @@
         <v>59.04999923706055</v>
       </c>
       <c r="G287" t="n">
-        <v>1075.781860351562</v>
+        <v>1075.78173828125</v>
       </c>
       <c r="H287" t="n">
         <v>115.8000030517578</v>
@@ -8787,7 +8787,7 @@
         <v>58.5</v>
       </c>
       <c r="G288" t="n">
-        <v>1083.142944335938</v>
+        <v>1083.142822265625</v>
       </c>
       <c r="H288" t="n">
         <v>126.9499969482422</v>
@@ -8816,7 +8816,7 @@
         <v>57.34999847412109</v>
       </c>
       <c r="G289" t="n">
-        <v>1075.940673828125</v>
+        <v>1075.940795898438</v>
       </c>
       <c r="H289" t="n">
         <v>127.75</v>
@@ -8845,7 +8845,7 @@
         <v>58.40000152587891</v>
       </c>
       <c r="G290" t="n">
-        <v>1055.356567382812</v>
+        <v>1055.356689453125</v>
       </c>
       <c r="H290" t="n">
         <v>130.6999969482422</v>
@@ -8874,7 +8874,7 @@
         <v>58.90000152587891</v>
       </c>
       <c r="G291" t="n">
-        <v>1065.057861328125</v>
+        <v>1065.057983398438</v>
       </c>
       <c r="H291" t="n">
         <v>135.6999969482422</v>
@@ -8909,7 +8909,7 @@
         <v>135.8000030517578</v>
       </c>
       <c r="I292" t="n">
-        <v>827.482421875</v>
+        <v>827.4823608398438</v>
       </c>
       <c r="J292" t="n">
         <v>9.800000190734863</v>
@@ -8961,13 +8961,13 @@
         <v>59.15000152587891</v>
       </c>
       <c r="G294" t="n">
-        <v>1094.5029296875</v>
+        <v>1094.502807617188</v>
       </c>
       <c r="H294" t="n">
         <v>140.8000030517578</v>
       </c>
       <c r="I294" t="n">
-        <v>843.8319702148438</v>
+        <v>843.83203125</v>
       </c>
       <c r="J294" t="n">
         <v>10.69999980926514</v>
@@ -9025,7 +9025,7 @@
         <v>146.3500061035156</v>
       </c>
       <c r="I296" t="n">
-        <v>854.5183715820312</v>
+        <v>854.5184326171875</v>
       </c>
       <c r="J296" t="n">
         <v>11.19999980926514</v>
@@ -9048,13 +9048,13 @@
         <v>58.25</v>
       </c>
       <c r="G297" t="n">
-        <v>1055.424926757812</v>
+        <v>1055.4248046875</v>
       </c>
       <c r="H297" t="n">
         <v>147.25</v>
       </c>
       <c r="I297" t="n">
-        <v>835.9034423828125</v>
+        <v>835.9033813476562</v>
       </c>
       <c r="J297" t="n">
         <v>11.44999980926514</v>
@@ -9077,7 +9077,7 @@
         <v>55.40000152587891</v>
       </c>
       <c r="G298" t="n">
-        <v>1038.06689453125</v>
+        <v>1038.067016601562</v>
       </c>
       <c r="H298" t="n">
         <v>139.6499938964844</v>
@@ -9170,7 +9170,7 @@
         <v>141.25</v>
       </c>
       <c r="I301" t="n">
-        <v>772.7699584960938</v>
+        <v>772.7698974609375</v>
       </c>
       <c r="J301" t="n">
         <v>10.55000019073486</v>
@@ -9228,7 +9228,7 @@
         <v>148.0500030517578</v>
       </c>
       <c r="I303" t="n">
-        <v>771.5879516601562</v>
+        <v>771.5880126953125</v>
       </c>
       <c r="J303" t="n">
         <v>10.30000019073486</v>
@@ -9251,7 +9251,7 @@
         <v>59.59999847412109</v>
       </c>
       <c r="G304" t="n">
-        <v>1031.341918945312</v>
+        <v>1031.341796875</v>
       </c>
       <c r="H304" t="n">
         <v>146.8500061035156</v>
@@ -9286,7 +9286,7 @@
         <v>148.8999938964844</v>
       </c>
       <c r="I305" t="n">
-        <v>778.1377563476562</v>
+        <v>778.1376953125</v>
       </c>
       <c r="J305" t="n">
         <v>10.30000019073486</v>
@@ -9309,7 +9309,7 @@
         <v>56.20000076293945</v>
       </c>
       <c r="G306" t="n">
-        <v>1021.390625</v>
+        <v>1021.390686035156</v>
       </c>
       <c r="H306" t="n">
         <v>148.1999969482422</v>
@@ -9344,7 +9344,7 @@
         <v>143.1000061035156</v>
       </c>
       <c r="I307" t="n">
-        <v>753.7608642578125</v>
+        <v>753.7608032226562</v>
       </c>
       <c r="J307" t="n">
         <v>9.850000381469727</v>
@@ -9367,13 +9367,13 @@
         <v>53.59999847412109</v>
       </c>
       <c r="G308" t="n">
-        <v>1016.73291015625</v>
+        <v>1016.732971191406</v>
       </c>
       <c r="H308" t="n">
         <v>142.1999969482422</v>
       </c>
       <c r="I308" t="n">
-        <v>736.9678955078125</v>
+        <v>736.9679565429688</v>
       </c>
       <c r="J308" t="n">
         <v>9.399999618530273</v>
@@ -9454,7 +9454,7 @@
         <v>54.25</v>
       </c>
       <c r="G311" t="n">
-        <v>1059.218994140625</v>
+        <v>1059.219116210938</v>
       </c>
       <c r="H311" t="n">
         <v>144.25</v>
@@ -9483,7 +9483,7 @@
         <v>56</v>
       </c>
       <c r="G312" t="n">
-        <v>1059.400756835938</v>
+        <v>1059.40087890625</v>
       </c>
       <c r="H312" t="n">
         <v>146.3999938964844</v>
@@ -9518,7 +9518,7 @@
         <v>151.3999938964844</v>
       </c>
       <c r="I313" t="n">
-        <v>782.5698852539062</v>
+        <v>782.56982421875</v>
       </c>
       <c r="J313" t="n">
         <v>10.80000019073486</v>
@@ -9541,13 +9541,13 @@
         <v>56.54999923706055</v>
       </c>
       <c r="G314" t="n">
-        <v>1063.94482421875</v>
+        <v>1063.944702148438</v>
       </c>
       <c r="H314" t="n">
         <v>151.3999938964844</v>
       </c>
       <c r="I314" t="n">
-        <v>792.2221069335938</v>
+        <v>792.2220458984375</v>
       </c>
       <c r="J314" t="n">
         <v>11.14999961853027</v>
@@ -9570,7 +9570,7 @@
         <v>56.29999923706055</v>
       </c>
       <c r="G315" t="n">
-        <v>1056.40185546875</v>
+        <v>1056.401733398438</v>
       </c>
       <c r="H315" t="n">
         <v>146.8000030517578</v>
@@ -9605,7 +9605,7 @@
         <v>157.3500061035156</v>
       </c>
       <c r="I316" t="n">
-        <v>804.1397094726562</v>
+        <v>804.1396484375</v>
       </c>
       <c r="J316" t="n">
         <v>12.55000019073486</v>
@@ -9634,7 +9634,7 @@
         <v>155.6999969482422</v>
       </c>
       <c r="I317" t="n">
-        <v>799.6090087890625</v>
+        <v>799.6090698242188</v>
       </c>
       <c r="J317" t="n">
         <v>12.14999961853027</v>
@@ -9657,7 +9657,7 @@
         <v>55.20000076293945</v>
       </c>
       <c r="G318" t="n">
-        <v>1070.328979492188</v>
+        <v>1070.3291015625</v>
       </c>
       <c r="H318" t="n">
         <v>165.5500030517578</v>
@@ -9692,7 +9692,7 @@
         <v>162</v>
       </c>
       <c r="I319" t="n">
-        <v>843.8319702148438</v>
+        <v>843.83203125</v>
       </c>
       <c r="J319" t="n">
         <v>12.69999980926514</v>
@@ -9744,13 +9744,13 @@
         <v>55</v>
       </c>
       <c r="G321" t="n">
-        <v>1068.73876953125</v>
+        <v>1068.738647460938</v>
       </c>
       <c r="H321" t="n">
         <v>159.1999969482422</v>
       </c>
       <c r="I321" t="n">
-        <v>823.4932861328125</v>
+        <v>823.4933471679688</v>
       </c>
       <c r="J321" t="n">
         <v>12.25</v>
@@ -9837,7 +9837,7 @@
         <v>157.8500061035156</v>
       </c>
       <c r="I324" t="n">
-        <v>821.6712646484375</v>
+        <v>821.6712036132812</v>
       </c>
       <c r="J324" t="n">
         <v>11.80000019073486</v>
@@ -9947,7 +9947,7 @@
         <v>58.04999923706055</v>
       </c>
       <c r="G328" t="n">
-        <v>1099.86474609375</v>
+        <v>1099.864624023438</v>
       </c>
       <c r="H328" t="n">
         <v>157.5500030517578</v>
@@ -9976,7 +9976,7 @@
         <v>58.40000152587891</v>
       </c>
       <c r="G329" t="n">
-        <v>1109.20263671875</v>
+        <v>1109.202514648438</v>
       </c>
       <c r="H329" t="n">
         <v>154.9499969482422</v>
@@ -10005,7 +10005,7 @@
         <v>58.34999847412109</v>
       </c>
       <c r="G330" t="n">
-        <v>1099.682983398438</v>
+        <v>1099.682861328125</v>
       </c>
       <c r="H330" t="n">
         <v>153.75</v>
@@ -10063,7 +10063,7 @@
         <v>57.5</v>
       </c>
       <c r="G332" t="n">
-        <v>1109.520629882812</v>
+        <v>1109.5205078125</v>
       </c>
       <c r="H332" t="n">
         <v>153.6000061035156</v>
@@ -10092,13 +10092,13 @@
         <v>57.09999847412109</v>
       </c>
       <c r="G333" t="n">
-        <v>1123.220825195312</v>
+        <v>1123.220703125</v>
       </c>
       <c r="H333" t="n">
         <v>152.4499969482422</v>
       </c>
       <c r="I333" t="n">
-        <v>868.3566284179688</v>
+        <v>868.3565673828125</v>
       </c>
       <c r="J333" t="n">
         <v>12.14999961853027</v>
@@ -10121,7 +10121,7 @@
         <v>56.25</v>
       </c>
       <c r="G334" t="n">
-        <v>1126.696899414062</v>
+        <v>1126.69677734375</v>
       </c>
       <c r="H334" t="n">
         <v>150.3000030517578</v>
@@ -10179,7 +10179,7 @@
         <v>58.59999847412109</v>
       </c>
       <c r="G336" t="n">
-        <v>1127.037719726562</v>
+        <v>1127.03759765625</v>
       </c>
       <c r="H336" t="n">
         <v>147.8500061035156</v>
@@ -10243,7 +10243,7 @@
         <v>144.1499938964844</v>
       </c>
       <c r="I338" t="n">
-        <v>873.1334228515625</v>
+        <v>873.1334838867188</v>
       </c>
       <c r="J338" t="n">
         <v>11.60000038146973</v>
@@ -10266,13 +10266,13 @@
         <v>59.54999923706055</v>
       </c>
       <c r="G339" t="n">
-        <v>1114.996215820312</v>
+        <v>1114.99609375</v>
       </c>
       <c r="H339" t="n">
         <v>140.8999938964844</v>
       </c>
       <c r="I339" t="n">
-        <v>886.9715576171875</v>
+        <v>886.9716186523438</v>
       </c>
       <c r="J339" t="n">
         <v>11.69999980926514</v>
@@ -10382,7 +10382,7 @@
         <v>58.29999923706055</v>
       </c>
       <c r="G343" t="n">
-        <v>1115.54150390625</v>
+        <v>1115.541259765625</v>
       </c>
       <c r="H343" t="n">
         <v>134.6499938964844</v>
@@ -10498,13 +10498,13 @@
         <v>60.20000076293945</v>
       </c>
       <c r="G347" t="n">
-        <v>1138.94287109375</v>
+        <v>1138.942749023438</v>
       </c>
       <c r="H347" t="n">
         <v>138</v>
       </c>
       <c r="I347" t="n">
-        <v>887.020751953125</v>
+        <v>887.0208740234375</v>
       </c>
       <c r="J347" t="n">
         <v>13.05000019073486</v>
@@ -10533,7 +10533,7 @@
         <v>139.6499938964844</v>
       </c>
       <c r="I348" t="n">
-        <v>897.3624877929688</v>
+        <v>897.3624267578125</v>
       </c>
       <c r="J348" t="n">
         <v>13.30000019073486</v>
@@ -10562,7 +10562,7 @@
         <v>138.6000061035156</v>
       </c>
       <c r="I349" t="n">
-        <v>902.0902099609375</v>
+        <v>902.0901489257812</v>
       </c>
       <c r="J349" t="n">
         <v>12.94999980926514</v>
@@ -10585,13 +10585,13 @@
         <v>61.29999923706055</v>
       </c>
       <c r="G350" t="n">
-        <v>1122.311767578125</v>
+        <v>1122.311889648438</v>
       </c>
       <c r="H350" t="n">
         <v>134.6999969482422</v>
       </c>
       <c r="I350" t="n">
-        <v>894.8018188476562</v>
+        <v>894.8017578125</v>
       </c>
       <c r="J350" t="n">
         <v>12.94999980926514</v>
@@ -10614,7 +10614,7 @@
         <v>65.15000152587891</v>
       </c>
       <c r="G351" t="n">
-        <v>1119.290161132812</v>
+        <v>1119.2900390625</v>
       </c>
       <c r="H351" t="n">
         <v>133.9499969482422</v>
@@ -10678,7 +10678,7 @@
         <v>132.8000030517578</v>
       </c>
       <c r="I353" t="n">
-        <v>922.5765991210938</v>
+        <v>922.5765380859375</v>
       </c>
       <c r="J353" t="n">
         <v>13.10000038146973</v>
@@ -10730,7 +10730,7 @@
         <v>66.75</v>
       </c>
       <c r="G355" t="n">
-        <v>1135.148559570312</v>
+        <v>1135.148681640625</v>
       </c>
       <c r="H355" t="n">
         <v>136.0500030517578</v>
@@ -10759,13 +10759,13 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G356" t="n">
-        <v>1135.830078125</v>
+        <v>1135.830200195312</v>
       </c>
       <c r="H356" t="n">
         <v>137.0500030517578</v>
       </c>
       <c r="I356" t="n">
-        <v>935.3805541992188</v>
+        <v>935.3804931640625</v>
       </c>
       <c r="J356" t="n">
         <v>14.05000019073486</v>
@@ -10788,13 +10788,13 @@
         <v>63.75</v>
       </c>
       <c r="G357" t="n">
-        <v>1127.787353515625</v>
+        <v>1127.787231445312</v>
       </c>
       <c r="H357" t="n">
         <v>137.1999969482422</v>
       </c>
       <c r="I357" t="n">
-        <v>927.402587890625</v>
+        <v>927.4026489257812</v>
       </c>
       <c r="J357" t="n">
         <v>13.94999980926514</v>
@@ -10852,7 +10852,7 @@
         <v>143.8500061035156</v>
       </c>
       <c r="I359" t="n">
-        <v>949.0529174804688</v>
+        <v>949.0528564453125</v>
       </c>
       <c r="J359" t="n">
         <v>16.04999923706055</v>
@@ -10910,7 +10910,7 @@
         <v>149.4499969482422</v>
       </c>
       <c r="I361" t="n">
-        <v>938.8209228515625</v>
+        <v>938.8209838867188</v>
       </c>
       <c r="J361" t="n">
         <v>16.75</v>
@@ -10933,7 +10933,7 @@
         <v>65.59999847412109</v>
       </c>
       <c r="G362" t="n">
-        <v>1171.159423828125</v>
+        <v>1171.159545898438</v>
       </c>
       <c r="H362" t="n">
         <v>151.5500030517578</v>
@@ -11055,7 +11055,7 @@
         <v>145.1499938964844</v>
       </c>
       <c r="I366" t="n">
-        <v>939.512939453125</v>
+        <v>939.5128784179688</v>
       </c>
       <c r="J366" t="n">
         <v>14.75</v>
@@ -11084,7 +11084,7 @@
         <v>143.25</v>
       </c>
       <c r="I367" t="n">
-        <v>917.368408203125</v>
+        <v>917.3683471679688</v>
       </c>
       <c r="J367" t="n">
         <v>14.75</v>
@@ -11107,13 +11107,13 @@
         <v>63.29999923706055</v>
       </c>
       <c r="G368" t="n">
-        <v>1133.967041015625</v>
+        <v>1133.967163085938</v>
       </c>
       <c r="H368" t="n">
         <v>140.1999969482422</v>
       </c>
       <c r="I368" t="n">
-        <v>924.0414428710938</v>
+        <v>924.0413818359375</v>
       </c>
       <c r="J368" t="n">
         <v>14.10000038146973</v>
@@ -11252,7 +11252,7 @@
         <v>62.45000076293945</v>
       </c>
       <c r="G373" t="n">
-        <v>1176.316772460938</v>
+        <v>1176.31689453125</v>
       </c>
       <c r="H373" t="n">
         <v>137.1000061035156</v>
@@ -11316,7 +11316,7 @@
         <v>138.75</v>
       </c>
       <c r="I375" t="n">
-        <v>952.908447265625</v>
+        <v>952.9085083007812</v>
       </c>
       <c r="J375" t="n">
         <v>15.30000019073486</v>
@@ -11339,7 +11339,7 @@
         <v>64.15000152587891</v>
       </c>
       <c r="G376" t="n">
-        <v>1196.696533203125</v>
+        <v>1196.696411132812</v>
       </c>
       <c r="H376" t="n">
         <v>138.6000061035156</v>
@@ -11403,7 +11403,7 @@
         <v>136.8000030517578</v>
       </c>
       <c r="I378" t="n">
-        <v>948.6079711914062</v>
+        <v>948.6080322265625</v>
       </c>
       <c r="J378" t="n">
         <v>15.35000038146973</v>
@@ -11426,7 +11426,7 @@
         <v>63.45000076293945</v>
       </c>
       <c r="G379" t="n">
-        <v>1257.653564453125</v>
+        <v>1257.653686523438</v>
       </c>
       <c r="H379" t="n">
         <v>137.5500030517578</v>
@@ -11455,13 +11455,13 @@
         <v>62.79999923706055</v>
       </c>
       <c r="G380" t="n">
-        <v>1246.407470703125</v>
+        <v>1246.407348632812</v>
       </c>
       <c r="H380" t="n">
         <v>136.4499969482422</v>
       </c>
       <c r="I380" t="n">
-        <v>929.0338134765625</v>
+        <v>929.0338745117188</v>
       </c>
       <c r="J380" t="n">
         <v>15.19999980926514</v>
@@ -11542,7 +11542,7 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G383" t="n">
-        <v>1281.600219726562</v>
+        <v>1281.600341796875</v>
       </c>
       <c r="H383" t="n">
         <v>141.6999969482422</v>
@@ -11664,7 +11664,7 @@
         <v>162.6000061035156</v>
       </c>
       <c r="I387" t="n">
-        <v>949.4484252929688</v>
+        <v>949.4483642578125</v>
       </c>
       <c r="J387" t="n">
         <v>15.64999961853027</v>
@@ -11722,7 +11722,7 @@
         <v>170.9499969482422</v>
       </c>
       <c r="I389" t="n">
-        <v>949.4484252929688</v>
+        <v>949.4483642578125</v>
       </c>
       <c r="J389" t="n">
         <v>15.75</v>
@@ -11745,7 +11745,7 @@
         <v>57.45000076293945</v>
       </c>
       <c r="G390" t="n">
-        <v>1232.087280273438</v>
+        <v>1232.087158203125</v>
       </c>
       <c r="H390" t="n">
         <v>178.6000061035156</v>
@@ -11774,7 +11774,7 @@
         <v>58.45000076293945</v>
       </c>
       <c r="G391" t="n">
-        <v>1244.468505859375</v>
+        <v>1244.468627929688</v>
       </c>
       <c r="H391" t="n">
         <v>184.8500061035156</v>
@@ -11867,7 +11867,7 @@
         <v>181.1999969482422</v>
       </c>
       <c r="I394" t="n">
-        <v>977.178466796875</v>
+        <v>977.1785278320312</v>
       </c>
       <c r="J394" t="n">
         <v>18.14999961853027</v>
@@ -11948,13 +11948,13 @@
         <v>59.04999923706055</v>
       </c>
       <c r="G397" t="n">
-        <v>1242.49951171875</v>
+        <v>1242.499633789062</v>
       </c>
       <c r="H397" t="n">
         <v>210.0500030517578</v>
       </c>
       <c r="I397" t="n">
-        <v>977.178466796875</v>
+        <v>977.1785278320312</v>
       </c>
       <c r="J397" t="n">
         <v>18.64999961853027</v>
@@ -11977,7 +11977,7 @@
         <v>60.20000076293945</v>
       </c>
       <c r="G398" t="n">
-        <v>1235.016357421875</v>
+        <v>1235.016235351562</v>
       </c>
       <c r="H398" t="n">
         <v>194.6999969482422</v>
@@ -12041,7 +12041,7 @@
         <v>175.8500061035156</v>
       </c>
       <c r="I400" t="n">
-        <v>983.5549926757812</v>
+        <v>983.554931640625</v>
       </c>
       <c r="J400" t="n">
         <v>17.5</v>
@@ -12064,7 +12064,7 @@
         <v>62.20000076293945</v>
       </c>
       <c r="G401" t="n">
-        <v>1253.970092773438</v>
+        <v>1253.969970703125</v>
       </c>
       <c r="H401" t="n">
         <v>170</v>
@@ -12128,7 +12128,7 @@
         <v>163</v>
       </c>
       <c r="I403" t="n">
-        <v>956.1214599609375</v>
+        <v>956.1213989257812</v>
       </c>
       <c r="J403" t="n">
         <v>16.75</v>
@@ -12244,13 +12244,13 @@
         <v>67.80000305175781</v>
       </c>
       <c r="G407" t="n">
-        <v>1244.689819335938</v>
+        <v>1244.68994140625</v>
       </c>
       <c r="H407" t="n">
         <v>170.4499969482422</v>
       </c>
       <c r="I407" t="n">
-        <v>1037.186401367188</v>
+        <v>1037.186279296875</v>
       </c>
       <c r="J407" t="n">
         <v>17.39999961853027</v>
@@ -12276,7 +12276,7 @@
         <v>67.84999847412109</v>
       </c>
       <c r="G408" t="n">
-        <v>1246.073364257812</v>
+        <v>1246.0732421875</v>
       </c>
       <c r="H408" t="n">
         <v>178.9499969482422</v>
@@ -12308,7 +12308,7 @@
         <v>66.94999694824219</v>
       </c>
       <c r="G409" t="n">
-        <v>1225.125854492188</v>
+        <v>1225.1259765625</v>
       </c>
       <c r="H409" t="n">
         <v>177.3000030517578</v>
@@ -12340,7 +12340,7 @@
         <v>67.5</v>
       </c>
       <c r="G410" t="n">
-        <v>1219.469116210938</v>
+        <v>1219.46923828125</v>
       </c>
       <c r="H410" t="n">
         <v>177.25</v>
@@ -12372,13 +12372,13 @@
         <v>68.65000152587891</v>
       </c>
       <c r="G411" t="n">
-        <v>1207.315673828125</v>
+        <v>1207.315551757812</v>
       </c>
       <c r="H411" t="n">
         <v>177.8999938964844</v>
       </c>
       <c r="I411" t="n">
-        <v>1001.794555664062</v>
+        <v>1001.794494628906</v>
       </c>
       <c r="J411" t="n">
         <v>17.45000076293945</v>
@@ -12436,7 +12436,7 @@
         <v>68.75</v>
       </c>
       <c r="G413" t="n">
-        <v>1194.618774414062</v>
+        <v>1194.618896484375</v>
       </c>
       <c r="H413" t="n">
         <v>188.0500030517578</v>
@@ -12500,7 +12500,7 @@
         <v>69.15000152587891</v>
       </c>
       <c r="G415" t="n">
-        <v>1191.950927734375</v>
+        <v>1191.950805664062</v>
       </c>
       <c r="H415" t="n">
         <v>186.8999938964844</v>
@@ -12532,7 +12532,7 @@
         <v>70.75</v>
       </c>
       <c r="G416" t="n">
-        <v>1190.987426757812</v>
+        <v>1190.987548828125</v>
       </c>
       <c r="H416" t="n">
         <v>192.8999938964844</v>
@@ -12596,7 +12596,7 @@
         <v>72.15000152587891</v>
       </c>
       <c r="G418" t="n">
-        <v>1199.880249023438</v>
+        <v>1199.88037109375</v>
       </c>
       <c r="H418" t="n">
         <v>190.3999938964844</v>
@@ -12634,7 +12634,7 @@
         <v>189.8000030517578</v>
       </c>
       <c r="I419" t="n">
-        <v>1005.304077148438</v>
+        <v>1005.304138183594</v>
       </c>
       <c r="J419" t="n">
         <v>21.20000076293945</v>
@@ -12666,7 +12666,7 @@
         <v>186.5</v>
       </c>
       <c r="I420" t="n">
-        <v>996.752685546875</v>
+        <v>996.7527465820312</v>
       </c>
       <c r="J420" t="n">
         <v>21.14999961853027</v>
@@ -12698,7 +12698,7 @@
         <v>182.8500061035156</v>
       </c>
       <c r="I421" t="n">
-        <v>991.216552734375</v>
+        <v>991.2166137695312</v>
       </c>
       <c r="J421" t="n">
         <v>20.79999923706055</v>
@@ -12756,13 +12756,13 @@
         <v>68.55000305175781</v>
       </c>
       <c r="G423" t="n">
-        <v>1210.922119140625</v>
+        <v>1210.922241210938</v>
       </c>
       <c r="H423" t="n">
         <v>172.6499938964844</v>
       </c>
       <c r="I423" t="n">
-        <v>952.908447265625</v>
+        <v>952.9085083007812</v>
       </c>
       <c r="J423" t="n">
         <v>19</v>
@@ -12788,7 +12788,7 @@
         <v>68.55000305175781</v>
       </c>
       <c r="G424" t="n">
-        <v>1212.033813476562</v>
+        <v>1212.03369140625</v>
       </c>
       <c r="H424" t="n">
         <v>175.3000030517578</v>
@@ -12820,7 +12820,7 @@
         <v>66.15000152587891</v>
       </c>
       <c r="G425" t="n">
-        <v>1214.28173828125</v>
+        <v>1214.281616210938</v>
       </c>
       <c r="H425" t="n">
         <v>183.75</v>
@@ -12954,7 +12954,7 @@
         <v>175.75</v>
       </c>
       <c r="I429" t="n">
-        <v>936.102294921875</v>
+        <v>936.1023559570312</v>
       </c>
       <c r="J429" t="n">
         <v>18.89999961853027</v>
@@ -12986,7 +12986,7 @@
         <v>173.5500030517578</v>
       </c>
       <c r="I430" t="n">
-        <v>939.2164306640625</v>
+        <v>939.2163696289062</v>
       </c>
       <c r="J430" t="n">
         <v>18.95000076293945</v>
@@ -13082,7 +13082,7 @@
         <v>170.8999938964844</v>
       </c>
       <c r="I433" t="n">
-        <v>946.4826049804688</v>
+        <v>946.4825439453125</v>
       </c>
       <c r="J433" t="n">
         <v>19.14999961853027</v>
@@ -13146,7 +13146,7 @@
         <v>174.3500061035156</v>
       </c>
       <c r="I435" t="n">
-        <v>943.2695922851562</v>
+        <v>943.2696533203125</v>
       </c>
       <c r="J435" t="n">
         <v>19.25</v>
@@ -13178,7 +13178,7 @@
         <v>170.3999938964844</v>
       </c>
       <c r="I436" t="n">
-        <v>931.5546875</v>
+        <v>931.5547485351562</v>
       </c>
       <c r="J436" t="n">
         <v>18.79999923706055</v>
@@ -13210,7 +13210,7 @@
         <v>172.1999969482422</v>
       </c>
       <c r="I437" t="n">
-        <v>968.7259521484375</v>
+        <v>968.7260131835938</v>
       </c>
       <c r="J437" t="n">
         <v>18.89999961853027</v>
@@ -13236,7 +13236,7 @@
         <v>72.40000152587891</v>
       </c>
       <c r="G438" t="n">
-        <v>1145.18994140625</v>
+        <v>1145.189819335938</v>
       </c>
       <c r="H438" t="n">
         <v>171.6499938964844</v>
@@ -13338,7 +13338,7 @@
         <v>170.5</v>
       </c>
       <c r="I441" t="n">
-        <v>975.2506713867188</v>
+        <v>975.250732421875</v>
       </c>
       <c r="J441" t="n">
         <v>18.20000076293945</v>
@@ -13370,7 +13370,7 @@
         <v>169.3500061035156</v>
       </c>
       <c r="I442" t="n">
-        <v>980.0453491210938</v>
+        <v>980.04541015625</v>
       </c>
       <c r="J442" t="n">
         <v>18</v>
@@ -13428,13 +13428,13 @@
         <v>78.75</v>
       </c>
       <c r="G444" t="n">
-        <v>1158.059814453125</v>
+        <v>1158.059692382812</v>
       </c>
       <c r="H444" t="n">
         <v>170.75</v>
       </c>
       <c r="I444" t="n">
-        <v>1058.243286132812</v>
+        <v>1058.243408203125</v>
       </c>
       <c r="J444" t="n">
         <v>18.39999961853027</v>
@@ -13460,7 +13460,7 @@
         <v>77.65000152587891</v>
       </c>
       <c r="G445" t="n">
-        <v>1163.593017578125</v>
+        <v>1163.592895507812</v>
       </c>
       <c r="H445" t="n">
         <v>172.3500061035156</v>
@@ -13498,7 +13498,7 @@
         <v>169.1999969482422</v>
       </c>
       <c r="I446" t="n">
-        <v>1029.079711914062</v>
+        <v>1029.079833984375</v>
       </c>
       <c r="J446" t="n">
         <v>18.14999961853027</v>
@@ -13620,13 +13620,13 @@
         <v>68.59999847412109</v>
       </c>
       <c r="G450" t="n">
-        <v>1115.522583007812</v>
+        <v>1115.522705078125</v>
       </c>
       <c r="H450" t="n">
         <v>162.3000030517578</v>
       </c>
       <c r="I450" t="n">
-        <v>1000.26220703125</v>
+        <v>1000.262268066406</v>
       </c>
       <c r="J450" t="n">
         <v>16.29999923706055</v>
@@ -13652,7 +13652,7 @@
         <v>68.19999694824219</v>
       </c>
       <c r="G451" t="n">
-        <v>1099.984985351562</v>
+        <v>1099.98486328125</v>
       </c>
       <c r="H451" t="n">
         <v>159.0500030517578</v>
@@ -13690,7 +13690,7 @@
         <v>162.9499969482422</v>
       </c>
       <c r="I452" t="n">
-        <v>1005.353454589844</v>
+        <v>1005.353515625</v>
       </c>
       <c r="J452" t="n">
         <v>16.79999923706055</v>
@@ -13786,7 +13786,7 @@
         <v>172.25</v>
       </c>
       <c r="I455" t="n">
-        <v>979.5510864257812</v>
+        <v>979.5511474609375</v>
       </c>
       <c r="J455" t="n">
         <v>17.39999961853027</v>
@@ -13978,7 +13978,7 @@
         <v>178.1000061035156</v>
       </c>
       <c r="I461" t="n">
-        <v>1038.174926757812</v>
+        <v>1038.175048828125</v>
       </c>
       <c r="J461" t="n">
         <v>21.20000076293945</v>
@@ -14042,7 +14042,7 @@
         <v>181.1499938964844</v>
       </c>
       <c r="I463" t="n">
-        <v>1030.216674804688</v>
+        <v>1030.216552734375</v>
       </c>
       <c r="J463" t="n">
         <v>22.5</v>
@@ -14074,7 +14074,7 @@
         <v>181.75</v>
       </c>
       <c r="I464" t="n">
-        <v>1070.156005859375</v>
+        <v>1070.156127929688</v>
       </c>
       <c r="J464" t="n">
         <v>22.29999923706055</v>
@@ -14202,7 +14202,7 @@
         <v>179.5500030517578</v>
       </c>
       <c r="I468" t="n">
-        <v>1109.156005859375</v>
+        <v>1109.156127929688</v>
       </c>
       <c r="J468" t="n">
         <v>21.35000038146973</v>
@@ -14234,7 +14234,7 @@
         <v>174.8500061035156</v>
       </c>
       <c r="I469" t="n">
-        <v>1108.31591796875</v>
+        <v>1108.315795898438</v>
       </c>
       <c r="J469" t="n">
         <v>20.89999961853027</v>
@@ -14266,7 +14266,7 @@
         <v>174.25</v>
       </c>
       <c r="I470" t="n">
-        <v>1095.661743164062</v>
+        <v>1095.661865234375</v>
       </c>
       <c r="J470" t="n">
         <v>21.35000038146973</v>
@@ -14420,7 +14420,7 @@
         <v>87.69999694824219</v>
       </c>
       <c r="G475" t="n">
-        <v>1182.885375976562</v>
+        <v>1182.88525390625</v>
       </c>
       <c r="H475" t="n">
         <v>194.0500030517578</v>
@@ -14458,7 +14458,7 @@
         <v>192.6999969482422</v>
       </c>
       <c r="I476" t="n">
-        <v>1102.8291015625</v>
+        <v>1102.829223632812</v>
       </c>
       <c r="J476" t="n">
         <v>20.89999961853027</v>
@@ -14490,7 +14490,7 @@
         <v>202.3000030517578</v>
       </c>
       <c r="I477" t="n">
-        <v>1095.167602539062</v>
+        <v>1095.16748046875</v>
       </c>
       <c r="J477" t="n">
         <v>22.29999923706055</v>
@@ -14516,7 +14516,7 @@
         <v>98.44999694824219</v>
       </c>
       <c r="G478" t="n">
-        <v>1215.887451171875</v>
+        <v>1215.887329101562</v>
       </c>
       <c r="H478" t="n">
         <v>212.3999938964844</v>
@@ -14548,7 +14548,7 @@
         <v>90.65000152587891</v>
       </c>
       <c r="G479" t="n">
-        <v>1213.886474609375</v>
+        <v>1213.886352539062</v>
       </c>
       <c r="H479" t="n">
         <v>220.5</v>
@@ -14682,7 +14682,7 @@
         <v>215.8000030517578</v>
       </c>
       <c r="I483" t="n">
-        <v>1170.548095703125</v>
+        <v>1170.547973632812</v>
       </c>
       <c r="J483" t="n">
         <v>23.79999923706055</v>
@@ -14772,7 +14772,7 @@
         <v>86.19999694824219</v>
       </c>
       <c r="G486" t="n">
-        <v>1245.480346679688</v>
+        <v>1245.48046875</v>
       </c>
       <c r="H486" t="n">
         <v>213.4499969482422</v>
@@ -14804,7 +14804,7 @@
         <v>87.65000152587891</v>
       </c>
       <c r="G487" t="n">
-        <v>1263.809448242188</v>
+        <v>1263.809326171875</v>
       </c>
       <c r="H487" t="n">
         <v>209.6499938964844</v>
@@ -14842,7 +14842,7 @@
         <v>190.8000030517578</v>
       </c>
       <c r="I488" t="n">
-        <v>1227.293334960938</v>
+        <v>1227.29345703125</v>
       </c>
       <c r="J488" t="n">
         <v>21.39999961853027</v>
@@ -14868,7 +14868,7 @@
         <v>85.90000152587891</v>
       </c>
       <c r="G489" t="n">
-        <v>1266.008056640625</v>
+        <v>1266.007934570312</v>
       </c>
       <c r="H489" t="n">
         <v>193.3999938964844</v>
@@ -14996,7 +14996,7 @@
         <v>88.05000305175781</v>
       </c>
       <c r="G493" t="n">
-        <v>1287.251831054688</v>
+        <v>1287.251708984375</v>
       </c>
       <c r="H493" t="n">
         <v>190.8000030517578</v>
@@ -15028,7 +15028,7 @@
         <v>87.34999847412109</v>
       </c>
       <c r="G494" t="n">
-        <v>1277.074462890625</v>
+        <v>1277.074340820312</v>
       </c>
       <c r="H494" t="n">
         <v>209.8000030517578</v>
@@ -15066,7 +15066,7 @@
         <v>211.8000030517578</v>
       </c>
       <c r="I495" t="n">
-        <v>1402.621215820312</v>
+        <v>1402.62109375</v>
       </c>
       <c r="J495" t="n">
         <v>23.95000076293945</v>
@@ -15156,7 +15156,7 @@
         <v>90.25</v>
       </c>
       <c r="G498" t="n">
-        <v>1282.854736328125</v>
+        <v>1282.854614257812</v>
       </c>
       <c r="H498" t="n">
         <v>231.5500030517578</v>
@@ -15220,7 +15220,7 @@
         <v>100.5500030517578</v>
       </c>
       <c r="G500" t="n">
-        <v>1278.26025390625</v>
+        <v>1278.260131835938</v>
       </c>
       <c r="H500" t="n">
         <v>241</v>
@@ -15284,7 +15284,7 @@
         <v>119.4000015258789</v>
       </c>
       <c r="G502" t="n">
-        <v>1309.261474609375</v>
+        <v>1309.261352539062</v>
       </c>
       <c r="H502" t="n">
         <v>237.4499969482422</v>
@@ -15316,13 +15316,13 @@
         <v>130.9499969482422</v>
       </c>
       <c r="G503" t="n">
-        <v>1343.696044921875</v>
+        <v>1343.696166992188</v>
       </c>
       <c r="H503" t="n">
         <v>239.8999938964844</v>
       </c>
       <c r="I503" t="n">
-        <v>1498.168823242188</v>
+        <v>1498.1689453125</v>
       </c>
       <c r="J503" t="n">
         <v>31.10000038146973</v>
@@ -15348,13 +15348,13 @@
         <v>124.1999969482422</v>
       </c>
       <c r="G504" t="n">
-        <v>1354.39208984375</v>
+        <v>1354.391967773438</v>
       </c>
       <c r="H504" t="n">
         <v>238.4499969482422</v>
       </c>
       <c r="I504" t="n">
-        <v>1496.3896484375</v>
+        <v>1496.389526367188</v>
       </c>
       <c r="J504" t="n">
         <v>30.89999961853027</v>
@@ -15380,7 +15380,7 @@
         <v>122.8499984741211</v>
       </c>
       <c r="G505" t="n">
-        <v>1377.51318359375</v>
+        <v>1377.513305664062</v>
       </c>
       <c r="H505" t="n">
         <v>232.6499938964844</v>
@@ -15412,13 +15412,13 @@
         <v>118.5500030517578</v>
       </c>
       <c r="G506" t="n">
-        <v>1358.24560546875</v>
+        <v>1358.245483398438</v>
       </c>
       <c r="H506" t="n">
         <v>221.8999938964844</v>
       </c>
       <c r="I506" t="n">
-        <v>1395.750366210938</v>
+        <v>1395.750244140625</v>
       </c>
       <c r="J506" t="n">
         <v>30.04999923706055</v>
@@ -15476,13 +15476,13 @@
         <v>126.25</v>
       </c>
       <c r="G508" t="n">
-        <v>1351.650146484375</v>
+        <v>1351.650024414062</v>
       </c>
       <c r="H508" t="n">
         <v>218.8999938964844</v>
       </c>
       <c r="I508" t="n">
-        <v>1424.419555664062</v>
+        <v>1424.419677734375</v>
       </c>
       <c r="J508" t="n">
         <v>29.75</v>
@@ -15508,7 +15508,7 @@
         <v>127.0999984741211</v>
       </c>
       <c r="G509" t="n">
-        <v>1351.156127929688</v>
+        <v>1351.156005859375</v>
       </c>
       <c r="H509" t="n">
         <v>216.75</v>
@@ -15604,7 +15604,7 @@
         <v>120.5500030517578</v>
       </c>
       <c r="G512" t="n">
-        <v>1336.952392578125</v>
+        <v>1336.952270507812</v>
       </c>
       <c r="H512" t="n">
         <v>215.25</v>
@@ -15636,7 +15636,7 @@
         <v>117</v>
       </c>
       <c r="G513" t="n">
-        <v>1430.795654296875</v>
+        <v>1430.795776367188</v>
       </c>
       <c r="H513" t="n">
         <v>227.9499969482422</v>
@@ -15706,7 +15706,7 @@
         <v>231.0500030517578</v>
       </c>
       <c r="I515" t="n">
-        <v>1394.31689453125</v>
+        <v>1394.317016601562</v>
       </c>
       <c r="J515" t="n">
         <v>29.79999923706055</v>
@@ -15770,7 +15770,7 @@
         <v>221.9499969482422</v>
       </c>
       <c r="I517" t="n">
-        <v>1373.704711914062</v>
+        <v>1373.704833984375</v>
       </c>
       <c r="J517" t="n">
         <v>28.79999923706055</v>
@@ -15802,7 +15802,7 @@
         <v>214.5</v>
       </c>
       <c r="I518" t="n">
-        <v>1374.149536132812</v>
+        <v>1374.1494140625</v>
       </c>
       <c r="J518" t="n">
         <v>27.39999961853027</v>
@@ -15828,7 +15828,7 @@
         <v>113.6999969482422</v>
       </c>
       <c r="G519" t="n">
-        <v>1410.786987304688</v>
+        <v>1410.786865234375</v>
       </c>
       <c r="H519" t="n">
         <v>214.9499969482422</v>
@@ -15860,7 +15860,7 @@
         <v>110.3000030517578</v>
       </c>
       <c r="G520" t="n">
-        <v>1424.966064453125</v>
+        <v>1424.965942382812</v>
       </c>
       <c r="H520" t="n">
         <v>216.4499969482422</v>
@@ -15924,7 +15924,7 @@
         <v>108.3499984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>1443.344360351562</v>
+        <v>1443.34423828125</v>
       </c>
       <c r="H522" t="n">
         <v>213</v>
@@ -16020,13 +16020,13 @@
         <v>109.5</v>
       </c>
       <c r="G525" t="n">
-        <v>1463.7236328125</v>
+        <v>1463.723510742188</v>
       </c>
       <c r="H525" t="n">
         <v>229.1499938964844</v>
       </c>
       <c r="I525" t="n">
-        <v>1340.784423828125</v>
+        <v>1340.784301757812</v>
       </c>
       <c r="J525" t="n">
         <v>26.45000076293945</v>
@@ -16084,13 +16084,13 @@
         <v>112.3000030517578</v>
       </c>
       <c r="G527" t="n">
-        <v>1443.171264648438</v>
+        <v>1443.17138671875</v>
       </c>
       <c r="H527" t="n">
         <v>225.25</v>
       </c>
       <c r="I527" t="n">
-        <v>1455.264038085938</v>
+        <v>1455.263916015625</v>
       </c>
       <c r="J527" t="n">
         <v>26.20000076293945</v>
@@ -16148,7 +16148,7 @@
         <v>119</v>
       </c>
       <c r="G529" t="n">
-        <v>1453.496948242188</v>
+        <v>1453.4970703125</v>
       </c>
       <c r="H529" t="n">
         <v>241.1999969482422</v>
@@ -16212,7 +16212,7 @@
         <v>116.3499984741211</v>
       </c>
       <c r="G531" t="n">
-        <v>1464.094116210938</v>
+        <v>1464.093994140625</v>
       </c>
       <c r="H531" t="n">
         <v>229.4499969482422</v>
@@ -16250,7 +16250,7 @@
         <v>228.5</v>
       </c>
       <c r="I532" t="n">
-        <v>1499.948486328125</v>
+        <v>1499.948364257812</v>
       </c>
       <c r="J532" t="n">
         <v>25.60000038146973</v>
@@ -16276,7 +16276,7 @@
         <v>118.5999984741211</v>
       </c>
       <c r="G533" t="n">
-        <v>1469.6025390625</v>
+        <v>1469.602661132812</v>
       </c>
       <c r="H533" t="n">
         <v>228.5500030517578</v>
@@ -16340,7 +16340,7 @@
         <v>112.5999984741211</v>
       </c>
       <c r="G535" t="n">
-        <v>1438.2802734375</v>
+        <v>1438.280395507812</v>
       </c>
       <c r="H535" t="n">
         <v>212.1000061035156</v>
@@ -16474,7 +16474,7 @@
         <v>226.6999969482422</v>
       </c>
       <c r="I539" t="n">
-        <v>1419.278930664062</v>
+        <v>1419.279052734375</v>
       </c>
       <c r="J539" t="n">
         <v>23.04999923706055</v>
@@ -16570,7 +16570,7 @@
         <v>223.6499938964844</v>
       </c>
       <c r="I542" t="n">
-        <v>1328.77294921875</v>
+        <v>1328.772827148438</v>
       </c>
       <c r="J542" t="n">
         <v>22.54999923706055</v>
@@ -16596,7 +16596,7 @@
         <v>87.5</v>
       </c>
       <c r="G543" t="n">
-        <v>1457.844482421875</v>
+        <v>1457.844604492188</v>
       </c>
       <c r="H543" t="n">
         <v>217.5500030517578</v>
@@ -16666,7 +16666,7 @@
         <v>214.25</v>
       </c>
       <c r="I545" t="n">
-        <v>1232.7802734375</v>
+        <v>1232.780151367188</v>
       </c>
       <c r="J545" t="n">
         <v>21.04999923706055</v>
@@ -16698,7 +16698,7 @@
         <v>237.5</v>
       </c>
       <c r="I546" t="n">
-        <v>1219.236450195312</v>
+        <v>1219.236328125</v>
       </c>
       <c r="J546" t="n">
         <v>22.10000038146973</v>
@@ -16730,7 +16730,7 @@
         <v>255.9499969482422</v>
       </c>
       <c r="I547" t="n">
-        <v>1217.01220703125</v>
+        <v>1217.012084960938</v>
       </c>
       <c r="J547" t="n">
         <v>23.20000076293945</v>
@@ -16788,7 +16788,7 @@
         <v>86</v>
       </c>
       <c r="G549" t="n">
-        <v>1426.546875</v>
+        <v>1426.546752929688</v>
       </c>
       <c r="H549" t="n">
         <v>249.3000030517578</v>
@@ -16826,7 +16826,7 @@
         <v>271.2000122070312</v>
       </c>
       <c r="I550" t="n">
-        <v>1225.909545898438</v>
+        <v>1225.909423828125</v>
       </c>
       <c r="J550" t="n">
         <v>25.04999923706055</v>
@@ -16852,7 +16852,7 @@
         <v>91.40000152587891</v>
       </c>
       <c r="G551" t="n">
-        <v>1437.687622070312</v>
+        <v>1437.6875</v>
       </c>
       <c r="H551" t="n">
         <v>277.3500061035156</v>
@@ -16884,13 +16884,13 @@
         <v>90.94999694824219</v>
       </c>
       <c r="G552" t="n">
-        <v>1424.397705078125</v>
+        <v>1424.397827148438</v>
       </c>
       <c r="H552" t="n">
         <v>273.7000122070312</v>
       </c>
       <c r="I552" t="n">
-        <v>1234.36181640625</v>
+        <v>1234.361938476562</v>
       </c>
       <c r="J552" t="n">
         <v>27.60000038146973</v>
@@ -16922,7 +16922,7 @@
         <v>266.9500122070312</v>
       </c>
       <c r="I553" t="n">
-        <v>1257.198364257812</v>
+        <v>1257.198486328125</v>
       </c>
       <c r="J553" t="n">
         <v>27.64999961853027</v>
@@ -16986,7 +16986,7 @@
         <v>268.6499938964844</v>
       </c>
       <c r="I555" t="n">
-        <v>1305.936401367188</v>
+        <v>1305.936279296875</v>
       </c>
       <c r="J555" t="n">
         <v>28.89999961853027</v>
@@ -17076,7 +17076,7 @@
         <v>91.94999694824219</v>
       </c>
       <c r="G558" t="n">
-        <v>1445.493408203125</v>
+        <v>1445.493530273438</v>
       </c>
       <c r="H558" t="n">
         <v>295</v>
@@ -17146,7 +17146,7 @@
         <v>287.6000061035156</v>
       </c>
       <c r="I560" t="n">
-        <v>1300.844970703125</v>
+        <v>1300.845092773438</v>
       </c>
       <c r="J560" t="n">
         <v>31</v>
@@ -17274,7 +17274,7 @@
         <v>199.9499969482422</v>
       </c>
       <c r="I564" t="n">
-        <v>1234.658447265625</v>
+        <v>1234.658569335938</v>
       </c>
       <c r="J564" t="n">
         <v>26.04999923706055</v>
@@ -17306,7 +17306,7 @@
         <v>194.1999969482422</v>
       </c>
       <c r="I565" t="n">
-        <v>1241.380981445312</v>
+        <v>1241.380859375</v>
       </c>
       <c r="J565" t="n">
         <v>27.35000038146973</v>
@@ -17332,7 +17332,7 @@
         <v>89.5</v>
       </c>
       <c r="G566" t="n">
-        <v>1446.876708984375</v>
+        <v>1446.876586914062</v>
       </c>
       <c r="H566" t="n">
         <v>194.6999969482422</v>
@@ -17364,13 +17364,13 @@
         <v>87.59999847412109</v>
       </c>
       <c r="G567" t="n">
-        <v>1452.607788085938</v>
+        <v>1452.607666015625</v>
       </c>
       <c r="H567" t="n">
         <v>188.75</v>
       </c>
       <c r="I567" t="n">
-        <v>1248.350708007812</v>
+        <v>1248.3505859375</v>
       </c>
       <c r="J567" t="n">
         <v>28.04999923706055</v>
@@ -17428,7 +17428,7 @@
         <v>88.05000305175781</v>
       </c>
       <c r="G569" t="n">
-        <v>1441.936279296875</v>
+        <v>1441.936401367188</v>
       </c>
       <c r="H569" t="n">
         <v>192.9499969482422</v>
@@ -17460,13 +17460,13 @@
         <v>92.44999694824219</v>
       </c>
       <c r="G570" t="n">
-        <v>1432.895263671875</v>
+        <v>1432.895385742188</v>
       </c>
       <c r="H570" t="n">
         <v>191.6999969482422</v>
       </c>
       <c r="I570" t="n">
-        <v>1292.491455078125</v>
+        <v>1292.491333007812</v>
       </c>
       <c r="J570" t="n">
         <v>27.60000038146973</v>
@@ -17492,7 +17492,7 @@
         <v>92.75</v>
       </c>
       <c r="G571" t="n">
-        <v>1442.57861328125</v>
+        <v>1442.578491210938</v>
       </c>
       <c r="H571" t="n">
         <v>192.6499938964844</v>
@@ -17588,7 +17588,7 @@
         <v>88.90000152587891</v>
       </c>
       <c r="G574" t="n">
-        <v>1449.519897460938</v>
+        <v>1449.519775390625</v>
       </c>
       <c r="H574" t="n">
         <v>177.8999938964844</v>
@@ -17780,7 +17780,7 @@
         <v>77.55000305175781</v>
       </c>
       <c r="G580" t="n">
-        <v>1377.51318359375</v>
+        <v>1377.513305664062</v>
       </c>
       <c r="H580" t="n">
         <v>161.1999969482422</v>
@@ -17844,7 +17844,7 @@
         <v>76.44999694824219</v>
       </c>
       <c r="G582" t="n">
-        <v>1385.985961914062</v>
+        <v>1385.986083984375</v>
       </c>
       <c r="H582" t="n">
         <v>164.6999969482422</v>
@@ -17876,7 +17876,7 @@
         <v>80.25</v>
       </c>
       <c r="G583" t="n">
-        <v>1403.153930664062</v>
+        <v>1403.15380859375</v>
       </c>
       <c r="H583" t="n">
         <v>171.4499969482422</v>
@@ -17908,13 +17908,13 @@
         <v>80.5</v>
       </c>
       <c r="G584" t="n">
-        <v>1399.399291992188</v>
+        <v>1399.3994140625</v>
       </c>
       <c r="H584" t="n">
         <v>171.6000061035156</v>
       </c>
       <c r="I584" t="n">
-        <v>1211.426513671875</v>
+        <v>1211.426635742188</v>
       </c>
       <c r="J584" t="n">
         <v>25.79999923706055</v>
@@ -17972,7 +17972,7 @@
         <v>81.69999694824219</v>
       </c>
       <c r="G586" t="n">
-        <v>1418.5927734375</v>
+        <v>1418.592895507812</v>
       </c>
       <c r="H586" t="n">
         <v>170.1000061035156</v>
@@ -18138,7 +18138,7 @@
         <v>170</v>
       </c>
       <c r="I591" t="n">
-        <v>1222.053833007812</v>
+        <v>1222.053955078125</v>
       </c>
       <c r="J591" t="n">
         <v>25.29999923706055</v>
@@ -18170,7 +18170,7 @@
         <v>168.8999938964844</v>
       </c>
       <c r="I592" t="n">
-        <v>1209.647094726562</v>
+        <v>1209.64697265625</v>
       </c>
       <c r="J592" t="n">
         <v>24.95000076293945</v>
@@ -18196,7 +18196,7 @@
         <v>77.80000305175781</v>
       </c>
       <c r="G593" t="n">
-        <v>1423.607299804688</v>
+        <v>1423.607421875</v>
       </c>
       <c r="H593" t="n">
         <v>170.5</v>
@@ -18266,7 +18266,7 @@
         <v>166.3500061035156</v>
       </c>
       <c r="I595" t="n">
-        <v>1168.373046875</v>
+        <v>1168.373168945312</v>
       </c>
       <c r="J595" t="n">
         <v>24.54999923706055</v>
@@ -18330,7 +18330,7 @@
         <v>155.9499969482422</v>
       </c>
       <c r="I597" t="n">
-        <v>1059.578002929688</v>
+        <v>1059.578125</v>
       </c>
       <c r="J597" t="n">
         <v>24.5</v>
@@ -18356,7 +18356,7 @@
         <v>76.09999847412109</v>
       </c>
       <c r="G598" t="n">
-        <v>1403.821044921875</v>
+        <v>1403.820922851562</v>
       </c>
       <c r="H598" t="n">
         <v>149.9499969482422</v>
@@ -18426,7 +18426,7 @@
         <v>167.8000030517578</v>
       </c>
       <c r="I600" t="n">
-        <v>1198.286254882812</v>
+        <v>1198.286376953125</v>
       </c>
       <c r="J600" t="n">
         <v>25</v>
@@ -18484,13 +18484,13 @@
         <v>79.94000244140625</v>
       </c>
       <c r="G602" t="n">
-        <v>1439.31787109375</v>
+        <v>1439.317993164062</v>
       </c>
       <c r="H602" t="n">
         <v>189.3000030517578</v>
       </c>
       <c r="I602" t="n">
-        <v>1350.433837890625</v>
+        <v>1350.433959960938</v>
       </c>
       <c r="J602" t="n">
         <v>28.68000030517578</v>
@@ -18516,7 +18516,7 @@
         <v>83.27999877929688</v>
       </c>
       <c r="G603" t="n">
-        <v>1445.888549804688</v>
+        <v>1445.888671875</v>
       </c>
       <c r="H603" t="n">
         <v>190.3000030517578</v>
@@ -18650,7 +18650,7 @@
         <v>209.8200073242188</v>
       </c>
       <c r="I607" t="n">
-        <v>1320.678955078125</v>
+        <v>1320.678833007812</v>
       </c>
       <c r="J607" t="n">
         <v>30.82999992370605</v>
@@ -18676,7 +18676,7 @@
         <v>84.08999633789062</v>
       </c>
       <c r="G608" t="n">
-        <v>1456.140014648438</v>
+        <v>1456.14013671875</v>
       </c>
       <c r="H608" t="n">
         <v>213.25</v>
@@ -18714,7 +18714,7 @@
         <v>214.8000030517578</v>
       </c>
       <c r="I609" t="n">
-        <v>1319.934936523438</v>
+        <v>1319.93505859375</v>
       </c>
       <c r="J609" t="n">
         <v>29.8700008392334</v>
@@ -18938,7 +18938,7 @@
         <v>187.5500030517578</v>
       </c>
       <c r="I616" t="n">
-        <v>1366.005615234375</v>
+        <v>1366.005737304688</v>
       </c>
       <c r="J616" t="n">
         <v>28.70999908447266</v>
@@ -18970,7 +18970,7 @@
         <v>185.7400054931641</v>
       </c>
       <c r="I617" t="n">
-        <v>1360.153930664062</v>
+        <v>1360.15380859375</v>
       </c>
       <c r="J617" t="n">
         <v>28.3799991607666</v>
@@ -19028,7 +19028,7 @@
         <v>85.66999816894531</v>
       </c>
       <c r="G619" t="n">
-        <v>1569.695678710938</v>
+        <v>1569.695556640625</v>
       </c>
       <c r="H619" t="n">
         <v>199.1399993896484</v>
@@ -19066,7 +19066,7 @@
         <v>199.9100036621094</v>
       </c>
       <c r="I620" t="n">
-        <v>1385.0986328125</v>
+        <v>1385.098510742188</v>
       </c>
       <c r="J620" t="n">
         <v>28.32999992370605</v>
@@ -19092,7 +19092,7 @@
         <v>84.80999755859375</v>
       </c>
       <c r="G621" t="n">
-        <v>1571.325927734375</v>
+        <v>1571.326049804688</v>
       </c>
       <c r="H621" t="n">
         <v>196.5800018310547</v>
@@ -19188,7 +19188,7 @@
         <v>82.91999816894531</v>
       </c>
       <c r="G624" t="n">
-        <v>1577.69921875</v>
+        <v>1577.699096679688</v>
       </c>
       <c r="H624" t="n">
         <v>190.6000061035156</v>
@@ -19316,13 +19316,13 @@
         <v>78.91999816894531</v>
       </c>
       <c r="G628" t="n">
-        <v>1536.61962890625</v>
+        <v>1536.619506835938</v>
       </c>
       <c r="H628" t="n">
         <v>181.7400054931641</v>
       </c>
       <c r="I628" t="n">
-        <v>1227.396606445312</v>
+        <v>1227.396728515625</v>
       </c>
       <c r="J628" t="n">
         <v>27.1200008392334</v>
@@ -19380,13 +19380,13 @@
         <v>85.40000152587891</v>
       </c>
       <c r="G630" t="n">
-        <v>1470.1708984375</v>
+        <v>1470.170776367188</v>
       </c>
       <c r="H630" t="n">
         <v>175.1699981689453</v>
       </c>
       <c r="I630" t="n">
-        <v>1242.423095703125</v>
+        <v>1242.422973632812</v>
       </c>
       <c r="J630" t="n">
         <v>26.94000053405762</v>
@@ -19412,7 +19412,7 @@
         <v>83.40000152587891</v>
       </c>
       <c r="G631" t="n">
-        <v>1477.8779296875</v>
+        <v>1477.877807617188</v>
       </c>
       <c r="H631" t="n">
         <v>184.3899993896484</v>
@@ -19540,7 +19540,7 @@
         <v>90.97000122070312</v>
       </c>
       <c r="G635" t="n">
-        <v>1495.119995117188</v>
+        <v>1495.119873046875</v>
       </c>
       <c r="H635" t="n">
         <v>201.2599945068359</v>
@@ -19604,13 +19604,13 @@
         <v>93.66000366210938</v>
       </c>
       <c r="G637" t="n">
-        <v>1497.244384765625</v>
+        <v>1497.244506835938</v>
       </c>
       <c r="H637" t="n">
         <v>214.4400024414062</v>
       </c>
       <c r="I637" t="n">
-        <v>1270.442260742188</v>
+        <v>1270.4423828125</v>
       </c>
       <c r="J637" t="n">
         <v>32.90000152587891</v>
@@ -19642,7 +19642,7 @@
         <v>215.7200012207031</v>
       </c>
       <c r="I638" t="n">
-        <v>1249.117919921875</v>
+        <v>1249.117797851562</v>
       </c>
       <c r="J638" t="n">
         <v>34.54000091552734</v>
@@ -19738,7 +19738,7 @@
         <v>214.0500030517578</v>
       </c>
       <c r="I641" t="n">
-        <v>1203.3447265625</v>
+        <v>1203.344604492188</v>
       </c>
       <c r="J641" t="n">
         <v>31.86000061035156</v>
@@ -19796,13 +19796,13 @@
         <v>99.91999816894531</v>
       </c>
       <c r="G643" t="n">
-        <v>1456.733032226562</v>
+        <v>1456.73291015625</v>
       </c>
       <c r="H643" t="n">
         <v>230.0200042724609</v>
       </c>
       <c r="I643" t="n">
-        <v>1192.236206054688</v>
+        <v>1192.236083984375</v>
       </c>
       <c r="J643" t="n">
         <v>32.31999969482422</v>
@@ -19828,7 +19828,7 @@
         <v>96.81999969482422</v>
       </c>
       <c r="G644" t="n">
-        <v>1443.220947265625</v>
+        <v>1443.220825195312</v>
       </c>
       <c r="H644" t="n">
         <v>226.0599975585938</v>
@@ -19898,7 +19898,7 @@
         <v>220.2799987792969</v>
       </c>
       <c r="I646" t="n">
-        <v>1131.6845703125</v>
+        <v>1131.684448242188</v>
       </c>
       <c r="J646" t="n">
         <v>29.75</v>
@@ -19924,7 +19924,7 @@
         <v>95.01000213623047</v>
       </c>
       <c r="G647" t="n">
-        <v>1460.586303710938</v>
+        <v>1460.58642578125</v>
       </c>
       <c r="H647" t="n">
         <v>217.9700012207031</v>
@@ -19962,7 +19962,7 @@
         <v>225.7100067138672</v>
       </c>
       <c r="I648" t="n">
-        <v>1198.087768554688</v>
+        <v>1198.087890625</v>
       </c>
       <c r="J648" t="n">
         <v>32.79000091552734</v>
@@ -20026,7 +20026,7 @@
         <v>243.1000061035156</v>
       </c>
       <c r="I650" t="n">
-        <v>1205.477172851562</v>
+        <v>1205.47705078125</v>
       </c>
       <c r="J650" t="n">
         <v>36.13999938964844</v>
@@ -20116,13 +20116,13 @@
         <v>95.69999694824219</v>
       </c>
       <c r="G653" t="n">
-        <v>1499.649047851562</v>
+        <v>1499.649169921875</v>
       </c>
       <c r="H653" t="n">
         <v>206.75</v>
       </c>
       <c r="I653" t="n">
-        <v>1203.3447265625</v>
+        <v>1203.344604492188</v>
       </c>
       <c r="J653" t="n">
         <v>32.75</v>
@@ -20180,7 +20180,7 @@
         <v>96.19000244140625</v>
       </c>
       <c r="G655" t="n">
-        <v>1485.471557617188</v>
+        <v>1485.4716796875</v>
       </c>
       <c r="H655" t="n">
         <v>213.5</v>
@@ -20218,7 +20218,7 @@
         <v>212.25</v>
       </c>
       <c r="I656" t="n">
-        <v>1204.435668945312</v>
+        <v>1204.435546875</v>
       </c>
       <c r="J656" t="n">
         <v>30.56999969482422</v>
@@ -20276,7 +20276,7 @@
         <v>94.29000091552734</v>
       </c>
       <c r="G658" t="n">
-        <v>1503.267822265625</v>
+        <v>1503.267944335938</v>
       </c>
       <c r="H658" t="n">
         <v>204.75</v>
@@ -20436,13 +20436,13 @@
         <v>89.33999633789062</v>
       </c>
       <c r="G663" t="n">
-        <v>1449.928344726562</v>
+        <v>1449.928466796875</v>
       </c>
       <c r="H663" t="n">
         <v>211.75</v>
       </c>
       <c r="I663" t="n">
-        <v>1144.380004882812</v>
+        <v>1144.380126953125</v>
       </c>
       <c r="J663" t="n">
         <v>29.71999931335449</v>
@@ -20468,7 +20468,7 @@
         <v>90.38999938964844</v>
       </c>
       <c r="G664" t="n">
-        <v>1449.011352539062</v>
+        <v>1449.011474609375</v>
       </c>
       <c r="H664" t="n">
         <v>216.9700012207031</v>
@@ -20500,7 +20500,7 @@
         <v>88.48999786376953</v>
       </c>
       <c r="G665" t="n">
-        <v>1439.072143554688</v>
+        <v>1439.072265625</v>
       </c>
       <c r="H665" t="n">
         <v>210.9799957275391</v>
@@ -20596,7 +20596,7 @@
         <v>91.58000183105469</v>
       </c>
       <c r="G668" t="n">
-        <v>1458.752197265625</v>
+        <v>1458.752319335938</v>
       </c>
       <c r="H668" t="n">
         <v>216.0500030517578</v>
@@ -20660,7 +20660,7 @@
         <v>90.40000152587891</v>
       </c>
       <c r="G670" t="n">
-        <v>1450.919921875</v>
+        <v>1450.919799804688</v>
       </c>
       <c r="H670" t="n">
         <v>282.7300109863281</v>
@@ -20698,7 +20698,7 @@
         <v>284.8900146484375</v>
       </c>
       <c r="I671" t="n">
-        <v>1130.395141601562</v>
+        <v>1130.39501953125</v>
       </c>
       <c r="J671" t="n">
         <v>34.61000061035156</v>
@@ -20826,7 +20826,7 @@
         <v>335.1600036621094</v>
       </c>
       <c r="I675" t="n">
-        <v>1262.408447265625</v>
+        <v>1262.408569335938</v>
       </c>
       <c r="J675" t="n">
         <v>42.04999923706055</v>
@@ -20890,7 +20890,7 @@
         <v>322.9500122070312</v>
       </c>
       <c r="I677" t="n">
-        <v>1261.962158203125</v>
+        <v>1261.962036132812</v>
       </c>
       <c r="J677" t="n">
         <v>46.34999847412109</v>
@@ -20954,7 +20954,7 @@
         <v>332</v>
       </c>
       <c r="I679" t="n">
-        <v>1235.876953125</v>
+        <v>1235.876831054688</v>
       </c>
       <c r="J679" t="n">
         <v>51.09000015258789</v>
@@ -21044,7 +21044,7 @@
         <v>74</v>
       </c>
       <c r="G682" t="n">
-        <v>1358.988891601562</v>
+        <v>1358.98876953125</v>
       </c>
       <c r="H682" t="n">
         <v>288.25</v>
@@ -21076,13 +21076,13 @@
         <v>75.75</v>
       </c>
       <c r="G683" t="n">
-        <v>1385.385864257812</v>
+        <v>1385.3857421875</v>
       </c>
       <c r="H683" t="n">
         <v>299.5</v>
       </c>
       <c r="I683" t="n">
-        <v>1158.86083984375</v>
+        <v>1158.860717773438</v>
       </c>
       <c r="J683" t="n">
         <v>45.97999954223633</v>
@@ -21268,7 +21268,7 @@
         <v>85.95999908447266</v>
       </c>
       <c r="G689" t="n">
-        <v>1342.481323242188</v>
+        <v>1342.4814453125</v>
       </c>
       <c r="H689" t="n">
         <v>291.4500122070312</v>
@@ -21306,7 +21306,7 @@
         <v>277.9500122070312</v>
       </c>
       <c r="I690" t="n">
-        <v>1192.781494140625</v>
+        <v>1192.781616210938</v>
       </c>
       <c r="J690" t="n">
         <v>41.7400016784668</v>
@@ -21364,7 +21364,7 @@
         <v>80</v>
       </c>
       <c r="G692" t="n">
-        <v>1357.476806640625</v>
+        <v>1357.476928710938</v>
       </c>
       <c r="H692" t="n">
         <v>267.9500122070312</v>
@@ -21396,13 +21396,13 @@
         <v>76.08000183105469</v>
       </c>
       <c r="G693" t="n">
-        <v>1331.848266601562</v>
+        <v>1331.84814453125</v>
       </c>
       <c r="H693" t="n">
         <v>254.5500030517578</v>
       </c>
       <c r="I693" t="n">
-        <v>1128.80810546875</v>
+        <v>1128.808227539062</v>
       </c>
       <c r="J693" t="n">
         <v>38.43000030517578</v>
@@ -21428,13 +21428,13 @@
         <v>79.12999725341797</v>
       </c>
       <c r="G694" t="n">
-        <v>1327.064575195312</v>
+        <v>1327.064453125</v>
       </c>
       <c r="H694" t="n">
         <v>267.25</v>
       </c>
       <c r="I694" t="n">
-        <v>1138.925048828125</v>
+        <v>1138.924926757812</v>
       </c>
       <c r="J694" t="n">
         <v>40.34999847412109</v>
@@ -21658,7 +21658,7 @@
         <v>291.0499877929688</v>
       </c>
       <c r="I701" t="n">
-        <v>1116.360595703125</v>
+        <v>1116.360717773438</v>
       </c>
       <c r="J701" t="n">
         <v>43.02999877929688</v>
@@ -21748,7 +21748,7 @@
         <v>86.12000274658203</v>
       </c>
       <c r="G704" t="n">
-        <v>1314.002197265625</v>
+        <v>1314.002319335938</v>
       </c>
       <c r="H704" t="n">
         <v>303.3500061035156</v>
@@ -21780,13 +21780,13 @@
         <v>83.80999755859375</v>
       </c>
       <c r="G705" t="n">
-        <v>1294.470947265625</v>
+        <v>1294.471069335938</v>
       </c>
       <c r="H705" t="n">
         <v>288.25</v>
       </c>
       <c r="I705" t="n">
-        <v>1128.461059570312</v>
+        <v>1128.4609375</v>
       </c>
       <c r="J705" t="n">
         <v>43.77000045776367</v>
@@ -21812,7 +21812,7 @@
         <v>82.36000061035156</v>
       </c>
       <c r="G706" t="n">
-        <v>1272.758544921875</v>
+        <v>1272.758422851562</v>
       </c>
       <c r="H706" t="n">
         <v>274.2999877929688</v>
@@ -21850,7 +21850,7 @@
         <v>260.6000061035156</v>
       </c>
       <c r="I707" t="n">
-        <v>1073.166259765625</v>
+        <v>1073.166137695312</v>
       </c>
       <c r="J707" t="n">
         <v>39.5</v>
@@ -22036,7 +22036,7 @@
         <v>84.30000305175781</v>
       </c>
       <c r="G713" t="n">
-        <v>1212.528564453125</v>
+        <v>1212.528686523438</v>
       </c>
       <c r="H713" t="n">
         <v>248.6000061035156</v>
@@ -22068,7 +22068,7 @@
         <v>79.55999755859375</v>
       </c>
       <c r="G714" t="n">
-        <v>1254.565673828125</v>
+        <v>1254.565551757812</v>
       </c>
       <c r="H714" t="n">
         <v>257.6499938964844</v>
@@ -22132,13 +22132,13 @@
         <v>79.15000152587891</v>
       </c>
       <c r="G716" t="n">
-        <v>1284.606079101562</v>
+        <v>1284.606201171875</v>
       </c>
       <c r="H716" t="n">
         <v>271.75</v>
       </c>
       <c r="I716" t="n">
-        <v>1131.287841796875</v>
+        <v>1131.287719726562</v>
       </c>
       <c r="J716" t="n">
         <v>36.31000137329102</v>
@@ -22260,13 +22260,13 @@
         <v>79.05000305175781</v>
       </c>
       <c r="G720" t="n">
-        <v>1297.941040039062</v>
+        <v>1297.941162109375</v>
       </c>
       <c r="H720" t="n">
         <v>274.0499877929688</v>
       </c>
       <c r="I720" t="n">
-        <v>1195.410034179688</v>
+        <v>1195.409912109375</v>
       </c>
       <c r="J720" t="n">
         <v>38.86999893188477</v>
@@ -22292,13 +22292,13 @@
         <v>79.80999755859375</v>
       </c>
       <c r="G721" t="n">
-        <v>1311.969970703125</v>
+        <v>1311.969848632812</v>
       </c>
       <c r="H721" t="n">
         <v>281.3999938964844</v>
       </c>
       <c r="I721" t="n">
-        <v>1192.781494140625</v>
+        <v>1192.781616210938</v>
       </c>
       <c r="J721" t="n">
         <v>39.13999938964844</v>
@@ -22330,7 +22330,7 @@
         <v>295.4500122070312</v>
       </c>
       <c r="I722" t="n">
-        <v>1207.11376953125</v>
+        <v>1207.113647460938</v>
       </c>
       <c r="J722" t="n">
         <v>41.09000015258789</v>
@@ -22362,7 +22362,7 @@
         <v>302.1499938964844</v>
       </c>
       <c r="I723" t="n">
-        <v>1191.045776367188</v>
+        <v>1191.0458984375</v>
       </c>
       <c r="J723" t="n">
         <v>43.13999938964844</v>
@@ -22388,7 +22388,7 @@
         <v>79.58999633789062</v>
       </c>
       <c r="G724" t="n">
-        <v>1300.320556640625</v>
+        <v>1300.320434570312</v>
       </c>
       <c r="H724" t="n">
         <v>303.25</v>
@@ -22426,7 +22426,7 @@
         <v>298.3500061035156</v>
       </c>
       <c r="I725" t="n">
-        <v>1185.144409179688</v>
+        <v>1185.14453125</v>
       </c>
       <c r="J725" t="n">
         <v>44.38999938964844</v>
@@ -22548,7 +22548,7 @@
         <v>74.69000244140625</v>
       </c>
       <c r="G729" t="n">
-        <v>1261.951782226562</v>
+        <v>1261.951904296875</v>
       </c>
       <c r="H729" t="n">
         <v>294.7000122070312</v>
@@ -22580,7 +22580,7 @@
         <v>74.36000061035156</v>
       </c>
       <c r="G730" t="n">
-        <v>1257.440795898438</v>
+        <v>1257.44091796875</v>
       </c>
       <c r="H730" t="n">
         <v>291.9500122070312</v>
@@ -22612,13 +22612,13 @@
         <v>73.54000091552734</v>
       </c>
       <c r="G731" t="n">
-        <v>1234.637817382812</v>
+        <v>1234.6376953125</v>
       </c>
       <c r="H731" t="n">
         <v>286.7000122070312</v>
       </c>
       <c r="I731" t="n">
-        <v>1144.231323242188</v>
+        <v>1144.231201171875</v>
       </c>
       <c r="J731" t="n">
         <v>46.70999908447266</v>
@@ -22708,13 +22708,13 @@
         <v>74.33999633789062</v>
       </c>
       <c r="G734" t="n">
-        <v>1194.980346679688</v>
+        <v>1194.980224609375</v>
       </c>
       <c r="H734" t="n">
         <v>290.2999877929688</v>
       </c>
       <c r="I734" t="n">
-        <v>1070.240356445312</v>
+        <v>1070.240234375</v>
       </c>
       <c r="J734" t="n">
         <v>44.75</v>
@@ -22772,7 +22772,7 @@
         <v>73.47000122070312</v>
       </c>
       <c r="G736" t="n">
-        <v>1212.280883789062</v>
+        <v>1212.28076171875</v>
       </c>
       <c r="H736" t="n">
         <v>302.2999877929688</v>
@@ -22810,7 +22810,7 @@
         <v>302.1499938964844</v>
       </c>
       <c r="I737" t="n">
-        <v>1035.972290039062</v>
+        <v>1035.972412109375</v>
       </c>
       <c r="J737" t="n">
         <v>44.13000106811523</v>
@@ -22868,13 +22868,13 @@
         <v>70.33999633789062</v>
       </c>
       <c r="G739" t="n">
-        <v>1200.333862304688</v>
+        <v>1200.333984375</v>
       </c>
       <c r="H739" t="n">
         <v>297.0499877929688</v>
       </c>
       <c r="I739" t="n">
-        <v>1085.812133789062</v>
+        <v>1085.81201171875</v>
       </c>
       <c r="J739" t="n">
         <v>41.84999847412109</v>
@@ -22906,7 +22906,7 @@
         <v>304.1499938964844</v>
       </c>
       <c r="I740" t="n">
-        <v>1074.158081054688</v>
+        <v>1074.157958984375</v>
       </c>
       <c r="J740" t="n">
         <v>42.59999847412109</v>
@@ -22938,7 +22938,7 @@
         <v>319.2000122070312</v>
       </c>
       <c r="I741" t="n">
-        <v>1075.34814453125</v>
+        <v>1075.348266601562</v>
       </c>
       <c r="J741" t="n">
         <v>44.72999954223633</v>
@@ -22996,7 +22996,7 @@
         <v>72.80000305175781</v>
       </c>
       <c r="G743" t="n">
-        <v>1240.437622070312</v>
+        <v>1240.437744140625</v>
       </c>
       <c r="H743" t="n">
         <v>319.2000122070312</v>
@@ -23028,7 +23028,7 @@
         <v>68.94999694824219</v>
       </c>
       <c r="G744" t="n">
-        <v>1207.571533203125</v>
+        <v>1207.571411132812</v>
       </c>
       <c r="H744" t="n">
         <v>303.25</v>
@@ -23098,7 +23098,7 @@
         <v>302.1499938964844</v>
       </c>
       <c r="I746" t="n">
-        <v>1107.731567382812</v>
+        <v>1107.731689453125</v>
       </c>
       <c r="J746" t="n">
         <v>42.38000106811523</v>
@@ -23124,13 +23124,13 @@
         <v>66.61000061035156</v>
       </c>
       <c r="G747" t="n">
-        <v>1244.0068359375</v>
+        <v>1244.006713867188</v>
       </c>
       <c r="H747" t="n">
         <v>287.0499877929688</v>
       </c>
       <c r="I747" t="n">
-        <v>1079.5634765625</v>
+        <v>1079.563598632812</v>
       </c>
       <c r="J747" t="n">
         <v>40.2599983215332</v>
@@ -23290,7 +23290,7 @@
         <v>279.2999877929688</v>
       </c>
       <c r="I752" t="n">
-        <v>1016.433288574219</v>
+        <v>1016.433227539062</v>
       </c>
       <c r="J752" t="n">
         <v>41.20000076293945</v>
@@ -23354,7 +23354,7 @@
         <v>280.9500122070312</v>
       </c>
       <c r="I754" t="n">
-        <v>1028.682373046875</v>
+        <v>1028.682495117188</v>
       </c>
       <c r="J754" t="n">
         <v>40.77999877929688</v>
@@ -23412,7 +23412,7 @@
         <v>54.09999847412109</v>
       </c>
       <c r="G756" t="n">
-        <v>1266.16552734375</v>
+        <v>1266.165405273438</v>
       </c>
       <c r="H756" t="n">
         <v>274.3999938964844</v>
@@ -23444,7 +23444,7 @@
         <v>53.88999938964844</v>
       </c>
       <c r="G757" t="n">
-        <v>1252.830688476562</v>
+        <v>1252.83056640625</v>
       </c>
       <c r="H757" t="n">
         <v>274.3999938964844</v>
@@ -23540,13 +23540,13 @@
         <v>49.66999816894531</v>
       </c>
       <c r="G760" t="n">
-        <v>1223.8310546875</v>
+        <v>1223.831176757812</v>
       </c>
       <c r="H760" t="n">
         <v>240.6000061035156</v>
       </c>
       <c r="I760" t="n">
-        <v>913.7285766601562</v>
+        <v>913.7286376953125</v>
       </c>
       <c r="J760" t="n">
         <v>36.84999847412109</v>
@@ -23578,7 +23578,7 @@
         <v>248.25</v>
       </c>
       <c r="I761" t="n">
-        <v>942.9877319335938</v>
+        <v>942.98779296875</v>
       </c>
       <c r="J761" t="n">
         <v>38.65000152587891</v>
@@ -23706,7 +23706,7 @@
         <v>234.0500030517578</v>
       </c>
       <c r="I765" t="n">
-        <v>932.474365234375</v>
+        <v>932.4743041992188</v>
       </c>
       <c r="J765" t="n">
         <v>38</v>
@@ -23834,7 +23834,7 @@
         <v>286.5</v>
       </c>
       <c r="I769" t="n">
-        <v>945.665771484375</v>
+        <v>945.6657104492188</v>
       </c>
       <c r="J769" t="n">
         <v>41.84000015258789</v>
@@ -23866,7 +23866,7 @@
         <v>284.4500122070312</v>
       </c>
       <c r="I770" t="n">
-        <v>928.3086547851562</v>
+        <v>928.30859375</v>
       </c>
       <c r="J770" t="n">
         <v>41</v>
@@ -23930,7 +23930,7 @@
         <v>266.7999877929688</v>
       </c>
       <c r="I772" t="n">
-        <v>890.4205322265625</v>
+        <v>890.4204711914062</v>
       </c>
       <c r="J772" t="n">
         <v>39.45000076293945</v>
@@ -23956,13 +23956,13 @@
         <v>49.22999954223633</v>
       </c>
       <c r="G773" t="n">
-        <v>1205.687622070312</v>
+        <v>1205.687744140625</v>
       </c>
       <c r="H773" t="n">
         <v>266.7000122070312</v>
       </c>
       <c r="I773" t="n">
-        <v>898.15673828125</v>
+        <v>898.1567993164062</v>
       </c>
       <c r="J773" t="n">
         <v>39.56000137329102</v>
@@ -24020,13 +24020,13 @@
         <v>46.41999816894531</v>
       </c>
       <c r="G775" t="n">
-        <v>1214.412475585938</v>
+        <v>1214.412353515625</v>
       </c>
       <c r="H775" t="n">
         <v>244.3500061035156</v>
       </c>
       <c r="I775" t="n">
-        <v>836.2662963867188</v>
+        <v>836.2662353515625</v>
       </c>
       <c r="J775" t="n">
         <v>36.93999862670898</v>
@@ -24058,7 +24058,7 @@
         <v>248.6000061035156</v>
       </c>
       <c r="I776" t="n">
-        <v>815.8344116210938</v>
+        <v>815.83447265625</v>
       </c>
       <c r="J776" t="n">
         <v>36.77999877929688</v>
@@ -24084,7 +24084,7 @@
         <v>46.93000030517578</v>
       </c>
       <c r="G777" t="n">
-        <v>1216.9404296875</v>
+        <v>1216.940551757812</v>
       </c>
       <c r="H777" t="n">
         <v>256.25</v>
@@ -24180,13 +24180,13 @@
         <v>45.2599983215332</v>
       </c>
       <c r="G780" t="n">
-        <v>1204.151123046875</v>
+        <v>1204.151000976562</v>
       </c>
       <c r="H780" t="n">
         <v>240.8000030517578</v>
       </c>
       <c r="I780" t="n">
-        <v>826.0007934570312</v>
+        <v>826.000732421875</v>
       </c>
       <c r="J780" t="n">
         <v>36.79999923706055</v>
@@ -24212,7 +24212,7 @@
         <v>45.16999816894531</v>
       </c>
       <c r="G781" t="n">
-        <v>1193.69140625</v>
+        <v>1193.691284179688</v>
       </c>
       <c r="H781" t="n">
         <v>238.8000030517578</v>
@@ -24250,7 +24250,7 @@
         <v>222.9499969482422</v>
       </c>
       <c r="I782" t="n">
-        <v>815.8839721679688</v>
+        <v>815.884033203125</v>
       </c>
       <c r="J782" t="n">
         <v>34.75</v>
@@ -24282,7 +24282,7 @@
         <v>211.9499969482422</v>
       </c>
       <c r="I783" t="n">
-        <v>781.3681640625</v>
+        <v>781.3681030273438</v>
       </c>
       <c r="J783" t="n">
         <v>33.2599983215332</v>
@@ -24372,7 +24372,7 @@
         <v>43</v>
       </c>
       <c r="G786" t="n">
-        <v>1165.534423828125</v>
+        <v>1165.534545898438</v>
       </c>
       <c r="H786" t="n">
         <v>219.6000061035156</v>
@@ -24404,7 +24404,7 @@
         <v>44.04999923706055</v>
       </c>
       <c r="G787" t="n">
-        <v>1199.243286132812</v>
+        <v>1199.243408203125</v>
       </c>
       <c r="H787" t="n">
         <v>235.8600006103516</v>
@@ -24442,7 +24442,7 @@
         <v>239.3500061035156</v>
       </c>
       <c r="I788" t="n">
-        <v>835.62158203125</v>
+        <v>835.6215209960938</v>
       </c>
       <c r="J788" t="n">
         <v>36.04000091552734</v>
@@ -24468,7 +24468,7 @@
         <v>44.18999862670898</v>
       </c>
       <c r="G789" t="n">
-        <v>1227.796875</v>
+        <v>1227.796752929688</v>
       </c>
       <c r="H789" t="n">
         <v>229.7200012207031</v>
@@ -24532,7 +24532,7 @@
         <v>41.93000030517578</v>
       </c>
       <c r="G791" t="n">
-        <v>1246.287231445312</v>
+        <v>1246.287109375</v>
       </c>
       <c r="H791" t="n">
         <v>220.3300018310547</v>
@@ -24564,13 +24564,13 @@
         <v>41.4900016784668</v>
       </c>
       <c r="G792" t="n">
-        <v>1237.215454101562</v>
+        <v>1237.215576171875</v>
       </c>
       <c r="H792" t="n">
         <v>218.4400024414062</v>
       </c>
       <c r="I792" t="n">
-        <v>780.9218139648438</v>
+        <v>780.9217529296875</v>
       </c>
       <c r="J792" t="n">
         <v>33.38999938964844</v>
@@ -24596,13 +24596,13 @@
         <v>40.52999877929688</v>
       </c>
       <c r="G793" t="n">
-        <v>1228.242919921875</v>
+        <v>1228.242797851562</v>
       </c>
       <c r="H793" t="n">
         <v>219.3800048828125</v>
       </c>
       <c r="I793" t="n">
-        <v>770.3587646484375</v>
+        <v>770.3588256835938</v>
       </c>
       <c r="J793" t="n">
         <v>33.02000045776367</v>
@@ -24628,13 +24628,13 @@
         <v>40.52999877929688</v>
       </c>
       <c r="G794" t="n">
-        <v>1228.242919921875</v>
+        <v>1228.242797851562</v>
       </c>
       <c r="H794" t="n">
         <v>219.3800048828125</v>
       </c>
       <c r="I794" t="n">
-        <v>770.3587646484375</v>
+        <v>770.3588256835938</v>
       </c>
       <c r="J794" t="n">
         <v>33.02000045776367</v>
@@ -24692,7 +24692,7 @@
         <v>44.0099983215332</v>
       </c>
       <c r="G796" t="n">
-        <v>1258.283447265625</v>
+        <v>1258.283569335938</v>
       </c>
       <c r="H796" t="n">
         <v>237.2799987792969</v>
@@ -24724,7 +24724,7 @@
         <v>47.43999862670898</v>
       </c>
       <c r="G797" t="n">
-        <v>1265.421875</v>
+        <v>1265.421752929688</v>
       </c>
       <c r="H797" t="n">
         <v>239.5</v>
@@ -24756,7 +24756,7 @@
         <v>47.4900016784668</v>
       </c>
       <c r="G798" t="n">
-        <v>1290.951416015625</v>
+        <v>1290.951293945312</v>
       </c>
       <c r="H798" t="n">
         <v>243.6399993896484</v>
@@ -24826,7 +24826,7 @@
         <v>253.7799987792969</v>
       </c>
       <c r="I800" t="n">
-        <v>802.4942626953125</v>
+        <v>802.4942016601562</v>
       </c>
       <c r="J800" t="n">
         <v>39.47000122070312</v>
@@ -24948,13 +24948,13 @@
         <v>44.70000076293945</v>
       </c>
       <c r="G804" t="n">
-        <v>1240.437622070312</v>
+        <v>1240.437744140625</v>
       </c>
       <c r="H804" t="n">
         <v>257.2000122070312</v>
       </c>
       <c r="I804" t="n">
-        <v>811.1232299804688</v>
+        <v>811.1231689453125</v>
       </c>
       <c r="J804" t="n">
         <v>42.31000137329102</v>
@@ -24980,13 +24980,13 @@
         <v>45.41999816894531</v>
       </c>
       <c r="G805" t="n">
-        <v>1238.008544921875</v>
+        <v>1238.008666992188</v>
       </c>
       <c r="H805" t="n">
         <v>262.25</v>
       </c>
       <c r="I805" t="n">
-        <v>818.7603759765625</v>
+        <v>818.7603149414062</v>
       </c>
       <c r="J805" t="n">
         <v>43.15999984741211</v>
@@ -25018,7 +25018,7 @@
         <v>250.3500061035156</v>
       </c>
       <c r="I806" t="n">
-        <v>788.6085815429688</v>
+        <v>788.6085205078125</v>
       </c>
       <c r="J806" t="n">
         <v>41.34999847412109</v>
@@ -25044,7 +25044,7 @@
         <v>41.22999954223633</v>
       </c>
       <c r="G807" t="n">
-        <v>1155.71923828125</v>
+        <v>1155.719116210938</v>
       </c>
       <c r="H807" t="n">
         <v>241.5</v>
@@ -25114,7 +25114,7 @@
         <v>243.75</v>
       </c>
       <c r="I809" t="n">
-        <v>774.7227783203125</v>
+        <v>774.7228393554688</v>
       </c>
       <c r="J809" t="n">
         <v>39</v>
@@ -25210,7 +25210,7 @@
         <v>253.1999969482422</v>
       </c>
       <c r="I812" t="n">
-        <v>832.8939819335938</v>
+        <v>832.89404296875</v>
       </c>
       <c r="J812" t="n">
         <v>41.83000183105469</v>
@@ -25268,7 +25268,7 @@
         <v>45.11000061035156</v>
       </c>
       <c r="G814" t="n">
-        <v>1284.407958984375</v>
+        <v>1284.407836914062</v>
       </c>
       <c r="H814" t="n">
         <v>271.25</v>
@@ -25300,7 +25300,7 @@
         <v>45.79000091552734</v>
       </c>
       <c r="G815" t="n">
-        <v>1280.144653320312</v>
+        <v>1280.144775390625</v>
       </c>
       <c r="H815" t="n">
         <v>266.5499877929688</v>
@@ -25338,7 +25338,7 @@
         <v>266.25</v>
       </c>
       <c r="I816" t="n">
-        <v>866.1204833984375</v>
+        <v>866.1205444335938</v>
       </c>
       <c r="J816" t="n">
         <v>43.52999877929688</v>
@@ -25402,7 +25402,7 @@
         <v>256.8999938964844</v>
       </c>
       <c r="I818" t="n">
-        <v>844.3992919921875</v>
+        <v>844.3992309570312</v>
       </c>
       <c r="J818" t="n">
         <v>41.36000061035156</v>
@@ -25428,13 +25428,13 @@
         <v>43.45000076293945</v>
       </c>
       <c r="G819" t="n">
-        <v>1357.080322265625</v>
+        <v>1357.080444335938</v>
       </c>
       <c r="H819" t="n">
         <v>255.3000030517578</v>
       </c>
       <c r="I819" t="n">
-        <v>861.7068481445312</v>
+        <v>861.706787109375</v>
       </c>
       <c r="J819" t="n">
         <v>41.36000061035156</v>
@@ -25466,7 +25466,7 @@
         <v>256.7000122070312</v>
       </c>
       <c r="I820" t="n">
-        <v>865.029541015625</v>
+        <v>865.0294799804688</v>
       </c>
       <c r="J820" t="n">
         <v>41.0099983215332</v>
@@ -25530,7 +25530,7 @@
         <v>251.75</v>
       </c>
       <c r="I822" t="n">
-        <v>849.7056274414062</v>
+        <v>849.7056884765625</v>
       </c>
       <c r="J822" t="n">
         <v>40.22999954223633</v>
@@ -25594,7 +25594,7 @@
         <v>236.3500061035156</v>
       </c>
       <c r="I824" t="n">
-        <v>841.0270385742188</v>
+        <v>841.027099609375</v>
       </c>
       <c r="J824" t="n">
         <v>38.25</v>
@@ -25684,7 +25684,7 @@
         <v>42.4900016784668</v>
       </c>
       <c r="G827" t="n">
-        <v>1365.408447265625</v>
+        <v>1365.408325195312</v>
       </c>
       <c r="H827" t="n">
         <v>234.6000061035156</v>
@@ -25716,7 +25716,7 @@
         <v>45.20000076293945</v>
       </c>
       <c r="G828" t="n">
-        <v>1424.20068359375</v>
+        <v>1424.200561523438</v>
       </c>
       <c r="H828" t="n">
         <v>255.3500061035156</v>
@@ -25748,7 +25748,7 @@
         <v>45.61000061035156</v>
       </c>
       <c r="G829" t="n">
-        <v>1403.578735351562</v>
+        <v>1403.57861328125</v>
       </c>
       <c r="H829" t="n">
         <v>265.0499877929688</v>
@@ -25780,7 +25780,7 @@
         <v>46.59000015258789</v>
       </c>
       <c r="G830" t="n">
-        <v>1412.204223632812</v>
+        <v>1412.204345703125</v>
       </c>
       <c r="H830" t="n">
         <v>271.6499938964844</v>
@@ -25882,7 +25882,7 @@
         <v>279.5</v>
       </c>
       <c r="I833" t="n">
-        <v>921.0185546875</v>
+        <v>921.0186157226562</v>
       </c>
       <c r="J833" t="n">
         <v>45.68999862670898</v>
@@ -25908,13 +25908,13 @@
         <v>46.61999893188477</v>
       </c>
       <c r="G834" t="n">
-        <v>1412.402587890625</v>
+        <v>1412.402465820312</v>
       </c>
       <c r="H834" t="n">
         <v>274.6499938964844</v>
       </c>
       <c r="I834" t="n">
-        <v>912.0921020507812</v>
+        <v>912.092041015625</v>
       </c>
       <c r="J834" t="n">
         <v>44.72999954223633</v>
@@ -25940,7 +25940,7 @@
         <v>46.68999862670898</v>
       </c>
       <c r="G835" t="n">
-        <v>1416.963134765625</v>
+        <v>1416.963012695312</v>
       </c>
       <c r="H835" t="n">
         <v>276.1499938964844</v>
@@ -26100,13 +26100,13 @@
         <v>52.68999862670898</v>
       </c>
       <c r="G840" t="n">
-        <v>1400.802734375</v>
+        <v>1400.802856445312</v>
       </c>
       <c r="H840" t="n">
         <v>308.2999877929688</v>
       </c>
       <c r="I840" t="n">
-        <v>920.7706298828125</v>
+        <v>920.7705688476562</v>
       </c>
       <c r="J840" t="n">
         <v>50.43000030517578</v>
@@ -26228,7 +26228,7 @@
         <v>55.09000015258789</v>
       </c>
       <c r="G844" t="n">
-        <v>1393.466186523438</v>
+        <v>1393.466064453125</v>
       </c>
       <c r="H844" t="n">
         <v>342.0499877929688</v>
@@ -26260,13 +26260,13 @@
         <v>55.31999969482422</v>
       </c>
       <c r="G845" t="n">
-        <v>1411.31201171875</v>
+        <v>1411.311889648438</v>
       </c>
       <c r="H845" t="n">
         <v>380.6000061035156</v>
       </c>
       <c r="I845" t="n">
-        <v>941.9463500976562</v>
+        <v>941.9464111328125</v>
       </c>
       <c r="J845" t="n">
         <v>60.93000030517578</v>
@@ -26324,7 +26324,7 @@
         <v>54.13999938964844</v>
       </c>
       <c r="G847" t="n">
-        <v>1431.140747070312</v>
+        <v>1431.140625</v>
       </c>
       <c r="H847" t="n">
         <v>371.7999877929688</v>
@@ -26452,13 +26452,13 @@
         <v>55.16999816894531</v>
       </c>
       <c r="G851" t="n">
-        <v>1429.257080078125</v>
+        <v>1429.256958007812</v>
       </c>
       <c r="H851" t="n">
         <v>395.4500122070312</v>
       </c>
       <c r="I851" t="n">
-        <v>992.3812255859375</v>
+        <v>992.3811645507812</v>
       </c>
       <c r="J851" t="n">
         <v>69.72000122070312</v>
@@ -26490,7 +26490,7 @@
         <v>384.5499877929688</v>
       </c>
       <c r="I852" t="n">
-        <v>967.0894165039062</v>
+        <v>967.08935546875</v>
       </c>
       <c r="J852" t="n">
         <v>67.05000305175781</v>
@@ -26516,7 +26516,7 @@
         <v>54.61999893188477</v>
       </c>
       <c r="G853" t="n">
-        <v>1425.489624023438</v>
+        <v>1425.489501953125</v>
       </c>
       <c r="H853" t="n">
         <v>380.8999938964844</v>
@@ -26548,7 +26548,7 @@
         <v>53.13999938964844</v>
       </c>
       <c r="G854" t="n">
-        <v>1418.946044921875</v>
+        <v>1418.945922851562</v>
       </c>
       <c r="H854" t="n">
         <v>368.1000061035156</v>
@@ -26612,7 +26612,7 @@
         <v>52.4900016784668</v>
       </c>
       <c r="G856" t="n">
-        <v>1421.028198242188</v>
+        <v>1421.028076171875</v>
       </c>
       <c r="H856" t="n">
         <v>382.7999877929688</v>
@@ -26708,7 +26708,7 @@
         <v>53.65999984741211</v>
       </c>
       <c r="G859" t="n">
-        <v>1438.378295898438</v>
+        <v>1438.378173828125</v>
       </c>
       <c r="H859" t="n">
         <v>385.3999938964844</v>
@@ -26772,7 +26772,7 @@
         <v>59.54000091552734</v>
       </c>
       <c r="G861" t="n">
-        <v>1482.497314453125</v>
+        <v>1482.497192382812</v>
       </c>
       <c r="H861" t="n">
         <v>417.3999938964844</v>
@@ -26804,7 +26804,7 @@
         <v>58.88000106811523</v>
       </c>
       <c r="G862" t="n">
-        <v>1502.425170898438</v>
+        <v>1502.425048828125</v>
       </c>
       <c r="H862" t="n">
         <v>413.0499877929688</v>
@@ -26900,7 +26900,7 @@
         <v>57.02000045776367</v>
       </c>
       <c r="G865" t="n">
-        <v>1505.796020507812</v>
+        <v>1505.796142578125</v>
       </c>
       <c r="H865" t="n">
         <v>396.75</v>
@@ -26932,7 +26932,7 @@
         <v>58.11000061035156</v>
       </c>
       <c r="G866" t="n">
-        <v>1504.8046875</v>
+        <v>1504.804565429688</v>
       </c>
       <c r="H866" t="n">
         <v>376.9500122070312</v>
@@ -27028,7 +27028,7 @@
         <v>55.86000061035156</v>
       </c>
       <c r="G869" t="n">
-        <v>1524.434936523438</v>
+        <v>1524.43505859375</v>
       </c>
       <c r="H869" t="n">
         <v>373.4500122070312</v>
@@ -27092,7 +27092,7 @@
         <v>55.68000030517578</v>
       </c>
       <c r="G871" t="n">
-        <v>1504.209594726562</v>
+        <v>1504.209716796875</v>
       </c>
       <c r="H871" t="n">
         <v>372.1499938964844</v>
@@ -27252,7 +27252,7 @@
         <v>60.77999877929688</v>
       </c>
       <c r="G876" t="n">
-        <v>1463.759155273438</v>
+        <v>1463.759033203125</v>
       </c>
       <c r="H876" t="n">
         <v>396.3500061035156</v>
@@ -27284,7 +27284,7 @@
         <v>61.22999954223633</v>
       </c>
       <c r="G877" t="n">
-        <v>1463.362548828125</v>
+        <v>1463.362426757812</v>
       </c>
       <c r="H877" t="n">
         <v>390.2999877929688</v>
@@ -27380,7 +27380,7 @@
         <v>60.09999847412109</v>
       </c>
       <c r="G880" t="n">
-        <v>1412.402587890625</v>
+        <v>1412.402465820312</v>
       </c>
       <c r="H880" t="n">
         <v>378.75</v>
@@ -27412,7 +27412,7 @@
         <v>59.95000076293945</v>
       </c>
       <c r="G881" t="n">
-        <v>1390.888427734375</v>
+        <v>1390.888305664062</v>
       </c>
       <c r="H881" t="n">
         <v>359.8500061035156</v>
@@ -27476,7 +27476,7 @@
         <v>56.25</v>
       </c>
       <c r="G883" t="n">
-        <v>1375.71923828125</v>
+        <v>1375.719360351562</v>
       </c>
       <c r="H883" t="n">
         <v>326.3999938964844</v>
@@ -27508,7 +27508,7 @@
         <v>56.45999908447266</v>
       </c>
       <c r="G884" t="n">
-        <v>1404.966674804688</v>
+        <v>1404.966796875</v>
       </c>
       <c r="H884" t="n">
         <v>340.25</v>
@@ -27540,7 +27540,7 @@
         <v>56.16999816894531</v>
       </c>
       <c r="G885" t="n">
-        <v>1398.026611328125</v>
+        <v>1398.026733398438</v>
       </c>
       <c r="H885" t="n">
         <v>327.4500122070312</v>
@@ -27700,7 +27700,7 @@
         <v>57.2400016784668</v>
       </c>
       <c r="G890" t="n">
-        <v>1380.874755859375</v>
+        <v>1380.874877929688</v>
       </c>
       <c r="H890" t="n">
         <v>295.0499877929688</v>
@@ -27732,7 +27732,7 @@
         <v>56.29000091552734</v>
       </c>
       <c r="G891" t="n">
-        <v>1377.504028320312</v>
+        <v>1377.50390625</v>
       </c>
       <c r="H891" t="n">
         <v>281.2999877929688</v>
@@ -37180,7 +37180,7 @@
         <v>22.02878904102883</v>
       </c>
       <c r="I20" t="n">
-        <v>2.551410974090174</v>
+        <v>2.551418984708165</v>
       </c>
       <c r="J20" t="n">
         <v>29.22429859056908</v>
@@ -37212,7 +37212,7 @@
         <v>-15.42298811409775</v>
       </c>
       <c r="I21" t="n">
-        <v>-18.74999523997749</v>
+        <v>-18.75000158667417</v>
       </c>
       <c r="J21" t="n">
         <v>-17.03667200064552</v>
@@ -37244,7 +37244,7 @@
         <v>-17.60644052854861</v>
       </c>
       <c r="I22" t="n">
-        <v>-10.47092091451074</v>
+        <v>-10.47091074017598</v>
       </c>
       <c r="J22" t="n">
         <v>-5.892015050324451</v>
@@ -37276,7 +37276,7 @@
         <v>8.975273108262826</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.731624790012059</v>
+        <v>-7.731635275646898</v>
       </c>
       <c r="J23" t="n">
         <v>10.07751326691555</v>
@@ -37468,7 +37468,7 @@
         <v>20.18634526010754</v>
       </c>
       <c r="I29" t="n">
-        <v>14.89905459147085</v>
+        <v>14.89904258694705</v>
       </c>
       <c r="J29" t="n">
         <v>17.84114543475508</v>
@@ -37494,13 +37494,13 @@
         <v>-10.12373435941966</v>
       </c>
       <c r="G30" t="n">
-        <v>-2.494890928578097</v>
+        <v>-2.4948827172523</v>
       </c>
       <c r="H30" t="n">
         <v>-6.49240482812462</v>
       </c>
       <c r="I30" t="n">
-        <v>-10.79031925231471</v>
+        <v>-10.79030993178678</v>
       </c>
       <c r="J30" t="n">
         <v>-10.07326035477244</v>
@@ -37526,7 +37526,7 @@
         <v>3.132256001421796</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.268632380719259</v>
+        <v>-1.268640695312884</v>
       </c>
       <c r="H31" t="n">
         <v>-34.34213475489638</v>
@@ -37596,7 +37596,7 @@
         <v>-4.392992435061648</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7267486143703428</v>
+        <v>0.7267397958982569</v>
       </c>
       <c r="J33" t="n">
         <v>-18.79194166943702</v>
@@ -37622,13 +37622,13 @@
         <v>33.94390617495342</v>
       </c>
       <c r="G34" t="n">
-        <v>10.37930970539087</v>
+        <v>10.3793202560976</v>
       </c>
       <c r="H34" t="n">
         <v>10.12869384694794</v>
       </c>
       <c r="I34" t="n">
-        <v>4.617430052899274</v>
+        <v>4.617439211995333</v>
       </c>
       <c r="J34" t="n">
         <v>27.89699662161886</v>
@@ -37654,7 +37654,7 @@
         <v>0.9243158800178009</v>
       </c>
       <c r="G35" t="n">
-        <v>8.727841537326796</v>
+        <v>8.72783114447817</v>
       </c>
       <c r="H35" t="n">
         <v>10.5665365226655</v>
@@ -37837,13 +37837,13 @@
         <v>2.446982085920046</v>
       </c>
       <c r="G41" t="n">
-        <v>3.25318376876691</v>
+        <v>3.253172538244864</v>
       </c>
       <c r="H41" t="n">
         <v>2.635488591081314</v>
       </c>
       <c r="I41" t="n">
-        <v>5.350305819753065</v>
+        <v>5.350313005783192</v>
       </c>
       <c r="J41" t="n">
         <v>8.494211565028188</v>
@@ -37866,13 +37866,13 @@
         <v>5.598621951273208</v>
       </c>
       <c r="G42" t="n">
-        <v>2.040889260620204</v>
+        <v>2.040911684465785</v>
       </c>
       <c r="H42" t="n">
         <v>-14.50333586855534</v>
       </c>
       <c r="I42" t="n">
-        <v>7.78906670291879</v>
+        <v>7.789059350539329</v>
       </c>
       <c r="J42" t="n">
         <v>6.147541079717245</v>
@@ -37895,7 +37895,7 @@
         <v>7.004606888590881</v>
       </c>
       <c r="G43" t="n">
-        <v>3.837332239883229</v>
+        <v>3.837308748533363</v>
       </c>
       <c r="H43" t="n">
         <v>9.220106101738512</v>
@@ -37924,7 +37924,7 @@
         <v>-7.106166810697612</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3659831072441166</v>
+        <v>0.3659830649118234</v>
       </c>
       <c r="H44" t="n">
         <v>10.36725582872331</v>
@@ -37953,13 +37953,13 @@
         <v>-5.117786759101961</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.329743130358585</v>
+        <v>-1.329731717430038</v>
       </c>
       <c r="H45" t="n">
         <v>4.476417699780821</v>
       </c>
       <c r="I45" t="n">
-        <v>-7.821836608719702</v>
+        <v>-7.821843174509246</v>
       </c>
       <c r="J45" t="n">
         <v>-23.13725340600107</v>
@@ -37982,13 +37982,13 @@
         <v>-6.883508838267105</v>
       </c>
       <c r="G46" t="n">
-        <v>-7.590699242184062</v>
+        <v>-7.590679750087537</v>
       </c>
       <c r="H46" t="n">
         <v>-9.150325892060184</v>
       </c>
       <c r="I46" t="n">
-        <v>-7.873151044662352</v>
+        <v>-7.873144482527428</v>
       </c>
       <c r="J46" t="n">
         <v>-11.14982814589901</v>
@@ -38011,13 +38011,13 @@
         <v>-2.865546642449923</v>
       </c>
       <c r="G47" t="n">
-        <v>-6.742080393201555</v>
+        <v>-6.742100064294965</v>
       </c>
       <c r="H47" t="n">
         <v>-12.68230842551258</v>
       </c>
       <c r="I47" t="n">
-        <v>-10.50510919721274</v>
+        <v>-10.50509868554349</v>
       </c>
       <c r="J47" t="n">
         <v>-10.59189368473866</v>
@@ -38046,7 +38046,7 @@
         <v>11.48815860769938</v>
       </c>
       <c r="I48" t="n">
-        <v>-3.906749435665913</v>
+        <v>-3.90674987660834</v>
       </c>
       <c r="J48" t="n">
         <v>-0.3105661069842447</v>
@@ -38075,7 +38075,7 @@
         <v>3.474762330681291</v>
       </c>
       <c r="I49" t="n">
-        <v>1.992291639014976</v>
+        <v>1.992280127469637</v>
       </c>
       <c r="J49" t="n">
         <v>-1.829263683162408</v>
@@ -38098,13 +38098,13 @@
         <v>-8.498583753085121</v>
       </c>
       <c r="G50" t="n">
-        <v>-9.863710381250424</v>
+        <v>-9.863701201961927</v>
       </c>
       <c r="H50" t="n">
         <v>-15.6172858344184</v>
       </c>
       <c r="I50" t="n">
-        <v>5.378692749161718</v>
+        <v>5.378686357567153</v>
       </c>
       <c r="J50" t="n">
         <v>-2.380950218425493</v>
@@ -38127,13 +38127,13 @@
         <v>8.782737772308536</v>
       </c>
       <c r="G51" t="n">
-        <v>5.463643374052984</v>
+        <v>5.463621306864352</v>
       </c>
       <c r="H51" t="n">
         <v>38.34329813061588</v>
       </c>
       <c r="I51" t="n">
-        <v>4.312846044487295</v>
+        <v>4.312852371434839</v>
       </c>
       <c r="J51" t="n">
         <v>35.48386898298783</v>
@@ -38156,13 +38156,13 @@
         <v>-5.942026774088538</v>
       </c>
       <c r="G52" t="n">
-        <v>-3.320959644468446</v>
+        <v>-3.32094926095331</v>
       </c>
       <c r="H52" t="n">
         <v>29.24944861623748</v>
       </c>
       <c r="I52" t="n">
-        <v>3.064809031177451</v>
+        <v>3.064815751886085</v>
       </c>
       <c r="J52" t="n">
         <v>7.826083639393677</v>
@@ -38191,7 +38191,7 @@
         <v>-16.0722547147822</v>
       </c>
       <c r="I53" t="n">
-        <v>2.955485477722197</v>
+        <v>2.955471852145508</v>
       </c>
       <c r="J53" t="n">
         <v>-8.730161493387333</v>
@@ -38214,13 +38214,13 @@
         <v>-12.41298993858072</v>
       </c>
       <c r="G54" t="n">
-        <v>-5.648240672096827</v>
+        <v>-5.648249785852466</v>
       </c>
       <c r="H54" t="n">
         <v>-12.62647164563844</v>
       </c>
       <c r="I54" t="n">
-        <v>-16.35937610199863</v>
+        <v>-16.35936109340738</v>
       </c>
       <c r="J54" t="n">
         <v>-11.57894469144052</v>
@@ -38243,13 +38243,13 @@
         <v>1.233112628945943</v>
       </c>
       <c r="G55" t="n">
-        <v>5.901885722416633</v>
+        <v>5.90190678499245</v>
       </c>
       <c r="H55" t="n">
         <v>10.01780916676824</v>
       </c>
       <c r="I55" t="n">
-        <v>42.15600259621435</v>
+        <v>42.15598663130014</v>
       </c>
       <c r="J55" t="n">
         <v>5.555555555555558</v>
@@ -38272,13 +38272,13 @@
         <v>10.65627667685571</v>
       </c>
       <c r="G56" t="n">
-        <v>11.66325857150592</v>
+        <v>11.66324714899951</v>
       </c>
       <c r="H56" t="n">
         <v>7.361381156751889</v>
       </c>
       <c r="I56" t="n">
-        <v>11.44042835922838</v>
+        <v>11.44043827261805</v>
       </c>
       <c r="J56" t="n">
         <v>3.4482743501002</v>
@@ -38301,13 +38301,13 @@
         <v>-6.15854030702172</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.133414869096705</v>
+        <v>-1.133426034140439</v>
       </c>
       <c r="H57" t="n">
         <v>3.513107684464867</v>
       </c>
       <c r="I57" t="n">
-        <v>-20.63636310365917</v>
+        <v>-20.63635895754907</v>
       </c>
       <c r="J57" t="n">
         <v>-11.82432417193846</v>
@@ -38614,7 +38614,7 @@
         <v>-14.96300514920803</v>
       </c>
       <c r="I8" t="n">
-        <v>-25.40166188931352</v>
+        <v>-25.40165341174989</v>
       </c>
       <c r="J8" t="n">
         <v>0.8920213186065729</v>
@@ -38646,7 +38646,7 @@
         <v>-9.514179193100469</v>
       </c>
       <c r="I9" t="n">
-        <v>-13.68453939027434</v>
+        <v>-13.68454919940341</v>
       </c>
       <c r="J9" t="n">
         <v>-12.45376365041914</v>
@@ -38736,7 +38736,7 @@
         <v>-1.316544414387844</v>
       </c>
       <c r="G12" t="n">
-        <v>14.96160218792302</v>
+        <v>14.96161317663234</v>
       </c>
       <c r="H12" t="n">
         <v>29.14681042220371</v>
@@ -38768,7 +38768,7 @@
         <v>36.80501262584171</v>
       </c>
       <c r="G13" t="n">
-        <v>10.23240719569851</v>
+        <v>10.23239665903461</v>
       </c>
       <c r="H13" t="n">
         <v>21.06174227192534</v>
@@ -38826,7 +38826,7 @@
         <v>15.76036725725447</v>
       </c>
       <c r="G15" t="n">
-        <v>9.403498072287109</v>
+        <v>9.403485464018434</v>
       </c>
       <c r="H15" t="n">
         <v>-4.159445407279028</v>
@@ -38855,7 +38855,7 @@
         <v>-17.92738085880669</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.485800364111073</v>
+        <v>-8.4857705142105</v>
       </c>
       <c r="H16" t="n">
         <v>4.756719823472322</v>
@@ -38884,7 +38884,7 @@
         <v>2.321981478994783</v>
       </c>
       <c r="G17" t="n">
-        <v>7.126481195260181</v>
+        <v>7.126458598841245</v>
       </c>
       <c r="H17" t="n">
         <v>0.7315289117223678</v>
@@ -38919,7 +38919,7 @@
         <v>50.88300138028043</v>
       </c>
       <c r="I18" t="n">
-        <v>13.2924593012159</v>
+        <v>13.29246668885498</v>
       </c>
       <c r="J18" t="n">
         <v>42.60869233504585</v>
@@ -38942,13 +38942,13 @@
         <v>-18.96653110566366</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.484012998322481</v>
+        <v>-1.484002920704985</v>
       </c>
       <c r="H19" t="n">
         <v>-19.32324486904549</v>
       </c>
       <c r="I19" t="n">
-        <v>22.41424466278947</v>
+        <v>22.41423668033238</v>
       </c>
       <c r="J19" t="n">
         <v>-14.81481481481481</v>
@@ -39057,7 +39057,7 @@
         <v>48.02197768635678</v>
       </c>
       <c r="G2" t="n">
-        <v>20.74572935508516</v>
+        <v>20.74573916003721</v>
       </c>
       <c r="H2" t="n">
         <v>26.11641041112731</v>
@@ -39089,13 +39089,13 @@
         <v>37.25662738916504</v>
       </c>
       <c r="G3" t="n">
-        <v>20.20696515539304</v>
+        <v>20.20695336635119</v>
       </c>
       <c r="H3" t="n">
         <v>16.15136360938538</v>
       </c>
       <c r="I3" t="n">
-        <v>13.18952182341448</v>
+        <v>13.18953514511048</v>
       </c>
       <c r="J3" t="n">
         <v>70.0000032885322</v>
@@ -39121,7 +39121,7 @@
         <v>35.23950508448274</v>
       </c>
       <c r="G4" t="n">
-        <v>20.50513561497333</v>
+        <v>20.50514742013778</v>
       </c>
       <c r="H4" t="n">
         <v>18.55826056452661</v>
@@ -39153,7 +39153,7 @@
         <v>37.43092805121666</v>
       </c>
       <c r="G5" t="n">
-        <v>20.81959851262889</v>
+        <v>20.81958647428637</v>
       </c>
       <c r="H5" t="n">
         <v>18.42639458918014</v>
@@ -39185,7 +39185,7 @@
         <v>32.87407769097221</v>
       </c>
       <c r="G6" t="n">
-        <v>19.09141951598872</v>
+        <v>19.09140759479682</v>
       </c>
       <c r="H6" t="n">
         <v>20.42312944893776</v>
@@ -39217,13 +39217,13 @@
         <v>30.13837487565421</v>
       </c>
       <c r="G7" t="n">
-        <v>20.09521421428811</v>
+        <v>20.09523646786675</v>
       </c>
       <c r="H7" t="n">
         <v>19.02754764747889</v>
       </c>
       <c r="I7" t="n">
-        <v>14.23300300571448</v>
+        <v>14.23302215061948</v>
       </c>
       <c r="J7" t="n">
         <v>70.31517486505918</v>
@@ -39249,7 +39249,7 @@
         <v>30.24495302920487</v>
       </c>
       <c r="G8" t="n">
-        <v>21.1796060813265</v>
+        <v>21.17961628996452</v>
       </c>
       <c r="H8" t="n">
         <v>17.59891665078761</v>
@@ -39281,7 +39281,7 @@
         <v>28.71272416548296</v>
       </c>
       <c r="G9" t="n">
-        <v>20.46287689229769</v>
+        <v>20.46287480132978</v>
       </c>
       <c r="H9" t="n">
         <v>12.19356144837187</v>
@@ -39345,7 +39345,7 @@
         <v>28.25741212487847</v>
       </c>
       <c r="G11" t="n">
-        <v>22.48963639778619</v>
+        <v>22.48964894222016</v>
       </c>
       <c r="H11" t="n">
         <v>13.73462507545713</v>
@@ -39377,7 +39377,7 @@
         <v>29.44169870113738</v>
       </c>
       <c r="G12" t="n">
-        <v>22.48258583524598</v>
+        <v>22.48258353089252</v>
       </c>
       <c r="H12" t="n">
         <v>12.00104193248259</v>
@@ -39441,7 +39441,7 @@
         <v>25.29452475957892</v>
       </c>
       <c r="G14" t="n">
-        <v>20.92206060195419</v>
+        <v>20.92203812635944</v>
       </c>
       <c r="H14" t="n">
         <v>48.492657589076</v>
@@ -39479,7 +39479,7 @@
         <v>50.10011067847504</v>
       </c>
       <c r="I15" t="n">
-        <v>12.44310724452127</v>
+        <v>12.4430882751237</v>
       </c>
       <c r="J15" t="n">
         <v>63.25471398498556</v>
@@ -39511,7 +39511,7 @@
         <v>69.59249787931468</v>
       </c>
       <c r="I16" t="n">
-        <v>15.6815136261576</v>
+        <v>15.68150654251597</v>
       </c>
       <c r="J16" t="n">
         <v>71.82033478974208</v>
@@ -39543,7 +39543,7 @@
         <v>80.21875186197276</v>
       </c>
       <c r="I17" t="n">
-        <v>38.57650560107664</v>
+        <v>38.57649706808945</v>
       </c>
       <c r="J17" t="n">
         <v>83.413475601984</v>
@@ -39601,13 +39601,13 @@
         <v>18.99342970595615</v>
       </c>
       <c r="G19" t="n">
-        <v>22.31659394060852</v>
+        <v>22.31658161015133</v>
       </c>
       <c r="H19" t="n">
         <v>94.1268552045597</v>
       </c>
       <c r="I19" t="n">
-        <v>32.47951058552494</v>
+        <v>32.47951491030909</v>
       </c>
       <c r="J19" t="n">
         <v>121.3157854582134</v>
@@ -39633,7 +39633,7 @@
         <v>19.92705386519244</v>
       </c>
       <c r="G20" t="n">
-        <v>22.53160722132512</v>
+        <v>22.53161956213026</v>
       </c>
       <c r="H20" t="n">
         <v>87.55847280153539</v>
@@ -39665,13 +39665,13 @@
         <v>23.86999327483017</v>
       </c>
       <c r="G21" t="n">
-        <v>24.60929473401883</v>
+        <v>24.60930726084567</v>
       </c>
       <c r="H21" t="n">
         <v>75.75510868409864</v>
       </c>
       <c r="I21" t="n">
-        <v>31.45755910332362</v>
+        <v>31.45754638735967</v>
       </c>
       <c r="J21" t="n">
         <v>142.036550378158</v>
@@ -39735,7 +39735,7 @@
         <v>91.13414267872835</v>
       </c>
       <c r="I23" t="n">
-        <v>30.90392562284006</v>
+        <v>30.90391269316848</v>
       </c>
       <c r="J23" t="n">
         <v>168.1889879197244</v>
@@ -39799,7 +39799,7 @@
         <v>71.35134787851175</v>
       </c>
       <c r="I25" t="n">
-        <v>25.73533458085297</v>
+        <v>25.73532638273688</v>
       </c>
       <c r="J25" t="n">
         <v>169.5767290544607</v>
@@ -39825,13 +39825,13 @@
         <v>12.20622202314199</v>
       </c>
       <c r="G26" t="n">
-        <v>17.5310103032488</v>
+        <v>17.53099974610059</v>
       </c>
       <c r="H26" t="n">
         <v>66.09046092268591</v>
       </c>
       <c r="I26" t="n">
-        <v>19.3941404935573</v>
+        <v>19.39414825240846</v>
       </c>
       <c r="J26" t="n">
         <v>155.4089687454518</v>
@@ -39857,13 +39857,13 @@
         <v>17.44186046511629</v>
       </c>
       <c r="G27" t="n">
-        <v>19.70907390202596</v>
+        <v>19.70906335411693</v>
       </c>
       <c r="H27" t="n">
         <v>75.14619883040936</v>
       </c>
       <c r="I27" t="n">
-        <v>22.59875492383123</v>
+        <v>22.5987420097109</v>
       </c>
       <c r="J27" t="n">
         <v>141.9999975907175</v>
@@ -39927,7 +39927,7 @@
         <v>72.05968302788671</v>
       </c>
       <c r="I29" t="n">
-        <v>23.95292474688</v>
+        <v>23.95293274014536</v>
       </c>
       <c r="J29" t="n">
         <v>143.1331712833967</v>
@@ -39991,7 +39991,7 @@
         <v>65.98794595089427</v>
       </c>
       <c r="I31" t="n">
-        <v>28.69149231270651</v>
+        <v>28.69148398560164</v>
       </c>
       <c r="J31" t="n">
         <v>126.1298637885552</v>
@@ -40023,7 +40023,7 @@
         <v>68.60328526038532</v>
       </c>
       <c r="I32" t="n">
-        <v>28.59036001224431</v>
+        <v>28.59035158704684</v>
       </c>
       <c r="J32" t="n">
         <v>136.0106421941653</v>
@@ -40049,13 +40049,13 @@
         <v>17.99588316396285</v>
       </c>
       <c r="G33" t="n">
-        <v>17.42539622610888</v>
+        <v>17.4254069034677</v>
       </c>
       <c r="H33" t="n">
         <v>69.25088116850071</v>
       </c>
       <c r="I33" t="n">
-        <v>25.14077025349546</v>
+        <v>25.14076236892711</v>
       </c>
       <c r="J33" t="n">
         <v>132.4867699130986</v>
@@ -40081,13 +40081,13 @@
         <v>13.01104692045925</v>
       </c>
       <c r="G34" t="n">
-        <v>17.43128634587006</v>
+        <v>17.43129886333536</v>
       </c>
       <c r="H34" t="n">
         <v>61.92835542694652</v>
       </c>
       <c r="I34" t="n">
-        <v>22.52245948834504</v>
+        <v>22.52247202740185</v>
       </c>
       <c r="J34" t="n">
         <v>121.4323651658852</v>
@@ -40145,7 +40145,7 @@
         <v>11.65387061590668</v>
       </c>
       <c r="G36" t="n">
-        <v>19.03023823708794</v>
+        <v>19.03024894081289</v>
       </c>
       <c r="H36" t="n">
         <v>56.8334812026194</v>
@@ -40177,13 +40177,13 @@
         <v>5.373968208882274</v>
       </c>
       <c r="G37" t="n">
-        <v>14.95783527583134</v>
+        <v>14.95782473939171</v>
       </c>
       <c r="H37" t="n">
         <v>49.29618947317174</v>
       </c>
       <c r="I37" t="n">
-        <v>15.74543228600769</v>
+        <v>15.74543755900113</v>
       </c>
       <c r="J37" t="n">
         <v>111.15383897912</v>
@@ -40209,13 +40209,13 @@
         <v>-1.762887330280316</v>
       </c>
       <c r="G38" t="n">
-        <v>14.3328526745135</v>
+        <v>14.33284215758213</v>
       </c>
       <c r="H38" t="n">
         <v>57.80926505349091</v>
       </c>
       <c r="I38" t="n">
-        <v>16.21146407658735</v>
+        <v>16.21144438360587</v>
       </c>
       <c r="J38" t="n">
         <v>124.1666581895616</v>
@@ -40273,13 +40273,13 @@
         <v>-2.996826171875</v>
       </c>
       <c r="G40" t="n">
-        <v>13.67986510978487</v>
+        <v>13.67987709270488</v>
       </c>
       <c r="H40" t="n">
         <v>62.45973288227488</v>
       </c>
       <c r="I40" t="n">
-        <v>1.128983084690516</v>
+        <v>1.128971419277369</v>
       </c>
       <c r="J40" t="n">
         <v>134.7826177095873</v>
@@ -40305,7 +40305,7 @@
         <v>-0.8370914528086359</v>
       </c>
       <c r="G41" t="n">
-        <v>13.69311700167664</v>
+        <v>13.69312892900481</v>
       </c>
       <c r="H41" t="n">
         <v>59.2399202134017</v>
@@ -40343,7 +40343,7 @@
         <v>61.70213418337656</v>
       </c>
       <c r="I42" t="n">
-        <v>4.688868773428356</v>
+        <v>4.688856355146998</v>
       </c>
       <c r="J42" t="n">
         <v>126.3361029997708</v>
@@ -40439,7 +40439,7 @@
         <v>71.45801931839102</v>
       </c>
       <c r="I45" t="n">
-        <v>12.16106151167788</v>
+        <v>12.16107377611635</v>
       </c>
       <c r="J45" t="n">
         <v>157.6646515776742</v>
@@ -40465,13 +40465,13 @@
         <v>23.51312717433578</v>
       </c>
       <c r="G46" t="n">
-        <v>15.7305998307574</v>
+        <v>15.73058716649658</v>
       </c>
       <c r="H46" t="n">
         <v>82.7479978598209</v>
       </c>
       <c r="I46" t="n">
-        <v>8.661815725075982</v>
+        <v>8.66180909462404</v>
       </c>
       <c r="J46" t="n">
         <v>157.8527653163028</v>
@@ -40497,7 +40497,7 @@
         <v>22.59531429862704</v>
       </c>
       <c r="G47" t="n">
-        <v>17.64924436890285</v>
+        <v>17.64925742497345</v>
       </c>
       <c r="H47" t="n">
         <v>85.00471194850942</v>
@@ -40529,13 +40529,13 @@
         <v>25.26545854048294</v>
       </c>
       <c r="G48" t="n">
-        <v>17.38441714906611</v>
+        <v>17.38442805403455</v>
       </c>
       <c r="H48" t="n">
         <v>86.16140643431169</v>
       </c>
       <c r="I48" t="n">
-        <v>12.55596944361153</v>
+        <v>12.55596261032248</v>
       </c>
       <c r="J48" t="n">
         <v>159.4642984056154</v>
@@ -40561,13 +40561,13 @@
         <v>21.11271857609913</v>
       </c>
       <c r="G49" t="n">
-        <v>13.30432638226435</v>
+        <v>13.30433706701131</v>
       </c>
       <c r="H49" t="n">
         <v>71.57738095238095</v>
       </c>
       <c r="I49" t="n">
-        <v>11.99740298068421</v>
+        <v>11.99739086546068</v>
       </c>
       <c r="J49" t="n">
         <v>158.230079573006</v>
@@ -40593,7 +40593,7 @@
         <v>20.76246964183235</v>
       </c>
       <c r="G50" t="n">
-        <v>12.60169068234773</v>
+        <v>12.60167988271601</v>
       </c>
       <c r="H50" t="n">
         <v>62.06793961179837</v>
@@ -40631,7 +40631,7 @@
         <v>51.29173068418904</v>
       </c>
       <c r="I51" t="n">
-        <v>9.55694650714236</v>
+        <v>9.556927218862565</v>
       </c>
       <c r="J51" t="n">
         <v>127.0114992297709</v>
@@ -40817,13 +40817,13 @@
         <v>17.16470691777749</v>
       </c>
       <c r="G57" t="n">
-        <v>6.221525178895981</v>
+        <v>6.221535872660366</v>
       </c>
       <c r="H57" t="n">
         <v>39.5845017315855</v>
       </c>
       <c r="I57" t="n">
-        <v>-4.840900868211085</v>
+        <v>-4.840912057172886</v>
       </c>
       <c r="J57" t="n">
         <v>61.69810163036917</v>
@@ -40849,7 +40849,7 @@
         <v>2.990288101739491</v>
       </c>
       <c r="G58" t="n">
-        <v>9.697594656504771</v>
+        <v>9.697583982835024</v>
       </c>
       <c r="H58" t="n">
         <v>45.31866297896825</v>
@@ -40887,7 +40887,7 @@
         <v>42.8926386006018</v>
       </c>
       <c r="I59" t="n">
-        <v>12.67964407991673</v>
+        <v>12.67965743132262</v>
       </c>
       <c r="J59" t="n">
         <v>53.73333401150173</v>
@@ -40913,13 +40913,13 @@
         <v>-5.322962953904497</v>
       </c>
       <c r="G60" t="n">
-        <v>10.34373456670381</v>
+        <v>10.34374505217044</v>
       </c>
       <c r="H60" t="n">
         <v>49.51856946354882</v>
       </c>
       <c r="I60" t="n">
-        <v>5.712422824596386</v>
+        <v>5.712399359441078</v>
       </c>
       <c r="J60" t="n">
         <v>62.82512383653869</v>
@@ -41041,13 +41041,13 @@
         <v>-7.543856079815425</v>
       </c>
       <c r="G64" t="n">
-        <v>10.43703440501735</v>
+        <v>10.43704479153176</v>
       </c>
       <c r="H64" t="n">
         <v>52.6315695544544</v>
       </c>
       <c r="I64" t="n">
-        <v>7.776546118368888</v>
+        <v>7.77652325112117</v>
       </c>
       <c r="J64" t="n">
         <v>82.06088167389984</v>
@@ -41073,13 +41073,13 @@
         <v>-2.789282531167381</v>
       </c>
       <c r="G65" t="n">
-        <v>11.19599714779607</v>
+        <v>11.19598680172837</v>
       </c>
       <c r="H65" t="n">
         <v>60.93793770295235</v>
       </c>
       <c r="I65" t="n">
-        <v>7.621073991852256</v>
+        <v>7.621096859314291</v>
       </c>
       <c r="J65" t="n">
         <v>87.27272777051292</v>
@@ -41111,7 +41111,7 @@
         <v>69.55524373430775</v>
       </c>
       <c r="I66" t="n">
-        <v>10.17211991406539</v>
+        <v>10.17209649828614</v>
       </c>
       <c r="J66" t="n">
         <v>92.45901366939118</v>
@@ -41143,7 +41143,7 @@
         <v>74.20005719956657</v>
       </c>
       <c r="I67" t="n">
-        <v>10.42934932447941</v>
+        <v>10.42936064238629</v>
       </c>
       <c r="J67" t="n">
         <v>106.4114841006974</v>
@@ -41169,7 +41169,7 @@
         <v>-3.992768548930603</v>
       </c>
       <c r="G68" t="n">
-        <v>9.923275140520182</v>
+        <v>9.923264821242771</v>
       </c>
       <c r="H68" t="n">
         <v>70.46093895677912</v>
@@ -41207,7 +41207,7 @@
         <v>59.75903941285979</v>
       </c>
       <c r="I69" t="n">
-        <v>9.336020963787828</v>
+        <v>9.336032225438418</v>
       </c>
       <c r="J69" t="n">
         <v>106.4651134402253</v>
@@ -41265,7 +41265,7 @@
         <v>-11.76738888704267</v>
       </c>
       <c r="G71" t="n">
-        <v>7.132610410294027</v>
+        <v>7.132621466067346</v>
       </c>
       <c r="H71" t="n">
         <v>51.19813928486645</v>
@@ -41303,7 +41303,7 @@
         <v>52.95796817224014</v>
       </c>
       <c r="I72" t="n">
-        <v>6.87044683550917</v>
+        <v>6.870435006199105</v>
       </c>
       <c r="J72" t="n">
         <v>121.2440312078746</v>
@@ -41329,13 +41329,13 @@
         <v>-17.74229082477954</v>
       </c>
       <c r="G73" t="n">
-        <v>4.782685507174245</v>
+        <v>4.782695642945956</v>
       </c>
       <c r="H73" t="n">
         <v>45.67474432100389</v>
       </c>
       <c r="I73" t="n">
-        <v>5.919994542787355</v>
+        <v>5.920006348914786</v>
       </c>
       <c r="J73" t="n">
         <v>112.7802797593012</v>
@@ -41361,7 +41361,7 @@
         <v>-24.46927078175064</v>
       </c>
       <c r="G74" t="n">
-        <v>3.417532164388515</v>
+        <v>3.417552586709838</v>
       </c>
       <c r="H74" t="n">
         <v>37.45292871774588</v>
@@ -41393,13 +41393,13 @@
         <v>-18.87479351610046</v>
       </c>
       <c r="G75" t="n">
-        <v>1.709496168504154</v>
+        <v>1.709496340413774</v>
       </c>
       <c r="H75" t="n">
         <v>30.02268127303005</v>
       </c>
       <c r="I75" t="n">
-        <v>-2.413077659927665</v>
+        <v>-2.413088070817371</v>
       </c>
       <c r="J75" t="n">
         <v>100.9032218686996</v>
@@ -41489,13 +41489,13 @@
         <v>-14.20658392523141</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.2173261574215601</v>
+        <v>-0.217336350478059</v>
       </c>
       <c r="H78" t="n">
         <v>37.16040451905292</v>
       </c>
       <c r="I78" t="n">
-        <v>-5.63649022866074</v>
+        <v>-5.63650099164782</v>
       </c>
       <c r="J78" t="n">
         <v>92.88792469130138</v>
@@ -41527,7 +41527,7 @@
         <v>33.92029467705142</v>
       </c>
       <c r="I79" t="n">
-        <v>-10.19617003836636</v>
+        <v>-10.19616067319565</v>
       </c>
       <c r="J79" t="n">
         <v>83.99160638349537</v>
@@ -41553,7 +41553,7 @@
         <v>-14.96527786669417</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.4200085592022895</v>
+        <v>-0.4200185863839745</v>
       </c>
       <c r="H80" t="n">
         <v>40.86671910305058</v>
@@ -41591,7 +41591,7 @@
         <v>44.05244047508194</v>
       </c>
       <c r="I81" t="n">
-        <v>-11.30203660674795</v>
+        <v>-11.30202615532158</v>
       </c>
       <c r="J81" t="n">
         <v>86.99152692711512</v>
@@ -41617,7 +41617,7 @@
         <v>-15.09280158634767</v>
       </c>
       <c r="G82" t="n">
-        <v>-2.800918359596094</v>
+        <v>-2.800927886138316</v>
       </c>
       <c r="H82" t="n">
         <v>40.05622697643856</v>
@@ -41649,13 +41649,13 @@
         <v>-19.74900728652863</v>
       </c>
       <c r="G83" t="n">
-        <v>-5.022559850758135</v>
+        <v>-5.022541018046145</v>
       </c>
       <c r="H83" t="n">
         <v>41.68852680226573</v>
       </c>
       <c r="I83" t="n">
-        <v>-18.32409720995372</v>
+        <v>-18.32410639220786</v>
       </c>
       <c r="J83" t="n">
         <v>76.21051989103617</v>
@@ -41687,7 +41687,7 @@
         <v>59.40775106485634</v>
       </c>
       <c r="I84" t="n">
-        <v>-12.47747784038312</v>
+        <v>-12.47749649193932</v>
       </c>
       <c r="J84" t="n">
         <v>99.06541697895044</v>
@@ -41713,13 +41713,13 @@
         <v>-16.67054649645153</v>
       </c>
       <c r="G85" t="n">
-        <v>-4.36130538423074</v>
+        <v>-4.361296162609751</v>
       </c>
       <c r="H85" t="n">
         <v>65.04654719786612</v>
       </c>
       <c r="I85" t="n">
-        <v>-15.66178711285019</v>
+        <v>-15.66177753902792</v>
       </c>
       <c r="J85" t="n">
         <v>97.04844951046681</v>
@@ -41777,7 +41777,7 @@
         <v>-18.06414822509883</v>
       </c>
       <c r="G87" t="n">
-        <v>-2.608840748224917</v>
+        <v>-2.608831164051528</v>
       </c>
       <c r="H87" t="n">
         <v>62.23634673800827</v>
@@ -41809,7 +41809,7 @@
         <v>-22.44094964591114</v>
       </c>
       <c r="G88" t="n">
-        <v>-5.511809369019527</v>
+        <v>-5.51181892058864</v>
       </c>
       <c r="H88" t="n">
         <v>55.75244209203252</v>
@@ -41841,7 +41841,7 @@
         <v>-21.64679673751331</v>
       </c>
       <c r="G89" t="n">
-        <v>-4.430067347439826</v>
+        <v>-4.430058284525817</v>
       </c>
       <c r="H89" t="n">
         <v>62.23793649992655</v>
@@ -41873,13 +41873,13 @@
         <v>-21.60274235468711</v>
       </c>
       <c r="G90" t="n">
-        <v>-1.754765960790283</v>
+        <v>-1.754756569930216</v>
       </c>
       <c r="H90" t="n">
         <v>44.01810748398501</v>
       </c>
       <c r="I90" t="n">
-        <v>-16.88544388826343</v>
+        <v>-16.88543472916736</v>
       </c>
       <c r="J90" t="n">
         <v>81.88842255714064</v>
@@ -41905,13 +41905,13 @@
         <v>-24.73446258717338</v>
       </c>
       <c r="G91" t="n">
-        <v>-2.788640615443083</v>
+        <v>-2.788650154475081</v>
       </c>
       <c r="H91" t="n">
         <v>35.52879303916819</v>
       </c>
       <c r="I91" t="n">
-        <v>-23.03242925559732</v>
+        <v>-23.03241385408457</v>
       </c>
       <c r="J91" t="n">
         <v>68.10019640513771</v>
@@ -42001,7 +42001,7 @@
         <v>-31.92243919478229</v>
       </c>
       <c r="G94" t="n">
-        <v>-4.264780411272239</v>
+        <v>-4.264771301566395</v>
       </c>
       <c r="H94" t="n">
         <v>18.74325570428619</v>
@@ -42065,13 +42065,13 @@
         <v>-43.65987090351605</v>
       </c>
       <c r="G96" t="n">
-        <v>-1.772228030575917</v>
+        <v>-1.77221865009497</v>
       </c>
       <c r="H96" t="n">
         <v>15.89211111741442</v>
       </c>
       <c r="I96" t="n">
-        <v>-23.57126754833715</v>
+        <v>-23.57127213775751</v>
       </c>
       <c r="J96" t="n">
         <v>28.54914740621408</v>
@@ -42129,13 +42129,13 @@
         <v>-52.13567772568902</v>
       </c>
       <c r="G98" t="n">
-        <v>-1.144826287332867</v>
+        <v>-1.144817070470294</v>
       </c>
       <c r="H98" t="n">
         <v>18.31965290286819</v>
       </c>
       <c r="I98" t="n">
-        <v>-26.40582942938569</v>
+        <v>-26.40582069621047</v>
       </c>
       <c r="J98" t="n">
         <v>32.4025967189887</v>
@@ -42161,13 +42161,13 @@
         <v>-57.77777609465646</v>
       </c>
       <c r="G99" t="n">
-        <v>-6.02081769635009</v>
+        <v>-6.020826234045174</v>
       </c>
       <c r="H99" t="n">
         <v>15.27719667733658</v>
       </c>
       <c r="I99" t="n">
-        <v>-33.24731795382694</v>
+        <v>-33.24732339281348</v>
       </c>
       <c r="J99" t="n">
         <v>28.97106147384567</v>
@@ -42193,13 +42193,13 @@
         <v>-56.44122399079755</v>
       </c>
       <c r="G100" t="n">
-        <v>-6.514107927947088</v>
+        <v>-6.514108515058659</v>
       </c>
       <c r="H100" t="n">
         <v>15.07653487454037</v>
       </c>
       <c r="I100" t="n">
-        <v>-33.8904169084052</v>
+        <v>-33.89041151541271</v>
       </c>
       <c r="J100" t="n">
         <v>27.6699069578042</v>
@@ -42225,7 +42225,7 @@
         <v>-56.13349608547158</v>
       </c>
       <c r="G101" t="n">
-        <v>-9.051274180324532</v>
+        <v>-9.051291101519077</v>
       </c>
       <c r="H101" t="n">
         <v>17.94541203322633</v>
@@ -42257,13 +42257,13 @@
         <v>-55.91733700865703</v>
       </c>
       <c r="G102" t="n">
-        <v>-9.027552345033785</v>
+        <v>-9.027544169019031</v>
       </c>
       <c r="H102" t="n">
         <v>18.40919658725724</v>
       </c>
       <c r="I102" t="n">
-        <v>-29.82360396246734</v>
+        <v>-29.82359782494049</v>
       </c>
       <c r="J102" t="n">
         <v>28.18636085107484</v>
@@ -42321,13 +42321,13 @@
         <v>-60.6574271929146</v>
       </c>
       <c r="G104" t="n">
-        <v>-9.45652187656183</v>
+        <v>-9.456504668185772</v>
       </c>
       <c r="H104" t="n">
         <v>9.913208228453851</v>
       </c>
       <c r="I104" t="n">
-        <v>-35.85256724208779</v>
+        <v>-35.85256845449841</v>
       </c>
       <c r="J104" t="n">
         <v>23.86554108948267</v>
@@ -42353,13 +42353,13 @@
         <v>-59.55940035959599</v>
       </c>
       <c r="G105" t="n">
-        <v>-9.342702479818943</v>
+        <v>-9.342694289377128</v>
       </c>
       <c r="H105" t="n">
         <v>14.53287197231834</v>
       </c>
       <c r="I105" t="n">
-        <v>-33.59567847641735</v>
+        <v>-33.59567417837825</v>
       </c>
       <c r="J105" t="n">
         <v>30.79527080801228</v>
@@ -42449,7 +42449,7 @@
         <v>-56.18415731425067</v>
       </c>
       <c r="G108" t="n">
-        <v>-6.221607598175138</v>
+        <v>-6.221599035747061</v>
       </c>
       <c r="H108" t="n">
         <v>14.44831874727788</v>
@@ -42481,13 +42481,13 @@
         <v>-56.1025635808961</v>
       </c>
       <c r="G109" t="n">
-        <v>-13.66812847760248</v>
+        <v>-13.66813584312502</v>
       </c>
       <c r="H109" t="n">
         <v>2.676028157570309</v>
       </c>
       <c r="I109" t="n">
-        <v>-34.05137407827211</v>
+        <v>-34.05137839494272</v>
       </c>
       <c r="J109" t="n">
         <v>26.24584557611403</v>
@@ -42551,7 +42551,7 @@
         <v>10.12767521636539</v>
       </c>
       <c r="I111" t="n">
-        <v>-30.90738562405075</v>
+        <v>-30.90739167300298</v>
       </c>
       <c r="J111" t="n">
         <v>33.95972882878166</v>
@@ -42615,7 +42615,7 @@
         <v>29.08312860522841</v>
       </c>
       <c r="I113" t="n">
-        <v>-31.15945783088099</v>
+        <v>-31.15946839130254</v>
       </c>
       <c r="J113" t="n">
         <v>45.27778215614377</v>
@@ -42647,7 +42647,7 @@
         <v>32.61072830164626</v>
       </c>
       <c r="I114" t="n">
-        <v>-32.44485913828271</v>
+        <v>-32.44485757880052</v>
       </c>
       <c r="J114" t="n">
         <v>49.6350385796072</v>
@@ -42673,7 +42673,7 @@
         <v>-56.60509984441939</v>
       </c>
       <c r="G115" t="n">
-        <v>-13.22026410105521</v>
+        <v>-13.22025659231684</v>
       </c>
       <c r="H115" t="n">
         <v>24.44754770776356</v>
@@ -42705,13 +42705,13 @@
         <v>-55.79329376930953</v>
       </c>
       <c r="G116" t="n">
-        <v>-15.35700805648983</v>
+        <v>-15.35700080551199</v>
       </c>
       <c r="H116" t="n">
         <v>23.26171935995283</v>
       </c>
       <c r="I116" t="n">
-        <v>-36.44571369224542</v>
+        <v>-36.4457180486654</v>
       </c>
       <c r="J116" t="n">
         <v>44.24131704827239</v>
@@ -42737,13 +42737,13 @@
         <v>-55.92658828357197</v>
       </c>
       <c r="G117" t="n">
-        <v>-15.85364606912631</v>
+        <v>-15.85363754969596</v>
       </c>
       <c r="H117" t="n">
         <v>24.94730195367547</v>
       </c>
       <c r="I117" t="n">
-        <v>-36.19966728478108</v>
+        <v>-36.19966294916446</v>
       </c>
       <c r="J117" t="n">
         <v>38.56393145516608</v>
@@ -42769,7 +42769,7 @@
         <v>-56.78818610596754</v>
       </c>
       <c r="G118" t="n">
-        <v>-16.38669786568314</v>
+        <v>-16.38669079411861</v>
       </c>
       <c r="H118" t="n">
         <v>17.44131168849032</v>
@@ -42801,13 +42801,13 @@
         <v>-56.31058995863971</v>
       </c>
       <c r="G119" t="n">
-        <v>-15.37457327751788</v>
+        <v>-15.37458178389647</v>
       </c>
       <c r="H119" t="n">
         <v>20.81582502027968</v>
       </c>
       <c r="I119" t="n">
-        <v>-36.0658704982447</v>
+        <v>-36.06587516449706</v>
       </c>
       <c r="J119" t="n">
         <v>41.26194709591032</v>
@@ -42839,7 +42839,7 @@
         <v>18.29646125327557</v>
       </c>
       <c r="I120" t="n">
-        <v>-38.54755360836089</v>
+        <v>-38.54754901090875</v>
       </c>
       <c r="J120" t="n">
         <v>41.19001864296059</v>
@@ -42865,13 +42865,13 @@
         <v>-57.14155223271617</v>
       </c>
       <c r="G121" t="n">
-        <v>-16.85995891525053</v>
+        <v>-16.85994364190014</v>
       </c>
       <c r="H121" t="n">
         <v>11.82631761961019</v>
       </c>
       <c r="I121" t="n">
-        <v>-37.32898531697771</v>
+        <v>-37.32897961116035</v>
       </c>
       <c r="J121" t="n">
         <v>43.47825961545257</v>
@@ -42929,13 +42929,13 @@
         <v>-58.76224388707519</v>
       </c>
       <c r="G123" t="n">
-        <v>-15.62785711500458</v>
+        <v>-15.62786425160246</v>
       </c>
       <c r="H123" t="n">
         <v>12.00888037813888</v>
       </c>
       <c r="I123" t="n">
-        <v>-42.35447517905221</v>
+        <v>-42.35447034363565</v>
       </c>
       <c r="J123" t="n">
         <v>43.89312849283209</v>
@@ -42961,13 +42961,13 @@
         <v>-61.61153711978648</v>
       </c>
       <c r="G124" t="n">
-        <v>-17.32209371336002</v>
+        <v>-17.32210209479792</v>
       </c>
       <c r="H124" t="n">
         <v>-0.8441437102060356</v>
       </c>
       <c r="I124" t="n">
-        <v>-42.70334090588286</v>
+        <v>-42.70334513966879</v>
       </c>
       <c r="J124" t="n">
         <v>36.54915842401909</v>
@@ -42993,7 +42993,7 @@
         <v>-62.04201834542411</v>
       </c>
       <c r="G125" t="n">
-        <v>-17.87451582243691</v>
+        <v>-17.87453111804034</v>
       </c>
       <c r="H125" t="n">
         <v>-0.9950223577321893</v>
@@ -43031,7 +43031,7 @@
         <v>-4.313306030797348</v>
       </c>
       <c r="I126" t="n">
-        <v>-41.76580426395932</v>
+        <v>-41.76579990753935</v>
       </c>
       <c r="J126" t="n">
         <v>36.54223559239848</v>
@@ -43057,13 +43057,13 @@
         <v>-64.48646305395978</v>
       </c>
       <c r="G127" t="n">
-        <v>-18.73304496909627</v>
+        <v>-18.73303819338198</v>
       </c>
       <c r="H127" t="n">
         <v>-7.626934073983682</v>
       </c>
       <c r="I127" t="n">
-        <v>-45.25499275935716</v>
+        <v>-45.25499703566405</v>
       </c>
       <c r="J127" t="n">
         <v>29.66861136912165</v>
@@ -43095,7 +43095,7 @@
         <v>-9.592997010479355</v>
       </c>
       <c r="I128" t="n">
-        <v>-49.59648679341039</v>
+        <v>-49.59648269142077</v>
       </c>
       <c r="J128" t="n">
         <v>28.59374093124656</v>
@@ -43121,7 +43121,7 @@
         <v>-64.86509384058901</v>
       </c>
       <c r="G129" t="n">
-        <v>-21.6147392504218</v>
+        <v>-21.6147457613744</v>
       </c>
       <c r="H129" t="n">
         <v>-9.914680971138623</v>
@@ -43153,7 +43153,7 @@
         <v>-63.12178339389629</v>
       </c>
       <c r="G130" t="n">
-        <v>-20.60108967440408</v>
+        <v>-20.60108135869104</v>
       </c>
       <c r="H130" t="n">
         <v>-0.430739938833391</v>
@@ -43185,7 +43185,7 @@
         <v>-60.87921861989671</v>
       </c>
       <c r="G131" t="n">
-        <v>-16.61963886450222</v>
+        <v>-16.61963745395354</v>
       </c>
       <c r="H131" t="n">
         <v>11.20226017119483</v>
@@ -43223,7 +43223,7 @@
         <v>8.352201320420626</v>
       </c>
       <c r="I132" t="n">
-        <v>-40.50186632108546</v>
+        <v>-40.50187066692568</v>
       </c>
       <c r="J132" t="n">
         <v>48.92561892278942</v>
@@ -43249,7 +43249,7 @@
         <v>-56.86676433086298</v>
       </c>
       <c r="G133" t="n">
-        <v>-16.72257899137246</v>
+        <v>-16.72258727099999</v>
       </c>
       <c r="H133" t="n">
         <v>2.898096851378784</v>
@@ -43313,13 +43313,13 @@
         <v>-55.97900230427739</v>
       </c>
       <c r="G135" t="n">
-        <v>-15.92343863232097</v>
+        <v>-15.92344686738257</v>
       </c>
       <c r="H135" t="n">
         <v>-2.809878783828057</v>
       </c>
       <c r="I135" t="n">
-        <v>-44.35211507824253</v>
+        <v>-44.35211986444345</v>
       </c>
       <c r="J135" t="n">
         <v>45.94360305036773</v>
@@ -43345,13 +43345,13 @@
         <v>-54.15469427793725</v>
       </c>
       <c r="G136" t="n">
-        <v>-16.69092990921731</v>
+        <v>-16.69092168949762</v>
       </c>
       <c r="H136" t="n">
         <v>0.04121654929012397</v>
       </c>
       <c r="I136" t="n">
-        <v>-42.32406993188314</v>
+        <v>-42.32407443970882</v>
       </c>
       <c r="J136" t="n">
         <v>49.730944089708</v>
@@ -43377,13 +43377,13 @@
         <v>-56.62921337306769</v>
       </c>
       <c r="G137" t="n">
-        <v>-15.94877718164233</v>
+        <v>-15.94878553516822</v>
       </c>
       <c r="H137" t="n">
         <v>-0.8227812344208774</v>
       </c>
       <c r="I137" t="n">
-        <v>-43.53504640515198</v>
+        <v>-43.53504193146073</v>
       </c>
       <c r="J137" t="n">
         <v>46.43016219484324</v>
@@ -43409,13 +43409,13 @@
         <v>-55.96958453493185</v>
       </c>
       <c r="G138" t="n">
-        <v>-15.24241637006719</v>
+        <v>-15.24242479379555</v>
       </c>
       <c r="H138" t="n">
         <v>-1.909228316656353</v>
       </c>
       <c r="I138" t="n">
-        <v>-42.02480076815466</v>
+        <v>-42.02479084880196</v>
       </c>
       <c r="J138" t="n">
         <v>46.43016219484324</v>
@@ -43441,7 +43441,7 @@
         <v>-49.86285836356027</v>
       </c>
       <c r="G139" t="n">
-        <v>-15.18492275842689</v>
+        <v>-15.18492986028326</v>
       </c>
       <c r="H139" t="n">
         <v>11.39967947776015</v>
@@ -43473,7 +43473,7 @@
         <v>-47.07156041622452</v>
       </c>
       <c r="G140" t="n">
-        <v>-11.08227849193191</v>
+        <v>-11.08226986572446</v>
       </c>
       <c r="H140" t="n">
         <v>26.95559471805855</v>
@@ -43505,13 +43505,13 @@
         <v>-43.95747457582054</v>
       </c>
       <c r="G141" t="n">
-        <v>-10.53410770115322</v>
+        <v>-10.53411633157888</v>
       </c>
       <c r="H141" t="n">
         <v>11.78529754959159</v>
       </c>
       <c r="I141" t="n">
-        <v>-32.26880534741482</v>
+        <v>-32.26879864064875</v>
       </c>
       <c r="J141" t="n">
         <v>79.66746349443316</v>
@@ -43537,13 +43537,13 @@
         <v>-46.5503629780039</v>
       </c>
       <c r="G142" t="n">
-        <v>-7.876442017505214</v>
+        <v>-7.876450728562324</v>
       </c>
       <c r="H142" t="n">
         <v>2.585262900904595</v>
       </c>
       <c r="I142" t="n">
-        <v>-31.06492450679491</v>
+        <v>-31.06491760499416</v>
       </c>
       <c r="J142" t="n">
         <v>72.89592047478308</v>
@@ -43575,7 +43575,7 @@
         <v>-7.09122645551531</v>
       </c>
       <c r="I143" t="n">
-        <v>-32.10435572998518</v>
+        <v>-32.10434891982889</v>
       </c>
       <c r="J143" t="n">
         <v>60.56033954750786</v>
@@ -43607,7 +43607,7 @@
         <v>5.829856359310237</v>
       </c>
       <c r="I144" t="n">
-        <v>-32.77704074443481</v>
+        <v>-32.77704585719886</v>
       </c>
       <c r="J144" t="n">
         <v>73.11404623446703</v>
@@ -43633,7 +43633,7 @@
         <v>-47.72093129712481</v>
       </c>
       <c r="G145" t="n">
-        <v>-11.16618712965093</v>
+        <v>-11.16617952809754</v>
       </c>
       <c r="H145" t="n">
         <v>2.334533491450208</v>
@@ -43671,7 +43671,7 @@
         <v>-4.631267327895838</v>
       </c>
       <c r="I146" t="n">
-        <v>-34.63595419177665</v>
+        <v>-34.63594768313144</v>
       </c>
       <c r="J146" t="n">
         <v>71.57684970564392</v>
@@ -43697,7 +43697,7 @@
         <v>-50.80962983163329</v>
       </c>
       <c r="G147" t="n">
-        <v>-13.61996145713659</v>
+        <v>-13.6199541228318</v>
       </c>
       <c r="H147" t="n">
         <v>-8.328828410010559</v>
@@ -43729,13 +43729,13 @@
         <v>-50.8521140595779</v>
       </c>
       <c r="G148" t="n">
-        <v>-12.91493817716609</v>
+        <v>-12.91493707036117</v>
       </c>
       <c r="H148" t="n">
         <v>-6.028498086992817</v>
       </c>
       <c r="I148" t="n">
-        <v>-34.28804916033518</v>
+        <v>-34.28806060348938</v>
       </c>
       <c r="J148" t="n">
         <v>53.29710430619193</v>
@@ -43761,13 +43761,13 @@
         <v>-48.09143066406249</v>
       </c>
       <c r="G149" t="n">
-        <v>-16.07073888832293</v>
+        <v>-16.07073061271678</v>
       </c>
       <c r="H149" t="n">
         <v>-1.760633823603719</v>
       </c>
       <c r="I149" t="n">
-        <v>-34.87420925337283</v>
+        <v>-34.87422043175192</v>
       </c>
       <c r="J149" t="n">
         <v>56.09403415140542</v>
@@ -43799,7 +43799,7 @@
         <v>-7.602880670023849</v>
       </c>
       <c r="I150" t="n">
-        <v>-37.45697692204924</v>
+        <v>-37.45698176262956</v>
       </c>
       <c r="J150" t="n">
         <v>46.37167601458793</v>
@@ -43825,13 +43825,13 @@
         <v>-54.39159419656274</v>
       </c>
       <c r="G151" t="n">
-        <v>-21.22332983451548</v>
+        <v>-21.22333815512868</v>
       </c>
       <c r="H151" t="n">
         <v>-10.10608394316426</v>
       </c>
       <c r="I151" t="n">
-        <v>-43.26666717142301</v>
+        <v>-43.26666186836514</v>
       </c>
       <c r="J151" t="n">
         <v>35.01730440420005</v>
@@ -43895,7 +43895,7 @@
         <v>-16.46675455896869</v>
       </c>
       <c r="I153" t="n">
-        <v>-41.94473500657481</v>
+        <v>-41.94473043279401</v>
       </c>
       <c r="J153" t="n">
         <v>22.64151237635372</v>
@@ -43921,7 +43921,7 @@
         <v>-54.55138411907664</v>
       </c>
       <c r="G154" t="n">
-        <v>-16.39440907818802</v>
+        <v>-16.3944161385867</v>
       </c>
       <c r="H154" t="n">
         <v>-15.20339189949682</v>
@@ -43991,7 +43991,7 @@
         <v>-11.96105995313918</v>
       </c>
       <c r="I156" t="n">
-        <v>-35.97284836459775</v>
+        <v>-35.97284968089498</v>
       </c>
       <c r="J156" t="n">
         <v>34.93548977759578</v>
@@ -44049,7 +44049,7 @@
         <v>-49.31460605578476</v>
       </c>
       <c r="G158" t="n">
-        <v>-12.14389741566937</v>
+        <v>-12.14390576552569</v>
       </c>
       <c r="H158" t="n">
         <v>19.17837993230622</v>
@@ -44081,7 +44081,7 @@
         <v>-48.69467684534752</v>
       </c>
       <c r="G159" t="n">
-        <v>-11.69394833020523</v>
+        <v>-11.6939399096355</v>
       </c>
       <c r="H159" t="n">
         <v>34.79139711401707</v>
@@ -44119,7 +44119,7 @@
         <v>33.15829160473547</v>
       </c>
       <c r="I160" t="n">
-        <v>-29.84938585107336</v>
+        <v>-29.84938784335838</v>
       </c>
       <c r="J160" t="n">
         <v>67.10172765520876</v>
@@ -44151,7 +44151,7 @@
         <v>38.5684914172453</v>
       </c>
       <c r="I161" t="n">
-        <v>-29.7419029828034</v>
+        <v>-29.74189607402291</v>
       </c>
       <c r="J161" t="n">
         <v>62.23034118107906</v>
@@ -44177,13 +44177,13 @@
         <v>-51.18435907630281</v>
       </c>
       <c r="G162" t="n">
-        <v>-10.8931684914654</v>
+        <v>-10.89316097368617</v>
       </c>
       <c r="H162" t="n">
         <v>31.94658342227763</v>
       </c>
       <c r="I162" t="n">
-        <v>-31.73167254623591</v>
+        <v>-31.73167748083034</v>
       </c>
       <c r="J162" t="n">
         <v>44.11149655354738</v>
@@ -44209,13 +44209,13 @@
         <v>-50.39954164408403</v>
       </c>
       <c r="G163" t="n">
-        <v>-6.576273829991408</v>
+        <v>-6.576257575571676</v>
       </c>
       <c r="H163" t="n">
         <v>35.25827976252069</v>
       </c>
       <c r="I163" t="n">
-        <v>-30.97237478082654</v>
+        <v>-30.97237292020486</v>
       </c>
       <c r="J163" t="n">
         <v>47.45098657865709</v>
@@ -44247,7 +44247,7 @@
         <v>31.4724774427817</v>
       </c>
       <c r="I164" t="n">
-        <v>-33.50502133447838</v>
+        <v>-33.50502602626197</v>
       </c>
       <c r="J164" t="n">
         <v>45.68383260132476</v>
@@ -44273,7 +44273,7 @@
         <v>-50.55082406989408</v>
       </c>
       <c r="G165" t="n">
-        <v>-3.395846479893661</v>
+        <v>-3.395854658131747</v>
       </c>
       <c r="H165" t="n">
         <v>31.92537293485394</v>
@@ -44305,13 +44305,13 @@
         <v>-53.59653548729015</v>
       </c>
       <c r="G166" t="n">
-        <v>-1.762277226693731</v>
+        <v>-1.762285595699331</v>
       </c>
       <c r="H166" t="n">
         <v>31.32498904941086</v>
       </c>
       <c r="I166" t="n">
-        <v>-34.25831760024707</v>
+        <v>-34.25830666893714</v>
       </c>
       <c r="J166" t="n">
         <v>45.76086589203896</v>
@@ -44337,7 +44337,7 @@
         <v>-53.46630744214328</v>
       </c>
       <c r="G167" t="n">
-        <v>-1.631337452160353</v>
+        <v>-1.631329128250458</v>
       </c>
       <c r="H167" t="n">
         <v>33.09109889422288</v>
@@ -44375,7 +44375,7 @@
         <v>23.80828374026902</v>
       </c>
       <c r="I168" t="n">
-        <v>-34.97454409134397</v>
+        <v>-34.9745393723056</v>
       </c>
       <c r="J168" t="n">
         <v>38.0866387959659</v>
@@ -44433,7 +44433,7 @@
         <v>-52.14848123130358</v>
       </c>
       <c r="G170" t="n">
-        <v>-3.764463701823417</v>
+        <v>-3.764455597413807</v>
       </c>
       <c r="H170" t="n">
         <v>31.30973250029547</v>
@@ -44465,7 +44465,7 @@
         <v>-51.04838688412199</v>
       </c>
       <c r="G171" t="n">
-        <v>-5.77381100302633</v>
+        <v>-5.77381942704066</v>
       </c>
       <c r="H171" t="n">
         <v>33.71331443951104</v>
@@ -44497,7 +44497,7 @@
         <v>-45.99760763325964</v>
       </c>
       <c r="G172" t="n">
-        <v>0.5143291941176686</v>
+        <v>0.5143205788882721</v>
       </c>
       <c r="H172" t="n">
         <v>44.92055080938697</v>
@@ -44529,7 +44529,7 @@
         <v>-43.44699349358814</v>
       </c>
       <c r="G173" t="n">
-        <v>0.06902412197677954</v>
+        <v>0.06901541889747786</v>
       </c>
       <c r="H173" t="n">
         <v>59.14138873392913</v>
@@ -44561,7 +44561,7 @@
         <v>-41.76249980926514</v>
       </c>
       <c r="G174" t="n">
-        <v>1.98072439885395</v>
+        <v>1.980733214022967</v>
       </c>
       <c r="H174" t="n">
         <v>59.09223654259699</v>
@@ -44625,7 +44625,7 @@
         <v>-38.62024938625434</v>
       </c>
       <c r="G176" t="n">
-        <v>4.821522947935719</v>
+        <v>4.821513659026477</v>
       </c>
       <c r="H176" t="n">
         <v>73.38710005667144</v>
@@ -44663,7 +44663,7 @@
         <v>71.52501088341694</v>
       </c>
       <c r="I177" t="n">
-        <v>-22.33078549632175</v>
+        <v>-22.33078034924558</v>
       </c>
       <c r="J177" t="n">
         <v>83.1262414010687</v>
@@ -44689,13 +44689,13 @@
         <v>-39.01896560774591</v>
       </c>
       <c r="G178" t="n">
-        <v>1.905980774876026</v>
+        <v>1.905962992066756</v>
       </c>
       <c r="H178" t="n">
         <v>66.75774073195311</v>
       </c>
       <c r="I178" t="n">
-        <v>-21.79922030085473</v>
+        <v>-21.79922553387539</v>
       </c>
       <c r="J178" t="n">
         <v>83.31967312108763</v>
@@ -44721,7 +44721,7 @@
         <v>-41.81931635301061</v>
       </c>
       <c r="G179" t="n">
-        <v>0.9841546105370691</v>
+        <v>0.9841546961556702</v>
       </c>
       <c r="H179" t="n">
         <v>61.06736588618858</v>
@@ -44753,13 +44753,13 @@
         <v>-39.6770169275888</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.147672528644105</v>
+        <v>-0.1476812388126914</v>
       </c>
       <c r="H180" t="n">
         <v>65.15150572053405</v>
       </c>
       <c r="I180" t="n">
-        <v>-25.31920577234636</v>
+        <v>-25.31921329761254</v>
       </c>
       <c r="J180" t="n">
         <v>72.82946306655833</v>
@@ -44817,7 +44817,7 @@
         <v>-38.78824946197358</v>
       </c>
       <c r="G182" t="n">
-        <v>0.2765053808964302</v>
+        <v>0.2764967520753059</v>
       </c>
       <c r="H182" t="n">
         <v>72.57494253958269</v>
@@ -44881,13 +44881,13 @@
         <v>-35.9392113960985</v>
       </c>
       <c r="G184" t="n">
-        <v>-2.940793371060713</v>
+        <v>-2.94078491301919</v>
       </c>
       <c r="H184" t="n">
         <v>84.22466480357787</v>
       </c>
       <c r="I184" t="n">
-        <v>-25.14133469574373</v>
+        <v>-25.14133965790279</v>
       </c>
       <c r="J184" t="n">
         <v>90.30188794405956</v>
@@ -44983,7 +44983,7 @@
         <v>109.9117682961857</v>
       </c>
       <c r="I187" t="n">
-        <v>-23.41613005209735</v>
+        <v>-23.41613770201895</v>
       </c>
       <c r="J187" t="n">
         <v>144.9407236737255</v>
@@ -45009,13 +45009,13 @@
         <v>-30.48580422386386</v>
       </c>
       <c r="G188" t="n">
-        <v>-3.154072432221577</v>
+        <v>-3.154080916110713</v>
       </c>
       <c r="H188" t="n">
         <v>102.5162819144948</v>
       </c>
       <c r="I188" t="n">
-        <v>-23.99993985526311</v>
+        <v>-23.99993218579317</v>
       </c>
       <c r="J188" t="n">
         <v>136.0320544643959</v>
@@ -45041,13 +45041,13 @@
         <v>-28.89460472383064</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.8636713289981279</v>
+        <v>-0.86368840437544</v>
       </c>
       <c r="H189" t="n">
         <v>123.2258100313875</v>
       </c>
       <c r="I189" t="n">
-        <v>-21.52762841287986</v>
+        <v>-21.52762332811739</v>
       </c>
       <c r="J189" t="n">
         <v>141.7857081765763</v>
@@ -45105,13 +45105,13 @@
         <v>-32.24030243339486</v>
       </c>
       <c r="G191" t="n">
-        <v>1.258337643152507</v>
+        <v>1.258329006240344</v>
       </c>
       <c r="H191" t="n">
         <v>123.5046433130916</v>
       </c>
       <c r="I191" t="n">
-        <v>-17.95774706748667</v>
+        <v>-17.95775563916884</v>
       </c>
       <c r="J191" t="n">
         <v>151.0794350518636</v>
@@ -45175,7 +45175,7 @@
         <v>159.4421378782054</v>
       </c>
       <c r="I193" t="n">
-        <v>-7.811469801544069</v>
+        <v>-7.811480422264172</v>
       </c>
       <c r="J193" t="n">
         <v>190.7755014847736</v>
@@ -45201,7 +45201,7 @@
         <v>-25.51905198204355</v>
       </c>
       <c r="G194" t="n">
-        <v>2.327466312907478</v>
+        <v>2.327475210869889</v>
       </c>
       <c r="H194" t="n">
         <v>167.3891432924977</v>
@@ -45233,13 +45233,13 @@
         <v>-30.90795338358637</v>
       </c>
       <c r="G195" t="n">
-        <v>1.040298414081908</v>
+        <v>1.040289784409199</v>
       </c>
       <c r="H195" t="n">
         <v>150.8404868487914</v>
       </c>
       <c r="I195" t="n">
-        <v>-14.28142889256946</v>
+        <v>-14.28143416458211</v>
       </c>
       <c r="J195" t="n">
         <v>183.9918671584078</v>
@@ -45271,7 +45271,7 @@
         <v>129.1716214536388</v>
       </c>
       <c r="I196" t="n">
-        <v>-19.29395730250751</v>
+        <v>-19.293970617628</v>
       </c>
       <c r="J196" t="n">
         <v>168.2000122070312</v>
@@ -45297,7 +45297,7 @@
         <v>-31.52814186982629</v>
       </c>
       <c r="G197" t="n">
-        <v>-1.951884126406522</v>
+        <v>-1.951892522654342</v>
       </c>
       <c r="H197" t="n">
         <v>105.2926634038812</v>
@@ -45329,13 +45329,13 @@
         <v>-33.52514665157967</v>
       </c>
       <c r="G198" t="n">
-        <v>-1.415380617513928</v>
+        <v>-1.415397459717427</v>
       </c>
       <c r="H198" t="n">
         <v>94.45324890083117</v>
       </c>
       <c r="I198" t="n">
-        <v>-28.42348749687464</v>
+        <v>-28.42349396691873</v>
       </c>
       <c r="J198" t="n">
         <v>121.8619260496735</v>
@@ -45361,7 +45361,7 @@
         <v>-36.51537018870842</v>
       </c>
       <c r="G199" t="n">
-        <v>-1.938813407055073</v>
+        <v>-1.938821685949521</v>
       </c>
       <c r="H199" t="n">
         <v>103.1003645832206</v>
@@ -45393,7 +45393,7 @@
         <v>-37.59362584999582</v>
       </c>
       <c r="G200" t="n">
-        <v>-1.848511108739048</v>
+        <v>-1.848519540227556</v>
       </c>
       <c r="H200" t="n">
         <v>88.43219261331876</v>
@@ -45489,13 +45489,13 @@
         <v>-36.18741564478685</v>
       </c>
       <c r="G203" t="n">
-        <v>-0.2005949243657046</v>
+        <v>-0.2006033940044616</v>
       </c>
       <c r="H203" t="n">
         <v>83.68124127503025</v>
       </c>
       <c r="I203" t="n">
-        <v>-28.09564597547907</v>
+        <v>-28.09563932936137</v>
       </c>
       <c r="J203" t="n">
         <v>106.2277067414659</v>
@@ -45521,7 +45521,7 @@
         <v>-26.48352671295293</v>
       </c>
       <c r="G204" t="n">
-        <v>-0.09634747259529286</v>
+        <v>-0.09635584766152228</v>
       </c>
       <c r="H204" t="n">
         <v>89.75380721992235</v>
@@ -45553,13 +45553,13 @@
         <v>-28.65188365140916</v>
       </c>
       <c r="G205" t="n">
-        <v>3.175299540611221</v>
+        <v>3.175291045053807</v>
       </c>
       <c r="H205" t="n">
         <v>94.32029234930152</v>
       </c>
       <c r="I205" t="n">
-        <v>-27.0860000922971</v>
+        <v>-27.08600683553397</v>
       </c>
       <c r="J205" t="n">
         <v>122.9661754366069</v>
@@ -45585,7 +45585,7 @@
         <v>-28.80289813678555</v>
       </c>
       <c r="G206" t="n">
-        <v>5.485240348763276</v>
+        <v>5.485231778209143</v>
       </c>
       <c r="H206" t="n">
         <v>93.58391397352406</v>
@@ -45681,7 +45681,7 @@
         <v>-28.01413821889418</v>
       </c>
       <c r="G209" t="n">
-        <v>-0.4309030730417995</v>
+        <v>-0.4308950012773538</v>
       </c>
       <c r="H209" t="n">
         <v>100.6930017200002</v>
@@ -45713,7 +45713,7 @@
         <v>-27.03415236602241</v>
       </c>
       <c r="G210" t="n">
-        <v>-2.71167406087387</v>
+        <v>-2.711681952938827</v>
       </c>
       <c r="H210" t="n">
         <v>88.54100235891897</v>
@@ -45783,7 +45783,7 @@
         <v>98.29378184219588</v>
       </c>
       <c r="I212" t="n">
-        <v>-31.41071594212068</v>
+        <v>-31.41072207146195</v>
       </c>
       <c r="J212" t="n">
         <v>127.3423849684713</v>
@@ -45809,13 +45809,13 @@
         <v>-36.81710406455739</v>
       </c>
       <c r="G213" t="n">
-        <v>-0.6188081582501281</v>
+        <v>-0.6188002002239346</v>
       </c>
       <c r="H213" t="n">
         <v>101.0606230012067</v>
       </c>
       <c r="I213" t="n">
-        <v>-31.06074006982888</v>
+        <v>-31.06073388270728</v>
       </c>
       <c r="J213" t="n">
         <v>129.4573808043165</v>
@@ -45873,7 +45873,7 @@
         <v>-35.00641823830535</v>
       </c>
       <c r="G215" t="n">
-        <v>-4.17189681239063</v>
+        <v>-4.171881583451709</v>
       </c>
       <c r="H215" t="n">
         <v>86.87857539273911</v>
@@ -45911,7 +45911,7 @@
         <v>88.96002855288734</v>
       </c>
       <c r="I216" t="n">
-        <v>-32.92037140574799</v>
+        <v>-32.92036549394376</v>
       </c>
       <c r="J216" t="n">
         <v>128.768082361913</v>
@@ -45937,7 +45937,7 @@
         <v>-33.86392905643432</v>
       </c>
       <c r="G217" t="n">
-        <v>-6.385019555942673</v>
+        <v>-6.385026828532547</v>
       </c>
       <c r="H217" t="n">
         <v>98.08728775531479</v>
@@ -46033,7 +46033,7 @@
         <v>-26.70043400693196</v>
       </c>
       <c r="G220" t="n">
-        <v>-7.221912904719341</v>
+        <v>-7.221913463495833</v>
       </c>
       <c r="H220" t="n">
         <v>107.9485799639777</v>
@@ -46065,7 +46065,7 @@
         <v>-27.85436837434032</v>
       </c>
       <c r="G221" t="n">
-        <v>-7.276085447728553</v>
+        <v>-7.27609318254262</v>
       </c>
       <c r="H221" t="n">
         <v>100.7819275777789</v>
@@ -46161,13 +46161,13 @@
         <v>-23.84693377024153</v>
       </c>
       <c r="G224" t="n">
-        <v>-8.083785907644659</v>
+        <v>-8.083786549827233</v>
       </c>
       <c r="H224" t="n">
         <v>108.4021066095138</v>
       </c>
       <c r="I224" t="n">
-        <v>-23.58793030177627</v>
+        <v>-23.58793790131195</v>
       </c>
       <c r="J224" t="n">
         <v>132.0058857738733</v>
@@ -46193,7 +46193,7 @@
         <v>-23.3081717190626</v>
       </c>
       <c r="G225" t="n">
-        <v>-6.198115986388785</v>
+        <v>-6.198124218843004</v>
       </c>
       <c r="H225" t="n">
         <v>102.435878276131</v>
@@ -46225,13 +46225,13 @@
         <v>-32.43559750352636</v>
       </c>
       <c r="G226" t="n">
-        <v>-6.148041621968114</v>
+        <v>-6.148033829310229</v>
       </c>
       <c r="H226" t="n">
         <v>95.15328519545527</v>
       </c>
       <c r="I226" t="n">
-        <v>-27.24830098065127</v>
+        <v>-27.24829383266478</v>
       </c>
       <c r="J226" t="n">
         <v>110.7646535029406</v>
@@ -46257,7 +46257,7 @@
         <v>-32.55395806851909</v>
       </c>
       <c r="G227" t="n">
-        <v>-6.91252567983417</v>
+        <v>-6.912509731121618</v>
       </c>
       <c r="H227" t="n">
         <v>77.01610443999401</v>
@@ -46289,7 +46289,7 @@
         <v>-33.03285408680733</v>
       </c>
       <c r="G228" t="n">
-        <v>-4.723294512346953</v>
+        <v>-4.723286234245117</v>
       </c>
       <c r="H228" t="n">
         <v>77.41683291570176</v>
@@ -46321,7 +46321,7 @@
         <v>-38.67234368945173</v>
       </c>
       <c r="G229" t="n">
-        <v>-6.238418605092876</v>
+        <v>-6.23841041819182</v>
       </c>
       <c r="H229" t="n">
         <v>72.01618573078785</v>
@@ -46385,7 +46385,7 @@
         <v>-36.82532653673968</v>
       </c>
       <c r="G231" t="n">
-        <v>-7.581525606214157</v>
+        <v>-7.581518060630521</v>
       </c>
       <c r="H231" t="n">
         <v>54.87430225307104</v>
@@ -46449,13 +46449,13 @@
         <v>-37.74290081852664</v>
       </c>
       <c r="G233" t="n">
-        <v>-7.845092375919105</v>
+        <v>-7.84509988930675</v>
       </c>
       <c r="H233" t="n">
         <v>31.20220243440443</v>
       </c>
       <c r="I233" t="n">
-        <v>-32.79411610687446</v>
+        <v>-32.79412256434421</v>
       </c>
       <c r="J233" t="n">
         <v>37.38601418418006</v>
@@ -46481,13 +46481,13 @@
         <v>-38.63636103394656</v>
       </c>
       <c r="G234" t="n">
-        <v>-6.789576929754382</v>
+        <v>-6.78956868988656</v>
       </c>
       <c r="H234" t="n">
         <v>36.77451609649452</v>
       </c>
       <c r="I234" t="n">
-        <v>-32.68282383642989</v>
+        <v>-32.68281725784399</v>
       </c>
       <c r="J234" t="n">
         <v>37.40589990296488</v>
@@ -46513,7 +46513,7 @@
         <v>-35.84453808293154</v>
       </c>
       <c r="G235" t="n">
-        <v>-3.676383408951556</v>
+        <v>-3.676391944864155</v>
       </c>
       <c r="H235" t="n">
         <v>44.01268886295892</v>
@@ -46583,7 +46583,7 @@
         <v>28.45130029759806</v>
       </c>
       <c r="I237" t="n">
-        <v>-30.34968755706141</v>
+        <v>-30.34968049155801</v>
       </c>
       <c r="J237" t="n">
         <v>37.53923055665842</v>
@@ -46641,13 +46641,13 @@
         <v>-43.07445745551136</v>
       </c>
       <c r="G239" t="n">
-        <v>-5.901626815877281</v>
+        <v>-5.901618930685871</v>
       </c>
       <c r="H239" t="n">
         <v>11.90330802341504</v>
       </c>
       <c r="I239" t="n">
-        <v>-29.36257314192705</v>
+        <v>-29.36256590952326</v>
       </c>
       <c r="J239" t="n">
         <v>30.84777634543028</v>
@@ -46673,7 +46673,7 @@
         <v>-41.94381402432754</v>
       </c>
       <c r="G240" t="n">
-        <v>-5.248228306063862</v>
+        <v>-5.248220291782069</v>
       </c>
       <c r="H240" t="n">
         <v>14.92523692770091</v>
@@ -46743,7 +46743,7 @@
         <v>24.7957124658932</v>
       </c>
       <c r="I242" t="n">
-        <v>-20.2304989019239</v>
+        <v>-20.23049029750423</v>
       </c>
       <c r="J242" t="n">
         <v>52.73949118221508</v>
@@ -46769,7 +46769,7 @@
         <v>-39.34322726834358</v>
       </c>
       <c r="G243" t="n">
-        <v>-3.703263225960984</v>
+        <v>-3.703271274079567</v>
       </c>
       <c r="H243" t="n">
         <v>32.40354383046355</v>
@@ -46807,7 +46807,7 @@
         <v>34.13228966130708</v>
       </c>
       <c r="I244" t="n">
-        <v>-23.24332750705954</v>
+        <v>-23.2433353276135</v>
       </c>
       <c r="J244" t="n">
         <v>52.75998400130671</v>
@@ -46871,7 +46871,7 @@
         <v>13.38954626727096</v>
       </c>
       <c r="I246" t="n">
-        <v>-26.33158144856611</v>
+        <v>-26.33157398867555</v>
       </c>
       <c r="J246" t="n">
         <v>28.55561668266151</v>
@@ -46961,13 +46961,13 @@
         <v>-44.79623457080469</v>
       </c>
       <c r="G249" t="n">
-        <v>-9.915340706749021</v>
+        <v>-9.915348039572402</v>
       </c>
       <c r="H249" t="n">
         <v>28.24667177580864</v>
       </c>
       <c r="I249" t="n">
-        <v>-27.19372983830064</v>
+        <v>-27.19372245264892</v>
       </c>
       <c r="J249" t="n">
         <v>34.10686463800094</v>
@@ -47025,7 +47025,7 @@
         <v>-44.10021926081409</v>
       </c>
       <c r="G251" t="n">
-        <v>-8.432380914658189</v>
+        <v>-8.432388439330673</v>
       </c>
       <c r="H251" t="n">
         <v>30.84309419368414</v>
@@ -47063,7 +47063,7 @@
         <v>38.13899279483215</v>
       </c>
       <c r="I252" t="n">
-        <v>-22.31720071184628</v>
+        <v>-22.31719283864492</v>
       </c>
       <c r="J252" t="n">
         <v>56.19888935780564</v>
@@ -47121,7 +47121,7 @@
         <v>-42.68745318611167</v>
       </c>
       <c r="G254" t="n">
-        <v>-8.95355739490059</v>
+        <v>-8.953564788171864</v>
       </c>
       <c r="H254" t="n">
         <v>38.11965215773809</v>
@@ -47281,13 +47281,13 @@
         <v>-39.33288226479107</v>
       </c>
       <c r="G259" t="n">
-        <v>-4.231140867430727</v>
+        <v>-4.231148930266126</v>
       </c>
       <c r="H259" t="n">
         <v>17.21369395430563</v>
       </c>
       <c r="I259" t="n">
-        <v>-20.11943557814434</v>
+        <v>-20.11944409895419</v>
       </c>
       <c r="J259" t="n">
         <v>54.07133907621559</v>
@@ -47313,7 +47313,7 @@
         <v>-40.19249724712132</v>
       </c>
       <c r="G260" t="n">
-        <v>-3.87515025945846</v>
+        <v>-3.875158357386355</v>
       </c>
       <c r="H260" t="n">
         <v>14.30151569558824</v>
@@ -47345,7 +47345,7 @@
         <v>-38.08339672481785</v>
       </c>
       <c r="G261" t="n">
-        <v>-2.796228547260515</v>
+        <v>-2.796236792638485</v>
       </c>
       <c r="H261" t="n">
         <v>23.4240208407088</v>
@@ -47441,7 +47441,7 @@
         <v>-39.47368508745812</v>
       </c>
       <c r="G264" t="n">
-        <v>-3.964310585570097</v>
+        <v>-3.964318621962881</v>
       </c>
       <c r="H264" t="n">
         <v>19.41679997949015</v>
@@ -47505,7 +47505,7 @@
         <v>-39.77876359755991</v>
       </c>
       <c r="G266" t="n">
-        <v>-4.653331466701482</v>
+        <v>-4.653323444895163</v>
       </c>
       <c r="H266" t="n">
         <v>-6.341747425683231</v>
@@ -47543,7 +47543,7 @@
         <v>-9.789748048156266</v>
       </c>
       <c r="I267" t="n">
-        <v>-20.82640358515051</v>
+        <v>-20.82639503526708</v>
       </c>
       <c r="J267" t="n">
         <v>34.23865433442628</v>
@@ -47671,7 +47671,7 @@
         <v>-27.76584214756481</v>
       </c>
       <c r="I271" t="n">
-        <v>-32.16928633245178</v>
+        <v>-32.16929289143484</v>
       </c>
       <c r="J271" t="n">
         <v>5.493463531992426</v>
@@ -47735,7 +47735,7 @@
         <v>-22.71868945740797</v>
       </c>
       <c r="I273" t="n">
-        <v>-29.55401212266132</v>
+        <v>-29.55400530838046</v>
       </c>
       <c r="J273" t="n">
         <v>0.2804769630959436</v>
@@ -47799,7 +47799,7 @@
         <v>-29.18674514954349</v>
       </c>
       <c r="I275" t="n">
-        <v>-27.13681355281311</v>
+        <v>-27.13680635595359</v>
       </c>
       <c r="J275" t="n">
         <v>-12.78136378898818</v>
@@ -47889,7 +47889,7 @@
         <v>-29.18918712719066</v>
       </c>
       <c r="G278" t="n">
-        <v>1.203251246739723</v>
+        <v>1.203260337258172</v>
       </c>
       <c r="H278" t="n">
         <v>-16.10060838234497</v>
@@ -47921,13 +47921,13 @@
         <v>-31.85478688860097</v>
       </c>
       <c r="G279" t="n">
-        <v>-1.206450108162938</v>
+        <v>-1.206441403179814</v>
       </c>
       <c r="H279" t="n">
         <v>-20.91819495708994</v>
       </c>
       <c r="I279" t="n">
-        <v>-21.13048049863758</v>
+        <v>-21.13047219079976</v>
       </c>
       <c r="J279" t="n">
         <v>0.5219697278298963</v>
@@ -48113,7 +48113,7 @@
         <v>-43.19450633885003</v>
       </c>
       <c r="G285" t="n">
-        <v>8.638879348934726</v>
+        <v>8.638869470524856</v>
       </c>
       <c r="H285" t="n">
         <v>-22.43266500066909</v>
@@ -48151,7 +48151,7 @@
         <v>-17.3628377931779</v>
       </c>
       <c r="I286" t="n">
-        <v>-23.84493473005442</v>
+        <v>-23.84494252383033</v>
       </c>
       <c r="J286" t="n">
         <v>8.001916670527965</v>
@@ -48209,7 +48209,7 @@
         <v>-40.31249999999999</v>
       </c>
       <c r="G288" t="n">
-        <v>8.824669864978496</v>
+        <v>8.824660078984214</v>
       </c>
       <c r="H288" t="n">
         <v>-15.80145910348596</v>
@@ -48241,13 +48241,13 @@
         <v>-36.1724497836834</v>
       </c>
       <c r="G289" t="n">
-        <v>11.12804077466287</v>
+        <v>11.12805096008431</v>
       </c>
       <c r="H289" t="n">
         <v>-15.80435876850455</v>
       </c>
       <c r="I289" t="n">
-        <v>-19.52014967564222</v>
+        <v>-19.52015837880386</v>
       </c>
       <c r="J289" t="n">
         <v>13.66120207730763</v>
@@ -48273,13 +48273,13 @@
         <v>-38.08921600038258</v>
       </c>
       <c r="G290" t="n">
-        <v>12.82624279146409</v>
+        <v>12.82625316981061</v>
       </c>
       <c r="H290" t="n">
         <v>-18.49578771778532</v>
       </c>
       <c r="I290" t="n">
-        <v>-19.80676144690814</v>
+        <v>-19.80675285177297</v>
       </c>
       <c r="J290" t="n">
         <v>14.74597518697689</v>
@@ -48503,7 +48503,7 @@
         <v>-41.72135295266101</v>
       </c>
       <c r="I297" t="n">
-        <v>-22.88069753552291</v>
+        <v>-22.88070596826082</v>
       </c>
       <c r="J297" t="n">
         <v>-4.48524369027955</v>
@@ -48593,7 +48593,7 @@
         <v>-45.71528273452657</v>
       </c>
       <c r="G300" t="n">
-        <v>14.45539545234036</v>
+        <v>14.45538481947792</v>
       </c>
       <c r="H300" t="n">
         <v>-39.12642164276215</v>
@@ -48625,13 +48625,13 @@
         <v>-44.79178880131202</v>
       </c>
       <c r="G301" t="n">
-        <v>16.79748773752852</v>
+        <v>16.79747672337286</v>
       </c>
       <c r="H301" t="n">
         <v>-35.27146510631234</v>
       </c>
       <c r="I301" t="n">
-        <v>-23.42536032537918</v>
+        <v>-23.42535204198196</v>
       </c>
       <c r="J301" t="n">
         <v>-5.574591275281082</v>
@@ -48657,7 +48657,7 @@
         <v>-43.0791637679723</v>
       </c>
       <c r="G302" t="n">
-        <v>18.74305491482327</v>
+        <v>18.74306630347453</v>
       </c>
       <c r="H302" t="n">
         <v>-31.04994046679992</v>
@@ -48695,7 +48695,7 @@
         <v>-31.05525941638822</v>
       </c>
       <c r="I303" t="n">
-        <v>-20.08279589388603</v>
+        <v>-20.082786803478</v>
       </c>
       <c r="J303" t="n">
         <v>1.417724995673453</v>
@@ -48881,7 +48881,7 @@
         <v>-46.45314619747551</v>
       </c>
       <c r="G309" t="n">
-        <v>28.87736012984552</v>
+        <v>28.87734715522496</v>
       </c>
       <c r="H309" t="n">
         <v>-36.46017585048106</v>
@@ -48913,7 +48913,7 @@
         <v>-43.11211700553351</v>
       </c>
       <c r="G310" t="n">
-        <v>24.04330394004244</v>
+        <v>24.04331600956311</v>
       </c>
       <c r="H310" t="n">
         <v>-35.62972636042486</v>
@@ -48977,13 +48977,13 @@
         <v>-42.96904798556517</v>
       </c>
       <c r="G312" t="n">
-        <v>21.35177929989596</v>
+        <v>21.35176776838568</v>
       </c>
       <c r="H312" t="n">
         <v>-39.16467071785878</v>
       </c>
       <c r="I312" t="n">
-        <v>-23.67829654351601</v>
+        <v>-23.67828830810955</v>
       </c>
       <c r="J312" t="n">
         <v>7.188093354284919</v>
@@ -49105,13 +49105,13 @@
         <v>-45.28779464855661</v>
       </c>
       <c r="G316" t="n">
-        <v>18.1494071185649</v>
+        <v>18.14939600670908</v>
       </c>
       <c r="H316" t="n">
         <v>-43.54679306508746</v>
       </c>
       <c r="I316" t="n">
-        <v>-30.43282109639951</v>
+        <v>-30.43281399248713</v>
       </c>
       <c r="J316" t="n">
         <v>-3.061483559066525</v>
@@ -49137,13 +49137,13 @@
         <v>-47.19959819731769</v>
       </c>
       <c r="G317" t="n">
-        <v>17.06812777258078</v>
+        <v>17.06813866501322</v>
       </c>
       <c r="H317" t="n">
         <v>-47.77185344404541</v>
       </c>
       <c r="I317" t="n">
-        <v>-31.74836812343457</v>
+        <v>-31.74837510836619</v>
       </c>
       <c r="J317" t="n">
         <v>-9.555436694152498</v>
@@ -49175,7 +49175,7 @@
         <v>-52.72973501715575</v>
       </c>
       <c r="I318" t="n">
-        <v>-32.59171905318771</v>
+        <v>-32.59171223647252</v>
       </c>
       <c r="J318" t="n">
         <v>-13.31224434263872</v>
@@ -49207,7 +49207,7 @@
         <v>-55.27717768906935</v>
       </c>
       <c r="I319" t="n">
-        <v>-31.59039820142303</v>
+        <v>-31.59040521272418</v>
       </c>
       <c r="J319" t="n">
         <v>-21.23319419798155</v>
@@ -49233,7 +49233,7 @@
         <v>-45.88515934593683</v>
       </c>
       <c r="G320" t="n">
-        <v>18.27002168373071</v>
+        <v>18.27003278657746</v>
       </c>
       <c r="H320" t="n">
         <v>-57.36521243655967</v>
@@ -49271,7 +49271,7 @@
         <v>-54.49974954822018</v>
       </c>
       <c r="I321" t="n">
-        <v>-30.81718021449415</v>
+        <v>-30.81718734034944</v>
       </c>
       <c r="J321" t="n">
         <v>-22.21221163758537</v>
@@ -49393,7 +49393,7 @@
         <v>-44.55750636787307</v>
       </c>
       <c r="G325" t="n">
-        <v>21.81861921980548</v>
+        <v>21.81860743612587</v>
       </c>
       <c r="H325" t="n">
         <v>-44.02443166579163</v>
@@ -49425,7 +49425,7 @@
         <v>-43.7062933475497</v>
       </c>
       <c r="G326" t="n">
-        <v>23.89425058162082</v>
+        <v>23.89423855416915</v>
       </c>
       <c r="H326" t="n">
         <v>-40.67477660339317</v>
@@ -49457,13 +49457,13 @@
         <v>-42.01795096708333</v>
       </c>
       <c r="G327" t="n">
-        <v>27.0129194209342</v>
+        <v>27.01293197887475</v>
       </c>
       <c r="H327" t="n">
         <v>-39.58842358779834</v>
       </c>
       <c r="I327" t="n">
-        <v>-28.9524729336602</v>
+        <v>-28.95246535407854</v>
       </c>
       <c r="J327" t="n">
         <v>-24.47013600772119</v>
@@ -49553,13 +49553,13 @@
         <v>-40.89319237117981</v>
       </c>
       <c r="G330" t="n">
-        <v>29.87862538191015</v>
+        <v>29.87863864934677</v>
       </c>
       <c r="H330" t="n">
         <v>-40.33758035437396</v>
       </c>
       <c r="I330" t="n">
-        <v>-23.96619685473781</v>
+        <v>-23.96618818241377</v>
       </c>
       <c r="J330" t="n">
         <v>-18.34636666921264</v>
@@ -49617,7 +49617,7 @@
         <v>-41.81298585856907</v>
       </c>
       <c r="G332" t="n">
-        <v>26.43219895670177</v>
+        <v>26.43221168776087</v>
       </c>
       <c r="H332" t="n">
         <v>-45.57062522979041</v>
@@ -49655,7 +49655,7 @@
         <v>-45.54360529211075</v>
       </c>
       <c r="I333" t="n">
-        <v>-22.58020063193108</v>
+        <v>-22.58020975443182</v>
       </c>
       <c r="J333" t="n">
         <v>-21.02878397775322</v>
@@ -49713,13 +49713,13 @@
         <v>-37.75945257518652</v>
       </c>
       <c r="G335" t="n">
-        <v>32.04424631615452</v>
+        <v>32.04423288765659</v>
       </c>
       <c r="H335" t="n">
         <v>-44.60865172604881</v>
       </c>
       <c r="I335" t="n">
-        <v>-25.07036277681787</v>
+        <v>-25.07035435299852</v>
       </c>
       <c r="J335" t="n">
         <v>-14.14575480237133</v>
@@ -49751,7 +49751,7 @@
         <v>-48.60430364584478</v>
       </c>
       <c r="I336" t="n">
-        <v>-24.60030981295194</v>
+        <v>-24.60030124432042</v>
       </c>
       <c r="J336" t="n">
         <v>-15.84507099008591</v>
@@ -49783,7 +49783,7 @@
         <v>-51.0275685005831</v>
       </c>
       <c r="I337" t="n">
-        <v>-25.72518642899533</v>
+        <v>-25.72519486044957</v>
       </c>
       <c r="J337" t="n">
         <v>-21.41738903286038</v>
@@ -49841,7 +49841,7 @@
         <v>-41.2774749891061</v>
       </c>
       <c r="G339" t="n">
-        <v>18.00930260936568</v>
+        <v>18.00929099618114</v>
       </c>
       <c r="H339" t="n">
         <v>-51.0275685005831</v>
@@ -49873,7 +49873,7 @@
         <v>-39.3328445504433</v>
       </c>
       <c r="G340" t="n">
-        <v>21.60855183551538</v>
+        <v>21.60856412861356</v>
       </c>
       <c r="H340" t="n">
         <v>-48.45177004972177</v>
@@ -49943,7 +49943,7 @@
         <v>-50.84891692643389</v>
       </c>
       <c r="I342" t="n">
-        <v>-30.42624103025863</v>
+        <v>-30.42624869717885</v>
       </c>
       <c r="J342" t="n">
         <v>-21.04766814258902</v>
@@ -49969,13 +49969,13 @@
         <v>-38.56778592704874</v>
       </c>
       <c r="G343" t="n">
-        <v>16.72654359220733</v>
+        <v>16.72655504620151</v>
       </c>
       <c r="H343" t="n">
         <v>-48.263368464608</v>
       </c>
       <c r="I343" t="n">
-        <v>-29.51919110643136</v>
+        <v>-29.51919907596125</v>
       </c>
       <c r="J343" t="n">
         <v>-17.58568880160797</v>
@@ -50135,7 +50135,7 @@
         <v>-49.48442445243727</v>
       </c>
       <c r="I348" t="n">
-        <v>-31.66427704201518</v>
+        <v>-31.66427293856655</v>
       </c>
       <c r="J348" t="n">
         <v>-28.13106781059436</v>
@@ -50199,7 +50199,7 @@
         <v>-49.7811033252699</v>
       </c>
       <c r="I350" t="n">
-        <v>-32.73927413496151</v>
+        <v>-32.73928211656697</v>
       </c>
       <c r="J350" t="n">
         <v>-30.67679915646358</v>
@@ -50257,7 +50257,7 @@
         <v>-30.979665054058</v>
       </c>
       <c r="G352" t="n">
-        <v>9.801745550800645</v>
+        <v>9.801756136726736</v>
       </c>
       <c r="H352" t="n">
         <v>-51.15160485874554</v>
@@ -50289,7 +50289,7 @@
         <v>-31.89830918797701</v>
       </c>
       <c r="G353" t="n">
-        <v>10.51757889287628</v>
+        <v>10.51758966122418</v>
       </c>
       <c r="H353" t="n">
         <v>-51.15160485874554</v>
@@ -50385,13 +50385,13 @@
         <v>-24.46144183427424</v>
       </c>
       <c r="G356" t="n">
-        <v>16.88590156582772</v>
+        <v>16.88588990711302</v>
       </c>
       <c r="H356" t="n">
         <v>-47.48545500046233</v>
       </c>
       <c r="I356" t="n">
-        <v>-19.94134609404918</v>
+        <v>-19.94135144179933</v>
       </c>
       <c r="J356" t="n">
         <v>-23.55494913771275</v>
@@ -50423,7 +50423,7 @@
         <v>-46.56193205957327</v>
       </c>
       <c r="I357" t="n">
-        <v>-21.40143072668833</v>
+        <v>-21.40143581400335</v>
       </c>
       <c r="J357" t="n">
         <v>-25.1228993751003</v>
@@ -50551,7 +50551,7 @@
         <v>-48.79726777384864</v>
       </c>
       <c r="I361" t="n">
-        <v>-16.44787225268791</v>
+        <v>-16.44786678377885</v>
       </c>
       <c r="J361" t="n">
         <v>-25.10526556717722</v>
@@ -50679,7 +50679,7 @@
         <v>-65.47643851235274</v>
       </c>
       <c r="I365" t="n">
-        <v>-22.14508162884377</v>
+        <v>-22.14507660393162</v>
       </c>
       <c r="J365" t="n">
         <v>-36.2810713427707</v>
@@ -50711,7 +50711,7 @@
         <v>-63.49094954563196</v>
       </c>
       <c r="I366" t="n">
-        <v>-20.31942858529217</v>
+        <v>-20.31942334639192</v>
       </c>
       <c r="J366" t="n">
         <v>-33.34146360071693</v>
@@ -50775,7 +50775,7 @@
         <v>-59.44152772284181</v>
       </c>
       <c r="I368" t="n">
-        <v>-19.10899911917826</v>
+        <v>-19.10899357438787</v>
       </c>
       <c r="J368" t="n">
         <v>-32.21799935619129</v>
@@ -50801,13 +50801,13 @@
         <v>-26.71135046405951</v>
       </c>
       <c r="G369" t="n">
-        <v>17.18354968966769</v>
+        <v>17.18353782537481</v>
       </c>
       <c r="H369" t="n">
         <v>-61.07611818254843</v>
       </c>
       <c r="I369" t="n">
-        <v>-19.05207469725594</v>
+        <v>-19.0520801981543</v>
       </c>
       <c r="J369" t="n">
         <v>-33.64509836007559</v>
@@ -50865,13 +50865,13 @@
         <v>-25.2692804931725</v>
       </c>
       <c r="G371" t="n">
-        <v>17.11212390813579</v>
+        <v>17.11213568001337</v>
       </c>
       <c r="H371" t="n">
         <v>-60.87988788615164</v>
       </c>
       <c r="I371" t="n">
-        <v>-15.53129621110622</v>
+        <v>-15.5312900461311</v>
       </c>
       <c r="J371" t="n">
         <v>-31.13156069349836</v>
@@ -50903,7 +50903,7 @@
         <v>-60.72807930150839</v>
       </c>
       <c r="I372" t="n">
-        <v>-13.58057239703857</v>
+        <v>-13.58057886234917</v>
       </c>
       <c r="J372" t="n">
         <v>-30.56008220994402</v>
@@ -50929,7 +50929,7 @@
         <v>-28.85148269226424</v>
       </c>
       <c r="G373" t="n">
-        <v>15.06935979463098</v>
+        <v>15.0693482521175</v>
       </c>
       <c r="H373" t="n">
         <v>-63.36000023818598</v>
@@ -51025,13 +51025,13 @@
         <v>-28.413604225734</v>
       </c>
       <c r="G376" t="n">
-        <v>11.18288318627598</v>
+        <v>11.18289445739504</v>
       </c>
       <c r="H376" t="n">
         <v>-64.01993426427576</v>
       </c>
       <c r="I376" t="n">
-        <v>-19.42269812521018</v>
+        <v>-19.42269217116194</v>
       </c>
       <c r="J376" t="n">
         <v>-37.03804196560988</v>
@@ -51057,7 +51057,7 @@
         <v>-26.25635881430726</v>
       </c>
       <c r="G377" t="n">
-        <v>15.85956035145704</v>
+        <v>15.85957219958973</v>
       </c>
       <c r="H377" t="n">
         <v>-62.27387136240345</v>
@@ -51095,7 +51095,7 @@
         <v>-57.84704882559338</v>
       </c>
       <c r="I378" t="n">
-        <v>-16.06874254111276</v>
+        <v>-16.06874881989406</v>
       </c>
       <c r="J378" t="n">
         <v>-35.42445889479823</v>
@@ -51127,7 +51127,7 @@
         <v>-57.86270401296439</v>
       </c>
       <c r="I379" t="n">
-        <v>-14.80091761121131</v>
+        <v>-14.80091095603907</v>
       </c>
       <c r="J379" t="n">
         <v>-33.13288967690797</v>
@@ -51217,7 +51217,7 @@
         <v>-23.55814201887264</v>
       </c>
       <c r="G382" t="n">
-        <v>18.89761247784627</v>
+        <v>18.89760002530356</v>
       </c>
       <c r="H382" t="n">
         <v>-59.06648593293944</v>
@@ -51249,7 +51249,7 @@
         <v>-29.39840880790665</v>
       </c>
       <c r="G383" t="n">
-        <v>14.60106526729248</v>
+        <v>14.60105360211445</v>
       </c>
       <c r="H383" t="n">
         <v>-63.74968210856202</v>
@@ -51287,7 +51287,7 @@
         <v>-66.06225139522131</v>
       </c>
       <c r="I384" t="n">
-        <v>-24.65691619437953</v>
+        <v>-24.65691069119804</v>
       </c>
       <c r="J384" t="n">
         <v>-37.79134432087488</v>
@@ -51313,7 +51313,7 @@
         <v>-30.70830099386722</v>
       </c>
       <c r="G385" t="n">
-        <v>13.30601607935962</v>
+        <v>13.30602734449839</v>
       </c>
       <c r="H385" t="n">
         <v>-66.09785963800563</v>
@@ -51377,7 +51377,7 @@
         <v>-27.73670637603035</v>
       </c>
       <c r="G387" t="n">
-        <v>10.60265427047231</v>
+        <v>10.60266510369081</v>
       </c>
       <c r="H387" t="n">
         <v>-65.63790747729136</v>
@@ -51409,13 +51409,13 @@
         <v>-25.50012389260924</v>
       </c>
       <c r="G388" t="n">
-        <v>13.79509512771688</v>
+        <v>13.79508390008357</v>
       </c>
       <c r="H388" t="n">
         <v>-64.53946245251012</v>
       </c>
       <c r="I388" t="n">
-        <v>-8.856579830449085</v>
+        <v>-8.856572706876376</v>
       </c>
       <c r="J388" t="n">
         <v>-32.25516246566315</v>
@@ -51441,13 +51441,13 @@
         <v>-27.92992853630824</v>
       </c>
       <c r="G389" t="n">
-        <v>14.09151236472803</v>
+        <v>14.09152370384321</v>
       </c>
       <c r="H389" t="n">
         <v>-66.45546781840915</v>
       </c>
       <c r="I389" t="n">
-        <v>-14.83676579389011</v>
+        <v>-14.83677254133186</v>
       </c>
       <c r="J389" t="n">
         <v>-36.49303748442554</v>
@@ -51473,13 +51473,13 @@
         <v>-25.73402100163619</v>
       </c>
       <c r="G390" t="n">
-        <v>14.41568011023115</v>
+        <v>14.41569148156412</v>
       </c>
       <c r="H390" t="n">
         <v>-66.94776163626966</v>
       </c>
       <c r="I390" t="n">
-        <v>-13.80299484421812</v>
+        <v>-13.80300167356505</v>
       </c>
       <c r="J390" t="n">
         <v>-35.19079551224324</v>
@@ -51537,7 +51537,7 @@
         <v>-34.6966578795431</v>
       </c>
       <c r="G392" t="n">
-        <v>6.644940199991112</v>
+        <v>6.644929854007509</v>
       </c>
       <c r="H392" t="n">
         <v>-70.29248220397415</v>
@@ -51569,7 +51569,7 @@
         <v>-41.98987931194888</v>
       </c>
       <c r="G393" t="n">
-        <v>5.71296357748774</v>
+        <v>5.712973775205987</v>
       </c>
       <c r="H393" t="n">
         <v>-72.03757777841206</v>
@@ -51601,7 +51601,7 @@
         <v>-36.04969516561641</v>
       </c>
       <c r="G394" t="n">
-        <v>5.573178091119124</v>
+        <v>5.573188073951862</v>
       </c>
       <c r="H394" t="n">
         <v>-71.34296508383973</v>
@@ -51671,7 +51671,7 @@
         <v>-69.6705801911359</v>
       </c>
       <c r="I396" t="n">
-        <v>-15.75995283260672</v>
+        <v>-15.75994642557669</v>
       </c>
       <c r="J396" t="n">
         <v>-40.96782742221188</v>
@@ -51793,13 +51793,13 @@
         <v>-25.63758140687569</v>
       </c>
       <c r="G400" t="n">
-        <v>8.347726479863283</v>
+        <v>8.347715817465362</v>
       </c>
       <c r="H400" t="n">
         <v>-65.36158938197161</v>
       </c>
       <c r="I400" t="n">
-        <v>-10.88795820863222</v>
+        <v>-10.88795150315567</v>
       </c>
       <c r="J400" t="n">
         <v>-40.41598140815249</v>
@@ -51825,13 +51825,13 @@
         <v>-25.91368806155924</v>
       </c>
       <c r="G401" t="n">
-        <v>5.73816236738256</v>
+        <v>5.738151941372749</v>
       </c>
       <c r="H401" t="n">
         <v>-66.77216419841814</v>
       </c>
       <c r="I401" t="n">
-        <v>-12.15685631369474</v>
+        <v>-12.15684976535586</v>
       </c>
       <c r="J401" t="n">
         <v>-39.50416890022966</v>
@@ -51863,7 +51863,7 @@
         <v>-65.19273127014925</v>
       </c>
       <c r="I402" t="n">
-        <v>2.310061875786684</v>
+        <v>2.310069794177694</v>
       </c>
       <c r="J402" t="n">
         <v>-30.01208802421185</v>
@@ -51889,7 +51889,7 @@
         <v>-13.55808929093354</v>
       </c>
       <c r="G403" t="n">
-        <v>15.69572899384135</v>
+        <v>15.69574121395054</v>
       </c>
       <c r="H403" t="n">
         <v>-63.91718451774392</v>
@@ -51959,7 +51959,7 @@
         <v>-66.03487141927083</v>
       </c>
       <c r="I405" t="n">
-        <v>1.36837001768999</v>
+        <v>1.368362031563874</v>
       </c>
       <c r="J405" t="n">
         <v>-27.97435858310797</v>
@@ -52055,7 +52055,7 @@
         <v>-67.3025268904522</v>
       </c>
       <c r="I408" t="n">
-        <v>-5.191521262247512</v>
+        <v>-5.191528209890328</v>
       </c>
       <c r="J408" t="n">
         <v>-28.0659841371343</v>
@@ -52113,7 +52113,7 @@
         <v>-21.59166824801976</v>
       </c>
       <c r="G410" t="n">
-        <v>5.847534706283208</v>
+        <v>5.847544766048696</v>
       </c>
       <c r="H410" t="n">
         <v>-71.00092030889978</v>
@@ -52145,7 +52145,7 @@
         <v>-23.4112273561191</v>
       </c>
       <c r="G411" t="n">
-        <v>7.996218155048962</v>
+        <v>7.99620785689179</v>
       </c>
       <c r="H411" t="n">
         <v>-70.48958646991004</v>
@@ -52183,7 +52183,7 @@
         <v>-70.45633665272888</v>
       </c>
       <c r="I412" t="n">
-        <v>-8.242447527285467</v>
+        <v>-8.24245399340221</v>
       </c>
       <c r="J412" t="n">
         <v>-33.40224997914316</v>
@@ -52247,7 +52247,7 @@
         <v>-69.38107998017129</v>
       </c>
       <c r="I414" t="n">
-        <v>-7.644551306655078</v>
+        <v>-7.644544630986704</v>
       </c>
       <c r="J414" t="n">
         <v>-30.8268854251635</v>
@@ -52273,13 +52273,13 @@
         <v>-20.80552533209156</v>
       </c>
       <c r="G415" t="n">
-        <v>7.31614843375159</v>
+        <v>7.316138780590764</v>
       </c>
       <c r="H415" t="n">
         <v>-70.72855367660009</v>
       </c>
       <c r="I415" t="n">
-        <v>-8.696650884443169</v>
+        <v>-8.69664441737773</v>
       </c>
       <c r="J415" t="n">
         <v>-30.53675261541027</v>
@@ -52311,7 +52311,7 @@
         <v>-70.8881964147851</v>
       </c>
       <c r="I416" t="n">
-        <v>-5.721571782936197</v>
+        <v>-5.721565130794593</v>
       </c>
       <c r="J416" t="n">
         <v>-30.8217459147344</v>
@@ -52375,7 +52375,7 @@
         <v>-70.31578814024485</v>
       </c>
       <c r="I418" t="n">
-        <v>-6.07737902106924</v>
+        <v>-6.077385767619159</v>
       </c>
       <c r="J418" t="n">
         <v>-27.61620390111826</v>
@@ -52439,7 +52439,7 @@
         <v>-69.95980614914657</v>
       </c>
       <c r="I420" t="n">
-        <v>-8.179710752009505</v>
+        <v>-8.179717415606557</v>
       </c>
       <c r="J420" t="n">
         <v>-26.82353001014859</v>
@@ -52529,7 +52529,7 @@
         <v>-22.82890181163548</v>
       </c>
       <c r="G423" t="n">
-        <v>-0.7232893946104491</v>
+        <v>-0.7232805190683367</v>
       </c>
       <c r="H423" t="n">
         <v>-69.73572116248295</v>
@@ -52561,7 +52561,7 @@
         <v>-28.71681266182397</v>
       </c>
       <c r="G424" t="n">
-        <v>-6.596764975419667</v>
+        <v>-6.59675696969183</v>
       </c>
       <c r="H424" t="n">
         <v>-72.19502709891556</v>
@@ -52593,7 +52593,7 @@
         <v>-31.15545012423484</v>
       </c>
       <c r="G425" t="n">
-        <v>-5.259904730487608</v>
+        <v>-5.259896490868588</v>
       </c>
       <c r="H425" t="n">
         <v>-74.55197130553066</v>
@@ -52625,7 +52625,7 @@
         <v>-30.92938355917067</v>
       </c>
       <c r="G426" t="n">
-        <v>-6.768978259326808</v>
+        <v>-6.768986318174663</v>
       </c>
       <c r="H426" t="n">
         <v>-75.17025640944985</v>
@@ -52727,7 +52727,7 @@
         <v>-75.86762184320494</v>
       </c>
       <c r="I429" t="n">
-        <v>-18.76462561086942</v>
+        <v>-18.76463099427176</v>
       </c>
       <c r="J429" t="n">
         <v>-40.73101173639364</v>
@@ -52753,13 +52753,13 @@
         <v>-32.41098037149195</v>
       </c>
       <c r="G430" t="n">
-        <v>-3.660002478738422</v>
+        <v>-3.659994152320223</v>
       </c>
       <c r="H430" t="n">
         <v>-76.66848598030319</v>
       </c>
       <c r="I430" t="n">
-        <v>-17.1674021931759</v>
+        <v>-17.167396650204</v>
       </c>
       <c r="J430" t="n">
         <v>-40.24144910398108</v>
@@ -52785,7 +52785,7 @@
         <v>-32.61940456242382</v>
       </c>
       <c r="G431" t="n">
-        <v>-4.721728443432937</v>
+        <v>-4.721720235280513</v>
       </c>
       <c r="H431" t="n">
         <v>-76.79521881319495</v>
@@ -52945,13 +52945,13 @@
         <v>-42.55076628068165</v>
       </c>
       <c r="G436" t="n">
-        <v>-6.585718847033862</v>
+        <v>-6.585726987444507</v>
       </c>
       <c r="H436" t="n">
         <v>-77.08725196671594</v>
       </c>
       <c r="I436" t="n">
-        <v>-19.52656340295372</v>
+        <v>-19.52655806860775</v>
       </c>
       <c r="J436" t="n">
         <v>-46.51993029913489</v>
@@ -53073,7 +53073,7 @@
         <v>-42.14920901985823</v>
       </c>
       <c r="G440" t="n">
-        <v>-9.341176625179859</v>
+        <v>-9.341168683292222</v>
       </c>
       <c r="H440" t="n">
         <v>-74.90425393909189</v>
@@ -53105,13 +53105,13 @@
         <v>-42.29934878455828</v>
       </c>
       <c r="G441" t="n">
-        <v>-10.06949982476274</v>
+        <v>-10.06949204629482</v>
       </c>
       <c r="H441" t="n">
         <v>-77.44613900123169</v>
       </c>
       <c r="I441" t="n">
-        <v>-17.76890968090208</v>
+        <v>-17.76891500921736</v>
       </c>
       <c r="J441" t="n">
         <v>-54.40669531018253</v>
@@ -53169,7 +53169,7 @@
         <v>-45.10528325008265</v>
       </c>
       <c r="G443" t="n">
-        <v>-11.74872194887284</v>
+        <v>-11.74871442140775</v>
       </c>
       <c r="H443" t="n">
         <v>-76.91231867772697</v>
@@ -53297,13 +53297,13 @@
         <v>-38.00978448792061</v>
       </c>
       <c r="G447" t="n">
-        <v>-6.755756557173886</v>
+        <v>-6.755748593347743</v>
       </c>
       <c r="H447" t="n">
         <v>-79.37792374904173</v>
       </c>
       <c r="I447" t="n">
-        <v>-11.5511279970311</v>
+        <v>-11.55112255709438</v>
       </c>
       <c r="J447" t="n">
         <v>-61.48881251956044</v>
@@ -53335,7 +53335,7 @@
         <v>-78.79339341036149</v>
       </c>
       <c r="I448" t="n">
-        <v>-10.86656670112384</v>
+        <v>-10.86656107571498</v>
       </c>
       <c r="J448" t="n">
         <v>-60.23862992693305</v>
@@ -53361,7 +53361,7 @@
         <v>-37.7883555351</v>
       </c>
       <c r="G449" t="n">
-        <v>-8.13682695887027</v>
+        <v>-8.136819092262881</v>
       </c>
       <c r="H449" t="n">
         <v>-78.59018000564203</v>
@@ -53393,7 +53393,7 @@
         <v>-35.79224816752393</v>
       </c>
       <c r="G450" t="n">
-        <v>-6.515120518692097</v>
+        <v>-6.515112476293671</v>
       </c>
       <c r="H450" t="n">
         <v>-78.95137134685486</v>
@@ -53457,7 +53457,7 @@
         <v>-36.80701636831384</v>
       </c>
       <c r="G452" t="n">
-        <v>-7.5598938000765</v>
+        <v>-7.559885859211124</v>
       </c>
       <c r="H452" t="n">
         <v>-79.75966409935273</v>
@@ -53553,7 +53553,7 @@
         <v>-41.48341463321004</v>
       </c>
       <c r="G455" t="n">
-        <v>-9.55091551994175</v>
+        <v>-9.550907843832491</v>
       </c>
       <c r="H455" t="n">
         <v>-80.90036279810563</v>
@@ -53617,7 +53617,7 @@
         <v>-45.07893809183386</v>
       </c>
       <c r="G457" t="n">
-        <v>-11.77049784521835</v>
+        <v>-11.77049058031225</v>
       </c>
       <c r="H457" t="n">
         <v>-82.36463783259975</v>
@@ -53649,7 +53649,7 @@
         <v>-43.76698367914717</v>
       </c>
       <c r="G458" t="n">
-        <v>-13.24027144589717</v>
+        <v>-13.2402643967687</v>
       </c>
       <c r="H458" t="n">
         <v>-82.17891229009145</v>
@@ -53745,7 +53745,7 @@
         <v>-44.03718065374491</v>
       </c>
       <c r="G461" t="n">
-        <v>-13.10907941084746</v>
+        <v>-13.10908645483005</v>
       </c>
       <c r="H461" t="n">
         <v>-82.374291038393</v>
@@ -53777,7 +53777,7 @@
         <v>-46.7217367763071</v>
       </c>
       <c r="G462" t="n">
-        <v>-15.21158626015627</v>
+        <v>-15.21157938208825</v>
       </c>
       <c r="H462" t="n">
         <v>-81.44846848638161</v>
@@ -53873,7 +53873,7 @@
         <v>-43.08986650881587</v>
       </c>
       <c r="G465" t="n">
-        <v>-14.92585263286353</v>
+        <v>-14.92585944524146</v>
       </c>
       <c r="H465" t="n">
         <v>-82.20913100290016</v>
@@ -53937,7 +53937,7 @@
         <v>-42.95977001650706</v>
       </c>
       <c r="G467" t="n">
-        <v>-13.87503413475447</v>
+        <v>-13.87504112400696</v>
       </c>
       <c r="H467" t="n">
         <v>-82.14698279428512</v>
@@ -54097,7 +54097,7 @@
         <v>-52.68180189783389</v>
       </c>
       <c r="G472" t="n">
-        <v>-11.96639345048396</v>
+        <v>-11.96638610891365</v>
       </c>
       <c r="H472" t="n">
         <v>-84.05702090232704</v>
@@ -54129,7 +54129,7 @@
         <v>-54.05846909836642</v>
       </c>
       <c r="G473" t="n">
-        <v>-13.063242448656</v>
+        <v>-13.06323519659256</v>
       </c>
       <c r="H473" t="n">
         <v>-83.80988967383018</v>
@@ -54225,7 +54225,7 @@
         <v>-51.98003104313121</v>
       </c>
       <c r="G476" t="n">
-        <v>-10.24514100720096</v>
+        <v>-10.24513324991935</v>
       </c>
       <c r="H476" t="n">
         <v>-84.14785454375516</v>
@@ -54257,7 +54257,7 @@
         <v>-51.22602268723562</v>
       </c>
       <c r="G477" t="n">
-        <v>-8.26726292543951</v>
+        <v>-8.267254874581775</v>
       </c>
       <c r="H477" t="n">
         <v>-83.31527028006884</v>
@@ -54321,7 +54321,7 @@
         <v>-47.64444308810764</v>
       </c>
       <c r="G479" t="n">
-        <v>-4.936994959667762</v>
+        <v>-4.93700339479709</v>
       </c>
       <c r="H479" t="n">
         <v>-81.60539153240039</v>
@@ -54353,7 +54353,7 @@
         <v>-47.96316040173912</v>
       </c>
       <c r="G480" t="n">
-        <v>-6.118769672358115</v>
+        <v>-6.118777829213606</v>
       </c>
       <c r="H480" t="n">
         <v>-81.47244646127044</v>
@@ -54385,7 +54385,7 @@
         <v>-46.50169090859205</v>
       </c>
       <c r="G481" t="n">
-        <v>-7.662700126451261</v>
+        <v>-7.66270818898882</v>
       </c>
       <c r="H481" t="n">
         <v>-79.78622691284023</v>
@@ -54545,7 +54545,7 @@
         <v>-49.09154693367059</v>
       </c>
       <c r="G486" t="n">
-        <v>-4.125988342067622</v>
+        <v>-4.125996817397826</v>
       </c>
       <c r="H486" t="n">
         <v>-75.83799225046901</v>
@@ -54577,7 +54577,7 @@
         <v>-48.99627177559144</v>
       </c>
       <c r="G487" t="n">
-        <v>-3.521153283265299</v>
+        <v>-3.521144733595927</v>
       </c>
       <c r="H487" t="n">
         <v>-75.16174696814954</v>

--- a/dashboards/Reliance Group.xlsx
+++ b/dashboards/Reliance Group.xlsx
@@ -493,13 +493,13 @@
         <v>91.84999847412109</v>
       </c>
       <c r="G2" t="n">
-        <v>1088.74658203125</v>
+        <v>1088.746704101562</v>
       </c>
       <c r="H2" t="n">
         <v>100.8000030517578</v>
       </c>
       <c r="I2" t="n">
-        <v>850.676025390625</v>
+        <v>850.6759643554688</v>
       </c>
       <c r="J2" t="n">
         <v>14.25</v>
@@ -522,7 +522,7 @@
         <v>90.40000152587891</v>
       </c>
       <c r="G3" t="n">
-        <v>1113.317626953125</v>
+        <v>1113.317504882812</v>
       </c>
       <c r="H3" t="n">
         <v>97.5</v>
@@ -667,13 +667,13 @@
         <v>89.34999847412109</v>
       </c>
       <c r="G8" t="n">
-        <v>1112.16259765625</v>
+        <v>1112.162719726562</v>
       </c>
       <c r="H8" t="n">
         <v>98.40000152587891</v>
       </c>
       <c r="I8" t="n">
-        <v>968.8118896484375</v>
+        <v>968.811767578125</v>
       </c>
       <c r="J8" t="n">
         <v>14.30000019073486</v>
@@ -702,7 +702,7 @@
         <v>96.40000152587891</v>
       </c>
       <c r="I9" t="n">
-        <v>941.8935546875</v>
+        <v>941.8936157226562</v>
       </c>
       <c r="J9" t="n">
         <v>14.35000038146973</v>
@@ -731,7 +731,7 @@
         <v>99.05000305175781</v>
       </c>
       <c r="I10" t="n">
-        <v>931.4307861328125</v>
+        <v>931.4307250976562</v>
       </c>
       <c r="J10" t="n">
         <v>14.25</v>
@@ -754,13 +754,13 @@
         <v>89.59999847412109</v>
       </c>
       <c r="G11" t="n">
-        <v>1149.958618164062</v>
+        <v>1149.958740234375</v>
       </c>
       <c r="H11" t="n">
         <v>102.75</v>
       </c>
       <c r="I11" t="n">
-        <v>931.529052734375</v>
+        <v>931.5289916992188</v>
       </c>
       <c r="J11" t="n">
         <v>14.94999980926514</v>
@@ -789,7 +789,7 @@
         <v>105.5500030517578</v>
       </c>
       <c r="I12" t="n">
-        <v>934.6728515625</v>
+        <v>934.6727294921875</v>
       </c>
       <c r="J12" t="n">
         <v>15.64999961853027</v>
@@ -812,7 +812,7 @@
         <v>89.80000305175781</v>
       </c>
       <c r="G13" t="n">
-        <v>1142.168579101562</v>
+        <v>1142.16845703125</v>
       </c>
       <c r="H13" t="n">
         <v>101.9499969482422</v>
@@ -841,7 +841,7 @@
         <v>90.69999694824219</v>
       </c>
       <c r="G14" t="n">
-        <v>1142.077880859375</v>
+        <v>1142.077758789062</v>
       </c>
       <c r="H14" t="n">
         <v>99.75</v>
@@ -876,7 +876,7 @@
         <v>101.5500030517578</v>
       </c>
       <c r="I15" t="n">
-        <v>936.3428344726562</v>
+        <v>936.3428955078125</v>
       </c>
       <c r="J15" t="n">
         <v>16.54999923706055</v>
@@ -928,7 +928,7 @@
         <v>82.09999847412109</v>
       </c>
       <c r="G17" t="n">
-        <v>1076.993774414062</v>
+        <v>1076.99365234375</v>
       </c>
       <c r="H17" t="n">
         <v>93.55000305175781</v>
@@ -957,7 +957,7 @@
         <v>78</v>
       </c>
       <c r="G18" t="n">
-        <v>1074.887573242188</v>
+        <v>1074.887451171875</v>
       </c>
       <c r="H18" t="n">
         <v>98.05000305175781</v>
@@ -992,7 +992,7 @@
         <v>97.80000305175781</v>
       </c>
       <c r="I19" t="n">
-        <v>855.3916625976562</v>
+        <v>855.3916015625</v>
       </c>
       <c r="J19" t="n">
         <v>14.80000019073486</v>
@@ -1015,13 +1015,13 @@
         <v>84.25</v>
       </c>
       <c r="G20" t="n">
-        <v>1057.948364257812</v>
+        <v>1057.9482421875</v>
       </c>
       <c r="H20" t="n">
         <v>102.3000030517578</v>
       </c>
       <c r="I20" t="n">
-        <v>885.7974243164062</v>
+        <v>885.7974853515625</v>
       </c>
       <c r="J20" t="n">
         <v>15.19999980926514</v>
@@ -1044,13 +1044,13 @@
         <v>82</v>
       </c>
       <c r="G21" t="n">
-        <v>1080.933959960938</v>
+        <v>1080.933837890625</v>
       </c>
       <c r="H21" t="n">
         <v>101.0500030517578</v>
       </c>
       <c r="I21" t="n">
-        <v>864.528076171875</v>
+        <v>864.5281372070312</v>
       </c>
       <c r="J21" t="n">
         <v>14.80000019073486</v>
@@ -1131,13 +1131,13 @@
         <v>87.75</v>
       </c>
       <c r="G24" t="n">
-        <v>1065.602661132812</v>
+        <v>1065.6025390625</v>
       </c>
       <c r="H24" t="n">
         <v>115.5999984741211</v>
       </c>
       <c r="I24" t="n">
-        <v>910.0140380859375</v>
+        <v>910.0140991210938</v>
       </c>
       <c r="J24" t="n">
         <v>16.85000038146973</v>
@@ -1160,7 +1160,7 @@
         <v>85.44999694824219</v>
       </c>
       <c r="G25" t="n">
-        <v>1055.887573242188</v>
+        <v>1055.887451171875</v>
       </c>
       <c r="H25" t="n">
         <v>121.3499984741211</v>
@@ -1189,13 +1189,13 @@
         <v>83.25</v>
       </c>
       <c r="G26" t="n">
-        <v>1049.456176757812</v>
+        <v>1049.4560546875</v>
       </c>
       <c r="H26" t="n">
         <v>133.4499969482422</v>
       </c>
       <c r="I26" t="n">
-        <v>874.7943115234375</v>
+        <v>874.7943725585938</v>
       </c>
       <c r="J26" t="n">
         <v>18.5</v>
@@ -1224,7 +1224,7 @@
         <v>134.4499969482422</v>
       </c>
       <c r="I27" t="n">
-        <v>865.2157592773438</v>
+        <v>865.2158203125</v>
       </c>
       <c r="J27" t="n">
         <v>17.60000038146973</v>
@@ -1247,7 +1247,7 @@
         <v>87.75</v>
       </c>
       <c r="G28" t="n">
-        <v>1079.529907226562</v>
+        <v>1079.52978515625</v>
       </c>
       <c r="H28" t="n">
         <v>147.8500061035156</v>
@@ -1276,13 +1276,13 @@
         <v>92.09999847412109</v>
       </c>
       <c r="G29" t="n">
-        <v>1078.420166015625</v>
+        <v>1078.420288085938</v>
       </c>
       <c r="H29" t="n">
         <v>133.1000061035156</v>
       </c>
       <c r="I29" t="n">
-        <v>879.510009765625</v>
+        <v>879.5099487304688</v>
       </c>
       <c r="J29" t="n">
         <v>16.14999961853027</v>
@@ -1311,7 +1311,7 @@
         <v>134</v>
       </c>
       <c r="I30" t="n">
-        <v>853.6724243164062</v>
+        <v>853.6724853515625</v>
       </c>
       <c r="J30" t="n">
         <v>15.94999980926514</v>
@@ -1340,7 +1340,7 @@
         <v>120.5999984741211</v>
       </c>
       <c r="I31" t="n">
-        <v>771.345703125</v>
+        <v>771.3457641601562</v>
       </c>
       <c r="J31" t="n">
         <v>15.19999980926514</v>
@@ -1398,7 +1398,7 @@
         <v>122.5999984741211</v>
       </c>
       <c r="I33" t="n">
-        <v>794.4325561523438</v>
+        <v>794.4324951171875</v>
       </c>
       <c r="J33" t="n">
         <v>14.80000019073486</v>
@@ -1421,13 +1421,13 @@
         <v>85.30000305175781</v>
       </c>
       <c r="G34" t="n">
-        <v>1106.704956054688</v>
+        <v>1106.704833984375</v>
       </c>
       <c r="H34" t="n">
         <v>113.3499984741211</v>
       </c>
       <c r="I34" t="n">
-        <v>801.1129760742188</v>
+        <v>801.113037109375</v>
       </c>
       <c r="J34" t="n">
         <v>14.14999961853027</v>
@@ -1450,13 +1450,13 @@
         <v>83.09999847412109</v>
       </c>
       <c r="G35" t="n">
-        <v>1098.054443359375</v>
+        <v>1098.054321289062</v>
       </c>
       <c r="H35" t="n">
         <v>120.0999984741211</v>
       </c>
       <c r="I35" t="n">
-        <v>790.3063354492188</v>
+        <v>790.306396484375</v>
       </c>
       <c r="J35" t="n">
         <v>14.14999961853027</v>
@@ -1479,7 +1479,7 @@
         <v>82.15000152587891</v>
       </c>
       <c r="G36" t="n">
-        <v>1086.957763671875</v>
+        <v>1086.957885742188</v>
       </c>
       <c r="H36" t="n">
         <v>112.6999969482422</v>
@@ -1514,7 +1514,7 @@
         <v>114.3499984741211</v>
       </c>
       <c r="I37" t="n">
-        <v>725.5650024414062</v>
+        <v>725.5650634765625</v>
       </c>
       <c r="J37" t="n">
         <v>12.94999980926514</v>
@@ -1537,7 +1537,7 @@
         <v>78.65000152587891</v>
       </c>
       <c r="G38" t="n">
-        <v>1075.249755859375</v>
+        <v>1075.249877929688</v>
       </c>
       <c r="H38" t="n">
         <v>113.25</v>
@@ -1566,7 +1566,7 @@
         <v>74.75</v>
       </c>
       <c r="G39" t="n">
-        <v>1021.669494628906</v>
+        <v>1021.66943359375</v>
       </c>
       <c r="H39" t="n">
         <v>101.9499969482422</v>
@@ -1630,7 +1630,7 @@
         <v>104.5999984741211</v>
       </c>
       <c r="I41" t="n">
-        <v>686.1209716796875</v>
+        <v>686.1209106445312</v>
       </c>
       <c r="J41" t="n">
         <v>13.05000019073486</v>
@@ -1659,7 +1659,7 @@
         <v>107.5999984741211</v>
       </c>
       <c r="I42" t="n">
-        <v>692.8505249023438</v>
+        <v>692.8504638671875</v>
       </c>
       <c r="J42" t="n">
         <v>13.14999961853027</v>
@@ -1798,13 +1798,13 @@
         <v>77.80000305175781</v>
       </c>
       <c r="G47" t="n">
-        <v>1066.214233398438</v>
+        <v>1066.214111328125</v>
       </c>
       <c r="H47" t="n">
         <v>107.5</v>
       </c>
       <c r="I47" t="n">
-        <v>693.882080078125</v>
+        <v>693.8820190429688</v>
       </c>
       <c r="J47" t="n">
         <v>13.35000038146973</v>
@@ -1833,7 +1833,7 @@
         <v>111.4000015258789</v>
       </c>
       <c r="I48" t="n">
-        <v>701.8396606445312</v>
+        <v>701.8397216796875</v>
       </c>
       <c r="J48" t="n">
         <v>13.55000019073486</v>
@@ -1856,7 +1856,7 @@
         <v>77.84999847412109</v>
       </c>
       <c r="G49" t="n">
-        <v>1086.617919921875</v>
+        <v>1086.618041992188</v>
       </c>
       <c r="H49" t="n">
         <v>122.5</v>
@@ -1885,13 +1885,13 @@
         <v>76.5</v>
       </c>
       <c r="G50" t="n">
-        <v>1095.540405273438</v>
+        <v>1095.540283203125</v>
       </c>
       <c r="H50" t="n">
         <v>117.25</v>
       </c>
       <c r="I50" t="n">
-        <v>737.84521484375</v>
+        <v>737.8451538085938</v>
       </c>
       <c r="J50" t="n">
         <v>13.85000038146973</v>
@@ -1914,13 +1914,13 @@
         <v>78.84999847412109</v>
       </c>
       <c r="G51" t="n">
-        <v>1070.44873046875</v>
+        <v>1070.448852539062</v>
       </c>
       <c r="H51" t="n">
         <v>115.5500030517578</v>
       </c>
       <c r="I51" t="n">
-        <v>747.3255615234375</v>
+        <v>747.3256225585938</v>
       </c>
       <c r="J51" t="n">
         <v>13.44999980926514</v>
@@ -1978,7 +1978,7 @@
         <v>116.8000030517578</v>
       </c>
       <c r="I53" t="n">
-        <v>758.770751953125</v>
+        <v>758.7706909179688</v>
       </c>
       <c r="J53" t="n">
         <v>13.75</v>
@@ -2001,13 +2001,13 @@
         <v>79.15000152587891</v>
       </c>
       <c r="G54" t="n">
-        <v>1117.529541015625</v>
+        <v>1117.529663085938</v>
       </c>
       <c r="H54" t="n">
         <v>115.4000015258789</v>
       </c>
       <c r="I54" t="n">
-        <v>744.8695678710938</v>
+        <v>744.86962890625</v>
       </c>
       <c r="J54" t="n">
         <v>13.64999961853027</v>
@@ -2030,7 +2030,7 @@
         <v>83.09999847412109</v>
       </c>
       <c r="G55" t="n">
-        <v>1146.403198242188</v>
+        <v>1146.4033203125</v>
       </c>
       <c r="H55" t="n">
         <v>113.1500015258789</v>
@@ -2088,13 +2088,13 @@
         <v>85.55000305175781</v>
       </c>
       <c r="G57" t="n">
-        <v>1167.916625976562</v>
+        <v>1167.916748046875</v>
       </c>
       <c r="H57" t="n">
         <v>109.6999969482422</v>
       </c>
       <c r="I57" t="n">
-        <v>756.3638305664062</v>
+        <v>756.3638916015625</v>
       </c>
       <c r="J57" t="n">
         <v>13</v>
@@ -2152,7 +2152,7 @@
         <v>100.6999969482422</v>
       </c>
       <c r="I59" t="n">
-        <v>731.4595947265625</v>
+        <v>731.4595336914062</v>
       </c>
       <c r="J59" t="n">
         <v>12.35000038146973</v>
@@ -2181,7 +2181,7 @@
         <v>110.75</v>
       </c>
       <c r="I60" t="n">
-        <v>735.4382934570312</v>
+        <v>735.4383544921875</v>
       </c>
       <c r="J60" t="n">
         <v>12.94999980926514</v>
@@ -2210,7 +2210,7 @@
         <v>114.8000030517578</v>
       </c>
       <c r="I61" t="n">
-        <v>769.7738647460938</v>
+        <v>769.7738037109375</v>
       </c>
       <c r="J61" t="n">
         <v>13.55000019073486</v>
@@ -2262,13 +2262,13 @@
         <v>87.84999847412109</v>
       </c>
       <c r="G63" t="n">
-        <v>1202.882080078125</v>
+        <v>1202.881958007812</v>
       </c>
       <c r="H63" t="n">
         <v>122.6500015258789</v>
       </c>
       <c r="I63" t="n">
-        <v>790.2572021484375</v>
+        <v>790.25732421875</v>
       </c>
       <c r="J63" t="n">
         <v>14.14999961853027</v>
@@ -2291,7 +2291,7 @@
         <v>92.19999694824219</v>
       </c>
       <c r="G64" t="n">
-        <v>1206.437622070312</v>
+        <v>1206.4375</v>
       </c>
       <c r="H64" t="n">
         <v>124.6999969482422</v>
@@ -2326,7 +2326,7 @@
         <v>132.1499938964844</v>
       </c>
       <c r="I65" t="n">
-        <v>804.3058471679688</v>
+        <v>804.305908203125</v>
       </c>
       <c r="J65" t="n">
         <v>15.55000019073486</v>
@@ -2378,7 +2378,7 @@
         <v>96.30000305175781</v>
       </c>
       <c r="G67" t="n">
-        <v>1165.2900390625</v>
+        <v>1165.289794921875</v>
       </c>
       <c r="H67" t="n">
         <v>125.1500015258789</v>
@@ -2407,7 +2407,7 @@
         <v>97.19999694824219</v>
       </c>
       <c r="G68" t="n">
-        <v>1184.674682617188</v>
+        <v>1184.6748046875</v>
       </c>
       <c r="H68" t="n">
         <v>126.75</v>
@@ -2436,13 +2436,13 @@
         <v>98.40000152587891</v>
       </c>
       <c r="G69" t="n">
-        <v>1182.206420898438</v>
+        <v>1182.20654296875</v>
       </c>
       <c r="H69" t="n">
         <v>125.8499984741211</v>
       </c>
       <c r="I69" t="n">
-        <v>816.3895874023438</v>
+        <v>816.3896484375</v>
       </c>
       <c r="J69" t="n">
         <v>15.69999980926514</v>
@@ -2465,7 +2465,7 @@
         <v>94.84999847412109</v>
       </c>
       <c r="G70" t="n">
-        <v>1159.945434570312</v>
+        <v>1159.945556640625</v>
       </c>
       <c r="H70" t="n">
         <v>122.9499969482422</v>
@@ -2523,7 +2523,7 @@
         <v>103</v>
       </c>
       <c r="G72" t="n">
-        <v>1152.1552734375</v>
+        <v>1152.155151367188</v>
       </c>
       <c r="H72" t="n">
         <v>119.5500030517578</v>
@@ -2558,7 +2558,7 @@
         <v>123.5999984741211</v>
       </c>
       <c r="I73" t="n">
-        <v>979.8148803710938</v>
+        <v>979.8148193359375</v>
       </c>
       <c r="J73" t="n">
         <v>14.39999961853027</v>
@@ -2587,7 +2587,7 @@
         <v>125.75</v>
       </c>
       <c r="I74" t="n">
-        <v>945.7249145507812</v>
+        <v>945.7250366210938</v>
       </c>
       <c r="J74" t="n">
         <v>14.75</v>
@@ -2610,13 +2610,13 @@
         <v>103.4499969482422</v>
       </c>
       <c r="G75" t="n">
-        <v>1260.062866210938</v>
+        <v>1260.06298828125</v>
       </c>
       <c r="H75" t="n">
         <v>130.3000030517578</v>
       </c>
       <c r="I75" t="n">
-        <v>987.2322387695312</v>
+        <v>987.232177734375</v>
       </c>
       <c r="J75" t="n">
         <v>15.14999961853027</v>
@@ -2645,7 +2645,7 @@
         <v>128.8999938964844</v>
       </c>
       <c r="I76" t="n">
-        <v>962.5243530273438</v>
+        <v>962.5242919921875</v>
       </c>
       <c r="J76" t="n">
         <v>14.94999980926514</v>
@@ -2674,7 +2674,7 @@
         <v>123.25</v>
       </c>
       <c r="I77" t="n">
-        <v>902.3511352539062</v>
+        <v>902.3512573242188</v>
       </c>
       <c r="J77" t="n">
         <v>14.55000019073486</v>
@@ -2726,7 +2726,7 @@
         <v>113.6999969482422</v>
       </c>
       <c r="G79" t="n">
-        <v>1258.364501953125</v>
+        <v>1258.364624023438</v>
       </c>
       <c r="H79" t="n">
         <v>123</v>
@@ -2755,7 +2755,7 @@
         <v>91.34999847412109</v>
       </c>
       <c r="G80" t="n">
-        <v>1277.160522460938</v>
+        <v>1277.16064453125</v>
       </c>
       <c r="H80" t="n">
         <v>120.5999984741211</v>
@@ -2784,13 +2784,13 @@
         <v>86.19999694824219</v>
       </c>
       <c r="G81" t="n">
-        <v>1263.75439453125</v>
+        <v>1263.754272460938</v>
       </c>
       <c r="H81" t="n">
         <v>123.5500030517578</v>
       </c>
       <c r="I81" t="n">
-        <v>1086.947631835938</v>
+        <v>1086.947509765625</v>
       </c>
       <c r="J81" t="n">
         <v>14.25</v>
@@ -2819,7 +2819,7 @@
         <v>124.25</v>
       </c>
       <c r="I82" t="n">
-        <v>1096.476928710938</v>
+        <v>1096.477172851562</v>
       </c>
       <c r="J82" t="n">
         <v>14.19999980926514</v>
@@ -2871,7 +2871,7 @@
         <v>80.30000305175781</v>
       </c>
       <c r="G84" t="n">
-        <v>1196.111083984375</v>
+        <v>1196.110961914062</v>
       </c>
       <c r="H84" t="n">
         <v>115.0999984741211</v>
@@ -2929,13 +2929,13 @@
         <v>74.19999694824219</v>
       </c>
       <c r="G86" t="n">
-        <v>1140.583251953125</v>
+        <v>1140.583129882812</v>
       </c>
       <c r="H86" t="n">
         <v>112.3000030517578</v>
       </c>
       <c r="I86" t="n">
-        <v>1002.950927734375</v>
+        <v>1002.950805664062</v>
       </c>
       <c r="J86" t="n">
         <v>13.69999980926514</v>
@@ -2964,7 +2964,7 @@
         <v>108.1999969482422</v>
       </c>
       <c r="I87" t="n">
-        <v>953.977294921875</v>
+        <v>953.9772338867188</v>
       </c>
       <c r="J87" t="n">
         <v>13.10000038146973</v>
@@ -3045,13 +3045,13 @@
         <v>76.65000152587891</v>
       </c>
       <c r="G90" t="n">
-        <v>1099.050659179688</v>
+        <v>1099.050537109375</v>
       </c>
       <c r="H90" t="n">
         <v>102.0500030517578</v>
       </c>
       <c r="I90" t="n">
-        <v>955.7456665039062</v>
+        <v>955.74560546875</v>
       </c>
       <c r="J90" t="n">
         <v>12.5</v>
@@ -3074,7 +3074,7 @@
         <v>74.59999847412109</v>
       </c>
       <c r="G91" t="n">
-        <v>1099.322509765625</v>
+        <v>1099.322387695312</v>
       </c>
       <c r="H91" t="n">
         <v>98.30000305175781</v>
@@ -3103,7 +3103,7 @@
         <v>77.90000152587891</v>
       </c>
       <c r="G92" t="n">
-        <v>1145.497314453125</v>
+        <v>1145.497192382812</v>
       </c>
       <c r="H92" t="n">
         <v>107.0500030517578</v>
@@ -3167,7 +3167,7 @@
         <v>102.0999984741211</v>
       </c>
       <c r="I94" t="n">
-        <v>977.5061645507812</v>
+        <v>977.5062255859375</v>
       </c>
       <c r="J94" t="n">
         <v>12.30000019073486</v>
@@ -3190,13 +3190,13 @@
         <v>80.75</v>
       </c>
       <c r="G95" t="n">
-        <v>1188.660400390625</v>
+        <v>1188.660522460938</v>
       </c>
       <c r="H95" t="n">
         <v>104</v>
       </c>
       <c r="I95" t="n">
-        <v>1021.665893554688</v>
+        <v>1021.665954589844</v>
       </c>
       <c r="J95" t="n">
         <v>12.85000038146973</v>
@@ -3219,13 +3219,13 @@
         <v>80.05000305175781</v>
       </c>
       <c r="G96" t="n">
-        <v>1180.711669921875</v>
+        <v>1180.711791992188</v>
       </c>
       <c r="H96" t="n">
         <v>101.6999969482422</v>
       </c>
       <c r="I96" t="n">
-        <v>979.0289916992188</v>
+        <v>979.0289306640625</v>
       </c>
       <c r="J96" t="n">
         <v>12.39999961853027</v>
@@ -3254,7 +3254,7 @@
         <v>100.9000015258789</v>
       </c>
       <c r="I97" t="n">
-        <v>945.7249145507812</v>
+        <v>945.7250366210938</v>
       </c>
       <c r="J97" t="n">
         <v>12.55000019073486</v>
@@ -3277,7 +3277,7 @@
         <v>74.65000152587891</v>
       </c>
       <c r="G98" t="n">
-        <v>1183.021728515625</v>
+        <v>1183.021606445312</v>
       </c>
       <c r="H98" t="n">
         <v>100.6500015258789</v>
@@ -3306,13 +3306,13 @@
         <v>71.59999847412109</v>
       </c>
       <c r="G99" t="n">
-        <v>1171.744140625</v>
+        <v>1171.744018554688</v>
       </c>
       <c r="H99" t="n">
         <v>100.3499984741211</v>
       </c>
       <c r="I99" t="n">
-        <v>832.8451538085938</v>
+        <v>832.8450927734375</v>
       </c>
       <c r="J99" t="n">
         <v>11.89999961853027</v>
@@ -3335,13 +3335,13 @@
         <v>71.65000152587891</v>
       </c>
       <c r="G100" t="n">
-        <v>1166.308715820312</v>
+        <v>1166.308837890625</v>
       </c>
       <c r="H100" t="n">
         <v>99.84999847412109</v>
       </c>
       <c r="I100" t="n">
-        <v>871.9944458007812</v>
+        <v>871.9945068359375</v>
       </c>
       <c r="J100" t="n">
         <v>11.85000038146973</v>
@@ -3370,7 +3370,7 @@
         <v>102.5500030517578</v>
       </c>
       <c r="I101" t="n">
-        <v>914.9261474609375</v>
+        <v>914.9262084960938</v>
       </c>
       <c r="J101" t="n">
         <v>12</v>
@@ -3393,13 +3393,13 @@
         <v>75.5</v>
       </c>
       <c r="G102" t="n">
-        <v>1192.374389648438</v>
+        <v>1192.374267578125</v>
       </c>
       <c r="H102" t="n">
         <v>107.9499969482422</v>
       </c>
       <c r="I102" t="n">
-        <v>909.1298217773438</v>
+        <v>909.1298828125</v>
       </c>
       <c r="J102" t="n">
         <v>12.60000038146973</v>
@@ -3422,7 +3422,7 @@
         <v>76.05000305175781</v>
       </c>
       <c r="G103" t="n">
-        <v>1192.75927734375</v>
+        <v>1192.759399414062</v>
       </c>
       <c r="H103" t="n">
         <v>108.0500030517578</v>
@@ -3457,7 +3457,7 @@
         <v>109.3000030517578</v>
       </c>
       <c r="I104" t="n">
-        <v>936.2446899414062</v>
+        <v>936.24462890625</v>
       </c>
       <c r="J104" t="n">
         <v>13.85000038146973</v>
@@ -3509,13 +3509,13 @@
         <v>74.65000152587891</v>
       </c>
       <c r="G106" t="n">
-        <v>1253.47314453125</v>
+        <v>1253.473022460938</v>
       </c>
       <c r="H106" t="n">
         <v>105.1500015258789</v>
       </c>
       <c r="I106" t="n">
-        <v>990.7197875976562</v>
+        <v>990.7198486328125</v>
       </c>
       <c r="J106" t="n">
         <v>13.80000019073486</v>
@@ -3538,13 +3538,13 @@
         <v>75.90000152587891</v>
       </c>
       <c r="G107" t="n">
-        <v>1255.828125</v>
+        <v>1255.828002929688</v>
       </c>
       <c r="H107" t="n">
         <v>105.5</v>
       </c>
       <c r="I107" t="n">
-        <v>978.3903198242188</v>
+        <v>978.3904418945312</v>
       </c>
       <c r="J107" t="n">
         <v>14.30000019073486</v>
@@ -3596,7 +3596,7 @@
         <v>80.94999694824219</v>
       </c>
       <c r="G109" t="n">
-        <v>1267.604125976562</v>
+        <v>1267.60400390625</v>
       </c>
       <c r="H109" t="n">
         <v>104.4499969482422</v>
@@ -3625,7 +3625,7 @@
         <v>78.59999847412109</v>
       </c>
       <c r="G110" t="n">
-        <v>1229.332397460938</v>
+        <v>1229.33251953125</v>
       </c>
       <c r="H110" t="n">
         <v>103.5999984741211</v>
@@ -3654,7 +3654,7 @@
         <v>73.55000305175781</v>
       </c>
       <c r="G111" t="n">
-        <v>1206.075073242188</v>
+        <v>1206.0751953125</v>
       </c>
       <c r="H111" t="n">
         <v>96.94999694824219</v>
@@ -3683,7 +3683,7 @@
         <v>72.84999847412109</v>
       </c>
       <c r="G112" t="n">
-        <v>1190.313598632812</v>
+        <v>1190.3134765625</v>
       </c>
       <c r="H112" t="n">
         <v>95.75</v>
@@ -3712,7 +3712,7 @@
         <v>74.59999847412109</v>
       </c>
       <c r="G113" t="n">
-        <v>1175.910888671875</v>
+        <v>1175.911010742188</v>
       </c>
       <c r="H113" t="n">
         <v>95.5</v>
@@ -3741,13 +3741,13 @@
         <v>67.25</v>
       </c>
       <c r="G114" t="n">
-        <v>1159.469970703125</v>
+        <v>1159.469848632812</v>
       </c>
       <c r="H114" t="n">
         <v>95.40000152587891</v>
       </c>
       <c r="I114" t="n">
-        <v>825.7225952148438</v>
+        <v>825.72265625</v>
       </c>
       <c r="J114" t="n">
         <v>12.05000019073486</v>
@@ -3770,7 +3770,7 @@
         <v>62.75</v>
       </c>
       <c r="G115" t="n">
-        <v>1173.057495117188</v>
+        <v>1173.057373046875</v>
       </c>
       <c r="H115" t="n">
         <v>95.59999847412109</v>
@@ -3799,13 +3799,13 @@
         <v>58.90000152587891</v>
       </c>
       <c r="G116" t="n">
-        <v>1151.792846679688</v>
+        <v>1151.79296875</v>
       </c>
       <c r="H116" t="n">
         <v>90.65000152587891</v>
       </c>
       <c r="I116" t="n">
-        <v>730.182373046875</v>
+        <v>730.1824340820312</v>
       </c>
       <c r="J116" t="n">
         <v>11.10000038146973</v>
@@ -3828,13 +3828,13 @@
         <v>62.29999923706055</v>
       </c>
       <c r="G117" t="n">
-        <v>1170.385131835938</v>
+        <v>1170.385375976562</v>
       </c>
       <c r="H117" t="n">
         <v>94.5</v>
       </c>
       <c r="I117" t="n">
-        <v>770.3141479492188</v>
+        <v>770.314208984375</v>
       </c>
       <c r="J117" t="n">
         <v>11.44999980926514</v>
@@ -3857,13 +3857,13 @@
         <v>59.15000152587891</v>
       </c>
       <c r="G118" t="n">
-        <v>1134.831176757812</v>
+        <v>1134.8310546875</v>
       </c>
       <c r="H118" t="n">
         <v>91.19999694824219</v>
       </c>
       <c r="I118" t="n">
-        <v>743.8380126953125</v>
+        <v>743.8379516601562</v>
       </c>
       <c r="J118" t="n">
         <v>11.39999961853027</v>
@@ -3886,13 +3886,13 @@
         <v>61.40000152587891</v>
       </c>
       <c r="G119" t="n">
-        <v>1116.419921875</v>
+        <v>1116.419799804688</v>
       </c>
       <c r="H119" t="n">
         <v>90.30000305175781</v>
       </c>
       <c r="I119" t="n">
-        <v>755.8726806640625</v>
+        <v>755.8726196289062</v>
       </c>
       <c r="J119" t="n">
         <v>11.60000038146973</v>
@@ -3950,7 +3950,7 @@
         <v>93.09999847412109</v>
       </c>
       <c r="I121" t="n">
-        <v>801.5059814453125</v>
+        <v>801.5060424804688</v>
       </c>
       <c r="J121" t="n">
         <v>11.80000019073486</v>
@@ -4031,7 +4031,7 @@
         <v>69</v>
       </c>
       <c r="G124" t="n">
-        <v>1175.616577148438</v>
+        <v>1175.616455078125</v>
       </c>
       <c r="H124" t="n">
         <v>90.59999847412109</v>
@@ -4182,7 +4182,7 @@
         <v>94.90000152587891</v>
       </c>
       <c r="I129" t="n">
-        <v>936.490234375</v>
+        <v>936.4902954101562</v>
       </c>
       <c r="J129" t="n">
         <v>11.44999980926514</v>
@@ -4205,13 +4205,13 @@
         <v>67.40000152587891</v>
       </c>
       <c r="G130" t="n">
-        <v>1083.10791015625</v>
+        <v>1083.108032226562</v>
       </c>
       <c r="H130" t="n">
         <v>94.80000305175781</v>
       </c>
       <c r="I130" t="n">
-        <v>933.3464965820312</v>
+        <v>933.346435546875</v>
       </c>
       <c r="J130" t="n">
         <v>11.39999961853027</v>
@@ -4263,13 +4263,13 @@
         <v>69.19999694824219</v>
       </c>
       <c r="G132" t="n">
-        <v>1096.265014648438</v>
+        <v>1096.26513671875</v>
       </c>
       <c r="H132" t="n">
         <v>102.5999984741211</v>
       </c>
       <c r="I132" t="n">
-        <v>951.2265625</v>
+        <v>951.2265014648438</v>
       </c>
       <c r="J132" t="n">
         <v>11.5</v>
@@ -4298,7 +4298,7 @@
         <v>101.6500015258789</v>
       </c>
       <c r="I133" t="n">
-        <v>945.1845703125</v>
+        <v>945.1846313476562</v>
       </c>
       <c r="J133" t="n">
         <v>11.5</v>
@@ -4327,7 +4327,7 @@
         <v>100.4000015258789</v>
       </c>
       <c r="I134" t="n">
-        <v>937.9639282226562</v>
+        <v>937.9638671875</v>
       </c>
       <c r="J134" t="n">
         <v>11.39999961853027</v>
@@ -4356,7 +4356,7 @@
         <v>99.44999694824219</v>
       </c>
       <c r="I135" t="n">
-        <v>945.3319702148438</v>
+        <v>945.33203125</v>
       </c>
       <c r="J135" t="n">
         <v>11.30000019073486</v>
@@ -4379,7 +4379,7 @@
         <v>68.15000152587891</v>
       </c>
       <c r="G136" t="n">
-        <v>1097.08056640625</v>
+        <v>1097.080444335938</v>
       </c>
       <c r="H136" t="n">
         <v>102.25</v>
@@ -4414,7 +4414,7 @@
         <v>102.3000030517578</v>
       </c>
       <c r="I137" t="n">
-        <v>978.8323974609375</v>
+        <v>978.83251953125</v>
       </c>
       <c r="J137" t="n">
         <v>11.80000019073486</v>
@@ -4437,13 +4437,13 @@
         <v>67</v>
       </c>
       <c r="G138" t="n">
-        <v>1133.653442382812</v>
+        <v>1133.653564453125</v>
       </c>
       <c r="H138" t="n">
         <v>104.4000015258789</v>
       </c>
       <c r="I138" t="n">
-        <v>959.6753540039062</v>
+        <v>959.67529296875</v>
       </c>
       <c r="J138" t="n">
         <v>11.85000038146973</v>
@@ -4472,7 +4472,7 @@
         <v>105.8000030517578</v>
       </c>
       <c r="I139" t="n">
-        <v>961.9349365234375</v>
+        <v>961.9348754882812</v>
       </c>
       <c r="J139" t="n">
         <v>11.85000038146973</v>
@@ -4495,7 +4495,7 @@
         <v>63.75</v>
       </c>
       <c r="G140" t="n">
-        <v>1133.698974609375</v>
+        <v>1133.698852539062</v>
       </c>
       <c r="H140" t="n">
         <v>104.5</v>
@@ -4559,7 +4559,7 @@
         <v>113.9000015258789</v>
       </c>
       <c r="I142" t="n">
-        <v>945.135498046875</v>
+        <v>945.1355590820312</v>
       </c>
       <c r="J142" t="n">
         <v>11.89999961853027</v>
@@ -4588,7 +4588,7 @@
         <v>115.8499984741211</v>
       </c>
       <c r="I143" t="n">
-        <v>945.8231811523438</v>
+        <v>945.8232421875</v>
       </c>
       <c r="J143" t="n">
         <v>11.89999961853027</v>
@@ -4646,7 +4646,7 @@
         <v>117.0999984741211</v>
       </c>
       <c r="I145" t="n">
-        <v>964.6856689453125</v>
+        <v>964.6856079101562</v>
       </c>
       <c r="J145" t="n">
         <v>12.39999961853027</v>
@@ -4675,7 +4675,7 @@
         <v>123.25</v>
       </c>
       <c r="I146" t="n">
-        <v>1014.592407226562</v>
+        <v>1014.592468261719</v>
       </c>
       <c r="J146" t="n">
         <v>13</v>
@@ -4698,13 +4698,13 @@
         <v>68.05000305175781</v>
       </c>
       <c r="G147" t="n">
-        <v>1170.63427734375</v>
+        <v>1170.634155273438</v>
       </c>
       <c r="H147" t="n">
         <v>128.6999969482422</v>
       </c>
       <c r="I147" t="n">
-        <v>994.7967529296875</v>
+        <v>994.7966918945312</v>
       </c>
       <c r="J147" t="n">
         <v>13.30000019073486</v>
@@ -4756,13 +4756,13 @@
         <v>67.90000152587891</v>
       </c>
       <c r="G149" t="n">
-        <v>1164.859497070312</v>
+        <v>1164.859619140625</v>
       </c>
       <c r="H149" t="n">
         <v>121.3499984741211</v>
       </c>
       <c r="I149" t="n">
-        <v>952.7493286132812</v>
+        <v>952.749267578125</v>
       </c>
       <c r="J149" t="n">
         <v>13.19999980926514</v>
@@ -4785,7 +4785,7 @@
         <v>68.09999847412109</v>
       </c>
       <c r="G150" t="n">
-        <v>1147.694091796875</v>
+        <v>1147.693969726562</v>
       </c>
       <c r="H150" t="n">
         <v>120</v>
@@ -4814,13 +4814,13 @@
         <v>67.5</v>
       </c>
       <c r="G151" t="n">
-        <v>1162.708251953125</v>
+        <v>1162.708374023438</v>
       </c>
       <c r="H151" t="n">
         <v>115.8499984741211</v>
       </c>
       <c r="I151" t="n">
-        <v>944.7916870117188</v>
+        <v>944.7916259765625</v>
       </c>
       <c r="J151" t="n">
         <v>13.30000019073486</v>
@@ -4849,7 +4849,7 @@
         <v>117.5500030517578</v>
       </c>
       <c r="I152" t="n">
-        <v>944.4969482421875</v>
+        <v>944.4968872070312</v>
       </c>
       <c r="J152" t="n">
         <v>14.14999961853027</v>
@@ -4878,7 +4878,7 @@
         <v>115.3499984741211</v>
       </c>
       <c r="I153" t="n">
-        <v>953.8790893554688</v>
+        <v>953.8790283203125</v>
       </c>
       <c r="J153" t="n">
         <v>13.60000038146973</v>
@@ -4901,13 +4901,13 @@
         <v>68.34999847412109</v>
       </c>
       <c r="G154" t="n">
-        <v>1192.53271484375</v>
+        <v>1192.532836914062</v>
       </c>
       <c r="H154" t="n">
         <v>115.1500015258789</v>
       </c>
       <c r="I154" t="n">
-        <v>954.0264282226562</v>
+        <v>954.0263061523438</v>
       </c>
       <c r="J154" t="n">
         <v>13.39999961853027</v>
@@ -4965,7 +4965,7 @@
         <v>121.8000030517578</v>
       </c>
       <c r="I156" t="n">
-        <v>975.4921875</v>
+        <v>975.4923095703125</v>
       </c>
       <c r="J156" t="n">
         <v>13.64999961853027</v>
@@ -4994,7 +4994,7 @@
         <v>129.8999938964844</v>
       </c>
       <c r="I157" t="n">
-        <v>1020.8798828125</v>
+        <v>1020.879943847656</v>
       </c>
       <c r="J157" t="n">
         <v>14.19999980926514</v>
@@ -5104,7 +5104,7 @@
         <v>74.15000152587891</v>
       </c>
       <c r="G161" t="n">
-        <v>1199.490966796875</v>
+        <v>1199.490844726562</v>
       </c>
       <c r="H161" t="n">
         <v>139.6999969482422</v>
@@ -5133,7 +5133,7 @@
         <v>74.05000305175781</v>
       </c>
       <c r="G162" t="n">
-        <v>1195.992065429688</v>
+        <v>1195.9921875</v>
       </c>
       <c r="H162" t="n">
         <v>139.75</v>
@@ -5191,13 +5191,13 @@
         <v>69.65000152587891</v>
       </c>
       <c r="G164" t="n">
-        <v>1180.360961914062</v>
+        <v>1180.36083984375</v>
       </c>
       <c r="H164" t="n">
         <v>158.75</v>
       </c>
       <c r="I164" t="n">
-        <v>992.144287109375</v>
+        <v>992.1442260742188</v>
       </c>
       <c r="J164" t="n">
         <v>16.29999923706055</v>
@@ -5220,7 +5220,7 @@
         <v>70.59999847412109</v>
       </c>
       <c r="G165" t="n">
-        <v>1198.673095703125</v>
+        <v>1198.672973632812</v>
       </c>
       <c r="H165" t="n">
         <v>162</v>
@@ -5313,7 +5313,7 @@
         <v>182.6999969482422</v>
       </c>
       <c r="I168" t="n">
-        <v>1193.93310546875</v>
+        <v>1193.932983398438</v>
       </c>
       <c r="J168" t="n">
         <v>23.29999923706055</v>
@@ -5336,7 +5336,7 @@
         <v>73.94999694824219</v>
       </c>
       <c r="G169" t="n">
-        <v>1179.997436523438</v>
+        <v>1179.997314453125</v>
       </c>
       <c r="H169" t="n">
         <v>178.75</v>
@@ -5365,7 +5365,7 @@
         <v>75.09999847412109</v>
       </c>
       <c r="G170" t="n">
-        <v>1173.135986328125</v>
+        <v>1173.136108398438</v>
       </c>
       <c r="H170" t="n">
         <v>180.6999969482422</v>
@@ -5400,7 +5400,7 @@
         <v>180.3000030517578</v>
       </c>
       <c r="I171" t="n">
-        <v>1188.775390625</v>
+        <v>1188.775268554688</v>
       </c>
       <c r="J171" t="n">
         <v>21.29999923706055</v>
@@ -5429,7 +5429,7 @@
         <v>162.4499969482422</v>
       </c>
       <c r="I172" t="n">
-        <v>1153.801025390625</v>
+        <v>1153.801147460938</v>
       </c>
       <c r="J172" t="n">
         <v>19.20000076293945</v>
@@ -5452,7 +5452,7 @@
         <v>73.90000152587891</v>
       </c>
       <c r="G173" t="n">
-        <v>1180.542602539062</v>
+        <v>1180.542724609375</v>
       </c>
       <c r="H173" t="n">
         <v>174.1999969482422</v>
@@ -5539,7 +5539,7 @@
         <v>71.75</v>
       </c>
       <c r="G176" t="n">
-        <v>1164.479736328125</v>
+        <v>1164.479858398438</v>
       </c>
       <c r="H176" t="n">
         <v>154.4499969482422</v>
@@ -5568,13 +5568,13 @@
         <v>68.65000152587891</v>
       </c>
       <c r="G177" t="n">
-        <v>1135.625732421875</v>
+        <v>1135.625610351562</v>
       </c>
       <c r="H177" t="n">
         <v>156.3500061035156</v>
       </c>
       <c r="I177" t="n">
-        <v>1119.121704101562</v>
+        <v>1119.121826171875</v>
       </c>
       <c r="J177" t="n">
         <v>18.45000076293945</v>
@@ -5597,7 +5597,7 @@
         <v>67.05000305175781</v>
       </c>
       <c r="G178" t="n">
-        <v>1137.102416992188</v>
+        <v>1137.1025390625</v>
       </c>
       <c r="H178" t="n">
         <v>151.8000030517578</v>
@@ -5684,7 +5684,7 @@
         <v>70</v>
       </c>
       <c r="G181" t="n">
-        <v>1129.672973632812</v>
+        <v>1129.673095703125</v>
       </c>
       <c r="H181" t="n">
         <v>146.1499938964844</v>
@@ -5713,7 +5713,7 @@
         <v>67.69999694824219</v>
       </c>
       <c r="G182" t="n">
-        <v>1108.498168945312</v>
+        <v>1108.498291015625</v>
       </c>
       <c r="H182" t="n">
         <v>144.1499938964844</v>
@@ -5777,7 +5777,7 @@
         <v>138.3500061035156</v>
       </c>
       <c r="I184" t="n">
-        <v>1044.90380859375</v>
+        <v>1044.903930664062</v>
       </c>
       <c r="J184" t="n">
         <v>16.20000076293945</v>
@@ -5800,13 +5800,13 @@
         <v>61.70000076293945</v>
       </c>
       <c r="G185" t="n">
-        <v>1059.855224609375</v>
+        <v>1059.855102539062</v>
       </c>
       <c r="H185" t="n">
         <v>136.3500061035156</v>
       </c>
       <c r="I185" t="n">
-        <v>1021.610412597656</v>
+        <v>1021.610534667969</v>
       </c>
       <c r="J185" t="n">
         <v>16.10000038146973</v>
@@ -5835,7 +5835,7 @@
         <v>137.6499938964844</v>
       </c>
       <c r="I186" t="n">
-        <v>1032.690795898438</v>
+        <v>1032.690673828125</v>
       </c>
       <c r="J186" t="n">
         <v>16.04999923706055</v>
@@ -5858,7 +5858,7 @@
         <v>64.59999847412109</v>
       </c>
       <c r="G187" t="n">
-        <v>1080.439331054688</v>
+        <v>1080.439208984375</v>
       </c>
       <c r="H187" t="n">
         <v>136.6999969482422</v>
@@ -5887,13 +5887,13 @@
         <v>63.95000076293945</v>
       </c>
       <c r="G188" t="n">
-        <v>1076.690673828125</v>
+        <v>1076.690551757812</v>
       </c>
       <c r="H188" t="n">
         <v>135.4499969482422</v>
       </c>
       <c r="I188" t="n">
-        <v>1031.90283203125</v>
+        <v>1031.902954101562</v>
       </c>
       <c r="J188" t="n">
         <v>16.45000076293945</v>
@@ -5916,7 +5916,7 @@
         <v>66</v>
       </c>
       <c r="G189" t="n">
-        <v>1096.547607421875</v>
+        <v>1096.547485351562</v>
       </c>
       <c r="H189" t="n">
         <v>137.5500030517578</v>
@@ -5951,7 +5951,7 @@
         <v>144.3999938964844</v>
       </c>
       <c r="I190" t="n">
-        <v>1120.152099609375</v>
+        <v>1120.15185546875</v>
       </c>
       <c r="J190" t="n">
         <v>16.75</v>
@@ -5974,13 +5974,13 @@
         <v>68.19999694824219</v>
       </c>
       <c r="G191" t="n">
-        <v>1105.249267578125</v>
+        <v>1105.249389648438</v>
       </c>
       <c r="H191" t="n">
         <v>151.6000061035156</v>
       </c>
       <c r="I191" t="n">
-        <v>1158.268310546875</v>
+        <v>1158.268432617188</v>
       </c>
       <c r="J191" t="n">
         <v>17.54999923706055</v>
@@ -6003,7 +6003,7 @@
         <v>67.25</v>
       </c>
       <c r="G192" t="n">
-        <v>1093.18505859375</v>
+        <v>1093.185180664062</v>
       </c>
       <c r="H192" t="n">
         <v>157.6999969482422</v>
@@ -6032,13 +6032,13 @@
         <v>66.94999694824219</v>
       </c>
       <c r="G193" t="n">
-        <v>1071.419555664062</v>
+        <v>1071.41943359375</v>
       </c>
       <c r="H193" t="n">
         <v>149.8500061035156</v>
       </c>
       <c r="I193" t="n">
-        <v>1184.811889648438</v>
+        <v>1184.81201171875</v>
       </c>
       <c r="J193" t="n">
         <v>16.89999961853027</v>
@@ -6067,7 +6067,7 @@
         <v>142.6999969482422</v>
       </c>
       <c r="I194" t="n">
-        <v>1128.179077148438</v>
+        <v>1128.178955078125</v>
       </c>
       <c r="J194" t="n">
         <v>16.35000038146973</v>
@@ -6096,7 +6096,7 @@
         <v>142.3500061035156</v>
       </c>
       <c r="I195" t="n">
-        <v>1122.663452148438</v>
+        <v>1122.66357421875</v>
       </c>
       <c r="J195" t="n">
         <v>16.5</v>
@@ -6119,13 +6119,13 @@
         <v>67.19999694824219</v>
       </c>
       <c r="G196" t="n">
-        <v>1077.23583984375</v>
+        <v>1077.235717773438</v>
       </c>
       <c r="H196" t="n">
         <v>138.8500061035156</v>
       </c>
       <c r="I196" t="n">
-        <v>1100.404174804688</v>
+        <v>1100.404296875</v>
       </c>
       <c r="J196" t="n">
         <v>16.20000076293945</v>
@@ -6148,7 +6148,7 @@
         <v>66.40000152587891</v>
       </c>
       <c r="G197" t="n">
-        <v>1094.525512695312</v>
+        <v>1094.525634765625</v>
       </c>
       <c r="H197" t="n">
         <v>138.6999969482422</v>
@@ -6177,7 +6177,7 @@
         <v>70</v>
       </c>
       <c r="G198" t="n">
-        <v>1113.837280273438</v>
+        <v>1113.83740234375</v>
       </c>
       <c r="H198" t="n">
         <v>143.6999969482422</v>
@@ -6212,7 +6212,7 @@
         <v>141.3500061035156</v>
       </c>
       <c r="I199" t="n">
-        <v>1121.087646484375</v>
+        <v>1121.087524414062</v>
       </c>
       <c r="J199" t="n">
         <v>16.35000038146973</v>
@@ -6235,13 +6235,13 @@
         <v>65.09999847412109</v>
       </c>
       <c r="G200" t="n">
-        <v>1136.261962890625</v>
+        <v>1136.261840820312</v>
       </c>
       <c r="H200" t="n">
         <v>139.1000061035156</v>
       </c>
       <c r="I200" t="n">
-        <v>1117.492553710938</v>
+        <v>1117.49267578125</v>
       </c>
       <c r="J200" t="n">
         <v>16.10000038146973</v>
@@ -6264,7 +6264,7 @@
         <v>63.70000076293945</v>
       </c>
       <c r="G201" t="n">
-        <v>1123.084350585938</v>
+        <v>1123.084228515625</v>
       </c>
       <c r="H201" t="n">
         <v>139.1499938964844</v>
@@ -6328,7 +6328,7 @@
         <v>141.6000061035156</v>
       </c>
       <c r="I203" t="n">
-        <v>1089.7177734375</v>
+        <v>1089.717895507812</v>
       </c>
       <c r="J203" t="n">
         <v>16.29999923706055</v>
@@ -6351,13 +6351,13 @@
         <v>64.30000305175781</v>
       </c>
       <c r="G204" t="n">
-        <v>1113.7919921875</v>
+        <v>1113.791870117188</v>
       </c>
       <c r="H204" t="n">
         <v>141.8500061035156</v>
       </c>
       <c r="I204" t="n">
-        <v>1086.56591796875</v>
+        <v>1086.566040039062</v>
       </c>
       <c r="J204" t="n">
         <v>16.14999961853027</v>
@@ -6415,7 +6415,7 @@
         <v>141.4499969482422</v>
       </c>
       <c r="I206" t="n">
-        <v>1081.542846679688</v>
+        <v>1081.54296875</v>
       </c>
       <c r="J206" t="n">
         <v>16.10000038146973</v>
@@ -6438,7 +6438,7 @@
         <v>62.90000152587891</v>
       </c>
       <c r="G207" t="n">
-        <v>1149.552978515625</v>
+        <v>1149.552856445312</v>
       </c>
       <c r="H207" t="n">
         <v>140.6499938964844</v>
@@ -6531,7 +6531,7 @@
         <v>147.1499938964844</v>
       </c>
       <c r="I210" t="n">
-        <v>1074.0576171875</v>
+        <v>1074.057495117188</v>
       </c>
       <c r="J210" t="n">
         <v>16.79999923706055</v>
@@ -6589,7 +6589,7 @@
         <v>146.6499938964844</v>
       </c>
       <c r="I212" t="n">
-        <v>1074.0576171875</v>
+        <v>1074.057495117188</v>
       </c>
       <c r="J212" t="n">
         <v>16.45000076293945</v>
@@ -6618,7 +6618,7 @@
         <v>142.8500061035156</v>
       </c>
       <c r="I213" t="n">
-        <v>1053.669677734375</v>
+        <v>1053.669799804688</v>
       </c>
       <c r="J213" t="n">
         <v>16.10000038146973</v>
@@ -6647,7 +6647,7 @@
         <v>146.1999969482422</v>
       </c>
       <c r="I214" t="n">
-        <v>1057.2646484375</v>
+        <v>1057.264526367188</v>
       </c>
       <c r="J214" t="n">
         <v>16</v>
@@ -6699,7 +6699,7 @@
         <v>63.04999923706055</v>
       </c>
       <c r="G216" t="n">
-        <v>1184.745849609375</v>
+        <v>1184.745971679688</v>
       </c>
       <c r="H216" t="n">
         <v>151.3500061035156</v>
@@ -6734,7 +6734,7 @@
         <v>148.6499938964844</v>
       </c>
       <c r="I217" t="n">
-        <v>1012.499877929688</v>
+        <v>1012.499938964844</v>
       </c>
       <c r="J217" t="n">
         <v>16</v>
@@ -6757,13 +6757,13 @@
         <v>62.29999923706055</v>
       </c>
       <c r="G218" t="n">
-        <v>1180.997192382812</v>
+        <v>1180.997314453125</v>
       </c>
       <c r="H218" t="n">
         <v>146.0500030517578</v>
       </c>
       <c r="I218" t="n">
-        <v>1011.121032714844</v>
+        <v>1011.12109375</v>
       </c>
       <c r="J218" t="n">
         <v>15.64999961853027</v>
@@ -6786,7 +6786,7 @@
         <v>61.59999847412109</v>
       </c>
       <c r="G219" t="n">
-        <v>1180.360961914062</v>
+        <v>1180.36083984375</v>
       </c>
       <c r="H219" t="n">
         <v>147.6499938964844</v>
@@ -6850,7 +6850,7 @@
         <v>141.3000030517578</v>
       </c>
       <c r="I221" t="n">
-        <v>985.0698852539062</v>
+        <v>985.06982421875</v>
       </c>
       <c r="J221" t="n">
         <v>15.05000019073486</v>
@@ -6908,7 +6908,7 @@
         <v>147.0500030517578</v>
       </c>
       <c r="I223" t="n">
-        <v>990.5853881835938</v>
+        <v>990.58544921875</v>
       </c>
       <c r="J223" t="n">
         <v>15.25</v>
@@ -6931,13 +6931,13 @@
         <v>62.95000076293945</v>
       </c>
       <c r="G224" t="n">
-        <v>1189.426025390625</v>
+        <v>1189.426147460938</v>
       </c>
       <c r="H224" t="n">
         <v>154.3000030517578</v>
       </c>
       <c r="I224" t="n">
-        <v>1008.067810058594</v>
+        <v>1008.067749023438</v>
       </c>
       <c r="J224" t="n">
         <v>16</v>
@@ -6995,7 +6995,7 @@
         <v>154.1499938964844</v>
       </c>
       <c r="I226" t="n">
-        <v>1044.657592773438</v>
+        <v>1044.65771484375</v>
       </c>
       <c r="J226" t="n">
         <v>15.89999961853027</v>
@@ -7018,7 +7018,7 @@
         <v>68.05000305175781</v>
       </c>
       <c r="G227" t="n">
-        <v>1241.113525390625</v>
+        <v>1241.113647460938</v>
       </c>
       <c r="H227" t="n">
         <v>157.6999969482422</v>
@@ -7140,7 +7140,7 @@
         <v>156.3999938964844</v>
       </c>
       <c r="I231" t="n">
-        <v>1050.419555664062</v>
+        <v>1050.41943359375</v>
       </c>
       <c r="J231" t="n">
         <v>15.85000038146973</v>
@@ -7169,7 +7169,7 @@
         <v>154.1999969482422</v>
       </c>
       <c r="I232" t="n">
-        <v>1031.90283203125</v>
+        <v>1031.902954101562</v>
       </c>
       <c r="J232" t="n">
         <v>15.69999980926514</v>
@@ -7227,7 +7227,7 @@
         <v>154.75</v>
       </c>
       <c r="I234" t="n">
-        <v>1009.98828125</v>
+        <v>1009.988342285156</v>
       </c>
       <c r="J234" t="n">
         <v>15.89999961853027</v>
@@ -7256,7 +7256,7 @@
         <v>161.8000030517578</v>
       </c>
       <c r="I235" t="n">
-        <v>1015.454711914062</v>
+        <v>1015.454650878906</v>
       </c>
       <c r="J235" t="n">
         <v>15.94999980926514</v>
@@ -7285,7 +7285,7 @@
         <v>157.25</v>
       </c>
       <c r="I236" t="n">
-        <v>1016.488891601562</v>
+        <v>1016.488952636719</v>
       </c>
       <c r="J236" t="n">
         <v>15.75</v>
@@ -7308,13 +7308,13 @@
         <v>75.40000152587891</v>
       </c>
       <c r="G237" t="n">
-        <v>1188.472045898438</v>
+        <v>1188.471923828125</v>
       </c>
       <c r="H237" t="n">
         <v>156.6499938964844</v>
       </c>
       <c r="I237" t="n">
-        <v>1012.943054199219</v>
+        <v>1012.943115234375</v>
       </c>
       <c r="J237" t="n">
         <v>16.45000076293945</v>
@@ -7343,7 +7343,7 @@
         <v>148.8999938964844</v>
       </c>
       <c r="I238" t="n">
-        <v>1001.271850585938</v>
+        <v>1001.271789550781</v>
       </c>
       <c r="J238" t="n">
         <v>15.89999961853027</v>
@@ -7372,7 +7372,7 @@
         <v>151.1000061035156</v>
       </c>
       <c r="I239" t="n">
-        <v>982.7553100585938</v>
+        <v>982.7552490234375</v>
       </c>
       <c r="J239" t="n">
         <v>15.75</v>
@@ -7424,7 +7424,7 @@
         <v>71.34999847412109</v>
       </c>
       <c r="G241" t="n">
-        <v>1191.334716796875</v>
+        <v>1191.334594726562</v>
       </c>
       <c r="H241" t="n">
         <v>149.8000030517578</v>
@@ -7453,13 +7453,13 @@
         <v>66.59999847412109</v>
       </c>
       <c r="G242" t="n">
-        <v>1174.385620117188</v>
+        <v>1174.3857421875</v>
       </c>
       <c r="H242" t="n">
         <v>142.5500030517578</v>
       </c>
       <c r="I242" t="n">
-        <v>939.5665283203125</v>
+        <v>939.5664672851562</v>
       </c>
       <c r="J242" t="n">
         <v>15</v>
@@ -7517,7 +7517,7 @@
         <v>128.6999969482422</v>
       </c>
       <c r="I244" t="n">
-        <v>796.0140991210938</v>
+        <v>796.0140380859375</v>
       </c>
       <c r="J244" t="n">
         <v>13.55000019073486</v>
@@ -7540,7 +7540,7 @@
         <v>62.90000152587891</v>
       </c>
       <c r="G245" t="n">
-        <v>1146.917358398438</v>
+        <v>1146.91748046875</v>
       </c>
       <c r="H245" t="n">
         <v>128.1999969482422</v>
@@ -7569,7 +7569,7 @@
         <v>65.80000305175781</v>
       </c>
       <c r="G246" t="n">
-        <v>1156.300659179688</v>
+        <v>1156.300537109375</v>
       </c>
       <c r="H246" t="n">
         <v>134.6000061035156</v>
@@ -7598,7 +7598,7 @@
         <v>67.05000305175781</v>
       </c>
       <c r="G247" t="n">
-        <v>1156.187255859375</v>
+        <v>1156.187133789062</v>
       </c>
       <c r="H247" t="n">
         <v>136.5</v>
@@ -7656,13 +7656,13 @@
         <v>66.09999847412109</v>
       </c>
       <c r="G249" t="n">
-        <v>1157.436767578125</v>
+        <v>1157.436645507812</v>
       </c>
       <c r="H249" t="n">
         <v>137.6999969482422</v>
       </c>
       <c r="I249" t="n">
-        <v>930.1112670898438</v>
+        <v>930.1112060546875</v>
       </c>
       <c r="J249" t="n">
         <v>14.35000038146973</v>
@@ -7691,7 +7691,7 @@
         <v>137.8500061035156</v>
       </c>
       <c r="I250" t="n">
-        <v>937.20263671875</v>
+        <v>937.2026977539062</v>
       </c>
       <c r="J250" t="n">
         <v>14.69999980926514</v>
@@ -7720,7 +7720,7 @@
         <v>138.6000061035156</v>
       </c>
       <c r="I251" t="n">
-        <v>926.0238037109375</v>
+        <v>926.0237426757812</v>
       </c>
       <c r="J251" t="n">
         <v>14.80000019073486</v>
@@ -7749,7 +7749,7 @@
         <v>136.4499969482422</v>
       </c>
       <c r="I252" t="n">
-        <v>901.9915771484375</v>
+        <v>901.99169921875</v>
       </c>
       <c r="J252" t="n">
         <v>14.44999980926514</v>
@@ -7807,7 +7807,7 @@
         <v>130.1999969482422</v>
       </c>
       <c r="I254" t="n">
-        <v>892.9302978515625</v>
+        <v>892.9303588867188</v>
       </c>
       <c r="J254" t="n">
         <v>14.44999980926514</v>
@@ -7830,13 +7830,13 @@
         <v>64.75</v>
       </c>
       <c r="G255" t="n">
-        <v>1179.974731445312</v>
+        <v>1179.974609375</v>
       </c>
       <c r="H255" t="n">
         <v>135.0500030517578</v>
       </c>
       <c r="I255" t="n">
-        <v>922.3302612304688</v>
+        <v>922.330322265625</v>
       </c>
       <c r="J255" t="n">
         <v>14.55000019073486</v>
@@ -7894,7 +7894,7 @@
         <v>134.3000030517578</v>
       </c>
       <c r="I257" t="n">
-        <v>902.3363647460938</v>
+        <v>902.3364868164062</v>
       </c>
       <c r="J257" t="n">
         <v>14.25</v>
@@ -7917,7 +7917,7 @@
         <v>63.59999847412109</v>
       </c>
       <c r="G258" t="n">
-        <v>1123.084350585938</v>
+        <v>1123.084228515625</v>
       </c>
       <c r="H258" t="n">
         <v>132.3000030517578</v>
@@ -7946,13 +7946,13 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G259" t="n">
-        <v>1121.266723632812</v>
+        <v>1121.266845703125</v>
       </c>
       <c r="H259" t="n">
         <v>132.6499938964844</v>
       </c>
       <c r="I259" t="n">
-        <v>899.3323364257812</v>
+        <v>899.3323974609375</v>
       </c>
       <c r="J259" t="n">
         <v>14.14999961853027</v>
@@ -7975,13 +7975,13 @@
         <v>65.44999694824219</v>
       </c>
       <c r="G260" t="n">
-        <v>1110.588623046875</v>
+        <v>1110.588500976562</v>
       </c>
       <c r="H260" t="n">
         <v>139.25</v>
       </c>
       <c r="I260" t="n">
-        <v>888.0057373046875</v>
+        <v>888.0056762695312</v>
       </c>
       <c r="J260" t="n">
         <v>14.25</v>
@@ -8010,7 +8010,7 @@
         <v>141.3000030517578</v>
       </c>
       <c r="I261" t="n">
-        <v>883.5242919921875</v>
+        <v>883.5243530273438</v>
       </c>
       <c r="J261" t="n">
         <v>14.14999961853027</v>
@@ -8039,7 +8039,7 @@
         <v>139.5</v>
       </c>
       <c r="I262" t="n">
-        <v>899.6771240234375</v>
+        <v>899.6770629882812</v>
       </c>
       <c r="J262" t="n">
         <v>14</v>
@@ -8062,7 +8062,7 @@
         <v>62.25</v>
       </c>
       <c r="G263" t="n">
-        <v>1123.288818359375</v>
+        <v>1123.288696289062</v>
       </c>
       <c r="H263" t="n">
         <v>137.5</v>
@@ -8120,13 +8120,13 @@
         <v>61.5</v>
       </c>
       <c r="G265" t="n">
-        <v>1104.31787109375</v>
+        <v>1104.317749023438</v>
       </c>
       <c r="H265" t="n">
         <v>133.6999969482422</v>
       </c>
       <c r="I265" t="n">
-        <v>892.0438842773438</v>
+        <v>892.0440063476562</v>
       </c>
       <c r="J265" t="n">
         <v>13.19999980926514</v>
@@ -8155,7 +8155,7 @@
         <v>132.1000061035156</v>
       </c>
       <c r="I266" t="n">
-        <v>882.8841552734375</v>
+        <v>882.8842163085938</v>
       </c>
       <c r="J266" t="n">
         <v>13.19999980926514</v>
@@ -8213,7 +8213,7 @@
         <v>121.9000015258789</v>
       </c>
       <c r="I268" t="n">
-        <v>835.4601440429688</v>
+        <v>835.460205078125</v>
       </c>
       <c r="J268" t="n">
         <v>12.64999961853027</v>
@@ -8265,7 +8265,7 @@
         <v>61.54999923706055</v>
       </c>
       <c r="G270" t="n">
-        <v>1069.579223632812</v>
+        <v>1069.579345703125</v>
       </c>
       <c r="H270" t="n">
         <v>125.0999984741211</v>
@@ -8329,7 +8329,7 @@
         <v>121.3000030517578</v>
       </c>
       <c r="I272" t="n">
-        <v>828.8119506835938</v>
+        <v>828.8118896484375</v>
       </c>
       <c r="J272" t="n">
         <v>11.94999980926514</v>
@@ -8381,7 +8381,7 @@
         <v>59.70000076293945</v>
       </c>
       <c r="G274" t="n">
-        <v>1050.312866210938</v>
+        <v>1050.312744140625</v>
       </c>
       <c r="H274" t="n">
         <v>124.4499969482422</v>
@@ -8416,7 +8416,7 @@
         <v>123.25</v>
       </c>
       <c r="I275" t="n">
-        <v>819.7999267578125</v>
+        <v>819.7998657226562</v>
       </c>
       <c r="J275" t="n">
         <v>11.64999961853027</v>
@@ -8445,7 +8445,7 @@
         <v>123.5500030517578</v>
       </c>
       <c r="I276" t="n">
-        <v>842.8471069335938</v>
+        <v>842.8470458984375</v>
       </c>
       <c r="J276" t="n">
         <v>11.69999980926514</v>
@@ -8474,7 +8474,7 @@
         <v>127.3000030517578</v>
       </c>
       <c r="I277" t="n">
-        <v>831.4219970703125</v>
+        <v>831.4220581054688</v>
       </c>
       <c r="J277" t="n">
         <v>11.69999980926514</v>
@@ -8584,13 +8584,13 @@
         <v>60.25</v>
       </c>
       <c r="G281" t="n">
-        <v>1105.067504882812</v>
+        <v>1105.067626953125</v>
       </c>
       <c r="H281" t="n">
         <v>128.4499969482422</v>
       </c>
       <c r="I281" t="n">
-        <v>837.183837890625</v>
+        <v>837.1837768554688</v>
       </c>
       <c r="J281" t="n">
         <v>11.10000038146973</v>
@@ -8619,7 +8619,7 @@
         <v>129.5500030517578</v>
       </c>
       <c r="I282" t="n">
-        <v>852.2531127929688</v>
+        <v>852.2530517578125</v>
       </c>
       <c r="J282" t="n">
         <v>11.05000019073486</v>
@@ -8700,7 +8700,7 @@
         <v>60.40000152587891</v>
       </c>
       <c r="G285" t="n">
-        <v>1106.044555664062</v>
+        <v>1106.044677734375</v>
       </c>
       <c r="H285" t="n">
         <v>120.8000030517578</v>
@@ -8735,7 +8735,7 @@
         <v>118.5500030517578</v>
       </c>
       <c r="I286" t="n">
-        <v>818.1256103515625</v>
+        <v>818.1255493164062</v>
       </c>
       <c r="J286" t="n">
         <v>10.39999961853027</v>
@@ -8758,7 +8758,7 @@
         <v>59.04999923706055</v>
       </c>
       <c r="G287" t="n">
-        <v>1075.781860351562</v>
+        <v>1075.78173828125</v>
       </c>
       <c r="H287" t="n">
         <v>115.8000030517578</v>
@@ -8787,7 +8787,7 @@
         <v>58.5</v>
       </c>
       <c r="G288" t="n">
-        <v>1083.14306640625</v>
+        <v>1083.142944335938</v>
       </c>
       <c r="H288" t="n">
         <v>126.9499969482422</v>
@@ -8816,7 +8816,7 @@
         <v>57.34999847412109</v>
       </c>
       <c r="G289" t="n">
-        <v>1075.940673828125</v>
+        <v>1075.940795898438</v>
       </c>
       <c r="H289" t="n">
         <v>127.75</v>
@@ -8851,7 +8851,7 @@
         <v>130.6999969482422</v>
       </c>
       <c r="I290" t="n">
-        <v>789.8582763671875</v>
+        <v>789.8583374023438</v>
       </c>
       <c r="J290" t="n">
         <v>9.800000190734863</v>
@@ -8874,7 +8874,7 @@
         <v>58.90000152587891</v>
       </c>
       <c r="G291" t="n">
-        <v>1065.057861328125</v>
+        <v>1065.057983398438</v>
       </c>
       <c r="H291" t="n">
         <v>135.6999969482422</v>
@@ -8938,7 +8938,7 @@
         <v>143.25</v>
       </c>
       <c r="I293" t="n">
-        <v>841.07421875</v>
+        <v>841.0742797851562</v>
       </c>
       <c r="J293" t="n">
         <v>10.69999980926514</v>
@@ -9025,7 +9025,7 @@
         <v>146.3500061035156</v>
       </c>
       <c r="I296" t="n">
-        <v>854.5184326171875</v>
+        <v>854.5183715820312</v>
       </c>
       <c r="J296" t="n">
         <v>11.19999980926514</v>
@@ -9077,7 +9077,7 @@
         <v>55.40000152587891</v>
       </c>
       <c r="G298" t="n">
-        <v>1038.06689453125</v>
+        <v>1038.067016601562</v>
       </c>
       <c r="H298" t="n">
         <v>139.6499938964844</v>
@@ -9106,7 +9106,7 @@
         <v>53.70000076293945</v>
       </c>
       <c r="G299" t="n">
-        <v>1034.182006835938</v>
+        <v>1034.181884765625</v>
       </c>
       <c r="H299" t="n">
         <v>144.3000030517578</v>
@@ -9199,7 +9199,7 @@
         <v>148.6499938964844</v>
       </c>
       <c r="I302" t="n">
-        <v>778.8271484375</v>
+        <v>778.8272094726562</v>
       </c>
       <c r="J302" t="n">
         <v>10.69999980926514</v>
@@ -9222,7 +9222,7 @@
         <v>59.20000076293945</v>
       </c>
       <c r="G303" t="n">
-        <v>1000.238464355469</v>
+        <v>1000.238525390625</v>
       </c>
       <c r="H303" t="n">
         <v>148.0500030517578</v>
@@ -9251,7 +9251,7 @@
         <v>59.59999847412109</v>
       </c>
       <c r="G304" t="n">
-        <v>1031.341918945312</v>
+        <v>1031.341796875</v>
       </c>
       <c r="H304" t="n">
         <v>146.8500061035156</v>
@@ -9315,7 +9315,7 @@
         <v>148.1999969482422</v>
       </c>
       <c r="I306" t="n">
-        <v>773.0160522460938</v>
+        <v>773.01611328125</v>
       </c>
       <c r="J306" t="n">
         <v>9.949999809265137</v>
@@ -9338,13 +9338,13 @@
         <v>52.25</v>
       </c>
       <c r="G307" t="n">
-        <v>1001.169921875</v>
+        <v>1001.169982910156</v>
       </c>
       <c r="H307" t="n">
         <v>143.1000061035156</v>
       </c>
       <c r="I307" t="n">
-        <v>753.7608032226562</v>
+        <v>753.7608642578125</v>
       </c>
       <c r="J307" t="n">
         <v>9.850000381469727</v>
@@ -9373,7 +9373,7 @@
         <v>142.1999969482422</v>
       </c>
       <c r="I308" t="n">
-        <v>736.9679565429688</v>
+        <v>736.968017578125</v>
       </c>
       <c r="J308" t="n">
         <v>9.399999618530273</v>
@@ -9396,7 +9396,7 @@
         <v>52.34999847412109</v>
       </c>
       <c r="G309" t="n">
-        <v>1021.481567382812</v>
+        <v>1021.481506347656</v>
       </c>
       <c r="H309" t="n">
         <v>137.5</v>
@@ -9431,7 +9431,7 @@
         <v>141.5500030517578</v>
       </c>
       <c r="I310" t="n">
-        <v>763.905517578125</v>
+        <v>763.9055786132812</v>
       </c>
       <c r="J310" t="n">
         <v>9.800000190734863</v>
@@ -9454,7 +9454,7 @@
         <v>54.25</v>
       </c>
       <c r="G311" t="n">
-        <v>1059.218994140625</v>
+        <v>1059.219116210938</v>
       </c>
       <c r="H311" t="n">
         <v>144.25</v>
@@ -9489,7 +9489,7 @@
         <v>146.3999938964844</v>
       </c>
       <c r="I312" t="n">
-        <v>785.7708129882812</v>
+        <v>785.7708740234375</v>
       </c>
       <c r="J312" t="n">
         <v>10.39999961853027</v>
@@ -9547,7 +9547,7 @@
         <v>151.3999938964844</v>
       </c>
       <c r="I314" t="n">
-        <v>792.2220458984375</v>
+        <v>792.2219848632812</v>
       </c>
       <c r="J314" t="n">
         <v>11.14999961853027</v>
@@ -9628,13 +9628,13 @@
         <v>55</v>
       </c>
       <c r="G317" t="n">
-        <v>1066.3076171875</v>
+        <v>1066.307495117188</v>
       </c>
       <c r="H317" t="n">
         <v>155.6999969482422</v>
       </c>
       <c r="I317" t="n">
-        <v>799.6090698242188</v>
+        <v>799.6089477539062</v>
       </c>
       <c r="J317" t="n">
         <v>12.14999961853027</v>
@@ -9663,7 +9663,7 @@
         <v>165.5500030517578</v>
       </c>
       <c r="I318" t="n">
-        <v>838.8582153320312</v>
+        <v>838.858154296875</v>
       </c>
       <c r="J318" t="n">
         <v>12.80000019073486</v>
@@ -9744,7 +9744,7 @@
         <v>55</v>
       </c>
       <c r="G321" t="n">
-        <v>1068.738647460938</v>
+        <v>1068.738525390625</v>
       </c>
       <c r="H321" t="n">
         <v>159.1999969482422</v>
@@ -9860,7 +9860,7 @@
         <v>54.95000076293945</v>
       </c>
       <c r="G325" t="n">
-        <v>1079.666748046875</v>
+        <v>1079.666870117188</v>
       </c>
       <c r="H325" t="n">
         <v>157.8999938964844</v>
@@ -9924,7 +9924,7 @@
         <v>160.6999969482422</v>
       </c>
       <c r="I327" t="n">
-        <v>822.409912109375</v>
+        <v>822.4099731445312</v>
       </c>
       <c r="J327" t="n">
         <v>12.5</v>
@@ -9947,7 +9947,7 @@
         <v>58.04999923706055</v>
       </c>
       <c r="G328" t="n">
-        <v>1099.864624023438</v>
+        <v>1099.864501953125</v>
       </c>
       <c r="H328" t="n">
         <v>157.5500030517578</v>
@@ -10005,7 +10005,7 @@
         <v>58.34999847412109</v>
       </c>
       <c r="G330" t="n">
-        <v>1099.682983398438</v>
+        <v>1099.682861328125</v>
       </c>
       <c r="H330" t="n">
         <v>153.75</v>
@@ -10040,7 +10040,7 @@
         <v>154.5500030517578</v>
       </c>
       <c r="I331" t="n">
-        <v>882.3917846679688</v>
+        <v>882.3917236328125</v>
       </c>
       <c r="J331" t="n">
         <v>12.19999980926514</v>
@@ -10063,13 +10063,13 @@
         <v>57.5</v>
       </c>
       <c r="G332" t="n">
-        <v>1109.520751953125</v>
+        <v>1109.520629882812</v>
       </c>
       <c r="H332" t="n">
         <v>153.6000061035156</v>
       </c>
       <c r="I332" t="n">
-        <v>868.258056640625</v>
+        <v>868.2579956054688</v>
       </c>
       <c r="J332" t="n">
         <v>12.39999961853027</v>
@@ -10121,13 +10121,13 @@
         <v>56.25</v>
       </c>
       <c r="G334" t="n">
-        <v>1126.696899414062</v>
+        <v>1126.69677734375</v>
       </c>
       <c r="H334" t="n">
         <v>150.3000030517578</v>
       </c>
       <c r="I334" t="n">
-        <v>860.8711547851562</v>
+        <v>860.8712158203125</v>
       </c>
       <c r="J334" t="n">
         <v>12</v>
@@ -10156,7 +10156,7 @@
         <v>148.8000030517578</v>
       </c>
       <c r="I335" t="n">
-        <v>873.0349731445312</v>
+        <v>873.0350341796875</v>
       </c>
       <c r="J335" t="n">
         <v>11.89999961853027</v>
@@ -10179,7 +10179,7 @@
         <v>58.59999847412109</v>
       </c>
       <c r="G336" t="n">
-        <v>1127.037719726562</v>
+        <v>1127.03759765625</v>
       </c>
       <c r="H336" t="n">
         <v>147.8500061035156</v>
@@ -10208,13 +10208,13 @@
         <v>58.09999847412109</v>
       </c>
       <c r="G337" t="n">
-        <v>1128.877807617188</v>
+        <v>1128.8779296875</v>
       </c>
       <c r="H337" t="n">
         <v>146.6000061035156</v>
       </c>
       <c r="I337" t="n">
-        <v>866.1405639648438</v>
+        <v>866.1405029296875</v>
       </c>
       <c r="J337" t="n">
         <v>11.80000019073486</v>
@@ -10266,13 +10266,13 @@
         <v>59.54999923706055</v>
       </c>
       <c r="G339" t="n">
-        <v>1114.996215820312</v>
+        <v>1114.99609375</v>
       </c>
       <c r="H339" t="n">
         <v>140.8999938964844</v>
       </c>
       <c r="I339" t="n">
-        <v>886.9716186523438</v>
+        <v>886.9715576171875</v>
       </c>
       <c r="J339" t="n">
         <v>11.69999980926514</v>
@@ -10330,7 +10330,7 @@
         <v>135.8999938964844</v>
       </c>
       <c r="I341" t="n">
-        <v>875.1525268554688</v>
+        <v>875.1524658203125</v>
       </c>
       <c r="J341" t="n">
         <v>11.39999961853027</v>
@@ -10353,7 +10353,7 @@
         <v>58.5</v>
       </c>
       <c r="G342" t="n">
-        <v>1109.611450195312</v>
+        <v>1109.611328125</v>
       </c>
       <c r="H342" t="n">
         <v>137.4499969482422</v>
@@ -10417,7 +10417,7 @@
         <v>139.6499938964844</v>
       </c>
       <c r="I344" t="n">
-        <v>899.4308471679688</v>
+        <v>899.430908203125</v>
       </c>
       <c r="J344" t="n">
         <v>12.94999980926514</v>
@@ -10440,13 +10440,13 @@
         <v>60.65000152587891</v>
       </c>
       <c r="G345" t="n">
-        <v>1108.838989257812</v>
+        <v>1108.839111328125</v>
       </c>
       <c r="H345" t="n">
         <v>138.6000061035156</v>
       </c>
       <c r="I345" t="n">
-        <v>881.3082885742188</v>
+        <v>881.308349609375</v>
       </c>
       <c r="J345" t="n">
         <v>12.10000038146973</v>
@@ -10469,7 +10469,7 @@
         <v>60.34999847412109</v>
       </c>
       <c r="G346" t="n">
-        <v>1108.70263671875</v>
+        <v>1108.702758789062</v>
       </c>
       <c r="H346" t="n">
         <v>138.8999938964844</v>
@@ -10504,7 +10504,7 @@
         <v>138</v>
       </c>
       <c r="I347" t="n">
-        <v>887.0208740234375</v>
+        <v>887.0208129882812</v>
       </c>
       <c r="J347" t="n">
         <v>13.05000019073486</v>
@@ -10533,7 +10533,7 @@
         <v>139.6499938964844</v>
       </c>
       <c r="I348" t="n">
-        <v>897.3624267578125</v>
+        <v>897.3624877929688</v>
       </c>
       <c r="J348" t="n">
         <v>13.30000019073486</v>
@@ -10556,13 +10556,13 @@
         <v>61.25</v>
       </c>
       <c r="G349" t="n">
-        <v>1145.054321289062</v>
+        <v>1145.054443359375</v>
       </c>
       <c r="H349" t="n">
         <v>138.6000061035156</v>
       </c>
       <c r="I349" t="n">
-        <v>902.0901489257812</v>
+        <v>902.0902099609375</v>
       </c>
       <c r="J349" t="n">
         <v>12.94999980926514</v>
@@ -10620,7 +10620,7 @@
         <v>133.9499969482422</v>
       </c>
       <c r="I351" t="n">
-        <v>904.7001953125</v>
+        <v>904.7001342773438</v>
       </c>
       <c r="J351" t="n">
         <v>12.94999980926514</v>
@@ -10649,7 +10649,7 @@
         <v>134.6000061035156</v>
       </c>
       <c r="I352" t="n">
-        <v>931.1946411132812</v>
+        <v>931.1947021484375</v>
       </c>
       <c r="J352" t="n">
         <v>13.14999961853027</v>
@@ -10736,7 +10736,7 @@
         <v>136.0500030517578</v>
       </c>
       <c r="I355" t="n">
-        <v>942.6196899414062</v>
+        <v>942.61962890625</v>
       </c>
       <c r="J355" t="n">
         <v>14.75</v>
@@ -10759,13 +10759,13 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G356" t="n">
-        <v>1135.830078125</v>
+        <v>1135.830200195312</v>
       </c>
       <c r="H356" t="n">
         <v>137.0500030517578</v>
       </c>
       <c r="I356" t="n">
-        <v>935.3804931640625</v>
+        <v>935.3805541992188</v>
       </c>
       <c r="J356" t="n">
         <v>14.05000019073486</v>
@@ -10852,7 +10852,7 @@
         <v>143.8500061035156</v>
       </c>
       <c r="I359" t="n">
-        <v>949.0528564453125</v>
+        <v>949.0529174804688</v>
       </c>
       <c r="J359" t="n">
         <v>16.04999923706055</v>
@@ -10991,7 +10991,7 @@
         <v>66.15000152587891</v>
       </c>
       <c r="G364" t="n">
-        <v>1161.935302734375</v>
+        <v>1161.935180664062</v>
       </c>
       <c r="H364" t="n">
         <v>146.5</v>
@@ -11020,13 +11020,13 @@
         <v>65.75</v>
       </c>
       <c r="G365" t="n">
-        <v>1165.206909179688</v>
+        <v>1165.206787109375</v>
       </c>
       <c r="H365" t="n">
         <v>147.75</v>
       </c>
       <c r="I365" t="n">
-        <v>959.8780517578125</v>
+        <v>959.8781127929688</v>
       </c>
       <c r="J365" t="n">
         <v>15</v>
@@ -11055,7 +11055,7 @@
         <v>145.1499938964844</v>
       </c>
       <c r="I366" t="n">
-        <v>939.5128784179688</v>
+        <v>939.512939453125</v>
       </c>
       <c r="J366" t="n">
         <v>14.75</v>
@@ -11142,7 +11142,7 @@
         <v>141.25</v>
       </c>
       <c r="I369" t="n">
-        <v>933.630859375</v>
+        <v>933.6307983398438</v>
       </c>
       <c r="J369" t="n">
         <v>13.85000038146973</v>
@@ -11200,7 +11200,7 @@
         <v>138.25</v>
       </c>
       <c r="I371" t="n">
-        <v>942.6764526367188</v>
+        <v>942.6763916015625</v>
       </c>
       <c r="J371" t="n">
         <v>14.05000019073486</v>
@@ -11258,7 +11258,7 @@
         <v>137.1000061035156</v>
       </c>
       <c r="I373" t="n">
-        <v>939.61181640625</v>
+        <v>939.6118774414062</v>
       </c>
       <c r="J373" t="n">
         <v>14.64999961853027</v>
@@ -11281,13 +11281,13 @@
         <v>62.54999923706055</v>
       </c>
       <c r="G374" t="n">
-        <v>1174.385620117188</v>
+        <v>1174.3857421875</v>
       </c>
       <c r="H374" t="n">
         <v>138.5</v>
       </c>
       <c r="I374" t="n">
-        <v>944.50537109375</v>
+        <v>944.5054321289062</v>
       </c>
       <c r="J374" t="n">
         <v>14.35000038146973</v>
@@ -11403,7 +11403,7 @@
         <v>136.8000030517578</v>
       </c>
       <c r="I378" t="n">
-        <v>948.6080322265625</v>
+        <v>948.6080932617188</v>
       </c>
       <c r="J378" t="n">
         <v>15.35000038146973</v>
@@ -11461,7 +11461,7 @@
         <v>136.4499969482422</v>
       </c>
       <c r="I380" t="n">
-        <v>929.0338745117188</v>
+        <v>929.0338134765625</v>
       </c>
       <c r="J380" t="n">
         <v>15.19999980926514</v>
@@ -11519,7 +11519,7 @@
         <v>135</v>
       </c>
       <c r="I382" t="n">
-        <v>963.9312744140625</v>
+        <v>963.9312133789062</v>
       </c>
       <c r="J382" t="n">
         <v>15.25</v>
@@ -11542,7 +11542,7 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G383" t="n">
-        <v>1281.600219726562</v>
+        <v>1281.60009765625</v>
       </c>
       <c r="H383" t="n">
         <v>141.6999969482422</v>
@@ -11577,7 +11577,7 @@
         <v>154.8500061035156</v>
       </c>
       <c r="I384" t="n">
-        <v>954.7868041992188</v>
+        <v>954.7867431640625</v>
       </c>
       <c r="J384" t="n">
         <v>15.64999961853027</v>
@@ -11600,7 +11600,7 @@
         <v>59.70000076293945</v>
       </c>
       <c r="G385" t="n">
-        <v>1289.760620117188</v>
+        <v>1289.760498046875</v>
       </c>
       <c r="H385" t="n">
         <v>162.3999938964844</v>
@@ -11635,7 +11635,7 @@
         <v>163.0500030517578</v>
       </c>
       <c r="I386" t="n">
-        <v>951.0795288085938</v>
+        <v>951.0794677734375</v>
       </c>
       <c r="J386" t="n">
         <v>15.80000019073486</v>
@@ -11658,7 +11658,7 @@
         <v>58.25</v>
       </c>
       <c r="G387" t="n">
-        <v>1224.554931640625</v>
+        <v>1224.554809570312</v>
       </c>
       <c r="H387" t="n">
         <v>162.6000061035156</v>
@@ -11716,7 +11716,7 @@
         <v>58.29999923706055</v>
       </c>
       <c r="G389" t="n">
-        <v>1243.65625</v>
+        <v>1243.656127929688</v>
       </c>
       <c r="H389" t="n">
         <v>170.9499969482422</v>
@@ -11745,7 +11745,7 @@
         <v>57.45000076293945</v>
       </c>
       <c r="G390" t="n">
-        <v>1232.087158203125</v>
+        <v>1232.087036132812</v>
       </c>
       <c r="H390" t="n">
         <v>178.6000061035156</v>
@@ -11774,13 +11774,13 @@
         <v>58.45000076293945</v>
       </c>
       <c r="G391" t="n">
-        <v>1244.468505859375</v>
+        <v>1244.468627929688</v>
       </c>
       <c r="H391" t="n">
         <v>184.8500061035156</v>
       </c>
       <c r="I391" t="n">
-        <v>947.7183227539062</v>
+        <v>947.7183837890625</v>
       </c>
       <c r="J391" t="n">
         <v>16.10000038146973</v>
@@ -11861,7 +11861,7 @@
         <v>58.15000152587891</v>
       </c>
       <c r="G394" t="n">
-        <v>1224.038208007812</v>
+        <v>1224.0380859375</v>
       </c>
       <c r="H394" t="n">
         <v>181.1999969482422</v>
@@ -11925,7 +11925,7 @@
         <v>199.1499938964844</v>
       </c>
       <c r="I396" t="n">
-        <v>968.0339965820312</v>
+        <v>968.033935546875</v>
       </c>
       <c r="J396" t="n">
         <v>19.04999923706055</v>
@@ -11977,7 +11977,7 @@
         <v>60.20000076293945</v>
       </c>
       <c r="G398" t="n">
-        <v>1235.016357421875</v>
+        <v>1235.016235351562</v>
       </c>
       <c r="H398" t="n">
         <v>194.6999969482422</v>
@@ -12012,7 +12012,7 @@
         <v>191.4499969482422</v>
       </c>
       <c r="I399" t="n">
-        <v>976.634765625</v>
+        <v>976.6348266601562</v>
       </c>
       <c r="J399" t="n">
         <v>18.25</v>
@@ -12070,7 +12070,7 @@
         <v>170</v>
       </c>
       <c r="I401" t="n">
-        <v>973.8666381835938</v>
+        <v>973.86669921875</v>
       </c>
       <c r="J401" t="n">
         <v>17.39999961853027</v>
@@ -12206,7 +12206,7 @@
         <v>16.75</v>
       </c>
       <c r="E406" t="n">
-        <v>247.9318389892578</v>
+        <v>247.9318237304688</v>
       </c>
       <c r="F406" t="n">
         <v>63.70000076293945</v>
@@ -12218,7 +12218,7 @@
         <v>162.3500061035156</v>
       </c>
       <c r="I406" t="n">
-        <v>1040.003662109375</v>
+        <v>1040.003784179688</v>
       </c>
       <c r="J406" t="n">
         <v>16.35000038146973</v>
@@ -12270,7 +12270,7 @@
         <v>16.89999961853027</v>
       </c>
       <c r="E408" t="n">
-        <v>223.7761535644531</v>
+        <v>223.7761688232422</v>
       </c>
       <c r="F408" t="n">
         <v>67.84999847412109</v>
@@ -12302,7 +12302,7 @@
         <v>16.70000076293945</v>
       </c>
       <c r="E409" t="n">
-        <v>212.6197204589844</v>
+        <v>212.6197357177734</v>
       </c>
       <c r="F409" t="n">
         <v>66.94999694824219</v>
@@ -12314,7 +12314,7 @@
         <v>177.3000030517578</v>
       </c>
       <c r="I409" t="n">
-        <v>1017.513244628906</v>
+        <v>1017.513305664062</v>
       </c>
       <c r="J409" t="n">
         <v>17.29999923706055</v>
@@ -12334,7 +12334,7 @@
         <v>16.64999961853027</v>
       </c>
       <c r="E410" t="n">
-        <v>213.6656646728516</v>
+        <v>213.6656494140625</v>
       </c>
       <c r="F410" t="n">
         <v>67.5</v>
@@ -12398,7 +12398,7 @@
         <v>16.64999961853027</v>
       </c>
       <c r="E412" t="n">
-        <v>219.3932800292969</v>
+        <v>219.3932952880859</v>
       </c>
       <c r="F412" t="n">
         <v>69.40000152587891</v>
@@ -12462,7 +12462,7 @@
         <v>16.5</v>
       </c>
       <c r="E414" t="n">
-        <v>232.5917358398438</v>
+        <v>232.5917510986328</v>
       </c>
       <c r="F414" t="n">
         <v>68.34999847412109</v>
@@ -12506,7 +12506,7 @@
         <v>186.8999938964844</v>
       </c>
       <c r="I415" t="n">
-        <v>1000.114013671875</v>
+        <v>1000.113952636719</v>
       </c>
       <c r="J415" t="n">
         <v>19</v>
@@ -12634,7 +12634,7 @@
         <v>189.8000030517578</v>
       </c>
       <c r="I419" t="n">
-        <v>1005.304138183594</v>
+        <v>1005.304077148438</v>
       </c>
       <c r="J419" t="n">
         <v>21.20000076293945</v>
@@ -12666,7 +12666,7 @@
         <v>186.5</v>
       </c>
       <c r="I420" t="n">
-        <v>996.7527465820312</v>
+        <v>996.752685546875</v>
       </c>
       <c r="J420" t="n">
         <v>21.14999961853027</v>
@@ -12686,7 +12686,7 @@
         <v>18.60000038146973</v>
       </c>
       <c r="E421" t="n">
-        <v>249.1769866943359</v>
+        <v>249.1769714355469</v>
       </c>
       <c r="F421" t="n">
         <v>70.94999694824219</v>
@@ -12730,7 +12730,7 @@
         <v>173.6999969482422</v>
       </c>
       <c r="I422" t="n">
-        <v>954.5890502929688</v>
+        <v>954.5889892578125</v>
       </c>
       <c r="J422" t="n">
         <v>18.39999961853027</v>
@@ -12750,7 +12750,7 @@
         <v>17.35000038146973</v>
       </c>
       <c r="E423" t="n">
-        <v>239.2656707763672</v>
+        <v>239.2656860351562</v>
       </c>
       <c r="F423" t="n">
         <v>68.55000305175781</v>
@@ -12794,7 +12794,7 @@
         <v>175.3000030517578</v>
       </c>
       <c r="I424" t="n">
-        <v>959.6802978515625</v>
+        <v>959.6802368164062</v>
       </c>
       <c r="J424" t="n">
         <v>18.75</v>
@@ -12922,7 +12922,7 @@
         <v>175.1499938964844</v>
       </c>
       <c r="I428" t="n">
-        <v>941.0453491210938</v>
+        <v>941.0452880859375</v>
       </c>
       <c r="J428" t="n">
         <v>19</v>
@@ -12942,7 +12942,7 @@
         <v>19.14999961853027</v>
       </c>
       <c r="E429" t="n">
-        <v>226.9139251708984</v>
+        <v>226.9139099121094</v>
       </c>
       <c r="F429" t="n">
         <v>68.05000305175781</v>
@@ -13038,7 +13038,7 @@
         <v>19.79999923706055</v>
       </c>
       <c r="E432" t="n">
-        <v>226.4656829833984</v>
+        <v>226.4656677246094</v>
       </c>
       <c r="F432" t="n">
         <v>63.95000076293945</v>
@@ -13050,7 +13050,7 @@
         <v>172.6499938964844</v>
       </c>
       <c r="I432" t="n">
-        <v>956.4180297851562</v>
+        <v>956.41796875</v>
       </c>
       <c r="J432" t="n">
         <v>19.20000076293945</v>
@@ -13114,7 +13114,7 @@
         <v>173.3000030517578</v>
       </c>
       <c r="I434" t="n">
-        <v>951.0795288085938</v>
+        <v>951.0794677734375</v>
       </c>
       <c r="J434" t="n">
         <v>19.25</v>
@@ -13166,7 +13166,7 @@
         <v>20.89999961853027</v>
       </c>
       <c r="E436" t="n">
-        <v>223.7761535644531</v>
+        <v>223.7761688232422</v>
       </c>
       <c r="F436" t="n">
         <v>68.05000305175781</v>
@@ -13198,7 +13198,7 @@
         <v>21.04999923706055</v>
       </c>
       <c r="E437" t="n">
-        <v>224.5232543945312</v>
+        <v>224.5232391357422</v>
       </c>
       <c r="F437" t="n">
         <v>72.84999847412109</v>
@@ -13210,7 +13210,7 @@
         <v>172.1999969482422</v>
       </c>
       <c r="I437" t="n">
-        <v>968.7260131835938</v>
+        <v>968.72607421875</v>
       </c>
       <c r="J437" t="n">
         <v>18.89999961853027</v>
@@ -13274,7 +13274,7 @@
         <v>171.25</v>
       </c>
       <c r="I439" t="n">
-        <v>943.46728515625</v>
+        <v>943.4673461914062</v>
       </c>
       <c r="J439" t="n">
         <v>17.85000038146973</v>
@@ -13294,7 +13294,7 @@
         <v>19.5</v>
       </c>
       <c r="E440" t="n">
-        <v>219.2936553955078</v>
+        <v>219.2936706542969</v>
       </c>
       <c r="F440" t="n">
         <v>71.65000152587891</v>
@@ -13306,7 +13306,7 @@
         <v>170.8500061035156</v>
       </c>
       <c r="I440" t="n">
-        <v>970.3078002929688</v>
+        <v>970.3077392578125</v>
       </c>
       <c r="J440" t="n">
         <v>17.79999923706055</v>
@@ -13370,7 +13370,7 @@
         <v>169.3500061035156</v>
       </c>
       <c r="I442" t="n">
-        <v>980.04541015625</v>
+        <v>980.0453491210938</v>
       </c>
       <c r="J442" t="n">
         <v>18</v>
@@ -13390,7 +13390,7 @@
         <v>20.29999923706055</v>
       </c>
       <c r="E443" t="n">
-        <v>223.6765747070312</v>
+        <v>223.6765594482422</v>
       </c>
       <c r="F443" t="n">
         <v>78.75</v>
@@ -13434,7 +13434,7 @@
         <v>170.75</v>
       </c>
       <c r="I444" t="n">
-        <v>1058.243408203125</v>
+        <v>1058.243286132812</v>
       </c>
       <c r="J444" t="n">
         <v>18.39999961853027</v>
@@ -13486,7 +13486,7 @@
         <v>19.70000076293945</v>
       </c>
       <c r="E446" t="n">
-        <v>215.1598205566406</v>
+        <v>215.1598052978516</v>
       </c>
       <c r="F446" t="n">
         <v>77.94999694824219</v>
@@ -13518,7 +13518,7 @@
         <v>19.89999961853027</v>
       </c>
       <c r="E447" t="n">
-        <v>213.3668060302734</v>
+        <v>213.3668212890625</v>
       </c>
       <c r="F447" t="n">
         <v>77.84999847412109</v>
@@ -13550,7 +13550,7 @@
         <v>19.39999961853027</v>
       </c>
       <c r="E448" t="n">
-        <v>213.3668060302734</v>
+        <v>213.3668212890625</v>
       </c>
       <c r="F448" t="n">
         <v>76.80000305175781</v>
@@ -13594,7 +13594,7 @@
         <v>169.75</v>
       </c>
       <c r="I449" t="n">
-        <v>995.3192138671875</v>
+        <v>995.3192749023438</v>
       </c>
       <c r="J449" t="n">
         <v>16.70000076293945</v>
@@ -13626,7 +13626,7 @@
         <v>162.3000030517578</v>
       </c>
       <c r="I450" t="n">
-        <v>1000.262268066406</v>
+        <v>1000.26220703125</v>
       </c>
       <c r="J450" t="n">
         <v>16.29999923706055</v>
@@ -13678,7 +13678,7 @@
         <v>18.39999961853027</v>
       </c>
       <c r="E452" t="n">
-        <v>222.0329742431641</v>
+        <v>222.032958984375</v>
       </c>
       <c r="F452" t="n">
         <v>68.75</v>
@@ -13754,7 +13754,7 @@
         <v>169.25</v>
       </c>
       <c r="I454" t="n">
-        <v>993.984619140625</v>
+        <v>993.9846801757812</v>
       </c>
       <c r="J454" t="n">
         <v>17.10000038146973</v>
@@ -13786,7 +13786,7 @@
         <v>172.25</v>
       </c>
       <c r="I455" t="n">
-        <v>979.5511474609375</v>
+        <v>979.5510864257812</v>
       </c>
       <c r="J455" t="n">
         <v>17.39999961853027</v>
@@ -13806,7 +13806,7 @@
         <v>18.04999923706055</v>
       </c>
       <c r="E456" t="n">
-        <v>216.5045623779297</v>
+        <v>216.5045776367188</v>
       </c>
       <c r="F456" t="n">
         <v>67.59999847412109</v>
@@ -13818,7 +13818,7 @@
         <v>176.9499969482422</v>
       </c>
       <c r="I456" t="n">
-        <v>988.6956787109375</v>
+        <v>988.6956176757812</v>
       </c>
       <c r="J456" t="n">
         <v>18.25</v>
@@ -13978,7 +13978,7 @@
         <v>178.1000061035156</v>
       </c>
       <c r="I461" t="n">
-        <v>1038.175048828125</v>
+        <v>1038.174926757812</v>
       </c>
       <c r="J461" t="n">
         <v>21.20000076293945</v>
@@ -14010,7 +14010,7 @@
         <v>177.3000030517578</v>
       </c>
       <c r="I462" t="n">
-        <v>1031.057006835938</v>
+        <v>1031.056884765625</v>
       </c>
       <c r="J462" t="n">
         <v>20.5</v>
@@ -14030,7 +14030,7 @@
         <v>19.10000038146973</v>
       </c>
       <c r="E463" t="n">
-        <v>223.8757781982422</v>
+        <v>223.8757934570312</v>
       </c>
       <c r="F463" t="n">
         <v>76</v>
@@ -14042,7 +14042,7 @@
         <v>181.1499938964844</v>
       </c>
       <c r="I463" t="n">
-        <v>1030.216552734375</v>
+        <v>1030.216674804688</v>
       </c>
       <c r="J463" t="n">
         <v>22.5</v>
@@ -14074,7 +14074,7 @@
         <v>181.75</v>
       </c>
       <c r="I464" t="n">
-        <v>1070.156127929688</v>
+        <v>1070.156005859375</v>
       </c>
       <c r="J464" t="n">
         <v>22.29999923706055</v>
@@ -14202,7 +14202,7 @@
         <v>179.5500030517578</v>
       </c>
       <c r="I468" t="n">
-        <v>1109.156127929688</v>
+        <v>1109.15625</v>
       </c>
       <c r="J468" t="n">
         <v>21.35000038146973</v>
@@ -14254,7 +14254,7 @@
         <v>20.14999961853027</v>
       </c>
       <c r="E470" t="n">
-        <v>220.3893890380859</v>
+        <v>220.389404296875</v>
       </c>
       <c r="F470" t="n">
         <v>82.40000152587891</v>
@@ -14330,7 +14330,7 @@
         <v>177.8999938964844</v>
       </c>
       <c r="I472" t="n">
-        <v>1087.851928710938</v>
+        <v>1087.851806640625</v>
       </c>
       <c r="J472" t="n">
         <v>20.89999961853027</v>
@@ -14426,7 +14426,7 @@
         <v>194.0500030517578</v>
       </c>
       <c r="I475" t="n">
-        <v>1081.030517578125</v>
+        <v>1081.030639648438</v>
       </c>
       <c r="J475" t="n">
         <v>20.85000038146973</v>
@@ -14586,7 +14586,7 @@
         <v>214.75</v>
       </c>
       <c r="I480" t="n">
-        <v>1130.9052734375</v>
+        <v>1130.905151367188</v>
       </c>
       <c r="J480" t="n">
         <v>23.95000076293945</v>
@@ -14618,7 +14618,7 @@
         <v>218.6999969482422</v>
       </c>
       <c r="I481" t="n">
-        <v>1148.106811523438</v>
+        <v>1148.10693359375</v>
       </c>
       <c r="J481" t="n">
         <v>24.5</v>
@@ -14638,7 +14638,7 @@
         <v>20.54999923706055</v>
       </c>
       <c r="E482" t="n">
-        <v>239.6143341064453</v>
+        <v>239.6143188476562</v>
       </c>
       <c r="F482" t="n">
         <v>86.65000152587891</v>
@@ -14650,7 +14650,7 @@
         <v>211.6499938964844</v>
       </c>
       <c r="I482" t="n">
-        <v>1134.167602539062</v>
+        <v>1134.167724609375</v>
       </c>
       <c r="J482" t="n">
         <v>23.20000076293945</v>
@@ -14714,7 +14714,7 @@
         <v>214.6000061035156</v>
       </c>
       <c r="I484" t="n">
-        <v>1157.74560546875</v>
+        <v>1157.745727539062</v>
       </c>
       <c r="J484" t="n">
         <v>23.85000038146973</v>
@@ -14734,7 +14734,7 @@
         <v>20.35000038146973</v>
       </c>
       <c r="E485" t="n">
-        <v>236.7256011962891</v>
+        <v>236.7255859375</v>
       </c>
       <c r="F485" t="n">
         <v>85.90000152587891</v>
@@ -14746,7 +14746,7 @@
         <v>209.75</v>
       </c>
       <c r="I485" t="n">
-        <v>1167.9775390625</v>
+        <v>1167.977661132812</v>
       </c>
       <c r="J485" t="n">
         <v>23.60000038146973</v>
@@ -14766,7 +14766,7 @@
         <v>21.5</v>
       </c>
       <c r="E486" t="n">
-        <v>239.2158813476562</v>
+        <v>239.2158660888672</v>
       </c>
       <c r="F486" t="n">
         <v>86.19999694824219</v>
@@ -14842,7 +14842,7 @@
         <v>190.8000030517578</v>
       </c>
       <c r="I488" t="n">
-        <v>1227.29345703125</v>
+        <v>1227.293579101562</v>
       </c>
       <c r="J488" t="n">
         <v>21.39999961853027</v>
@@ -14862,7 +14862,7 @@
         <v>21.64999961853027</v>
       </c>
       <c r="E489" t="n">
-        <v>237.0742340087891</v>
+        <v>237.0742492675781</v>
       </c>
       <c r="F489" t="n">
         <v>85.90000152587891</v>
@@ -14894,7 +14894,7 @@
         <v>22.04999923706055</v>
       </c>
       <c r="E490" t="n">
-        <v>235.8291168212891</v>
+        <v>235.8291015625</v>
       </c>
       <c r="F490" t="n">
         <v>86.09999847412109</v>
@@ -14938,7 +14938,7 @@
         <v>196.75</v>
       </c>
       <c r="I491" t="n">
-        <v>1333.221557617188</v>
+        <v>1333.2216796875</v>
       </c>
       <c r="J491" t="n">
         <v>22.60000038146973</v>
@@ -14958,7 +14958,7 @@
         <v>21.64999961853027</v>
       </c>
       <c r="E492" t="n">
-        <v>233.0898132324219</v>
+        <v>233.0897979736328</v>
       </c>
       <c r="F492" t="n">
         <v>88.90000152587891</v>
@@ -15022,7 +15022,7 @@
         <v>21.20000076293945</v>
       </c>
       <c r="E494" t="n">
-        <v>232.0438690185547</v>
+        <v>232.0438842773438</v>
       </c>
       <c r="F494" t="n">
         <v>87.34999847412109</v>
@@ -15214,7 +15214,7 @@
         <v>24.79999923706055</v>
       </c>
       <c r="E500" t="n">
-        <v>241.4571075439453</v>
+        <v>241.4571228027344</v>
       </c>
       <c r="F500" t="n">
         <v>100.5500030517578</v>
@@ -15246,7 +15246,7 @@
         <v>24.10000038146973</v>
       </c>
       <c r="E501" t="n">
-        <v>241.2080993652344</v>
+        <v>241.2080841064453</v>
       </c>
       <c r="F501" t="n">
         <v>99.5</v>
@@ -15258,7 +15258,7 @@
         <v>236.8500061035156</v>
       </c>
       <c r="I501" t="n">
-        <v>1350.423095703125</v>
+        <v>1350.423217773438</v>
       </c>
       <c r="J501" t="n">
         <v>31.29999923706055</v>
@@ -15278,7 +15278,7 @@
         <v>24.89999961853027</v>
       </c>
       <c r="E502" t="n">
-        <v>240.0127563476562</v>
+        <v>240.0127716064453</v>
       </c>
       <c r="F502" t="n">
         <v>119.4000015258789</v>
@@ -15386,7 +15386,7 @@
         <v>232.6499938964844</v>
       </c>
       <c r="I505" t="n">
-        <v>1442.313232421875</v>
+        <v>1442.313110351562</v>
       </c>
       <c r="J505" t="n">
         <v>30.79999923706055</v>
@@ -15418,7 +15418,7 @@
         <v>221.8999938964844</v>
       </c>
       <c r="I506" t="n">
-        <v>1395.750244140625</v>
+        <v>1395.750366210938</v>
       </c>
       <c r="J506" t="n">
         <v>30.04999923706055</v>
@@ -15630,7 +15630,7 @@
         <v>23.85000038146973</v>
       </c>
       <c r="E513" t="n">
-        <v>250.023681640625</v>
+        <v>250.0236663818359</v>
       </c>
       <c r="F513" t="n">
         <v>117</v>
@@ -15706,7 +15706,7 @@
         <v>231.0500030517578</v>
       </c>
       <c r="I515" t="n">
-        <v>1394.317016601562</v>
+        <v>1394.31689453125</v>
       </c>
       <c r="J515" t="n">
         <v>29.79999923706055</v>
@@ -15758,7 +15758,7 @@
         <v>24</v>
       </c>
       <c r="E517" t="n">
-        <v>252.8127899169922</v>
+        <v>252.8127746582031</v>
       </c>
       <c r="F517" t="n">
         <v>113.1500015258789</v>
@@ -15770,7 +15770,7 @@
         <v>221.9499969482422</v>
       </c>
       <c r="I517" t="n">
-        <v>1373.704833984375</v>
+        <v>1373.704711914062</v>
       </c>
       <c r="J517" t="n">
         <v>28.79999923706055</v>
@@ -15790,7 +15790,7 @@
         <v>26</v>
       </c>
       <c r="E518" t="n">
-        <v>287.9754638671875</v>
+        <v>287.9754943847656</v>
       </c>
       <c r="F518" t="n">
         <v>114.4000015258789</v>
@@ -15802,7 +15802,7 @@
         <v>214.5</v>
       </c>
       <c r="I518" t="n">
-        <v>1374.1494140625</v>
+        <v>1374.149536132812</v>
       </c>
       <c r="J518" t="n">
         <v>27.39999961853027</v>
@@ -15950,7 +15950,7 @@
         <v>23.45000076293945</v>
       </c>
       <c r="E523" t="n">
-        <v>270.3941650390625</v>
+        <v>270.3941345214844</v>
       </c>
       <c r="F523" t="n">
         <v>106.25</v>
@@ -15982,7 +15982,7 @@
         <v>23.64999961853027</v>
       </c>
       <c r="E524" t="n">
-        <v>271.6890563964844</v>
+        <v>271.6890869140625</v>
       </c>
       <c r="F524" t="n">
         <v>105.4000015258789</v>
@@ -15994,7 +15994,7 @@
         <v>210.1499938964844</v>
       </c>
       <c r="I524" t="n">
-        <v>1327.586547851562</v>
+        <v>1327.586669921875</v>
       </c>
       <c r="J524" t="n">
         <v>26.04999923706055</v>
@@ -16026,7 +16026,7 @@
         <v>229.1499938964844</v>
       </c>
       <c r="I525" t="n">
-        <v>1340.784301757812</v>
+        <v>1340.784423828125</v>
       </c>
       <c r="J525" t="n">
         <v>26.45000076293945</v>
@@ -16142,7 +16142,7 @@
         <v>24.85000038146973</v>
       </c>
       <c r="E529" t="n">
-        <v>280.6042785644531</v>
+        <v>280.604248046875</v>
       </c>
       <c r="F529" t="n">
         <v>119</v>
@@ -16218,7 +16218,7 @@
         <v>229.4499969482422</v>
       </c>
       <c r="I531" t="n">
-        <v>1427.28662109375</v>
+        <v>1427.286499023438</v>
       </c>
       <c r="J531" t="n">
         <v>25.64999961853027</v>
@@ -16398,7 +16398,7 @@
         <v>22.64999961853027</v>
       </c>
       <c r="E537" t="n">
-        <v>316.6634216308594</v>
+        <v>316.6634521484375</v>
       </c>
       <c r="F537" t="n">
         <v>102.4499969482422</v>
@@ -16462,7 +16462,7 @@
         <v>22</v>
       </c>
       <c r="E539" t="n">
-        <v>320.4486694335938</v>
+        <v>320.4486999511719</v>
       </c>
       <c r="F539" t="n">
         <v>95.25</v>
@@ -16474,7 +16474,7 @@
         <v>226.6999969482422</v>
       </c>
       <c r="I539" t="n">
-        <v>1419.279052734375</v>
+        <v>1419.278930664062</v>
       </c>
       <c r="J539" t="n">
         <v>23.04999923706055</v>
@@ -16538,7 +16538,7 @@
         <v>221.1999969482422</v>
       </c>
       <c r="I541" t="n">
-        <v>1364.313110351562</v>
+        <v>1364.31298828125</v>
       </c>
       <c r="J541" t="n">
         <v>22.54999923706055</v>
@@ -16558,7 +16558,7 @@
         <v>21.25</v>
       </c>
       <c r="E542" t="n">
-        <v>354.2666015625</v>
+        <v>354.2666320800781</v>
       </c>
       <c r="F542" t="n">
         <v>92.05000305175781</v>
@@ -16570,7 +16570,7 @@
         <v>223.6499938964844</v>
       </c>
       <c r="I542" t="n">
-        <v>1328.772827148438</v>
+        <v>1328.77294921875</v>
       </c>
       <c r="J542" t="n">
         <v>22.54999923706055</v>
@@ -16654,7 +16654,7 @@
         <v>20.20000076293945</v>
       </c>
       <c r="E545" t="n">
-        <v>337.033935546875</v>
+        <v>337.0339050292969</v>
       </c>
       <c r="F545" t="n">
         <v>84.65000152587891</v>
@@ -16666,7 +16666,7 @@
         <v>214.25</v>
       </c>
       <c r="I545" t="n">
-        <v>1232.780151367188</v>
+        <v>1232.7802734375</v>
       </c>
       <c r="J545" t="n">
         <v>21.04999923706055</v>
@@ -16698,7 +16698,7 @@
         <v>237.5</v>
       </c>
       <c r="I546" t="n">
-        <v>1219.236328125</v>
+        <v>1219.236450195312</v>
       </c>
       <c r="J546" t="n">
         <v>22.10000038146973</v>
@@ -16750,7 +16750,7 @@
         <v>19.70000076293945</v>
       </c>
       <c r="E548" t="n">
-        <v>351.9257507324219</v>
+        <v>351.9257202148438</v>
       </c>
       <c r="F548" t="n">
         <v>88.15000152587891</v>
@@ -16762,7 +16762,7 @@
         <v>239.8000030517578</v>
       </c>
       <c r="I548" t="n">
-        <v>1193.780029296875</v>
+        <v>1193.780151367188</v>
       </c>
       <c r="J548" t="n">
         <v>22.79999923706055</v>
@@ -16814,7 +16814,7 @@
         <v>19.39999961853027</v>
       </c>
       <c r="E550" t="n">
-        <v>337.382568359375</v>
+        <v>337.3825378417969</v>
       </c>
       <c r="F550" t="n">
         <v>87.05000305175781</v>
@@ -16878,7 +16878,7 @@
         <v>19.85000038146973</v>
       </c>
       <c r="E552" t="n">
-        <v>344.8035888671875</v>
+        <v>344.8035583496094</v>
       </c>
       <c r="F552" t="n">
         <v>90.94999694824219</v>
@@ -16974,7 +16974,7 @@
         <v>21.5</v>
       </c>
       <c r="E555" t="n">
-        <v>355.5615844726562</v>
+        <v>355.5615539550781</v>
       </c>
       <c r="F555" t="n">
         <v>90.40000152587891</v>
@@ -17006,7 +17006,7 @@
         <v>21.5</v>
       </c>
       <c r="E556" t="n">
-        <v>355.7109680175781</v>
+        <v>355.7109985351562</v>
       </c>
       <c r="F556" t="n">
         <v>89.90000152587891</v>
@@ -17038,7 +17038,7 @@
         <v>21.95000076293945</v>
       </c>
       <c r="E557" t="n">
-        <v>355.7109680175781</v>
+        <v>355.7109985351562</v>
       </c>
       <c r="F557" t="n">
         <v>92.40000152587891</v>
@@ -17050,7 +17050,7 @@
         <v>291.7999877929688</v>
       </c>
       <c r="I557" t="n">
-        <v>1334.457397460938</v>
+        <v>1334.457275390625</v>
       </c>
       <c r="J557" t="n">
         <v>31.79999923706055</v>
@@ -17082,7 +17082,7 @@
         <v>295</v>
       </c>
       <c r="I558" t="n">
-        <v>1325.807250976562</v>
+        <v>1325.80712890625</v>
       </c>
       <c r="J558" t="n">
         <v>33.34999847412109</v>
@@ -17102,7 +17102,7 @@
         <v>22.10000038146973</v>
       </c>
       <c r="E559" t="n">
-        <v>371.7483825683594</v>
+        <v>371.7483520507812</v>
       </c>
       <c r="F559" t="n">
         <v>90.84999847412109</v>
@@ -17146,7 +17146,7 @@
         <v>287.6000061035156</v>
       </c>
       <c r="I560" t="n">
-        <v>1300.845092773438</v>
+        <v>1300.844970703125</v>
       </c>
       <c r="J560" t="n">
         <v>31</v>
@@ -17242,7 +17242,7 @@
         <v>197.75</v>
       </c>
       <c r="I563" t="n">
-        <v>1273.362182617188</v>
+        <v>1273.362060546875</v>
       </c>
       <c r="J563" t="n">
         <v>27.35000038146973</v>
@@ -17262,7 +17262,7 @@
         <v>20.75</v>
       </c>
       <c r="E564" t="n">
-        <v>352.921875</v>
+        <v>352.9218444824219</v>
       </c>
       <c r="F564" t="n">
         <v>85.90000152587891</v>
@@ -17306,7 +17306,7 @@
         <v>194.1999969482422</v>
       </c>
       <c r="I565" t="n">
-        <v>1241.380859375</v>
+        <v>1241.380981445312</v>
       </c>
       <c r="J565" t="n">
         <v>27.35000038146973</v>
@@ -17326,7 +17326,7 @@
         <v>22</v>
       </c>
       <c r="E566" t="n">
-        <v>376.9281005859375</v>
+        <v>376.9281311035156</v>
       </c>
       <c r="F566" t="n">
         <v>89.5</v>
@@ -17358,7 +17358,7 @@
         <v>22.10000038146973</v>
       </c>
       <c r="E567" t="n">
-        <v>368.6604309082031</v>
+        <v>368.660400390625</v>
       </c>
       <c r="F567" t="n">
         <v>87.59999847412109</v>
@@ -17390,7 +17390,7 @@
         <v>22.25</v>
       </c>
       <c r="E568" t="n">
-        <v>381.2113952636719</v>
+        <v>381.21142578125</v>
       </c>
       <c r="F568" t="n">
         <v>87.19999694824219</v>
@@ -17422,7 +17422,7 @@
         <v>22.64999961853027</v>
       </c>
       <c r="E569" t="n">
-        <v>386.4409790039062</v>
+        <v>386.4410095214844</v>
       </c>
       <c r="F569" t="n">
         <v>88.05000305175781</v>
@@ -17454,7 +17454,7 @@
         <v>22.75</v>
       </c>
       <c r="E570" t="n">
-        <v>380.3646850585938</v>
+        <v>380.3647155761719</v>
       </c>
       <c r="F570" t="n">
         <v>92.44999694824219</v>
@@ -17466,7 +17466,7 @@
         <v>191.6999969482422</v>
       </c>
       <c r="I570" t="n">
-        <v>1292.491333007812</v>
+        <v>1292.491455078125</v>
       </c>
       <c r="J570" t="n">
         <v>27.60000038146973</v>
@@ -17486,7 +17486,7 @@
         <v>22.35000038146973</v>
       </c>
       <c r="E571" t="n">
-        <v>380.8129577636719</v>
+        <v>380.8129272460938</v>
       </c>
       <c r="F571" t="n">
         <v>92.75</v>
@@ -17498,7 +17498,7 @@
         <v>192.6499938964844</v>
       </c>
       <c r="I571" t="n">
-        <v>1290.761474609375</v>
+        <v>1290.761352539062</v>
       </c>
       <c r="J571" t="n">
         <v>27.5</v>
@@ -17658,7 +17658,7 @@
         <v>176.1999969482422</v>
       </c>
       <c r="I576" t="n">
-        <v>1283.791870117188</v>
+        <v>1283.791748046875</v>
       </c>
       <c r="J576" t="n">
         <v>26.79999923706055</v>
@@ -17678,7 +17678,7 @@
         <v>21.45000076293945</v>
       </c>
       <c r="E577" t="n">
-        <v>368.809814453125</v>
+        <v>368.8098449707031</v>
       </c>
       <c r="F577" t="n">
         <v>80.65000152587891</v>
@@ -17710,7 +17710,7 @@
         <v>21.04999923706055</v>
       </c>
       <c r="E578" t="n">
-        <v>354.8642578125</v>
+        <v>354.8642883300781</v>
       </c>
       <c r="F578" t="n">
         <v>80</v>
@@ -17806,7 +17806,7 @@
         <v>20.79999923706055</v>
       </c>
       <c r="E581" t="n">
-        <v>346.4969482421875</v>
+        <v>346.4969787597656</v>
       </c>
       <c r="F581" t="n">
         <v>78</v>
@@ -17902,7 +17902,7 @@
         <v>20.85000038146973</v>
       </c>
       <c r="E584" t="n">
-        <v>352.4736328125</v>
+        <v>352.4736022949219</v>
       </c>
       <c r="F584" t="n">
         <v>80.5</v>
@@ -17914,7 +17914,7 @@
         <v>171.6000061035156</v>
       </c>
       <c r="I584" t="n">
-        <v>1211.426635742188</v>
+        <v>1211.426513671875</v>
       </c>
       <c r="J584" t="n">
         <v>25.79999923706055</v>
@@ -18030,7 +18030,7 @@
         <v>21.20000076293945</v>
       </c>
       <c r="E588" t="n">
-        <v>356.2588195800781</v>
+        <v>356.2588500976562</v>
       </c>
       <c r="F588" t="n">
         <v>82.25</v>
@@ -18042,7 +18042,7 @@
         <v>167.3500061035156</v>
       </c>
       <c r="I588" t="n">
-        <v>1230.012084960938</v>
+        <v>1230.011962890625</v>
       </c>
       <c r="J588" t="n">
         <v>26.5</v>
@@ -18074,7 +18074,7 @@
         <v>166.0500030517578</v>
       </c>
       <c r="I589" t="n">
-        <v>1219.977905273438</v>
+        <v>1219.97802734375</v>
       </c>
       <c r="J589" t="n">
         <v>26.39999961853027</v>
@@ -18094,7 +18094,7 @@
         <v>21.39999961853027</v>
       </c>
       <c r="E590" t="n">
-        <v>363.9786987304688</v>
+        <v>363.9786682128906</v>
       </c>
       <c r="F590" t="n">
         <v>82.19999694824219</v>
@@ -18190,7 +18190,7 @@
         <v>20.79999923706055</v>
       </c>
       <c r="E593" t="n">
-        <v>347.8417053222656</v>
+        <v>347.8417358398438</v>
       </c>
       <c r="F593" t="n">
         <v>77.80000305175781</v>
@@ -18202,7 +18202,7 @@
         <v>170.5</v>
       </c>
       <c r="I593" t="n">
-        <v>1200.354125976562</v>
+        <v>1200.354248046875</v>
       </c>
       <c r="J593" t="n">
         <v>25.20000076293945</v>
@@ -18222,7 +18222,7 @@
         <v>20.54999923706055</v>
       </c>
       <c r="E594" t="n">
-        <v>346.3973388671875</v>
+        <v>346.3973693847656</v>
       </c>
       <c r="F594" t="n">
         <v>80.94999694824219</v>
@@ -18318,7 +18318,7 @@
         <v>19.39999961853027</v>
       </c>
       <c r="E597" t="n">
-        <v>331.6549072265625</v>
+        <v>331.6549377441406</v>
       </c>
       <c r="F597" t="n">
         <v>75.59999847412109</v>
@@ -18330,7 +18330,7 @@
         <v>155.9499969482422</v>
       </c>
       <c r="I597" t="n">
-        <v>1059.578125</v>
+        <v>1059.578002929688</v>
       </c>
       <c r="J597" t="n">
         <v>24.5</v>
@@ -18350,7 +18350,7 @@
         <v>19.95000076293945</v>
       </c>
       <c r="E598" t="n">
-        <v>344.2557373046875</v>
+        <v>344.2557067871094</v>
       </c>
       <c r="F598" t="n">
         <v>76.09999847412109</v>
@@ -18382,7 +18382,7 @@
         <v>20.29999923706055</v>
       </c>
       <c r="E599" t="n">
-        <v>348.0409240722656</v>
+        <v>348.0408935546875</v>
       </c>
       <c r="F599" t="n">
         <v>79.84999847412109</v>
@@ -18478,7 +18478,7 @@
         <v>21.68000030517578</v>
       </c>
       <c r="E602" t="n">
-        <v>348.8876342773438</v>
+        <v>348.8876037597656</v>
       </c>
       <c r="F602" t="n">
         <v>79.94000244140625</v>
@@ -18670,7 +18670,7 @@
         <v>22.73999977111816</v>
       </c>
       <c r="E608" t="n">
-        <v>364.1280822753906</v>
+        <v>364.1281127929688</v>
       </c>
       <c r="F608" t="n">
         <v>84.08999633789062</v>
@@ -18734,7 +18734,7 @@
         <v>22.72999954223633</v>
       </c>
       <c r="E610" t="n">
-        <v>353.9677734375</v>
+        <v>353.9678039550781</v>
       </c>
       <c r="F610" t="n">
         <v>82.69999694824219</v>
@@ -18798,7 +18798,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="E612" t="n">
-        <v>354.8642578125</v>
+        <v>354.8642883300781</v>
       </c>
       <c r="F612" t="n">
         <v>81.08999633789062</v>
@@ -18958,7 +18958,7 @@
         <v>23.46999931335449</v>
       </c>
       <c r="E617" t="n">
-        <v>349.9335021972656</v>
+        <v>349.9335327148438</v>
       </c>
       <c r="F617" t="n">
         <v>88.41000366210938</v>
@@ -19118,7 +19118,7 @@
         <v>23.09000015258789</v>
       </c>
       <c r="E622" t="n">
-        <v>346.5965881347656</v>
+        <v>346.5965576171875</v>
       </c>
       <c r="F622" t="n">
         <v>82.37999725341797</v>
@@ -19438,7 +19438,7 @@
         <v>23.82999992370605</v>
       </c>
       <c r="E632" t="n">
-        <v>327.9194946289062</v>
+        <v>327.9195251464844</v>
       </c>
       <c r="F632" t="n">
         <v>84.30999755859375</v>
@@ -19470,7 +19470,7 @@
         <v>23.92000007629395</v>
       </c>
       <c r="E633" t="n">
-        <v>330.6090087890625</v>
+        <v>330.6089782714844</v>
       </c>
       <c r="F633" t="n">
         <v>91.58999633789062</v>
@@ -19534,7 +19534,7 @@
         <v>24.17000007629395</v>
       </c>
       <c r="E635" t="n">
-        <v>328.0689392089844</v>
+        <v>328.0689086914062</v>
       </c>
       <c r="F635" t="n">
         <v>90.97000122070312</v>
@@ -19630,7 +19630,7 @@
         <v>23.06999969482422</v>
       </c>
       <c r="E638" t="n">
-        <v>324.98095703125</v>
+        <v>324.9809875488281</v>
       </c>
       <c r="F638" t="n">
         <v>93.27999877929688</v>
@@ -19790,7 +19790,7 @@
         <v>21.71999931335449</v>
       </c>
       <c r="E643" t="n">
-        <v>324.33349609375</v>
+        <v>324.3335266113281</v>
       </c>
       <c r="F643" t="n">
         <v>99.91999816894531</v>
@@ -20014,7 +20014,7 @@
         <v>21.45999908447266</v>
       </c>
       <c r="E650" t="n">
-        <v>329.8121337890625</v>
+        <v>329.8121032714844</v>
       </c>
       <c r="F650" t="n">
         <v>98.65000152587891</v>
@@ -20142,7 +20142,7 @@
         <v>21.40999984741211</v>
       </c>
       <c r="E654" t="n">
-        <v>322.3412780761719</v>
+        <v>322.34130859375</v>
       </c>
       <c r="F654" t="n">
         <v>97.77999877929688</v>
@@ -20174,7 +20174,7 @@
         <v>21.23999977111816</v>
       </c>
       <c r="E655" t="n">
-        <v>320.9965209960938</v>
+        <v>320.9965515136719</v>
       </c>
       <c r="F655" t="n">
         <v>96.19000244140625</v>
@@ -20238,7 +20238,7 @@
         <v>21.11000061035156</v>
       </c>
       <c r="E657" t="n">
-        <v>320.4486694335938</v>
+        <v>320.4486999511719</v>
       </c>
       <c r="F657" t="n">
         <v>95.16000366210938</v>
@@ -20302,7 +20302,7 @@
         <v>20.65999984741211</v>
       </c>
       <c r="E659" t="n">
-        <v>348.8377990722656</v>
+        <v>348.8378295898438</v>
       </c>
       <c r="F659" t="n">
         <v>93.05999755859375</v>
@@ -20334,7 +20334,7 @@
         <v>20.5</v>
       </c>
       <c r="E660" t="n">
-        <v>345.8494873046875</v>
+        <v>345.8495178222656</v>
       </c>
       <c r="F660" t="n">
         <v>91.76000213623047</v>
@@ -20590,7 +20590,7 @@
         <v>21.73999977111816</v>
       </c>
       <c r="E668" t="n">
-        <v>347.4432678222656</v>
+        <v>347.4432373046875</v>
       </c>
       <c r="F668" t="n">
         <v>91.58000183105469</v>
@@ -20686,7 +20686,7 @@
         <v>20.45000076293945</v>
       </c>
       <c r="E671" t="n">
-        <v>345.3016052246094</v>
+        <v>345.3016357421875</v>
       </c>
       <c r="F671" t="n">
         <v>83.73999786376953</v>
@@ -20750,7 +20750,7 @@
         <v>20.71999931335449</v>
       </c>
       <c r="E673" t="n">
-        <v>352.8720397949219</v>
+        <v>352.8720703125</v>
       </c>
       <c r="F673" t="n">
         <v>83.36000061035156</v>
@@ -20974,7 +20974,7 @@
         <v>20.25</v>
       </c>
       <c r="E680" t="n">
-        <v>344.2557373046875</v>
+        <v>344.2557067871094</v>
       </c>
       <c r="F680" t="n">
         <v>80.34999847412109</v>
@@ -21070,7 +21070,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="E683" t="n">
-        <v>344.2557373046875</v>
+        <v>344.2557067871094</v>
       </c>
       <c r="F683" t="n">
         <v>75.75</v>
@@ -21166,7 +21166,7 @@
         <v>20.09000015258789</v>
       </c>
       <c r="E686" t="n">
-        <v>340.1716613769531</v>
+        <v>340.171630859375</v>
       </c>
       <c r="F686" t="n">
         <v>81.36000061035156</v>
@@ -21198,7 +21198,7 @@
         <v>20.72999954223633</v>
       </c>
       <c r="E687" t="n">
-        <v>338.727294921875</v>
+        <v>338.7272644042969</v>
       </c>
       <c r="F687" t="n">
         <v>79.09999847412109</v>
@@ -21262,7 +21262,7 @@
         <v>20.48999977111816</v>
       </c>
       <c r="E689" t="n">
-        <v>332.3522033691406</v>
+        <v>332.3521728515625</v>
       </c>
       <c r="F689" t="n">
         <v>85.95999908447266</v>
@@ -21390,7 +21390,7 @@
         <v>18.84000015258789</v>
       </c>
       <c r="E693" t="n">
-        <v>312.8283996582031</v>
+        <v>312.8284301757812</v>
       </c>
       <c r="F693" t="n">
         <v>76.08000183105469</v>
@@ -21422,7 +21422,7 @@
         <v>18.93000030517578</v>
       </c>
       <c r="E694" t="n">
-        <v>313.4758911132812</v>
+        <v>313.4759216308594</v>
       </c>
       <c r="F694" t="n">
         <v>79.12999725341797</v>
@@ -21582,7 +21582,7 @@
         <v>19.28000068664551</v>
       </c>
       <c r="E699" t="n">
-        <v>318.7054748535156</v>
+        <v>318.7055053710938</v>
       </c>
       <c r="F699" t="n">
         <v>81.11000061035156</v>
@@ -21774,7 +21774,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="E705" t="n">
-        <v>320.2992553710938</v>
+        <v>320.2992248535156</v>
       </c>
       <c r="F705" t="n">
         <v>83.80999755859375</v>
@@ -21902,7 +21902,7 @@
         <v>18.28000068664551</v>
       </c>
       <c r="E709" t="n">
-        <v>298.2354125976562</v>
+        <v>298.2353820800781</v>
       </c>
       <c r="F709" t="n">
         <v>77.97000122070312</v>
@@ -22030,7 +22030,7 @@
         <v>18.11000061035156</v>
       </c>
       <c r="E713" t="n">
-        <v>312.9778747558594</v>
+        <v>312.9778442382812</v>
       </c>
       <c r="F713" t="n">
         <v>84.30000305175781</v>
@@ -22062,7 +22062,7 @@
         <v>18.17000007629395</v>
       </c>
       <c r="E714" t="n">
-        <v>312.5793762207031</v>
+        <v>312.5794067382812</v>
       </c>
       <c r="F714" t="n">
         <v>79.55999755859375</v>
@@ -22158,7 +22158,7 @@
         <v>17.02000045776367</v>
       </c>
       <c r="E717" t="n">
-        <v>327.6206665039062</v>
+        <v>327.6206359863281</v>
       </c>
       <c r="F717" t="n">
         <v>79.70999908447266</v>
@@ -22222,7 +22222,7 @@
         <v>17.28000068664551</v>
       </c>
       <c r="E719" t="n">
-        <v>327.0728149414062</v>
+        <v>327.0727844238281</v>
       </c>
       <c r="F719" t="n">
         <v>78.83999633789062</v>
@@ -22286,7 +22286,7 @@
         <v>17.86000061035156</v>
       </c>
       <c r="E721" t="n">
-        <v>339.0261535644531</v>
+        <v>339.026123046875</v>
       </c>
       <c r="F721" t="n">
         <v>79.80999755859375</v>
@@ -22350,7 +22350,7 @@
         <v>17.93000030517578</v>
       </c>
       <c r="E723" t="n">
-        <v>340.1716613769531</v>
+        <v>340.171630859375</v>
       </c>
       <c r="F723" t="n">
         <v>79.20999908447266</v>
@@ -22382,7 +22382,7 @@
         <v>18.06999969482422</v>
       </c>
       <c r="E724" t="n">
-        <v>337.581787109375</v>
+        <v>337.5817565917969</v>
       </c>
       <c r="F724" t="n">
         <v>79.58999633789062</v>
@@ -22574,7 +22574,7 @@
         <v>17.80999946594238</v>
       </c>
       <c r="E730" t="n">
-        <v>339.0261535644531</v>
+        <v>339.026123046875</v>
       </c>
       <c r="F730" t="n">
         <v>74.36000061035156</v>
@@ -22606,7 +22606,7 @@
         <v>17.55999946594238</v>
       </c>
       <c r="E731" t="n">
-        <v>335.7887573242188</v>
+        <v>335.7887878417969</v>
       </c>
       <c r="F731" t="n">
         <v>73.54000091552734</v>
@@ -22638,7 +22638,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="E732" t="n">
-        <v>323.3373718261719</v>
+        <v>323.33740234375</v>
       </c>
       <c r="F732" t="n">
         <v>72.55999755859375</v>
@@ -22670,7 +22670,7 @@
         <v>17.13999938964844</v>
       </c>
       <c r="E733" t="n">
-        <v>311.7825317382812</v>
+        <v>311.7825012207031</v>
       </c>
       <c r="F733" t="n">
         <v>70.18000030517578</v>
@@ -22702,7 +22702,7 @@
         <v>16.61000061035156</v>
       </c>
       <c r="E734" t="n">
-        <v>303.1163635253906</v>
+        <v>303.1163330078125</v>
       </c>
       <c r="F734" t="n">
         <v>74.33999633789062</v>
@@ -22830,7 +22830,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="E738" t="n">
-        <v>303.7638549804688</v>
+        <v>303.7638244628906</v>
       </c>
       <c r="F738" t="n">
         <v>73.19000244140625</v>
@@ -22862,7 +22862,7 @@
         <v>15.19999980926514</v>
       </c>
       <c r="E739" t="n">
-        <v>305.0587463378906</v>
+        <v>305.0587768554688</v>
       </c>
       <c r="F739" t="n">
         <v>70.33999633789062</v>
@@ -22990,7 +22990,7 @@
         <v>16.32999992370605</v>
       </c>
       <c r="E743" t="n">
-        <v>306.2540893554688</v>
+        <v>306.2541198730469</v>
       </c>
       <c r="F743" t="n">
         <v>72.80000305175781</v>
@@ -23022,7 +23022,7 @@
         <v>15.73999977111816</v>
       </c>
       <c r="E744" t="n">
-        <v>295.5458984375</v>
+        <v>295.5459289550781</v>
       </c>
       <c r="F744" t="n">
         <v>68.94999694824219</v>
@@ -23118,7 +23118,7 @@
         <v>15.77999973297119</v>
       </c>
       <c r="E747" t="n">
-        <v>288.1249084472656</v>
+        <v>288.1248779296875</v>
       </c>
       <c r="F747" t="n">
         <v>66.61000061035156</v>
@@ -23182,7 +23182,7 @@
         <v>14.53999996185303</v>
       </c>
       <c r="E749" t="n">
-        <v>265.1147155761719</v>
+        <v>265.11474609375</v>
       </c>
       <c r="F749" t="n">
         <v>59.84000015258789</v>
@@ -23214,7 +23214,7 @@
         <v>15.23999977111816</v>
       </c>
       <c r="E750" t="n">
-        <v>271.7886657714844</v>
+        <v>271.7886962890625</v>
       </c>
       <c r="F750" t="n">
         <v>61.43999862670898</v>
@@ -23502,7 +23502,7 @@
         <v>14.88000011444092</v>
       </c>
       <c r="E759" t="n">
-        <v>232.3925323486328</v>
+        <v>232.3925170898438</v>
       </c>
       <c r="F759" t="n">
         <v>50.02999877929688</v>
@@ -23534,7 +23534,7 @@
         <v>14.77999973297119</v>
       </c>
       <c r="E760" t="n">
-        <v>232.4921417236328</v>
+        <v>232.4921264648438</v>
       </c>
       <c r="F760" t="n">
         <v>49.66999816894531</v>
@@ -23662,7 +23662,7 @@
         <v>15.10999965667725</v>
       </c>
       <c r="E764" t="n">
-        <v>240.5705871582031</v>
+        <v>240.5705718994141</v>
       </c>
       <c r="F764" t="n">
         <v>52.81999969482422</v>
@@ -23726,7 +23726,7 @@
         <v>14.75</v>
       </c>
       <c r="E766" t="n">
-        <v>244.1466369628906</v>
+        <v>244.1466217041016</v>
       </c>
       <c r="F766" t="n">
         <v>51.83000183105469</v>
@@ -23758,7 +23758,7 @@
         <v>14.84000015258789</v>
       </c>
       <c r="E767" t="n">
-        <v>248.8482666015625</v>
+        <v>248.8482818603516</v>
       </c>
       <c r="F767" t="n">
         <v>53.2599983215332</v>
@@ -23822,7 +23822,7 @@
         <v>14.69999980926514</v>
       </c>
       <c r="E769" t="n">
-        <v>248.4797058105469</v>
+        <v>248.4796905517578</v>
       </c>
       <c r="F769" t="n">
         <v>51.79000091552734</v>
@@ -23854,7 +23854,7 @@
         <v>14.82999992370605</v>
       </c>
       <c r="E770" t="n">
-        <v>242.0149536132812</v>
+        <v>242.0149688720703</v>
       </c>
       <c r="F770" t="n">
         <v>50.41999816894531</v>
@@ -23950,7 +23950,7 @@
         <v>14.34000015258789</v>
       </c>
       <c r="E773" t="n">
-        <v>227.1728973388672</v>
+        <v>227.1729125976562</v>
       </c>
       <c r="F773" t="n">
         <v>49.22999954223633</v>
@@ -24078,7 +24078,7 @@
         <v>14.14000034332275</v>
       </c>
       <c r="E777" t="n">
-        <v>228.0295715332031</v>
+        <v>228.0295562744141</v>
       </c>
       <c r="F777" t="n">
         <v>46.93000030517578</v>
@@ -24270,7 +24270,7 @@
         <v>13.22000026702881</v>
       </c>
       <c r="E783" t="n">
-        <v>206.8024597167969</v>
+        <v>206.8024444580078</v>
       </c>
       <c r="F783" t="n">
         <v>41.31999969482422</v>
@@ -24398,7 +24398,7 @@
         <v>13.89999961853027</v>
       </c>
       <c r="E787" t="n">
-        <v>219.0845031738281</v>
+        <v>219.0844879150391</v>
       </c>
       <c r="F787" t="n">
         <v>44.04999923706055</v>
@@ -24430,7 +24430,7 @@
         <v>14.17000007629395</v>
       </c>
       <c r="E788" t="n">
-        <v>220.9472045898438</v>
+        <v>220.9472198486328</v>
       </c>
       <c r="F788" t="n">
         <v>45.45000076293945</v>
@@ -24526,7 +24526,7 @@
         <v>13.38000011444092</v>
       </c>
       <c r="E791" t="n">
-        <v>224.6527557373047</v>
+        <v>224.6527404785156</v>
       </c>
       <c r="F791" t="n">
         <v>41.93000030517578</v>
@@ -24590,7 +24590,7 @@
         <v>13.01000022888184</v>
       </c>
       <c r="E793" t="n">
-        <v>218.6661376953125</v>
+        <v>218.6661224365234</v>
       </c>
       <c r="F793" t="n">
         <v>40.52999877929688</v>
@@ -24622,7 +24622,7 @@
         <v>13.01000022888184</v>
       </c>
       <c r="E794" t="n">
-        <v>218.6661376953125</v>
+        <v>218.6661224365234</v>
       </c>
       <c r="F794" t="n">
         <v>40.52999877929688</v>
@@ -24654,7 +24654,7 @@
         <v>13.55000019073486</v>
       </c>
       <c r="E795" t="n">
-        <v>227.9498748779297</v>
+        <v>227.9498596191406</v>
       </c>
       <c r="F795" t="n">
         <v>43.86999893188477</v>
@@ -24718,7 +24718,7 @@
         <v>13.71000003814697</v>
       </c>
       <c r="E797" t="n">
-        <v>228.2287750244141</v>
+        <v>228.2287902832031</v>
       </c>
       <c r="F797" t="n">
         <v>47.43999862670898</v>
@@ -24750,7 +24750,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="E798" t="n">
-        <v>231.7749328613281</v>
+        <v>231.7749176025391</v>
       </c>
       <c r="F798" t="n">
         <v>47.4900016784668</v>
@@ -24782,7 +24782,7 @@
         <v>13.32999992370605</v>
       </c>
       <c r="E799" t="n">
-        <v>226.6449584960938</v>
+        <v>226.6449737548828</v>
       </c>
       <c r="F799" t="n">
         <v>45.36000061035156</v>
@@ -24846,7 +24846,7 @@
         <v>13.07999992370605</v>
       </c>
       <c r="E801" t="n">
-        <v>224.9017639160156</v>
+        <v>224.9017791748047</v>
       </c>
       <c r="F801" t="n">
         <v>44.95999908447266</v>
@@ -24878,7 +24878,7 @@
         <v>13</v>
       </c>
       <c r="E802" t="n">
-        <v>226.6250305175781</v>
+        <v>226.6250457763672</v>
       </c>
       <c r="F802" t="n">
         <v>43.40999984741211</v>
@@ -25038,7 +25038,7 @@
         <v>12.46000003814697</v>
       </c>
       <c r="E807" t="n">
-        <v>212.6894683837891</v>
+        <v>212.689453125</v>
       </c>
       <c r="F807" t="n">
         <v>41.22999954223633</v>
@@ -25070,7 +25070,7 @@
         <v>12.98999977111816</v>
       </c>
       <c r="E808" t="n">
-        <v>223.935546875</v>
+        <v>223.9355316162109</v>
       </c>
       <c r="F808" t="n">
         <v>41.70999908447266</v>
@@ -25262,7 +25262,7 @@
         <v>14.10999965667725</v>
       </c>
       <c r="E814" t="n">
-        <v>245.4216461181641</v>
+        <v>245.4216613769531</v>
       </c>
       <c r="F814" t="n">
         <v>45.11000061035156</v>
@@ -25326,7 +25326,7 @@
         <v>14.72999954223633</v>
       </c>
       <c r="E816" t="n">
-        <v>257.1359252929688</v>
+        <v>257.1358947753906</v>
       </c>
       <c r="F816" t="n">
         <v>45.86999893188477</v>
@@ -25422,7 +25422,7 @@
         <v>14.02000045776367</v>
       </c>
       <c r="E819" t="n">
-        <v>256.8968200683594</v>
+        <v>256.8968505859375</v>
       </c>
       <c r="F819" t="n">
         <v>43.45000076293945</v>
@@ -25454,7 +25454,7 @@
         <v>13.90999984741211</v>
       </c>
       <c r="E820" t="n">
-        <v>256.6278991699219</v>
+        <v>256.6278686523438</v>
       </c>
       <c r="F820" t="n">
         <v>45.27000045776367</v>
@@ -25678,7 +25678,7 @@
         <v>13.15999984741211</v>
       </c>
       <c r="E827" t="n">
-        <v>247.3839874267578</v>
+        <v>247.3840026855469</v>
       </c>
       <c r="F827" t="n">
         <v>42.4900016784668</v>
@@ -25902,7 +25902,7 @@
         <v>15.01000022888184</v>
       </c>
       <c r="E834" t="n">
-        <v>270.3941650390625</v>
+        <v>270.3941345214844</v>
       </c>
       <c r="F834" t="n">
         <v>46.61999893188477</v>
@@ -25934,7 +25934,7 @@
         <v>15.14999961853027</v>
       </c>
       <c r="E835" t="n">
-        <v>273.2828674316406</v>
+        <v>273.2828369140625</v>
       </c>
       <c r="F835" t="n">
         <v>46.68999862670898</v>
@@ -25998,7 +25998,7 @@
         <v>15.3100004196167</v>
       </c>
       <c r="E837" t="n">
-        <v>280.654052734375</v>
+        <v>280.6540832519531</v>
       </c>
       <c r="F837" t="n">
         <v>48.81999969482422</v>
@@ -26030,7 +26030,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="E838" t="n">
-        <v>280.654052734375</v>
+        <v>280.6540832519531</v>
       </c>
       <c r="F838" t="n">
         <v>50.0099983215332</v>
@@ -26094,7 +26094,7 @@
         <v>15.52000045776367</v>
       </c>
       <c r="E840" t="n">
-        <v>289.2206420898438</v>
+        <v>289.2206115722656</v>
       </c>
       <c r="F840" t="n">
         <v>52.68999862670898</v>
@@ -26254,7 +26254,7 @@
         <v>15.72999954223633</v>
       </c>
       <c r="E845" t="n">
-        <v>289.2206420898438</v>
+        <v>289.2206115722656</v>
       </c>
       <c r="F845" t="n">
         <v>55.31999969482422</v>
@@ -26286,7 +26286,7 @@
         <v>15.75</v>
       </c>
       <c r="E846" t="n">
-        <v>290.3661499023438</v>
+        <v>290.3661193847656</v>
       </c>
       <c r="F846" t="n">
         <v>54.68999862670898</v>
@@ -26350,7 +26350,7 @@
         <v>15.80000019073486</v>
       </c>
       <c r="E848" t="n">
-        <v>303.0665283203125</v>
+        <v>303.0665588378906</v>
       </c>
       <c r="F848" t="n">
         <v>54.47999954223633</v>
@@ -26382,7 +26382,7 @@
         <v>15.98999977111816</v>
       </c>
       <c r="E849" t="n">
-        <v>301.6221618652344</v>
+        <v>301.6221923828125</v>
       </c>
       <c r="F849" t="n">
         <v>57.08000183105469</v>
@@ -26542,7 +26542,7 @@
         <v>15.03999996185303</v>
       </c>
       <c r="E854" t="n">
-        <v>288.6727600097656</v>
+        <v>288.6727294921875</v>
       </c>
       <c r="F854" t="n">
         <v>53.13999938964844</v>
@@ -26574,7 +26574,7 @@
         <v>14.89000034332275</v>
       </c>
       <c r="E855" t="n">
-        <v>287.0291748046875</v>
+        <v>287.0291442871094</v>
       </c>
       <c r="F855" t="n">
         <v>52.86999893188477</v>
@@ -26702,7 +26702,7 @@
         <v>15.15999984741211</v>
       </c>
       <c r="E859" t="n">
-        <v>299.6299743652344</v>
+        <v>299.6299438476562</v>
       </c>
       <c r="F859" t="n">
         <v>53.65999984741211</v>
@@ -26734,7 +26734,7 @@
         <v>16.04999923706055</v>
       </c>
       <c r="E860" t="n">
-        <v>302.1202392578125</v>
+        <v>302.1202087402344</v>
       </c>
       <c r="F860" t="n">
         <v>61.81999969482422</v>
@@ -26894,7 +26894,7 @@
         <v>15.85999965667725</v>
       </c>
       <c r="E865" t="n">
-        <v>325.4292297363281</v>
+        <v>325.4292602539062</v>
       </c>
       <c r="F865" t="n">
         <v>57.02000045776367</v>
@@ -26926,7 +26926,7 @@
         <v>15.96000003814697</v>
       </c>
       <c r="E866" t="n">
-        <v>323.7856140136719</v>
+        <v>323.78564453125</v>
       </c>
       <c r="F866" t="n">
         <v>58.11000061035156</v>
@@ -26958,7 +26958,7 @@
         <v>15.98999977111816</v>
       </c>
       <c r="E867" t="n">
-        <v>323.6860656738281</v>
+        <v>323.68603515625</v>
       </c>
       <c r="F867" t="n">
         <v>56.41999816894531</v>
@@ -27086,7 +27086,7 @@
         <v>15.57999992370605</v>
       </c>
       <c r="E871" t="n">
-        <v>330.3599853515625</v>
+        <v>330.3599548339844</v>
       </c>
       <c r="F871" t="n">
         <v>55.68000030517578</v>
@@ -27118,7 +27118,7 @@
         <v>15.35999965667725</v>
       </c>
       <c r="E872" t="n">
-        <v>324.53271484375</v>
+        <v>324.5326843261719</v>
       </c>
       <c r="F872" t="n">
         <v>54.81000137329102</v>
@@ -27310,7 +27310,7 @@
         <v>15.86999988555908</v>
       </c>
       <c r="E878" t="n">
-        <v>316.0159606933594</v>
+        <v>316.0159912109375</v>
       </c>
       <c r="F878" t="n">
         <v>59.61000061035156</v>
@@ -27470,7 +27470,7 @@
         <v>14.85999965667725</v>
       </c>
       <c r="E883" t="n">
-        <v>306.1544799804688</v>
+        <v>306.1545104980469</v>
       </c>
       <c r="F883" t="n">
         <v>56.25</v>
@@ -27598,7 +27598,7 @@
         <v>15.10000038146973</v>
       </c>
       <c r="E887" t="n">
-        <v>328.2183227539062</v>
+        <v>328.2183532714844</v>
       </c>
       <c r="F887" t="n">
         <v>57.47000122070312</v>
@@ -27726,7 +27726,7 @@
         <v>14.31999969482422</v>
       </c>
       <c r="E891" t="n">
-        <v>324.2339172363281</v>
+        <v>324.23388671875</v>
       </c>
       <c r="F891" t="n">
         <v>56.29000091552734</v>
@@ -37168,7 +37168,7 @@
         <v>3.846153846153855</v>
       </c>
       <c r="E19" t="n">
-        <v>14.46530988416585</v>
+        <v>14.46530217715354</v>
       </c>
       <c r="F19" t="n">
         <v>0.2994726297447459</v>
@@ -37200,7 +37200,7 @@
         <v>-1.664147220764423</v>
       </c>
       <c r="E20" t="n">
-        <v>9.585268389905522</v>
+        <v>9.585283854023508</v>
       </c>
       <c r="F20" t="n">
         <v>5.058083659302848</v>
@@ -37232,7 +37232,7 @@
         <v>-12.04257816433491</v>
       </c>
       <c r="E21" t="n">
-        <v>-14.08648260149032</v>
+        <v>-14.08648894056502</v>
       </c>
       <c r="F21" t="n">
         <v>-21.56416200558649</v>
@@ -37296,7 +37296,7 @@
         <v>-8.96991367371337</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.029997792400145</v>
+        <v>-9.02998930442963</v>
       </c>
       <c r="F23" t="n">
         <v>-9.284627137033763</v>
@@ -37328,7 +37328,7 @@
         <v>-10.92782976067592</v>
       </c>
       <c r="E24" t="n">
-        <v>1.877140080946416</v>
+        <v>1.877130575284558</v>
       </c>
       <c r="F24" t="n">
         <v>-8.750005850085408</v>
@@ -37392,7 +37392,7 @@
         <v>-2.652777627189706</v>
       </c>
       <c r="E26" t="n">
-        <v>8.983528534268292</v>
+        <v>8.983518155342285</v>
       </c>
       <c r="F26" t="n">
         <v>-13.86086794220902</v>
@@ -37424,7 +37424,7 @@
         <v>-12.37027614512571</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.070018161948173</v>
+        <v>-2.070008835693593</v>
       </c>
       <c r="F27" t="n">
         <v>-3.095716273530114</v>
@@ -37628,7 +37628,7 @@
         <v>-4.392992435061648</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7267397958982569</v>
+        <v>0.7267486143703428</v>
       </c>
       <c r="J33" t="n">
         <v>-18.79194166943702</v>
@@ -37648,7 +37648,7 @@
         <v>12.97169764638586</v>
       </c>
       <c r="E34" t="n">
-        <v>6.56794299184198</v>
+        <v>6.567935984125439</v>
       </c>
       <c r="F34" t="n">
         <v>33.94390617495342</v>
@@ -37660,7 +37660,7 @@
         <v>10.12869384694794</v>
       </c>
       <c r="I34" t="n">
-        <v>4.617439211995333</v>
+        <v>4.617430052899274</v>
       </c>
       <c r="J34" t="n">
         <v>27.89699662161886</v>
@@ -37680,7 +37680,7 @@
         <v>5.735668676501682</v>
       </c>
       <c r="E35" t="n">
-        <v>1.547509662461577</v>
+        <v>1.547516340043864</v>
       </c>
       <c r="F35" t="n">
         <v>0.9243158800178009</v>
@@ -37724,7 +37724,7 @@
         <v>12.11225997045791</v>
       </c>
       <c r="I36" t="n">
-        <v>8.906468868764028</v>
+        <v>8.906462181414131</v>
       </c>
       <c r="J36" t="n">
         <v>23.68420553633026</v>
@@ -37756,7 +37756,7 @@
         <v>-2.336989602099571</v>
       </c>
       <c r="I37" t="n">
-        <v>4.51119901463739</v>
+        <v>4.511212139064336</v>
       </c>
       <c r="J37" t="n">
         <v>-11.16882918717025</v>
@@ -37776,7 +37776,7 @@
         <v>21.21212121212121</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9850075430692273</v>
+        <v>-0.9850140387806072</v>
       </c>
       <c r="F38" t="n">
         <v>-6.583760205501399</v>
@@ -37788,7 +37788,7 @@
         <v>-7.202140266796353</v>
       </c>
       <c r="I38" t="n">
-        <v>-5.426396062627347</v>
+        <v>-5.426402131851338</v>
       </c>
       <c r="J38" t="n">
         <v>0.5221952138994457</v>
@@ -37846,7 +37846,7 @@
         <v>36.60036607849231</v>
       </c>
       <c r="I40" t="n">
-        <v>1.693669155291055</v>
+        <v>1.693675739617384</v>
       </c>
       <c r="J40" t="n">
         <v>17.08185437454475</v>
@@ -37875,7 +37875,7 @@
         <v>2.635488591081314</v>
       </c>
       <c r="I41" t="n">
-        <v>5.350313005783192</v>
+        <v>5.350306184701781</v>
       </c>
       <c r="J41" t="n">
         <v>8.494211565028188</v>
@@ -37898,7 +37898,7 @@
         <v>5.598621951273208</v>
       </c>
       <c r="G42" t="n">
-        <v>2.040900585798755</v>
+        <v>2.040911910979792</v>
       </c>
       <c r="H42" t="n">
         <v>-14.50333586855534</v>
@@ -37927,7 +37927,7 @@
         <v>7.004606888590881</v>
       </c>
       <c r="G43" t="n">
-        <v>3.837320715324744</v>
+        <v>3.837297223976188</v>
       </c>
       <c r="H43" t="n">
         <v>9.220106101738512</v>
@@ -37956,13 +37956,13 @@
         <v>-7.106166810697612</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3659714981767426</v>
+        <v>0.3659830649118234</v>
       </c>
       <c r="H44" t="n">
         <v>10.36725582872331</v>
       </c>
       <c r="I44" t="n">
-        <v>-2.506390909291822</v>
+        <v>-2.506398442968916</v>
       </c>
       <c r="J44" t="n">
         <v>1.53060832255989</v>
@@ -37985,13 +37985,13 @@
         <v>-5.117786759101961</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.329731717430038</v>
+        <v>-1.329742978595971</v>
       </c>
       <c r="H45" t="n">
         <v>4.476417699780821</v>
       </c>
       <c r="I45" t="n">
-        <v>-7.821843174509246</v>
+        <v>-7.82183605157546</v>
       </c>
       <c r="J45" t="n">
         <v>-23.13725340600107</v>
@@ -38014,13 +38014,13 @@
         <v>-6.883508838267105</v>
       </c>
       <c r="G46" t="n">
-        <v>-7.590699242184062</v>
+        <v>-7.590678949528251</v>
       </c>
       <c r="H46" t="n">
         <v>-9.150325892060184</v>
       </c>
       <c r="I46" t="n">
-        <v>-7.873144482527428</v>
+        <v>-7.873138437038474</v>
       </c>
       <c r="J46" t="n">
         <v>-11.14982814589901</v>
@@ -38043,13 +38043,13 @@
         <v>-2.865546642449923</v>
       </c>
       <c r="G47" t="n">
-        <v>-6.742071220774404</v>
+        <v>-6.742090228748266</v>
       </c>
       <c r="H47" t="n">
         <v>-12.68230842551258</v>
       </c>
       <c r="I47" t="n">
-        <v>-10.50509868554349</v>
+        <v>-10.50510455831967</v>
       </c>
       <c r="J47" t="n">
         <v>-10.59189368473866</v>
@@ -38072,13 +38072,13 @@
         <v>6.079503403138031</v>
       </c>
       <c r="G48" t="n">
-        <v>7.128559619963015</v>
+        <v>7.128570156643566</v>
       </c>
       <c r="H48" t="n">
         <v>11.48815860769938</v>
       </c>
       <c r="I48" t="n">
-        <v>-3.90674987660834</v>
+        <v>-3.906760722347635</v>
       </c>
       <c r="J48" t="n">
         <v>-0.3105661069842447</v>
@@ -38101,13 +38101,13 @@
         <v>-0.696589719615015</v>
       </c>
       <c r="G49" t="n">
-        <v>7.227420215142799</v>
+        <v>7.227432329924066</v>
       </c>
       <c r="H49" t="n">
         <v>3.474762330681291</v>
       </c>
       <c r="I49" t="n">
-        <v>1.992280127469637</v>
+        <v>1.992291639014976</v>
       </c>
       <c r="J49" t="n">
         <v>-1.829263683162408</v>
@@ -38130,7 +38130,7 @@
         <v>-8.498583753085121</v>
       </c>
       <c r="G50" t="n">
-        <v>-9.863720565037227</v>
+        <v>-9.863721569537597</v>
       </c>
       <c r="H50" t="n">
         <v>-15.6172858344184</v>
@@ -38159,13 +38159,13 @@
         <v>8.782737772308536</v>
       </c>
       <c r="G51" t="n">
-        <v>5.463632047055778</v>
+        <v>5.463621306864352</v>
       </c>
       <c r="H51" t="n">
         <v>38.34329813061588</v>
       </c>
       <c r="I51" t="n">
-        <v>4.312852371434839</v>
+        <v>4.312858971254707</v>
       </c>
       <c r="J51" t="n">
         <v>35.48386898298783</v>
@@ -38188,13 +38188,13 @@
         <v>-5.942026774088538</v>
       </c>
       <c r="G52" t="n">
-        <v>-3.320959299636128</v>
+        <v>-3.32094926095331</v>
       </c>
       <c r="H52" t="n">
         <v>29.24944861623748</v>
       </c>
       <c r="I52" t="n">
-        <v>3.064815751886085</v>
+        <v>3.064809231029253</v>
       </c>
       <c r="J52" t="n">
         <v>7.826083639393677</v>
@@ -38217,13 +38217,13 @@
         <v>-8.609271523178808</v>
       </c>
       <c r="G53" t="n">
-        <v>-1.405415333093574</v>
+        <v>-1.405415476974137</v>
       </c>
       <c r="H53" t="n">
         <v>-16.0722547147822</v>
       </c>
       <c r="I53" t="n">
-        <v>2.955485676141079</v>
+        <v>2.955478764142816</v>
       </c>
       <c r="J53" t="n">
         <v>-8.730161493387333</v>
@@ -38246,13 +38246,13 @@
         <v>-12.41298993858072</v>
       </c>
       <c r="G54" t="n">
-        <v>-5.648249785852466</v>
+        <v>-5.648250331436078</v>
       </c>
       <c r="H54" t="n">
         <v>-12.62647164563844</v>
       </c>
       <c r="I54" t="n">
-        <v>-16.35937232396798</v>
+        <v>-16.35935731537461</v>
       </c>
       <c r="J54" t="n">
         <v>-11.57894469144052</v>
@@ -38275,13 +38275,13 @@
         <v>1.233112628945943</v>
       </c>
       <c r="G55" t="n">
-        <v>5.90190678499245</v>
+        <v>5.901896555568986</v>
       </c>
       <c r="H55" t="n">
         <v>10.01780916676824</v>
       </c>
       <c r="I55" t="n">
-        <v>42.15598663130014</v>
+        <v>42.1559706663859</v>
       </c>
       <c r="J55" t="n">
         <v>5.555555555555558</v>
@@ -38310,7 +38310,7 @@
         <v>7.361381156751889</v>
       </c>
       <c r="I56" t="n">
-        <v>11.44042835922838</v>
+        <v>11.44043827261805</v>
       </c>
       <c r="J56" t="n">
         <v>3.4482743501002</v>
@@ -38333,13 +38333,13 @@
         <v>-6.15854030702172</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.133414741099703</v>
+        <v>-1.133403576054681</v>
       </c>
       <c r="H57" t="n">
         <v>3.513107684464867</v>
       </c>
       <c r="I57" t="n">
-        <v>-20.63635750063468</v>
+        <v>-20.63637016359784</v>
       </c>
       <c r="J57" t="n">
         <v>-11.82432417193846</v>
@@ -38602,7 +38602,7 @@
         <v>22.99999823937049</v>
       </c>
       <c r="E7" t="n">
-        <v>43.62007306981142</v>
+        <v>43.62006339979285</v>
       </c>
       <c r="F7" t="n">
         <v>35.63695294881548</v>
@@ -38634,7 +38634,7 @@
         <v>-17.35536949575909</v>
       </c>
       <c r="E8" t="n">
-        <v>-23.83328563970489</v>
+        <v>-23.83328051135775</v>
       </c>
       <c r="F8" t="n">
         <v>-39.30368863961553</v>
@@ -38762,7 +38762,7 @@
         <v>-7.547171339100844</v>
       </c>
       <c r="E12" t="n">
-        <v>51.8566402671572</v>
+        <v>51.85663028133727</v>
       </c>
       <c r="F12" t="n">
         <v>-1.316544414387844</v>
@@ -38794,7 +38794,7 @@
         <v>6.000003814697275</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7569145032003677</v>
+        <v>0.7569211287945299</v>
       </c>
       <c r="F13" t="n">
         <v>36.80501262584171</v>
@@ -38806,7 +38806,7 @@
         <v>21.06174227192534</v>
       </c>
       <c r="I13" t="n">
-        <v>40.1330609163993</v>
+        <v>40.13306990938417</v>
       </c>
       <c r="J13" t="n">
         <v>21.03895707563921</v>
@@ -38835,7 +38835,7 @@
         <v>25.35262426890257</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8914061816619245</v>
+        <v>0.8914062393774902</v>
       </c>
       <c r="J14" t="n">
         <v>37.01067429660412</v>
@@ -38858,13 +38858,13 @@
         <v>15.76036725725447</v>
       </c>
       <c r="G15" t="n">
-        <v>9.403498072287109</v>
+        <v>9.403485464018434</v>
       </c>
       <c r="H15" t="n">
         <v>-4.159445407279028</v>
       </c>
       <c r="I15" t="n">
-        <v>22.41576135094123</v>
+        <v>22.41575342492897</v>
       </c>
       <c r="J15" t="n">
         <v>41.20603477451257</v>
@@ -38887,13 +38887,13 @@
         <v>-17.92738085880669</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.485800364111073</v>
+        <v>-8.485780165858081</v>
       </c>
       <c r="H16" t="n">
         <v>4.756719823472322</v>
       </c>
       <c r="I16" t="n">
-        <v>-17.20761079032843</v>
+        <v>-17.2076053573798</v>
       </c>
       <c r="J16" t="n">
         <v>-30.66202407831533</v>
@@ -38916,13 +38916,13 @@
         <v>2.321981478994783</v>
       </c>
       <c r="G17" t="n">
-        <v>7.126493298635772</v>
+        <v>7.126494103802106</v>
       </c>
       <c r="H17" t="n">
         <v>0.7315289117223678</v>
       </c>
       <c r="I17" t="n">
-        <v>-12.28810842402225</v>
+        <v>-12.28811417979492</v>
       </c>
       <c r="J17" t="n">
         <v>-12.49999563868442</v>
@@ -38945,7 +38945,7 @@
         <v>-6.376813805621606</v>
       </c>
       <c r="G18" t="n">
-        <v>-8.095942839170478</v>
+        <v>-8.095943679813933</v>
       </c>
       <c r="H18" t="n">
         <v>50.88300138028043</v>
@@ -38974,7 +38974,7 @@
         <v>-18.96653110566366</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.483992691281522</v>
+        <v>-1.484002920704985</v>
       </c>
       <c r="H19" t="n">
         <v>-19.32324486904549</v>
@@ -39083,7 +39083,7 @@
         <v>24.71641426655784</v>
       </c>
       <c r="E2" t="n">
-        <v>38.56970207824606</v>
+        <v>38.56971060642054</v>
       </c>
       <c r="F2" t="n">
         <v>48.02197768635678</v>
@@ -39095,7 +39095,7 @@
         <v>26.11641041112731</v>
       </c>
       <c r="I2" t="n">
-        <v>13.54570754168862</v>
+        <v>13.54569421427558</v>
       </c>
       <c r="J2" t="n">
         <v>84.03669388711693</v>
@@ -39115,7 +39115,7 @@
         <v>21.52941086713005</v>
       </c>
       <c r="E3" t="n">
-        <v>48.10741480535528</v>
+        <v>48.10742776232155</v>
       </c>
       <c r="F3" t="n">
         <v>37.25662738916504</v>
@@ -39147,7 +39147,7 @@
         <v>21.30177788597374</v>
       </c>
       <c r="E4" t="n">
-        <v>54.55153813119511</v>
+        <v>54.55154123022257</v>
       </c>
       <c r="F4" t="n">
         <v>35.23950508448274</v>
@@ -39179,7 +39179,7 @@
         <v>25.38921902642992</v>
       </c>
       <c r="E5" t="n">
-        <v>61.79434466708855</v>
+        <v>61.79433305581566</v>
       </c>
       <c r="F5" t="n">
         <v>37.43092805121666</v>
@@ -39191,7 +39191,7 @@
         <v>18.42639458918014</v>
       </c>
       <c r="I5" t="n">
-        <v>15.59243490632829</v>
+        <v>15.5924279725592</v>
       </c>
       <c r="J5" t="n">
         <v>78.32370949116567</v>
@@ -39211,7 +39211,7 @@
         <v>23.483483105072</v>
       </c>
       <c r="E6" t="n">
-        <v>57.03962773712359</v>
+        <v>57.03963895200328</v>
       </c>
       <c r="F6" t="n">
         <v>32.87407769097221</v>
@@ -39275,7 +39275,7 @@
         <v>28.34835632939052</v>
       </c>
       <c r="E8" t="n">
-        <v>59.59137463922708</v>
+        <v>59.59136353965761</v>
       </c>
       <c r="F8" t="n">
         <v>30.24495302920487</v>
@@ -39339,7 +39339,7 @@
         <v>27.15151237718987</v>
       </c>
       <c r="E10" t="n">
-        <v>49.80728369996403</v>
+        <v>49.80727387211014</v>
       </c>
       <c r="F10" t="n">
         <v>30.0219527879438</v>
@@ -39383,7 +39383,7 @@
         <v>13.73462507545713</v>
       </c>
       <c r="I11" t="n">
-        <v>16.10095968062235</v>
+        <v>16.10096676605517</v>
       </c>
       <c r="J11" t="n">
         <v>56.99999959845292</v>
@@ -39403,7 +39403,7 @@
         <v>17.83197220667512</v>
       </c>
       <c r="E12" t="n">
-        <v>37.62083806523711</v>
+        <v>37.62082597735093</v>
       </c>
       <c r="F12" t="n">
         <v>29.44169870113738</v>
@@ -39499,7 +39499,7 @@
         <v>10.24259624810628</v>
       </c>
       <c r="E15" t="n">
-        <v>37.66877358173188</v>
+        <v>37.66878574882724</v>
       </c>
       <c r="F15" t="n">
         <v>18.36042100886153</v>
@@ -39511,7 +39511,7 @@
         <v>50.10011067847504</v>
       </c>
       <c r="I15" t="n">
-        <v>12.4430882751237</v>
+        <v>12.44309510189545</v>
       </c>
       <c r="J15" t="n">
         <v>63.25471398498556</v>
@@ -39543,7 +39543,7 @@
         <v>69.59249787931468</v>
       </c>
       <c r="I16" t="n">
-        <v>15.68150654251597</v>
+        <v>15.6815136261576</v>
       </c>
       <c r="J16" t="n">
         <v>71.82033478974208</v>
@@ -39563,7 +39563,7 @@
         <v>11.39784348605077</v>
       </c>
       <c r="E17" t="n">
-        <v>41.61502010126967</v>
+        <v>41.61504102066482</v>
       </c>
       <c r="F17" t="n">
         <v>17.49119689344376</v>
@@ -39607,7 +39607,7 @@
         <v>94.03570205320759</v>
       </c>
       <c r="I18" t="n">
-        <v>36.0335018181281</v>
+        <v>36.03351051593013</v>
       </c>
       <c r="J18" t="n">
         <v>117.663043844452</v>
@@ -39627,7 +39627,7 @@
         <v>18.21325520423087</v>
       </c>
       <c r="E19" t="n">
-        <v>46.87759936456168</v>
+        <v>46.8775899976761</v>
       </c>
       <c r="F19" t="n">
         <v>18.99342970595615</v>
@@ -39671,7 +39671,7 @@
         <v>87.55847280153539</v>
       </c>
       <c r="I20" t="n">
-        <v>32.77454840879854</v>
+        <v>32.77455685318971</v>
       </c>
       <c r="J20" t="n">
         <v>135.4666748046875</v>
@@ -39787,7 +39787,7 @@
         <v>1.75879592049748</v>
       </c>
       <c r="E24" t="n">
-        <v>51.81200920138686</v>
+        <v>51.81199574355784</v>
       </c>
       <c r="F24" t="n">
         <v>19.30215336975127</v>
@@ -39799,7 +39799,7 @@
         <v>86.52584846797919</v>
       </c>
       <c r="I24" t="n">
-        <v>25.56498092143338</v>
+        <v>25.56498906543911</v>
       </c>
       <c r="J24" t="n">
         <v>182.3157862613076</v>
@@ -39819,7 +39819,7 @@
         <v>4.647526447655226</v>
       </c>
       <c r="E25" t="n">
-        <v>48.72694435241242</v>
+        <v>48.72695435353167</v>
       </c>
       <c r="F25" t="n">
         <v>15.13592205797443</v>
@@ -39883,7 +39883,7 @@
         <v>-2.630266944568471</v>
       </c>
       <c r="E27" t="n">
-        <v>50.0000166214994</v>
+        <v>50.00000332429988</v>
       </c>
       <c r="F27" t="n">
         <v>17.44186046511629</v>
@@ -39915,7 +39915,7 @@
         <v>0.101012416840085</v>
       </c>
       <c r="E28" t="n">
-        <v>50.86870028982617</v>
+        <v>50.86871045504766</v>
       </c>
       <c r="F28" t="n">
         <v>21.00077612236952</v>
@@ -39927,7 +39927,7 @@
         <v>73.99363134446153</v>
       </c>
       <c r="I28" t="n">
-        <v>21.57638252010072</v>
+        <v>21.57639027866838</v>
       </c>
       <c r="J28" t="n">
         <v>151.4062423941993</v>
@@ -39979,7 +39979,7 @@
         <v>0.450000762939462</v>
       </c>
       <c r="E30" t="n">
-        <v>47.7076172998504</v>
+        <v>47.70760404866208</v>
       </c>
       <c r="F30" t="n">
         <v>27.42365317882882</v>
@@ -39991,7 +39991,7 @@
         <v>64.25273449733912</v>
       </c>
       <c r="I30" t="n">
-        <v>27.04550948767035</v>
+        <v>27.04551764076668</v>
       </c>
       <c r="J30" t="n">
         <v>129.7662313882407</v>
@@ -40011,7 +40011,7 @@
         <v>0.1449216337739756</v>
       </c>
       <c r="E31" t="n">
-        <v>46.95333165365223</v>
+        <v>46.95331841391677</v>
       </c>
       <c r="F31" t="n">
         <v>15.39021874936699</v>
@@ -40043,7 +40043,7 @@
         <v>-1.052628312774884</v>
       </c>
       <c r="E32" t="n">
-        <v>49.89985267357972</v>
+        <v>49.89984245224899</v>
       </c>
       <c r="F32" t="n">
         <v>27.97941577115182</v>
@@ -40075,7 +40075,7 @@
         <v>-2.660330100898289</v>
       </c>
       <c r="E33" t="n">
-        <v>48.02573758579716</v>
+        <v>48.02573405358237</v>
       </c>
       <c r="F33" t="n">
         <v>17.99588316396285</v>
@@ -40087,7 +40087,7 @@
         <v>69.25088116850071</v>
       </c>
       <c r="I33" t="n">
-        <v>25.14076236892711</v>
+        <v>25.14075448435975</v>
       </c>
       <c r="J33" t="n">
         <v>132.4867699130986</v>
@@ -40151,7 +40151,7 @@
         <v>64.23357664233578</v>
       </c>
       <c r="I35" t="n">
-        <v>27.1980016778619</v>
+        <v>27.19799344911933</v>
       </c>
       <c r="J35" t="n">
         <v>137.8151252422787</v>
@@ -40171,7 +40171,7 @@
         <v>-0.4102560190054061</v>
       </c>
       <c r="E36" t="n">
-        <v>48.62594908343376</v>
+        <v>48.62593874181287</v>
       </c>
       <c r="F36" t="n">
         <v>11.65387061590668</v>
@@ -40183,7 +40183,7 @@
         <v>56.8334812026194</v>
       </c>
       <c r="I36" t="n">
-        <v>22.65728440839494</v>
+        <v>22.657292123892</v>
       </c>
       <c r="J36" t="n">
         <v>127.3033753857291</v>
@@ -40203,7 +40203,7 @@
         <v>-5.088162264342754</v>
       </c>
       <c r="E37" t="n">
-        <v>39.51575431044456</v>
+        <v>39.51576792072717</v>
       </c>
       <c r="F37" t="n">
         <v>5.373968208882274</v>
@@ -40235,7 +40235,7 @@
         <v>-9.425834207230599</v>
       </c>
       <c r="E38" t="n">
-        <v>39.77348672798779</v>
+        <v>39.77350033524889</v>
       </c>
       <c r="F38" t="n">
         <v>-1.762887330280316</v>
@@ -40247,7 +40247,7 @@
         <v>57.80926505349091</v>
       </c>
       <c r="I38" t="n">
-        <v>16.21144438360587</v>
+        <v>16.21145162100939</v>
       </c>
       <c r="J38" t="n">
         <v>124.1666581895616</v>
@@ -40267,7 +40267,7 @@
         <v>-7.586202295846512</v>
       </c>
       <c r="E39" t="n">
-        <v>40.77041965314101</v>
+        <v>40.77042925623107</v>
       </c>
       <c r="F39" t="n">
         <v>-0.3809562562003932</v>
@@ -40311,7 +40311,7 @@
         <v>62.45973288227488</v>
       </c>
       <c r="I40" t="n">
-        <v>1.128971419277369</v>
+        <v>1.128983084690516</v>
       </c>
       <c r="J40" t="n">
         <v>134.7826177095873</v>
@@ -40363,7 +40363,7 @@
         <v>-4.7715761302202</v>
       </c>
       <c r="E42" t="n">
-        <v>51.01852289181952</v>
+        <v>51.01853360181148</v>
       </c>
       <c r="F42" t="n">
         <v>0.8595328089425314</v>
@@ -40395,7 +40395,7 @@
         <v>-3.115572581757442</v>
       </c>
       <c r="E43" t="n">
-        <v>49.36975473509047</v>
+        <v>49.36975835587943</v>
       </c>
       <c r="F43" t="n">
         <v>4.18754296740822</v>
@@ -40427,7 +40427,7 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>50.46685642285065</v>
+        <v>50.46684566231154</v>
       </c>
       <c r="F44" t="n">
         <v>12.49999751647324</v>
@@ -40471,7 +40471,7 @@
         <v>71.45801931839102</v>
       </c>
       <c r="I45" t="n">
-        <v>12.16107377611635</v>
+        <v>12.16106689815384</v>
       </c>
       <c r="J45" t="n">
         <v>157.6646515776742</v>
@@ -40503,7 +40503,7 @@
         <v>82.7479978598209</v>
       </c>
       <c r="I46" t="n">
-        <v>8.66180909462404</v>
+        <v>8.661815725075982</v>
       </c>
       <c r="J46" t="n">
         <v>157.8527653163028</v>
@@ -40555,7 +40555,7 @@
         <v>6.467394340917232</v>
       </c>
       <c r="E48" t="n">
-        <v>46.27635349583639</v>
+        <v>46.2763635483981</v>
       </c>
       <c r="F48" t="n">
         <v>25.26545854048294</v>
@@ -40587,7 +40587,7 @@
         <v>8.154267621721157</v>
       </c>
       <c r="E49" t="n">
-        <v>46.82648416678226</v>
+        <v>46.82647017740005</v>
       </c>
       <c r="F49" t="n">
         <v>21.11271857609913</v>
@@ -40631,7 +40631,7 @@
         <v>62.06793961179837</v>
       </c>
       <c r="I50" t="n">
-        <v>10.18127599100154</v>
+        <v>10.18126922537272</v>
       </c>
       <c r="J50" t="n">
         <v>143.1579000203562</v>
@@ -40663,7 +40663,7 @@
         <v>51.29173068418904</v>
       </c>
       <c r="I51" t="n">
-        <v>9.556927218862565</v>
+        <v>9.556934045279553</v>
       </c>
       <c r="J51" t="n">
         <v>127.0114992297709</v>
@@ -40683,7 +40683,7 @@
         <v>3.767314869352423</v>
       </c>
       <c r="E52" t="n">
-        <v>42.74212492167262</v>
+        <v>42.7421148615067</v>
       </c>
       <c r="F52" t="n">
         <v>20.88757849896625</v>
@@ -40695,7 +40695,7 @@
         <v>48.54479267405647</v>
       </c>
       <c r="I52" t="n">
-        <v>8.042045115715425</v>
+        <v>8.042051785476056</v>
       </c>
       <c r="J52" t="n">
         <v>110.3013757156999</v>
@@ -40715,7 +40715,7 @@
         <v>-0.6521681215901576</v>
       </c>
       <c r="E53" t="n">
-        <v>36.68112349098636</v>
+        <v>36.68110950479731</v>
       </c>
       <c r="F53" t="n">
         <v>9.971790610249332</v>
@@ -40843,7 +40843,7 @@
         <v>-2.895437100396392</v>
       </c>
       <c r="E57" t="n">
-        <v>46.03767088371107</v>
+        <v>46.03765664399515</v>
       </c>
       <c r="F57" t="n">
         <v>17.16470691777749</v>
@@ -40855,7 +40855,7 @@
         <v>39.5845017315855</v>
       </c>
       <c r="I57" t="n">
-        <v>-4.840912057172886</v>
+        <v>-4.840900868211085</v>
       </c>
       <c r="J57" t="n">
         <v>61.69810163036917</v>
@@ -40875,7 +40875,7 @@
         <v>-4.116098444549698</v>
       </c>
       <c r="E58" t="n">
-        <v>41.38318530518315</v>
+        <v>41.38319910862871</v>
       </c>
       <c r="F58" t="n">
         <v>2.990288101739491</v>
@@ -40887,7 +40887,7 @@
         <v>45.31866297896825</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.8026833620259688</v>
+        <v>-0.8026716177200743</v>
       </c>
       <c r="J58" t="n">
         <v>70.97560603444168</v>
@@ -40907,7 +40907,7 @@
         <v>-4.293192033753879</v>
       </c>
       <c r="E59" t="n">
-        <v>43.82647727908604</v>
+        <v>43.82646747624919</v>
       </c>
       <c r="F59" t="n">
         <v>5.94736400403475</v>
@@ -40919,7 +40919,7 @@
         <v>42.8926386006018</v>
       </c>
       <c r="I59" t="n">
-        <v>12.67965743132262</v>
+        <v>12.67964407991673</v>
       </c>
       <c r="J59" t="n">
         <v>53.73333401150173</v>
@@ -40951,7 +40951,7 @@
         <v>49.51856946354882</v>
       </c>
       <c r="I60" t="n">
-        <v>5.712399359441078</v>
+        <v>5.712411417819085</v>
       </c>
       <c r="J60" t="n">
         <v>62.82512383653869</v>
@@ -40971,7 +40971,7 @@
         <v>-16.15763006192025</v>
       </c>
       <c r="E61" t="n">
-        <v>44.92179529589908</v>
+        <v>44.92178179656079</v>
       </c>
       <c r="F61" t="n">
         <v>-6.880840531123522</v>
@@ -41035,7 +41035,7 @@
         <v>-13.16582403069547</v>
       </c>
       <c r="E63" t="n">
-        <v>52.36659633483563</v>
+        <v>52.36658211824747</v>
       </c>
       <c r="F63" t="n">
         <v>-4.954792961494691</v>
@@ -41079,7 +41079,7 @@
         <v>52.6315695544544</v>
       </c>
       <c r="I64" t="n">
-        <v>7.77652325112117</v>
+        <v>7.776511389569785</v>
       </c>
       <c r="J64" t="n">
         <v>82.06088167389984</v>
@@ -41099,7 +41099,7 @@
         <v>-9.5696171627769</v>
       </c>
       <c r="E65" t="n">
-        <v>53.37992447951525</v>
+        <v>53.37991067295851</v>
       </c>
       <c r="F65" t="n">
         <v>-2.789282531167381</v>
@@ -41131,7 +41131,7 @@
         <v>-11.31513063255917</v>
       </c>
       <c r="E66" t="n">
-        <v>56.02260652743436</v>
+        <v>56.02259572511812</v>
       </c>
       <c r="F66" t="n">
         <v>-3.191753439454137</v>
@@ -41163,7 +41163,7 @@
         <v>-11.01736652795241</v>
       </c>
       <c r="E67" t="n">
-        <v>50.77263103718916</v>
+        <v>50.77261751103143</v>
       </c>
       <c r="F67" t="n">
         <v>-5.080884384452744</v>
@@ -41195,7 +41195,7 @@
         <v>-9.423563890822795</v>
       </c>
       <c r="E68" t="n">
-        <v>49.72388691054292</v>
+        <v>49.7238733754217</v>
       </c>
       <c r="F68" t="n">
         <v>-3.992768548930603</v>
@@ -41207,7 +41207,7 @@
         <v>70.46093895677912</v>
       </c>
       <c r="I68" t="n">
-        <v>8.984565541660317</v>
+        <v>8.984577771064984</v>
       </c>
       <c r="J68" t="n">
         <v>112.8708253134189</v>
@@ -41303,7 +41303,7 @@
         <v>51.19813928486645</v>
       </c>
       <c r="I71" t="n">
-        <v>10.13101918945343</v>
+        <v>10.13100675342484</v>
       </c>
       <c r="J71" t="n">
         <v>111.2230221092348</v>
@@ -41387,7 +41387,7 @@
         <v>-10.50251353091357</v>
       </c>
       <c r="E74" t="n">
-        <v>37.76564791574937</v>
+        <v>37.76563551471814</v>
       </c>
       <c r="F74" t="n">
         <v>-24.46927078175064</v>
@@ -41419,7 +41419,7 @@
         <v>-11.97995591778075</v>
       </c>
       <c r="E75" t="n">
-        <v>35.300020332275</v>
+        <v>35.3000326287824</v>
       </c>
       <c r="F75" t="n">
         <v>-18.87479351610046</v>
@@ -41451,7 +41451,7 @@
         <v>-11.60304744813735</v>
       </c>
       <c r="E76" t="n">
-        <v>32.8966170006417</v>
+        <v>32.89662954383419</v>
       </c>
       <c r="F76" t="n">
         <v>-17.12165045191634</v>
@@ -41463,7 +41463,7 @@
         <v>29.75552684353173</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.790587515014507</v>
+        <v>-0.7905768063145135</v>
       </c>
       <c r="J76" t="n">
         <v>87.39039515006255</v>
@@ -41483,7 +41483,7 @@
         <v>-16.59367383947344</v>
       </c>
       <c r="E77" t="n">
-        <v>27.44300298995188</v>
+        <v>27.44299051570651</v>
       </c>
       <c r="F77" t="n">
         <v>-16.99586307263094</v>
@@ -41495,7 +41495,7 @@
         <v>33.76771462059234</v>
       </c>
       <c r="I77" t="n">
-        <v>-4.073877140005555</v>
+        <v>-4.073887339170335</v>
       </c>
       <c r="J77" t="n">
         <v>91.51019660794005</v>
@@ -41515,7 +41515,7 @@
         <v>-19.17274342085357</v>
       </c>
       <c r="E78" t="n">
-        <v>26.50176570435701</v>
+        <v>26.50176102394366</v>
       </c>
       <c r="F78" t="n">
         <v>-14.20658392523141</v>
@@ -41527,7 +41527,7 @@
         <v>37.16040451905292</v>
       </c>
       <c r="I78" t="n">
-        <v>-5.63650099164782</v>
+        <v>-5.636511147977929</v>
       </c>
       <c r="J78" t="n">
         <v>92.88792469130138</v>
@@ -41591,7 +41591,7 @@
         <v>40.86671910305058</v>
       </c>
       <c r="I80" t="n">
-        <v>-9.661436663639901</v>
+        <v>-9.661446188750977</v>
       </c>
       <c r="J80" t="n">
         <v>86.33122815895915</v>
@@ -41611,7 +41611,7 @@
         <v>-24.76658411486981</v>
       </c>
       <c r="E81" t="n">
-        <v>28.57142580895549</v>
+        <v>28.5714340963751</v>
       </c>
       <c r="F81" t="n">
         <v>-16.15832902940159</v>
@@ -41623,7 +41623,7 @@
         <v>44.05244047508194</v>
       </c>
       <c r="I81" t="n">
-        <v>-11.30202615532158</v>
+        <v>-11.30203542552404</v>
       </c>
       <c r="J81" t="n">
         <v>86.99152692711512</v>
@@ -41643,7 +41643,7 @@
         <v>-27.62790502503861</v>
       </c>
       <c r="E82" t="n">
-        <v>26.98314730158067</v>
+        <v>26.98314264407708</v>
       </c>
       <c r="F82" t="n">
         <v>-15.09280158634767</v>
@@ -41675,7 +41675,7 @@
         <v>-34.48276159737812</v>
       </c>
       <c r="E83" t="n">
-        <v>28.51446747407287</v>
+        <v>28.51448033045003</v>
       </c>
       <c r="F83" t="n">
         <v>-19.74900728652863</v>
@@ -41719,7 +41719,7 @@
         <v>59.40775106485634</v>
       </c>
       <c r="I84" t="n">
-        <v>-12.47749649193932</v>
+        <v>-12.47750519719089</v>
       </c>
       <c r="J84" t="n">
         <v>99.06541697895044</v>
@@ -41739,7 +41739,7 @@
         <v>-24.665128160175</v>
       </c>
       <c r="E85" t="n">
-        <v>27.92017608149169</v>
+        <v>27.92016784817664</v>
       </c>
       <c r="F85" t="n">
         <v>-16.67054649645153</v>
@@ -41771,7 +41771,7 @@
         <v>-26.6666637832975</v>
       </c>
       <c r="E86" t="n">
-        <v>28.70115663257717</v>
+        <v>28.70116495989465</v>
       </c>
       <c r="F86" t="n">
         <v>-17.14285992776975</v>
@@ -41803,7 +41803,7 @@
         <v>-26.10859890573426</v>
       </c>
       <c r="E87" t="n">
-        <v>30.99702123862926</v>
+        <v>30.99703429220788</v>
       </c>
       <c r="F87" t="n">
         <v>-18.06414822509883</v>
@@ -41815,7 +41815,7 @@
         <v>62.23634673800827</v>
       </c>
       <c r="I87" t="n">
-        <v>-12.2486586628829</v>
+        <v>-12.24866669743097</v>
       </c>
       <c r="J87" t="n">
         <v>102.6548604601487</v>
@@ -41835,7 +41835,7 @@
         <v>-27.29792125425134</v>
       </c>
       <c r="E88" t="n">
-        <v>26.79485831618089</v>
+        <v>26.79487970919705</v>
       </c>
       <c r="F88" t="n">
         <v>-22.44094964591114</v>
@@ -41899,7 +41899,7 @@
         <v>-25.66037895417199</v>
       </c>
       <c r="E90" t="n">
-        <v>28.18202818962325</v>
+        <v>28.1820197606033</v>
       </c>
       <c r="F90" t="n">
         <v>-21.60274235468711</v>
@@ -41931,7 +41931,7 @@
         <v>-27.11316392142076</v>
       </c>
       <c r="E91" t="n">
-        <v>23.32125845384157</v>
+        <v>23.32124539191589</v>
       </c>
       <c r="F91" t="n">
         <v>-24.73446258717338</v>
@@ -41995,7 +41995,7 @@
         <v>-33.75854461744496</v>
       </c>
       <c r="E93" t="n">
-        <v>13.49678679972988</v>
+        <v>13.49679986444057</v>
       </c>
       <c r="F93" t="n">
         <v>-33.28873780551388</v>
@@ -42027,7 +42027,7 @@
         <v>-32.86343938807552</v>
       </c>
       <c r="E94" t="n">
-        <v>13.0281626461012</v>
+        <v>13.02817533738021</v>
       </c>
       <c r="F94" t="n">
         <v>-31.92243919478229</v>
@@ -42091,7 +42091,7 @@
         <v>-39.19354682410292</v>
       </c>
       <c r="E96" t="n">
-        <v>14.19141889163848</v>
+        <v>14.19141167535614</v>
       </c>
       <c r="F96" t="n">
         <v>-43.65987090351605</v>
@@ -42123,7 +42123,7 @@
         <v>-37.38589247413267</v>
       </c>
       <c r="E97" t="n">
-        <v>15.21784099939436</v>
+        <v>15.21784828805857</v>
       </c>
       <c r="F97" t="n">
         <v>-43.28643185409469</v>
@@ -42135,7 +42135,7 @@
         <v>20.58264671468648</v>
       </c>
       <c r="I97" t="n">
-        <v>-25.00399542027211</v>
+        <v>-25.00400219946962</v>
       </c>
       <c r="J97" t="n">
         <v>34.37700446807093</v>
@@ -42155,7 +42155,7 @@
         <v>-36.22489816175252</v>
       </c>
       <c r="E98" t="n">
-        <v>14.42208246479413</v>
+        <v>14.42207519042114</v>
       </c>
       <c r="F98" t="n">
         <v>-52.13567772568902</v>
@@ -42263,7 +42263,7 @@
         <v>17.94541203322633</v>
       </c>
       <c r="I101" t="n">
-        <v>-31.17109576206706</v>
+        <v>-31.17108993672595</v>
       </c>
       <c r="J101" t="n">
         <v>28.66883782396286</v>
@@ -42295,7 +42295,7 @@
         <v>18.40919658725724</v>
       </c>
       <c r="I102" t="n">
-        <v>-29.82359782494049</v>
+        <v>-29.82360396246734</v>
       </c>
       <c r="J102" t="n">
         <v>28.18636085107484</v>
@@ -42315,7 +42315,7 @@
         <v>-37.47898911160345</v>
       </c>
       <c r="E103" t="n">
-        <v>-3.813640407312757</v>
+        <v>-3.813646722865827</v>
       </c>
       <c r="F103" t="n">
         <v>-61.42636857635259</v>
@@ -42347,7 +42347,7 @@
         <v>-38.02935221563132</v>
       </c>
       <c r="E104" t="n">
-        <v>-4.049327871322895</v>
+        <v>-4.049334168701613</v>
       </c>
       <c r="F104" t="n">
         <v>-60.6574271929146</v>
@@ -42475,7 +42475,7 @@
         <v>-34.87069327681005</v>
       </c>
       <c r="E108" t="n">
-        <v>0.6920954001579327</v>
+        <v>0.6920890135108326</v>
       </c>
       <c r="F108" t="n">
         <v>-56.18415731425067</v>
@@ -42507,7 +42507,7 @@
         <v>-38.2809222994163</v>
       </c>
       <c r="E109" t="n">
-        <v>-6.784861443789014</v>
+        <v>-6.78485575492701</v>
       </c>
       <c r="F109" t="n">
         <v>-56.1025635808961</v>
@@ -42539,7 +42539,7 @@
         <v>-38.41336313097599</v>
       </c>
       <c r="E110" t="n">
-        <v>-1.049651814667596</v>
+        <v>-1.049657998912068</v>
       </c>
       <c r="F110" t="n">
         <v>-55.1449584922653</v>
@@ -42571,7 +42571,7 @@
         <v>-38.03757962483449</v>
       </c>
       <c r="E111" t="n">
-        <v>0.6324251301784045</v>
+        <v>0.632431300721481</v>
       </c>
       <c r="F111" t="n">
         <v>-54.47863391321948</v>
@@ -42583,7 +42583,7 @@
         <v>10.12767521636539</v>
       </c>
       <c r="I111" t="n">
-        <v>-30.90739167300298</v>
+        <v>-30.90738562405075</v>
       </c>
       <c r="J111" t="n">
         <v>33.95972882878166</v>
@@ -42635,7 +42635,7 @@
         <v>-38.7500007947286</v>
       </c>
       <c r="E113" t="n">
-        <v>-1.713949720608687</v>
+        <v>-1.713949824055983</v>
       </c>
       <c r="F113" t="n">
         <v>-54.22889949879295</v>
@@ -42647,7 +42647,7 @@
         <v>29.08312860522841</v>
       </c>
       <c r="I113" t="n">
-        <v>-31.15946839130254</v>
+        <v>-31.15946227398697</v>
       </c>
       <c r="J113" t="n">
         <v>45.27778215614377</v>
@@ -42667,7 +42667,7 @@
         <v>-42.96153875497671</v>
       </c>
       <c r="E114" t="n">
-        <v>-15.959870204464</v>
+        <v>-15.95987381179289</v>
       </c>
       <c r="F114" t="n">
         <v>-55.92657561500155</v>
@@ -42679,7 +42679,7 @@
         <v>32.61072830164626</v>
       </c>
       <c r="I114" t="n">
-        <v>-32.44485757880052</v>
+        <v>-32.44486357995042</v>
       </c>
       <c r="J114" t="n">
         <v>49.6350385796072</v>
@@ -42763,7 +42763,7 @@
         <v>-44.84615325927734</v>
       </c>
       <c r="E117" t="n">
-        <v>-13.21917958333557</v>
+        <v>-13.21917375442618</v>
       </c>
       <c r="F117" t="n">
         <v>-55.92658828357197</v>
@@ -42827,7 +42827,7 @@
         <v>-41.87633402561816</v>
       </c>
       <c r="E119" t="n">
-        <v>-18.05122097776638</v>
+        <v>-18.0512117287556</v>
       </c>
       <c r="F119" t="n">
         <v>-56.31058995863971</v>
@@ -42859,7 +42859,7 @@
         <v>-42.79069788072998</v>
       </c>
       <c r="E120" t="n">
-        <v>-18.96607964296703</v>
+        <v>-18.96608874513238</v>
       </c>
       <c r="F120" t="n">
         <v>-56.69829342607511</v>
@@ -42871,7 +42871,7 @@
         <v>18.29646125327557</v>
       </c>
       <c r="I120" t="n">
-        <v>-38.54754901090875</v>
+        <v>-38.54755466140228</v>
       </c>
       <c r="J120" t="n">
         <v>41.19001864296059</v>
@@ -42891,7 +42891,7 @@
         <v>-41.32780033399969</v>
       </c>
       <c r="E121" t="n">
-        <v>-16.14651905964717</v>
+        <v>-16.14652467077281</v>
       </c>
       <c r="F121" t="n">
         <v>-57.14155223271617</v>
@@ -42903,7 +42903,7 @@
         <v>11.82631761961019</v>
       </c>
       <c r="I121" t="n">
-        <v>-37.32897961116035</v>
+        <v>-37.32898531697771</v>
       </c>
       <c r="J121" t="n">
         <v>43.47825961545257</v>
@@ -43019,7 +43019,7 @@
         <v>-44.06438871165855</v>
       </c>
       <c r="E125" t="n">
-        <v>-19.65921433551706</v>
+        <v>-19.65920559792231</v>
       </c>
       <c r="F125" t="n">
         <v>-62.04201834542411</v>
@@ -43083,7 +43083,7 @@
         <v>-45.25879720144958</v>
       </c>
       <c r="E127" t="n">
-        <v>-31.44790974132207</v>
+        <v>-31.44791479939482</v>
       </c>
       <c r="F127" t="n">
         <v>-64.48646305395978</v>
@@ -43095,7 +43095,7 @@
         <v>-7.626934073983682</v>
       </c>
       <c r="I127" t="n">
-        <v>-45.25499703566405</v>
+        <v>-45.25499235353499</v>
       </c>
       <c r="J127" t="n">
         <v>29.66861136912165</v>
@@ -43211,7 +43211,7 @@
         <v>-38.22222391764323</v>
       </c>
       <c r="E131" t="n">
-        <v>-28.66038601708145</v>
+        <v>-28.66039098574015</v>
       </c>
       <c r="F131" t="n">
         <v>-60.87921861989671</v>
@@ -43243,7 +43243,7 @@
         <v>-37.71428537892771</v>
       </c>
       <c r="E132" t="n">
-        <v>-28.44839309277756</v>
+        <v>-28.44838815136688</v>
       </c>
       <c r="F132" t="n">
         <v>-57.52336377295379</v>
@@ -43275,7 +43275,7 @@
         <v>-39.29359721158256</v>
       </c>
       <c r="E133" t="n">
-        <v>-31.89681766180208</v>
+        <v>-31.89682422506088</v>
       </c>
       <c r="F133" t="n">
         <v>-56.86676433086298</v>
@@ -43339,7 +43339,7 @@
         <v>-39.18181766163219</v>
       </c>
       <c r="E135" t="n">
-        <v>-29.89430845995157</v>
+        <v>-29.8943198980845</v>
       </c>
       <c r="F135" t="n">
         <v>-55.97900230427739</v>
@@ -43351,7 +43351,7 @@
         <v>-2.809878783828057</v>
       </c>
       <c r="I135" t="n">
-        <v>-44.35211986444345</v>
+        <v>-44.35211507824253</v>
       </c>
       <c r="J135" t="n">
         <v>45.94360305036773</v>
@@ -43403,7 +43403,7 @@
         <v>-41.2641063072619</v>
       </c>
       <c r="E137" t="n">
-        <v>-34.25575730483226</v>
+        <v>-34.25576189254548</v>
       </c>
       <c r="F137" t="n">
         <v>-56.62921337306769</v>
@@ -43415,7 +43415,7 @@
         <v>-0.8227812344208774</v>
       </c>
       <c r="I137" t="n">
-        <v>-43.53504193146073</v>
+        <v>-43.53503687932449</v>
       </c>
       <c r="J137" t="n">
         <v>46.43016219484324</v>
@@ -43435,7 +43435,7 @@
         <v>-38.77646951114431</v>
       </c>
       <c r="E138" t="n">
-        <v>-38.27638938277526</v>
+        <v>-38.27639900697836</v>
       </c>
       <c r="F138" t="n">
         <v>-55.96958453493185</v>
@@ -43447,7 +43447,7 @@
         <v>-1.909228316656353</v>
       </c>
       <c r="I138" t="n">
-        <v>-42.02479084880196</v>
+        <v>-42.02479617480736</v>
       </c>
       <c r="J138" t="n">
         <v>46.43016219484324</v>
@@ -43467,7 +43467,7 @@
         <v>-33.90243809397627</v>
       </c>
       <c r="E139" t="n">
-        <v>-36.75832572741635</v>
+        <v>-36.75832996076532</v>
       </c>
       <c r="F139" t="n">
         <v>-49.86285836356027</v>
@@ -43531,7 +43531,7 @@
         <v>-32.12871524589028</v>
       </c>
       <c r="E141" t="n">
-        <v>-32.2831469020805</v>
+        <v>-32.28313624311352</v>
       </c>
       <c r="F141" t="n">
         <v>-43.95747457582054</v>
@@ -43543,7 +43543,7 @@
         <v>11.78529754959159</v>
       </c>
       <c r="I141" t="n">
-        <v>-32.26879864064875</v>
+        <v>-32.26880534741482</v>
       </c>
       <c r="J141" t="n">
         <v>79.66746349443316</v>
@@ -43563,7 +43563,7 @@
         <v>-31.4987748448557</v>
       </c>
       <c r="E142" t="n">
-        <v>-32.50761786349332</v>
+        <v>-32.50762230682122</v>
       </c>
       <c r="F142" t="n">
         <v>-46.5503629780039</v>
@@ -43575,7 +43575,7 @@
         <v>2.585262900904595</v>
       </c>
       <c r="I142" t="n">
-        <v>-31.06491760499416</v>
+        <v>-31.06492450679491</v>
       </c>
       <c r="J142" t="n">
         <v>72.89592047478308</v>
@@ -43595,7 +43595,7 @@
         <v>-33.84615297239228</v>
       </c>
       <c r="E143" t="n">
-        <v>-35.46164071660527</v>
+        <v>-35.46163637158381</v>
       </c>
       <c r="F143" t="n">
         <v>-51.06795889575086</v>
@@ -43627,7 +43627,7 @@
         <v>-33.90862967753029</v>
       </c>
       <c r="E144" t="n">
-        <v>-36.97424007121808</v>
+        <v>-36.97423460587854</v>
       </c>
       <c r="F144" t="n">
         <v>-49.50652575035288</v>
@@ -43639,7 +43639,7 @@
         <v>5.829856359310237</v>
       </c>
       <c r="I144" t="n">
-        <v>-32.77704585719886</v>
+        <v>-32.77705273110023</v>
       </c>
       <c r="J144" t="n">
         <v>73.11404623446703</v>
@@ -43659,7 +43659,7 @@
         <v>-32.57731865513828</v>
       </c>
       <c r="E145" t="n">
-        <v>-33.10222787693342</v>
+        <v>-33.10222333815624</v>
       </c>
       <c r="F145" t="n">
         <v>-47.72093129712481</v>
@@ -43691,7 +43691,7 @@
         <v>-32.98968940399975</v>
       </c>
       <c r="E146" t="n">
-        <v>-32.82847077144174</v>
+        <v>-32.82846017281587</v>
       </c>
       <c r="F146" t="n">
         <v>-50.13210990744989</v>
@@ -43755,7 +43755,7 @@
         <v>-32.69521712881676</v>
       </c>
       <c r="E148" t="n">
-        <v>-33.61837794033982</v>
+        <v>-33.61837206509205</v>
       </c>
       <c r="F148" t="n">
         <v>-50.8521140595779</v>
@@ -43851,7 +43851,7 @@
         <v>-42.04651145047919</v>
       </c>
       <c r="E151" t="n">
-        <v>-40.1821013090503</v>
+        <v>-40.1821004663875</v>
       </c>
       <c r="F151" t="n">
         <v>-54.39159419656274</v>
@@ -43883,7 +43883,7 @@
         <v>-39.58139641340389</v>
       </c>
       <c r="E152" t="n">
-        <v>-37.04564463586239</v>
+        <v>-37.04565432657586</v>
       </c>
       <c r="F152" t="n">
         <v>-53.60400625525475</v>
@@ -43915,7 +43915,7 @@
         <v>-41.59453644999592</v>
       </c>
       <c r="E153" t="n">
-        <v>-38.13497790868293</v>
+        <v>-38.13498321627997</v>
       </c>
       <c r="F153" t="n">
         <v>-55.56276981035423</v>
@@ -43927,7 +43927,7 @@
         <v>-16.46675455896869</v>
       </c>
       <c r="I153" t="n">
-        <v>-41.94473043279401</v>
+        <v>-41.94472512215197</v>
       </c>
       <c r="J153" t="n">
         <v>22.64151237635372</v>
@@ -43959,7 +43959,7 @@
         <v>-15.20339189949682</v>
       </c>
       <c r="I154" t="n">
-        <v>-40.56723806517864</v>
+        <v>-40.56723259305854</v>
       </c>
       <c r="J154" t="n">
         <v>20.02998683900788</v>
@@ -43979,7 +43979,7 @@
         <v>-39.45701410186536</v>
       </c>
       <c r="E155" t="n">
-        <v>-36.07449555886241</v>
+        <v>-36.07449031108776</v>
       </c>
       <c r="F155" t="n">
         <v>-51.83269228782829</v>
@@ -44023,7 +44023,7 @@
         <v>-11.96105995313918</v>
       </c>
       <c r="I156" t="n">
-        <v>-35.97284968089498</v>
+        <v>-35.9728436726354</v>
       </c>
       <c r="J156" t="n">
         <v>34.93548977759578</v>
@@ -44075,7 +44075,7 @@
         <v>-34.9769623935906</v>
       </c>
       <c r="E158" t="n">
-        <v>-33.49170244123877</v>
+        <v>-33.49169830616715</v>
       </c>
       <c r="F158" t="n">
         <v>-49.31460605578476</v>
@@ -44119,7 +44119,7 @@
         <v>34.79139711401707</v>
       </c>
       <c r="I159" t="n">
-        <v>-31.78687811577813</v>
+        <v>-31.78687157655621</v>
       </c>
       <c r="J159" t="n">
         <v>59.30529830757856</v>
@@ -44139,7 +44139,7 @@
         <v>-29.01205039886107</v>
       </c>
       <c r="E160" t="n">
-        <v>-27.1408366814982</v>
+        <v>-27.14083902839913</v>
       </c>
       <c r="F160" t="n">
         <v>-46.60070067860755</v>
@@ -44183,7 +44183,7 @@
         <v>38.5684914172453</v>
       </c>
       <c r="I161" t="n">
-        <v>-29.74189607402291</v>
+        <v>-29.7419029828034</v>
       </c>
       <c r="J161" t="n">
         <v>62.23034118107906</v>
@@ -44203,7 +44203,7 @@
         <v>-36.22727394104004</v>
       </c>
       <c r="E162" t="n">
-        <v>-33.12631667581559</v>
+        <v>-33.12632209017097</v>
       </c>
       <c r="F162" t="n">
         <v>-51.18435907630281</v>
@@ -44235,7 +44235,7 @@
         <v>-36.56108499654562</v>
       </c>
       <c r="E163" t="n">
-        <v>-30.31613958799745</v>
+        <v>-30.31612554162724</v>
       </c>
       <c r="F163" t="n">
         <v>-50.39954164408403</v>
@@ -44267,7 +44267,7 @@
         <v>-37.483146753204</v>
       </c>
       <c r="E164" t="n">
-        <v>-32.68094753767251</v>
+        <v>-32.68096093226646</v>
       </c>
       <c r="F164" t="n">
         <v>-48.08486004347705</v>
@@ -44299,7 +44299,7 @@
         <v>-40.39734998955379</v>
       </c>
       <c r="E165" t="n">
-        <v>-32.87279104672564</v>
+        <v>-32.87279634781893</v>
       </c>
       <c r="F165" t="n">
         <v>-50.55082406989408</v>
@@ -44331,7 +44331,7 @@
         <v>-40.43955960116543</v>
       </c>
       <c r="E166" t="n">
-        <v>-32.08065123048447</v>
+        <v>-32.08065667981757</v>
       </c>
       <c r="F166" t="n">
         <v>-53.59653548729015</v>
@@ -44343,7 +44343,7 @@
         <v>31.32498904941086</v>
       </c>
       <c r="I166" t="n">
-        <v>-34.25830666893714</v>
+        <v>-34.25831287796005</v>
       </c>
       <c r="J166" t="n">
         <v>45.76086589203896</v>
@@ -44363,7 +44363,7 @@
         <v>-38.52349200624654</v>
       </c>
       <c r="E167" t="n">
-        <v>-31.8336393401792</v>
+        <v>-31.83363387746486</v>
       </c>
       <c r="F167" t="n">
         <v>-53.46630744214328</v>
@@ -44375,7 +44375,7 @@
         <v>33.09109889422288</v>
       </c>
       <c r="I167" t="n">
-        <v>-32.89464226978117</v>
+        <v>-32.89463592347094</v>
       </c>
       <c r="J167" t="n">
         <v>48.14546064897016</v>
@@ -44491,7 +44491,7 @@
         <v>-40.04556086562169</v>
       </c>
       <c r="E171" t="n">
-        <v>-34.58448249718911</v>
+        <v>-34.58447846232172</v>
       </c>
       <c r="F171" t="n">
         <v>-51.04838688412199</v>
@@ -44535,7 +44535,7 @@
         <v>44.92055080938697</v>
       </c>
       <c r="I172" t="n">
-        <v>-32.8123236456485</v>
+        <v>-32.81231725705731</v>
       </c>
       <c r="J172" t="n">
         <v>59.58955849005739</v>
@@ -44555,7 +44555,7 @@
         <v>-32.91375369932255</v>
       </c>
       <c r="E173" t="n">
-        <v>-27.77852341218486</v>
+        <v>-27.77852938823074</v>
       </c>
       <c r="F173" t="n">
         <v>-43.44699349358814</v>
@@ -44587,7 +44587,7 @@
         <v>-30.59382334344727</v>
       </c>
       <c r="E174" t="n">
-        <v>-24.91227355035074</v>
+        <v>-24.91228000773636</v>
       </c>
       <c r="F174" t="n">
         <v>-41.76249980926514</v>
@@ -44683,7 +44683,7 @@
         <v>-26.87499713439198</v>
       </c>
       <c r="E177" t="n">
-        <v>-20.35359835800773</v>
+        <v>-20.35360537283162</v>
       </c>
       <c r="F177" t="n">
         <v>-38.99999765249399</v>
@@ -44715,7 +44715,7 @@
         <v>-27.66264949936464</v>
       </c>
       <c r="E178" t="n">
-        <v>-20.47750781759832</v>
+        <v>-20.47751679276931</v>
       </c>
       <c r="F178" t="n">
         <v>-39.01896560774591</v>
@@ -44747,7 +44747,7 @@
         <v>-28.19905523871372</v>
       </c>
       <c r="E179" t="n">
-        <v>-22.15916869716422</v>
+        <v>-22.15917738967272</v>
       </c>
       <c r="F179" t="n">
         <v>-41.81931635301061</v>
@@ -44779,7 +44779,7 @@
         <v>-27.29016992783636</v>
       </c>
       <c r="E180" t="n">
-        <v>-22.41063438366677</v>
+        <v>-22.41062766588845</v>
       </c>
       <c r="F180" t="n">
         <v>-39.6770169275888</v>
@@ -44791,7 +44791,7 @@
         <v>65.15150572053405</v>
       </c>
       <c r="I180" t="n">
-        <v>-25.31921329761254</v>
+        <v>-25.31920577234636</v>
       </c>
       <c r="J180" t="n">
         <v>72.82946306655833</v>
@@ -44811,7 +44811,7 @@
         <v>-26.03864804185331</v>
       </c>
       <c r="E181" t="n">
-        <v>-20.64498270087283</v>
+        <v>-20.64497407201848</v>
       </c>
       <c r="F181" t="n">
         <v>-39.39168486008041</v>
@@ -44843,7 +44843,7 @@
         <v>-27.65957226150498</v>
       </c>
       <c r="E182" t="n">
-        <v>-21.12262914734645</v>
+        <v>-21.12262057043012</v>
       </c>
       <c r="F182" t="n">
         <v>-38.78824946197358</v>
@@ -44907,7 +44907,7 @@
         <v>-26.79245330549804</v>
       </c>
       <c r="E184" t="n">
-        <v>-18.81726817858214</v>
+        <v>-18.81728369892127</v>
       </c>
       <c r="F184" t="n">
         <v>-35.9392113960985</v>
@@ -44919,7 +44919,7 @@
         <v>84.22466480357787</v>
       </c>
       <c r="I184" t="n">
-        <v>-25.14133965790279</v>
+        <v>-25.14133222869045</v>
       </c>
       <c r="J184" t="n">
         <v>90.30188794405956</v>
@@ -44951,7 +44951,7 @@
         <v>88.55766356470485</v>
       </c>
       <c r="I185" t="n">
-        <v>-25.0215553060073</v>
+        <v>-25.02156280830814</v>
       </c>
       <c r="J185" t="n">
         <v>97.80303778508271</v>
@@ -44971,7 +44971,7 @@
         <v>-25.23364352705133</v>
       </c>
       <c r="E186" t="n">
-        <v>-21.55172688455815</v>
+        <v>-21.55172030710867</v>
       </c>
       <c r="F186" t="n">
         <v>-33.64963145939185</v>
@@ -45067,7 +45067,7 @@
         <v>-24.3749994268784</v>
       </c>
       <c r="E189" t="n">
-        <v>-16.85279894143548</v>
+        <v>-16.85281500968847</v>
       </c>
       <c r="F189" t="n">
         <v>-28.89460472383064</v>
@@ -45079,7 +45079,7 @@
         <v>123.2258100313875</v>
       </c>
       <c r="I189" t="n">
-        <v>-21.52762332811739</v>
+        <v>-21.52763130838451</v>
       </c>
       <c r="J189" t="n">
         <v>141.7857081765763</v>
@@ -45099,7 +45099,7 @@
         <v>-23.35766138815261</v>
       </c>
       <c r="E190" t="n">
-        <v>-16.1754097615417</v>
+        <v>-16.17542595647212</v>
       </c>
       <c r="F190" t="n">
         <v>-32.43977679001436</v>
@@ -45163,7 +45163,7 @@
         <v>-24.58234073821581</v>
       </c>
       <c r="E192" t="n">
-        <v>-14.560524436397</v>
+        <v>-14.56051583298611</v>
       </c>
       <c r="F192" t="n">
         <v>-31.51477378726198</v>
@@ -45195,7 +45195,7 @@
         <v>-17.57731914672299</v>
       </c>
       <c r="E193" t="n">
-        <v>-9.055420169258021</v>
+        <v>-9.055419336014003</v>
       </c>
       <c r="F193" t="n">
         <v>-24.49735055141047</v>
@@ -45207,7 +45207,7 @@
         <v>159.4421378782054</v>
       </c>
       <c r="I193" t="n">
-        <v>-7.811480422264172</v>
+        <v>-7.811469801544069</v>
       </c>
       <c r="J193" t="n">
         <v>190.7755014847736</v>
@@ -45227,7 +45227,7 @@
         <v>-19.49875262272378</v>
       </c>
       <c r="E194" t="n">
-        <v>-12.42766767500797</v>
+        <v>-12.4276599118963</v>
       </c>
       <c r="F194" t="n">
         <v>-25.51905198204355</v>
@@ -45259,7 +45259,7 @@
         <v>-22.51231461369236</v>
       </c>
       <c r="E195" t="n">
-        <v>-15.28334387731973</v>
+        <v>-15.28333644903409</v>
       </c>
       <c r="F195" t="n">
         <v>-30.90795338358637</v>
@@ -45355,7 +45355,7 @@
         <v>-30.62730742553335</v>
       </c>
       <c r="E198" t="n">
-        <v>-17.25910245924941</v>
+        <v>-17.25910396892187</v>
       </c>
       <c r="F198" t="n">
         <v>-33.52514665157967</v>
@@ -45387,7 +45387,7 @@
         <v>-33.10871432964622</v>
       </c>
       <c r="E199" t="n">
-        <v>-20.1689956791109</v>
+        <v>-20.16900416692024</v>
       </c>
       <c r="F199" t="n">
         <v>-36.51537018870842</v>
@@ -45515,7 +45515,7 @@
         <v>-33.21586194762303</v>
       </c>
       <c r="E203" t="n">
-        <v>-16.04799614881611</v>
+        <v>-16.04800469940202</v>
       </c>
       <c r="F203" t="n">
         <v>-36.18741564478685</v>
@@ -45547,7 +45547,7 @@
         <v>-29.41952771061378</v>
       </c>
       <c r="E204" t="n">
-        <v>-17.02912959365807</v>
+        <v>-17.02914492844722</v>
       </c>
       <c r="F204" t="n">
         <v>-26.48352671295293</v>
@@ -45611,7 +45611,7 @@
         <v>-29.47645838329669</v>
       </c>
       <c r="E206" t="n">
-        <v>-8.977062831240701</v>
+        <v>-8.977070678845955</v>
       </c>
       <c r="F206" t="n">
         <v>-28.80289813678555</v>
@@ -45675,7 +45675,7 @@
         <v>-27.65476350642918</v>
       </c>
       <c r="E208" t="n">
-        <v>-7.480690033325899</v>
+        <v>-7.480697989790852</v>
       </c>
       <c r="F208" t="n">
         <v>-28.56085470297766</v>
@@ -45707,7 +45707,7 @@
         <v>-26.7097961922128</v>
       </c>
       <c r="E209" t="n">
-        <v>-7.60746146904766</v>
+        <v>-7.607452804809</v>
       </c>
       <c r="F209" t="n">
         <v>-28.01413821889418</v>
@@ -45739,7 +45739,7 @@
         <v>-26.72176522045333</v>
       </c>
       <c r="E210" t="n">
-        <v>-9.241946894024998</v>
+        <v>-9.241938339858734</v>
       </c>
       <c r="F210" t="n">
         <v>-27.03415236602241</v>
@@ -45771,7 +45771,7 @@
         <v>-27.28512988836156</v>
       </c>
       <c r="E211" t="n">
-        <v>-7.893973574240542</v>
+        <v>-7.893982258126419</v>
       </c>
       <c r="F211" t="n">
         <v>-31.35418360746799</v>
@@ -45835,7 +45835,7 @@
         <v>-32.08351066583373</v>
       </c>
       <c r="E213" t="n">
-        <v>-6.390539985580757</v>
+        <v>-6.390548149228259</v>
       </c>
       <c r="F213" t="n">
         <v>-36.81710406455739</v>
@@ -45899,7 +45899,7 @@
         <v>-31.69662302286084</v>
       </c>
       <c r="E215" t="n">
-        <v>-5.981569662750863</v>
+        <v>-5.981578347866867</v>
       </c>
       <c r="F215" t="n">
         <v>-35.00641823830535</v>
@@ -45931,7 +45931,7 @@
         <v>-33.33333747254461</v>
       </c>
       <c r="E216" t="n">
-        <v>-6.459947047595593</v>
+        <v>-6.459955843676058</v>
       </c>
       <c r="F216" t="n">
         <v>-35.39603519665386</v>
@@ -45995,7 +45995,7 @@
         <v>-31.83196333000435</v>
       </c>
       <c r="E218" t="n">
-        <v>-7.687890327936886</v>
+        <v>-7.68788219992188</v>
       </c>
       <c r="F218" t="n">
         <v>-32.37436156607637</v>
@@ -46123,7 +46123,7 @@
         <v>-36.29064639593801</v>
       </c>
       <c r="E222" t="n">
-        <v>-7.84314091942816</v>
+        <v>-7.843132019864541</v>
       </c>
       <c r="F222" t="n">
         <v>-28.89180566823137</v>
@@ -46283,7 +46283,7 @@
         <v>-34.85313456992967</v>
       </c>
       <c r="E227" t="n">
-        <v>-8.171498781349463</v>
+        <v>-8.1714896278546</v>
       </c>
       <c r="F227" t="n">
         <v>-32.55395806851909</v>
@@ -46315,7 +46315,7 @@
         <v>-36.55056678989862</v>
       </c>
       <c r="E228" t="n">
-        <v>-2.460506794340878</v>
+        <v>-2.460515871778712</v>
       </c>
       <c r="F228" t="n">
         <v>-33.03285408680733</v>
@@ -46347,7 +46347,7 @@
         <v>-37.24916312288149</v>
       </c>
       <c r="E229" t="n">
-        <v>-3.495035167181182</v>
+        <v>-3.495026259081291</v>
       </c>
       <c r="F229" t="n">
         <v>-38.67234368945173</v>
@@ -46411,7 +46411,7 @@
         <v>-37.52585712120092</v>
       </c>
       <c r="E231" t="n">
-        <v>0.04553419329549335</v>
+        <v>0.04555280190197131</v>
       </c>
       <c r="F231" t="n">
         <v>-36.82532653673968</v>
@@ -46507,7 +46507,7 @@
         <v>-37.23450483839871</v>
       </c>
       <c r="E234" t="n">
-        <v>0.09195250322659998</v>
+        <v>0.09194310401834382</v>
       </c>
       <c r="F234" t="n">
         <v>-38.63636103394656</v>
@@ -46539,7 +46539,7 @@
         <v>-34.25161045286568</v>
       </c>
       <c r="E235" t="n">
-        <v>2.665208703368349</v>
+        <v>2.665199040303001</v>
       </c>
       <c r="F235" t="n">
         <v>-35.84453808293154</v>
@@ -46667,7 +46667,7 @@
         <v>-33.56353240626703</v>
       </c>
       <c r="E239" t="n">
-        <v>1.693959968986869</v>
+        <v>1.693950400277155</v>
       </c>
       <c r="F239" t="n">
         <v>-43.07445745551136</v>
@@ -46891,7 +46891,7 @@
         <v>-31.36067022065163</v>
       </c>
       <c r="E246" t="n">
-        <v>-3.292501612801146</v>
+        <v>-3.292492664437496</v>
       </c>
       <c r="F246" t="n">
         <v>-44.01419291641084</v>
@@ -47019,7 +47019,7 @@
         <v>-32.32134575251007</v>
       </c>
       <c r="E250" t="n">
-        <v>-2.799844619809422</v>
+        <v>-2.79985382220842</v>
       </c>
       <c r="F250" t="n">
         <v>-45.22397009414632</v>
@@ -47051,7 +47051,7 @@
         <v>-31.40301388027185</v>
       </c>
       <c r="E251" t="n">
-        <v>-3.107483694785163</v>
+        <v>-3.107492906488285</v>
       </c>
       <c r="F251" t="n">
         <v>-44.10021926081409</v>
@@ -47115,7 +47115,7 @@
         <v>-30.50687043040482</v>
       </c>
       <c r="E253" t="n">
-        <v>-3.657896195424548</v>
+        <v>-3.657905370458425</v>
       </c>
       <c r="F253" t="n">
         <v>-43.2534700274485</v>
@@ -47179,7 +47179,7 @@
         <v>-28.36398693106126</v>
       </c>
       <c r="E255" t="n">
-        <v>-11.0265174091879</v>
+        <v>-11.02652519290564</v>
       </c>
       <c r="F255" t="n">
         <v>-40.86610764775907</v>
@@ -47211,7 +47211,7 @@
         <v>-28.43902401807832</v>
       </c>
       <c r="E256" t="n">
-        <v>-11.16641471354466</v>
+        <v>-11.16642255217313</v>
       </c>
       <c r="F256" t="n">
         <v>-40.68221552091195</v>
@@ -47467,7 +47467,7 @@
         <v>-30.63477422966672</v>
       </c>
       <c r="E264" t="n">
-        <v>-8.975257928817172</v>
+        <v>-8.975249933684793</v>
       </c>
       <c r="F264" t="n">
         <v>-39.47368508745812</v>
@@ -47563,7 +47563,7 @@
         <v>-29.24205512377247</v>
       </c>
       <c r="E267" t="n">
-        <v>-11.37217723657323</v>
+        <v>-11.3721850694539</v>
       </c>
       <c r="F267" t="n">
         <v>-35.66993037243454</v>
@@ -47627,7 +47627,7 @@
         <v>-31.51544377109349</v>
       </c>
       <c r="E269" t="n">
-        <v>-16.3552932302255</v>
+        <v>-16.35530046410454</v>
       </c>
       <c r="F269" t="n">
         <v>-38.0038388594275</v>
@@ -47851,7 +47851,7 @@
         <v>-30.96296522352431</v>
       </c>
       <c r="E276" t="n">
-        <v>-11.7115071824372</v>
+        <v>-11.71149935583935</v>
       </c>
       <c r="F276" t="n">
         <v>-34.97199627598184</v>
@@ -47947,7 +47947,7 @@
         <v>-28.54230449507224</v>
       </c>
       <c r="E279" t="n">
-        <v>-10.61025096954303</v>
+        <v>-10.61024304532102</v>
       </c>
       <c r="F279" t="n">
         <v>-31.85478688860097</v>
@@ -48043,7 +48043,7 @@
         <v>-31.95619725003812</v>
       </c>
       <c r="E282" t="n">
-        <v>-8.466570285765041</v>
+        <v>-8.466562074090877</v>
       </c>
       <c r="F282" t="n">
         <v>-36.50442544264273</v>
@@ -48075,7 +48075,7 @@
         <v>-34.78050768782048</v>
       </c>
       <c r="E283" t="n">
-        <v>-8.900954788972681</v>
+        <v>-8.900946581418934</v>
       </c>
       <c r="F283" t="n">
         <v>-36.51074312329671</v>
@@ -48139,7 +48139,7 @@
         <v>-33.6261564988414</v>
       </c>
       <c r="E285" t="n">
-        <v>-6.403066080333931</v>
+        <v>-6.403057485981378</v>
       </c>
       <c r="F285" t="n">
         <v>-43.19450633885003</v>
@@ -48267,7 +48267,7 @@
         <v>-27.07006549980937</v>
       </c>
       <c r="E289" t="n">
-        <v>-1.789447632229446</v>
+        <v>-1.789457213034507</v>
       </c>
       <c r="F289" t="n">
         <v>-36.1724497836834</v>
@@ -48299,7 +48299,7 @@
         <v>-26.88853708679655</v>
       </c>
       <c r="E290" t="n">
-        <v>-1.419444239463907</v>
+        <v>-1.419453836500251</v>
       </c>
       <c r="F290" t="n">
         <v>-38.08921600038258</v>
@@ -48459,7 +48459,7 @@
         <v>-30.8609987086815</v>
       </c>
       <c r="E295" t="n">
-        <v>-6.683905083631759</v>
+        <v>-6.68391401909465</v>
       </c>
       <c r="F295" t="n">
         <v>-41.6964609053498</v>
@@ -48651,7 +48651,7 @@
         <v>-32.60315788154286</v>
       </c>
       <c r="E301" t="n">
-        <v>-1.915399321961297</v>
+        <v>-1.915389976623461</v>
       </c>
       <c r="F301" t="n">
         <v>-44.79178880131202</v>
@@ -48779,7 +48779,7 @@
         <v>-27.57111994645234</v>
       </c>
       <c r="E305" t="n">
-        <v>3.149916020112609</v>
+        <v>3.14992657515003</v>
       </c>
       <c r="F305" t="n">
         <v>-41.52879384528914</v>
@@ -48907,7 +48907,7 @@
         <v>-27.55384073228704</v>
       </c>
       <c r="E309" t="n">
-        <v>-1.820419341165691</v>
+        <v>-1.820409767954434</v>
       </c>
       <c r="F309" t="n">
         <v>-46.45314619747551</v>
@@ -48939,7 +48939,7 @@
         <v>-28.12327812449581</v>
       </c>
       <c r="E310" t="n">
-        <v>-2.189961319395339</v>
+        <v>-2.189970868730429</v>
       </c>
       <c r="F310" t="n">
         <v>-43.11211700553351</v>
@@ -49035,7 +49035,7 @@
         <v>-23.67802924944825</v>
       </c>
       <c r="E313" t="n">
-        <v>-7.167713321274871</v>
+        <v>-7.167704674027875</v>
       </c>
       <c r="F313" t="n">
         <v>-43.89662309077295</v>
@@ -49099,7 +49099,7 @@
         <v>-25.69444651405009</v>
       </c>
       <c r="E315" t="n">
-        <v>-7.8052930518827</v>
+        <v>-7.805284449640915</v>
       </c>
       <c r="F315" t="n">
         <v>-44.86300958919328</v>
@@ -49163,7 +49163,7 @@
         <v>-30.79507707567796</v>
       </c>
       <c r="E317" t="n">
-        <v>-12.54196405882723</v>
+        <v>-12.54195618625559</v>
       </c>
       <c r="F317" t="n">
         <v>-47.19959819731769</v>
@@ -49227,7 +49227,7 @@
         <v>-28.38817660877887</v>
       </c>
       <c r="E319" t="n">
-        <v>-14.69882014884166</v>
+        <v>-14.69881249627694</v>
       </c>
       <c r="F319" t="n">
         <v>-46.19366314291567</v>
@@ -49259,7 +49259,7 @@
         <v>-30.04980322748305</v>
       </c>
       <c r="E320" t="n">
-        <v>-11.79834711640336</v>
+        <v>-11.798339142925</v>
       </c>
       <c r="F320" t="n">
         <v>-45.88515934593683</v>
@@ -49451,7 +49451,7 @@
         <v>-30.20774464959777</v>
       </c>
       <c r="E326" t="n">
-        <v>-12.61553365320609</v>
+        <v>-12.61552578725684</v>
       </c>
       <c r="F326" t="n">
         <v>-43.7062933475497</v>
@@ -49483,7 +49483,7 @@
         <v>-28.4168560528505</v>
       </c>
       <c r="E327" t="n">
-        <v>-11.23824265940424</v>
+        <v>-11.2382507263617</v>
       </c>
       <c r="F327" t="n">
         <v>-42.01795096708333</v>
@@ -49515,7 +49515,7 @@
         <v>-26.30973188082025</v>
       </c>
       <c r="E328" t="n">
-        <v>-7.835551445906363</v>
+        <v>-7.835560144670373</v>
       </c>
       <c r="F328" t="n">
         <v>-39.07111277288545</v>
@@ -49547,7 +49547,7 @@
         <v>-26.77945952370142</v>
       </c>
       <c r="E329" t="n">
-        <v>-4.355889351430875</v>
+        <v>-4.35587998969117</v>
       </c>
       <c r="F329" t="n">
         <v>-37.83128971446084</v>
@@ -49579,7 +49579,7 @@
         <v>-24.20228964506092</v>
       </c>
       <c r="E330" t="n">
-        <v>-2.263212839202788</v>
+        <v>-2.263202999119251</v>
       </c>
       <c r="F330" t="n">
         <v>-40.89319237117981</v>
@@ -49707,7 +49707,7 @@
         <v>-19.98714991312431</v>
       </c>
       <c r="E334" t="n">
-        <v>-2.882084250995653</v>
+        <v>-2.88207449406167</v>
       </c>
       <c r="F334" t="n">
         <v>-41.09851185636433</v>
@@ -49739,7 +49739,7 @@
         <v>-16.57894431388936</v>
       </c>
       <c r="E335" t="n">
-        <v>-1.332080853007134</v>
+        <v>-1.332090723583423</v>
       </c>
       <c r="F335" t="n">
         <v>-37.75945257518652</v>
@@ -49867,7 +49867,7 @@
         <v>-25.53582422398183</v>
       </c>
       <c r="E339" t="n">
-        <v>-4.372171369682365</v>
+        <v>-4.37218089879411</v>
       </c>
       <c r="F339" t="n">
         <v>-41.2774749891061</v>
@@ -49899,7 +49899,7 @@
         <v>-23.0622628159228</v>
       </c>
       <c r="E340" t="n">
-        <v>-3.0340603821715</v>
+        <v>-3.034070394712185</v>
       </c>
       <c r="F340" t="n">
         <v>-39.3328445504433</v>
@@ -49995,7 +49995,7 @@
         <v>-23.89099852905706</v>
       </c>
       <c r="E343" t="n">
-        <v>-0.6231572275657182</v>
+        <v>-0.6231467017805636</v>
       </c>
       <c r="F343" t="n">
         <v>-38.56778592704874</v>
@@ -50059,7 +50059,7 @@
         <v>-17.2627251407637</v>
       </c>
       <c r="E345" t="n">
-        <v>4.916314993451909</v>
+        <v>4.916302916447957</v>
       </c>
       <c r="F345" t="n">
         <v>-32.87099253590478</v>
@@ -50091,7 +50091,7 @@
         <v>-21.78477522759588</v>
       </c>
       <c r="E346" t="n">
-        <v>1.183745152549909</v>
+        <v>1.183733791213348</v>
       </c>
       <c r="F346" t="n">
         <v>-35.87239191644272</v>
@@ -50379,7 +50379,7 @@
         <v>-27.28494884671743</v>
       </c>
       <c r="E355" t="n">
-        <v>4.792385488267725</v>
+        <v>4.792392368889042</v>
       </c>
       <c r="F355" t="n">
         <v>-27.42354135671774</v>
@@ -50411,7 +50411,7 @@
         <v>-25.3721249509532</v>
       </c>
       <c r="E356" t="n">
-        <v>13.24400678497606</v>
+        <v>13.24401421734134</v>
       </c>
       <c r="F356" t="n">
         <v>-24.46144183427424</v>
@@ -50539,7 +50539,7 @@
         <v>-21.90601946492874</v>
       </c>
       <c r="E360" t="n">
-        <v>11.65991396441235</v>
+        <v>11.65992104672113</v>
       </c>
       <c r="F360" t="n">
         <v>-25.74782005433018</v>
@@ -50603,7 +50603,7 @@
         <v>-20.94915357686705</v>
       </c>
       <c r="E362" t="n">
-        <v>10.45348008305296</v>
+        <v>10.4534869862259</v>
       </c>
       <c r="F362" t="n">
         <v>-24.44530491228184</v>
@@ -50635,7 +50635,7 @@
         <v>-22.84366784680649</v>
       </c>
       <c r="E363" t="n">
-        <v>7.26410489731748</v>
+        <v>7.264098320135837</v>
       </c>
       <c r="F363" t="n">
         <v>-29.10251687659797</v>
@@ -50699,7 +50699,7 @@
         <v>-24.28571252479959</v>
       </c>
       <c r="E365" t="n">
-        <v>5.415672922114378</v>
+        <v>5.415679395542905</v>
       </c>
       <c r="F365" t="n">
         <v>-28.71211138002472</v>
@@ -50731,7 +50731,7 @@
         <v>-23.19622116035478</v>
       </c>
       <c r="E366" t="n">
-        <v>8.128497798204526</v>
+        <v>8.128490980816538</v>
       </c>
       <c r="F366" t="n">
         <v>-26.12058438561582</v>
@@ -50827,7 +50827,7 @@
         <v>-22.73361362756691</v>
       </c>
       <c r="E369" t="n">
-        <v>13.56803192476519</v>
+        <v>13.56802429660819</v>
       </c>
       <c r="F369" t="n">
         <v>-26.71135046405951</v>
@@ -50955,7 +50955,7 @@
         <v>-24.32815028665871</v>
       </c>
       <c r="E373" t="n">
-        <v>12.06946184813773</v>
+        <v>12.0694693473598</v>
       </c>
       <c r="F373" t="n">
         <v>-28.85148269226424</v>
@@ -51147,7 +51147,7 @@
         <v>-24.13010945252098</v>
       </c>
       <c r="E379" t="n">
-        <v>12.04284864922218</v>
+        <v>12.0428569162337</v>
       </c>
       <c r="F379" t="n">
         <v>-21.73281609041534</v>
@@ -51275,7 +51275,7 @@
         <v>-29.13668595833225</v>
       </c>
       <c r="E383" t="n">
-        <v>7.127772389347142</v>
+        <v>7.127779850578642</v>
       </c>
       <c r="F383" t="n">
         <v>-29.39840880790665</v>
@@ -51307,7 +51307,7 @@
         <v>-31.12208767584927</v>
       </c>
       <c r="E384" t="n">
-        <v>5.818247463604265</v>
+        <v>5.818240155712728</v>
       </c>
       <c r="F384" t="n">
         <v>-32.58526100040748</v>
@@ -51403,7 +51403,7 @@
         <v>-26.75635196626188</v>
       </c>
       <c r="E387" t="n">
-        <v>6.337682199015493</v>
+        <v>6.33768942164834</v>
       </c>
       <c r="F387" t="n">
         <v>-27.73670637603035</v>
@@ -51467,7 +51467,7 @@
         <v>-28.43965983222077</v>
       </c>
       <c r="E389" t="n">
-        <v>3.158053617653644</v>
+        <v>3.1580608161486</v>
       </c>
       <c r="F389" t="n">
         <v>-27.92992853630824</v>
@@ -51499,7 +51499,7 @@
         <v>-27.36356923125641</v>
       </c>
       <c r="E390" t="n">
-        <v>6.169301512354353</v>
+        <v>6.169308920977867</v>
       </c>
       <c r="F390" t="n">
         <v>-25.73402100163619</v>
@@ -51531,7 +51531,7 @@
         <v>-27.97047902954666</v>
       </c>
       <c r="E391" t="n">
-        <v>3.880493928511441</v>
+        <v>3.880500882192162</v>
       </c>
       <c r="F391" t="n">
         <v>-30.45361073235145</v>
@@ -51595,7 +51595,7 @@
         <v>-35.30269977477008</v>
       </c>
       <c r="E393" t="n">
-        <v>-2.038462945038977</v>
+        <v>-2.038469494495021</v>
       </c>
       <c r="F393" t="n">
         <v>-41.98987931194888</v>
@@ -51627,7 +51627,7 @@
         <v>-30.55953661004619</v>
       </c>
       <c r="E394" t="n">
-        <v>-0.1668970655057334</v>
+        <v>-0.1668904930419157</v>
       </c>
       <c r="F394" t="n">
         <v>-36.04969516561641</v>
@@ -51659,7 +51659,7 @@
         <v>-26.6316594977735</v>
       </c>
       <c r="E395" t="n">
-        <v>1.014306215598793</v>
+        <v>1.014299414847986</v>
       </c>
       <c r="F395" t="n">
         <v>-34.01675506515429</v>
@@ -51723,7 +51723,7 @@
         <v>-22.62996984260145</v>
       </c>
       <c r="E397" t="n">
-        <v>4.392318912024984</v>
+        <v>4.392311829375939</v>
       </c>
       <c r="F397" t="n">
         <v>-32.47330687594106</v>
@@ -51755,7 +51755,7 @@
         <v>-18.38461802555964</v>
       </c>
       <c r="E398" t="n">
-        <v>8.674330050879009</v>
+        <v>8.674322733776552</v>
       </c>
       <c r="F398" t="n">
         <v>-26.03086679746717</v>
@@ -51915,7 +51915,7 @@
         <v>-7.945423499897474</v>
       </c>
       <c r="E403" t="n">
-        <v>13.17263868232146</v>
+        <v>13.17264680156478</v>
       </c>
       <c r="F403" t="n">
         <v>-13.55808929093354</v>
@@ -51947,7 +51947,7 @@
         <v>-10.77751842338764</v>
       </c>
       <c r="E404" t="n">
-        <v>8.642973758231221</v>
+        <v>8.642981161077067</v>
       </c>
       <c r="F404" t="n">
         <v>-12.82665689655393</v>
@@ -52139,7 +52139,7 @@
         <v>-21.33238375936532</v>
       </c>
       <c r="E410" t="n">
-        <v>3.107196346569774</v>
+        <v>3.107189936007027</v>
       </c>
       <c r="F410" t="n">
         <v>-21.59166824801976</v>
@@ -52203,7 +52203,7 @@
         <v>-24.71146980834059</v>
       </c>
       <c r="E412" t="n">
-        <v>-2.726841153927861</v>
+        <v>-2.726829609288295</v>
       </c>
       <c r="F412" t="n">
         <v>-24.11161503408237</v>
@@ -52299,7 +52299,7 @@
         <v>-22.53923464985733</v>
       </c>
       <c r="E415" t="n">
-        <v>-1.847951917291468</v>
+        <v>-1.847963577079392</v>
       </c>
       <c r="F415" t="n">
         <v>-20.80552533209156</v>
@@ -52331,7 +52331,7 @@
         <v>-21.78288832645033</v>
       </c>
       <c r="E416" t="n">
-        <v>-3.412876137907805</v>
+        <v>-3.412864651995873</v>
       </c>
       <c r="F416" t="n">
         <v>-24.29865228356438</v>
@@ -52555,7 +52555,7 @@
         <v>-20.82066719519743</v>
       </c>
       <c r="E423" t="n">
-        <v>-5.578780694495011</v>
+        <v>-5.578786518450696</v>
       </c>
       <c r="F423" t="n">
         <v>-22.82890181163548</v>
@@ -52779,7 +52779,7 @@
         <v>-30.24650161641759</v>
       </c>
       <c r="E430" t="n">
-        <v>-10.80606292625648</v>
+        <v>-10.80605285953314</v>
       </c>
       <c r="F430" t="n">
         <v>-32.41098037149195</v>
@@ -52811,7 +52811,7 @@
         <v>-30.16501524682917</v>
       </c>
       <c r="E431" t="n">
-        <v>-12.13950456134066</v>
+        <v>-12.13949474993221</v>
       </c>
       <c r="F431" t="n">
         <v>-32.61940456242382</v>
@@ -52875,7 +52875,7 @@
         <v>-28.28217347291736</v>
       </c>
       <c r="E433" t="n">
-        <v>-13.65793860950155</v>
+        <v>-13.65794799810753</v>
       </c>
       <c r="F433" t="n">
         <v>-35.94838047268804</v>
@@ -52907,7 +52907,7 @@
         <v>-29.41176433922557</v>
       </c>
       <c r="E434" t="n">
-        <v>-15.05851917996379</v>
+        <v>-15.05852841627437</v>
       </c>
       <c r="F434" t="n">
         <v>-37.55248832154153</v>
@@ -52971,7 +52971,7 @@
         <v>-31.18556707365781</v>
       </c>
       <c r="E436" t="n">
-        <v>-18.02633419934322</v>
+        <v>-18.02632554975999</v>
       </c>
       <c r="F436" t="n">
         <v>-42.55076628068165</v>
@@ -53131,7 +53131,7 @@
         <v>-31.21424024348101</v>
       </c>
       <c r="E441" t="n">
-        <v>-19.20950236051181</v>
+        <v>-19.20949383577247</v>
       </c>
       <c r="F441" t="n">
         <v>-42.29934878455828</v>
@@ -53163,7 +53163,7 @@
         <v>-32.31746128627232</v>
       </c>
       <c r="E442" t="n">
-        <v>-20.9163266846164</v>
+        <v>-20.91631837289538</v>
       </c>
       <c r="F442" t="n">
         <v>-44.41396894882384</v>
@@ -53227,7 +53227,7 @@
         <v>-32.40506217564133</v>
       </c>
       <c r="E444" t="n">
-        <v>-22.34746171639906</v>
+        <v>-22.34746953569596</v>
       </c>
       <c r="F444" t="n">
         <v>-42.16226047422541</v>
@@ -53259,7 +53259,7 @@
         <v>-29.89368231014634</v>
       </c>
       <c r="E445" t="n">
-        <v>-20.77492865674345</v>
+        <v>-20.7749366725903</v>
       </c>
       <c r="F445" t="n">
         <v>-42.99229174547121</v>
@@ -53419,7 +53419,7 @@
         <v>-18.88297978584559</v>
       </c>
       <c r="E450" t="n">
-        <v>-15.88698719525661</v>
+        <v>-15.88697830309197</v>
       </c>
       <c r="F450" t="n">
         <v>-35.79224816752393</v>
@@ -53451,7 +53451,7 @@
         <v>-21.15514103139139</v>
       </c>
       <c r="E451" t="n">
-        <v>-17.34137682167169</v>
+        <v>-17.34136803322271</v>
       </c>
       <c r="F451" t="n">
         <v>-37.43143086937941</v>
@@ -53579,7 +53579,7 @@
         <v>-26.51714739149942</v>
       </c>
       <c r="E455" t="n">
-        <v>-21.18380265372481</v>
+        <v>-21.18379462622453</v>
       </c>
       <c r="F455" t="n">
         <v>-41.48341463321004</v>
@@ -53611,7 +53611,7 @@
         <v>-30.5295940900473</v>
       </c>
       <c r="E456" t="n">
-        <v>-21.92261802067016</v>
+        <v>-21.92261013396634</v>
       </c>
       <c r="F456" t="n">
         <v>-48.90003185290745</v>
@@ -53771,7 +53771,7 @@
         <v>-30.07565956712446</v>
       </c>
       <c r="E461" t="n">
-        <v>-25.48238809077367</v>
+        <v>-25.4823950787656</v>
       </c>
       <c r="F461" t="n">
         <v>-44.03718065374491</v>
@@ -53803,7 +53803,7 @@
         <v>-32.39348410987978</v>
       </c>
       <c r="E462" t="n">
-        <v>-29.13438953225068</v>
+        <v>-29.13439621150543</v>
       </c>
       <c r="F462" t="n">
         <v>-46.7217367763071</v>
@@ -53835,7 +53835,7 @@
         <v>-31.89493121198945</v>
       </c>
       <c r="E463" t="n">
-        <v>-28.07081853704482</v>
+        <v>-28.07081175545964</v>
       </c>
       <c r="F463" t="n">
         <v>-45.49804856795367</v>
@@ -53963,7 +53963,7 @@
         <v>-28.04877989062005</v>
       </c>
       <c r="E467" t="n">
-        <v>-28.55151148667798</v>
+        <v>-28.551504886499</v>
       </c>
       <c r="F467" t="n">
         <v>-42.95977001650706</v>
@@ -53995,7 +53995,7 @@
         <v>-27.86458221768647</v>
       </c>
       <c r="E468" t="n">
-        <v>-27.55756191669814</v>
+        <v>-27.55755510454062</v>
       </c>
       <c r="F468" t="n">
         <v>-44.69987464603042</v>
@@ -54187,7 +54187,7 @@
         <v>-32.19911590123635</v>
       </c>
       <c r="E474" t="n">
-        <v>-25.90196375525328</v>
+        <v>-25.90197091088043</v>
       </c>
       <c r="F474" t="n">
         <v>-51.98792057340895</v>
@@ -54347,7 +54347,7 @@
         <v>-27.52354840786123</v>
       </c>
       <c r="E479" t="n">
-        <v>-16.42755184124513</v>
+        <v>-16.4275601717731</v>
       </c>
       <c r="F479" t="n">
         <v>-47.64444308810764</v>
@@ -54475,7 +54475,7 @@
         <v>-28.27814801252383</v>
       </c>
       <c r="E483" t="n">
-        <v>-20.02722811908593</v>
+        <v>-20.0272355549142</v>
       </c>
       <c r="F483" t="n">
         <v>-47.95545639098183</v>
@@ -54603,7 +54603,7 @@
         <v>-25.48882469494409</v>
       </c>
       <c r="E487" t="n">
-        <v>-21.0292402548563</v>
+        <v>-21.02923282196163</v>
       </c>
       <c r="F487" t="n">
         <v>-48.99627177559144</v>

--- a/dashboards/Reliance Group.xlsx
+++ b/dashboards/Reliance Group.xlsx
@@ -493,13 +493,13 @@
         <v>91.84999847412109</v>
       </c>
       <c r="G2" t="n">
-        <v>1088.746704101562</v>
+        <v>1088.74658203125</v>
       </c>
       <c r="H2" t="n">
         <v>100.8000030517578</v>
       </c>
       <c r="I2" t="n">
-        <v>850.6759643554688</v>
+        <v>850.676025390625</v>
       </c>
       <c r="J2" t="n">
         <v>14.25</v>
@@ -522,7 +522,7 @@
         <v>90.40000152587891</v>
       </c>
       <c r="G3" t="n">
-        <v>1113.317504882812</v>
+        <v>1113.3173828125</v>
       </c>
       <c r="H3" t="n">
         <v>97.5</v>
@@ -580,7 +580,7 @@
         <v>89.90000152587891</v>
       </c>
       <c r="G5" t="n">
-        <v>1094.47607421875</v>
+        <v>1094.476196289062</v>
       </c>
       <c r="H5" t="n">
         <v>100.1500015258789</v>
@@ -644,7 +644,7 @@
         <v>103.4499969482422</v>
       </c>
       <c r="I7" t="n">
-        <v>939.3392333984375</v>
+        <v>939.3392944335938</v>
       </c>
       <c r="J7" t="n">
         <v>14.85000038146973</v>
@@ -667,13 +667,13 @@
         <v>89.34999847412109</v>
       </c>
       <c r="G8" t="n">
-        <v>1112.162719726562</v>
+        <v>1112.16259765625</v>
       </c>
       <c r="H8" t="n">
         <v>98.40000152587891</v>
       </c>
       <c r="I8" t="n">
-        <v>968.811767578125</v>
+        <v>968.8118896484375</v>
       </c>
       <c r="J8" t="n">
         <v>14.30000019073486</v>
@@ -702,7 +702,7 @@
         <v>96.40000152587891</v>
       </c>
       <c r="I9" t="n">
-        <v>941.8936157226562</v>
+        <v>941.8934936523438</v>
       </c>
       <c r="J9" t="n">
         <v>14.35000038146973</v>
@@ -725,13 +725,13 @@
         <v>90.09999847412109</v>
       </c>
       <c r="G10" t="n">
-        <v>1148.282836914062</v>
+        <v>1148.28271484375</v>
       </c>
       <c r="H10" t="n">
         <v>99.05000305175781</v>
       </c>
       <c r="I10" t="n">
-        <v>931.4307250976562</v>
+        <v>931.4307861328125</v>
       </c>
       <c r="J10" t="n">
         <v>14.25</v>
@@ -754,13 +754,13 @@
         <v>89.59999847412109</v>
       </c>
       <c r="G11" t="n">
-        <v>1149.958740234375</v>
+        <v>1149.958618164062</v>
       </c>
       <c r="H11" t="n">
         <v>102.75</v>
       </c>
       <c r="I11" t="n">
-        <v>931.5289916992188</v>
+        <v>931.5291137695312</v>
       </c>
       <c r="J11" t="n">
         <v>14.94999980926514</v>
@@ -783,13 +783,13 @@
         <v>91.40000152587891</v>
       </c>
       <c r="G12" t="n">
-        <v>1155.959716796875</v>
+        <v>1155.959594726562</v>
       </c>
       <c r="H12" t="n">
         <v>105.5500030517578</v>
       </c>
       <c r="I12" t="n">
-        <v>934.6727294921875</v>
+        <v>934.6727905273438</v>
       </c>
       <c r="J12" t="n">
         <v>15.64999961853027</v>
@@ -812,7 +812,7 @@
         <v>89.80000305175781</v>
       </c>
       <c r="G13" t="n">
-        <v>1142.16845703125</v>
+        <v>1142.168334960938</v>
       </c>
       <c r="H13" t="n">
         <v>101.9499969482422</v>
@@ -847,7 +847,7 @@
         <v>99.75</v>
       </c>
       <c r="I14" t="n">
-        <v>957.71044921875</v>
+        <v>957.7103881835938</v>
       </c>
       <c r="J14" t="n">
         <v>15.85000038146973</v>
@@ -870,13 +870,13 @@
         <v>88.75</v>
       </c>
       <c r="G15" t="n">
-        <v>1122.081420898438</v>
+        <v>1122.08154296875</v>
       </c>
       <c r="H15" t="n">
         <v>101.5500030517578</v>
       </c>
       <c r="I15" t="n">
-        <v>936.3428955078125</v>
+        <v>936.3428344726562</v>
       </c>
       <c r="J15" t="n">
         <v>16.54999923706055</v>
@@ -928,13 +928,13 @@
         <v>82.09999847412109</v>
       </c>
       <c r="G17" t="n">
-        <v>1076.99365234375</v>
+        <v>1076.993408203125</v>
       </c>
       <c r="H17" t="n">
         <v>93.55000305175781</v>
       </c>
       <c r="I17" t="n">
-        <v>835.7432250976562</v>
+        <v>835.7432861328125</v>
       </c>
       <c r="J17" t="n">
         <v>15.25</v>
@@ -963,7 +963,7 @@
         <v>98.05000305175781</v>
       </c>
       <c r="I18" t="n">
-        <v>835.7432250976562</v>
+        <v>835.7432861328125</v>
       </c>
       <c r="J18" t="n">
         <v>14.75</v>
@@ -1021,7 +1021,7 @@
         <v>102.3000030517578</v>
       </c>
       <c r="I20" t="n">
-        <v>885.7974853515625</v>
+        <v>885.7974243164062</v>
       </c>
       <c r="J20" t="n">
         <v>15.19999980926514</v>
@@ -1050,7 +1050,7 @@
         <v>101.0500030517578</v>
       </c>
       <c r="I21" t="n">
-        <v>864.5281372070312</v>
+        <v>864.528076171875</v>
       </c>
       <c r="J21" t="n">
         <v>14.80000019073486</v>
@@ -1166,7 +1166,7 @@
         <v>121.3499984741211</v>
       </c>
       <c r="I25" t="n">
-        <v>898.3724365234375</v>
+        <v>898.3724975585938</v>
       </c>
       <c r="J25" t="n">
         <v>17.64999961853027</v>
@@ -1189,7 +1189,7 @@
         <v>83.25</v>
       </c>
       <c r="G26" t="n">
-        <v>1049.4560546875</v>
+        <v>1049.456176757812</v>
       </c>
       <c r="H26" t="n">
         <v>133.4499969482422</v>
@@ -1218,7 +1218,7 @@
         <v>83.59999847412109</v>
       </c>
       <c r="G27" t="n">
-        <v>1067.097290039062</v>
+        <v>1067.09716796875</v>
       </c>
       <c r="H27" t="n">
         <v>134.4499969482422</v>
@@ -1282,7 +1282,7 @@
         <v>133.1000061035156</v>
       </c>
       <c r="I29" t="n">
-        <v>879.5099487304688</v>
+        <v>879.510009765625</v>
       </c>
       <c r="J29" t="n">
         <v>16.14999961853027</v>
@@ -1305,13 +1305,13 @@
         <v>91.44999694824219</v>
       </c>
       <c r="G30" t="n">
-        <v>1076.314208984375</v>
+        <v>1076.314086914062</v>
       </c>
       <c r="H30" t="n">
         <v>134</v>
       </c>
       <c r="I30" t="n">
-        <v>853.6724853515625</v>
+        <v>853.6724243164062</v>
       </c>
       <c r="J30" t="n">
         <v>15.94999980926514</v>
@@ -1334,13 +1334,13 @@
         <v>86.90000152587891</v>
       </c>
       <c r="G31" t="n">
-        <v>1059.171142578125</v>
+        <v>1059.171264648438</v>
       </c>
       <c r="H31" t="n">
         <v>120.5999984741211</v>
       </c>
       <c r="I31" t="n">
-        <v>771.3457641601562</v>
+        <v>771.345703125</v>
       </c>
       <c r="J31" t="n">
         <v>15.19999980926514</v>
@@ -1363,13 +1363,13 @@
         <v>87.05000305175781</v>
       </c>
       <c r="G32" t="n">
-        <v>1095.132934570312</v>
+        <v>1095.1328125</v>
       </c>
       <c r="H32" t="n">
         <v>111.8499984741211</v>
       </c>
       <c r="I32" t="n">
-        <v>784.4609985351562</v>
+        <v>784.4610595703125</v>
       </c>
       <c r="J32" t="n">
         <v>14.55000019073486</v>
@@ -1398,7 +1398,7 @@
         <v>122.5999984741211</v>
       </c>
       <c r="I33" t="n">
-        <v>794.4324951171875</v>
+        <v>794.4325561523438</v>
       </c>
       <c r="J33" t="n">
         <v>14.80000019073486</v>
@@ -1450,7 +1450,7 @@
         <v>83.09999847412109</v>
       </c>
       <c r="G35" t="n">
-        <v>1098.054321289062</v>
+        <v>1098.05419921875</v>
       </c>
       <c r="H35" t="n">
         <v>120.0999984741211</v>
@@ -1479,13 +1479,13 @@
         <v>82.15000152587891</v>
       </c>
       <c r="G36" t="n">
-        <v>1086.957885742188</v>
+        <v>1086.957763671875</v>
       </c>
       <c r="H36" t="n">
         <v>112.6999969482422</v>
       </c>
       <c r="I36" t="n">
-        <v>750.4693603515625</v>
+        <v>750.4694213867188</v>
       </c>
       <c r="J36" t="n">
         <v>13.60000038146973</v>
@@ -1537,7 +1537,7 @@
         <v>78.65000152587891</v>
       </c>
       <c r="G38" t="n">
-        <v>1075.249877929688</v>
+        <v>1075.249755859375</v>
       </c>
       <c r="H38" t="n">
         <v>113.25</v>
@@ -1566,13 +1566,13 @@
         <v>74.75</v>
       </c>
       <c r="G39" t="n">
-        <v>1021.66943359375</v>
+        <v>1021.669555664062</v>
       </c>
       <c r="H39" t="n">
         <v>101.9499969482422</v>
       </c>
       <c r="I39" t="n">
-        <v>655.5676879882812</v>
+        <v>655.5677490234375</v>
       </c>
       <c r="J39" t="n">
         <v>12.89999961853027</v>
@@ -1601,7 +1601,7 @@
         <v>104.5999984741211</v>
       </c>
       <c r="I40" t="n">
-        <v>681.9456787109375</v>
+        <v>681.9456176757812</v>
       </c>
       <c r="J40" t="n">
         <v>13</v>
@@ -1624,7 +1624,7 @@
         <v>76.94999694824219</v>
       </c>
       <c r="G41" t="n">
-        <v>1068.682495117188</v>
+        <v>1068.682373046875</v>
       </c>
       <c r="H41" t="n">
         <v>104.5999984741211</v>
@@ -1659,7 +1659,7 @@
         <v>107.5999984741211</v>
       </c>
       <c r="I42" t="n">
-        <v>692.8504638671875</v>
+        <v>692.8505249023438</v>
       </c>
       <c r="J42" t="n">
         <v>13.14999961853027</v>
@@ -1775,7 +1775,7 @@
         <v>101.75</v>
       </c>
       <c r="I46" t="n">
-        <v>667.5040893554688</v>
+        <v>667.504150390625</v>
       </c>
       <c r="J46" t="n">
         <v>12.80000019073486</v>
@@ -1827,13 +1827,13 @@
         <v>78</v>
       </c>
       <c r="G48" t="n">
-        <v>1083.492919921875</v>
+        <v>1083.49267578125</v>
       </c>
       <c r="H48" t="n">
         <v>111.4000015258789</v>
       </c>
       <c r="I48" t="n">
-        <v>701.8397216796875</v>
+        <v>701.839599609375</v>
       </c>
       <c r="J48" t="n">
         <v>13.55000019073486</v>
@@ -1891,7 +1891,7 @@
         <v>117.25</v>
       </c>
       <c r="I50" t="n">
-        <v>737.8451538085938</v>
+        <v>737.84521484375</v>
       </c>
       <c r="J50" t="n">
         <v>13.85000038146973</v>
@@ -1914,7 +1914,7 @@
         <v>78.84999847412109</v>
       </c>
       <c r="G51" t="n">
-        <v>1070.448852539062</v>
+        <v>1070.448974609375</v>
       </c>
       <c r="H51" t="n">
         <v>115.5500030517578</v>
@@ -1943,13 +1943,13 @@
         <v>77.75</v>
       </c>
       <c r="G52" t="n">
-        <v>1088.520385742188</v>
+        <v>1088.520263671875</v>
       </c>
       <c r="H52" t="n">
         <v>118.9499969482422</v>
       </c>
       <c r="I52" t="n">
-        <v>750.5184936523438</v>
+        <v>750.5185546875</v>
       </c>
       <c r="J52" t="n">
         <v>14.10000038146973</v>
@@ -1972,13 +1972,13 @@
         <v>78.75</v>
       </c>
       <c r="G53" t="n">
-        <v>1124.006469726562</v>
+        <v>1124.006591796875</v>
       </c>
       <c r="H53" t="n">
         <v>116.8000030517578</v>
       </c>
       <c r="I53" t="n">
-        <v>758.7706909179688</v>
+        <v>758.770751953125</v>
       </c>
       <c r="J53" t="n">
         <v>13.75</v>
@@ -2001,13 +2001,13 @@
         <v>79.15000152587891</v>
       </c>
       <c r="G54" t="n">
-        <v>1117.529663085938</v>
+        <v>1117.52978515625</v>
       </c>
       <c r="H54" t="n">
         <v>115.4000015258789</v>
       </c>
       <c r="I54" t="n">
-        <v>744.86962890625</v>
+        <v>744.8695678710938</v>
       </c>
       <c r="J54" t="n">
         <v>13.64999961853027</v>
@@ -2036,7 +2036,7 @@
         <v>113.1500015258789</v>
       </c>
       <c r="I55" t="n">
-        <v>751.1078491210938</v>
+        <v>751.1079711914062</v>
       </c>
       <c r="J55" t="n">
         <v>13</v>
@@ -2059,13 +2059,13 @@
         <v>81.65000152587891</v>
       </c>
       <c r="G56" t="n">
-        <v>1150.049072265625</v>
+        <v>1150.049194335938</v>
       </c>
       <c r="H56" t="n">
         <v>111.8000030517578</v>
       </c>
       <c r="I56" t="n">
-        <v>756.51123046875</v>
+        <v>756.5111083984375</v>
       </c>
       <c r="J56" t="n">
         <v>12.85000038146973</v>
@@ -2094,7 +2094,7 @@
         <v>109.6999969482422</v>
       </c>
       <c r="I57" t="n">
-        <v>756.3638916015625</v>
+        <v>756.3638305664062</v>
       </c>
       <c r="J57" t="n">
         <v>13</v>
@@ -2181,7 +2181,7 @@
         <v>110.75</v>
       </c>
       <c r="I60" t="n">
-        <v>735.4383544921875</v>
+        <v>735.4382934570312</v>
       </c>
       <c r="J60" t="n">
         <v>12.94999980926514</v>
@@ -2204,13 +2204,13 @@
         <v>85.80000305175781</v>
       </c>
       <c r="G61" t="n">
-        <v>1210.626953125</v>
+        <v>1210.627075195312</v>
       </c>
       <c r="H61" t="n">
         <v>114.8000030517578</v>
       </c>
       <c r="I61" t="n">
-        <v>769.7738037109375</v>
+        <v>769.7738647460938</v>
       </c>
       <c r="J61" t="n">
         <v>13.55000019073486</v>
@@ -2262,13 +2262,13 @@
         <v>87.84999847412109</v>
       </c>
       <c r="G63" t="n">
-        <v>1202.881958007812</v>
+        <v>1202.882080078125</v>
       </c>
       <c r="H63" t="n">
         <v>122.6500015258789</v>
       </c>
       <c r="I63" t="n">
-        <v>790.25732421875</v>
+        <v>790.2572631835938</v>
       </c>
       <c r="J63" t="n">
         <v>14.14999961853027</v>
@@ -2349,7 +2349,7 @@
         <v>94.5</v>
       </c>
       <c r="G66" t="n">
-        <v>1186.214721679688</v>
+        <v>1186.214599609375</v>
       </c>
       <c r="H66" t="n">
         <v>136.1499938964844</v>
@@ -2413,7 +2413,7 @@
         <v>126.75</v>
       </c>
       <c r="I68" t="n">
-        <v>815.8493041992188</v>
+        <v>815.8492431640625</v>
       </c>
       <c r="J68" t="n">
         <v>15.60000038146973</v>
@@ -2436,13 +2436,13 @@
         <v>98.40000152587891</v>
       </c>
       <c r="G69" t="n">
-        <v>1182.20654296875</v>
+        <v>1182.206420898438</v>
       </c>
       <c r="H69" t="n">
         <v>125.8499984741211</v>
       </c>
       <c r="I69" t="n">
-        <v>816.3896484375</v>
+        <v>816.3895874023438</v>
       </c>
       <c r="J69" t="n">
         <v>15.69999980926514</v>
@@ -2523,13 +2523,13 @@
         <v>103</v>
       </c>
       <c r="G72" t="n">
-        <v>1152.155151367188</v>
+        <v>1152.1552734375</v>
       </c>
       <c r="H72" t="n">
         <v>119.5500030517578</v>
       </c>
       <c r="I72" t="n">
-        <v>982.61474609375</v>
+        <v>982.6148071289062</v>
       </c>
       <c r="J72" t="n">
         <v>14.39999961853027</v>
@@ -2558,7 +2558,7 @@
         <v>123.5999984741211</v>
       </c>
       <c r="I73" t="n">
-        <v>979.8148193359375</v>
+        <v>979.81494140625</v>
       </c>
       <c r="J73" t="n">
         <v>14.39999961853027</v>
@@ -2581,13 +2581,13 @@
         <v>101.5500030517578</v>
       </c>
       <c r="G74" t="n">
-        <v>1231.234741210938</v>
+        <v>1231.234619140625</v>
       </c>
       <c r="H74" t="n">
         <v>125.75</v>
       </c>
       <c r="I74" t="n">
-        <v>945.7250366210938</v>
+        <v>945.7249755859375</v>
       </c>
       <c r="J74" t="n">
         <v>14.75</v>
@@ -2610,7 +2610,7 @@
         <v>103.4499969482422</v>
       </c>
       <c r="G75" t="n">
-        <v>1260.06298828125</v>
+        <v>1260.062866210938</v>
       </c>
       <c r="H75" t="n">
         <v>130.3000030517578</v>
@@ -2639,13 +2639,13 @@
         <v>98.90000152587891</v>
       </c>
       <c r="G76" t="n">
-        <v>1249.509887695312</v>
+        <v>1249.509765625</v>
       </c>
       <c r="H76" t="n">
         <v>128.8999938964844</v>
       </c>
       <c r="I76" t="n">
-        <v>962.5242919921875</v>
+        <v>962.5243530273438</v>
       </c>
       <c r="J76" t="n">
         <v>14.94999980926514</v>
@@ -2674,7 +2674,7 @@
         <v>123.25</v>
       </c>
       <c r="I77" t="n">
-        <v>902.3512573242188</v>
+        <v>902.3511962890625</v>
       </c>
       <c r="J77" t="n">
         <v>14.55000019073486</v>
@@ -2697,7 +2697,7 @@
         <v>114.1999969482422</v>
       </c>
       <c r="G78" t="n">
-        <v>1257.141723632812</v>
+        <v>1257.1416015625</v>
       </c>
       <c r="H78" t="n">
         <v>121.1999969482422</v>
@@ -2726,7 +2726,7 @@
         <v>113.6999969482422</v>
       </c>
       <c r="G79" t="n">
-        <v>1258.364624023438</v>
+        <v>1258.364501953125</v>
       </c>
       <c r="H79" t="n">
         <v>123</v>
@@ -2755,13 +2755,13 @@
         <v>91.34999847412109</v>
       </c>
       <c r="G80" t="n">
-        <v>1277.16064453125</v>
+        <v>1277.160766601562</v>
       </c>
       <c r="H80" t="n">
         <v>120.5999984741211</v>
       </c>
       <c r="I80" t="n">
-        <v>1080.66015625</v>
+        <v>1080.660034179688</v>
       </c>
       <c r="J80" t="n">
         <v>13.94999980926514</v>
@@ -2790,7 +2790,7 @@
         <v>123.5500030517578</v>
       </c>
       <c r="I81" t="n">
-        <v>1086.947509765625</v>
+        <v>1086.947631835938</v>
       </c>
       <c r="J81" t="n">
         <v>14.25</v>
@@ -2813,13 +2813,13 @@
         <v>85</v>
       </c>
       <c r="G82" t="n">
-        <v>1259.3154296875</v>
+        <v>1259.315673828125</v>
       </c>
       <c r="H82" t="n">
         <v>124.25</v>
       </c>
       <c r="I82" t="n">
-        <v>1096.477172851562</v>
+        <v>1096.476928710938</v>
       </c>
       <c r="J82" t="n">
         <v>14.19999980926514</v>
@@ -2871,7 +2871,7 @@
         <v>80.30000305175781</v>
       </c>
       <c r="G84" t="n">
-        <v>1196.110961914062</v>
+        <v>1196.11083984375</v>
       </c>
       <c r="H84" t="n">
         <v>115.0999984741211</v>
@@ -2900,7 +2900,7 @@
         <v>78.34999847412109</v>
       </c>
       <c r="G85" t="n">
-        <v>1186.939453125</v>
+        <v>1186.939331054688</v>
       </c>
       <c r="H85" t="n">
         <v>111.3000030517578</v>
@@ -2935,7 +2935,7 @@
         <v>112.3000030517578</v>
       </c>
       <c r="I86" t="n">
-        <v>1002.950805664062</v>
+        <v>1002.950866699219</v>
       </c>
       <c r="J86" t="n">
         <v>13.69999980926514</v>
@@ -2958,13 +2958,13 @@
         <v>72.80000305175781</v>
       </c>
       <c r="G87" t="n">
-        <v>1120.813232421875</v>
+        <v>1120.813354492188</v>
       </c>
       <c r="H87" t="n">
         <v>108.1999969482422</v>
       </c>
       <c r="I87" t="n">
-        <v>953.9772338867188</v>
+        <v>953.977294921875</v>
       </c>
       <c r="J87" t="n">
         <v>13.10000038146973</v>
@@ -3016,7 +3016,7 @@
         <v>72.75</v>
       </c>
       <c r="G89" t="n">
-        <v>1086.731323242188</v>
+        <v>1086.731201171875</v>
       </c>
       <c r="H89" t="n">
         <v>100.9000015258789</v>
@@ -3051,7 +3051,7 @@
         <v>102.0500030517578</v>
       </c>
       <c r="I90" t="n">
-        <v>955.74560546875</v>
+        <v>955.7456665039062</v>
       </c>
       <c r="J90" t="n">
         <v>12.5</v>
@@ -3103,7 +3103,7 @@
         <v>77.90000152587891</v>
       </c>
       <c r="G92" t="n">
-        <v>1145.497192382812</v>
+        <v>1145.497436523438</v>
       </c>
       <c r="H92" t="n">
         <v>107.0500030517578</v>
@@ -3138,7 +3138,7 @@
         <v>104.0999984741211</v>
       </c>
       <c r="I93" t="n">
-        <v>1021.715026855469</v>
+        <v>1021.714904785156</v>
       </c>
       <c r="J93" t="n">
         <v>12.44999980926514</v>
@@ -3167,7 +3167,7 @@
         <v>102.0999984741211</v>
       </c>
       <c r="I94" t="n">
-        <v>977.5062255859375</v>
+        <v>977.5061645507812</v>
       </c>
       <c r="J94" t="n">
         <v>12.30000019073486</v>
@@ -3190,13 +3190,13 @@
         <v>80.75</v>
       </c>
       <c r="G95" t="n">
-        <v>1188.660522460938</v>
+        <v>1188.660400390625</v>
       </c>
       <c r="H95" t="n">
         <v>104</v>
       </c>
       <c r="I95" t="n">
-        <v>1021.665954589844</v>
+        <v>1021.665771484375</v>
       </c>
       <c r="J95" t="n">
         <v>12.85000038146973</v>
@@ -3248,13 +3248,13 @@
         <v>78.94999694824219</v>
       </c>
       <c r="G97" t="n">
-        <v>1184.765258789062</v>
+        <v>1184.765502929688</v>
       </c>
       <c r="H97" t="n">
         <v>100.9000015258789</v>
       </c>
       <c r="I97" t="n">
-        <v>945.7250366210938</v>
+        <v>945.7249755859375</v>
       </c>
       <c r="J97" t="n">
         <v>12.55000019073486</v>
@@ -3306,13 +3306,13 @@
         <v>71.59999847412109</v>
       </c>
       <c r="G99" t="n">
-        <v>1171.744018554688</v>
+        <v>1171.743896484375</v>
       </c>
       <c r="H99" t="n">
         <v>100.3499984741211</v>
       </c>
       <c r="I99" t="n">
-        <v>832.8450927734375</v>
+        <v>832.8451538085938</v>
       </c>
       <c r="J99" t="n">
         <v>11.89999961853027</v>
@@ -3335,13 +3335,13 @@
         <v>71.65000152587891</v>
       </c>
       <c r="G100" t="n">
-        <v>1166.308837890625</v>
+        <v>1166.308959960938</v>
       </c>
       <c r="H100" t="n">
         <v>99.84999847412109</v>
       </c>
       <c r="I100" t="n">
-        <v>871.9945068359375</v>
+        <v>871.9944458007812</v>
       </c>
       <c r="J100" t="n">
         <v>11.85000038146973</v>
@@ -3364,13 +3364,13 @@
         <v>73.15000152587891</v>
       </c>
       <c r="G101" t="n">
-        <v>1206.935791015625</v>
+        <v>1206.935668945312</v>
       </c>
       <c r="H101" t="n">
         <v>102.5500030517578</v>
       </c>
       <c r="I101" t="n">
-        <v>914.9262084960938</v>
+        <v>914.9261474609375</v>
       </c>
       <c r="J101" t="n">
         <v>12</v>
@@ -3399,7 +3399,7 @@
         <v>107.9499969482422</v>
       </c>
       <c r="I102" t="n">
-        <v>909.1298828125</v>
+        <v>909.1299438476562</v>
       </c>
       <c r="J102" t="n">
         <v>12.60000038146973</v>
@@ -3428,7 +3428,7 @@
         <v>108.0500030517578</v>
       </c>
       <c r="I103" t="n">
-        <v>929.4659423828125</v>
+        <v>929.4660034179688</v>
       </c>
       <c r="J103" t="n">
         <v>13.19999980926514</v>
@@ -3451,7 +3451,7 @@
         <v>76.5</v>
       </c>
       <c r="G104" t="n">
-        <v>1233.88427734375</v>
+        <v>1233.884399414062</v>
       </c>
       <c r="H104" t="n">
         <v>109.3000030517578</v>
@@ -3486,7 +3486,7 @@
         <v>106.5999984741211</v>
       </c>
       <c r="I105" t="n">
-        <v>965.9136352539062</v>
+        <v>965.9136962890625</v>
       </c>
       <c r="J105" t="n">
         <v>13.25</v>
@@ -3515,7 +3515,7 @@
         <v>105.1500015258789</v>
       </c>
       <c r="I106" t="n">
-        <v>990.7198486328125</v>
+        <v>990.7197875976562</v>
       </c>
       <c r="J106" t="n">
         <v>13.80000019073486</v>
@@ -3538,13 +3538,13 @@
         <v>75.90000152587891</v>
       </c>
       <c r="G107" t="n">
-        <v>1255.828002929688</v>
+        <v>1255.828125</v>
       </c>
       <c r="H107" t="n">
         <v>105.5</v>
       </c>
       <c r="I107" t="n">
-        <v>978.3904418945312</v>
+        <v>978.390380859375</v>
       </c>
       <c r="J107" t="n">
         <v>14.30000019073486</v>
@@ -3573,7 +3573,7 @@
         <v>104.8499984741211</v>
       </c>
       <c r="I108" t="n">
-        <v>969.3521728515625</v>
+        <v>969.3521118164062</v>
       </c>
       <c r="J108" t="n">
         <v>13.85000038146973</v>
@@ -3596,13 +3596,13 @@
         <v>80.94999694824219</v>
       </c>
       <c r="G109" t="n">
-        <v>1267.60400390625</v>
+        <v>1267.603881835938</v>
       </c>
       <c r="H109" t="n">
         <v>104.4499969482422</v>
       </c>
       <c r="I109" t="n">
-        <v>974.7554321289062</v>
+        <v>974.7554931640625</v>
       </c>
       <c r="J109" t="n">
         <v>13.94999980926514</v>
@@ -3625,7 +3625,7 @@
         <v>78.59999847412109</v>
       </c>
       <c r="G110" t="n">
-        <v>1229.33251953125</v>
+        <v>1229.332641601562</v>
       </c>
       <c r="H110" t="n">
         <v>103.5999984741211</v>
@@ -3689,7 +3689,7 @@
         <v>95.75</v>
       </c>
       <c r="I112" t="n">
-        <v>879.7064819335938</v>
+        <v>879.70654296875</v>
       </c>
       <c r="J112" t="n">
         <v>12.85000038146973</v>
@@ -3712,7 +3712,7 @@
         <v>74.59999847412109</v>
       </c>
       <c r="G113" t="n">
-        <v>1175.911010742188</v>
+        <v>1175.910766601562</v>
       </c>
       <c r="H113" t="n">
         <v>95.5</v>
@@ -3747,7 +3747,7 @@
         <v>95.40000152587891</v>
       </c>
       <c r="I114" t="n">
-        <v>825.72265625</v>
+        <v>825.7225952148438</v>
       </c>
       <c r="J114" t="n">
         <v>12.05000019073486</v>
@@ -3770,13 +3770,13 @@
         <v>62.75</v>
       </c>
       <c r="G115" t="n">
-        <v>1173.057373046875</v>
+        <v>1173.057495117188</v>
       </c>
       <c r="H115" t="n">
         <v>95.59999847412109</v>
       </c>
       <c r="I115" t="n">
-        <v>833.4837036132812</v>
+        <v>833.4837646484375</v>
       </c>
       <c r="J115" t="n">
         <v>12.14999961853027</v>
@@ -3828,13 +3828,13 @@
         <v>62.29999923706055</v>
       </c>
       <c r="G117" t="n">
-        <v>1170.385375976562</v>
+        <v>1170.385131835938</v>
       </c>
       <c r="H117" t="n">
         <v>94.5</v>
       </c>
       <c r="I117" t="n">
-        <v>770.314208984375</v>
+        <v>770.3141479492188</v>
       </c>
       <c r="J117" t="n">
         <v>11.44999980926514</v>
@@ -3857,13 +3857,13 @@
         <v>59.15000152587891</v>
       </c>
       <c r="G118" t="n">
-        <v>1134.8310546875</v>
+        <v>1134.831176757812</v>
       </c>
       <c r="H118" t="n">
         <v>91.19999694824219</v>
       </c>
       <c r="I118" t="n">
-        <v>743.8379516601562</v>
+        <v>743.8380126953125</v>
       </c>
       <c r="J118" t="n">
         <v>11.39999961853027</v>
@@ -3886,7 +3886,7 @@
         <v>61.40000152587891</v>
       </c>
       <c r="G119" t="n">
-        <v>1116.419799804688</v>
+        <v>1116.420043945312</v>
       </c>
       <c r="H119" t="n">
         <v>90.30000305175781</v>
@@ -3944,13 +3944,13 @@
         <v>62.84999847412109</v>
       </c>
       <c r="G121" t="n">
-        <v>1128.9658203125</v>
+        <v>1128.965698242188</v>
       </c>
       <c r="H121" t="n">
         <v>93.09999847412109</v>
       </c>
       <c r="I121" t="n">
-        <v>801.5060424804688</v>
+        <v>801.5059814453125</v>
       </c>
       <c r="J121" t="n">
         <v>11.80000019073486</v>
@@ -4060,7 +4060,7 @@
         <v>67.65000152587891</v>
       </c>
       <c r="G125" t="n">
-        <v>1090.943481445312</v>
+        <v>1090.943359375</v>
       </c>
       <c r="H125" t="n">
         <v>91.09999847412109</v>
@@ -4095,7 +4095,7 @@
         <v>94.5</v>
       </c>
       <c r="I126" t="n">
-        <v>935.7042846679688</v>
+        <v>935.704345703125</v>
       </c>
       <c r="J126" t="n">
         <v>11.35000038146973</v>
@@ -4147,7 +4147,7 @@
         <v>65.30000305175781</v>
       </c>
       <c r="G128" t="n">
-        <v>1092.369995117188</v>
+        <v>1092.3701171875</v>
       </c>
       <c r="H128" t="n">
         <v>91.75</v>
@@ -4182,7 +4182,7 @@
         <v>94.90000152587891</v>
       </c>
       <c r="I129" t="n">
-        <v>936.4902954101562</v>
+        <v>936.490234375</v>
       </c>
       <c r="J129" t="n">
         <v>11.44999980926514</v>
@@ -4211,7 +4211,7 @@
         <v>94.80000305175781</v>
       </c>
       <c r="I130" t="n">
-        <v>933.346435546875</v>
+        <v>933.3464965820312</v>
       </c>
       <c r="J130" t="n">
         <v>11.39999961853027</v>
@@ -4327,7 +4327,7 @@
         <v>100.4000015258789</v>
       </c>
       <c r="I134" t="n">
-        <v>937.9638671875</v>
+        <v>937.9639282226562</v>
       </c>
       <c r="J134" t="n">
         <v>11.39999961853027</v>
@@ -4408,13 +4408,13 @@
         <v>67.09999847412109</v>
       </c>
       <c r="G137" t="n">
-        <v>1103.806396484375</v>
+        <v>1103.806518554688</v>
       </c>
       <c r="H137" t="n">
         <v>102.3000030517578</v>
       </c>
       <c r="I137" t="n">
-        <v>978.83251953125</v>
+        <v>978.8323974609375</v>
       </c>
       <c r="J137" t="n">
         <v>11.80000019073486</v>
@@ -4466,7 +4466,7 @@
         <v>65</v>
       </c>
       <c r="G139" t="n">
-        <v>1126.08984375</v>
+        <v>1126.089965820312</v>
       </c>
       <c r="H139" t="n">
         <v>105.8000030517578</v>
@@ -4495,7 +4495,7 @@
         <v>63.75</v>
       </c>
       <c r="G140" t="n">
-        <v>1133.698852539062</v>
+        <v>1133.698974609375</v>
       </c>
       <c r="H140" t="n">
         <v>104.5</v>
@@ -4524,13 +4524,13 @@
         <v>62.95000076293945</v>
       </c>
       <c r="G141" t="n">
-        <v>1096.242553710938</v>
+        <v>1096.242431640625</v>
       </c>
       <c r="H141" t="n">
         <v>104.25</v>
       </c>
       <c r="I141" t="n">
-        <v>962.13134765625</v>
+        <v>962.1312866210938</v>
       </c>
       <c r="J141" t="n">
         <v>11.55000019073486</v>
@@ -4553,13 +4553,13 @@
         <v>62.90000152587891</v>
       </c>
       <c r="G142" t="n">
-        <v>1096.740844726562</v>
+        <v>1096.74072265625</v>
       </c>
       <c r="H142" t="n">
         <v>113.9000015258789</v>
       </c>
       <c r="I142" t="n">
-        <v>945.1355590820312</v>
+        <v>945.135498046875</v>
       </c>
       <c r="J142" t="n">
         <v>11.89999961853027</v>
@@ -4640,13 +4640,13 @@
         <v>64.90000152587891</v>
       </c>
       <c r="G145" t="n">
-        <v>1136.574829101562</v>
+        <v>1136.57470703125</v>
       </c>
       <c r="H145" t="n">
         <v>117.0999984741211</v>
       </c>
       <c r="I145" t="n">
-        <v>964.6856079101562</v>
+        <v>964.6856689453125</v>
       </c>
       <c r="J145" t="n">
         <v>12.39999961853027</v>
@@ -4669,13 +4669,13 @@
         <v>66.94999694824219</v>
       </c>
       <c r="G146" t="n">
-        <v>1166.19580078125</v>
+        <v>1166.195678710938</v>
       </c>
       <c r="H146" t="n">
         <v>123.25</v>
       </c>
       <c r="I146" t="n">
-        <v>1014.592468261719</v>
+        <v>1014.592407226562</v>
       </c>
       <c r="J146" t="n">
         <v>13</v>
@@ -4698,13 +4698,13 @@
         <v>68.05000305175781</v>
       </c>
       <c r="G147" t="n">
-        <v>1170.634155273438</v>
+        <v>1170.63427734375</v>
       </c>
       <c r="H147" t="n">
         <v>128.6999969482422</v>
       </c>
       <c r="I147" t="n">
-        <v>994.7966918945312</v>
+        <v>994.7967529296875</v>
       </c>
       <c r="J147" t="n">
         <v>13.30000019073486</v>
@@ -4727,13 +4727,13 @@
         <v>69.19999694824219</v>
       </c>
       <c r="G148" t="n">
-        <v>1180.462768554688</v>
+        <v>1180.462524414062</v>
       </c>
       <c r="H148" t="n">
         <v>125.0500030517578</v>
       </c>
       <c r="I148" t="n">
-        <v>966.0609741210938</v>
+        <v>966.06103515625</v>
       </c>
       <c r="J148" t="n">
         <v>13</v>
@@ -4762,7 +4762,7 @@
         <v>121.3499984741211</v>
       </c>
       <c r="I149" t="n">
-        <v>952.749267578125</v>
+        <v>952.7492065429688</v>
       </c>
       <c r="J149" t="n">
         <v>13.19999980926514</v>
@@ -4785,13 +4785,13 @@
         <v>68.09999847412109</v>
       </c>
       <c r="G150" t="n">
-        <v>1147.693969726562</v>
+        <v>1147.694091796875</v>
       </c>
       <c r="H150" t="n">
         <v>120</v>
       </c>
       <c r="I150" t="n">
-        <v>942.0409545898438</v>
+        <v>942.0408935546875</v>
       </c>
       <c r="J150" t="n">
         <v>13.14999961853027</v>
@@ -4814,7 +4814,7 @@
         <v>67.5</v>
       </c>
       <c r="G151" t="n">
-        <v>1162.708374023438</v>
+        <v>1162.708251953125</v>
       </c>
       <c r="H151" t="n">
         <v>115.8499984741211</v>
@@ -4843,13 +4843,13 @@
         <v>66.65000152587891</v>
       </c>
       <c r="G152" t="n">
-        <v>1169.66064453125</v>
+        <v>1169.660522460938</v>
       </c>
       <c r="H152" t="n">
         <v>117.5500030517578</v>
       </c>
       <c r="I152" t="n">
-        <v>944.4968872070312</v>
+        <v>944.4969482421875</v>
       </c>
       <c r="J152" t="n">
         <v>14.14999961853027</v>
@@ -4878,7 +4878,7 @@
         <v>115.3499984741211</v>
       </c>
       <c r="I153" t="n">
-        <v>953.8790283203125</v>
+        <v>953.879150390625</v>
       </c>
       <c r="J153" t="n">
         <v>13.60000038146973</v>
@@ -4907,7 +4907,7 @@
         <v>115.1500015258789</v>
       </c>
       <c r="I154" t="n">
-        <v>954.0263061523438</v>
+        <v>954.0264282226562</v>
       </c>
       <c r="J154" t="n">
         <v>13.39999961853027</v>
@@ -4965,7 +4965,7 @@
         <v>121.8000030517578</v>
       </c>
       <c r="I156" t="n">
-        <v>975.4923095703125</v>
+        <v>975.4922485351562</v>
       </c>
       <c r="J156" t="n">
         <v>13.64999961853027</v>
@@ -4994,7 +4994,7 @@
         <v>129.8999938964844</v>
       </c>
       <c r="I157" t="n">
-        <v>1020.879943847656</v>
+        <v>1020.880126953125</v>
       </c>
       <c r="J157" t="n">
         <v>14.19999980926514</v>
@@ -5017,13 +5017,13 @@
         <v>73.75</v>
       </c>
       <c r="G158" t="n">
-        <v>1187.72216796875</v>
+        <v>1187.722045898438</v>
       </c>
       <c r="H158" t="n">
         <v>135.6000061035156</v>
       </c>
       <c r="I158" t="n">
-        <v>1000.396484375</v>
+        <v>1000.396545410156</v>
       </c>
       <c r="J158" t="n">
         <v>14.94999980926514</v>
@@ -5046,7 +5046,7 @@
         <v>72.15000152587891</v>
       </c>
       <c r="G159" t="n">
-        <v>1184.427612304688</v>
+        <v>1184.427734375</v>
       </c>
       <c r="H159" t="n">
         <v>140.6999969482422</v>
@@ -5075,7 +5075,7 @@
         <v>72.25</v>
       </c>
       <c r="G160" t="n">
-        <v>1202.694580078125</v>
+        <v>1202.694458007812</v>
       </c>
       <c r="H160" t="n">
         <v>138.6999969482422</v>
@@ -5104,7 +5104,7 @@
         <v>74.15000152587891</v>
       </c>
       <c r="G161" t="n">
-        <v>1199.490844726562</v>
+        <v>1199.490966796875</v>
       </c>
       <c r="H161" t="n">
         <v>139.6999969482422</v>
@@ -5133,7 +5133,7 @@
         <v>74.05000305175781</v>
       </c>
       <c r="G162" t="n">
-        <v>1195.9921875</v>
+        <v>1195.992065429688</v>
       </c>
       <c r="H162" t="n">
         <v>139.75</v>
@@ -5168,7 +5168,7 @@
         <v>157.3500061035156</v>
       </c>
       <c r="I163" t="n">
-        <v>997.1054077148438</v>
+        <v>997.10546875</v>
       </c>
       <c r="J163" t="n">
         <v>16.25</v>
@@ -5191,13 +5191,13 @@
         <v>69.65000152587891</v>
       </c>
       <c r="G164" t="n">
-        <v>1180.36083984375</v>
+        <v>1180.360961914062</v>
       </c>
       <c r="H164" t="n">
         <v>158.75</v>
       </c>
       <c r="I164" t="n">
-        <v>992.1442260742188</v>
+        <v>992.144287109375</v>
       </c>
       <c r="J164" t="n">
         <v>16.29999923706055</v>
@@ -5220,7 +5220,7 @@
         <v>70.59999847412109</v>
       </c>
       <c r="G165" t="n">
-        <v>1198.672973632812</v>
+        <v>1198.673095703125</v>
       </c>
       <c r="H165" t="n">
         <v>162</v>
@@ -5255,7 +5255,7 @@
         <v>193.8500061035156</v>
       </c>
       <c r="I166" t="n">
-        <v>1039.644165039062</v>
+        <v>1039.644287109375</v>
       </c>
       <c r="J166" t="n">
         <v>20.14999961853027</v>
@@ -5284,7 +5284,7 @@
         <v>179.1499938964844</v>
       </c>
       <c r="I167" t="n">
-        <v>1082.084716796875</v>
+        <v>1082.08447265625</v>
       </c>
       <c r="J167" t="n">
         <v>21.20000076293945</v>
@@ -5313,7 +5313,7 @@
         <v>182.6999969482422</v>
       </c>
       <c r="I168" t="n">
-        <v>1193.932983398438</v>
+        <v>1193.93310546875</v>
       </c>
       <c r="J168" t="n">
         <v>23.29999923706055</v>
@@ -5336,7 +5336,7 @@
         <v>73.94999694824219</v>
       </c>
       <c r="G169" t="n">
-        <v>1179.997314453125</v>
+        <v>1179.997436523438</v>
       </c>
       <c r="H169" t="n">
         <v>178.75</v>
@@ -5365,7 +5365,7 @@
         <v>75.09999847412109</v>
       </c>
       <c r="G170" t="n">
-        <v>1173.136108398438</v>
+        <v>1173.135986328125</v>
       </c>
       <c r="H170" t="n">
         <v>180.6999969482422</v>
@@ -5394,7 +5394,7 @@
         <v>73.65000152587891</v>
       </c>
       <c r="G171" t="n">
-        <v>1174.79443359375</v>
+        <v>1174.794555664062</v>
       </c>
       <c r="H171" t="n">
         <v>180.3000030517578</v>
@@ -5481,13 +5481,13 @@
         <v>74.15000152587891</v>
       </c>
       <c r="G174" t="n">
-        <v>1190.403076171875</v>
+        <v>1190.402954101562</v>
       </c>
       <c r="H174" t="n">
         <v>165.5</v>
       </c>
       <c r="I174" t="n">
-        <v>1137.443969726562</v>
+        <v>1137.44384765625</v>
       </c>
       <c r="J174" t="n">
         <v>20.04999923706055</v>
@@ -5539,13 +5539,13 @@
         <v>71.75</v>
       </c>
       <c r="G176" t="n">
-        <v>1164.479858398438</v>
+        <v>1164.479736328125</v>
       </c>
       <c r="H176" t="n">
         <v>154.4499969482422</v>
       </c>
       <c r="I176" t="n">
-        <v>1170.551391601562</v>
+        <v>1170.55126953125</v>
       </c>
       <c r="J176" t="n">
         <v>18.10000038146973</v>
@@ -5568,7 +5568,7 @@
         <v>68.65000152587891</v>
       </c>
       <c r="G177" t="n">
-        <v>1135.625610351562</v>
+        <v>1135.625732421875</v>
       </c>
       <c r="H177" t="n">
         <v>156.3500061035156</v>
@@ -5597,13 +5597,13 @@
         <v>67.05000305175781</v>
       </c>
       <c r="G178" t="n">
-        <v>1137.1025390625</v>
+        <v>1137.102416992188</v>
       </c>
       <c r="H178" t="n">
         <v>151.8000030517578</v>
       </c>
       <c r="I178" t="n">
-        <v>1159.351806640625</v>
+        <v>1159.351928710938</v>
       </c>
       <c r="J178" t="n">
         <v>17.64999961853027</v>
@@ -5690,7 +5690,7 @@
         <v>146.1499938964844</v>
       </c>
       <c r="I181" t="n">
-        <v>1187.077392578125</v>
+        <v>1187.077270507812</v>
       </c>
       <c r="J181" t="n">
         <v>17.29999923706055</v>
@@ -5719,7 +5719,7 @@
         <v>144.1499938964844</v>
       </c>
       <c r="I182" t="n">
-        <v>1157.628173828125</v>
+        <v>1157.628051757812</v>
       </c>
       <c r="J182" t="n">
         <v>16.89999961853027</v>
@@ -5800,13 +5800,13 @@
         <v>61.70000076293945</v>
       </c>
       <c r="G185" t="n">
-        <v>1059.855102539062</v>
+        <v>1059.855224609375</v>
       </c>
       <c r="H185" t="n">
         <v>136.3500061035156</v>
       </c>
       <c r="I185" t="n">
-        <v>1021.610534667969</v>
+        <v>1021.610412597656</v>
       </c>
       <c r="J185" t="n">
         <v>16.10000038146973</v>
@@ -5829,7 +5829,7 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G186" t="n">
-        <v>1056.606323242188</v>
+        <v>1056.606201171875</v>
       </c>
       <c r="H186" t="n">
         <v>137.6499938964844</v>
@@ -5858,7 +5858,7 @@
         <v>64.59999847412109</v>
       </c>
       <c r="G187" t="n">
-        <v>1080.439208984375</v>
+        <v>1080.439331054688</v>
       </c>
       <c r="H187" t="n">
         <v>136.6999969482422</v>
@@ -5887,13 +5887,13 @@
         <v>63.95000076293945</v>
       </c>
       <c r="G188" t="n">
-        <v>1076.690551757812</v>
+        <v>1076.690673828125</v>
       </c>
       <c r="H188" t="n">
         <v>135.4499969482422</v>
       </c>
       <c r="I188" t="n">
-        <v>1031.902954101562</v>
+        <v>1031.90283203125</v>
       </c>
       <c r="J188" t="n">
         <v>16.45000076293945</v>
@@ -5916,7 +5916,7 @@
         <v>66</v>
       </c>
       <c r="G189" t="n">
-        <v>1096.547485351562</v>
+        <v>1096.547607421875</v>
       </c>
       <c r="H189" t="n">
         <v>137.5500030517578</v>
@@ -5945,13 +5945,13 @@
         <v>67.30000305175781</v>
       </c>
       <c r="G190" t="n">
-        <v>1100.591796875</v>
+        <v>1100.591674804688</v>
       </c>
       <c r="H190" t="n">
         <v>144.3999938964844</v>
       </c>
       <c r="I190" t="n">
-        <v>1120.15185546875</v>
+        <v>1120.152099609375</v>
       </c>
       <c r="J190" t="n">
         <v>16.75</v>
@@ -5974,13 +5974,13 @@
         <v>68.19999694824219</v>
       </c>
       <c r="G191" t="n">
-        <v>1105.249389648438</v>
+        <v>1105.249267578125</v>
       </c>
       <c r="H191" t="n">
         <v>151.6000061035156</v>
       </c>
       <c r="I191" t="n">
-        <v>1158.268432617188</v>
+        <v>1158.268310546875</v>
       </c>
       <c r="J191" t="n">
         <v>17.54999923706055</v>
@@ -6009,7 +6009,7 @@
         <v>157.6999969482422</v>
       </c>
       <c r="I192" t="n">
-        <v>1173.87939453125</v>
+        <v>1173.879516601562</v>
       </c>
       <c r="J192" t="n">
         <v>17.75</v>
@@ -6032,7 +6032,7 @@
         <v>66.94999694824219</v>
       </c>
       <c r="G193" t="n">
-        <v>1071.41943359375</v>
+        <v>1071.419555664062</v>
       </c>
       <c r="H193" t="n">
         <v>149.8500061035156</v>
@@ -6125,7 +6125,7 @@
         <v>138.8500061035156</v>
       </c>
       <c r="I196" t="n">
-        <v>1100.404296875</v>
+        <v>1100.404174804688</v>
       </c>
       <c r="J196" t="n">
         <v>16.20000076293945</v>
@@ -6148,7 +6148,7 @@
         <v>66.40000152587891</v>
       </c>
       <c r="G197" t="n">
-        <v>1094.525634765625</v>
+        <v>1094.525512695312</v>
       </c>
       <c r="H197" t="n">
         <v>138.6999969482422</v>
@@ -6206,7 +6206,7 @@
         <v>65.59999847412109</v>
       </c>
       <c r="G199" t="n">
-        <v>1133.21728515625</v>
+        <v>1133.217407226562</v>
       </c>
       <c r="H199" t="n">
         <v>141.3500061035156</v>
@@ -6235,7 +6235,7 @@
         <v>65.09999847412109</v>
       </c>
       <c r="G200" t="n">
-        <v>1136.261840820312</v>
+        <v>1136.261962890625</v>
       </c>
       <c r="H200" t="n">
         <v>139.1000061035156</v>
@@ -6264,13 +6264,13 @@
         <v>63.70000076293945</v>
       </c>
       <c r="G201" t="n">
-        <v>1123.084228515625</v>
+        <v>1123.084350585938</v>
       </c>
       <c r="H201" t="n">
         <v>139.1499938964844</v>
       </c>
       <c r="I201" t="n">
-        <v>1088.585205078125</v>
+        <v>1088.585327148438</v>
       </c>
       <c r="J201" t="n">
         <v>16.35000038146973</v>
@@ -6322,13 +6322,13 @@
         <v>65.05000305175781</v>
       </c>
       <c r="G203" t="n">
-        <v>1109.4296875</v>
+        <v>1109.429809570312</v>
       </c>
       <c r="H203" t="n">
         <v>141.6000061035156</v>
       </c>
       <c r="I203" t="n">
-        <v>1089.717895507812</v>
+        <v>1089.7177734375</v>
       </c>
       <c r="J203" t="n">
         <v>16.29999923706055</v>
@@ -6351,13 +6351,13 @@
         <v>64.30000305175781</v>
       </c>
       <c r="G204" t="n">
-        <v>1113.791870117188</v>
+        <v>1113.7919921875</v>
       </c>
       <c r="H204" t="n">
         <v>141.8500061035156</v>
       </c>
       <c r="I204" t="n">
-        <v>1086.566040039062</v>
+        <v>1086.56591796875</v>
       </c>
       <c r="J204" t="n">
         <v>16.14999961853027</v>
@@ -6380,7 +6380,7 @@
         <v>63.25</v>
       </c>
       <c r="G205" t="n">
-        <v>1147.87158203125</v>
+        <v>1147.871826171875</v>
       </c>
       <c r="H205" t="n">
         <v>141.8999938964844</v>
@@ -6409,13 +6409,13 @@
         <v>64.15000152587891</v>
       </c>
       <c r="G206" t="n">
-        <v>1158.527221679688</v>
+        <v>1158.527099609375</v>
       </c>
       <c r="H206" t="n">
         <v>141.4499969482422</v>
       </c>
       <c r="I206" t="n">
-        <v>1081.54296875</v>
+        <v>1081.542846679688</v>
       </c>
       <c r="J206" t="n">
         <v>16.10000038146973</v>
@@ -6438,13 +6438,13 @@
         <v>62.90000152587891</v>
       </c>
       <c r="G207" t="n">
-        <v>1149.552856445312</v>
+        <v>1149.552978515625</v>
       </c>
       <c r="H207" t="n">
         <v>140.6499938964844</v>
       </c>
       <c r="I207" t="n">
-        <v>1085.728881835938</v>
+        <v>1085.728759765625</v>
       </c>
       <c r="J207" t="n">
         <v>16.04999923706055</v>
@@ -6554,7 +6554,7 @@
         <v>65.40000152587891</v>
       </c>
       <c r="G211" t="n">
-        <v>1184.427612304688</v>
+        <v>1184.427734375</v>
       </c>
       <c r="H211" t="n">
         <v>152.9499969482422</v>
@@ -6583,7 +6583,7 @@
         <v>65.25</v>
       </c>
       <c r="G212" t="n">
-        <v>1183.246459960938</v>
+        <v>1183.246337890625</v>
       </c>
       <c r="H212" t="n">
         <v>146.6499938964844</v>
@@ -6670,7 +6670,7 @@
         <v>64.05000305175781</v>
       </c>
       <c r="G215" t="n">
-        <v>1190.085083007812</v>
+        <v>1190.0849609375</v>
       </c>
       <c r="H215" t="n">
         <v>153.3999938964844</v>
@@ -6699,7 +6699,7 @@
         <v>63.04999923706055</v>
       </c>
       <c r="G216" t="n">
-        <v>1184.745971679688</v>
+        <v>1184.745849609375</v>
       </c>
       <c r="H216" t="n">
         <v>151.3500061035156</v>
@@ -6757,13 +6757,13 @@
         <v>62.29999923706055</v>
       </c>
       <c r="G218" t="n">
-        <v>1180.997314453125</v>
+        <v>1180.9970703125</v>
       </c>
       <c r="H218" t="n">
         <v>146.0500030517578</v>
       </c>
       <c r="I218" t="n">
-        <v>1011.12109375</v>
+        <v>1011.121032714844</v>
       </c>
       <c r="J218" t="n">
         <v>15.64999961853027</v>
@@ -6786,7 +6786,7 @@
         <v>61.59999847412109</v>
       </c>
       <c r="G219" t="n">
-        <v>1180.36083984375</v>
+        <v>1180.360961914062</v>
       </c>
       <c r="H219" t="n">
         <v>147.6499938964844</v>
@@ -6873,7 +6873,7 @@
         <v>60.54999923706055</v>
       </c>
       <c r="G222" t="n">
-        <v>1161.912475585938</v>
+        <v>1161.912353515625</v>
       </c>
       <c r="H222" t="n">
         <v>146.1499938964844</v>
@@ -6902,7 +6902,7 @@
         <v>60.40000152587891</v>
       </c>
       <c r="G223" t="n">
-        <v>1171.931884765625</v>
+        <v>1171.932006835938</v>
       </c>
       <c r="H223" t="n">
         <v>147.0500030517578</v>
@@ -6937,7 +6937,7 @@
         <v>154.3000030517578</v>
       </c>
       <c r="I224" t="n">
-        <v>1008.067749023438</v>
+        <v>1008.067810058594</v>
       </c>
       <c r="J224" t="n">
         <v>16</v>
@@ -6960,13 +6960,13 @@
         <v>63.75</v>
       </c>
       <c r="G225" t="n">
-        <v>1230.299072265625</v>
+        <v>1230.299194335938</v>
       </c>
       <c r="H225" t="n">
         <v>153.6499938964844</v>
       </c>
       <c r="I225" t="n">
-        <v>1027.52001953125</v>
+        <v>1027.519897460938</v>
       </c>
       <c r="J225" t="n">
         <v>16</v>
@@ -6989,13 +6989,13 @@
         <v>63.95000076293945</v>
       </c>
       <c r="G226" t="n">
-        <v>1232.411865234375</v>
+        <v>1232.411987304688</v>
       </c>
       <c r="H226" t="n">
         <v>154.1499938964844</v>
       </c>
       <c r="I226" t="n">
-        <v>1044.65771484375</v>
+        <v>1044.657592773438</v>
       </c>
       <c r="J226" t="n">
         <v>15.89999961853027</v>
@@ -7053,7 +7053,7 @@
         <v>156.1000061035156</v>
       </c>
       <c r="I228" t="n">
-        <v>1040.225463867188</v>
+        <v>1040.2255859375</v>
       </c>
       <c r="J228" t="n">
         <v>16</v>
@@ -7082,7 +7082,7 @@
         <v>162.8999938964844</v>
       </c>
       <c r="I229" t="n">
-        <v>1033.67578125</v>
+        <v>1033.675903320312</v>
       </c>
       <c r="J229" t="n">
         <v>16.79999923706055</v>
@@ -7140,7 +7140,7 @@
         <v>156.3999938964844</v>
       </c>
       <c r="I231" t="n">
-        <v>1050.41943359375</v>
+        <v>1050.419555664062</v>
       </c>
       <c r="J231" t="n">
         <v>15.85000038146973</v>
@@ -7163,13 +7163,13 @@
         <v>71.19999694824219</v>
       </c>
       <c r="G232" t="n">
-        <v>1204.375854492188</v>
+        <v>1204.375732421875</v>
       </c>
       <c r="H232" t="n">
         <v>154.1999969482422</v>
       </c>
       <c r="I232" t="n">
-        <v>1031.902954101562</v>
+        <v>1031.90283203125</v>
       </c>
       <c r="J232" t="n">
         <v>15.69999980926514</v>
@@ -7221,7 +7221,7 @@
         <v>72.90000152587891</v>
       </c>
       <c r="G234" t="n">
-        <v>1185.563842773438</v>
+        <v>1185.56396484375</v>
       </c>
       <c r="H234" t="n">
         <v>154.75</v>
@@ -7250,13 +7250,13 @@
         <v>72.40000152587891</v>
       </c>
       <c r="G235" t="n">
-        <v>1187.38134765625</v>
+        <v>1187.381225585938</v>
       </c>
       <c r="H235" t="n">
         <v>161.8000030517578</v>
       </c>
       <c r="I235" t="n">
-        <v>1015.454650878906</v>
+        <v>1015.454711914062</v>
       </c>
       <c r="J235" t="n">
         <v>15.94999980926514</v>
@@ -7279,13 +7279,13 @@
         <v>72.15000152587891</v>
       </c>
       <c r="G236" t="n">
-        <v>1192.78857421875</v>
+        <v>1192.788696289062</v>
       </c>
       <c r="H236" t="n">
         <v>157.25</v>
       </c>
       <c r="I236" t="n">
-        <v>1016.488952636719</v>
+        <v>1016.488891601562</v>
       </c>
       <c r="J236" t="n">
         <v>15.75</v>
@@ -7314,7 +7314,7 @@
         <v>156.6499938964844</v>
       </c>
       <c r="I237" t="n">
-        <v>1012.943115234375</v>
+        <v>1012.943176269531</v>
       </c>
       <c r="J237" t="n">
         <v>16.45000076293945</v>
@@ -7337,7 +7337,7 @@
         <v>73.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1171.591064453125</v>
+        <v>1171.591186523438</v>
       </c>
       <c r="H238" t="n">
         <v>148.8999938964844</v>
@@ -7372,7 +7372,7 @@
         <v>151.1000061035156</v>
       </c>
       <c r="I239" t="n">
-        <v>982.7552490234375</v>
+        <v>982.7553100585938</v>
       </c>
       <c r="J239" t="n">
         <v>15.75</v>
@@ -7395,7 +7395,7 @@
         <v>70.94999694824219</v>
       </c>
       <c r="G240" t="n">
-        <v>1181.110595703125</v>
+        <v>1181.110717773438</v>
       </c>
       <c r="H240" t="n">
         <v>150.6499938964844</v>
@@ -7430,7 +7430,7 @@
         <v>149.8000030517578</v>
       </c>
       <c r="I241" t="n">
-        <v>982.2135620117188</v>
+        <v>982.213623046875</v>
       </c>
       <c r="J241" t="n">
         <v>15.75</v>
@@ -7453,13 +7453,13 @@
         <v>66.59999847412109</v>
       </c>
       <c r="G242" t="n">
-        <v>1174.3857421875</v>
+        <v>1174.385620117188</v>
       </c>
       <c r="H242" t="n">
         <v>142.5500030517578</v>
       </c>
       <c r="I242" t="n">
-        <v>939.5664672851562</v>
+        <v>939.5665283203125</v>
       </c>
       <c r="J242" t="n">
         <v>15</v>
@@ -7511,13 +7511,13 @@
         <v>60.59999847412109</v>
       </c>
       <c r="G244" t="n">
-        <v>1136.988891601562</v>
+        <v>1136.98876953125</v>
       </c>
       <c r="H244" t="n">
         <v>128.6999969482422</v>
       </c>
       <c r="I244" t="n">
-        <v>796.0140380859375</v>
+        <v>796.0140991210938</v>
       </c>
       <c r="J244" t="n">
         <v>13.55000019073486</v>
@@ -7540,7 +7540,7 @@
         <v>62.90000152587891</v>
       </c>
       <c r="G245" t="n">
-        <v>1146.91748046875</v>
+        <v>1146.917236328125</v>
       </c>
       <c r="H245" t="n">
         <v>128.1999969482422</v>
@@ -7569,7 +7569,7 @@
         <v>65.80000305175781</v>
       </c>
       <c r="G246" t="n">
-        <v>1156.300537109375</v>
+        <v>1156.300659179688</v>
       </c>
       <c r="H246" t="n">
         <v>134.6000061035156</v>
@@ -7598,7 +7598,7 @@
         <v>67.05000305175781</v>
       </c>
       <c r="G247" t="n">
-        <v>1156.187133789062</v>
+        <v>1156.187255859375</v>
       </c>
       <c r="H247" t="n">
         <v>136.5</v>
@@ -7685,13 +7685,13 @@
         <v>67.55000305175781</v>
       </c>
       <c r="G250" t="n">
-        <v>1170.477905273438</v>
+        <v>1170.477783203125</v>
       </c>
       <c r="H250" t="n">
         <v>137.8500061035156</v>
       </c>
       <c r="I250" t="n">
-        <v>937.2026977539062</v>
+        <v>937.20263671875</v>
       </c>
       <c r="J250" t="n">
         <v>14.69999980926514</v>
@@ -7714,7 +7714,7 @@
         <v>66.84999847412109</v>
       </c>
       <c r="G251" t="n">
-        <v>1161.912475585938</v>
+        <v>1161.912353515625</v>
       </c>
       <c r="H251" t="n">
         <v>138.6000061035156</v>
@@ -7743,13 +7743,13 @@
         <v>65.75</v>
       </c>
       <c r="G252" t="n">
-        <v>1144.418212890625</v>
+        <v>1144.418334960938</v>
       </c>
       <c r="H252" t="n">
         <v>136.4499969482422</v>
       </c>
       <c r="I252" t="n">
-        <v>901.99169921875</v>
+        <v>901.9916381835938</v>
       </c>
       <c r="J252" t="n">
         <v>14.44999980926514</v>
@@ -7772,7 +7772,7 @@
         <v>65.75</v>
       </c>
       <c r="G253" t="n">
-        <v>1142.373413085938</v>
+        <v>1142.37353515625</v>
       </c>
       <c r="H253" t="n">
         <v>133.75</v>
@@ -7801,13 +7801,13 @@
         <v>65.40000152587891</v>
       </c>
       <c r="G254" t="n">
-        <v>1152.756469726562</v>
+        <v>1152.756225585938</v>
       </c>
       <c r="H254" t="n">
         <v>130.1999969482422</v>
       </c>
       <c r="I254" t="n">
-        <v>892.9303588867188</v>
+        <v>892.9302978515625</v>
       </c>
       <c r="J254" t="n">
         <v>14.44999980926514</v>
@@ -7830,13 +7830,13 @@
         <v>64.75</v>
       </c>
       <c r="G255" t="n">
-        <v>1179.974609375</v>
+        <v>1179.974731445312</v>
       </c>
       <c r="H255" t="n">
         <v>135.0500030517578</v>
       </c>
       <c r="I255" t="n">
-        <v>922.330322265625</v>
+        <v>922.3302612304688</v>
       </c>
       <c r="J255" t="n">
         <v>14.55000019073486</v>
@@ -7888,13 +7888,13 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G257" t="n">
-        <v>1147.87158203125</v>
+        <v>1147.871826171875</v>
       </c>
       <c r="H257" t="n">
         <v>134.3000030517578</v>
       </c>
       <c r="I257" t="n">
-        <v>902.3364868164062</v>
+        <v>902.33642578125</v>
       </c>
       <c r="J257" t="n">
         <v>14.25</v>
@@ -7917,7 +7917,7 @@
         <v>63.59999847412109</v>
       </c>
       <c r="G258" t="n">
-        <v>1123.084228515625</v>
+        <v>1123.084350585938</v>
       </c>
       <c r="H258" t="n">
         <v>132.3000030517578</v>
@@ -7946,7 +7946,7 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G259" t="n">
-        <v>1121.266845703125</v>
+        <v>1121.266723632812</v>
       </c>
       <c r="H259" t="n">
         <v>132.6499938964844</v>
@@ -7975,13 +7975,13 @@
         <v>65.44999694824219</v>
       </c>
       <c r="G260" t="n">
-        <v>1110.588500976562</v>
+        <v>1110.58837890625</v>
       </c>
       <c r="H260" t="n">
         <v>139.25</v>
       </c>
       <c r="I260" t="n">
-        <v>888.0056762695312</v>
+        <v>888.0057373046875</v>
       </c>
       <c r="J260" t="n">
         <v>14.25</v>
@@ -8010,7 +8010,7 @@
         <v>141.3000030517578</v>
       </c>
       <c r="I261" t="n">
-        <v>883.5243530273438</v>
+        <v>883.5242919921875</v>
       </c>
       <c r="J261" t="n">
         <v>14.14999961853027</v>
@@ -8039,7 +8039,7 @@
         <v>139.5</v>
       </c>
       <c r="I262" t="n">
-        <v>899.6770629882812</v>
+        <v>899.6771240234375</v>
       </c>
       <c r="J262" t="n">
         <v>14</v>
@@ -8062,7 +8062,7 @@
         <v>62.25</v>
       </c>
       <c r="G263" t="n">
-        <v>1123.288696289062</v>
+        <v>1123.288940429688</v>
       </c>
       <c r="H263" t="n">
         <v>137.5</v>
@@ -8091,13 +8091,13 @@
         <v>61.34999847412109</v>
       </c>
       <c r="G264" t="n">
-        <v>1109.929565429688</v>
+        <v>1109.9296875</v>
       </c>
       <c r="H264" t="n">
         <v>136.25</v>
       </c>
       <c r="I264" t="n">
-        <v>895.3926391601562</v>
+        <v>895.3927001953125</v>
       </c>
       <c r="J264" t="n">
         <v>13.85000038146973</v>
@@ -8126,7 +8126,7 @@
         <v>133.6999969482422</v>
       </c>
       <c r="I265" t="n">
-        <v>892.0440063476562</v>
+        <v>892.0438842773438</v>
       </c>
       <c r="J265" t="n">
         <v>13.19999980926514</v>
@@ -8155,7 +8155,7 @@
         <v>132.1000061035156</v>
       </c>
       <c r="I266" t="n">
-        <v>882.8842163085938</v>
+        <v>882.8841552734375</v>
       </c>
       <c r="J266" t="n">
         <v>13.19999980926514</v>
@@ -8178,7 +8178,7 @@
         <v>60.90000152587891</v>
       </c>
       <c r="G267" t="n">
-        <v>1082.620361328125</v>
+        <v>1082.620483398438</v>
       </c>
       <c r="H267" t="n">
         <v>128.1499938964844</v>
@@ -8207,7 +8207,7 @@
         <v>59.04999923706055</v>
       </c>
       <c r="G268" t="n">
-        <v>1062.081787109375</v>
+        <v>1062.081665039062</v>
       </c>
       <c r="H268" t="n">
         <v>121.9000015258789</v>
@@ -8265,7 +8265,7 @@
         <v>61.54999923706055</v>
       </c>
       <c r="G270" t="n">
-        <v>1069.579345703125</v>
+        <v>1069.5791015625</v>
       </c>
       <c r="H270" t="n">
         <v>125.0999984741211</v>
@@ -8329,7 +8329,7 @@
         <v>121.3000030517578</v>
       </c>
       <c r="I272" t="n">
-        <v>828.8118896484375</v>
+        <v>828.81201171875</v>
       </c>
       <c r="J272" t="n">
         <v>11.94999980926514</v>
@@ -8358,7 +8358,7 @@
         <v>121.4000015258789</v>
       </c>
       <c r="I273" t="n">
-        <v>817.8793334960938</v>
+        <v>817.8792724609375</v>
       </c>
       <c r="J273" t="n">
         <v>11.75</v>
@@ -8381,7 +8381,7 @@
         <v>59.70000076293945</v>
       </c>
       <c r="G274" t="n">
-        <v>1050.312744140625</v>
+        <v>1050.312866210938</v>
       </c>
       <c r="H274" t="n">
         <v>124.4499969482422</v>
@@ -8410,13 +8410,13 @@
         <v>59.54999923706055</v>
       </c>
       <c r="G275" t="n">
-        <v>1047.790893554688</v>
+        <v>1047.791015625</v>
       </c>
       <c r="H275" t="n">
         <v>123.25</v>
       </c>
       <c r="I275" t="n">
-        <v>819.7998657226562</v>
+        <v>819.7999267578125</v>
       </c>
       <c r="J275" t="n">
         <v>11.64999961853027</v>
@@ -8445,7 +8445,7 @@
         <v>123.5500030517578</v>
       </c>
       <c r="I276" t="n">
-        <v>842.8470458984375</v>
+        <v>842.8471069335938</v>
       </c>
       <c r="J276" t="n">
         <v>11.69999980926514</v>
@@ -8468,13 +8468,13 @@
         <v>60.95000076293945</v>
       </c>
       <c r="G277" t="n">
-        <v>1070.578979492188</v>
+        <v>1070.578857421875</v>
       </c>
       <c r="H277" t="n">
         <v>127.3000030517578</v>
       </c>
       <c r="I277" t="n">
-        <v>831.4220581054688</v>
+        <v>831.4219970703125</v>
       </c>
       <c r="J277" t="n">
         <v>11.69999980926514</v>
@@ -8497,13 +8497,13 @@
         <v>60.84999847412109</v>
       </c>
       <c r="G278" t="n">
-        <v>1061.763671875</v>
+        <v>1061.763549804688</v>
       </c>
       <c r="H278" t="n">
         <v>130.9499969482422</v>
       </c>
       <c r="I278" t="n">
-        <v>833.8350219726562</v>
+        <v>833.8350830078125</v>
       </c>
       <c r="J278" t="n">
         <v>11.64999961853027</v>
@@ -8526,7 +8526,7 @@
         <v>60.29999923706055</v>
       </c>
       <c r="G279" t="n">
-        <v>1055.720336914062</v>
+        <v>1055.72021484375</v>
       </c>
       <c r="H279" t="n">
         <v>127.5500030517578</v>
@@ -8555,7 +8555,7 @@
         <v>60.04999923706055</v>
       </c>
       <c r="G280" t="n">
-        <v>1080.598388671875</v>
+        <v>1080.598510742188</v>
       </c>
       <c r="H280" t="n">
         <v>123.3000030517578</v>
@@ -8584,7 +8584,7 @@
         <v>60.25</v>
       </c>
       <c r="G281" t="n">
-        <v>1105.067626953125</v>
+        <v>1105.067504882812</v>
       </c>
       <c r="H281" t="n">
         <v>128.4499969482422</v>
@@ -8619,7 +8619,7 @@
         <v>129.5500030517578</v>
       </c>
       <c r="I282" t="n">
-        <v>852.2530517578125</v>
+        <v>852.2531127929688</v>
       </c>
       <c r="J282" t="n">
         <v>11.05000019073486</v>
@@ -8642,7 +8642,7 @@
         <v>61.40000152587891</v>
       </c>
       <c r="G283" t="n">
-        <v>1108.81640625</v>
+        <v>1108.816284179688</v>
       </c>
       <c r="H283" t="n">
         <v>127.0500030517578</v>
@@ -8671,7 +8671,7 @@
         <v>60.45000076293945</v>
       </c>
       <c r="G284" t="n">
-        <v>1097.093017578125</v>
+        <v>1097.092895507812</v>
       </c>
       <c r="H284" t="n">
         <v>123.6500015258789</v>
@@ -8700,7 +8700,7 @@
         <v>60.40000152587891</v>
       </c>
       <c r="G285" t="n">
-        <v>1106.044677734375</v>
+        <v>1106.044555664062</v>
       </c>
       <c r="H285" t="n">
         <v>120.8000030517578</v>
@@ -8758,7 +8758,7 @@
         <v>59.04999923706055</v>
       </c>
       <c r="G287" t="n">
-        <v>1075.78173828125</v>
+        <v>1075.781860351562</v>
       </c>
       <c r="H287" t="n">
         <v>115.8000030517578</v>
@@ -8787,13 +8787,13 @@
         <v>58.5</v>
       </c>
       <c r="G288" t="n">
-        <v>1083.142944335938</v>
+        <v>1083.14306640625</v>
       </c>
       <c r="H288" t="n">
         <v>126.9499969482422</v>
       </c>
       <c r="I288" t="n">
-        <v>802.1698608398438</v>
+        <v>802.1697998046875</v>
       </c>
       <c r="J288" t="n">
         <v>10.10000038146973</v>
@@ -8903,13 +8903,13 @@
         <v>58.54999923706055</v>
       </c>
       <c r="G292" t="n">
-        <v>1056.947143554688</v>
+        <v>1056.947021484375</v>
       </c>
       <c r="H292" t="n">
         <v>135.8000030517578</v>
       </c>
       <c r="I292" t="n">
-        <v>827.4823608398438</v>
+        <v>827.4822998046875</v>
       </c>
       <c r="J292" t="n">
         <v>9.800000190734863</v>
@@ -8938,7 +8938,7 @@
         <v>143.25</v>
       </c>
       <c r="I293" t="n">
-        <v>841.0742797851562</v>
+        <v>841.07421875</v>
       </c>
       <c r="J293" t="n">
         <v>10.69999980926514</v>
@@ -8961,13 +8961,13 @@
         <v>59.15000152587891</v>
       </c>
       <c r="G294" t="n">
-        <v>1094.5029296875</v>
+        <v>1094.502807617188</v>
       </c>
       <c r="H294" t="n">
         <v>140.8000030517578</v>
       </c>
       <c r="I294" t="n">
-        <v>843.83203125</v>
+        <v>843.8320922851562</v>
       </c>
       <c r="J294" t="n">
         <v>10.69999980926514</v>
@@ -9019,7 +9019,7 @@
         <v>58.95000076293945</v>
       </c>
       <c r="G296" t="n">
-        <v>1072.032958984375</v>
+        <v>1072.033081054688</v>
       </c>
       <c r="H296" t="n">
         <v>146.3500061035156</v>
@@ -9054,7 +9054,7 @@
         <v>147.25</v>
       </c>
       <c r="I297" t="n">
-        <v>835.9033813476562</v>
+        <v>835.9034423828125</v>
       </c>
       <c r="J297" t="n">
         <v>11.44999980926514</v>
@@ -9077,13 +9077,13 @@
         <v>55.40000152587891</v>
       </c>
       <c r="G298" t="n">
-        <v>1038.067016601562</v>
+        <v>1038.06689453125</v>
       </c>
       <c r="H298" t="n">
         <v>139.6499938964844</v>
       </c>
       <c r="I298" t="n">
-        <v>793.7979736328125</v>
+        <v>793.7980346679688</v>
       </c>
       <c r="J298" t="n">
         <v>10.75</v>
@@ -9112,7 +9112,7 @@
         <v>144.3000030517578</v>
       </c>
       <c r="I299" t="n">
-        <v>785.1306762695312</v>
+        <v>785.1307373046875</v>
       </c>
       <c r="J299" t="n">
         <v>10.69999980926514</v>
@@ -9135,13 +9135,13 @@
         <v>50.95000076293945</v>
       </c>
       <c r="G300" t="n">
-        <v>1016.505737304688</v>
+        <v>1016.505798339844</v>
       </c>
       <c r="H300" t="n">
         <v>146.6999969482422</v>
       </c>
       <c r="I300" t="n">
-        <v>778.630126953125</v>
+        <v>778.6301879882812</v>
       </c>
       <c r="J300" t="n">
         <v>10.75</v>
@@ -9164,7 +9164,7 @@
         <v>54.70000076293945</v>
       </c>
       <c r="G301" t="n">
-        <v>1011.439331054688</v>
+        <v>1011.439208984375</v>
       </c>
       <c r="H301" t="n">
         <v>141.25</v>
@@ -9199,7 +9199,7 @@
         <v>148.6499938964844</v>
       </c>
       <c r="I302" t="n">
-        <v>778.8272094726562</v>
+        <v>778.8271484375</v>
       </c>
       <c r="J302" t="n">
         <v>10.69999980926514</v>
@@ -9222,7 +9222,7 @@
         <v>59.20000076293945</v>
       </c>
       <c r="G303" t="n">
-        <v>1000.238525390625</v>
+        <v>1000.238464355469</v>
       </c>
       <c r="H303" t="n">
         <v>148.0500030517578</v>
@@ -9251,7 +9251,7 @@
         <v>59.59999847412109</v>
       </c>
       <c r="G304" t="n">
-        <v>1031.341796875</v>
+        <v>1031.341918945312</v>
       </c>
       <c r="H304" t="n">
         <v>146.8500061035156</v>
@@ -9280,7 +9280,7 @@
         <v>58.09999847412109</v>
       </c>
       <c r="G305" t="n">
-        <v>1034.477172851562</v>
+        <v>1034.477294921875</v>
       </c>
       <c r="H305" t="n">
         <v>148.8999938964844</v>
@@ -9315,7 +9315,7 @@
         <v>148.1999969482422</v>
       </c>
       <c r="I306" t="n">
-        <v>773.01611328125</v>
+        <v>773.0160522460938</v>
       </c>
       <c r="J306" t="n">
         <v>9.949999809265137</v>
@@ -9373,7 +9373,7 @@
         <v>142.1999969482422</v>
       </c>
       <c r="I308" t="n">
-        <v>736.968017578125</v>
+        <v>736.9679565429688</v>
       </c>
       <c r="J308" t="n">
         <v>9.399999618530273</v>
@@ -9396,7 +9396,7 @@
         <v>52.34999847412109</v>
       </c>
       <c r="G309" t="n">
-        <v>1021.481506347656</v>
+        <v>1021.481567382812</v>
       </c>
       <c r="H309" t="n">
         <v>137.5</v>
@@ -9431,7 +9431,7 @@
         <v>141.5500030517578</v>
       </c>
       <c r="I310" t="n">
-        <v>763.9055786132812</v>
+        <v>763.905517578125</v>
       </c>
       <c r="J310" t="n">
         <v>9.800000190734863</v>
@@ -9454,13 +9454,13 @@
         <v>54.25</v>
       </c>
       <c r="G311" t="n">
-        <v>1059.219116210938</v>
+        <v>1059.218994140625</v>
       </c>
       <c r="H311" t="n">
         <v>144.25</v>
       </c>
       <c r="I311" t="n">
-        <v>770.0613403320312</v>
+        <v>770.061279296875</v>
       </c>
       <c r="J311" t="n">
         <v>9.949999809265137</v>
@@ -9541,13 +9541,13 @@
         <v>56.54999923706055</v>
       </c>
       <c r="G314" t="n">
-        <v>1063.94482421875</v>
+        <v>1063.944580078125</v>
       </c>
       <c r="H314" t="n">
         <v>151.3999938964844</v>
       </c>
       <c r="I314" t="n">
-        <v>792.2219848632812</v>
+        <v>792.2220458984375</v>
       </c>
       <c r="J314" t="n">
         <v>11.14999961853027</v>
@@ -9570,7 +9570,7 @@
         <v>56.29999923706055</v>
       </c>
       <c r="G315" t="n">
-        <v>1056.40185546875</v>
+        <v>1056.401733398438</v>
       </c>
       <c r="H315" t="n">
         <v>146.8000030517578</v>
@@ -9628,13 +9628,13 @@
         <v>55</v>
       </c>
       <c r="G317" t="n">
-        <v>1066.307495117188</v>
+        <v>1066.3076171875</v>
       </c>
       <c r="H317" t="n">
         <v>155.6999969482422</v>
       </c>
       <c r="I317" t="n">
-        <v>799.6089477539062</v>
+        <v>799.6090087890625</v>
       </c>
       <c r="J317" t="n">
         <v>12.14999961853027</v>
@@ -9657,7 +9657,7 @@
         <v>55.20000076293945</v>
       </c>
       <c r="G318" t="n">
-        <v>1070.328979492188</v>
+        <v>1070.3291015625</v>
       </c>
       <c r="H318" t="n">
         <v>165.5500030517578</v>
@@ -9686,13 +9686,13 @@
         <v>57.34999847412109</v>
       </c>
       <c r="G319" t="n">
-        <v>1075.759033203125</v>
+        <v>1075.758911132812</v>
       </c>
       <c r="H319" t="n">
         <v>162</v>
       </c>
       <c r="I319" t="n">
-        <v>843.83203125</v>
+        <v>843.8320922851562</v>
       </c>
       <c r="J319" t="n">
         <v>12.69999980926514</v>
@@ -9715,13 +9715,13 @@
         <v>55.40000152587891</v>
       </c>
       <c r="G320" t="n">
-        <v>1063.444946289062</v>
+        <v>1063.44482421875</v>
       </c>
       <c r="H320" t="n">
         <v>159.6499938964844</v>
       </c>
       <c r="I320" t="n">
-        <v>820.9818115234375</v>
+        <v>820.9817504882812</v>
       </c>
       <c r="J320" t="n">
         <v>12.39999961853027</v>
@@ -9744,7 +9744,7 @@
         <v>55</v>
       </c>
       <c r="G321" t="n">
-        <v>1068.738525390625</v>
+        <v>1068.738647460938</v>
       </c>
       <c r="H321" t="n">
         <v>159.1999969482422</v>
@@ -9802,7 +9802,7 @@
         <v>54.20000076293945</v>
       </c>
       <c r="G323" t="n">
-        <v>1067.375366210938</v>
+        <v>1067.37548828125</v>
       </c>
       <c r="H323" t="n">
         <v>159.3500061035156</v>
@@ -9860,7 +9860,7 @@
         <v>54.95000076293945</v>
       </c>
       <c r="G325" t="n">
-        <v>1079.666870117188</v>
+        <v>1079.666748046875</v>
       </c>
       <c r="H325" t="n">
         <v>157.8999938964844</v>
@@ -9918,7 +9918,7 @@
         <v>58.90000152587891</v>
       </c>
       <c r="G327" t="n">
-        <v>1080.121215820312</v>
+        <v>1080.121337890625</v>
       </c>
       <c r="H327" t="n">
         <v>160.6999969482422</v>
@@ -9947,7 +9947,7 @@
         <v>58.04999923706055</v>
       </c>
       <c r="G328" t="n">
-        <v>1099.864501953125</v>
+        <v>1099.864868164062</v>
       </c>
       <c r="H328" t="n">
         <v>157.5500030517578</v>
@@ -9976,7 +9976,7 @@
         <v>58.40000152587891</v>
       </c>
       <c r="G329" t="n">
-        <v>1109.20263671875</v>
+        <v>1109.202514648438</v>
       </c>
       <c r="H329" t="n">
         <v>154.9499969482422</v>
@@ -10005,7 +10005,7 @@
         <v>58.34999847412109</v>
       </c>
       <c r="G330" t="n">
-        <v>1099.682861328125</v>
+        <v>1099.68310546875</v>
       </c>
       <c r="H330" t="n">
         <v>153.75</v>
@@ -10034,13 +10034,13 @@
         <v>59.54999923706055</v>
       </c>
       <c r="G331" t="n">
-        <v>1112.360595703125</v>
+        <v>1112.360717773438</v>
       </c>
       <c r="H331" t="n">
         <v>154.5500030517578</v>
       </c>
       <c r="I331" t="n">
-        <v>882.3917236328125</v>
+        <v>882.3917846679688</v>
       </c>
       <c r="J331" t="n">
         <v>12.19999980926514</v>
@@ -10069,7 +10069,7 @@
         <v>153.6000061035156</v>
       </c>
       <c r="I332" t="n">
-        <v>868.2579956054688</v>
+        <v>868.258056640625</v>
       </c>
       <c r="J332" t="n">
         <v>12.39999961853027</v>
@@ -10092,13 +10092,13 @@
         <v>57.09999847412109</v>
       </c>
       <c r="G333" t="n">
-        <v>1123.220703125</v>
+        <v>1123.220581054688</v>
       </c>
       <c r="H333" t="n">
         <v>152.4499969482422</v>
       </c>
       <c r="I333" t="n">
-        <v>868.3565673828125</v>
+        <v>868.3565063476562</v>
       </c>
       <c r="J333" t="n">
         <v>12.14999961853027</v>
@@ -10121,13 +10121,13 @@
         <v>56.25</v>
       </c>
       <c r="G334" t="n">
-        <v>1126.69677734375</v>
+        <v>1126.696899414062</v>
       </c>
       <c r="H334" t="n">
         <v>150.3000030517578</v>
       </c>
       <c r="I334" t="n">
-        <v>860.8712158203125</v>
+        <v>860.8711547851562</v>
       </c>
       <c r="J334" t="n">
         <v>12</v>
@@ -10150,13 +10150,13 @@
         <v>59.25</v>
       </c>
       <c r="G335" t="n">
-        <v>1134.4443359375</v>
+        <v>1134.444213867188</v>
       </c>
       <c r="H335" t="n">
         <v>148.8000030517578</v>
       </c>
       <c r="I335" t="n">
-        <v>873.0350341796875</v>
+        <v>873.0349731445312</v>
       </c>
       <c r="J335" t="n">
         <v>11.89999961853027</v>
@@ -10179,7 +10179,7 @@
         <v>58.59999847412109</v>
       </c>
       <c r="G336" t="n">
-        <v>1127.03759765625</v>
+        <v>1127.037719726562</v>
       </c>
       <c r="H336" t="n">
         <v>147.8500061035156</v>
@@ -10237,7 +10237,7 @@
         <v>60.59999847412109</v>
       </c>
       <c r="G338" t="n">
-        <v>1131.104370117188</v>
+        <v>1131.1044921875</v>
       </c>
       <c r="H338" t="n">
         <v>144.1499938964844</v>
@@ -10272,7 +10272,7 @@
         <v>140.8999938964844</v>
       </c>
       <c r="I339" t="n">
-        <v>886.9715576171875</v>
+        <v>886.9716186523438</v>
       </c>
       <c r="J339" t="n">
         <v>11.69999980926514</v>
@@ -10353,7 +10353,7 @@
         <v>58.5</v>
       </c>
       <c r="G342" t="n">
-        <v>1109.611328125</v>
+        <v>1109.611572265625</v>
       </c>
       <c r="H342" t="n">
         <v>137.4499969482422</v>
@@ -10388,7 +10388,7 @@
         <v>134.6499938964844</v>
       </c>
       <c r="I343" t="n">
-        <v>881.4067993164062</v>
+        <v>881.4068603515625</v>
       </c>
       <c r="J343" t="n">
         <v>11.5</v>
@@ -10411,13 +10411,13 @@
         <v>59.79999923706055</v>
       </c>
       <c r="G344" t="n">
-        <v>1115.3369140625</v>
+        <v>1115.336791992188</v>
       </c>
       <c r="H344" t="n">
         <v>139.6499938964844</v>
       </c>
       <c r="I344" t="n">
-        <v>899.430908203125</v>
+        <v>899.4308471679688</v>
       </c>
       <c r="J344" t="n">
         <v>12.94999980926514</v>
@@ -10440,13 +10440,13 @@
         <v>60.65000152587891</v>
       </c>
       <c r="G345" t="n">
-        <v>1108.839111328125</v>
+        <v>1108.838989257812</v>
       </c>
       <c r="H345" t="n">
         <v>138.6000061035156</v>
       </c>
       <c r="I345" t="n">
-        <v>881.308349609375</v>
+        <v>881.3082885742188</v>
       </c>
       <c r="J345" t="n">
         <v>12.10000038146973</v>
@@ -10469,7 +10469,7 @@
         <v>60.34999847412109</v>
       </c>
       <c r="G346" t="n">
-        <v>1108.702758789062</v>
+        <v>1108.70263671875</v>
       </c>
       <c r="H346" t="n">
         <v>138.8999938964844</v>
@@ -10504,7 +10504,7 @@
         <v>138</v>
       </c>
       <c r="I347" t="n">
-        <v>887.0208129882812</v>
+        <v>887.0208740234375</v>
       </c>
       <c r="J347" t="n">
         <v>13.05000019073486</v>
@@ -10527,13 +10527,13 @@
         <v>61.09999847412109</v>
       </c>
       <c r="G348" t="n">
-        <v>1145.349731445312</v>
+        <v>1145.349609375</v>
       </c>
       <c r="H348" t="n">
         <v>139.6499938964844</v>
       </c>
       <c r="I348" t="n">
-        <v>897.3624877929688</v>
+        <v>897.3624267578125</v>
       </c>
       <c r="J348" t="n">
         <v>13.30000019073486</v>
@@ -10556,13 +10556,13 @@
         <v>61.25</v>
       </c>
       <c r="G349" t="n">
-        <v>1145.054443359375</v>
+        <v>1145.054321289062</v>
       </c>
       <c r="H349" t="n">
         <v>138.6000061035156</v>
       </c>
       <c r="I349" t="n">
-        <v>902.0902099609375</v>
+        <v>902.0901489257812</v>
       </c>
       <c r="J349" t="n">
         <v>12.94999980926514</v>
@@ -10620,7 +10620,7 @@
         <v>133.9499969482422</v>
       </c>
       <c r="I351" t="n">
-        <v>904.7001342773438</v>
+        <v>904.7001953125</v>
       </c>
       <c r="J351" t="n">
         <v>12.94999980926514</v>
@@ -10649,7 +10649,7 @@
         <v>134.6000061035156</v>
       </c>
       <c r="I352" t="n">
-        <v>931.1947021484375</v>
+        <v>931.1946411132812</v>
       </c>
       <c r="J352" t="n">
         <v>13.14999961853027</v>
@@ -10736,7 +10736,7 @@
         <v>136.0500030517578</v>
       </c>
       <c r="I355" t="n">
-        <v>942.61962890625</v>
+        <v>942.6196899414062</v>
       </c>
       <c r="J355" t="n">
         <v>14.75</v>
@@ -10759,7 +10759,7 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G356" t="n">
-        <v>1135.830200195312</v>
+        <v>1135.830078125</v>
       </c>
       <c r="H356" t="n">
         <v>137.0500030517578</v>
@@ -10817,7 +10817,7 @@
         <v>63.54999923706055</v>
       </c>
       <c r="G358" t="n">
-        <v>1128.786987304688</v>
+        <v>1128.786865234375</v>
       </c>
       <c r="H358" t="n">
         <v>139.3999938964844</v>
@@ -10846,7 +10846,7 @@
         <v>64.65000152587891</v>
       </c>
       <c r="G359" t="n">
-        <v>1145.463256835938</v>
+        <v>1145.46337890625</v>
       </c>
       <c r="H359" t="n">
         <v>143.8500061035156</v>
@@ -10875,7 +10875,7 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G360" t="n">
-        <v>1159.549560546875</v>
+        <v>1159.549682617188</v>
       </c>
       <c r="H360" t="n">
         <v>149.9499969482422</v>
@@ -10933,7 +10933,7 @@
         <v>65.59999847412109</v>
       </c>
       <c r="G362" t="n">
-        <v>1171.159423828125</v>
+        <v>1171.159545898438</v>
       </c>
       <c r="H362" t="n">
         <v>151.5500030517578</v>
@@ -10962,7 +10962,7 @@
         <v>66.5</v>
       </c>
       <c r="G363" t="n">
-        <v>1159.526977539062</v>
+        <v>1159.52685546875</v>
       </c>
       <c r="H363" t="n">
         <v>150.75</v>
@@ -11020,7 +11020,7 @@
         <v>65.75</v>
       </c>
       <c r="G365" t="n">
-        <v>1165.206787109375</v>
+        <v>1165.206909179688</v>
       </c>
       <c r="H365" t="n">
         <v>147.75</v>
@@ -11049,7 +11049,7 @@
         <v>65.25</v>
       </c>
       <c r="G366" t="n">
-        <v>1152.1201171875</v>
+        <v>1152.120239257812</v>
       </c>
       <c r="H366" t="n">
         <v>145.1499938964844</v>
@@ -11078,7 +11078,7 @@
         <v>63.15000152587891</v>
       </c>
       <c r="G367" t="n">
-        <v>1142.691650390625</v>
+        <v>1142.691528320312</v>
       </c>
       <c r="H367" t="n">
         <v>143.25</v>
@@ -11136,7 +11136,7 @@
         <v>63.29999923706055</v>
       </c>
       <c r="G369" t="n">
-        <v>1134.376220703125</v>
+        <v>1134.376098632812</v>
       </c>
       <c r="H369" t="n">
         <v>141.25</v>
@@ -11281,7 +11281,7 @@
         <v>62.54999923706055</v>
       </c>
       <c r="G374" t="n">
-        <v>1174.3857421875</v>
+        <v>1174.385620117188</v>
       </c>
       <c r="H374" t="n">
         <v>138.5</v>
@@ -11368,7 +11368,7 @@
         <v>63.29999923706055</v>
       </c>
       <c r="G377" t="n">
-        <v>1242.794799804688</v>
+        <v>1242.794921875</v>
       </c>
       <c r="H377" t="n">
         <v>135.6499938964844</v>
@@ -11513,7 +11513,7 @@
         <v>65</v>
       </c>
       <c r="G382" t="n">
-        <v>1270.80859375</v>
+        <v>1270.808471679688</v>
       </c>
       <c r="H382" t="n">
         <v>135</v>
@@ -11542,7 +11542,7 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G383" t="n">
-        <v>1281.60009765625</v>
+        <v>1281.600341796875</v>
       </c>
       <c r="H383" t="n">
         <v>141.6999969482422</v>
@@ -11571,7 +11571,7 @@
         <v>59.5</v>
       </c>
       <c r="G384" t="n">
-        <v>1291.324340820312</v>
+        <v>1291.32421875</v>
       </c>
       <c r="H384" t="n">
         <v>154.8500061035156</v>
@@ -11600,7 +11600,7 @@
         <v>59.70000076293945</v>
       </c>
       <c r="G385" t="n">
-        <v>1289.760498046875</v>
+        <v>1289.760620117188</v>
       </c>
       <c r="H385" t="n">
         <v>162.3999938964844</v>
@@ -11629,7 +11629,7 @@
         <v>58.79999923706055</v>
       </c>
       <c r="G386" t="n">
-        <v>1249.834716796875</v>
+        <v>1249.834594726562</v>
       </c>
       <c r="H386" t="n">
         <v>163.0500030517578</v>
@@ -11658,7 +11658,7 @@
         <v>58.25</v>
       </c>
       <c r="G387" t="n">
-        <v>1224.554809570312</v>
+        <v>1224.554931640625</v>
       </c>
       <c r="H387" t="n">
         <v>162.6000061035156</v>
@@ -11687,7 +11687,7 @@
         <v>57.40000152587891</v>
       </c>
       <c r="G388" t="n">
-        <v>1223.767211914062</v>
+        <v>1223.767333984375</v>
       </c>
       <c r="H388" t="n">
         <v>175.1999969482422</v>
@@ -11716,7 +11716,7 @@
         <v>58.29999923706055</v>
       </c>
       <c r="G389" t="n">
-        <v>1243.656127929688</v>
+        <v>1243.65625</v>
       </c>
       <c r="H389" t="n">
         <v>170.9499969482422</v>
@@ -11745,7 +11745,7 @@
         <v>57.45000076293945</v>
       </c>
       <c r="G390" t="n">
-        <v>1232.087036132812</v>
+        <v>1232.087158203125</v>
       </c>
       <c r="H390" t="n">
         <v>178.6000061035156</v>
@@ -11861,7 +11861,7 @@
         <v>58.15000152587891</v>
       </c>
       <c r="G394" t="n">
-        <v>1224.0380859375</v>
+        <v>1224.038208007812</v>
       </c>
       <c r="H394" t="n">
         <v>181.1999969482422</v>
@@ -11948,7 +11948,7 @@
         <v>59.04999923706055</v>
       </c>
       <c r="G397" t="n">
-        <v>1242.49951171875</v>
+        <v>1242.499389648438</v>
       </c>
       <c r="H397" t="n">
         <v>210.0500030517578</v>
@@ -11977,7 +11977,7 @@
         <v>60.20000076293945</v>
       </c>
       <c r="G398" t="n">
-        <v>1235.016235351562</v>
+        <v>1235.016357421875</v>
       </c>
       <c r="H398" t="n">
         <v>194.6999969482422</v>
@@ -12006,7 +12006,7 @@
         <v>60.04999923706055</v>
       </c>
       <c r="G399" t="n">
-        <v>1243.163940429688</v>
+        <v>1243.1640625</v>
       </c>
       <c r="H399" t="n">
         <v>191.4499969482422</v>
@@ -12035,7 +12035,7 @@
         <v>62</v>
       </c>
       <c r="G400" t="n">
-        <v>1248.702392578125</v>
+        <v>1248.702514648438</v>
       </c>
       <c r="H400" t="n">
         <v>175.8500061035156</v>
@@ -12064,7 +12064,7 @@
         <v>62.20000076293945</v>
       </c>
       <c r="G401" t="n">
-        <v>1253.969970703125</v>
+        <v>1253.970092773438</v>
       </c>
       <c r="H401" t="n">
         <v>170</v>
@@ -12122,7 +12122,7 @@
         <v>62.54999923706055</v>
       </c>
       <c r="G403" t="n">
-        <v>1267.754516601562</v>
+        <v>1267.754638671875</v>
       </c>
       <c r="H403" t="n">
         <v>163</v>
@@ -12151,7 +12151,7 @@
         <v>60.95000076293945</v>
       </c>
       <c r="G404" t="n">
-        <v>1249.465576171875</v>
+        <v>1249.465454101562</v>
       </c>
       <c r="H404" t="n">
         <v>158.0500030517578</v>
@@ -12180,7 +12180,7 @@
         <v>63.5</v>
       </c>
       <c r="G405" t="n">
-        <v>1258.720825195312</v>
+        <v>1258.720703125</v>
       </c>
       <c r="H405" t="n">
         <v>160.6000061035156</v>
@@ -37898,7 +37898,7 @@
         <v>5.598621951273208</v>
       </c>
       <c r="G42" t="n">
-        <v>2.040911910979792</v>
+        <v>2.040877935444163</v>
       </c>
       <c r="H42" t="n">
         <v>-14.50333586855534</v>
@@ -37927,13 +37927,13 @@
         <v>7.004606888590881</v>
       </c>
       <c r="G43" t="n">
-        <v>3.837297223976188</v>
+        <v>3.837343764441714</v>
       </c>
       <c r="H43" t="n">
         <v>9.220106101738512</v>
       </c>
       <c r="I43" t="n">
-        <v>7.802001872916686</v>
+        <v>7.802010417317251</v>
       </c>
       <c r="J43" t="n">
         <v>22.61306576011055</v>
@@ -37956,13 +37956,13 @@
         <v>-7.106166810697612</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3659830649118234</v>
+        <v>0.3659714981767426</v>
       </c>
       <c r="H44" t="n">
         <v>10.36725582872331</v>
       </c>
       <c r="I44" t="n">
-        <v>-2.506398442968916</v>
+        <v>-2.506406170323727</v>
       </c>
       <c r="J44" t="n">
         <v>1.53060832255989</v>
@@ -37985,7 +37985,7 @@
         <v>-5.117786759101961</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.329742978595971</v>
+        <v>-1.329720456261541</v>
       </c>
       <c r="H45" t="n">
         <v>4.476417699780821</v>
@@ -38014,7 +38014,7 @@
         <v>-6.883508838267105</v>
       </c>
       <c r="G46" t="n">
-        <v>-7.590678949528251</v>
+        <v>-7.590700042745402</v>
       </c>
       <c r="H46" t="n">
         <v>-9.150325892060184</v>
@@ -38072,13 +38072,13 @@
         <v>6.079503403138031</v>
       </c>
       <c r="G48" t="n">
-        <v>7.128570156643566</v>
+        <v>7.128581444439974</v>
       </c>
       <c r="H48" t="n">
         <v>11.48815860769938</v>
       </c>
       <c r="I48" t="n">
-        <v>-3.906760722347635</v>
+        <v>-3.90674987660834</v>
       </c>
       <c r="J48" t="n">
         <v>-0.3105661069842447</v>
@@ -38101,13 +38101,13 @@
         <v>-0.696589719615015</v>
       </c>
       <c r="G49" t="n">
-        <v>7.227432329924066</v>
+        <v>7.227408916932054</v>
       </c>
       <c r="H49" t="n">
         <v>3.474762330681291</v>
       </c>
       <c r="I49" t="n">
-        <v>1.992291639014976</v>
+        <v>1.992280127469637</v>
       </c>
       <c r="J49" t="n">
         <v>-1.829263683162408</v>
@@ -38130,7 +38130,7 @@
         <v>-8.498583753085121</v>
       </c>
       <c r="G50" t="n">
-        <v>-9.863721569537597</v>
+        <v>-9.863720565037227</v>
       </c>
       <c r="H50" t="n">
         <v>-15.6172858344184</v>
@@ -38159,13 +38159,13 @@
         <v>8.782737772308536</v>
       </c>
       <c r="G51" t="n">
-        <v>5.463621306864352</v>
+        <v>5.463643374052984</v>
       </c>
       <c r="H51" t="n">
         <v>38.34329813061588</v>
       </c>
       <c r="I51" t="n">
-        <v>4.312858971254707</v>
+        <v>4.312852371434839</v>
       </c>
       <c r="J51" t="n">
         <v>35.48386898298783</v>
@@ -38188,13 +38188,13 @@
         <v>-5.942026774088538</v>
       </c>
       <c r="G52" t="n">
-        <v>-3.32094926095331</v>
+        <v>-3.320959644468446</v>
       </c>
       <c r="H52" t="n">
         <v>29.24944861623748</v>
       </c>
       <c r="I52" t="n">
-        <v>3.064809231029253</v>
+        <v>3.064815751886085</v>
       </c>
       <c r="J52" t="n">
         <v>7.826083639393677</v>
@@ -38223,7 +38223,7 @@
         <v>-16.0722547147822</v>
       </c>
       <c r="I53" t="n">
-        <v>2.955478764142816</v>
+        <v>2.955471852145508</v>
       </c>
       <c r="J53" t="n">
         <v>-8.730161493387333</v>
@@ -38252,7 +38252,7 @@
         <v>-12.62647164563844</v>
       </c>
       <c r="I54" t="n">
-        <v>-16.35935731537461</v>
+        <v>-16.35936109340738</v>
       </c>
       <c r="J54" t="n">
         <v>-11.57894469144052</v>
@@ -38281,7 +38281,7 @@
         <v>10.01780916676824</v>
       </c>
       <c r="I55" t="n">
-        <v>42.1559706663859</v>
+        <v>42.15598663130014</v>
       </c>
       <c r="J55" t="n">
         <v>5.555555555555558</v>
@@ -38304,7 +38304,7 @@
         <v>10.65627667685571</v>
       </c>
       <c r="G56" t="n">
-        <v>11.66323439425943</v>
+        <v>11.66324714899951</v>
       </c>
       <c r="H56" t="n">
         <v>7.361381156751889</v>
@@ -38333,13 +38333,13 @@
         <v>-6.15854030702172</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.133403576054681</v>
+        <v>-1.133414869096705</v>
       </c>
       <c r="H57" t="n">
         <v>3.513107684464867</v>
       </c>
       <c r="I57" t="n">
-        <v>-20.63637016359784</v>
+        <v>-20.63636456057385</v>
       </c>
       <c r="J57" t="n">
         <v>-11.82432417193846</v>
@@ -38858,13 +38858,13 @@
         <v>15.76036725725447</v>
       </c>
       <c r="G15" t="n">
-        <v>9.403485464018434</v>
+        <v>9.403498072287109</v>
       </c>
       <c r="H15" t="n">
         <v>-4.159445407279028</v>
       </c>
       <c r="I15" t="n">
-        <v>22.41575342492897</v>
+        <v>22.41576312761737</v>
       </c>
       <c r="J15" t="n">
         <v>41.20603477451257</v>
@@ -38887,13 +38887,13 @@
         <v>-17.92738085880669</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.485780165858081</v>
+        <v>-8.485790712466645</v>
       </c>
       <c r="H16" t="n">
         <v>4.756719823472322</v>
       </c>
       <c r="I16" t="n">
-        <v>-17.2076053573798</v>
+        <v>-17.20761191951514</v>
       </c>
       <c r="J16" t="n">
         <v>-30.66202407831533</v>
@@ -38916,7 +38916,7 @@
         <v>2.321981478994783</v>
       </c>
       <c r="G17" t="n">
-        <v>7.126494103802106</v>
+        <v>7.12648200042505</v>
       </c>
       <c r="H17" t="n">
         <v>0.7315289117223678</v>
@@ -38945,7 +38945,7 @@
         <v>-6.376813805621606</v>
       </c>
       <c r="G18" t="n">
-        <v>-8.095943679813933</v>
+        <v>-8.095933296298796</v>
       </c>
       <c r="H18" t="n">
         <v>50.88300138028043</v>

--- a/dashboards/Reliance Group.xlsx
+++ b/dashboards/Reliance Group.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1166"/>
+  <dimension ref="A1:J1168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,13 +493,13 @@
         <v>91.84999847412109</v>
       </c>
       <c r="G2" t="n">
-        <v>1088.74658203125</v>
+        <v>1088.746704101562</v>
       </c>
       <c r="H2" t="n">
         <v>100.8000030517578</v>
       </c>
       <c r="I2" t="n">
-        <v>850.676025390625</v>
+        <v>850.6759643554688</v>
       </c>
       <c r="J2" t="n">
         <v>14.25</v>
@@ -522,13 +522,13 @@
         <v>90.40000152587891</v>
       </c>
       <c r="G3" t="n">
-        <v>1113.3173828125</v>
+        <v>1113.317626953125</v>
       </c>
       <c r="H3" t="n">
         <v>97.5</v>
       </c>
       <c r="I3" t="n">
-        <v>857.11083984375</v>
+        <v>857.1109008789062</v>
       </c>
       <c r="J3" t="n">
         <v>13.89999961853027</v>
@@ -557,7 +557,7 @@
         <v>97.05000305175781</v>
       </c>
       <c r="I4" t="n">
-        <v>844.1920776367188</v>
+        <v>844.1920166015625</v>
       </c>
       <c r="J4" t="n">
         <v>13.85000038146973</v>
@@ -586,7 +586,7 @@
         <v>100.1500015258789</v>
       </c>
       <c r="I5" t="n">
-        <v>844.6341552734375</v>
+        <v>844.6340942382812</v>
       </c>
       <c r="J5" t="n">
         <v>14.30000019073486</v>
@@ -609,13 +609,13 @@
         <v>91</v>
       </c>
       <c r="G6" t="n">
-        <v>1103.30810546875</v>
+        <v>1103.307983398438</v>
       </c>
       <c r="H6" t="n">
         <v>98.55000305175781</v>
       </c>
       <c r="I6" t="n">
-        <v>844.0447387695312</v>
+        <v>844.044677734375</v>
       </c>
       <c r="J6" t="n">
         <v>14.14999961853027</v>
@@ -667,13 +667,13 @@
         <v>89.34999847412109</v>
       </c>
       <c r="G8" t="n">
-        <v>1112.16259765625</v>
+        <v>1112.162719726562</v>
       </c>
       <c r="H8" t="n">
         <v>98.40000152587891</v>
       </c>
       <c r="I8" t="n">
-        <v>968.8118896484375</v>
+        <v>968.811767578125</v>
       </c>
       <c r="J8" t="n">
         <v>14.30000019073486</v>
@@ -702,7 +702,7 @@
         <v>96.40000152587891</v>
       </c>
       <c r="I9" t="n">
-        <v>941.8934936523438</v>
+        <v>941.8935546875</v>
       </c>
       <c r="J9" t="n">
         <v>14.35000038146973</v>
@@ -725,13 +725,13 @@
         <v>90.09999847412109</v>
       </c>
       <c r="G10" t="n">
-        <v>1148.28271484375</v>
+        <v>1148.282836914062</v>
       </c>
       <c r="H10" t="n">
         <v>99.05000305175781</v>
       </c>
       <c r="I10" t="n">
-        <v>931.4307861328125</v>
+        <v>931.4307250976562</v>
       </c>
       <c r="J10" t="n">
         <v>14.25</v>
@@ -760,7 +760,7 @@
         <v>102.75</v>
       </c>
       <c r="I11" t="n">
-        <v>931.5291137695312</v>
+        <v>931.5289916992188</v>
       </c>
       <c r="J11" t="n">
         <v>14.94999980926514</v>
@@ -789,7 +789,7 @@
         <v>105.5500030517578</v>
       </c>
       <c r="I12" t="n">
-        <v>934.6727905273438</v>
+        <v>934.6727294921875</v>
       </c>
       <c r="J12" t="n">
         <v>15.64999961853027</v>
@@ -818,7 +818,7 @@
         <v>101.9499969482422</v>
       </c>
       <c r="I13" t="n">
-        <v>930.49755859375</v>
+        <v>930.4974975585938</v>
       </c>
       <c r="J13" t="n">
         <v>16.10000038146973</v>
@@ -847,7 +847,7 @@
         <v>99.75</v>
       </c>
       <c r="I14" t="n">
-        <v>957.7103881835938</v>
+        <v>957.71044921875</v>
       </c>
       <c r="J14" t="n">
         <v>15.85000038146973</v>
@@ -899,13 +899,13 @@
         <v>86.40000152587891</v>
       </c>
       <c r="G16" t="n">
-        <v>1122.2626953125</v>
+        <v>1122.262573242188</v>
       </c>
       <c r="H16" t="n">
         <v>98.25</v>
       </c>
       <c r="I16" t="n">
-        <v>898.8636474609375</v>
+        <v>898.8637084960938</v>
       </c>
       <c r="J16" t="n">
         <v>16.04999923706055</v>
@@ -928,7 +928,7 @@
         <v>82.09999847412109</v>
       </c>
       <c r="G17" t="n">
-        <v>1076.993408203125</v>
+        <v>1076.993530273438</v>
       </c>
       <c r="H17" t="n">
         <v>93.55000305175781</v>
@@ -957,7 +957,7 @@
         <v>78</v>
       </c>
       <c r="G18" t="n">
-        <v>1074.887451171875</v>
+        <v>1074.887329101562</v>
       </c>
       <c r="H18" t="n">
         <v>98.05000305175781</v>
@@ -1021,7 +1021,7 @@
         <v>102.3000030517578</v>
       </c>
       <c r="I20" t="n">
-        <v>885.7974243164062</v>
+        <v>885.7974853515625</v>
       </c>
       <c r="J20" t="n">
         <v>15.19999980926514</v>
@@ -1050,7 +1050,7 @@
         <v>101.0500030517578</v>
       </c>
       <c r="I21" t="n">
-        <v>864.528076171875</v>
+        <v>864.5281372070312</v>
       </c>
       <c r="J21" t="n">
         <v>14.80000019073486</v>
@@ -1079,7 +1079,7 @@
         <v>106.0999984741211</v>
       </c>
       <c r="I22" t="n">
-        <v>907.7545166015625</v>
+        <v>907.7544555664062</v>
       </c>
       <c r="J22" t="n">
         <v>15.5</v>
@@ -1137,7 +1137,7 @@
         <v>115.5999984741211</v>
       </c>
       <c r="I24" t="n">
-        <v>910.0140991210938</v>
+        <v>910.0140380859375</v>
       </c>
       <c r="J24" t="n">
         <v>16.85000038146973</v>
@@ -1160,13 +1160,13 @@
         <v>85.44999694824219</v>
       </c>
       <c r="G25" t="n">
-        <v>1055.887451171875</v>
+        <v>1055.887573242188</v>
       </c>
       <c r="H25" t="n">
         <v>121.3499984741211</v>
       </c>
       <c r="I25" t="n">
-        <v>898.3724975585938</v>
+        <v>898.3724365234375</v>
       </c>
       <c r="J25" t="n">
         <v>17.64999961853027</v>
@@ -1189,13 +1189,13 @@
         <v>83.25</v>
       </c>
       <c r="G26" t="n">
-        <v>1049.456176757812</v>
+        <v>1049.4560546875</v>
       </c>
       <c r="H26" t="n">
         <v>133.4499969482422</v>
       </c>
       <c r="I26" t="n">
-        <v>874.7943725585938</v>
+        <v>874.79443359375</v>
       </c>
       <c r="J26" t="n">
         <v>18.5</v>
@@ -1253,7 +1253,7 @@
         <v>147.8500061035156</v>
       </c>
       <c r="I28" t="n">
-        <v>866.5420532226562</v>
+        <v>866.5421142578125</v>
       </c>
       <c r="J28" t="n">
         <v>17</v>
@@ -1276,13 +1276,13 @@
         <v>92.09999847412109</v>
       </c>
       <c r="G29" t="n">
-        <v>1078.420288085938</v>
+        <v>1078.42041015625</v>
       </c>
       <c r="H29" t="n">
         <v>133.1000061035156</v>
       </c>
       <c r="I29" t="n">
-        <v>879.510009765625</v>
+        <v>879.5098876953125</v>
       </c>
       <c r="J29" t="n">
         <v>16.14999961853027</v>
@@ -1340,7 +1340,7 @@
         <v>120.5999984741211</v>
       </c>
       <c r="I31" t="n">
-        <v>771.345703125</v>
+        <v>771.3457641601562</v>
       </c>
       <c r="J31" t="n">
         <v>15.19999980926514</v>
@@ -1363,13 +1363,13 @@
         <v>87.05000305175781</v>
       </c>
       <c r="G32" t="n">
-        <v>1095.1328125</v>
+        <v>1095.132690429688</v>
       </c>
       <c r="H32" t="n">
         <v>111.8499984741211</v>
       </c>
       <c r="I32" t="n">
-        <v>784.4610595703125</v>
+        <v>784.4609985351562</v>
       </c>
       <c r="J32" t="n">
         <v>14.55000019073486</v>
@@ -1479,13 +1479,13 @@
         <v>82.15000152587891</v>
       </c>
       <c r="G36" t="n">
-        <v>1086.957763671875</v>
+        <v>1086.957885742188</v>
       </c>
       <c r="H36" t="n">
         <v>112.6999969482422</v>
       </c>
       <c r="I36" t="n">
-        <v>750.4694213867188</v>
+        <v>750.4693603515625</v>
       </c>
       <c r="J36" t="n">
         <v>13.60000038146973</v>
@@ -1514,7 +1514,7 @@
         <v>114.3499984741211</v>
       </c>
       <c r="I37" t="n">
-        <v>725.5650634765625</v>
+        <v>725.5650024414062</v>
       </c>
       <c r="J37" t="n">
         <v>12.94999980926514</v>
@@ -1572,7 +1572,7 @@
         <v>101.9499969482422</v>
       </c>
       <c r="I39" t="n">
-        <v>655.5677490234375</v>
+        <v>655.5676879882812</v>
       </c>
       <c r="J39" t="n">
         <v>12.89999961853027</v>
@@ -1601,7 +1601,7 @@
         <v>104.5999984741211</v>
       </c>
       <c r="I40" t="n">
-        <v>681.9456176757812</v>
+        <v>681.9456787109375</v>
       </c>
       <c r="J40" t="n">
         <v>13</v>
@@ -1624,7 +1624,7 @@
         <v>76.94999694824219</v>
       </c>
       <c r="G41" t="n">
-        <v>1068.682373046875</v>
+        <v>1068.682495117188</v>
       </c>
       <c r="H41" t="n">
         <v>104.5999984741211</v>
@@ -1659,7 +1659,7 @@
         <v>107.5999984741211</v>
       </c>
       <c r="I42" t="n">
-        <v>692.8505249023438</v>
+        <v>692.8504638671875</v>
       </c>
       <c r="J42" t="n">
         <v>13.14999961853027</v>
@@ -1717,7 +1717,7 @@
         <v>103.5</v>
       </c>
       <c r="I44" t="n">
-        <v>674.7249145507812</v>
+        <v>674.7249755859375</v>
       </c>
       <c r="J44" t="n">
         <v>12.85000038146973</v>
@@ -1775,7 +1775,7 @@
         <v>101.75</v>
       </c>
       <c r="I46" t="n">
-        <v>667.504150390625</v>
+        <v>667.5040893554688</v>
       </c>
       <c r="J46" t="n">
         <v>12.80000019073486</v>
@@ -1798,13 +1798,13 @@
         <v>77.80000305175781</v>
       </c>
       <c r="G47" t="n">
-        <v>1066.214111328125</v>
+        <v>1066.213989257812</v>
       </c>
       <c r="H47" t="n">
         <v>107.5</v>
       </c>
       <c r="I47" t="n">
-        <v>693.8820190429688</v>
+        <v>693.882080078125</v>
       </c>
       <c r="J47" t="n">
         <v>13.35000038146973</v>
@@ -1827,13 +1827,13 @@
         <v>78</v>
       </c>
       <c r="G48" t="n">
-        <v>1083.49267578125</v>
+        <v>1083.492797851562</v>
       </c>
       <c r="H48" t="n">
         <v>111.4000015258789</v>
       </c>
       <c r="I48" t="n">
-        <v>701.839599609375</v>
+        <v>701.8396606445312</v>
       </c>
       <c r="J48" t="n">
         <v>13.55000019073486</v>
@@ -1914,13 +1914,13 @@
         <v>78.84999847412109</v>
       </c>
       <c r="G51" t="n">
-        <v>1070.448974609375</v>
+        <v>1070.448852539062</v>
       </c>
       <c r="H51" t="n">
         <v>115.5500030517578</v>
       </c>
       <c r="I51" t="n">
-        <v>747.3256225585938</v>
+        <v>747.3255615234375</v>
       </c>
       <c r="J51" t="n">
         <v>13.44999980926514</v>
@@ -1949,7 +1949,7 @@
         <v>118.9499969482422</v>
       </c>
       <c r="I52" t="n">
-        <v>750.5185546875</v>
+        <v>750.5184936523438</v>
       </c>
       <c r="J52" t="n">
         <v>14.10000038146973</v>
@@ -1972,13 +1972,13 @@
         <v>78.75</v>
       </c>
       <c r="G53" t="n">
-        <v>1124.006591796875</v>
+        <v>1124.006469726562</v>
       </c>
       <c r="H53" t="n">
         <v>116.8000030517578</v>
       </c>
       <c r="I53" t="n">
-        <v>758.770751953125</v>
+        <v>758.7708129882812</v>
       </c>
       <c r="J53" t="n">
         <v>13.75</v>
@@ -2030,7 +2030,7 @@
         <v>83.09999847412109</v>
       </c>
       <c r="G55" t="n">
-        <v>1146.4033203125</v>
+        <v>1146.403198242188</v>
       </c>
       <c r="H55" t="n">
         <v>113.1500015258789</v>
@@ -2059,13 +2059,13 @@
         <v>81.65000152587891</v>
       </c>
       <c r="G56" t="n">
-        <v>1150.049194335938</v>
+        <v>1150.04931640625</v>
       </c>
       <c r="H56" t="n">
         <v>111.8000030517578</v>
       </c>
       <c r="I56" t="n">
-        <v>756.5111083984375</v>
+        <v>756.51123046875</v>
       </c>
       <c r="J56" t="n">
         <v>12.85000038146973</v>
@@ -2094,7 +2094,7 @@
         <v>109.6999969482422</v>
       </c>
       <c r="I57" t="n">
-        <v>756.3638305664062</v>
+        <v>756.3638916015625</v>
       </c>
       <c r="J57" t="n">
         <v>13</v>
@@ -2152,7 +2152,7 @@
         <v>100.6999969482422</v>
       </c>
       <c r="I59" t="n">
-        <v>731.4595336914062</v>
+        <v>731.4595947265625</v>
       </c>
       <c r="J59" t="n">
         <v>12.35000038146973</v>
@@ -2175,13 +2175,13 @@
         <v>84.30000305175781</v>
       </c>
       <c r="G60" t="n">
-        <v>1187.799926757812</v>
+        <v>1187.7998046875</v>
       </c>
       <c r="H60" t="n">
         <v>110.75</v>
       </c>
       <c r="I60" t="n">
-        <v>735.4382934570312</v>
+        <v>735.4383544921875</v>
       </c>
       <c r="J60" t="n">
         <v>12.94999980926514</v>
@@ -2233,7 +2233,7 @@
         <v>85.15000152587891</v>
       </c>
       <c r="G62" t="n">
-        <v>1193.325439453125</v>
+        <v>1193.325317382812</v>
       </c>
       <c r="H62" t="n">
         <v>112.3000030517578</v>
@@ -2262,7 +2262,7 @@
         <v>87.84999847412109</v>
       </c>
       <c r="G63" t="n">
-        <v>1202.882080078125</v>
+        <v>1202.882202148438</v>
       </c>
       <c r="H63" t="n">
         <v>122.6500015258789</v>
@@ -2297,7 +2297,7 @@
         <v>124.6999969482422</v>
       </c>
       <c r="I64" t="n">
-        <v>794.3342895507812</v>
+        <v>794.3343505859375</v>
       </c>
       <c r="J64" t="n">
         <v>14.85000038146973</v>
@@ -2349,13 +2349,13 @@
         <v>94.5</v>
       </c>
       <c r="G66" t="n">
-        <v>1186.214599609375</v>
+        <v>1186.214721679688</v>
       </c>
       <c r="H66" t="n">
         <v>136.1499938964844</v>
       </c>
       <c r="I66" t="n">
-        <v>822.13671875</v>
+        <v>822.1367797851562</v>
       </c>
       <c r="J66" t="n">
         <v>16.29999923706055</v>
@@ -2378,13 +2378,13 @@
         <v>96.30000305175781</v>
       </c>
       <c r="G67" t="n">
-        <v>1165.289794921875</v>
+        <v>1165.289916992188</v>
       </c>
       <c r="H67" t="n">
         <v>125.1500015258789</v>
       </c>
       <c r="I67" t="n">
-        <v>798.95166015625</v>
+        <v>798.9517211914062</v>
       </c>
       <c r="J67" t="n">
         <v>15.5</v>
@@ -2436,13 +2436,13 @@
         <v>98.40000152587891</v>
       </c>
       <c r="G69" t="n">
-        <v>1182.206420898438</v>
+        <v>1182.20654296875</v>
       </c>
       <c r="H69" t="n">
         <v>125.8499984741211</v>
       </c>
       <c r="I69" t="n">
-        <v>816.3895874023438</v>
+        <v>816.3896484375</v>
       </c>
       <c r="J69" t="n">
         <v>15.69999980926514</v>
@@ -2465,13 +2465,13 @@
         <v>94.84999847412109</v>
       </c>
       <c r="G70" t="n">
-        <v>1159.945556640625</v>
+        <v>1159.945434570312</v>
       </c>
       <c r="H70" t="n">
         <v>122.9499969482422</v>
       </c>
       <c r="I70" t="n">
-        <v>794.8745727539062</v>
+        <v>794.8746337890625</v>
       </c>
       <c r="J70" t="n">
         <v>15.14999961853027</v>
@@ -2500,7 +2500,7 @@
         <v>123.4000015258789</v>
       </c>
       <c r="I71" t="n">
-        <v>944.153076171875</v>
+        <v>944.1531372070312</v>
       </c>
       <c r="J71" t="n">
         <v>14.85000038146973</v>
@@ -2523,7 +2523,7 @@
         <v>103</v>
       </c>
       <c r="G72" t="n">
-        <v>1152.1552734375</v>
+        <v>1152.155151367188</v>
       </c>
       <c r="H72" t="n">
         <v>119.5500030517578</v>
@@ -2558,7 +2558,7 @@
         <v>123.5999984741211</v>
       </c>
       <c r="I73" t="n">
-        <v>979.81494140625</v>
+        <v>979.8148193359375</v>
       </c>
       <c r="J73" t="n">
         <v>14.39999961853027</v>
@@ -2587,7 +2587,7 @@
         <v>125.75</v>
       </c>
       <c r="I74" t="n">
-        <v>945.7249755859375</v>
+        <v>945.7249145507812</v>
       </c>
       <c r="J74" t="n">
         <v>14.75</v>
@@ -2639,7 +2639,7 @@
         <v>98.90000152587891</v>
       </c>
       <c r="G76" t="n">
-        <v>1249.509765625</v>
+        <v>1249.509887695312</v>
       </c>
       <c r="H76" t="n">
         <v>128.8999938964844</v>
@@ -2668,13 +2668,13 @@
         <v>105.6999969482422</v>
       </c>
       <c r="G77" t="n">
-        <v>1220.61376953125</v>
+        <v>1220.613891601562</v>
       </c>
       <c r="H77" t="n">
         <v>123.25</v>
       </c>
       <c r="I77" t="n">
-        <v>902.3511962890625</v>
+        <v>902.3511352539062</v>
       </c>
       <c r="J77" t="n">
         <v>14.55000019073486</v>
@@ -2703,7 +2703,7 @@
         <v>121.1999969482422</v>
       </c>
       <c r="I78" t="n">
-        <v>926.4695434570312</v>
+        <v>926.4696044921875</v>
       </c>
       <c r="J78" t="n">
         <v>14.5</v>
@@ -2732,7 +2732,7 @@
         <v>123</v>
       </c>
       <c r="I79" t="n">
-        <v>1111.753784179688</v>
+        <v>1111.753662109375</v>
       </c>
       <c r="J79" t="n">
         <v>14.39999961853027</v>
@@ -2755,13 +2755,13 @@
         <v>91.34999847412109</v>
       </c>
       <c r="G80" t="n">
-        <v>1277.160766601562</v>
+        <v>1277.16064453125</v>
       </c>
       <c r="H80" t="n">
         <v>120.5999984741211</v>
       </c>
       <c r="I80" t="n">
-        <v>1080.660034179688</v>
+        <v>1080.66015625</v>
       </c>
       <c r="J80" t="n">
         <v>13.94999980926514</v>
@@ -2790,7 +2790,7 @@
         <v>123.5500030517578</v>
       </c>
       <c r="I81" t="n">
-        <v>1086.947631835938</v>
+        <v>1086.947509765625</v>
       </c>
       <c r="J81" t="n">
         <v>14.25</v>
@@ -2819,7 +2819,7 @@
         <v>124.25</v>
       </c>
       <c r="I82" t="n">
-        <v>1096.476928710938</v>
+        <v>1096.47705078125</v>
       </c>
       <c r="J82" t="n">
         <v>14.19999980926514</v>
@@ -2848,7 +2848,7 @@
         <v>116.0999984741211</v>
       </c>
       <c r="I83" t="n">
-        <v>1001.133361816406</v>
+        <v>1001.13330078125</v>
       </c>
       <c r="J83" t="n">
         <v>13.55000019073486</v>
@@ -2906,7 +2906,7 @@
         <v>111.3000030517578</v>
       </c>
       <c r="I85" t="n">
-        <v>1049.321044921875</v>
+        <v>1049.32080078125</v>
       </c>
       <c r="J85" t="n">
         <v>13.10000038146973</v>
@@ -2929,7 +2929,7 @@
         <v>74.19999694824219</v>
       </c>
       <c r="G86" t="n">
-        <v>1140.583129882812</v>
+        <v>1140.583251953125</v>
       </c>
       <c r="H86" t="n">
         <v>112.3000030517578</v>
@@ -2987,13 +2987,13 @@
         <v>68.44999694824219</v>
       </c>
       <c r="G88" t="n">
-        <v>1109.331787109375</v>
+        <v>1109.331909179688</v>
       </c>
       <c r="H88" t="n">
         <v>101</v>
       </c>
       <c r="I88" t="n">
-        <v>964.9312133789062</v>
+        <v>964.9312744140625</v>
       </c>
       <c r="J88" t="n">
         <v>13</v>
@@ -3016,13 +3016,13 @@
         <v>72.75</v>
       </c>
       <c r="G89" t="n">
-        <v>1086.731201171875</v>
+        <v>1086.731323242188</v>
       </c>
       <c r="H89" t="n">
         <v>100.9000015258789</v>
       </c>
       <c r="I89" t="n">
-        <v>943.907470703125</v>
+        <v>943.9075317382812</v>
       </c>
       <c r="J89" t="n">
         <v>12.39999961853027</v>
@@ -3080,7 +3080,7 @@
         <v>98.30000305175781</v>
       </c>
       <c r="I91" t="n">
-        <v>964.9312133789062</v>
+        <v>964.9312744140625</v>
       </c>
       <c r="J91" t="n">
         <v>11.89999961853027</v>
@@ -3109,7 +3109,7 @@
         <v>107.0500030517578</v>
       </c>
       <c r="I92" t="n">
-        <v>1028.100708007812</v>
+        <v>1028.100830078125</v>
       </c>
       <c r="J92" t="n">
         <v>12.44999980926514</v>
@@ -3132,13 +3132,13 @@
         <v>78.30000305175781</v>
       </c>
       <c r="G93" t="n">
-        <v>1149.664184570312</v>
+        <v>1149.6640625</v>
       </c>
       <c r="H93" t="n">
         <v>104.0999984741211</v>
       </c>
       <c r="I93" t="n">
-        <v>1021.714904785156</v>
+        <v>1021.714965820312</v>
       </c>
       <c r="J93" t="n">
         <v>12.44999980926514</v>
@@ -3167,7 +3167,7 @@
         <v>102.0999984741211</v>
       </c>
       <c r="I94" t="n">
-        <v>977.5061645507812</v>
+        <v>977.5062255859375</v>
       </c>
       <c r="J94" t="n">
         <v>12.30000019073486</v>
@@ -3196,7 +3196,7 @@
         <v>104</v>
       </c>
       <c r="I95" t="n">
-        <v>1021.665771484375</v>
+        <v>1021.665832519531</v>
       </c>
       <c r="J95" t="n">
         <v>12.85000038146973</v>
@@ -3248,13 +3248,13 @@
         <v>78.94999694824219</v>
       </c>
       <c r="G97" t="n">
-        <v>1184.765502929688</v>
+        <v>1184.765258789062</v>
       </c>
       <c r="H97" t="n">
         <v>100.9000015258789</v>
       </c>
       <c r="I97" t="n">
-        <v>945.7249755859375</v>
+        <v>945.7249145507812</v>
       </c>
       <c r="J97" t="n">
         <v>12.55000019073486</v>
@@ -3283,7 +3283,7 @@
         <v>100.6500015258789</v>
       </c>
       <c r="I98" t="n">
-        <v>869.98046875</v>
+        <v>869.9805297851562</v>
       </c>
       <c r="J98" t="n">
         <v>12.10000038146973</v>
@@ -3312,7 +3312,7 @@
         <v>100.3499984741211</v>
       </c>
       <c r="I99" t="n">
-        <v>832.8451538085938</v>
+        <v>832.8450927734375</v>
       </c>
       <c r="J99" t="n">
         <v>11.89999961853027</v>
@@ -3335,13 +3335,13 @@
         <v>71.65000152587891</v>
       </c>
       <c r="G100" t="n">
-        <v>1166.308959960938</v>
+        <v>1166.308837890625</v>
       </c>
       <c r="H100" t="n">
         <v>99.84999847412109</v>
       </c>
       <c r="I100" t="n">
-        <v>871.9944458007812</v>
+        <v>871.9945068359375</v>
       </c>
       <c r="J100" t="n">
         <v>11.85000038146973</v>
@@ -3370,7 +3370,7 @@
         <v>102.5500030517578</v>
       </c>
       <c r="I101" t="n">
-        <v>914.9261474609375</v>
+        <v>914.9260864257812</v>
       </c>
       <c r="J101" t="n">
         <v>12</v>
@@ -3399,7 +3399,7 @@
         <v>107.9499969482422</v>
       </c>
       <c r="I102" t="n">
-        <v>909.1299438476562</v>
+        <v>909.1300048828125</v>
       </c>
       <c r="J102" t="n">
         <v>12.60000038146973</v>
@@ -3428,7 +3428,7 @@
         <v>108.0500030517578</v>
       </c>
       <c r="I103" t="n">
-        <v>929.4660034179688</v>
+        <v>929.4659423828125</v>
       </c>
       <c r="J103" t="n">
         <v>13.19999980926514</v>
@@ -3509,13 +3509,13 @@
         <v>74.65000152587891</v>
       </c>
       <c r="G106" t="n">
-        <v>1253.473022460938</v>
+        <v>1253.472900390625</v>
       </c>
       <c r="H106" t="n">
         <v>105.1500015258789</v>
       </c>
       <c r="I106" t="n">
-        <v>990.7197875976562</v>
+        <v>990.7197265625</v>
       </c>
       <c r="J106" t="n">
         <v>13.80000019073486</v>
@@ -3538,7 +3538,7 @@
         <v>75.90000152587891</v>
       </c>
       <c r="G107" t="n">
-        <v>1255.828125</v>
+        <v>1255.828247070312</v>
       </c>
       <c r="H107" t="n">
         <v>105.5</v>
@@ -3573,7 +3573,7 @@
         <v>104.8499984741211</v>
       </c>
       <c r="I108" t="n">
-        <v>969.3521118164062</v>
+        <v>969.3522338867188</v>
       </c>
       <c r="J108" t="n">
         <v>13.85000038146973</v>
@@ -3596,7 +3596,7 @@
         <v>80.94999694824219</v>
       </c>
       <c r="G109" t="n">
-        <v>1267.603881835938</v>
+        <v>1267.60400390625</v>
       </c>
       <c r="H109" t="n">
         <v>104.4499969482422</v>
@@ -3625,13 +3625,13 @@
         <v>78.59999847412109</v>
       </c>
       <c r="G110" t="n">
-        <v>1229.332641601562</v>
+        <v>1229.332397460938</v>
       </c>
       <c r="H110" t="n">
         <v>103.5999984741211</v>
       </c>
       <c r="I110" t="n">
-        <v>944.0548095703125</v>
+        <v>944.0548706054688</v>
       </c>
       <c r="J110" t="n">
         <v>13.55000019073486</v>
@@ -3654,13 +3654,13 @@
         <v>73.55000305175781</v>
       </c>
       <c r="G111" t="n">
-        <v>1206.0751953125</v>
+        <v>1206.075073242188</v>
       </c>
       <c r="H111" t="n">
         <v>96.94999694824219</v>
       </c>
       <c r="I111" t="n">
-        <v>874.548828125</v>
+        <v>874.5487670898438</v>
       </c>
       <c r="J111" t="n">
         <v>12.89999961853027</v>
@@ -3683,13 +3683,13 @@
         <v>72.84999847412109</v>
       </c>
       <c r="G112" t="n">
-        <v>1190.3134765625</v>
+        <v>1190.313598632812</v>
       </c>
       <c r="H112" t="n">
         <v>95.75</v>
       </c>
       <c r="I112" t="n">
-        <v>879.70654296875</v>
+        <v>879.7064819335938</v>
       </c>
       <c r="J112" t="n">
         <v>12.85000038146973</v>
@@ -3712,7 +3712,7 @@
         <v>74.59999847412109</v>
       </c>
       <c r="G113" t="n">
-        <v>1175.910766601562</v>
+        <v>1175.910888671875</v>
       </c>
       <c r="H113" t="n">
         <v>95.5</v>
@@ -3770,13 +3770,13 @@
         <v>62.75</v>
       </c>
       <c r="G115" t="n">
-        <v>1173.057495117188</v>
+        <v>1173.057373046875</v>
       </c>
       <c r="H115" t="n">
         <v>95.59999847412109</v>
       </c>
       <c r="I115" t="n">
-        <v>833.4837646484375</v>
+        <v>833.4837036132812</v>
       </c>
       <c r="J115" t="n">
         <v>12.14999961853027</v>
@@ -3886,13 +3886,13 @@
         <v>61.40000152587891</v>
       </c>
       <c r="G119" t="n">
-        <v>1116.420043945312</v>
+        <v>1116.419921875</v>
       </c>
       <c r="H119" t="n">
         <v>90.30000305175781</v>
       </c>
       <c r="I119" t="n">
-        <v>755.8726196289062</v>
+        <v>755.8726806640625</v>
       </c>
       <c r="J119" t="n">
         <v>11.60000038146973</v>
@@ -3944,13 +3944,13 @@
         <v>62.84999847412109</v>
       </c>
       <c r="G121" t="n">
-        <v>1128.965698242188</v>
+        <v>1128.9658203125</v>
       </c>
       <c r="H121" t="n">
         <v>93.09999847412109</v>
       </c>
       <c r="I121" t="n">
-        <v>801.5059814453125</v>
+        <v>801.5059204101562</v>
       </c>
       <c r="J121" t="n">
         <v>11.80000019073486</v>
@@ -3973,13 +3973,13 @@
         <v>67.80000305175781</v>
       </c>
       <c r="G122" t="n">
-        <v>1144.840576171875</v>
+        <v>1144.840454101562</v>
       </c>
       <c r="H122" t="n">
         <v>92.19999694824219</v>
       </c>
       <c r="I122" t="n">
-        <v>827.1961669921875</v>
+        <v>827.1962280273438</v>
       </c>
       <c r="J122" t="n">
         <v>11.80000019073486</v>
@@ -4008,7 +4008,7 @@
         <v>92.09999847412109</v>
       </c>
       <c r="I123" t="n">
-        <v>938.111328125</v>
+        <v>938.1112670898438</v>
       </c>
       <c r="J123" t="n">
         <v>11.75</v>
@@ -4031,7 +4031,7 @@
         <v>69</v>
       </c>
       <c r="G124" t="n">
-        <v>1175.616455078125</v>
+        <v>1175.616577148438</v>
       </c>
       <c r="H124" t="n">
         <v>90.59999847412109</v>
@@ -4095,7 +4095,7 @@
         <v>94.5</v>
       </c>
       <c r="I126" t="n">
-        <v>935.704345703125</v>
+        <v>935.7042846679688</v>
       </c>
       <c r="J126" t="n">
         <v>11.35000038146973</v>
@@ -4118,13 +4118,13 @@
         <v>65.40000152587891</v>
       </c>
       <c r="G127" t="n">
-        <v>1102.0625</v>
+        <v>1102.062622070312</v>
       </c>
       <c r="H127" t="n">
         <v>93.15000152587891</v>
       </c>
       <c r="I127" t="n">
-        <v>927.0098876953125</v>
+        <v>927.0098266601562</v>
       </c>
       <c r="J127" t="n">
         <v>11.35000038146973</v>
@@ -4147,7 +4147,7 @@
         <v>65.30000305175781</v>
       </c>
       <c r="G128" t="n">
-        <v>1092.3701171875</v>
+        <v>1092.369995117188</v>
       </c>
       <c r="H128" t="n">
         <v>91.75</v>
@@ -4211,7 +4211,7 @@
         <v>94.80000305175781</v>
       </c>
       <c r="I130" t="n">
-        <v>933.3464965820312</v>
+        <v>933.3465576171875</v>
       </c>
       <c r="J130" t="n">
         <v>11.39999961853027</v>
@@ -4234,7 +4234,7 @@
         <v>68.30000305175781</v>
       </c>
       <c r="G131" t="n">
-        <v>1097.827758789062</v>
+        <v>1097.827880859375</v>
       </c>
       <c r="H131" t="n">
         <v>101.3499984741211</v>
@@ -4292,7 +4292,7 @@
         <v>70.59999847412109</v>
       </c>
       <c r="G133" t="n">
-        <v>1076.8349609375</v>
+        <v>1076.834838867188</v>
       </c>
       <c r="H133" t="n">
         <v>101.6500015258789</v>
@@ -4321,13 +4321,13 @@
         <v>69.75</v>
       </c>
       <c r="G134" t="n">
-        <v>1085.712280273438</v>
+        <v>1085.712158203125</v>
       </c>
       <c r="H134" t="n">
         <v>100.4000015258789</v>
       </c>
       <c r="I134" t="n">
-        <v>937.9639282226562</v>
+        <v>937.9638671875</v>
       </c>
       <c r="J134" t="n">
         <v>11.39999961853027</v>
@@ -4379,7 +4379,7 @@
         <v>68.15000152587891</v>
       </c>
       <c r="G136" t="n">
-        <v>1097.080444335938</v>
+        <v>1097.080322265625</v>
       </c>
       <c r="H136" t="n">
         <v>102.25</v>
@@ -4408,13 +4408,13 @@
         <v>67.09999847412109</v>
       </c>
       <c r="G137" t="n">
-        <v>1103.806518554688</v>
+        <v>1103.806396484375</v>
       </c>
       <c r="H137" t="n">
         <v>102.3000030517578</v>
       </c>
       <c r="I137" t="n">
-        <v>978.8323974609375</v>
+        <v>978.8324584960938</v>
       </c>
       <c r="J137" t="n">
         <v>11.80000019073486</v>
@@ -4437,7 +4437,7 @@
         <v>67</v>
       </c>
       <c r="G138" t="n">
-        <v>1133.653564453125</v>
+        <v>1133.653442382812</v>
       </c>
       <c r="H138" t="n">
         <v>104.4000015258789</v>
@@ -4466,13 +4466,13 @@
         <v>65</v>
       </c>
       <c r="G139" t="n">
-        <v>1126.089965820312</v>
+        <v>1126.08984375</v>
       </c>
       <c r="H139" t="n">
         <v>105.8000030517578</v>
       </c>
       <c r="I139" t="n">
-        <v>961.9348754882812</v>
+        <v>961.934814453125</v>
       </c>
       <c r="J139" t="n">
         <v>11.85000038146973</v>
@@ -4495,13 +4495,13 @@
         <v>63.75</v>
       </c>
       <c r="G140" t="n">
-        <v>1133.698974609375</v>
+        <v>1133.698852539062</v>
       </c>
       <c r="H140" t="n">
         <v>104.5</v>
       </c>
       <c r="I140" t="n">
-        <v>971.4152221679688</v>
+        <v>971.4151611328125</v>
       </c>
       <c r="J140" t="n">
         <v>11.75</v>
@@ -4524,13 +4524,13 @@
         <v>62.95000076293945</v>
       </c>
       <c r="G141" t="n">
-        <v>1096.242431640625</v>
+        <v>1096.242553710938</v>
       </c>
       <c r="H141" t="n">
         <v>104.25</v>
       </c>
       <c r="I141" t="n">
-        <v>962.1312866210938</v>
+        <v>962.13134765625</v>
       </c>
       <c r="J141" t="n">
         <v>11.55000019073486</v>
@@ -4559,7 +4559,7 @@
         <v>113.9000015258789</v>
       </c>
       <c r="I142" t="n">
-        <v>945.135498046875</v>
+        <v>945.1355590820312</v>
       </c>
       <c r="J142" t="n">
         <v>11.89999961853027</v>
@@ -4588,7 +4588,7 @@
         <v>115.8499984741211</v>
       </c>
       <c r="I143" t="n">
-        <v>945.8232421875</v>
+        <v>945.8231811523438</v>
       </c>
       <c r="J143" t="n">
         <v>11.89999961853027</v>
@@ -4611,7 +4611,7 @@
         <v>65.15000152587891</v>
       </c>
       <c r="G144" t="n">
-        <v>1112.864624023438</v>
+        <v>1112.864501953125</v>
       </c>
       <c r="H144" t="n">
         <v>114.25</v>
@@ -4640,13 +4640,13 @@
         <v>64.90000152587891</v>
       </c>
       <c r="G145" t="n">
-        <v>1136.57470703125</v>
+        <v>1136.574829101562</v>
       </c>
       <c r="H145" t="n">
         <v>117.0999984741211</v>
       </c>
       <c r="I145" t="n">
-        <v>964.6856689453125</v>
+        <v>964.6856079101562</v>
       </c>
       <c r="J145" t="n">
         <v>12.39999961853027</v>
@@ -4669,13 +4669,13 @@
         <v>66.94999694824219</v>
       </c>
       <c r="G146" t="n">
-        <v>1166.195678710938</v>
+        <v>1166.19580078125</v>
       </c>
       <c r="H146" t="n">
         <v>123.25</v>
       </c>
       <c r="I146" t="n">
-        <v>1014.592407226562</v>
+        <v>1014.592468261719</v>
       </c>
       <c r="J146" t="n">
         <v>13</v>
@@ -4785,13 +4785,13 @@
         <v>68.09999847412109</v>
       </c>
       <c r="G150" t="n">
-        <v>1147.694091796875</v>
+        <v>1147.693969726562</v>
       </c>
       <c r="H150" t="n">
         <v>120</v>
       </c>
       <c r="I150" t="n">
-        <v>942.0408935546875</v>
+        <v>942.041015625</v>
       </c>
       <c r="J150" t="n">
         <v>13.14999961853027</v>
@@ -4820,7 +4820,7 @@
         <v>115.8499984741211</v>
       </c>
       <c r="I151" t="n">
-        <v>944.7916259765625</v>
+        <v>944.791748046875</v>
       </c>
       <c r="J151" t="n">
         <v>13.30000019073486</v>
@@ -4843,7 +4843,7 @@
         <v>66.65000152587891</v>
       </c>
       <c r="G152" t="n">
-        <v>1169.660522460938</v>
+        <v>1169.66064453125</v>
       </c>
       <c r="H152" t="n">
         <v>117.5500030517578</v>
@@ -4878,7 +4878,7 @@
         <v>115.3499984741211</v>
       </c>
       <c r="I153" t="n">
-        <v>953.879150390625</v>
+        <v>953.8790283203125</v>
       </c>
       <c r="J153" t="n">
         <v>13.60000038146973</v>
@@ -4901,7 +4901,7 @@
         <v>68.34999847412109</v>
       </c>
       <c r="G154" t="n">
-        <v>1192.532836914062</v>
+        <v>1192.53271484375</v>
       </c>
       <c r="H154" t="n">
         <v>115.1500015258789</v>
@@ -4930,7 +4930,7 @@
         <v>71.90000152587891</v>
       </c>
       <c r="G155" t="n">
-        <v>1200.821166992188</v>
+        <v>1200.8212890625</v>
       </c>
       <c r="H155" t="n">
         <v>116.5500030517578</v>
@@ -4959,13 +4959,13 @@
         <v>72.55000305175781</v>
       </c>
       <c r="G156" t="n">
-        <v>1207.094116210938</v>
+        <v>1207.094360351562</v>
       </c>
       <c r="H156" t="n">
         <v>121.8000030517578</v>
       </c>
       <c r="I156" t="n">
-        <v>975.4922485351562</v>
+        <v>975.4921875</v>
       </c>
       <c r="J156" t="n">
         <v>13.64999961853027</v>
@@ -4994,7 +4994,7 @@
         <v>129.8999938964844</v>
       </c>
       <c r="I157" t="n">
-        <v>1020.880126953125</v>
+        <v>1020.879943847656</v>
       </c>
       <c r="J157" t="n">
         <v>14.19999980926514</v>
@@ -5023,7 +5023,7 @@
         <v>135.6000061035156</v>
       </c>
       <c r="I158" t="n">
-        <v>1000.396545410156</v>
+        <v>1000.396484375</v>
       </c>
       <c r="J158" t="n">
         <v>14.94999980926514</v>
@@ -5052,7 +5052,7 @@
         <v>140.6999969482422</v>
       </c>
       <c r="I159" t="n">
-        <v>973.0361938476562</v>
+        <v>973.0361328125</v>
       </c>
       <c r="J159" t="n">
         <v>15.64999961853027</v>
@@ -5075,7 +5075,7 @@
         <v>72.25</v>
       </c>
       <c r="G160" t="n">
-        <v>1202.694458007812</v>
+        <v>1202.694580078125</v>
       </c>
       <c r="H160" t="n">
         <v>138.6999969482422</v>
@@ -5133,13 +5133,13 @@
         <v>74.05000305175781</v>
       </c>
       <c r="G162" t="n">
-        <v>1195.992065429688</v>
+        <v>1195.9921875</v>
       </c>
       <c r="H162" t="n">
         <v>139.75</v>
       </c>
       <c r="I162" t="n">
-        <v>1002.8525390625</v>
+        <v>1002.852600097656</v>
       </c>
       <c r="J162" t="n">
         <v>15.05000019073486</v>
@@ -5168,7 +5168,7 @@
         <v>157.3500061035156</v>
       </c>
       <c r="I163" t="n">
-        <v>997.10546875</v>
+        <v>997.1054077148438</v>
       </c>
       <c r="J163" t="n">
         <v>16.25</v>
@@ -5226,7 +5226,7 @@
         <v>162</v>
       </c>
       <c r="I165" t="n">
-        <v>1006.291137695312</v>
+        <v>1006.291076660156</v>
       </c>
       <c r="J165" t="n">
         <v>16.79999923706055</v>
@@ -5255,7 +5255,7 @@
         <v>193.8500061035156</v>
       </c>
       <c r="I166" t="n">
-        <v>1039.644287109375</v>
+        <v>1039.644165039062</v>
       </c>
       <c r="J166" t="n">
         <v>20.14999961853027</v>
@@ -5278,13 +5278,13 @@
         <v>71.69999694824219</v>
       </c>
       <c r="G167" t="n">
-        <v>1149.84814453125</v>
+        <v>1149.848266601562</v>
       </c>
       <c r="H167" t="n">
         <v>179.1499938964844</v>
       </c>
       <c r="I167" t="n">
-        <v>1082.08447265625</v>
+        <v>1082.084594726562</v>
       </c>
       <c r="J167" t="n">
         <v>21.20000076293945</v>
@@ -5313,7 +5313,7 @@
         <v>182.6999969482422</v>
       </c>
       <c r="I168" t="n">
-        <v>1193.93310546875</v>
+        <v>1193.932983398438</v>
       </c>
       <c r="J168" t="n">
         <v>23.29999923706055</v>
@@ -5365,7 +5365,7 @@
         <v>75.09999847412109</v>
       </c>
       <c r="G170" t="n">
-        <v>1173.135986328125</v>
+        <v>1173.136108398438</v>
       </c>
       <c r="H170" t="n">
         <v>180.6999969482422</v>
@@ -5394,13 +5394,13 @@
         <v>73.65000152587891</v>
       </c>
       <c r="G171" t="n">
-        <v>1174.794555664062</v>
+        <v>1174.794677734375</v>
       </c>
       <c r="H171" t="n">
         <v>180.3000030517578</v>
       </c>
       <c r="I171" t="n">
-        <v>1188.775268554688</v>
+        <v>1188.775390625</v>
       </c>
       <c r="J171" t="n">
         <v>21.29999923706055</v>
@@ -5423,13 +5423,13 @@
         <v>74.05000305175781</v>
       </c>
       <c r="G172" t="n">
-        <v>1167.478759765625</v>
+        <v>1167.478881835938</v>
       </c>
       <c r="H172" t="n">
         <v>162.4499969482422</v>
       </c>
       <c r="I172" t="n">
-        <v>1153.801147460938</v>
+        <v>1153.80126953125</v>
       </c>
       <c r="J172" t="n">
         <v>19.20000076293945</v>
@@ -5481,13 +5481,13 @@
         <v>74.15000152587891</v>
       </c>
       <c r="G174" t="n">
-        <v>1190.402954101562</v>
+        <v>1190.403076171875</v>
       </c>
       <c r="H174" t="n">
         <v>165.5</v>
       </c>
       <c r="I174" t="n">
-        <v>1137.44384765625</v>
+        <v>1137.443969726562</v>
       </c>
       <c r="J174" t="n">
         <v>20.04999923706055</v>
@@ -5545,7 +5545,7 @@
         <v>154.4499969482422</v>
       </c>
       <c r="I176" t="n">
-        <v>1170.55126953125</v>
+        <v>1170.551391601562</v>
       </c>
       <c r="J176" t="n">
         <v>18.10000038146973</v>
@@ -5568,13 +5568,13 @@
         <v>68.65000152587891</v>
       </c>
       <c r="G177" t="n">
-        <v>1135.625732421875</v>
+        <v>1135.625610351562</v>
       </c>
       <c r="H177" t="n">
         <v>156.3500061035156</v>
       </c>
       <c r="I177" t="n">
-        <v>1119.121826171875</v>
+        <v>1119.121948242188</v>
       </c>
       <c r="J177" t="n">
         <v>18.45000076293945</v>
@@ -5597,13 +5597,13 @@
         <v>67.05000305175781</v>
       </c>
       <c r="G178" t="n">
-        <v>1137.102416992188</v>
+        <v>1137.1025390625</v>
       </c>
       <c r="H178" t="n">
         <v>151.8000030517578</v>
       </c>
       <c r="I178" t="n">
-        <v>1159.351928710938</v>
+        <v>1159.351806640625</v>
       </c>
       <c r="J178" t="n">
         <v>17.64999961853027</v>
@@ -5655,7 +5655,7 @@
         <v>69.90000152587891</v>
       </c>
       <c r="G180" t="n">
-        <v>1140.419677734375</v>
+        <v>1140.419555664062</v>
       </c>
       <c r="H180" t="n">
         <v>146.75</v>
@@ -5690,7 +5690,7 @@
         <v>146.1499938964844</v>
       </c>
       <c r="I181" t="n">
-        <v>1187.077270507812</v>
+        <v>1187.077392578125</v>
       </c>
       <c r="J181" t="n">
         <v>17.29999923706055</v>
@@ -5748,7 +5748,7 @@
         <v>137.1999969482422</v>
       </c>
       <c r="I183" t="n">
-        <v>1051.699951171875</v>
+        <v>1051.69970703125</v>
       </c>
       <c r="J183" t="n">
         <v>16.35000038146973</v>
@@ -5800,13 +5800,13 @@
         <v>61.70000076293945</v>
       </c>
       <c r="G185" t="n">
-        <v>1059.855224609375</v>
+        <v>1059.855102539062</v>
       </c>
       <c r="H185" t="n">
         <v>136.3500061035156</v>
       </c>
       <c r="I185" t="n">
-        <v>1021.610412597656</v>
+        <v>1021.610595703125</v>
       </c>
       <c r="J185" t="n">
         <v>16.10000038146973</v>
@@ -5829,13 +5829,13 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G186" t="n">
-        <v>1056.606201171875</v>
+        <v>1056.606323242188</v>
       </c>
       <c r="H186" t="n">
         <v>137.6499938964844</v>
       </c>
       <c r="I186" t="n">
-        <v>1032.690673828125</v>
+        <v>1032.690795898438</v>
       </c>
       <c r="J186" t="n">
         <v>16.04999923706055</v>
@@ -5887,7 +5887,7 @@
         <v>63.95000076293945</v>
       </c>
       <c r="G188" t="n">
-        <v>1076.690673828125</v>
+        <v>1076.690551757812</v>
       </c>
       <c r="H188" t="n">
         <v>135.4499969482422</v>
@@ -5945,13 +5945,13 @@
         <v>67.30000305175781</v>
       </c>
       <c r="G190" t="n">
-        <v>1100.591674804688</v>
+        <v>1100.591796875</v>
       </c>
       <c r="H190" t="n">
         <v>144.3999938964844</v>
       </c>
       <c r="I190" t="n">
-        <v>1120.152099609375</v>
+        <v>1120.151977539062</v>
       </c>
       <c r="J190" t="n">
         <v>16.75</v>
@@ -5974,13 +5974,13 @@
         <v>68.19999694824219</v>
       </c>
       <c r="G191" t="n">
-        <v>1105.249267578125</v>
+        <v>1105.249389648438</v>
       </c>
       <c r="H191" t="n">
         <v>151.6000061035156</v>
       </c>
       <c r="I191" t="n">
-        <v>1158.268310546875</v>
+        <v>1158.268432617188</v>
       </c>
       <c r="J191" t="n">
         <v>17.54999923706055</v>
@@ -6003,13 +6003,13 @@
         <v>67.25</v>
       </c>
       <c r="G192" t="n">
-        <v>1093.185180664062</v>
+        <v>1093.185302734375</v>
       </c>
       <c r="H192" t="n">
         <v>157.6999969482422</v>
       </c>
       <c r="I192" t="n">
-        <v>1173.879516601562</v>
+        <v>1173.87939453125</v>
       </c>
       <c r="J192" t="n">
         <v>17.75</v>
@@ -6067,7 +6067,7 @@
         <v>142.6999969482422</v>
       </c>
       <c r="I194" t="n">
-        <v>1128.178955078125</v>
+        <v>1128.179077148438</v>
       </c>
       <c r="J194" t="n">
         <v>16.35000038146973</v>
@@ -6096,7 +6096,7 @@
         <v>142.3500061035156</v>
       </c>
       <c r="I195" t="n">
-        <v>1122.66357421875</v>
+        <v>1122.663452148438</v>
       </c>
       <c r="J195" t="n">
         <v>16.5</v>
@@ -6125,7 +6125,7 @@
         <v>138.8500061035156</v>
       </c>
       <c r="I196" t="n">
-        <v>1100.404174804688</v>
+        <v>1100.404296875</v>
       </c>
       <c r="J196" t="n">
         <v>16.20000076293945</v>
@@ -6154,7 +6154,7 @@
         <v>138.6999969482422</v>
       </c>
       <c r="I197" t="n">
-        <v>1122.56494140625</v>
+        <v>1122.564819335938</v>
       </c>
       <c r="J197" t="n">
         <v>16.20000076293945</v>
@@ -6206,7 +6206,7 @@
         <v>65.59999847412109</v>
       </c>
       <c r="G199" t="n">
-        <v>1133.217407226562</v>
+        <v>1133.217529296875</v>
       </c>
       <c r="H199" t="n">
         <v>141.3500061035156</v>
@@ -6241,7 +6241,7 @@
         <v>139.1000061035156</v>
       </c>
       <c r="I200" t="n">
-        <v>1117.49267578125</v>
+        <v>1117.492553710938</v>
       </c>
       <c r="J200" t="n">
         <v>16.10000038146973</v>
@@ -6264,13 +6264,13 @@
         <v>63.70000076293945</v>
       </c>
       <c r="G201" t="n">
-        <v>1123.084350585938</v>
+        <v>1123.084228515625</v>
       </c>
       <c r="H201" t="n">
         <v>139.1499938964844</v>
       </c>
       <c r="I201" t="n">
-        <v>1088.585327148438</v>
+        <v>1088.585083007812</v>
       </c>
       <c r="J201" t="n">
         <v>16.35000038146973</v>
@@ -6322,7 +6322,7 @@
         <v>65.05000305175781</v>
       </c>
       <c r="G203" t="n">
-        <v>1109.429809570312</v>
+        <v>1109.4296875</v>
       </c>
       <c r="H203" t="n">
         <v>141.6000061035156</v>
@@ -6357,7 +6357,7 @@
         <v>141.8500061035156</v>
       </c>
       <c r="I204" t="n">
-        <v>1086.56591796875</v>
+        <v>1086.566040039062</v>
       </c>
       <c r="J204" t="n">
         <v>16.14999961853027</v>
@@ -6380,7 +6380,7 @@
         <v>63.25</v>
       </c>
       <c r="G205" t="n">
-        <v>1147.871826171875</v>
+        <v>1147.871704101562</v>
       </c>
       <c r="H205" t="n">
         <v>141.8999938964844</v>
@@ -6409,7 +6409,7 @@
         <v>64.15000152587891</v>
       </c>
       <c r="G206" t="n">
-        <v>1158.527099609375</v>
+        <v>1158.527221679688</v>
       </c>
       <c r="H206" t="n">
         <v>141.4499969482422</v>
@@ -6438,7 +6438,7 @@
         <v>62.90000152587891</v>
       </c>
       <c r="G207" t="n">
-        <v>1149.552978515625</v>
+        <v>1149.552856445312</v>
       </c>
       <c r="H207" t="n">
         <v>140.6499938964844</v>
@@ -6467,13 +6467,13 @@
         <v>63.20000076293945</v>
       </c>
       <c r="G208" t="n">
-        <v>1156.732299804688</v>
+        <v>1156.732421875</v>
       </c>
       <c r="H208" t="n">
         <v>140.5500030517578</v>
       </c>
       <c r="I208" t="n">
-        <v>1097.301635742188</v>
+        <v>1097.301513671875</v>
       </c>
       <c r="J208" t="n">
         <v>16.10000038146973</v>
@@ -6531,7 +6531,7 @@
         <v>147.1499938964844</v>
       </c>
       <c r="I210" t="n">
-        <v>1074.057495117188</v>
+        <v>1074.0576171875</v>
       </c>
       <c r="J210" t="n">
         <v>16.79999923706055</v>
@@ -6560,7 +6560,7 @@
         <v>152.9499969482422</v>
       </c>
       <c r="I211" t="n">
-        <v>1081.936889648438</v>
+        <v>1081.93701171875</v>
       </c>
       <c r="J211" t="n">
         <v>16.85000038146973</v>
@@ -6583,13 +6583,13 @@
         <v>65.25</v>
       </c>
       <c r="G212" t="n">
-        <v>1183.246337890625</v>
+        <v>1183.246459960938</v>
       </c>
       <c r="H212" t="n">
         <v>146.6499938964844</v>
       </c>
       <c r="I212" t="n">
-        <v>1074.057495117188</v>
+        <v>1074.0576171875</v>
       </c>
       <c r="J212" t="n">
         <v>16.45000076293945</v>
@@ -6618,7 +6618,7 @@
         <v>142.8500061035156</v>
       </c>
       <c r="I213" t="n">
-        <v>1053.669799804688</v>
+        <v>1053.669555664062</v>
       </c>
       <c r="J213" t="n">
         <v>16.10000038146973</v>
@@ -6641,7 +6641,7 @@
         <v>63.95000076293945</v>
       </c>
       <c r="G214" t="n">
-        <v>1195.878662109375</v>
+        <v>1195.878540039062</v>
       </c>
       <c r="H214" t="n">
         <v>146.1999969482422</v>
@@ -6699,13 +6699,13 @@
         <v>63.04999923706055</v>
       </c>
       <c r="G216" t="n">
-        <v>1184.745849609375</v>
+        <v>1184.745971679688</v>
       </c>
       <c r="H216" t="n">
         <v>151.3500061035156</v>
       </c>
       <c r="I216" t="n">
-        <v>1058.939086914062</v>
+        <v>1058.93896484375</v>
       </c>
       <c r="J216" t="n">
         <v>16.10000038146973</v>
@@ -6815,13 +6815,13 @@
         <v>60.75</v>
       </c>
       <c r="G220" t="n">
-        <v>1159.118041992188</v>
+        <v>1159.117919921875</v>
       </c>
       <c r="H220" t="n">
         <v>145.25</v>
       </c>
       <c r="I220" t="n">
-        <v>978.7662963867188</v>
+        <v>978.766357421875</v>
       </c>
       <c r="J220" t="n">
         <v>15.5</v>
@@ -6908,7 +6908,7 @@
         <v>147.0500030517578</v>
       </c>
       <c r="I223" t="n">
-        <v>990.58544921875</v>
+        <v>990.5853881835938</v>
       </c>
       <c r="J223" t="n">
         <v>15.25</v>
@@ -6960,13 +6960,13 @@
         <v>63.75</v>
       </c>
       <c r="G225" t="n">
-        <v>1230.299194335938</v>
+        <v>1230.299072265625</v>
       </c>
       <c r="H225" t="n">
         <v>153.6499938964844</v>
       </c>
       <c r="I225" t="n">
-        <v>1027.519897460938</v>
+        <v>1027.52001953125</v>
       </c>
       <c r="J225" t="n">
         <v>16</v>
@@ -7024,7 +7024,7 @@
         <v>157.6999969482422</v>
       </c>
       <c r="I227" t="n">
-        <v>1039.289672851562</v>
+        <v>1039.289794921875</v>
       </c>
       <c r="J227" t="n">
         <v>16.04999923706055</v>
@@ -7047,13 +7047,13 @@
         <v>73.40000152587891</v>
       </c>
       <c r="G228" t="n">
-        <v>1237.455810546875</v>
+        <v>1237.455688476562</v>
       </c>
       <c r="H228" t="n">
         <v>156.1000061035156</v>
       </c>
       <c r="I228" t="n">
-        <v>1040.2255859375</v>
+        <v>1040.225463867188</v>
       </c>
       <c r="J228" t="n">
         <v>16</v>
@@ -7082,7 +7082,7 @@
         <v>162.8999938964844</v>
       </c>
       <c r="I229" t="n">
-        <v>1033.675903320312</v>
+        <v>1033.67578125</v>
       </c>
       <c r="J229" t="n">
         <v>16.79999923706055</v>
@@ -7140,7 +7140,7 @@
         <v>156.3999938964844</v>
       </c>
       <c r="I231" t="n">
-        <v>1050.419555664062</v>
+        <v>1050.41943359375</v>
       </c>
       <c r="J231" t="n">
         <v>15.85000038146973</v>
@@ -7198,7 +7198,7 @@
         <v>154.0500030517578</v>
       </c>
       <c r="I233" t="n">
-        <v>1031.311889648438</v>
+        <v>1031.31201171875</v>
       </c>
       <c r="J233" t="n">
         <v>15.85000038146973</v>
@@ -7221,7 +7221,7 @@
         <v>72.90000152587891</v>
       </c>
       <c r="G234" t="n">
-        <v>1185.56396484375</v>
+        <v>1185.563842773438</v>
       </c>
       <c r="H234" t="n">
         <v>154.75</v>
@@ -7285,7 +7285,7 @@
         <v>157.25</v>
       </c>
       <c r="I236" t="n">
-        <v>1016.488891601562</v>
+        <v>1016.488952636719</v>
       </c>
       <c r="J236" t="n">
         <v>15.75</v>
@@ -7314,7 +7314,7 @@
         <v>156.6499938964844</v>
       </c>
       <c r="I237" t="n">
-        <v>1012.943176269531</v>
+        <v>1012.942993164062</v>
       </c>
       <c r="J237" t="n">
         <v>16.45000076293945</v>
@@ -7366,13 +7366,13 @@
         <v>71.84999847412109</v>
       </c>
       <c r="G239" t="n">
-        <v>1165.797485351562</v>
+        <v>1165.797607421875</v>
       </c>
       <c r="H239" t="n">
         <v>151.1000061035156</v>
       </c>
       <c r="I239" t="n">
-        <v>982.7553100585938</v>
+        <v>982.7552490234375</v>
       </c>
       <c r="J239" t="n">
         <v>15.75</v>
@@ -7424,13 +7424,13 @@
         <v>71.34999847412109</v>
       </c>
       <c r="G241" t="n">
-        <v>1191.334594726562</v>
+        <v>1191.334716796875</v>
       </c>
       <c r="H241" t="n">
         <v>149.8000030517578</v>
       </c>
       <c r="I241" t="n">
-        <v>982.213623046875</v>
+        <v>982.2135620117188</v>
       </c>
       <c r="J241" t="n">
         <v>15.75</v>
@@ -7459,7 +7459,7 @@
         <v>142.5500030517578</v>
       </c>
       <c r="I242" t="n">
-        <v>939.5665283203125</v>
+        <v>939.5664672851562</v>
       </c>
       <c r="J242" t="n">
         <v>15</v>
@@ -7488,7 +7488,7 @@
         <v>135.4499969482422</v>
       </c>
       <c r="I243" t="n">
-        <v>898.8892211914062</v>
+        <v>898.88916015625</v>
       </c>
       <c r="J243" t="n">
         <v>14.25</v>
@@ -7511,13 +7511,13 @@
         <v>60.59999847412109</v>
       </c>
       <c r="G244" t="n">
-        <v>1136.98876953125</v>
+        <v>1136.988891601562</v>
       </c>
       <c r="H244" t="n">
         <v>128.6999969482422</v>
       </c>
       <c r="I244" t="n">
-        <v>796.0140991210938</v>
+        <v>796.0140380859375</v>
       </c>
       <c r="J244" t="n">
         <v>13.55000019073486</v>
@@ -7540,7 +7540,7 @@
         <v>62.90000152587891</v>
       </c>
       <c r="G245" t="n">
-        <v>1146.917236328125</v>
+        <v>1146.917358398438</v>
       </c>
       <c r="H245" t="n">
         <v>128.1999969482422</v>
@@ -7569,7 +7569,7 @@
         <v>65.80000305175781</v>
       </c>
       <c r="G246" t="n">
-        <v>1156.300659179688</v>
+        <v>1156.30078125</v>
       </c>
       <c r="H246" t="n">
         <v>134.6000061035156</v>
@@ -7598,7 +7598,7 @@
         <v>67.05000305175781</v>
       </c>
       <c r="G247" t="n">
-        <v>1156.187255859375</v>
+        <v>1156.187133789062</v>
       </c>
       <c r="H247" t="n">
         <v>136.5</v>
@@ -7656,13 +7656,13 @@
         <v>66.09999847412109</v>
       </c>
       <c r="G249" t="n">
-        <v>1157.436645507812</v>
+        <v>1157.4365234375</v>
       </c>
       <c r="H249" t="n">
         <v>137.6999969482422</v>
       </c>
       <c r="I249" t="n">
-        <v>930.1112060546875</v>
+        <v>930.1111450195312</v>
       </c>
       <c r="J249" t="n">
         <v>14.35000038146973</v>
@@ -7778,7 +7778,7 @@
         <v>133.75</v>
       </c>
       <c r="I253" t="n">
-        <v>905.3404541015625</v>
+        <v>905.3403930664062</v>
       </c>
       <c r="J253" t="n">
         <v>14.60000038146973</v>
@@ -7807,7 +7807,7 @@
         <v>130.1999969482422</v>
       </c>
       <c r="I254" t="n">
-        <v>892.9302978515625</v>
+        <v>892.9303588867188</v>
       </c>
       <c r="J254" t="n">
         <v>14.44999980926514</v>
@@ -7836,7 +7836,7 @@
         <v>135.0500030517578</v>
       </c>
       <c r="I255" t="n">
-        <v>922.3302612304688</v>
+        <v>922.330322265625</v>
       </c>
       <c r="J255" t="n">
         <v>14.55000019073486</v>
@@ -7888,13 +7888,13 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G257" t="n">
-        <v>1147.871826171875</v>
+        <v>1147.871704101562</v>
       </c>
       <c r="H257" t="n">
         <v>134.3000030517578</v>
       </c>
       <c r="I257" t="n">
-        <v>902.33642578125</v>
+        <v>902.3363647460938</v>
       </c>
       <c r="J257" t="n">
         <v>14.25</v>
@@ -7917,13 +7917,13 @@
         <v>63.59999847412109</v>
       </c>
       <c r="G258" t="n">
-        <v>1123.084350585938</v>
+        <v>1123.084228515625</v>
       </c>
       <c r="H258" t="n">
         <v>132.3000030517578</v>
       </c>
       <c r="I258" t="n">
-        <v>899.0369262695312</v>
+        <v>899.036865234375</v>
       </c>
       <c r="J258" t="n">
         <v>13.94999980926514</v>
@@ -7946,13 +7946,13 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G259" t="n">
-        <v>1121.266723632812</v>
+        <v>1121.266845703125</v>
       </c>
       <c r="H259" t="n">
         <v>132.6499938964844</v>
       </c>
       <c r="I259" t="n">
-        <v>899.3323974609375</v>
+        <v>899.3323364257812</v>
       </c>
       <c r="J259" t="n">
         <v>14.14999961853027</v>
@@ -8010,7 +8010,7 @@
         <v>141.3000030517578</v>
       </c>
       <c r="I261" t="n">
-        <v>883.5242919921875</v>
+        <v>883.5243530273438</v>
       </c>
       <c r="J261" t="n">
         <v>14.14999961853027</v>
@@ -8068,7 +8068,7 @@
         <v>137.5</v>
       </c>
       <c r="I263" t="n">
-        <v>901.8439331054688</v>
+        <v>901.843994140625</v>
       </c>
       <c r="J263" t="n">
         <v>14</v>
@@ -8097,7 +8097,7 @@
         <v>136.25</v>
       </c>
       <c r="I264" t="n">
-        <v>895.3927001953125</v>
+        <v>895.3926391601562</v>
       </c>
       <c r="J264" t="n">
         <v>13.85000038146973</v>
@@ -8126,7 +8126,7 @@
         <v>133.6999969482422</v>
       </c>
       <c r="I265" t="n">
-        <v>892.0438842773438</v>
+        <v>892.0440063476562</v>
       </c>
       <c r="J265" t="n">
         <v>13.19999980926514</v>
@@ -8184,7 +8184,7 @@
         <v>128.1499938964844</v>
       </c>
       <c r="I267" t="n">
-        <v>869.78466796875</v>
+        <v>869.7847290039062</v>
       </c>
       <c r="J267" t="n">
         <v>12.94999980926514</v>
@@ -8213,7 +8213,7 @@
         <v>121.9000015258789</v>
       </c>
       <c r="I268" t="n">
-        <v>835.460205078125</v>
+        <v>835.4601440429688</v>
       </c>
       <c r="J268" t="n">
         <v>12.64999961853027</v>
@@ -8265,7 +8265,7 @@
         <v>61.54999923706055</v>
       </c>
       <c r="G270" t="n">
-        <v>1069.5791015625</v>
+        <v>1069.579223632812</v>
       </c>
       <c r="H270" t="n">
         <v>125.0999984741211</v>
@@ -8323,13 +8323,13 @@
         <v>59.20000076293945</v>
       </c>
       <c r="G272" t="n">
-        <v>1057.35595703125</v>
+        <v>1057.356079101562</v>
       </c>
       <c r="H272" t="n">
         <v>121.3000030517578</v>
       </c>
       <c r="I272" t="n">
-        <v>828.81201171875</v>
+        <v>828.8119506835938</v>
       </c>
       <c r="J272" t="n">
         <v>11.94999980926514</v>
@@ -8358,7 +8358,7 @@
         <v>121.4000015258789</v>
       </c>
       <c r="I273" t="n">
-        <v>817.8792724609375</v>
+        <v>817.8793334960938</v>
       </c>
       <c r="J273" t="n">
         <v>11.75</v>
@@ -8387,7 +8387,7 @@
         <v>124.4499969482422</v>
       </c>
       <c r="I274" t="n">
-        <v>824.0843505859375</v>
+        <v>824.0844116210938</v>
       </c>
       <c r="J274" t="n">
         <v>12</v>
@@ -8410,7 +8410,7 @@
         <v>59.54999923706055</v>
       </c>
       <c r="G275" t="n">
-        <v>1047.791015625</v>
+        <v>1047.791137695312</v>
       </c>
       <c r="H275" t="n">
         <v>123.25</v>
@@ -8445,7 +8445,7 @@
         <v>123.5500030517578</v>
       </c>
       <c r="I276" t="n">
-        <v>842.8471069335938</v>
+        <v>842.8469848632812</v>
       </c>
       <c r="J276" t="n">
         <v>11.69999980926514</v>
@@ -8474,7 +8474,7 @@
         <v>127.3000030517578</v>
       </c>
       <c r="I277" t="n">
-        <v>831.4219970703125</v>
+        <v>831.4220581054688</v>
       </c>
       <c r="J277" t="n">
         <v>11.69999980926514</v>
@@ -8503,7 +8503,7 @@
         <v>130.9499969482422</v>
       </c>
       <c r="I278" t="n">
-        <v>833.8350830078125</v>
+        <v>833.8350219726562</v>
       </c>
       <c r="J278" t="n">
         <v>11.64999961853027</v>
@@ -8532,7 +8532,7 @@
         <v>127.5500030517578</v>
       </c>
       <c r="I279" t="n">
-        <v>823.7888793945312</v>
+        <v>823.788818359375</v>
       </c>
       <c r="J279" t="n">
         <v>11.35000038146973</v>
@@ -8613,7 +8613,7 @@
         <v>60.40000152587891</v>
       </c>
       <c r="G282" t="n">
-        <v>1104.204223632812</v>
+        <v>1104.2041015625</v>
       </c>
       <c r="H282" t="n">
         <v>129.5500030517578</v>
@@ -8700,7 +8700,7 @@
         <v>60.40000152587891</v>
       </c>
       <c r="G285" t="n">
-        <v>1106.044555664062</v>
+        <v>1106.044677734375</v>
       </c>
       <c r="H285" t="n">
         <v>120.8000030517578</v>
@@ -8758,13 +8758,13 @@
         <v>59.04999923706055</v>
       </c>
       <c r="G287" t="n">
-        <v>1075.781860351562</v>
+        <v>1075.78173828125</v>
       </c>
       <c r="H287" t="n">
         <v>115.8000030517578</v>
       </c>
       <c r="I287" t="n">
-        <v>808.4732666015625</v>
+        <v>808.4733276367188</v>
       </c>
       <c r="J287" t="n">
         <v>10.05000019073486</v>
@@ -8787,7 +8787,7 @@
         <v>58.5</v>
       </c>
       <c r="G288" t="n">
-        <v>1083.14306640625</v>
+        <v>1083.142944335938</v>
       </c>
       <c r="H288" t="n">
         <v>126.9499969482422</v>
@@ -8851,7 +8851,7 @@
         <v>130.6999969482422</v>
       </c>
       <c r="I290" t="n">
-        <v>789.8583374023438</v>
+        <v>789.8582763671875</v>
       </c>
       <c r="J290" t="n">
         <v>9.800000190734863</v>
@@ -8874,7 +8874,7 @@
         <v>58.90000152587891</v>
       </c>
       <c r="G291" t="n">
-        <v>1065.057983398438</v>
+        <v>1065.05810546875</v>
       </c>
       <c r="H291" t="n">
         <v>135.6999969482422</v>
@@ -8903,13 +8903,13 @@
         <v>58.54999923706055</v>
       </c>
       <c r="G292" t="n">
-        <v>1056.947021484375</v>
+        <v>1056.946899414062</v>
       </c>
       <c r="H292" t="n">
         <v>135.8000030517578</v>
       </c>
       <c r="I292" t="n">
-        <v>827.4822998046875</v>
+        <v>827.4823608398438</v>
       </c>
       <c r="J292" t="n">
         <v>9.800000190734863</v>
@@ -8967,7 +8967,7 @@
         <v>140.8000030517578</v>
       </c>
       <c r="I294" t="n">
-        <v>843.8320922851562</v>
+        <v>843.83203125</v>
       </c>
       <c r="J294" t="n">
         <v>10.69999980926514</v>
@@ -8996,7 +8996,7 @@
         <v>153.8000030517578</v>
       </c>
       <c r="I295" t="n">
-        <v>869.341552734375</v>
+        <v>869.3414916992188</v>
       </c>
       <c r="J295" t="n">
         <v>11.69999980926514</v>
@@ -9048,13 +9048,13 @@
         <v>58.25</v>
       </c>
       <c r="G297" t="n">
-        <v>1055.4248046875</v>
+        <v>1055.424682617188</v>
       </c>
       <c r="H297" t="n">
         <v>147.25</v>
       </c>
       <c r="I297" t="n">
-        <v>835.9034423828125</v>
+        <v>835.9033813476562</v>
       </c>
       <c r="J297" t="n">
         <v>11.44999980926514</v>
@@ -9083,7 +9083,7 @@
         <v>139.6499938964844</v>
       </c>
       <c r="I298" t="n">
-        <v>793.7980346679688</v>
+        <v>793.7979125976562</v>
       </c>
       <c r="J298" t="n">
         <v>10.75</v>
@@ -9112,7 +9112,7 @@
         <v>144.3000030517578</v>
       </c>
       <c r="I299" t="n">
-        <v>785.1307373046875</v>
+        <v>785.1306762695312</v>
       </c>
       <c r="J299" t="n">
         <v>10.69999980926514</v>
@@ -9164,7 +9164,7 @@
         <v>54.70000076293945</v>
       </c>
       <c r="G301" t="n">
-        <v>1011.439208984375</v>
+        <v>1011.439270019531</v>
       </c>
       <c r="H301" t="n">
         <v>141.25</v>
@@ -9228,7 +9228,7 @@
         <v>148.0500030517578</v>
       </c>
       <c r="I303" t="n">
-        <v>771.5880126953125</v>
+        <v>771.5880737304688</v>
       </c>
       <c r="J303" t="n">
         <v>10.30000019073486</v>
@@ -9251,7 +9251,7 @@
         <v>59.59999847412109</v>
       </c>
       <c r="G304" t="n">
-        <v>1031.341918945312</v>
+        <v>1031.341796875</v>
       </c>
       <c r="H304" t="n">
         <v>146.8500061035156</v>
@@ -9286,7 +9286,7 @@
         <v>148.8999938964844</v>
       </c>
       <c r="I305" t="n">
-        <v>778.1376953125</v>
+        <v>778.1377563476562</v>
       </c>
       <c r="J305" t="n">
         <v>10.30000019073486</v>
@@ -9309,7 +9309,7 @@
         <v>56.20000076293945</v>
       </c>
       <c r="G306" t="n">
-        <v>1021.390625</v>
+        <v>1021.390686035156</v>
       </c>
       <c r="H306" t="n">
         <v>148.1999969482422</v>
@@ -9367,7 +9367,7 @@
         <v>53.59999847412109</v>
       </c>
       <c r="G308" t="n">
-        <v>1016.733032226562</v>
+        <v>1016.732971191406</v>
       </c>
       <c r="H308" t="n">
         <v>142.1999969482422</v>
@@ -9402,7 +9402,7 @@
         <v>137.5</v>
       </c>
       <c r="I309" t="n">
-        <v>721.9971923828125</v>
+        <v>721.9970703125</v>
       </c>
       <c r="J309" t="n">
         <v>9.149999618530273</v>
@@ -9431,7 +9431,7 @@
         <v>141.5500030517578</v>
       </c>
       <c r="I310" t="n">
-        <v>763.905517578125</v>
+        <v>763.9055786132812</v>
       </c>
       <c r="J310" t="n">
         <v>9.800000190734863</v>
@@ -9454,7 +9454,7 @@
         <v>54.25</v>
       </c>
       <c r="G311" t="n">
-        <v>1059.218994140625</v>
+        <v>1059.219116210938</v>
       </c>
       <c r="H311" t="n">
         <v>144.25</v>
@@ -9483,13 +9483,13 @@
         <v>56</v>
       </c>
       <c r="G312" t="n">
-        <v>1059.400756835938</v>
+        <v>1059.40087890625</v>
       </c>
       <c r="H312" t="n">
         <v>146.3999938964844</v>
       </c>
       <c r="I312" t="n">
-        <v>785.7708740234375</v>
+        <v>785.7708129882812</v>
       </c>
       <c r="J312" t="n">
         <v>10.39999961853027</v>
@@ -9518,7 +9518,7 @@
         <v>151.3999938964844</v>
       </c>
       <c r="I313" t="n">
-        <v>782.56982421875</v>
+        <v>782.5698852539062</v>
       </c>
       <c r="J313" t="n">
         <v>10.80000019073486</v>
@@ -9541,13 +9541,13 @@
         <v>56.54999923706055</v>
       </c>
       <c r="G314" t="n">
-        <v>1063.944580078125</v>
+        <v>1063.944702148438</v>
       </c>
       <c r="H314" t="n">
         <v>151.3999938964844</v>
       </c>
       <c r="I314" t="n">
-        <v>792.2220458984375</v>
+        <v>792.2221069335938</v>
       </c>
       <c r="J314" t="n">
         <v>11.14999961853027</v>
@@ -9570,7 +9570,7 @@
         <v>56.29999923706055</v>
       </c>
       <c r="G315" t="n">
-        <v>1056.401733398438</v>
+        <v>1056.401611328125</v>
       </c>
       <c r="H315" t="n">
         <v>146.8000030517578</v>
@@ -9663,7 +9663,7 @@
         <v>165.5500030517578</v>
       </c>
       <c r="I318" t="n">
-        <v>838.858154296875</v>
+        <v>838.8582153320312</v>
       </c>
       <c r="J318" t="n">
         <v>12.80000019073486</v>
@@ -9692,7 +9692,7 @@
         <v>162</v>
       </c>
       <c r="I319" t="n">
-        <v>843.8320922851562</v>
+        <v>843.83203125</v>
       </c>
       <c r="J319" t="n">
         <v>12.69999980926514</v>
@@ -9744,13 +9744,13 @@
         <v>55</v>
       </c>
       <c r="G321" t="n">
-        <v>1068.738647460938</v>
+        <v>1068.738525390625</v>
       </c>
       <c r="H321" t="n">
         <v>159.1999969482422</v>
       </c>
       <c r="I321" t="n">
-        <v>823.4933471679688</v>
+        <v>823.4932861328125</v>
       </c>
       <c r="J321" t="n">
         <v>12.25</v>
@@ -9779,7 +9779,7 @@
         <v>159.5500030517578</v>
       </c>
       <c r="I322" t="n">
-        <v>827.580810546875</v>
+        <v>827.5807495117188</v>
       </c>
       <c r="J322" t="n">
         <v>12.10000038146973</v>
@@ -9802,7 +9802,7 @@
         <v>54.20000076293945</v>
       </c>
       <c r="G323" t="n">
-        <v>1067.37548828125</v>
+        <v>1067.375366210938</v>
       </c>
       <c r="H323" t="n">
         <v>159.3500061035156</v>
@@ -9837,7 +9837,7 @@
         <v>157.8500061035156</v>
       </c>
       <c r="I324" t="n">
-        <v>821.6712036132812</v>
+        <v>821.6712646484375</v>
       </c>
       <c r="J324" t="n">
         <v>11.80000019073486</v>
@@ -9924,7 +9924,7 @@
         <v>160.6999969482422</v>
       </c>
       <c r="I327" t="n">
-        <v>822.4099731445312</v>
+        <v>822.409912109375</v>
       </c>
       <c r="J327" t="n">
         <v>12.5</v>
@@ -9947,7 +9947,7 @@
         <v>58.04999923706055</v>
       </c>
       <c r="G328" t="n">
-        <v>1099.864868164062</v>
+        <v>1099.86474609375</v>
       </c>
       <c r="H328" t="n">
         <v>157.5500030517578</v>
@@ -9982,7 +9982,7 @@
         <v>154.9499969482422</v>
       </c>
       <c r="I329" t="n">
-        <v>833.736572265625</v>
+        <v>833.7366333007812</v>
       </c>
       <c r="J329" t="n">
         <v>12.14999961853027</v>
@@ -10005,7 +10005,7 @@
         <v>58.34999847412109</v>
       </c>
       <c r="G330" t="n">
-        <v>1099.68310546875</v>
+        <v>1099.682983398438</v>
       </c>
       <c r="H330" t="n">
         <v>153.75</v>
@@ -10034,13 +10034,13 @@
         <v>59.54999923706055</v>
       </c>
       <c r="G331" t="n">
-        <v>1112.360717773438</v>
+        <v>1112.360595703125</v>
       </c>
       <c r="H331" t="n">
         <v>154.5500030517578</v>
       </c>
       <c r="I331" t="n">
-        <v>882.3917846679688</v>
+        <v>882.3917236328125</v>
       </c>
       <c r="J331" t="n">
         <v>12.19999980926514</v>
@@ -10063,13 +10063,13 @@
         <v>57.5</v>
       </c>
       <c r="G332" t="n">
-        <v>1109.520629882812</v>
+        <v>1109.5205078125</v>
       </c>
       <c r="H332" t="n">
         <v>153.6000061035156</v>
       </c>
       <c r="I332" t="n">
-        <v>868.258056640625</v>
+        <v>868.2579956054688</v>
       </c>
       <c r="J332" t="n">
         <v>12.39999961853027</v>
@@ -10092,13 +10092,13 @@
         <v>57.09999847412109</v>
       </c>
       <c r="G333" t="n">
-        <v>1123.220581054688</v>
+        <v>1123.220703125</v>
       </c>
       <c r="H333" t="n">
         <v>152.4499969482422</v>
       </c>
       <c r="I333" t="n">
-        <v>868.3565063476562</v>
+        <v>868.3565673828125</v>
       </c>
       <c r="J333" t="n">
         <v>12.14999961853027</v>
@@ -10179,13 +10179,13 @@
         <v>58.59999847412109</v>
       </c>
       <c r="G336" t="n">
-        <v>1127.037719726562</v>
+        <v>1127.03759765625</v>
       </c>
       <c r="H336" t="n">
         <v>147.8500061035156</v>
       </c>
       <c r="I336" t="n">
-        <v>878.6982421875</v>
+        <v>878.6983032226562</v>
       </c>
       <c r="J336" t="n">
         <v>11.85000038146973</v>
@@ -10272,7 +10272,7 @@
         <v>140.8999938964844</v>
       </c>
       <c r="I339" t="n">
-        <v>886.9716186523438</v>
+        <v>886.9715576171875</v>
       </c>
       <c r="J339" t="n">
         <v>11.69999980926514</v>
@@ -10353,13 +10353,13 @@
         <v>58.5</v>
       </c>
       <c r="G342" t="n">
-        <v>1109.611572265625</v>
+        <v>1109.611450195312</v>
       </c>
       <c r="H342" t="n">
         <v>137.4499969482422</v>
       </c>
       <c r="I342" t="n">
-        <v>884.16455078125</v>
+        <v>884.1646118164062</v>
       </c>
       <c r="J342" t="n">
         <v>11.44999980926514</v>
@@ -10388,7 +10388,7 @@
         <v>134.6499938964844</v>
       </c>
       <c r="I343" t="n">
-        <v>881.4068603515625</v>
+        <v>881.4067993164062</v>
       </c>
       <c r="J343" t="n">
         <v>11.5</v>
@@ -10411,7 +10411,7 @@
         <v>59.79999923706055</v>
       </c>
       <c r="G344" t="n">
-        <v>1115.336791992188</v>
+        <v>1115.3369140625</v>
       </c>
       <c r="H344" t="n">
         <v>139.6499938964844</v>
@@ -10504,7 +10504,7 @@
         <v>138</v>
       </c>
       <c r="I347" t="n">
-        <v>887.0208740234375</v>
+        <v>887.0208129882812</v>
       </c>
       <c r="J347" t="n">
         <v>13.05000019073486</v>
@@ -10533,7 +10533,7 @@
         <v>139.6499938964844</v>
       </c>
       <c r="I348" t="n">
-        <v>897.3624267578125</v>
+        <v>897.362548828125</v>
       </c>
       <c r="J348" t="n">
         <v>13.30000019073486</v>
@@ -10562,7 +10562,7 @@
         <v>138.6000061035156</v>
       </c>
       <c r="I349" t="n">
-        <v>902.0901489257812</v>
+        <v>902.090087890625</v>
       </c>
       <c r="J349" t="n">
         <v>12.94999980926514</v>
@@ -10585,7 +10585,7 @@
         <v>61.29999923706055</v>
       </c>
       <c r="G350" t="n">
-        <v>1122.311767578125</v>
+        <v>1122.311889648438</v>
       </c>
       <c r="H350" t="n">
         <v>134.6999969482422</v>
@@ -10620,7 +10620,7 @@
         <v>133.9499969482422</v>
       </c>
       <c r="I351" t="n">
-        <v>904.7001953125</v>
+        <v>904.7001342773438</v>
       </c>
       <c r="J351" t="n">
         <v>12.94999980926514</v>
@@ -10643,7 +10643,7 @@
         <v>66.19999694824219</v>
       </c>
       <c r="G352" t="n">
-        <v>1115.63232421875</v>
+        <v>1115.632202148438</v>
       </c>
       <c r="H352" t="n">
         <v>134.6000061035156</v>
@@ -10707,7 +10707,7 @@
         <v>132.5</v>
       </c>
       <c r="I354" t="n">
-        <v>943.4075927734375</v>
+        <v>943.4076538085938</v>
       </c>
       <c r="J354" t="n">
         <v>13.60000038146973</v>
@@ -10765,7 +10765,7 @@
         <v>137.0500030517578</v>
       </c>
       <c r="I356" t="n">
-        <v>935.3805541992188</v>
+        <v>935.3804931640625</v>
       </c>
       <c r="J356" t="n">
         <v>14.05000019073486</v>
@@ -10788,7 +10788,7 @@
         <v>63.75</v>
       </c>
       <c r="G357" t="n">
-        <v>1127.787353515625</v>
+        <v>1127.787475585938</v>
       </c>
       <c r="H357" t="n">
         <v>137.1999969482422</v>
@@ -10817,7 +10817,7 @@
         <v>63.54999923706055</v>
       </c>
       <c r="G358" t="n">
-        <v>1128.786865234375</v>
+        <v>1128.786987304688</v>
       </c>
       <c r="H358" t="n">
         <v>139.3999938964844</v>
@@ -10846,7 +10846,7 @@
         <v>64.65000152587891</v>
       </c>
       <c r="G359" t="n">
-        <v>1145.46337890625</v>
+        <v>1145.463256835938</v>
       </c>
       <c r="H359" t="n">
         <v>143.8500061035156</v>
@@ -10875,13 +10875,13 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G360" t="n">
-        <v>1159.549682617188</v>
+        <v>1159.549560546875</v>
       </c>
       <c r="H360" t="n">
         <v>149.9499969482422</v>
       </c>
       <c r="I360" t="n">
-        <v>950.980712890625</v>
+        <v>950.9806518554688</v>
       </c>
       <c r="J360" t="n">
         <v>15.89999961853027</v>
@@ -10904,7 +10904,7 @@
         <v>62.95000076293945</v>
       </c>
       <c r="G361" t="n">
-        <v>1159.86767578125</v>
+        <v>1159.867797851562</v>
       </c>
       <c r="H361" t="n">
         <v>149.4499969482422</v>
@@ -10968,7 +10968,7 @@
         <v>150.75</v>
       </c>
       <c r="I363" t="n">
-        <v>959.729736328125</v>
+        <v>959.7296752929688</v>
       </c>
       <c r="J363" t="n">
         <v>15.69999980926514</v>
@@ -10997,7 +10997,7 @@
         <v>146.5</v>
       </c>
       <c r="I364" t="n">
-        <v>962.7449340820312</v>
+        <v>962.7449951171875</v>
       </c>
       <c r="J364" t="n">
         <v>15.30000019073486</v>
@@ -11020,13 +11020,13 @@
         <v>65.75</v>
       </c>
       <c r="G365" t="n">
-        <v>1165.206909179688</v>
+        <v>1165.206787109375</v>
       </c>
       <c r="H365" t="n">
         <v>147.75</v>
       </c>
       <c r="I365" t="n">
-        <v>959.8781127929688</v>
+        <v>959.8780517578125</v>
       </c>
       <c r="J365" t="n">
         <v>15</v>
@@ -11084,7 +11084,7 @@
         <v>143.25</v>
       </c>
       <c r="I367" t="n">
-        <v>917.3683471679688</v>
+        <v>917.368408203125</v>
       </c>
       <c r="J367" t="n">
         <v>14.75</v>
@@ -11200,7 +11200,7 @@
         <v>138.25</v>
       </c>
       <c r="I371" t="n">
-        <v>942.6763916015625</v>
+        <v>942.6764526367188</v>
       </c>
       <c r="J371" t="n">
         <v>14.05000019073486</v>
@@ -11258,7 +11258,7 @@
         <v>137.1000061035156</v>
       </c>
       <c r="I373" t="n">
-        <v>939.6118774414062</v>
+        <v>939.61181640625</v>
       </c>
       <c r="J373" t="n">
         <v>14.64999961853027</v>
@@ -11310,7 +11310,7 @@
         <v>63.54999923706055</v>
       </c>
       <c r="G375" t="n">
-        <v>1199.03662109375</v>
+        <v>1199.036743164062</v>
       </c>
       <c r="H375" t="n">
         <v>138.75</v>
@@ -11339,7 +11339,7 @@
         <v>64.15000152587891</v>
       </c>
       <c r="G376" t="n">
-        <v>1196.696533203125</v>
+        <v>1196.696655273438</v>
       </c>
       <c r="H376" t="n">
         <v>138.6000061035156</v>
@@ -11403,7 +11403,7 @@
         <v>136.8000030517578</v>
       </c>
       <c r="I378" t="n">
-        <v>948.6080932617188</v>
+        <v>948.6080322265625</v>
       </c>
       <c r="J378" t="n">
         <v>15.35000038146973</v>
@@ -11484,13 +11484,13 @@
         <v>63.5</v>
       </c>
       <c r="G381" t="n">
-        <v>1245.362182617188</v>
+        <v>1245.3623046875</v>
       </c>
       <c r="H381" t="n">
         <v>136.1499938964844</v>
       </c>
       <c r="I381" t="n">
-        <v>958.6422729492188</v>
+        <v>958.642333984375</v>
       </c>
       <c r="J381" t="n">
         <v>15.25</v>
@@ -11519,7 +11519,7 @@
         <v>135</v>
       </c>
       <c r="I382" t="n">
-        <v>963.9312133789062</v>
+        <v>963.9313354492188</v>
       </c>
       <c r="J382" t="n">
         <v>15.25</v>
@@ -11542,13 +11542,13 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G383" t="n">
-        <v>1281.600341796875</v>
+        <v>1281.600219726562</v>
       </c>
       <c r="H383" t="n">
         <v>141.6999969482422</v>
       </c>
       <c r="I383" t="n">
-        <v>947.6194458007812</v>
+        <v>947.619384765625</v>
       </c>
       <c r="J383" t="n">
         <v>15.19999980926514</v>
@@ -11571,13 +11571,13 @@
         <v>59.5</v>
       </c>
       <c r="G384" t="n">
-        <v>1291.32421875</v>
+        <v>1291.324340820312</v>
       </c>
       <c r="H384" t="n">
         <v>154.8500061035156</v>
       </c>
       <c r="I384" t="n">
-        <v>954.7867431640625</v>
+        <v>954.7868041992188</v>
       </c>
       <c r="J384" t="n">
         <v>15.64999961853027</v>
@@ -11600,7 +11600,7 @@
         <v>59.70000076293945</v>
       </c>
       <c r="G385" t="n">
-        <v>1289.760620117188</v>
+        <v>1289.760498046875</v>
       </c>
       <c r="H385" t="n">
         <v>162.3999938964844</v>
@@ -11635,7 +11635,7 @@
         <v>163.0500030517578</v>
       </c>
       <c r="I386" t="n">
-        <v>951.0794677734375</v>
+        <v>951.0795288085938</v>
       </c>
       <c r="J386" t="n">
         <v>15.80000019073486</v>
@@ -11751,7 +11751,7 @@
         <v>178.6000061035156</v>
       </c>
       <c r="I390" t="n">
-        <v>955.478759765625</v>
+        <v>955.4788208007812</v>
       </c>
       <c r="J390" t="n">
         <v>16.54999923706055</v>
@@ -11780,7 +11780,7 @@
         <v>184.8500061035156</v>
       </c>
       <c r="I391" t="n">
-        <v>947.7183837890625</v>
+        <v>947.7183227539062</v>
       </c>
       <c r="J391" t="n">
         <v>16.10000038146973</v>
@@ -11803,13 +11803,13 @@
         <v>58.25</v>
       </c>
       <c r="G392" t="n">
-        <v>1255.00390625</v>
+        <v>1255.003784179688</v>
       </c>
       <c r="H392" t="n">
         <v>188.8500061035156</v>
       </c>
       <c r="I392" t="n">
-        <v>958.6422729492188</v>
+        <v>958.642333984375</v>
       </c>
       <c r="J392" t="n">
         <v>16.45000076293945</v>
@@ -11861,13 +11861,13 @@
         <v>58.15000152587891</v>
       </c>
       <c r="G394" t="n">
-        <v>1224.038208007812</v>
+        <v>1224.0380859375</v>
       </c>
       <c r="H394" t="n">
         <v>181.1999969482422</v>
       </c>
       <c r="I394" t="n">
-        <v>977.1785278320312</v>
+        <v>977.178466796875</v>
       </c>
       <c r="J394" t="n">
         <v>18.14999961853027</v>
@@ -11896,7 +11896,7 @@
         <v>187.0500030517578</v>
       </c>
       <c r="I395" t="n">
-        <v>970.0111694335938</v>
+        <v>970.01123046875</v>
       </c>
       <c r="J395" t="n">
         <v>18.04999923706055</v>
@@ -11925,7 +11925,7 @@
         <v>199.1499938964844</v>
       </c>
       <c r="I396" t="n">
-        <v>968.033935546875</v>
+        <v>968.0339965820312</v>
       </c>
       <c r="J396" t="n">
         <v>19.04999923706055</v>
@@ -11954,7 +11954,7 @@
         <v>210.0500030517578</v>
       </c>
       <c r="I397" t="n">
-        <v>977.1785278320312</v>
+        <v>977.178466796875</v>
       </c>
       <c r="J397" t="n">
         <v>18.64999961853027</v>
@@ -12012,7 +12012,7 @@
         <v>191.4499969482422</v>
       </c>
       <c r="I399" t="n">
-        <v>976.6348266601562</v>
+        <v>976.634765625</v>
       </c>
       <c r="J399" t="n">
         <v>18.25</v>
@@ -12041,7 +12041,7 @@
         <v>175.8500061035156</v>
       </c>
       <c r="I400" t="n">
-        <v>983.554931640625</v>
+        <v>983.5549926757812</v>
       </c>
       <c r="J400" t="n">
         <v>17.5</v>
@@ -12064,7 +12064,7 @@
         <v>62.20000076293945</v>
       </c>
       <c r="G401" t="n">
-        <v>1253.970092773438</v>
+        <v>1253.969970703125</v>
       </c>
       <c r="H401" t="n">
         <v>170</v>
@@ -12151,13 +12151,13 @@
         <v>60.95000076293945</v>
       </c>
       <c r="G404" t="n">
-        <v>1249.465454101562</v>
+        <v>1249.46533203125</v>
       </c>
       <c r="H404" t="n">
         <v>158.0500030517578</v>
       </c>
       <c r="I404" t="n">
-        <v>1023.296569824219</v>
+        <v>1023.296447753906</v>
       </c>
       <c r="J404" t="n">
         <v>16.54999923706055</v>
@@ -12250,7 +12250,7 @@
         <v>170.4499969482422</v>
       </c>
       <c r="I407" t="n">
-        <v>1037.186279296875</v>
+        <v>1037.186401367188</v>
       </c>
       <c r="J407" t="n">
         <v>17.39999961853027</v>
@@ -12276,13 +12276,13 @@
         <v>67.84999847412109</v>
       </c>
       <c r="G408" t="n">
-        <v>1246.0732421875</v>
+        <v>1246.073364257812</v>
       </c>
       <c r="H408" t="n">
         <v>178.9499969482422</v>
       </c>
       <c r="I408" t="n">
-        <v>1023.593200683594</v>
+        <v>1023.593078613281</v>
       </c>
       <c r="J408" t="n">
         <v>17.29999923706055</v>
@@ -12346,7 +12346,7 @@
         <v>177.25</v>
       </c>
       <c r="I410" t="n">
-        <v>988.15185546875</v>
+        <v>988.1519165039062</v>
       </c>
       <c r="J410" t="n">
         <v>17.35000038146973</v>
@@ -12474,7 +12474,7 @@
         <v>186.75</v>
       </c>
       <c r="I414" t="n">
-        <v>1005.650085449219</v>
+        <v>1005.650024414062</v>
       </c>
       <c r="J414" t="n">
         <v>19.14999961853027</v>
@@ -12538,7 +12538,7 @@
         <v>192.8999938964844</v>
       </c>
       <c r="I416" t="n">
-        <v>1005.501770019531</v>
+        <v>1005.501708984375</v>
       </c>
       <c r="J416" t="n">
         <v>19.54999923706055</v>
@@ -12570,7 +12570,7 @@
         <v>190.8000030517578</v>
       </c>
       <c r="I417" t="n">
-        <v>996.8021240234375</v>
+        <v>996.8020629882812</v>
       </c>
       <c r="J417" t="n">
         <v>19.79999923706055</v>
@@ -12628,7 +12628,7 @@
         <v>70.75</v>
       </c>
       <c r="G419" t="n">
-        <v>1201.510620117188</v>
+        <v>1201.5107421875</v>
       </c>
       <c r="H419" t="n">
         <v>189.8000030517578</v>
@@ -12692,7 +12692,7 @@
         <v>70.94999694824219</v>
       </c>
       <c r="G421" t="n">
-        <v>1222.556884765625</v>
+        <v>1222.557006835938</v>
       </c>
       <c r="H421" t="n">
         <v>182.8500061035156</v>
@@ -12788,13 +12788,13 @@
         <v>68.55000305175781</v>
       </c>
       <c r="G424" t="n">
-        <v>1212.033935546875</v>
+        <v>1212.033813476562</v>
       </c>
       <c r="H424" t="n">
         <v>175.3000030517578</v>
       </c>
       <c r="I424" t="n">
-        <v>959.6802368164062</v>
+        <v>959.6802978515625</v>
       </c>
       <c r="J424" t="n">
         <v>18.75</v>
@@ -12826,7 +12826,7 @@
         <v>183.75</v>
       </c>
       <c r="I425" t="n">
-        <v>959.9768676757812</v>
+        <v>959.9769287109375</v>
       </c>
       <c r="J425" t="n">
         <v>19.14999961853027</v>
@@ -12954,7 +12954,7 @@
         <v>175.75</v>
       </c>
       <c r="I429" t="n">
-        <v>936.1023559570312</v>
+        <v>936.102294921875</v>
       </c>
       <c r="J429" t="n">
         <v>18.89999961853027</v>
@@ -12980,7 +12980,7 @@
         <v>65.94999694824219</v>
       </c>
       <c r="G430" t="n">
-        <v>1156.281127929688</v>
+        <v>1156.281005859375</v>
       </c>
       <c r="H430" t="n">
         <v>173.5500030517578</v>
@@ -13012,7 +13012,7 @@
         <v>64.5</v>
       </c>
       <c r="G431" t="n">
-        <v>1157.2939453125</v>
+        <v>1157.293823242188</v>
       </c>
       <c r="H431" t="n">
         <v>171</v>
@@ -13076,13 +13076,13 @@
         <v>63.20000076293945</v>
       </c>
       <c r="G433" t="n">
-        <v>1153.143920898438</v>
+        <v>1153.14404296875</v>
       </c>
       <c r="H433" t="n">
         <v>170.8999938964844</v>
       </c>
       <c r="I433" t="n">
-        <v>946.4825439453125</v>
+        <v>946.4826049804688</v>
       </c>
       <c r="J433" t="n">
         <v>19.14999961853027</v>
@@ -13108,13 +13108,13 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G434" t="n">
-        <v>1158.528930664062</v>
+        <v>1158.529052734375</v>
       </c>
       <c r="H434" t="n">
         <v>173.3000030517578</v>
       </c>
       <c r="I434" t="n">
-        <v>951.0794677734375</v>
+        <v>951.0795288085938</v>
       </c>
       <c r="J434" t="n">
         <v>19.25</v>
@@ -13140,7 +13140,7 @@
         <v>68.55000305175781</v>
       </c>
       <c r="G435" t="n">
-        <v>1145.263793945312</v>
+        <v>1145.263916015625</v>
       </c>
       <c r="H435" t="n">
         <v>174.3500061035156</v>
@@ -13210,7 +13210,7 @@
         <v>172.1999969482422</v>
       </c>
       <c r="I437" t="n">
-        <v>968.72607421875</v>
+        <v>968.7260131835938</v>
       </c>
       <c r="J437" t="n">
         <v>18.89999961853027</v>
@@ -13236,7 +13236,7 @@
         <v>72.40000152587891</v>
       </c>
       <c r="G438" t="n">
-        <v>1145.18994140625</v>
+        <v>1145.189819335938</v>
       </c>
       <c r="H438" t="n">
         <v>171.6499938964844</v>
@@ -13274,7 +13274,7 @@
         <v>171.25</v>
       </c>
       <c r="I439" t="n">
-        <v>943.4673461914062</v>
+        <v>943.46728515625</v>
       </c>
       <c r="J439" t="n">
         <v>17.85000038146973</v>
@@ -13332,13 +13332,13 @@
         <v>72.19999694824219</v>
       </c>
       <c r="G441" t="n">
-        <v>1158.553588867188</v>
+        <v>1158.5537109375</v>
       </c>
       <c r="H441" t="n">
         <v>170.5</v>
       </c>
       <c r="I441" t="n">
-        <v>975.250732421875</v>
+        <v>975.2506713867188</v>
       </c>
       <c r="J441" t="n">
         <v>18.20000076293945</v>
@@ -13370,7 +13370,7 @@
         <v>169.3500061035156</v>
       </c>
       <c r="I442" t="n">
-        <v>980.0453491210938</v>
+        <v>980.04541015625</v>
       </c>
       <c r="J442" t="n">
         <v>18</v>
@@ -13434,7 +13434,7 @@
         <v>170.75</v>
       </c>
       <c r="I444" t="n">
-        <v>1058.243286132812</v>
+        <v>1058.243408203125</v>
       </c>
       <c r="J444" t="n">
         <v>18.39999961853027</v>
@@ -13460,7 +13460,7 @@
         <v>77.65000152587891</v>
       </c>
       <c r="G445" t="n">
-        <v>1163.593017578125</v>
+        <v>1163.592895507812</v>
       </c>
       <c r="H445" t="n">
         <v>172.3500061035156</v>
@@ -13492,13 +13492,13 @@
         <v>77.94999694824219</v>
       </c>
       <c r="G446" t="n">
-        <v>1148.154174804688</v>
+        <v>1148.154052734375</v>
       </c>
       <c r="H446" t="n">
         <v>169.1999969482422</v>
       </c>
       <c r="I446" t="n">
-        <v>1029.079833984375</v>
+        <v>1029.079711914062</v>
       </c>
       <c r="J446" t="n">
         <v>18.14999961853027</v>
@@ -13594,7 +13594,7 @@
         <v>169.75</v>
       </c>
       <c r="I449" t="n">
-        <v>995.3192749023438</v>
+        <v>995.3192138671875</v>
       </c>
       <c r="J449" t="n">
         <v>16.70000076293945</v>
@@ -13658,7 +13658,7 @@
         <v>159.0500030517578</v>
       </c>
       <c r="I451" t="n">
-        <v>1007.726135253906</v>
+        <v>1007.72607421875</v>
       </c>
       <c r="J451" t="n">
         <v>16.5</v>
@@ -13684,7 +13684,7 @@
         <v>68.75</v>
       </c>
       <c r="G452" t="n">
-        <v>1119.400756835938</v>
+        <v>1119.40087890625</v>
       </c>
       <c r="H452" t="n">
         <v>162.9499969482422</v>
@@ -13722,7 +13722,7 @@
         <v>168</v>
       </c>
       <c r="I453" t="n">
-        <v>1007.577880859375</v>
+        <v>1007.577819824219</v>
       </c>
       <c r="J453" t="n">
         <v>16.95000076293945</v>
@@ -13882,7 +13882,7 @@
         <v>183.3500061035156</v>
       </c>
       <c r="I458" t="n">
-        <v>1032.3916015625</v>
+        <v>1032.391723632812</v>
       </c>
       <c r="J458" t="n">
         <v>19.29999923706055</v>
@@ -13908,13 +13908,13 @@
         <v>70.90000152587891</v>
       </c>
       <c r="G459" t="n">
-        <v>1148.055419921875</v>
+        <v>1148.055297851562</v>
       </c>
       <c r="H459" t="n">
         <v>185.5500030517578</v>
       </c>
       <c r="I459" t="n">
-        <v>1038.817626953125</v>
+        <v>1038.817504882812</v>
       </c>
       <c r="J459" t="n">
         <v>20.70000076293945</v>
@@ -13946,7 +13946,7 @@
         <v>179.1000061035156</v>
       </c>
       <c r="I460" t="n">
-        <v>1039.509521484375</v>
+        <v>1039.509399414062</v>
       </c>
       <c r="J460" t="n">
         <v>20.45000076293945</v>
@@ -13978,7 +13978,7 @@
         <v>178.1000061035156</v>
       </c>
       <c r="I461" t="n">
-        <v>1038.174926757812</v>
+        <v>1038.1748046875</v>
       </c>
       <c r="J461" t="n">
         <v>21.20000076293945</v>
@@ -14010,7 +14010,7 @@
         <v>177.3000030517578</v>
       </c>
       <c r="I462" t="n">
-        <v>1031.056884765625</v>
+        <v>1031.057006835938</v>
       </c>
       <c r="J462" t="n">
         <v>20.5</v>
@@ -14068,7 +14068,7 @@
         <v>83.59999847412109</v>
       </c>
       <c r="G464" t="n">
-        <v>1164.185668945312</v>
+        <v>1164.185791015625</v>
       </c>
       <c r="H464" t="n">
         <v>181.75</v>
@@ -14132,7 +14132,7 @@
         <v>85.15000152587891</v>
       </c>
       <c r="G466" t="n">
-        <v>1163.7412109375</v>
+        <v>1163.741088867188</v>
       </c>
       <c r="H466" t="n">
         <v>186</v>
@@ -14202,7 +14202,7 @@
         <v>179.5500030517578</v>
       </c>
       <c r="I468" t="n">
-        <v>1109.15625</v>
+        <v>1109.156127929688</v>
       </c>
       <c r="J468" t="n">
         <v>21.35000038146973</v>
@@ -14234,7 +14234,7 @@
         <v>174.8500061035156</v>
       </c>
       <c r="I469" t="n">
-        <v>1108.315795898438</v>
+        <v>1108.31591796875</v>
       </c>
       <c r="J469" t="n">
         <v>20.89999961853027</v>
@@ -14260,7 +14260,7 @@
         <v>82.40000152587891</v>
       </c>
       <c r="G470" t="n">
-        <v>1183.478149414062</v>
+        <v>1183.47802734375</v>
       </c>
       <c r="H470" t="n">
         <v>174.25</v>
@@ -14292,13 +14292,13 @@
         <v>83.44999694824219</v>
       </c>
       <c r="G471" t="n">
-        <v>1182.687622070312</v>
+        <v>1182.6875</v>
       </c>
       <c r="H471" t="n">
         <v>173.4499969482422</v>
       </c>
       <c r="I471" t="n">
-        <v>1078.55908203125</v>
+        <v>1078.558959960938</v>
       </c>
       <c r="J471" t="n">
         <v>20.89999961853027</v>
@@ -14324,13 +14324,13 @@
         <v>82.90000152587891</v>
       </c>
       <c r="G472" t="n">
-        <v>1182.934692382812</v>
+        <v>1182.9345703125</v>
       </c>
       <c r="H472" t="n">
         <v>177.8999938964844</v>
       </c>
       <c r="I472" t="n">
-        <v>1087.851806640625</v>
+        <v>1087.851928710938</v>
       </c>
       <c r="J472" t="n">
         <v>20.89999961853027</v>
@@ -14388,13 +14388,13 @@
         <v>86.55000305175781</v>
       </c>
       <c r="G474" t="n">
-        <v>1174.560791015625</v>
+        <v>1174.560668945312</v>
       </c>
       <c r="H474" t="n">
         <v>189.75</v>
       </c>
       <c r="I474" t="n">
-        <v>1082.513549804688</v>
+        <v>1082.513427734375</v>
       </c>
       <c r="J474" t="n">
         <v>21.14999961853027</v>
@@ -14420,7 +14420,7 @@
         <v>87.69999694824219</v>
       </c>
       <c r="G475" t="n">
-        <v>1182.88525390625</v>
+        <v>1182.885375976562</v>
       </c>
       <c r="H475" t="n">
         <v>194.0500030517578</v>
@@ -14490,7 +14490,7 @@
         <v>202.3000030517578</v>
       </c>
       <c r="I477" t="n">
-        <v>1095.16748046875</v>
+        <v>1095.167602539062</v>
       </c>
       <c r="J477" t="n">
         <v>22.29999923706055</v>
@@ -14522,7 +14522,7 @@
         <v>212.3999938964844</v>
       </c>
       <c r="I478" t="n">
-        <v>1103.867065429688</v>
+        <v>1103.8671875</v>
       </c>
       <c r="J478" t="n">
         <v>23.20000076293945</v>
@@ -14586,7 +14586,7 @@
         <v>214.75</v>
       </c>
       <c r="I480" t="n">
-        <v>1130.905151367188</v>
+        <v>1130.9052734375</v>
       </c>
       <c r="J480" t="n">
         <v>23.95000076293945</v>
@@ -14618,7 +14618,7 @@
         <v>218.6999969482422</v>
       </c>
       <c r="I481" t="n">
-        <v>1148.10693359375</v>
+        <v>1148.106811523438</v>
       </c>
       <c r="J481" t="n">
         <v>24.5</v>
@@ -14676,13 +14676,13 @@
         <v>86.69999694824219</v>
       </c>
       <c r="G483" t="n">
-        <v>1202.473876953125</v>
+        <v>1202.473999023438</v>
       </c>
       <c r="H483" t="n">
         <v>215.8000030517578</v>
       </c>
       <c r="I483" t="n">
-        <v>1170.547973632812</v>
+        <v>1170.548095703125</v>
       </c>
       <c r="J483" t="n">
         <v>23.79999923706055</v>
@@ -14714,7 +14714,7 @@
         <v>214.6000061035156</v>
       </c>
       <c r="I484" t="n">
-        <v>1157.745727539062</v>
+        <v>1157.74560546875</v>
       </c>
       <c r="J484" t="n">
         <v>23.85000038146973</v>
@@ -14746,7 +14746,7 @@
         <v>209.75</v>
       </c>
       <c r="I485" t="n">
-        <v>1167.977661132812</v>
+        <v>1167.977783203125</v>
       </c>
       <c r="J485" t="n">
         <v>23.60000038146973</v>
@@ -14842,7 +14842,7 @@
         <v>190.8000030517578</v>
       </c>
       <c r="I488" t="n">
-        <v>1227.293579101562</v>
+        <v>1227.29345703125</v>
       </c>
       <c r="J488" t="n">
         <v>21.39999961853027</v>
@@ -14874,7 +14874,7 @@
         <v>193.3999938964844</v>
       </c>
       <c r="I489" t="n">
-        <v>1275.042602539062</v>
+        <v>1275.042724609375</v>
       </c>
       <c r="J489" t="n">
         <v>22.70000076293945</v>
@@ -14900,7 +14900,7 @@
         <v>86.09999847412109</v>
       </c>
       <c r="G490" t="n">
-        <v>1267.242919921875</v>
+        <v>1267.243041992188</v>
       </c>
       <c r="H490" t="n">
         <v>193.0500030517578</v>
@@ -14932,13 +14932,13 @@
         <v>88.84999847412109</v>
       </c>
       <c r="G491" t="n">
-        <v>1273.66552734375</v>
+        <v>1273.665649414062</v>
       </c>
       <c r="H491" t="n">
         <v>196.75</v>
       </c>
       <c r="I491" t="n">
-        <v>1333.2216796875</v>
+        <v>1333.221557617188</v>
       </c>
       <c r="J491" t="n">
         <v>22.60000038146973</v>
@@ -14970,7 +14970,7 @@
         <v>194.6999969482422</v>
       </c>
       <c r="I492" t="n">
-        <v>1348.198852539062</v>
+        <v>1348.198974609375</v>
       </c>
       <c r="J492" t="n">
         <v>22.60000038146973</v>
@@ -15002,7 +15002,7 @@
         <v>190.8000030517578</v>
       </c>
       <c r="I493" t="n">
-        <v>1333.122802734375</v>
+        <v>1333.122680664062</v>
       </c>
       <c r="J493" t="n">
         <v>22.35000038146973</v>
@@ -15034,7 +15034,7 @@
         <v>209.8000030517578</v>
       </c>
       <c r="I494" t="n">
-        <v>1332.77685546875</v>
+        <v>1332.776733398438</v>
       </c>
       <c r="J494" t="n">
         <v>23.29999923706055</v>
@@ -15098,7 +15098,7 @@
         <v>207.9499969482422</v>
       </c>
       <c r="I496" t="n">
-        <v>1399.062133789062</v>
+        <v>1399.06201171875</v>
       </c>
       <c r="J496" t="n">
         <v>24.10000038146973</v>
@@ -15124,13 +15124,13 @@
         <v>89.69999694824219</v>
       </c>
       <c r="G497" t="n">
-        <v>1276.25927734375</v>
+        <v>1276.259399414062</v>
       </c>
       <c r="H497" t="n">
         <v>215.1499938964844</v>
       </c>
       <c r="I497" t="n">
-        <v>1368.218017578125</v>
+        <v>1368.217895507812</v>
       </c>
       <c r="J497" t="n">
         <v>25.95000076293945</v>
@@ -15156,13 +15156,13 @@
         <v>90.25</v>
       </c>
       <c r="G498" t="n">
-        <v>1282.854736328125</v>
+        <v>1282.854614257812</v>
       </c>
       <c r="H498" t="n">
         <v>231.5500030517578</v>
       </c>
       <c r="I498" t="n">
-        <v>1382.1572265625</v>
+        <v>1382.157104492188</v>
       </c>
       <c r="J498" t="n">
         <v>30.39999961853027</v>
@@ -15194,7 +15194,7 @@
         <v>229.6000061035156</v>
       </c>
       <c r="I499" t="n">
-        <v>1356.552490234375</v>
+        <v>1356.552368164062</v>
       </c>
       <c r="J499" t="n">
         <v>31.39999961853027</v>
@@ -15226,7 +15226,7 @@
         <v>241</v>
       </c>
       <c r="I500" t="n">
-        <v>1329.909912109375</v>
+        <v>1329.909790039062</v>
       </c>
       <c r="J500" t="n">
         <v>32.04999923706055</v>
@@ -15284,7 +15284,7 @@
         <v>119.4000015258789</v>
       </c>
       <c r="G502" t="n">
-        <v>1309.261474609375</v>
+        <v>1309.261352539062</v>
       </c>
       <c r="H502" t="n">
         <v>237.4499969482422</v>
@@ -15316,13 +15316,13 @@
         <v>130.9499969482422</v>
       </c>
       <c r="G503" t="n">
-        <v>1343.696044921875</v>
+        <v>1343.696166992188</v>
       </c>
       <c r="H503" t="n">
         <v>239.8999938964844</v>
       </c>
       <c r="I503" t="n">
-        <v>1498.1689453125</v>
+        <v>1498.168823242188</v>
       </c>
       <c r="J503" t="n">
         <v>31.10000038146973</v>
@@ -15386,7 +15386,7 @@
         <v>232.6499938964844</v>
       </c>
       <c r="I505" t="n">
-        <v>1442.313110351562</v>
+        <v>1442.313354492188</v>
       </c>
       <c r="J505" t="n">
         <v>30.79999923706055</v>
@@ -15450,7 +15450,7 @@
         <v>217.3000030517578</v>
       </c>
       <c r="I507" t="n">
-        <v>1387.594482421875</v>
+        <v>1387.594360351562</v>
       </c>
       <c r="J507" t="n">
         <v>29.85000038146973</v>
@@ -15572,7 +15572,7 @@
         <v>120.4000015258789</v>
       </c>
       <c r="G511" t="n">
-        <v>1327.861938476562</v>
+        <v>1327.862060546875</v>
       </c>
       <c r="H511" t="n">
         <v>213.3999938964844</v>
@@ -15604,7 +15604,7 @@
         <v>120.5500030517578</v>
       </c>
       <c r="G512" t="n">
-        <v>1336.952392578125</v>
+        <v>1336.952270507812</v>
       </c>
       <c r="H512" t="n">
         <v>215.25</v>
@@ -15674,7 +15674,7 @@
         <v>231.5500030517578</v>
       </c>
       <c r="I514" t="n">
-        <v>1382.997436523438</v>
+        <v>1382.99755859375</v>
       </c>
       <c r="J514" t="n">
         <v>29.95000076293945</v>
@@ -15700,7 +15700,7 @@
         <v>117</v>
       </c>
       <c r="G515" t="n">
-        <v>1409.6259765625</v>
+        <v>1409.625854492188</v>
       </c>
       <c r="H515" t="n">
         <v>231.0500030517578</v>
@@ -15738,7 +15738,7 @@
         <v>224.6000061035156</v>
       </c>
       <c r="I516" t="n">
-        <v>1375.929077148438</v>
+        <v>1375.928955078125</v>
       </c>
       <c r="J516" t="n">
         <v>29</v>
@@ -15834,7 +15834,7 @@
         <v>214.9499969482422</v>
       </c>
       <c r="I519" t="n">
-        <v>1380.179931640625</v>
+        <v>1380.179809570312</v>
       </c>
       <c r="J519" t="n">
         <v>26.04999923706055</v>
@@ -15898,7 +15898,7 @@
         <v>213.4499969482422</v>
       </c>
       <c r="I521" t="n">
-        <v>1407.761840820312</v>
+        <v>1407.76171875</v>
       </c>
       <c r="J521" t="n">
         <v>28.54999923706055</v>
@@ -15924,13 +15924,13 @@
         <v>108.3499984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>1443.344482421875</v>
+        <v>1443.344360351562</v>
       </c>
       <c r="H522" t="n">
         <v>213</v>
       </c>
       <c r="I522" t="n">
-        <v>1366.685546875</v>
+        <v>1366.685424804688</v>
       </c>
       <c r="J522" t="n">
         <v>27.5</v>
@@ -15956,7 +15956,7 @@
         <v>106.25</v>
       </c>
       <c r="G523" t="n">
-        <v>1435.044311523438</v>
+        <v>1435.04443359375</v>
       </c>
       <c r="H523" t="n">
         <v>202.25</v>
@@ -15988,7 +15988,7 @@
         <v>105.4000015258789</v>
       </c>
       <c r="G524" t="n">
-        <v>1447.642578125</v>
+        <v>1447.642456054688</v>
       </c>
       <c r="H524" t="n">
         <v>210.1499938964844</v>
@@ -16020,7 +16020,7 @@
         <v>109.5</v>
       </c>
       <c r="G525" t="n">
-        <v>1463.7236328125</v>
+        <v>1463.723510742188</v>
       </c>
       <c r="H525" t="n">
         <v>229.1499938964844</v>
@@ -16058,7 +16058,7 @@
         <v>234.3500061035156</v>
       </c>
       <c r="I526" t="n">
-        <v>1455.36279296875</v>
+        <v>1455.362670898438</v>
       </c>
       <c r="J526" t="n">
         <v>26.75</v>
@@ -16116,13 +16116,13 @@
         <v>117.9000015258789</v>
       </c>
       <c r="G528" t="n">
-        <v>1456.436401367188</v>
+        <v>1456.4365234375</v>
       </c>
       <c r="H528" t="n">
         <v>242.8500061035156</v>
       </c>
       <c r="I528" t="n">
-        <v>1441.621215820312</v>
+        <v>1441.621337890625</v>
       </c>
       <c r="J528" t="n">
         <v>26.95000076293945</v>
@@ -16148,7 +16148,7 @@
         <v>119</v>
       </c>
       <c r="G529" t="n">
-        <v>1453.496826171875</v>
+        <v>1453.496948242188</v>
       </c>
       <c r="H529" t="n">
         <v>241.1999969482422</v>
@@ -16218,7 +16218,7 @@
         <v>229.4499969482422</v>
       </c>
       <c r="I531" t="n">
-        <v>1427.286499023438</v>
+        <v>1427.28662109375</v>
       </c>
       <c r="J531" t="n">
         <v>25.64999961853027</v>
@@ -16250,7 +16250,7 @@
         <v>228.5</v>
       </c>
       <c r="I532" t="n">
-        <v>1499.948364257812</v>
+        <v>1499.948608398438</v>
       </c>
       <c r="J532" t="n">
         <v>25.60000038146973</v>
@@ -16282,7 +16282,7 @@
         <v>228.5500030517578</v>
       </c>
       <c r="I533" t="n">
-        <v>1470.438842773438</v>
+        <v>1470.43896484375</v>
       </c>
       <c r="J533" t="n">
         <v>25.25</v>
@@ -16314,7 +16314,7 @@
         <v>220.5500030517578</v>
       </c>
       <c r="I534" t="n">
-        <v>1447.602294921875</v>
+        <v>1447.602416992188</v>
       </c>
       <c r="J534" t="n">
         <v>24.64999961853027</v>
@@ -16340,7 +16340,7 @@
         <v>112.5999984741211</v>
       </c>
       <c r="G535" t="n">
-        <v>1438.280395507812</v>
+        <v>1438.280517578125</v>
       </c>
       <c r="H535" t="n">
         <v>212.1000061035156</v>
@@ -16372,7 +16372,7 @@
         <v>107</v>
       </c>
       <c r="G536" t="n">
-        <v>1443.393798828125</v>
+        <v>1443.393920898438</v>
       </c>
       <c r="H536" t="n">
         <v>220.8999938964844</v>
@@ -16404,7 +16404,7 @@
         <v>102.4499969482422</v>
       </c>
       <c r="G537" t="n">
-        <v>1474.345458984375</v>
+        <v>1474.345581054688</v>
       </c>
       <c r="H537" t="n">
         <v>223.25</v>
@@ -16474,7 +16474,7 @@
         <v>226.6999969482422</v>
       </c>
       <c r="I539" t="n">
-        <v>1419.278930664062</v>
+        <v>1419.279052734375</v>
       </c>
       <c r="J539" t="n">
         <v>23.04999923706055</v>
@@ -16532,7 +16532,7 @@
         <v>93.44999694824219</v>
       </c>
       <c r="G541" t="n">
-        <v>1461.302734375</v>
+        <v>1461.302856445312</v>
       </c>
       <c r="H541" t="n">
         <v>221.1999969482422</v>
@@ -16564,7 +16564,7 @@
         <v>92.05000305175781</v>
       </c>
       <c r="G542" t="n">
-        <v>1449.12451171875</v>
+        <v>1449.124633789062</v>
       </c>
       <c r="H542" t="n">
         <v>223.6499938964844</v>
@@ -16666,7 +16666,7 @@
         <v>214.25</v>
       </c>
       <c r="I545" t="n">
-        <v>1232.7802734375</v>
+        <v>1232.780151367188</v>
       </c>
       <c r="J545" t="n">
         <v>21.04999923706055</v>
@@ -16762,7 +16762,7 @@
         <v>239.8000030517578</v>
       </c>
       <c r="I548" t="n">
-        <v>1193.780151367188</v>
+        <v>1193.780029296875</v>
       </c>
       <c r="J548" t="n">
         <v>22.79999923706055</v>
@@ -16794,7 +16794,7 @@
         <v>249.3000030517578</v>
       </c>
       <c r="I549" t="n">
-        <v>1200.205932617188</v>
+        <v>1200.2060546875</v>
       </c>
       <c r="J549" t="n">
         <v>23.89999961853027</v>
@@ -16820,7 +16820,7 @@
         <v>87.05000305175781</v>
       </c>
       <c r="G550" t="n">
-        <v>1433.685791015625</v>
+        <v>1433.685668945312</v>
       </c>
       <c r="H550" t="n">
         <v>271.2000122070312</v>
@@ -16852,13 +16852,13 @@
         <v>91.40000152587891</v>
       </c>
       <c r="G551" t="n">
-        <v>1437.687622070312</v>
+        <v>1437.6875</v>
       </c>
       <c r="H551" t="n">
         <v>277.3500061035156</v>
       </c>
       <c r="I551" t="n">
-        <v>1234.707885742188</v>
+        <v>1234.7080078125</v>
       </c>
       <c r="J551" t="n">
         <v>26.29999923706055</v>
@@ -16954,7 +16954,7 @@
         <v>270.9500122070312</v>
       </c>
       <c r="I554" t="n">
-        <v>1260.90576171875</v>
+        <v>1260.905639648438</v>
       </c>
       <c r="J554" t="n">
         <v>28.25</v>
@@ -17012,7 +17012,7 @@
         <v>89.90000152587891</v>
       </c>
       <c r="G556" t="n">
-        <v>1469.232177734375</v>
+        <v>1469.232055664062</v>
       </c>
       <c r="H556" t="n">
         <v>289.7999877929688</v>
@@ -17108,7 +17108,7 @@
         <v>90.84999847412109</v>
       </c>
       <c r="G559" t="n">
-        <v>1442.7021484375</v>
+        <v>1442.702026367188</v>
       </c>
       <c r="H559" t="n">
         <v>298.8999938964844</v>
@@ -17146,7 +17146,7 @@
         <v>287.6000061035156</v>
       </c>
       <c r="I560" t="n">
-        <v>1300.844970703125</v>
+        <v>1300.845092773438</v>
       </c>
       <c r="J560" t="n">
         <v>31</v>
@@ -17172,7 +17172,7 @@
         <v>89.44999694824219</v>
       </c>
       <c r="G561" t="n">
-        <v>1446.209838867188</v>
+        <v>1446.209716796875</v>
       </c>
       <c r="H561" t="n">
         <v>284.5</v>
@@ -17204,13 +17204,13 @@
         <v>89</v>
       </c>
       <c r="G562" t="n">
-        <v>1461.944946289062</v>
+        <v>1461.945068359375</v>
       </c>
       <c r="H562" t="n">
         <v>227.6000061035156</v>
       </c>
       <c r="I562" t="n">
-        <v>1280.974243164062</v>
+        <v>1280.974365234375</v>
       </c>
       <c r="J562" t="n">
         <v>28.35000038146973</v>
@@ -17242,7 +17242,7 @@
         <v>197.75</v>
       </c>
       <c r="I563" t="n">
-        <v>1273.362060546875</v>
+        <v>1273.362182617188</v>
       </c>
       <c r="J563" t="n">
         <v>27.35000038146973</v>
@@ -17306,7 +17306,7 @@
         <v>194.1999969482422</v>
       </c>
       <c r="I565" t="n">
-        <v>1241.380981445312</v>
+        <v>1241.380859375</v>
       </c>
       <c r="J565" t="n">
         <v>27.35000038146973</v>
@@ -17338,7 +17338,7 @@
         <v>194.6999969482422</v>
       </c>
       <c r="I566" t="n">
-        <v>1236.882934570312</v>
+        <v>1236.8828125</v>
       </c>
       <c r="J566" t="n">
         <v>28.70000076293945</v>
@@ -17364,13 +17364,13 @@
         <v>87.59999847412109</v>
       </c>
       <c r="G567" t="n">
-        <v>1452.607666015625</v>
+        <v>1452.607543945312</v>
       </c>
       <c r="H567" t="n">
         <v>188.75</v>
       </c>
       <c r="I567" t="n">
-        <v>1248.3505859375</v>
+        <v>1248.350463867188</v>
       </c>
       <c r="J567" t="n">
         <v>28.04999923706055</v>
@@ -17492,7 +17492,7 @@
         <v>92.75</v>
       </c>
       <c r="G571" t="n">
-        <v>1442.57861328125</v>
+        <v>1442.578491210938</v>
       </c>
       <c r="H571" t="n">
         <v>192.6499938964844</v>
@@ -17524,7 +17524,7 @@
         <v>90.59999847412109</v>
       </c>
       <c r="G572" t="n">
-        <v>1435.2421875</v>
+        <v>1435.242065429688</v>
       </c>
       <c r="H572" t="n">
         <v>190.8999938964844</v>
@@ -17556,7 +17556,7 @@
         <v>88.75</v>
       </c>
       <c r="G573" t="n">
-        <v>1447.568359375</v>
+        <v>1447.568481445312</v>
       </c>
       <c r="H573" t="n">
         <v>185.8000030517578</v>
@@ -17594,7 +17594,7 @@
         <v>177.8999938964844</v>
       </c>
       <c r="I574" t="n">
-        <v>1309.693115234375</v>
+        <v>1309.692993164062</v>
       </c>
       <c r="J574" t="n">
         <v>27.29999923706055</v>
@@ -17626,7 +17626,7 @@
         <v>175.4499969482422</v>
       </c>
       <c r="I575" t="n">
-        <v>1296.544555664062</v>
+        <v>1296.544677734375</v>
       </c>
       <c r="J575" t="n">
         <v>26.95000076293945</v>
@@ -17652,7 +17652,7 @@
         <v>83.69999694824219</v>
       </c>
       <c r="G576" t="n">
-        <v>1416.912963867188</v>
+        <v>1416.9130859375</v>
       </c>
       <c r="H576" t="n">
         <v>176.1999969482422</v>
@@ -17690,7 +17690,7 @@
         <v>166.5500030517578</v>
       </c>
       <c r="I577" t="n">
-        <v>1268.072998046875</v>
+        <v>1268.073120117188</v>
       </c>
       <c r="J577" t="n">
         <v>25.85000038146973</v>
@@ -17716,7 +17716,7 @@
         <v>80</v>
       </c>
       <c r="G578" t="n">
-        <v>1384.775634765625</v>
+        <v>1384.775512695312</v>
       </c>
       <c r="H578" t="n">
         <v>170.75</v>
@@ -17748,7 +17748,7 @@
         <v>80.59999847412109</v>
       </c>
       <c r="G579" t="n">
-        <v>1401.647338867188</v>
+        <v>1401.647216796875</v>
       </c>
       <c r="H579" t="n">
         <v>166.8000030517578</v>
@@ -17812,7 +17812,7 @@
         <v>78</v>
       </c>
       <c r="G581" t="n">
-        <v>1390.654663085938</v>
+        <v>1390.65478515625</v>
       </c>
       <c r="H581" t="n">
         <v>162.9499969482422</v>
@@ -17876,13 +17876,13 @@
         <v>80.25</v>
       </c>
       <c r="G583" t="n">
-        <v>1403.154052734375</v>
+        <v>1403.153930664062</v>
       </c>
       <c r="H583" t="n">
         <v>171.4499969482422</v>
       </c>
       <c r="I583" t="n">
-        <v>1204.901733398438</v>
+        <v>1204.901977539062</v>
       </c>
       <c r="J583" t="n">
         <v>25.60000038146973</v>
@@ -17908,13 +17908,13 @@
         <v>80.5</v>
       </c>
       <c r="G584" t="n">
-        <v>1399.399169921875</v>
+        <v>1399.399291992188</v>
       </c>
       <c r="H584" t="n">
         <v>171.6000061035156</v>
       </c>
       <c r="I584" t="n">
-        <v>1211.426513671875</v>
+        <v>1211.426391601562</v>
       </c>
       <c r="J584" t="n">
         <v>25.79999923706055</v>
@@ -17978,7 +17978,7 @@
         <v>170.1000061035156</v>
       </c>
       <c r="I586" t="n">
-        <v>1220.47216796875</v>
+        <v>1220.472290039062</v>
       </c>
       <c r="J586" t="n">
         <v>26.14999961853027</v>
@@ -18004,7 +18004,7 @@
         <v>80.5</v>
       </c>
       <c r="G587" t="n">
-        <v>1419.012817382812</v>
+        <v>1419.0126953125</v>
       </c>
       <c r="H587" t="n">
         <v>167.8500061035156</v>
@@ -18036,13 +18036,13 @@
         <v>82.25</v>
       </c>
       <c r="G588" t="n">
-        <v>1443.245483398438</v>
+        <v>1443.24560546875</v>
       </c>
       <c r="H588" t="n">
         <v>167.3500061035156</v>
       </c>
       <c r="I588" t="n">
-        <v>1230.011962890625</v>
+        <v>1230.012084960938</v>
       </c>
       <c r="J588" t="n">
         <v>26.5</v>
@@ -18074,7 +18074,7 @@
         <v>166.0500030517578</v>
       </c>
       <c r="I589" t="n">
-        <v>1219.97802734375</v>
+        <v>1219.977905273438</v>
       </c>
       <c r="J589" t="n">
         <v>26.39999961853027</v>
@@ -18138,7 +18138,7 @@
         <v>170</v>
       </c>
       <c r="I591" t="n">
-        <v>1222.053955078125</v>
+        <v>1222.053833007812</v>
       </c>
       <c r="J591" t="n">
         <v>25.29999923706055</v>
@@ -18202,7 +18202,7 @@
         <v>170.5</v>
       </c>
       <c r="I593" t="n">
-        <v>1200.354248046875</v>
+        <v>1200.354125976562</v>
       </c>
       <c r="J593" t="n">
         <v>25.20000076293945</v>
@@ -18234,7 +18234,7 @@
         <v>167.1000061035156</v>
       </c>
       <c r="I594" t="n">
-        <v>1165.16015625</v>
+        <v>1165.160034179688</v>
       </c>
       <c r="J594" t="n">
         <v>24.70000076293945</v>
@@ -18298,7 +18298,7 @@
         <v>173.25</v>
       </c>
       <c r="I596" t="n">
-        <v>1223.04248046875</v>
+        <v>1223.042602539062</v>
       </c>
       <c r="J596" t="n">
         <v>25.75</v>
@@ -18426,7 +18426,7 @@
         <v>167.8000030517578</v>
       </c>
       <c r="I600" t="n">
-        <v>1198.286376953125</v>
+        <v>1198.286254882812</v>
       </c>
       <c r="J600" t="n">
         <v>25</v>
@@ -18484,13 +18484,13 @@
         <v>79.94000244140625</v>
       </c>
       <c r="G602" t="n">
-        <v>1439.31787109375</v>
+        <v>1439.317993164062</v>
       </c>
       <c r="H602" t="n">
         <v>189.3000030517578</v>
       </c>
       <c r="I602" t="n">
-        <v>1350.433959960938</v>
+        <v>1350.433837890625</v>
       </c>
       <c r="J602" t="n">
         <v>28.68000030517578</v>
@@ -18548,7 +18548,7 @@
         <v>84.11000061035156</v>
       </c>
       <c r="G604" t="n">
-        <v>1447.790771484375</v>
+        <v>1447.790649414062</v>
       </c>
       <c r="H604" t="n">
         <v>203.1499938964844</v>
@@ -18612,7 +18612,7 @@
         <v>84.55999755859375</v>
       </c>
       <c r="G606" t="n">
-        <v>1463.377685546875</v>
+        <v>1463.377807617188</v>
       </c>
       <c r="H606" t="n">
         <v>211.0299987792969</v>
@@ -18650,7 +18650,7 @@
         <v>209.8200073242188</v>
       </c>
       <c r="I607" t="n">
-        <v>1320.678833007812</v>
+        <v>1320.678955078125</v>
       </c>
       <c r="J607" t="n">
         <v>30.82999992370605</v>
@@ -18708,13 +18708,13 @@
         <v>83.44999694824219</v>
       </c>
       <c r="G609" t="n">
-        <v>1436.872314453125</v>
+        <v>1436.872436523438</v>
       </c>
       <c r="H609" t="n">
         <v>214.8000030517578</v>
       </c>
       <c r="I609" t="n">
-        <v>1319.93505859375</v>
+        <v>1319.934936523438</v>
       </c>
       <c r="J609" t="n">
         <v>29.8700008392334</v>
@@ -18772,7 +18772,7 @@
         <v>80.86000061035156</v>
       </c>
       <c r="G611" t="n">
-        <v>1436.822998046875</v>
+        <v>1436.822875976562</v>
       </c>
       <c r="H611" t="n">
         <v>208.3999938964844</v>
@@ -18868,7 +18868,7 @@
         <v>79.63999938964844</v>
       </c>
       <c r="G614" t="n">
-        <v>1546.747314453125</v>
+        <v>1546.747436523438</v>
       </c>
       <c r="H614" t="n">
         <v>199.9299926757812</v>
@@ -18938,7 +18938,7 @@
         <v>187.5500030517578</v>
       </c>
       <c r="I616" t="n">
-        <v>1366.005737304688</v>
+        <v>1366.005615234375</v>
       </c>
       <c r="J616" t="n">
         <v>28.70999908447266</v>
@@ -18970,7 +18970,7 @@
         <v>185.7400054931641</v>
       </c>
       <c r="I617" t="n">
-        <v>1360.15380859375</v>
+        <v>1360.153930664062</v>
       </c>
       <c r="J617" t="n">
         <v>28.3799991607666</v>
@@ -19028,7 +19028,7 @@
         <v>85.66999816894531</v>
       </c>
       <c r="G619" t="n">
-        <v>1569.695678710938</v>
+        <v>1569.695556640625</v>
       </c>
       <c r="H619" t="n">
         <v>199.1399993896484</v>
@@ -19066,7 +19066,7 @@
         <v>199.9100036621094</v>
       </c>
       <c r="I620" t="n">
-        <v>1385.098510742188</v>
+        <v>1385.0986328125</v>
       </c>
       <c r="J620" t="n">
         <v>28.32999992370605</v>
@@ -19092,7 +19092,7 @@
         <v>84.80999755859375</v>
       </c>
       <c r="G621" t="n">
-        <v>1571.325927734375</v>
+        <v>1571.326049804688</v>
       </c>
       <c r="H621" t="n">
         <v>196.5800018310547</v>
@@ -19284,7 +19284,7 @@
         <v>80.31999969482422</v>
       </c>
       <c r="G627" t="n">
-        <v>1567.768920898438</v>
+        <v>1567.76904296875</v>
       </c>
       <c r="H627" t="n">
         <v>188</v>
@@ -19322,7 +19322,7 @@
         <v>181.7400054931641</v>
       </c>
       <c r="I628" t="n">
-        <v>1227.396728515625</v>
+        <v>1227.396606445312</v>
       </c>
       <c r="J628" t="n">
         <v>27.1200008392334</v>
@@ -19386,7 +19386,7 @@
         <v>175.1699981689453</v>
       </c>
       <c r="I630" t="n">
-        <v>1242.422973632812</v>
+        <v>1242.423095703125</v>
       </c>
       <c r="J630" t="n">
         <v>26.94000053405762</v>
@@ -19508,7 +19508,7 @@
         <v>93.55999755859375</v>
       </c>
       <c r="G634" t="n">
-        <v>1501.987182617188</v>
+        <v>1501.987060546875</v>
       </c>
       <c r="H634" t="n">
         <v>199.3699951171875</v>
@@ -19572,7 +19572,7 @@
         <v>98.19999694824219</v>
       </c>
       <c r="G636" t="n">
-        <v>1487.486938476562</v>
+        <v>1487.487060546875</v>
       </c>
       <c r="H636" t="n">
         <v>207.1699981689453</v>
@@ -19610,7 +19610,7 @@
         <v>214.4400024414062</v>
       </c>
       <c r="I637" t="n">
-        <v>1270.4423828125</v>
+        <v>1270.442260742188</v>
       </c>
       <c r="J637" t="n">
         <v>32.90000152587891</v>
@@ -19636,13 +19636,13 @@
         <v>93.27999877929688</v>
       </c>
       <c r="G638" t="n">
-        <v>1481.459716796875</v>
+        <v>1481.459594726562</v>
       </c>
       <c r="H638" t="n">
         <v>215.7200012207031</v>
       </c>
       <c r="I638" t="n">
-        <v>1249.117797851562</v>
+        <v>1249.117919921875</v>
       </c>
       <c r="J638" t="n">
         <v>34.54000091552734</v>
@@ -19738,7 +19738,7 @@
         <v>214.0500030517578</v>
       </c>
       <c r="I641" t="n">
-        <v>1203.344604492188</v>
+        <v>1203.3447265625</v>
       </c>
       <c r="J641" t="n">
         <v>31.86000061035156</v>
@@ -19802,7 +19802,7 @@
         <v>230.0200042724609</v>
       </c>
       <c r="I643" t="n">
-        <v>1192.236083984375</v>
+        <v>1192.236206054688</v>
       </c>
       <c r="J643" t="n">
         <v>32.31999969482422</v>
@@ -19828,7 +19828,7 @@
         <v>96.81999969482422</v>
       </c>
       <c r="G644" t="n">
-        <v>1443.220825195312</v>
+        <v>1443.220703125</v>
       </c>
       <c r="H644" t="n">
         <v>226.0599975585938</v>
@@ -19892,13 +19892,13 @@
         <v>93.84999847412109</v>
       </c>
       <c r="G646" t="n">
-        <v>1444.43115234375</v>
+        <v>1444.431274414062</v>
       </c>
       <c r="H646" t="n">
         <v>220.2799987792969</v>
       </c>
       <c r="I646" t="n">
-        <v>1131.684448242188</v>
+        <v>1131.6845703125</v>
       </c>
       <c r="J646" t="n">
         <v>29.75</v>
@@ -19924,7 +19924,7 @@
         <v>95.01000213623047</v>
       </c>
       <c r="G647" t="n">
-        <v>1460.586303710938</v>
+        <v>1460.58642578125</v>
       </c>
       <c r="H647" t="n">
         <v>217.9700012207031</v>
@@ -19962,7 +19962,7 @@
         <v>225.7100067138672</v>
       </c>
       <c r="I648" t="n">
-        <v>1198.087890625</v>
+        <v>1198.087768554688</v>
       </c>
       <c r="J648" t="n">
         <v>32.79000091552734</v>
@@ -20026,7 +20026,7 @@
         <v>243.1000061035156</v>
       </c>
       <c r="I650" t="n">
-        <v>1205.47705078125</v>
+        <v>1205.477172851562</v>
       </c>
       <c r="J650" t="n">
         <v>36.13999938964844</v>
@@ -20122,7 +20122,7 @@
         <v>206.75</v>
       </c>
       <c r="I653" t="n">
-        <v>1203.344604492188</v>
+        <v>1203.3447265625</v>
       </c>
       <c r="J653" t="n">
         <v>32.75</v>
@@ -20218,7 +20218,7 @@
         <v>212.25</v>
       </c>
       <c r="I656" t="n">
-        <v>1204.435546875</v>
+        <v>1204.435668945312</v>
       </c>
       <c r="J656" t="n">
         <v>30.56999969482422</v>
@@ -20442,7 +20442,7 @@
         <v>211.75</v>
       </c>
       <c r="I663" t="n">
-        <v>1144.380126953125</v>
+        <v>1144.380004882812</v>
       </c>
       <c r="J663" t="n">
         <v>29.71999931335449</v>
@@ -20698,7 +20698,7 @@
         <v>284.8900146484375</v>
       </c>
       <c r="I671" t="n">
-        <v>1130.39501953125</v>
+        <v>1130.395141601562</v>
       </c>
       <c r="J671" t="n">
         <v>34.61000061035156</v>
@@ -20826,7 +20826,7 @@
         <v>335.1600036621094</v>
       </c>
       <c r="I675" t="n">
-        <v>1262.408569335938</v>
+        <v>1262.408447265625</v>
       </c>
       <c r="J675" t="n">
         <v>42.04999923706055</v>
@@ -20890,7 +20890,7 @@
         <v>322.9500122070312</v>
       </c>
       <c r="I677" t="n">
-        <v>1261.962036132812</v>
+        <v>1261.962158203125</v>
       </c>
       <c r="J677" t="n">
         <v>46.34999847412109</v>
@@ -20954,7 +20954,7 @@
         <v>332</v>
       </c>
       <c r="I679" t="n">
-        <v>1235.876831054688</v>
+        <v>1235.876953125</v>
       </c>
       <c r="J679" t="n">
         <v>51.09000015258789</v>
@@ -21082,7 +21082,7 @@
         <v>299.5</v>
       </c>
       <c r="I683" t="n">
-        <v>1158.860717773438</v>
+        <v>1158.86083984375</v>
       </c>
       <c r="J683" t="n">
         <v>45.97999954223633</v>
@@ -21306,7 +21306,7 @@
         <v>277.9500122070312</v>
       </c>
       <c r="I690" t="n">
-        <v>1192.781616210938</v>
+        <v>1192.781494140625</v>
       </c>
       <c r="J690" t="n">
         <v>41.7400016784668</v>
@@ -21402,7 +21402,7 @@
         <v>254.5500030517578</v>
       </c>
       <c r="I693" t="n">
-        <v>1128.808227539062</v>
+        <v>1128.80810546875</v>
       </c>
       <c r="J693" t="n">
         <v>38.43000030517578</v>
@@ -21434,7 +21434,7 @@
         <v>267.25</v>
       </c>
       <c r="I694" t="n">
-        <v>1138.924926757812</v>
+        <v>1138.925048828125</v>
       </c>
       <c r="J694" t="n">
         <v>40.34999847412109</v>
@@ -21658,7 +21658,7 @@
         <v>291.0499877929688</v>
       </c>
       <c r="I701" t="n">
-        <v>1116.360717773438</v>
+        <v>1116.360595703125</v>
       </c>
       <c r="J701" t="n">
         <v>43.02999877929688</v>
@@ -21786,7 +21786,7 @@
         <v>288.25</v>
       </c>
       <c r="I705" t="n">
-        <v>1128.4609375</v>
+        <v>1128.461059570312</v>
       </c>
       <c r="J705" t="n">
         <v>43.77000045776367</v>
@@ -21850,7 +21850,7 @@
         <v>260.6000061035156</v>
       </c>
       <c r="I707" t="n">
-        <v>1073.166137695312</v>
+        <v>1073.166259765625</v>
       </c>
       <c r="J707" t="n">
         <v>39.5</v>
@@ -22138,7 +22138,7 @@
         <v>271.75</v>
       </c>
       <c r="I716" t="n">
-        <v>1131.287719726562</v>
+        <v>1131.287841796875</v>
       </c>
       <c r="J716" t="n">
         <v>36.31000137329102</v>
@@ -22266,7 +22266,7 @@
         <v>274.0499877929688</v>
       </c>
       <c r="I720" t="n">
-        <v>1195.409912109375</v>
+        <v>1195.410034179688</v>
       </c>
       <c r="J720" t="n">
         <v>38.86999893188477</v>
@@ -22298,7 +22298,7 @@
         <v>281.3999938964844</v>
       </c>
       <c r="I721" t="n">
-        <v>1192.781616210938</v>
+        <v>1192.781494140625</v>
       </c>
       <c r="J721" t="n">
         <v>39.13999938964844</v>
@@ -22330,7 +22330,7 @@
         <v>295.4500122070312</v>
       </c>
       <c r="I722" t="n">
-        <v>1207.113647460938</v>
+        <v>1207.11376953125</v>
       </c>
       <c r="J722" t="n">
         <v>41.09000015258789</v>
@@ -22362,7 +22362,7 @@
         <v>302.1499938964844</v>
       </c>
       <c r="I723" t="n">
-        <v>1191.0458984375</v>
+        <v>1191.045776367188</v>
       </c>
       <c r="J723" t="n">
         <v>43.13999938964844</v>
@@ -22426,7 +22426,7 @@
         <v>298.3500061035156</v>
       </c>
       <c r="I725" t="n">
-        <v>1185.14453125</v>
+        <v>1185.144409179688</v>
       </c>
       <c r="J725" t="n">
         <v>44.38999938964844</v>
@@ -22618,7 +22618,7 @@
         <v>286.7000122070312</v>
       </c>
       <c r="I731" t="n">
-        <v>1144.231201171875</v>
+        <v>1144.231323242188</v>
       </c>
       <c r="J731" t="n">
         <v>46.70999908447266</v>
@@ -22714,7 +22714,7 @@
         <v>290.2999877929688</v>
       </c>
       <c r="I734" t="n">
-        <v>1070.240234375</v>
+        <v>1070.240356445312</v>
       </c>
       <c r="J734" t="n">
         <v>44.75</v>
@@ -22810,7 +22810,7 @@
         <v>302.1499938964844</v>
       </c>
       <c r="I737" t="n">
-        <v>1035.972412109375</v>
+        <v>1035.972290039062</v>
       </c>
       <c r="J737" t="n">
         <v>44.13000106811523</v>
@@ -22874,7 +22874,7 @@
         <v>297.0499877929688</v>
       </c>
       <c r="I739" t="n">
-        <v>1085.81201171875</v>
+        <v>1085.812133789062</v>
       </c>
       <c r="J739" t="n">
         <v>41.84999847412109</v>
@@ -22906,7 +22906,7 @@
         <v>304.1499938964844</v>
       </c>
       <c r="I740" t="n">
-        <v>1074.157958984375</v>
+        <v>1074.158081054688</v>
       </c>
       <c r="J740" t="n">
         <v>42.59999847412109</v>
@@ -22938,7 +22938,7 @@
         <v>319.2000122070312</v>
       </c>
       <c r="I741" t="n">
-        <v>1075.348266601562</v>
+        <v>1075.34814453125</v>
       </c>
       <c r="J741" t="n">
         <v>44.72999954223633</v>
@@ -23098,7 +23098,7 @@
         <v>302.1499938964844</v>
       </c>
       <c r="I746" t="n">
-        <v>1107.731689453125</v>
+        <v>1107.731567382812</v>
       </c>
       <c r="J746" t="n">
         <v>42.38000106811523</v>
@@ -23130,7 +23130,7 @@
         <v>287.0499877929688</v>
       </c>
       <c r="I747" t="n">
-        <v>1079.563598632812</v>
+        <v>1079.5634765625</v>
       </c>
       <c r="J747" t="n">
         <v>40.2599983215332</v>
@@ -23290,7 +23290,7 @@
         <v>279.2999877929688</v>
       </c>
       <c r="I752" t="n">
-        <v>1016.433227539062</v>
+        <v>1016.433288574219</v>
       </c>
       <c r="J752" t="n">
         <v>41.20000076293945</v>
@@ -23354,7 +23354,7 @@
         <v>280.9500122070312</v>
       </c>
       <c r="I754" t="n">
-        <v>1028.682495117188</v>
+        <v>1028.682373046875</v>
       </c>
       <c r="J754" t="n">
         <v>40.77999877929688</v>
@@ -23546,7 +23546,7 @@
         <v>240.6000061035156</v>
       </c>
       <c r="I760" t="n">
-        <v>913.7286376953125</v>
+        <v>913.7285766601562</v>
       </c>
       <c r="J760" t="n">
         <v>36.84999847412109</v>
@@ -23578,7 +23578,7 @@
         <v>248.25</v>
       </c>
       <c r="I761" t="n">
-        <v>942.98779296875</v>
+        <v>942.9877319335938</v>
       </c>
       <c r="J761" t="n">
         <v>38.65000152587891</v>
@@ -23706,7 +23706,7 @@
         <v>234.0500030517578</v>
       </c>
       <c r="I765" t="n">
-        <v>932.4743041992188</v>
+        <v>932.474365234375</v>
       </c>
       <c r="J765" t="n">
         <v>38</v>
@@ -23834,7 +23834,7 @@
         <v>286.5</v>
       </c>
       <c r="I769" t="n">
-        <v>945.6657104492188</v>
+        <v>945.665771484375</v>
       </c>
       <c r="J769" t="n">
         <v>41.84000015258789</v>
@@ -23866,7 +23866,7 @@
         <v>284.4500122070312</v>
       </c>
       <c r="I770" t="n">
-        <v>928.30859375</v>
+        <v>928.3086547851562</v>
       </c>
       <c r="J770" t="n">
         <v>41</v>
@@ -23930,7 +23930,7 @@
         <v>266.7999877929688</v>
       </c>
       <c r="I772" t="n">
-        <v>890.4204711914062</v>
+        <v>890.4205322265625</v>
       </c>
       <c r="J772" t="n">
         <v>39.45000076293945</v>
@@ -23962,7 +23962,7 @@
         <v>266.7000122070312</v>
       </c>
       <c r="I773" t="n">
-        <v>898.1567993164062</v>
+        <v>898.15673828125</v>
       </c>
       <c r="J773" t="n">
         <v>39.56000137329102</v>
@@ -24026,7 +24026,7 @@
         <v>244.3500061035156</v>
       </c>
       <c r="I775" t="n">
-        <v>836.2662353515625</v>
+        <v>836.2662963867188</v>
       </c>
       <c r="J775" t="n">
         <v>36.93999862670898</v>
@@ -24058,7 +24058,7 @@
         <v>248.6000061035156</v>
       </c>
       <c r="I776" t="n">
-        <v>815.83447265625</v>
+        <v>815.8344116210938</v>
       </c>
       <c r="J776" t="n">
         <v>36.77999877929688</v>
@@ -24186,7 +24186,7 @@
         <v>240.8000030517578</v>
       </c>
       <c r="I780" t="n">
-        <v>826.000732421875</v>
+        <v>826.0007934570312</v>
       </c>
       <c r="J780" t="n">
         <v>36.79999923706055</v>
@@ -24250,7 +24250,7 @@
         <v>222.9499969482422</v>
       </c>
       <c r="I782" t="n">
-        <v>815.884033203125</v>
+        <v>815.8839721679688</v>
       </c>
       <c r="J782" t="n">
         <v>34.75</v>
@@ -24282,7 +24282,7 @@
         <v>211.9499969482422</v>
       </c>
       <c r="I783" t="n">
-        <v>781.3681030273438</v>
+        <v>781.3681640625</v>
       </c>
       <c r="J783" t="n">
         <v>33.2599983215332</v>
@@ -24442,7 +24442,7 @@
         <v>239.3500061035156</v>
       </c>
       <c r="I788" t="n">
-        <v>835.6215209960938</v>
+        <v>835.62158203125</v>
       </c>
       <c r="J788" t="n">
         <v>36.04000091552734</v>
@@ -24570,7 +24570,7 @@
         <v>218.4400024414062</v>
       </c>
       <c r="I792" t="n">
-        <v>780.9217529296875</v>
+        <v>780.9218139648438</v>
       </c>
       <c r="J792" t="n">
         <v>33.38999938964844</v>
@@ -24602,7 +24602,7 @@
         <v>219.3800048828125</v>
       </c>
       <c r="I793" t="n">
-        <v>770.3588256835938</v>
+        <v>770.3587646484375</v>
       </c>
       <c r="J793" t="n">
         <v>33.02000045776367</v>
@@ -24634,7 +24634,7 @@
         <v>219.3800048828125</v>
       </c>
       <c r="I794" t="n">
-        <v>770.3588256835938</v>
+        <v>770.3587646484375</v>
       </c>
       <c r="J794" t="n">
         <v>33.02000045776367</v>
@@ -24826,7 +24826,7 @@
         <v>253.7799987792969</v>
       </c>
       <c r="I800" t="n">
-        <v>802.4942016601562</v>
+        <v>802.4942626953125</v>
       </c>
       <c r="J800" t="n">
         <v>39.47000122070312</v>
@@ -24954,7 +24954,7 @@
         <v>257.2000122070312</v>
       </c>
       <c r="I804" t="n">
-        <v>811.1231689453125</v>
+        <v>811.1232299804688</v>
       </c>
       <c r="J804" t="n">
         <v>42.31000137329102</v>
@@ -24986,7 +24986,7 @@
         <v>262.25</v>
       </c>
       <c r="I805" t="n">
-        <v>818.7603149414062</v>
+        <v>818.7603759765625</v>
       </c>
       <c r="J805" t="n">
         <v>43.15999984741211</v>
@@ -25018,7 +25018,7 @@
         <v>250.3500061035156</v>
       </c>
       <c r="I806" t="n">
-        <v>788.6085205078125</v>
+        <v>788.6085815429688</v>
       </c>
       <c r="J806" t="n">
         <v>41.34999847412109</v>
@@ -25114,7 +25114,7 @@
         <v>243.75</v>
       </c>
       <c r="I809" t="n">
-        <v>774.7228393554688</v>
+        <v>774.7227783203125</v>
       </c>
       <c r="J809" t="n">
         <v>39</v>
@@ -25210,7 +25210,7 @@
         <v>253.1999969482422</v>
       </c>
       <c r="I812" t="n">
-        <v>832.89404296875</v>
+        <v>832.8939819335938</v>
       </c>
       <c r="J812" t="n">
         <v>41.83000183105469</v>
@@ -25338,7 +25338,7 @@
         <v>266.25</v>
       </c>
       <c r="I816" t="n">
-        <v>866.1205444335938</v>
+        <v>866.1204833984375</v>
       </c>
       <c r="J816" t="n">
         <v>43.52999877929688</v>
@@ -25402,7 +25402,7 @@
         <v>256.8999938964844</v>
       </c>
       <c r="I818" t="n">
-        <v>844.3992309570312</v>
+        <v>844.3992919921875</v>
       </c>
       <c r="J818" t="n">
         <v>41.36000061035156</v>
@@ -25434,7 +25434,7 @@
         <v>255.3000030517578</v>
       </c>
       <c r="I819" t="n">
-        <v>861.706787109375</v>
+        <v>861.7068481445312</v>
       </c>
       <c r="J819" t="n">
         <v>41.36000061035156</v>
@@ -25466,7 +25466,7 @@
         <v>256.7000122070312</v>
       </c>
       <c r="I820" t="n">
-        <v>865.0294799804688</v>
+        <v>865.029541015625</v>
       </c>
       <c r="J820" t="n">
         <v>41.0099983215332</v>
@@ -25530,7 +25530,7 @@
         <v>251.75</v>
       </c>
       <c r="I822" t="n">
-        <v>849.7056884765625</v>
+        <v>849.7056274414062</v>
       </c>
       <c r="J822" t="n">
         <v>40.22999954223633</v>
@@ -25594,7 +25594,7 @@
         <v>236.3500061035156</v>
       </c>
       <c r="I824" t="n">
-        <v>841.027099609375</v>
+        <v>841.0270385742188</v>
       </c>
       <c r="J824" t="n">
         <v>38.25</v>
@@ -25882,7 +25882,7 @@
         <v>279.5</v>
       </c>
       <c r="I833" t="n">
-        <v>921.0186157226562</v>
+        <v>921.0185546875</v>
       </c>
       <c r="J833" t="n">
         <v>45.68999862670898</v>
@@ -25914,7 +25914,7 @@
         <v>274.6499938964844</v>
       </c>
       <c r="I834" t="n">
-        <v>912.092041015625</v>
+        <v>912.0921020507812</v>
       </c>
       <c r="J834" t="n">
         <v>44.72999954223633</v>
@@ -26106,7 +26106,7 @@
         <v>308.2999877929688</v>
       </c>
       <c r="I840" t="n">
-        <v>920.7705688476562</v>
+        <v>920.7706298828125</v>
       </c>
       <c r="J840" t="n">
         <v>50.43000030517578</v>
@@ -26266,7 +26266,7 @@
         <v>380.6000061035156</v>
       </c>
       <c r="I845" t="n">
-        <v>941.9464111328125</v>
+        <v>941.9463500976562</v>
       </c>
       <c r="J845" t="n">
         <v>60.93000030517578</v>
@@ -26458,7 +26458,7 @@
         <v>395.4500122070312</v>
       </c>
       <c r="I851" t="n">
-        <v>992.3811645507812</v>
+        <v>992.3812255859375</v>
       </c>
       <c r="J851" t="n">
         <v>69.72000122070312</v>
@@ -26490,7 +26490,7 @@
         <v>384.5499877929688</v>
       </c>
       <c r="I852" t="n">
-        <v>967.08935546875</v>
+        <v>967.0894165039062</v>
       </c>
       <c r="J852" t="n">
         <v>67.05000305175781</v>
@@ -36514,34 +36514,98 @@
     </row>
     <row r="1166">
       <c r="A1166" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1166" t="n">
+        <v>7.360000133514404</v>
+      </c>
+      <c r="C1166" t="n">
+        <v>26.97999954223633</v>
+      </c>
+      <c r="D1166" t="n">
+        <v>10.22999954223633</v>
+      </c>
+      <c r="E1166" t="n">
+        <v>229.8999938964844</v>
+      </c>
+      <c r="F1166" t="n">
+        <v>26.63999938964844</v>
+      </c>
+      <c r="G1166" t="n">
+        <v>1257.5</v>
+      </c>
+      <c r="H1166" t="n">
+        <v>53.65999984741211</v>
+      </c>
+      <c r="I1166" t="n">
+        <v>710.75</v>
+      </c>
+      <c r="J1166" t="n">
+        <v>21.57999992370605</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="2" t="n">
         <v>46280</v>
       </c>
-      <c r="B1166" t="n">
+      <c r="B1167" t="n">
         <v>7.380000114440918</v>
       </c>
-      <c r="C1166" t="n">
+      <c r="C1167" t="n">
         <v>26.6200008392334</v>
       </c>
-      <c r="D1166" t="n">
+      <c r="D1167" t="n">
         <v>9.949999809265137</v>
       </c>
-      <c r="E1166" t="n">
+      <c r="E1167" t="n">
         <v>225.6000061035156</v>
       </c>
-      <c r="F1166" t="n">
+      <c r="F1167" t="n">
         <v>25.95000076293945</v>
       </c>
-      <c r="G1166" t="n">
+      <c r="G1167" t="n">
         <v>1235.300048828125</v>
       </c>
-      <c r="H1166" t="n">
+      <c r="H1167" t="n">
         <v>52.59000015258789</v>
       </c>
-      <c r="I1166" t="n">
+      <c r="I1167" t="n">
         <v>697.25</v>
       </c>
-      <c r="J1166" t="n">
+      <c r="J1167" t="n">
         <v>21.03000068664551</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1168" t="n">
+        <v>7.480000019073486</v>
+      </c>
+      <c r="C1168" t="n">
+        <v>26.42000007629395</v>
+      </c>
+      <c r="D1168" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1168" t="n">
+        <v>224.8399963378906</v>
+      </c>
+      <c r="F1168" t="n">
+        <v>26.1200008392334</v>
+      </c>
+      <c r="G1168" t="n">
+        <v>1240</v>
+      </c>
+      <c r="H1168" t="n">
+        <v>51.54000091552734</v>
+      </c>
+      <c r="I1168" t="n">
+        <v>693.6500244140625</v>
+      </c>
+      <c r="J1168" t="n">
+        <v>20.78000068664551</v>
       </c>
     </row>
   </sheetData>
@@ -36615,31 +36679,31 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-13.17646924187156</v>
+        <v>-11.99999977560604</v>
       </c>
       <c r="C2" t="n">
-        <v>-5.836574431597297</v>
+        <v>-6.544040861384803</v>
       </c>
       <c r="D2" t="n">
-        <v>-6.484967216101967</v>
+        <v>-6.015040626614199</v>
       </c>
       <c r="E2" t="n">
-        <v>-6.525792252619533</v>
+        <v>-6.840691671059584</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.700693355912378</v>
+        <v>-4.076381644007066</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.265462112128037</v>
+        <v>-2.8974158183242</v>
       </c>
       <c r="H2" t="n">
-        <v>-11.44973784634484</v>
+        <v>-13.21771098635393</v>
       </c>
       <c r="I2" t="n">
-        <v>-7.336037120276284</v>
+        <v>-7.814470973360866</v>
       </c>
       <c r="J2" t="n">
-        <v>-4.798548929924751</v>
+        <v>-5.930282738313664</v>
       </c>
     </row>
     <row r="3">
@@ -37212,7 +37276,7 @@
         <v>22.02878904102883</v>
       </c>
       <c r="I20" t="n">
-        <v>2.551418984708165</v>
+        <v>2.551410974090174</v>
       </c>
       <c r="J20" t="n">
         <v>29.22429859056908</v>
@@ -37244,7 +37308,7 @@
         <v>-15.42298811409775</v>
       </c>
       <c r="I21" t="n">
-        <v>-18.75000158667417</v>
+        <v>-18.74999523997749</v>
       </c>
       <c r="J21" t="n">
         <v>-17.03667200064552</v>
@@ -37276,7 +37340,7 @@
         <v>-17.60644052854861</v>
       </c>
       <c r="I22" t="n">
-        <v>-10.47091074017598</v>
+        <v>-10.47092091451074</v>
       </c>
       <c r="J22" t="n">
         <v>-5.892015050324451</v>
@@ -37308,7 +37372,7 @@
         <v>8.975273108262826</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.731635275646898</v>
+        <v>-7.731624790012059</v>
       </c>
       <c r="J23" t="n">
         <v>10.07751326691555</v>
@@ -37430,7 +37494,7 @@
         <v>-3.095716273530114</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6193430171434144</v>
+        <v>0.6193347598382193</v>
       </c>
       <c r="H27" t="n">
         <v>0.9847026900382971</v>
@@ -37462,7 +37526,7 @@
         <v>23.30486903670943</v>
       </c>
       <c r="G28" t="n">
-        <v>-3.831290051246339</v>
+        <v>-3.831289748878441</v>
       </c>
       <c r="H28" t="n">
         <v>3.621270323810255</v>
@@ -37494,7 +37558,7 @@
         <v>-0.3254094258637208</v>
       </c>
       <c r="G29" t="n">
-        <v>9.437907214178898</v>
+        <v>9.437915851090327</v>
       </c>
       <c r="H29" t="n">
         <v>20.18634526010754</v>
@@ -37532,7 +37596,7 @@
         <v>-6.49240482812462</v>
       </c>
       <c r="I30" t="n">
-        <v>-10.79030993178678</v>
+        <v>-10.79030161697194</v>
       </c>
       <c r="J30" t="n">
         <v>-10.07326035477244</v>
@@ -37564,7 +37628,7 @@
         <v>-34.34213475489638</v>
       </c>
       <c r="I31" t="n">
-        <v>3.869230754336672</v>
+        <v>3.869231128923167</v>
       </c>
       <c r="J31" t="n">
         <v>-3.36283455907771</v>
@@ -37590,13 +37654,13 @@
         <v>-19.4392551885587</v>
       </c>
       <c r="G32" t="n">
-        <v>1.714801795153398</v>
+        <v>1.714793192957242</v>
       </c>
       <c r="H32" t="n">
         <v>22.65731991554547</v>
       </c>
       <c r="I32" t="n">
-        <v>-10.22067742088289</v>
+        <v>-10.22068611256335</v>
       </c>
       <c r="J32" t="n">
         <v>16.73553350982875</v>
@@ -37622,7 +37686,7 @@
         <v>-8.54700854700855</v>
       </c>
       <c r="G33" t="n">
-        <v>2.395516458058666</v>
+        <v>2.395533985038512</v>
       </c>
       <c r="H33" t="n">
         <v>-4.392992435061648</v>
@@ -37654,13 +37718,13 @@
         <v>33.94390617495342</v>
       </c>
       <c r="G34" t="n">
-        <v>10.37930970539087</v>
+        <v>10.37930014680082</v>
       </c>
       <c r="H34" t="n">
         <v>10.12869384694794</v>
       </c>
       <c r="I34" t="n">
-        <v>4.617430052899274</v>
+        <v>4.61743963491108</v>
       </c>
       <c r="J34" t="n">
         <v>27.89699662161886</v>
@@ -37686,13 +37750,13 @@
         <v>0.9243158800178009</v>
       </c>
       <c r="G35" t="n">
-        <v>8.727830237407975</v>
+        <v>8.727841537326796</v>
       </c>
       <c r="H35" t="n">
         <v>10.5665365226655</v>
       </c>
       <c r="I35" t="n">
-        <v>23.11872269028099</v>
+        <v>23.11872529727841</v>
       </c>
       <c r="J35" t="n">
         <v>10.16548301327902</v>
@@ -37718,13 +37782,13 @@
         <v>26.90616851118288</v>
       </c>
       <c r="G36" t="n">
-        <v>3.914078129935761</v>
+        <v>3.914067330304039</v>
       </c>
       <c r="H36" t="n">
         <v>12.11225997045791</v>
       </c>
       <c r="I36" t="n">
-        <v>8.906462181414131</v>
+        <v>8.906449900509328</v>
       </c>
       <c r="J36" t="n">
         <v>23.68420553633026</v>
@@ -37750,13 +37814,13 @@
         <v>6.812840372868889</v>
       </c>
       <c r="G37" t="n">
-        <v>-2.434960064459102</v>
+        <v>-2.434970344559451</v>
       </c>
       <c r="H37" t="n">
         <v>-2.336989602099571</v>
       </c>
       <c r="I37" t="n">
-        <v>4.511212139064336</v>
+        <v>4.51120543209822</v>
       </c>
       <c r="J37" t="n">
         <v>-11.16882918717025</v>
@@ -37782,13 +37846,13 @@
         <v>-6.583760205501399</v>
       </c>
       <c r="G38" t="n">
-        <v>-2.575820489355185</v>
+        <v>-2.575810224095743</v>
       </c>
       <c r="H38" t="n">
         <v>-7.202140266796353</v>
       </c>
       <c r="I38" t="n">
-        <v>-5.426402131851338</v>
+        <v>-5.426390322743146</v>
       </c>
       <c r="J38" t="n">
         <v>0.5221952138994457</v>
@@ -37811,13 +37875,13 @@
         <v>17.33905317445681</v>
       </c>
       <c r="G39" t="n">
-        <v>-5.246546247677264</v>
+        <v>-5.246537031303699</v>
       </c>
       <c r="H39" t="n">
         <v>-1.111996841749918</v>
       </c>
       <c r="I39" t="n">
-        <v>4.90358226696832</v>
+        <v>4.903569221099491</v>
       </c>
       <c r="J39" t="n">
         <v>16.41336614204727</v>
@@ -37840,13 +37904,13 @@
         <v>-7.245221803084723</v>
       </c>
       <c r="G40" t="n">
-        <v>8.299913357895106</v>
+        <v>8.299902823900585</v>
       </c>
       <c r="H40" t="n">
         <v>36.60036607849231</v>
       </c>
       <c r="I40" t="n">
-        <v>1.693675739617384</v>
+        <v>1.693675629957525</v>
       </c>
       <c r="J40" t="n">
         <v>17.08185437454475</v>
@@ -37869,13 +37933,13 @@
         <v>2.446982085920046</v>
       </c>
       <c r="G41" t="n">
-        <v>3.25318376876691</v>
+        <v>3.253172538244864</v>
       </c>
       <c r="H41" t="n">
         <v>2.635488591081314</v>
       </c>
       <c r="I41" t="n">
-        <v>5.350306184701781</v>
+        <v>5.350313005783192</v>
       </c>
       <c r="J41" t="n">
         <v>8.494211565028188</v>
@@ -37898,7 +37962,7 @@
         <v>5.598621951273208</v>
       </c>
       <c r="G42" t="n">
-        <v>2.040877935444163</v>
+        <v>2.040900359286013</v>
       </c>
       <c r="H42" t="n">
         <v>-14.50333586855534</v>
@@ -37927,7 +37991,7 @@
         <v>7.004606888590881</v>
       </c>
       <c r="G43" t="n">
-        <v>3.837343764441714</v>
+        <v>3.837320273090516</v>
       </c>
       <c r="H43" t="n">
         <v>9.220106101738512</v>
@@ -37956,13 +38020,13 @@
         <v>-7.106166810697612</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3659714981767426</v>
+        <v>0.3659830649118234</v>
       </c>
       <c r="H44" t="n">
         <v>10.36725582872331</v>
       </c>
       <c r="I44" t="n">
-        <v>-2.506406170323727</v>
+        <v>-2.506398636647234</v>
       </c>
       <c r="J44" t="n">
         <v>1.53060832255989</v>
@@ -37985,13 +38049,13 @@
         <v>-5.117786759101961</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.329720456261541</v>
+        <v>-1.329731717430038</v>
       </c>
       <c r="H45" t="n">
         <v>4.476417699780821</v>
       </c>
       <c r="I45" t="n">
-        <v>-7.82183605157546</v>
+        <v>-7.821843174509246</v>
       </c>
       <c r="J45" t="n">
         <v>-23.13725340600107</v>
@@ -38014,13 +38078,13 @@
         <v>-6.883508838267105</v>
       </c>
       <c r="G46" t="n">
-        <v>-7.590700042745402</v>
+        <v>-7.590679750087537</v>
       </c>
       <c r="H46" t="n">
         <v>-9.150325892060184</v>
       </c>
       <c r="I46" t="n">
-        <v>-7.873138437038474</v>
+        <v>-7.873132391548731</v>
       </c>
       <c r="J46" t="n">
         <v>-11.14982814589901</v>
@@ -38043,13 +38107,13 @@
         <v>-2.865546642449923</v>
       </c>
       <c r="G47" t="n">
-        <v>-6.742090228748266</v>
+        <v>-6.742100064294965</v>
       </c>
       <c r="H47" t="n">
         <v>-12.68230842551258</v>
       </c>
       <c r="I47" t="n">
-        <v>-10.50510455831967</v>
+        <v>-10.50512094276369</v>
       </c>
       <c r="J47" t="n">
         <v>-10.59189368473866</v>
@@ -38072,13 +38136,13 @@
         <v>6.079503403138031</v>
       </c>
       <c r="G48" t="n">
-        <v>7.128581444439974</v>
+        <v>7.128570156643566</v>
       </c>
       <c r="H48" t="n">
         <v>11.48815860769938</v>
       </c>
       <c r="I48" t="n">
-        <v>-3.90674987660834</v>
+        <v>-3.906738589925352</v>
       </c>
       <c r="J48" t="n">
         <v>-0.3105661069842447</v>
@@ -38101,7 +38165,7 @@
         <v>-0.696589719615015</v>
       </c>
       <c r="G49" t="n">
-        <v>7.227408916932054</v>
+        <v>7.227420215142799</v>
       </c>
       <c r="H49" t="n">
         <v>3.474762330681291</v>
@@ -38136,7 +38200,7 @@
         <v>-15.6172858344184</v>
       </c>
       <c r="I50" t="n">
-        <v>5.378686357567153</v>
+        <v>5.378692749161718</v>
       </c>
       <c r="J50" t="n">
         <v>-2.380950218425493</v>
@@ -38159,13 +38223,13 @@
         <v>8.782737772308536</v>
       </c>
       <c r="G51" t="n">
-        <v>5.463643374052984</v>
+        <v>5.463632047055778</v>
       </c>
       <c r="H51" t="n">
         <v>38.34329813061588</v>
       </c>
       <c r="I51" t="n">
-        <v>4.312852371434839</v>
+        <v>4.312852644306764</v>
       </c>
       <c r="J51" t="n">
         <v>35.48386898298783</v>
@@ -38188,13 +38252,13 @@
         <v>-5.942026774088538</v>
       </c>
       <c r="G52" t="n">
-        <v>-3.320959644468446</v>
+        <v>-3.320959299636128</v>
       </c>
       <c r="H52" t="n">
         <v>29.24944861623748</v>
       </c>
       <c r="I52" t="n">
-        <v>3.064815751886085</v>
+        <v>3.064809231029253</v>
       </c>
       <c r="J52" t="n">
         <v>7.826083639393677</v>
@@ -38217,13 +38281,13 @@
         <v>-8.609271523178808</v>
       </c>
       <c r="G53" t="n">
-        <v>-1.405415476974137</v>
+        <v>-1.405405239390534</v>
       </c>
       <c r="H53" t="n">
         <v>-16.0722547147822</v>
       </c>
       <c r="I53" t="n">
-        <v>2.955471852145508</v>
+        <v>2.955464940149111</v>
       </c>
       <c r="J53" t="n">
         <v>-8.730161493387333</v>
@@ -38252,7 +38316,7 @@
         <v>-12.62647164563844</v>
       </c>
       <c r="I54" t="n">
-        <v>-16.35936109340738</v>
+        <v>-16.35934608481275</v>
       </c>
       <c r="J54" t="n">
         <v>-11.57894469144052</v>
@@ -38275,13 +38339,13 @@
         <v>1.233112628945943</v>
       </c>
       <c r="G55" t="n">
-        <v>5.901896555568986</v>
+        <v>5.90190738872356</v>
       </c>
       <c r="H55" t="n">
         <v>10.01780916676824</v>
       </c>
       <c r="I55" t="n">
-        <v>42.15598663130014</v>
+        <v>42.1559706663859</v>
       </c>
       <c r="J55" t="n">
         <v>5.555555555555558</v>
@@ -38304,7 +38368,7 @@
         <v>10.65627667685571</v>
       </c>
       <c r="G56" t="n">
-        <v>11.66324714899951</v>
+        <v>11.6632229717543</v>
       </c>
       <c r="H56" t="n">
         <v>7.361381156751889</v>
@@ -38333,13 +38397,13 @@
         <v>-6.15854030702172</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.133414869096705</v>
+        <v>-1.133403576054681</v>
       </c>
       <c r="H57" t="n">
         <v>3.513107684464867</v>
       </c>
       <c r="I57" t="n">
-        <v>-20.63636456057385</v>
+        <v>-20.63637016359784</v>
       </c>
       <c r="J57" t="n">
         <v>-11.82432417193846</v>
@@ -38433,31 +38497,31 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-41.93548314483822</v>
+        <v>-41.14870183616446</v>
       </c>
       <c r="C2" t="n">
-        <v>-8.80438385681307</v>
+        <v>-9.48955261077079</v>
       </c>
       <c r="D2" t="n">
-        <v>-10.76233049614502</v>
+        <v>-10.3138982769029</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.361216234188625</v>
+        <v>-4.683407757539748</v>
       </c>
       <c r="F2" t="n">
-        <v>-17.85374916874257</v>
+        <v>-17.31560394723957</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.528941531821539</v>
+        <v>-4.165702403357708</v>
       </c>
       <c r="H2" t="n">
-        <v>-28.55590311570747</v>
+        <v>-29.98233869287671</v>
       </c>
       <c r="I2" t="n">
-        <v>-14.46359821908981</v>
+        <v>-14.9052317194415</v>
       </c>
       <c r="J2" t="n">
-        <v>-15.3381620069976</v>
+        <v>-16.34460322464773</v>
       </c>
     </row>
     <row r="3">
@@ -38646,7 +38710,7 @@
         <v>-14.96300514920803</v>
       </c>
       <c r="I8" t="n">
-        <v>-25.40165341174989</v>
+        <v>-25.40166188931352</v>
       </c>
       <c r="J8" t="n">
         <v>0.8920213186065729</v>
@@ -38678,7 +38742,7 @@
         <v>-9.514179193100469</v>
       </c>
       <c r="I9" t="n">
-        <v>-13.68454919940341</v>
+        <v>-13.68453939027434</v>
       </c>
       <c r="J9" t="n">
         <v>-12.45376365041914</v>
@@ -38704,7 +38768,7 @@
         <v>2.925667816312849</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.354127242510708</v>
+        <v>-5.354134712024472</v>
       </c>
       <c r="H10" t="n">
         <v>68.12385194646686</v>
@@ -38736,13 +38800,13 @@
         <v>-7.610206253873331</v>
       </c>
       <c r="G11" t="n">
-        <v>5.353842111674156</v>
+        <v>5.353850426268458</v>
       </c>
       <c r="H11" t="n">
         <v>-26.21148416003172</v>
       </c>
       <c r="I11" t="n">
-        <v>6.467083085656977</v>
+        <v>6.467093392907319</v>
       </c>
       <c r="J11" t="n">
         <v>2.407080726285948</v>
@@ -38774,7 +38838,7 @@
         <v>29.14681042220371</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.392582670916979</v>
+        <v>-5.392583164828846</v>
       </c>
       <c r="J12" t="n">
         <v>21.24463916318964</v>
@@ -38800,13 +38864,13 @@
         <v>36.80501262584171</v>
       </c>
       <c r="G13" t="n">
-        <v>10.23241881051799</v>
+        <v>10.23240719569851</v>
       </c>
       <c r="H13" t="n">
         <v>21.06174227192534</v>
       </c>
       <c r="I13" t="n">
-        <v>40.13306990938417</v>
+        <v>40.13304808147762</v>
       </c>
       <c r="J13" t="n">
         <v>21.03895707563921</v>
@@ -38829,13 +38893,13 @@
         <v>1.671973327733589</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.02534479080803509</v>
+        <v>-0.02533425681351398</v>
       </c>
       <c r="H14" t="n">
         <v>25.35262426890257</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8914062393774902</v>
+        <v>0.8914061816619245</v>
       </c>
       <c r="J14" t="n">
         <v>37.01067429660412</v>
@@ -38858,13 +38922,13 @@
         <v>15.76036725725447</v>
       </c>
       <c r="G15" t="n">
-        <v>9.403498072287109</v>
+        <v>9.403485464018434</v>
       </c>
       <c r="H15" t="n">
         <v>-4.159445407279028</v>
       </c>
       <c r="I15" t="n">
-        <v>22.41576312761737</v>
+        <v>22.41577105363026</v>
       </c>
       <c r="J15" t="n">
         <v>41.20603477451257</v>
@@ -38887,13 +38951,13 @@
         <v>-17.92738085880669</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.485790712466645</v>
+        <v>-8.4857705142105</v>
       </c>
       <c r="H16" t="n">
         <v>4.756719823472322</v>
       </c>
       <c r="I16" t="n">
-        <v>-17.20761191951514</v>
+        <v>-17.20760648656623</v>
       </c>
       <c r="J16" t="n">
         <v>-30.66202407831533</v>
@@ -38916,13 +38980,13 @@
         <v>2.321981478994783</v>
       </c>
       <c r="G17" t="n">
-        <v>7.12648200042505</v>
+        <v>7.126470702214305</v>
       </c>
       <c r="H17" t="n">
         <v>0.7315289117223678</v>
       </c>
       <c r="I17" t="n">
-        <v>-12.28811417979492</v>
+        <v>-12.28811993556758</v>
       </c>
       <c r="J17" t="n">
         <v>-12.49999563868442</v>
@@ -38945,7 +39009,7 @@
         <v>-6.376813805621606</v>
       </c>
       <c r="G18" t="n">
-        <v>-8.095933296298796</v>
+        <v>-8.095942839170478</v>
       </c>
       <c r="H18" t="n">
         <v>50.88300138028043</v>
@@ -38974,7 +39038,7 @@
         <v>-18.96653110566366</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.484002920704985</v>
+        <v>-1.483982613660928</v>
       </c>
       <c r="H19" t="n">
         <v>-19.32324486904549</v>
@@ -39014,7 +39078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J510"/>
+  <dimension ref="A1:J512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39127,7 +39191,7 @@
         <v>16.15136360938538</v>
       </c>
       <c r="I3" t="n">
-        <v>13.18953514511048</v>
+        <v>13.18952182341448</v>
       </c>
       <c r="J3" t="n">
         <v>70.0000032885322</v>
@@ -39153,13 +39217,13 @@
         <v>35.23950508448274</v>
       </c>
       <c r="G4" t="n">
-        <v>20.50514742013778</v>
+        <v>20.50513561497333</v>
       </c>
       <c r="H4" t="n">
         <v>18.55826056452661</v>
       </c>
       <c r="I4" t="n">
-        <v>15.84090469060915</v>
+        <v>15.84091850541089</v>
       </c>
       <c r="J4" t="n">
         <v>79.47977229122856</v>
@@ -39223,7 +39287,7 @@
         <v>20.42312944893776</v>
       </c>
       <c r="I6" t="n">
-        <v>16.8489945570937</v>
+        <v>16.84898733968458</v>
       </c>
       <c r="J6" t="n">
         <v>74.1786665643551</v>
@@ -39255,7 +39319,7 @@
         <v>19.02754764747889</v>
       </c>
       <c r="I7" t="n">
-        <v>14.23302215061948</v>
+        <v>14.23300996545445</v>
       </c>
       <c r="J7" t="n">
         <v>70.31517486505918</v>
@@ -39351,7 +39415,7 @@
         <v>14.29718712087935</v>
       </c>
       <c r="I10" t="n">
-        <v>15.13143116975007</v>
+        <v>15.13143815733493</v>
       </c>
       <c r="J10" t="n">
         <v>54.93472933327954</v>
@@ -39415,7 +39479,7 @@
         <v>12.00104193248259</v>
       </c>
       <c r="I12" t="n">
-        <v>16.53925992256591</v>
+        <v>16.53926699663837</v>
       </c>
       <c r="J12" t="n">
         <v>58.82353170735514</v>
@@ -39447,7 +39511,7 @@
         <v>23.48532329238919</v>
       </c>
       <c r="I13" t="n">
-        <v>16.79517617557025</v>
+        <v>16.79518332705205</v>
       </c>
       <c r="J13" t="n">
         <v>58.58586276992115</v>
@@ -39505,13 +39569,13 @@
         <v>18.36042100886153</v>
       </c>
       <c r="G15" t="n">
-        <v>21.27164341356986</v>
+        <v>21.27163109269175</v>
       </c>
       <c r="H15" t="n">
         <v>50.10011067847504</v>
       </c>
       <c r="I15" t="n">
-        <v>12.44309510189545</v>
+        <v>12.44310724452127</v>
       </c>
       <c r="J15" t="n">
         <v>63.25471398498556</v>
@@ -39569,7 +39633,7 @@
         <v>17.49119689344376</v>
       </c>
       <c r="G17" t="n">
-        <v>21.10591855208681</v>
+        <v>21.10590645985941</v>
       </c>
       <c r="H17" t="n">
         <v>80.21875186197276</v>
@@ -39639,7 +39703,7 @@
         <v>94.1268552045597</v>
       </c>
       <c r="I19" t="n">
-        <v>32.47951491030909</v>
+        <v>32.47950210002233</v>
       </c>
       <c r="J19" t="n">
         <v>121.3157854582134</v>
@@ -39665,13 +39729,13 @@
         <v>19.92705386519244</v>
       </c>
       <c r="G20" t="n">
-        <v>22.5315948805225</v>
+        <v>22.53160722132512</v>
       </c>
       <c r="H20" t="n">
         <v>87.55847280153539</v>
       </c>
       <c r="I20" t="n">
-        <v>32.77455685318971</v>
+        <v>32.77454840879854</v>
       </c>
       <c r="J20" t="n">
         <v>135.4666748046875</v>
@@ -39703,7 +39767,7 @@
         <v>75.75510868409864</v>
       </c>
       <c r="I21" t="n">
-        <v>31.45754638735967</v>
+        <v>31.45755074527625</v>
       </c>
       <c r="J21" t="n">
         <v>142.036550378158</v>
@@ -39767,7 +39831,7 @@
         <v>91.13414267872835</v>
       </c>
       <c r="I23" t="n">
-        <v>30.90391269316848</v>
+        <v>30.90392562284006</v>
       </c>
       <c r="J23" t="n">
         <v>168.1889879197244</v>
@@ -39831,7 +39895,7 @@
         <v>71.35134787851175</v>
       </c>
       <c r="I25" t="n">
-        <v>25.73532638273688</v>
+        <v>25.73533458085297</v>
       </c>
       <c r="J25" t="n">
         <v>169.5767290544607</v>
@@ -39857,7 +39921,7 @@
         <v>12.20622202314199</v>
       </c>
       <c r="G26" t="n">
-        <v>17.5310103032488</v>
+        <v>17.53102271117308</v>
       </c>
       <c r="H26" t="n">
         <v>66.09046092268591</v>
@@ -39889,13 +39953,13 @@
         <v>17.44186046511629</v>
       </c>
       <c r="G27" t="n">
-        <v>19.70907390202596</v>
+        <v>19.7090865288315</v>
       </c>
       <c r="H27" t="n">
         <v>75.14619883040936</v>
       </c>
       <c r="I27" t="n">
-        <v>22.5987420097109</v>
+        <v>22.59875492383123</v>
       </c>
       <c r="J27" t="n">
         <v>141.9999975907175</v>
@@ -39953,13 +40017,13 @@
         <v>20.66455888549516</v>
       </c>
       <c r="G29" t="n">
-        <v>17.8786975781118</v>
+        <v>17.87868509962784</v>
       </c>
       <c r="H29" t="n">
         <v>72.05968302788671</v>
       </c>
       <c r="I29" t="n">
-        <v>23.95293274014536</v>
+        <v>23.95292474688</v>
       </c>
       <c r="J29" t="n">
         <v>143.1331712833967</v>
@@ -39985,13 +40049,13 @@
         <v>27.42365317882882</v>
       </c>
       <c r="G30" t="n">
-        <v>17.420637048874</v>
+        <v>17.42062467665613</v>
       </c>
       <c r="H30" t="n">
         <v>64.25273449733912</v>
       </c>
       <c r="I30" t="n">
-        <v>27.04551764076668</v>
+        <v>27.04550948767035</v>
       </c>
       <c r="J30" t="n">
         <v>129.7662313882407</v>
@@ -40017,7 +40081,7 @@
         <v>15.39021874936699</v>
       </c>
       <c r="G31" t="n">
-        <v>18.81746761698277</v>
+        <v>18.81745495257836</v>
       </c>
       <c r="H31" t="n">
         <v>65.98794595089427</v>
@@ -40087,7 +40151,7 @@
         <v>69.25088116850071</v>
       </c>
       <c r="I33" t="n">
-        <v>25.14075448435975</v>
+        <v>25.14076236892711</v>
       </c>
       <c r="J33" t="n">
         <v>132.4867699130986</v>
@@ -40113,13 +40177,13 @@
         <v>13.01104692045925</v>
       </c>
       <c r="G34" t="n">
-        <v>17.43128634587006</v>
+        <v>17.43129886333536</v>
       </c>
       <c r="H34" t="n">
         <v>61.92835542694652</v>
       </c>
       <c r="I34" t="n">
-        <v>22.52247202740185</v>
+        <v>22.52245948834504</v>
       </c>
       <c r="J34" t="n">
         <v>121.4323651658852</v>
@@ -40151,7 +40215,7 @@
         <v>64.23357664233578</v>
       </c>
       <c r="I35" t="n">
-        <v>27.19799344911933</v>
+        <v>27.1980016778619</v>
       </c>
       <c r="J35" t="n">
         <v>137.8151252422787</v>
@@ -40209,13 +40273,13 @@
         <v>5.373968208882274</v>
       </c>
       <c r="G37" t="n">
-        <v>14.95784738829555</v>
+        <v>14.95783527583134</v>
       </c>
       <c r="H37" t="n">
         <v>49.29618947317174</v>
       </c>
       <c r="I37" t="n">
-        <v>15.74543755900113</v>
+        <v>15.74543228600769</v>
       </c>
       <c r="J37" t="n">
         <v>111.15383897912</v>
@@ -40247,7 +40311,7 @@
         <v>57.80926505349091</v>
       </c>
       <c r="I38" t="n">
-        <v>16.21145162100939</v>
+        <v>16.21145683918306</v>
       </c>
       <c r="J38" t="n">
         <v>124.1666581895616</v>
@@ -40311,7 +40375,7 @@
         <v>62.45973288227488</v>
       </c>
       <c r="I40" t="n">
-        <v>1.128983084690516</v>
+        <v>1.128971419277369</v>
       </c>
       <c r="J40" t="n">
         <v>134.7826177095873</v>
@@ -40337,7 +40401,7 @@
         <v>-0.8370914528086359</v>
       </c>
       <c r="G41" t="n">
-        <v>13.69311700167664</v>
+        <v>13.69312892900481</v>
       </c>
       <c r="H41" t="n">
         <v>59.2399202134017</v>
@@ -40369,13 +40433,13 @@
         <v>0.8595328089425314</v>
       </c>
       <c r="G42" t="n">
-        <v>15.70979617739452</v>
+        <v>15.70980847951631</v>
       </c>
       <c r="H42" t="n">
         <v>61.70213418337656</v>
       </c>
       <c r="I42" t="n">
-        <v>4.688856355146998</v>
+        <v>4.688868773428356</v>
       </c>
       <c r="J42" t="n">
         <v>126.3361029997708</v>
@@ -40471,7 +40535,7 @@
         <v>71.45801931839102</v>
       </c>
       <c r="I45" t="n">
-        <v>12.16106689815384</v>
+        <v>12.16106151167788</v>
       </c>
       <c r="J45" t="n">
         <v>157.6646515776742</v>
@@ -40535,7 +40599,7 @@
         <v>85.00471194850942</v>
       </c>
       <c r="I47" t="n">
-        <v>9.613838637455906</v>
+        <v>9.613845276460232</v>
       </c>
       <c r="J47" t="n">
         <v>151.6363664106889</v>
@@ -40561,7 +40625,7 @@
         <v>25.26545854048294</v>
       </c>
       <c r="G48" t="n">
-        <v>17.38442994980116</v>
+        <v>17.38441714906611</v>
       </c>
       <c r="H48" t="n">
         <v>86.16140643431169</v>
@@ -40599,7 +40663,7 @@
         <v>71.57738095238095</v>
       </c>
       <c r="I49" t="n">
-        <v>11.99739086546068</v>
+        <v>11.99740976505248</v>
       </c>
       <c r="J49" t="n">
         <v>158.230079573006</v>
@@ -40663,7 +40727,7 @@
         <v>51.29173068418904</v>
       </c>
       <c r="I51" t="n">
-        <v>9.556934045279553</v>
+        <v>9.55694650714236</v>
       </c>
       <c r="J51" t="n">
         <v>127.0114992297709</v>
@@ -40759,7 +40823,7 @@
         <v>41.15079311579386</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.52174699598645</v>
+        <v>-1.521758640085147</v>
       </c>
       <c r="J54" t="n">
         <v>86.16581204926534</v>
@@ -40785,13 +40849,13 @@
         <v>19.57686453413079</v>
       </c>
       <c r="G55" t="n">
-        <v>8.875880262034453</v>
+        <v>8.875891838578509</v>
       </c>
       <c r="H55" t="n">
         <v>36.97116125920574</v>
       </c>
       <c r="I55" t="n">
-        <v>-4.102535207427882</v>
+        <v>-4.102523938621339</v>
       </c>
       <c r="J55" t="n">
         <v>64.87922613616699</v>
@@ -40823,7 +40887,7 @@
         <v>43.77442279436383</v>
       </c>
       <c r="I56" t="n">
-        <v>-3.550945305250486</v>
+        <v>-3.550933979170845</v>
       </c>
       <c r="J56" t="n">
         <v>74.76772784887457</v>
@@ -40855,7 +40919,7 @@
         <v>39.5845017315855</v>
       </c>
       <c r="I57" t="n">
-        <v>-4.840900868211085</v>
+        <v>-4.840889679246652</v>
       </c>
       <c r="J57" t="n">
         <v>61.69810163036917</v>
@@ -40887,7 +40951,7 @@
         <v>45.31866297896825</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.8026716177200743</v>
+        <v>-0.8026833620259688</v>
       </c>
       <c r="J58" t="n">
         <v>70.97560603444168</v>
@@ -40945,13 +41009,13 @@
         <v>-5.322962953904497</v>
       </c>
       <c r="G60" t="n">
-        <v>10.34374613676048</v>
+        <v>10.34373456670381</v>
       </c>
       <c r="H60" t="n">
         <v>49.51856946354882</v>
       </c>
       <c r="I60" t="n">
-        <v>5.712411417819085</v>
+        <v>5.712422824596386</v>
       </c>
       <c r="J60" t="n">
         <v>62.82512383653869</v>
@@ -41009,7 +41073,7 @@
         <v>-6.987674070479477</v>
       </c>
       <c r="G62" t="n">
-        <v>8.264571345614691</v>
+        <v>8.264582701998147</v>
       </c>
       <c r="H62" t="n">
         <v>50.16128375966063</v>
@@ -41079,7 +41143,7 @@
         <v>52.6315695544544</v>
       </c>
       <c r="I64" t="n">
-        <v>7.776511389569785</v>
+        <v>7.776534256813661</v>
       </c>
       <c r="J64" t="n">
         <v>82.06088167389984</v>
@@ -41111,7 +41175,7 @@
         <v>60.93793770295235</v>
       </c>
       <c r="I65" t="n">
-        <v>7.621096859314291</v>
+        <v>7.621073991852256</v>
       </c>
       <c r="J65" t="n">
         <v>87.27272777051292</v>
@@ -41137,13 +41201,13 @@
         <v>-3.191753439454137</v>
       </c>
       <c r="G66" t="n">
-        <v>9.654975583939551</v>
+        <v>9.654986894345697</v>
       </c>
       <c r="H66" t="n">
         <v>69.55524373430775</v>
       </c>
       <c r="I66" t="n">
-        <v>10.17209649828614</v>
+        <v>10.17210763952565</v>
       </c>
       <c r="J66" t="n">
         <v>92.45901366939118</v>
@@ -41169,13 +41233,13 @@
         <v>-5.080884384452744</v>
       </c>
       <c r="G67" t="n">
-        <v>10.82644025020392</v>
+        <v>10.82645168908207</v>
       </c>
       <c r="H67" t="n">
         <v>74.20005719956657</v>
       </c>
       <c r="I67" t="n">
-        <v>10.42936064238629</v>
+        <v>10.42936182277174</v>
       </c>
       <c r="J67" t="n">
         <v>106.4114841006974</v>
@@ -41201,13 +41265,13 @@
         <v>-3.992768548930603</v>
       </c>
       <c r="G68" t="n">
-        <v>9.923275140520182</v>
+        <v>9.923286483809047</v>
       </c>
       <c r="H68" t="n">
         <v>70.46093895677912</v>
       </c>
       <c r="I68" t="n">
-        <v>8.984577771064984</v>
+        <v>8.984565541660317</v>
       </c>
       <c r="J68" t="n">
         <v>112.8708253134189</v>
@@ -41239,7 +41303,7 @@
         <v>59.75903941285979</v>
       </c>
       <c r="I69" t="n">
-        <v>9.336032225438418</v>
+        <v>9.336020963787828</v>
       </c>
       <c r="J69" t="n">
         <v>106.4651134402253</v>
@@ -41265,13 +41329,13 @@
         <v>-9.416523672454547</v>
       </c>
       <c r="G70" t="n">
-        <v>8.453220026352115</v>
+        <v>8.453231297731101</v>
       </c>
       <c r="H70" t="n">
         <v>60.65876474493577</v>
       </c>
       <c r="I70" t="n">
-        <v>8.995189531381032</v>
+        <v>8.995201822292632</v>
       </c>
       <c r="J70" t="n">
         <v>112.1040256239442</v>
@@ -41297,7 +41361,7 @@
         <v>-11.76738888704267</v>
       </c>
       <c r="G71" t="n">
-        <v>7.132621466067346</v>
+        <v>7.132610410294027</v>
       </c>
       <c r="H71" t="n">
         <v>51.19813928486645</v>
@@ -41367,7 +41431,7 @@
         <v>45.67474432100389</v>
       </c>
       <c r="I73" t="n">
-        <v>5.920006348914786</v>
+        <v>5.919994542787355</v>
       </c>
       <c r="J73" t="n">
         <v>112.7802797593012</v>
@@ -41399,7 +41463,7 @@
         <v>37.45292871774588</v>
       </c>
       <c r="I74" t="n">
-        <v>4.406870864909274</v>
+        <v>4.406859319154965</v>
       </c>
       <c r="J74" t="n">
         <v>103.5775775390632</v>
@@ -41431,7 +41495,7 @@
         <v>30.02268127303005</v>
       </c>
       <c r="I75" t="n">
-        <v>-2.413088070817371</v>
+        <v>-2.413077659927665</v>
       </c>
       <c r="J75" t="n">
         <v>100.9032218686996</v>
@@ -41463,7 +41527,7 @@
         <v>29.75552684353173</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7905768063145135</v>
+        <v>-0.790587515014507</v>
       </c>
       <c r="J76" t="n">
         <v>87.39039515006255</v>
@@ -41495,7 +41559,7 @@
         <v>33.76771462059234</v>
       </c>
       <c r="I77" t="n">
-        <v>-4.073887339170335</v>
+        <v>-4.073877140005555</v>
       </c>
       <c r="J77" t="n">
         <v>91.51019660794005</v>
@@ -41527,7 +41591,7 @@
         <v>37.16040451905292</v>
       </c>
       <c r="I78" t="n">
-        <v>-5.636511147977929</v>
+        <v>-5.636500384992004</v>
       </c>
       <c r="J78" t="n">
         <v>92.88792469130138</v>
@@ -41553,13 +41617,13 @@
         <v>-12.50287972254698</v>
       </c>
       <c r="G79" t="n">
-        <v>0.7784651311901092</v>
+        <v>0.7784549005666275</v>
       </c>
       <c r="H79" t="n">
         <v>33.92029467705142</v>
       </c>
       <c r="I79" t="n">
-        <v>-10.19616067319565</v>
+        <v>-10.19617003836636</v>
       </c>
       <c r="J79" t="n">
         <v>83.99160638349537</v>
@@ -41591,7 +41655,7 @@
         <v>40.86671910305058</v>
       </c>
       <c r="I80" t="n">
-        <v>-9.661446188750977</v>
+        <v>-9.661436663639901</v>
       </c>
       <c r="J80" t="n">
         <v>86.33122815895915</v>
@@ -41623,7 +41687,7 @@
         <v>44.05244047508194</v>
       </c>
       <c r="I81" t="n">
-        <v>-11.30203542552404</v>
+        <v>-11.30205514714874</v>
       </c>
       <c r="J81" t="n">
         <v>86.99152692711512</v>
@@ -41687,7 +41751,7 @@
         <v>41.68852680226573</v>
       </c>
       <c r="I83" t="n">
-        <v>-18.32410639220786</v>
+        <v>-18.32409720995372</v>
       </c>
       <c r="J83" t="n">
         <v>76.21051989103617</v>
@@ -41719,7 +41783,7 @@
         <v>59.40775106485634</v>
       </c>
       <c r="I84" t="n">
-        <v>-12.47750519719089</v>
+        <v>-12.47748654563742</v>
       </c>
       <c r="J84" t="n">
         <v>99.06541697895044</v>
@@ -41751,7 +41815,7 @@
         <v>65.04654719786612</v>
       </c>
       <c r="I85" t="n">
-        <v>-15.66177753902792</v>
+        <v>-15.66179518724001</v>
       </c>
       <c r="J85" t="n">
         <v>97.04844951046681</v>
@@ -41777,7 +41841,7 @@
         <v>-17.14285992776975</v>
       </c>
       <c r="G86" t="n">
-        <v>-2.846746645443798</v>
+        <v>-2.846756003970619</v>
       </c>
       <c r="H86" t="n">
         <v>67.13286132918634</v>
@@ -41809,13 +41873,13 @@
         <v>-18.06414822509883</v>
       </c>
       <c r="G87" t="n">
-        <v>-2.608840748224917</v>
+        <v>-2.608850082361591</v>
       </c>
       <c r="H87" t="n">
         <v>62.23634673800827</v>
       </c>
       <c r="I87" t="n">
-        <v>-12.24866669743097</v>
+        <v>-12.2486586628829</v>
       </c>
       <c r="J87" t="n">
         <v>102.6548604601487</v>
@@ -41847,7 +41911,7 @@
         <v>55.75244209203252</v>
       </c>
       <c r="I88" t="n">
-        <v>-20.06894868868467</v>
+        <v>-20.06895592590158</v>
       </c>
       <c r="J88" t="n">
         <v>92.52211321734347</v>
@@ -41879,7 +41943,7 @@
         <v>62.23793649992655</v>
       </c>
       <c r="I89" t="n">
-        <v>-15.4971246985837</v>
+        <v>-15.49711696089192</v>
       </c>
       <c r="J89" t="n">
         <v>94.18344870303281</v>
@@ -41911,7 +41975,7 @@
         <v>44.01810748398501</v>
       </c>
       <c r="I90" t="n">
-        <v>-16.88543472916736</v>
+        <v>-16.88543627572069</v>
       </c>
       <c r="J90" t="n">
         <v>81.88842255714064</v>
@@ -41943,7 +42007,7 @@
         <v>35.52879303916819</v>
       </c>
       <c r="I91" t="n">
-        <v>-23.03241385408457</v>
+        <v>-23.03242255709873</v>
       </c>
       <c r="J91" t="n">
         <v>68.10019640513771</v>
@@ -41975,7 +42039,7 @@
         <v>40.49050165131725</v>
       </c>
       <c r="I92" t="n">
-        <v>-26.51242457432378</v>
+        <v>-26.51241816241978</v>
       </c>
       <c r="J92" t="n">
         <v>61.74273412961313</v>
@@ -42001,13 +42065,13 @@
         <v>-33.28873780551388</v>
       </c>
       <c r="G93" t="n">
-        <v>-3.684588482805928</v>
+        <v>-3.684597695080793</v>
       </c>
       <c r="H93" t="n">
         <v>29.00301913394756</v>
       </c>
       <c r="I93" t="n">
-        <v>-29.45170256490599</v>
+        <v>-29.45169627069456</v>
       </c>
       <c r="J93" t="n">
         <v>42.69748628362795</v>
@@ -42033,13 +42097,13 @@
         <v>-31.92243919478229</v>
       </c>
       <c r="G94" t="n">
-        <v>-4.264780411272239</v>
+        <v>-4.264771301566395</v>
       </c>
       <c r="H94" t="n">
         <v>18.74325570428619</v>
       </c>
       <c r="I94" t="n">
-        <v>-28.0068053081651</v>
+        <v>-28.00679894982006</v>
       </c>
       <c r="J94" t="n">
         <v>27.89474196050972</v>
@@ -42071,7 +42135,7 @@
         <v>19.81707264392938</v>
       </c>
       <c r="I95" t="n">
-        <v>-26.00453725848516</v>
+        <v>-26.00453059995175</v>
       </c>
       <c r="J95" t="n">
         <v>24.96815972988056</v>
@@ -42103,7 +42167,7 @@
         <v>15.89211111741442</v>
       </c>
       <c r="I96" t="n">
-        <v>-23.57127213775751</v>
+        <v>-23.5712605330649</v>
       </c>
       <c r="J96" t="n">
         <v>28.54914740621408</v>
@@ -42161,13 +42225,13 @@
         <v>-52.13567772568902</v>
       </c>
       <c r="G98" t="n">
-        <v>-1.144826287332867</v>
+        <v>-1.144817070470294</v>
       </c>
       <c r="H98" t="n">
         <v>18.31965290286819</v>
       </c>
       <c r="I98" t="n">
-        <v>-26.40582069621047</v>
+        <v>-26.40582942938569</v>
       </c>
       <c r="J98" t="n">
         <v>32.4025967189887</v>
@@ -42193,13 +42257,13 @@
         <v>-57.77777609465646</v>
       </c>
       <c r="G99" t="n">
-        <v>-6.02081769635009</v>
+        <v>-6.020826234045174</v>
       </c>
       <c r="H99" t="n">
         <v>15.27719667733658</v>
       </c>
       <c r="I99" t="n">
-        <v>-33.24732339281348</v>
+        <v>-33.24731795382694</v>
       </c>
       <c r="J99" t="n">
         <v>28.97106147384567</v>
@@ -42263,7 +42327,7 @@
         <v>17.94541203322633</v>
       </c>
       <c r="I101" t="n">
-        <v>-31.17108993672595</v>
+        <v>-31.17110158740718</v>
       </c>
       <c r="J101" t="n">
         <v>28.66883782396286</v>
@@ -42327,7 +42391,7 @@
         <v>14.88724822383976</v>
       </c>
       <c r="I103" t="n">
-        <v>-32.84210745784308</v>
+        <v>-32.84210154978727</v>
       </c>
       <c r="J103" t="n">
         <v>22.98156990062044</v>
@@ -42359,7 +42423,7 @@
         <v>9.913208228453851</v>
       </c>
       <c r="I104" t="n">
-        <v>-35.85256845449841</v>
+        <v>-35.85257273941228</v>
       </c>
       <c r="J104" t="n">
         <v>23.86554108948267</v>
@@ -42391,7 +42455,7 @@
         <v>14.53287197231834</v>
       </c>
       <c r="I105" t="n">
-        <v>-33.59567417837825</v>
+        <v>-33.59567847641735</v>
       </c>
       <c r="J105" t="n">
         <v>30.79527080801228</v>
@@ -42449,7 +42513,7 @@
         <v>-56.24584747712591</v>
       </c>
       <c r="G107" t="n">
-        <v>-5.542274228029543</v>
+        <v>-5.542282911524943</v>
       </c>
       <c r="H107" t="n">
         <v>17.43205870243658</v>
@@ -42481,7 +42545,7 @@
         <v>-56.18415731425067</v>
       </c>
       <c r="G108" t="n">
-        <v>-6.221607598175138</v>
+        <v>-6.221599035747061</v>
       </c>
       <c r="H108" t="n">
         <v>14.44831874727788</v>
@@ -42519,7 +42583,7 @@
         <v>2.676028157570309</v>
       </c>
       <c r="I109" t="n">
-        <v>-34.05137839494272</v>
+        <v>-34.05137407827211</v>
       </c>
       <c r="J109" t="n">
         <v>26.24584557611403</v>
@@ -42551,7 +42615,7 @@
         <v>6.024615316080983</v>
       </c>
       <c r="I110" t="n">
-        <v>-31.27061043654561</v>
+        <v>-31.27061650294681</v>
       </c>
       <c r="J110" t="n">
         <v>33.22203842896631</v>
@@ -42577,7 +42641,7 @@
         <v>-54.47863391321948</v>
       </c>
       <c r="G111" t="n">
-        <v>-10.09984190731003</v>
+        <v>-10.09983412216593</v>
       </c>
       <c r="H111" t="n">
         <v>10.12767521636539</v>
@@ -42615,7 +42679,7 @@
         <v>21.10418192715375</v>
       </c>
       <c r="I112" t="n">
-        <v>-30.21470932593397</v>
+        <v>-30.21470313468972</v>
       </c>
       <c r="J112" t="n">
         <v>46.17241168844289</v>
@@ -42647,7 +42711,7 @@
         <v>29.08312860522841</v>
       </c>
       <c r="I113" t="n">
-        <v>-31.15946227398697</v>
+        <v>-31.15945783088099</v>
       </c>
       <c r="J113" t="n">
         <v>45.27778215614377</v>
@@ -42679,7 +42743,7 @@
         <v>32.61072830164626</v>
       </c>
       <c r="I114" t="n">
-        <v>-32.44486357995042</v>
+        <v>-32.44485913828271</v>
       </c>
       <c r="J114" t="n">
         <v>49.6350385796072</v>
@@ -42711,7 +42775,7 @@
         <v>24.44754770776356</v>
       </c>
       <c r="I115" t="n">
-        <v>-34.41802693935152</v>
+        <v>-34.41802113893922</v>
       </c>
       <c r="J115" t="n">
         <v>50.05758655445842</v>
@@ -42743,7 +42807,7 @@
         <v>23.26171935995283</v>
       </c>
       <c r="I116" t="n">
-        <v>-36.4457180486654</v>
+        <v>-36.44571369224542</v>
       </c>
       <c r="J116" t="n">
         <v>44.24131704827239</v>
@@ -42775,7 +42839,7 @@
         <v>24.94730195367547</v>
       </c>
       <c r="I117" t="n">
-        <v>-36.19966294916446</v>
+        <v>-36.19966175250494</v>
       </c>
       <c r="J117" t="n">
         <v>38.56393145516608</v>
@@ -42801,13 +42865,13 @@
         <v>-56.78818610596754</v>
       </c>
       <c r="G118" t="n">
-        <v>-16.38670493724648</v>
+        <v>-16.38669786568314</v>
       </c>
       <c r="H118" t="n">
         <v>17.44131168849032</v>
       </c>
       <c r="I118" t="n">
-        <v>-36.78223647824987</v>
+        <v>-36.78223083173312</v>
       </c>
       <c r="J118" t="n">
         <v>35.52727439186789</v>
@@ -42833,13 +42897,13 @@
         <v>-56.31058995863971</v>
       </c>
       <c r="G119" t="n">
-        <v>-15.37456607895809</v>
+        <v>-15.37457327751788</v>
       </c>
       <c r="H119" t="n">
         <v>20.81582502027968</v>
       </c>
       <c r="I119" t="n">
-        <v>-36.06587516449706</v>
+        <v>-36.0658704982447</v>
       </c>
       <c r="J119" t="n">
         <v>41.26194709591032</v>
@@ -42865,13 +42929,13 @@
         <v>-56.69829342607511</v>
       </c>
       <c r="G120" t="n">
-        <v>-16.07678431933383</v>
+        <v>-16.07677724263259</v>
       </c>
       <c r="H120" t="n">
         <v>18.29646125327557</v>
       </c>
       <c r="I120" t="n">
-        <v>-38.54755466140228</v>
+        <v>-38.547559258854</v>
       </c>
       <c r="J120" t="n">
         <v>41.19001864296059</v>
@@ -42897,7 +42961,7 @@
         <v>-57.14155223271617</v>
       </c>
       <c r="G121" t="n">
-        <v>-16.85995891525053</v>
+        <v>-16.85995198161126</v>
       </c>
       <c r="H121" t="n">
         <v>11.82631761961019</v>
@@ -42935,7 +42999,7 @@
         <v>10.24109211646398</v>
       </c>
       <c r="I122" t="n">
-        <v>-41.40768769062964</v>
+        <v>-41.40768277612826</v>
       </c>
       <c r="J122" t="n">
         <v>42.65420503705462</v>
@@ -42993,13 +43057,13 @@
         <v>-61.61153711978648</v>
       </c>
       <c r="G124" t="n">
-        <v>-17.32209371336002</v>
+        <v>-17.3221006429568</v>
       </c>
       <c r="H124" t="n">
         <v>-0.8441437102060356</v>
       </c>
       <c r="I124" t="n">
-        <v>-42.70334513966879</v>
+        <v>-42.70334575751823</v>
       </c>
       <c r="J124" t="n">
         <v>36.54915842401909</v>
@@ -43025,7 +43089,7 @@
         <v>-62.04201834542411</v>
       </c>
       <c r="G125" t="n">
-        <v>-17.87450892521957</v>
+        <v>-17.87451582243691</v>
       </c>
       <c r="H125" t="n">
         <v>-0.9950223577321893</v>
@@ -43063,7 +43127,7 @@
         <v>-4.313306030797348</v>
       </c>
       <c r="I126" t="n">
-        <v>-41.76579990753935</v>
+        <v>-41.76580426395932</v>
       </c>
       <c r="J126" t="n">
         <v>36.54223559239848</v>
@@ -43095,7 +43159,7 @@
         <v>-7.626934073983682</v>
       </c>
       <c r="I127" t="n">
-        <v>-45.25499235353499</v>
+        <v>-45.25499275935716</v>
       </c>
       <c r="J127" t="n">
         <v>29.66861136912165</v>
@@ -43127,7 +43191,7 @@
         <v>-9.592997010479355</v>
       </c>
       <c r="I128" t="n">
-        <v>-49.59648269142077</v>
+        <v>-49.59649089539933</v>
       </c>
       <c r="J128" t="n">
         <v>28.59374093124656</v>
@@ -43159,7 +43223,7 @@
         <v>-9.914680971138623</v>
       </c>
       <c r="I129" t="n">
-        <v>-47.76541850357405</v>
+        <v>-47.76542283989256</v>
       </c>
       <c r="J129" t="n">
         <v>31.00990824180074</v>
@@ -43191,7 +43255,7 @@
         <v>-0.430739938833391</v>
       </c>
       <c r="I130" t="n">
-        <v>-44.80370541333249</v>
+        <v>-44.80371006780727</v>
       </c>
       <c r="J130" t="n">
         <v>40.60852082673853</v>
@@ -43217,7 +43281,7 @@
         <v>-60.87921861989671</v>
       </c>
       <c r="G131" t="n">
-        <v>-16.61964594119378</v>
+        <v>-16.61965301788414</v>
       </c>
       <c r="H131" t="n">
         <v>11.20226017119483</v>
@@ -43249,13 +43313,13 @@
         <v>-57.52336377295379</v>
       </c>
       <c r="G132" t="n">
-        <v>-14.15376426238819</v>
+        <v>-14.15377152255236</v>
       </c>
       <c r="H132" t="n">
         <v>8.352201320420626</v>
       </c>
       <c r="I132" t="n">
-        <v>-40.50187066692568</v>
+        <v>-40.50186632108546</v>
       </c>
       <c r="J132" t="n">
         <v>48.92561892278942</v>
@@ -43281,7 +43345,7 @@
         <v>-56.86676433086298</v>
       </c>
       <c r="G133" t="n">
-        <v>-16.72257899137246</v>
+        <v>-16.72258588643216</v>
       </c>
       <c r="H133" t="n">
         <v>2.898096851378784</v>
@@ -43351,7 +43415,7 @@
         <v>-2.809878783828057</v>
       </c>
       <c r="I135" t="n">
-        <v>-44.35211507824253</v>
+        <v>-44.35211986444345</v>
       </c>
       <c r="J135" t="n">
         <v>45.94360305036773</v>
@@ -43383,7 +43447,7 @@
         <v>0.04121654929012397</v>
       </c>
       <c r="I136" t="n">
-        <v>-42.32407443970882</v>
+        <v>-42.32406993188314</v>
       </c>
       <c r="J136" t="n">
         <v>49.730944089708</v>
@@ -43409,13 +43473,13 @@
         <v>-56.62921337306769</v>
       </c>
       <c r="G137" t="n">
-        <v>-15.94877016040107</v>
+        <v>-15.94877718164233</v>
       </c>
       <c r="H137" t="n">
         <v>-0.8227812344208774</v>
       </c>
       <c r="I137" t="n">
-        <v>-43.53503687932449</v>
+        <v>-43.53504135301615</v>
       </c>
       <c r="J137" t="n">
         <v>46.43016219484324</v>
@@ -43441,13 +43505,13 @@
         <v>-55.96958453493185</v>
       </c>
       <c r="G138" t="n">
-        <v>-15.24241637006719</v>
+        <v>-15.24242350981521</v>
       </c>
       <c r="H138" t="n">
         <v>-1.909228316656353</v>
       </c>
       <c r="I138" t="n">
-        <v>-42.02479617480736</v>
+        <v>-42.02480076815466</v>
       </c>
       <c r="J138" t="n">
         <v>46.43016219484324</v>
@@ -43543,7 +43607,7 @@
         <v>11.78529754959159</v>
       </c>
       <c r="I141" t="n">
-        <v>-32.26880534741482</v>
+        <v>-32.26879864064875</v>
       </c>
       <c r="J141" t="n">
         <v>79.66746349443316</v>
@@ -43639,7 +43703,7 @@
         <v>5.829856359310237</v>
       </c>
       <c r="I144" t="n">
-        <v>-32.77705273110023</v>
+        <v>-32.77704074443481</v>
       </c>
       <c r="J144" t="n">
         <v>73.11404623446703</v>
@@ -43671,7 +43735,7 @@
         <v>2.334533491450208</v>
       </c>
       <c r="I145" t="n">
-        <v>-33.51296118514819</v>
+        <v>-33.51296794739835</v>
       </c>
       <c r="J145" t="n">
         <v>79.7908029562787</v>
@@ -43697,7 +43761,7 @@
         <v>-50.13210990744989</v>
       </c>
       <c r="G146" t="n">
-        <v>-11.82290408126045</v>
+        <v>-11.82289657347413</v>
       </c>
       <c r="H146" t="n">
         <v>-4.631267327895838</v>
@@ -43729,13 +43793,13 @@
         <v>-50.80962983163329</v>
       </c>
       <c r="G147" t="n">
-        <v>-13.61996145713659</v>
+        <v>-13.6199541228318</v>
       </c>
       <c r="H147" t="n">
         <v>-8.328828410010559</v>
       </c>
       <c r="I147" t="n">
-        <v>-34.47114291863736</v>
+        <v>-34.47114939719585</v>
       </c>
       <c r="J147" t="n">
         <v>59.65780569033912</v>
@@ -43767,7 +43831,7 @@
         <v>-6.028498086992817</v>
       </c>
       <c r="I148" t="n">
-        <v>-34.28806060348938</v>
+        <v>-34.28805565881679</v>
       </c>
       <c r="J148" t="n">
         <v>53.29710430619193</v>
@@ -43799,7 +43863,7 @@
         <v>-1.760633823603719</v>
       </c>
       <c r="I149" t="n">
-        <v>-34.87422043175192</v>
+        <v>-34.87421557689749</v>
       </c>
       <c r="J149" t="n">
         <v>56.09403415140542</v>
@@ -43831,7 +43895,7 @@
         <v>-7.602880670023849</v>
       </c>
       <c r="I150" t="n">
-        <v>-37.45698176262956</v>
+        <v>-37.4569708671581</v>
       </c>
       <c r="J150" t="n">
         <v>46.37167601458793</v>
@@ -43889,7 +43953,7 @@
         <v>-53.60400625525475</v>
       </c>
       <c r="G152" t="n">
-        <v>-20.22513386978178</v>
+        <v>-20.22512724173225</v>
       </c>
       <c r="H152" t="n">
         <v>-15.33815857894649</v>
@@ -43927,7 +43991,7 @@
         <v>-16.46675455896869</v>
       </c>
       <c r="I153" t="n">
-        <v>-41.94472512215197</v>
+        <v>-41.94472969593319</v>
       </c>
       <c r="J153" t="n">
         <v>22.64151237635372</v>
@@ -43985,7 +44049,7 @@
         <v>-51.83269228782829</v>
       </c>
       <c r="G155" t="n">
-        <v>-14.77920088105071</v>
+        <v>-14.77919367032432</v>
       </c>
       <c r="H155" t="n">
         <v>-14.68718460786851</v>
@@ -44023,7 +44087,7 @@
         <v>-11.96105995313918</v>
       </c>
       <c r="I156" t="n">
-        <v>-35.9728436726354</v>
+        <v>-35.97285437285689</v>
       </c>
       <c r="J156" t="n">
         <v>34.93548977759578</v>
@@ -44049,7 +44113,7 @@
         <v>-49.81553837768958</v>
       </c>
       <c r="G157" t="n">
-        <v>-12.62763296200138</v>
+        <v>-12.62762558715662</v>
       </c>
       <c r="H157" t="n">
         <v>-7.803167735336114</v>
@@ -44081,13 +44145,13 @@
         <v>-49.31460605578476</v>
       </c>
       <c r="G158" t="n">
-        <v>-12.14389007981044</v>
+        <v>-12.14389741566937</v>
       </c>
       <c r="H158" t="n">
         <v>19.17837993230622</v>
       </c>
       <c r="I158" t="n">
-        <v>-31.90961164374077</v>
+        <v>-31.90961813240691</v>
       </c>
       <c r="J158" t="n">
         <v>55.97883818585918</v>
@@ -44119,7 +44183,7 @@
         <v>34.79139711401707</v>
       </c>
       <c r="I159" t="n">
-        <v>-31.78687157655621</v>
+        <v>-31.78687811577813</v>
       </c>
       <c r="J159" t="n">
         <v>59.30529830757856</v>
@@ -44151,7 +44215,7 @@
         <v>33.15829160473547</v>
       </c>
       <c r="I160" t="n">
-        <v>-29.84938784335838</v>
+        <v>-29.84939278684298</v>
       </c>
       <c r="J160" t="n">
         <v>67.10172765520876</v>
@@ -44183,7 +44247,7 @@
         <v>38.5684914172453</v>
       </c>
       <c r="I161" t="n">
-        <v>-29.7419029828034</v>
+        <v>-29.74189607402291</v>
       </c>
       <c r="J161" t="n">
         <v>62.23034118107906</v>
@@ -44215,7 +44279,7 @@
         <v>31.94658342227763</v>
       </c>
       <c r="I162" t="n">
-        <v>-31.73167748083034</v>
+        <v>-31.7316658087051</v>
       </c>
       <c r="J162" t="n">
         <v>44.11149655354738</v>
@@ -44241,13 +44305,13 @@
         <v>-50.39954164408403</v>
       </c>
       <c r="G163" t="n">
-        <v>-6.576265979101093</v>
+        <v>-6.576258128209467</v>
       </c>
       <c r="H163" t="n">
         <v>35.25827976252069</v>
       </c>
       <c r="I163" t="n">
-        <v>-30.97237292020486</v>
+        <v>-30.9723612810538</v>
       </c>
       <c r="J163" t="n">
         <v>47.45098657865709</v>
@@ -44279,7 +44343,7 @@
         <v>31.4724774427817</v>
       </c>
       <c r="I164" t="n">
-        <v>-33.50502602626197</v>
+        <v>-33.50502133447838</v>
       </c>
       <c r="J164" t="n">
         <v>45.68383260132476</v>
@@ -44343,7 +44407,7 @@
         <v>31.32498904941086</v>
       </c>
       <c r="I166" t="n">
-        <v>-34.25831287796005</v>
+        <v>-34.25831760024707</v>
       </c>
       <c r="J166" t="n">
         <v>45.76086589203896</v>
@@ -44369,7 +44433,7 @@
         <v>-53.46630744214328</v>
       </c>
       <c r="G167" t="n">
-        <v>-1.631337452160353</v>
+        <v>-1.631329128250458</v>
       </c>
       <c r="H167" t="n">
         <v>33.09109889422288</v>
@@ -44401,13 +44465,13 @@
         <v>-53.21192041547695</v>
       </c>
       <c r="G168" t="n">
-        <v>-1.846931117352801</v>
+        <v>-1.846922769230852</v>
       </c>
       <c r="H168" t="n">
         <v>23.80828374026902</v>
       </c>
       <c r="I168" t="n">
-        <v>-34.9745393723056</v>
+        <v>-34.97454409134397</v>
       </c>
       <c r="J168" t="n">
         <v>38.0866387959659</v>
@@ -44433,7 +44497,7 @@
         <v>-52.13521178339568</v>
       </c>
       <c r="G169" t="n">
-        <v>-3.703214914559028</v>
+        <v>-3.703223035058201</v>
       </c>
       <c r="H169" t="n">
         <v>29.44025621625235</v>
@@ -44471,7 +44535,7 @@
         <v>31.30973250029547</v>
       </c>
       <c r="I170" t="n">
-        <v>-37.60952319348129</v>
+        <v>-37.60951737835894</v>
       </c>
       <c r="J170" t="n">
         <v>40.14651791489481</v>
@@ -44503,7 +44567,7 @@
         <v>33.71331443951104</v>
       </c>
       <c r="I171" t="n">
-        <v>-37.94833171441556</v>
+        <v>-37.94833755661033</v>
       </c>
       <c r="J171" t="n">
         <v>43.41373072994053</v>
@@ -44529,7 +44593,7 @@
         <v>-45.99760763325964</v>
       </c>
       <c r="G172" t="n">
-        <v>0.5143378536584198</v>
+        <v>0.5143291941176686</v>
       </c>
       <c r="H172" t="n">
         <v>44.92055080938697</v>
@@ -44567,7 +44631,7 @@
         <v>59.14138873392913</v>
       </c>
       <c r="I173" t="n">
-        <v>-31.15038678081573</v>
+        <v>-31.15039340858322</v>
       </c>
       <c r="J173" t="n">
         <v>68.31720572322637</v>
@@ -44593,7 +44657,7 @@
         <v>-41.76249980926514</v>
       </c>
       <c r="G174" t="n">
-        <v>1.98072439885395</v>
+        <v>1.980733388627964</v>
       </c>
       <c r="H174" t="n">
         <v>59.09223654259699</v>
@@ -44625,7 +44689,7 @@
         <v>-42.28287675129394</v>
       </c>
       <c r="G175" t="n">
-        <v>2.861048248629738</v>
+        <v>2.861057206861273</v>
       </c>
       <c r="H175" t="n">
         <v>63.09951008127501</v>
@@ -44689,13 +44753,13 @@
         <v>-38.99999765249399</v>
       </c>
       <c r="G177" t="n">
-        <v>2.718806120971973</v>
+        <v>2.71879710441596</v>
       </c>
       <c r="H177" t="n">
         <v>71.52501088341694</v>
       </c>
       <c r="I177" t="n">
-        <v>-22.33078034924558</v>
+        <v>-22.33078549632175</v>
       </c>
       <c r="J177" t="n">
         <v>83.1262414010687</v>
@@ -44727,7 +44791,7 @@
         <v>66.75774073195311</v>
       </c>
       <c r="I178" t="n">
-        <v>-21.79922553387539</v>
+        <v>-21.79922030085473</v>
       </c>
       <c r="J178" t="n">
         <v>83.31967312108763</v>
@@ -44753,13 +44817,13 @@
         <v>-41.81931635301061</v>
       </c>
       <c r="G179" t="n">
-        <v>0.9841458252099811</v>
+        <v>0.9841546105370691</v>
       </c>
       <c r="H179" t="n">
         <v>61.06736588618858</v>
       </c>
       <c r="I179" t="n">
-        <v>-24.21510239292522</v>
+        <v>-24.21511774867416</v>
       </c>
       <c r="J179" t="n">
         <v>75.58593786379788</v>
@@ -44785,13 +44849,13 @@
         <v>-39.6770169275888</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.1476638184739976</v>
+        <v>-0.147672528644105</v>
       </c>
       <c r="H180" t="n">
         <v>65.15150572053405</v>
       </c>
       <c r="I180" t="n">
-        <v>-25.31920577234636</v>
+        <v>-25.31919824707868</v>
       </c>
       <c r="J180" t="n">
         <v>72.82946306655833</v>
@@ -44855,7 +44919,7 @@
         <v>72.57494253958269</v>
       </c>
       <c r="I182" t="n">
-        <v>-25.49482362062903</v>
+        <v>-25.49483107255582</v>
       </c>
       <c r="J182" t="n">
         <v>93.80497531351087</v>
@@ -44881,7 +44945,7 @@
         <v>-37.81366289032172</v>
       </c>
       <c r="G183" t="n">
-        <v>-0.6405063489323015</v>
+        <v>-0.6404978015496887</v>
       </c>
       <c r="H183" t="n">
         <v>82.78223213394497</v>
@@ -44913,13 +44977,13 @@
         <v>-35.9392113960985</v>
       </c>
       <c r="G184" t="n">
-        <v>-2.940785161752024</v>
+        <v>-2.940793371060713</v>
       </c>
       <c r="H184" t="n">
         <v>84.22466480357787</v>
       </c>
       <c r="I184" t="n">
-        <v>-25.14133222869045</v>
+        <v>-25.14133469574373</v>
       </c>
       <c r="J184" t="n">
         <v>90.30188794405956</v>
@@ -44951,7 +45015,7 @@
         <v>88.55766356470485</v>
       </c>
       <c r="I185" t="n">
-        <v>-25.02156280830814</v>
+        <v>-25.0215553060073</v>
       </c>
       <c r="J185" t="n">
         <v>97.80303778508271</v>
@@ -45015,7 +45079,7 @@
         <v>109.9117682961857</v>
       </c>
       <c r="I187" t="n">
-        <v>-23.41613770201895</v>
+        <v>-23.41613005209735</v>
       </c>
       <c r="J187" t="n">
         <v>144.9407236737255</v>
@@ -45079,7 +45143,7 @@
         <v>123.2258100313875</v>
       </c>
       <c r="I189" t="n">
-        <v>-21.52763130838451</v>
+        <v>-21.52762841287986</v>
       </c>
       <c r="J189" t="n">
         <v>141.7857081765763</v>
@@ -45111,7 +45175,7 @@
         <v>122.2920398799532</v>
       </c>
       <c r="I190" t="n">
-        <v>-17.22076875496595</v>
+        <v>-17.22076008243486</v>
       </c>
       <c r="J190" t="n">
         <v>146.51820853791</v>
@@ -45175,7 +45239,7 @@
         <v>125.310248833198</v>
       </c>
       <c r="I192" t="n">
-        <v>-20.91945994695765</v>
+        <v>-20.91946783988486</v>
       </c>
       <c r="J192" t="n">
         <v>150.9514669770176</v>
@@ -45271,7 +45335,7 @@
         <v>150.8404868487914</v>
       </c>
       <c r="I195" t="n">
-        <v>-14.28143416458211</v>
+        <v>-14.28142889256946</v>
       </c>
       <c r="J195" t="n">
         <v>183.9918671584078</v>
@@ -45303,7 +45367,7 @@
         <v>129.1716214536388</v>
       </c>
       <c r="I196" t="n">
-        <v>-19.293970617628</v>
+        <v>-19.29395730250751</v>
       </c>
       <c r="J196" t="n">
         <v>168.2000122070312</v>
@@ -45361,13 +45425,13 @@
         <v>-33.52514665157967</v>
       </c>
       <c r="G198" t="n">
-        <v>-1.415380617513928</v>
+        <v>-1.4153889785956</v>
       </c>
       <c r="H198" t="n">
         <v>94.45324890083117</v>
       </c>
       <c r="I198" t="n">
-        <v>-28.42349396691873</v>
+        <v>-28.42348749687464</v>
       </c>
       <c r="J198" t="n">
         <v>121.8619260496735</v>
@@ -45425,7 +45489,7 @@
         <v>-37.59362584999582</v>
       </c>
       <c r="G200" t="n">
-        <v>-1.848511108739048</v>
+        <v>-1.848502833106846</v>
       </c>
       <c r="H200" t="n">
         <v>88.43219261331876</v>
@@ -45489,7 +45553,7 @@
         <v>-35.84436900863341</v>
       </c>
       <c r="G202" t="n">
-        <v>-1.301836254451327</v>
+        <v>-1.301844487537573</v>
       </c>
       <c r="H202" t="n">
         <v>78.76605325413581</v>
@@ -45527,7 +45591,7 @@
         <v>83.68124127503025</v>
       </c>
       <c r="I203" t="n">
-        <v>-28.09563932936137</v>
+        <v>-28.09564597547907</v>
       </c>
       <c r="J203" t="n">
         <v>106.2277067414659</v>
@@ -45585,13 +45649,13 @@
         <v>-28.65188365140916</v>
       </c>
       <c r="G205" t="n">
-        <v>3.175299540611221</v>
+        <v>3.17529077529517</v>
       </c>
       <c r="H205" t="n">
         <v>94.32029234930152</v>
       </c>
       <c r="I205" t="n">
-        <v>-27.08600683553397</v>
+        <v>-27.0860000922971</v>
       </c>
       <c r="J205" t="n">
         <v>122.9661754366069</v>
@@ -45649,7 +45713,7 @@
         <v>-27.18278428929728</v>
       </c>
       <c r="G207" t="n">
-        <v>3.544544670919225</v>
+        <v>3.544553467908163</v>
       </c>
       <c r="H207" t="n">
         <v>96.56910071694344</v>
@@ -45745,7 +45809,7 @@
         <v>-27.03415236602241</v>
       </c>
       <c r="G210" t="n">
-        <v>-2.71166638281537</v>
+        <v>-2.71167406087387</v>
       </c>
       <c r="H210" t="n">
         <v>88.54100235891897</v>
@@ -45815,7 +45879,7 @@
         <v>98.29378184219588</v>
       </c>
       <c r="I212" t="n">
-        <v>-31.41072207146195</v>
+        <v>-31.41071594212068</v>
       </c>
       <c r="J212" t="n">
         <v>127.3423849684713</v>
@@ -45847,7 +45911,7 @@
         <v>101.0606230012067</v>
       </c>
       <c r="I213" t="n">
-        <v>-31.06073388270728</v>
+        <v>-31.06074006982888</v>
       </c>
       <c r="J213" t="n">
         <v>129.4573808043165</v>
@@ -45905,7 +45969,7 @@
         <v>-35.00641823830535</v>
       </c>
       <c r="G215" t="n">
-        <v>-4.17189681239063</v>
+        <v>-4.171889360138847</v>
       </c>
       <c r="H215" t="n">
         <v>86.87857539273911</v>
@@ -45943,7 +46007,7 @@
         <v>88.96002855288734</v>
       </c>
       <c r="I216" t="n">
-        <v>-32.92036549394376</v>
+        <v>-32.92037140574799</v>
       </c>
       <c r="J216" t="n">
         <v>128.768082361913</v>
@@ -45969,7 +46033,7 @@
         <v>-33.86392905643432</v>
       </c>
       <c r="G217" t="n">
-        <v>-6.385019555942673</v>
+        <v>-6.385026828532547</v>
       </c>
       <c r="H217" t="n">
         <v>98.08728775531479</v>
@@ -46161,7 +46225,7 @@
         <v>-26.85507940336083</v>
       </c>
       <c r="G223" t="n">
-        <v>-10.6562456616022</v>
+        <v>-10.65625261812432</v>
       </c>
       <c r="H223" t="n">
         <v>100.0265892515791</v>
@@ -46199,7 +46263,7 @@
         <v>108.4021066095138</v>
       </c>
       <c r="I224" t="n">
-        <v>-23.58793790131195</v>
+        <v>-23.58793030177627</v>
       </c>
       <c r="J224" t="n">
         <v>132.0058857738733</v>
@@ -46263,7 +46327,7 @@
         <v>95.15328519545527</v>
       </c>
       <c r="I226" t="n">
-        <v>-27.24829383266478</v>
+        <v>-27.24830098065127</v>
       </c>
       <c r="J226" t="n">
         <v>110.7646535029406</v>
@@ -46385,7 +46449,7 @@
         <v>-40.67977613483576</v>
       </c>
       <c r="G230" t="n">
-        <v>-8.235102601298294</v>
+        <v>-8.235095143331449</v>
       </c>
       <c r="H230" t="n">
         <v>64.56839752173443</v>
@@ -46449,7 +46513,7 @@
         <v>-39.58248098284007</v>
       </c>
       <c r="G232" t="n">
-        <v>-5.920876570197042</v>
+        <v>-5.920884290780492</v>
       </c>
       <c r="H232" t="n">
         <v>42.95023242456983</v>
@@ -46487,7 +46551,7 @@
         <v>31.20220243440443</v>
       </c>
       <c r="I233" t="n">
-        <v>-32.79412256434421</v>
+        <v>-32.79411610687446</v>
       </c>
       <c r="J233" t="n">
         <v>37.38601418418006</v>
@@ -46513,13 +46577,13 @@
         <v>-38.63636103394656</v>
       </c>
       <c r="G234" t="n">
-        <v>-6.789584610169408</v>
+        <v>-6.789576929754382</v>
       </c>
       <c r="H234" t="n">
         <v>36.77451609649452</v>
       </c>
       <c r="I234" t="n">
-        <v>-32.68281725784399</v>
+        <v>-32.68282383642989</v>
       </c>
       <c r="J234" t="n">
         <v>37.40589990296488</v>
@@ -46615,7 +46679,7 @@
         <v>28.45130029759806</v>
       </c>
       <c r="I237" t="n">
-        <v>-30.34968049155801</v>
+        <v>-30.34968755706141</v>
       </c>
       <c r="J237" t="n">
         <v>37.53923055665842</v>
@@ -46679,7 +46743,7 @@
         <v>11.90330802341504</v>
       </c>
       <c r="I239" t="n">
-        <v>-29.36256590952326</v>
+        <v>-29.36257314192705</v>
       </c>
       <c r="J239" t="n">
         <v>30.84777634543028</v>
@@ -46705,7 +46769,7 @@
         <v>-41.94381402432754</v>
       </c>
       <c r="G240" t="n">
-        <v>-5.248220291782069</v>
+        <v>-5.24821227749892</v>
       </c>
       <c r="H240" t="n">
         <v>14.92523692770091</v>
@@ -46769,13 +46833,13 @@
         <v>-38.30580451011441</v>
       </c>
       <c r="G242" t="n">
-        <v>-2.136961897373224</v>
+        <v>-2.136970167875163</v>
       </c>
       <c r="H242" t="n">
         <v>24.7957124658932</v>
       </c>
       <c r="I242" t="n">
-        <v>-20.23049029750423</v>
+        <v>-20.2304989019239</v>
       </c>
       <c r="J242" t="n">
         <v>52.73949118221508</v>
@@ -46801,7 +46865,7 @@
         <v>-39.34322726834358</v>
       </c>
       <c r="G243" t="n">
-        <v>-3.703263225960984</v>
+        <v>-3.703271274079567</v>
       </c>
       <c r="H243" t="n">
         <v>32.40354383046355</v>
@@ -46839,7 +46903,7 @@
         <v>34.13228966130708</v>
       </c>
       <c r="I244" t="n">
-        <v>-23.2433353276135</v>
+        <v>-23.24332750705954</v>
       </c>
       <c r="J244" t="n">
         <v>52.75998400130671</v>
@@ -46903,7 +46967,7 @@
         <v>13.38954626727096</v>
       </c>
       <c r="I246" t="n">
-        <v>-26.33157398867555</v>
+        <v>-26.33158144856611</v>
       </c>
       <c r="J246" t="n">
         <v>28.55561668266151</v>
@@ -46999,7 +47063,7 @@
         <v>28.24667177580864</v>
       </c>
       <c r="I249" t="n">
-        <v>-27.19372245264892</v>
+        <v>-27.19372983830064</v>
       </c>
       <c r="J249" t="n">
         <v>34.10686463800094</v>
@@ -47095,7 +47159,7 @@
         <v>38.13899279483215</v>
       </c>
       <c r="I252" t="n">
-        <v>-22.31719283864492</v>
+        <v>-22.31720071184628</v>
       </c>
       <c r="J252" t="n">
         <v>56.19888935780564</v>
@@ -47319,7 +47383,7 @@
         <v>17.21369395430563</v>
       </c>
       <c r="I259" t="n">
-        <v>-20.11944409895419</v>
+        <v>-20.11943557814434</v>
       </c>
       <c r="J259" t="n">
         <v>54.07133907621559</v>
@@ -47575,7 +47639,7 @@
         <v>-9.789748048156266</v>
       </c>
       <c r="I267" t="n">
-        <v>-20.82639503526708</v>
+        <v>-20.82640358515051</v>
       </c>
       <c r="J267" t="n">
         <v>34.23865433442628</v>
@@ -47703,7 +47767,7 @@
         <v>-27.76584214756481</v>
       </c>
       <c r="I271" t="n">
-        <v>-32.16929289143484</v>
+        <v>-32.16928633245178</v>
       </c>
       <c r="J271" t="n">
         <v>5.493463531992426</v>
@@ -47767,7 +47831,7 @@
         <v>-22.71868945740797</v>
       </c>
       <c r="I273" t="n">
-        <v>-29.55400530838046</v>
+        <v>-29.55401212266132</v>
       </c>
       <c r="J273" t="n">
         <v>0.2804769630959436</v>
@@ -47831,7 +47895,7 @@
         <v>-29.18674514954349</v>
       </c>
       <c r="I275" t="n">
-        <v>-27.13680635595359</v>
+        <v>-27.13681355281311</v>
       </c>
       <c r="J275" t="n">
         <v>-12.78136378898818</v>
@@ -47959,7 +48023,7 @@
         <v>-20.91819495708994</v>
       </c>
       <c r="I279" t="n">
-        <v>-21.13047219079976</v>
+        <v>-21.13048049863758</v>
       </c>
       <c r="J279" t="n">
         <v>0.5219697278298963</v>
@@ -48183,7 +48247,7 @@
         <v>-17.3628377931779</v>
       </c>
       <c r="I286" t="n">
-        <v>-23.84494252383033</v>
+        <v>-23.84493473005442</v>
       </c>
       <c r="J286" t="n">
         <v>8.001916670527965</v>
@@ -48279,7 +48343,7 @@
         <v>-15.80435876850455</v>
       </c>
       <c r="I289" t="n">
-        <v>-19.52015837880386</v>
+        <v>-19.52014967564222</v>
       </c>
       <c r="J289" t="n">
         <v>13.66120207730763</v>
@@ -48311,7 +48375,7 @@
         <v>-18.49578771778532</v>
       </c>
       <c r="I290" t="n">
-        <v>-19.80675285177297</v>
+        <v>-19.80676144690814</v>
       </c>
       <c r="J290" t="n">
         <v>14.74597518697689</v>
@@ -48535,7 +48599,7 @@
         <v>-41.72135295266101</v>
       </c>
       <c r="I297" t="n">
-        <v>-22.88070596826082</v>
+        <v>-22.88069753552291</v>
       </c>
       <c r="J297" t="n">
         <v>-4.48524369027955</v>
@@ -48663,7 +48727,7 @@
         <v>-35.27146510631234</v>
       </c>
       <c r="I301" t="n">
-        <v>-23.42535204198196</v>
+        <v>-23.42536032537918</v>
       </c>
       <c r="J301" t="n">
         <v>-5.574591275281082</v>
@@ -48727,7 +48791,7 @@
         <v>-31.05525941638822</v>
       </c>
       <c r="I303" t="n">
-        <v>-20.082786803478</v>
+        <v>-20.08279589388603</v>
       </c>
       <c r="J303" t="n">
         <v>1.417724995673453</v>
@@ -49015,7 +49079,7 @@
         <v>-39.16467071785878</v>
       </c>
       <c r="I312" t="n">
-        <v>-23.67828830810955</v>
+        <v>-23.67829654351601</v>
       </c>
       <c r="J312" t="n">
         <v>7.188093354284919</v>
@@ -49143,7 +49207,7 @@
         <v>-43.54679306508746</v>
       </c>
       <c r="I316" t="n">
-        <v>-30.43281399248713</v>
+        <v>-30.43282109639951</v>
       </c>
       <c r="J316" t="n">
         <v>-3.061483559066525</v>
@@ -49175,7 +49239,7 @@
         <v>-47.77185344404541</v>
       </c>
       <c r="I317" t="n">
-        <v>-31.74837510836619</v>
+        <v>-31.74836812343457</v>
       </c>
       <c r="J317" t="n">
         <v>-9.555436694152498</v>
@@ -49207,7 +49271,7 @@
         <v>-52.72973501715575</v>
       </c>
       <c r="I318" t="n">
-        <v>-32.59171223647252</v>
+        <v>-32.59171905318771</v>
       </c>
       <c r="J318" t="n">
         <v>-13.31224434263872</v>
@@ -49239,7 +49303,7 @@
         <v>-55.27717768906935</v>
       </c>
       <c r="I319" t="n">
-        <v>-31.59040521272418</v>
+        <v>-31.59039820142303</v>
       </c>
       <c r="J319" t="n">
         <v>-21.23319419798155</v>
@@ -49303,7 +49367,7 @@
         <v>-54.49974954822018</v>
       </c>
       <c r="I321" t="n">
-        <v>-30.81718734034944</v>
+        <v>-30.81718021449415</v>
       </c>
       <c r="J321" t="n">
         <v>-22.21221163758537</v>
@@ -49495,7 +49559,7 @@
         <v>-39.58842358779834</v>
       </c>
       <c r="I327" t="n">
-        <v>-28.95246535407854</v>
+        <v>-28.9524729336602</v>
       </c>
       <c r="J327" t="n">
         <v>-24.47013600772119</v>
@@ -49591,7 +49655,7 @@
         <v>-40.33758035437396</v>
       </c>
       <c r="I330" t="n">
-        <v>-23.96618818241377</v>
+        <v>-23.96619685473781</v>
       </c>
       <c r="J330" t="n">
         <v>-18.34636666921264</v>
@@ -49687,7 +49751,7 @@
         <v>-45.54360529211075</v>
       </c>
       <c r="I333" t="n">
-        <v>-22.58020975443182</v>
+        <v>-22.58020063193108</v>
       </c>
       <c r="J333" t="n">
         <v>-21.02878397775322</v>
@@ -49751,7 +49815,7 @@
         <v>-44.60865172604881</v>
       </c>
       <c r="I335" t="n">
-        <v>-25.07035435299852</v>
+        <v>-25.07036277681787</v>
       </c>
       <c r="J335" t="n">
         <v>-14.14575480237133</v>
@@ -49783,7 +49847,7 @@
         <v>-48.60430364584478</v>
       </c>
       <c r="I336" t="n">
-        <v>-24.60030124432042</v>
+        <v>-24.60030981295194</v>
       </c>
       <c r="J336" t="n">
         <v>-15.84507099008591</v>
@@ -49815,7 +49879,7 @@
         <v>-51.0275685005831</v>
       </c>
       <c r="I337" t="n">
-        <v>-25.72519486044957</v>
+        <v>-25.72518642899533</v>
       </c>
       <c r="J337" t="n">
         <v>-21.41738903286038</v>
@@ -49975,7 +50039,7 @@
         <v>-50.84891692643389</v>
       </c>
       <c r="I342" t="n">
-        <v>-30.42624869717885</v>
+        <v>-30.42624103025863</v>
       </c>
       <c r="J342" t="n">
         <v>-21.04766814258902</v>
@@ -50007,7 +50071,7 @@
         <v>-48.263368464608</v>
       </c>
       <c r="I343" t="n">
-        <v>-29.51919907596125</v>
+        <v>-29.51919110643136</v>
       </c>
       <c r="J343" t="n">
         <v>-17.58568880160797</v>
@@ -50167,7 +50231,7 @@
         <v>-49.48442445243727</v>
       </c>
       <c r="I348" t="n">
-        <v>-31.66427293856655</v>
+        <v>-31.66427704201518</v>
       </c>
       <c r="J348" t="n">
         <v>-28.13106781059436</v>
@@ -50231,7 +50295,7 @@
         <v>-49.7811033252699</v>
       </c>
       <c r="I350" t="n">
-        <v>-32.73928211656697</v>
+        <v>-32.73927413496151</v>
       </c>
       <c r="J350" t="n">
         <v>-30.67679915646358</v>
@@ -50423,7 +50487,7 @@
         <v>-47.48545500046233</v>
       </c>
       <c r="I356" t="n">
-        <v>-19.94135144179933</v>
+        <v>-19.94134609404918</v>
       </c>
       <c r="J356" t="n">
         <v>-23.55494913771275</v>
@@ -50455,7 +50519,7 @@
         <v>-46.56193205957327</v>
       </c>
       <c r="I357" t="n">
-        <v>-21.40143581400335</v>
+        <v>-21.40143072668833</v>
       </c>
       <c r="J357" t="n">
         <v>-25.1228993751003</v>
@@ -50583,7 +50647,7 @@
         <v>-48.79726777384864</v>
       </c>
       <c r="I361" t="n">
-        <v>-16.44786678377885</v>
+        <v>-16.44787225268791</v>
       </c>
       <c r="J361" t="n">
         <v>-25.10526556717722</v>
@@ -50711,7 +50775,7 @@
         <v>-65.47643851235274</v>
       </c>
       <c r="I365" t="n">
-        <v>-22.14507660393162</v>
+        <v>-22.14508162884377</v>
       </c>
       <c r="J365" t="n">
         <v>-36.2810713427707</v>
@@ -50743,7 +50807,7 @@
         <v>-63.49094954563196</v>
       </c>
       <c r="I366" t="n">
-        <v>-20.31942334639192</v>
+        <v>-20.31942858529217</v>
       </c>
       <c r="J366" t="n">
         <v>-33.34146360071693</v>
@@ -50807,7 +50871,7 @@
         <v>-59.44152772284181</v>
       </c>
       <c r="I368" t="n">
-        <v>-19.10899357438787</v>
+        <v>-19.10899911917826</v>
       </c>
       <c r="J368" t="n">
         <v>-32.21799935619129</v>
@@ -50839,7 +50903,7 @@
         <v>-61.07611818254843</v>
       </c>
       <c r="I369" t="n">
-        <v>-19.0520801981543</v>
+        <v>-19.05207469725594</v>
       </c>
       <c r="J369" t="n">
         <v>-33.64509836007559</v>
@@ -50903,7 +50967,7 @@
         <v>-60.87988788615164</v>
       </c>
       <c r="I371" t="n">
-        <v>-15.5312900461311</v>
+        <v>-15.53129621110622</v>
       </c>
       <c r="J371" t="n">
         <v>-31.13156069349836</v>
@@ -50935,7 +50999,7 @@
         <v>-60.72807930150839</v>
       </c>
       <c r="I372" t="n">
-        <v>-13.58057886234917</v>
+        <v>-13.58057239703857</v>
       </c>
       <c r="J372" t="n">
         <v>-30.56008220994402</v>
@@ -51063,7 +51127,7 @@
         <v>-64.01993426427576</v>
       </c>
       <c r="I376" t="n">
-        <v>-19.42269217116194</v>
+        <v>-19.42269812521018</v>
       </c>
       <c r="J376" t="n">
         <v>-37.03804196560988</v>
@@ -51127,7 +51191,7 @@
         <v>-57.84704882559338</v>
       </c>
       <c r="I378" t="n">
-        <v>-16.06874881989406</v>
+        <v>-16.06874254111276</v>
       </c>
       <c r="J378" t="n">
         <v>-35.42445889479823</v>
@@ -51159,7 +51223,7 @@
         <v>-57.86270401296439</v>
       </c>
       <c r="I379" t="n">
-        <v>-14.80091095603907</v>
+        <v>-14.80091761121131</v>
       </c>
       <c r="J379" t="n">
         <v>-33.13288967690797</v>
@@ -51319,7 +51383,7 @@
         <v>-66.06225139522131</v>
       </c>
       <c r="I384" t="n">
-        <v>-24.65691069119804</v>
+        <v>-24.65691619437953</v>
       </c>
       <c r="J384" t="n">
         <v>-37.79134432087488</v>
@@ -51447,7 +51511,7 @@
         <v>-64.53946245251012</v>
       </c>
       <c r="I388" t="n">
-        <v>-8.856572706876376</v>
+        <v>-8.856579830449085</v>
       </c>
       <c r="J388" t="n">
         <v>-32.25516246566315</v>
@@ -51479,7 +51543,7 @@
         <v>-66.45546781840915</v>
       </c>
       <c r="I389" t="n">
-        <v>-14.83677254133186</v>
+        <v>-14.83676579389011</v>
       </c>
       <c r="J389" t="n">
         <v>-36.49303748442554</v>
@@ -51511,7 +51575,7 @@
         <v>-66.94776163626966</v>
       </c>
       <c r="I390" t="n">
-        <v>-13.80300167356505</v>
+        <v>-13.80299484421812</v>
       </c>
       <c r="J390" t="n">
         <v>-35.19079551224324</v>
@@ -51703,7 +51767,7 @@
         <v>-69.6705801911359</v>
       </c>
       <c r="I396" t="n">
-        <v>-15.75994642557669</v>
+        <v>-15.75995283260672</v>
       </c>
       <c r="J396" t="n">
         <v>-40.96782742221188</v>
@@ -51831,7 +51895,7 @@
         <v>-65.36158938197161</v>
       </c>
       <c r="I400" t="n">
-        <v>-10.88795150315567</v>
+        <v>-10.88795820863222</v>
       </c>
       <c r="J400" t="n">
         <v>-40.41598140815249</v>
@@ -51863,7 +51927,7 @@
         <v>-66.77216419841814</v>
       </c>
       <c r="I401" t="n">
-        <v>-12.15684976535586</v>
+        <v>-12.15685631369474</v>
       </c>
       <c r="J401" t="n">
         <v>-39.50416890022966</v>
@@ -51895,7 +51959,7 @@
         <v>-65.19273127014925</v>
       </c>
       <c r="I402" t="n">
-        <v>2.310069794177694</v>
+        <v>2.310061875786684</v>
       </c>
       <c r="J402" t="n">
         <v>-30.01208802421185</v>
@@ -51991,7 +52055,7 @@
         <v>-66.03487141927083</v>
       </c>
       <c r="I405" t="n">
-        <v>1.368362031563874</v>
+        <v>1.36837001768999</v>
       </c>
       <c r="J405" t="n">
         <v>-27.97435858310797</v>
@@ -52087,7 +52151,7 @@
         <v>-67.3025268904522</v>
       </c>
       <c r="I408" t="n">
-        <v>-5.191528209890328</v>
+        <v>-5.191521262247512</v>
       </c>
       <c r="J408" t="n">
         <v>-28.0659841371343</v>
@@ -52215,7 +52279,7 @@
         <v>-70.45633665272888</v>
       </c>
       <c r="I412" t="n">
-        <v>-8.24245399340221</v>
+        <v>-8.242447527285467</v>
       </c>
       <c r="J412" t="n">
         <v>-33.40224997914316</v>
@@ -52279,7 +52343,7 @@
         <v>-69.38107998017129</v>
       </c>
       <c r="I414" t="n">
-        <v>-7.644544630986704</v>
+        <v>-7.644551306655078</v>
       </c>
       <c r="J414" t="n">
         <v>-30.8268854251635</v>
@@ -52311,7 +52375,7 @@
         <v>-70.72855367660009</v>
       </c>
       <c r="I415" t="n">
-        <v>-8.69664441737773</v>
+        <v>-8.696650884443169</v>
       </c>
       <c r="J415" t="n">
         <v>-30.53675261541027</v>
@@ -52343,7 +52407,7 @@
         <v>-70.8881964147851</v>
       </c>
       <c r="I416" t="n">
-        <v>-5.721565130794593</v>
+        <v>-5.721571782936197</v>
       </c>
       <c r="J416" t="n">
         <v>-30.8217459147344</v>
@@ -52407,7 +52471,7 @@
         <v>-70.31578814024485</v>
       </c>
       <c r="I418" t="n">
-        <v>-6.077385767619159</v>
+        <v>-6.07737902106924</v>
       </c>
       <c r="J418" t="n">
         <v>-27.61620390111826</v>
@@ -52471,7 +52535,7 @@
         <v>-69.95980614914657</v>
       </c>
       <c r="I420" t="n">
-        <v>-8.179717415606557</v>
+        <v>-8.179710752009505</v>
       </c>
       <c r="J420" t="n">
         <v>-26.82353001014859</v>
@@ -52759,7 +52823,7 @@
         <v>-75.86762184320494</v>
       </c>
       <c r="I429" t="n">
-        <v>-18.76463099427176</v>
+        <v>-18.76462561086942</v>
       </c>
       <c r="J429" t="n">
         <v>-40.73101173639364</v>
@@ -52791,7 +52855,7 @@
         <v>-76.66848598030319</v>
       </c>
       <c r="I430" t="n">
-        <v>-17.167396650204</v>
+        <v>-17.1674021931759</v>
       </c>
       <c r="J430" t="n">
         <v>-40.24144910398108</v>
@@ -52983,7 +53047,7 @@
         <v>-77.08725196671594</v>
       </c>
       <c r="I436" t="n">
-        <v>-19.52655806860775</v>
+        <v>-19.52656340295372</v>
       </c>
       <c r="J436" t="n">
         <v>-46.51993029913489</v>
@@ -53143,7 +53207,7 @@
         <v>-77.44613900123169</v>
       </c>
       <c r="I441" t="n">
-        <v>-17.76891500921736</v>
+        <v>-17.76890968090208</v>
       </c>
       <c r="J441" t="n">
         <v>-54.40669531018253</v>
@@ -53335,7 +53399,7 @@
         <v>-79.37792374904173</v>
       </c>
       <c r="I447" t="n">
-        <v>-11.55112255709438</v>
+        <v>-11.5511279970311</v>
       </c>
       <c r="J447" t="n">
         <v>-61.48881251956044</v>
@@ -53367,7 +53431,7 @@
         <v>-78.79339341036149</v>
       </c>
       <c r="I448" t="n">
-        <v>-10.86656107571498</v>
+        <v>-10.86656670112384</v>
       </c>
       <c r="J448" t="n">
         <v>-60.23862992693305</v>
@@ -55327,34 +55391,98 @@
     </row>
     <row r="510">
       <c r="A510" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B510" t="n">
+        <v>-60.7675903852956</v>
+      </c>
+      <c r="C510" t="n">
+        <v>-25.0138969274723</v>
+      </c>
+      <c r="D510" t="n">
+        <v>-31.15747120734593</v>
+      </c>
+      <c r="E510" t="n">
+        <v>-25.83251281771577</v>
+      </c>
+      <c r="F510" t="n">
+        <v>-50.8668410367421</v>
+      </c>
+      <c r="G510" t="n">
+        <v>-8.673889995435225</v>
+      </c>
+      <c r="H510" t="n">
+        <v>-79.19348541398179</v>
+      </c>
+      <c r="I510" t="n">
+        <v>-22.98294933146208</v>
+      </c>
+      <c r="J510" t="n">
+        <v>-53.4913810042223</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="n">
         <v>46280</v>
       </c>
-      <c r="B510" t="n">
-        <v>-60.66098068016499</v>
-      </c>
-      <c r="C510" t="n">
-        <v>-26.01444919979885</v>
-      </c>
-      <c r="D510" t="n">
-        <v>-33.04172248217942</v>
-      </c>
-      <c r="E510" t="n">
-        <v>-27.21972159538363</v>
-      </c>
-      <c r="F510" t="n">
-        <v>-52.13943161434158</v>
-      </c>
-      <c r="G510" t="n">
-        <v>-10.28616449469456</v>
-      </c>
-      <c r="H510" t="n">
-        <v>-79.60837479752078</v>
-      </c>
-      <c r="I510" t="n">
-        <v>-24.44581276308396</v>
-      </c>
-      <c r="J510" t="n">
-        <v>-54.67672414856206</v>
+      <c r="B511" t="n">
+        <v>-60.17269378862111</v>
+      </c>
+      <c r="C511" t="n">
+        <v>-25.32959410980806</v>
+      </c>
+      <c r="D511" t="n">
+        <v>-32.90627201312483</v>
+      </c>
+      <c r="E511" t="n">
+        <v>-27.33665134068886</v>
+      </c>
+      <c r="F511" t="n">
+        <v>-52.12177048402666</v>
+      </c>
+      <c r="G511" t="n">
+        <v>-11.03860083553357</v>
+      </c>
+      <c r="H511" t="n">
+        <v>-78.81144206317028</v>
+      </c>
+      <c r="I511" t="n">
+        <v>-23.72589206117235</v>
+      </c>
+      <c r="J511" t="n">
+        <v>-54.07294110903968</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B512" t="n">
+        <v>-60.02137688354509</v>
+      </c>
+      <c r="C512" t="n">
+        <v>-26.91563219608577</v>
+      </c>
+      <c r="D512" t="n">
+        <v>-32.88590432201372</v>
+      </c>
+      <c r="E512" t="n">
+        <v>-28.53447284117577</v>
+      </c>
+      <c r="F512" t="n">
+        <v>-51.68331451035017</v>
+      </c>
+      <c r="G512" t="n">
+        <v>-10.97454065442049</v>
+      </c>
+      <c r="H512" t="n">
+        <v>-79.21774156631962</v>
+      </c>
+      <c r="I512" t="n">
+        <v>-24.5551381715447</v>
+      </c>
+      <c r="J512" t="n">
+        <v>-54.47973714772964</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Reliance Group.xlsx
+++ b/dashboards/Reliance Group.xlsx
@@ -493,13 +493,13 @@
         <v>91.84999847412109</v>
       </c>
       <c r="G2" t="n">
-        <v>1088.746704101562</v>
+        <v>1088.74658203125</v>
       </c>
       <c r="H2" t="n">
         <v>100.8000030517578</v>
       </c>
       <c r="I2" t="n">
-        <v>850.6759643554688</v>
+        <v>850.676025390625</v>
       </c>
       <c r="J2" t="n">
         <v>14.25</v>
@@ -522,13 +522,13 @@
         <v>90.40000152587891</v>
       </c>
       <c r="G3" t="n">
-        <v>1113.317626953125</v>
+        <v>1113.317504882812</v>
       </c>
       <c r="H3" t="n">
         <v>97.5</v>
       </c>
       <c r="I3" t="n">
-        <v>857.1109008789062</v>
+        <v>857.11083984375</v>
       </c>
       <c r="J3" t="n">
         <v>13.89999961853027</v>
@@ -557,7 +557,7 @@
         <v>97.05000305175781</v>
       </c>
       <c r="I4" t="n">
-        <v>844.1920166015625</v>
+        <v>844.1920776367188</v>
       </c>
       <c r="J4" t="n">
         <v>13.85000038146973</v>
@@ -580,13 +580,13 @@
         <v>89.90000152587891</v>
       </c>
       <c r="G5" t="n">
-        <v>1094.476196289062</v>
+        <v>1094.47607421875</v>
       </c>
       <c r="H5" t="n">
         <v>100.1500015258789</v>
       </c>
       <c r="I5" t="n">
-        <v>844.6340942382812</v>
+        <v>844.6341552734375</v>
       </c>
       <c r="J5" t="n">
         <v>14.30000019073486</v>
@@ -615,7 +615,7 @@
         <v>98.55000305175781</v>
       </c>
       <c r="I6" t="n">
-        <v>844.044677734375</v>
+        <v>844.0447387695312</v>
       </c>
       <c r="J6" t="n">
         <v>14.14999961853027</v>
@@ -644,7 +644,7 @@
         <v>103.4499969482422</v>
       </c>
       <c r="I7" t="n">
-        <v>939.3392944335938</v>
+        <v>939.3392333984375</v>
       </c>
       <c r="J7" t="n">
         <v>14.85000038146973</v>
@@ -667,13 +667,13 @@
         <v>89.34999847412109</v>
       </c>
       <c r="G8" t="n">
-        <v>1112.162719726562</v>
+        <v>1112.16259765625</v>
       </c>
       <c r="H8" t="n">
         <v>98.40000152587891</v>
       </c>
       <c r="I8" t="n">
-        <v>968.811767578125</v>
+        <v>968.8118896484375</v>
       </c>
       <c r="J8" t="n">
         <v>14.30000019073486</v>
@@ -702,7 +702,7 @@
         <v>96.40000152587891</v>
       </c>
       <c r="I9" t="n">
-        <v>941.8935546875</v>
+        <v>941.8934936523438</v>
       </c>
       <c r="J9" t="n">
         <v>14.35000038146973</v>
@@ -731,7 +731,7 @@
         <v>99.05000305175781</v>
       </c>
       <c r="I10" t="n">
-        <v>931.4307250976562</v>
+        <v>931.4307861328125</v>
       </c>
       <c r="J10" t="n">
         <v>14.25</v>
@@ -754,13 +754,13 @@
         <v>89.59999847412109</v>
       </c>
       <c r="G11" t="n">
-        <v>1149.958618164062</v>
+        <v>1149.958740234375</v>
       </c>
       <c r="H11" t="n">
         <v>102.75</v>
       </c>
       <c r="I11" t="n">
-        <v>931.5289916992188</v>
+        <v>931.529052734375</v>
       </c>
       <c r="J11" t="n">
         <v>14.94999980926514</v>
@@ -783,13 +783,13 @@
         <v>91.40000152587891</v>
       </c>
       <c r="G12" t="n">
-        <v>1155.959594726562</v>
+        <v>1155.959716796875</v>
       </c>
       <c r="H12" t="n">
         <v>105.5500030517578</v>
       </c>
       <c r="I12" t="n">
-        <v>934.6727294921875</v>
+        <v>934.6727905273438</v>
       </c>
       <c r="J12" t="n">
         <v>15.64999961853027</v>
@@ -818,7 +818,7 @@
         <v>101.9499969482422</v>
       </c>
       <c r="I13" t="n">
-        <v>930.4974975585938</v>
+        <v>930.49755859375</v>
       </c>
       <c r="J13" t="n">
         <v>16.10000038146973</v>
@@ -905,7 +905,7 @@
         <v>98.25</v>
       </c>
       <c r="I16" t="n">
-        <v>898.8637084960938</v>
+        <v>898.8635864257812</v>
       </c>
       <c r="J16" t="n">
         <v>16.04999923706055</v>
@@ -934,7 +934,7 @@
         <v>93.55000305175781</v>
       </c>
       <c r="I17" t="n">
-        <v>835.7432861328125</v>
+        <v>835.7432250976562</v>
       </c>
       <c r="J17" t="n">
         <v>15.25</v>
@@ -957,13 +957,13 @@
         <v>78</v>
       </c>
       <c r="G18" t="n">
-        <v>1074.887329101562</v>
+        <v>1074.887451171875</v>
       </c>
       <c r="H18" t="n">
         <v>98.05000305175781</v>
       </c>
       <c r="I18" t="n">
-        <v>835.7432861328125</v>
+        <v>835.7432250976562</v>
       </c>
       <c r="J18" t="n">
         <v>14.75</v>
@@ -1044,13 +1044,13 @@
         <v>82</v>
       </c>
       <c r="G21" t="n">
-        <v>1080.933837890625</v>
+        <v>1080.933959960938</v>
       </c>
       <c r="H21" t="n">
         <v>101.0500030517578</v>
       </c>
       <c r="I21" t="n">
-        <v>864.5281372070312</v>
+        <v>864.5280151367188</v>
       </c>
       <c r="J21" t="n">
         <v>14.80000019073486</v>
@@ -1079,7 +1079,7 @@
         <v>106.0999984741211</v>
       </c>
       <c r="I22" t="n">
-        <v>907.7544555664062</v>
+        <v>907.7545166015625</v>
       </c>
       <c r="J22" t="n">
         <v>15.5</v>
@@ -1102,13 +1102,13 @@
         <v>85.90000152587891</v>
       </c>
       <c r="G23" t="n">
-        <v>1079.552490234375</v>
+        <v>1079.552368164062</v>
       </c>
       <c r="H23" t="n">
         <v>110.0999984741211</v>
       </c>
       <c r="I23" t="n">
-        <v>921.5574340820312</v>
+        <v>921.5574951171875</v>
       </c>
       <c r="J23" t="n">
         <v>16.04999923706055</v>
@@ -1160,13 +1160,13 @@
         <v>85.44999694824219</v>
       </c>
       <c r="G25" t="n">
-        <v>1055.887573242188</v>
+        <v>1055.887451171875</v>
       </c>
       <c r="H25" t="n">
         <v>121.3499984741211</v>
       </c>
       <c r="I25" t="n">
-        <v>898.3724365234375</v>
+        <v>898.3723754882812</v>
       </c>
       <c r="J25" t="n">
         <v>17.64999961853027</v>
@@ -1189,13 +1189,13 @@
         <v>83.25</v>
       </c>
       <c r="G26" t="n">
-        <v>1049.4560546875</v>
+        <v>1049.456176757812</v>
       </c>
       <c r="H26" t="n">
         <v>133.4499969482422</v>
       </c>
       <c r="I26" t="n">
-        <v>874.79443359375</v>
+        <v>874.7943725585938</v>
       </c>
       <c r="J26" t="n">
         <v>18.5</v>
@@ -1224,7 +1224,7 @@
         <v>134.4499969482422</v>
       </c>
       <c r="I27" t="n">
-        <v>865.2158203125</v>
+        <v>865.2157592773438</v>
       </c>
       <c r="J27" t="n">
         <v>17.60000038146973</v>
@@ -1247,13 +1247,13 @@
         <v>87.75</v>
       </c>
       <c r="G28" t="n">
-        <v>1079.52978515625</v>
+        <v>1079.529907226562</v>
       </c>
       <c r="H28" t="n">
         <v>147.8500061035156</v>
       </c>
       <c r="I28" t="n">
-        <v>866.5421142578125</v>
+        <v>866.5420532226562</v>
       </c>
       <c r="J28" t="n">
         <v>17</v>
@@ -1276,13 +1276,13 @@
         <v>92.09999847412109</v>
       </c>
       <c r="G29" t="n">
-        <v>1078.42041015625</v>
+        <v>1078.420288085938</v>
       </c>
       <c r="H29" t="n">
         <v>133.1000061035156</v>
       </c>
       <c r="I29" t="n">
-        <v>879.5098876953125</v>
+        <v>879.510009765625</v>
       </c>
       <c r="J29" t="n">
         <v>16.14999961853027</v>
@@ -1340,7 +1340,7 @@
         <v>120.5999984741211</v>
       </c>
       <c r="I31" t="n">
-        <v>771.3457641601562</v>
+        <v>771.345703125</v>
       </c>
       <c r="J31" t="n">
         <v>15.19999980926514</v>
@@ -1363,13 +1363,13 @@
         <v>87.05000305175781</v>
       </c>
       <c r="G32" t="n">
-        <v>1095.132690429688</v>
+        <v>1095.1328125</v>
       </c>
       <c r="H32" t="n">
         <v>111.8499984741211</v>
       </c>
       <c r="I32" t="n">
-        <v>784.4609985351562</v>
+        <v>784.4610595703125</v>
       </c>
       <c r="J32" t="n">
         <v>14.55000019073486</v>
@@ -1392,13 +1392,13 @@
         <v>86.69999694824219</v>
       </c>
       <c r="G33" t="n">
-        <v>1092.868286132812</v>
+        <v>1092.868408203125</v>
       </c>
       <c r="H33" t="n">
         <v>122.5999984741211</v>
       </c>
       <c r="I33" t="n">
-        <v>794.4325561523438</v>
+        <v>794.4324951171875</v>
       </c>
       <c r="J33" t="n">
         <v>14.80000019073486</v>
@@ -1427,7 +1427,7 @@
         <v>113.3499984741211</v>
       </c>
       <c r="I34" t="n">
-        <v>801.113037109375</v>
+        <v>801.1129760742188</v>
       </c>
       <c r="J34" t="n">
         <v>14.14999961853027</v>
@@ -1456,7 +1456,7 @@
         <v>120.0999984741211</v>
       </c>
       <c r="I35" t="n">
-        <v>790.306396484375</v>
+        <v>790.3064575195312</v>
       </c>
       <c r="J35" t="n">
         <v>14.14999961853027</v>
@@ -1479,7 +1479,7 @@
         <v>82.15000152587891</v>
       </c>
       <c r="G36" t="n">
-        <v>1086.957885742188</v>
+        <v>1086.957763671875</v>
       </c>
       <c r="H36" t="n">
         <v>112.6999969482422</v>
@@ -1514,7 +1514,7 @@
         <v>114.3499984741211</v>
       </c>
       <c r="I37" t="n">
-        <v>725.5650024414062</v>
+        <v>725.5650634765625</v>
       </c>
       <c r="J37" t="n">
         <v>12.94999980926514</v>
@@ -1566,7 +1566,7 @@
         <v>74.75</v>
       </c>
       <c r="G39" t="n">
-        <v>1021.669555664062</v>
+        <v>1021.66943359375</v>
       </c>
       <c r="H39" t="n">
         <v>101.9499969482422</v>
@@ -1630,7 +1630,7 @@
         <v>104.5999984741211</v>
       </c>
       <c r="I41" t="n">
-        <v>686.1209106445312</v>
+        <v>686.1209716796875</v>
       </c>
       <c r="J41" t="n">
         <v>13.05000019073486</v>
@@ -1688,7 +1688,7 @@
         <v>106.4000015258789</v>
       </c>
       <c r="I43" t="n">
-        <v>688.6752319335938</v>
+        <v>688.6751708984375</v>
       </c>
       <c r="J43" t="n">
         <v>13.05000019073486</v>
@@ -1717,7 +1717,7 @@
         <v>103.5</v>
       </c>
       <c r="I44" t="n">
-        <v>674.7249755859375</v>
+        <v>674.7249145507812</v>
       </c>
       <c r="J44" t="n">
         <v>12.85000038146973</v>
@@ -1769,7 +1769,7 @@
         <v>74.09999847412109</v>
       </c>
       <c r="G46" t="n">
-        <v>1012.497924804688</v>
+        <v>1012.497985839844</v>
       </c>
       <c r="H46" t="n">
         <v>101.75</v>
@@ -1798,13 +1798,13 @@
         <v>77.80000305175781</v>
       </c>
       <c r="G47" t="n">
-        <v>1066.213989257812</v>
+        <v>1066.214111328125</v>
       </c>
       <c r="H47" t="n">
         <v>107.5</v>
       </c>
       <c r="I47" t="n">
-        <v>693.882080078125</v>
+        <v>693.8820190429688</v>
       </c>
       <c r="J47" t="n">
         <v>13.35000038146973</v>
@@ -1827,7 +1827,7 @@
         <v>78</v>
       </c>
       <c r="G48" t="n">
-        <v>1083.492797851562</v>
+        <v>1083.49267578125</v>
       </c>
       <c r="H48" t="n">
         <v>111.4000015258789</v>
@@ -1862,7 +1862,7 @@
         <v>122.5</v>
       </c>
       <c r="I49" t="n">
-        <v>746.5888061523438</v>
+        <v>746.5887451171875</v>
       </c>
       <c r="J49" t="n">
         <v>14.19999980926514</v>
@@ -1885,13 +1885,13 @@
         <v>76.5</v>
       </c>
       <c r="G50" t="n">
-        <v>1095.540283203125</v>
+        <v>1095.540405273438</v>
       </c>
       <c r="H50" t="n">
         <v>117.25</v>
       </c>
       <c r="I50" t="n">
-        <v>737.84521484375</v>
+        <v>737.8452758789062</v>
       </c>
       <c r="J50" t="n">
         <v>13.85000038146973</v>
@@ -1920,7 +1920,7 @@
         <v>115.5500030517578</v>
       </c>
       <c r="I51" t="n">
-        <v>747.3255615234375</v>
+        <v>747.3256225585938</v>
       </c>
       <c r="J51" t="n">
         <v>13.44999980926514</v>
@@ -1949,7 +1949,7 @@
         <v>118.9499969482422</v>
       </c>
       <c r="I52" t="n">
-        <v>750.5184936523438</v>
+        <v>750.5184326171875</v>
       </c>
       <c r="J52" t="n">
         <v>14.10000038146973</v>
@@ -1978,7 +1978,7 @@
         <v>116.8000030517578</v>
       </c>
       <c r="I53" t="n">
-        <v>758.7708129882812</v>
+        <v>758.770751953125</v>
       </c>
       <c r="J53" t="n">
         <v>13.75</v>
@@ -2036,7 +2036,7 @@
         <v>113.1500015258789</v>
       </c>
       <c r="I55" t="n">
-        <v>751.1079711914062</v>
+        <v>751.10791015625</v>
       </c>
       <c r="J55" t="n">
         <v>13</v>
@@ -2059,7 +2059,7 @@
         <v>81.65000152587891</v>
       </c>
       <c r="G56" t="n">
-        <v>1150.04931640625</v>
+        <v>1150.049194335938</v>
       </c>
       <c r="H56" t="n">
         <v>111.8000030517578</v>
@@ -2088,13 +2088,13 @@
         <v>85.55000305175781</v>
       </c>
       <c r="G57" t="n">
-        <v>1167.916748046875</v>
+        <v>1167.916870117188</v>
       </c>
       <c r="H57" t="n">
         <v>109.6999969482422</v>
       </c>
       <c r="I57" t="n">
-        <v>756.3638916015625</v>
+        <v>756.3638305664062</v>
       </c>
       <c r="J57" t="n">
         <v>13</v>
@@ -2117,7 +2117,7 @@
         <v>85.59999847412109</v>
       </c>
       <c r="G58" t="n">
-        <v>1175.706909179688</v>
+        <v>1175.70703125</v>
       </c>
       <c r="H58" t="n">
         <v>109.1999969482422</v>
@@ -2152,7 +2152,7 @@
         <v>100.6999969482422</v>
       </c>
       <c r="I59" t="n">
-        <v>731.4595947265625</v>
+        <v>731.4595336914062</v>
       </c>
       <c r="J59" t="n">
         <v>12.35000038146973</v>
@@ -2175,13 +2175,13 @@
         <v>84.30000305175781</v>
       </c>
       <c r="G60" t="n">
-        <v>1187.7998046875</v>
+        <v>1187.799926757812</v>
       </c>
       <c r="H60" t="n">
         <v>110.75</v>
       </c>
       <c r="I60" t="n">
-        <v>735.4383544921875</v>
+        <v>735.4382934570312</v>
       </c>
       <c r="J60" t="n">
         <v>12.94999980926514</v>
@@ -2233,7 +2233,7 @@
         <v>85.15000152587891</v>
       </c>
       <c r="G62" t="n">
-        <v>1193.325317382812</v>
+        <v>1193.325439453125</v>
       </c>
       <c r="H62" t="n">
         <v>112.3000030517578</v>
@@ -2262,7 +2262,7 @@
         <v>87.84999847412109</v>
       </c>
       <c r="G63" t="n">
-        <v>1202.882202148438</v>
+        <v>1202.882080078125</v>
       </c>
       <c r="H63" t="n">
         <v>122.6500015258789</v>
@@ -2297,7 +2297,7 @@
         <v>124.6999969482422</v>
       </c>
       <c r="I64" t="n">
-        <v>794.3343505859375</v>
+        <v>794.3342895507812</v>
       </c>
       <c r="J64" t="n">
         <v>14.85000038146973</v>
@@ -2320,13 +2320,13 @@
         <v>93.05000305175781</v>
       </c>
       <c r="G65" t="n">
-        <v>1189.385131835938</v>
+        <v>1189.38525390625</v>
       </c>
       <c r="H65" t="n">
         <v>132.1499938964844</v>
       </c>
       <c r="I65" t="n">
-        <v>804.305908203125</v>
+        <v>804.3058471679688</v>
       </c>
       <c r="J65" t="n">
         <v>15.55000019073486</v>
@@ -2349,13 +2349,13 @@
         <v>94.5</v>
       </c>
       <c r="G66" t="n">
-        <v>1186.214721679688</v>
+        <v>1186.214599609375</v>
       </c>
       <c r="H66" t="n">
         <v>136.1499938964844</v>
       </c>
       <c r="I66" t="n">
-        <v>822.1367797851562</v>
+        <v>822.13671875</v>
       </c>
       <c r="J66" t="n">
         <v>16.29999923706055</v>
@@ -2378,13 +2378,13 @@
         <v>96.30000305175781</v>
       </c>
       <c r="G67" t="n">
-        <v>1165.289916992188</v>
+        <v>1165.289794921875</v>
       </c>
       <c r="H67" t="n">
         <v>125.1500015258789</v>
       </c>
       <c r="I67" t="n">
-        <v>798.9517211914062</v>
+        <v>798.95166015625</v>
       </c>
       <c r="J67" t="n">
         <v>15.5</v>
@@ -2442,7 +2442,7 @@
         <v>125.8499984741211</v>
       </c>
       <c r="I69" t="n">
-        <v>816.3896484375</v>
+        <v>816.3895874023438</v>
       </c>
       <c r="J69" t="n">
         <v>15.69999980926514</v>
@@ -2465,7 +2465,7 @@
         <v>94.84999847412109</v>
       </c>
       <c r="G70" t="n">
-        <v>1159.945434570312</v>
+        <v>1159.945556640625</v>
       </c>
       <c r="H70" t="n">
         <v>122.9499969482422</v>
@@ -2500,7 +2500,7 @@
         <v>123.4000015258789</v>
       </c>
       <c r="I71" t="n">
-        <v>944.1531372070312</v>
+        <v>944.153076171875</v>
       </c>
       <c r="J71" t="n">
         <v>14.85000038146973</v>
@@ -2523,13 +2523,13 @@
         <v>103</v>
       </c>
       <c r="G72" t="n">
-        <v>1152.155151367188</v>
+        <v>1152.1552734375</v>
       </c>
       <c r="H72" t="n">
         <v>119.5500030517578</v>
       </c>
       <c r="I72" t="n">
-        <v>982.6148071289062</v>
+        <v>982.6146850585938</v>
       </c>
       <c r="J72" t="n">
         <v>14.39999961853027</v>
@@ -2558,7 +2558,7 @@
         <v>123.5999984741211</v>
       </c>
       <c r="I73" t="n">
-        <v>979.8148193359375</v>
+        <v>979.8148803710938</v>
       </c>
       <c r="J73" t="n">
         <v>14.39999961853027</v>
@@ -2581,13 +2581,13 @@
         <v>101.5500030517578</v>
       </c>
       <c r="G74" t="n">
-        <v>1231.234619140625</v>
+        <v>1231.234497070312</v>
       </c>
       <c r="H74" t="n">
         <v>125.75</v>
       </c>
       <c r="I74" t="n">
-        <v>945.7249145507812</v>
+        <v>945.7249755859375</v>
       </c>
       <c r="J74" t="n">
         <v>14.75</v>
@@ -2616,7 +2616,7 @@
         <v>130.3000030517578</v>
       </c>
       <c r="I75" t="n">
-        <v>987.232177734375</v>
+        <v>987.2321166992188</v>
       </c>
       <c r="J75" t="n">
         <v>15.14999961853027</v>
@@ -2645,7 +2645,7 @@
         <v>128.8999938964844</v>
       </c>
       <c r="I76" t="n">
-        <v>962.5243530273438</v>
+        <v>962.5242919921875</v>
       </c>
       <c r="J76" t="n">
         <v>14.94999980926514</v>
@@ -2668,13 +2668,13 @@
         <v>105.6999969482422</v>
       </c>
       <c r="G77" t="n">
-        <v>1220.613891601562</v>
+        <v>1220.61376953125</v>
       </c>
       <c r="H77" t="n">
         <v>123.25</v>
       </c>
       <c r="I77" t="n">
-        <v>902.3511352539062</v>
+        <v>902.3511962890625</v>
       </c>
       <c r="J77" t="n">
         <v>14.55000019073486</v>
@@ -2703,7 +2703,7 @@
         <v>121.1999969482422</v>
       </c>
       <c r="I78" t="n">
-        <v>926.4696044921875</v>
+        <v>926.4695434570312</v>
       </c>
       <c r="J78" t="n">
         <v>14.5</v>
@@ -2732,7 +2732,7 @@
         <v>123</v>
       </c>
       <c r="I79" t="n">
-        <v>1111.753662109375</v>
+        <v>1111.753784179688</v>
       </c>
       <c r="J79" t="n">
         <v>14.39999961853027</v>
@@ -2761,7 +2761,7 @@
         <v>120.5999984741211</v>
       </c>
       <c r="I80" t="n">
-        <v>1080.66015625</v>
+        <v>1080.660034179688</v>
       </c>
       <c r="J80" t="n">
         <v>13.94999980926514</v>
@@ -2790,7 +2790,7 @@
         <v>123.5500030517578</v>
       </c>
       <c r="I81" t="n">
-        <v>1086.947509765625</v>
+        <v>1086.947631835938</v>
       </c>
       <c r="J81" t="n">
         <v>14.25</v>
@@ -2848,7 +2848,7 @@
         <v>116.0999984741211</v>
       </c>
       <c r="I83" t="n">
-        <v>1001.13330078125</v>
+        <v>1001.133422851562</v>
       </c>
       <c r="J83" t="n">
         <v>13.55000019073486</v>
@@ -2906,7 +2906,7 @@
         <v>111.3000030517578</v>
       </c>
       <c r="I85" t="n">
-        <v>1049.32080078125</v>
+        <v>1049.321044921875</v>
       </c>
       <c r="J85" t="n">
         <v>13.10000038146973</v>
@@ -2929,7 +2929,7 @@
         <v>74.19999694824219</v>
       </c>
       <c r="G86" t="n">
-        <v>1140.583251953125</v>
+        <v>1140.583129882812</v>
       </c>
       <c r="H86" t="n">
         <v>112.3000030517578</v>
@@ -2987,7 +2987,7 @@
         <v>68.44999694824219</v>
       </c>
       <c r="G88" t="n">
-        <v>1109.331909179688</v>
+        <v>1109.331787109375</v>
       </c>
       <c r="H88" t="n">
         <v>101</v>
@@ -3016,13 +3016,13 @@
         <v>72.75</v>
       </c>
       <c r="G89" t="n">
-        <v>1086.731323242188</v>
+        <v>1086.731201171875</v>
       </c>
       <c r="H89" t="n">
         <v>100.9000015258789</v>
       </c>
       <c r="I89" t="n">
-        <v>943.9075317382812</v>
+        <v>943.907470703125</v>
       </c>
       <c r="J89" t="n">
         <v>12.39999961853027</v>
@@ -3109,7 +3109,7 @@
         <v>107.0500030517578</v>
       </c>
       <c r="I92" t="n">
-        <v>1028.100830078125</v>
+        <v>1028.100708007812</v>
       </c>
       <c r="J92" t="n">
         <v>12.44999980926514</v>
@@ -3138,7 +3138,7 @@
         <v>104.0999984741211</v>
       </c>
       <c r="I93" t="n">
-        <v>1021.714965820312</v>
+        <v>1021.715026855469</v>
       </c>
       <c r="J93" t="n">
         <v>12.44999980926514</v>
@@ -3167,7 +3167,7 @@
         <v>102.0999984741211</v>
       </c>
       <c r="I94" t="n">
-        <v>977.5062255859375</v>
+        <v>977.5061645507812</v>
       </c>
       <c r="J94" t="n">
         <v>12.30000019073486</v>
@@ -3196,7 +3196,7 @@
         <v>104</v>
       </c>
       <c r="I95" t="n">
-        <v>1021.665832519531</v>
+        <v>1021.665893554688</v>
       </c>
       <c r="J95" t="n">
         <v>12.85000038146973</v>
@@ -3219,7 +3219,7 @@
         <v>80.05000305175781</v>
       </c>
       <c r="G96" t="n">
-        <v>1180.711791992188</v>
+        <v>1180.711669921875</v>
       </c>
       <c r="H96" t="n">
         <v>101.6999969482422</v>
@@ -3248,13 +3248,13 @@
         <v>78.94999694824219</v>
       </c>
       <c r="G97" t="n">
-        <v>1184.765258789062</v>
+        <v>1184.765380859375</v>
       </c>
       <c r="H97" t="n">
         <v>100.9000015258789</v>
       </c>
       <c r="I97" t="n">
-        <v>945.7249145507812</v>
+        <v>945.7249755859375</v>
       </c>
       <c r="J97" t="n">
         <v>12.55000019073486</v>
@@ -3283,7 +3283,7 @@
         <v>100.6500015258789</v>
       </c>
       <c r="I98" t="n">
-        <v>869.9805297851562</v>
+        <v>869.98046875</v>
       </c>
       <c r="J98" t="n">
         <v>12.10000038146973</v>
@@ -3306,7 +3306,7 @@
         <v>71.59999847412109</v>
       </c>
       <c r="G99" t="n">
-        <v>1171.743896484375</v>
+        <v>1171.744018554688</v>
       </c>
       <c r="H99" t="n">
         <v>100.3499984741211</v>
@@ -3335,7 +3335,7 @@
         <v>71.65000152587891</v>
       </c>
       <c r="G100" t="n">
-        <v>1166.308837890625</v>
+        <v>1166.308959960938</v>
       </c>
       <c r="H100" t="n">
         <v>99.84999847412109</v>
@@ -3370,7 +3370,7 @@
         <v>102.5500030517578</v>
       </c>
       <c r="I101" t="n">
-        <v>914.9260864257812</v>
+        <v>914.9262084960938</v>
       </c>
       <c r="J101" t="n">
         <v>12</v>
@@ -3399,7 +3399,7 @@
         <v>107.9499969482422</v>
       </c>
       <c r="I102" t="n">
-        <v>909.1300048828125</v>
+        <v>909.1299438476562</v>
       </c>
       <c r="J102" t="n">
         <v>12.60000038146973</v>
@@ -3428,7 +3428,7 @@
         <v>108.0500030517578</v>
       </c>
       <c r="I103" t="n">
-        <v>929.4659423828125</v>
+        <v>929.4658813476562</v>
       </c>
       <c r="J103" t="n">
         <v>13.19999980926514</v>
@@ -3451,13 +3451,13 @@
         <v>76.5</v>
       </c>
       <c r="G104" t="n">
-        <v>1233.884399414062</v>
+        <v>1233.88427734375</v>
       </c>
       <c r="H104" t="n">
         <v>109.3000030517578</v>
       </c>
       <c r="I104" t="n">
-        <v>936.24462890625</v>
+        <v>936.2446899414062</v>
       </c>
       <c r="J104" t="n">
         <v>13.85000038146973</v>
@@ -3480,7 +3480,7 @@
         <v>76.59999847412109</v>
       </c>
       <c r="G105" t="n">
-        <v>1258.885375976562</v>
+        <v>1258.88525390625</v>
       </c>
       <c r="H105" t="n">
         <v>106.5999984741211</v>
@@ -3509,7 +3509,7 @@
         <v>74.65000152587891</v>
       </c>
       <c r="G106" t="n">
-        <v>1253.472900390625</v>
+        <v>1253.473022460938</v>
       </c>
       <c r="H106" t="n">
         <v>105.1500015258789</v>
@@ -3567,13 +3567,13 @@
         <v>80.05000305175781</v>
       </c>
       <c r="G108" t="n">
-        <v>1233.771118164062</v>
+        <v>1233.77099609375</v>
       </c>
       <c r="H108" t="n">
         <v>104.8499984741211</v>
       </c>
       <c r="I108" t="n">
-        <v>969.3522338867188</v>
+        <v>969.3521728515625</v>
       </c>
       <c r="J108" t="n">
         <v>13.85000038146973</v>
@@ -3596,13 +3596,13 @@
         <v>80.94999694824219</v>
       </c>
       <c r="G109" t="n">
-        <v>1267.60400390625</v>
+        <v>1267.603881835938</v>
       </c>
       <c r="H109" t="n">
         <v>104.4499969482422</v>
       </c>
       <c r="I109" t="n">
-        <v>974.7554931640625</v>
+        <v>974.7554321289062</v>
       </c>
       <c r="J109" t="n">
         <v>13.94999980926514</v>
@@ -3625,7 +3625,7 @@
         <v>78.59999847412109</v>
       </c>
       <c r="G110" t="n">
-        <v>1229.332397460938</v>
+        <v>1229.332641601562</v>
       </c>
       <c r="H110" t="n">
         <v>103.5999984741211</v>
@@ -3654,13 +3654,13 @@
         <v>73.55000305175781</v>
       </c>
       <c r="G111" t="n">
-        <v>1206.075073242188</v>
+        <v>1206.0751953125</v>
       </c>
       <c r="H111" t="n">
         <v>96.94999694824219</v>
       </c>
       <c r="I111" t="n">
-        <v>874.5487670898438</v>
+        <v>874.548828125</v>
       </c>
       <c r="J111" t="n">
         <v>12.89999961853027</v>
@@ -3712,13 +3712,13 @@
         <v>74.59999847412109</v>
       </c>
       <c r="G113" t="n">
-        <v>1175.910888671875</v>
+        <v>1175.910766601562</v>
       </c>
       <c r="H113" t="n">
         <v>95.5</v>
       </c>
       <c r="I113" t="n">
-        <v>876.5136108398438</v>
+        <v>876.513671875</v>
       </c>
       <c r="J113" t="n">
         <v>12.64999961853027</v>
@@ -3741,13 +3741,13 @@
         <v>67.25</v>
       </c>
       <c r="G114" t="n">
-        <v>1159.469848632812</v>
+        <v>1159.4697265625</v>
       </c>
       <c r="H114" t="n">
         <v>95.40000152587891</v>
       </c>
       <c r="I114" t="n">
-        <v>825.7225952148438</v>
+        <v>825.72265625</v>
       </c>
       <c r="J114" t="n">
         <v>12.05000019073486</v>
@@ -3770,13 +3770,13 @@
         <v>62.75</v>
       </c>
       <c r="G115" t="n">
-        <v>1173.057373046875</v>
+        <v>1173.057495117188</v>
       </c>
       <c r="H115" t="n">
         <v>95.59999847412109</v>
       </c>
       <c r="I115" t="n">
-        <v>833.4837036132812</v>
+        <v>833.483642578125</v>
       </c>
       <c r="J115" t="n">
         <v>12.14999961853027</v>
@@ -3834,7 +3834,7 @@
         <v>94.5</v>
       </c>
       <c r="I117" t="n">
-        <v>770.3141479492188</v>
+        <v>770.314208984375</v>
       </c>
       <c r="J117" t="n">
         <v>11.44999980926514</v>
@@ -3857,7 +3857,7 @@
         <v>59.15000152587891</v>
       </c>
       <c r="G118" t="n">
-        <v>1134.831176757812</v>
+        <v>1134.8310546875</v>
       </c>
       <c r="H118" t="n">
         <v>91.19999694824219</v>
@@ -3886,7 +3886,7 @@
         <v>61.40000152587891</v>
       </c>
       <c r="G119" t="n">
-        <v>1116.419921875</v>
+        <v>1116.420043945312</v>
       </c>
       <c r="H119" t="n">
         <v>90.30000305175781</v>
@@ -3921,7 +3921,7 @@
         <v>90.69999694824219</v>
       </c>
       <c r="I120" t="n">
-        <v>775.5701293945312</v>
+        <v>775.570068359375</v>
       </c>
       <c r="J120" t="n">
         <v>11.85000038146973</v>
@@ -3950,7 +3950,7 @@
         <v>93.09999847412109</v>
       </c>
       <c r="I121" t="n">
-        <v>801.5059204101562</v>
+        <v>801.5059814453125</v>
       </c>
       <c r="J121" t="n">
         <v>11.80000019073486</v>
@@ -3973,7 +3973,7 @@
         <v>67.80000305175781</v>
       </c>
       <c r="G122" t="n">
-        <v>1144.840454101562</v>
+        <v>1144.840576171875</v>
       </c>
       <c r="H122" t="n">
         <v>92.19999694824219</v>
@@ -4031,7 +4031,7 @@
         <v>69</v>
       </c>
       <c r="G124" t="n">
-        <v>1175.616577148438</v>
+        <v>1175.616455078125</v>
       </c>
       <c r="H124" t="n">
         <v>90.59999847412109</v>
@@ -4060,7 +4060,7 @@
         <v>67.65000152587891</v>
       </c>
       <c r="G125" t="n">
-        <v>1090.943359375</v>
+        <v>1090.943237304688</v>
       </c>
       <c r="H125" t="n">
         <v>91.09999847412109</v>
@@ -4089,13 +4089,13 @@
         <v>65.55000305175781</v>
       </c>
       <c r="G126" t="n">
-        <v>1093.2080078125</v>
+        <v>1093.207885742188</v>
       </c>
       <c r="H126" t="n">
         <v>94.5</v>
       </c>
       <c r="I126" t="n">
-        <v>935.7042846679688</v>
+        <v>935.704345703125</v>
       </c>
       <c r="J126" t="n">
         <v>11.35000038146973</v>
@@ -4124,7 +4124,7 @@
         <v>93.15000152587891</v>
       </c>
       <c r="I127" t="n">
-        <v>927.0098266601562</v>
+        <v>927.0098876953125</v>
       </c>
       <c r="J127" t="n">
         <v>11.35000038146973</v>
@@ -4147,7 +4147,7 @@
         <v>65.30000305175781</v>
       </c>
       <c r="G128" t="n">
-        <v>1092.369995117188</v>
+        <v>1092.3701171875</v>
       </c>
       <c r="H128" t="n">
         <v>91.75</v>
@@ -4176,7 +4176,7 @@
         <v>67.25</v>
       </c>
       <c r="G129" t="n">
-        <v>1081.61328125</v>
+        <v>1081.613403320312</v>
       </c>
       <c r="H129" t="n">
         <v>94.90000152587891</v>
@@ -4205,7 +4205,7 @@
         <v>67.40000152587891</v>
       </c>
       <c r="G130" t="n">
-        <v>1083.108032226562</v>
+        <v>1083.10791015625</v>
       </c>
       <c r="H130" t="n">
         <v>94.80000305175781</v>
@@ -4234,7 +4234,7 @@
         <v>68.30000305175781</v>
       </c>
       <c r="G131" t="n">
-        <v>1097.827880859375</v>
+        <v>1097.827758789062</v>
       </c>
       <c r="H131" t="n">
         <v>101.3499984741211</v>
@@ -4263,13 +4263,13 @@
         <v>69.19999694824219</v>
       </c>
       <c r="G132" t="n">
-        <v>1096.26513671875</v>
+        <v>1096.265014648438</v>
       </c>
       <c r="H132" t="n">
         <v>102.5999984741211</v>
       </c>
       <c r="I132" t="n">
-        <v>951.2265014648438</v>
+        <v>951.2265625</v>
       </c>
       <c r="J132" t="n">
         <v>11.5</v>
@@ -4292,7 +4292,7 @@
         <v>70.59999847412109</v>
       </c>
       <c r="G133" t="n">
-        <v>1076.834838867188</v>
+        <v>1076.8349609375</v>
       </c>
       <c r="H133" t="n">
         <v>101.6500015258789</v>
@@ -4321,7 +4321,7 @@
         <v>69.75</v>
       </c>
       <c r="G134" t="n">
-        <v>1085.712158203125</v>
+        <v>1085.712280273438</v>
       </c>
       <c r="H134" t="n">
         <v>100.4000015258789</v>
@@ -4379,13 +4379,13 @@
         <v>68.15000152587891</v>
       </c>
       <c r="G136" t="n">
-        <v>1097.080322265625</v>
+        <v>1097.08056640625</v>
       </c>
       <c r="H136" t="n">
         <v>102.25</v>
       </c>
       <c r="I136" t="n">
-        <v>964.4400634765625</v>
+        <v>964.4400024414062</v>
       </c>
       <c r="J136" t="n">
         <v>11.5</v>
@@ -4414,7 +4414,7 @@
         <v>102.3000030517578</v>
       </c>
       <c r="I137" t="n">
-        <v>978.8324584960938</v>
+        <v>978.8323974609375</v>
       </c>
       <c r="J137" t="n">
         <v>11.80000019073486</v>
@@ -4443,7 +4443,7 @@
         <v>104.4000015258789</v>
       </c>
       <c r="I138" t="n">
-        <v>959.67529296875</v>
+        <v>959.6753540039062</v>
       </c>
       <c r="J138" t="n">
         <v>11.85000038146973</v>
@@ -4472,7 +4472,7 @@
         <v>105.8000030517578</v>
       </c>
       <c r="I139" t="n">
-        <v>961.934814453125</v>
+        <v>961.9349365234375</v>
       </c>
       <c r="J139" t="n">
         <v>11.85000038146973</v>
@@ -4495,13 +4495,13 @@
         <v>63.75</v>
       </c>
       <c r="G140" t="n">
-        <v>1133.698852539062</v>
+        <v>1133.698974609375</v>
       </c>
       <c r="H140" t="n">
         <v>104.5</v>
       </c>
       <c r="I140" t="n">
-        <v>971.4151611328125</v>
+        <v>971.4152221679688</v>
       </c>
       <c r="J140" t="n">
         <v>11.75</v>
@@ -4524,7 +4524,7 @@
         <v>62.95000076293945</v>
       </c>
       <c r="G141" t="n">
-        <v>1096.242553710938</v>
+        <v>1096.242431640625</v>
       </c>
       <c r="H141" t="n">
         <v>104.25</v>
@@ -4559,7 +4559,7 @@
         <v>113.9000015258789</v>
       </c>
       <c r="I142" t="n">
-        <v>945.1355590820312</v>
+        <v>945.135498046875</v>
       </c>
       <c r="J142" t="n">
         <v>11.89999961853027</v>
@@ -4588,7 +4588,7 @@
         <v>115.8499984741211</v>
       </c>
       <c r="I143" t="n">
-        <v>945.8231811523438</v>
+        <v>945.8232421875</v>
       </c>
       <c r="J143" t="n">
         <v>11.89999961853027</v>
@@ -4611,7 +4611,7 @@
         <v>65.15000152587891</v>
       </c>
       <c r="G144" t="n">
-        <v>1112.864501953125</v>
+        <v>1112.864624023438</v>
       </c>
       <c r="H144" t="n">
         <v>114.25</v>
@@ -4640,13 +4640,13 @@
         <v>64.90000152587891</v>
       </c>
       <c r="G145" t="n">
-        <v>1136.574829101562</v>
+        <v>1136.57470703125</v>
       </c>
       <c r="H145" t="n">
         <v>117.0999984741211</v>
       </c>
       <c r="I145" t="n">
-        <v>964.6856079101562</v>
+        <v>964.6856689453125</v>
       </c>
       <c r="J145" t="n">
         <v>12.39999961853027</v>
@@ -4669,13 +4669,13 @@
         <v>66.94999694824219</v>
       </c>
       <c r="G146" t="n">
-        <v>1166.19580078125</v>
+        <v>1166.195678710938</v>
       </c>
       <c r="H146" t="n">
         <v>123.25</v>
       </c>
       <c r="I146" t="n">
-        <v>1014.592468261719</v>
+        <v>1014.592407226562</v>
       </c>
       <c r="J146" t="n">
         <v>13</v>
@@ -4698,7 +4698,7 @@
         <v>68.05000305175781</v>
       </c>
       <c r="G147" t="n">
-        <v>1170.63427734375</v>
+        <v>1170.634399414062</v>
       </c>
       <c r="H147" t="n">
         <v>128.6999969482422</v>
@@ -4762,7 +4762,7 @@
         <v>121.3499984741211</v>
       </c>
       <c r="I149" t="n">
-        <v>952.7492065429688</v>
+        <v>952.749267578125</v>
       </c>
       <c r="J149" t="n">
         <v>13.19999980926514</v>
@@ -4791,7 +4791,7 @@
         <v>120</v>
       </c>
       <c r="I150" t="n">
-        <v>942.041015625</v>
+        <v>942.0408935546875</v>
       </c>
       <c r="J150" t="n">
         <v>13.14999961853027</v>
@@ -4814,13 +4814,13 @@
         <v>67.5</v>
       </c>
       <c r="G151" t="n">
-        <v>1162.708251953125</v>
+        <v>1162.708129882812</v>
       </c>
       <c r="H151" t="n">
         <v>115.8499984741211</v>
       </c>
       <c r="I151" t="n">
-        <v>944.791748046875</v>
+        <v>944.7916870117188</v>
       </c>
       <c r="J151" t="n">
         <v>13.30000019073486</v>
@@ -4849,7 +4849,7 @@
         <v>117.5500030517578</v>
       </c>
       <c r="I152" t="n">
-        <v>944.4969482421875</v>
+        <v>944.4968872070312</v>
       </c>
       <c r="J152" t="n">
         <v>14.14999961853027</v>
@@ -4878,7 +4878,7 @@
         <v>115.3499984741211</v>
       </c>
       <c r="I153" t="n">
-        <v>953.8790283203125</v>
+        <v>953.8790893554688</v>
       </c>
       <c r="J153" t="n">
         <v>13.60000038146973</v>
@@ -4901,13 +4901,13 @@
         <v>68.34999847412109</v>
       </c>
       <c r="G154" t="n">
-        <v>1192.53271484375</v>
+        <v>1192.532836914062</v>
       </c>
       <c r="H154" t="n">
         <v>115.1500015258789</v>
       </c>
       <c r="I154" t="n">
-        <v>954.0264282226562</v>
+        <v>954.0263671875</v>
       </c>
       <c r="J154" t="n">
         <v>13.39999961853027</v>
@@ -4930,7 +4930,7 @@
         <v>71.90000152587891</v>
       </c>
       <c r="G155" t="n">
-        <v>1200.8212890625</v>
+        <v>1200.821166992188</v>
       </c>
       <c r="H155" t="n">
         <v>116.5500030517578</v>
@@ -4959,7 +4959,7 @@
         <v>72.55000305175781</v>
       </c>
       <c r="G156" t="n">
-        <v>1207.094360351562</v>
+        <v>1207.09423828125</v>
       </c>
       <c r="H156" t="n">
         <v>121.8000030517578</v>
@@ -4994,7 +4994,7 @@
         <v>129.8999938964844</v>
       </c>
       <c r="I157" t="n">
-        <v>1020.879943847656</v>
+        <v>1020.880004882812</v>
       </c>
       <c r="J157" t="n">
         <v>14.19999980926514</v>
@@ -5023,7 +5023,7 @@
         <v>135.6000061035156</v>
       </c>
       <c r="I158" t="n">
-        <v>1000.396484375</v>
+        <v>1000.396545410156</v>
       </c>
       <c r="J158" t="n">
         <v>14.94999980926514</v>
@@ -5052,7 +5052,7 @@
         <v>140.6999969482422</v>
       </c>
       <c r="I159" t="n">
-        <v>973.0361328125</v>
+        <v>973.0361938476562</v>
       </c>
       <c r="J159" t="n">
         <v>15.64999961853027</v>
@@ -5075,7 +5075,7 @@
         <v>72.25</v>
       </c>
       <c r="G160" t="n">
-        <v>1202.694580078125</v>
+        <v>1202.694458007812</v>
       </c>
       <c r="H160" t="n">
         <v>138.6999969482422</v>
@@ -5133,13 +5133,13 @@
         <v>74.05000305175781</v>
       </c>
       <c r="G162" t="n">
-        <v>1195.9921875</v>
+        <v>1195.992065429688</v>
       </c>
       <c r="H162" t="n">
         <v>139.75</v>
       </c>
       <c r="I162" t="n">
-        <v>1002.852600097656</v>
+        <v>1002.8525390625</v>
       </c>
       <c r="J162" t="n">
         <v>15.05000019073486</v>
@@ -5226,7 +5226,7 @@
         <v>162</v>
       </c>
       <c r="I165" t="n">
-        <v>1006.291076660156</v>
+        <v>1006.291137695312</v>
       </c>
       <c r="J165" t="n">
         <v>16.79999923706055</v>
@@ -5255,7 +5255,7 @@
         <v>193.8500061035156</v>
       </c>
       <c r="I166" t="n">
-        <v>1039.644165039062</v>
+        <v>1039.644287109375</v>
       </c>
       <c r="J166" t="n">
         <v>20.14999961853027</v>
@@ -5278,7 +5278,7 @@
         <v>71.69999694824219</v>
       </c>
       <c r="G167" t="n">
-        <v>1149.848266601562</v>
+        <v>1149.84814453125</v>
       </c>
       <c r="H167" t="n">
         <v>179.1499938964844</v>
@@ -5342,7 +5342,7 @@
         <v>178.75</v>
       </c>
       <c r="I169" t="n">
-        <v>1173.302124023438</v>
+        <v>1173.30224609375</v>
       </c>
       <c r="J169" t="n">
         <v>21.95000076293945</v>
@@ -5365,13 +5365,13 @@
         <v>75.09999847412109</v>
       </c>
       <c r="G170" t="n">
-        <v>1173.136108398438</v>
+        <v>1173.135986328125</v>
       </c>
       <c r="H170" t="n">
         <v>180.6999969482422</v>
       </c>
       <c r="I170" t="n">
-        <v>1191.771606445312</v>
+        <v>1191.771484375</v>
       </c>
       <c r="J170" t="n">
         <v>21.64999961853027</v>
@@ -5394,7 +5394,7 @@
         <v>73.65000152587891</v>
       </c>
       <c r="G171" t="n">
-        <v>1174.794677734375</v>
+        <v>1174.794555664062</v>
       </c>
       <c r="H171" t="n">
         <v>180.3000030517578</v>
@@ -5423,13 +5423,13 @@
         <v>74.05000305175781</v>
       </c>
       <c r="G172" t="n">
-        <v>1167.478881835938</v>
+        <v>1167.478759765625</v>
       </c>
       <c r="H172" t="n">
         <v>162.4499969482422</v>
       </c>
       <c r="I172" t="n">
-        <v>1153.80126953125</v>
+        <v>1153.801025390625</v>
       </c>
       <c r="J172" t="n">
         <v>19.20000076293945</v>
@@ -5481,13 +5481,13 @@
         <v>74.15000152587891</v>
       </c>
       <c r="G174" t="n">
-        <v>1190.403076171875</v>
+        <v>1190.402954101562</v>
       </c>
       <c r="H174" t="n">
         <v>165.5</v>
       </c>
       <c r="I174" t="n">
-        <v>1137.443969726562</v>
+        <v>1137.44384765625</v>
       </c>
       <c r="J174" t="n">
         <v>20.04999923706055</v>
@@ -5516,7 +5516,7 @@
         <v>157.4499969482422</v>
       </c>
       <c r="I175" t="n">
-        <v>1151.19775390625</v>
+        <v>1151.197875976562</v>
       </c>
       <c r="J175" t="n">
         <v>19.04999923706055</v>
@@ -5568,13 +5568,13 @@
         <v>68.65000152587891</v>
       </c>
       <c r="G177" t="n">
-        <v>1135.625610351562</v>
+        <v>1135.625732421875</v>
       </c>
       <c r="H177" t="n">
         <v>156.3500061035156</v>
       </c>
       <c r="I177" t="n">
-        <v>1119.121948242188</v>
+        <v>1119.121704101562</v>
       </c>
       <c r="J177" t="n">
         <v>18.45000076293945</v>
@@ -5597,7 +5597,7 @@
         <v>67.05000305175781</v>
       </c>
       <c r="G178" t="n">
-        <v>1137.1025390625</v>
+        <v>1137.102416992188</v>
       </c>
       <c r="H178" t="n">
         <v>151.8000030517578</v>
@@ -5655,7 +5655,7 @@
         <v>69.90000152587891</v>
       </c>
       <c r="G180" t="n">
-        <v>1140.419555664062</v>
+        <v>1140.419677734375</v>
       </c>
       <c r="H180" t="n">
         <v>146.75</v>
@@ -5719,7 +5719,7 @@
         <v>144.1499938964844</v>
       </c>
       <c r="I182" t="n">
-        <v>1157.628051757812</v>
+        <v>1157.628173828125</v>
       </c>
       <c r="J182" t="n">
         <v>16.89999961853027</v>
@@ -5748,7 +5748,7 @@
         <v>137.1999969482422</v>
       </c>
       <c r="I183" t="n">
-        <v>1051.69970703125</v>
+        <v>1051.699829101562</v>
       </c>
       <c r="J183" t="n">
         <v>16.35000038146973</v>
@@ -5800,13 +5800,13 @@
         <v>61.70000076293945</v>
       </c>
       <c r="G185" t="n">
-        <v>1059.855102539062</v>
+        <v>1059.855224609375</v>
       </c>
       <c r="H185" t="n">
         <v>136.3500061035156</v>
       </c>
       <c r="I185" t="n">
-        <v>1021.610595703125</v>
+        <v>1021.610412597656</v>
       </c>
       <c r="J185" t="n">
         <v>16.10000038146973</v>
@@ -5829,7 +5829,7 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G186" t="n">
-        <v>1056.606323242188</v>
+        <v>1056.606201171875</v>
       </c>
       <c r="H186" t="n">
         <v>137.6499938964844</v>
@@ -5864,7 +5864,7 @@
         <v>136.6999969482422</v>
       </c>
       <c r="I187" t="n">
-        <v>1060.416381835938</v>
+        <v>1060.41650390625</v>
       </c>
       <c r="J187" t="n">
         <v>16.39999961853027</v>
@@ -5887,13 +5887,13 @@
         <v>63.95000076293945</v>
       </c>
       <c r="G188" t="n">
-        <v>1076.690551757812</v>
+        <v>1076.690673828125</v>
       </c>
       <c r="H188" t="n">
         <v>135.4499969482422</v>
       </c>
       <c r="I188" t="n">
-        <v>1031.90283203125</v>
+        <v>1031.902709960938</v>
       </c>
       <c r="J188" t="n">
         <v>16.45000076293945</v>
@@ -5945,7 +5945,7 @@
         <v>67.30000305175781</v>
       </c>
       <c r="G190" t="n">
-        <v>1100.591796875</v>
+        <v>1100.591674804688</v>
       </c>
       <c r="H190" t="n">
         <v>144.3999938964844</v>
@@ -5974,7 +5974,7 @@
         <v>68.19999694824219</v>
       </c>
       <c r="G191" t="n">
-        <v>1105.249389648438</v>
+        <v>1105.249267578125</v>
       </c>
       <c r="H191" t="n">
         <v>151.6000061035156</v>
@@ -6003,7 +6003,7 @@
         <v>67.25</v>
       </c>
       <c r="G192" t="n">
-        <v>1093.185302734375</v>
+        <v>1093.185180664062</v>
       </c>
       <c r="H192" t="n">
         <v>157.6999969482422</v>
@@ -6125,7 +6125,7 @@
         <v>138.8500061035156</v>
       </c>
       <c r="I196" t="n">
-        <v>1100.404296875</v>
+        <v>1100.404174804688</v>
       </c>
       <c r="J196" t="n">
         <v>16.20000076293945</v>
@@ -6154,7 +6154,7 @@
         <v>138.6999969482422</v>
       </c>
       <c r="I197" t="n">
-        <v>1122.564819335938</v>
+        <v>1122.56494140625</v>
       </c>
       <c r="J197" t="n">
         <v>16.20000076293945</v>
@@ -6206,7 +6206,7 @@
         <v>65.59999847412109</v>
       </c>
       <c r="G199" t="n">
-        <v>1133.217529296875</v>
+        <v>1133.217407226562</v>
       </c>
       <c r="H199" t="n">
         <v>141.3500061035156</v>
@@ -6264,13 +6264,13 @@
         <v>63.70000076293945</v>
       </c>
       <c r="G201" t="n">
-        <v>1123.084228515625</v>
+        <v>1123.084350585938</v>
       </c>
       <c r="H201" t="n">
         <v>139.1499938964844</v>
       </c>
       <c r="I201" t="n">
-        <v>1088.585083007812</v>
+        <v>1088.585205078125</v>
       </c>
       <c r="J201" t="n">
         <v>16.35000038146973</v>
@@ -6322,13 +6322,13 @@
         <v>65.05000305175781</v>
       </c>
       <c r="G203" t="n">
-        <v>1109.4296875</v>
+        <v>1109.429809570312</v>
       </c>
       <c r="H203" t="n">
         <v>141.6000061035156</v>
       </c>
       <c r="I203" t="n">
-        <v>1089.7177734375</v>
+        <v>1089.717895507812</v>
       </c>
       <c r="J203" t="n">
         <v>16.29999923706055</v>
@@ -6357,7 +6357,7 @@
         <v>141.8500061035156</v>
       </c>
       <c r="I204" t="n">
-        <v>1086.566040039062</v>
+        <v>1086.56591796875</v>
       </c>
       <c r="J204" t="n">
         <v>16.14999961853027</v>
@@ -6380,13 +6380,13 @@
         <v>63.25</v>
       </c>
       <c r="G205" t="n">
-        <v>1147.871704101562</v>
+        <v>1147.871826171875</v>
       </c>
       <c r="H205" t="n">
         <v>141.8999938964844</v>
       </c>
       <c r="I205" t="n">
-        <v>1081.690673828125</v>
+        <v>1081.690551757812</v>
       </c>
       <c r="J205" t="n">
         <v>16</v>
@@ -6409,13 +6409,13 @@
         <v>64.15000152587891</v>
       </c>
       <c r="G206" t="n">
-        <v>1158.527221679688</v>
+        <v>1158.527099609375</v>
       </c>
       <c r="H206" t="n">
         <v>141.4499969482422</v>
       </c>
       <c r="I206" t="n">
-        <v>1081.542846679688</v>
+        <v>1081.54296875</v>
       </c>
       <c r="J206" t="n">
         <v>16.10000038146973</v>
@@ -6438,13 +6438,13 @@
         <v>62.90000152587891</v>
       </c>
       <c r="G207" t="n">
-        <v>1149.552856445312</v>
+        <v>1149.552978515625</v>
       </c>
       <c r="H207" t="n">
         <v>140.6499938964844</v>
       </c>
       <c r="I207" t="n">
-        <v>1085.728759765625</v>
+        <v>1085.72900390625</v>
       </c>
       <c r="J207" t="n">
         <v>16.04999923706055</v>
@@ -6467,13 +6467,13 @@
         <v>63.20000076293945</v>
       </c>
       <c r="G208" t="n">
-        <v>1156.732421875</v>
+        <v>1156.732299804688</v>
       </c>
       <c r="H208" t="n">
         <v>140.5500030517578</v>
       </c>
       <c r="I208" t="n">
-        <v>1097.301513671875</v>
+        <v>1097.301635742188</v>
       </c>
       <c r="J208" t="n">
         <v>16.10000038146973</v>
@@ -6583,7 +6583,7 @@
         <v>65.25</v>
       </c>
       <c r="G212" t="n">
-        <v>1183.246459960938</v>
+        <v>1183.246337890625</v>
       </c>
       <c r="H212" t="n">
         <v>146.6499938964844</v>
@@ -6618,7 +6618,7 @@
         <v>142.8500061035156</v>
       </c>
       <c r="I213" t="n">
-        <v>1053.669555664062</v>
+        <v>1053.669677734375</v>
       </c>
       <c r="J213" t="n">
         <v>16.10000038146973</v>
@@ -6641,13 +6641,13 @@
         <v>63.95000076293945</v>
       </c>
       <c r="G214" t="n">
-        <v>1195.878540039062</v>
+        <v>1195.878662109375</v>
       </c>
       <c r="H214" t="n">
         <v>146.1999969482422</v>
       </c>
       <c r="I214" t="n">
-        <v>1057.264526367188</v>
+        <v>1057.2646484375</v>
       </c>
       <c r="J214" t="n">
         <v>16</v>
@@ -6699,7 +6699,7 @@
         <v>63.04999923706055</v>
       </c>
       <c r="G216" t="n">
-        <v>1184.745971679688</v>
+        <v>1184.745849609375</v>
       </c>
       <c r="H216" t="n">
         <v>151.3500061035156</v>
@@ -6734,7 +6734,7 @@
         <v>148.6499938964844</v>
       </c>
       <c r="I217" t="n">
-        <v>1012.499938964844</v>
+        <v>1012.499816894531</v>
       </c>
       <c r="J217" t="n">
         <v>16</v>
@@ -6815,13 +6815,13 @@
         <v>60.75</v>
       </c>
       <c r="G220" t="n">
-        <v>1159.117919921875</v>
+        <v>1159.118041992188</v>
       </c>
       <c r="H220" t="n">
         <v>145.25</v>
       </c>
       <c r="I220" t="n">
-        <v>978.766357421875</v>
+        <v>978.7662963867188</v>
       </c>
       <c r="J220" t="n">
         <v>15.5</v>
@@ -6850,7 +6850,7 @@
         <v>141.3000030517578</v>
       </c>
       <c r="I221" t="n">
-        <v>985.06982421875</v>
+        <v>985.0698852539062</v>
       </c>
       <c r="J221" t="n">
         <v>15.05000019073486</v>
@@ -6937,7 +6937,7 @@
         <v>154.3000030517578</v>
       </c>
       <c r="I224" t="n">
-        <v>1008.067810058594</v>
+        <v>1008.067749023438</v>
       </c>
       <c r="J224" t="n">
         <v>16</v>
@@ -6960,7 +6960,7 @@
         <v>63.75</v>
       </c>
       <c r="G225" t="n">
-        <v>1230.299072265625</v>
+        <v>1230.299194335938</v>
       </c>
       <c r="H225" t="n">
         <v>153.6499938964844</v>
@@ -7047,7 +7047,7 @@
         <v>73.40000152587891</v>
       </c>
       <c r="G228" t="n">
-        <v>1237.455688476562</v>
+        <v>1237.455810546875</v>
       </c>
       <c r="H228" t="n">
         <v>156.1000061035156</v>
@@ -7111,7 +7111,7 @@
         <v>157.8999938964844</v>
       </c>
       <c r="I230" t="n">
-        <v>1054.162109375</v>
+        <v>1054.162231445312</v>
       </c>
       <c r="J230" t="n">
         <v>16.04999923706055</v>
@@ -7140,7 +7140,7 @@
         <v>156.3999938964844</v>
       </c>
       <c r="I231" t="n">
-        <v>1050.41943359375</v>
+        <v>1050.419555664062</v>
       </c>
       <c r="J231" t="n">
         <v>15.85000038146973</v>
@@ -7169,7 +7169,7 @@
         <v>154.1999969482422</v>
       </c>
       <c r="I232" t="n">
-        <v>1031.90283203125</v>
+        <v>1031.902709960938</v>
       </c>
       <c r="J232" t="n">
         <v>15.69999980926514</v>
@@ -7221,13 +7221,13 @@
         <v>72.90000152587891</v>
       </c>
       <c r="G234" t="n">
-        <v>1185.563842773438</v>
+        <v>1185.56396484375</v>
       </c>
       <c r="H234" t="n">
         <v>154.75</v>
       </c>
       <c r="I234" t="n">
-        <v>1009.988342285156</v>
+        <v>1009.98828125</v>
       </c>
       <c r="J234" t="n">
         <v>15.89999961853027</v>
@@ -7256,7 +7256,7 @@
         <v>161.8000030517578</v>
       </c>
       <c r="I235" t="n">
-        <v>1015.454711914062</v>
+        <v>1015.454650878906</v>
       </c>
       <c r="J235" t="n">
         <v>15.94999980926514</v>
@@ -7285,7 +7285,7 @@
         <v>157.25</v>
       </c>
       <c r="I236" t="n">
-        <v>1016.488952636719</v>
+        <v>1016.488891601562</v>
       </c>
       <c r="J236" t="n">
         <v>15.75</v>
@@ -7366,13 +7366,13 @@
         <v>71.84999847412109</v>
       </c>
       <c r="G239" t="n">
-        <v>1165.797607421875</v>
+        <v>1165.797485351562</v>
       </c>
       <c r="H239" t="n">
         <v>151.1000061035156</v>
       </c>
       <c r="I239" t="n">
-        <v>982.7552490234375</v>
+        <v>982.7553100585938</v>
       </c>
       <c r="J239" t="n">
         <v>15.75</v>
@@ -7424,13 +7424,13 @@
         <v>71.34999847412109</v>
       </c>
       <c r="G241" t="n">
-        <v>1191.334716796875</v>
+        <v>1191.334594726562</v>
       </c>
       <c r="H241" t="n">
         <v>149.8000030517578</v>
       </c>
       <c r="I241" t="n">
-        <v>982.2135620117188</v>
+        <v>982.213623046875</v>
       </c>
       <c r="J241" t="n">
         <v>15.75</v>
@@ -7511,13 +7511,13 @@
         <v>60.59999847412109</v>
       </c>
       <c r="G244" t="n">
-        <v>1136.988891601562</v>
+        <v>1136.98876953125</v>
       </c>
       <c r="H244" t="n">
         <v>128.6999969482422</v>
       </c>
       <c r="I244" t="n">
-        <v>796.0140380859375</v>
+        <v>796.0140991210938</v>
       </c>
       <c r="J244" t="n">
         <v>13.55000019073486</v>
@@ -7540,7 +7540,7 @@
         <v>62.90000152587891</v>
       </c>
       <c r="G245" t="n">
-        <v>1146.917358398438</v>
+        <v>1146.917236328125</v>
       </c>
       <c r="H245" t="n">
         <v>128.1999969482422</v>
@@ -7569,13 +7569,13 @@
         <v>65.80000305175781</v>
       </c>
       <c r="G246" t="n">
-        <v>1156.30078125</v>
+        <v>1156.300659179688</v>
       </c>
       <c r="H246" t="n">
         <v>134.6000061035156</v>
       </c>
       <c r="I246" t="n">
-        <v>890.7142944335938</v>
+        <v>890.71435546875</v>
       </c>
       <c r="J246" t="n">
         <v>14.80000019073486</v>
@@ -7598,7 +7598,7 @@
         <v>67.05000305175781</v>
       </c>
       <c r="G247" t="n">
-        <v>1156.187133789062</v>
+        <v>1156.187255859375</v>
       </c>
       <c r="H247" t="n">
         <v>136.5</v>
@@ -7633,7 +7633,7 @@
         <v>135.8000030517578</v>
       </c>
       <c r="I248" t="n">
-        <v>928.7815551757812</v>
+        <v>928.7816162109375</v>
       </c>
       <c r="J248" t="n">
         <v>14.30000019073486</v>
@@ -7656,13 +7656,13 @@
         <v>66.09999847412109</v>
       </c>
       <c r="G249" t="n">
-        <v>1157.4365234375</v>
+        <v>1157.436645507812</v>
       </c>
       <c r="H249" t="n">
         <v>137.6999969482422</v>
       </c>
       <c r="I249" t="n">
-        <v>930.1111450195312</v>
+        <v>930.1112670898438</v>
       </c>
       <c r="J249" t="n">
         <v>14.35000038146973</v>
@@ -7720,7 +7720,7 @@
         <v>138.6000061035156</v>
       </c>
       <c r="I251" t="n">
-        <v>926.0237426757812</v>
+        <v>926.0238037109375</v>
       </c>
       <c r="J251" t="n">
         <v>14.80000019073486</v>
@@ -7807,7 +7807,7 @@
         <v>130.1999969482422</v>
       </c>
       <c r="I254" t="n">
-        <v>892.9303588867188</v>
+        <v>892.9302978515625</v>
       </c>
       <c r="J254" t="n">
         <v>14.44999980926514</v>
@@ -7888,7 +7888,7 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G257" t="n">
-        <v>1147.871704101562</v>
+        <v>1147.871826171875</v>
       </c>
       <c r="H257" t="n">
         <v>134.3000030517578</v>
@@ -7917,7 +7917,7 @@
         <v>63.59999847412109</v>
       </c>
       <c r="G258" t="n">
-        <v>1123.084228515625</v>
+        <v>1123.084350585938</v>
       </c>
       <c r="H258" t="n">
         <v>132.3000030517578</v>
@@ -7946,7 +7946,7 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G259" t="n">
-        <v>1121.266845703125</v>
+        <v>1121.266723632812</v>
       </c>
       <c r="H259" t="n">
         <v>132.6499938964844</v>
@@ -8010,7 +8010,7 @@
         <v>141.3000030517578</v>
       </c>
       <c r="I261" t="n">
-        <v>883.5243530273438</v>
+        <v>883.5242919921875</v>
       </c>
       <c r="J261" t="n">
         <v>14.14999961853027</v>
@@ -8068,7 +8068,7 @@
         <v>137.5</v>
       </c>
       <c r="I263" t="n">
-        <v>901.843994140625</v>
+        <v>901.8438720703125</v>
       </c>
       <c r="J263" t="n">
         <v>14</v>
@@ -8126,7 +8126,7 @@
         <v>133.6999969482422</v>
       </c>
       <c r="I265" t="n">
-        <v>892.0440063476562</v>
+        <v>892.0438842773438</v>
       </c>
       <c r="J265" t="n">
         <v>13.19999980926514</v>
@@ -8242,7 +8242,7 @@
         <v>119.1500015258789</v>
       </c>
       <c r="I269" t="n">
-        <v>839.6953125</v>
+        <v>839.6952514648438</v>
       </c>
       <c r="J269" t="n">
         <v>12.5</v>
@@ -8265,13 +8265,13 @@
         <v>61.54999923706055</v>
       </c>
       <c r="G270" t="n">
-        <v>1069.579223632812</v>
+        <v>1069.5791015625</v>
       </c>
       <c r="H270" t="n">
         <v>125.0999984741211</v>
       </c>
       <c r="I270" t="n">
-        <v>856.8822631835938</v>
+        <v>856.8822021484375</v>
       </c>
       <c r="J270" t="n">
         <v>12.75</v>
@@ -8323,7 +8323,7 @@
         <v>59.20000076293945</v>
       </c>
       <c r="G272" t="n">
-        <v>1057.356079101562</v>
+        <v>1057.35595703125</v>
       </c>
       <c r="H272" t="n">
         <v>121.3000030517578</v>
@@ -8387,7 +8387,7 @@
         <v>124.4499969482422</v>
       </c>
       <c r="I274" t="n">
-        <v>824.0844116210938</v>
+        <v>824.0843505859375</v>
       </c>
       <c r="J274" t="n">
         <v>12</v>
@@ -8410,7 +8410,7 @@
         <v>59.54999923706055</v>
       </c>
       <c r="G275" t="n">
-        <v>1047.791137695312</v>
+        <v>1047.791015625</v>
       </c>
       <c r="H275" t="n">
         <v>123.25</v>
@@ -8445,7 +8445,7 @@
         <v>123.5500030517578</v>
       </c>
       <c r="I276" t="n">
-        <v>842.8469848632812</v>
+        <v>842.8471069335938</v>
       </c>
       <c r="J276" t="n">
         <v>11.69999980926514</v>
@@ -8474,7 +8474,7 @@
         <v>127.3000030517578</v>
       </c>
       <c r="I277" t="n">
-        <v>831.4220581054688</v>
+        <v>831.4219970703125</v>
       </c>
       <c r="J277" t="n">
         <v>11.69999980926514</v>
@@ -8532,7 +8532,7 @@
         <v>127.5500030517578</v>
       </c>
       <c r="I279" t="n">
-        <v>823.788818359375</v>
+        <v>823.7888793945312</v>
       </c>
       <c r="J279" t="n">
         <v>11.35000038146973</v>
@@ -8561,7 +8561,7 @@
         <v>123.3000030517578</v>
       </c>
       <c r="I280" t="n">
-        <v>822.0652465820312</v>
+        <v>822.0653076171875</v>
       </c>
       <c r="J280" t="n">
         <v>11.30000019073486</v>
@@ -8613,7 +8613,7 @@
         <v>60.40000152587891</v>
       </c>
       <c r="G282" t="n">
-        <v>1104.2041015625</v>
+        <v>1104.204223632812</v>
       </c>
       <c r="H282" t="n">
         <v>129.5500030517578</v>
@@ -8700,13 +8700,13 @@
         <v>60.40000152587891</v>
       </c>
       <c r="G285" t="n">
-        <v>1106.044677734375</v>
+        <v>1106.044555664062</v>
       </c>
       <c r="H285" t="n">
         <v>120.8000030517578</v>
       </c>
       <c r="I285" t="n">
-        <v>833.342529296875</v>
+        <v>833.3425903320312</v>
       </c>
       <c r="J285" t="n">
         <v>10.60000038146973</v>
@@ -8735,7 +8735,7 @@
         <v>118.5500030517578</v>
       </c>
       <c r="I286" t="n">
-        <v>818.1255493164062</v>
+        <v>818.1256103515625</v>
       </c>
       <c r="J286" t="n">
         <v>10.39999961853027</v>
@@ -8758,13 +8758,13 @@
         <v>59.04999923706055</v>
       </c>
       <c r="G287" t="n">
-        <v>1075.78173828125</v>
+        <v>1075.781860351562</v>
       </c>
       <c r="H287" t="n">
         <v>115.8000030517578</v>
       </c>
       <c r="I287" t="n">
-        <v>808.4733276367188</v>
+        <v>808.4732666015625</v>
       </c>
       <c r="J287" t="n">
         <v>10.05000019073486</v>
@@ -8787,13 +8787,13 @@
         <v>58.5</v>
       </c>
       <c r="G288" t="n">
-        <v>1083.142944335938</v>
+        <v>1083.14306640625</v>
       </c>
       <c r="H288" t="n">
         <v>126.9499969482422</v>
       </c>
       <c r="I288" t="n">
-        <v>802.1697998046875</v>
+        <v>802.1698608398438</v>
       </c>
       <c r="J288" t="n">
         <v>10.10000038146973</v>
@@ -8874,7 +8874,7 @@
         <v>58.90000152587891</v>
       </c>
       <c r="G291" t="n">
-        <v>1065.05810546875</v>
+        <v>1065.057983398438</v>
       </c>
       <c r="H291" t="n">
         <v>135.6999969482422</v>
@@ -8903,7 +8903,7 @@
         <v>58.54999923706055</v>
       </c>
       <c r="G292" t="n">
-        <v>1056.946899414062</v>
+        <v>1056.947021484375</v>
       </c>
       <c r="H292" t="n">
         <v>135.8000030517578</v>
@@ -9048,7 +9048,7 @@
         <v>58.25</v>
       </c>
       <c r="G297" t="n">
-        <v>1055.424682617188</v>
+        <v>1055.4248046875</v>
       </c>
       <c r="H297" t="n">
         <v>147.25</v>
@@ -9083,7 +9083,7 @@
         <v>139.6499938964844</v>
       </c>
       <c r="I298" t="n">
-        <v>793.7979125976562</v>
+        <v>793.7979736328125</v>
       </c>
       <c r="J298" t="n">
         <v>10.75</v>
@@ -9141,7 +9141,7 @@
         <v>146.6999969482422</v>
       </c>
       <c r="I300" t="n">
-        <v>778.6301879882812</v>
+        <v>778.630126953125</v>
       </c>
       <c r="J300" t="n">
         <v>10.75</v>
@@ -9164,7 +9164,7 @@
         <v>54.70000076293945</v>
       </c>
       <c r="G301" t="n">
-        <v>1011.439270019531</v>
+        <v>1011.439208984375</v>
       </c>
       <c r="H301" t="n">
         <v>141.25</v>
@@ -9228,7 +9228,7 @@
         <v>148.0500030517578</v>
       </c>
       <c r="I303" t="n">
-        <v>771.5880737304688</v>
+        <v>771.5880126953125</v>
       </c>
       <c r="J303" t="n">
         <v>10.30000019073486</v>
@@ -9251,7 +9251,7 @@
         <v>59.59999847412109</v>
       </c>
       <c r="G304" t="n">
-        <v>1031.341796875</v>
+        <v>1031.341918945312</v>
       </c>
       <c r="H304" t="n">
         <v>146.8500061035156</v>
@@ -9286,7 +9286,7 @@
         <v>148.8999938964844</v>
       </c>
       <c r="I305" t="n">
-        <v>778.1377563476562</v>
+        <v>778.1376342773438</v>
       </c>
       <c r="J305" t="n">
         <v>10.30000019073486</v>
@@ -9309,7 +9309,7 @@
         <v>56.20000076293945</v>
       </c>
       <c r="G306" t="n">
-        <v>1021.390686035156</v>
+        <v>1021.390625</v>
       </c>
       <c r="H306" t="n">
         <v>148.1999969482422</v>
@@ -9344,7 +9344,7 @@
         <v>143.1000061035156</v>
       </c>
       <c r="I307" t="n">
-        <v>753.7608642578125</v>
+        <v>753.7608032226562</v>
       </c>
       <c r="J307" t="n">
         <v>9.850000381469727</v>
@@ -9367,7 +9367,7 @@
         <v>53.59999847412109</v>
       </c>
       <c r="G308" t="n">
-        <v>1016.732971191406</v>
+        <v>1016.733032226562</v>
       </c>
       <c r="H308" t="n">
         <v>142.1999969482422</v>
@@ -9402,7 +9402,7 @@
         <v>137.5</v>
       </c>
       <c r="I309" t="n">
-        <v>721.9970703125</v>
+        <v>721.9971923828125</v>
       </c>
       <c r="J309" t="n">
         <v>9.149999618530273</v>
@@ -9431,7 +9431,7 @@
         <v>141.5500030517578</v>
       </c>
       <c r="I310" t="n">
-        <v>763.9055786132812</v>
+        <v>763.905517578125</v>
       </c>
       <c r="J310" t="n">
         <v>9.800000190734863</v>
@@ -9454,13 +9454,13 @@
         <v>54.25</v>
       </c>
       <c r="G311" t="n">
-        <v>1059.219116210938</v>
+        <v>1059.218994140625</v>
       </c>
       <c r="H311" t="n">
         <v>144.25</v>
       </c>
       <c r="I311" t="n">
-        <v>770.061279296875</v>
+        <v>770.0613403320312</v>
       </c>
       <c r="J311" t="n">
         <v>9.949999809265137</v>
@@ -9483,7 +9483,7 @@
         <v>56</v>
       </c>
       <c r="G312" t="n">
-        <v>1059.40087890625</v>
+        <v>1059.400756835938</v>
       </c>
       <c r="H312" t="n">
         <v>146.3999938964844</v>
@@ -9518,7 +9518,7 @@
         <v>151.3999938964844</v>
       </c>
       <c r="I313" t="n">
-        <v>782.5698852539062</v>
+        <v>782.56982421875</v>
       </c>
       <c r="J313" t="n">
         <v>10.80000019073486</v>
@@ -9541,13 +9541,13 @@
         <v>56.54999923706055</v>
       </c>
       <c r="G314" t="n">
-        <v>1063.944702148438</v>
+        <v>1063.944580078125</v>
       </c>
       <c r="H314" t="n">
         <v>151.3999938964844</v>
       </c>
       <c r="I314" t="n">
-        <v>792.2221069335938</v>
+        <v>792.2220458984375</v>
       </c>
       <c r="J314" t="n">
         <v>11.14999961853027</v>
@@ -9570,7 +9570,7 @@
         <v>56.29999923706055</v>
       </c>
       <c r="G315" t="n">
-        <v>1056.401611328125</v>
+        <v>1056.401733398438</v>
       </c>
       <c r="H315" t="n">
         <v>146.8000030517578</v>
@@ -9605,7 +9605,7 @@
         <v>157.3500061035156</v>
       </c>
       <c r="I316" t="n">
-        <v>804.1396484375</v>
+        <v>804.1397094726562</v>
       </c>
       <c r="J316" t="n">
         <v>12.55000019073486</v>
@@ -9721,7 +9721,7 @@
         <v>159.6499938964844</v>
       </c>
       <c r="I320" t="n">
-        <v>820.9817504882812</v>
+        <v>820.9818115234375</v>
       </c>
       <c r="J320" t="n">
         <v>12.39999961853027</v>
@@ -9744,13 +9744,13 @@
         <v>55</v>
       </c>
       <c r="G321" t="n">
-        <v>1068.738525390625</v>
+        <v>1068.738647460938</v>
       </c>
       <c r="H321" t="n">
         <v>159.1999969482422</v>
       </c>
       <c r="I321" t="n">
-        <v>823.4932861328125</v>
+        <v>823.4933471679688</v>
       </c>
       <c r="J321" t="n">
         <v>12.25</v>
@@ -9779,7 +9779,7 @@
         <v>159.5500030517578</v>
       </c>
       <c r="I322" t="n">
-        <v>827.5807495117188</v>
+        <v>827.580810546875</v>
       </c>
       <c r="J322" t="n">
         <v>12.10000038146973</v>
@@ -9802,7 +9802,7 @@
         <v>54.20000076293945</v>
       </c>
       <c r="G323" t="n">
-        <v>1067.375366210938</v>
+        <v>1067.37548828125</v>
       </c>
       <c r="H323" t="n">
         <v>159.3500061035156</v>
@@ -9837,7 +9837,7 @@
         <v>157.8500061035156</v>
       </c>
       <c r="I324" t="n">
-        <v>821.6712646484375</v>
+        <v>821.6712036132812</v>
       </c>
       <c r="J324" t="n">
         <v>11.80000019073486</v>
@@ -9866,7 +9866,7 @@
         <v>157.8999938964844</v>
       </c>
       <c r="I325" t="n">
-        <v>825.66015625</v>
+        <v>825.6600952148438</v>
       </c>
       <c r="J325" t="n">
         <v>11.85000038146973</v>
@@ -9924,7 +9924,7 @@
         <v>160.6999969482422</v>
       </c>
       <c r="I327" t="n">
-        <v>822.409912109375</v>
+        <v>822.4099731445312</v>
       </c>
       <c r="J327" t="n">
         <v>12.5</v>
@@ -9947,7 +9947,7 @@
         <v>58.04999923706055</v>
       </c>
       <c r="G328" t="n">
-        <v>1099.86474609375</v>
+        <v>1099.864868164062</v>
       </c>
       <c r="H328" t="n">
         <v>157.5500030517578</v>
@@ -9982,7 +9982,7 @@
         <v>154.9499969482422</v>
       </c>
       <c r="I329" t="n">
-        <v>833.7366333007812</v>
+        <v>833.736572265625</v>
       </c>
       <c r="J329" t="n">
         <v>12.14999961853027</v>
@@ -10005,13 +10005,13 @@
         <v>58.34999847412109</v>
       </c>
       <c r="G330" t="n">
-        <v>1099.682983398438</v>
+        <v>1099.68310546875</v>
       </c>
       <c r="H330" t="n">
         <v>153.75</v>
       </c>
       <c r="I330" t="n">
-        <v>825.8079223632812</v>
+        <v>825.807861328125</v>
       </c>
       <c r="J330" t="n">
         <v>11.89999961853027</v>
@@ -10034,13 +10034,13 @@
         <v>59.54999923706055</v>
       </c>
       <c r="G331" t="n">
-        <v>1112.360595703125</v>
+        <v>1112.360717773438</v>
       </c>
       <c r="H331" t="n">
         <v>154.5500030517578</v>
       </c>
       <c r="I331" t="n">
-        <v>882.3917236328125</v>
+        <v>882.3917846679688</v>
       </c>
       <c r="J331" t="n">
         <v>12.19999980926514</v>
@@ -10063,13 +10063,13 @@
         <v>57.5</v>
       </c>
       <c r="G332" t="n">
-        <v>1109.5205078125</v>
+        <v>1109.520629882812</v>
       </c>
       <c r="H332" t="n">
         <v>153.6000061035156</v>
       </c>
       <c r="I332" t="n">
-        <v>868.2579956054688</v>
+        <v>868.258056640625</v>
       </c>
       <c r="J332" t="n">
         <v>12.39999961853027</v>
@@ -10092,7 +10092,7 @@
         <v>57.09999847412109</v>
       </c>
       <c r="G333" t="n">
-        <v>1123.220703125</v>
+        <v>1123.220581054688</v>
       </c>
       <c r="H333" t="n">
         <v>152.4499969482422</v>
@@ -10179,13 +10179,13 @@
         <v>58.59999847412109</v>
       </c>
       <c r="G336" t="n">
-        <v>1127.03759765625</v>
+        <v>1127.037719726562</v>
       </c>
       <c r="H336" t="n">
         <v>147.8500061035156</v>
       </c>
       <c r="I336" t="n">
-        <v>878.6983032226562</v>
+        <v>878.6982421875</v>
       </c>
       <c r="J336" t="n">
         <v>11.85000038146973</v>
@@ -10214,7 +10214,7 @@
         <v>146.6000061035156</v>
       </c>
       <c r="I337" t="n">
-        <v>866.1405029296875</v>
+        <v>866.1405639648438</v>
       </c>
       <c r="J337" t="n">
         <v>11.80000019073486</v>
@@ -10243,7 +10243,7 @@
         <v>144.1499938964844</v>
       </c>
       <c r="I338" t="n">
-        <v>873.1334838867188</v>
+        <v>873.1334228515625</v>
       </c>
       <c r="J338" t="n">
         <v>11.60000038146973</v>
@@ -10272,7 +10272,7 @@
         <v>140.8999938964844</v>
       </c>
       <c r="I339" t="n">
-        <v>886.9715576171875</v>
+        <v>886.9716186523438</v>
       </c>
       <c r="J339" t="n">
         <v>11.69999980926514</v>
@@ -10353,13 +10353,13 @@
         <v>58.5</v>
       </c>
       <c r="G342" t="n">
-        <v>1109.611450195312</v>
+        <v>1109.611572265625</v>
       </c>
       <c r="H342" t="n">
         <v>137.4499969482422</v>
       </c>
       <c r="I342" t="n">
-        <v>884.1646118164062</v>
+        <v>884.16455078125</v>
       </c>
       <c r="J342" t="n">
         <v>11.44999980926514</v>
@@ -10411,13 +10411,13 @@
         <v>59.79999923706055</v>
       </c>
       <c r="G344" t="n">
-        <v>1115.3369140625</v>
+        <v>1115.336791992188</v>
       </c>
       <c r="H344" t="n">
         <v>139.6499938964844</v>
       </c>
       <c r="I344" t="n">
-        <v>899.4308471679688</v>
+        <v>899.430908203125</v>
       </c>
       <c r="J344" t="n">
         <v>12.94999980926514</v>
@@ -10446,7 +10446,7 @@
         <v>138.6000061035156</v>
       </c>
       <c r="I345" t="n">
-        <v>881.3082885742188</v>
+        <v>881.308349609375</v>
       </c>
       <c r="J345" t="n">
         <v>12.10000038146973</v>
@@ -10533,7 +10533,7 @@
         <v>139.6499938964844</v>
       </c>
       <c r="I348" t="n">
-        <v>897.362548828125</v>
+        <v>897.3624267578125</v>
       </c>
       <c r="J348" t="n">
         <v>13.30000019073486</v>
@@ -10562,7 +10562,7 @@
         <v>138.6000061035156</v>
       </c>
       <c r="I349" t="n">
-        <v>902.090087890625</v>
+        <v>902.0902099609375</v>
       </c>
       <c r="J349" t="n">
         <v>12.94999980926514</v>
@@ -10585,7 +10585,7 @@
         <v>61.29999923706055</v>
       </c>
       <c r="G350" t="n">
-        <v>1122.311889648438</v>
+        <v>1122.311767578125</v>
       </c>
       <c r="H350" t="n">
         <v>134.6999969482422</v>
@@ -10620,7 +10620,7 @@
         <v>133.9499969482422</v>
       </c>
       <c r="I351" t="n">
-        <v>904.7001342773438</v>
+        <v>904.7001953125</v>
       </c>
       <c r="J351" t="n">
         <v>12.94999980926514</v>
@@ -10643,13 +10643,13 @@
         <v>66.19999694824219</v>
       </c>
       <c r="G352" t="n">
-        <v>1115.632202148438</v>
+        <v>1115.63232421875</v>
       </c>
       <c r="H352" t="n">
         <v>134.6000061035156</v>
       </c>
       <c r="I352" t="n">
-        <v>931.1946411132812</v>
+        <v>931.194580078125</v>
       </c>
       <c r="J352" t="n">
         <v>13.14999961853027</v>
@@ -10707,7 +10707,7 @@
         <v>132.5</v>
       </c>
       <c r="I354" t="n">
-        <v>943.4076538085938</v>
+        <v>943.4075927734375</v>
       </c>
       <c r="J354" t="n">
         <v>13.60000038146973</v>
@@ -10788,7 +10788,7 @@
         <v>63.75</v>
       </c>
       <c r="G357" t="n">
-        <v>1127.787475585938</v>
+        <v>1127.787353515625</v>
       </c>
       <c r="H357" t="n">
         <v>137.1999969482422</v>
@@ -10817,7 +10817,7 @@
         <v>63.54999923706055</v>
       </c>
       <c r="G358" t="n">
-        <v>1128.786987304688</v>
+        <v>1128.786865234375</v>
       </c>
       <c r="H358" t="n">
         <v>139.3999938964844</v>
@@ -10846,7 +10846,7 @@
         <v>64.65000152587891</v>
       </c>
       <c r="G359" t="n">
-        <v>1145.463256835938</v>
+        <v>1145.46337890625</v>
       </c>
       <c r="H359" t="n">
         <v>143.8500061035156</v>
@@ -10875,13 +10875,13 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G360" t="n">
-        <v>1159.549560546875</v>
+        <v>1159.549682617188</v>
       </c>
       <c r="H360" t="n">
         <v>149.9499969482422</v>
       </c>
       <c r="I360" t="n">
-        <v>950.9806518554688</v>
+        <v>950.980712890625</v>
       </c>
       <c r="J360" t="n">
         <v>15.89999961853027</v>
@@ -10904,13 +10904,13 @@
         <v>62.95000076293945</v>
       </c>
       <c r="G361" t="n">
-        <v>1159.867797851562</v>
+        <v>1159.86767578125</v>
       </c>
       <c r="H361" t="n">
         <v>149.4499969482422</v>
       </c>
       <c r="I361" t="n">
-        <v>938.8209838867188</v>
+        <v>938.8209228515625</v>
       </c>
       <c r="J361" t="n">
         <v>16.75</v>
@@ -10968,7 +10968,7 @@
         <v>150.75</v>
       </c>
       <c r="I363" t="n">
-        <v>959.7296752929688</v>
+        <v>959.729736328125</v>
       </c>
       <c r="J363" t="n">
         <v>15.69999980926514</v>
@@ -10997,7 +10997,7 @@
         <v>146.5</v>
       </c>
       <c r="I364" t="n">
-        <v>962.7449951171875</v>
+        <v>962.7449340820312</v>
       </c>
       <c r="J364" t="n">
         <v>15.30000019073486</v>
@@ -11020,7 +11020,7 @@
         <v>65.75</v>
       </c>
       <c r="G365" t="n">
-        <v>1165.206787109375</v>
+        <v>1165.206909179688</v>
       </c>
       <c r="H365" t="n">
         <v>147.75</v>
@@ -11113,7 +11113,7 @@
         <v>140.1999969482422</v>
       </c>
       <c r="I368" t="n">
-        <v>924.0413818359375</v>
+        <v>924.0414428710938</v>
       </c>
       <c r="J368" t="n">
         <v>14.10000038146973</v>
@@ -11142,7 +11142,7 @@
         <v>141.25</v>
       </c>
       <c r="I369" t="n">
-        <v>933.6307983398438</v>
+        <v>933.630859375</v>
       </c>
       <c r="J369" t="n">
         <v>13.85000038146973</v>
@@ -11287,7 +11287,7 @@
         <v>138.5</v>
       </c>
       <c r="I374" t="n">
-        <v>944.5054321289062</v>
+        <v>944.50537109375</v>
       </c>
       <c r="J374" t="n">
         <v>14.35000038146973</v>
@@ -11310,13 +11310,13 @@
         <v>63.54999923706055</v>
       </c>
       <c r="G375" t="n">
-        <v>1199.036743164062</v>
+        <v>1199.03662109375</v>
       </c>
       <c r="H375" t="n">
         <v>138.75</v>
       </c>
       <c r="I375" t="n">
-        <v>952.9085083007812</v>
+        <v>952.908447265625</v>
       </c>
       <c r="J375" t="n">
         <v>15.30000019073486</v>
@@ -11339,7 +11339,7 @@
         <v>64.15000152587891</v>
       </c>
       <c r="G376" t="n">
-        <v>1196.696655273438</v>
+        <v>1196.696533203125</v>
       </c>
       <c r="H376" t="n">
         <v>138.6000061035156</v>
@@ -11403,7 +11403,7 @@
         <v>136.8000030517578</v>
       </c>
       <c r="I378" t="n">
-        <v>948.6080322265625</v>
+        <v>948.6079711914062</v>
       </c>
       <c r="J378" t="n">
         <v>15.35000038146973</v>
@@ -11484,13 +11484,13 @@
         <v>63.5</v>
       </c>
       <c r="G381" t="n">
-        <v>1245.3623046875</v>
+        <v>1245.362182617188</v>
       </c>
       <c r="H381" t="n">
         <v>136.1499938964844</v>
       </c>
       <c r="I381" t="n">
-        <v>958.642333984375</v>
+        <v>958.6422729492188</v>
       </c>
       <c r="J381" t="n">
         <v>15.25</v>
@@ -11519,7 +11519,7 @@
         <v>135</v>
       </c>
       <c r="I382" t="n">
-        <v>963.9313354492188</v>
+        <v>963.9312744140625</v>
       </c>
       <c r="J382" t="n">
         <v>15.25</v>
@@ -11542,13 +11542,13 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G383" t="n">
-        <v>1281.600219726562</v>
+        <v>1281.600341796875</v>
       </c>
       <c r="H383" t="n">
         <v>141.6999969482422</v>
       </c>
       <c r="I383" t="n">
-        <v>947.619384765625</v>
+        <v>947.6194458007812</v>
       </c>
       <c r="J383" t="n">
         <v>15.19999980926514</v>
@@ -11571,7 +11571,7 @@
         <v>59.5</v>
       </c>
       <c r="G384" t="n">
-        <v>1291.324340820312</v>
+        <v>1291.32421875</v>
       </c>
       <c r="H384" t="n">
         <v>154.8500061035156</v>
@@ -11600,7 +11600,7 @@
         <v>59.70000076293945</v>
       </c>
       <c r="G385" t="n">
-        <v>1289.760498046875</v>
+        <v>1289.760620117188</v>
       </c>
       <c r="H385" t="n">
         <v>162.3999938964844</v>
@@ -11664,7 +11664,7 @@
         <v>162.6000061035156</v>
       </c>
       <c r="I387" t="n">
-        <v>949.4483642578125</v>
+        <v>949.4484252929688</v>
       </c>
       <c r="J387" t="n">
         <v>15.64999961853027</v>
@@ -11722,7 +11722,7 @@
         <v>170.9499969482422</v>
       </c>
       <c r="I389" t="n">
-        <v>949.4483642578125</v>
+        <v>949.4484252929688</v>
       </c>
       <c r="J389" t="n">
         <v>15.75</v>
@@ -11751,7 +11751,7 @@
         <v>178.6000061035156</v>
       </c>
       <c r="I390" t="n">
-        <v>955.4788208007812</v>
+        <v>955.478759765625</v>
       </c>
       <c r="J390" t="n">
         <v>16.54999923706055</v>
@@ -11803,13 +11803,13 @@
         <v>58.25</v>
       </c>
       <c r="G392" t="n">
-        <v>1255.003784179688</v>
+        <v>1255.00390625</v>
       </c>
       <c r="H392" t="n">
         <v>188.8500061035156</v>
       </c>
       <c r="I392" t="n">
-        <v>958.642333984375</v>
+        <v>958.6422729492188</v>
       </c>
       <c r="J392" t="n">
         <v>16.45000076293945</v>
@@ -11861,7 +11861,7 @@
         <v>58.15000152587891</v>
       </c>
       <c r="G394" t="n">
-        <v>1224.0380859375</v>
+        <v>1224.038208007812</v>
       </c>
       <c r="H394" t="n">
         <v>181.1999969482422</v>
@@ -11896,7 +11896,7 @@
         <v>187.0500030517578</v>
       </c>
       <c r="I395" t="n">
-        <v>970.01123046875</v>
+        <v>970.0111694335938</v>
       </c>
       <c r="J395" t="n">
         <v>18.04999923706055</v>
@@ -12064,13 +12064,13 @@
         <v>62.20000076293945</v>
       </c>
       <c r="G401" t="n">
-        <v>1253.969970703125</v>
+        <v>1253.970092773438</v>
       </c>
       <c r="H401" t="n">
         <v>170</v>
       </c>
       <c r="I401" t="n">
-        <v>973.86669921875</v>
+        <v>973.8666381835938</v>
       </c>
       <c r="J401" t="n">
         <v>17.39999961853027</v>
@@ -12128,7 +12128,7 @@
         <v>163</v>
       </c>
       <c r="I403" t="n">
-        <v>956.1213989257812</v>
+        <v>956.1214599609375</v>
       </c>
       <c r="J403" t="n">
         <v>16.75</v>
@@ -12151,13 +12151,13 @@
         <v>60.95000076293945</v>
       </c>
       <c r="G404" t="n">
-        <v>1249.46533203125</v>
+        <v>1249.465454101562</v>
       </c>
       <c r="H404" t="n">
         <v>158.0500030517578</v>
       </c>
       <c r="I404" t="n">
-        <v>1023.296447753906</v>
+        <v>1023.296569824219</v>
       </c>
       <c r="J404" t="n">
         <v>16.54999923706055</v>
@@ -12218,7 +12218,7 @@
         <v>162.3500061035156</v>
       </c>
       <c r="I406" t="n">
-        <v>1040.003784179688</v>
+        <v>1040.003662109375</v>
       </c>
       <c r="J406" t="n">
         <v>16.35000038146973</v>
@@ -12276,13 +12276,13 @@
         <v>67.84999847412109</v>
       </c>
       <c r="G408" t="n">
-        <v>1246.073364257812</v>
+        <v>1246.0732421875</v>
       </c>
       <c r="H408" t="n">
         <v>178.9499969482422</v>
       </c>
       <c r="I408" t="n">
-        <v>1023.593078613281</v>
+        <v>1023.593200683594</v>
       </c>
       <c r="J408" t="n">
         <v>17.29999923706055</v>
@@ -12314,7 +12314,7 @@
         <v>177.3000030517578</v>
       </c>
       <c r="I409" t="n">
-        <v>1017.513305664062</v>
+        <v>1017.513244628906</v>
       </c>
       <c r="J409" t="n">
         <v>17.29999923706055</v>
@@ -12346,7 +12346,7 @@
         <v>177.25</v>
       </c>
       <c r="I410" t="n">
-        <v>988.1519165039062</v>
+        <v>988.15185546875</v>
       </c>
       <c r="J410" t="n">
         <v>17.35000038146973</v>
@@ -12378,7 +12378,7 @@
         <v>177.8999938964844</v>
       </c>
       <c r="I411" t="n">
-        <v>1001.794494628906</v>
+        <v>1001.794555664062</v>
       </c>
       <c r="J411" t="n">
         <v>17.45000076293945</v>
@@ -12474,7 +12474,7 @@
         <v>186.75</v>
       </c>
       <c r="I414" t="n">
-        <v>1005.650024414062</v>
+        <v>1005.650085449219</v>
       </c>
       <c r="J414" t="n">
         <v>19.14999961853027</v>
@@ -12506,7 +12506,7 @@
         <v>186.8999938964844</v>
       </c>
       <c r="I415" t="n">
-        <v>1000.113952636719</v>
+        <v>1000.114013671875</v>
       </c>
       <c r="J415" t="n">
         <v>19</v>
@@ -12538,7 +12538,7 @@
         <v>192.8999938964844</v>
       </c>
       <c r="I416" t="n">
-        <v>1005.501708984375</v>
+        <v>1005.501770019531</v>
       </c>
       <c r="J416" t="n">
         <v>19.54999923706055</v>
@@ -12570,7 +12570,7 @@
         <v>190.8000030517578</v>
       </c>
       <c r="I417" t="n">
-        <v>996.8020629882812</v>
+        <v>996.8021240234375</v>
       </c>
       <c r="J417" t="n">
         <v>19.79999923706055</v>
@@ -12628,7 +12628,7 @@
         <v>70.75</v>
       </c>
       <c r="G419" t="n">
-        <v>1201.5107421875</v>
+        <v>1201.510620117188</v>
       </c>
       <c r="H419" t="n">
         <v>189.8000030517578</v>
@@ -12692,13 +12692,13 @@
         <v>70.94999694824219</v>
       </c>
       <c r="G421" t="n">
-        <v>1222.557006835938</v>
+        <v>1222.556884765625</v>
       </c>
       <c r="H421" t="n">
         <v>182.8500061035156</v>
       </c>
       <c r="I421" t="n">
-        <v>991.2166137695312</v>
+        <v>991.216552734375</v>
       </c>
       <c r="J421" t="n">
         <v>20.79999923706055</v>
@@ -12730,7 +12730,7 @@
         <v>173.6999969482422</v>
       </c>
       <c r="I422" t="n">
-        <v>954.5889892578125</v>
+        <v>954.5890502929688</v>
       </c>
       <c r="J422" t="n">
         <v>18.39999961853027</v>
@@ -12762,7 +12762,7 @@
         <v>172.6499938964844</v>
       </c>
       <c r="I423" t="n">
-        <v>952.9085083007812</v>
+        <v>952.908447265625</v>
       </c>
       <c r="J423" t="n">
         <v>19</v>
@@ -12788,7 +12788,7 @@
         <v>68.55000305175781</v>
       </c>
       <c r="G424" t="n">
-        <v>1212.033813476562</v>
+        <v>1212.033935546875</v>
       </c>
       <c r="H424" t="n">
         <v>175.3000030517578</v>
@@ -12826,7 +12826,7 @@
         <v>183.75</v>
       </c>
       <c r="I425" t="n">
-        <v>959.9769287109375</v>
+        <v>959.9768676757812</v>
       </c>
       <c r="J425" t="n">
         <v>19.14999961853027</v>
@@ -12922,7 +12922,7 @@
         <v>175.1499938964844</v>
       </c>
       <c r="I428" t="n">
-        <v>941.0452880859375</v>
+        <v>941.0453491210938</v>
       </c>
       <c r="J428" t="n">
         <v>19</v>
@@ -12980,13 +12980,13 @@
         <v>65.94999694824219</v>
       </c>
       <c r="G430" t="n">
-        <v>1156.281005859375</v>
+        <v>1156.281127929688</v>
       </c>
       <c r="H430" t="n">
         <v>173.5500030517578</v>
       </c>
       <c r="I430" t="n">
-        <v>939.2163696289062</v>
+        <v>939.2164306640625</v>
       </c>
       <c r="J430" t="n">
         <v>18.95000076293945</v>
@@ -13012,7 +13012,7 @@
         <v>64.5</v>
       </c>
       <c r="G431" t="n">
-        <v>1157.293823242188</v>
+        <v>1157.2939453125</v>
       </c>
       <c r="H431" t="n">
         <v>171</v>
@@ -13050,7 +13050,7 @@
         <v>172.6499938964844</v>
       </c>
       <c r="I432" t="n">
-        <v>956.41796875</v>
+        <v>956.4180297851562</v>
       </c>
       <c r="J432" t="n">
         <v>19.20000076293945</v>
@@ -13076,7 +13076,7 @@
         <v>63.20000076293945</v>
       </c>
       <c r="G433" t="n">
-        <v>1153.14404296875</v>
+        <v>1153.143920898438</v>
       </c>
       <c r="H433" t="n">
         <v>170.8999938964844</v>
@@ -13108,7 +13108,7 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G434" t="n">
-        <v>1158.529052734375</v>
+        <v>1158.528930664062</v>
       </c>
       <c r="H434" t="n">
         <v>173.3000030517578</v>
@@ -13140,13 +13140,13 @@
         <v>68.55000305175781</v>
       </c>
       <c r="G435" t="n">
-        <v>1145.263916015625</v>
+        <v>1145.263793945312</v>
       </c>
       <c r="H435" t="n">
         <v>174.3500061035156</v>
       </c>
       <c r="I435" t="n">
-        <v>943.2696533203125</v>
+        <v>943.2695922851562</v>
       </c>
       <c r="J435" t="n">
         <v>19.25</v>
@@ -13178,7 +13178,7 @@
         <v>170.3999938964844</v>
       </c>
       <c r="I436" t="n">
-        <v>931.5547485351562</v>
+        <v>931.5546875</v>
       </c>
       <c r="J436" t="n">
         <v>18.79999923706055</v>
@@ -13210,7 +13210,7 @@
         <v>172.1999969482422</v>
       </c>
       <c r="I437" t="n">
-        <v>968.7260131835938</v>
+        <v>968.7259521484375</v>
       </c>
       <c r="J437" t="n">
         <v>18.89999961853027</v>
@@ -13236,7 +13236,7 @@
         <v>72.40000152587891</v>
       </c>
       <c r="G438" t="n">
-        <v>1145.189819335938</v>
+        <v>1145.18994140625</v>
       </c>
       <c r="H438" t="n">
         <v>171.6499938964844</v>
@@ -13306,7 +13306,7 @@
         <v>170.8500061035156</v>
       </c>
       <c r="I440" t="n">
-        <v>970.3077392578125</v>
+        <v>970.3078002929688</v>
       </c>
       <c r="J440" t="n">
         <v>17.79999923706055</v>
@@ -13332,7 +13332,7 @@
         <v>72.19999694824219</v>
       </c>
       <c r="G441" t="n">
-        <v>1158.5537109375</v>
+        <v>1158.553588867188</v>
       </c>
       <c r="H441" t="n">
         <v>170.5</v>
@@ -13370,7 +13370,7 @@
         <v>169.3500061035156</v>
       </c>
       <c r="I442" t="n">
-        <v>980.04541015625</v>
+        <v>980.0453491210938</v>
       </c>
       <c r="J442" t="n">
         <v>18</v>
@@ -13434,7 +13434,7 @@
         <v>170.75</v>
       </c>
       <c r="I444" t="n">
-        <v>1058.243408203125</v>
+        <v>1058.243286132812</v>
       </c>
       <c r="J444" t="n">
         <v>18.39999961853027</v>
@@ -13460,7 +13460,7 @@
         <v>77.65000152587891</v>
       </c>
       <c r="G445" t="n">
-        <v>1163.592895507812</v>
+        <v>1163.593017578125</v>
       </c>
       <c r="H445" t="n">
         <v>172.3500061035156</v>
@@ -13492,7 +13492,7 @@
         <v>77.94999694824219</v>
       </c>
       <c r="G446" t="n">
-        <v>1148.154052734375</v>
+        <v>1148.154174804688</v>
       </c>
       <c r="H446" t="n">
         <v>169.1999969482422</v>
@@ -13658,7 +13658,7 @@
         <v>159.0500030517578</v>
       </c>
       <c r="I451" t="n">
-        <v>1007.72607421875</v>
+        <v>1007.726135253906</v>
       </c>
       <c r="J451" t="n">
         <v>16.5</v>
@@ -13684,13 +13684,13 @@
         <v>68.75</v>
       </c>
       <c r="G452" t="n">
-        <v>1119.40087890625</v>
+        <v>1119.400756835938</v>
       </c>
       <c r="H452" t="n">
         <v>162.9499969482422</v>
       </c>
       <c r="I452" t="n">
-        <v>1005.353515625</v>
+        <v>1005.353454589844</v>
       </c>
       <c r="J452" t="n">
         <v>16.79999923706055</v>
@@ -13722,7 +13722,7 @@
         <v>168</v>
       </c>
       <c r="I453" t="n">
-        <v>1007.577819824219</v>
+        <v>1007.577880859375</v>
       </c>
       <c r="J453" t="n">
         <v>16.95000076293945</v>
@@ -13754,7 +13754,7 @@
         <v>169.25</v>
       </c>
       <c r="I454" t="n">
-        <v>993.9846801757812</v>
+        <v>993.984619140625</v>
       </c>
       <c r="J454" t="n">
         <v>17.10000038146973</v>
@@ -13818,7 +13818,7 @@
         <v>176.9499969482422</v>
       </c>
       <c r="I456" t="n">
-        <v>988.6956176757812</v>
+        <v>988.6956787109375</v>
       </c>
       <c r="J456" t="n">
         <v>18.25</v>
@@ -13882,7 +13882,7 @@
         <v>183.3500061035156</v>
       </c>
       <c r="I458" t="n">
-        <v>1032.391723632812</v>
+        <v>1032.3916015625</v>
       </c>
       <c r="J458" t="n">
         <v>19.29999923706055</v>
@@ -13908,13 +13908,13 @@
         <v>70.90000152587891</v>
       </c>
       <c r="G459" t="n">
-        <v>1148.055297851562</v>
+        <v>1148.055419921875</v>
       </c>
       <c r="H459" t="n">
         <v>185.5500030517578</v>
       </c>
       <c r="I459" t="n">
-        <v>1038.817504882812</v>
+        <v>1038.817626953125</v>
       </c>
       <c r="J459" t="n">
         <v>20.70000076293945</v>
@@ -13946,7 +13946,7 @@
         <v>179.1000061035156</v>
       </c>
       <c r="I460" t="n">
-        <v>1039.509399414062</v>
+        <v>1039.509521484375</v>
       </c>
       <c r="J460" t="n">
         <v>20.45000076293945</v>
@@ -13978,7 +13978,7 @@
         <v>178.1000061035156</v>
       </c>
       <c r="I461" t="n">
-        <v>1038.1748046875</v>
+        <v>1038.174926757812</v>
       </c>
       <c r="J461" t="n">
         <v>21.20000076293945</v>
@@ -14068,7 +14068,7 @@
         <v>83.59999847412109</v>
       </c>
       <c r="G464" t="n">
-        <v>1164.185791015625</v>
+        <v>1164.185668945312</v>
       </c>
       <c r="H464" t="n">
         <v>181.75</v>
@@ -14132,7 +14132,7 @@
         <v>85.15000152587891</v>
       </c>
       <c r="G466" t="n">
-        <v>1163.741088867188</v>
+        <v>1163.7412109375</v>
       </c>
       <c r="H466" t="n">
         <v>186</v>
@@ -14202,7 +14202,7 @@
         <v>179.5500030517578</v>
       </c>
       <c r="I468" t="n">
-        <v>1109.156127929688</v>
+        <v>1109.156005859375</v>
       </c>
       <c r="J468" t="n">
         <v>21.35000038146973</v>
@@ -14260,13 +14260,13 @@
         <v>82.40000152587891</v>
       </c>
       <c r="G470" t="n">
-        <v>1183.47802734375</v>
+        <v>1183.478149414062</v>
       </c>
       <c r="H470" t="n">
         <v>174.25</v>
       </c>
       <c r="I470" t="n">
-        <v>1095.661865234375</v>
+        <v>1095.661743164062</v>
       </c>
       <c r="J470" t="n">
         <v>21.35000038146973</v>
@@ -14292,13 +14292,13 @@
         <v>83.44999694824219</v>
       </c>
       <c r="G471" t="n">
-        <v>1182.6875</v>
+        <v>1182.687622070312</v>
       </c>
       <c r="H471" t="n">
         <v>173.4499969482422</v>
       </c>
       <c r="I471" t="n">
-        <v>1078.558959960938</v>
+        <v>1078.55908203125</v>
       </c>
       <c r="J471" t="n">
         <v>20.89999961853027</v>
@@ -14324,7 +14324,7 @@
         <v>82.90000152587891</v>
       </c>
       <c r="G472" t="n">
-        <v>1182.9345703125</v>
+        <v>1182.934692382812</v>
       </c>
       <c r="H472" t="n">
         <v>177.8999938964844</v>
@@ -14388,13 +14388,13 @@
         <v>86.55000305175781</v>
       </c>
       <c r="G474" t="n">
-        <v>1174.560668945312</v>
+        <v>1174.560791015625</v>
       </c>
       <c r="H474" t="n">
         <v>189.75</v>
       </c>
       <c r="I474" t="n">
-        <v>1082.513427734375</v>
+        <v>1082.513549804688</v>
       </c>
       <c r="J474" t="n">
         <v>21.14999961853027</v>
@@ -14420,13 +14420,13 @@
         <v>87.69999694824219</v>
       </c>
       <c r="G475" t="n">
-        <v>1182.885375976562</v>
+        <v>1182.88525390625</v>
       </c>
       <c r="H475" t="n">
         <v>194.0500030517578</v>
       </c>
       <c r="I475" t="n">
-        <v>1081.030639648438</v>
+        <v>1081.030517578125</v>
       </c>
       <c r="J475" t="n">
         <v>20.85000038146973</v>
@@ -14458,7 +14458,7 @@
         <v>192.6999969482422</v>
       </c>
       <c r="I476" t="n">
-        <v>1102.829223632812</v>
+        <v>1102.8291015625</v>
       </c>
       <c r="J476" t="n">
         <v>20.89999961853027</v>
@@ -14522,7 +14522,7 @@
         <v>212.3999938964844</v>
       </c>
       <c r="I478" t="n">
-        <v>1103.8671875</v>
+        <v>1103.867065429688</v>
       </c>
       <c r="J478" t="n">
         <v>23.20000076293945</v>
@@ -14650,7 +14650,7 @@
         <v>211.6499938964844</v>
       </c>
       <c r="I482" t="n">
-        <v>1134.167724609375</v>
+        <v>1134.167602539062</v>
       </c>
       <c r="J482" t="n">
         <v>23.20000076293945</v>
@@ -14676,7 +14676,7 @@
         <v>86.69999694824219</v>
       </c>
       <c r="G483" t="n">
-        <v>1202.473999023438</v>
+        <v>1202.473876953125</v>
       </c>
       <c r="H483" t="n">
         <v>215.8000030517578</v>
@@ -14746,7 +14746,7 @@
         <v>209.75</v>
       </c>
       <c r="I485" t="n">
-        <v>1167.977783203125</v>
+        <v>1167.9775390625</v>
       </c>
       <c r="J485" t="n">
         <v>23.60000038146973</v>
@@ -14842,7 +14842,7 @@
         <v>190.8000030517578</v>
       </c>
       <c r="I488" t="n">
-        <v>1227.29345703125</v>
+        <v>1227.293334960938</v>
       </c>
       <c r="J488" t="n">
         <v>21.39999961853027</v>
@@ -14874,7 +14874,7 @@
         <v>193.3999938964844</v>
       </c>
       <c r="I489" t="n">
-        <v>1275.042724609375</v>
+        <v>1275.042602539062</v>
       </c>
       <c r="J489" t="n">
         <v>22.70000076293945</v>
@@ -14900,7 +14900,7 @@
         <v>86.09999847412109</v>
       </c>
       <c r="G490" t="n">
-        <v>1267.243041992188</v>
+        <v>1267.242919921875</v>
       </c>
       <c r="H490" t="n">
         <v>193.0500030517578</v>
@@ -14932,7 +14932,7 @@
         <v>88.84999847412109</v>
       </c>
       <c r="G491" t="n">
-        <v>1273.665649414062</v>
+        <v>1273.66552734375</v>
       </c>
       <c r="H491" t="n">
         <v>196.75</v>
@@ -14970,7 +14970,7 @@
         <v>194.6999969482422</v>
       </c>
       <c r="I492" t="n">
-        <v>1348.198974609375</v>
+        <v>1348.198852539062</v>
       </c>
       <c r="J492" t="n">
         <v>22.60000038146973</v>
@@ -15002,7 +15002,7 @@
         <v>190.8000030517578</v>
       </c>
       <c r="I493" t="n">
-        <v>1333.122680664062</v>
+        <v>1333.122802734375</v>
       </c>
       <c r="J493" t="n">
         <v>22.35000038146973</v>
@@ -15034,7 +15034,7 @@
         <v>209.8000030517578</v>
       </c>
       <c r="I494" t="n">
-        <v>1332.776733398438</v>
+        <v>1332.77685546875</v>
       </c>
       <c r="J494" t="n">
         <v>23.29999923706055</v>
@@ -15066,7 +15066,7 @@
         <v>211.8000030517578</v>
       </c>
       <c r="I495" t="n">
-        <v>1402.62109375</v>
+        <v>1402.621215820312</v>
       </c>
       <c r="J495" t="n">
         <v>23.95000076293945</v>
@@ -15098,7 +15098,7 @@
         <v>207.9499969482422</v>
       </c>
       <c r="I496" t="n">
-        <v>1399.06201171875</v>
+        <v>1399.062133789062</v>
       </c>
       <c r="J496" t="n">
         <v>24.10000038146973</v>
@@ -15124,13 +15124,13 @@
         <v>89.69999694824219</v>
       </c>
       <c r="G497" t="n">
-        <v>1276.259399414062</v>
+        <v>1276.25927734375</v>
       </c>
       <c r="H497" t="n">
         <v>215.1499938964844</v>
       </c>
       <c r="I497" t="n">
-        <v>1368.217895507812</v>
+        <v>1368.218017578125</v>
       </c>
       <c r="J497" t="n">
         <v>25.95000076293945</v>
@@ -15156,13 +15156,13 @@
         <v>90.25</v>
       </c>
       <c r="G498" t="n">
-        <v>1282.854614257812</v>
+        <v>1282.854736328125</v>
       </c>
       <c r="H498" t="n">
         <v>231.5500030517578</v>
       </c>
       <c r="I498" t="n">
-        <v>1382.157104492188</v>
+        <v>1382.1572265625</v>
       </c>
       <c r="J498" t="n">
         <v>30.39999961853027</v>
@@ -15194,7 +15194,7 @@
         <v>229.6000061035156</v>
       </c>
       <c r="I499" t="n">
-        <v>1356.552368164062</v>
+        <v>1356.552490234375</v>
       </c>
       <c r="J499" t="n">
         <v>31.39999961853027</v>
@@ -15226,7 +15226,7 @@
         <v>241</v>
       </c>
       <c r="I500" t="n">
-        <v>1329.909790039062</v>
+        <v>1329.909912109375</v>
       </c>
       <c r="J500" t="n">
         <v>32.04999923706055</v>
@@ -15258,7 +15258,7 @@
         <v>236.8500061035156</v>
       </c>
       <c r="I501" t="n">
-        <v>1350.423217773438</v>
+        <v>1350.423095703125</v>
       </c>
       <c r="J501" t="n">
         <v>31.29999923706055</v>
@@ -15284,7 +15284,7 @@
         <v>119.4000015258789</v>
       </c>
       <c r="G502" t="n">
-        <v>1309.261352539062</v>
+        <v>1309.261474609375</v>
       </c>
       <c r="H502" t="n">
         <v>237.4499969482422</v>
@@ -15316,7 +15316,7 @@
         <v>130.9499969482422</v>
       </c>
       <c r="G503" t="n">
-        <v>1343.696166992188</v>
+        <v>1343.696044921875</v>
       </c>
       <c r="H503" t="n">
         <v>239.8999938964844</v>
@@ -15354,7 +15354,7 @@
         <v>238.4499969482422</v>
       </c>
       <c r="I504" t="n">
-        <v>1496.389526367188</v>
+        <v>1496.3896484375</v>
       </c>
       <c r="J504" t="n">
         <v>30.89999961853027</v>
@@ -15386,7 +15386,7 @@
         <v>232.6499938964844</v>
       </c>
       <c r="I505" t="n">
-        <v>1442.313354492188</v>
+        <v>1442.313232421875</v>
       </c>
       <c r="J505" t="n">
         <v>30.79999923706055</v>
@@ -15450,7 +15450,7 @@
         <v>217.3000030517578</v>
       </c>
       <c r="I507" t="n">
-        <v>1387.594360351562</v>
+        <v>1387.594482421875</v>
       </c>
       <c r="J507" t="n">
         <v>29.85000038146973</v>
@@ -15482,7 +15482,7 @@
         <v>218.8999938964844</v>
       </c>
       <c r="I508" t="n">
-        <v>1424.419677734375</v>
+        <v>1424.419555664062</v>
       </c>
       <c r="J508" t="n">
         <v>29.75</v>
@@ -15572,7 +15572,7 @@
         <v>120.4000015258789</v>
       </c>
       <c r="G511" t="n">
-        <v>1327.862060546875</v>
+        <v>1327.861938476562</v>
       </c>
       <c r="H511" t="n">
         <v>213.3999938964844</v>
@@ -15604,7 +15604,7 @@
         <v>120.5500030517578</v>
       </c>
       <c r="G512" t="n">
-        <v>1336.952270507812</v>
+        <v>1336.952392578125</v>
       </c>
       <c r="H512" t="n">
         <v>215.25</v>
@@ -15674,7 +15674,7 @@
         <v>231.5500030517578</v>
       </c>
       <c r="I514" t="n">
-        <v>1382.99755859375</v>
+        <v>1382.997436523438</v>
       </c>
       <c r="J514" t="n">
         <v>29.95000076293945</v>
@@ -15700,7 +15700,7 @@
         <v>117</v>
       </c>
       <c r="G515" t="n">
-        <v>1409.625854492188</v>
+        <v>1409.6259765625</v>
       </c>
       <c r="H515" t="n">
         <v>231.0500030517578</v>
@@ -15738,7 +15738,7 @@
         <v>224.6000061035156</v>
       </c>
       <c r="I516" t="n">
-        <v>1375.928955078125</v>
+        <v>1375.929077148438</v>
       </c>
       <c r="J516" t="n">
         <v>29</v>
@@ -15834,7 +15834,7 @@
         <v>214.9499969482422</v>
       </c>
       <c r="I519" t="n">
-        <v>1380.179809570312</v>
+        <v>1380.179931640625</v>
       </c>
       <c r="J519" t="n">
         <v>26.04999923706055</v>
@@ -15898,7 +15898,7 @@
         <v>213.4499969482422</v>
       </c>
       <c r="I521" t="n">
-        <v>1407.76171875</v>
+        <v>1407.761840820312</v>
       </c>
       <c r="J521" t="n">
         <v>28.54999923706055</v>
@@ -15924,13 +15924,13 @@
         <v>108.3499984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>1443.344360351562</v>
+        <v>1443.344482421875</v>
       </c>
       <c r="H522" t="n">
         <v>213</v>
       </c>
       <c r="I522" t="n">
-        <v>1366.685424804688</v>
+        <v>1366.685546875</v>
       </c>
       <c r="J522" t="n">
         <v>27.5</v>
@@ -15956,7 +15956,7 @@
         <v>106.25</v>
       </c>
       <c r="G523" t="n">
-        <v>1435.04443359375</v>
+        <v>1435.044311523438</v>
       </c>
       <c r="H523" t="n">
         <v>202.25</v>
@@ -15988,13 +15988,13 @@
         <v>105.4000015258789</v>
       </c>
       <c r="G524" t="n">
-        <v>1447.642456054688</v>
+        <v>1447.642578125</v>
       </c>
       <c r="H524" t="n">
         <v>210.1499938964844</v>
       </c>
       <c r="I524" t="n">
-        <v>1327.586669921875</v>
+        <v>1327.586547851562</v>
       </c>
       <c r="J524" t="n">
         <v>26.04999923706055</v>
@@ -16020,7 +16020,7 @@
         <v>109.5</v>
       </c>
       <c r="G525" t="n">
-        <v>1463.723510742188</v>
+        <v>1463.7236328125</v>
       </c>
       <c r="H525" t="n">
         <v>229.1499938964844</v>
@@ -16058,7 +16058,7 @@
         <v>234.3500061035156</v>
       </c>
       <c r="I526" t="n">
-        <v>1455.362670898438</v>
+        <v>1455.36279296875</v>
       </c>
       <c r="J526" t="n">
         <v>26.75</v>
@@ -16090,7 +16090,7 @@
         <v>225.25</v>
       </c>
       <c r="I527" t="n">
-        <v>1455.263916015625</v>
+        <v>1455.264038085938</v>
       </c>
       <c r="J527" t="n">
         <v>26.20000076293945</v>
@@ -16116,13 +16116,13 @@
         <v>117.9000015258789</v>
       </c>
       <c r="G528" t="n">
-        <v>1456.4365234375</v>
+        <v>1456.436401367188</v>
       </c>
       <c r="H528" t="n">
         <v>242.8500061035156</v>
       </c>
       <c r="I528" t="n">
-        <v>1441.621337890625</v>
+        <v>1441.621215820312</v>
       </c>
       <c r="J528" t="n">
         <v>26.95000076293945</v>
@@ -16148,7 +16148,7 @@
         <v>119</v>
       </c>
       <c r="G529" t="n">
-        <v>1453.496948242188</v>
+        <v>1453.496826171875</v>
       </c>
       <c r="H529" t="n">
         <v>241.1999969482422</v>
@@ -16250,7 +16250,7 @@
         <v>228.5</v>
       </c>
       <c r="I532" t="n">
-        <v>1499.948608398438</v>
+        <v>1499.948486328125</v>
       </c>
       <c r="J532" t="n">
         <v>25.60000038146973</v>
@@ -16282,7 +16282,7 @@
         <v>228.5500030517578</v>
       </c>
       <c r="I533" t="n">
-        <v>1470.43896484375</v>
+        <v>1470.438842773438</v>
       </c>
       <c r="J533" t="n">
         <v>25.25</v>
@@ -16314,7 +16314,7 @@
         <v>220.5500030517578</v>
       </c>
       <c r="I534" t="n">
-        <v>1447.602416992188</v>
+        <v>1447.602294921875</v>
       </c>
       <c r="J534" t="n">
         <v>24.64999961853027</v>
@@ -16340,7 +16340,7 @@
         <v>112.5999984741211</v>
       </c>
       <c r="G535" t="n">
-        <v>1438.280517578125</v>
+        <v>1438.280395507812</v>
       </c>
       <c r="H535" t="n">
         <v>212.1000061035156</v>
@@ -16372,7 +16372,7 @@
         <v>107</v>
       </c>
       <c r="G536" t="n">
-        <v>1443.393920898438</v>
+        <v>1443.393798828125</v>
       </c>
       <c r="H536" t="n">
         <v>220.8999938964844</v>
@@ -16404,7 +16404,7 @@
         <v>102.4499969482422</v>
       </c>
       <c r="G537" t="n">
-        <v>1474.345581054688</v>
+        <v>1474.345458984375</v>
       </c>
       <c r="H537" t="n">
         <v>223.25</v>
@@ -16474,7 +16474,7 @@
         <v>226.6999969482422</v>
       </c>
       <c r="I539" t="n">
-        <v>1419.279052734375</v>
+        <v>1419.278930664062</v>
       </c>
       <c r="J539" t="n">
         <v>23.04999923706055</v>
@@ -16532,13 +16532,13 @@
         <v>93.44999694824219</v>
       </c>
       <c r="G541" t="n">
-        <v>1461.302856445312</v>
+        <v>1461.302734375</v>
       </c>
       <c r="H541" t="n">
         <v>221.1999969482422</v>
       </c>
       <c r="I541" t="n">
-        <v>1364.31298828125</v>
+        <v>1364.313110351562</v>
       </c>
       <c r="J541" t="n">
         <v>22.54999923706055</v>
@@ -16564,7 +16564,7 @@
         <v>92.05000305175781</v>
       </c>
       <c r="G542" t="n">
-        <v>1449.124633789062</v>
+        <v>1449.12451171875</v>
       </c>
       <c r="H542" t="n">
         <v>223.6499938964844</v>
@@ -16666,7 +16666,7 @@
         <v>214.25</v>
       </c>
       <c r="I545" t="n">
-        <v>1232.780151367188</v>
+        <v>1232.7802734375</v>
       </c>
       <c r="J545" t="n">
         <v>21.04999923706055</v>
@@ -16730,7 +16730,7 @@
         <v>255.9499969482422</v>
       </c>
       <c r="I547" t="n">
-        <v>1217.012084960938</v>
+        <v>1217.01220703125</v>
       </c>
       <c r="J547" t="n">
         <v>23.20000076293945</v>
@@ -16794,7 +16794,7 @@
         <v>249.3000030517578</v>
       </c>
       <c r="I549" t="n">
-        <v>1200.2060546875</v>
+        <v>1200.205932617188</v>
       </c>
       <c r="J549" t="n">
         <v>23.89999961853027</v>
@@ -16820,13 +16820,13 @@
         <v>87.05000305175781</v>
       </c>
       <c r="G550" t="n">
-        <v>1433.685668945312</v>
+        <v>1433.685791015625</v>
       </c>
       <c r="H550" t="n">
         <v>271.2000122070312</v>
       </c>
       <c r="I550" t="n">
-        <v>1225.909423828125</v>
+        <v>1225.909545898438</v>
       </c>
       <c r="J550" t="n">
         <v>25.04999923706055</v>
@@ -16852,13 +16852,13 @@
         <v>91.40000152587891</v>
       </c>
       <c r="G551" t="n">
-        <v>1437.6875</v>
+        <v>1437.687622070312</v>
       </c>
       <c r="H551" t="n">
         <v>277.3500061035156</v>
       </c>
       <c r="I551" t="n">
-        <v>1234.7080078125</v>
+        <v>1234.707885742188</v>
       </c>
       <c r="J551" t="n">
         <v>26.29999923706055</v>
@@ -16890,7 +16890,7 @@
         <v>273.7000122070312</v>
       </c>
       <c r="I552" t="n">
-        <v>1234.361938476562</v>
+        <v>1234.36181640625</v>
       </c>
       <c r="J552" t="n">
         <v>27.60000038146973</v>
@@ -16922,7 +16922,7 @@
         <v>266.9500122070312</v>
       </c>
       <c r="I553" t="n">
-        <v>1257.198486328125</v>
+        <v>1257.198364257812</v>
       </c>
       <c r="J553" t="n">
         <v>27.64999961853027</v>
@@ -16954,7 +16954,7 @@
         <v>270.9500122070312</v>
       </c>
       <c r="I554" t="n">
-        <v>1260.905639648438</v>
+        <v>1260.90576171875</v>
       </c>
       <c r="J554" t="n">
         <v>28.25</v>
@@ -16986,7 +16986,7 @@
         <v>268.6499938964844</v>
       </c>
       <c r="I555" t="n">
-        <v>1305.936279296875</v>
+        <v>1305.936401367188</v>
       </c>
       <c r="J555" t="n">
         <v>28.89999961853027</v>
@@ -17012,7 +17012,7 @@
         <v>89.90000152587891</v>
       </c>
       <c r="G556" t="n">
-        <v>1469.232055664062</v>
+        <v>1469.232177734375</v>
       </c>
       <c r="H556" t="n">
         <v>289.7999877929688</v>
@@ -17050,7 +17050,7 @@
         <v>291.7999877929688</v>
       </c>
       <c r="I557" t="n">
-        <v>1334.457275390625</v>
+        <v>1334.457397460938</v>
       </c>
       <c r="J557" t="n">
         <v>31.79999923706055</v>
@@ -17082,7 +17082,7 @@
         <v>295</v>
       </c>
       <c r="I558" t="n">
-        <v>1325.80712890625</v>
+        <v>1325.807250976562</v>
       </c>
       <c r="J558" t="n">
         <v>33.34999847412109</v>
@@ -17108,7 +17108,7 @@
         <v>90.84999847412109</v>
       </c>
       <c r="G559" t="n">
-        <v>1442.702026367188</v>
+        <v>1442.7021484375</v>
       </c>
       <c r="H559" t="n">
         <v>298.8999938964844</v>
@@ -17146,7 +17146,7 @@
         <v>287.6000061035156</v>
       </c>
       <c r="I560" t="n">
-        <v>1300.845092773438</v>
+        <v>1300.844970703125</v>
       </c>
       <c r="J560" t="n">
         <v>31</v>
@@ -17172,7 +17172,7 @@
         <v>89.44999694824219</v>
       </c>
       <c r="G561" t="n">
-        <v>1446.209716796875</v>
+        <v>1446.209838867188</v>
       </c>
       <c r="H561" t="n">
         <v>284.5</v>
@@ -17204,13 +17204,13 @@
         <v>89</v>
       </c>
       <c r="G562" t="n">
-        <v>1461.945068359375</v>
+        <v>1461.944946289062</v>
       </c>
       <c r="H562" t="n">
         <v>227.6000061035156</v>
       </c>
       <c r="I562" t="n">
-        <v>1280.974365234375</v>
+        <v>1280.974243164062</v>
       </c>
       <c r="J562" t="n">
         <v>28.35000038146973</v>
@@ -17274,7 +17274,7 @@
         <v>199.9499969482422</v>
       </c>
       <c r="I564" t="n">
-        <v>1234.658569335938</v>
+        <v>1234.658447265625</v>
       </c>
       <c r="J564" t="n">
         <v>26.04999923706055</v>
@@ -17306,7 +17306,7 @@
         <v>194.1999969482422</v>
       </c>
       <c r="I565" t="n">
-        <v>1241.380859375</v>
+        <v>1241.380981445312</v>
       </c>
       <c r="J565" t="n">
         <v>27.35000038146973</v>
@@ -17338,7 +17338,7 @@
         <v>194.6999969482422</v>
       </c>
       <c r="I566" t="n">
-        <v>1236.8828125</v>
+        <v>1236.882934570312</v>
       </c>
       <c r="J566" t="n">
         <v>28.70000076293945</v>
@@ -17364,13 +17364,13 @@
         <v>87.59999847412109</v>
       </c>
       <c r="G567" t="n">
-        <v>1452.607543945312</v>
+        <v>1452.607666015625</v>
       </c>
       <c r="H567" t="n">
         <v>188.75</v>
       </c>
       <c r="I567" t="n">
-        <v>1248.350463867188</v>
+        <v>1248.350708007812</v>
       </c>
       <c r="J567" t="n">
         <v>28.04999923706055</v>
@@ -17492,13 +17492,13 @@
         <v>92.75</v>
       </c>
       <c r="G571" t="n">
-        <v>1442.578491210938</v>
+        <v>1442.57861328125</v>
       </c>
       <c r="H571" t="n">
         <v>192.6499938964844</v>
       </c>
       <c r="I571" t="n">
-        <v>1290.761352539062</v>
+        <v>1290.761474609375</v>
       </c>
       <c r="J571" t="n">
         <v>27.5</v>
@@ -17524,7 +17524,7 @@
         <v>90.59999847412109</v>
       </c>
       <c r="G572" t="n">
-        <v>1435.242065429688</v>
+        <v>1435.2421875</v>
       </c>
       <c r="H572" t="n">
         <v>190.8999938964844</v>
@@ -17556,7 +17556,7 @@
         <v>88.75</v>
       </c>
       <c r="G573" t="n">
-        <v>1447.568481445312</v>
+        <v>1447.568359375</v>
       </c>
       <c r="H573" t="n">
         <v>185.8000030517578</v>
@@ -17594,7 +17594,7 @@
         <v>177.8999938964844</v>
       </c>
       <c r="I574" t="n">
-        <v>1309.692993164062</v>
+        <v>1309.693115234375</v>
       </c>
       <c r="J574" t="n">
         <v>27.29999923706055</v>
@@ -17626,7 +17626,7 @@
         <v>175.4499969482422</v>
       </c>
       <c r="I575" t="n">
-        <v>1296.544677734375</v>
+        <v>1296.544555664062</v>
       </c>
       <c r="J575" t="n">
         <v>26.95000076293945</v>
@@ -17652,13 +17652,13 @@
         <v>83.69999694824219</v>
       </c>
       <c r="G576" t="n">
-        <v>1416.9130859375</v>
+        <v>1416.912963867188</v>
       </c>
       <c r="H576" t="n">
         <v>176.1999969482422</v>
       </c>
       <c r="I576" t="n">
-        <v>1283.791748046875</v>
+        <v>1283.791870117188</v>
       </c>
       <c r="J576" t="n">
         <v>26.79999923706055</v>
@@ -17690,7 +17690,7 @@
         <v>166.5500030517578</v>
       </c>
       <c r="I577" t="n">
-        <v>1268.073120117188</v>
+        <v>1268.072998046875</v>
       </c>
       <c r="J577" t="n">
         <v>25.85000038146973</v>
@@ -17716,7 +17716,7 @@
         <v>80</v>
       </c>
       <c r="G578" t="n">
-        <v>1384.775512695312</v>
+        <v>1384.775634765625</v>
       </c>
       <c r="H578" t="n">
         <v>170.75</v>
@@ -17748,7 +17748,7 @@
         <v>80.59999847412109</v>
       </c>
       <c r="G579" t="n">
-        <v>1401.647216796875</v>
+        <v>1401.647338867188</v>
       </c>
       <c r="H579" t="n">
         <v>166.8000030517578</v>
@@ -17812,7 +17812,7 @@
         <v>78</v>
       </c>
       <c r="G581" t="n">
-        <v>1390.65478515625</v>
+        <v>1390.654663085938</v>
       </c>
       <c r="H581" t="n">
         <v>162.9499969482422</v>
@@ -17876,13 +17876,13 @@
         <v>80.25</v>
       </c>
       <c r="G583" t="n">
-        <v>1403.153930664062</v>
+        <v>1403.154052734375</v>
       </c>
       <c r="H583" t="n">
         <v>171.4499969482422</v>
       </c>
       <c r="I583" t="n">
-        <v>1204.901977539062</v>
+        <v>1204.901733398438</v>
       </c>
       <c r="J583" t="n">
         <v>25.60000038146973</v>
@@ -17908,13 +17908,13 @@
         <v>80.5</v>
       </c>
       <c r="G584" t="n">
-        <v>1399.399291992188</v>
+        <v>1399.399169921875</v>
       </c>
       <c r="H584" t="n">
         <v>171.6000061035156</v>
       </c>
       <c r="I584" t="n">
-        <v>1211.426391601562</v>
+        <v>1211.426513671875</v>
       </c>
       <c r="J584" t="n">
         <v>25.79999923706055</v>
@@ -17978,7 +17978,7 @@
         <v>170.1000061035156</v>
       </c>
       <c r="I586" t="n">
-        <v>1220.472290039062</v>
+        <v>1220.47216796875</v>
       </c>
       <c r="J586" t="n">
         <v>26.14999961853027</v>
@@ -18004,7 +18004,7 @@
         <v>80.5</v>
       </c>
       <c r="G587" t="n">
-        <v>1419.0126953125</v>
+        <v>1419.012817382812</v>
       </c>
       <c r="H587" t="n">
         <v>167.8500061035156</v>
@@ -18036,7 +18036,7 @@
         <v>82.25</v>
       </c>
       <c r="G588" t="n">
-        <v>1443.24560546875</v>
+        <v>1443.245483398438</v>
       </c>
       <c r="H588" t="n">
         <v>167.3500061035156</v>
@@ -18170,7 +18170,7 @@
         <v>168.8999938964844</v>
       </c>
       <c r="I592" t="n">
-        <v>1209.64697265625</v>
+        <v>1209.647094726562</v>
       </c>
       <c r="J592" t="n">
         <v>24.95000076293945</v>
@@ -18234,7 +18234,7 @@
         <v>167.1000061035156</v>
       </c>
       <c r="I594" t="n">
-        <v>1165.160034179688</v>
+        <v>1165.16015625</v>
       </c>
       <c r="J594" t="n">
         <v>24.70000076293945</v>
@@ -18266,7 +18266,7 @@
         <v>166.3500061035156</v>
       </c>
       <c r="I595" t="n">
-        <v>1168.373168945312</v>
+        <v>1168.373046875</v>
       </c>
       <c r="J595" t="n">
         <v>24.54999923706055</v>
@@ -18298,7 +18298,7 @@
         <v>173.25</v>
       </c>
       <c r="I596" t="n">
-        <v>1223.042602539062</v>
+        <v>1223.04248046875</v>
       </c>
       <c r="J596" t="n">
         <v>25.75</v>
@@ -18484,7 +18484,7 @@
         <v>79.94000244140625</v>
       </c>
       <c r="G602" t="n">
-        <v>1439.317993164062</v>
+        <v>1439.31787109375</v>
       </c>
       <c r="H602" t="n">
         <v>189.3000030517578</v>
@@ -18548,7 +18548,7 @@
         <v>84.11000061035156</v>
       </c>
       <c r="G604" t="n">
-        <v>1447.790649414062</v>
+        <v>1447.790771484375</v>
       </c>
       <c r="H604" t="n">
         <v>203.1499938964844</v>
@@ -18612,7 +18612,7 @@
         <v>84.55999755859375</v>
       </c>
       <c r="G606" t="n">
-        <v>1463.377807617188</v>
+        <v>1463.377685546875</v>
       </c>
       <c r="H606" t="n">
         <v>211.0299987792969</v>
@@ -18708,7 +18708,7 @@
         <v>83.44999694824219</v>
       </c>
       <c r="G609" t="n">
-        <v>1436.872436523438</v>
+        <v>1436.872314453125</v>
       </c>
       <c r="H609" t="n">
         <v>214.8000030517578</v>
@@ -18772,7 +18772,7 @@
         <v>80.86000061035156</v>
       </c>
       <c r="G611" t="n">
-        <v>1436.822875976562</v>
+        <v>1436.822998046875</v>
       </c>
       <c r="H611" t="n">
         <v>208.3999938964844</v>
@@ -18868,7 +18868,7 @@
         <v>79.63999938964844</v>
       </c>
       <c r="G614" t="n">
-        <v>1546.747436523438</v>
+        <v>1546.747314453125</v>
       </c>
       <c r="H614" t="n">
         <v>199.9299926757812</v>
@@ -19028,7 +19028,7 @@
         <v>85.66999816894531</v>
       </c>
       <c r="G619" t="n">
-        <v>1569.695556640625</v>
+        <v>1569.695678710938</v>
       </c>
       <c r="H619" t="n">
         <v>199.1399993896484</v>
@@ -19092,7 +19092,7 @@
         <v>84.80999755859375</v>
       </c>
       <c r="G621" t="n">
-        <v>1571.326049804688</v>
+        <v>1571.325927734375</v>
       </c>
       <c r="H621" t="n">
         <v>196.5800018310547</v>
@@ -19284,7 +19284,7 @@
         <v>80.31999969482422</v>
       </c>
       <c r="G627" t="n">
-        <v>1567.76904296875</v>
+        <v>1567.768920898438</v>
       </c>
       <c r="H627" t="n">
         <v>188</v>
@@ -19508,7 +19508,7 @@
         <v>93.55999755859375</v>
       </c>
       <c r="G634" t="n">
-        <v>1501.987060546875</v>
+        <v>1501.987182617188</v>
       </c>
       <c r="H634" t="n">
         <v>199.3699951171875</v>
@@ -19572,7 +19572,7 @@
         <v>98.19999694824219</v>
       </c>
       <c r="G636" t="n">
-        <v>1487.487060546875</v>
+        <v>1487.486938476562</v>
       </c>
       <c r="H636" t="n">
         <v>207.1699981689453</v>
@@ -19636,7 +19636,7 @@
         <v>93.27999877929688</v>
       </c>
       <c r="G638" t="n">
-        <v>1481.459594726562</v>
+        <v>1481.459716796875</v>
       </c>
       <c r="H638" t="n">
         <v>215.7200012207031</v>
@@ -19828,7 +19828,7 @@
         <v>96.81999969482422</v>
       </c>
       <c r="G644" t="n">
-        <v>1443.220703125</v>
+        <v>1443.220825195312</v>
       </c>
       <c r="H644" t="n">
         <v>226.0599975585938</v>
@@ -19892,7 +19892,7 @@
         <v>93.84999847412109</v>
       </c>
       <c r="G646" t="n">
-        <v>1444.431274414062</v>
+        <v>1444.43115234375</v>
       </c>
       <c r="H646" t="n">
         <v>220.2799987792969</v>
@@ -19924,7 +19924,7 @@
         <v>95.01000213623047</v>
       </c>
       <c r="G647" t="n">
-        <v>1460.58642578125</v>
+        <v>1460.586303710938</v>
       </c>
       <c r="H647" t="n">
         <v>217.9700012207031</v>
@@ -37494,7 +37494,7 @@
         <v>-3.095716273530114</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6193347598382193</v>
+        <v>0.6193430171434144</v>
       </c>
       <c r="H27" t="n">
         <v>0.9847026900382971</v>
@@ -37526,7 +37526,7 @@
         <v>23.30486903670943</v>
       </c>
       <c r="G28" t="n">
-        <v>-3.831289748878441</v>
+        <v>-3.831290051246339</v>
       </c>
       <c r="H28" t="n">
         <v>3.621270323810255</v>
@@ -37558,13 +37558,13 @@
         <v>-0.3254094258637208</v>
       </c>
       <c r="G29" t="n">
-        <v>9.437915851090327</v>
+        <v>9.437907214178898</v>
       </c>
       <c r="H29" t="n">
         <v>20.18634526010754</v>
       </c>
       <c r="I29" t="n">
-        <v>14.89904258694705</v>
+        <v>14.89905459147085</v>
       </c>
       <c r="J29" t="n">
         <v>17.84114543475508</v>
@@ -37596,7 +37596,7 @@
         <v>-6.49240482812462</v>
       </c>
       <c r="I30" t="n">
-        <v>-10.79030161697194</v>
+        <v>-10.79031925231471</v>
       </c>
       <c r="J30" t="n">
         <v>-10.07326035477244</v>
@@ -37628,7 +37628,7 @@
         <v>-34.34213475489638</v>
       </c>
       <c r="I31" t="n">
-        <v>3.869231128923167</v>
+        <v>3.869230754336672</v>
       </c>
       <c r="J31" t="n">
         <v>-3.36283455907771</v>
@@ -37654,13 +37654,13 @@
         <v>-19.4392551885587</v>
       </c>
       <c r="G32" t="n">
-        <v>1.714793192957242</v>
+        <v>1.714801795153398</v>
       </c>
       <c r="H32" t="n">
         <v>22.65731991554547</v>
       </c>
       <c r="I32" t="n">
-        <v>-10.22068611256335</v>
+        <v>-10.22067742088289</v>
       </c>
       <c r="J32" t="n">
         <v>16.73553350982875</v>
@@ -37686,7 +37686,7 @@
         <v>-8.54700854700855</v>
       </c>
       <c r="G33" t="n">
-        <v>2.395533985038512</v>
+        <v>2.395516458058666</v>
       </c>
       <c r="H33" t="n">
         <v>-4.392992435061648</v>
@@ -37718,13 +37718,13 @@
         <v>33.94390617495342</v>
       </c>
       <c r="G34" t="n">
-        <v>10.37930014680082</v>
+        <v>10.37930970539087</v>
       </c>
       <c r="H34" t="n">
         <v>10.12869384694794</v>
       </c>
       <c r="I34" t="n">
-        <v>4.61743963491108</v>
+        <v>4.617430052899274</v>
       </c>
       <c r="J34" t="n">
         <v>27.89699662161886</v>
@@ -37750,13 +37750,13 @@
         <v>0.9243158800178009</v>
       </c>
       <c r="G35" t="n">
-        <v>8.727841537326796</v>
+        <v>8.727830237407975</v>
       </c>
       <c r="H35" t="n">
         <v>10.5665365226655</v>
       </c>
       <c r="I35" t="n">
-        <v>23.11872529727841</v>
+        <v>23.11872269028099</v>
       </c>
       <c r="J35" t="n">
         <v>10.16548301327902</v>
@@ -37782,13 +37782,13 @@
         <v>26.90616851118288</v>
       </c>
       <c r="G36" t="n">
-        <v>3.914067330304039</v>
+        <v>3.914078129935761</v>
       </c>
       <c r="H36" t="n">
         <v>12.11225997045791</v>
       </c>
       <c r="I36" t="n">
-        <v>8.906449900509328</v>
+        <v>8.906468868764028</v>
       </c>
       <c r="J36" t="n">
         <v>23.68420553633026</v>
@@ -37814,13 +37814,13 @@
         <v>6.812840372868889</v>
       </c>
       <c r="G37" t="n">
-        <v>-2.434970344559451</v>
+        <v>-2.434960064459102</v>
       </c>
       <c r="H37" t="n">
         <v>-2.336989602099571</v>
       </c>
       <c r="I37" t="n">
-        <v>4.51120543209822</v>
+        <v>4.51119901463739</v>
       </c>
       <c r="J37" t="n">
         <v>-11.16882918717025</v>
@@ -37846,13 +37846,13 @@
         <v>-6.583760205501399</v>
       </c>
       <c r="G38" t="n">
-        <v>-2.575810224095743</v>
+        <v>-2.575820489355185</v>
       </c>
       <c r="H38" t="n">
         <v>-7.202140266796353</v>
       </c>
       <c r="I38" t="n">
-        <v>-5.426390322743146</v>
+        <v>-5.426396062627347</v>
       </c>
       <c r="J38" t="n">
         <v>0.5221952138994457</v>
@@ -37875,13 +37875,13 @@
         <v>17.33905317445681</v>
       </c>
       <c r="G39" t="n">
-        <v>-5.246537031303699</v>
+        <v>-5.246546247677264</v>
       </c>
       <c r="H39" t="n">
         <v>-1.111996841749918</v>
       </c>
       <c r="I39" t="n">
-        <v>4.903569221099491</v>
+        <v>4.90358226696832</v>
       </c>
       <c r="J39" t="n">
         <v>16.41336614204727</v>
@@ -37904,13 +37904,13 @@
         <v>-7.245221803084723</v>
       </c>
       <c r="G40" t="n">
-        <v>8.299902823900585</v>
+        <v>8.299913357895106</v>
       </c>
       <c r="H40" t="n">
         <v>36.60036607849231</v>
       </c>
       <c r="I40" t="n">
-        <v>1.693675629957525</v>
+        <v>1.693669155291055</v>
       </c>
       <c r="J40" t="n">
         <v>17.08185437454475</v>
@@ -37933,7 +37933,7 @@
         <v>2.446982085920046</v>
       </c>
       <c r="G41" t="n">
-        <v>3.253172538244864</v>
+        <v>3.25318376876691</v>
       </c>
       <c r="H41" t="n">
         <v>2.635488591081314</v>
@@ -37962,7 +37962,7 @@
         <v>5.598621951273208</v>
       </c>
       <c r="G42" t="n">
-        <v>2.040900359286013</v>
+        <v>2.040877935444163</v>
       </c>
       <c r="H42" t="n">
         <v>-14.50333586855534</v>
@@ -37991,13 +37991,13 @@
         <v>7.004606888590881</v>
       </c>
       <c r="G43" t="n">
-        <v>3.837320273090516</v>
+        <v>3.837343764441714</v>
       </c>
       <c r="H43" t="n">
         <v>9.220106101738512</v>
       </c>
       <c r="I43" t="n">
-        <v>7.802010417317251</v>
+        <v>7.802001872916686</v>
       </c>
       <c r="J43" t="n">
         <v>22.61306576011055</v>
@@ -38020,13 +38020,13 @@
         <v>-7.106166810697612</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3659830649118234</v>
+        <v>0.3659714981767426</v>
       </c>
       <c r="H44" t="n">
         <v>10.36725582872331</v>
       </c>
       <c r="I44" t="n">
-        <v>-2.506398636647234</v>
+        <v>-2.506390909291822</v>
       </c>
       <c r="J44" t="n">
         <v>1.53060832255989</v>
@@ -38049,13 +38049,13 @@
         <v>-5.117786759101961</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.329731717430038</v>
+        <v>-1.329720456261541</v>
       </c>
       <c r="H45" t="n">
         <v>4.476417699780821</v>
       </c>
       <c r="I45" t="n">
-        <v>-7.821843174509246</v>
+        <v>-7.821836608719702</v>
       </c>
       <c r="J45" t="n">
         <v>-23.13725340600107</v>
@@ -38078,13 +38078,13 @@
         <v>-6.883508838267105</v>
       </c>
       <c r="G46" t="n">
-        <v>-7.590679750087537</v>
+        <v>-7.590700042745402</v>
       </c>
       <c r="H46" t="n">
         <v>-9.150325892060184</v>
       </c>
       <c r="I46" t="n">
-        <v>-7.873132391548731</v>
+        <v>-7.873151044662352</v>
       </c>
       <c r="J46" t="n">
         <v>-11.14982814589901</v>
@@ -38107,13 +38107,13 @@
         <v>-2.865546642449923</v>
       </c>
       <c r="G47" t="n">
-        <v>-6.742100064294965</v>
+        <v>-6.742090228748266</v>
       </c>
       <c r="H47" t="n">
         <v>-12.68230842551258</v>
       </c>
       <c r="I47" t="n">
-        <v>-10.50512094276369</v>
+        <v>-10.50510919721274</v>
       </c>
       <c r="J47" t="n">
         <v>-10.59189368473866</v>
@@ -38136,13 +38136,13 @@
         <v>6.079503403138031</v>
       </c>
       <c r="G48" t="n">
-        <v>7.128570156643566</v>
+        <v>7.128581444439974</v>
       </c>
       <c r="H48" t="n">
         <v>11.48815860769938</v>
       </c>
       <c r="I48" t="n">
-        <v>-3.906738589925352</v>
+        <v>-3.906749435665913</v>
       </c>
       <c r="J48" t="n">
         <v>-0.3105661069842447</v>
@@ -38165,13 +38165,13 @@
         <v>-0.696589719615015</v>
       </c>
       <c r="G49" t="n">
-        <v>7.227420215142799</v>
+        <v>7.227408916932054</v>
       </c>
       <c r="H49" t="n">
         <v>3.474762330681291</v>
       </c>
       <c r="I49" t="n">
-        <v>1.992280127469637</v>
+        <v>1.992279898127447</v>
       </c>
       <c r="J49" t="n">
         <v>-1.829263683162408</v>
@@ -38200,7 +38200,7 @@
         <v>-15.6172858344184</v>
       </c>
       <c r="I50" t="n">
-        <v>5.378692749161718</v>
+        <v>5.378698488282385</v>
       </c>
       <c r="J50" t="n">
         <v>-2.380950218425493</v>
@@ -38223,13 +38223,13 @@
         <v>8.782737772308536</v>
       </c>
       <c r="G51" t="n">
-        <v>5.463632047055778</v>
+        <v>5.463643374052984</v>
       </c>
       <c r="H51" t="n">
         <v>38.34329813061588</v>
       </c>
       <c r="I51" t="n">
-        <v>4.312852644306764</v>
+        <v>4.312852371434839</v>
       </c>
       <c r="J51" t="n">
         <v>35.48386898298783</v>
@@ -38252,13 +38252,13 @@
         <v>-5.942026774088538</v>
       </c>
       <c r="G52" t="n">
-        <v>-3.320959299636128</v>
+        <v>-3.320959644468446</v>
       </c>
       <c r="H52" t="n">
         <v>29.24944861623748</v>
       </c>
       <c r="I52" t="n">
-        <v>3.064809231029253</v>
+        <v>3.064815751886085</v>
       </c>
       <c r="J52" t="n">
         <v>7.826083639393677</v>
@@ -38281,13 +38281,13 @@
         <v>-8.609271523178808</v>
       </c>
       <c r="G53" t="n">
-        <v>-1.405405239390534</v>
+        <v>-1.405415476974137</v>
       </c>
       <c r="H53" t="n">
         <v>-16.0722547147822</v>
       </c>
       <c r="I53" t="n">
-        <v>2.955464940149111</v>
+        <v>2.955471852145508</v>
       </c>
       <c r="J53" t="n">
         <v>-8.730161493387333</v>
@@ -38316,7 +38316,7 @@
         <v>-12.62647164563844</v>
       </c>
       <c r="I54" t="n">
-        <v>-16.35934608481275</v>
+        <v>-16.35936109340738</v>
       </c>
       <c r="J54" t="n">
         <v>-11.57894469144052</v>
@@ -38339,13 +38339,13 @@
         <v>1.233112628945943</v>
       </c>
       <c r="G55" t="n">
-        <v>5.90190738872356</v>
+        <v>5.901896555568986</v>
       </c>
       <c r="H55" t="n">
         <v>10.01780916676824</v>
       </c>
       <c r="I55" t="n">
-        <v>42.1559706663859</v>
+        <v>42.15598663130014</v>
       </c>
       <c r="J55" t="n">
         <v>5.555555555555558</v>
@@ -38368,13 +38368,13 @@
         <v>10.65627667685571</v>
       </c>
       <c r="G56" t="n">
-        <v>11.6632229717543</v>
+        <v>11.66323439425943</v>
       </c>
       <c r="H56" t="n">
         <v>7.361381156751889</v>
       </c>
       <c r="I56" t="n">
-        <v>11.44043827261805</v>
+        <v>11.44042835922838</v>
       </c>
       <c r="J56" t="n">
         <v>3.4482743501002</v>
@@ -38397,13 +38397,13 @@
         <v>-6.15854030702172</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.133403576054681</v>
+        <v>-1.133414741099703</v>
       </c>
       <c r="H57" t="n">
         <v>3.513107684464867</v>
       </c>
       <c r="I57" t="n">
-        <v>-20.63637016359784</v>
+        <v>-20.63635189760942</v>
       </c>
       <c r="J57" t="n">
         <v>-11.82432417193846</v>
@@ -38768,7 +38768,7 @@
         <v>2.925667816312849</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.354134712024472</v>
+        <v>-5.354127242510708</v>
       </c>
       <c r="H10" t="n">
         <v>68.12385194646686</v>
@@ -38800,13 +38800,13 @@
         <v>-7.610206253873331</v>
       </c>
       <c r="G11" t="n">
-        <v>5.353850426268458</v>
+        <v>5.353842111674156</v>
       </c>
       <c r="H11" t="n">
         <v>-26.21148416003172</v>
       </c>
       <c r="I11" t="n">
-        <v>6.467093392907319</v>
+        <v>6.467083085656977</v>
       </c>
       <c r="J11" t="n">
         <v>2.407080726285948</v>
@@ -38838,7 +38838,7 @@
         <v>29.14681042220371</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.392583164828846</v>
+        <v>-5.392582670916979</v>
       </c>
       <c r="J12" t="n">
         <v>21.24463916318964</v>
@@ -38864,13 +38864,13 @@
         <v>36.80501262584171</v>
       </c>
       <c r="G13" t="n">
-        <v>10.23240719569851</v>
+        <v>10.23241881051799</v>
       </c>
       <c r="H13" t="n">
         <v>21.06174227192534</v>
       </c>
       <c r="I13" t="n">
-        <v>40.13304808147762</v>
+        <v>40.1330609163993</v>
       </c>
       <c r="J13" t="n">
         <v>21.03895707563921</v>
@@ -38893,7 +38893,7 @@
         <v>1.671973327733589</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.02533425681351398</v>
+        <v>-0.02534479080803509</v>
       </c>
       <c r="H14" t="n">
         <v>25.35262426890257</v>
@@ -38922,13 +38922,13 @@
         <v>15.76036725725447</v>
       </c>
       <c r="G15" t="n">
-        <v>9.403485464018434</v>
+        <v>9.403498072287109</v>
       </c>
       <c r="H15" t="n">
         <v>-4.159445407279028</v>
       </c>
       <c r="I15" t="n">
-        <v>22.41577105363026</v>
+        <v>22.41576135094123</v>
       </c>
       <c r="J15" t="n">
         <v>41.20603477451257</v>
@@ -38951,13 +38951,13 @@
         <v>-17.92738085880669</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.4857705142105</v>
+        <v>-8.485790712466645</v>
       </c>
       <c r="H16" t="n">
         <v>4.756719823472322</v>
       </c>
       <c r="I16" t="n">
-        <v>-17.20760648656623</v>
+        <v>-17.20761079032843</v>
       </c>
       <c r="J16" t="n">
         <v>-30.66202407831533</v>
@@ -38980,13 +38980,13 @@
         <v>2.321981478994783</v>
       </c>
       <c r="G17" t="n">
-        <v>7.126470702214305</v>
+        <v>7.12648200042505</v>
       </c>
       <c r="H17" t="n">
         <v>0.7315289117223678</v>
       </c>
       <c r="I17" t="n">
-        <v>-12.28811993556758</v>
+        <v>-12.28811852101525</v>
       </c>
       <c r="J17" t="n">
         <v>-12.49999563868442</v>
@@ -39009,13 +39009,13 @@
         <v>-6.376813805621606</v>
       </c>
       <c r="G18" t="n">
-        <v>-8.095942839170478</v>
+        <v>-8.095933296298796</v>
       </c>
       <c r="H18" t="n">
         <v>50.88300138028043</v>
       </c>
       <c r="I18" t="n">
-        <v>13.29246668885498</v>
+        <v>13.29247973056862</v>
       </c>
       <c r="J18" t="n">
         <v>42.60869233504585</v>
@@ -39038,7 +39038,7 @@
         <v>-18.96653110566366</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.483982613660928</v>
+        <v>-1.484002920704985</v>
       </c>
       <c r="H19" t="n">
         <v>-19.32324486904549</v>
@@ -39159,7 +39159,7 @@
         <v>26.11641041112731</v>
       </c>
       <c r="I2" t="n">
-        <v>13.54569421427558</v>
+        <v>13.54570754168862</v>
       </c>
       <c r="J2" t="n">
         <v>84.03669388711693</v>
@@ -39217,13 +39217,13 @@
         <v>35.23950508448274</v>
       </c>
       <c r="G4" t="n">
-        <v>20.50513561497333</v>
+        <v>20.50514742013778</v>
       </c>
       <c r="H4" t="n">
         <v>18.55826056452661</v>
       </c>
       <c r="I4" t="n">
-        <v>15.84091850541089</v>
+        <v>15.84090469060915</v>
       </c>
       <c r="J4" t="n">
         <v>79.47977229122856</v>
@@ -39255,7 +39255,7 @@
         <v>18.42639458918014</v>
       </c>
       <c r="I5" t="n">
-        <v>15.5924279725592</v>
+        <v>15.59243490632829</v>
       </c>
       <c r="J5" t="n">
         <v>78.32370949116567</v>
@@ -39287,7 +39287,7 @@
         <v>20.42312944893776</v>
       </c>
       <c r="I6" t="n">
-        <v>16.84898733968458</v>
+        <v>16.8489945570937</v>
       </c>
       <c r="J6" t="n">
         <v>74.1786665643551</v>
@@ -39319,7 +39319,7 @@
         <v>19.02754764747889</v>
       </c>
       <c r="I7" t="n">
-        <v>14.23300996545445</v>
+        <v>14.23300300571448</v>
       </c>
       <c r="J7" t="n">
         <v>70.31517486505918</v>
@@ -39415,7 +39415,7 @@
         <v>14.29718712087935</v>
       </c>
       <c r="I10" t="n">
-        <v>15.13143815733493</v>
+        <v>15.13143116975007</v>
       </c>
       <c r="J10" t="n">
         <v>54.93472933327954</v>
@@ -39447,7 +39447,7 @@
         <v>13.73462507545713</v>
       </c>
       <c r="I11" t="n">
-        <v>16.10096676605517</v>
+        <v>16.10095968062235</v>
       </c>
       <c r="J11" t="n">
         <v>56.99999959845292</v>
@@ -39479,7 +39479,7 @@
         <v>12.00104193248259</v>
       </c>
       <c r="I12" t="n">
-        <v>16.53926699663837</v>
+        <v>16.53925992256591</v>
       </c>
       <c r="J12" t="n">
         <v>58.82353170735514</v>
@@ -39511,7 +39511,7 @@
         <v>23.48532329238919</v>
       </c>
       <c r="I13" t="n">
-        <v>16.79518332705205</v>
+        <v>16.79517617557025</v>
       </c>
       <c r="J13" t="n">
         <v>58.58586276992115</v>
@@ -39569,7 +39569,7 @@
         <v>18.36042100886153</v>
       </c>
       <c r="G15" t="n">
-        <v>21.27163109269175</v>
+        <v>21.27164341356986</v>
       </c>
       <c r="H15" t="n">
         <v>50.10011067847504</v>
@@ -39633,13 +39633,13 @@
         <v>17.49119689344376</v>
       </c>
       <c r="G17" t="n">
-        <v>21.10590645985941</v>
+        <v>21.10591855208681</v>
       </c>
       <c r="H17" t="n">
         <v>80.21875186197276</v>
       </c>
       <c r="I17" t="n">
-        <v>38.57649706808945</v>
+        <v>38.57650560107664</v>
       </c>
       <c r="J17" t="n">
         <v>83.413475601984</v>
@@ -39671,7 +39671,7 @@
         <v>94.03570205320759</v>
       </c>
       <c r="I18" t="n">
-        <v>36.03351051593013</v>
+        <v>36.0335018181281</v>
       </c>
       <c r="J18" t="n">
         <v>117.663043844452</v>
@@ -39703,7 +39703,7 @@
         <v>94.1268552045597</v>
       </c>
       <c r="I19" t="n">
-        <v>32.47950210002233</v>
+        <v>32.47951058552494</v>
       </c>
       <c r="J19" t="n">
         <v>121.3157854582134</v>
@@ -39729,7 +39729,7 @@
         <v>19.92705386519244</v>
       </c>
       <c r="G20" t="n">
-        <v>22.53160722132512</v>
+        <v>22.5315948805225</v>
       </c>
       <c r="H20" t="n">
         <v>87.55847280153539</v>
@@ -39767,7 +39767,7 @@
         <v>75.75510868409864</v>
       </c>
       <c r="I21" t="n">
-        <v>31.45755074527625</v>
+        <v>31.45755910332362</v>
       </c>
       <c r="J21" t="n">
         <v>142.036550378158</v>
@@ -39863,7 +39863,7 @@
         <v>86.52584846797919</v>
       </c>
       <c r="I24" t="n">
-        <v>25.56498906543911</v>
+        <v>25.56498092143338</v>
       </c>
       <c r="J24" t="n">
         <v>182.3157862613076</v>
@@ -39921,13 +39921,13 @@
         <v>12.20622202314199</v>
       </c>
       <c r="G26" t="n">
-        <v>17.53102271117308</v>
+        <v>17.5310103032488</v>
       </c>
       <c r="H26" t="n">
         <v>66.09046092268591</v>
       </c>
       <c r="I26" t="n">
-        <v>19.39414825240846</v>
+        <v>19.3941404935573</v>
       </c>
       <c r="J26" t="n">
         <v>155.4089687454518</v>
@@ -39953,7 +39953,7 @@
         <v>17.44186046511629</v>
       </c>
       <c r="G27" t="n">
-        <v>19.7090865288315</v>
+        <v>19.70907390202596</v>
       </c>
       <c r="H27" t="n">
         <v>75.14619883040936</v>
@@ -39991,7 +39991,7 @@
         <v>73.99363134446153</v>
       </c>
       <c r="I28" t="n">
-        <v>21.57639027866838</v>
+        <v>21.57638252010072</v>
       </c>
       <c r="J28" t="n">
         <v>151.4062423941993</v>
@@ -40017,7 +40017,7 @@
         <v>20.66455888549516</v>
       </c>
       <c r="G29" t="n">
-        <v>17.87868509962784</v>
+        <v>17.8786975781118</v>
       </c>
       <c r="H29" t="n">
         <v>72.05968302788671</v>
@@ -40049,7 +40049,7 @@
         <v>27.42365317882882</v>
       </c>
       <c r="G30" t="n">
-        <v>17.42062467665613</v>
+        <v>17.420637048874</v>
       </c>
       <c r="H30" t="n">
         <v>64.25273449733912</v>
@@ -40081,13 +40081,13 @@
         <v>15.39021874936699</v>
       </c>
       <c r="G31" t="n">
-        <v>18.81745495257836</v>
+        <v>18.81746761698277</v>
       </c>
       <c r="H31" t="n">
         <v>65.98794595089427</v>
       </c>
       <c r="I31" t="n">
-        <v>28.69148398560164</v>
+        <v>28.69149231270651</v>
       </c>
       <c r="J31" t="n">
         <v>126.1298637885552</v>
@@ -40119,7 +40119,7 @@
         <v>68.60328526038532</v>
       </c>
       <c r="I32" t="n">
-        <v>28.59035158704684</v>
+        <v>28.59036001224431</v>
       </c>
       <c r="J32" t="n">
         <v>136.0106421941653</v>
@@ -40151,7 +40151,7 @@
         <v>69.25088116850071</v>
       </c>
       <c r="I33" t="n">
-        <v>25.14076236892711</v>
+        <v>25.14077025349546</v>
       </c>
       <c r="J33" t="n">
         <v>132.4867699130986</v>
@@ -40177,7 +40177,7 @@
         <v>13.01104692045925</v>
       </c>
       <c r="G34" t="n">
-        <v>17.43129886333536</v>
+        <v>17.43128634587006</v>
       </c>
       <c r="H34" t="n">
         <v>61.92835542694652</v>
@@ -40247,7 +40247,7 @@
         <v>56.8334812026194</v>
       </c>
       <c r="I36" t="n">
-        <v>22.657292123892</v>
+        <v>22.65728440839494</v>
       </c>
       <c r="J36" t="n">
         <v>127.3033753857291</v>
@@ -40273,7 +40273,7 @@
         <v>5.373968208882274</v>
       </c>
       <c r="G37" t="n">
-        <v>14.95783527583134</v>
+        <v>14.95784738829555</v>
       </c>
       <c r="H37" t="n">
         <v>49.29618947317174</v>
@@ -40311,7 +40311,7 @@
         <v>57.80926505349091</v>
       </c>
       <c r="I38" t="n">
-        <v>16.21145683918306</v>
+        <v>16.21146407658735</v>
       </c>
       <c r="J38" t="n">
         <v>124.1666581895616</v>
@@ -40375,7 +40375,7 @@
         <v>62.45973288227488</v>
       </c>
       <c r="I40" t="n">
-        <v>1.128971419277369</v>
+        <v>1.128983084690516</v>
       </c>
       <c r="J40" t="n">
         <v>134.7826177095873</v>
@@ -40401,7 +40401,7 @@
         <v>-0.8370914528086359</v>
       </c>
       <c r="G41" t="n">
-        <v>13.69312892900481</v>
+        <v>13.69311700167664</v>
       </c>
       <c r="H41" t="n">
         <v>59.2399202134017</v>
@@ -40433,7 +40433,7 @@
         <v>0.8595328089425314</v>
       </c>
       <c r="G42" t="n">
-        <v>15.70980847951631</v>
+        <v>15.70979617739452</v>
       </c>
       <c r="H42" t="n">
         <v>61.70213418337656</v>
@@ -40599,7 +40599,7 @@
         <v>85.00471194850942</v>
       </c>
       <c r="I47" t="n">
-        <v>9.613845276460232</v>
+        <v>9.613838637455906</v>
       </c>
       <c r="J47" t="n">
         <v>151.6363664106889</v>
@@ -40625,13 +40625,13 @@
         <v>25.26545854048294</v>
       </c>
       <c r="G48" t="n">
-        <v>17.38441714906611</v>
+        <v>17.38442994980116</v>
       </c>
       <c r="H48" t="n">
         <v>86.16140643431169</v>
       </c>
       <c r="I48" t="n">
-        <v>12.55596261032248</v>
+        <v>12.55596944361153</v>
       </c>
       <c r="J48" t="n">
         <v>159.4642984056154</v>
@@ -40663,7 +40663,7 @@
         <v>71.57738095238095</v>
       </c>
       <c r="I49" t="n">
-        <v>11.99740976505248</v>
+        <v>11.99740298068421</v>
       </c>
       <c r="J49" t="n">
         <v>158.230079573006</v>
@@ -40695,7 +40695,7 @@
         <v>62.06793961179837</v>
       </c>
       <c r="I50" t="n">
-        <v>10.18126922537272</v>
+        <v>10.18127599100154</v>
       </c>
       <c r="J50" t="n">
         <v>143.1579000203562</v>
@@ -40759,7 +40759,7 @@
         <v>48.54479267405647</v>
       </c>
       <c r="I52" t="n">
-        <v>8.042051785476056</v>
+        <v>8.042045115715425</v>
       </c>
       <c r="J52" t="n">
         <v>110.3013757156999</v>
@@ -40823,7 +40823,7 @@
         <v>41.15079311579386</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.521758640085147</v>
+        <v>-1.52174699598645</v>
       </c>
       <c r="J54" t="n">
         <v>86.16581204926534</v>
@@ -40849,13 +40849,13 @@
         <v>19.57686453413079</v>
       </c>
       <c r="G55" t="n">
-        <v>8.875891838578509</v>
+        <v>8.875880262034453</v>
       </c>
       <c r="H55" t="n">
         <v>36.97116125920574</v>
       </c>
       <c r="I55" t="n">
-        <v>-4.102523938621339</v>
+        <v>-4.102535207427882</v>
       </c>
       <c r="J55" t="n">
         <v>64.87922613616699</v>
@@ -40887,7 +40887,7 @@
         <v>43.77442279436383</v>
       </c>
       <c r="I56" t="n">
-        <v>-3.550933979170845</v>
+        <v>-3.550945305250486</v>
       </c>
       <c r="J56" t="n">
         <v>74.76772784887457</v>
@@ -40919,7 +40919,7 @@
         <v>39.5845017315855</v>
       </c>
       <c r="I57" t="n">
-        <v>-4.840889679246652</v>
+        <v>-4.840900868211085</v>
       </c>
       <c r="J57" t="n">
         <v>61.69810163036917</v>
@@ -41009,7 +41009,7 @@
         <v>-5.322962953904497</v>
       </c>
       <c r="G60" t="n">
-        <v>10.34373456670381</v>
+        <v>10.34374613676048</v>
       </c>
       <c r="H60" t="n">
         <v>49.51856946354882</v>
@@ -41073,7 +41073,7 @@
         <v>-6.987674070479477</v>
       </c>
       <c r="G62" t="n">
-        <v>8.264582701998147</v>
+        <v>8.264571345614691</v>
       </c>
       <c r="H62" t="n">
         <v>50.16128375966063</v>
@@ -41143,7 +41143,7 @@
         <v>52.6315695544544</v>
       </c>
       <c r="I64" t="n">
-        <v>7.776534256813661</v>
+        <v>7.776546118368888</v>
       </c>
       <c r="J64" t="n">
         <v>82.06088167389984</v>
@@ -41201,13 +41201,13 @@
         <v>-3.191753439454137</v>
       </c>
       <c r="G66" t="n">
-        <v>9.654986894345697</v>
+        <v>9.654975583939551</v>
       </c>
       <c r="H66" t="n">
         <v>69.55524373430775</v>
       </c>
       <c r="I66" t="n">
-        <v>10.17210763952565</v>
+        <v>10.17211991406539</v>
       </c>
       <c r="J66" t="n">
         <v>92.45901366939118</v>
@@ -41233,13 +41233,13 @@
         <v>-5.080884384452744</v>
       </c>
       <c r="G67" t="n">
-        <v>10.82645168908207</v>
+        <v>10.82644025020392</v>
       </c>
       <c r="H67" t="n">
         <v>74.20005719956657</v>
       </c>
       <c r="I67" t="n">
-        <v>10.42936182277174</v>
+        <v>10.42934932447941</v>
       </c>
       <c r="J67" t="n">
         <v>106.4114841006974</v>
@@ -41265,7 +41265,7 @@
         <v>-3.992768548930603</v>
       </c>
       <c r="G68" t="n">
-        <v>9.923286483809047</v>
+        <v>9.923275140520182</v>
       </c>
       <c r="H68" t="n">
         <v>70.46093895677912</v>
@@ -41329,13 +41329,13 @@
         <v>-9.416523672454547</v>
       </c>
       <c r="G70" t="n">
-        <v>8.453231297731101</v>
+        <v>8.453220026352115</v>
       </c>
       <c r="H70" t="n">
         <v>60.65876474493577</v>
       </c>
       <c r="I70" t="n">
-        <v>8.995201822292632</v>
+        <v>8.995189531381032</v>
       </c>
       <c r="J70" t="n">
         <v>112.1040256239442</v>
@@ -41361,13 +41361,13 @@
         <v>-11.76738888704267</v>
       </c>
       <c r="G71" t="n">
-        <v>7.132610410294027</v>
+        <v>7.132621466067346</v>
       </c>
       <c r="H71" t="n">
         <v>51.19813928486645</v>
       </c>
       <c r="I71" t="n">
-        <v>10.13100675342484</v>
+        <v>10.13101918945343</v>
       </c>
       <c r="J71" t="n">
         <v>111.2230221092348</v>
@@ -41399,7 +41399,7 @@
         <v>52.95796817224014</v>
       </c>
       <c r="I72" t="n">
-        <v>6.870435006199105</v>
+        <v>6.87044683550917</v>
       </c>
       <c r="J72" t="n">
         <v>121.2440312078746</v>
@@ -41463,7 +41463,7 @@
         <v>37.45292871774588</v>
       </c>
       <c r="I74" t="n">
-        <v>4.406859319154965</v>
+        <v>4.406870864909274</v>
       </c>
       <c r="J74" t="n">
         <v>103.5775775390632</v>
@@ -41591,7 +41591,7 @@
         <v>37.16040451905292</v>
       </c>
       <c r="I78" t="n">
-        <v>-5.636500384992004</v>
+        <v>-5.63649022866074</v>
       </c>
       <c r="J78" t="n">
         <v>92.88792469130138</v>
@@ -41617,7 +41617,7 @@
         <v>-12.50287972254698</v>
       </c>
       <c r="G79" t="n">
-        <v>0.7784549005666275</v>
+        <v>0.7784651311901092</v>
       </c>
       <c r="H79" t="n">
         <v>33.92029467705142</v>
@@ -41687,7 +41687,7 @@
         <v>44.05244047508194</v>
       </c>
       <c r="I81" t="n">
-        <v>-11.30205514714874</v>
+        <v>-11.30203660674795</v>
       </c>
       <c r="J81" t="n">
         <v>86.99152692711512</v>
@@ -41783,7 +41783,7 @@
         <v>59.40775106485634</v>
       </c>
       <c r="I84" t="n">
-        <v>-12.47748654563742</v>
+        <v>-12.47747784038312</v>
       </c>
       <c r="J84" t="n">
         <v>99.06541697895044</v>
@@ -41815,7 +41815,7 @@
         <v>65.04654719786612</v>
       </c>
       <c r="I85" t="n">
-        <v>-15.66179518724001</v>
+        <v>-15.66178711285019</v>
       </c>
       <c r="J85" t="n">
         <v>97.04844951046681</v>
@@ -41841,7 +41841,7 @@
         <v>-17.14285992776975</v>
       </c>
       <c r="G86" t="n">
-        <v>-2.846756003970619</v>
+        <v>-2.846746645443798</v>
       </c>
       <c r="H86" t="n">
         <v>67.13286132918634</v>
@@ -41873,7 +41873,7 @@
         <v>-18.06414822509883</v>
       </c>
       <c r="G87" t="n">
-        <v>-2.608850082361591</v>
+        <v>-2.608840748224917</v>
       </c>
       <c r="H87" t="n">
         <v>62.23634673800827</v>
@@ -41911,7 +41911,7 @@
         <v>55.75244209203252</v>
       </c>
       <c r="I88" t="n">
-        <v>-20.06895592590158</v>
+        <v>-20.06894868868467</v>
       </c>
       <c r="J88" t="n">
         <v>92.52211321734347</v>
@@ -41943,7 +41943,7 @@
         <v>62.23793649992655</v>
       </c>
       <c r="I89" t="n">
-        <v>-15.49711696089192</v>
+        <v>-15.4971246985837</v>
       </c>
       <c r="J89" t="n">
         <v>94.18344870303281</v>
@@ -41975,7 +41975,7 @@
         <v>44.01810748398501</v>
       </c>
       <c r="I90" t="n">
-        <v>-16.88543627572069</v>
+        <v>-16.88544388826343</v>
       </c>
       <c r="J90" t="n">
         <v>81.88842255714064</v>
@@ -42007,7 +42007,7 @@
         <v>35.52879303916819</v>
       </c>
       <c r="I91" t="n">
-        <v>-23.03242255709873</v>
+        <v>-23.03242925559732</v>
       </c>
       <c r="J91" t="n">
         <v>68.10019640513771</v>
@@ -42039,7 +42039,7 @@
         <v>40.49050165131725</v>
       </c>
       <c r="I92" t="n">
-        <v>-26.51241816241978</v>
+        <v>-26.51242457432378</v>
       </c>
       <c r="J92" t="n">
         <v>61.74273412961313</v>
@@ -42065,13 +42065,13 @@
         <v>-33.28873780551388</v>
       </c>
       <c r="G93" t="n">
-        <v>-3.684597695080793</v>
+        <v>-3.684588482805928</v>
       </c>
       <c r="H93" t="n">
         <v>29.00301913394756</v>
       </c>
       <c r="I93" t="n">
-        <v>-29.45169627069456</v>
+        <v>-29.45170256490599</v>
       </c>
       <c r="J93" t="n">
         <v>42.69748628362795</v>
@@ -42097,13 +42097,13 @@
         <v>-31.92243919478229</v>
       </c>
       <c r="G94" t="n">
-        <v>-4.264771301566395</v>
+        <v>-4.264780411272239</v>
       </c>
       <c r="H94" t="n">
         <v>18.74325570428619</v>
       </c>
       <c r="I94" t="n">
-        <v>-28.00679894982006</v>
+        <v>-28.0068053081651</v>
       </c>
       <c r="J94" t="n">
         <v>27.89474196050972</v>
@@ -42135,7 +42135,7 @@
         <v>19.81707264392938</v>
       </c>
       <c r="I95" t="n">
-        <v>-26.00453059995175</v>
+        <v>-26.00453725848516</v>
       </c>
       <c r="J95" t="n">
         <v>24.96815972988056</v>
@@ -42167,7 +42167,7 @@
         <v>15.89211111741442</v>
       </c>
       <c r="I96" t="n">
-        <v>-23.5712605330649</v>
+        <v>-23.57126754833715</v>
       </c>
       <c r="J96" t="n">
         <v>28.54914740621408</v>
@@ -42199,7 +42199,7 @@
         <v>20.58264671468648</v>
       </c>
       <c r="I97" t="n">
-        <v>-25.00400219946962</v>
+        <v>-25.00399542027211</v>
       </c>
       <c r="J97" t="n">
         <v>34.37700446807093</v>
@@ -42225,7 +42225,7 @@
         <v>-52.13567772568902</v>
       </c>
       <c r="G98" t="n">
-        <v>-1.144817070470294</v>
+        <v>-1.144826287332867</v>
       </c>
       <c r="H98" t="n">
         <v>18.31965290286819</v>
@@ -42257,7 +42257,7 @@
         <v>-57.77777609465646</v>
       </c>
       <c r="G99" t="n">
-        <v>-6.020826234045174</v>
+        <v>-6.02081769635009</v>
       </c>
       <c r="H99" t="n">
         <v>15.27719667733658</v>
@@ -42295,7 +42295,7 @@
         <v>15.07653487454037</v>
       </c>
       <c r="I100" t="n">
-        <v>-33.89041151541271</v>
+        <v>-33.8904169084052</v>
       </c>
       <c r="J100" t="n">
         <v>27.6699069578042</v>
@@ -42327,7 +42327,7 @@
         <v>17.94541203322633</v>
       </c>
       <c r="I101" t="n">
-        <v>-31.17110158740718</v>
+        <v>-31.17109576206706</v>
       </c>
       <c r="J101" t="n">
         <v>28.66883782396286</v>
@@ -42391,7 +42391,7 @@
         <v>14.88724822383976</v>
       </c>
       <c r="I103" t="n">
-        <v>-32.84210154978727</v>
+        <v>-32.84210745784308</v>
       </c>
       <c r="J103" t="n">
         <v>22.98156990062044</v>
@@ -42423,7 +42423,7 @@
         <v>9.913208228453851</v>
       </c>
       <c r="I104" t="n">
-        <v>-35.85257273941228</v>
+        <v>-35.85256724208779</v>
       </c>
       <c r="J104" t="n">
         <v>23.86554108948267</v>
@@ -42513,7 +42513,7 @@
         <v>-56.24584747712591</v>
       </c>
       <c r="G107" t="n">
-        <v>-5.542282911524943</v>
+        <v>-5.542274228029543</v>
       </c>
       <c r="H107" t="n">
         <v>17.43205870243658</v>
@@ -42545,7 +42545,7 @@
         <v>-56.18415731425067</v>
       </c>
       <c r="G108" t="n">
-        <v>-6.221599035747061</v>
+        <v>-6.221607598175138</v>
       </c>
       <c r="H108" t="n">
         <v>14.44831874727788</v>
@@ -42615,7 +42615,7 @@
         <v>6.024615316080983</v>
       </c>
       <c r="I110" t="n">
-        <v>-31.27061650294681</v>
+        <v>-31.27061043654561</v>
       </c>
       <c r="J110" t="n">
         <v>33.22203842896631</v>
@@ -42641,7 +42641,7 @@
         <v>-54.47863391321948</v>
       </c>
       <c r="G111" t="n">
-        <v>-10.09983412216593</v>
+        <v>-10.09984190731003</v>
       </c>
       <c r="H111" t="n">
         <v>10.12767521636539</v>
@@ -42679,7 +42679,7 @@
         <v>21.10418192715375</v>
       </c>
       <c r="I112" t="n">
-        <v>-30.21470313468972</v>
+        <v>-30.21470932593397</v>
       </c>
       <c r="J112" t="n">
         <v>46.17241168844289</v>
@@ -42775,7 +42775,7 @@
         <v>24.44754770776356</v>
       </c>
       <c r="I115" t="n">
-        <v>-34.41802113893922</v>
+        <v>-34.41802693935152</v>
       </c>
       <c r="J115" t="n">
         <v>50.05758655445842</v>
@@ -42839,7 +42839,7 @@
         <v>24.94730195367547</v>
       </c>
       <c r="I117" t="n">
-        <v>-36.19966175250494</v>
+        <v>-36.19966728478108</v>
       </c>
       <c r="J117" t="n">
         <v>38.56393145516608</v>
@@ -42865,13 +42865,13 @@
         <v>-56.78818610596754</v>
       </c>
       <c r="G118" t="n">
-        <v>-16.38669786568314</v>
+        <v>-16.38670493724648</v>
       </c>
       <c r="H118" t="n">
         <v>17.44131168849032</v>
       </c>
       <c r="I118" t="n">
-        <v>-36.78223083173312</v>
+        <v>-36.78223647824987</v>
       </c>
       <c r="J118" t="n">
         <v>35.52727439186789</v>
@@ -42897,7 +42897,7 @@
         <v>-56.31058995863971</v>
       </c>
       <c r="G119" t="n">
-        <v>-15.37457327751788</v>
+        <v>-15.37456607895809</v>
       </c>
       <c r="H119" t="n">
         <v>20.81582502027968</v>
@@ -42929,13 +42929,13 @@
         <v>-56.69829342607511</v>
       </c>
       <c r="G120" t="n">
-        <v>-16.07677724263259</v>
+        <v>-16.07678431933383</v>
       </c>
       <c r="H120" t="n">
         <v>18.29646125327557</v>
       </c>
       <c r="I120" t="n">
-        <v>-38.547559258854</v>
+        <v>-38.54755360836089</v>
       </c>
       <c r="J120" t="n">
         <v>41.19001864296059</v>
@@ -42961,7 +42961,7 @@
         <v>-57.14155223271617</v>
       </c>
       <c r="G121" t="n">
-        <v>-16.85995198161126</v>
+        <v>-16.85995891525053</v>
       </c>
       <c r="H121" t="n">
         <v>11.82631761961019</v>
@@ -42999,7 +42999,7 @@
         <v>10.24109211646398</v>
       </c>
       <c r="I122" t="n">
-        <v>-41.40768277612826</v>
+        <v>-41.40768769062964</v>
       </c>
       <c r="J122" t="n">
         <v>42.65420503705462</v>
@@ -43031,7 +43031,7 @@
         <v>12.00888037813888</v>
       </c>
       <c r="I123" t="n">
-        <v>-42.35447034363565</v>
+        <v>-42.35447517905221</v>
       </c>
       <c r="J123" t="n">
         <v>43.89312849283209</v>
@@ -43057,13 +43057,13 @@
         <v>-61.61153711978648</v>
       </c>
       <c r="G124" t="n">
-        <v>-17.3221006429568</v>
+        <v>-17.32209371336002</v>
       </c>
       <c r="H124" t="n">
         <v>-0.8441437102060356</v>
       </c>
       <c r="I124" t="n">
-        <v>-42.70334575751823</v>
+        <v>-42.70334090588286</v>
       </c>
       <c r="J124" t="n">
         <v>36.54915842401909</v>
@@ -43089,7 +43089,7 @@
         <v>-62.04201834542411</v>
       </c>
       <c r="G125" t="n">
-        <v>-17.87451582243691</v>
+        <v>-17.87450892521957</v>
       </c>
       <c r="H125" t="n">
         <v>-0.9950223577321893</v>
@@ -43191,7 +43191,7 @@
         <v>-9.592997010479355</v>
       </c>
       <c r="I128" t="n">
-        <v>-49.59649089539933</v>
+        <v>-49.59648679341039</v>
       </c>
       <c r="J128" t="n">
         <v>28.59374093124656</v>
@@ -43223,7 +43223,7 @@
         <v>-9.914680971138623</v>
       </c>
       <c r="I129" t="n">
-        <v>-47.76542283989256</v>
+        <v>-47.76541850357405</v>
       </c>
       <c r="J129" t="n">
         <v>31.00990824180074</v>
@@ -43255,7 +43255,7 @@
         <v>-0.430739938833391</v>
       </c>
       <c r="I130" t="n">
-        <v>-44.80371006780727</v>
+        <v>-44.80370541333249</v>
       </c>
       <c r="J130" t="n">
         <v>40.60852082673853</v>
@@ -43281,7 +43281,7 @@
         <v>-60.87921861989671</v>
       </c>
       <c r="G131" t="n">
-        <v>-16.61965301788414</v>
+        <v>-16.61964594119378</v>
       </c>
       <c r="H131" t="n">
         <v>11.20226017119483</v>
@@ -43313,7 +43313,7 @@
         <v>-57.52336377295379</v>
       </c>
       <c r="G132" t="n">
-        <v>-14.15377152255236</v>
+        <v>-14.15376426238819</v>
       </c>
       <c r="H132" t="n">
         <v>8.352201320420626</v>
@@ -43345,7 +43345,7 @@
         <v>-56.86676433086298</v>
       </c>
       <c r="G133" t="n">
-        <v>-16.72258588643216</v>
+        <v>-16.72257899137246</v>
       </c>
       <c r="H133" t="n">
         <v>2.898096851378784</v>
@@ -43415,7 +43415,7 @@
         <v>-2.809878783828057</v>
       </c>
       <c r="I135" t="n">
-        <v>-44.35211986444345</v>
+        <v>-44.35211507824253</v>
       </c>
       <c r="J135" t="n">
         <v>45.94360305036773</v>
@@ -43473,13 +43473,13 @@
         <v>-56.62921337306769</v>
       </c>
       <c r="G137" t="n">
-        <v>-15.94877718164233</v>
+        <v>-15.94877016040107</v>
       </c>
       <c r="H137" t="n">
         <v>-0.8227812344208774</v>
       </c>
       <c r="I137" t="n">
-        <v>-43.53504135301615</v>
+        <v>-43.53504640515198</v>
       </c>
       <c r="J137" t="n">
         <v>46.43016219484324</v>
@@ -43505,7 +43505,7 @@
         <v>-55.96958453493185</v>
       </c>
       <c r="G138" t="n">
-        <v>-15.24242350981521</v>
+        <v>-15.24241637006719</v>
       </c>
       <c r="H138" t="n">
         <v>-1.909228316656353</v>
@@ -43607,7 +43607,7 @@
         <v>11.78529754959159</v>
       </c>
       <c r="I141" t="n">
-        <v>-32.26879864064875</v>
+        <v>-32.26880534741482</v>
       </c>
       <c r="J141" t="n">
         <v>79.66746349443316</v>
@@ -43671,7 +43671,7 @@
         <v>-7.09122645551531</v>
       </c>
       <c r="I143" t="n">
-        <v>-32.10434891982889</v>
+        <v>-32.10435572998518</v>
       </c>
       <c r="J143" t="n">
         <v>60.56033954750786</v>
@@ -43735,7 +43735,7 @@
         <v>2.334533491450208</v>
       </c>
       <c r="I145" t="n">
-        <v>-33.51296794739835</v>
+        <v>-33.51296118514819</v>
       </c>
       <c r="J145" t="n">
         <v>79.7908029562787</v>
@@ -43761,13 +43761,13 @@
         <v>-50.13210990744989</v>
       </c>
       <c r="G146" t="n">
-        <v>-11.82289657347413</v>
+        <v>-11.82290408126045</v>
       </c>
       <c r="H146" t="n">
         <v>-4.631267327895838</v>
       </c>
       <c r="I146" t="n">
-        <v>-34.63594768313144</v>
+        <v>-34.63595419177665</v>
       </c>
       <c r="J146" t="n">
         <v>71.57684970564392</v>
@@ -43793,13 +43793,13 @@
         <v>-50.80962983163329</v>
       </c>
       <c r="G147" t="n">
-        <v>-13.6199541228318</v>
+        <v>-13.61996145713659</v>
       </c>
       <c r="H147" t="n">
         <v>-8.328828410010559</v>
       </c>
       <c r="I147" t="n">
-        <v>-34.47114939719585</v>
+        <v>-34.47114291863736</v>
       </c>
       <c r="J147" t="n">
         <v>59.65780569033912</v>
@@ -43831,7 +43831,7 @@
         <v>-6.028498086992817</v>
       </c>
       <c r="I148" t="n">
-        <v>-34.28805565881679</v>
+        <v>-34.28804916033518</v>
       </c>
       <c r="J148" t="n">
         <v>53.29710430619193</v>
@@ -43863,7 +43863,7 @@
         <v>-1.760633823603719</v>
       </c>
       <c r="I149" t="n">
-        <v>-34.87421557689749</v>
+        <v>-34.87420925337283</v>
       </c>
       <c r="J149" t="n">
         <v>56.09403415140542</v>
@@ -43895,7 +43895,7 @@
         <v>-7.602880670023849</v>
       </c>
       <c r="I150" t="n">
-        <v>-37.4569708671581</v>
+        <v>-37.45697692204924</v>
       </c>
       <c r="J150" t="n">
         <v>46.37167601458793</v>
@@ -43927,7 +43927,7 @@
         <v>-10.10608394316426</v>
       </c>
       <c r="I151" t="n">
-        <v>-43.26666186836514</v>
+        <v>-43.26666717142301</v>
       </c>
       <c r="J151" t="n">
         <v>35.01730440420005</v>
@@ -43953,7 +43953,7 @@
         <v>-53.60400625525475</v>
       </c>
       <c r="G152" t="n">
-        <v>-20.22512724173225</v>
+        <v>-20.22513386978178</v>
       </c>
       <c r="H152" t="n">
         <v>-15.33815857894649</v>
@@ -43991,7 +43991,7 @@
         <v>-16.46675455896869</v>
       </c>
       <c r="I153" t="n">
-        <v>-41.94472969593319</v>
+        <v>-41.94473500657481</v>
       </c>
       <c r="J153" t="n">
         <v>22.64151237635372</v>
@@ -44023,7 +44023,7 @@
         <v>-15.20339189949682</v>
       </c>
       <c r="I154" t="n">
-        <v>-40.56723259305854</v>
+        <v>-40.56723806517864</v>
       </c>
       <c r="J154" t="n">
         <v>20.02998683900788</v>
@@ -44049,7 +44049,7 @@
         <v>-51.83269228782829</v>
       </c>
       <c r="G155" t="n">
-        <v>-14.77919367032432</v>
+        <v>-14.77920088105071</v>
       </c>
       <c r="H155" t="n">
         <v>-14.68718460786851</v>
@@ -44087,7 +44087,7 @@
         <v>-11.96105995313918</v>
       </c>
       <c r="I156" t="n">
-        <v>-35.97285437285689</v>
+        <v>-35.97284836459775</v>
       </c>
       <c r="J156" t="n">
         <v>34.93548977759578</v>
@@ -44113,7 +44113,7 @@
         <v>-49.81553837768958</v>
       </c>
       <c r="G157" t="n">
-        <v>-12.62762558715662</v>
+        <v>-12.62763296200138</v>
       </c>
       <c r="H157" t="n">
         <v>-7.803167735336114</v>
@@ -44145,13 +44145,13 @@
         <v>-49.31460605578476</v>
       </c>
       <c r="G158" t="n">
-        <v>-12.14389741566937</v>
+        <v>-12.14389007981044</v>
       </c>
       <c r="H158" t="n">
         <v>19.17837993230622</v>
       </c>
       <c r="I158" t="n">
-        <v>-31.90961813240691</v>
+        <v>-31.90961164374077</v>
       </c>
       <c r="J158" t="n">
         <v>55.97883818585918</v>
@@ -44215,7 +44215,7 @@
         <v>33.15829160473547</v>
       </c>
       <c r="I160" t="n">
-        <v>-29.84939278684298</v>
+        <v>-29.84938585107336</v>
       </c>
       <c r="J160" t="n">
         <v>67.10172765520876</v>
@@ -44247,7 +44247,7 @@
         <v>38.5684914172453</v>
       </c>
       <c r="I161" t="n">
-        <v>-29.74189607402291</v>
+        <v>-29.7419029828034</v>
       </c>
       <c r="J161" t="n">
         <v>62.23034118107906</v>
@@ -44279,7 +44279,7 @@
         <v>31.94658342227763</v>
       </c>
       <c r="I162" t="n">
-        <v>-31.7316658087051</v>
+        <v>-31.73167254623591</v>
       </c>
       <c r="J162" t="n">
         <v>44.11149655354738</v>
@@ -44305,13 +44305,13 @@
         <v>-50.39954164408403</v>
       </c>
       <c r="G163" t="n">
-        <v>-6.576258128209467</v>
+        <v>-6.576265979101093</v>
       </c>
       <c r="H163" t="n">
         <v>35.25827976252069</v>
       </c>
       <c r="I163" t="n">
-        <v>-30.9723612810538</v>
+        <v>-30.97237478082654</v>
       </c>
       <c r="J163" t="n">
         <v>47.45098657865709</v>
@@ -44433,13 +44433,13 @@
         <v>-53.46630744214328</v>
       </c>
       <c r="G167" t="n">
-        <v>-1.631329128250458</v>
+        <v>-1.631337452160353</v>
       </c>
       <c r="H167" t="n">
         <v>33.09109889422288</v>
       </c>
       <c r="I167" t="n">
-        <v>-32.89463592347094</v>
+        <v>-32.89464226978117</v>
       </c>
       <c r="J167" t="n">
         <v>48.14546064897016</v>
@@ -44465,7 +44465,7 @@
         <v>-53.21192041547695</v>
       </c>
       <c r="G168" t="n">
-        <v>-1.846922769230852</v>
+        <v>-1.846931117352801</v>
       </c>
       <c r="H168" t="n">
         <v>23.80828374026902</v>
@@ -44497,7 +44497,7 @@
         <v>-52.13521178339568</v>
       </c>
       <c r="G169" t="n">
-        <v>-3.703223035058201</v>
+        <v>-3.703214914559028</v>
       </c>
       <c r="H169" t="n">
         <v>29.44025621625235</v>
@@ -44535,7 +44535,7 @@
         <v>31.30973250029547</v>
       </c>
       <c r="I170" t="n">
-        <v>-37.60951737835894</v>
+        <v>-37.60952319348129</v>
       </c>
       <c r="J170" t="n">
         <v>40.14651791489481</v>
@@ -44567,7 +44567,7 @@
         <v>33.71331443951104</v>
       </c>
       <c r="I171" t="n">
-        <v>-37.94833755661033</v>
+        <v>-37.94833171441556</v>
       </c>
       <c r="J171" t="n">
         <v>43.41373072994053</v>
@@ -44593,13 +44593,13 @@
         <v>-45.99760763325964</v>
       </c>
       <c r="G172" t="n">
-        <v>0.5143291941176686</v>
+        <v>0.5143378536584198</v>
       </c>
       <c r="H172" t="n">
         <v>44.92055080938697</v>
       </c>
       <c r="I172" t="n">
-        <v>-32.81231725705731</v>
+        <v>-32.8123236456485</v>
       </c>
       <c r="J172" t="n">
         <v>59.58955849005739</v>
@@ -44631,7 +44631,7 @@
         <v>59.14138873392913</v>
       </c>
       <c r="I173" t="n">
-        <v>-31.15039340858322</v>
+        <v>-31.15038678081573</v>
       </c>
       <c r="J173" t="n">
         <v>68.31720572322637</v>
@@ -44657,7 +44657,7 @@
         <v>-41.76249980926514</v>
       </c>
       <c r="G174" t="n">
-        <v>1.980733388627964</v>
+        <v>1.98072439885395</v>
       </c>
       <c r="H174" t="n">
         <v>59.09223654259699</v>
@@ -44689,7 +44689,7 @@
         <v>-42.28287675129394</v>
       </c>
       <c r="G175" t="n">
-        <v>2.861057206861273</v>
+        <v>2.861048248629738</v>
       </c>
       <c r="H175" t="n">
         <v>63.09951008127501</v>
@@ -44753,7 +44753,7 @@
         <v>-38.99999765249399</v>
       </c>
       <c r="G177" t="n">
-        <v>2.71879710441596</v>
+        <v>2.718806120971973</v>
       </c>
       <c r="H177" t="n">
         <v>71.52501088341694</v>
@@ -44817,13 +44817,13 @@
         <v>-41.81931635301061</v>
       </c>
       <c r="G179" t="n">
-        <v>0.9841546105370691</v>
+        <v>0.9841458252099811</v>
       </c>
       <c r="H179" t="n">
         <v>61.06736588618858</v>
       </c>
       <c r="I179" t="n">
-        <v>-24.21511774867416</v>
+        <v>-24.21510239292522</v>
       </c>
       <c r="J179" t="n">
         <v>75.58593786379788</v>
@@ -44849,13 +44849,13 @@
         <v>-39.6770169275888</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.147672528644105</v>
+        <v>-0.1476638184739976</v>
       </c>
       <c r="H180" t="n">
         <v>65.15150572053405</v>
       </c>
       <c r="I180" t="n">
-        <v>-25.31919824707868</v>
+        <v>-25.31920577234636</v>
       </c>
       <c r="J180" t="n">
         <v>72.82946306655833</v>
@@ -44919,7 +44919,7 @@
         <v>72.57494253958269</v>
       </c>
       <c r="I182" t="n">
-        <v>-25.49483107255582</v>
+        <v>-25.49482362062903</v>
       </c>
       <c r="J182" t="n">
         <v>93.80497531351087</v>
@@ -44945,7 +44945,7 @@
         <v>-37.81366289032172</v>
       </c>
       <c r="G183" t="n">
-        <v>-0.6404978015496887</v>
+        <v>-0.6405063489323015</v>
       </c>
       <c r="H183" t="n">
         <v>82.78223213394497</v>
@@ -44977,7 +44977,7 @@
         <v>-35.9392113960985</v>
       </c>
       <c r="G184" t="n">
-        <v>-2.940793371060713</v>
+        <v>-2.940785161752024</v>
       </c>
       <c r="H184" t="n">
         <v>84.22466480357787</v>
@@ -45111,7 +45111,7 @@
         <v>102.5162819144948</v>
       </c>
       <c r="I188" t="n">
-        <v>-23.99993218579317</v>
+        <v>-23.99993985526311</v>
       </c>
       <c r="J188" t="n">
         <v>136.0320544643959</v>
@@ -45175,7 +45175,7 @@
         <v>122.2920398799532</v>
       </c>
       <c r="I190" t="n">
-        <v>-17.22076008243486</v>
+        <v>-17.22076875496595</v>
       </c>
       <c r="J190" t="n">
         <v>146.51820853791</v>
@@ -45207,7 +45207,7 @@
         <v>123.5046433130916</v>
       </c>
       <c r="I191" t="n">
-        <v>-17.95775563916884</v>
+        <v>-17.95774706748667</v>
       </c>
       <c r="J191" t="n">
         <v>151.0794350518636</v>
@@ -45239,7 +45239,7 @@
         <v>125.310248833198</v>
       </c>
       <c r="I192" t="n">
-        <v>-20.91946783988486</v>
+        <v>-20.91945994695765</v>
       </c>
       <c r="J192" t="n">
         <v>150.9514669770176</v>
@@ -45425,7 +45425,7 @@
         <v>-33.52514665157967</v>
       </c>
       <c r="G198" t="n">
-        <v>-1.4153889785956</v>
+        <v>-1.415380617513928</v>
       </c>
       <c r="H198" t="n">
         <v>94.45324890083117</v>
@@ -45489,7 +45489,7 @@
         <v>-37.59362584999582</v>
       </c>
       <c r="G200" t="n">
-        <v>-1.848502833106846</v>
+        <v>-1.848511108739048</v>
       </c>
       <c r="H200" t="n">
         <v>88.43219261331876</v>
@@ -45553,7 +45553,7 @@
         <v>-35.84436900863341</v>
       </c>
       <c r="G202" t="n">
-        <v>-1.301844487537573</v>
+        <v>-1.301836254451327</v>
       </c>
       <c r="H202" t="n">
         <v>78.76605325413581</v>
@@ -45649,7 +45649,7 @@
         <v>-28.65188365140916</v>
       </c>
       <c r="G205" t="n">
-        <v>3.17529077529517</v>
+        <v>3.175299540611221</v>
       </c>
       <c r="H205" t="n">
         <v>94.32029234930152</v>
@@ -45713,7 +45713,7 @@
         <v>-27.18278428929728</v>
       </c>
       <c r="G207" t="n">
-        <v>3.544553467908163</v>
+        <v>3.544544670919225</v>
       </c>
       <c r="H207" t="n">
         <v>96.56910071694344</v>
@@ -45809,7 +45809,7 @@
         <v>-27.03415236602241</v>
       </c>
       <c r="G210" t="n">
-        <v>-2.71167406087387</v>
+        <v>-2.71166638281537</v>
       </c>
       <c r="H210" t="n">
         <v>88.54100235891897</v>
@@ -45969,7 +45969,7 @@
         <v>-35.00641823830535</v>
       </c>
       <c r="G215" t="n">
-        <v>-4.171889360138847</v>
+        <v>-4.17189681239063</v>
       </c>
       <c r="H215" t="n">
         <v>86.87857539273911</v>
@@ -46033,7 +46033,7 @@
         <v>-33.86392905643432</v>
       </c>
       <c r="G217" t="n">
-        <v>-6.385026828532547</v>
+        <v>-6.385019555942673</v>
       </c>
       <c r="H217" t="n">
         <v>98.08728775531479</v>
@@ -46225,7 +46225,7 @@
         <v>-26.85507940336083</v>
       </c>
       <c r="G223" t="n">
-        <v>-10.65625261812432</v>
+        <v>-10.6562456616022</v>
       </c>
       <c r="H223" t="n">
         <v>100.0265892515791</v>
@@ -46449,7 +46449,7 @@
         <v>-40.67977613483576</v>
       </c>
       <c r="G230" t="n">
-        <v>-8.235095143331449</v>
+        <v>-8.235102601298294</v>
       </c>
       <c r="H230" t="n">
         <v>64.56839752173443</v>
@@ -46513,7 +46513,7 @@
         <v>-39.58248098284007</v>
       </c>
       <c r="G232" t="n">
-        <v>-5.920884290780492</v>
+        <v>-5.920876570197042</v>
       </c>
       <c r="H232" t="n">
         <v>42.95023242456983</v>
@@ -46577,7 +46577,7 @@
         <v>-38.63636103394656</v>
       </c>
       <c r="G234" t="n">
-        <v>-6.789576929754382</v>
+        <v>-6.789584610169408</v>
       </c>
       <c r="H234" t="n">
         <v>36.77451609649452</v>
@@ -46769,7 +46769,7 @@
         <v>-41.94381402432754</v>
       </c>
       <c r="G240" t="n">
-        <v>-5.24821227749892</v>
+        <v>-5.248220291782069</v>
       </c>
       <c r="H240" t="n">
         <v>14.92523692770091</v>
@@ -46833,7 +46833,7 @@
         <v>-38.30580451011441</v>
       </c>
       <c r="G242" t="n">
-        <v>-2.136970167875163</v>
+        <v>-2.136961897373224</v>
       </c>
       <c r="H242" t="n">
         <v>24.7957124658932</v>
@@ -46865,7 +46865,7 @@
         <v>-39.34322726834358</v>
       </c>
       <c r="G243" t="n">
-        <v>-3.703271274079567</v>
+        <v>-3.703263225960984</v>
       </c>
       <c r="H243" t="n">
         <v>32.40354383046355</v>

--- a/dashboards/Reliance Group.xlsx
+++ b/dashboards/Reliance Group.xlsx
@@ -522,13 +522,13 @@
         <v>90.40000152587891</v>
       </c>
       <c r="G3" t="n">
-        <v>1113.317504882812</v>
+        <v>1113.3173828125</v>
       </c>
       <c r="H3" t="n">
         <v>97.5</v>
       </c>
       <c r="I3" t="n">
-        <v>857.11083984375</v>
+        <v>857.1109008789062</v>
       </c>
       <c r="J3" t="n">
         <v>13.89999961853027</v>
@@ -557,7 +557,7 @@
         <v>97.05000305175781</v>
       </c>
       <c r="I4" t="n">
-        <v>844.1920776367188</v>
+        <v>844.1919555664062</v>
       </c>
       <c r="J4" t="n">
         <v>13.85000038146973</v>
@@ -580,7 +580,7 @@
         <v>89.90000152587891</v>
       </c>
       <c r="G5" t="n">
-        <v>1094.47607421875</v>
+        <v>1094.476196289062</v>
       </c>
       <c r="H5" t="n">
         <v>100.1500015258789</v>
@@ -609,13 +609,13 @@
         <v>91</v>
       </c>
       <c r="G6" t="n">
-        <v>1103.307983398438</v>
+        <v>1103.30810546875</v>
       </c>
       <c r="H6" t="n">
         <v>98.55000305175781</v>
       </c>
       <c r="I6" t="n">
-        <v>844.0447387695312</v>
+        <v>844.044677734375</v>
       </c>
       <c r="J6" t="n">
         <v>14.14999961853027</v>
@@ -673,7 +673,7 @@
         <v>98.40000152587891</v>
       </c>
       <c r="I8" t="n">
-        <v>968.8118896484375</v>
+        <v>968.811767578125</v>
       </c>
       <c r="J8" t="n">
         <v>14.30000019073486</v>
@@ -725,7 +725,7 @@
         <v>90.09999847412109</v>
       </c>
       <c r="G10" t="n">
-        <v>1148.282836914062</v>
+        <v>1148.28271484375</v>
       </c>
       <c r="H10" t="n">
         <v>99.05000305175781</v>
@@ -754,7 +754,7 @@
         <v>89.59999847412109</v>
       </c>
       <c r="G11" t="n">
-        <v>1149.958740234375</v>
+        <v>1149.958618164062</v>
       </c>
       <c r="H11" t="n">
         <v>102.75</v>
@@ -789,7 +789,7 @@
         <v>105.5500030517578</v>
       </c>
       <c r="I12" t="n">
-        <v>934.6727905273438</v>
+        <v>934.6727294921875</v>
       </c>
       <c r="J12" t="n">
         <v>15.64999961853027</v>
@@ -812,7 +812,7 @@
         <v>89.80000305175781</v>
       </c>
       <c r="G13" t="n">
-        <v>1142.168334960938</v>
+        <v>1142.16845703125</v>
       </c>
       <c r="H13" t="n">
         <v>101.9499969482422</v>
@@ -847,7 +847,7 @@
         <v>99.75</v>
       </c>
       <c r="I14" t="n">
-        <v>957.71044921875</v>
+        <v>957.7103881835938</v>
       </c>
       <c r="J14" t="n">
         <v>15.85000038146973</v>
@@ -899,13 +899,13 @@
         <v>86.40000152587891</v>
       </c>
       <c r="G16" t="n">
-        <v>1122.262573242188</v>
+        <v>1122.262817382812</v>
       </c>
       <c r="H16" t="n">
         <v>98.25</v>
       </c>
       <c r="I16" t="n">
-        <v>898.8635864257812</v>
+        <v>898.8636474609375</v>
       </c>
       <c r="J16" t="n">
         <v>16.04999923706055</v>
@@ -957,7 +957,7 @@
         <v>78</v>
       </c>
       <c r="G18" t="n">
-        <v>1074.887451171875</v>
+        <v>1074.887573242188</v>
       </c>
       <c r="H18" t="n">
         <v>98.05000305175781</v>
@@ -992,7 +992,7 @@
         <v>97.80000305175781</v>
       </c>
       <c r="I19" t="n">
-        <v>855.3916015625</v>
+        <v>855.3916625976562</v>
       </c>
       <c r="J19" t="n">
         <v>14.80000019073486</v>
@@ -1044,13 +1044,13 @@
         <v>82</v>
       </c>
       <c r="G21" t="n">
-        <v>1080.933959960938</v>
+        <v>1080.933837890625</v>
       </c>
       <c r="H21" t="n">
         <v>101.0500030517578</v>
       </c>
       <c r="I21" t="n">
-        <v>864.5280151367188</v>
+        <v>864.5281372070312</v>
       </c>
       <c r="J21" t="n">
         <v>14.80000019073486</v>
@@ -1102,7 +1102,7 @@
         <v>85.90000152587891</v>
       </c>
       <c r="G23" t="n">
-        <v>1079.552368164062</v>
+        <v>1079.552490234375</v>
       </c>
       <c r="H23" t="n">
         <v>110.0999984741211</v>
@@ -1160,13 +1160,13 @@
         <v>85.44999694824219</v>
       </c>
       <c r="G25" t="n">
-        <v>1055.887451171875</v>
+        <v>1055.887329101562</v>
       </c>
       <c r="H25" t="n">
         <v>121.3499984741211</v>
       </c>
       <c r="I25" t="n">
-        <v>898.3723754882812</v>
+        <v>898.3724365234375</v>
       </c>
       <c r="J25" t="n">
         <v>17.64999961853027</v>
@@ -1195,7 +1195,7 @@
         <v>133.4499969482422</v>
       </c>
       <c r="I26" t="n">
-        <v>874.7943725585938</v>
+        <v>874.79443359375</v>
       </c>
       <c r="J26" t="n">
         <v>18.5</v>
@@ -1218,7 +1218,7 @@
         <v>83.59999847412109</v>
       </c>
       <c r="G27" t="n">
-        <v>1067.09716796875</v>
+        <v>1067.097290039062</v>
       </c>
       <c r="H27" t="n">
         <v>134.4499969482422</v>
@@ -1247,7 +1247,7 @@
         <v>87.75</v>
       </c>
       <c r="G28" t="n">
-        <v>1079.529907226562</v>
+        <v>1079.52978515625</v>
       </c>
       <c r="H28" t="n">
         <v>147.8500061035156</v>
@@ -1276,13 +1276,13 @@
         <v>92.09999847412109</v>
       </c>
       <c r="G29" t="n">
-        <v>1078.420288085938</v>
+        <v>1078.420166015625</v>
       </c>
       <c r="H29" t="n">
         <v>133.1000061035156</v>
       </c>
       <c r="I29" t="n">
-        <v>879.510009765625</v>
+        <v>879.5099487304688</v>
       </c>
       <c r="J29" t="n">
         <v>16.14999961853027</v>
@@ -1305,13 +1305,13 @@
         <v>91.44999694824219</v>
       </c>
       <c r="G30" t="n">
-        <v>1076.314086914062</v>
+        <v>1076.314208984375</v>
       </c>
       <c r="H30" t="n">
         <v>134</v>
       </c>
       <c r="I30" t="n">
-        <v>853.6724243164062</v>
+        <v>853.67236328125</v>
       </c>
       <c r="J30" t="n">
         <v>15.94999980926514</v>
@@ -1334,13 +1334,13 @@
         <v>86.90000152587891</v>
       </c>
       <c r="G31" t="n">
-        <v>1059.171264648438</v>
+        <v>1059.171142578125</v>
       </c>
       <c r="H31" t="n">
         <v>120.5999984741211</v>
       </c>
       <c r="I31" t="n">
-        <v>771.345703125</v>
+        <v>771.3457641601562</v>
       </c>
       <c r="J31" t="n">
         <v>15.19999980926514</v>
@@ -1363,13 +1363,13 @@
         <v>87.05000305175781</v>
       </c>
       <c r="G32" t="n">
-        <v>1095.1328125</v>
+        <v>1095.132934570312</v>
       </c>
       <c r="H32" t="n">
         <v>111.8499984741211</v>
       </c>
       <c r="I32" t="n">
-        <v>784.4610595703125</v>
+        <v>784.4609985351562</v>
       </c>
       <c r="J32" t="n">
         <v>14.55000019073486</v>
@@ -1392,13 +1392,13 @@
         <v>86.69999694824219</v>
       </c>
       <c r="G33" t="n">
-        <v>1092.868408203125</v>
+        <v>1092.868286132812</v>
       </c>
       <c r="H33" t="n">
         <v>122.5999984741211</v>
       </c>
       <c r="I33" t="n">
-        <v>794.4324951171875</v>
+        <v>794.4325561523438</v>
       </c>
       <c r="J33" t="n">
         <v>14.80000019073486</v>
@@ -1566,7 +1566,7 @@
         <v>74.75</v>
       </c>
       <c r="G39" t="n">
-        <v>1021.66943359375</v>
+        <v>1021.669555664062</v>
       </c>
       <c r="H39" t="n">
         <v>101.9499969482422</v>
@@ -1601,7 +1601,7 @@
         <v>104.5999984741211</v>
       </c>
       <c r="I40" t="n">
-        <v>681.9456787109375</v>
+        <v>681.9457397460938</v>
       </c>
       <c r="J40" t="n">
         <v>13</v>
@@ -1624,13 +1624,13 @@
         <v>76.94999694824219</v>
       </c>
       <c r="G41" t="n">
-        <v>1068.682495117188</v>
+        <v>1068.682373046875</v>
       </c>
       <c r="H41" t="n">
         <v>104.5999984741211</v>
       </c>
       <c r="I41" t="n">
-        <v>686.1209716796875</v>
+        <v>686.1209106445312</v>
       </c>
       <c r="J41" t="n">
         <v>13.05000019073486</v>
@@ -1659,7 +1659,7 @@
         <v>107.5999984741211</v>
       </c>
       <c r="I42" t="n">
-        <v>692.8504638671875</v>
+        <v>692.8505249023438</v>
       </c>
       <c r="J42" t="n">
         <v>13.14999961853027</v>
@@ -1682,7 +1682,7 @@
         <v>76.75</v>
       </c>
       <c r="G43" t="n">
-        <v>1077.174682617188</v>
+        <v>1077.1748046875</v>
       </c>
       <c r="H43" t="n">
         <v>106.4000015258789</v>
@@ -1711,7 +1711,7 @@
         <v>77.5</v>
       </c>
       <c r="G44" t="n">
-        <v>1053.283325195312</v>
+        <v>1053.283447265625</v>
       </c>
       <c r="H44" t="n">
         <v>103.5</v>
@@ -1769,13 +1769,13 @@
         <v>74.09999847412109</v>
       </c>
       <c r="G46" t="n">
-        <v>1012.497985839844</v>
+        <v>1012.497924804688</v>
       </c>
       <c r="H46" t="n">
         <v>101.75</v>
       </c>
       <c r="I46" t="n">
-        <v>667.5040893554688</v>
+        <v>667.504150390625</v>
       </c>
       <c r="J46" t="n">
         <v>12.80000019073486</v>
@@ -1804,7 +1804,7 @@
         <v>107.5</v>
       </c>
       <c r="I47" t="n">
-        <v>693.8820190429688</v>
+        <v>693.882080078125</v>
       </c>
       <c r="J47" t="n">
         <v>13.35000038146973</v>
@@ -1827,13 +1827,13 @@
         <v>78</v>
       </c>
       <c r="G48" t="n">
-        <v>1083.49267578125</v>
+        <v>1083.492797851562</v>
       </c>
       <c r="H48" t="n">
         <v>111.4000015258789</v>
       </c>
       <c r="I48" t="n">
-        <v>701.8396606445312</v>
+        <v>701.839599609375</v>
       </c>
       <c r="J48" t="n">
         <v>13.55000019073486</v>
@@ -1862,7 +1862,7 @@
         <v>122.5</v>
       </c>
       <c r="I49" t="n">
-        <v>746.5887451171875</v>
+        <v>746.5888061523438</v>
       </c>
       <c r="J49" t="n">
         <v>14.19999980926514</v>
@@ -1891,7 +1891,7 @@
         <v>117.25</v>
       </c>
       <c r="I50" t="n">
-        <v>737.8452758789062</v>
+        <v>737.8451538085938</v>
       </c>
       <c r="J50" t="n">
         <v>13.85000038146973</v>
@@ -1920,7 +1920,7 @@
         <v>115.5500030517578</v>
       </c>
       <c r="I51" t="n">
-        <v>747.3256225585938</v>
+        <v>747.3255615234375</v>
       </c>
       <c r="J51" t="n">
         <v>13.44999980926514</v>
@@ -1972,13 +1972,13 @@
         <v>78.75</v>
       </c>
       <c r="G53" t="n">
-        <v>1124.006469726562</v>
+        <v>1124.006591796875</v>
       </c>
       <c r="H53" t="n">
         <v>116.8000030517578</v>
       </c>
       <c r="I53" t="n">
-        <v>758.770751953125</v>
+        <v>758.7706909179688</v>
       </c>
       <c r="J53" t="n">
         <v>13.75</v>
@@ -2030,7 +2030,7 @@
         <v>83.09999847412109</v>
       </c>
       <c r="G55" t="n">
-        <v>1146.403198242188</v>
+        <v>1146.4033203125</v>
       </c>
       <c r="H55" t="n">
         <v>113.1500015258789</v>
@@ -2059,13 +2059,13 @@
         <v>81.65000152587891</v>
       </c>
       <c r="G56" t="n">
-        <v>1150.049194335938</v>
+        <v>1150.049072265625</v>
       </c>
       <c r="H56" t="n">
         <v>111.8000030517578</v>
       </c>
       <c r="I56" t="n">
-        <v>756.51123046875</v>
+        <v>756.5111694335938</v>
       </c>
       <c r="J56" t="n">
         <v>12.85000038146973</v>
@@ -2088,7 +2088,7 @@
         <v>85.55000305175781</v>
       </c>
       <c r="G57" t="n">
-        <v>1167.916870117188</v>
+        <v>1167.916748046875</v>
       </c>
       <c r="H57" t="n">
         <v>109.6999969482422</v>
@@ -2117,13 +2117,13 @@
         <v>85.59999847412109</v>
       </c>
       <c r="G58" t="n">
-        <v>1175.70703125</v>
+        <v>1175.706909179688</v>
       </c>
       <c r="H58" t="n">
         <v>109.1999969482422</v>
       </c>
       <c r="I58" t="n">
-        <v>755.577880859375</v>
+        <v>755.5779418945312</v>
       </c>
       <c r="J58" t="n">
         <v>13</v>
@@ -2146,7 +2146,7 @@
         <v>87.59999847412109</v>
       </c>
       <c r="G59" t="n">
-        <v>1187.528198242188</v>
+        <v>1187.528076171875</v>
       </c>
       <c r="H59" t="n">
         <v>100.6999969482422</v>
@@ -2210,7 +2210,7 @@
         <v>114.8000030517578</v>
       </c>
       <c r="I61" t="n">
-        <v>769.7738647460938</v>
+        <v>769.7738037109375</v>
       </c>
       <c r="J61" t="n">
         <v>13.55000019073486</v>
@@ -2233,7 +2233,7 @@
         <v>85.15000152587891</v>
       </c>
       <c r="G62" t="n">
-        <v>1193.325439453125</v>
+        <v>1193.325561523438</v>
       </c>
       <c r="H62" t="n">
         <v>112.3000030517578</v>
@@ -2262,13 +2262,13 @@
         <v>87.84999847412109</v>
       </c>
       <c r="G63" t="n">
-        <v>1202.882080078125</v>
+        <v>1202.881958007812</v>
       </c>
       <c r="H63" t="n">
         <v>122.6500015258789</v>
       </c>
       <c r="I63" t="n">
-        <v>790.2572631835938</v>
+        <v>790.2573852539062</v>
       </c>
       <c r="J63" t="n">
         <v>14.14999961853027</v>
@@ -2320,13 +2320,13 @@
         <v>93.05000305175781</v>
       </c>
       <c r="G65" t="n">
-        <v>1189.38525390625</v>
+        <v>1189.385131835938</v>
       </c>
       <c r="H65" t="n">
         <v>132.1499938964844</v>
       </c>
       <c r="I65" t="n">
-        <v>804.3058471679688</v>
+        <v>804.305908203125</v>
       </c>
       <c r="J65" t="n">
         <v>15.55000019073486</v>
@@ -2349,13 +2349,13 @@
         <v>94.5</v>
       </c>
       <c r="G66" t="n">
-        <v>1186.214599609375</v>
+        <v>1186.214721679688</v>
       </c>
       <c r="H66" t="n">
         <v>136.1499938964844</v>
       </c>
       <c r="I66" t="n">
-        <v>822.13671875</v>
+        <v>822.1367797851562</v>
       </c>
       <c r="J66" t="n">
         <v>16.29999923706055</v>
@@ -2378,7 +2378,7 @@
         <v>96.30000305175781</v>
       </c>
       <c r="G67" t="n">
-        <v>1165.289794921875</v>
+        <v>1165.289916992188</v>
       </c>
       <c r="H67" t="n">
         <v>125.1500015258789</v>
@@ -2413,7 +2413,7 @@
         <v>126.75</v>
       </c>
       <c r="I68" t="n">
-        <v>815.8492431640625</v>
+        <v>815.8493041992188</v>
       </c>
       <c r="J68" t="n">
         <v>15.60000038146973</v>
@@ -2436,7 +2436,7 @@
         <v>98.40000152587891</v>
       </c>
       <c r="G69" t="n">
-        <v>1182.20654296875</v>
+        <v>1182.206420898438</v>
       </c>
       <c r="H69" t="n">
         <v>125.8499984741211</v>
@@ -2494,13 +2494,13 @@
         <v>93.80000305175781</v>
       </c>
       <c r="G71" t="n">
-        <v>1155.68798828125</v>
+        <v>1155.687866210938</v>
       </c>
       <c r="H71" t="n">
         <v>123.4000015258789</v>
       </c>
       <c r="I71" t="n">
-        <v>944.153076171875</v>
+        <v>944.1530151367188</v>
       </c>
       <c r="J71" t="n">
         <v>14.85000038146973</v>
@@ -2529,7 +2529,7 @@
         <v>119.5500030517578</v>
       </c>
       <c r="I72" t="n">
-        <v>982.6146850585938</v>
+        <v>982.6148071289062</v>
       </c>
       <c r="J72" t="n">
         <v>14.39999961853027</v>
@@ -2558,7 +2558,7 @@
         <v>123.5999984741211</v>
       </c>
       <c r="I73" t="n">
-        <v>979.8148803710938</v>
+        <v>979.8148193359375</v>
       </c>
       <c r="J73" t="n">
         <v>14.39999961853027</v>
@@ -2581,13 +2581,13 @@
         <v>101.5500030517578</v>
       </c>
       <c r="G74" t="n">
-        <v>1231.234497070312</v>
+        <v>1231.234619140625</v>
       </c>
       <c r="H74" t="n">
         <v>125.75</v>
       </c>
       <c r="I74" t="n">
-        <v>945.7249755859375</v>
+        <v>945.7249145507812</v>
       </c>
       <c r="J74" t="n">
         <v>14.75</v>
@@ -2610,13 +2610,13 @@
         <v>103.4499969482422</v>
       </c>
       <c r="G75" t="n">
-        <v>1260.062866210938</v>
+        <v>1260.06298828125</v>
       </c>
       <c r="H75" t="n">
         <v>130.3000030517578</v>
       </c>
       <c r="I75" t="n">
-        <v>987.2321166992188</v>
+        <v>987.2322387695312</v>
       </c>
       <c r="J75" t="n">
         <v>15.14999961853027</v>
@@ -2639,13 +2639,13 @@
         <v>98.90000152587891</v>
       </c>
       <c r="G76" t="n">
-        <v>1249.509887695312</v>
+        <v>1249.509765625</v>
       </c>
       <c r="H76" t="n">
         <v>128.8999938964844</v>
       </c>
       <c r="I76" t="n">
-        <v>962.5242919921875</v>
+        <v>962.5242309570312</v>
       </c>
       <c r="J76" t="n">
         <v>14.94999980926514</v>
@@ -2674,7 +2674,7 @@
         <v>123.25</v>
       </c>
       <c r="I77" t="n">
-        <v>902.3511962890625</v>
+        <v>902.3512573242188</v>
       </c>
       <c r="J77" t="n">
         <v>14.55000019073486</v>
@@ -2703,7 +2703,7 @@
         <v>121.1999969482422</v>
       </c>
       <c r="I78" t="n">
-        <v>926.4695434570312</v>
+        <v>926.469482421875</v>
       </c>
       <c r="J78" t="n">
         <v>14.5</v>
@@ -2755,13 +2755,13 @@
         <v>91.34999847412109</v>
       </c>
       <c r="G80" t="n">
-        <v>1277.16064453125</v>
+        <v>1277.160766601562</v>
       </c>
       <c r="H80" t="n">
         <v>120.5999984741211</v>
       </c>
       <c r="I80" t="n">
-        <v>1080.660034179688</v>
+        <v>1080.66015625</v>
       </c>
       <c r="J80" t="n">
         <v>13.94999980926514</v>
@@ -2790,7 +2790,7 @@
         <v>123.5500030517578</v>
       </c>
       <c r="I81" t="n">
-        <v>1086.947631835938</v>
+        <v>1086.94775390625</v>
       </c>
       <c r="J81" t="n">
         <v>14.25</v>
@@ -2819,7 +2819,7 @@
         <v>124.25</v>
       </c>
       <c r="I82" t="n">
-        <v>1096.47705078125</v>
+        <v>1096.477172851562</v>
       </c>
       <c r="J82" t="n">
         <v>14.19999980926514</v>
@@ -2871,7 +2871,7 @@
         <v>80.30000305175781</v>
       </c>
       <c r="G84" t="n">
-        <v>1196.11083984375</v>
+        <v>1196.110961914062</v>
       </c>
       <c r="H84" t="n">
         <v>115.0999984741211</v>
@@ -2935,7 +2935,7 @@
         <v>112.3000030517578</v>
       </c>
       <c r="I86" t="n">
-        <v>1002.950866699219</v>
+        <v>1002.950927734375</v>
       </c>
       <c r="J86" t="n">
         <v>13.69999980926514</v>
@@ -2958,7 +2958,7 @@
         <v>72.80000305175781</v>
       </c>
       <c r="G87" t="n">
-        <v>1120.813354492188</v>
+        <v>1120.813232421875</v>
       </c>
       <c r="H87" t="n">
         <v>108.1999969482422</v>
@@ -3051,7 +3051,7 @@
         <v>102.0500030517578</v>
       </c>
       <c r="I90" t="n">
-        <v>955.7456665039062</v>
+        <v>955.74560546875</v>
       </c>
       <c r="J90" t="n">
         <v>12.5</v>
@@ -3109,7 +3109,7 @@
         <v>107.0500030517578</v>
       </c>
       <c r="I92" t="n">
-        <v>1028.100708007812</v>
+        <v>1028.1005859375</v>
       </c>
       <c r="J92" t="n">
         <v>12.44999980926514</v>
@@ -3132,13 +3132,13 @@
         <v>78.30000305175781</v>
       </c>
       <c r="G93" t="n">
-        <v>1149.6640625</v>
+        <v>1149.664306640625</v>
       </c>
       <c r="H93" t="n">
         <v>104.0999984741211</v>
       </c>
       <c r="I93" t="n">
-        <v>1021.715026855469</v>
+        <v>1021.714965820312</v>
       </c>
       <c r="J93" t="n">
         <v>12.44999980926514</v>
@@ -3167,7 +3167,7 @@
         <v>102.0999984741211</v>
       </c>
       <c r="I94" t="n">
-        <v>977.5061645507812</v>
+        <v>977.5062255859375</v>
       </c>
       <c r="J94" t="n">
         <v>12.30000019073486</v>
@@ -3196,7 +3196,7 @@
         <v>104</v>
       </c>
       <c r="I95" t="n">
-        <v>1021.665893554688</v>
+        <v>1021.665832519531</v>
       </c>
       <c r="J95" t="n">
         <v>12.85000038146973</v>
@@ -3219,7 +3219,7 @@
         <v>80.05000305175781</v>
       </c>
       <c r="G96" t="n">
-        <v>1180.711669921875</v>
+        <v>1180.711791992188</v>
       </c>
       <c r="H96" t="n">
         <v>101.6999969482422</v>
@@ -3254,7 +3254,7 @@
         <v>100.9000015258789</v>
       </c>
       <c r="I97" t="n">
-        <v>945.7249755859375</v>
+        <v>945.7249145507812</v>
       </c>
       <c r="J97" t="n">
         <v>12.55000019073486</v>
@@ -3283,7 +3283,7 @@
         <v>100.6500015258789</v>
       </c>
       <c r="I98" t="n">
-        <v>869.98046875</v>
+        <v>869.9805908203125</v>
       </c>
       <c r="J98" t="n">
         <v>12.10000038146973</v>
@@ -3341,7 +3341,7 @@
         <v>99.84999847412109</v>
       </c>
       <c r="I100" t="n">
-        <v>871.9945068359375</v>
+        <v>871.9944458007812</v>
       </c>
       <c r="J100" t="n">
         <v>11.85000038146973</v>
@@ -3364,7 +3364,7 @@
         <v>73.15000152587891</v>
       </c>
       <c r="G101" t="n">
-        <v>1206.935668945312</v>
+        <v>1206.935791015625</v>
       </c>
       <c r="H101" t="n">
         <v>102.5500030517578</v>
@@ -3393,13 +3393,13 @@
         <v>75.5</v>
       </c>
       <c r="G102" t="n">
-        <v>1192.374267578125</v>
+        <v>1192.374389648438</v>
       </c>
       <c r="H102" t="n">
         <v>107.9499969482422</v>
       </c>
       <c r="I102" t="n">
-        <v>909.1299438476562</v>
+        <v>909.1298828125</v>
       </c>
       <c r="J102" t="n">
         <v>12.60000038146973</v>
@@ -3422,13 +3422,13 @@
         <v>76.05000305175781</v>
       </c>
       <c r="G103" t="n">
-        <v>1192.759399414062</v>
+        <v>1192.75927734375</v>
       </c>
       <c r="H103" t="n">
         <v>108.0500030517578</v>
       </c>
       <c r="I103" t="n">
-        <v>929.4658813476562</v>
+        <v>929.4659423828125</v>
       </c>
       <c r="J103" t="n">
         <v>13.19999980926514</v>
@@ -3480,13 +3480,13 @@
         <v>76.59999847412109</v>
       </c>
       <c r="G105" t="n">
-        <v>1258.88525390625</v>
+        <v>1258.885375976562</v>
       </c>
       <c r="H105" t="n">
         <v>106.5999984741211</v>
       </c>
       <c r="I105" t="n">
-        <v>965.9136962890625</v>
+        <v>965.9136352539062</v>
       </c>
       <c r="J105" t="n">
         <v>13.25</v>
@@ -3509,7 +3509,7 @@
         <v>74.65000152587891</v>
       </c>
       <c r="G106" t="n">
-        <v>1253.473022460938</v>
+        <v>1253.47314453125</v>
       </c>
       <c r="H106" t="n">
         <v>105.1500015258789</v>
@@ -3538,7 +3538,7 @@
         <v>75.90000152587891</v>
       </c>
       <c r="G107" t="n">
-        <v>1255.828247070312</v>
+        <v>1255.828125</v>
       </c>
       <c r="H107" t="n">
         <v>105.5</v>
@@ -3567,13 +3567,13 @@
         <v>80.05000305175781</v>
       </c>
       <c r="G108" t="n">
-        <v>1233.77099609375</v>
+        <v>1233.771118164062</v>
       </c>
       <c r="H108" t="n">
         <v>104.8499984741211</v>
       </c>
       <c r="I108" t="n">
-        <v>969.3521728515625</v>
+        <v>969.3521118164062</v>
       </c>
       <c r="J108" t="n">
         <v>13.85000038146973</v>
@@ -3602,7 +3602,7 @@
         <v>104.4499969482422</v>
       </c>
       <c r="I109" t="n">
-        <v>974.7554321289062</v>
+        <v>974.7554931640625</v>
       </c>
       <c r="J109" t="n">
         <v>13.94999980926514</v>
@@ -3660,7 +3660,7 @@
         <v>96.94999694824219</v>
       </c>
       <c r="I111" t="n">
-        <v>874.548828125</v>
+        <v>874.5487670898438</v>
       </c>
       <c r="J111" t="n">
         <v>12.89999961853027</v>
@@ -3683,13 +3683,13 @@
         <v>72.84999847412109</v>
       </c>
       <c r="G112" t="n">
-        <v>1190.313598632812</v>
+        <v>1190.3134765625</v>
       </c>
       <c r="H112" t="n">
         <v>95.75</v>
       </c>
       <c r="I112" t="n">
-        <v>879.7064819335938</v>
+        <v>879.7064208984375</v>
       </c>
       <c r="J112" t="n">
         <v>12.85000038146973</v>
@@ -3741,13 +3741,13 @@
         <v>67.25</v>
       </c>
       <c r="G114" t="n">
-        <v>1159.4697265625</v>
+        <v>1159.469848632812</v>
       </c>
       <c r="H114" t="n">
         <v>95.40000152587891</v>
       </c>
       <c r="I114" t="n">
-        <v>825.72265625</v>
+        <v>825.7225341796875</v>
       </c>
       <c r="J114" t="n">
         <v>12.05000019073486</v>
@@ -3770,13 +3770,13 @@
         <v>62.75</v>
       </c>
       <c r="G115" t="n">
-        <v>1173.057495117188</v>
+        <v>1173.057373046875</v>
       </c>
       <c r="H115" t="n">
         <v>95.59999847412109</v>
       </c>
       <c r="I115" t="n">
-        <v>833.483642578125</v>
+        <v>833.4837036132812</v>
       </c>
       <c r="J115" t="n">
         <v>12.14999961853027</v>
@@ -3799,13 +3799,13 @@
         <v>58.90000152587891</v>
       </c>
       <c r="G116" t="n">
-        <v>1151.79296875</v>
+        <v>1151.792846679688</v>
       </c>
       <c r="H116" t="n">
         <v>90.65000152587891</v>
       </c>
       <c r="I116" t="n">
-        <v>730.1824340820312</v>
+        <v>730.1823120117188</v>
       </c>
       <c r="J116" t="n">
         <v>11.10000038146973</v>
@@ -3828,13 +3828,13 @@
         <v>62.29999923706055</v>
       </c>
       <c r="G117" t="n">
-        <v>1170.385131835938</v>
+        <v>1170.38525390625</v>
       </c>
       <c r="H117" t="n">
         <v>94.5</v>
       </c>
       <c r="I117" t="n">
-        <v>770.314208984375</v>
+        <v>770.3141479492188</v>
       </c>
       <c r="J117" t="n">
         <v>11.44999980926514</v>
@@ -3857,7 +3857,7 @@
         <v>59.15000152587891</v>
       </c>
       <c r="G118" t="n">
-        <v>1134.8310546875</v>
+        <v>1134.831176757812</v>
       </c>
       <c r="H118" t="n">
         <v>91.19999694824219</v>
@@ -3921,7 +3921,7 @@
         <v>90.69999694824219</v>
       </c>
       <c r="I120" t="n">
-        <v>775.570068359375</v>
+        <v>775.5701293945312</v>
       </c>
       <c r="J120" t="n">
         <v>11.85000038146973</v>
@@ -3944,13 +3944,13 @@
         <v>62.84999847412109</v>
       </c>
       <c r="G121" t="n">
-        <v>1128.9658203125</v>
+        <v>1128.965698242188</v>
       </c>
       <c r="H121" t="n">
         <v>93.09999847412109</v>
       </c>
       <c r="I121" t="n">
-        <v>801.5059814453125</v>
+        <v>801.5059204101562</v>
       </c>
       <c r="J121" t="n">
         <v>11.80000019073486</v>
@@ -3979,7 +3979,7 @@
         <v>92.19999694824219</v>
       </c>
       <c r="I122" t="n">
-        <v>827.1962280273438</v>
+        <v>827.1961669921875</v>
       </c>
       <c r="J122" t="n">
         <v>11.80000019073486</v>
@@ -4037,7 +4037,7 @@
         <v>90.59999847412109</v>
       </c>
       <c r="I124" t="n">
-        <v>935.9990234375</v>
+        <v>935.9990844726562</v>
       </c>
       <c r="J124" t="n">
         <v>11.5</v>
@@ -4060,7 +4060,7 @@
         <v>67.65000152587891</v>
       </c>
       <c r="G125" t="n">
-        <v>1090.943237304688</v>
+        <v>1090.943359375</v>
       </c>
       <c r="H125" t="n">
         <v>91.09999847412109</v>
@@ -4089,13 +4089,13 @@
         <v>65.55000305175781</v>
       </c>
       <c r="G126" t="n">
-        <v>1093.207885742188</v>
+        <v>1093.2080078125</v>
       </c>
       <c r="H126" t="n">
         <v>94.5</v>
       </c>
       <c r="I126" t="n">
-        <v>935.704345703125</v>
+        <v>935.7042846679688</v>
       </c>
       <c r="J126" t="n">
         <v>11.35000038146973</v>
@@ -4118,7 +4118,7 @@
         <v>65.40000152587891</v>
       </c>
       <c r="G127" t="n">
-        <v>1102.062622070312</v>
+        <v>1102.0625</v>
       </c>
       <c r="H127" t="n">
         <v>93.15000152587891</v>
@@ -4147,7 +4147,7 @@
         <v>65.30000305175781</v>
       </c>
       <c r="G128" t="n">
-        <v>1092.3701171875</v>
+        <v>1092.369995117188</v>
       </c>
       <c r="H128" t="n">
         <v>91.75</v>
@@ -4176,7 +4176,7 @@
         <v>67.25</v>
       </c>
       <c r="G129" t="n">
-        <v>1081.613403320312</v>
+        <v>1081.61328125</v>
       </c>
       <c r="H129" t="n">
         <v>94.90000152587891</v>
@@ -4205,13 +4205,13 @@
         <v>67.40000152587891</v>
       </c>
       <c r="G130" t="n">
-        <v>1083.10791015625</v>
+        <v>1083.108032226562</v>
       </c>
       <c r="H130" t="n">
         <v>94.80000305175781</v>
       </c>
       <c r="I130" t="n">
-        <v>933.3465576171875</v>
+        <v>933.3464965820312</v>
       </c>
       <c r="J130" t="n">
         <v>11.39999961853027</v>
@@ -4269,7 +4269,7 @@
         <v>102.5999984741211</v>
       </c>
       <c r="I132" t="n">
-        <v>951.2265625</v>
+        <v>951.2265014648438</v>
       </c>
       <c r="J132" t="n">
         <v>11.5</v>
@@ -4292,7 +4292,7 @@
         <v>70.59999847412109</v>
       </c>
       <c r="G133" t="n">
-        <v>1076.8349609375</v>
+        <v>1076.835083007812</v>
       </c>
       <c r="H133" t="n">
         <v>101.6500015258789</v>
@@ -4385,7 +4385,7 @@
         <v>102.25</v>
       </c>
       <c r="I136" t="n">
-        <v>964.4400024414062</v>
+        <v>964.4401245117188</v>
       </c>
       <c r="J136" t="n">
         <v>11.5</v>
@@ -4408,13 +4408,13 @@
         <v>67.09999847412109</v>
       </c>
       <c r="G137" t="n">
-        <v>1103.806396484375</v>
+        <v>1103.806518554688</v>
       </c>
       <c r="H137" t="n">
         <v>102.3000030517578</v>
       </c>
       <c r="I137" t="n">
-        <v>978.8323974609375</v>
+        <v>978.8324584960938</v>
       </c>
       <c r="J137" t="n">
         <v>11.80000019073486</v>
@@ -4437,13 +4437,13 @@
         <v>67</v>
       </c>
       <c r="G138" t="n">
-        <v>1133.653442382812</v>
+        <v>1133.653564453125</v>
       </c>
       <c r="H138" t="n">
         <v>104.4000015258789</v>
       </c>
       <c r="I138" t="n">
-        <v>959.6753540039062</v>
+        <v>959.67529296875</v>
       </c>
       <c r="J138" t="n">
         <v>11.85000038146973</v>
@@ -4466,7 +4466,7 @@
         <v>65</v>
       </c>
       <c r="G139" t="n">
-        <v>1126.08984375</v>
+        <v>1126.089965820312</v>
       </c>
       <c r="H139" t="n">
         <v>105.8000030517578</v>
@@ -4553,7 +4553,7 @@
         <v>62.90000152587891</v>
       </c>
       <c r="G142" t="n">
-        <v>1096.74072265625</v>
+        <v>1096.740844726562</v>
       </c>
       <c r="H142" t="n">
         <v>113.9000015258789</v>
@@ -4588,7 +4588,7 @@
         <v>115.8499984741211</v>
       </c>
       <c r="I143" t="n">
-        <v>945.8232421875</v>
+        <v>945.8231811523438</v>
       </c>
       <c r="J143" t="n">
         <v>11.89999961853027</v>
@@ -4611,13 +4611,13 @@
         <v>65.15000152587891</v>
       </c>
       <c r="G144" t="n">
-        <v>1112.864624023438</v>
+        <v>1112.86474609375</v>
       </c>
       <c r="H144" t="n">
         <v>114.25</v>
       </c>
       <c r="I144" t="n">
-        <v>955.1071166992188</v>
+        <v>955.1070556640625</v>
       </c>
       <c r="J144" t="n">
         <v>11.75</v>
@@ -4675,7 +4675,7 @@
         <v>123.25</v>
       </c>
       <c r="I146" t="n">
-        <v>1014.592407226562</v>
+        <v>1014.592529296875</v>
       </c>
       <c r="J146" t="n">
         <v>13</v>
@@ -4698,13 +4698,13 @@
         <v>68.05000305175781</v>
       </c>
       <c r="G147" t="n">
-        <v>1170.634399414062</v>
+        <v>1170.634155273438</v>
       </c>
       <c r="H147" t="n">
         <v>128.6999969482422</v>
       </c>
       <c r="I147" t="n">
-        <v>994.7967529296875</v>
+        <v>994.7968139648438</v>
       </c>
       <c r="J147" t="n">
         <v>13.30000019073486</v>
@@ -4727,13 +4727,13 @@
         <v>69.19999694824219</v>
       </c>
       <c r="G148" t="n">
-        <v>1180.462524414062</v>
+        <v>1180.462646484375</v>
       </c>
       <c r="H148" t="n">
         <v>125.0500030517578</v>
       </c>
       <c r="I148" t="n">
-        <v>966.06103515625</v>
+        <v>966.0609741210938</v>
       </c>
       <c r="J148" t="n">
         <v>13</v>
@@ -4756,7 +4756,7 @@
         <v>67.90000152587891</v>
       </c>
       <c r="G149" t="n">
-        <v>1164.859619140625</v>
+        <v>1164.859497070312</v>
       </c>
       <c r="H149" t="n">
         <v>121.3499984741211</v>
@@ -4785,7 +4785,7 @@
         <v>68.09999847412109</v>
       </c>
       <c r="G150" t="n">
-        <v>1147.693969726562</v>
+        <v>1147.694091796875</v>
       </c>
       <c r="H150" t="n">
         <v>120</v>
@@ -4814,7 +4814,7 @@
         <v>67.5</v>
       </c>
       <c r="G151" t="n">
-        <v>1162.708129882812</v>
+        <v>1162.708251953125</v>
       </c>
       <c r="H151" t="n">
         <v>115.8499984741211</v>
@@ -4843,13 +4843,13 @@
         <v>66.65000152587891</v>
       </c>
       <c r="G152" t="n">
-        <v>1169.66064453125</v>
+        <v>1169.660522460938</v>
       </c>
       <c r="H152" t="n">
         <v>117.5500030517578</v>
       </c>
       <c r="I152" t="n">
-        <v>944.4968872070312</v>
+        <v>944.4970092773438</v>
       </c>
       <c r="J152" t="n">
         <v>14.14999961853027</v>
@@ -4878,7 +4878,7 @@
         <v>115.3499984741211</v>
       </c>
       <c r="I153" t="n">
-        <v>953.8790893554688</v>
+        <v>953.8790283203125</v>
       </c>
       <c r="J153" t="n">
         <v>13.60000038146973</v>
@@ -4936,7 +4936,7 @@
         <v>116.5500030517578</v>
       </c>
       <c r="I155" t="n">
-        <v>979.5201416015625</v>
+        <v>979.5202026367188</v>
       </c>
       <c r="J155" t="n">
         <v>13.39999961853027</v>
@@ -4959,13 +4959,13 @@
         <v>72.55000305175781</v>
       </c>
       <c r="G156" t="n">
-        <v>1207.09423828125</v>
+        <v>1207.094116210938</v>
       </c>
       <c r="H156" t="n">
         <v>121.8000030517578</v>
       </c>
       <c r="I156" t="n">
-        <v>975.4921875</v>
+        <v>975.4923095703125</v>
       </c>
       <c r="J156" t="n">
         <v>13.64999961853027</v>
@@ -5017,7 +5017,7 @@
         <v>73.75</v>
       </c>
       <c r="G158" t="n">
-        <v>1187.722045898438</v>
+        <v>1187.72216796875</v>
       </c>
       <c r="H158" t="n">
         <v>135.6000061035156</v>
@@ -5052,7 +5052,7 @@
         <v>140.6999969482422</v>
       </c>
       <c r="I159" t="n">
-        <v>973.0361938476562</v>
+        <v>973.0362548828125</v>
       </c>
       <c r="J159" t="n">
         <v>15.64999961853027</v>
@@ -5139,7 +5139,7 @@
         <v>139.75</v>
       </c>
       <c r="I162" t="n">
-        <v>1002.8525390625</v>
+        <v>1002.852600097656</v>
       </c>
       <c r="J162" t="n">
         <v>15.05000019073486</v>
@@ -5162,7 +5162,7 @@
         <v>74</v>
       </c>
       <c r="G163" t="n">
-        <v>1189.607788085938</v>
+        <v>1189.60791015625</v>
       </c>
       <c r="H163" t="n">
         <v>157.3500061035156</v>
@@ -5197,7 +5197,7 @@
         <v>158.75</v>
       </c>
       <c r="I164" t="n">
-        <v>992.144287109375</v>
+        <v>992.1442260742188</v>
       </c>
       <c r="J164" t="n">
         <v>16.29999923706055</v>
@@ -5255,7 +5255,7 @@
         <v>193.8500061035156</v>
       </c>
       <c r="I166" t="n">
-        <v>1039.644287109375</v>
+        <v>1039.644165039062</v>
       </c>
       <c r="J166" t="n">
         <v>20.14999961853027</v>
@@ -5284,7 +5284,7 @@
         <v>179.1499938964844</v>
       </c>
       <c r="I167" t="n">
-        <v>1082.084594726562</v>
+        <v>1082.08447265625</v>
       </c>
       <c r="J167" t="n">
         <v>21.20000076293945</v>
@@ -5313,7 +5313,7 @@
         <v>182.6999969482422</v>
       </c>
       <c r="I168" t="n">
-        <v>1193.932983398438</v>
+        <v>1193.93310546875</v>
       </c>
       <c r="J168" t="n">
         <v>23.29999923706055</v>
@@ -5371,7 +5371,7 @@
         <v>180.6999969482422</v>
       </c>
       <c r="I170" t="n">
-        <v>1191.771484375</v>
+        <v>1191.771606445312</v>
       </c>
       <c r="J170" t="n">
         <v>21.64999961853027</v>
@@ -5394,7 +5394,7 @@
         <v>73.65000152587891</v>
       </c>
       <c r="G171" t="n">
-        <v>1174.794555664062</v>
+        <v>1174.79443359375</v>
       </c>
       <c r="H171" t="n">
         <v>180.3000030517578</v>
@@ -5429,7 +5429,7 @@
         <v>162.4499969482422</v>
       </c>
       <c r="I172" t="n">
-        <v>1153.801025390625</v>
+        <v>1153.801147460938</v>
       </c>
       <c r="J172" t="n">
         <v>19.20000076293945</v>
@@ -5487,7 +5487,7 @@
         <v>165.5</v>
       </c>
       <c r="I174" t="n">
-        <v>1137.44384765625</v>
+        <v>1137.443969726562</v>
       </c>
       <c r="J174" t="n">
         <v>20.04999923706055</v>
@@ -5545,7 +5545,7 @@
         <v>154.4499969482422</v>
       </c>
       <c r="I176" t="n">
-        <v>1170.551391601562</v>
+        <v>1170.55126953125</v>
       </c>
       <c r="J176" t="n">
         <v>18.10000038146973</v>
@@ -5574,7 +5574,7 @@
         <v>156.3500061035156</v>
       </c>
       <c r="I177" t="n">
-        <v>1119.121704101562</v>
+        <v>1119.121826171875</v>
       </c>
       <c r="J177" t="n">
         <v>18.45000076293945</v>
@@ -5603,7 +5603,7 @@
         <v>151.8000030517578</v>
       </c>
       <c r="I178" t="n">
-        <v>1159.351806640625</v>
+        <v>1159.351928710938</v>
       </c>
       <c r="J178" t="n">
         <v>17.64999961853027</v>
@@ -5632,7 +5632,7 @@
         <v>154.4499969482422</v>
       </c>
       <c r="I179" t="n">
-        <v>1188.16064453125</v>
+        <v>1188.160766601562</v>
       </c>
       <c r="J179" t="n">
         <v>18.20000076293945</v>
@@ -5655,13 +5655,13 @@
         <v>69.90000152587891</v>
       </c>
       <c r="G180" t="n">
-        <v>1140.419677734375</v>
+        <v>1140.419799804688</v>
       </c>
       <c r="H180" t="n">
         <v>146.75</v>
       </c>
       <c r="I180" t="n">
-        <v>1156.446411132812</v>
+        <v>1156.4462890625</v>
       </c>
       <c r="J180" t="n">
         <v>17.29999923706055</v>
@@ -5719,7 +5719,7 @@
         <v>144.1499938964844</v>
       </c>
       <c r="I182" t="n">
-        <v>1157.628173828125</v>
+        <v>1157.628295898438</v>
       </c>
       <c r="J182" t="n">
         <v>16.89999961853027</v>
@@ -5742,13 +5742,13 @@
         <v>64</v>
       </c>
       <c r="G183" t="n">
-        <v>1080.257568359375</v>
+        <v>1080.257446289062</v>
       </c>
       <c r="H183" t="n">
         <v>137.1999969482422</v>
       </c>
       <c r="I183" t="n">
-        <v>1051.699829101562</v>
+        <v>1051.699951171875</v>
       </c>
       <c r="J183" t="n">
         <v>16.35000038146973</v>
@@ -5806,7 +5806,7 @@
         <v>136.3500061035156</v>
       </c>
       <c r="I185" t="n">
-        <v>1021.610412597656</v>
+        <v>1021.610473632812</v>
       </c>
       <c r="J185" t="n">
         <v>16.10000038146973</v>
@@ -5829,13 +5829,13 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G186" t="n">
-        <v>1056.606201171875</v>
+        <v>1056.606323242188</v>
       </c>
       <c r="H186" t="n">
         <v>137.6499938964844</v>
       </c>
       <c r="I186" t="n">
-        <v>1032.690795898438</v>
+        <v>1032.69091796875</v>
       </c>
       <c r="J186" t="n">
         <v>16.04999923706055</v>
@@ -5864,7 +5864,7 @@
         <v>136.6999969482422</v>
       </c>
       <c r="I187" t="n">
-        <v>1060.41650390625</v>
+        <v>1060.416259765625</v>
       </c>
       <c r="J187" t="n">
         <v>16.39999961853027</v>
@@ -5916,7 +5916,7 @@
         <v>66</v>
       </c>
       <c r="G189" t="n">
-        <v>1096.547607421875</v>
+        <v>1096.547485351562</v>
       </c>
       <c r="H189" t="n">
         <v>137.5500030517578</v>
@@ -5945,7 +5945,7 @@
         <v>67.30000305175781</v>
       </c>
       <c r="G190" t="n">
-        <v>1100.591674804688</v>
+        <v>1100.591796875</v>
       </c>
       <c r="H190" t="n">
         <v>144.3999938964844</v>
@@ -6003,13 +6003,13 @@
         <v>67.25</v>
       </c>
       <c r="G192" t="n">
-        <v>1093.185180664062</v>
+        <v>1093.18505859375</v>
       </c>
       <c r="H192" t="n">
         <v>157.6999969482422</v>
       </c>
       <c r="I192" t="n">
-        <v>1173.87939453125</v>
+        <v>1173.879272460938</v>
       </c>
       <c r="J192" t="n">
         <v>17.75</v>
@@ -6038,7 +6038,7 @@
         <v>149.8500061035156</v>
       </c>
       <c r="I193" t="n">
-        <v>1184.81201171875</v>
+        <v>1184.811889648438</v>
       </c>
       <c r="J193" t="n">
         <v>16.89999961853027</v>
@@ -6067,7 +6067,7 @@
         <v>142.6999969482422</v>
       </c>
       <c r="I194" t="n">
-        <v>1128.179077148438</v>
+        <v>1128.178955078125</v>
       </c>
       <c r="J194" t="n">
         <v>16.35000038146973</v>
@@ -6096,7 +6096,7 @@
         <v>142.3500061035156</v>
       </c>
       <c r="I195" t="n">
-        <v>1122.663452148438</v>
+        <v>1122.663330078125</v>
       </c>
       <c r="J195" t="n">
         <v>16.5</v>
@@ -6125,7 +6125,7 @@
         <v>138.8500061035156</v>
       </c>
       <c r="I196" t="n">
-        <v>1100.404174804688</v>
+        <v>1100.404296875</v>
       </c>
       <c r="J196" t="n">
         <v>16.20000076293945</v>
@@ -6177,7 +6177,7 @@
         <v>70</v>
       </c>
       <c r="G198" t="n">
-        <v>1113.83740234375</v>
+        <v>1113.837280273438</v>
       </c>
       <c r="H198" t="n">
         <v>143.6999969482422</v>
@@ -6206,13 +6206,13 @@
         <v>65.59999847412109</v>
       </c>
       <c r="G199" t="n">
-        <v>1133.217407226562</v>
+        <v>1133.21728515625</v>
       </c>
       <c r="H199" t="n">
         <v>141.3500061035156</v>
       </c>
       <c r="I199" t="n">
-        <v>1121.087524414062</v>
+        <v>1121.087646484375</v>
       </c>
       <c r="J199" t="n">
         <v>16.35000038146973</v>
@@ -6270,7 +6270,7 @@
         <v>139.1499938964844</v>
       </c>
       <c r="I201" t="n">
-        <v>1088.585205078125</v>
+        <v>1088.5849609375</v>
       </c>
       <c r="J201" t="n">
         <v>16.35000038146973</v>
@@ -6357,7 +6357,7 @@
         <v>141.8500061035156</v>
       </c>
       <c r="I204" t="n">
-        <v>1086.56591796875</v>
+        <v>1086.566040039062</v>
       </c>
       <c r="J204" t="n">
         <v>16.14999961853027</v>
@@ -6380,13 +6380,13 @@
         <v>63.25</v>
       </c>
       <c r="G205" t="n">
-        <v>1147.871826171875</v>
+        <v>1147.871704101562</v>
       </c>
       <c r="H205" t="n">
         <v>141.8999938964844</v>
       </c>
       <c r="I205" t="n">
-        <v>1081.690551757812</v>
+        <v>1081.690673828125</v>
       </c>
       <c r="J205" t="n">
         <v>16</v>
@@ -6409,7 +6409,7 @@
         <v>64.15000152587891</v>
       </c>
       <c r="G206" t="n">
-        <v>1158.527099609375</v>
+        <v>1158.527221679688</v>
       </c>
       <c r="H206" t="n">
         <v>141.4499969482422</v>
@@ -6444,7 +6444,7 @@
         <v>140.6499938964844</v>
       </c>
       <c r="I207" t="n">
-        <v>1085.72900390625</v>
+        <v>1085.728759765625</v>
       </c>
       <c r="J207" t="n">
         <v>16.04999923706055</v>
@@ -6473,7 +6473,7 @@
         <v>140.5500030517578</v>
       </c>
       <c r="I208" t="n">
-        <v>1097.301635742188</v>
+        <v>1097.3017578125</v>
       </c>
       <c r="J208" t="n">
         <v>16.10000038146973</v>
@@ -6502,7 +6502,7 @@
         <v>140.1499938964844</v>
       </c>
       <c r="I209" t="n">
-        <v>1067.310913085938</v>
+        <v>1067.310791015625</v>
       </c>
       <c r="J209" t="n">
         <v>16</v>
@@ -6560,7 +6560,7 @@
         <v>152.9499969482422</v>
       </c>
       <c r="I211" t="n">
-        <v>1081.93701171875</v>
+        <v>1081.936889648438</v>
       </c>
       <c r="J211" t="n">
         <v>16.85000038146973</v>
@@ -6618,7 +6618,7 @@
         <v>142.8500061035156</v>
       </c>
       <c r="I213" t="n">
-        <v>1053.669677734375</v>
+        <v>1053.669799804688</v>
       </c>
       <c r="J213" t="n">
         <v>16.10000038146973</v>
@@ -6647,7 +6647,7 @@
         <v>146.1999969482422</v>
       </c>
       <c r="I214" t="n">
-        <v>1057.2646484375</v>
+        <v>1057.264526367188</v>
       </c>
       <c r="J214" t="n">
         <v>16</v>
@@ -6670,13 +6670,13 @@
         <v>64.05000305175781</v>
       </c>
       <c r="G215" t="n">
-        <v>1190.0849609375</v>
+        <v>1190.085083007812</v>
       </c>
       <c r="H215" t="n">
         <v>153.3999938964844</v>
       </c>
       <c r="I215" t="n">
-        <v>1071.693725585938</v>
+        <v>1071.693603515625</v>
       </c>
       <c r="J215" t="n">
         <v>16.04999923706055</v>
@@ -6699,13 +6699,13 @@
         <v>63.04999923706055</v>
       </c>
       <c r="G216" t="n">
-        <v>1184.745849609375</v>
+        <v>1184.745727539062</v>
       </c>
       <c r="H216" t="n">
         <v>151.3500061035156</v>
       </c>
       <c r="I216" t="n">
-        <v>1058.93896484375</v>
+        <v>1058.939086914062</v>
       </c>
       <c r="J216" t="n">
         <v>16.10000038146973</v>
@@ -6728,13 +6728,13 @@
         <v>62.54999923706055</v>
       </c>
       <c r="G217" t="n">
-        <v>1177.952758789062</v>
+        <v>1177.95263671875</v>
       </c>
       <c r="H217" t="n">
         <v>148.6499938964844</v>
       </c>
       <c r="I217" t="n">
-        <v>1012.499816894531</v>
+        <v>1012.499938964844</v>
       </c>
       <c r="J217" t="n">
         <v>16</v>
@@ -6757,13 +6757,13 @@
         <v>62.29999923706055</v>
       </c>
       <c r="G218" t="n">
-        <v>1180.9970703125</v>
+        <v>1180.997192382812</v>
       </c>
       <c r="H218" t="n">
         <v>146.0500030517578</v>
       </c>
       <c r="I218" t="n">
-        <v>1011.121032714844</v>
+        <v>1011.120971679688</v>
       </c>
       <c r="J218" t="n">
         <v>15.64999961853027</v>
@@ -6792,7 +6792,7 @@
         <v>147.6499938964844</v>
       </c>
       <c r="I219" t="n">
-        <v>990.6838989257812</v>
+        <v>990.683837890625</v>
       </c>
       <c r="J219" t="n">
         <v>15.5</v>
@@ -6821,7 +6821,7 @@
         <v>145.25</v>
       </c>
       <c r="I220" t="n">
-        <v>978.7662963867188</v>
+        <v>978.766357421875</v>
       </c>
       <c r="J220" t="n">
         <v>15.5</v>
@@ -6873,7 +6873,7 @@
         <v>60.54999923706055</v>
       </c>
       <c r="G222" t="n">
-        <v>1161.912353515625</v>
+        <v>1161.912475585938</v>
       </c>
       <c r="H222" t="n">
         <v>146.1499938964844</v>
@@ -6908,7 +6908,7 @@
         <v>147.0500030517578</v>
       </c>
       <c r="I223" t="n">
-        <v>990.5853881835938</v>
+        <v>990.5853271484375</v>
       </c>
       <c r="J223" t="n">
         <v>15.25</v>
@@ -6937,7 +6937,7 @@
         <v>154.3000030517578</v>
       </c>
       <c r="I224" t="n">
-        <v>1008.067749023438</v>
+        <v>1008.067810058594</v>
       </c>
       <c r="J224" t="n">
         <v>16</v>
@@ -6960,7 +6960,7 @@
         <v>63.75</v>
       </c>
       <c r="G225" t="n">
-        <v>1230.299194335938</v>
+        <v>1230.299072265625</v>
       </c>
       <c r="H225" t="n">
         <v>153.6499938964844</v>
@@ -7053,7 +7053,7 @@
         <v>156.1000061035156</v>
       </c>
       <c r="I228" t="n">
-        <v>1040.225463867188</v>
+        <v>1040.2255859375</v>
       </c>
       <c r="J228" t="n">
         <v>16</v>
@@ -7082,7 +7082,7 @@
         <v>162.8999938964844</v>
       </c>
       <c r="I229" t="n">
-        <v>1033.67578125</v>
+        <v>1033.675659179688</v>
       </c>
       <c r="J229" t="n">
         <v>16.79999923706055</v>
@@ -7140,7 +7140,7 @@
         <v>156.3999938964844</v>
       </c>
       <c r="I231" t="n">
-        <v>1050.419555664062</v>
+        <v>1050.419311523438</v>
       </c>
       <c r="J231" t="n">
         <v>15.85000038146973</v>
@@ -7198,7 +7198,7 @@
         <v>154.0500030517578</v>
       </c>
       <c r="I233" t="n">
-        <v>1031.31201171875</v>
+        <v>1031.311889648438</v>
       </c>
       <c r="J233" t="n">
         <v>15.85000038146973</v>
@@ -7221,7 +7221,7 @@
         <v>72.90000152587891</v>
       </c>
       <c r="G234" t="n">
-        <v>1185.56396484375</v>
+        <v>1185.563842773438</v>
       </c>
       <c r="H234" t="n">
         <v>154.75</v>
@@ -7256,7 +7256,7 @@
         <v>161.8000030517578</v>
       </c>
       <c r="I235" t="n">
-        <v>1015.454650878906</v>
+        <v>1015.454772949219</v>
       </c>
       <c r="J235" t="n">
         <v>15.94999980926514</v>
@@ -7285,7 +7285,7 @@
         <v>157.25</v>
       </c>
       <c r="I236" t="n">
-        <v>1016.488891601562</v>
+        <v>1016.488952636719</v>
       </c>
       <c r="J236" t="n">
         <v>15.75</v>
@@ -7308,13 +7308,13 @@
         <v>75.40000152587891</v>
       </c>
       <c r="G237" t="n">
-        <v>1188.471923828125</v>
+        <v>1188.472045898438</v>
       </c>
       <c r="H237" t="n">
         <v>156.6499938964844</v>
       </c>
       <c r="I237" t="n">
-        <v>1012.942993164062</v>
+        <v>1012.943054199219</v>
       </c>
       <c r="J237" t="n">
         <v>16.45000076293945</v>
@@ -7372,7 +7372,7 @@
         <v>151.1000061035156</v>
       </c>
       <c r="I239" t="n">
-        <v>982.7553100585938</v>
+        <v>982.7552490234375</v>
       </c>
       <c r="J239" t="n">
         <v>15.75</v>
@@ -7395,7 +7395,7 @@
         <v>70.94999694824219</v>
       </c>
       <c r="G240" t="n">
-        <v>1181.110717773438</v>
+        <v>1181.110595703125</v>
       </c>
       <c r="H240" t="n">
         <v>150.6499938964844</v>
@@ -7430,7 +7430,7 @@
         <v>149.8000030517578</v>
       </c>
       <c r="I241" t="n">
-        <v>982.213623046875</v>
+        <v>982.2135009765625</v>
       </c>
       <c r="J241" t="n">
         <v>15.75</v>
@@ -7488,7 +7488,7 @@
         <v>135.4499969482422</v>
       </c>
       <c r="I243" t="n">
-        <v>898.88916015625</v>
+        <v>898.8892211914062</v>
       </c>
       <c r="J243" t="n">
         <v>14.25</v>
@@ -7511,13 +7511,13 @@
         <v>60.59999847412109</v>
       </c>
       <c r="G244" t="n">
-        <v>1136.98876953125</v>
+        <v>1136.988891601562</v>
       </c>
       <c r="H244" t="n">
         <v>128.6999969482422</v>
       </c>
       <c r="I244" t="n">
-        <v>796.0140991210938</v>
+        <v>796.0140380859375</v>
       </c>
       <c r="J244" t="n">
         <v>13.55000019073486</v>
@@ -7540,13 +7540,13 @@
         <v>62.90000152587891</v>
       </c>
       <c r="G245" t="n">
-        <v>1146.917236328125</v>
+        <v>1146.917358398438</v>
       </c>
       <c r="H245" t="n">
         <v>128.1999969482422</v>
       </c>
       <c r="I245" t="n">
-        <v>858.0149536132812</v>
+        <v>858.014892578125</v>
       </c>
       <c r="J245" t="n">
         <v>14.14999961853027</v>
@@ -7575,7 +7575,7 @@
         <v>134.6000061035156</v>
       </c>
       <c r="I246" t="n">
-        <v>890.71435546875</v>
+        <v>890.7142333984375</v>
       </c>
       <c r="J246" t="n">
         <v>14.80000019073486</v>
@@ -7633,7 +7633,7 @@
         <v>135.8000030517578</v>
       </c>
       <c r="I248" t="n">
-        <v>928.7816162109375</v>
+        <v>928.781494140625</v>
       </c>
       <c r="J248" t="n">
         <v>14.30000019073486</v>
@@ -7662,7 +7662,7 @@
         <v>137.6999969482422</v>
       </c>
       <c r="I249" t="n">
-        <v>930.1112670898438</v>
+        <v>930.1112060546875</v>
       </c>
       <c r="J249" t="n">
         <v>14.35000038146973</v>
@@ -7685,13 +7685,13 @@
         <v>67.55000305175781</v>
       </c>
       <c r="G250" t="n">
-        <v>1170.477783203125</v>
+        <v>1170.477905273438</v>
       </c>
       <c r="H250" t="n">
         <v>137.8500061035156</v>
       </c>
       <c r="I250" t="n">
-        <v>937.20263671875</v>
+        <v>937.2025756835938</v>
       </c>
       <c r="J250" t="n">
         <v>14.69999980926514</v>
@@ -7714,7 +7714,7 @@
         <v>66.84999847412109</v>
       </c>
       <c r="G251" t="n">
-        <v>1161.912353515625</v>
+        <v>1161.912475585938</v>
       </c>
       <c r="H251" t="n">
         <v>138.6000061035156</v>
@@ -7743,13 +7743,13 @@
         <v>65.75</v>
       </c>
       <c r="G252" t="n">
-        <v>1144.418334960938</v>
+        <v>1144.418212890625</v>
       </c>
       <c r="H252" t="n">
         <v>136.4499969482422</v>
       </c>
       <c r="I252" t="n">
-        <v>901.9916381835938</v>
+        <v>901.9915771484375</v>
       </c>
       <c r="J252" t="n">
         <v>14.44999980926514</v>
@@ -7778,7 +7778,7 @@
         <v>133.75</v>
       </c>
       <c r="I253" t="n">
-        <v>905.3403930664062</v>
+        <v>905.3404541015625</v>
       </c>
       <c r="J253" t="n">
         <v>14.60000038146973</v>
@@ -7801,13 +7801,13 @@
         <v>65.40000152587891</v>
       </c>
       <c r="G254" t="n">
-        <v>1152.756225585938</v>
+        <v>1152.75634765625</v>
       </c>
       <c r="H254" t="n">
         <v>130.1999969482422</v>
       </c>
       <c r="I254" t="n">
-        <v>892.9302978515625</v>
+        <v>892.9303588867188</v>
       </c>
       <c r="J254" t="n">
         <v>14.44999980926514</v>
@@ -7836,7 +7836,7 @@
         <v>135.0500030517578</v>
       </c>
       <c r="I255" t="n">
-        <v>922.330322265625</v>
+        <v>922.3302612304688</v>
       </c>
       <c r="J255" t="n">
         <v>14.55000019073486</v>
@@ -7888,13 +7888,13 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G257" t="n">
-        <v>1147.871826171875</v>
+        <v>1147.871704101562</v>
       </c>
       <c r="H257" t="n">
         <v>134.3000030517578</v>
       </c>
       <c r="I257" t="n">
-        <v>902.3363647460938</v>
+        <v>902.33642578125</v>
       </c>
       <c r="J257" t="n">
         <v>14.25</v>
@@ -7923,7 +7923,7 @@
         <v>132.3000030517578</v>
       </c>
       <c r="I258" t="n">
-        <v>899.036865234375</v>
+        <v>899.0369262695312</v>
       </c>
       <c r="J258" t="n">
         <v>13.94999980926514</v>
@@ -7952,7 +7952,7 @@
         <v>132.6499938964844</v>
       </c>
       <c r="I259" t="n">
-        <v>899.3323364257812</v>
+        <v>899.3323974609375</v>
       </c>
       <c r="J259" t="n">
         <v>14.14999961853027</v>
@@ -7975,7 +7975,7 @@
         <v>65.44999694824219</v>
       </c>
       <c r="G260" t="n">
-        <v>1110.58837890625</v>
+        <v>1110.588500976562</v>
       </c>
       <c r="H260" t="n">
         <v>139.25</v>
@@ -8004,13 +8004,13 @@
         <v>63.34999847412109</v>
       </c>
       <c r="G261" t="n">
-        <v>1126.356079101562</v>
+        <v>1126.35595703125</v>
       </c>
       <c r="H261" t="n">
         <v>141.3000030517578</v>
       </c>
       <c r="I261" t="n">
-        <v>883.5242919921875</v>
+        <v>883.5243530273438</v>
       </c>
       <c r="J261" t="n">
         <v>14.14999961853027</v>
@@ -8062,7 +8062,7 @@
         <v>62.25</v>
       </c>
       <c r="G263" t="n">
-        <v>1123.288940429688</v>
+        <v>1123.288818359375</v>
       </c>
       <c r="H263" t="n">
         <v>137.5</v>
@@ -8091,7 +8091,7 @@
         <v>61.34999847412109</v>
       </c>
       <c r="G264" t="n">
-        <v>1109.9296875</v>
+        <v>1109.929565429688</v>
       </c>
       <c r="H264" t="n">
         <v>136.25</v>
@@ -8126,7 +8126,7 @@
         <v>133.6999969482422</v>
       </c>
       <c r="I265" t="n">
-        <v>892.0438842773438</v>
+        <v>892.0439453125</v>
       </c>
       <c r="J265" t="n">
         <v>13.19999980926514</v>
@@ -8155,7 +8155,7 @@
         <v>132.1000061035156</v>
       </c>
       <c r="I266" t="n">
-        <v>882.8841552734375</v>
+        <v>882.8842163085938</v>
       </c>
       <c r="J266" t="n">
         <v>13.19999980926514</v>
@@ -8178,7 +8178,7 @@
         <v>60.90000152587891</v>
       </c>
       <c r="G267" t="n">
-        <v>1082.620483398438</v>
+        <v>1082.620361328125</v>
       </c>
       <c r="H267" t="n">
         <v>128.1499938964844</v>
@@ -8236,13 +8236,13 @@
         <v>58.45000076293945</v>
       </c>
       <c r="G269" t="n">
-        <v>1072.26025390625</v>
+        <v>1072.260131835938</v>
       </c>
       <c r="H269" t="n">
         <v>119.1500015258789</v>
       </c>
       <c r="I269" t="n">
-        <v>839.6952514648438</v>
+        <v>839.6953735351562</v>
       </c>
       <c r="J269" t="n">
         <v>12.5</v>
@@ -8265,13 +8265,13 @@
         <v>61.54999923706055</v>
       </c>
       <c r="G270" t="n">
-        <v>1069.5791015625</v>
+        <v>1069.579223632812</v>
       </c>
       <c r="H270" t="n">
         <v>125.0999984741211</v>
       </c>
       <c r="I270" t="n">
-        <v>856.8822021484375</v>
+        <v>856.8822631835938</v>
       </c>
       <c r="J270" t="n">
         <v>12.75</v>
@@ -8358,7 +8358,7 @@
         <v>121.4000015258789</v>
       </c>
       <c r="I273" t="n">
-        <v>817.8793334960938</v>
+        <v>817.87939453125</v>
       </c>
       <c r="J273" t="n">
         <v>11.75</v>
@@ -8387,7 +8387,7 @@
         <v>124.4499969482422</v>
       </c>
       <c r="I274" t="n">
-        <v>824.0843505859375</v>
+        <v>824.0844116210938</v>
       </c>
       <c r="J274" t="n">
         <v>12</v>
@@ -8410,13 +8410,13 @@
         <v>59.54999923706055</v>
       </c>
       <c r="G275" t="n">
-        <v>1047.791015625</v>
+        <v>1047.790893554688</v>
       </c>
       <c r="H275" t="n">
         <v>123.25</v>
       </c>
       <c r="I275" t="n">
-        <v>819.7999267578125</v>
+        <v>819.7998657226562</v>
       </c>
       <c r="J275" t="n">
         <v>11.64999961853027</v>
@@ -8468,7 +8468,7 @@
         <v>60.95000076293945</v>
       </c>
       <c r="G277" t="n">
-        <v>1070.578857421875</v>
+        <v>1070.578979492188</v>
       </c>
       <c r="H277" t="n">
         <v>127.3000030517578</v>
@@ -8526,7 +8526,7 @@
         <v>60.29999923706055</v>
       </c>
       <c r="G279" t="n">
-        <v>1055.72021484375</v>
+        <v>1055.720336914062</v>
       </c>
       <c r="H279" t="n">
         <v>127.5500030517578</v>
@@ -8555,13 +8555,13 @@
         <v>60.04999923706055</v>
       </c>
       <c r="G280" t="n">
-        <v>1080.598510742188</v>
+        <v>1080.598388671875</v>
       </c>
       <c r="H280" t="n">
         <v>123.3000030517578</v>
       </c>
       <c r="I280" t="n">
-        <v>822.0653076171875</v>
+        <v>822.0652465820312</v>
       </c>
       <c r="J280" t="n">
         <v>11.30000019073486</v>
@@ -8642,7 +8642,7 @@
         <v>61.40000152587891</v>
       </c>
       <c r="G283" t="n">
-        <v>1108.816284179688</v>
+        <v>1108.81640625</v>
       </c>
       <c r="H283" t="n">
         <v>127.0500030517578</v>
@@ -8671,7 +8671,7 @@
         <v>60.45000076293945</v>
       </c>
       <c r="G284" t="n">
-        <v>1097.092895507812</v>
+        <v>1097.093017578125</v>
       </c>
       <c r="H284" t="n">
         <v>123.6500015258789</v>
@@ -8735,7 +8735,7 @@
         <v>118.5500030517578</v>
       </c>
       <c r="I286" t="n">
-        <v>818.1256103515625</v>
+        <v>818.1255493164062</v>
       </c>
       <c r="J286" t="n">
         <v>10.39999961853027</v>
@@ -8764,7 +8764,7 @@
         <v>115.8000030517578</v>
       </c>
       <c r="I287" t="n">
-        <v>808.4732666015625</v>
+        <v>808.4733276367188</v>
       </c>
       <c r="J287" t="n">
         <v>10.05000019073486</v>
@@ -8793,7 +8793,7 @@
         <v>126.9499969482422</v>
       </c>
       <c r="I288" t="n">
-        <v>802.1698608398438</v>
+        <v>802.1697998046875</v>
       </c>
       <c r="J288" t="n">
         <v>10.10000038146973</v>
@@ -8822,7 +8822,7 @@
         <v>127.75</v>
       </c>
       <c r="I289" t="n">
-        <v>789.3165893554688</v>
+        <v>789.316650390625</v>
       </c>
       <c r="J289" t="n">
         <v>9.899999618530273</v>
@@ -8851,7 +8851,7 @@
         <v>130.6999969482422</v>
       </c>
       <c r="I290" t="n">
-        <v>789.8582763671875</v>
+        <v>789.8583374023438</v>
       </c>
       <c r="J290" t="n">
         <v>9.800000190734863</v>
@@ -8874,7 +8874,7 @@
         <v>58.90000152587891</v>
       </c>
       <c r="G291" t="n">
-        <v>1065.057983398438</v>
+        <v>1065.057861328125</v>
       </c>
       <c r="H291" t="n">
         <v>135.6999969482422</v>
@@ -8903,7 +8903,7 @@
         <v>58.54999923706055</v>
       </c>
       <c r="G292" t="n">
-        <v>1056.947021484375</v>
+        <v>1056.947143554688</v>
       </c>
       <c r="H292" t="n">
         <v>135.8000030517578</v>
@@ -9019,7 +9019,7 @@
         <v>58.95000076293945</v>
       </c>
       <c r="G296" t="n">
-        <v>1072.033081054688</v>
+        <v>1072.032958984375</v>
       </c>
       <c r="H296" t="n">
         <v>146.3500061035156</v>
@@ -9054,7 +9054,7 @@
         <v>147.25</v>
       </c>
       <c r="I297" t="n">
-        <v>835.9033813476562</v>
+        <v>835.9034423828125</v>
       </c>
       <c r="J297" t="n">
         <v>11.44999980926514</v>
@@ -9106,13 +9106,13 @@
         <v>53.70000076293945</v>
       </c>
       <c r="G299" t="n">
-        <v>1034.181884765625</v>
+        <v>1034.182006835938</v>
       </c>
       <c r="H299" t="n">
         <v>144.3000030517578</v>
       </c>
       <c r="I299" t="n">
-        <v>785.1306762695312</v>
+        <v>785.130615234375</v>
       </c>
       <c r="J299" t="n">
         <v>10.69999980926514</v>
@@ -9164,13 +9164,13 @@
         <v>54.70000076293945</v>
       </c>
       <c r="G301" t="n">
-        <v>1011.439208984375</v>
+        <v>1011.439270019531</v>
       </c>
       <c r="H301" t="n">
         <v>141.25</v>
       </c>
       <c r="I301" t="n">
-        <v>772.7698974609375</v>
+        <v>772.7698364257812</v>
       </c>
       <c r="J301" t="n">
         <v>10.55000019073486</v>
@@ -9222,13 +9222,13 @@
         <v>59.20000076293945</v>
       </c>
       <c r="G303" t="n">
-        <v>1000.238464355469</v>
+        <v>1000.238525390625</v>
       </c>
       <c r="H303" t="n">
         <v>148.0500030517578</v>
       </c>
       <c r="I303" t="n">
-        <v>771.5880126953125</v>
+        <v>771.5879516601562</v>
       </c>
       <c r="J303" t="n">
         <v>10.30000019073486</v>
@@ -9280,13 +9280,13 @@
         <v>58.09999847412109</v>
       </c>
       <c r="G305" t="n">
-        <v>1034.477294921875</v>
+        <v>1034.477172851562</v>
       </c>
       <c r="H305" t="n">
         <v>148.8999938964844</v>
       </c>
       <c r="I305" t="n">
-        <v>778.1376342773438</v>
+        <v>778.1377563476562</v>
       </c>
       <c r="J305" t="n">
         <v>10.30000019073486</v>
@@ -9309,13 +9309,13 @@
         <v>56.20000076293945</v>
       </c>
       <c r="G306" t="n">
-        <v>1021.390625</v>
+        <v>1021.390502929688</v>
       </c>
       <c r="H306" t="n">
         <v>148.1999969482422</v>
       </c>
       <c r="I306" t="n">
-        <v>773.0160522460938</v>
+        <v>773.01611328125</v>
       </c>
       <c r="J306" t="n">
         <v>9.949999809265137</v>
@@ -9344,7 +9344,7 @@
         <v>143.1000061035156</v>
       </c>
       <c r="I307" t="n">
-        <v>753.7608032226562</v>
+        <v>753.7608642578125</v>
       </c>
       <c r="J307" t="n">
         <v>9.850000381469727</v>
@@ -9402,7 +9402,7 @@
         <v>137.5</v>
       </c>
       <c r="I309" t="n">
-        <v>721.9971923828125</v>
+        <v>721.9971313476562</v>
       </c>
       <c r="J309" t="n">
         <v>9.149999618530273</v>
@@ -9431,7 +9431,7 @@
         <v>141.5500030517578</v>
       </c>
       <c r="I310" t="n">
-        <v>763.905517578125</v>
+        <v>763.9055786132812</v>
       </c>
       <c r="J310" t="n">
         <v>9.800000190734863</v>
@@ -9483,13 +9483,13 @@
         <v>56</v>
       </c>
       <c r="G312" t="n">
-        <v>1059.400756835938</v>
+        <v>1059.400634765625</v>
       </c>
       <c r="H312" t="n">
         <v>146.3999938964844</v>
       </c>
       <c r="I312" t="n">
-        <v>785.7708129882812</v>
+        <v>785.7708740234375</v>
       </c>
       <c r="J312" t="n">
         <v>10.39999961853027</v>
@@ -9541,13 +9541,13 @@
         <v>56.54999923706055</v>
       </c>
       <c r="G314" t="n">
-        <v>1063.944580078125</v>
+        <v>1063.944702148438</v>
       </c>
       <c r="H314" t="n">
         <v>151.3999938964844</v>
       </c>
       <c r="I314" t="n">
-        <v>792.2220458984375</v>
+        <v>792.2221069335938</v>
       </c>
       <c r="J314" t="n">
         <v>11.14999961853027</v>
@@ -9570,13 +9570,13 @@
         <v>56.29999923706055</v>
       </c>
       <c r="G315" t="n">
-        <v>1056.401733398438</v>
+        <v>1056.40185546875</v>
       </c>
       <c r="H315" t="n">
         <v>146.8000030517578</v>
       </c>
       <c r="I315" t="n">
-        <v>800.74169921875</v>
+        <v>800.7416381835938</v>
       </c>
       <c r="J315" t="n">
         <v>10.89999961853027</v>
@@ -9605,7 +9605,7 @@
         <v>157.3500061035156</v>
       </c>
       <c r="I316" t="n">
-        <v>804.1397094726562</v>
+        <v>804.1396484375</v>
       </c>
       <c r="J316" t="n">
         <v>12.55000019073486</v>
@@ -9634,7 +9634,7 @@
         <v>155.6999969482422</v>
       </c>
       <c r="I317" t="n">
-        <v>799.6090087890625</v>
+        <v>799.6089477539062</v>
       </c>
       <c r="J317" t="n">
         <v>12.14999961853027</v>
@@ -9657,13 +9657,13 @@
         <v>55.20000076293945</v>
       </c>
       <c r="G318" t="n">
-        <v>1070.3291015625</v>
+        <v>1070.328979492188</v>
       </c>
       <c r="H318" t="n">
         <v>165.5500030517578</v>
       </c>
       <c r="I318" t="n">
-        <v>838.8582153320312</v>
+        <v>838.858154296875</v>
       </c>
       <c r="J318" t="n">
         <v>12.80000019073486</v>
@@ -9721,7 +9721,7 @@
         <v>159.6499938964844</v>
       </c>
       <c r="I320" t="n">
-        <v>820.9818115234375</v>
+        <v>820.9818725585938</v>
       </c>
       <c r="J320" t="n">
         <v>12.39999961853027</v>
@@ -9779,7 +9779,7 @@
         <v>159.5500030517578</v>
       </c>
       <c r="I322" t="n">
-        <v>827.580810546875</v>
+        <v>827.5807495117188</v>
       </c>
       <c r="J322" t="n">
         <v>12.10000038146973</v>
@@ -9831,13 +9831,13 @@
         <v>54.25</v>
       </c>
       <c r="G324" t="n">
-        <v>1071.465087890625</v>
+        <v>1071.465209960938</v>
       </c>
       <c r="H324" t="n">
         <v>157.8500061035156</v>
       </c>
       <c r="I324" t="n">
-        <v>821.6712036132812</v>
+        <v>821.6712646484375</v>
       </c>
       <c r="J324" t="n">
         <v>11.80000019073486</v>
@@ -9860,13 +9860,13 @@
         <v>54.95000076293945</v>
       </c>
       <c r="G325" t="n">
-        <v>1079.666748046875</v>
+        <v>1079.666870117188</v>
       </c>
       <c r="H325" t="n">
         <v>157.8999938964844</v>
       </c>
       <c r="I325" t="n">
-        <v>825.6600952148438</v>
+        <v>825.6602172851562</v>
       </c>
       <c r="J325" t="n">
         <v>11.85000038146973</v>
@@ -9895,7 +9895,7 @@
         <v>153.6000061035156</v>
       </c>
       <c r="I326" t="n">
-        <v>816.9928588867188</v>
+        <v>816.992919921875</v>
       </c>
       <c r="J326" t="n">
         <v>11.89999961853027</v>
@@ -9918,7 +9918,7 @@
         <v>58.90000152587891</v>
       </c>
       <c r="G327" t="n">
-        <v>1080.121337890625</v>
+        <v>1080.121215820312</v>
       </c>
       <c r="H327" t="n">
         <v>160.6999969482422</v>
@@ -9947,7 +9947,7 @@
         <v>58.04999923706055</v>
       </c>
       <c r="G328" t="n">
-        <v>1099.864868164062</v>
+        <v>1099.86474609375</v>
       </c>
       <c r="H328" t="n">
         <v>157.5500030517578</v>
@@ -9976,13 +9976,13 @@
         <v>58.40000152587891</v>
       </c>
       <c r="G329" t="n">
-        <v>1109.202514648438</v>
+        <v>1109.20263671875</v>
       </c>
       <c r="H329" t="n">
         <v>154.9499969482422</v>
       </c>
       <c r="I329" t="n">
-        <v>833.736572265625</v>
+        <v>833.7366333007812</v>
       </c>
       <c r="J329" t="n">
         <v>12.14999961853027</v>
@@ -10005,13 +10005,13 @@
         <v>58.34999847412109</v>
       </c>
       <c r="G330" t="n">
-        <v>1099.68310546875</v>
+        <v>1099.682983398438</v>
       </c>
       <c r="H330" t="n">
         <v>153.75</v>
       </c>
       <c r="I330" t="n">
-        <v>825.807861328125</v>
+        <v>825.8079833984375</v>
       </c>
       <c r="J330" t="n">
         <v>11.89999961853027</v>
@@ -10034,13 +10034,13 @@
         <v>59.54999923706055</v>
       </c>
       <c r="G331" t="n">
-        <v>1112.360717773438</v>
+        <v>1112.360595703125</v>
       </c>
       <c r="H331" t="n">
         <v>154.5500030517578</v>
       </c>
       <c r="I331" t="n">
-        <v>882.3917846679688</v>
+        <v>882.3917236328125</v>
       </c>
       <c r="J331" t="n">
         <v>12.19999980926514</v>
@@ -10069,7 +10069,7 @@
         <v>153.6000061035156</v>
       </c>
       <c r="I332" t="n">
-        <v>868.258056640625</v>
+        <v>868.2581176757812</v>
       </c>
       <c r="J332" t="n">
         <v>12.39999961853027</v>
@@ -10092,13 +10092,13 @@
         <v>57.09999847412109</v>
       </c>
       <c r="G333" t="n">
-        <v>1123.220581054688</v>
+        <v>1123.220703125</v>
       </c>
       <c r="H333" t="n">
         <v>152.4499969482422</v>
       </c>
       <c r="I333" t="n">
-        <v>868.3565673828125</v>
+        <v>868.3566284179688</v>
       </c>
       <c r="J333" t="n">
         <v>12.14999961853027</v>
@@ -10185,7 +10185,7 @@
         <v>147.8500061035156</v>
       </c>
       <c r="I336" t="n">
-        <v>878.6982421875</v>
+        <v>878.6983032226562</v>
       </c>
       <c r="J336" t="n">
         <v>11.85000038146973</v>
@@ -10208,7 +10208,7 @@
         <v>58.09999847412109</v>
       </c>
       <c r="G337" t="n">
-        <v>1128.8779296875</v>
+        <v>1128.877807617188</v>
       </c>
       <c r="H337" t="n">
         <v>146.6000061035156</v>
@@ -10237,7 +10237,7 @@
         <v>60.59999847412109</v>
       </c>
       <c r="G338" t="n">
-        <v>1131.1044921875</v>
+        <v>1131.104370117188</v>
       </c>
       <c r="H338" t="n">
         <v>144.1499938964844</v>
@@ -10266,7 +10266,7 @@
         <v>59.54999923706055</v>
       </c>
       <c r="G339" t="n">
-        <v>1114.99609375</v>
+        <v>1114.996215820312</v>
       </c>
       <c r="H339" t="n">
         <v>140.8999938964844</v>
@@ -10359,7 +10359,7 @@
         <v>137.4499969482422</v>
       </c>
       <c r="I342" t="n">
-        <v>884.16455078125</v>
+        <v>884.1646118164062</v>
       </c>
       <c r="J342" t="n">
         <v>11.44999980926514</v>
@@ -10388,7 +10388,7 @@
         <v>134.6499938964844</v>
       </c>
       <c r="I343" t="n">
-        <v>881.4067993164062</v>
+        <v>881.40673828125</v>
       </c>
       <c r="J343" t="n">
         <v>11.5</v>
@@ -10411,13 +10411,13 @@
         <v>59.79999923706055</v>
       </c>
       <c r="G344" t="n">
-        <v>1115.336791992188</v>
+        <v>1115.3369140625</v>
       </c>
       <c r="H344" t="n">
         <v>139.6499938964844</v>
       </c>
       <c r="I344" t="n">
-        <v>899.430908203125</v>
+        <v>899.4308471679688</v>
       </c>
       <c r="J344" t="n">
         <v>12.94999980926514</v>
@@ -10446,7 +10446,7 @@
         <v>138.6000061035156</v>
       </c>
       <c r="I345" t="n">
-        <v>881.308349609375</v>
+        <v>881.3082885742188</v>
       </c>
       <c r="J345" t="n">
         <v>12.10000038146973</v>
@@ -10527,13 +10527,13 @@
         <v>61.09999847412109</v>
       </c>
       <c r="G348" t="n">
-        <v>1145.349609375</v>
+        <v>1145.349731445312</v>
       </c>
       <c r="H348" t="n">
         <v>139.6499938964844</v>
       </c>
       <c r="I348" t="n">
-        <v>897.3624267578125</v>
+        <v>897.3624877929688</v>
       </c>
       <c r="J348" t="n">
         <v>13.30000019073486</v>
@@ -10620,7 +10620,7 @@
         <v>133.9499969482422</v>
       </c>
       <c r="I351" t="n">
-        <v>904.7001953125</v>
+        <v>904.7002563476562</v>
       </c>
       <c r="J351" t="n">
         <v>12.94999980926514</v>
@@ -10649,7 +10649,7 @@
         <v>134.6000061035156</v>
       </c>
       <c r="I352" t="n">
-        <v>931.194580078125</v>
+        <v>931.1946411132812</v>
       </c>
       <c r="J352" t="n">
         <v>13.14999961853027</v>
@@ -10736,7 +10736,7 @@
         <v>136.0500030517578</v>
       </c>
       <c r="I355" t="n">
-        <v>942.6196899414062</v>
+        <v>942.61962890625</v>
       </c>
       <c r="J355" t="n">
         <v>14.75</v>
@@ -10765,7 +10765,7 @@
         <v>137.0500030517578</v>
       </c>
       <c r="I356" t="n">
-        <v>935.3804931640625</v>
+        <v>935.3805541992188</v>
       </c>
       <c r="J356" t="n">
         <v>14.05000019073486</v>
@@ -10794,7 +10794,7 @@
         <v>137.1999969482422</v>
       </c>
       <c r="I357" t="n">
-        <v>927.4026489257812</v>
+        <v>927.402587890625</v>
       </c>
       <c r="J357" t="n">
         <v>13.94999980926514</v>
@@ -10817,7 +10817,7 @@
         <v>63.54999923706055</v>
       </c>
       <c r="G358" t="n">
-        <v>1128.786865234375</v>
+        <v>1128.786987304688</v>
       </c>
       <c r="H358" t="n">
         <v>139.3999938964844</v>
@@ -10846,7 +10846,7 @@
         <v>64.65000152587891</v>
       </c>
       <c r="G359" t="n">
-        <v>1145.46337890625</v>
+        <v>1145.463256835938</v>
       </c>
       <c r="H359" t="n">
         <v>143.8500061035156</v>
@@ -10881,7 +10881,7 @@
         <v>149.9499969482422</v>
       </c>
       <c r="I360" t="n">
-        <v>950.980712890625</v>
+        <v>950.9806518554688</v>
       </c>
       <c r="J360" t="n">
         <v>15.89999961853027</v>
@@ -10904,7 +10904,7 @@
         <v>62.95000076293945</v>
       </c>
       <c r="G361" t="n">
-        <v>1159.86767578125</v>
+        <v>1159.867797851562</v>
       </c>
       <c r="H361" t="n">
         <v>149.4499969482422</v>
@@ -10933,7 +10933,7 @@
         <v>65.59999847412109</v>
       </c>
       <c r="G362" t="n">
-        <v>1171.159545898438</v>
+        <v>1171.159423828125</v>
       </c>
       <c r="H362" t="n">
         <v>151.5500030517578</v>
@@ -11049,7 +11049,7 @@
         <v>65.25</v>
       </c>
       <c r="G366" t="n">
-        <v>1152.120239257812</v>
+        <v>1152.1201171875</v>
       </c>
       <c r="H366" t="n">
         <v>145.1499938964844</v>
@@ -11107,7 +11107,7 @@
         <v>63.29999923706055</v>
       </c>
       <c r="G368" t="n">
-        <v>1133.967163085938</v>
+        <v>1133.96728515625</v>
       </c>
       <c r="H368" t="n">
         <v>140.1999969482422</v>
@@ -11258,7 +11258,7 @@
         <v>137.1000061035156</v>
       </c>
       <c r="I373" t="n">
-        <v>939.61181640625</v>
+        <v>939.6118774414062</v>
       </c>
       <c r="J373" t="n">
         <v>14.64999961853027</v>
@@ -11368,7 +11368,7 @@
         <v>63.29999923706055</v>
       </c>
       <c r="G377" t="n">
-        <v>1242.794921875</v>
+        <v>1242.794799804688</v>
       </c>
       <c r="H377" t="n">
         <v>135.6499938964844</v>
@@ -11403,7 +11403,7 @@
         <v>136.8000030517578</v>
       </c>
       <c r="I378" t="n">
-        <v>948.6079711914062</v>
+        <v>948.6080322265625</v>
       </c>
       <c r="J378" t="n">
         <v>15.35000038146973</v>
@@ -11629,7 +11629,7 @@
         <v>58.79999923706055</v>
       </c>
       <c r="G386" t="n">
-        <v>1249.834594726562</v>
+        <v>1249.834716796875</v>
       </c>
       <c r="H386" t="n">
         <v>163.0500030517578</v>
@@ -11751,7 +11751,7 @@
         <v>178.6000061035156</v>
       </c>
       <c r="I390" t="n">
-        <v>955.478759765625</v>
+        <v>955.4788208007812</v>
       </c>
       <c r="J390" t="n">
         <v>16.54999923706055</v>
@@ -11774,13 +11774,13 @@
         <v>58.45000076293945</v>
       </c>
       <c r="G391" t="n">
-        <v>1244.468627929688</v>
+        <v>1244.468505859375</v>
       </c>
       <c r="H391" t="n">
         <v>184.8500061035156</v>
       </c>
       <c r="I391" t="n">
-        <v>947.7183227539062</v>
+        <v>947.7183837890625</v>
       </c>
       <c r="J391" t="n">
         <v>16.10000038146973</v>
@@ -11925,7 +11925,7 @@
         <v>199.1499938964844</v>
       </c>
       <c r="I396" t="n">
-        <v>968.0339965820312</v>
+        <v>968.033935546875</v>
       </c>
       <c r="J396" t="n">
         <v>19.04999923706055</v>
@@ -11948,7 +11948,7 @@
         <v>59.04999923706055</v>
       </c>
       <c r="G397" t="n">
-        <v>1242.499389648438</v>
+        <v>1242.49951171875</v>
       </c>
       <c r="H397" t="n">
         <v>210.0500030517578</v>
@@ -12006,7 +12006,7 @@
         <v>60.04999923706055</v>
       </c>
       <c r="G399" t="n">
-        <v>1243.1640625</v>
+        <v>1243.163940429688</v>
       </c>
       <c r="H399" t="n">
         <v>191.4499969482422</v>
@@ -12035,13 +12035,13 @@
         <v>62</v>
       </c>
       <c r="G400" t="n">
-        <v>1248.702514648438</v>
+        <v>1248.702392578125</v>
       </c>
       <c r="H400" t="n">
         <v>175.8500061035156</v>
       </c>
       <c r="I400" t="n">
-        <v>983.5549926757812</v>
+        <v>983.554931640625</v>
       </c>
       <c r="J400" t="n">
         <v>17.5</v>
@@ -12064,7 +12064,7 @@
         <v>62.20000076293945</v>
       </c>
       <c r="G401" t="n">
-        <v>1253.970092773438</v>
+        <v>1253.969970703125</v>
       </c>
       <c r="H401" t="n">
         <v>170</v>
@@ -12122,13 +12122,13 @@
         <v>62.54999923706055</v>
       </c>
       <c r="G403" t="n">
-        <v>1267.754638671875</v>
+        <v>1267.754516601562</v>
       </c>
       <c r="H403" t="n">
         <v>163</v>
       </c>
       <c r="I403" t="n">
-        <v>956.1214599609375</v>
+        <v>956.1213989257812</v>
       </c>
       <c r="J403" t="n">
         <v>16.75</v>
@@ -12151,13 +12151,13 @@
         <v>60.95000076293945</v>
       </c>
       <c r="G404" t="n">
-        <v>1249.465454101562</v>
+        <v>1249.465576171875</v>
       </c>
       <c r="H404" t="n">
         <v>158.0500030517578</v>
       </c>
       <c r="I404" t="n">
-        <v>1023.296569824219</v>
+        <v>1023.296447753906</v>
       </c>
       <c r="J404" t="n">
         <v>16.54999923706055</v>
@@ -12180,7 +12180,7 @@
         <v>63.5</v>
       </c>
       <c r="G405" t="n">
-        <v>1258.720703125</v>
+        <v>1258.720825195312</v>
       </c>
       <c r="H405" t="n">
         <v>160.6000061035156</v>
@@ -12206,7 +12206,7 @@
         <v>16.75</v>
       </c>
       <c r="E406" t="n">
-        <v>247.9318237304688</v>
+        <v>247.9318389892578</v>
       </c>
       <c r="F406" t="n">
         <v>63.70000076293945</v>
@@ -12218,7 +12218,7 @@
         <v>162.3500061035156</v>
       </c>
       <c r="I406" t="n">
-        <v>1040.003662109375</v>
+        <v>1040.003784179688</v>
       </c>
       <c r="J406" t="n">
         <v>16.35000038146973</v>
@@ -12270,7 +12270,7 @@
         <v>16.89999961853027</v>
       </c>
       <c r="E408" t="n">
-        <v>223.7761688232422</v>
+        <v>223.7761535644531</v>
       </c>
       <c r="F408" t="n">
         <v>67.84999847412109</v>
@@ -12282,7 +12282,7 @@
         <v>178.9499969482422</v>
       </c>
       <c r="I408" t="n">
-        <v>1023.593200683594</v>
+        <v>1023.593078613281</v>
       </c>
       <c r="J408" t="n">
         <v>17.29999923706055</v>
@@ -12302,7 +12302,7 @@
         <v>16.70000076293945</v>
       </c>
       <c r="E409" t="n">
-        <v>212.6197357177734</v>
+        <v>212.6197204589844</v>
       </c>
       <c r="F409" t="n">
         <v>66.94999694824219</v>
@@ -12314,7 +12314,7 @@
         <v>177.3000030517578</v>
       </c>
       <c r="I409" t="n">
-        <v>1017.513244628906</v>
+        <v>1017.513305664062</v>
       </c>
       <c r="J409" t="n">
         <v>17.29999923706055</v>
@@ -12334,7 +12334,7 @@
         <v>16.64999961853027</v>
       </c>
       <c r="E410" t="n">
-        <v>213.6656494140625</v>
+        <v>213.6656646728516</v>
       </c>
       <c r="F410" t="n">
         <v>67.5</v>
@@ -12346,7 +12346,7 @@
         <v>177.25</v>
       </c>
       <c r="I410" t="n">
-        <v>988.15185546875</v>
+        <v>988.1519165039062</v>
       </c>
       <c r="J410" t="n">
         <v>17.35000038146973</v>
@@ -12398,7 +12398,7 @@
         <v>16.64999961853027</v>
       </c>
       <c r="E412" t="n">
-        <v>219.3932952880859</v>
+        <v>219.3932800292969</v>
       </c>
       <c r="F412" t="n">
         <v>69.40000152587891</v>
@@ -12410,7 +12410,7 @@
         <v>184.5</v>
       </c>
       <c r="I412" t="n">
-        <v>991.1671142578125</v>
+        <v>991.1670532226562</v>
       </c>
       <c r="J412" t="n">
         <v>18.25</v>
@@ -12462,7 +12462,7 @@
         <v>16.5</v>
       </c>
       <c r="E414" t="n">
-        <v>232.5917510986328</v>
+        <v>232.5917358398438</v>
       </c>
       <c r="F414" t="n">
         <v>68.34999847412109</v>
@@ -12506,7 +12506,7 @@
         <v>186.8999938964844</v>
       </c>
       <c r="I415" t="n">
-        <v>1000.114013671875</v>
+        <v>1000.113952636719</v>
       </c>
       <c r="J415" t="n">
         <v>19</v>
@@ -12686,7 +12686,7 @@
         <v>18.60000038146973</v>
       </c>
       <c r="E421" t="n">
-        <v>249.1769714355469</v>
+        <v>249.1769866943359</v>
       </c>
       <c r="F421" t="n">
         <v>70.94999694824219</v>
@@ -12730,7 +12730,7 @@
         <v>173.6999969482422</v>
       </c>
       <c r="I422" t="n">
-        <v>954.5890502929688</v>
+        <v>954.5889892578125</v>
       </c>
       <c r="J422" t="n">
         <v>18.39999961853027</v>
@@ -12750,7 +12750,7 @@
         <v>17.35000038146973</v>
       </c>
       <c r="E423" t="n">
-        <v>239.2656860351562</v>
+        <v>239.2656707763672</v>
       </c>
       <c r="F423" t="n">
         <v>68.55000305175781</v>
@@ -12922,7 +12922,7 @@
         <v>175.1499938964844</v>
       </c>
       <c r="I428" t="n">
-        <v>941.0453491210938</v>
+        <v>941.0452880859375</v>
       </c>
       <c r="J428" t="n">
         <v>19</v>
@@ -12942,7 +12942,7 @@
         <v>19.14999961853027</v>
       </c>
       <c r="E429" t="n">
-        <v>226.9139099121094</v>
+        <v>226.9139251708984</v>
       </c>
       <c r="F429" t="n">
         <v>68.05000305175781</v>
@@ -12986,7 +12986,7 @@
         <v>173.5500030517578</v>
       </c>
       <c r="I430" t="n">
-        <v>939.2164306640625</v>
+        <v>939.2163696289062</v>
       </c>
       <c r="J430" t="n">
         <v>18.95000076293945</v>
@@ -13038,7 +13038,7 @@
         <v>19.79999923706055</v>
       </c>
       <c r="E432" t="n">
-        <v>226.4656677246094</v>
+        <v>226.4656829833984</v>
       </c>
       <c r="F432" t="n">
         <v>63.95000076293945</v>
@@ -13050,7 +13050,7 @@
         <v>172.6499938964844</v>
       </c>
       <c r="I432" t="n">
-        <v>956.4180297851562</v>
+        <v>956.41796875</v>
       </c>
       <c r="J432" t="n">
         <v>19.20000076293945</v>
@@ -13082,7 +13082,7 @@
         <v>170.8999938964844</v>
       </c>
       <c r="I433" t="n">
-        <v>946.4826049804688</v>
+        <v>946.4825439453125</v>
       </c>
       <c r="J433" t="n">
         <v>19.14999961853027</v>
@@ -13146,7 +13146,7 @@
         <v>174.3500061035156</v>
       </c>
       <c r="I435" t="n">
-        <v>943.2695922851562</v>
+        <v>943.2696533203125</v>
       </c>
       <c r="J435" t="n">
         <v>19.25</v>
@@ -13166,7 +13166,7 @@
         <v>20.89999961853027</v>
       </c>
       <c r="E436" t="n">
-        <v>223.7761688232422</v>
+        <v>223.7761535644531</v>
       </c>
       <c r="F436" t="n">
         <v>68.05000305175781</v>
@@ -13178,7 +13178,7 @@
         <v>170.3999938964844</v>
       </c>
       <c r="I436" t="n">
-        <v>931.5546875</v>
+        <v>931.5547485351562</v>
       </c>
       <c r="J436" t="n">
         <v>18.79999923706055</v>
@@ -13198,7 +13198,7 @@
         <v>21.04999923706055</v>
       </c>
       <c r="E437" t="n">
-        <v>224.5232391357422</v>
+        <v>224.5232543945312</v>
       </c>
       <c r="F437" t="n">
         <v>72.84999847412109</v>
@@ -13274,7 +13274,7 @@
         <v>171.25</v>
       </c>
       <c r="I439" t="n">
-        <v>943.46728515625</v>
+        <v>943.4673461914062</v>
       </c>
       <c r="J439" t="n">
         <v>17.85000038146973</v>
@@ -13294,7 +13294,7 @@
         <v>19.5</v>
       </c>
       <c r="E440" t="n">
-        <v>219.2936706542969</v>
+        <v>219.2936553955078</v>
       </c>
       <c r="F440" t="n">
         <v>71.65000152587891</v>
@@ -13306,7 +13306,7 @@
         <v>170.8500061035156</v>
       </c>
       <c r="I440" t="n">
-        <v>970.3078002929688</v>
+        <v>970.3077392578125</v>
       </c>
       <c r="J440" t="n">
         <v>17.79999923706055</v>
@@ -13338,7 +13338,7 @@
         <v>170.5</v>
       </c>
       <c r="I441" t="n">
-        <v>975.2506713867188</v>
+        <v>975.250732421875</v>
       </c>
       <c r="J441" t="n">
         <v>18.20000076293945</v>
@@ -13390,7 +13390,7 @@
         <v>20.29999923706055</v>
       </c>
       <c r="E443" t="n">
-        <v>223.6765594482422</v>
+        <v>223.6765747070312</v>
       </c>
       <c r="F443" t="n">
         <v>78.75</v>
@@ -13434,7 +13434,7 @@
         <v>170.75</v>
       </c>
       <c r="I444" t="n">
-        <v>1058.243286132812</v>
+        <v>1058.243408203125</v>
       </c>
       <c r="J444" t="n">
         <v>18.39999961853027</v>
@@ -13486,7 +13486,7 @@
         <v>19.70000076293945</v>
       </c>
       <c r="E446" t="n">
-        <v>215.1598052978516</v>
+        <v>215.1598205566406</v>
       </c>
       <c r="F446" t="n">
         <v>77.94999694824219</v>
@@ -13518,7 +13518,7 @@
         <v>19.89999961853027</v>
       </c>
       <c r="E447" t="n">
-        <v>213.3668212890625</v>
+        <v>213.3668060302734</v>
       </c>
       <c r="F447" t="n">
         <v>77.84999847412109</v>
@@ -13550,7 +13550,7 @@
         <v>19.39999961853027</v>
       </c>
       <c r="E448" t="n">
-        <v>213.3668212890625</v>
+        <v>213.3668060302734</v>
       </c>
       <c r="F448" t="n">
         <v>76.80000305175781</v>
@@ -13594,7 +13594,7 @@
         <v>169.75</v>
       </c>
       <c r="I449" t="n">
-        <v>995.3192138671875</v>
+        <v>995.3191528320312</v>
       </c>
       <c r="J449" t="n">
         <v>16.70000076293945</v>
@@ -13658,7 +13658,7 @@
         <v>159.0500030517578</v>
       </c>
       <c r="I451" t="n">
-        <v>1007.726135253906</v>
+        <v>1007.72607421875</v>
       </c>
       <c r="J451" t="n">
         <v>16.5</v>
@@ -13678,7 +13678,7 @@
         <v>18.39999961853027</v>
       </c>
       <c r="E452" t="n">
-        <v>222.032958984375</v>
+        <v>222.0329742431641</v>
       </c>
       <c r="F452" t="n">
         <v>68.75</v>
@@ -13690,7 +13690,7 @@
         <v>162.9499969482422</v>
       </c>
       <c r="I452" t="n">
-        <v>1005.353454589844</v>
+        <v>1005.353515625</v>
       </c>
       <c r="J452" t="n">
         <v>16.79999923706055</v>
@@ -13722,7 +13722,7 @@
         <v>168</v>
       </c>
       <c r="I453" t="n">
-        <v>1007.577880859375</v>
+        <v>1007.577819824219</v>
       </c>
       <c r="J453" t="n">
         <v>16.95000076293945</v>
@@ -13806,7 +13806,7 @@
         <v>18.04999923706055</v>
       </c>
       <c r="E456" t="n">
-        <v>216.5045776367188</v>
+        <v>216.5045623779297</v>
       </c>
       <c r="F456" t="n">
         <v>67.59999847412109</v>
@@ -13818,7 +13818,7 @@
         <v>176.9499969482422</v>
       </c>
       <c r="I456" t="n">
-        <v>988.6956787109375</v>
+        <v>988.6956176757812</v>
       </c>
       <c r="J456" t="n">
         <v>18.25</v>
@@ -13882,7 +13882,7 @@
         <v>183.3500061035156</v>
       </c>
       <c r="I458" t="n">
-        <v>1032.3916015625</v>
+        <v>1032.391723632812</v>
       </c>
       <c r="J458" t="n">
         <v>19.29999923706055</v>
@@ -13914,7 +13914,7 @@
         <v>185.5500030517578</v>
       </c>
       <c r="I459" t="n">
-        <v>1038.817626953125</v>
+        <v>1038.817504882812</v>
       </c>
       <c r="J459" t="n">
         <v>20.70000076293945</v>
@@ -13946,7 +13946,7 @@
         <v>179.1000061035156</v>
       </c>
       <c r="I460" t="n">
-        <v>1039.509521484375</v>
+        <v>1039.509399414062</v>
       </c>
       <c r="J460" t="n">
         <v>20.45000076293945</v>
@@ -13978,7 +13978,7 @@
         <v>178.1000061035156</v>
       </c>
       <c r="I461" t="n">
-        <v>1038.174926757812</v>
+        <v>1038.1748046875</v>
       </c>
       <c r="J461" t="n">
         <v>21.20000076293945</v>
@@ -14030,7 +14030,7 @@
         <v>19.10000038146973</v>
       </c>
       <c r="E463" t="n">
-        <v>223.8757934570312</v>
+        <v>223.8757781982422</v>
       </c>
       <c r="F463" t="n">
         <v>76</v>
@@ -14170,7 +14170,7 @@
         <v>182.75</v>
       </c>
       <c r="I467" t="n">
-        <v>1104.608520507812</v>
+        <v>1104.608642578125</v>
       </c>
       <c r="J467" t="n">
         <v>22.10000038146973</v>
@@ -14254,7 +14254,7 @@
         <v>20.14999961853027</v>
       </c>
       <c r="E470" t="n">
-        <v>220.389404296875</v>
+        <v>220.3893890380859</v>
       </c>
       <c r="F470" t="n">
         <v>82.40000152587891</v>
@@ -14266,7 +14266,7 @@
         <v>174.25</v>
       </c>
       <c r="I470" t="n">
-        <v>1095.661743164062</v>
+        <v>1095.661865234375</v>
       </c>
       <c r="J470" t="n">
         <v>21.35000038146973</v>
@@ -14298,7 +14298,7 @@
         <v>173.4499969482422</v>
       </c>
       <c r="I471" t="n">
-        <v>1078.55908203125</v>
+        <v>1078.558959960938</v>
       </c>
       <c r="J471" t="n">
         <v>20.89999961853027</v>
@@ -14330,7 +14330,7 @@
         <v>177.8999938964844</v>
       </c>
       <c r="I472" t="n">
-        <v>1087.851928710938</v>
+        <v>1087.851806640625</v>
       </c>
       <c r="J472" t="n">
         <v>20.89999961853027</v>
@@ -14426,7 +14426,7 @@
         <v>194.0500030517578</v>
       </c>
       <c r="I475" t="n">
-        <v>1081.030517578125</v>
+        <v>1081.030639648438</v>
       </c>
       <c r="J475" t="n">
         <v>20.85000038146973</v>
@@ -14458,7 +14458,7 @@
         <v>192.6999969482422</v>
       </c>
       <c r="I476" t="n">
-        <v>1102.8291015625</v>
+        <v>1102.829223632812</v>
       </c>
       <c r="J476" t="n">
         <v>20.89999961853027</v>
@@ -14522,7 +14522,7 @@
         <v>212.3999938964844</v>
       </c>
       <c r="I478" t="n">
-        <v>1103.867065429688</v>
+        <v>1103.8671875</v>
       </c>
       <c r="J478" t="n">
         <v>23.20000076293945</v>
@@ -14586,7 +14586,7 @@
         <v>214.75</v>
       </c>
       <c r="I480" t="n">
-        <v>1130.9052734375</v>
+        <v>1130.905151367188</v>
       </c>
       <c r="J480" t="n">
         <v>23.95000076293945</v>
@@ -14638,7 +14638,7 @@
         <v>20.54999923706055</v>
       </c>
       <c r="E482" t="n">
-        <v>239.6143188476562</v>
+        <v>239.6143341064453</v>
       </c>
       <c r="F482" t="n">
         <v>86.65000152587891</v>
@@ -14650,7 +14650,7 @@
         <v>211.6499938964844</v>
       </c>
       <c r="I482" t="n">
-        <v>1134.167602539062</v>
+        <v>1134.167724609375</v>
       </c>
       <c r="J482" t="n">
         <v>23.20000076293945</v>
@@ -14734,7 +14734,7 @@
         <v>20.35000038146973</v>
       </c>
       <c r="E485" t="n">
-        <v>236.7255859375</v>
+        <v>236.7256011962891</v>
       </c>
       <c r="F485" t="n">
         <v>85.90000152587891</v>
@@ -14746,7 +14746,7 @@
         <v>209.75</v>
       </c>
       <c r="I485" t="n">
-        <v>1167.9775390625</v>
+        <v>1167.977661132812</v>
       </c>
       <c r="J485" t="n">
         <v>23.60000038146973</v>
@@ -14766,7 +14766,7 @@
         <v>21.5</v>
       </c>
       <c r="E486" t="n">
-        <v>239.2158660888672</v>
+        <v>239.2158813476562</v>
       </c>
       <c r="F486" t="n">
         <v>86.19999694824219</v>
@@ -14862,7 +14862,7 @@
         <v>21.64999961853027</v>
       </c>
       <c r="E489" t="n">
-        <v>237.0742492675781</v>
+        <v>237.0742340087891</v>
       </c>
       <c r="F489" t="n">
         <v>85.90000152587891</v>
@@ -14874,7 +14874,7 @@
         <v>193.3999938964844</v>
       </c>
       <c r="I489" t="n">
-        <v>1275.042602539062</v>
+        <v>1275.042724609375</v>
       </c>
       <c r="J489" t="n">
         <v>22.70000076293945</v>
@@ -14894,7 +14894,7 @@
         <v>22.04999923706055</v>
       </c>
       <c r="E490" t="n">
-        <v>235.8291015625</v>
+        <v>235.8291168212891</v>
       </c>
       <c r="F490" t="n">
         <v>86.09999847412109</v>
@@ -14958,7 +14958,7 @@
         <v>21.64999961853027</v>
       </c>
       <c r="E492" t="n">
-        <v>233.0897979736328</v>
+        <v>233.0898132324219</v>
       </c>
       <c r="F492" t="n">
         <v>88.90000152587891</v>
@@ -15002,7 +15002,7 @@
         <v>190.8000030517578</v>
       </c>
       <c r="I493" t="n">
-        <v>1333.122802734375</v>
+        <v>1333.122680664062</v>
       </c>
       <c r="J493" t="n">
         <v>22.35000038146973</v>
@@ -15022,7 +15022,7 @@
         <v>21.20000076293945</v>
       </c>
       <c r="E494" t="n">
-        <v>232.0438842773438</v>
+        <v>232.0438690185547</v>
       </c>
       <c r="F494" t="n">
         <v>87.34999847412109</v>
@@ -15034,7 +15034,7 @@
         <v>209.8000030517578</v>
       </c>
       <c r="I494" t="n">
-        <v>1332.77685546875</v>
+        <v>1332.776733398438</v>
       </c>
       <c r="J494" t="n">
         <v>23.29999923706055</v>
@@ -15066,7 +15066,7 @@
         <v>211.8000030517578</v>
       </c>
       <c r="I495" t="n">
-        <v>1402.621215820312</v>
+        <v>1402.62109375</v>
       </c>
       <c r="J495" t="n">
         <v>23.95000076293945</v>
@@ -15162,7 +15162,7 @@
         <v>231.5500030517578</v>
       </c>
       <c r="I498" t="n">
-        <v>1382.1572265625</v>
+        <v>1382.157104492188</v>
       </c>
       <c r="J498" t="n">
         <v>30.39999961853027</v>
@@ -15214,7 +15214,7 @@
         <v>24.79999923706055</v>
       </c>
       <c r="E500" t="n">
-        <v>241.4571228027344</v>
+        <v>241.4571075439453</v>
       </c>
       <c r="F500" t="n">
         <v>100.5500030517578</v>
@@ -15246,7 +15246,7 @@
         <v>24.10000038146973</v>
       </c>
       <c r="E501" t="n">
-        <v>241.2080841064453</v>
+        <v>241.2080993652344</v>
       </c>
       <c r="F501" t="n">
         <v>99.5</v>
@@ -15278,7 +15278,7 @@
         <v>24.89999961853027</v>
       </c>
       <c r="E502" t="n">
-        <v>240.0127716064453</v>
+        <v>240.0127563476562</v>
       </c>
       <c r="F502" t="n">
         <v>119.4000015258789</v>
@@ -15354,7 +15354,7 @@
         <v>238.4499969482422</v>
       </c>
       <c r="I504" t="n">
-        <v>1496.3896484375</v>
+        <v>1496.389526367188</v>
       </c>
       <c r="J504" t="n">
         <v>30.89999961853027</v>
@@ -15386,7 +15386,7 @@
         <v>232.6499938964844</v>
       </c>
       <c r="I505" t="n">
-        <v>1442.313232421875</v>
+        <v>1442.313354492188</v>
       </c>
       <c r="J505" t="n">
         <v>30.79999923706055</v>
@@ -15482,7 +15482,7 @@
         <v>218.8999938964844</v>
       </c>
       <c r="I508" t="n">
-        <v>1424.419555664062</v>
+        <v>1424.419677734375</v>
       </c>
       <c r="J508" t="n">
         <v>29.75</v>
@@ -15630,7 +15630,7 @@
         <v>23.85000038146973</v>
       </c>
       <c r="E513" t="n">
-        <v>250.0236663818359</v>
+        <v>250.023681640625</v>
       </c>
       <c r="F513" t="n">
         <v>117</v>
@@ -15642,7 +15642,7 @@
         <v>227.9499969482422</v>
       </c>
       <c r="I513" t="n">
-        <v>1413.940551757812</v>
+        <v>1413.9404296875</v>
       </c>
       <c r="J513" t="n">
         <v>30.10000038146973</v>
@@ -15674,7 +15674,7 @@
         <v>231.5500030517578</v>
       </c>
       <c r="I514" t="n">
-        <v>1382.997436523438</v>
+        <v>1382.99755859375</v>
       </c>
       <c r="J514" t="n">
         <v>29.95000076293945</v>
@@ -15758,7 +15758,7 @@
         <v>24</v>
       </c>
       <c r="E517" t="n">
-        <v>252.8127746582031</v>
+        <v>252.8127899169922</v>
       </c>
       <c r="F517" t="n">
         <v>113.1500015258789</v>
@@ -15790,7 +15790,7 @@
         <v>26</v>
       </c>
       <c r="E518" t="n">
-        <v>287.9754943847656</v>
+        <v>287.9754638671875</v>
       </c>
       <c r="F518" t="n">
         <v>114.4000015258789</v>
@@ -15950,7 +15950,7 @@
         <v>23.45000076293945</v>
       </c>
       <c r="E523" t="n">
-        <v>270.3941345214844</v>
+        <v>270.3941650390625</v>
       </c>
       <c r="F523" t="n">
         <v>106.25</v>
@@ -15982,7 +15982,7 @@
         <v>23.64999961853027</v>
       </c>
       <c r="E524" t="n">
-        <v>271.6890869140625</v>
+        <v>271.6890563964844</v>
       </c>
       <c r="F524" t="n">
         <v>105.4000015258789</v>
@@ -16058,7 +16058,7 @@
         <v>234.3500061035156</v>
       </c>
       <c r="I526" t="n">
-        <v>1455.36279296875</v>
+        <v>1455.362670898438</v>
       </c>
       <c r="J526" t="n">
         <v>26.75</v>
@@ -16090,7 +16090,7 @@
         <v>225.25</v>
       </c>
       <c r="I527" t="n">
-        <v>1455.264038085938</v>
+        <v>1455.263916015625</v>
       </c>
       <c r="J527" t="n">
         <v>26.20000076293945</v>
@@ -16122,7 +16122,7 @@
         <v>242.8500061035156</v>
       </c>
       <c r="I528" t="n">
-        <v>1441.621215820312</v>
+        <v>1441.621337890625</v>
       </c>
       <c r="J528" t="n">
         <v>26.95000076293945</v>
@@ -16142,7 +16142,7 @@
         <v>24.85000038146973</v>
       </c>
       <c r="E529" t="n">
-        <v>280.604248046875</v>
+        <v>280.6042785644531</v>
       </c>
       <c r="F529" t="n">
         <v>119</v>
@@ -16154,7 +16154,7 @@
         <v>241.1999969482422</v>
       </c>
       <c r="I529" t="n">
-        <v>1438.062377929688</v>
+        <v>1438.062255859375</v>
       </c>
       <c r="J529" t="n">
         <v>26.45000076293945</v>
@@ -16346,7 +16346,7 @@
         <v>212.1000061035156</v>
       </c>
       <c r="I535" t="n">
-        <v>1397.628662109375</v>
+        <v>1397.628784179688</v>
       </c>
       <c r="J535" t="n">
         <v>23.45000076293945</v>
@@ -16398,7 +16398,7 @@
         <v>22.64999961853027</v>
       </c>
       <c r="E537" t="n">
-        <v>316.6634521484375</v>
+        <v>316.6634216308594</v>
       </c>
       <c r="F537" t="n">
         <v>102.4499969482422</v>
@@ -16462,7 +16462,7 @@
         <v>22</v>
       </c>
       <c r="E539" t="n">
-        <v>320.4486999511719</v>
+        <v>320.4486694335938</v>
       </c>
       <c r="F539" t="n">
         <v>95.25</v>
@@ -16538,7 +16538,7 @@
         <v>221.1999969482422</v>
       </c>
       <c r="I541" t="n">
-        <v>1364.313110351562</v>
+        <v>1364.31298828125</v>
       </c>
       <c r="J541" t="n">
         <v>22.54999923706055</v>
@@ -16558,7 +16558,7 @@
         <v>21.25</v>
       </c>
       <c r="E542" t="n">
-        <v>354.2666320800781</v>
+        <v>354.2666015625</v>
       </c>
       <c r="F542" t="n">
         <v>92.05000305175781</v>
@@ -16602,7 +16602,7 @@
         <v>217.5500030517578</v>
       </c>
       <c r="I543" t="n">
-        <v>1278.206176757812</v>
+        <v>1278.2060546875</v>
       </c>
       <c r="J543" t="n">
         <v>21.45000076293945</v>
@@ -16654,7 +16654,7 @@
         <v>20.20000076293945</v>
       </c>
       <c r="E545" t="n">
-        <v>337.0339050292969</v>
+        <v>337.033935546875</v>
       </c>
       <c r="F545" t="n">
         <v>84.65000152587891</v>
@@ -16666,7 +16666,7 @@
         <v>214.25</v>
       </c>
       <c r="I545" t="n">
-        <v>1232.7802734375</v>
+        <v>1232.780151367188</v>
       </c>
       <c r="J545" t="n">
         <v>21.04999923706055</v>
@@ -16750,7 +16750,7 @@
         <v>19.70000076293945</v>
       </c>
       <c r="E548" t="n">
-        <v>351.9257202148438</v>
+        <v>351.9257507324219</v>
       </c>
       <c r="F548" t="n">
         <v>88.15000152587891</v>
@@ -16794,7 +16794,7 @@
         <v>249.3000030517578</v>
       </c>
       <c r="I549" t="n">
-        <v>1200.205932617188</v>
+        <v>1200.2060546875</v>
       </c>
       <c r="J549" t="n">
         <v>23.89999961853027</v>
@@ -16814,7 +16814,7 @@
         <v>19.39999961853027</v>
       </c>
       <c r="E550" t="n">
-        <v>337.3825378417969</v>
+        <v>337.382568359375</v>
       </c>
       <c r="F550" t="n">
         <v>87.05000305175781</v>
@@ -16826,7 +16826,7 @@
         <v>271.2000122070312</v>
       </c>
       <c r="I550" t="n">
-        <v>1225.909545898438</v>
+        <v>1225.909423828125</v>
       </c>
       <c r="J550" t="n">
         <v>25.04999923706055</v>
@@ -16878,7 +16878,7 @@
         <v>19.85000038146973</v>
       </c>
       <c r="E552" t="n">
-        <v>344.8035583496094</v>
+        <v>344.8035888671875</v>
       </c>
       <c r="F552" t="n">
         <v>90.94999694824219</v>
@@ -16890,7 +16890,7 @@
         <v>273.7000122070312</v>
       </c>
       <c r="I552" t="n">
-        <v>1234.36181640625</v>
+        <v>1234.361938476562</v>
       </c>
       <c r="J552" t="n">
         <v>27.60000038146973</v>
@@ -16974,7 +16974,7 @@
         <v>21.5</v>
       </c>
       <c r="E555" t="n">
-        <v>355.5615539550781</v>
+        <v>355.5615844726562</v>
       </c>
       <c r="F555" t="n">
         <v>90.40000152587891</v>
@@ -17006,7 +17006,7 @@
         <v>21.5</v>
       </c>
       <c r="E556" t="n">
-        <v>355.7109985351562</v>
+        <v>355.7109680175781</v>
       </c>
       <c r="F556" t="n">
         <v>89.90000152587891</v>
@@ -17038,7 +17038,7 @@
         <v>21.95000076293945</v>
       </c>
       <c r="E557" t="n">
-        <v>355.7109985351562</v>
+        <v>355.7109680175781</v>
       </c>
       <c r="F557" t="n">
         <v>92.40000152587891</v>
@@ -17050,7 +17050,7 @@
         <v>291.7999877929688</v>
       </c>
       <c r="I557" t="n">
-        <v>1334.457397460938</v>
+        <v>1334.457275390625</v>
       </c>
       <c r="J557" t="n">
         <v>31.79999923706055</v>
@@ -17082,7 +17082,7 @@
         <v>295</v>
       </c>
       <c r="I558" t="n">
-        <v>1325.807250976562</v>
+        <v>1325.80712890625</v>
       </c>
       <c r="J558" t="n">
         <v>33.34999847412109</v>
@@ -17102,7 +17102,7 @@
         <v>22.10000038146973</v>
       </c>
       <c r="E559" t="n">
-        <v>371.7483520507812</v>
+        <v>371.7483825683594</v>
       </c>
       <c r="F559" t="n">
         <v>90.84999847412109</v>
@@ -17114,7 +17114,7 @@
         <v>298.8999938964844</v>
       </c>
       <c r="I559" t="n">
-        <v>1317.107543945312</v>
+        <v>1317.107666015625</v>
       </c>
       <c r="J559" t="n">
         <v>32.59999847412109</v>
@@ -17146,7 +17146,7 @@
         <v>287.6000061035156</v>
       </c>
       <c r="I560" t="n">
-        <v>1300.844970703125</v>
+        <v>1300.845092773438</v>
       </c>
       <c r="J560" t="n">
         <v>31</v>
@@ -17262,7 +17262,7 @@
         <v>20.75</v>
       </c>
       <c r="E564" t="n">
-        <v>352.9218444824219</v>
+        <v>352.921875</v>
       </c>
       <c r="F564" t="n">
         <v>85.90000152587891</v>
@@ -17274,7 +17274,7 @@
         <v>199.9499969482422</v>
       </c>
       <c r="I564" t="n">
-        <v>1234.658447265625</v>
+        <v>1234.658569335938</v>
       </c>
       <c r="J564" t="n">
         <v>26.04999923706055</v>
@@ -17306,7 +17306,7 @@
         <v>194.1999969482422</v>
       </c>
       <c r="I565" t="n">
-        <v>1241.380981445312</v>
+        <v>1241.380859375</v>
       </c>
       <c r="J565" t="n">
         <v>27.35000038146973</v>
@@ -17326,7 +17326,7 @@
         <v>22</v>
       </c>
       <c r="E566" t="n">
-        <v>376.9281311035156</v>
+        <v>376.9281005859375</v>
       </c>
       <c r="F566" t="n">
         <v>89.5</v>
@@ -17358,7 +17358,7 @@
         <v>22.10000038146973</v>
       </c>
       <c r="E567" t="n">
-        <v>368.660400390625</v>
+        <v>368.6604309082031</v>
       </c>
       <c r="F567" t="n">
         <v>87.59999847412109</v>
@@ -17370,7 +17370,7 @@
         <v>188.75</v>
       </c>
       <c r="I567" t="n">
-        <v>1248.350708007812</v>
+        <v>1248.3505859375</v>
       </c>
       <c r="J567" t="n">
         <v>28.04999923706055</v>
@@ -17390,7 +17390,7 @@
         <v>22.25</v>
       </c>
       <c r="E568" t="n">
-        <v>381.21142578125</v>
+        <v>381.2113952636719</v>
       </c>
       <c r="F568" t="n">
         <v>87.19999694824219</v>
@@ -17422,7 +17422,7 @@
         <v>22.64999961853027</v>
       </c>
       <c r="E569" t="n">
-        <v>386.4410095214844</v>
+        <v>386.4409790039062</v>
       </c>
       <c r="F569" t="n">
         <v>88.05000305175781</v>
@@ -17454,7 +17454,7 @@
         <v>22.75</v>
       </c>
       <c r="E570" t="n">
-        <v>380.3647155761719</v>
+        <v>380.3646850585938</v>
       </c>
       <c r="F570" t="n">
         <v>92.44999694824219</v>
@@ -17486,7 +17486,7 @@
         <v>22.35000038146973</v>
       </c>
       <c r="E571" t="n">
-        <v>380.8129272460938</v>
+        <v>380.8129577636719</v>
       </c>
       <c r="F571" t="n">
         <v>92.75</v>
@@ -17498,7 +17498,7 @@
         <v>192.6499938964844</v>
       </c>
       <c r="I571" t="n">
-        <v>1290.761474609375</v>
+        <v>1290.761352539062</v>
       </c>
       <c r="J571" t="n">
         <v>27.5</v>
@@ -17562,7 +17562,7 @@
         <v>185.8000030517578</v>
       </c>
       <c r="I573" t="n">
-        <v>1286.362060546875</v>
+        <v>1286.362182617188</v>
       </c>
       <c r="J573" t="n">
         <v>27.54999923706055</v>
@@ -17594,7 +17594,7 @@
         <v>177.8999938964844</v>
       </c>
       <c r="I574" t="n">
-        <v>1309.693115234375</v>
+        <v>1309.692993164062</v>
       </c>
       <c r="J574" t="n">
         <v>27.29999923706055</v>
@@ -17658,7 +17658,7 @@
         <v>176.1999969482422</v>
       </c>
       <c r="I576" t="n">
-        <v>1283.791870117188</v>
+        <v>1283.791748046875</v>
       </c>
       <c r="J576" t="n">
         <v>26.79999923706055</v>
@@ -17678,7 +17678,7 @@
         <v>21.45000076293945</v>
       </c>
       <c r="E577" t="n">
-        <v>368.8098449707031</v>
+        <v>368.809814453125</v>
       </c>
       <c r="F577" t="n">
         <v>80.65000152587891</v>
@@ -17710,7 +17710,7 @@
         <v>21.04999923706055</v>
       </c>
       <c r="E578" t="n">
-        <v>354.8642883300781</v>
+        <v>354.8642578125</v>
       </c>
       <c r="F578" t="n">
         <v>80</v>
@@ -17722,7 +17722,7 @@
         <v>170.75</v>
       </c>
       <c r="I578" t="n">
-        <v>1236.932250976562</v>
+        <v>1236.93212890625</v>
       </c>
       <c r="J578" t="n">
         <v>25.64999961853027</v>
@@ -17806,7 +17806,7 @@
         <v>20.79999923706055</v>
       </c>
       <c r="E581" t="n">
-        <v>346.4969787597656</v>
+        <v>346.4969482421875</v>
       </c>
       <c r="F581" t="n">
         <v>78</v>
@@ -17818,7 +17818,7 @@
         <v>162.9499969482422</v>
       </c>
       <c r="I581" t="n">
-        <v>1185.821899414062</v>
+        <v>1185.82177734375</v>
       </c>
       <c r="J581" t="n">
         <v>24.95000076293945</v>
@@ -17882,7 +17882,7 @@
         <v>171.4499969482422</v>
       </c>
       <c r="I583" t="n">
-        <v>1204.901733398438</v>
+        <v>1204.90185546875</v>
       </c>
       <c r="J583" t="n">
         <v>25.60000038146973</v>
@@ -17902,7 +17902,7 @@
         <v>20.85000038146973</v>
       </c>
       <c r="E584" t="n">
-        <v>352.4736022949219</v>
+        <v>352.4736328125</v>
       </c>
       <c r="F584" t="n">
         <v>80.5</v>
@@ -17914,7 +17914,7 @@
         <v>171.6000061035156</v>
       </c>
       <c r="I584" t="n">
-        <v>1211.426513671875</v>
+        <v>1211.426391601562</v>
       </c>
       <c r="J584" t="n">
         <v>25.79999923706055</v>
@@ -17978,7 +17978,7 @@
         <v>170.1000061035156</v>
       </c>
       <c r="I586" t="n">
-        <v>1220.47216796875</v>
+        <v>1220.472290039062</v>
       </c>
       <c r="J586" t="n">
         <v>26.14999961853027</v>
@@ -18030,7 +18030,7 @@
         <v>21.20000076293945</v>
       </c>
       <c r="E588" t="n">
-        <v>356.2588500976562</v>
+        <v>356.2588195800781</v>
       </c>
       <c r="F588" t="n">
         <v>82.25</v>
@@ -18094,7 +18094,7 @@
         <v>21.39999961853027</v>
       </c>
       <c r="E590" t="n">
-        <v>363.9786682128906</v>
+        <v>363.9786987304688</v>
       </c>
       <c r="F590" t="n">
         <v>82.19999694824219</v>
@@ -18170,7 +18170,7 @@
         <v>168.8999938964844</v>
       </c>
       <c r="I592" t="n">
-        <v>1209.647094726562</v>
+        <v>1209.64697265625</v>
       </c>
       <c r="J592" t="n">
         <v>24.95000076293945</v>
@@ -18190,7 +18190,7 @@
         <v>20.79999923706055</v>
       </c>
       <c r="E593" t="n">
-        <v>347.8417358398438</v>
+        <v>347.8417053222656</v>
       </c>
       <c r="F593" t="n">
         <v>77.80000305175781</v>
@@ -18222,7 +18222,7 @@
         <v>20.54999923706055</v>
       </c>
       <c r="E594" t="n">
-        <v>346.3973693847656</v>
+        <v>346.3973388671875</v>
       </c>
       <c r="F594" t="n">
         <v>80.94999694824219</v>
@@ -18318,7 +18318,7 @@
         <v>19.39999961853027</v>
       </c>
       <c r="E597" t="n">
-        <v>331.6549377441406</v>
+        <v>331.6549072265625</v>
       </c>
       <c r="F597" t="n">
         <v>75.59999847412109</v>
@@ -18350,7 +18350,7 @@
         <v>19.95000076293945</v>
       </c>
       <c r="E598" t="n">
-        <v>344.2557067871094</v>
+        <v>344.2557373046875</v>
       </c>
       <c r="F598" t="n">
         <v>76.09999847412109</v>
@@ -18382,7 +18382,7 @@
         <v>20.29999923706055</v>
       </c>
       <c r="E599" t="n">
-        <v>348.0408935546875</v>
+        <v>348.0409240722656</v>
       </c>
       <c r="F599" t="n">
         <v>79.84999847412109</v>
@@ -18478,7 +18478,7 @@
         <v>21.68000030517578</v>
       </c>
       <c r="E602" t="n">
-        <v>348.8876037597656</v>
+        <v>348.8876342773438</v>
       </c>
       <c r="F602" t="n">
         <v>79.94000244140625</v>
@@ -18670,7 +18670,7 @@
         <v>22.73999977111816</v>
       </c>
       <c r="E608" t="n">
-        <v>364.1281127929688</v>
+        <v>364.1280822753906</v>
       </c>
       <c r="F608" t="n">
         <v>84.08999633789062</v>
@@ -18734,7 +18734,7 @@
         <v>22.72999954223633</v>
       </c>
       <c r="E610" t="n">
-        <v>353.9678039550781</v>
+        <v>353.9677734375</v>
       </c>
       <c r="F610" t="n">
         <v>82.69999694824219</v>
@@ -18798,7 +18798,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="E612" t="n">
-        <v>354.8642883300781</v>
+        <v>354.8642578125</v>
       </c>
       <c r="F612" t="n">
         <v>81.08999633789062</v>
@@ -18958,7 +18958,7 @@
         <v>23.46999931335449</v>
       </c>
       <c r="E617" t="n">
-        <v>349.9335327148438</v>
+        <v>349.9335021972656</v>
       </c>
       <c r="F617" t="n">
         <v>88.41000366210938</v>
@@ -19118,7 +19118,7 @@
         <v>23.09000015258789</v>
       </c>
       <c r="E622" t="n">
-        <v>346.5965576171875</v>
+        <v>346.5965881347656</v>
       </c>
       <c r="F622" t="n">
         <v>82.37999725341797</v>
@@ -19438,7 +19438,7 @@
         <v>23.82999992370605</v>
       </c>
       <c r="E632" t="n">
-        <v>327.9195251464844</v>
+        <v>327.9194946289062</v>
       </c>
       <c r="F632" t="n">
         <v>84.30999755859375</v>
@@ -19470,7 +19470,7 @@
         <v>23.92000007629395</v>
       </c>
       <c r="E633" t="n">
-        <v>330.6089782714844</v>
+        <v>330.6090087890625</v>
       </c>
       <c r="F633" t="n">
         <v>91.58999633789062</v>
@@ -19534,7 +19534,7 @@
         <v>24.17000007629395</v>
       </c>
       <c r="E635" t="n">
-        <v>328.0689086914062</v>
+        <v>328.0689392089844</v>
       </c>
       <c r="F635" t="n">
         <v>90.97000122070312</v>
@@ -19630,7 +19630,7 @@
         <v>23.06999969482422</v>
       </c>
       <c r="E638" t="n">
-        <v>324.9809875488281</v>
+        <v>324.98095703125</v>
       </c>
       <c r="F638" t="n">
         <v>93.27999877929688</v>
@@ -19790,7 +19790,7 @@
         <v>21.71999931335449</v>
       </c>
       <c r="E643" t="n">
-        <v>324.3335266113281</v>
+        <v>324.33349609375</v>
       </c>
       <c r="F643" t="n">
         <v>99.91999816894531</v>
@@ -20014,7 +20014,7 @@
         <v>21.45999908447266</v>
       </c>
       <c r="E650" t="n">
-        <v>329.8121032714844</v>
+        <v>329.8121337890625</v>
       </c>
       <c r="F650" t="n">
         <v>98.65000152587891</v>
@@ -20142,7 +20142,7 @@
         <v>21.40999984741211</v>
       </c>
       <c r="E654" t="n">
-        <v>322.34130859375</v>
+        <v>322.3412780761719</v>
       </c>
       <c r="F654" t="n">
         <v>97.77999877929688</v>
@@ -20174,7 +20174,7 @@
         <v>21.23999977111816</v>
       </c>
       <c r="E655" t="n">
-        <v>320.9965515136719</v>
+        <v>320.9965209960938</v>
       </c>
       <c r="F655" t="n">
         <v>96.19000244140625</v>
@@ -20238,7 +20238,7 @@
         <v>21.11000061035156</v>
       </c>
       <c r="E657" t="n">
-        <v>320.4486999511719</v>
+        <v>320.4486694335938</v>
       </c>
       <c r="F657" t="n">
         <v>95.16000366210938</v>
@@ -20302,7 +20302,7 @@
         <v>20.65999984741211</v>
       </c>
       <c r="E659" t="n">
-        <v>348.8378295898438</v>
+        <v>348.8377990722656</v>
       </c>
       <c r="F659" t="n">
         <v>93.05999755859375</v>
@@ -20334,7 +20334,7 @@
         <v>20.5</v>
       </c>
       <c r="E660" t="n">
-        <v>345.8495178222656</v>
+        <v>345.8494873046875</v>
       </c>
       <c r="F660" t="n">
         <v>91.76000213623047</v>
@@ -20590,7 +20590,7 @@
         <v>21.73999977111816</v>
       </c>
       <c r="E668" t="n">
-        <v>347.4432373046875</v>
+        <v>347.4432678222656</v>
       </c>
       <c r="F668" t="n">
         <v>91.58000183105469</v>
@@ -20686,7 +20686,7 @@
         <v>20.45000076293945</v>
       </c>
       <c r="E671" t="n">
-        <v>345.3016357421875</v>
+        <v>345.3016052246094</v>
       </c>
       <c r="F671" t="n">
         <v>83.73999786376953</v>
@@ -20750,7 +20750,7 @@
         <v>20.71999931335449</v>
       </c>
       <c r="E673" t="n">
-        <v>352.8720703125</v>
+        <v>352.8720397949219</v>
       </c>
       <c r="F673" t="n">
         <v>83.36000061035156</v>
@@ -20974,7 +20974,7 @@
         <v>20.25</v>
       </c>
       <c r="E680" t="n">
-        <v>344.2557067871094</v>
+        <v>344.2557373046875</v>
       </c>
       <c r="F680" t="n">
         <v>80.34999847412109</v>
@@ -21070,7 +21070,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="E683" t="n">
-        <v>344.2557067871094</v>
+        <v>344.2557373046875</v>
       </c>
       <c r="F683" t="n">
         <v>75.75</v>
@@ -21166,7 +21166,7 @@
         <v>20.09000015258789</v>
       </c>
       <c r="E686" t="n">
-        <v>340.171630859375</v>
+        <v>340.1716613769531</v>
       </c>
       <c r="F686" t="n">
         <v>81.36000061035156</v>
@@ -21198,7 +21198,7 @@
         <v>20.72999954223633</v>
       </c>
       <c r="E687" t="n">
-        <v>338.7272644042969</v>
+        <v>338.727294921875</v>
       </c>
       <c r="F687" t="n">
         <v>79.09999847412109</v>
@@ -21262,7 +21262,7 @@
         <v>20.48999977111816</v>
       </c>
       <c r="E689" t="n">
-        <v>332.3521728515625</v>
+        <v>332.3522033691406</v>
       </c>
       <c r="F689" t="n">
         <v>85.95999908447266</v>
@@ -21390,7 +21390,7 @@
         <v>18.84000015258789</v>
       </c>
       <c r="E693" t="n">
-        <v>312.8284301757812</v>
+        <v>312.8283996582031</v>
       </c>
       <c r="F693" t="n">
         <v>76.08000183105469</v>
@@ -21422,7 +21422,7 @@
         <v>18.93000030517578</v>
       </c>
       <c r="E694" t="n">
-        <v>313.4759216308594</v>
+        <v>313.4758911132812</v>
       </c>
       <c r="F694" t="n">
         <v>79.12999725341797</v>
@@ -21582,7 +21582,7 @@
         <v>19.28000068664551</v>
       </c>
       <c r="E699" t="n">
-        <v>318.7055053710938</v>
+        <v>318.7054748535156</v>
       </c>
       <c r="F699" t="n">
         <v>81.11000061035156</v>
@@ -21774,7 +21774,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="E705" t="n">
-        <v>320.2992248535156</v>
+        <v>320.2992553710938</v>
       </c>
       <c r="F705" t="n">
         <v>83.80999755859375</v>
@@ -21902,7 +21902,7 @@
         <v>18.28000068664551</v>
       </c>
       <c r="E709" t="n">
-        <v>298.2353820800781</v>
+        <v>298.2354125976562</v>
       </c>
       <c r="F709" t="n">
         <v>77.97000122070312</v>
@@ -22030,7 +22030,7 @@
         <v>18.11000061035156</v>
       </c>
       <c r="E713" t="n">
-        <v>312.9778442382812</v>
+        <v>312.9778747558594</v>
       </c>
       <c r="F713" t="n">
         <v>84.30000305175781</v>
@@ -22062,7 +22062,7 @@
         <v>18.17000007629395</v>
       </c>
       <c r="E714" t="n">
-        <v>312.5794067382812</v>
+        <v>312.5793762207031</v>
       </c>
       <c r="F714" t="n">
         <v>79.55999755859375</v>
@@ -22158,7 +22158,7 @@
         <v>17.02000045776367</v>
       </c>
       <c r="E717" t="n">
-        <v>327.6206359863281</v>
+        <v>327.6206665039062</v>
       </c>
       <c r="F717" t="n">
         <v>79.70999908447266</v>
@@ -22222,7 +22222,7 @@
         <v>17.28000068664551</v>
       </c>
       <c r="E719" t="n">
-        <v>327.0727844238281</v>
+        <v>327.0728149414062</v>
       </c>
       <c r="F719" t="n">
         <v>78.83999633789062</v>
@@ -22286,7 +22286,7 @@
         <v>17.86000061035156</v>
       </c>
       <c r="E721" t="n">
-        <v>339.026123046875</v>
+        <v>339.0261535644531</v>
       </c>
       <c r="F721" t="n">
         <v>79.80999755859375</v>
@@ -22350,7 +22350,7 @@
         <v>17.93000030517578</v>
       </c>
       <c r="E723" t="n">
-        <v>340.171630859375</v>
+        <v>340.1716613769531</v>
       </c>
       <c r="F723" t="n">
         <v>79.20999908447266</v>
@@ -22382,7 +22382,7 @@
         <v>18.06999969482422</v>
       </c>
       <c r="E724" t="n">
-        <v>337.5817565917969</v>
+        <v>337.581787109375</v>
       </c>
       <c r="F724" t="n">
         <v>79.58999633789062</v>
@@ -22574,7 +22574,7 @@
         <v>17.80999946594238</v>
       </c>
       <c r="E730" t="n">
-        <v>339.026123046875</v>
+        <v>339.0261535644531</v>
       </c>
       <c r="F730" t="n">
         <v>74.36000061035156</v>
@@ -22606,7 +22606,7 @@
         <v>17.55999946594238</v>
       </c>
       <c r="E731" t="n">
-        <v>335.7887878417969</v>
+        <v>335.7887573242188</v>
       </c>
       <c r="F731" t="n">
         <v>73.54000091552734</v>
@@ -22638,7 +22638,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="E732" t="n">
-        <v>323.33740234375</v>
+        <v>323.3373718261719</v>
       </c>
       <c r="F732" t="n">
         <v>72.55999755859375</v>
@@ -22670,7 +22670,7 @@
         <v>17.13999938964844</v>
       </c>
       <c r="E733" t="n">
-        <v>311.7825012207031</v>
+        <v>311.7825317382812</v>
       </c>
       <c r="F733" t="n">
         <v>70.18000030517578</v>
@@ -22702,7 +22702,7 @@
         <v>16.61000061035156</v>
       </c>
       <c r="E734" t="n">
-        <v>303.1163330078125</v>
+        <v>303.1163635253906</v>
       </c>
       <c r="F734" t="n">
         <v>74.33999633789062</v>
@@ -22830,7 +22830,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="E738" t="n">
-        <v>303.7638244628906</v>
+        <v>303.7638549804688</v>
       </c>
       <c r="F738" t="n">
         <v>73.19000244140625</v>
@@ -22862,7 +22862,7 @@
         <v>15.19999980926514</v>
       </c>
       <c r="E739" t="n">
-        <v>305.0587768554688</v>
+        <v>305.0587463378906</v>
       </c>
       <c r="F739" t="n">
         <v>70.33999633789062</v>
@@ -22990,7 +22990,7 @@
         <v>16.32999992370605</v>
       </c>
       <c r="E743" t="n">
-        <v>306.2541198730469</v>
+        <v>306.2540893554688</v>
       </c>
       <c r="F743" t="n">
         <v>72.80000305175781</v>
@@ -23022,7 +23022,7 @@
         <v>15.73999977111816</v>
       </c>
       <c r="E744" t="n">
-        <v>295.5459289550781</v>
+        <v>295.5458984375</v>
       </c>
       <c r="F744" t="n">
         <v>68.94999694824219</v>
@@ -23118,7 +23118,7 @@
         <v>15.77999973297119</v>
       </c>
       <c r="E747" t="n">
-        <v>288.1248779296875</v>
+        <v>288.1249084472656</v>
       </c>
       <c r="F747" t="n">
         <v>66.61000061035156</v>
@@ -23182,7 +23182,7 @@
         <v>14.53999996185303</v>
       </c>
       <c r="E749" t="n">
-        <v>265.11474609375</v>
+        <v>265.1147155761719</v>
       </c>
       <c r="F749" t="n">
         <v>59.84000015258789</v>
@@ -23214,7 +23214,7 @@
         <v>15.23999977111816</v>
       </c>
       <c r="E750" t="n">
-        <v>271.7886962890625</v>
+        <v>271.7886657714844</v>
       </c>
       <c r="F750" t="n">
         <v>61.43999862670898</v>
@@ -23502,7 +23502,7 @@
         <v>14.88000011444092</v>
       </c>
       <c r="E759" t="n">
-        <v>232.3925170898438</v>
+        <v>232.3925323486328</v>
       </c>
       <c r="F759" t="n">
         <v>50.02999877929688</v>
@@ -23534,7 +23534,7 @@
         <v>14.77999973297119</v>
       </c>
       <c r="E760" t="n">
-        <v>232.4921264648438</v>
+        <v>232.4921417236328</v>
       </c>
       <c r="F760" t="n">
         <v>49.66999816894531</v>
@@ -23662,7 +23662,7 @@
         <v>15.10999965667725</v>
       </c>
       <c r="E764" t="n">
-        <v>240.5705718994141</v>
+        <v>240.5705871582031</v>
       </c>
       <c r="F764" t="n">
         <v>52.81999969482422</v>
@@ -23726,7 +23726,7 @@
         <v>14.75</v>
       </c>
       <c r="E766" t="n">
-        <v>244.1466217041016</v>
+        <v>244.1466369628906</v>
       </c>
       <c r="F766" t="n">
         <v>51.83000183105469</v>
@@ -23758,7 +23758,7 @@
         <v>14.84000015258789</v>
       </c>
       <c r="E767" t="n">
-        <v>248.8482818603516</v>
+        <v>248.8482666015625</v>
       </c>
       <c r="F767" t="n">
         <v>53.2599983215332</v>
@@ -23822,7 +23822,7 @@
         <v>14.69999980926514</v>
       </c>
       <c r="E769" t="n">
-        <v>248.4796905517578</v>
+        <v>248.4797058105469</v>
       </c>
       <c r="F769" t="n">
         <v>51.79000091552734</v>
@@ -23854,7 +23854,7 @@
         <v>14.82999992370605</v>
       </c>
       <c r="E770" t="n">
-        <v>242.0149688720703</v>
+        <v>242.0149536132812</v>
       </c>
       <c r="F770" t="n">
         <v>50.41999816894531</v>
@@ -23950,7 +23950,7 @@
         <v>14.34000015258789</v>
       </c>
       <c r="E773" t="n">
-        <v>227.1729125976562</v>
+        <v>227.1728973388672</v>
       </c>
       <c r="F773" t="n">
         <v>49.22999954223633</v>
@@ -24078,7 +24078,7 @@
         <v>14.14000034332275</v>
       </c>
       <c r="E777" t="n">
-        <v>228.0295562744141</v>
+        <v>228.0295715332031</v>
       </c>
       <c r="F777" t="n">
         <v>46.93000030517578</v>
@@ -24270,7 +24270,7 @@
         <v>13.22000026702881</v>
       </c>
       <c r="E783" t="n">
-        <v>206.8024444580078</v>
+        <v>206.8024597167969</v>
       </c>
       <c r="F783" t="n">
         <v>41.31999969482422</v>
@@ -24398,7 +24398,7 @@
         <v>13.89999961853027</v>
       </c>
       <c r="E787" t="n">
-        <v>219.0844879150391</v>
+        <v>219.0845031738281</v>
       </c>
       <c r="F787" t="n">
         <v>44.04999923706055</v>
@@ -24430,7 +24430,7 @@
         <v>14.17000007629395</v>
       </c>
       <c r="E788" t="n">
-        <v>220.9472198486328</v>
+        <v>220.9472045898438</v>
       </c>
       <c r="F788" t="n">
         <v>45.45000076293945</v>
@@ -24526,7 +24526,7 @@
         <v>13.38000011444092</v>
       </c>
       <c r="E791" t="n">
-        <v>224.6527404785156</v>
+        <v>224.6527557373047</v>
       </c>
       <c r="F791" t="n">
         <v>41.93000030517578</v>
@@ -24590,7 +24590,7 @@
         <v>13.01000022888184</v>
       </c>
       <c r="E793" t="n">
-        <v>218.6661224365234</v>
+        <v>218.6661376953125</v>
       </c>
       <c r="F793" t="n">
         <v>40.52999877929688</v>
@@ -24622,7 +24622,7 @@
         <v>13.01000022888184</v>
       </c>
       <c r="E794" t="n">
-        <v>218.6661224365234</v>
+        <v>218.6661376953125</v>
       </c>
       <c r="F794" t="n">
         <v>40.52999877929688</v>
@@ -24654,7 +24654,7 @@
         <v>13.55000019073486</v>
       </c>
       <c r="E795" t="n">
-        <v>227.9498596191406</v>
+        <v>227.9498748779297</v>
       </c>
       <c r="F795" t="n">
         <v>43.86999893188477</v>
@@ -24718,7 +24718,7 @@
         <v>13.71000003814697</v>
       </c>
       <c r="E797" t="n">
-        <v>228.2287902832031</v>
+        <v>228.2287750244141</v>
       </c>
       <c r="F797" t="n">
         <v>47.43999862670898</v>
@@ -24750,7 +24750,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="E798" t="n">
-        <v>231.7749176025391</v>
+        <v>231.7749328613281</v>
       </c>
       <c r="F798" t="n">
         <v>47.4900016784668</v>
@@ -24782,7 +24782,7 @@
         <v>13.32999992370605</v>
       </c>
       <c r="E799" t="n">
-        <v>226.6449737548828</v>
+        <v>226.6449584960938</v>
       </c>
       <c r="F799" t="n">
         <v>45.36000061035156</v>
@@ -24846,7 +24846,7 @@
         <v>13.07999992370605</v>
       </c>
       <c r="E801" t="n">
-        <v>224.9017791748047</v>
+        <v>224.9017639160156</v>
       </c>
       <c r="F801" t="n">
         <v>44.95999908447266</v>
@@ -24878,7 +24878,7 @@
         <v>13</v>
       </c>
       <c r="E802" t="n">
-        <v>226.6250457763672</v>
+        <v>226.6250305175781</v>
       </c>
       <c r="F802" t="n">
         <v>43.40999984741211</v>
@@ -25038,7 +25038,7 @@
         <v>12.46000003814697</v>
       </c>
       <c r="E807" t="n">
-        <v>212.689453125</v>
+        <v>212.6894683837891</v>
       </c>
       <c r="F807" t="n">
         <v>41.22999954223633</v>
@@ -25070,7 +25070,7 @@
         <v>12.98999977111816</v>
       </c>
       <c r="E808" t="n">
-        <v>223.9355316162109</v>
+        <v>223.935546875</v>
       </c>
       <c r="F808" t="n">
         <v>41.70999908447266</v>
@@ -25262,7 +25262,7 @@
         <v>14.10999965667725</v>
       </c>
       <c r="E814" t="n">
-        <v>245.4216613769531</v>
+        <v>245.4216461181641</v>
       </c>
       <c r="F814" t="n">
         <v>45.11000061035156</v>
@@ -25326,7 +25326,7 @@
         <v>14.72999954223633</v>
       </c>
       <c r="E816" t="n">
-        <v>257.1358947753906</v>
+        <v>257.1359252929688</v>
       </c>
       <c r="F816" t="n">
         <v>45.86999893188477</v>
@@ -25422,7 +25422,7 @@
         <v>14.02000045776367</v>
       </c>
       <c r="E819" t="n">
-        <v>256.8968505859375</v>
+        <v>256.8968200683594</v>
       </c>
       <c r="F819" t="n">
         <v>43.45000076293945</v>
@@ -25454,7 +25454,7 @@
         <v>13.90999984741211</v>
       </c>
       <c r="E820" t="n">
-        <v>256.6278686523438</v>
+        <v>256.6278991699219</v>
       </c>
       <c r="F820" t="n">
         <v>45.27000045776367</v>
@@ -25678,7 +25678,7 @@
         <v>13.15999984741211</v>
       </c>
       <c r="E827" t="n">
-        <v>247.3840026855469</v>
+        <v>247.3839874267578</v>
       </c>
       <c r="F827" t="n">
         <v>42.4900016784668</v>
@@ -25902,7 +25902,7 @@
         <v>15.01000022888184</v>
       </c>
       <c r="E834" t="n">
-        <v>270.3941345214844</v>
+        <v>270.3941650390625</v>
       </c>
       <c r="F834" t="n">
         <v>46.61999893188477</v>
@@ -25934,7 +25934,7 @@
         <v>15.14999961853027</v>
       </c>
       <c r="E835" t="n">
-        <v>273.2828369140625</v>
+        <v>273.2828674316406</v>
       </c>
       <c r="F835" t="n">
         <v>46.68999862670898</v>
@@ -25998,7 +25998,7 @@
         <v>15.3100004196167</v>
       </c>
       <c r="E837" t="n">
-        <v>280.6540832519531</v>
+        <v>280.654052734375</v>
       </c>
       <c r="F837" t="n">
         <v>48.81999969482422</v>
@@ -26030,7 +26030,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="E838" t="n">
-        <v>280.6540832519531</v>
+        <v>280.654052734375</v>
       </c>
       <c r="F838" t="n">
         <v>50.0099983215332</v>
@@ -26094,7 +26094,7 @@
         <v>15.52000045776367</v>
       </c>
       <c r="E840" t="n">
-        <v>289.2206115722656</v>
+        <v>289.2206420898438</v>
       </c>
       <c r="F840" t="n">
         <v>52.68999862670898</v>
@@ -26254,7 +26254,7 @@
         <v>15.72999954223633</v>
       </c>
       <c r="E845" t="n">
-        <v>289.2206115722656</v>
+        <v>289.2206420898438</v>
       </c>
       <c r="F845" t="n">
         <v>55.31999969482422</v>
@@ -26286,7 +26286,7 @@
         <v>15.75</v>
       </c>
       <c r="E846" t="n">
-        <v>290.3661193847656</v>
+        <v>290.3661499023438</v>
       </c>
       <c r="F846" t="n">
         <v>54.68999862670898</v>
@@ -26350,7 +26350,7 @@
         <v>15.80000019073486</v>
       </c>
       <c r="E848" t="n">
-        <v>303.0665588378906</v>
+        <v>303.0665283203125</v>
       </c>
       <c r="F848" t="n">
         <v>54.47999954223633</v>
@@ -26382,7 +26382,7 @@
         <v>15.98999977111816</v>
       </c>
       <c r="E849" t="n">
-        <v>301.6221923828125</v>
+        <v>301.6221618652344</v>
       </c>
       <c r="F849" t="n">
         <v>57.08000183105469</v>
@@ -26542,7 +26542,7 @@
         <v>15.03999996185303</v>
       </c>
       <c r="E854" t="n">
-        <v>288.6727294921875</v>
+        <v>288.6727600097656</v>
       </c>
       <c r="F854" t="n">
         <v>53.13999938964844</v>
@@ -26574,7 +26574,7 @@
         <v>14.89000034332275</v>
       </c>
       <c r="E855" t="n">
-        <v>287.0291442871094</v>
+        <v>287.0291748046875</v>
       </c>
       <c r="F855" t="n">
         <v>52.86999893188477</v>
@@ -26702,7 +26702,7 @@
         <v>15.15999984741211</v>
       </c>
       <c r="E859" t="n">
-        <v>299.6299438476562</v>
+        <v>299.6299743652344</v>
       </c>
       <c r="F859" t="n">
         <v>53.65999984741211</v>
@@ -26734,7 +26734,7 @@
         <v>16.04999923706055</v>
       </c>
       <c r="E860" t="n">
-        <v>302.1202087402344</v>
+        <v>302.1202392578125</v>
       </c>
       <c r="F860" t="n">
         <v>61.81999969482422</v>
@@ -26894,7 +26894,7 @@
         <v>15.85999965667725</v>
       </c>
       <c r="E865" t="n">
-        <v>325.4292602539062</v>
+        <v>325.4292297363281</v>
       </c>
       <c r="F865" t="n">
         <v>57.02000045776367</v>
@@ -26926,7 +26926,7 @@
         <v>15.96000003814697</v>
       </c>
       <c r="E866" t="n">
-        <v>323.78564453125</v>
+        <v>323.7856140136719</v>
       </c>
       <c r="F866" t="n">
         <v>58.11000061035156</v>
@@ -26958,7 +26958,7 @@
         <v>15.98999977111816</v>
       </c>
       <c r="E867" t="n">
-        <v>323.68603515625</v>
+        <v>323.6860656738281</v>
       </c>
       <c r="F867" t="n">
         <v>56.41999816894531</v>
@@ -27086,7 +27086,7 @@
         <v>15.57999992370605</v>
       </c>
       <c r="E871" t="n">
-        <v>330.3599548339844</v>
+        <v>330.3599853515625</v>
       </c>
       <c r="F871" t="n">
         <v>55.68000030517578</v>
@@ -27118,7 +27118,7 @@
         <v>15.35999965667725</v>
       </c>
       <c r="E872" t="n">
-        <v>324.5326843261719</v>
+        <v>324.53271484375</v>
       </c>
       <c r="F872" t="n">
         <v>54.81000137329102</v>
@@ -27310,7 +27310,7 @@
         <v>15.86999988555908</v>
       </c>
       <c r="E878" t="n">
-        <v>316.0159912109375</v>
+        <v>316.0159606933594</v>
       </c>
       <c r="F878" t="n">
         <v>59.61000061035156</v>
@@ -27470,7 +27470,7 @@
         <v>14.85999965667725</v>
       </c>
       <c r="E883" t="n">
-        <v>306.1545104980469</v>
+        <v>306.1544799804688</v>
       </c>
       <c r="F883" t="n">
         <v>56.25</v>
@@ -27598,7 +27598,7 @@
         <v>15.10000038146973</v>
       </c>
       <c r="E887" t="n">
-        <v>328.2183532714844</v>
+        <v>328.2183227539062</v>
       </c>
       <c r="F887" t="n">
         <v>57.47000122070312</v>
@@ -27726,7 +27726,7 @@
         <v>14.31999969482422</v>
       </c>
       <c r="E891" t="n">
-        <v>324.23388671875</v>
+        <v>324.2339172363281</v>
       </c>
       <c r="F891" t="n">
         <v>56.29000091552734</v>
@@ -37232,7 +37232,7 @@
         <v>3.846153846153855</v>
       </c>
       <c r="E19" t="n">
-        <v>14.46530217715354</v>
+        <v>14.46530988416585</v>
       </c>
       <c r="F19" t="n">
         <v>0.2994726297447459</v>
@@ -37264,7 +37264,7 @@
         <v>-1.664147220764423</v>
       </c>
       <c r="E20" t="n">
-        <v>9.585283854023508</v>
+        <v>9.585268389905522</v>
       </c>
       <c r="F20" t="n">
         <v>5.058083659302848</v>
@@ -37296,7 +37296,7 @@
         <v>-12.04257816433491</v>
       </c>
       <c r="E21" t="n">
-        <v>-14.08648894056502</v>
+        <v>-14.08648260149032</v>
       </c>
       <c r="F21" t="n">
         <v>-21.56416200558649</v>
@@ -37360,7 +37360,7 @@
         <v>-8.96991367371337</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.02998930442963</v>
+        <v>-9.029997792400145</v>
       </c>
       <c r="F23" t="n">
         <v>-9.284627137033763</v>
@@ -37392,7 +37392,7 @@
         <v>-10.92782976067592</v>
       </c>
       <c r="E24" t="n">
-        <v>1.877130575284558</v>
+        <v>1.877140080946416</v>
       </c>
       <c r="F24" t="n">
         <v>-8.750005850085408</v>
@@ -37456,7 +37456,7 @@
         <v>-2.652777627189706</v>
       </c>
       <c r="E26" t="n">
-        <v>8.983518155342285</v>
+        <v>8.983528534268292</v>
       </c>
       <c r="F26" t="n">
         <v>-13.86086794220902</v>
@@ -37488,7 +37488,7 @@
         <v>-12.37027614512571</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.070008835693593</v>
+        <v>-2.070018161948173</v>
       </c>
       <c r="F27" t="n">
         <v>-3.095716273530114</v>
@@ -37596,7 +37596,7 @@
         <v>-6.49240482812462</v>
       </c>
       <c r="I30" t="n">
-        <v>-10.79031925231471</v>
+        <v>-10.79031093750072</v>
       </c>
       <c r="J30" t="n">
         <v>-10.07326035477244</v>
@@ -37628,7 +37628,7 @@
         <v>-34.34213475489638</v>
       </c>
       <c r="I31" t="n">
-        <v>3.869230754336672</v>
+        <v>3.869221073176021</v>
       </c>
       <c r="J31" t="n">
         <v>-3.36283455907771</v>
@@ -37712,7 +37712,7 @@
         <v>12.97169764638586</v>
       </c>
       <c r="E34" t="n">
-        <v>6.567935984125439</v>
+        <v>6.56794299184198</v>
       </c>
       <c r="F34" t="n">
         <v>33.94390617495342</v>
@@ -37724,7 +37724,7 @@
         <v>10.12869384694794</v>
       </c>
       <c r="I34" t="n">
-        <v>4.617430052899274</v>
+        <v>4.61743963491108</v>
       </c>
       <c r="J34" t="n">
         <v>27.89699662161886</v>
@@ -37744,7 +37744,7 @@
         <v>5.735668676501682</v>
       </c>
       <c r="E35" t="n">
-        <v>1.547516340043864</v>
+        <v>1.547509662461577</v>
       </c>
       <c r="F35" t="n">
         <v>0.9243158800178009</v>
@@ -37756,7 +37756,7 @@
         <v>10.5665365226655</v>
       </c>
       <c r="I35" t="n">
-        <v>23.11872269028099</v>
+        <v>23.11871141371891</v>
       </c>
       <c r="J35" t="n">
         <v>10.16548301327902</v>
@@ -37840,7 +37840,7 @@
         <v>21.21212121212121</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9850140387806072</v>
+        <v>-0.9850075430692273</v>
       </c>
       <c r="F38" t="n">
         <v>-6.583760205501399</v>
@@ -37962,7 +37962,7 @@
         <v>5.598621951273208</v>
       </c>
       <c r="G42" t="n">
-        <v>2.040877935444163</v>
+        <v>2.040889260620204</v>
       </c>
       <c r="H42" t="n">
         <v>-14.50333586855534</v>
@@ -37991,7 +37991,7 @@
         <v>7.004606888590881</v>
       </c>
       <c r="G43" t="n">
-        <v>3.837343764441714</v>
+        <v>3.837332239883229</v>
       </c>
       <c r="H43" t="n">
         <v>9.220106101738512</v>
@@ -38026,7 +38026,7 @@
         <v>10.36725582872331</v>
       </c>
       <c r="I44" t="n">
-        <v>-2.506390909291822</v>
+        <v>-2.506398442968916</v>
       </c>
       <c r="J44" t="n">
         <v>1.53060832255989</v>
@@ -38049,13 +38049,13 @@
         <v>-5.117786759101961</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.329720456261541</v>
+        <v>-1.329731717430038</v>
       </c>
       <c r="H45" t="n">
         <v>4.476417699780821</v>
       </c>
       <c r="I45" t="n">
-        <v>-7.821836608719702</v>
+        <v>-7.82183605157546</v>
       </c>
       <c r="J45" t="n">
         <v>-23.13725340600107</v>
@@ -38078,13 +38078,13 @@
         <v>-6.883508838267105</v>
       </c>
       <c r="G46" t="n">
-        <v>-7.590700042745402</v>
+        <v>-7.590689496136827</v>
       </c>
       <c r="H46" t="n">
         <v>-9.150325892060184</v>
       </c>
       <c r="I46" t="n">
-        <v>-7.873151044662352</v>
+        <v>-7.873138437038474</v>
       </c>
       <c r="J46" t="n">
         <v>-11.14982814589901</v>
@@ -38113,7 +38113,7 @@
         <v>-12.68230842551258</v>
       </c>
       <c r="I47" t="n">
-        <v>-10.50510919721274</v>
+        <v>-10.50511506998821</v>
       </c>
       <c r="J47" t="n">
         <v>-10.59189368473866</v>
@@ -38136,7 +38136,7 @@
         <v>6.079503403138031</v>
       </c>
       <c r="G48" t="n">
-        <v>7.128581444439974</v>
+        <v>7.128570156643566</v>
       </c>
       <c r="H48" t="n">
         <v>11.48815860769938</v>
@@ -38165,13 +38165,13 @@
         <v>-0.696589719615015</v>
       </c>
       <c r="G49" t="n">
-        <v>7.227408916932054</v>
+        <v>7.227420215142799</v>
       </c>
       <c r="H49" t="n">
         <v>3.474762330681291</v>
       </c>
       <c r="I49" t="n">
-        <v>1.992279898127447</v>
+        <v>1.992303379905214</v>
       </c>
       <c r="J49" t="n">
         <v>-1.829263683162408</v>
@@ -38200,7 +38200,7 @@
         <v>-15.6172858344184</v>
       </c>
       <c r="I50" t="n">
-        <v>5.378698488282385</v>
+        <v>5.378674226851898</v>
       </c>
       <c r="J50" t="n">
         <v>-2.380950218425493</v>
@@ -38258,7 +38258,7 @@
         <v>29.24944861623748</v>
       </c>
       <c r="I52" t="n">
-        <v>3.064815751886085</v>
+        <v>3.064809031177451</v>
       </c>
       <c r="J52" t="n">
         <v>7.826083639393677</v>
@@ -38281,13 +38281,13 @@
         <v>-8.609271523178808</v>
       </c>
       <c r="G53" t="n">
-        <v>-1.405415476974137</v>
+        <v>-1.405425570676122</v>
       </c>
       <c r="H53" t="n">
         <v>-16.0722547147822</v>
       </c>
       <c r="I53" t="n">
-        <v>2.955471852145508</v>
+        <v>2.955485477722197</v>
       </c>
       <c r="J53" t="n">
         <v>-8.730161493387333</v>
@@ -38310,13 +38310,13 @@
         <v>-12.41298993858072</v>
       </c>
       <c r="G54" t="n">
-        <v>-5.648250331436078</v>
+        <v>-5.648240672096827</v>
       </c>
       <c r="H54" t="n">
         <v>-12.62647164563844</v>
       </c>
       <c r="I54" t="n">
-        <v>-16.35936109340738</v>
+        <v>-16.35937610199863</v>
       </c>
       <c r="J54" t="n">
         <v>-11.57894469144052</v>
@@ -38339,13 +38339,13 @@
         <v>1.233112628945943</v>
       </c>
       <c r="G55" t="n">
-        <v>5.901896555568986</v>
+        <v>5.901885722416633</v>
       </c>
       <c r="H55" t="n">
         <v>10.01780916676824</v>
       </c>
       <c r="I55" t="n">
-        <v>42.15598663130014</v>
+        <v>42.15600259621435</v>
       </c>
       <c r="J55" t="n">
         <v>5.555555555555558</v>
@@ -38368,13 +38368,13 @@
         <v>10.65627667685571</v>
       </c>
       <c r="G56" t="n">
-        <v>11.66323439425943</v>
+        <v>11.66325857150592</v>
       </c>
       <c r="H56" t="n">
         <v>7.361381156751889</v>
       </c>
       <c r="I56" t="n">
-        <v>11.44042835922838</v>
+        <v>11.44043827261805</v>
       </c>
       <c r="J56" t="n">
         <v>3.4482743501002</v>
@@ -38397,13 +38397,13 @@
         <v>-6.15854030702172</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.133414741099703</v>
+        <v>-1.133414869096705</v>
       </c>
       <c r="H57" t="n">
         <v>3.513107684464867</v>
       </c>
       <c r="I57" t="n">
-        <v>-20.63635189760942</v>
+        <v>-20.63637016359784</v>
       </c>
       <c r="J57" t="n">
         <v>-11.82432417193846</v>
@@ -38666,7 +38666,7 @@
         <v>22.99999823937049</v>
       </c>
       <c r="E7" t="n">
-        <v>43.62006339979285</v>
+        <v>43.62007306981142</v>
       </c>
       <c r="F7" t="n">
         <v>35.63695294881548</v>
@@ -38698,7 +38698,7 @@
         <v>-17.35536949575909</v>
       </c>
       <c r="E8" t="n">
-        <v>-23.83328051135775</v>
+        <v>-23.83328563970489</v>
       </c>
       <c r="F8" t="n">
         <v>-39.30368863961553</v>
@@ -38826,7 +38826,7 @@
         <v>-7.547171339100844</v>
       </c>
       <c r="E12" t="n">
-        <v>51.85663028133727</v>
+        <v>51.8566402671572</v>
       </c>
       <c r="F12" t="n">
         <v>-1.316544414387844</v>
@@ -38838,7 +38838,7 @@
         <v>29.14681042220371</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.392582670916979</v>
+        <v>-5.392574005731943</v>
       </c>
       <c r="J12" t="n">
         <v>21.24463916318964</v>
@@ -38858,7 +38858,7 @@
         <v>6.000003814697275</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7569211287945299</v>
+        <v>0.7569145032003677</v>
       </c>
       <c r="F13" t="n">
         <v>36.80501262584171</v>
@@ -38870,7 +38870,7 @@
         <v>21.06174227192534</v>
       </c>
       <c r="I13" t="n">
-        <v>40.1330609163993</v>
+        <v>40.13304808147762</v>
       </c>
       <c r="J13" t="n">
         <v>21.03895707563921</v>
@@ -38957,7 +38957,7 @@
         <v>4.756719823472322</v>
       </c>
       <c r="I16" t="n">
-        <v>-17.20761079032843</v>
+        <v>-17.2076053573798</v>
       </c>
       <c r="J16" t="n">
         <v>-30.66202407831533</v>
@@ -38986,7 +38986,7 @@
         <v>0.7315289117223678</v>
       </c>
       <c r="I17" t="n">
-        <v>-12.28811852101525</v>
+        <v>-12.28810408280026</v>
       </c>
       <c r="J17" t="n">
         <v>-12.49999563868442</v>
@@ -39015,7 +39015,7 @@
         <v>50.88300138028043</v>
       </c>
       <c r="I18" t="n">
-        <v>13.29247973056862</v>
+        <v>13.2924462595031</v>
       </c>
       <c r="J18" t="n">
         <v>42.60869233504585</v>
@@ -39038,13 +39038,13 @@
         <v>-18.96653110566366</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.484002920704985</v>
+        <v>-1.484012998322481</v>
       </c>
       <c r="H19" t="n">
         <v>-19.32324486904549</v>
       </c>
       <c r="I19" t="n">
-        <v>22.41423668033238</v>
+        <v>22.41424466278947</v>
       </c>
       <c r="J19" t="n">
         <v>-14.81481481481481</v>
@@ -39147,7 +39147,7 @@
         <v>24.71641426655784</v>
       </c>
       <c r="E2" t="n">
-        <v>38.56971060642054</v>
+        <v>38.56970207824606</v>
       </c>
       <c r="F2" t="n">
         <v>48.02197768635678</v>
@@ -39159,7 +39159,7 @@
         <v>26.11641041112731</v>
       </c>
       <c r="I2" t="n">
-        <v>13.54570754168862</v>
+        <v>13.54569421427558</v>
       </c>
       <c r="J2" t="n">
         <v>84.03669388711693</v>
@@ -39179,7 +39179,7 @@
         <v>21.52941086713005</v>
       </c>
       <c r="E3" t="n">
-        <v>48.10742776232155</v>
+        <v>48.10741480535528</v>
       </c>
       <c r="F3" t="n">
         <v>37.25662738916504</v>
@@ -39211,7 +39211,7 @@
         <v>21.30177788597374</v>
       </c>
       <c r="E4" t="n">
-        <v>54.55154123022257</v>
+        <v>54.55153813119511</v>
       </c>
       <c r="F4" t="n">
         <v>35.23950508448274</v>
@@ -39223,7 +39223,7 @@
         <v>18.55826056452661</v>
       </c>
       <c r="I4" t="n">
-        <v>15.84090469060915</v>
+        <v>15.84091850541089</v>
       </c>
       <c r="J4" t="n">
         <v>79.47977229122856</v>
@@ -39243,7 +39243,7 @@
         <v>25.38921902642992</v>
       </c>
       <c r="E5" t="n">
-        <v>61.79433305581566</v>
+        <v>61.79434466708855</v>
       </c>
       <c r="F5" t="n">
         <v>37.43092805121666</v>
@@ -39255,7 +39255,7 @@
         <v>18.42639458918014</v>
       </c>
       <c r="I5" t="n">
-        <v>15.59243490632829</v>
+        <v>15.5924279725592</v>
       </c>
       <c r="J5" t="n">
         <v>78.32370949116567</v>
@@ -39275,7 +39275,7 @@
         <v>23.483483105072</v>
       </c>
       <c r="E6" t="n">
-        <v>57.03963895200328</v>
+        <v>57.03962773712359</v>
       </c>
       <c r="F6" t="n">
         <v>32.87407769097221</v>
@@ -39287,7 +39287,7 @@
         <v>20.42312944893776</v>
       </c>
       <c r="I6" t="n">
-        <v>16.8489945570937</v>
+        <v>16.84898733968458</v>
       </c>
       <c r="J6" t="n">
         <v>74.1786665643551</v>
@@ -39339,7 +39339,7 @@
         <v>28.34835632939052</v>
       </c>
       <c r="E8" t="n">
-        <v>59.59136353965761</v>
+        <v>59.59137463922708</v>
       </c>
       <c r="F8" t="n">
         <v>30.24495302920487</v>
@@ -39351,7 +39351,7 @@
         <v>17.59891665078761</v>
       </c>
       <c r="I8" t="n">
-        <v>16.76870935549983</v>
+        <v>16.76871654600964</v>
       </c>
       <c r="J8" t="n">
         <v>64.5479489679206</v>
@@ -39403,7 +39403,7 @@
         <v>27.15151237718987</v>
       </c>
       <c r="E10" t="n">
-        <v>49.80727387211014</v>
+        <v>49.80728369996403</v>
       </c>
       <c r="F10" t="n">
         <v>30.0219527879438</v>
@@ -39447,7 +39447,7 @@
         <v>13.73462507545713</v>
       </c>
       <c r="I11" t="n">
-        <v>16.10095968062235</v>
+        <v>16.10096676605517</v>
       </c>
       <c r="J11" t="n">
         <v>56.99999959845292</v>
@@ -39467,7 +39467,7 @@
         <v>17.83197220667512</v>
       </c>
       <c r="E12" t="n">
-        <v>37.62082597735093</v>
+        <v>37.62083806523711</v>
       </c>
       <c r="F12" t="n">
         <v>29.44169870113738</v>
@@ -39563,7 +39563,7 @@
         <v>10.24259624810628</v>
       </c>
       <c r="E15" t="n">
-        <v>37.66878574882724</v>
+        <v>37.66877358173188</v>
       </c>
       <c r="F15" t="n">
         <v>18.36042100886153</v>
@@ -39627,7 +39627,7 @@
         <v>11.39784348605077</v>
       </c>
       <c r="E17" t="n">
-        <v>41.61504102066482</v>
+        <v>41.61502010126967</v>
       </c>
       <c r="F17" t="n">
         <v>17.49119689344376</v>
@@ -39671,7 +39671,7 @@
         <v>94.03570205320759</v>
       </c>
       <c r="I18" t="n">
-        <v>36.0335018181281</v>
+        <v>36.03351051593013</v>
       </c>
       <c r="J18" t="n">
         <v>117.663043844452</v>
@@ -39691,7 +39691,7 @@
         <v>18.21325520423087</v>
       </c>
       <c r="E19" t="n">
-        <v>46.8775899976761</v>
+        <v>46.87759936456168</v>
       </c>
       <c r="F19" t="n">
         <v>18.99342970595615</v>
@@ -39851,7 +39851,7 @@
         <v>1.75879592049748</v>
       </c>
       <c r="E24" t="n">
-        <v>51.81199574355784</v>
+        <v>51.81200920138686</v>
       </c>
       <c r="F24" t="n">
         <v>19.30215336975127</v>
@@ -39863,7 +39863,7 @@
         <v>86.52584846797919</v>
       </c>
       <c r="I24" t="n">
-        <v>25.56498092143338</v>
+        <v>25.56498906543911</v>
       </c>
       <c r="J24" t="n">
         <v>182.3157862613076</v>
@@ -39883,7 +39883,7 @@
         <v>4.647526447655226</v>
       </c>
       <c r="E25" t="n">
-        <v>48.72695435353167</v>
+        <v>48.72694435241242</v>
       </c>
       <c r="F25" t="n">
         <v>15.13592205797443</v>
@@ -39927,7 +39927,7 @@
         <v>66.09046092268591</v>
       </c>
       <c r="I26" t="n">
-        <v>19.3941404935573</v>
+        <v>19.39414825240846</v>
       </c>
       <c r="J26" t="n">
         <v>155.4089687454518</v>
@@ -39947,7 +39947,7 @@
         <v>-2.630266944568471</v>
       </c>
       <c r="E27" t="n">
-        <v>50.00000332429988</v>
+        <v>50.0000166214994</v>
       </c>
       <c r="F27" t="n">
         <v>17.44186046511629</v>
@@ -39979,7 +39979,7 @@
         <v>0.101012416840085</v>
       </c>
       <c r="E28" t="n">
-        <v>50.86871045504766</v>
+        <v>50.86870028982617</v>
       </c>
       <c r="F28" t="n">
         <v>21.00077612236952</v>
@@ -39991,7 +39991,7 @@
         <v>73.99363134446153</v>
       </c>
       <c r="I28" t="n">
-        <v>21.57638252010072</v>
+        <v>21.57639027866838</v>
       </c>
       <c r="J28" t="n">
         <v>151.4062423941993</v>
@@ -40023,7 +40023,7 @@
         <v>72.05968302788671</v>
       </c>
       <c r="I29" t="n">
-        <v>23.95292474688</v>
+        <v>23.95293274014536</v>
       </c>
       <c r="J29" t="n">
         <v>143.1331712833967</v>
@@ -40043,7 +40043,7 @@
         <v>0.450000762939462</v>
       </c>
       <c r="E30" t="n">
-        <v>47.70760404866208</v>
+        <v>47.7076172998504</v>
       </c>
       <c r="F30" t="n">
         <v>27.42365317882882</v>
@@ -40075,7 +40075,7 @@
         <v>0.1449216337739756</v>
       </c>
       <c r="E31" t="n">
-        <v>46.95331841391677</v>
+        <v>46.95333165365223</v>
       </c>
       <c r="F31" t="n">
         <v>15.39021874936699</v>
@@ -40087,7 +40087,7 @@
         <v>65.98794595089427</v>
       </c>
       <c r="I31" t="n">
-        <v>28.69149231270651</v>
+        <v>28.69148398560164</v>
       </c>
       <c r="J31" t="n">
         <v>126.1298637885552</v>
@@ -40107,7 +40107,7 @@
         <v>-1.052628312774884</v>
       </c>
       <c r="E32" t="n">
-        <v>49.89984245224899</v>
+        <v>49.89985267357972</v>
       </c>
       <c r="F32" t="n">
         <v>27.97941577115182</v>
@@ -40119,7 +40119,7 @@
         <v>68.60328526038532</v>
       </c>
       <c r="I32" t="n">
-        <v>28.59036001224431</v>
+        <v>28.59035158704684</v>
       </c>
       <c r="J32" t="n">
         <v>136.0106421941653</v>
@@ -40139,7 +40139,7 @@
         <v>-2.660330100898289</v>
       </c>
       <c r="E33" t="n">
-        <v>48.02573405358237</v>
+        <v>48.02573758579716</v>
       </c>
       <c r="F33" t="n">
         <v>17.99588316396285</v>
@@ -40215,7 +40215,7 @@
         <v>64.23357664233578</v>
       </c>
       <c r="I35" t="n">
-        <v>27.1980016778619</v>
+        <v>27.19799344911933</v>
       </c>
       <c r="J35" t="n">
         <v>137.8151252422787</v>
@@ -40235,7 +40235,7 @@
         <v>-0.4102560190054061</v>
       </c>
       <c r="E36" t="n">
-        <v>48.62593874181287</v>
+        <v>48.62594908343376</v>
       </c>
       <c r="F36" t="n">
         <v>11.65387061590668</v>
@@ -40247,7 +40247,7 @@
         <v>56.8334812026194</v>
       </c>
       <c r="I36" t="n">
-        <v>22.65728440839494</v>
+        <v>22.657292123892</v>
       </c>
       <c r="J36" t="n">
         <v>127.3033753857291</v>
@@ -40267,7 +40267,7 @@
         <v>-5.088162264342754</v>
       </c>
       <c r="E37" t="n">
-        <v>39.51576792072717</v>
+        <v>39.51575431044456</v>
       </c>
       <c r="F37" t="n">
         <v>5.373968208882274</v>
@@ -40279,7 +40279,7 @@
         <v>49.29618947317174</v>
       </c>
       <c r="I37" t="n">
-        <v>15.74543228600769</v>
+        <v>15.74542504218792</v>
       </c>
       <c r="J37" t="n">
         <v>111.15383897912</v>
@@ -40299,7 +40299,7 @@
         <v>-9.425834207230599</v>
       </c>
       <c r="E38" t="n">
-        <v>39.77350033524889</v>
+        <v>39.77348672798779</v>
       </c>
       <c r="F38" t="n">
         <v>-1.762887330280316</v>
@@ -40331,7 +40331,7 @@
         <v>-7.586202295846512</v>
       </c>
       <c r="E39" t="n">
-        <v>40.77042925623107</v>
+        <v>40.77041965314101</v>
       </c>
       <c r="F39" t="n">
         <v>-0.3809562562003932</v>
@@ -40375,7 +40375,7 @@
         <v>62.45973288227488</v>
       </c>
       <c r="I40" t="n">
-        <v>1.128983084690516</v>
+        <v>1.128971419277369</v>
       </c>
       <c r="J40" t="n">
         <v>134.7826177095873</v>
@@ -40427,7 +40427,7 @@
         <v>-4.7715761302202</v>
       </c>
       <c r="E42" t="n">
-        <v>51.01853360181148</v>
+        <v>51.01852289181952</v>
       </c>
       <c r="F42" t="n">
         <v>0.8595328089425314</v>
@@ -40459,7 +40459,7 @@
         <v>-3.115572581757442</v>
       </c>
       <c r="E43" t="n">
-        <v>49.36975835587943</v>
+        <v>49.36975473509047</v>
       </c>
       <c r="F43" t="n">
         <v>4.18754296740822</v>
@@ -40491,7 +40491,7 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>50.46684566231154</v>
+        <v>50.46685642285065</v>
       </c>
       <c r="F44" t="n">
         <v>12.49999751647324</v>
@@ -40535,7 +40535,7 @@
         <v>71.45801931839102</v>
       </c>
       <c r="I45" t="n">
-        <v>12.16106151167788</v>
+        <v>12.1610683896405</v>
       </c>
       <c r="J45" t="n">
         <v>157.6646515776742</v>
@@ -40599,7 +40599,7 @@
         <v>85.00471194850942</v>
       </c>
       <c r="I47" t="n">
-        <v>9.613838637455906</v>
+        <v>9.613845276460232</v>
       </c>
       <c r="J47" t="n">
         <v>151.6363664106889</v>
@@ -40619,7 +40619,7 @@
         <v>6.467394340917232</v>
       </c>
       <c r="E48" t="n">
-        <v>46.2763635483981</v>
+        <v>46.27635349583639</v>
       </c>
       <c r="F48" t="n">
         <v>25.26545854048294</v>
@@ -40631,7 +40631,7 @@
         <v>86.16140643431169</v>
       </c>
       <c r="I48" t="n">
-        <v>12.55596944361153</v>
+        <v>12.55596261032248</v>
       </c>
       <c r="J48" t="n">
         <v>159.4642984056154</v>
@@ -40651,7 +40651,7 @@
         <v>8.154267621721157</v>
       </c>
       <c r="E49" t="n">
-        <v>46.82647017740005</v>
+        <v>46.82648416678226</v>
       </c>
       <c r="F49" t="n">
         <v>21.11271857609913</v>
@@ -40663,7 +40663,7 @@
         <v>71.57738095238095</v>
       </c>
       <c r="I49" t="n">
-        <v>11.99740298068421</v>
+        <v>11.99740976505248</v>
       </c>
       <c r="J49" t="n">
         <v>158.230079573006</v>
@@ -40747,7 +40747,7 @@
         <v>3.767314869352423</v>
       </c>
       <c r="E52" t="n">
-        <v>42.7421148615067</v>
+        <v>42.74212492167262</v>
       </c>
       <c r="F52" t="n">
         <v>20.88757849896625</v>
@@ -40759,7 +40759,7 @@
         <v>48.54479267405647</v>
       </c>
       <c r="I52" t="n">
-        <v>8.042045115715425</v>
+        <v>8.042051785476056</v>
       </c>
       <c r="J52" t="n">
         <v>110.3013757156999</v>
@@ -40779,7 +40779,7 @@
         <v>-0.6521681215901576</v>
       </c>
       <c r="E53" t="n">
-        <v>36.68110950479731</v>
+        <v>36.68112349098636</v>
       </c>
       <c r="F53" t="n">
         <v>9.971790610249332</v>
@@ -40823,7 +40823,7 @@
         <v>41.15079311579386</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.52174699598645</v>
+        <v>-1.521758640085147</v>
       </c>
       <c r="J54" t="n">
         <v>86.16581204926534</v>
@@ -40855,7 +40855,7 @@
         <v>36.97116125920574</v>
       </c>
       <c r="I55" t="n">
-        <v>-4.102535207427882</v>
+        <v>-4.102523938621339</v>
       </c>
       <c r="J55" t="n">
         <v>64.87922613616699</v>
@@ -40887,7 +40887,7 @@
         <v>43.77442279436383</v>
       </c>
       <c r="I56" t="n">
-        <v>-3.550945305250486</v>
+        <v>-3.550933979170845</v>
       </c>
       <c r="J56" t="n">
         <v>74.76772784887457</v>
@@ -40907,7 +40907,7 @@
         <v>-2.895437100396392</v>
       </c>
       <c r="E57" t="n">
-        <v>46.03765664399515</v>
+        <v>46.03767088371107</v>
       </c>
       <c r="F57" t="n">
         <v>17.16470691777749</v>
@@ -40919,7 +40919,7 @@
         <v>39.5845017315855</v>
       </c>
       <c r="I57" t="n">
-        <v>-4.840900868211085</v>
+        <v>-4.840889679246652</v>
       </c>
       <c r="J57" t="n">
         <v>61.69810163036917</v>
@@ -40939,7 +40939,7 @@
         <v>-4.116098444549698</v>
       </c>
       <c r="E58" t="n">
-        <v>41.38319910862871</v>
+        <v>41.38318530518315</v>
       </c>
       <c r="F58" t="n">
         <v>2.990288101739491</v>
@@ -40971,7 +40971,7 @@
         <v>-4.293192033753879</v>
       </c>
       <c r="E59" t="n">
-        <v>43.82646747624919</v>
+        <v>43.82647727908604</v>
       </c>
       <c r="F59" t="n">
         <v>5.94736400403475</v>
@@ -41035,7 +41035,7 @@
         <v>-16.15763006192025</v>
       </c>
       <c r="E61" t="n">
-        <v>44.92178179656079</v>
+        <v>44.92179529589908</v>
       </c>
       <c r="F61" t="n">
         <v>-6.880840531123522</v>
@@ -41099,7 +41099,7 @@
         <v>-13.16582403069547</v>
       </c>
       <c r="E63" t="n">
-        <v>52.36658211824747</v>
+        <v>52.36659633483563</v>
       </c>
       <c r="F63" t="n">
         <v>-4.954792961494691</v>
@@ -41111,7 +41111,7 @@
         <v>52.72230156143125</v>
       </c>
       <c r="I63" t="n">
-        <v>5.391828203771198</v>
+        <v>5.391816556919182</v>
       </c>
       <c r="J63" t="n">
         <v>75.11312260151992</v>
@@ -41163,7 +41163,7 @@
         <v>-9.5696171627769</v>
       </c>
       <c r="E65" t="n">
-        <v>53.37991067295851</v>
+        <v>53.37992447951525</v>
       </c>
       <c r="F65" t="n">
         <v>-2.789282531167381</v>
@@ -41195,7 +41195,7 @@
         <v>-11.31513063255917</v>
       </c>
       <c r="E66" t="n">
-        <v>56.02259572511812</v>
+        <v>56.02260652743436</v>
       </c>
       <c r="F66" t="n">
         <v>-3.191753439454137</v>
@@ -41207,7 +41207,7 @@
         <v>69.55524373430775</v>
       </c>
       <c r="I66" t="n">
-        <v>10.17211991406539</v>
+        <v>10.17210763952565</v>
       </c>
       <c r="J66" t="n">
         <v>92.45901366939118</v>
@@ -41227,7 +41227,7 @@
         <v>-11.01736652795241</v>
       </c>
       <c r="E67" t="n">
-        <v>50.77261751103143</v>
+        <v>50.77263103718916</v>
       </c>
       <c r="F67" t="n">
         <v>-5.080884384452744</v>
@@ -41239,7 +41239,7 @@
         <v>74.20005719956657</v>
       </c>
       <c r="I67" t="n">
-        <v>10.42934932447941</v>
+        <v>10.42936182277174</v>
       </c>
       <c r="J67" t="n">
         <v>106.4114841006974</v>
@@ -41259,7 +41259,7 @@
         <v>-9.423563890822795</v>
       </c>
       <c r="E68" t="n">
-        <v>49.7238733754217</v>
+        <v>49.72388691054292</v>
       </c>
       <c r="F68" t="n">
         <v>-3.992768548930603</v>
@@ -41271,7 +41271,7 @@
         <v>70.46093895677912</v>
       </c>
       <c r="I68" t="n">
-        <v>8.984565541660317</v>
+        <v>8.984577771064984</v>
       </c>
       <c r="J68" t="n">
         <v>112.8708253134189</v>
@@ -41367,7 +41367,7 @@
         <v>51.19813928486645</v>
       </c>
       <c r="I71" t="n">
-        <v>10.13101918945343</v>
+        <v>10.13100675342484</v>
       </c>
       <c r="J71" t="n">
         <v>111.2230221092348</v>
@@ -41399,7 +41399,7 @@
         <v>52.95796817224014</v>
       </c>
       <c r="I72" t="n">
-        <v>6.87044683550917</v>
+        <v>6.870435006199105</v>
       </c>
       <c r="J72" t="n">
         <v>121.2440312078746</v>
@@ -41451,7 +41451,7 @@
         <v>-10.50251353091357</v>
       </c>
       <c r="E74" t="n">
-        <v>37.76563551471814</v>
+        <v>37.76564791574937</v>
       </c>
       <c r="F74" t="n">
         <v>-24.46927078175064</v>
@@ -41463,7 +41463,7 @@
         <v>37.45292871774588</v>
       </c>
       <c r="I74" t="n">
-        <v>4.406870864909274</v>
+        <v>4.406859319154965</v>
       </c>
       <c r="J74" t="n">
         <v>103.5775775390632</v>
@@ -41483,7 +41483,7 @@
         <v>-11.97995591778075</v>
       </c>
       <c r="E75" t="n">
-        <v>35.3000326287824</v>
+        <v>35.300020332275</v>
       </c>
       <c r="F75" t="n">
         <v>-18.87479351610046</v>
@@ -41515,7 +41515,7 @@
         <v>-11.60304744813735</v>
       </c>
       <c r="E76" t="n">
-        <v>32.89662954383419</v>
+        <v>32.8966170006417</v>
       </c>
       <c r="F76" t="n">
         <v>-17.12165045191634</v>
@@ -41527,7 +41527,7 @@
         <v>29.75552684353173</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.790587515014507</v>
+        <v>-0.7905768063145135</v>
       </c>
       <c r="J76" t="n">
         <v>87.39039515006255</v>
@@ -41547,7 +41547,7 @@
         <v>-16.59367383947344</v>
       </c>
       <c r="E77" t="n">
-        <v>27.44299051570651</v>
+        <v>27.44300298995188</v>
       </c>
       <c r="F77" t="n">
         <v>-16.99586307263094</v>
@@ -41579,7 +41579,7 @@
         <v>-19.17274342085357</v>
       </c>
       <c r="E78" t="n">
-        <v>26.50176102394366</v>
+        <v>26.50176570435701</v>
       </c>
       <c r="F78" t="n">
         <v>-14.20658392523141</v>
@@ -41591,7 +41591,7 @@
         <v>37.16040451905292</v>
       </c>
       <c r="I78" t="n">
-        <v>-5.63649022866074</v>
+        <v>-5.636500384992004</v>
       </c>
       <c r="J78" t="n">
         <v>92.88792469130138</v>
@@ -41675,7 +41675,7 @@
         <v>-24.76658411486981</v>
       </c>
       <c r="E81" t="n">
-        <v>28.5714340963751</v>
+        <v>28.57142580895549</v>
       </c>
       <c r="F81" t="n">
         <v>-16.15832902940159</v>
@@ -41687,7 +41687,7 @@
         <v>44.05244047508194</v>
       </c>
       <c r="I81" t="n">
-        <v>-11.30203660674795</v>
+        <v>-11.30204587694931</v>
       </c>
       <c r="J81" t="n">
         <v>86.99152692711512</v>
@@ -41707,7 +41707,7 @@
         <v>-27.62790502503861</v>
       </c>
       <c r="E82" t="n">
-        <v>26.98314264407708</v>
+        <v>26.98314730158067</v>
       </c>
       <c r="F82" t="n">
         <v>-15.09280158634767</v>
@@ -41739,7 +41739,7 @@
         <v>-34.48276159737812</v>
       </c>
       <c r="E83" t="n">
-        <v>28.51448033045003</v>
+        <v>28.51446747407287</v>
       </c>
       <c r="F83" t="n">
         <v>-19.74900728652863</v>
@@ -41803,7 +41803,7 @@
         <v>-24.665128160175</v>
       </c>
       <c r="E85" t="n">
-        <v>27.92016784817664</v>
+        <v>27.92017608149169</v>
       </c>
       <c r="F85" t="n">
         <v>-16.67054649645153</v>
@@ -41815,7 +41815,7 @@
         <v>65.04654719786612</v>
       </c>
       <c r="I85" t="n">
-        <v>-15.66178711285019</v>
+        <v>-15.66179518724001</v>
       </c>
       <c r="J85" t="n">
         <v>97.04844951046681</v>
@@ -41835,7 +41835,7 @@
         <v>-26.6666637832975</v>
       </c>
       <c r="E86" t="n">
-        <v>28.70116495989465</v>
+        <v>28.70115663257717</v>
       </c>
       <c r="F86" t="n">
         <v>-17.14285992776975</v>
@@ -41867,7 +41867,7 @@
         <v>-26.10859890573426</v>
       </c>
       <c r="E87" t="n">
-        <v>30.99703429220788</v>
+        <v>30.99702123862926</v>
       </c>
       <c r="F87" t="n">
         <v>-18.06414822509883</v>
@@ -41899,7 +41899,7 @@
         <v>-27.29792125425134</v>
       </c>
       <c r="E88" t="n">
-        <v>26.79487970919705</v>
+        <v>26.79485831618089</v>
       </c>
       <c r="F88" t="n">
         <v>-22.44094964591114</v>
@@ -41943,7 +41943,7 @@
         <v>62.23793649992655</v>
       </c>
       <c r="I89" t="n">
-        <v>-15.4971246985837</v>
+        <v>-15.49711696089192</v>
       </c>
       <c r="J89" t="n">
         <v>94.18344870303281</v>
@@ -41963,7 +41963,7 @@
         <v>-25.66037895417199</v>
       </c>
       <c r="E90" t="n">
-        <v>28.1820197606033</v>
+        <v>28.18202818962325</v>
       </c>
       <c r="F90" t="n">
         <v>-21.60274235468711</v>
@@ -41975,7 +41975,7 @@
         <v>44.01810748398501</v>
       </c>
       <c r="I90" t="n">
-        <v>-16.88544388826343</v>
+        <v>-16.88543627572069</v>
       </c>
       <c r="J90" t="n">
         <v>81.88842255714064</v>
@@ -41995,7 +41995,7 @@
         <v>-27.11316392142076</v>
       </c>
       <c r="E91" t="n">
-        <v>23.32124539191589</v>
+        <v>23.32125845384157</v>
       </c>
       <c r="F91" t="n">
         <v>-24.73446258717338</v>
@@ -42007,7 +42007,7 @@
         <v>35.52879303916819</v>
       </c>
       <c r="I91" t="n">
-        <v>-23.03242925559732</v>
+        <v>-23.03242255709873</v>
       </c>
       <c r="J91" t="n">
         <v>68.10019640513771</v>
@@ -42059,7 +42059,7 @@
         <v>-33.75854461744496</v>
       </c>
       <c r="E93" t="n">
-        <v>13.49679986444057</v>
+        <v>13.49678679972988</v>
       </c>
       <c r="F93" t="n">
         <v>-33.28873780551388</v>
@@ -42091,7 +42091,7 @@
         <v>-32.86343938807552</v>
       </c>
       <c r="E94" t="n">
-        <v>13.02817533738021</v>
+        <v>13.0281626461012</v>
       </c>
       <c r="F94" t="n">
         <v>-31.92243919478229</v>
@@ -42103,7 +42103,7 @@
         <v>18.74325570428619</v>
       </c>
       <c r="I94" t="n">
-        <v>-28.0068053081651</v>
+        <v>-28.00679894982006</v>
       </c>
       <c r="J94" t="n">
         <v>27.89474196050972</v>
@@ -42155,7 +42155,7 @@
         <v>-39.19354682410292</v>
       </c>
       <c r="E96" t="n">
-        <v>14.19141167535614</v>
+        <v>14.19141889163848</v>
       </c>
       <c r="F96" t="n">
         <v>-43.65987090351605</v>
@@ -42187,7 +42187,7 @@
         <v>-37.38589247413267</v>
       </c>
       <c r="E97" t="n">
-        <v>15.21784828805857</v>
+        <v>15.21784099939436</v>
       </c>
       <c r="F97" t="n">
         <v>-43.28643185409469</v>
@@ -42219,7 +42219,7 @@
         <v>-36.22489816175252</v>
       </c>
       <c r="E98" t="n">
-        <v>14.42207519042114</v>
+        <v>14.42208246479413</v>
       </c>
       <c r="F98" t="n">
         <v>-52.13567772568902</v>
@@ -42295,7 +42295,7 @@
         <v>15.07653487454037</v>
       </c>
       <c r="I100" t="n">
-        <v>-33.8904169084052</v>
+        <v>-33.89041151541271</v>
       </c>
       <c r="J100" t="n">
         <v>27.6699069578042</v>
@@ -42327,7 +42327,7 @@
         <v>17.94541203322633</v>
       </c>
       <c r="I101" t="n">
-        <v>-31.17109576206706</v>
+        <v>-31.17110158740718</v>
       </c>
       <c r="J101" t="n">
         <v>28.66883782396286</v>
@@ -42379,7 +42379,7 @@
         <v>-37.47898911160345</v>
       </c>
       <c r="E103" t="n">
-        <v>-3.813646722865827</v>
+        <v>-3.813640407312757</v>
       </c>
       <c r="F103" t="n">
         <v>-61.42636857635259</v>
@@ -42411,7 +42411,7 @@
         <v>-38.02935221563132</v>
       </c>
       <c r="E104" t="n">
-        <v>-4.049334168701613</v>
+        <v>-4.049327871322895</v>
       </c>
       <c r="F104" t="n">
         <v>-60.6574271929146</v>
@@ -42423,7 +42423,7 @@
         <v>9.913208228453851</v>
       </c>
       <c r="I104" t="n">
-        <v>-35.85256724208779</v>
+        <v>-35.85257273941228</v>
       </c>
       <c r="J104" t="n">
         <v>23.86554108948267</v>
@@ -42539,7 +42539,7 @@
         <v>-34.87069327681005</v>
       </c>
       <c r="E108" t="n">
-        <v>0.6920890135108326</v>
+        <v>0.6920954001579327</v>
       </c>
       <c r="F108" t="n">
         <v>-56.18415731425067</v>
@@ -42571,7 +42571,7 @@
         <v>-38.2809222994163</v>
       </c>
       <c r="E109" t="n">
-        <v>-6.78485575492701</v>
+        <v>-6.784861443789014</v>
       </c>
       <c r="F109" t="n">
         <v>-56.1025635808961</v>
@@ -42583,7 +42583,7 @@
         <v>2.676028157570309</v>
       </c>
       <c r="I109" t="n">
-        <v>-34.05137407827211</v>
+        <v>-34.05136838470172</v>
       </c>
       <c r="J109" t="n">
         <v>26.24584557611403</v>
@@ -42603,7 +42603,7 @@
         <v>-38.41336313097599</v>
       </c>
       <c r="E110" t="n">
-        <v>-1.049657998912068</v>
+        <v>-1.049651814667596</v>
       </c>
       <c r="F110" t="n">
         <v>-55.1449584922653</v>
@@ -42615,7 +42615,7 @@
         <v>6.024615316080983</v>
       </c>
       <c r="I110" t="n">
-        <v>-31.27061043654561</v>
+        <v>-31.27061650294681</v>
       </c>
       <c r="J110" t="n">
         <v>33.22203842896631</v>
@@ -42635,7 +42635,7 @@
         <v>-38.03757962483449</v>
       </c>
       <c r="E111" t="n">
-        <v>0.632431300721481</v>
+        <v>0.6324251301784045</v>
       </c>
       <c r="F111" t="n">
         <v>-54.47863391321948</v>
@@ -42699,7 +42699,7 @@
         <v>-38.7500007947286</v>
       </c>
       <c r="E113" t="n">
-        <v>-1.713949824055983</v>
+        <v>-1.713949720608687</v>
       </c>
       <c r="F113" t="n">
         <v>-54.22889949879295</v>
@@ -42731,7 +42731,7 @@
         <v>-42.96153875497671</v>
       </c>
       <c r="E114" t="n">
-        <v>-15.95987381179289</v>
+        <v>-15.959870204464</v>
       </c>
       <c r="F114" t="n">
         <v>-55.92657561500155</v>
@@ -42827,7 +42827,7 @@
         <v>-44.84615325927734</v>
       </c>
       <c r="E117" t="n">
-        <v>-13.21917375442618</v>
+        <v>-13.21917958333557</v>
       </c>
       <c r="F117" t="n">
         <v>-55.92658828357197</v>
@@ -42891,7 +42891,7 @@
         <v>-41.87633402561816</v>
       </c>
       <c r="E119" t="n">
-        <v>-18.0512117287556</v>
+        <v>-18.05122097776638</v>
       </c>
       <c r="F119" t="n">
         <v>-56.31058995863971</v>
@@ -42923,7 +42923,7 @@
         <v>-42.79069788072998</v>
       </c>
       <c r="E120" t="n">
-        <v>-18.96608874513238</v>
+        <v>-18.96607964296703</v>
       </c>
       <c r="F120" t="n">
         <v>-56.69829342607511</v>
@@ -42955,7 +42955,7 @@
         <v>-41.32780033399969</v>
       </c>
       <c r="E121" t="n">
-        <v>-16.14652467077281</v>
+        <v>-16.14651905964717</v>
       </c>
       <c r="F121" t="n">
         <v>-57.14155223271617</v>
@@ -42999,7 +42999,7 @@
         <v>10.24109211646398</v>
       </c>
       <c r="I122" t="n">
-        <v>-41.40768769062964</v>
+        <v>-41.40768277612826</v>
       </c>
       <c r="J122" t="n">
         <v>42.65420503705462</v>
@@ -43031,7 +43031,7 @@
         <v>12.00888037813888</v>
       </c>
       <c r="I123" t="n">
-        <v>-42.35447517905221</v>
+        <v>-42.35447034363565</v>
       </c>
       <c r="J123" t="n">
         <v>43.89312849283209</v>
@@ -43063,7 +43063,7 @@
         <v>-0.8441437102060356</v>
       </c>
       <c r="I124" t="n">
-        <v>-42.70334090588286</v>
+        <v>-42.70334575751823</v>
       </c>
       <c r="J124" t="n">
         <v>36.54915842401909</v>
@@ -43083,7 +43083,7 @@
         <v>-44.06438871165855</v>
       </c>
       <c r="E125" t="n">
-        <v>-19.65920559792231</v>
+        <v>-19.65921433551706</v>
       </c>
       <c r="F125" t="n">
         <v>-62.04201834542411</v>
@@ -43095,7 +43095,7 @@
         <v>-0.9950223577321893</v>
       </c>
       <c r="I125" t="n">
-        <v>-42.56499686306486</v>
+        <v>-42.56499198767874</v>
       </c>
       <c r="J125" t="n">
         <v>38.07183139644308</v>
@@ -43147,7 +43147,7 @@
         <v>-45.25879720144958</v>
       </c>
       <c r="E127" t="n">
-        <v>-31.44791479939482</v>
+        <v>-31.44790974132207</v>
       </c>
       <c r="F127" t="n">
         <v>-64.48646305395978</v>
@@ -43275,7 +43275,7 @@
         <v>-38.22222391764323</v>
       </c>
       <c r="E131" t="n">
-        <v>-28.66039098574015</v>
+        <v>-28.66038601708145</v>
       </c>
       <c r="F131" t="n">
         <v>-60.87921861989671</v>
@@ -43287,7 +43287,7 @@
         <v>11.20226017119483</v>
       </c>
       <c r="I131" t="n">
-        <v>-41.57756135837645</v>
+        <v>-41.57756646105136</v>
       </c>
       <c r="J131" t="n">
         <v>50.06395514631925</v>
@@ -43307,7 +43307,7 @@
         <v>-37.71428537892771</v>
       </c>
       <c r="E132" t="n">
-        <v>-28.44838815136688</v>
+        <v>-28.44839309277756</v>
       </c>
       <c r="F132" t="n">
         <v>-57.52336377295379</v>
@@ -43339,7 +43339,7 @@
         <v>-39.29359721158256</v>
       </c>
       <c r="E133" t="n">
-        <v>-31.89682422506088</v>
+        <v>-31.89681766180208</v>
       </c>
       <c r="F133" t="n">
         <v>-56.86676433086298</v>
@@ -43403,7 +43403,7 @@
         <v>-39.18181766163219</v>
       </c>
       <c r="E135" t="n">
-        <v>-29.8943198980845</v>
+        <v>-29.89430845995157</v>
       </c>
       <c r="F135" t="n">
         <v>-55.97900230427739</v>
@@ -43467,7 +43467,7 @@
         <v>-41.2641063072619</v>
       </c>
       <c r="E137" t="n">
-        <v>-34.25576189254548</v>
+        <v>-34.25575730483226</v>
       </c>
       <c r="F137" t="n">
         <v>-56.62921337306769</v>
@@ -43479,7 +43479,7 @@
         <v>-0.8227812344208774</v>
       </c>
       <c r="I137" t="n">
-        <v>-43.53504640515198</v>
+        <v>-43.53504135301615</v>
       </c>
       <c r="J137" t="n">
         <v>46.43016219484324</v>
@@ -43499,7 +43499,7 @@
         <v>-38.77646951114431</v>
       </c>
       <c r="E138" t="n">
-        <v>-38.27639900697836</v>
+        <v>-38.27638938277526</v>
       </c>
       <c r="F138" t="n">
         <v>-55.96958453493185</v>
@@ -43531,7 +43531,7 @@
         <v>-33.90243809397627</v>
       </c>
       <c r="E139" t="n">
-        <v>-36.75832996076532</v>
+        <v>-36.75832572741635</v>
       </c>
       <c r="F139" t="n">
         <v>-49.86285836356027</v>
@@ -43543,7 +43543,7 @@
         <v>11.39967947776015</v>
       </c>
       <c r="I139" t="n">
-        <v>-36.11916743903318</v>
+        <v>-36.11916133833199</v>
       </c>
       <c r="J139" t="n">
         <v>75.85081528702973</v>
@@ -43595,7 +43595,7 @@
         <v>-32.12871524589028</v>
       </c>
       <c r="E141" t="n">
-        <v>-32.28313624311352</v>
+        <v>-32.2831469020805</v>
       </c>
       <c r="F141" t="n">
         <v>-43.95747457582054</v>
@@ -43607,7 +43607,7 @@
         <v>11.78529754959159</v>
       </c>
       <c r="I141" t="n">
-        <v>-32.26880534741482</v>
+        <v>-32.26879864064875</v>
       </c>
       <c r="J141" t="n">
         <v>79.66746349443316</v>
@@ -43627,7 +43627,7 @@
         <v>-31.4987748448557</v>
       </c>
       <c r="E142" t="n">
-        <v>-32.50762230682122</v>
+        <v>-32.50761786349332</v>
       </c>
       <c r="F142" t="n">
         <v>-46.5503629780039</v>
@@ -43659,7 +43659,7 @@
         <v>-33.84615297239228</v>
       </c>
       <c r="E143" t="n">
-        <v>-35.46163637158381</v>
+        <v>-35.46164071660527</v>
       </c>
       <c r="F143" t="n">
         <v>-51.06795889575086</v>
@@ -43691,7 +43691,7 @@
         <v>-33.90862967753029</v>
       </c>
       <c r="E144" t="n">
-        <v>-36.97423460587854</v>
+        <v>-36.97424007121808</v>
       </c>
       <c r="F144" t="n">
         <v>-49.50652575035288</v>
@@ -43723,7 +43723,7 @@
         <v>-32.57731865513828</v>
       </c>
       <c r="E145" t="n">
-        <v>-33.10222333815624</v>
+        <v>-33.10222787693342</v>
       </c>
       <c r="F145" t="n">
         <v>-47.72093129712481</v>
@@ -43735,7 +43735,7 @@
         <v>2.334533491450208</v>
       </c>
       <c r="I145" t="n">
-        <v>-33.51296118514819</v>
+        <v>-33.51296794739835</v>
       </c>
       <c r="J145" t="n">
         <v>79.7908029562787</v>
@@ -43755,7 +43755,7 @@
         <v>-32.98968940399975</v>
       </c>
       <c r="E146" t="n">
-        <v>-32.82846017281587</v>
+        <v>-32.82847077144174</v>
       </c>
       <c r="F146" t="n">
         <v>-50.13210990744989</v>
@@ -43767,7 +43767,7 @@
         <v>-4.631267327895838</v>
       </c>
       <c r="I146" t="n">
-        <v>-34.63595419177665</v>
+        <v>-34.63594768313144</v>
       </c>
       <c r="J146" t="n">
         <v>71.57684970564392</v>
@@ -43819,7 +43819,7 @@
         <v>-32.69521712881676</v>
       </c>
       <c r="E148" t="n">
-        <v>-33.61837206509205</v>
+        <v>-33.61837794033982</v>
       </c>
       <c r="F148" t="n">
         <v>-50.8521140595779</v>
@@ -43831,7 +43831,7 @@
         <v>-6.028498086992817</v>
       </c>
       <c r="I148" t="n">
-        <v>-34.28804916033518</v>
+        <v>-34.28805565881679</v>
       </c>
       <c r="J148" t="n">
         <v>53.29710430619193</v>
@@ -43915,7 +43915,7 @@
         <v>-42.04651145047919</v>
       </c>
       <c r="E151" t="n">
-        <v>-40.1821004663875</v>
+        <v>-40.1821013090503</v>
       </c>
       <c r="F151" t="n">
         <v>-54.39159419656274</v>
@@ -43947,7 +43947,7 @@
         <v>-39.58139641340389</v>
       </c>
       <c r="E152" t="n">
-        <v>-37.04565432657586</v>
+        <v>-37.04564463586239</v>
       </c>
       <c r="F152" t="n">
         <v>-53.60400625525475</v>
@@ -43979,7 +43979,7 @@
         <v>-41.59453644999592</v>
       </c>
       <c r="E153" t="n">
-        <v>-38.13498321627997</v>
+        <v>-38.13497790868293</v>
       </c>
       <c r="F153" t="n">
         <v>-55.56276981035423</v>
@@ -43991,7 +43991,7 @@
         <v>-16.46675455896869</v>
       </c>
       <c r="I153" t="n">
-        <v>-41.94473500657481</v>
+        <v>-41.94472969593319</v>
       </c>
       <c r="J153" t="n">
         <v>22.64151237635372</v>
@@ -44023,7 +44023,7 @@
         <v>-15.20339189949682</v>
       </c>
       <c r="I154" t="n">
-        <v>-40.56723806517864</v>
+        <v>-40.56723259305854</v>
       </c>
       <c r="J154" t="n">
         <v>20.02998683900788</v>
@@ -44043,7 +44043,7 @@
         <v>-39.45701410186536</v>
       </c>
       <c r="E155" t="n">
-        <v>-36.07449031108776</v>
+        <v>-36.07449555886241</v>
       </c>
       <c r="F155" t="n">
         <v>-51.83269228782829</v>
@@ -44055,7 +44055,7 @@
         <v>-14.68718460786851</v>
       </c>
       <c r="I155" t="n">
-        <v>-37.99085613237384</v>
+        <v>-37.99086187941774</v>
       </c>
       <c r="J155" t="n">
         <v>27.69939575660545</v>
@@ -44087,7 +44087,7 @@
         <v>-11.96105995313918</v>
       </c>
       <c r="I156" t="n">
-        <v>-35.97284836459775</v>
+        <v>-35.97285437285689</v>
       </c>
       <c r="J156" t="n">
         <v>34.93548977759578</v>
@@ -44139,7 +44139,7 @@
         <v>-34.9769623935906</v>
       </c>
       <c r="E158" t="n">
-        <v>-33.49169830616715</v>
+        <v>-33.49170244123877</v>
       </c>
       <c r="F158" t="n">
         <v>-49.31460605578476</v>
@@ -44203,7 +44203,7 @@
         <v>-29.01205039886107</v>
       </c>
       <c r="E160" t="n">
-        <v>-27.14083902839913</v>
+        <v>-27.1408366814982</v>
       </c>
       <c r="F160" t="n">
         <v>-46.60070067860755</v>
@@ -44215,7 +44215,7 @@
         <v>33.15829160473547</v>
       </c>
       <c r="I160" t="n">
-        <v>-29.84938585107336</v>
+        <v>-29.84939278684298</v>
       </c>
       <c r="J160" t="n">
         <v>67.10172765520876</v>
@@ -44247,7 +44247,7 @@
         <v>38.5684914172453</v>
       </c>
       <c r="I161" t="n">
-        <v>-29.7419029828034</v>
+        <v>-29.74189607402291</v>
       </c>
       <c r="J161" t="n">
         <v>62.23034118107906</v>
@@ -44267,7 +44267,7 @@
         <v>-36.22727394104004</v>
       </c>
       <c r="E162" t="n">
-        <v>-33.12632209017097</v>
+        <v>-33.12631667581559</v>
       </c>
       <c r="F162" t="n">
         <v>-51.18435907630281</v>
@@ -44299,7 +44299,7 @@
         <v>-36.56108499654562</v>
       </c>
       <c r="E163" t="n">
-        <v>-30.31612554162724</v>
+        <v>-30.31613958799745</v>
       </c>
       <c r="F163" t="n">
         <v>-50.39954164408403</v>
@@ -44311,7 +44311,7 @@
         <v>35.25827976252069</v>
       </c>
       <c r="I163" t="n">
-        <v>-30.97237478082654</v>
+        <v>-30.97236803094082</v>
       </c>
       <c r="J163" t="n">
         <v>47.45098657865709</v>
@@ -44331,7 +44331,7 @@
         <v>-37.483146753204</v>
       </c>
       <c r="E164" t="n">
-        <v>-32.68096093226646</v>
+        <v>-32.68094753767251</v>
       </c>
       <c r="F164" t="n">
         <v>-48.08486004347705</v>
@@ -44363,7 +44363,7 @@
         <v>-40.39734998955379</v>
       </c>
       <c r="E165" t="n">
-        <v>-32.87279634781893</v>
+        <v>-32.87279104672564</v>
       </c>
       <c r="F165" t="n">
         <v>-50.55082406989408</v>
@@ -44395,7 +44395,7 @@
         <v>-40.43955960116543</v>
       </c>
       <c r="E166" t="n">
-        <v>-32.08065667981757</v>
+        <v>-32.08065123048447</v>
       </c>
       <c r="F166" t="n">
         <v>-53.59653548729015</v>
@@ -44427,7 +44427,7 @@
         <v>-38.52349200624654</v>
       </c>
       <c r="E167" t="n">
-        <v>-31.83363387746486</v>
+        <v>-31.8336393401792</v>
       </c>
       <c r="F167" t="n">
         <v>-53.46630744214328</v>
@@ -44439,7 +44439,7 @@
         <v>33.09109889422288</v>
       </c>
       <c r="I167" t="n">
-        <v>-32.89464226978117</v>
+        <v>-32.89463592347094</v>
       </c>
       <c r="J167" t="n">
         <v>48.14546064897016</v>
@@ -44503,7 +44503,7 @@
         <v>29.44025621625235</v>
       </c>
       <c r="I169" t="n">
-        <v>-35.44473564791697</v>
+        <v>-35.44474177393761</v>
       </c>
       <c r="J169" t="n">
         <v>41.96007874200003</v>
@@ -44535,7 +44535,7 @@
         <v>31.30973250029547</v>
       </c>
       <c r="I170" t="n">
-        <v>-37.60952319348129</v>
+        <v>-37.60951737835894</v>
       </c>
       <c r="J170" t="n">
         <v>40.14651791489481</v>
@@ -44555,7 +44555,7 @@
         <v>-40.04556086562169</v>
       </c>
       <c r="E171" t="n">
-        <v>-34.58447846232172</v>
+        <v>-34.58448249718911</v>
       </c>
       <c r="F171" t="n">
         <v>-51.04838688412199</v>
@@ -44599,7 +44599,7 @@
         <v>44.92055080938697</v>
       </c>
       <c r="I172" t="n">
-        <v>-32.8123236456485</v>
+        <v>-32.81231725705731</v>
       </c>
       <c r="J172" t="n">
         <v>59.58955849005739</v>
@@ -44619,7 +44619,7 @@
         <v>-32.91375369932255</v>
       </c>
       <c r="E173" t="n">
-        <v>-27.77852938823074</v>
+        <v>-27.77852341218486</v>
       </c>
       <c r="F173" t="n">
         <v>-43.44699349358814</v>
@@ -44651,7 +44651,7 @@
         <v>-30.59382334344727</v>
       </c>
       <c r="E174" t="n">
-        <v>-24.91228000773636</v>
+        <v>-24.91227355035074</v>
       </c>
       <c r="F174" t="n">
         <v>-41.76249980926514</v>
@@ -44663,7 +44663,7 @@
         <v>59.09223654259699</v>
       </c>
       <c r="I174" t="n">
-        <v>-27.84140135315001</v>
+        <v>-27.84139423196488</v>
       </c>
       <c r="J174" t="n">
         <v>72.74854593479307</v>
@@ -44747,7 +44747,7 @@
         <v>-26.87499713439198</v>
       </c>
       <c r="E177" t="n">
-        <v>-20.35360537283162</v>
+        <v>-20.35359835800773</v>
       </c>
       <c r="F177" t="n">
         <v>-38.99999765249399</v>
@@ -44759,7 +44759,7 @@
         <v>71.52501088341694</v>
       </c>
       <c r="I177" t="n">
-        <v>-22.33078549632175</v>
+        <v>-22.33077750093369</v>
       </c>
       <c r="J177" t="n">
         <v>83.1262414010687</v>
@@ -44779,7 +44779,7 @@
         <v>-27.66264949936464</v>
       </c>
       <c r="E178" t="n">
-        <v>-20.47751679276931</v>
+        <v>-20.47750781759832</v>
       </c>
       <c r="F178" t="n">
         <v>-39.01896560774591</v>
@@ -44811,7 +44811,7 @@
         <v>-28.19905523871372</v>
       </c>
       <c r="E179" t="n">
-        <v>-22.15917738967272</v>
+        <v>-22.15916869716422</v>
       </c>
       <c r="F179" t="n">
         <v>-41.81931635301061</v>
@@ -44823,7 +44823,7 @@
         <v>61.06736588618858</v>
       </c>
       <c r="I179" t="n">
-        <v>-24.21510239292522</v>
+        <v>-24.21511007080047</v>
       </c>
       <c r="J179" t="n">
         <v>75.58593786379788</v>
@@ -44843,7 +44843,7 @@
         <v>-27.29016992783636</v>
       </c>
       <c r="E180" t="n">
-        <v>-22.41062766588845</v>
+        <v>-22.41063438366677</v>
       </c>
       <c r="F180" t="n">
         <v>-39.6770169275888</v>
@@ -44855,7 +44855,7 @@
         <v>65.15150572053405</v>
       </c>
       <c r="I180" t="n">
-        <v>-25.31920577234636</v>
+        <v>-25.31919824707868</v>
       </c>
       <c r="J180" t="n">
         <v>72.82946306655833</v>
@@ -44875,7 +44875,7 @@
         <v>-26.03864804185331</v>
       </c>
       <c r="E181" t="n">
-        <v>-20.64497407201848</v>
+        <v>-20.64498270087283</v>
       </c>
       <c r="F181" t="n">
         <v>-39.39168486008041</v>
@@ -44907,7 +44907,7 @@
         <v>-27.65957226150498</v>
       </c>
       <c r="E182" t="n">
-        <v>-21.12262057043012</v>
+        <v>-21.12262914734645</v>
       </c>
       <c r="F182" t="n">
         <v>-38.78824946197358</v>
@@ -44919,7 +44919,7 @@
         <v>72.57494253958269</v>
       </c>
       <c r="I182" t="n">
-        <v>-25.49482362062903</v>
+        <v>-25.49483107255582</v>
       </c>
       <c r="J182" t="n">
         <v>93.80497531351087</v>
@@ -44971,7 +44971,7 @@
         <v>-26.79245330549804</v>
       </c>
       <c r="E184" t="n">
-        <v>-18.81728369892127</v>
+        <v>-18.81726817858214</v>
       </c>
       <c r="F184" t="n">
         <v>-35.9392113960985</v>
@@ -45035,7 +45035,7 @@
         <v>-25.23364352705133</v>
       </c>
       <c r="E186" t="n">
-        <v>-21.55172030710867</v>
+        <v>-21.55172688455815</v>
       </c>
       <c r="F186" t="n">
         <v>-33.64963145939185</v>
@@ -45111,7 +45111,7 @@
         <v>102.5162819144948</v>
       </c>
       <c r="I188" t="n">
-        <v>-23.99993985526311</v>
+        <v>-23.99993218579317</v>
       </c>
       <c r="J188" t="n">
         <v>136.0320544643959</v>
@@ -45131,7 +45131,7 @@
         <v>-24.3749994268784</v>
       </c>
       <c r="E189" t="n">
-        <v>-16.85281500968847</v>
+        <v>-16.85279894143548</v>
       </c>
       <c r="F189" t="n">
         <v>-28.89460472383064</v>
@@ -45163,7 +45163,7 @@
         <v>-23.35766138815261</v>
       </c>
       <c r="E190" t="n">
-        <v>-16.17542595647212</v>
+        <v>-16.1754097615417</v>
       </c>
       <c r="F190" t="n">
         <v>-32.43977679001436</v>
@@ -45227,7 +45227,7 @@
         <v>-24.58234073821581</v>
       </c>
       <c r="E192" t="n">
-        <v>-14.56051583298611</v>
+        <v>-14.560524436397</v>
       </c>
       <c r="F192" t="n">
         <v>-31.51477378726198</v>
@@ -45259,7 +45259,7 @@
         <v>-17.57731914672299</v>
       </c>
       <c r="E193" t="n">
-        <v>-9.055419336014003</v>
+        <v>-9.055420169258021</v>
       </c>
       <c r="F193" t="n">
         <v>-24.49735055141047</v>
@@ -45291,7 +45291,7 @@
         <v>-19.49875262272378</v>
       </c>
       <c r="E194" t="n">
-        <v>-12.4276599118963</v>
+        <v>-12.42766767500797</v>
       </c>
       <c r="F194" t="n">
         <v>-25.51905198204355</v>
@@ -45323,7 +45323,7 @@
         <v>-22.51231461369236</v>
       </c>
       <c r="E195" t="n">
-        <v>-15.28333644903409</v>
+        <v>-15.28334387731973</v>
       </c>
       <c r="F195" t="n">
         <v>-30.90795338358637</v>
@@ -45419,7 +45419,7 @@
         <v>-30.62730742553335</v>
       </c>
       <c r="E198" t="n">
-        <v>-17.25910396892187</v>
+        <v>-17.25910245924941</v>
       </c>
       <c r="F198" t="n">
         <v>-33.52514665157967</v>
@@ -45451,7 +45451,7 @@
         <v>-33.10871432964622</v>
       </c>
       <c r="E199" t="n">
-        <v>-20.16900416692024</v>
+        <v>-20.1689956791109</v>
       </c>
       <c r="F199" t="n">
         <v>-36.51537018870842</v>
@@ -45579,7 +45579,7 @@
         <v>-33.21586194762303</v>
       </c>
       <c r="E203" t="n">
-        <v>-16.04800469940202</v>
+        <v>-16.04799614881611</v>
       </c>
       <c r="F203" t="n">
         <v>-36.18741564478685</v>
@@ -45611,7 +45611,7 @@
         <v>-29.41952771061378</v>
       </c>
       <c r="E204" t="n">
-        <v>-17.02914492844722</v>
+        <v>-17.02912959365807</v>
       </c>
       <c r="F204" t="n">
         <v>-26.48352671295293</v>
@@ -45675,7 +45675,7 @@
         <v>-29.47645838329669</v>
       </c>
       <c r="E206" t="n">
-        <v>-8.977070678845955</v>
+        <v>-8.977062831240701</v>
       </c>
       <c r="F206" t="n">
         <v>-28.80289813678555</v>
@@ -45739,7 +45739,7 @@
         <v>-27.65476350642918</v>
       </c>
       <c r="E208" t="n">
-        <v>-7.480697989790852</v>
+        <v>-7.480690033325899</v>
       </c>
       <c r="F208" t="n">
         <v>-28.56085470297766</v>
@@ -45771,7 +45771,7 @@
         <v>-26.7097961922128</v>
       </c>
       <c r="E209" t="n">
-        <v>-7.607452804809</v>
+        <v>-7.60746146904766</v>
       </c>
       <c r="F209" t="n">
         <v>-28.01413821889418</v>
@@ -45803,7 +45803,7 @@
         <v>-26.72176522045333</v>
       </c>
       <c r="E210" t="n">
-        <v>-9.241938339858734</v>
+        <v>-9.241946894024998</v>
       </c>
       <c r="F210" t="n">
         <v>-27.03415236602241</v>
@@ -45835,7 +45835,7 @@
         <v>-27.28512988836156</v>
       </c>
       <c r="E211" t="n">
-        <v>-7.893982258126419</v>
+        <v>-7.893973574240542</v>
       </c>
       <c r="F211" t="n">
         <v>-31.35418360746799</v>
@@ -45899,7 +45899,7 @@
         <v>-32.08351066583373</v>
       </c>
       <c r="E213" t="n">
-        <v>-6.390548149228259</v>
+        <v>-6.390539985580757</v>
       </c>
       <c r="F213" t="n">
         <v>-36.81710406455739</v>
@@ -45963,7 +45963,7 @@
         <v>-31.69662302286084</v>
       </c>
       <c r="E215" t="n">
-        <v>-5.981578347866867</v>
+        <v>-5.981569662750863</v>
       </c>
       <c r="F215" t="n">
         <v>-35.00641823830535</v>
@@ -45995,7 +45995,7 @@
         <v>-33.33333747254461</v>
       </c>
       <c r="E216" t="n">
-        <v>-6.459955843676058</v>
+        <v>-6.459947047595593</v>
       </c>
       <c r="F216" t="n">
         <v>-35.39603519665386</v>
@@ -46059,7 +46059,7 @@
         <v>-31.83196333000435</v>
       </c>
       <c r="E218" t="n">
-        <v>-7.68788219992188</v>
+        <v>-7.687890327936886</v>
       </c>
       <c r="F218" t="n">
         <v>-32.37436156607637</v>
@@ -46187,7 +46187,7 @@
         <v>-36.29064639593801</v>
       </c>
       <c r="E222" t="n">
-        <v>-7.843132019864541</v>
+        <v>-7.84314091942816</v>
       </c>
       <c r="F222" t="n">
         <v>-28.89180566823137</v>
@@ -46347,7 +46347,7 @@
         <v>-34.85313456992967</v>
       </c>
       <c r="E227" t="n">
-        <v>-8.1714896278546</v>
+        <v>-8.171498781349463</v>
       </c>
       <c r="F227" t="n">
         <v>-32.55395806851909</v>
@@ -46379,7 +46379,7 @@
         <v>-36.55056678989862</v>
       </c>
       <c r="E228" t="n">
-        <v>-2.460515871778712</v>
+        <v>-2.460506794340878</v>
       </c>
       <c r="F228" t="n">
         <v>-33.03285408680733</v>
@@ -46411,7 +46411,7 @@
         <v>-37.24916312288149</v>
       </c>
       <c r="E229" t="n">
-        <v>-3.495026259081291</v>
+        <v>-3.495035167181182</v>
       </c>
       <c r="F229" t="n">
         <v>-38.67234368945173</v>
@@ -46475,7 +46475,7 @@
         <v>-37.52585712120092</v>
       </c>
       <c r="E231" t="n">
-        <v>0.04555280190197131</v>
+        <v>0.04553419329549335</v>
       </c>
       <c r="F231" t="n">
         <v>-36.82532653673968</v>
@@ -46571,7 +46571,7 @@
         <v>-37.23450483839871</v>
       </c>
       <c r="E234" t="n">
-        <v>0.09194310401834382</v>
+        <v>0.09195250322659998</v>
       </c>
       <c r="F234" t="n">
         <v>-38.63636103394656</v>
@@ -46603,7 +46603,7 @@
         <v>-34.25161045286568</v>
       </c>
       <c r="E235" t="n">
-        <v>2.665199040303001</v>
+        <v>2.665208703368349</v>
       </c>
       <c r="F235" t="n">
         <v>-35.84453808293154</v>
@@ -46731,7 +46731,7 @@
         <v>-33.56353240626703</v>
       </c>
       <c r="E239" t="n">
-        <v>1.693950400277155</v>
+        <v>1.693959968986869</v>
       </c>
       <c r="F239" t="n">
         <v>-43.07445745551136</v>
@@ -46955,7 +46955,7 @@
         <v>-31.36067022065163</v>
       </c>
       <c r="E246" t="n">
-        <v>-3.292492664437496</v>
+        <v>-3.292501612801146</v>
       </c>
       <c r="F246" t="n">
         <v>-44.01419291641084</v>
@@ -47083,7 +47083,7 @@
         <v>-32.32134575251007</v>
       </c>
       <c r="E250" t="n">
-        <v>-2.79985382220842</v>
+        <v>-2.799844619809422</v>
       </c>
       <c r="F250" t="n">
         <v>-45.22397009414632</v>
@@ -47115,7 +47115,7 @@
         <v>-31.40301388027185</v>
       </c>
       <c r="E251" t="n">
-        <v>-3.107492906488285</v>
+        <v>-3.107483694785163</v>
       </c>
       <c r="F251" t="n">
         <v>-44.10021926081409</v>
@@ -47179,7 +47179,7 @@
         <v>-30.50687043040482</v>
       </c>
       <c r="E253" t="n">
-        <v>-3.657905370458425</v>
+        <v>-3.657896195424548</v>
       </c>
       <c r="F253" t="n">
         <v>-43.2534700274485</v>
@@ -47243,7 +47243,7 @@
         <v>-28.36398693106126</v>
       </c>
       <c r="E255" t="n">
-        <v>-11.02652519290564</v>
+        <v>-11.0265174091879</v>
       </c>
       <c r="F255" t="n">
         <v>-40.86610764775907</v>
@@ -47275,7 +47275,7 @@
         <v>-28.43902401807832</v>
       </c>
       <c r="E256" t="n">
-        <v>-11.16642255217313</v>
+        <v>-11.16641471354466</v>
       </c>
       <c r="F256" t="n">
         <v>-40.68221552091195</v>
@@ -47531,7 +47531,7 @@
         <v>-30.63477422966672</v>
       </c>
       <c r="E264" t="n">
-        <v>-8.975249933684793</v>
+        <v>-8.975257928817172</v>
       </c>
       <c r="F264" t="n">
         <v>-39.47368508745812</v>
@@ -47627,7 +47627,7 @@
         <v>-29.24205512377247</v>
       </c>
       <c r="E267" t="n">
-        <v>-11.3721850694539</v>
+        <v>-11.37217723657323</v>
       </c>
       <c r="F267" t="n">
         <v>-35.66993037243454</v>
@@ -47691,7 +47691,7 @@
         <v>-31.51544377109349</v>
       </c>
       <c r="E269" t="n">
-        <v>-16.35530046410454</v>
+        <v>-16.3552932302255</v>
       </c>
       <c r="F269" t="n">
         <v>-38.0038388594275</v>
@@ -47915,7 +47915,7 @@
         <v>-30.96296522352431</v>
       </c>
       <c r="E276" t="n">
-        <v>-11.71149935583935</v>
+        <v>-11.7115071824372</v>
       </c>
       <c r="F276" t="n">
         <v>-34.97199627598184</v>
@@ -48011,7 +48011,7 @@
         <v>-28.54230449507224</v>
       </c>
       <c r="E279" t="n">
-        <v>-10.61024304532102</v>
+        <v>-10.61025096954303</v>
       </c>
       <c r="F279" t="n">
         <v>-31.85478688860097</v>
@@ -48107,7 +48107,7 @@
         <v>-31.95619725003812</v>
       </c>
       <c r="E282" t="n">
-        <v>-8.466562074090877</v>
+        <v>-8.466570285765041</v>
       </c>
       <c r="F282" t="n">
         <v>-36.50442544264273</v>
@@ -48139,7 +48139,7 @@
         <v>-34.78050768782048</v>
       </c>
       <c r="E283" t="n">
-        <v>-8.900946581418934</v>
+        <v>-8.900954788972681</v>
       </c>
       <c r="F283" t="n">
         <v>-36.51074312329671</v>
@@ -48203,7 +48203,7 @@
         <v>-33.6261564988414</v>
       </c>
       <c r="E285" t="n">
-        <v>-6.403057485981378</v>
+        <v>-6.403066080333931</v>
       </c>
       <c r="F285" t="n">
         <v>-43.19450633885003</v>
@@ -48331,7 +48331,7 @@
         <v>-27.07006549980937</v>
       </c>
       <c r="E289" t="n">
-        <v>-1.789457213034507</v>
+        <v>-1.789447632229446</v>
       </c>
       <c r="F289" t="n">
         <v>-36.1724497836834</v>
@@ -48363,7 +48363,7 @@
         <v>-26.88853708679655</v>
       </c>
       <c r="E290" t="n">
-        <v>-1.419453836500251</v>
+        <v>-1.419444239463907</v>
       </c>
       <c r="F290" t="n">
         <v>-38.08921600038258</v>
@@ -48523,7 +48523,7 @@
         <v>-30.8609987086815</v>
       </c>
       <c r="E295" t="n">
-        <v>-6.68391401909465</v>
+        <v>-6.683905083631759</v>
       </c>
       <c r="F295" t="n">
         <v>-41.6964609053498</v>
@@ -48715,7 +48715,7 @@
         <v>-32.60315788154286</v>
       </c>
       <c r="E301" t="n">
-        <v>-1.915389976623461</v>
+        <v>-1.915399321961297</v>
       </c>
       <c r="F301" t="n">
         <v>-44.79178880131202</v>
@@ -48843,7 +48843,7 @@
         <v>-27.57111994645234</v>
       </c>
       <c r="E305" t="n">
-        <v>3.14992657515003</v>
+        <v>3.149916020112609</v>
       </c>
       <c r="F305" t="n">
         <v>-41.52879384528914</v>
@@ -48971,7 +48971,7 @@
         <v>-27.55384073228704</v>
       </c>
       <c r="E309" t="n">
-        <v>-1.820409767954434</v>
+        <v>-1.820419341165691</v>
       </c>
       <c r="F309" t="n">
         <v>-46.45314619747551</v>
@@ -49003,7 +49003,7 @@
         <v>-28.12327812449581</v>
       </c>
       <c r="E310" t="n">
-        <v>-2.189970868730429</v>
+        <v>-2.189961319395339</v>
       </c>
       <c r="F310" t="n">
         <v>-43.11211700553351</v>
@@ -49099,7 +49099,7 @@
         <v>-23.67802924944825</v>
       </c>
       <c r="E313" t="n">
-        <v>-7.167704674027875</v>
+        <v>-7.167713321274871</v>
       </c>
       <c r="F313" t="n">
         <v>-43.89662309077295</v>
@@ -49163,7 +49163,7 @@
         <v>-25.69444651405009</v>
       </c>
       <c r="E315" t="n">
-        <v>-7.805284449640915</v>
+        <v>-7.8052930518827</v>
       </c>
       <c r="F315" t="n">
         <v>-44.86300958919328</v>
@@ -49227,7 +49227,7 @@
         <v>-30.79507707567796</v>
       </c>
       <c r="E317" t="n">
-        <v>-12.54195618625559</v>
+        <v>-12.54196405882723</v>
       </c>
       <c r="F317" t="n">
         <v>-47.19959819731769</v>
@@ -49291,7 +49291,7 @@
         <v>-28.38817660877887</v>
       </c>
       <c r="E319" t="n">
-        <v>-14.69881249627694</v>
+        <v>-14.69882014884166</v>
       </c>
       <c r="F319" t="n">
         <v>-46.19366314291567</v>
@@ -49323,7 +49323,7 @@
         <v>-30.04980322748305</v>
       </c>
       <c r="E320" t="n">
-        <v>-11.798339142925</v>
+        <v>-11.79834711640336</v>
       </c>
       <c r="F320" t="n">
         <v>-45.88515934593683</v>
@@ -49515,7 +49515,7 @@
         <v>-30.20774464959777</v>
       </c>
       <c r="E326" t="n">
-        <v>-12.61552578725684</v>
+        <v>-12.61553365320609</v>
       </c>
       <c r="F326" t="n">
         <v>-43.7062933475497</v>
@@ -49547,7 +49547,7 @@
         <v>-28.4168560528505</v>
       </c>
       <c r="E327" t="n">
-        <v>-11.2382507263617</v>
+        <v>-11.23824265940424</v>
       </c>
       <c r="F327" t="n">
         <v>-42.01795096708333</v>
@@ -49579,7 +49579,7 @@
         <v>-26.30973188082025</v>
       </c>
       <c r="E328" t="n">
-        <v>-7.835560144670373</v>
+        <v>-7.835551445906363</v>
       </c>
       <c r="F328" t="n">
         <v>-39.07111277288545</v>
@@ -49611,7 +49611,7 @@
         <v>-26.77945952370142</v>
       </c>
       <c r="E329" t="n">
-        <v>-4.35587998969117</v>
+        <v>-4.355889351430875</v>
       </c>
       <c r="F329" t="n">
         <v>-37.83128971446084</v>
@@ -49643,7 +49643,7 @@
         <v>-24.20228964506092</v>
       </c>
       <c r="E330" t="n">
-        <v>-2.263202999119251</v>
+        <v>-2.263212839202788</v>
       </c>
       <c r="F330" t="n">
         <v>-40.89319237117981</v>
@@ -49771,7 +49771,7 @@
         <v>-19.98714991312431</v>
       </c>
       <c r="E334" t="n">
-        <v>-2.88207449406167</v>
+        <v>-2.882084250995653</v>
       </c>
       <c r="F334" t="n">
         <v>-41.09851185636433</v>
@@ -49803,7 +49803,7 @@
         <v>-16.57894431388936</v>
       </c>
       <c r="E335" t="n">
-        <v>-1.332090723583423</v>
+        <v>-1.332080853007134</v>
       </c>
       <c r="F335" t="n">
         <v>-37.75945257518652</v>
@@ -49931,7 +49931,7 @@
         <v>-25.53582422398183</v>
       </c>
       <c r="E339" t="n">
-        <v>-4.37218089879411</v>
+        <v>-4.372171369682365</v>
       </c>
       <c r="F339" t="n">
         <v>-41.2774749891061</v>
@@ -49963,7 +49963,7 @@
         <v>-23.0622628159228</v>
       </c>
       <c r="E340" t="n">
-        <v>-3.034070394712185</v>
+        <v>-3.0340603821715</v>
       </c>
       <c r="F340" t="n">
         <v>-39.3328445504433</v>
@@ -50059,7 +50059,7 @@
         <v>-23.89099852905706</v>
       </c>
       <c r="E343" t="n">
-        <v>-0.6231467017805636</v>
+        <v>-0.6231572275657182</v>
       </c>
       <c r="F343" t="n">
         <v>-38.56778592704874</v>
@@ -50123,7 +50123,7 @@
         <v>-17.2627251407637</v>
       </c>
       <c r="E345" t="n">
-        <v>4.916302916447957</v>
+        <v>4.916314993451909</v>
       </c>
       <c r="F345" t="n">
         <v>-32.87099253590478</v>
@@ -50155,7 +50155,7 @@
         <v>-21.78477522759588</v>
       </c>
       <c r="E346" t="n">
-        <v>1.183733791213348</v>
+        <v>1.183745152549909</v>
       </c>
       <c r="F346" t="n">
         <v>-35.87239191644272</v>
@@ -50443,7 +50443,7 @@
         <v>-27.28494884671743</v>
       </c>
       <c r="E355" t="n">
-        <v>4.792392368889042</v>
+        <v>4.792385488267725</v>
       </c>
       <c r="F355" t="n">
         <v>-27.42354135671774</v>
@@ -50475,7 +50475,7 @@
         <v>-25.3721249509532</v>
       </c>
       <c r="E356" t="n">
-        <v>13.24401421734134</v>
+        <v>13.24400678497606</v>
       </c>
       <c r="F356" t="n">
         <v>-24.46144183427424</v>
@@ -50603,7 +50603,7 @@
         <v>-21.90601946492874</v>
       </c>
       <c r="E360" t="n">
-        <v>11.65992104672113</v>
+        <v>11.65991396441235</v>
       </c>
       <c r="F360" t="n">
         <v>-25.74782005433018</v>
@@ -50667,7 +50667,7 @@
         <v>-20.94915357686705</v>
       </c>
       <c r="E362" t="n">
-        <v>10.4534869862259</v>
+        <v>10.45348008305296</v>
       </c>
       <c r="F362" t="n">
         <v>-24.44530491228184</v>
@@ -50699,7 +50699,7 @@
         <v>-22.84366784680649</v>
       </c>
       <c r="E363" t="n">
-        <v>7.264098320135837</v>
+        <v>7.26410489731748</v>
       </c>
       <c r="F363" t="n">
         <v>-29.10251687659797</v>
@@ -50763,7 +50763,7 @@
         <v>-24.28571252479959</v>
       </c>
       <c r="E365" t="n">
-        <v>5.415679395542905</v>
+        <v>5.415672922114378</v>
       </c>
       <c r="F365" t="n">
         <v>-28.71211138002472</v>
@@ -50795,7 +50795,7 @@
         <v>-23.19622116035478</v>
       </c>
       <c r="E366" t="n">
-        <v>8.128490980816538</v>
+        <v>8.128497798204526</v>
       </c>
       <c r="F366" t="n">
         <v>-26.12058438561582</v>
@@ -50891,7 +50891,7 @@
         <v>-22.73361362756691</v>
       </c>
       <c r="E369" t="n">
-        <v>13.56802429660819</v>
+        <v>13.56803192476519</v>
       </c>
       <c r="F369" t="n">
         <v>-26.71135046405951</v>
@@ -51019,7 +51019,7 @@
         <v>-24.32815028665871</v>
       </c>
       <c r="E373" t="n">
-        <v>12.0694693473598</v>
+        <v>12.06946184813773</v>
       </c>
       <c r="F373" t="n">
         <v>-28.85148269226424</v>
@@ -51211,7 +51211,7 @@
         <v>-24.13010945252098</v>
       </c>
       <c r="E379" t="n">
-        <v>12.0428569162337</v>
+        <v>12.04284864922218</v>
       </c>
       <c r="F379" t="n">
         <v>-21.73281609041534</v>
@@ -51339,7 +51339,7 @@
         <v>-29.13668595833225</v>
       </c>
       <c r="E383" t="n">
-        <v>7.127779850578642</v>
+        <v>7.127772389347142</v>
       </c>
       <c r="F383" t="n">
         <v>-29.39840880790665</v>
@@ -51371,7 +51371,7 @@
         <v>-31.12208767584927</v>
       </c>
       <c r="E384" t="n">
-        <v>5.818240155712728</v>
+        <v>5.818247463604265</v>
       </c>
       <c r="F384" t="n">
         <v>-32.58526100040748</v>
@@ -51467,7 +51467,7 @@
         <v>-26.75635196626188</v>
       </c>
       <c r="E387" t="n">
-        <v>6.33768942164834</v>
+        <v>6.337682199015493</v>
       </c>
       <c r="F387" t="n">
         <v>-27.73670637603035</v>
@@ -51531,7 +51531,7 @@
         <v>-28.43965983222077</v>
       </c>
       <c r="E389" t="n">
-        <v>3.1580608161486</v>
+        <v>3.158053617653644</v>
       </c>
       <c r="F389" t="n">
         <v>-27.92992853630824</v>
@@ -51563,7 +51563,7 @@
         <v>-27.36356923125641</v>
       </c>
       <c r="E390" t="n">
-        <v>6.169308920977867</v>
+        <v>6.169301512354353</v>
       </c>
       <c r="F390" t="n">
         <v>-25.73402100163619</v>
@@ -51595,7 +51595,7 @@
         <v>-27.97047902954666</v>
       </c>
       <c r="E391" t="n">
-        <v>3.880500882192162</v>
+        <v>3.880493928511441</v>
       </c>
       <c r="F391" t="n">
         <v>-30.45361073235145</v>
@@ -51659,7 +51659,7 @@
         <v>-35.30269977477008</v>
       </c>
       <c r="E393" t="n">
-        <v>-2.038469494495021</v>
+        <v>-2.038462945038977</v>
       </c>
       <c r="F393" t="n">
         <v>-41.98987931194888</v>
@@ -51691,7 +51691,7 @@
         <v>-30.55953661004619</v>
       </c>
       <c r="E394" t="n">
-        <v>-0.1668904930419157</v>
+        <v>-0.1668970655057334</v>
       </c>
       <c r="F394" t="n">
         <v>-36.04969516561641</v>
@@ -51723,7 +51723,7 @@
         <v>-26.6316594977735</v>
       </c>
       <c r="E395" t="n">
-        <v>1.014299414847986</v>
+        <v>1.014306215598793</v>
       </c>
       <c r="F395" t="n">
         <v>-34.01675506515429</v>
@@ -51787,7 +51787,7 @@
         <v>-22.62996984260145</v>
       </c>
       <c r="E397" t="n">
-        <v>4.392311829375939</v>
+        <v>4.392318912024984</v>
       </c>
       <c r="F397" t="n">
         <v>-32.47330687594106</v>
@@ -51819,7 +51819,7 @@
         <v>-18.38461802555964</v>
       </c>
       <c r="E398" t="n">
-        <v>8.674322733776552</v>
+        <v>8.674330050879009</v>
       </c>
       <c r="F398" t="n">
         <v>-26.03086679746717</v>
@@ -51979,7 +51979,7 @@
         <v>-7.945423499897474</v>
       </c>
       <c r="E403" t="n">
-        <v>13.17264680156478</v>
+        <v>13.17263868232146</v>
       </c>
       <c r="F403" t="n">
         <v>-13.55808929093354</v>
@@ -52011,7 +52011,7 @@
         <v>-10.77751842338764</v>
       </c>
       <c r="E404" t="n">
-        <v>8.642981161077067</v>
+        <v>8.642973758231221</v>
       </c>
       <c r="F404" t="n">
         <v>-12.82665689655393</v>
@@ -52203,7 +52203,7 @@
         <v>-21.33238375936532</v>
       </c>
       <c r="E410" t="n">
-        <v>3.107189936007027</v>
+        <v>3.107196346569774</v>
       </c>
       <c r="F410" t="n">
         <v>-21.59166824801976</v>
@@ -52267,7 +52267,7 @@
         <v>-24.71146980834059</v>
       </c>
       <c r="E412" t="n">
-        <v>-2.726829609288295</v>
+        <v>-2.726841153927861</v>
       </c>
       <c r="F412" t="n">
         <v>-24.11161503408237</v>
@@ -52363,7 +52363,7 @@
         <v>-22.53923464985733</v>
       </c>
       <c r="E415" t="n">
-        <v>-1.847963577079392</v>
+        <v>-1.847951917291468</v>
       </c>
       <c r="F415" t="n">
         <v>-20.80552533209156</v>
@@ -52395,7 +52395,7 @@
         <v>-21.78288832645033</v>
       </c>
       <c r="E416" t="n">
-        <v>-3.412864651995873</v>
+        <v>-3.412876137907805</v>
       </c>
       <c r="F416" t="n">
         <v>-24.29865228356438</v>
@@ -52619,7 +52619,7 @@
         <v>-20.82066719519743</v>
       </c>
       <c r="E423" t="n">
-        <v>-5.578786518450696</v>
+        <v>-5.578780694495011</v>
       </c>
       <c r="F423" t="n">
         <v>-22.82890181163548</v>
@@ -52843,7 +52843,7 @@
         <v>-30.24650161641759</v>
       </c>
       <c r="E430" t="n">
-        <v>-10.80605285953314</v>
+        <v>-10.80606292625648</v>
       </c>
       <c r="F430" t="n">
         <v>-32.41098037149195</v>
@@ -52875,7 +52875,7 @@
         <v>-30.16501524682917</v>
       </c>
       <c r="E431" t="n">
-        <v>-12.13949474993221</v>
+        <v>-12.13950456134066</v>
       </c>
       <c r="F431" t="n">
         <v>-32.61940456242382</v>
@@ -52939,7 +52939,7 @@
         <v>-28.28217347291736</v>
       </c>
       <c r="E433" t="n">
-        <v>-13.65794799810753</v>
+        <v>-13.65793860950155</v>
       </c>
       <c r="F433" t="n">
         <v>-35.94838047268804</v>
@@ -52971,7 +52971,7 @@
         <v>-29.41176433922557</v>
       </c>
       <c r="E434" t="n">
-        <v>-15.05852841627437</v>
+        <v>-15.05851917996379</v>
       </c>
       <c r="F434" t="n">
         <v>-37.55248832154153</v>
@@ -53035,7 +53035,7 @@
         <v>-31.18556707365781</v>
       </c>
       <c r="E436" t="n">
-        <v>-18.02632554975999</v>
+        <v>-18.02633419934322</v>
       </c>
       <c r="F436" t="n">
         <v>-42.55076628068165</v>
@@ -53195,7 +53195,7 @@
         <v>-31.21424024348101</v>
       </c>
       <c r="E441" t="n">
-        <v>-19.20949383577247</v>
+        <v>-19.20950236051181</v>
       </c>
       <c r="F441" t="n">
         <v>-42.29934878455828</v>
@@ -53227,7 +53227,7 @@
         <v>-32.31746128627232</v>
       </c>
       <c r="E442" t="n">
-        <v>-20.91631837289538</v>
+        <v>-20.9163266846164</v>
       </c>
       <c r="F442" t="n">
         <v>-44.41396894882384</v>
@@ -53291,7 +53291,7 @@
         <v>-32.40506217564133</v>
       </c>
       <c r="E444" t="n">
-        <v>-22.34746953569596</v>
+        <v>-22.34746171639906</v>
       </c>
       <c r="F444" t="n">
         <v>-42.16226047422541</v>
@@ -53323,7 +53323,7 @@
         <v>-29.89368231014634</v>
       </c>
       <c r="E445" t="n">
-        <v>-20.7749366725903</v>
+        <v>-20.77492865674345</v>
       </c>
       <c r="F445" t="n">
         <v>-42.99229174547121</v>
@@ -53483,7 +53483,7 @@
         <v>-18.88297978584559</v>
       </c>
       <c r="E450" t="n">
-        <v>-15.88697830309197</v>
+        <v>-15.88698719525661</v>
       </c>
       <c r="F450" t="n">
         <v>-35.79224816752393</v>
@@ -53515,7 +53515,7 @@
         <v>-21.15514103139139</v>
       </c>
       <c r="E451" t="n">
-        <v>-17.34136803322271</v>
+        <v>-17.34137682167169</v>
       </c>
       <c r="F451" t="n">
         <v>-37.43143086937941</v>
@@ -53643,7 +53643,7 @@
         <v>-26.51714739149942</v>
       </c>
       <c r="E455" t="n">
-        <v>-21.18379462622453</v>
+        <v>-21.18380265372481</v>
       </c>
       <c r="F455" t="n">
         <v>-41.48341463321004</v>
@@ -53675,7 +53675,7 @@
         <v>-30.5295940900473</v>
       </c>
       <c r="E456" t="n">
-        <v>-21.92261013396634</v>
+        <v>-21.92261802067016</v>
       </c>
       <c r="F456" t="n">
         <v>-48.90003185290745</v>
@@ -53835,7 +53835,7 @@
         <v>-30.07565956712446</v>
       </c>
       <c r="E461" t="n">
-        <v>-25.4823950787656</v>
+        <v>-25.48238809077367</v>
       </c>
       <c r="F461" t="n">
         <v>-44.03718065374491</v>
@@ -53867,7 +53867,7 @@
         <v>-32.39348410987978</v>
       </c>
       <c r="E462" t="n">
-        <v>-29.13439621150543</v>
+        <v>-29.13438953225068</v>
       </c>
       <c r="F462" t="n">
         <v>-46.7217367763071</v>
@@ -53899,7 +53899,7 @@
         <v>-31.89493121198945</v>
       </c>
       <c r="E463" t="n">
-        <v>-28.07081175545964</v>
+        <v>-28.07081853704482</v>
       </c>
       <c r="F463" t="n">
         <v>-45.49804856795367</v>
@@ -54027,7 +54027,7 @@
         <v>-28.04877989062005</v>
       </c>
       <c r="E467" t="n">
-        <v>-28.551504886499</v>
+        <v>-28.55151148667798</v>
       </c>
       <c r="F467" t="n">
         <v>-42.95977001650706</v>
@@ -54059,7 +54059,7 @@
         <v>-27.86458221768647</v>
       </c>
       <c r="E468" t="n">
-        <v>-27.55755510454062</v>
+        <v>-27.55756191669814</v>
       </c>
       <c r="F468" t="n">
         <v>-44.69987464603042</v>
@@ -54251,7 +54251,7 @@
         <v>-32.19911590123635</v>
       </c>
       <c r="E474" t="n">
-        <v>-25.90197091088043</v>
+        <v>-25.90196375525328</v>
       </c>
       <c r="F474" t="n">
         <v>-51.98792057340895</v>
@@ -54411,7 +54411,7 @@
         <v>-27.52354840786123</v>
       </c>
       <c r="E479" t="n">
-        <v>-16.4275601717731</v>
+        <v>-16.42755184124513</v>
       </c>
       <c r="F479" t="n">
         <v>-47.64444308810764</v>
@@ -54539,7 +54539,7 @@
         <v>-28.27814801252383</v>
       </c>
       <c r="E483" t="n">
-        <v>-20.0272355549142</v>
+        <v>-20.02722811908593</v>
       </c>
       <c r="F483" t="n">
         <v>-47.95545639098183</v>
@@ -54667,7 +54667,7 @@
         <v>-25.48882469494409</v>
       </c>
       <c r="E487" t="n">
-        <v>-21.02923282196163</v>
+        <v>-21.0292402548563</v>
       </c>
       <c r="F487" t="n">
         <v>-48.99627177559144</v>

--- a/dashboards/Reliance Group.xlsx
+++ b/dashboards/Reliance Group.xlsx
@@ -499,7 +499,7 @@
         <v>100.8000030517578</v>
       </c>
       <c r="I2" t="n">
-        <v>850.6759643554688</v>
+        <v>850.676025390625</v>
       </c>
       <c r="J2" t="n">
         <v>14.25</v>
@@ -522,7 +522,7 @@
         <v>90.40000152587891</v>
       </c>
       <c r="G3" t="n">
-        <v>1113.317504882812</v>
+        <v>1113.3173828125</v>
       </c>
       <c r="H3" t="n">
         <v>97.5</v>
@@ -551,13 +551,13 @@
         <v>89.94999694824219</v>
       </c>
       <c r="G4" t="n">
-        <v>1118.526000976562</v>
+        <v>1118.526123046875</v>
       </c>
       <c r="H4" t="n">
         <v>97.05000305175781</v>
       </c>
       <c r="I4" t="n">
-        <v>844.1920166015625</v>
+        <v>844.1919555664062</v>
       </c>
       <c r="J4" t="n">
         <v>13.85000038146973</v>
@@ -580,13 +580,13 @@
         <v>89.90000152587891</v>
       </c>
       <c r="G5" t="n">
-        <v>1094.47607421875</v>
+        <v>1094.476196289062</v>
       </c>
       <c r="H5" t="n">
         <v>100.1500015258789</v>
       </c>
       <c r="I5" t="n">
-        <v>844.6340942382812</v>
+        <v>844.6341552734375</v>
       </c>
       <c r="J5" t="n">
         <v>14.30000019073486</v>
@@ -609,7 +609,7 @@
         <v>91</v>
       </c>
       <c r="G6" t="n">
-        <v>1103.30810546875</v>
+        <v>1103.307983398438</v>
       </c>
       <c r="H6" t="n">
         <v>98.55000305175781</v>
@@ -673,7 +673,7 @@
         <v>98.40000152587891</v>
       </c>
       <c r="I8" t="n">
-        <v>968.8118286132812</v>
+        <v>968.811767578125</v>
       </c>
       <c r="J8" t="n">
         <v>14.30000019073486</v>
@@ -702,7 +702,7 @@
         <v>96.40000152587891</v>
       </c>
       <c r="I9" t="n">
-        <v>941.8934936523438</v>
+        <v>941.8935546875</v>
       </c>
       <c r="J9" t="n">
         <v>14.35000038146973</v>
@@ -760,7 +760,7 @@
         <v>102.75</v>
       </c>
       <c r="I11" t="n">
-        <v>931.5291137695312</v>
+        <v>931.5289916992188</v>
       </c>
       <c r="J11" t="n">
         <v>14.94999980926514</v>
@@ -783,13 +783,13 @@
         <v>91.40000152587891</v>
       </c>
       <c r="G12" t="n">
-        <v>1155.959594726562</v>
+        <v>1155.959716796875</v>
       </c>
       <c r="H12" t="n">
         <v>105.5500030517578</v>
       </c>
       <c r="I12" t="n">
-        <v>934.6727905273438</v>
+        <v>934.6727294921875</v>
       </c>
       <c r="J12" t="n">
         <v>15.64999961853027</v>
@@ -818,7 +818,7 @@
         <v>101.9499969482422</v>
       </c>
       <c r="I13" t="n">
-        <v>930.49755859375</v>
+        <v>930.4974975585938</v>
       </c>
       <c r="J13" t="n">
         <v>16.10000038146973</v>
@@ -841,7 +841,7 @@
         <v>90.69999694824219</v>
       </c>
       <c r="G14" t="n">
-        <v>1142.077758789062</v>
+        <v>1142.077880859375</v>
       </c>
       <c r="H14" t="n">
         <v>99.75</v>
@@ -870,13 +870,13 @@
         <v>88.75</v>
       </c>
       <c r="G15" t="n">
-        <v>1122.081665039062</v>
+        <v>1122.08154296875</v>
       </c>
       <c r="H15" t="n">
         <v>101.5500030517578</v>
       </c>
       <c r="I15" t="n">
-        <v>936.3428955078125</v>
+        <v>936.3428344726562</v>
       </c>
       <c r="J15" t="n">
         <v>16.54999923706055</v>
@@ -957,7 +957,7 @@
         <v>78</v>
       </c>
       <c r="G18" t="n">
-        <v>1074.887329101562</v>
+        <v>1074.887451171875</v>
       </c>
       <c r="H18" t="n">
         <v>98.05000305175781</v>
@@ -1015,7 +1015,7 @@
         <v>84.25</v>
       </c>
       <c r="G20" t="n">
-        <v>1057.948364257812</v>
+        <v>1057.948486328125</v>
       </c>
       <c r="H20" t="n">
         <v>102.3000030517578</v>
@@ -1044,7 +1044,7 @@
         <v>82</v>
       </c>
       <c r="G21" t="n">
-        <v>1080.933959960938</v>
+        <v>1080.93408203125</v>
       </c>
       <c r="H21" t="n">
         <v>101.0500030517578</v>
@@ -1102,7 +1102,7 @@
         <v>85.90000152587891</v>
       </c>
       <c r="G23" t="n">
-        <v>1079.552368164062</v>
+        <v>1079.552490234375</v>
       </c>
       <c r="H23" t="n">
         <v>110.0999984741211</v>
@@ -1131,7 +1131,7 @@
         <v>87.75</v>
       </c>
       <c r="G24" t="n">
-        <v>1065.602661132812</v>
+        <v>1065.6025390625</v>
       </c>
       <c r="H24" t="n">
         <v>115.5999984741211</v>
@@ -1166,7 +1166,7 @@
         <v>121.3499984741211</v>
       </c>
       <c r="I25" t="n">
-        <v>898.3724365234375</v>
+        <v>898.3724975585938</v>
       </c>
       <c r="J25" t="n">
         <v>17.64999961853027</v>
@@ -1195,7 +1195,7 @@
         <v>133.4499969482422</v>
       </c>
       <c r="I26" t="n">
-        <v>874.7943725585938</v>
+        <v>874.79443359375</v>
       </c>
       <c r="J26" t="n">
         <v>18.5</v>
@@ -1305,13 +1305,13 @@
         <v>91.44999694824219</v>
       </c>
       <c r="G30" t="n">
-        <v>1076.314086914062</v>
+        <v>1076.314208984375</v>
       </c>
       <c r="H30" t="n">
         <v>134</v>
       </c>
       <c r="I30" t="n">
-        <v>853.67236328125</v>
+        <v>853.6724243164062</v>
       </c>
       <c r="J30" t="n">
         <v>15.94999980926514</v>
@@ -1334,7 +1334,7 @@
         <v>86.90000152587891</v>
       </c>
       <c r="G31" t="n">
-        <v>1059.171264648438</v>
+        <v>1059.171142578125</v>
       </c>
       <c r="H31" t="n">
         <v>120.5999984741211</v>
@@ -1392,13 +1392,13 @@
         <v>86.69999694824219</v>
       </c>
       <c r="G33" t="n">
-        <v>1092.868286132812</v>
+        <v>1092.868408203125</v>
       </c>
       <c r="H33" t="n">
         <v>122.5999984741211</v>
       </c>
       <c r="I33" t="n">
-        <v>794.4324951171875</v>
+        <v>794.4325561523438</v>
       </c>
       <c r="J33" t="n">
         <v>14.80000019073486</v>
@@ -1456,7 +1456,7 @@
         <v>120.0999984741211</v>
       </c>
       <c r="I35" t="n">
-        <v>790.3063354492188</v>
+        <v>790.3064575195312</v>
       </c>
       <c r="J35" t="n">
         <v>14.14999961853027</v>
@@ -1485,7 +1485,7 @@
         <v>112.6999969482422</v>
       </c>
       <c r="I36" t="n">
-        <v>750.4694213867188</v>
+        <v>750.4693603515625</v>
       </c>
       <c r="J36" t="n">
         <v>13.60000038146973</v>
@@ -1514,7 +1514,7 @@
         <v>114.3499984741211</v>
       </c>
       <c r="I37" t="n">
-        <v>725.5650634765625</v>
+        <v>725.5650024414062</v>
       </c>
       <c r="J37" t="n">
         <v>12.94999980926514</v>
@@ -1543,7 +1543,7 @@
         <v>113.25</v>
       </c>
       <c r="I38" t="n">
-        <v>748.2589721679688</v>
+        <v>748.2589111328125</v>
       </c>
       <c r="J38" t="n">
         <v>13.55000019073486</v>
@@ -1566,7 +1566,7 @@
         <v>74.75</v>
       </c>
       <c r="G39" t="n">
-        <v>1021.669555664062</v>
+        <v>1021.66943359375</v>
       </c>
       <c r="H39" t="n">
         <v>101.9499969482422</v>
@@ -1595,13 +1595,13 @@
         <v>77.65000152587891</v>
       </c>
       <c r="G40" t="n">
-        <v>1034.44189453125</v>
+        <v>1034.442016601562</v>
       </c>
       <c r="H40" t="n">
         <v>104.5999984741211</v>
       </c>
       <c r="I40" t="n">
-        <v>681.9456176757812</v>
+        <v>681.9457397460938</v>
       </c>
       <c r="J40" t="n">
         <v>13</v>
@@ -1630,7 +1630,7 @@
         <v>104.5999984741211</v>
       </c>
       <c r="I41" t="n">
-        <v>686.1209716796875</v>
+        <v>686.1209106445312</v>
       </c>
       <c r="J41" t="n">
         <v>13.05000019073486</v>
@@ -1653,13 +1653,13 @@
         <v>76.25</v>
       </c>
       <c r="G42" t="n">
-        <v>1086.34619140625</v>
+        <v>1086.346313476562</v>
       </c>
       <c r="H42" t="n">
         <v>107.5999984741211</v>
       </c>
       <c r="I42" t="n">
-        <v>692.8505249023438</v>
+        <v>692.8504638671875</v>
       </c>
       <c r="J42" t="n">
         <v>13.14999961853027</v>
@@ -1688,7 +1688,7 @@
         <v>106.4000015258789</v>
       </c>
       <c r="I43" t="n">
-        <v>688.6751708984375</v>
+        <v>688.6752319335938</v>
       </c>
       <c r="J43" t="n">
         <v>13.05000019073486</v>
@@ -1711,13 +1711,13 @@
         <v>77.5</v>
       </c>
       <c r="G44" t="n">
-        <v>1053.283325195312</v>
+        <v>1053.283203125</v>
       </c>
       <c r="H44" t="n">
         <v>103.5</v>
       </c>
       <c r="I44" t="n">
-        <v>674.7249145507812</v>
+        <v>674.7249755859375</v>
       </c>
       <c r="J44" t="n">
         <v>12.85000038146973</v>
@@ -1775,7 +1775,7 @@
         <v>101.75</v>
       </c>
       <c r="I46" t="n">
-        <v>667.504150390625</v>
+        <v>667.5040893554688</v>
       </c>
       <c r="J46" t="n">
         <v>12.80000019073486</v>
@@ -1804,7 +1804,7 @@
         <v>107.5</v>
       </c>
       <c r="I47" t="n">
-        <v>693.8821411132812</v>
+        <v>693.882080078125</v>
       </c>
       <c r="J47" t="n">
         <v>13.35000038146973</v>
@@ -1833,7 +1833,7 @@
         <v>111.4000015258789</v>
       </c>
       <c r="I48" t="n">
-        <v>701.8396606445312</v>
+        <v>701.839599609375</v>
       </c>
       <c r="J48" t="n">
         <v>13.55000019073486</v>
@@ -1856,7 +1856,7 @@
         <v>77.84999847412109</v>
       </c>
       <c r="G49" t="n">
-        <v>1086.618041992188</v>
+        <v>1086.617919921875</v>
       </c>
       <c r="H49" t="n">
         <v>122.5</v>
@@ -1891,7 +1891,7 @@
         <v>117.25</v>
       </c>
       <c r="I50" t="n">
-        <v>737.84521484375</v>
+        <v>737.8451538085938</v>
       </c>
       <c r="J50" t="n">
         <v>13.85000038146973</v>
@@ -1949,7 +1949,7 @@
         <v>118.9499969482422</v>
       </c>
       <c r="I52" t="n">
-        <v>750.5184936523438</v>
+        <v>750.5184326171875</v>
       </c>
       <c r="J52" t="n">
         <v>14.10000038146973</v>
@@ -1972,13 +1972,13 @@
         <v>78.75</v>
       </c>
       <c r="G53" t="n">
-        <v>1124.006469726562</v>
+        <v>1124.00634765625</v>
       </c>
       <c r="H53" t="n">
         <v>116.8000030517578</v>
       </c>
       <c r="I53" t="n">
-        <v>758.770751953125</v>
+        <v>758.7706909179688</v>
       </c>
       <c r="J53" t="n">
         <v>13.75</v>
@@ -2001,13 +2001,13 @@
         <v>79.15000152587891</v>
       </c>
       <c r="G54" t="n">
-        <v>1117.529663085938</v>
+        <v>1117.52978515625</v>
       </c>
       <c r="H54" t="n">
         <v>115.4000015258789</v>
       </c>
       <c r="I54" t="n">
-        <v>744.8695678710938</v>
+        <v>744.8695068359375</v>
       </c>
       <c r="J54" t="n">
         <v>13.64999961853027</v>
@@ -2030,13 +2030,13 @@
         <v>83.09999847412109</v>
       </c>
       <c r="G55" t="n">
-        <v>1146.4033203125</v>
+        <v>1146.403076171875</v>
       </c>
       <c r="H55" t="n">
         <v>113.1500015258789</v>
       </c>
       <c r="I55" t="n">
-        <v>751.1078491210938</v>
+        <v>751.1079711914062</v>
       </c>
       <c r="J55" t="n">
         <v>13</v>
@@ -2059,13 +2059,13 @@
         <v>81.65000152587891</v>
       </c>
       <c r="G56" t="n">
-        <v>1150.049072265625</v>
+        <v>1150.048950195312</v>
       </c>
       <c r="H56" t="n">
         <v>111.8000030517578</v>
       </c>
       <c r="I56" t="n">
-        <v>756.5111694335938</v>
+        <v>756.51123046875</v>
       </c>
       <c r="J56" t="n">
         <v>12.85000038146973</v>
@@ -2088,13 +2088,13 @@
         <v>85.55000305175781</v>
       </c>
       <c r="G57" t="n">
-        <v>1167.916748046875</v>
+        <v>1167.916625976562</v>
       </c>
       <c r="H57" t="n">
         <v>109.6999969482422</v>
       </c>
       <c r="I57" t="n">
-        <v>756.3638305664062</v>
+        <v>756.3638916015625</v>
       </c>
       <c r="J57" t="n">
         <v>13</v>
@@ -2123,7 +2123,7 @@
         <v>109.1999969482422</v>
       </c>
       <c r="I58" t="n">
-        <v>755.577880859375</v>
+        <v>755.5779418945312</v>
       </c>
       <c r="J58" t="n">
         <v>13</v>
@@ -2146,7 +2146,7 @@
         <v>87.59999847412109</v>
       </c>
       <c r="G59" t="n">
-        <v>1187.528198242188</v>
+        <v>1187.5283203125</v>
       </c>
       <c r="H59" t="n">
         <v>100.6999969482422</v>
@@ -2204,13 +2204,13 @@
         <v>85.80000305175781</v>
       </c>
       <c r="G61" t="n">
-        <v>1210.627075195312</v>
+        <v>1210.626953125</v>
       </c>
       <c r="H61" t="n">
         <v>114.8000030517578</v>
       </c>
       <c r="I61" t="n">
-        <v>769.7738647460938</v>
+        <v>769.7738037109375</v>
       </c>
       <c r="J61" t="n">
         <v>13.55000019073486</v>
@@ -2262,13 +2262,13 @@
         <v>87.84999847412109</v>
       </c>
       <c r="G63" t="n">
-        <v>1202.882080078125</v>
+        <v>1202.881958007812</v>
       </c>
       <c r="H63" t="n">
         <v>122.6500015258789</v>
       </c>
       <c r="I63" t="n">
-        <v>790.2572631835938</v>
+        <v>790.2573852539062</v>
       </c>
       <c r="J63" t="n">
         <v>14.14999961853027</v>
@@ -2326,7 +2326,7 @@
         <v>132.1499938964844</v>
       </c>
       <c r="I65" t="n">
-        <v>804.3058471679688</v>
+        <v>804.305908203125</v>
       </c>
       <c r="J65" t="n">
         <v>15.55000019073486</v>
@@ -2384,7 +2384,7 @@
         <v>125.1500015258789</v>
       </c>
       <c r="I67" t="n">
-        <v>798.9517211914062</v>
+        <v>798.95166015625</v>
       </c>
       <c r="J67" t="n">
         <v>15.5</v>
@@ -2407,7 +2407,7 @@
         <v>97.19999694824219</v>
       </c>
       <c r="G68" t="n">
-        <v>1184.674926757812</v>
+        <v>1184.6748046875</v>
       </c>
       <c r="H68" t="n">
         <v>126.75</v>
@@ -2436,13 +2436,13 @@
         <v>98.40000152587891</v>
       </c>
       <c r="G69" t="n">
-        <v>1182.206420898438</v>
+        <v>1182.206298828125</v>
       </c>
       <c r="H69" t="n">
         <v>125.8499984741211</v>
       </c>
       <c r="I69" t="n">
-        <v>816.3895874023438</v>
+        <v>816.3896484375</v>
       </c>
       <c r="J69" t="n">
         <v>15.69999980926514</v>
@@ -2465,13 +2465,13 @@
         <v>94.84999847412109</v>
       </c>
       <c r="G70" t="n">
-        <v>1159.9453125</v>
+        <v>1159.945556640625</v>
       </c>
       <c r="H70" t="n">
         <v>122.9499969482422</v>
       </c>
       <c r="I70" t="n">
-        <v>794.8746337890625</v>
+        <v>794.8745727539062</v>
       </c>
       <c r="J70" t="n">
         <v>15.14999961853027</v>
@@ -2552,13 +2552,13 @@
         <v>99.09999847412109</v>
       </c>
       <c r="G73" t="n">
-        <v>1196.065551757812</v>
+        <v>1196.0654296875</v>
       </c>
       <c r="H73" t="n">
         <v>123.5999984741211</v>
       </c>
       <c r="I73" t="n">
-        <v>979.8148193359375</v>
+        <v>979.8148803710938</v>
       </c>
       <c r="J73" t="n">
         <v>14.39999961853027</v>
@@ -2587,7 +2587,7 @@
         <v>125.75</v>
       </c>
       <c r="I74" t="n">
-        <v>945.7249755859375</v>
+        <v>945.7249145507812</v>
       </c>
       <c r="J74" t="n">
         <v>14.75</v>
@@ -2610,7 +2610,7 @@
         <v>103.4499969482422</v>
       </c>
       <c r="G75" t="n">
-        <v>1260.062866210938</v>
+        <v>1260.06298828125</v>
       </c>
       <c r="H75" t="n">
         <v>130.3000030517578</v>
@@ -2639,7 +2639,7 @@
         <v>98.90000152587891</v>
       </c>
       <c r="G76" t="n">
-        <v>1249.510009765625</v>
+        <v>1249.509887695312</v>
       </c>
       <c r="H76" t="n">
         <v>128.8999938964844</v>
@@ -2697,13 +2697,13 @@
         <v>114.1999969482422</v>
       </c>
       <c r="G78" t="n">
-        <v>1257.141479492188</v>
+        <v>1257.1416015625</v>
       </c>
       <c r="H78" t="n">
         <v>121.1999969482422</v>
       </c>
       <c r="I78" t="n">
-        <v>926.469482421875</v>
+        <v>926.4695434570312</v>
       </c>
       <c r="J78" t="n">
         <v>14.5</v>
@@ -2761,7 +2761,7 @@
         <v>120.5999984741211</v>
       </c>
       <c r="I80" t="n">
-        <v>1080.660034179688</v>
+        <v>1080.66015625</v>
       </c>
       <c r="J80" t="n">
         <v>13.94999980926514</v>
@@ -2784,7 +2784,7 @@
         <v>86.19999694824219</v>
       </c>
       <c r="G81" t="n">
-        <v>1263.754150390625</v>
+        <v>1263.754272460938</v>
       </c>
       <c r="H81" t="n">
         <v>123.5500030517578</v>
@@ -2819,7 +2819,7 @@
         <v>124.25</v>
       </c>
       <c r="I82" t="n">
-        <v>1096.47705078125</v>
+        <v>1096.477172851562</v>
       </c>
       <c r="J82" t="n">
         <v>14.19999980926514</v>
@@ -2871,13 +2871,13 @@
         <v>80.30000305175781</v>
       </c>
       <c r="G84" t="n">
-        <v>1196.11083984375</v>
+        <v>1196.110961914062</v>
       </c>
       <c r="H84" t="n">
         <v>115.0999984741211</v>
       </c>
       <c r="I84" t="n">
-        <v>980.3551635742188</v>
+        <v>980.355224609375</v>
       </c>
       <c r="J84" t="n">
         <v>13.39999961853027</v>
@@ -2935,7 +2935,7 @@
         <v>112.3000030517578</v>
       </c>
       <c r="I86" t="n">
-        <v>1002.950866699219</v>
+        <v>1002.950927734375</v>
       </c>
       <c r="J86" t="n">
         <v>13.69999980926514</v>
@@ -2964,7 +2964,7 @@
         <v>108.1999969482422</v>
       </c>
       <c r="I87" t="n">
-        <v>953.9773559570312</v>
+        <v>953.977294921875</v>
       </c>
       <c r="J87" t="n">
         <v>13.10000038146973</v>
@@ -2987,7 +2987,7 @@
         <v>68.44999694824219</v>
       </c>
       <c r="G88" t="n">
-        <v>1109.331787109375</v>
+        <v>1109.331909179688</v>
       </c>
       <c r="H88" t="n">
         <v>101</v>
@@ -3045,13 +3045,13 @@
         <v>76.65000152587891</v>
       </c>
       <c r="G90" t="n">
-        <v>1099.050537109375</v>
+        <v>1099.050659179688</v>
       </c>
       <c r="H90" t="n">
         <v>102.0500030517578</v>
       </c>
       <c r="I90" t="n">
-        <v>955.7456665039062</v>
+        <v>955.74560546875</v>
       </c>
       <c r="J90" t="n">
         <v>12.5</v>
@@ -3103,13 +3103,13 @@
         <v>77.90000152587891</v>
       </c>
       <c r="G92" t="n">
-        <v>1145.497314453125</v>
+        <v>1145.497436523438</v>
       </c>
       <c r="H92" t="n">
         <v>107.0500030517578</v>
       </c>
       <c r="I92" t="n">
-        <v>1028.100708007812</v>
+        <v>1028.1005859375</v>
       </c>
       <c r="J92" t="n">
         <v>12.44999980926514</v>
@@ -3138,7 +3138,7 @@
         <v>104.0999984741211</v>
       </c>
       <c r="I93" t="n">
-        <v>1021.715026855469</v>
+        <v>1021.715087890625</v>
       </c>
       <c r="J93" t="n">
         <v>12.44999980926514</v>
@@ -3167,7 +3167,7 @@
         <v>102.0999984741211</v>
       </c>
       <c r="I94" t="n">
-        <v>977.5061645507812</v>
+        <v>977.5062255859375</v>
       </c>
       <c r="J94" t="n">
         <v>12.30000019073486</v>
@@ -3196,7 +3196,7 @@
         <v>104</v>
       </c>
       <c r="I95" t="n">
-        <v>1021.665893554688</v>
+        <v>1021.665832519531</v>
       </c>
       <c r="J95" t="n">
         <v>12.85000038146973</v>
@@ -3219,7 +3219,7 @@
         <v>80.05000305175781</v>
       </c>
       <c r="G96" t="n">
-        <v>1180.711791992188</v>
+        <v>1180.7119140625</v>
       </c>
       <c r="H96" t="n">
         <v>101.6999969482422</v>
@@ -3254,7 +3254,7 @@
         <v>100.9000015258789</v>
       </c>
       <c r="I97" t="n">
-        <v>945.7249755859375</v>
+        <v>945.7249145507812</v>
       </c>
       <c r="J97" t="n">
         <v>12.55000019073486</v>
@@ -3283,7 +3283,7 @@
         <v>100.6500015258789</v>
       </c>
       <c r="I98" t="n">
-        <v>869.9805297851562</v>
+        <v>869.9805908203125</v>
       </c>
       <c r="J98" t="n">
         <v>12.10000038146973</v>
@@ -3335,13 +3335,13 @@
         <v>71.65000152587891</v>
       </c>
       <c r="G100" t="n">
-        <v>1166.308837890625</v>
+        <v>1166.308959960938</v>
       </c>
       <c r="H100" t="n">
         <v>99.84999847412109</v>
       </c>
       <c r="I100" t="n">
-        <v>871.994384765625</v>
+        <v>871.9945068359375</v>
       </c>
       <c r="J100" t="n">
         <v>11.85000038146973</v>
@@ -3364,7 +3364,7 @@
         <v>73.15000152587891</v>
       </c>
       <c r="G101" t="n">
-        <v>1206.935668945312</v>
+        <v>1206.935791015625</v>
       </c>
       <c r="H101" t="n">
         <v>102.5500030517578</v>
@@ -3393,13 +3393,13 @@
         <v>75.5</v>
       </c>
       <c r="G102" t="n">
-        <v>1192.374267578125</v>
+        <v>1192.374389648438</v>
       </c>
       <c r="H102" t="n">
         <v>107.9499969482422</v>
       </c>
       <c r="I102" t="n">
-        <v>909.1298828125</v>
+        <v>909.1299438476562</v>
       </c>
       <c r="J102" t="n">
         <v>12.60000038146973</v>
@@ -3457,7 +3457,7 @@
         <v>109.3000030517578</v>
       </c>
       <c r="I104" t="n">
-        <v>936.24462890625</v>
+        <v>936.2446899414062</v>
       </c>
       <c r="J104" t="n">
         <v>13.85000038146973</v>
@@ -3509,13 +3509,13 @@
         <v>74.65000152587891</v>
       </c>
       <c r="G106" t="n">
-        <v>1253.472900390625</v>
+        <v>1253.473022460938</v>
       </c>
       <c r="H106" t="n">
         <v>105.1500015258789</v>
       </c>
       <c r="I106" t="n">
-        <v>990.7198486328125</v>
+        <v>990.7197265625</v>
       </c>
       <c r="J106" t="n">
         <v>13.80000019073486</v>
@@ -3538,7 +3538,7 @@
         <v>75.90000152587891</v>
       </c>
       <c r="G107" t="n">
-        <v>1255.828247070312</v>
+        <v>1255.828125</v>
       </c>
       <c r="H107" t="n">
         <v>105.5</v>
@@ -3596,7 +3596,7 @@
         <v>80.94999694824219</v>
       </c>
       <c r="G109" t="n">
-        <v>1267.60400390625</v>
+        <v>1267.604125976562</v>
       </c>
       <c r="H109" t="n">
         <v>104.4499969482422</v>
@@ -3625,7 +3625,7 @@
         <v>78.59999847412109</v>
       </c>
       <c r="G110" t="n">
-        <v>1229.33251953125</v>
+        <v>1229.332397460938</v>
       </c>
       <c r="H110" t="n">
         <v>103.5999984741211</v>
@@ -3654,13 +3654,13 @@
         <v>73.55000305175781</v>
       </c>
       <c r="G111" t="n">
-        <v>1206.0751953125</v>
+        <v>1206.074951171875</v>
       </c>
       <c r="H111" t="n">
         <v>96.94999694824219</v>
       </c>
       <c r="I111" t="n">
-        <v>874.548828125</v>
+        <v>874.5487670898438</v>
       </c>
       <c r="J111" t="n">
         <v>12.89999961853027</v>
@@ -3683,7 +3683,7 @@
         <v>72.84999847412109</v>
       </c>
       <c r="G112" t="n">
-        <v>1190.3134765625</v>
+        <v>1190.313598632812</v>
       </c>
       <c r="H112" t="n">
         <v>95.75</v>
@@ -3712,7 +3712,7 @@
         <v>74.59999847412109</v>
       </c>
       <c r="G113" t="n">
-        <v>1175.910766601562</v>
+        <v>1175.91064453125</v>
       </c>
       <c r="H113" t="n">
         <v>95.5</v>
@@ -3747,7 +3747,7 @@
         <v>95.40000152587891</v>
       </c>
       <c r="I114" t="n">
-        <v>825.72265625</v>
+        <v>825.7225341796875</v>
       </c>
       <c r="J114" t="n">
         <v>12.05000019073486</v>
@@ -3770,7 +3770,7 @@
         <v>62.75</v>
       </c>
       <c r="G115" t="n">
-        <v>1173.057495117188</v>
+        <v>1173.057373046875</v>
       </c>
       <c r="H115" t="n">
         <v>95.59999847412109</v>
@@ -3828,7 +3828,7 @@
         <v>62.29999923706055</v>
       </c>
       <c r="G117" t="n">
-        <v>1170.38525390625</v>
+        <v>1170.385131835938</v>
       </c>
       <c r="H117" t="n">
         <v>94.5</v>
@@ -3944,7 +3944,7 @@
         <v>62.84999847412109</v>
       </c>
       <c r="G121" t="n">
-        <v>1128.965942382812</v>
+        <v>1128.9658203125</v>
       </c>
       <c r="H121" t="n">
         <v>93.09999847412109</v>
@@ -3973,13 +3973,13 @@
         <v>67.80000305175781</v>
       </c>
       <c r="G122" t="n">
-        <v>1144.840454101562</v>
+        <v>1144.840576171875</v>
       </c>
       <c r="H122" t="n">
         <v>92.19999694824219</v>
       </c>
       <c r="I122" t="n">
-        <v>827.1961669921875</v>
+        <v>827.1962280273438</v>
       </c>
       <c r="J122" t="n">
         <v>11.80000019073486</v>
@@ -4031,7 +4031,7 @@
         <v>69</v>
       </c>
       <c r="G124" t="n">
-        <v>1175.616577148438</v>
+        <v>1175.616455078125</v>
       </c>
       <c r="H124" t="n">
         <v>90.59999847412109</v>
@@ -4089,13 +4089,13 @@
         <v>65.55000305175781</v>
       </c>
       <c r="G126" t="n">
-        <v>1093.207885742188</v>
+        <v>1093.2080078125</v>
       </c>
       <c r="H126" t="n">
         <v>94.5</v>
       </c>
       <c r="I126" t="n">
-        <v>935.704345703125</v>
+        <v>935.7042846679688</v>
       </c>
       <c r="J126" t="n">
         <v>11.35000038146973</v>
@@ -4147,13 +4147,13 @@
         <v>65.30000305175781</v>
       </c>
       <c r="G128" t="n">
-        <v>1092.3701171875</v>
+        <v>1092.369995117188</v>
       </c>
       <c r="H128" t="n">
         <v>91.75</v>
       </c>
       <c r="I128" t="n">
-        <v>925.6344604492188</v>
+        <v>925.634521484375</v>
       </c>
       <c r="J128" t="n">
         <v>11.19999980926514</v>
@@ -4176,13 +4176,13 @@
         <v>67.25</v>
       </c>
       <c r="G129" t="n">
-        <v>1081.613159179688</v>
+        <v>1081.61328125</v>
       </c>
       <c r="H129" t="n">
         <v>94.90000152587891</v>
       </c>
       <c r="I129" t="n">
-        <v>936.4902954101562</v>
+        <v>936.490234375</v>
       </c>
       <c r="J129" t="n">
         <v>11.44999980926514</v>
@@ -4211,7 +4211,7 @@
         <v>94.80000305175781</v>
       </c>
       <c r="I130" t="n">
-        <v>933.3464965820312</v>
+        <v>933.3465576171875</v>
       </c>
       <c r="J130" t="n">
         <v>11.39999961853027</v>
@@ -4240,7 +4240,7 @@
         <v>101.3499984741211</v>
       </c>
       <c r="I131" t="n">
-        <v>940.5672607421875</v>
+        <v>940.5673217773438</v>
       </c>
       <c r="J131" t="n">
         <v>11.64999961853027</v>
@@ -4292,13 +4292,13 @@
         <v>70.59999847412109</v>
       </c>
       <c r="G133" t="n">
-        <v>1076.8349609375</v>
+        <v>1076.835083007812</v>
       </c>
       <c r="H133" t="n">
         <v>101.6500015258789</v>
       </c>
       <c r="I133" t="n">
-        <v>945.1845703125</v>
+        <v>945.1846923828125</v>
       </c>
       <c r="J133" t="n">
         <v>11.5</v>
@@ -4321,7 +4321,7 @@
         <v>69.75</v>
       </c>
       <c r="G134" t="n">
-        <v>1085.712158203125</v>
+        <v>1085.712280273438</v>
       </c>
       <c r="H134" t="n">
         <v>100.4000015258789</v>
@@ -4356,7 +4356,7 @@
         <v>99.44999694824219</v>
       </c>
       <c r="I135" t="n">
-        <v>945.3319702148438</v>
+        <v>945.3320922851562</v>
       </c>
       <c r="J135" t="n">
         <v>11.30000019073486</v>
@@ -4379,13 +4379,13 @@
         <v>68.15000152587891</v>
       </c>
       <c r="G136" t="n">
-        <v>1097.080322265625</v>
+        <v>1097.080444335938</v>
       </c>
       <c r="H136" t="n">
         <v>102.25</v>
       </c>
       <c r="I136" t="n">
-        <v>964.4400634765625</v>
+        <v>964.4401245117188</v>
       </c>
       <c r="J136" t="n">
         <v>11.5</v>
@@ -4408,13 +4408,13 @@
         <v>67.09999847412109</v>
       </c>
       <c r="G137" t="n">
-        <v>1103.806274414062</v>
+        <v>1103.806396484375</v>
       </c>
       <c r="H137" t="n">
         <v>102.3000030517578</v>
       </c>
       <c r="I137" t="n">
-        <v>978.8323974609375</v>
+        <v>978.8324584960938</v>
       </c>
       <c r="J137" t="n">
         <v>11.80000019073486</v>
@@ -4437,7 +4437,7 @@
         <v>67</v>
       </c>
       <c r="G138" t="n">
-        <v>1133.653564453125</v>
+        <v>1133.653442382812</v>
       </c>
       <c r="H138" t="n">
         <v>104.4000015258789</v>
@@ -4495,7 +4495,7 @@
         <v>63.75</v>
       </c>
       <c r="G140" t="n">
-        <v>1133.69873046875</v>
+        <v>1133.698974609375</v>
       </c>
       <c r="H140" t="n">
         <v>104.5</v>
@@ -4524,7 +4524,7 @@
         <v>62.95000076293945</v>
       </c>
       <c r="G141" t="n">
-        <v>1096.242553710938</v>
+        <v>1096.242431640625</v>
       </c>
       <c r="H141" t="n">
         <v>104.25</v>
@@ -4559,7 +4559,7 @@
         <v>113.9000015258789</v>
       </c>
       <c r="I142" t="n">
-        <v>945.135498046875</v>
+        <v>945.1355590820312</v>
       </c>
       <c r="J142" t="n">
         <v>11.89999961853027</v>
@@ -4588,7 +4588,7 @@
         <v>115.8499984741211</v>
       </c>
       <c r="I143" t="n">
-        <v>945.8231201171875</v>
+        <v>945.8231811523438</v>
       </c>
       <c r="J143" t="n">
         <v>11.89999961853027</v>
@@ -4611,13 +4611,13 @@
         <v>65.15000152587891</v>
       </c>
       <c r="G144" t="n">
-        <v>1112.864624023438</v>
+        <v>1112.86474609375</v>
       </c>
       <c r="H144" t="n">
         <v>114.25</v>
       </c>
       <c r="I144" t="n">
-        <v>955.1070556640625</v>
+        <v>955.1071166992188</v>
       </c>
       <c r="J144" t="n">
         <v>11.75</v>
@@ -4640,13 +4640,13 @@
         <v>64.90000152587891</v>
       </c>
       <c r="G145" t="n">
-        <v>1136.574951171875</v>
+        <v>1136.574829101562</v>
       </c>
       <c r="H145" t="n">
         <v>117.0999984741211</v>
       </c>
       <c r="I145" t="n">
-        <v>964.6856079101562</v>
+        <v>964.6856689453125</v>
       </c>
       <c r="J145" t="n">
         <v>12.39999961853027</v>
@@ -4669,7 +4669,7 @@
         <v>66.94999694824219</v>
       </c>
       <c r="G146" t="n">
-        <v>1166.195678710938</v>
+        <v>1166.19580078125</v>
       </c>
       <c r="H146" t="n">
         <v>123.25</v>
@@ -4727,13 +4727,13 @@
         <v>69.19999694824219</v>
       </c>
       <c r="G148" t="n">
-        <v>1180.46240234375</v>
+        <v>1180.462646484375</v>
       </c>
       <c r="H148" t="n">
         <v>125.0500030517578</v>
       </c>
       <c r="I148" t="n">
-        <v>966.0609741210938</v>
+        <v>966.06103515625</v>
       </c>
       <c r="J148" t="n">
         <v>13</v>
@@ -4756,13 +4756,13 @@
         <v>67.90000152587891</v>
       </c>
       <c r="G149" t="n">
-        <v>1164.859619140625</v>
+        <v>1164.859497070312</v>
       </c>
       <c r="H149" t="n">
         <v>121.3499984741211</v>
       </c>
       <c r="I149" t="n">
-        <v>952.7492065429688</v>
+        <v>952.749267578125</v>
       </c>
       <c r="J149" t="n">
         <v>13.19999980926514</v>
@@ -4785,13 +4785,13 @@
         <v>68.09999847412109</v>
       </c>
       <c r="G150" t="n">
-        <v>1147.693969726562</v>
+        <v>1147.69384765625</v>
       </c>
       <c r="H150" t="n">
         <v>120</v>
       </c>
       <c r="I150" t="n">
-        <v>942.0408935546875</v>
+        <v>942.0409545898438</v>
       </c>
       <c r="J150" t="n">
         <v>13.14999961853027</v>
@@ -4814,7 +4814,7 @@
         <v>67.5</v>
       </c>
       <c r="G151" t="n">
-        <v>1162.708251953125</v>
+        <v>1162.708129882812</v>
       </c>
       <c r="H151" t="n">
         <v>115.8499984741211</v>
@@ -4843,13 +4843,13 @@
         <v>66.65000152587891</v>
       </c>
       <c r="G152" t="n">
-        <v>1169.66064453125</v>
+        <v>1169.660522460938</v>
       </c>
       <c r="H152" t="n">
         <v>117.5500030517578</v>
       </c>
       <c r="I152" t="n">
-        <v>944.4969482421875</v>
+        <v>944.4970092773438</v>
       </c>
       <c r="J152" t="n">
         <v>14.14999961853027</v>
@@ -4878,7 +4878,7 @@
         <v>115.3499984741211</v>
       </c>
       <c r="I153" t="n">
-        <v>953.8790893554688</v>
+        <v>953.8790283203125</v>
       </c>
       <c r="J153" t="n">
         <v>13.60000038146973</v>
@@ -4901,13 +4901,13 @@
         <v>68.34999847412109</v>
       </c>
       <c r="G154" t="n">
-        <v>1192.532836914062</v>
+        <v>1192.53271484375</v>
       </c>
       <c r="H154" t="n">
         <v>115.1500015258789</v>
       </c>
       <c r="I154" t="n">
-        <v>954.0264282226562</v>
+        <v>954.0263671875</v>
       </c>
       <c r="J154" t="n">
         <v>13.39999961853027</v>
@@ -4930,13 +4930,13 @@
         <v>71.90000152587891</v>
       </c>
       <c r="G155" t="n">
-        <v>1200.8212890625</v>
+        <v>1200.821166992188</v>
       </c>
       <c r="H155" t="n">
         <v>116.5500030517578</v>
       </c>
       <c r="I155" t="n">
-        <v>979.5202026367188</v>
+        <v>979.5201416015625</v>
       </c>
       <c r="J155" t="n">
         <v>13.39999961853027</v>
@@ -4965,7 +4965,7 @@
         <v>121.8000030517578</v>
       </c>
       <c r="I156" t="n">
-        <v>975.4922485351562</v>
+        <v>975.4923095703125</v>
       </c>
       <c r="J156" t="n">
         <v>13.64999961853027</v>
@@ -5017,7 +5017,7 @@
         <v>73.75</v>
       </c>
       <c r="G158" t="n">
-        <v>1187.722045898438</v>
+        <v>1187.72216796875</v>
       </c>
       <c r="H158" t="n">
         <v>135.6000061035156</v>
@@ -5046,7 +5046,7 @@
         <v>72.15000152587891</v>
       </c>
       <c r="G159" t="n">
-        <v>1184.427734375</v>
+        <v>1184.427856445312</v>
       </c>
       <c r="H159" t="n">
         <v>140.6999969482422</v>
@@ -5075,13 +5075,13 @@
         <v>72.25</v>
       </c>
       <c r="G160" t="n">
-        <v>1202.694458007812</v>
+        <v>1202.694580078125</v>
       </c>
       <c r="H160" t="n">
         <v>138.6999969482422</v>
       </c>
       <c r="I160" t="n">
-        <v>1004.915771484375</v>
+        <v>1004.915710449219</v>
       </c>
       <c r="J160" t="n">
         <v>15.39999961853027</v>
@@ -5104,7 +5104,7 @@
         <v>74.15000152587891</v>
       </c>
       <c r="G161" t="n">
-        <v>1199.491088867188</v>
+        <v>1199.490966796875</v>
       </c>
       <c r="H161" t="n">
         <v>139.6999969482422</v>
@@ -5133,13 +5133,13 @@
         <v>74.05000305175781</v>
       </c>
       <c r="G162" t="n">
-        <v>1195.992065429688</v>
+        <v>1195.9921875</v>
       </c>
       <c r="H162" t="n">
         <v>139.75</v>
       </c>
       <c r="I162" t="n">
-        <v>1002.852600097656</v>
+        <v>1002.8525390625</v>
       </c>
       <c r="J162" t="n">
         <v>15.05000019073486</v>
@@ -5162,7 +5162,7 @@
         <v>74</v>
       </c>
       <c r="G163" t="n">
-        <v>1189.60791015625</v>
+        <v>1189.607788085938</v>
       </c>
       <c r="H163" t="n">
         <v>157.3500061035156</v>
@@ -5220,13 +5220,13 @@
         <v>70.59999847412109</v>
       </c>
       <c r="G165" t="n">
-        <v>1198.673095703125</v>
+        <v>1198.672973632812</v>
       </c>
       <c r="H165" t="n">
         <v>162</v>
       </c>
       <c r="I165" t="n">
-        <v>1006.291198730469</v>
+        <v>1006.291076660156</v>
       </c>
       <c r="J165" t="n">
         <v>16.79999923706055</v>
@@ -5249,13 +5249,13 @@
         <v>73.30000305175781</v>
       </c>
       <c r="G166" t="n">
-        <v>1163.434692382812</v>
+        <v>1163.4345703125</v>
       </c>
       <c r="H166" t="n">
         <v>193.8500061035156</v>
       </c>
       <c r="I166" t="n">
-        <v>1039.644287109375</v>
+        <v>1039.644165039062</v>
       </c>
       <c r="J166" t="n">
         <v>20.14999961853027</v>
@@ -5284,7 +5284,7 @@
         <v>179.1499938964844</v>
       </c>
       <c r="I167" t="n">
-        <v>1082.084350585938</v>
+        <v>1082.08447265625</v>
       </c>
       <c r="J167" t="n">
         <v>21.20000076293945</v>
@@ -5307,13 +5307,13 @@
         <v>75.59999847412109</v>
       </c>
       <c r="G168" t="n">
-        <v>1167.7060546875</v>
+        <v>1167.705932617188</v>
       </c>
       <c r="H168" t="n">
         <v>182.6999969482422</v>
       </c>
       <c r="I168" t="n">
-        <v>1193.93310546875</v>
+        <v>1193.932983398438</v>
       </c>
       <c r="J168" t="n">
         <v>23.29999923706055</v>
@@ -5342,7 +5342,7 @@
         <v>178.75</v>
       </c>
       <c r="I169" t="n">
-        <v>1173.302124023438</v>
+        <v>1173.30224609375</v>
       </c>
       <c r="J169" t="n">
         <v>21.95000076293945</v>
@@ -5365,13 +5365,13 @@
         <v>75.09999847412109</v>
       </c>
       <c r="G170" t="n">
-        <v>1173.136108398438</v>
+        <v>1173.135986328125</v>
       </c>
       <c r="H170" t="n">
         <v>180.6999969482422</v>
       </c>
       <c r="I170" t="n">
-        <v>1191.771606445312</v>
+        <v>1191.771728515625</v>
       </c>
       <c r="J170" t="n">
         <v>21.64999961853027</v>
@@ -5400,7 +5400,7 @@
         <v>180.3000030517578</v>
       </c>
       <c r="I171" t="n">
-        <v>1188.775268554688</v>
+        <v>1188.775512695312</v>
       </c>
       <c r="J171" t="n">
         <v>21.29999923706055</v>
@@ -5423,7 +5423,7 @@
         <v>74.05000305175781</v>
       </c>
       <c r="G172" t="n">
-        <v>1167.478881835938</v>
+        <v>1167.47900390625</v>
       </c>
       <c r="H172" t="n">
         <v>162.4499969482422</v>
@@ -5487,7 +5487,7 @@
         <v>165.5</v>
       </c>
       <c r="I174" t="n">
-        <v>1137.44384765625</v>
+        <v>1137.443969726562</v>
       </c>
       <c r="J174" t="n">
         <v>20.04999923706055</v>
@@ -5539,13 +5539,13 @@
         <v>71.75</v>
       </c>
       <c r="G176" t="n">
-        <v>1164.479858398438</v>
+        <v>1164.47998046875</v>
       </c>
       <c r="H176" t="n">
         <v>154.4499969482422</v>
       </c>
       <c r="I176" t="n">
-        <v>1170.55126953125</v>
+        <v>1170.551391601562</v>
       </c>
       <c r="J176" t="n">
         <v>18.10000038146973</v>
@@ -5568,13 +5568,13 @@
         <v>68.65000152587891</v>
       </c>
       <c r="G177" t="n">
-        <v>1135.625732421875</v>
+        <v>1135.625854492188</v>
       </c>
       <c r="H177" t="n">
         <v>156.3500061035156</v>
       </c>
       <c r="I177" t="n">
-        <v>1119.121826171875</v>
+        <v>1119.121948242188</v>
       </c>
       <c r="J177" t="n">
         <v>18.45000076293945</v>
@@ -5597,7 +5597,7 @@
         <v>67.05000305175781</v>
       </c>
       <c r="G178" t="n">
-        <v>1137.102416992188</v>
+        <v>1137.1025390625</v>
       </c>
       <c r="H178" t="n">
         <v>151.8000030517578</v>
@@ -5632,7 +5632,7 @@
         <v>154.4499969482422</v>
       </c>
       <c r="I179" t="n">
-        <v>1188.160766601562</v>
+        <v>1188.16064453125</v>
       </c>
       <c r="J179" t="n">
         <v>18.20000076293945</v>
@@ -5655,13 +5655,13 @@
         <v>69.90000152587891</v>
       </c>
       <c r="G180" t="n">
-        <v>1140.419677734375</v>
+        <v>1140.419555664062</v>
       </c>
       <c r="H180" t="n">
         <v>146.75</v>
       </c>
       <c r="I180" t="n">
-        <v>1156.446411132812</v>
+        <v>1156.4462890625</v>
       </c>
       <c r="J180" t="n">
         <v>17.29999923706055</v>
@@ -5719,7 +5719,7 @@
         <v>144.1499938964844</v>
       </c>
       <c r="I182" t="n">
-        <v>1157.628051757812</v>
+        <v>1157.628173828125</v>
       </c>
       <c r="J182" t="n">
         <v>16.89999961853027</v>
@@ -5771,7 +5771,7 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G184" t="n">
-        <v>1088.845581054688</v>
+        <v>1088.845703125</v>
       </c>
       <c r="H184" t="n">
         <v>138.3500061035156</v>
@@ -5806,7 +5806,7 @@
         <v>136.3500061035156</v>
       </c>
       <c r="I185" t="n">
-        <v>1021.610412597656</v>
+        <v>1021.610473632812</v>
       </c>
       <c r="J185" t="n">
         <v>16.10000038146973</v>
@@ -5829,7 +5829,7 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G186" t="n">
-        <v>1056.606201171875</v>
+        <v>1056.606323242188</v>
       </c>
       <c r="H186" t="n">
         <v>137.6499938964844</v>
@@ -6003,7 +6003,7 @@
         <v>67.25</v>
       </c>
       <c r="G192" t="n">
-        <v>1093.185180664062</v>
+        <v>1093.18505859375</v>
       </c>
       <c r="H192" t="n">
         <v>157.6999969482422</v>
@@ -6032,13 +6032,13 @@
         <v>66.94999694824219</v>
       </c>
       <c r="G193" t="n">
-        <v>1071.419555664062</v>
+        <v>1071.41943359375</v>
       </c>
       <c r="H193" t="n">
         <v>149.8500061035156</v>
       </c>
       <c r="I193" t="n">
-        <v>1184.81201171875</v>
+        <v>1184.811889648438</v>
       </c>
       <c r="J193" t="n">
         <v>16.89999961853027</v>
@@ -6061,13 +6061,13 @@
         <v>68.69999694824219</v>
       </c>
       <c r="G194" t="n">
-        <v>1079.303466796875</v>
+        <v>1079.303344726562</v>
       </c>
       <c r="H194" t="n">
         <v>142.6999969482422</v>
       </c>
       <c r="I194" t="n">
-        <v>1128.178955078125</v>
+        <v>1128.179077148438</v>
       </c>
       <c r="J194" t="n">
         <v>16.35000038146973</v>
@@ -6119,13 +6119,13 @@
         <v>67.19999694824219</v>
       </c>
       <c r="G196" t="n">
-        <v>1077.23583984375</v>
+        <v>1077.235717773438</v>
       </c>
       <c r="H196" t="n">
         <v>138.8500061035156</v>
       </c>
       <c r="I196" t="n">
-        <v>1100.404174804688</v>
+        <v>1100.404296875</v>
       </c>
       <c r="J196" t="n">
         <v>16.20000076293945</v>
@@ -6148,13 +6148,13 @@
         <v>66.40000152587891</v>
       </c>
       <c r="G197" t="n">
-        <v>1094.525634765625</v>
+        <v>1094.525512695312</v>
       </c>
       <c r="H197" t="n">
         <v>138.6999969482422</v>
       </c>
       <c r="I197" t="n">
-        <v>1122.56494140625</v>
+        <v>1122.564819335938</v>
       </c>
       <c r="J197" t="n">
         <v>16.20000076293945</v>
@@ -6322,13 +6322,13 @@
         <v>65.05000305175781</v>
       </c>
       <c r="G203" t="n">
-        <v>1109.4296875</v>
+        <v>1109.429809570312</v>
       </c>
       <c r="H203" t="n">
         <v>141.6000061035156</v>
       </c>
       <c r="I203" t="n">
-        <v>1089.717895507812</v>
+        <v>1089.7177734375</v>
       </c>
       <c r="J203" t="n">
         <v>16.29999923706055</v>
@@ -6357,7 +6357,7 @@
         <v>141.8500061035156</v>
       </c>
       <c r="I204" t="n">
-        <v>1086.56591796875</v>
+        <v>1086.566040039062</v>
       </c>
       <c r="J204" t="n">
         <v>16.14999961853027</v>
@@ -6380,7 +6380,7 @@
         <v>63.25</v>
       </c>
       <c r="G205" t="n">
-        <v>1147.871826171875</v>
+        <v>1147.871704101562</v>
       </c>
       <c r="H205" t="n">
         <v>141.8999938964844</v>
@@ -6409,7 +6409,7 @@
         <v>64.15000152587891</v>
       </c>
       <c r="G206" t="n">
-        <v>1158.527221679688</v>
+        <v>1158.52734375</v>
       </c>
       <c r="H206" t="n">
         <v>141.4499969482422</v>
@@ -6444,7 +6444,7 @@
         <v>140.6499938964844</v>
       </c>
       <c r="I207" t="n">
-        <v>1085.728881835938</v>
+        <v>1085.728759765625</v>
       </c>
       <c r="J207" t="n">
         <v>16.04999923706055</v>
@@ -6473,7 +6473,7 @@
         <v>140.5500030517578</v>
       </c>
       <c r="I208" t="n">
-        <v>1097.3017578125</v>
+        <v>1097.301635742188</v>
       </c>
       <c r="J208" t="n">
         <v>16.10000038146973</v>
@@ -6496,13 +6496,13 @@
         <v>62.75</v>
       </c>
       <c r="G209" t="n">
-        <v>1161.049194335938</v>
+        <v>1161.049072265625</v>
       </c>
       <c r="H209" t="n">
         <v>140.1499938964844</v>
       </c>
       <c r="I209" t="n">
-        <v>1067.310791015625</v>
+        <v>1067.310913085938</v>
       </c>
       <c r="J209" t="n">
         <v>16</v>
@@ -6525,7 +6525,7 @@
         <v>64.84999847412109</v>
       </c>
       <c r="G210" t="n">
-        <v>1178.13427734375</v>
+        <v>1178.134399414062</v>
       </c>
       <c r="H210" t="n">
         <v>147.1499938964844</v>
@@ -6554,7 +6554,7 @@
         <v>65.40000152587891</v>
       </c>
       <c r="G211" t="n">
-        <v>1184.427734375</v>
+        <v>1184.427856445312</v>
       </c>
       <c r="H211" t="n">
         <v>152.9499969482422</v>
@@ -6583,7 +6583,7 @@
         <v>65.25</v>
       </c>
       <c r="G212" t="n">
-        <v>1183.246337890625</v>
+        <v>1183.246459960938</v>
       </c>
       <c r="H212" t="n">
         <v>146.6499938964844</v>
@@ -6612,13 +6612,13 @@
         <v>64.5</v>
       </c>
       <c r="G213" t="n">
-        <v>1168.932983398438</v>
+        <v>1168.932861328125</v>
       </c>
       <c r="H213" t="n">
         <v>142.8500061035156</v>
       </c>
       <c r="I213" t="n">
-        <v>1053.669799804688</v>
+        <v>1053.669677734375</v>
       </c>
       <c r="J213" t="n">
         <v>16.10000038146973</v>
@@ -6705,7 +6705,7 @@
         <v>151.3500061035156</v>
       </c>
       <c r="I216" t="n">
-        <v>1058.939086914062</v>
+        <v>1058.93896484375</v>
       </c>
       <c r="J216" t="n">
         <v>16.10000038146973</v>
@@ -6734,7 +6734,7 @@
         <v>148.6499938964844</v>
       </c>
       <c r="I217" t="n">
-        <v>1012.499877929688</v>
+        <v>1012.499938964844</v>
       </c>
       <c r="J217" t="n">
         <v>16</v>
@@ -6757,13 +6757,13 @@
         <v>62.29999923706055</v>
       </c>
       <c r="G218" t="n">
-        <v>1180.9970703125</v>
+        <v>1180.997192382812</v>
       </c>
       <c r="H218" t="n">
         <v>146.0500030517578</v>
       </c>
       <c r="I218" t="n">
-        <v>1011.121032714844</v>
+        <v>1011.120971679688</v>
       </c>
       <c r="J218" t="n">
         <v>15.64999961853027</v>
@@ -6815,13 +6815,13 @@
         <v>60.75</v>
       </c>
       <c r="G220" t="n">
-        <v>1159.117919921875</v>
+        <v>1159.118041992188</v>
       </c>
       <c r="H220" t="n">
         <v>145.25</v>
       </c>
       <c r="I220" t="n">
-        <v>978.766357421875</v>
+        <v>978.7662963867188</v>
       </c>
       <c r="J220" t="n">
         <v>15.5</v>
@@ -6873,13 +6873,13 @@
         <v>60.54999923706055</v>
       </c>
       <c r="G222" t="n">
-        <v>1161.912353515625</v>
+        <v>1161.912475585938</v>
       </c>
       <c r="H222" t="n">
         <v>146.1499938964844</v>
       </c>
       <c r="I222" t="n">
-        <v>995.8055419921875</v>
+        <v>995.8054809570312</v>
       </c>
       <c r="J222" t="n">
         <v>15.19999980926514</v>
@@ -6902,13 +6902,13 @@
         <v>60.40000152587891</v>
       </c>
       <c r="G223" t="n">
-        <v>1171.932006835938</v>
+        <v>1171.931884765625</v>
       </c>
       <c r="H223" t="n">
         <v>147.0500030517578</v>
       </c>
       <c r="I223" t="n">
-        <v>990.5853881835938</v>
+        <v>990.5853271484375</v>
       </c>
       <c r="J223" t="n">
         <v>15.25</v>
@@ -6931,13 +6931,13 @@
         <v>62.95000076293945</v>
       </c>
       <c r="G224" t="n">
-        <v>1189.42626953125</v>
+        <v>1189.426147460938</v>
       </c>
       <c r="H224" t="n">
         <v>154.3000030517578</v>
       </c>
       <c r="I224" t="n">
-        <v>1008.067749023438</v>
+        <v>1008.067810058594</v>
       </c>
       <c r="J224" t="n">
         <v>16</v>
@@ -6960,7 +6960,7 @@
         <v>63.75</v>
       </c>
       <c r="G225" t="n">
-        <v>1230.299194335938</v>
+        <v>1230.299072265625</v>
       </c>
       <c r="H225" t="n">
         <v>153.6499938964844</v>
@@ -6995,7 +6995,7 @@
         <v>154.1499938964844</v>
       </c>
       <c r="I226" t="n">
-        <v>1044.657592773438</v>
+        <v>1044.65771484375</v>
       </c>
       <c r="J226" t="n">
         <v>15.89999961853027</v>
@@ -7024,7 +7024,7 @@
         <v>157.6999969482422</v>
       </c>
       <c r="I227" t="n">
-        <v>1039.289672851562</v>
+        <v>1039.289794921875</v>
       </c>
       <c r="J227" t="n">
         <v>16.04999923706055</v>
@@ -7047,13 +7047,13 @@
         <v>73.40000152587891</v>
       </c>
       <c r="G228" t="n">
-        <v>1237.455810546875</v>
+        <v>1237.455688476562</v>
       </c>
       <c r="H228" t="n">
         <v>156.1000061035156</v>
       </c>
       <c r="I228" t="n">
-        <v>1040.2255859375</v>
+        <v>1040.225463867188</v>
       </c>
       <c r="J228" t="n">
         <v>16</v>
@@ -7082,7 +7082,7 @@
         <v>162.8999938964844</v>
       </c>
       <c r="I229" t="n">
-        <v>1033.675903320312</v>
+        <v>1033.675659179688</v>
       </c>
       <c r="J229" t="n">
         <v>16.79999923706055</v>
@@ -7250,7 +7250,7 @@
         <v>72.40000152587891</v>
       </c>
       <c r="G235" t="n">
-        <v>1187.381225585938</v>
+        <v>1187.38134765625</v>
       </c>
       <c r="H235" t="n">
         <v>161.8000030517578</v>
@@ -7314,7 +7314,7 @@
         <v>156.6499938964844</v>
       </c>
       <c r="I237" t="n">
-        <v>1012.943054199219</v>
+        <v>1012.942993164062</v>
       </c>
       <c r="J237" t="n">
         <v>16.45000076293945</v>
@@ -7337,13 +7337,13 @@
         <v>73.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1171.591064453125</v>
+        <v>1171.590942382812</v>
       </c>
       <c r="H238" t="n">
         <v>148.8999938964844</v>
       </c>
       <c r="I238" t="n">
-        <v>1001.271850585938</v>
+        <v>1001.271789550781</v>
       </c>
       <c r="J238" t="n">
         <v>15.89999961853027</v>
@@ -7366,13 +7366,13 @@
         <v>71.84999847412109</v>
       </c>
       <c r="G239" t="n">
-        <v>1165.797607421875</v>
+        <v>1165.797485351562</v>
       </c>
       <c r="H239" t="n">
         <v>151.1000061035156</v>
       </c>
       <c r="I239" t="n">
-        <v>982.7553100585938</v>
+        <v>982.7552490234375</v>
       </c>
       <c r="J239" t="n">
         <v>15.75</v>
@@ -7424,13 +7424,13 @@
         <v>71.34999847412109</v>
       </c>
       <c r="G241" t="n">
-        <v>1191.334716796875</v>
+        <v>1191.334594726562</v>
       </c>
       <c r="H241" t="n">
         <v>149.8000030517578</v>
       </c>
       <c r="I241" t="n">
-        <v>982.213623046875</v>
+        <v>982.2135009765625</v>
       </c>
       <c r="J241" t="n">
         <v>15.75</v>
@@ -7459,7 +7459,7 @@
         <v>142.5500030517578</v>
       </c>
       <c r="I242" t="n">
-        <v>939.5665283203125</v>
+        <v>939.5664672851562</v>
       </c>
       <c r="J242" t="n">
         <v>15</v>
@@ -7488,7 +7488,7 @@
         <v>135.4499969482422</v>
       </c>
       <c r="I243" t="n">
-        <v>898.88916015625</v>
+        <v>898.8892211914062</v>
       </c>
       <c r="J243" t="n">
         <v>14.25</v>
@@ -7517,7 +7517,7 @@
         <v>128.6999969482422</v>
       </c>
       <c r="I244" t="n">
-        <v>796.0140991210938</v>
+        <v>796.0140380859375</v>
       </c>
       <c r="J244" t="n">
         <v>13.55000019073486</v>
@@ -7546,7 +7546,7 @@
         <v>128.1999969482422</v>
       </c>
       <c r="I245" t="n">
-        <v>858.014892578125</v>
+        <v>858.0149536132812</v>
       </c>
       <c r="J245" t="n">
         <v>14.14999961853027</v>
@@ -7569,7 +7569,7 @@
         <v>65.80000305175781</v>
       </c>
       <c r="G246" t="n">
-        <v>1156.300659179688</v>
+        <v>1156.300537109375</v>
       </c>
       <c r="H246" t="n">
         <v>134.6000061035156</v>
@@ -7604,7 +7604,7 @@
         <v>136.5</v>
       </c>
       <c r="I247" t="n">
-        <v>919.81884765625</v>
+        <v>919.8187866210938</v>
       </c>
       <c r="J247" t="n">
         <v>14.60000038146973</v>
@@ -7627,13 +7627,13 @@
         <v>66.15000152587891</v>
       </c>
       <c r="G248" t="n">
-        <v>1155.66455078125</v>
+        <v>1155.664672851562</v>
       </c>
       <c r="H248" t="n">
         <v>135.8000030517578</v>
       </c>
       <c r="I248" t="n">
-        <v>928.7815551757812</v>
+        <v>928.781494140625</v>
       </c>
       <c r="J248" t="n">
         <v>14.30000019073486</v>
@@ -7691,7 +7691,7 @@
         <v>137.8500061035156</v>
       </c>
       <c r="I250" t="n">
-        <v>937.20263671875</v>
+        <v>937.2025756835938</v>
       </c>
       <c r="J250" t="n">
         <v>14.69999980926514</v>
@@ -7714,7 +7714,7 @@
         <v>66.84999847412109</v>
       </c>
       <c r="G251" t="n">
-        <v>1161.912353515625</v>
+        <v>1161.912475585938</v>
       </c>
       <c r="H251" t="n">
         <v>138.6000061035156</v>
@@ -7749,7 +7749,7 @@
         <v>136.4499969482422</v>
       </c>
       <c r="I252" t="n">
-        <v>901.9916381835938</v>
+        <v>901.9915771484375</v>
       </c>
       <c r="J252" t="n">
         <v>14.44999980926514</v>
@@ -7772,13 +7772,13 @@
         <v>65.75</v>
       </c>
       <c r="G253" t="n">
-        <v>1142.37353515625</v>
+        <v>1142.373291015625</v>
       </c>
       <c r="H253" t="n">
         <v>133.75</v>
       </c>
       <c r="I253" t="n">
-        <v>905.3404541015625</v>
+        <v>905.3403930664062</v>
       </c>
       <c r="J253" t="n">
         <v>14.60000038146973</v>
@@ -7801,13 +7801,13 @@
         <v>65.40000152587891</v>
       </c>
       <c r="G254" t="n">
-        <v>1152.75634765625</v>
+        <v>1152.756469726562</v>
       </c>
       <c r="H254" t="n">
         <v>130.1999969482422</v>
       </c>
       <c r="I254" t="n">
-        <v>892.9302978515625</v>
+        <v>892.930419921875</v>
       </c>
       <c r="J254" t="n">
         <v>14.44999980926514</v>
@@ -7836,7 +7836,7 @@
         <v>135.0500030517578</v>
       </c>
       <c r="I255" t="n">
-        <v>922.3302612304688</v>
+        <v>922.330322265625</v>
       </c>
       <c r="J255" t="n">
         <v>14.55000019073486</v>
@@ -7859,7 +7859,7 @@
         <v>63.75</v>
       </c>
       <c r="G256" t="n">
-        <v>1162.52587890625</v>
+        <v>1162.526000976562</v>
       </c>
       <c r="H256" t="n">
         <v>133</v>
@@ -7888,13 +7888,13 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G257" t="n">
-        <v>1147.871826171875</v>
+        <v>1147.871704101562</v>
       </c>
       <c r="H257" t="n">
         <v>134.3000030517578</v>
       </c>
       <c r="I257" t="n">
-        <v>902.3363647460938</v>
+        <v>902.33642578125</v>
       </c>
       <c r="J257" t="n">
         <v>14.25</v>
@@ -7923,7 +7923,7 @@
         <v>132.3000030517578</v>
       </c>
       <c r="I258" t="n">
-        <v>899.036865234375</v>
+        <v>899.0369262695312</v>
       </c>
       <c r="J258" t="n">
         <v>13.94999980926514</v>
@@ -7946,13 +7946,13 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G259" t="n">
-        <v>1121.266845703125</v>
+        <v>1121.266723632812</v>
       </c>
       <c r="H259" t="n">
         <v>132.6499938964844</v>
       </c>
       <c r="I259" t="n">
-        <v>899.3323364257812</v>
+        <v>899.3323974609375</v>
       </c>
       <c r="J259" t="n">
         <v>14.14999961853027</v>
@@ -7975,7 +7975,7 @@
         <v>65.44999694824219</v>
       </c>
       <c r="G260" t="n">
-        <v>1110.588500976562</v>
+        <v>1110.58837890625</v>
       </c>
       <c r="H260" t="n">
         <v>139.25</v>
@@ -8004,13 +8004,13 @@
         <v>63.34999847412109</v>
       </c>
       <c r="G261" t="n">
-        <v>1126.356201171875</v>
+        <v>1126.356079101562</v>
       </c>
       <c r="H261" t="n">
         <v>141.3000030517578</v>
       </c>
       <c r="I261" t="n">
-        <v>883.5243530273438</v>
+        <v>883.5242919921875</v>
       </c>
       <c r="J261" t="n">
         <v>14.14999961853027</v>
@@ -8062,7 +8062,7 @@
         <v>62.25</v>
       </c>
       <c r="G263" t="n">
-        <v>1123.288940429688</v>
+        <v>1123.288818359375</v>
       </c>
       <c r="H263" t="n">
         <v>137.5</v>
@@ -8097,7 +8097,7 @@
         <v>136.25</v>
       </c>
       <c r="I264" t="n">
-        <v>895.3927001953125</v>
+        <v>895.3926391601562</v>
       </c>
       <c r="J264" t="n">
         <v>13.85000038146973</v>
@@ -8178,13 +8178,13 @@
         <v>60.90000152587891</v>
       </c>
       <c r="G267" t="n">
-        <v>1082.620361328125</v>
+        <v>1082.620239257812</v>
       </c>
       <c r="H267" t="n">
         <v>128.1499938964844</v>
       </c>
       <c r="I267" t="n">
-        <v>869.78466796875</v>
+        <v>869.7847290039062</v>
       </c>
       <c r="J267" t="n">
         <v>12.94999980926514</v>
@@ -8265,13 +8265,13 @@
         <v>61.54999923706055</v>
       </c>
       <c r="G270" t="n">
-        <v>1069.5791015625</v>
+        <v>1069.579345703125</v>
       </c>
       <c r="H270" t="n">
         <v>125.0999984741211</v>
       </c>
       <c r="I270" t="n">
-        <v>856.8822021484375</v>
+        <v>856.8822631835938</v>
       </c>
       <c r="J270" t="n">
         <v>12.75</v>
@@ -8294,7 +8294,7 @@
         <v>59.25</v>
       </c>
       <c r="G271" t="n">
-        <v>1063.240356445312</v>
+        <v>1063.240600585938</v>
       </c>
       <c r="H271" t="n">
         <v>122.25</v>
@@ -8323,7 +8323,7 @@
         <v>59.20000076293945</v>
       </c>
       <c r="G272" t="n">
-        <v>1057.35595703125</v>
+        <v>1057.356079101562</v>
       </c>
       <c r="H272" t="n">
         <v>121.3000030517578</v>
@@ -8352,7 +8352,7 @@
         <v>59.34999847412109</v>
       </c>
       <c r="G273" t="n">
-        <v>1058.28759765625</v>
+        <v>1058.287475585938</v>
       </c>
       <c r="H273" t="n">
         <v>121.4000015258789</v>
@@ -8381,7 +8381,7 @@
         <v>59.70000076293945</v>
       </c>
       <c r="G274" t="n">
-        <v>1050.31298828125</v>
+        <v>1050.312866210938</v>
       </c>
       <c r="H274" t="n">
         <v>124.4499969482422</v>
@@ -8416,7 +8416,7 @@
         <v>123.25</v>
       </c>
       <c r="I275" t="n">
-        <v>819.7998657226562</v>
+        <v>819.7999267578125</v>
       </c>
       <c r="J275" t="n">
         <v>11.64999961853027</v>
@@ -8439,13 +8439,13 @@
         <v>59.45000076293945</v>
       </c>
       <c r="G276" t="n">
-        <v>1068.716064453125</v>
+        <v>1068.715942382812</v>
       </c>
       <c r="H276" t="n">
         <v>123.5500030517578</v>
       </c>
       <c r="I276" t="n">
-        <v>842.8471069335938</v>
+        <v>842.8470458984375</v>
       </c>
       <c r="J276" t="n">
         <v>11.69999980926514</v>
@@ -8468,7 +8468,7 @@
         <v>60.95000076293945</v>
       </c>
       <c r="G277" t="n">
-        <v>1070.578857421875</v>
+        <v>1070.578979492188</v>
       </c>
       <c r="H277" t="n">
         <v>127.3000030517578</v>
@@ -8503,7 +8503,7 @@
         <v>130.9499969482422</v>
       </c>
       <c r="I278" t="n">
-        <v>833.8350830078125</v>
+        <v>833.8350219726562</v>
       </c>
       <c r="J278" t="n">
         <v>11.64999961853027</v>
@@ -8555,7 +8555,7 @@
         <v>60.04999923706055</v>
       </c>
       <c r="G280" t="n">
-        <v>1080.598510742188</v>
+        <v>1080.598388671875</v>
       </c>
       <c r="H280" t="n">
         <v>123.3000030517578</v>
@@ -8590,7 +8590,7 @@
         <v>128.4499969482422</v>
       </c>
       <c r="I281" t="n">
-        <v>837.1837768554688</v>
+        <v>837.183837890625</v>
       </c>
       <c r="J281" t="n">
         <v>11.10000038146973</v>
@@ -8613,7 +8613,7 @@
         <v>60.40000152587891</v>
       </c>
       <c r="G282" t="n">
-        <v>1104.2041015625</v>
+        <v>1104.204223632812</v>
       </c>
       <c r="H282" t="n">
         <v>129.5500030517578</v>
@@ -8642,13 +8642,13 @@
         <v>61.40000152587891</v>
       </c>
       <c r="G283" t="n">
-        <v>1108.816162109375</v>
+        <v>1108.816284179688</v>
       </c>
       <c r="H283" t="n">
         <v>127.0500030517578</v>
       </c>
       <c r="I283" t="n">
-        <v>853.6812744140625</v>
+        <v>853.6812133789062</v>
       </c>
       <c r="J283" t="n">
         <v>11.05000019073486</v>
@@ -8706,7 +8706,7 @@
         <v>120.8000030517578</v>
       </c>
       <c r="I285" t="n">
-        <v>833.3425903320312</v>
+        <v>833.342529296875</v>
       </c>
       <c r="J285" t="n">
         <v>10.60000038146973</v>
@@ -8729,7 +8729,7 @@
         <v>59.34999847412109</v>
       </c>
       <c r="G286" t="n">
-        <v>1080.961791992188</v>
+        <v>1080.9619140625</v>
       </c>
       <c r="H286" t="n">
         <v>118.5500030517578</v>
@@ -8758,7 +8758,7 @@
         <v>59.04999923706055</v>
       </c>
       <c r="G287" t="n">
-        <v>1075.78173828125</v>
+        <v>1075.781616210938</v>
       </c>
       <c r="H287" t="n">
         <v>115.8000030517578</v>
@@ -8793,7 +8793,7 @@
         <v>126.9499969482422</v>
       </c>
       <c r="I288" t="n">
-        <v>802.1697387695312</v>
+        <v>802.1697998046875</v>
       </c>
       <c r="J288" t="n">
         <v>10.10000038146973</v>
@@ -8822,7 +8822,7 @@
         <v>127.75</v>
       </c>
       <c r="I289" t="n">
-        <v>789.316650390625</v>
+        <v>789.3165893554688</v>
       </c>
       <c r="J289" t="n">
         <v>9.899999618530273</v>
@@ -8880,7 +8880,7 @@
         <v>135.6999969482422</v>
       </c>
       <c r="I291" t="n">
-        <v>827.8270874023438</v>
+        <v>827.8270263671875</v>
       </c>
       <c r="J291" t="n">
         <v>10</v>
@@ -8903,13 +8903,13 @@
         <v>58.54999923706055</v>
       </c>
       <c r="G292" t="n">
-        <v>1056.947021484375</v>
+        <v>1056.947143554688</v>
       </c>
       <c r="H292" t="n">
         <v>135.8000030517578</v>
       </c>
       <c r="I292" t="n">
-        <v>827.4823608398438</v>
+        <v>827.482421875</v>
       </c>
       <c r="J292" t="n">
         <v>9.800000190734863</v>
@@ -8932,13 +8932,13 @@
         <v>59.29999923706055</v>
       </c>
       <c r="G293" t="n">
-        <v>1083.91552734375</v>
+        <v>1083.915405273438</v>
       </c>
       <c r="H293" t="n">
         <v>143.25</v>
       </c>
       <c r="I293" t="n">
-        <v>841.07421875</v>
+        <v>841.0741577148438</v>
       </c>
       <c r="J293" t="n">
         <v>10.69999980926514</v>
@@ -8967,7 +8967,7 @@
         <v>140.8000030517578</v>
       </c>
       <c r="I294" t="n">
-        <v>843.8320922851562</v>
+        <v>843.83203125</v>
       </c>
       <c r="J294" t="n">
         <v>10.69999980926514</v>
@@ -8990,7 +8990,7 @@
         <v>59.15000152587891</v>
       </c>
       <c r="G295" t="n">
-        <v>1098.433349609375</v>
+        <v>1098.433471679688</v>
       </c>
       <c r="H295" t="n">
         <v>153.8000030517578</v>
@@ -9083,7 +9083,7 @@
         <v>139.6499938964844</v>
       </c>
       <c r="I298" t="n">
-        <v>793.7979736328125</v>
+        <v>793.7979125976562</v>
       </c>
       <c r="J298" t="n">
         <v>10.75</v>
@@ -9112,7 +9112,7 @@
         <v>144.3000030517578</v>
       </c>
       <c r="I299" t="n">
-        <v>785.1306762695312</v>
+        <v>785.130615234375</v>
       </c>
       <c r="J299" t="n">
         <v>10.69999980926514</v>
@@ -9135,13 +9135,13 @@
         <v>50.95000076293945</v>
       </c>
       <c r="G300" t="n">
-        <v>1016.505920410156</v>
+        <v>1016.505859375</v>
       </c>
       <c r="H300" t="n">
         <v>146.6999969482422</v>
       </c>
       <c r="I300" t="n">
-        <v>778.630126953125</v>
+        <v>778.6301879882812</v>
       </c>
       <c r="J300" t="n">
         <v>10.75</v>
@@ -9170,7 +9170,7 @@
         <v>141.25</v>
       </c>
       <c r="I301" t="n">
-        <v>772.769775390625</v>
+        <v>772.7698974609375</v>
       </c>
       <c r="J301" t="n">
         <v>10.55000019073486</v>
@@ -9222,7 +9222,7 @@
         <v>59.20000076293945</v>
       </c>
       <c r="G303" t="n">
-        <v>1000.238525390625</v>
+        <v>1000.238464355469</v>
       </c>
       <c r="H303" t="n">
         <v>148.0500030517578</v>
@@ -9251,13 +9251,13 @@
         <v>59.59999847412109</v>
       </c>
       <c r="G304" t="n">
-        <v>1031.341674804688</v>
+        <v>1031.341796875</v>
       </c>
       <c r="H304" t="n">
         <v>146.8500061035156</v>
       </c>
       <c r="I304" t="n">
-        <v>780.2553100585938</v>
+        <v>780.25537109375</v>
       </c>
       <c r="J304" t="n">
         <v>10.25</v>
@@ -9286,7 +9286,7 @@
         <v>148.8999938964844</v>
       </c>
       <c r="I305" t="n">
-        <v>778.1376953125</v>
+        <v>778.1377563476562</v>
       </c>
       <c r="J305" t="n">
         <v>10.30000019073486</v>
@@ -9309,7 +9309,7 @@
         <v>56.20000076293945</v>
       </c>
       <c r="G306" t="n">
-        <v>1021.390686035156</v>
+        <v>1021.390808105469</v>
       </c>
       <c r="H306" t="n">
         <v>148.1999969482422</v>
@@ -9338,7 +9338,7 @@
         <v>52.25</v>
       </c>
       <c r="G307" t="n">
-        <v>1001.169921875</v>
+        <v>1001.169982910156</v>
       </c>
       <c r="H307" t="n">
         <v>143.1000061035156</v>
@@ -9367,7 +9367,7 @@
         <v>53.59999847412109</v>
       </c>
       <c r="G308" t="n">
-        <v>1016.73291015625</v>
+        <v>1016.732971191406</v>
       </c>
       <c r="H308" t="n">
         <v>142.1999969482422</v>
@@ -9425,7 +9425,7 @@
         <v>53.79999923706055</v>
       </c>
       <c r="G310" t="n">
-        <v>1015.438049316406</v>
+        <v>1015.438110351562</v>
       </c>
       <c r="H310" t="n">
         <v>141.5500030517578</v>
@@ -9460,7 +9460,7 @@
         <v>144.25</v>
       </c>
       <c r="I311" t="n">
-        <v>770.0613403320312</v>
+        <v>770.061279296875</v>
       </c>
       <c r="J311" t="n">
         <v>9.949999809265137</v>
@@ -9512,13 +9512,13 @@
         <v>56.65000152587891</v>
       </c>
       <c r="G313" t="n">
-        <v>1056.856201171875</v>
+        <v>1056.856323242188</v>
       </c>
       <c r="H313" t="n">
         <v>151.3999938964844</v>
       </c>
       <c r="I313" t="n">
-        <v>782.5697631835938</v>
+        <v>782.5698852539062</v>
       </c>
       <c r="J313" t="n">
         <v>10.80000019073486</v>
@@ -9547,7 +9547,7 @@
         <v>151.3999938964844</v>
       </c>
       <c r="I314" t="n">
-        <v>792.2220458984375</v>
+        <v>792.2221069335938</v>
       </c>
       <c r="J314" t="n">
         <v>11.14999961853027</v>
@@ -9628,13 +9628,13 @@
         <v>55</v>
       </c>
       <c r="G317" t="n">
-        <v>1066.3076171875</v>
+        <v>1066.307739257812</v>
       </c>
       <c r="H317" t="n">
         <v>155.6999969482422</v>
       </c>
       <c r="I317" t="n">
-        <v>799.6089477539062</v>
+        <v>799.6090087890625</v>
       </c>
       <c r="J317" t="n">
         <v>12.14999961853027</v>
@@ -9663,7 +9663,7 @@
         <v>165.5500030517578</v>
       </c>
       <c r="I318" t="n">
-        <v>838.8582153320312</v>
+        <v>838.858154296875</v>
       </c>
       <c r="J318" t="n">
         <v>12.80000019073486</v>
@@ -9692,7 +9692,7 @@
         <v>162</v>
       </c>
       <c r="I319" t="n">
-        <v>843.8320922851562</v>
+        <v>843.83203125</v>
       </c>
       <c r="J319" t="n">
         <v>12.69999980926514</v>
@@ -9750,7 +9750,7 @@
         <v>159.1999969482422</v>
       </c>
       <c r="I321" t="n">
-        <v>823.4932861328125</v>
+        <v>823.4933471679688</v>
       </c>
       <c r="J321" t="n">
         <v>12.25</v>
@@ -9773,7 +9773,7 @@
         <v>54.79999923706055</v>
       </c>
       <c r="G322" t="n">
-        <v>1066.034790039062</v>
+        <v>1066.034912109375</v>
       </c>
       <c r="H322" t="n">
         <v>159.5500030517578</v>
@@ -9802,7 +9802,7 @@
         <v>54.20000076293945</v>
       </c>
       <c r="G323" t="n">
-        <v>1067.37548828125</v>
+        <v>1067.375610351562</v>
       </c>
       <c r="H323" t="n">
         <v>159.3500061035156</v>
@@ -9860,7 +9860,7 @@
         <v>54.95000076293945</v>
       </c>
       <c r="G325" t="n">
-        <v>1079.666870117188</v>
+        <v>1079.666748046875</v>
       </c>
       <c r="H325" t="n">
         <v>157.8999938964844</v>
@@ -9918,7 +9918,7 @@
         <v>58.90000152587891</v>
       </c>
       <c r="G327" t="n">
-        <v>1080.121337890625</v>
+        <v>1080.121215820312</v>
       </c>
       <c r="H327" t="n">
         <v>160.6999969482422</v>
@@ -9947,7 +9947,7 @@
         <v>58.04999923706055</v>
       </c>
       <c r="G328" t="n">
-        <v>1099.86474609375</v>
+        <v>1099.864624023438</v>
       </c>
       <c r="H328" t="n">
         <v>157.5500030517578</v>
@@ -9976,7 +9976,7 @@
         <v>58.40000152587891</v>
       </c>
       <c r="G329" t="n">
-        <v>1109.20263671875</v>
+        <v>1109.202514648438</v>
       </c>
       <c r="H329" t="n">
         <v>154.9499969482422</v>
@@ -10005,7 +10005,7 @@
         <v>58.34999847412109</v>
       </c>
       <c r="G330" t="n">
-        <v>1099.682983398438</v>
+        <v>1099.682861328125</v>
       </c>
       <c r="H330" t="n">
         <v>153.75</v>
@@ -10034,13 +10034,13 @@
         <v>59.54999923706055</v>
       </c>
       <c r="G331" t="n">
-        <v>1112.360595703125</v>
+        <v>1112.360717773438</v>
       </c>
       <c r="H331" t="n">
         <v>154.5500030517578</v>
       </c>
       <c r="I331" t="n">
-        <v>882.3917846679688</v>
+        <v>882.3916625976562</v>
       </c>
       <c r="J331" t="n">
         <v>12.19999980926514</v>
@@ -10063,7 +10063,7 @@
         <v>57.5</v>
       </c>
       <c r="G332" t="n">
-        <v>1109.520629882812</v>
+        <v>1109.5205078125</v>
       </c>
       <c r="H332" t="n">
         <v>153.6000061035156</v>
@@ -10098,7 +10098,7 @@
         <v>152.4499969482422</v>
       </c>
       <c r="I333" t="n">
-        <v>868.3565063476562</v>
+        <v>868.3566284179688</v>
       </c>
       <c r="J333" t="n">
         <v>12.14999961853027</v>
@@ -10121,13 +10121,13 @@
         <v>56.25</v>
       </c>
       <c r="G334" t="n">
-        <v>1126.696899414062</v>
+        <v>1126.69677734375</v>
       </c>
       <c r="H334" t="n">
         <v>150.3000030517578</v>
       </c>
       <c r="I334" t="n">
-        <v>860.8712158203125</v>
+        <v>860.8711547851562</v>
       </c>
       <c r="J334" t="n">
         <v>12</v>
@@ -10156,7 +10156,7 @@
         <v>148.8000030517578</v>
       </c>
       <c r="I335" t="n">
-        <v>873.0349731445312</v>
+        <v>873.034912109375</v>
       </c>
       <c r="J335" t="n">
         <v>11.89999961853027</v>
@@ -10179,7 +10179,7 @@
         <v>58.59999847412109</v>
       </c>
       <c r="G336" t="n">
-        <v>1127.037719726562</v>
+        <v>1127.03759765625</v>
       </c>
       <c r="H336" t="n">
         <v>147.8500061035156</v>
@@ -10214,7 +10214,7 @@
         <v>146.6000061035156</v>
       </c>
       <c r="I337" t="n">
-        <v>866.1405639648438</v>
+        <v>866.1405029296875</v>
       </c>
       <c r="J337" t="n">
         <v>11.80000019073486</v>
@@ -10237,7 +10237,7 @@
         <v>60.59999847412109</v>
       </c>
       <c r="G338" t="n">
-        <v>1131.1044921875</v>
+        <v>1131.104370117188</v>
       </c>
       <c r="H338" t="n">
         <v>144.1499938964844</v>
@@ -10266,13 +10266,13 @@
         <v>59.54999923706055</v>
       </c>
       <c r="G339" t="n">
-        <v>1114.99609375</v>
+        <v>1114.996215820312</v>
       </c>
       <c r="H339" t="n">
         <v>140.8999938964844</v>
       </c>
       <c r="I339" t="n">
-        <v>886.9716186523438</v>
+        <v>886.9715576171875</v>
       </c>
       <c r="J339" t="n">
         <v>11.69999980926514</v>
@@ -10295,7 +10295,7 @@
         <v>59.25</v>
       </c>
       <c r="G340" t="n">
-        <v>1108.407348632812</v>
+        <v>1108.407470703125</v>
       </c>
       <c r="H340" t="n">
         <v>137.1000061035156</v>
@@ -10330,7 +10330,7 @@
         <v>135.8999938964844</v>
       </c>
       <c r="I341" t="n">
-        <v>875.1525268554688</v>
+        <v>875.1524658203125</v>
       </c>
       <c r="J341" t="n">
         <v>11.39999961853027</v>
@@ -10353,13 +10353,13 @@
         <v>58.5</v>
       </c>
       <c r="G342" t="n">
-        <v>1109.611450195312</v>
+        <v>1109.611572265625</v>
       </c>
       <c r="H342" t="n">
         <v>137.4499969482422</v>
       </c>
       <c r="I342" t="n">
-        <v>884.16455078125</v>
+        <v>884.1646118164062</v>
       </c>
       <c r="J342" t="n">
         <v>11.44999980926514</v>
@@ -10382,13 +10382,13 @@
         <v>58.29999923706055</v>
       </c>
       <c r="G343" t="n">
-        <v>1115.541259765625</v>
+        <v>1115.541381835938</v>
       </c>
       <c r="H343" t="n">
         <v>134.6499938964844</v>
       </c>
       <c r="I343" t="n">
-        <v>881.4067993164062</v>
+        <v>881.40673828125</v>
       </c>
       <c r="J343" t="n">
         <v>11.5</v>
@@ -10440,7 +10440,7 @@
         <v>60.65000152587891</v>
       </c>
       <c r="G345" t="n">
-        <v>1108.839111328125</v>
+        <v>1108.8388671875</v>
       </c>
       <c r="H345" t="n">
         <v>138.6000061035156</v>
@@ -10469,13 +10469,13 @@
         <v>60.34999847412109</v>
       </c>
       <c r="G346" t="n">
-        <v>1108.702758789062</v>
+        <v>1108.70263671875</v>
       </c>
       <c r="H346" t="n">
         <v>138.8999938964844</v>
       </c>
       <c r="I346" t="n">
-        <v>880.47119140625</v>
+        <v>880.4711303710938</v>
       </c>
       <c r="J346" t="n">
         <v>12.85000038146973</v>
@@ -10504,7 +10504,7 @@
         <v>138</v>
       </c>
       <c r="I347" t="n">
-        <v>887.0208740234375</v>
+        <v>887.0208129882812</v>
       </c>
       <c r="J347" t="n">
         <v>13.05000019073486</v>
@@ -10527,13 +10527,13 @@
         <v>61.09999847412109</v>
       </c>
       <c r="G348" t="n">
-        <v>1145.349609375</v>
+        <v>1145.349731445312</v>
       </c>
       <c r="H348" t="n">
         <v>139.6499938964844</v>
       </c>
       <c r="I348" t="n">
-        <v>897.3624267578125</v>
+        <v>897.362548828125</v>
       </c>
       <c r="J348" t="n">
         <v>13.30000019073486</v>
@@ -10562,7 +10562,7 @@
         <v>138.6000061035156</v>
       </c>
       <c r="I349" t="n">
-        <v>902.0902099609375</v>
+        <v>902.0901489257812</v>
       </c>
       <c r="J349" t="n">
         <v>12.94999980926514</v>
@@ -10591,7 +10591,7 @@
         <v>134.6999969482422</v>
       </c>
       <c r="I350" t="n">
-        <v>894.8016967773438</v>
+        <v>894.8017578125</v>
       </c>
       <c r="J350" t="n">
         <v>12.94999980926514</v>
@@ -10614,7 +10614,7 @@
         <v>65.15000152587891</v>
       </c>
       <c r="G351" t="n">
-        <v>1119.290161132812</v>
+        <v>1119.289916992188</v>
       </c>
       <c r="H351" t="n">
         <v>133.9499969482422</v>
@@ -10672,7 +10672,7 @@
         <v>64.65000152587891</v>
       </c>
       <c r="G353" t="n">
-        <v>1125.651611328125</v>
+        <v>1125.651733398438</v>
       </c>
       <c r="H353" t="n">
         <v>132.8000030517578</v>
@@ -10701,13 +10701,13 @@
         <v>65.34999847412109</v>
       </c>
       <c r="G354" t="n">
-        <v>1126.60595703125</v>
+        <v>1126.605834960938</v>
       </c>
       <c r="H354" t="n">
         <v>132.5</v>
       </c>
       <c r="I354" t="n">
-        <v>943.4076538085938</v>
+        <v>943.4075927734375</v>
       </c>
       <c r="J354" t="n">
         <v>13.60000038146973</v>
@@ -10759,13 +10759,13 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G356" t="n">
-        <v>1135.830078125</v>
+        <v>1135.830200195312</v>
       </c>
       <c r="H356" t="n">
         <v>137.0500030517578</v>
       </c>
       <c r="I356" t="n">
-        <v>935.3804931640625</v>
+        <v>935.3805541992188</v>
       </c>
       <c r="J356" t="n">
         <v>14.05000019073486</v>
@@ -10788,13 +10788,13 @@
         <v>63.75</v>
       </c>
       <c r="G357" t="n">
-        <v>1127.787475585938</v>
+        <v>1127.787231445312</v>
       </c>
       <c r="H357" t="n">
         <v>137.1999969482422</v>
       </c>
       <c r="I357" t="n">
-        <v>927.4026489257812</v>
+        <v>927.402587890625</v>
       </c>
       <c r="J357" t="n">
         <v>13.94999980926514</v>
@@ -10817,7 +10817,7 @@
         <v>63.54999923706055</v>
       </c>
       <c r="G358" t="n">
-        <v>1128.787109375</v>
+        <v>1128.786987304688</v>
       </c>
       <c r="H358" t="n">
         <v>139.3999938964844</v>
@@ -10910,7 +10910,7 @@
         <v>149.4499969482422</v>
       </c>
       <c r="I361" t="n">
-        <v>938.8209838867188</v>
+        <v>938.8209228515625</v>
       </c>
       <c r="J361" t="n">
         <v>16.75</v>
@@ -10933,7 +10933,7 @@
         <v>65.59999847412109</v>
       </c>
       <c r="G362" t="n">
-        <v>1171.159545898438</v>
+        <v>1171.15966796875</v>
       </c>
       <c r="H362" t="n">
         <v>151.5500030517578</v>
@@ -10962,13 +10962,13 @@
         <v>66.5</v>
       </c>
       <c r="G363" t="n">
-        <v>1159.52685546875</v>
+        <v>1159.526977539062</v>
       </c>
       <c r="H363" t="n">
         <v>150.75</v>
       </c>
       <c r="I363" t="n">
-        <v>959.7296752929688</v>
+        <v>959.729736328125</v>
       </c>
       <c r="J363" t="n">
         <v>15.69999980926514</v>
@@ -10997,7 +10997,7 @@
         <v>146.5</v>
       </c>
       <c r="I364" t="n">
-        <v>962.7449951171875</v>
+        <v>962.7449340820312</v>
       </c>
       <c r="J364" t="n">
         <v>15.30000019073486</v>
@@ -11020,7 +11020,7 @@
         <v>65.75</v>
       </c>
       <c r="G365" t="n">
-        <v>1165.206787109375</v>
+        <v>1165.206909179688</v>
       </c>
       <c r="H365" t="n">
         <v>147.75</v>
@@ -11078,7 +11078,7 @@
         <v>63.15000152587891</v>
       </c>
       <c r="G367" t="n">
-        <v>1142.691528320312</v>
+        <v>1142.691650390625</v>
       </c>
       <c r="H367" t="n">
         <v>143.25</v>
@@ -11113,7 +11113,7 @@
         <v>140.1999969482422</v>
       </c>
       <c r="I368" t="n">
-        <v>924.0413818359375</v>
+        <v>924.0414428710938</v>
       </c>
       <c r="J368" t="n">
         <v>14.10000038146973</v>
@@ -11142,7 +11142,7 @@
         <v>141.25</v>
       </c>
       <c r="I369" t="n">
-        <v>933.6307983398438</v>
+        <v>933.630859375</v>
       </c>
       <c r="J369" t="n">
         <v>13.85000038146973</v>
@@ -11194,7 +11194,7 @@
         <v>62.79999923706055</v>
       </c>
       <c r="G371" t="n">
-        <v>1158.822631835938</v>
+        <v>1158.822509765625</v>
       </c>
       <c r="H371" t="n">
         <v>138.25</v>
@@ -11223,7 +11223,7 @@
         <v>62</v>
       </c>
       <c r="G372" t="n">
-        <v>1188.562744140625</v>
+        <v>1188.562866210938</v>
       </c>
       <c r="H372" t="n">
         <v>139.6499938964844</v>
@@ -11252,13 +11252,13 @@
         <v>62.45000076293945</v>
       </c>
       <c r="G373" t="n">
-        <v>1176.316772460938</v>
+        <v>1176.31689453125</v>
       </c>
       <c r="H373" t="n">
         <v>137.1000061035156</v>
       </c>
       <c r="I373" t="n">
-        <v>939.61181640625</v>
+        <v>939.6118774414062</v>
       </c>
       <c r="J373" t="n">
         <v>14.64999961853027</v>
@@ -11287,7 +11287,7 @@
         <v>138.5</v>
       </c>
       <c r="I374" t="n">
-        <v>944.5054321289062</v>
+        <v>944.50537109375</v>
       </c>
       <c r="J374" t="n">
         <v>14.35000038146973</v>
@@ -11316,7 +11316,7 @@
         <v>138.75</v>
       </c>
       <c r="I375" t="n">
-        <v>952.9085083007812</v>
+        <v>952.908447265625</v>
       </c>
       <c r="J375" t="n">
         <v>15.30000019073486</v>
@@ -11339,7 +11339,7 @@
         <v>64.15000152587891</v>
       </c>
       <c r="G376" t="n">
-        <v>1196.696533203125</v>
+        <v>1196.696411132812</v>
       </c>
       <c r="H376" t="n">
         <v>138.6000061035156</v>
@@ -11426,7 +11426,7 @@
         <v>63.45000076293945</v>
       </c>
       <c r="G379" t="n">
-        <v>1257.653564453125</v>
+        <v>1257.653686523438</v>
       </c>
       <c r="H379" t="n">
         <v>137.5500030517578</v>
@@ -11484,13 +11484,13 @@
         <v>63.5</v>
       </c>
       <c r="G381" t="n">
-        <v>1245.362182617188</v>
+        <v>1245.3623046875</v>
       </c>
       <c r="H381" t="n">
         <v>136.1499938964844</v>
       </c>
       <c r="I381" t="n">
-        <v>958.642333984375</v>
+        <v>958.6422729492188</v>
       </c>
       <c r="J381" t="n">
         <v>15.25</v>
@@ -11519,7 +11519,7 @@
         <v>135</v>
       </c>
       <c r="I382" t="n">
-        <v>963.9313354492188</v>
+        <v>963.9312744140625</v>
       </c>
       <c r="J382" t="n">
         <v>15.25</v>
@@ -11548,7 +11548,7 @@
         <v>141.6999969482422</v>
       </c>
       <c r="I383" t="n">
-        <v>947.619384765625</v>
+        <v>947.6194458007812</v>
       </c>
       <c r="J383" t="n">
         <v>15.19999980926514</v>
@@ -11658,13 +11658,13 @@
         <v>58.25</v>
       </c>
       <c r="G387" t="n">
-        <v>1224.554931640625</v>
+        <v>1224.554809570312</v>
       </c>
       <c r="H387" t="n">
         <v>162.6000061035156</v>
       </c>
       <c r="I387" t="n">
-        <v>949.4483642578125</v>
+        <v>949.4484252929688</v>
       </c>
       <c r="J387" t="n">
         <v>15.64999961853027</v>
@@ -11722,7 +11722,7 @@
         <v>170.9499969482422</v>
       </c>
       <c r="I389" t="n">
-        <v>949.4483642578125</v>
+        <v>949.4484252929688</v>
       </c>
       <c r="J389" t="n">
         <v>15.75</v>
@@ -11780,7 +11780,7 @@
         <v>184.8500061035156</v>
       </c>
       <c r="I391" t="n">
-        <v>947.7183227539062</v>
+        <v>947.7183837890625</v>
       </c>
       <c r="J391" t="n">
         <v>16.10000038146973</v>
@@ -11809,7 +11809,7 @@
         <v>188.8500061035156</v>
       </c>
       <c r="I392" t="n">
-        <v>958.642333984375</v>
+        <v>958.6422729492188</v>
       </c>
       <c r="J392" t="n">
         <v>16.45000076293945</v>
@@ -11896,7 +11896,7 @@
         <v>187.0500030517578</v>
       </c>
       <c r="I395" t="n">
-        <v>970.01123046875</v>
+        <v>970.0111694335938</v>
       </c>
       <c r="J395" t="n">
         <v>18.04999923706055</v>
@@ -11919,13 +11919,13 @@
         <v>58.15000152587891</v>
       </c>
       <c r="G396" t="n">
-        <v>1235.459350585938</v>
+        <v>1235.45947265625</v>
       </c>
       <c r="H396" t="n">
         <v>199.1499938964844</v>
       </c>
       <c r="I396" t="n">
-        <v>968.0339965820312</v>
+        <v>968.033935546875</v>
       </c>
       <c r="J396" t="n">
         <v>19.04999923706055</v>
@@ -11948,7 +11948,7 @@
         <v>59.04999923706055</v>
       </c>
       <c r="G397" t="n">
-        <v>1242.499389648438</v>
+        <v>1242.499633789062</v>
       </c>
       <c r="H397" t="n">
         <v>210.0500030517578</v>
@@ -11977,7 +11977,7 @@
         <v>60.20000076293945</v>
       </c>
       <c r="G398" t="n">
-        <v>1235.016235351562</v>
+        <v>1235.016357421875</v>
       </c>
       <c r="H398" t="n">
         <v>194.6999969482422</v>
@@ -12035,13 +12035,13 @@
         <v>62</v>
       </c>
       <c r="G400" t="n">
-        <v>1248.702514648438</v>
+        <v>1248.702392578125</v>
       </c>
       <c r="H400" t="n">
         <v>175.8500061035156</v>
       </c>
       <c r="I400" t="n">
-        <v>983.5549926757812</v>
+        <v>983.554931640625</v>
       </c>
       <c r="J400" t="n">
         <v>17.5</v>
@@ -12070,7 +12070,7 @@
         <v>170</v>
       </c>
       <c r="I401" t="n">
-        <v>973.86669921875</v>
+        <v>973.8666381835938</v>
       </c>
       <c r="J401" t="n">
         <v>17.39999961853027</v>
@@ -12180,7 +12180,7 @@
         <v>63.5</v>
       </c>
       <c r="G405" t="n">
-        <v>1258.720703125</v>
+        <v>1258.720825195312</v>
       </c>
       <c r="H405" t="n">
         <v>160.6000061035156</v>
@@ -12206,7 +12206,7 @@
         <v>16.75</v>
       </c>
       <c r="E406" t="n">
-        <v>247.9318237304688</v>
+        <v>247.9318389892578</v>
       </c>
       <c r="F406" t="n">
         <v>63.70000076293945</v>
@@ -12270,7 +12270,7 @@
         <v>16.89999961853027</v>
       </c>
       <c r="E408" t="n">
-        <v>223.7761688232422</v>
+        <v>223.7761535644531</v>
       </c>
       <c r="F408" t="n">
         <v>67.84999847412109</v>
@@ -12302,7 +12302,7 @@
         <v>16.70000076293945</v>
       </c>
       <c r="E409" t="n">
-        <v>212.6197357177734</v>
+        <v>212.6197204589844</v>
       </c>
       <c r="F409" t="n">
         <v>66.94999694824219</v>
@@ -12334,7 +12334,7 @@
         <v>16.64999961853027</v>
       </c>
       <c r="E410" t="n">
-        <v>213.6656494140625</v>
+        <v>213.6656646728516</v>
       </c>
       <c r="F410" t="n">
         <v>67.5</v>
@@ -12378,7 +12378,7 @@
         <v>177.8999938964844</v>
       </c>
       <c r="I411" t="n">
-        <v>1001.794494628906</v>
+        <v>1001.794555664062</v>
       </c>
       <c r="J411" t="n">
         <v>17.45000076293945</v>
@@ -12398,7 +12398,7 @@
         <v>16.64999961853027</v>
       </c>
       <c r="E412" t="n">
-        <v>219.3932952880859</v>
+        <v>219.3932800292969</v>
       </c>
       <c r="F412" t="n">
         <v>69.40000152587891</v>
@@ -12410,7 +12410,7 @@
         <v>184.5</v>
       </c>
       <c r="I412" t="n">
-        <v>991.1671142578125</v>
+        <v>991.1670532226562</v>
       </c>
       <c r="J412" t="n">
         <v>18.25</v>
@@ -12462,7 +12462,7 @@
         <v>16.5</v>
       </c>
       <c r="E414" t="n">
-        <v>232.5917510986328</v>
+        <v>232.5917358398438</v>
       </c>
       <c r="F414" t="n">
         <v>68.34999847412109</v>
@@ -12474,7 +12474,7 @@
         <v>186.75</v>
       </c>
       <c r="I414" t="n">
-        <v>1005.650024414062</v>
+        <v>1005.650085449219</v>
       </c>
       <c r="J414" t="n">
         <v>19.14999961853027</v>
@@ -12538,7 +12538,7 @@
         <v>192.8999938964844</v>
       </c>
       <c r="I416" t="n">
-        <v>1005.501708984375</v>
+        <v>1005.501770019531</v>
       </c>
       <c r="J416" t="n">
         <v>19.54999923706055</v>
@@ -12570,7 +12570,7 @@
         <v>190.8000030517578</v>
       </c>
       <c r="I417" t="n">
-        <v>996.8020629882812</v>
+        <v>996.8021240234375</v>
       </c>
       <c r="J417" t="n">
         <v>19.79999923706055</v>
@@ -12686,7 +12686,7 @@
         <v>18.60000038146973</v>
       </c>
       <c r="E421" t="n">
-        <v>249.1769714355469</v>
+        <v>249.1769866943359</v>
       </c>
       <c r="F421" t="n">
         <v>70.94999694824219</v>
@@ -12698,7 +12698,7 @@
         <v>182.8500061035156</v>
       </c>
       <c r="I421" t="n">
-        <v>991.2166137695312</v>
+        <v>991.216552734375</v>
       </c>
       <c r="J421" t="n">
         <v>20.79999923706055</v>
@@ -12750,7 +12750,7 @@
         <v>17.35000038146973</v>
       </c>
       <c r="E423" t="n">
-        <v>239.2656860351562</v>
+        <v>239.2656707763672</v>
       </c>
       <c r="F423" t="n">
         <v>68.55000305175781</v>
@@ -12762,7 +12762,7 @@
         <v>172.6499938964844</v>
       </c>
       <c r="I423" t="n">
-        <v>952.9085083007812</v>
+        <v>952.908447265625</v>
       </c>
       <c r="J423" t="n">
         <v>19</v>
@@ -12826,7 +12826,7 @@
         <v>183.75</v>
       </c>
       <c r="I425" t="n">
-        <v>959.9769287109375</v>
+        <v>959.9768676757812</v>
       </c>
       <c r="J425" t="n">
         <v>19.14999961853027</v>
@@ -12942,7 +12942,7 @@
         <v>19.14999961853027</v>
       </c>
       <c r="E429" t="n">
-        <v>226.9139099121094</v>
+        <v>226.9139251708984</v>
       </c>
       <c r="F429" t="n">
         <v>68.05000305175781</v>
@@ -13038,7 +13038,7 @@
         <v>19.79999923706055</v>
       </c>
       <c r="E432" t="n">
-        <v>226.4656677246094</v>
+        <v>226.4656829833984</v>
       </c>
       <c r="F432" t="n">
         <v>63.95000076293945</v>
@@ -13082,7 +13082,7 @@
         <v>170.8999938964844</v>
       </c>
       <c r="I433" t="n">
-        <v>946.4826049804688</v>
+        <v>946.4825439453125</v>
       </c>
       <c r="J433" t="n">
         <v>19.14999961853027</v>
@@ -13166,7 +13166,7 @@
         <v>20.89999961853027</v>
       </c>
       <c r="E436" t="n">
-        <v>223.7761688232422</v>
+        <v>223.7761535644531</v>
       </c>
       <c r="F436" t="n">
         <v>68.05000305175781</v>
@@ -13198,7 +13198,7 @@
         <v>21.04999923706055</v>
       </c>
       <c r="E437" t="n">
-        <v>224.5232391357422</v>
+        <v>224.5232543945312</v>
       </c>
       <c r="F437" t="n">
         <v>72.84999847412109</v>
@@ -13210,7 +13210,7 @@
         <v>172.1999969482422</v>
       </c>
       <c r="I437" t="n">
-        <v>968.7260131835938</v>
+        <v>968.7259521484375</v>
       </c>
       <c r="J437" t="n">
         <v>18.89999961853027</v>
@@ -13274,7 +13274,7 @@
         <v>171.25</v>
       </c>
       <c r="I439" t="n">
-        <v>943.46728515625</v>
+        <v>943.4673461914062</v>
       </c>
       <c r="J439" t="n">
         <v>17.85000038146973</v>
@@ -13294,7 +13294,7 @@
         <v>19.5</v>
       </c>
       <c r="E440" t="n">
-        <v>219.2936706542969</v>
+        <v>219.2936553955078</v>
       </c>
       <c r="F440" t="n">
         <v>71.65000152587891</v>
@@ -13338,7 +13338,7 @@
         <v>170.5</v>
       </c>
       <c r="I441" t="n">
-        <v>975.2506713867188</v>
+        <v>975.250732421875</v>
       </c>
       <c r="J441" t="n">
         <v>18.20000076293945</v>
@@ -13370,7 +13370,7 @@
         <v>169.3500061035156</v>
       </c>
       <c r="I442" t="n">
-        <v>980.04541015625</v>
+        <v>980.0453491210938</v>
       </c>
       <c r="J442" t="n">
         <v>18</v>
@@ -13390,7 +13390,7 @@
         <v>20.29999923706055</v>
       </c>
       <c r="E443" t="n">
-        <v>223.6765594482422</v>
+        <v>223.6765747070312</v>
       </c>
       <c r="F443" t="n">
         <v>78.75</v>
@@ -13486,7 +13486,7 @@
         <v>19.70000076293945</v>
       </c>
       <c r="E446" t="n">
-        <v>215.1598052978516</v>
+        <v>215.1598205566406</v>
       </c>
       <c r="F446" t="n">
         <v>77.94999694824219</v>
@@ -13518,7 +13518,7 @@
         <v>19.89999961853027</v>
       </c>
       <c r="E447" t="n">
-        <v>213.3668212890625</v>
+        <v>213.3668060302734</v>
       </c>
       <c r="F447" t="n">
         <v>77.84999847412109</v>
@@ -13550,7 +13550,7 @@
         <v>19.39999961853027</v>
       </c>
       <c r="E448" t="n">
-        <v>213.3668212890625</v>
+        <v>213.3668060302734</v>
       </c>
       <c r="F448" t="n">
         <v>76.80000305175781</v>
@@ -13594,7 +13594,7 @@
         <v>169.75</v>
       </c>
       <c r="I449" t="n">
-        <v>995.3192138671875</v>
+        <v>995.3191528320312</v>
       </c>
       <c r="J449" t="n">
         <v>16.70000076293945</v>
@@ -13678,7 +13678,7 @@
         <v>18.39999961853027</v>
       </c>
       <c r="E452" t="n">
-        <v>222.032958984375</v>
+        <v>222.0329742431641</v>
       </c>
       <c r="F452" t="n">
         <v>68.75</v>
@@ -13754,7 +13754,7 @@
         <v>169.25</v>
       </c>
       <c r="I454" t="n">
-        <v>993.9846801757812</v>
+        <v>993.984619140625</v>
       </c>
       <c r="J454" t="n">
         <v>17.10000038146973</v>
@@ -13806,7 +13806,7 @@
         <v>18.04999923706055</v>
       </c>
       <c r="E456" t="n">
-        <v>216.5045776367188</v>
+        <v>216.5045623779297</v>
       </c>
       <c r="F456" t="n">
         <v>67.59999847412109</v>
@@ -14030,7 +14030,7 @@
         <v>19.10000038146973</v>
       </c>
       <c r="E463" t="n">
-        <v>223.8757934570312</v>
+        <v>223.8757781982422</v>
       </c>
       <c r="F463" t="n">
         <v>76</v>
@@ -14170,7 +14170,7 @@
         <v>182.75</v>
       </c>
       <c r="I467" t="n">
-        <v>1104.608520507812</v>
+        <v>1104.608642578125</v>
       </c>
       <c r="J467" t="n">
         <v>22.10000038146973</v>
@@ -14202,7 +14202,7 @@
         <v>179.5500030517578</v>
       </c>
       <c r="I468" t="n">
-        <v>1109.156127929688</v>
+        <v>1109.156005859375</v>
       </c>
       <c r="J468" t="n">
         <v>21.35000038146973</v>
@@ -14254,7 +14254,7 @@
         <v>20.14999961853027</v>
       </c>
       <c r="E470" t="n">
-        <v>220.389404296875</v>
+        <v>220.3893890380859</v>
       </c>
       <c r="F470" t="n">
         <v>82.40000152587891</v>
@@ -14330,7 +14330,7 @@
         <v>177.8999938964844</v>
       </c>
       <c r="I472" t="n">
-        <v>1087.851928710938</v>
+        <v>1087.851806640625</v>
       </c>
       <c r="J472" t="n">
         <v>20.89999961853027</v>
@@ -14394,7 +14394,7 @@
         <v>189.75</v>
       </c>
       <c r="I474" t="n">
-        <v>1082.513427734375</v>
+        <v>1082.513549804688</v>
       </c>
       <c r="J474" t="n">
         <v>21.14999961853027</v>
@@ -14586,7 +14586,7 @@
         <v>214.75</v>
       </c>
       <c r="I480" t="n">
-        <v>1130.9052734375</v>
+        <v>1130.905151367188</v>
       </c>
       <c r="J480" t="n">
         <v>23.95000076293945</v>
@@ -14638,7 +14638,7 @@
         <v>20.54999923706055</v>
       </c>
       <c r="E482" t="n">
-        <v>239.6143188476562</v>
+        <v>239.6143341064453</v>
       </c>
       <c r="F482" t="n">
         <v>86.65000152587891</v>
@@ -14734,7 +14734,7 @@
         <v>20.35000038146973</v>
       </c>
       <c r="E485" t="n">
-        <v>236.7255859375</v>
+        <v>236.7256011962891</v>
       </c>
       <c r="F485" t="n">
         <v>85.90000152587891</v>
@@ -14746,7 +14746,7 @@
         <v>209.75</v>
       </c>
       <c r="I485" t="n">
-        <v>1167.977783203125</v>
+        <v>1167.977661132812</v>
       </c>
       <c r="J485" t="n">
         <v>23.60000038146973</v>
@@ -14766,7 +14766,7 @@
         <v>21.5</v>
       </c>
       <c r="E486" t="n">
-        <v>239.2158660888672</v>
+        <v>239.2158813476562</v>
       </c>
       <c r="F486" t="n">
         <v>86.19999694824219</v>
@@ -14842,7 +14842,7 @@
         <v>190.8000030517578</v>
       </c>
       <c r="I488" t="n">
-        <v>1227.29345703125</v>
+        <v>1227.293334960938</v>
       </c>
       <c r="J488" t="n">
         <v>21.39999961853027</v>
@@ -14862,7 +14862,7 @@
         <v>21.64999961853027</v>
       </c>
       <c r="E489" t="n">
-        <v>237.0742492675781</v>
+        <v>237.0742340087891</v>
       </c>
       <c r="F489" t="n">
         <v>85.90000152587891</v>
@@ -14894,7 +14894,7 @@
         <v>22.04999923706055</v>
       </c>
       <c r="E490" t="n">
-        <v>235.8291015625</v>
+        <v>235.8291168212891</v>
       </c>
       <c r="F490" t="n">
         <v>86.09999847412109</v>
@@ -14958,7 +14958,7 @@
         <v>21.64999961853027</v>
       </c>
       <c r="E492" t="n">
-        <v>233.0897979736328</v>
+        <v>233.0898132324219</v>
       </c>
       <c r="F492" t="n">
         <v>88.90000152587891</v>
@@ -14970,7 +14970,7 @@
         <v>194.6999969482422</v>
       </c>
       <c r="I492" t="n">
-        <v>1348.198974609375</v>
+        <v>1348.198852539062</v>
       </c>
       <c r="J492" t="n">
         <v>22.60000038146973</v>
@@ -15022,7 +15022,7 @@
         <v>21.20000076293945</v>
       </c>
       <c r="E494" t="n">
-        <v>232.0438842773438</v>
+        <v>232.0438690185547</v>
       </c>
       <c r="F494" t="n">
         <v>87.34999847412109</v>
@@ -15098,7 +15098,7 @@
         <v>207.9499969482422</v>
       </c>
       <c r="I496" t="n">
-        <v>1399.06201171875</v>
+        <v>1399.062133789062</v>
       </c>
       <c r="J496" t="n">
         <v>24.10000038146973</v>
@@ -15130,7 +15130,7 @@
         <v>215.1499938964844</v>
       </c>
       <c r="I497" t="n">
-        <v>1368.217895507812</v>
+        <v>1368.218017578125</v>
       </c>
       <c r="J497" t="n">
         <v>25.95000076293945</v>
@@ -15194,7 +15194,7 @@
         <v>229.6000061035156</v>
       </c>
       <c r="I499" t="n">
-        <v>1356.552368164062</v>
+        <v>1356.552490234375</v>
       </c>
       <c r="J499" t="n">
         <v>31.39999961853027</v>
@@ -15214,7 +15214,7 @@
         <v>24.79999923706055</v>
       </c>
       <c r="E500" t="n">
-        <v>241.4571228027344</v>
+        <v>241.4571075439453</v>
       </c>
       <c r="F500" t="n">
         <v>100.5500030517578</v>
@@ -15226,7 +15226,7 @@
         <v>241</v>
       </c>
       <c r="I500" t="n">
-        <v>1329.909790039062</v>
+        <v>1329.909912109375</v>
       </c>
       <c r="J500" t="n">
         <v>32.04999923706055</v>
@@ -15246,7 +15246,7 @@
         <v>24.10000038146973</v>
       </c>
       <c r="E501" t="n">
-        <v>241.2080841064453</v>
+        <v>241.2080993652344</v>
       </c>
       <c r="F501" t="n">
         <v>99.5</v>
@@ -15258,7 +15258,7 @@
         <v>236.8500061035156</v>
       </c>
       <c r="I501" t="n">
-        <v>1350.423217773438</v>
+        <v>1350.423095703125</v>
       </c>
       <c r="J501" t="n">
         <v>31.29999923706055</v>
@@ -15278,7 +15278,7 @@
         <v>24.89999961853027</v>
       </c>
       <c r="E502" t="n">
-        <v>240.0127716064453</v>
+        <v>240.0127563476562</v>
       </c>
       <c r="F502" t="n">
         <v>119.4000015258789</v>
@@ -15450,7 +15450,7 @@
         <v>217.3000030517578</v>
       </c>
       <c r="I507" t="n">
-        <v>1387.594360351562</v>
+        <v>1387.594482421875</v>
       </c>
       <c r="J507" t="n">
         <v>29.85000038146973</v>
@@ -15630,7 +15630,7 @@
         <v>23.85000038146973</v>
       </c>
       <c r="E513" t="n">
-        <v>250.0236663818359</v>
+        <v>250.023681640625</v>
       </c>
       <c r="F513" t="n">
         <v>117</v>
@@ -15642,7 +15642,7 @@
         <v>227.9499969482422</v>
       </c>
       <c r="I513" t="n">
-        <v>1413.940551757812</v>
+        <v>1413.9404296875</v>
       </c>
       <c r="J513" t="n">
         <v>30.10000038146973</v>
@@ -15738,7 +15738,7 @@
         <v>224.6000061035156</v>
       </c>
       <c r="I516" t="n">
-        <v>1375.928955078125</v>
+        <v>1375.929077148438</v>
       </c>
       <c r="J516" t="n">
         <v>29</v>
@@ -15758,7 +15758,7 @@
         <v>24</v>
       </c>
       <c r="E517" t="n">
-        <v>252.8127746582031</v>
+        <v>252.8127899169922</v>
       </c>
       <c r="F517" t="n">
         <v>113.1500015258789</v>
@@ -15790,7 +15790,7 @@
         <v>26</v>
       </c>
       <c r="E518" t="n">
-        <v>287.9754943847656</v>
+        <v>287.9754638671875</v>
       </c>
       <c r="F518" t="n">
         <v>114.4000015258789</v>
@@ -15834,7 +15834,7 @@
         <v>214.9499969482422</v>
       </c>
       <c r="I519" t="n">
-        <v>1380.179809570312</v>
+        <v>1380.179931640625</v>
       </c>
       <c r="J519" t="n">
         <v>26.04999923706055</v>
@@ -15898,7 +15898,7 @@
         <v>213.4499969482422</v>
       </c>
       <c r="I521" t="n">
-        <v>1407.76171875</v>
+        <v>1407.761840820312</v>
       </c>
       <c r="J521" t="n">
         <v>28.54999923706055</v>
@@ -15930,7 +15930,7 @@
         <v>213</v>
       </c>
       <c r="I522" t="n">
-        <v>1366.685424804688</v>
+        <v>1366.685546875</v>
       </c>
       <c r="J522" t="n">
         <v>27.5</v>
@@ -15950,7 +15950,7 @@
         <v>23.45000076293945</v>
       </c>
       <c r="E523" t="n">
-        <v>270.3941345214844</v>
+        <v>270.3941650390625</v>
       </c>
       <c r="F523" t="n">
         <v>106.25</v>
@@ -15982,7 +15982,7 @@
         <v>23.64999961853027</v>
       </c>
       <c r="E524" t="n">
-        <v>271.6890869140625</v>
+        <v>271.6890563964844</v>
       </c>
       <c r="F524" t="n">
         <v>105.4000015258789</v>
@@ -15994,7 +15994,7 @@
         <v>210.1499938964844</v>
       </c>
       <c r="I524" t="n">
-        <v>1327.586669921875</v>
+        <v>1327.586547851562</v>
       </c>
       <c r="J524" t="n">
         <v>26.04999923706055</v>
@@ -16142,7 +16142,7 @@
         <v>24.85000038146973</v>
       </c>
       <c r="E529" t="n">
-        <v>280.604248046875</v>
+        <v>280.6042785644531</v>
       </c>
       <c r="F529" t="n">
         <v>119</v>
@@ -16154,7 +16154,7 @@
         <v>241.1999969482422</v>
       </c>
       <c r="I529" t="n">
-        <v>1438.062377929688</v>
+        <v>1438.062255859375</v>
       </c>
       <c r="J529" t="n">
         <v>26.45000076293945</v>
@@ -16250,7 +16250,7 @@
         <v>228.5</v>
       </c>
       <c r="I532" t="n">
-        <v>1499.948608398438</v>
+        <v>1499.948486328125</v>
       </c>
       <c r="J532" t="n">
         <v>25.60000038146973</v>
@@ -16282,7 +16282,7 @@
         <v>228.5500030517578</v>
       </c>
       <c r="I533" t="n">
-        <v>1470.43896484375</v>
+        <v>1470.438842773438</v>
       </c>
       <c r="J533" t="n">
         <v>25.25</v>
@@ -16314,7 +16314,7 @@
         <v>220.5500030517578</v>
       </c>
       <c r="I534" t="n">
-        <v>1447.602416992188</v>
+        <v>1447.602294921875</v>
       </c>
       <c r="J534" t="n">
         <v>24.64999961853027</v>
@@ -16346,7 +16346,7 @@
         <v>212.1000061035156</v>
       </c>
       <c r="I535" t="n">
-        <v>1397.628662109375</v>
+        <v>1397.628784179688</v>
       </c>
       <c r="J535" t="n">
         <v>23.45000076293945</v>
@@ -16398,7 +16398,7 @@
         <v>22.64999961853027</v>
       </c>
       <c r="E537" t="n">
-        <v>316.6634521484375</v>
+        <v>316.6634216308594</v>
       </c>
       <c r="F537" t="n">
         <v>102.4499969482422</v>
@@ -16462,7 +16462,7 @@
         <v>22</v>
       </c>
       <c r="E539" t="n">
-        <v>320.4486999511719</v>
+        <v>320.4486694335938</v>
       </c>
       <c r="F539" t="n">
         <v>95.25</v>
@@ -16474,7 +16474,7 @@
         <v>226.6999969482422</v>
       </c>
       <c r="I539" t="n">
-        <v>1419.279052734375</v>
+        <v>1419.278930664062</v>
       </c>
       <c r="J539" t="n">
         <v>23.04999923706055</v>
@@ -16558,7 +16558,7 @@
         <v>21.25</v>
       </c>
       <c r="E542" t="n">
-        <v>354.2666320800781</v>
+        <v>354.2666015625</v>
       </c>
       <c r="F542" t="n">
         <v>92.05000305175781</v>
@@ -16602,7 +16602,7 @@
         <v>217.5500030517578</v>
       </c>
       <c r="I543" t="n">
-        <v>1278.206176757812</v>
+        <v>1278.2060546875</v>
       </c>
       <c r="J543" t="n">
         <v>21.45000076293945</v>
@@ -16654,7 +16654,7 @@
         <v>20.20000076293945</v>
       </c>
       <c r="E545" t="n">
-        <v>337.0339050292969</v>
+        <v>337.033935546875</v>
       </c>
       <c r="F545" t="n">
         <v>84.65000152587891</v>
@@ -16730,7 +16730,7 @@
         <v>255.9499969482422</v>
       </c>
       <c r="I547" t="n">
-        <v>1217.012084960938</v>
+        <v>1217.01220703125</v>
       </c>
       <c r="J547" t="n">
         <v>23.20000076293945</v>
@@ -16750,7 +16750,7 @@
         <v>19.70000076293945</v>
       </c>
       <c r="E548" t="n">
-        <v>351.9257202148438</v>
+        <v>351.9257507324219</v>
       </c>
       <c r="F548" t="n">
         <v>88.15000152587891</v>
@@ -16814,7 +16814,7 @@
         <v>19.39999961853027</v>
       </c>
       <c r="E550" t="n">
-        <v>337.3825378417969</v>
+        <v>337.382568359375</v>
       </c>
       <c r="F550" t="n">
         <v>87.05000305175781</v>
@@ -16858,7 +16858,7 @@
         <v>277.3500061035156</v>
       </c>
       <c r="I551" t="n">
-        <v>1234.7080078125</v>
+        <v>1234.707885742188</v>
       </c>
       <c r="J551" t="n">
         <v>26.29999923706055</v>
@@ -16878,7 +16878,7 @@
         <v>19.85000038146973</v>
       </c>
       <c r="E552" t="n">
-        <v>344.8035583496094</v>
+        <v>344.8035888671875</v>
       </c>
       <c r="F552" t="n">
         <v>90.94999694824219</v>
@@ -16922,7 +16922,7 @@
         <v>266.9500122070312</v>
       </c>
       <c r="I553" t="n">
-        <v>1257.198486328125</v>
+        <v>1257.198364257812</v>
       </c>
       <c r="J553" t="n">
         <v>27.64999961853027</v>
@@ -16954,7 +16954,7 @@
         <v>270.9500122070312</v>
       </c>
       <c r="I554" t="n">
-        <v>1260.905639648438</v>
+        <v>1260.90576171875</v>
       </c>
       <c r="J554" t="n">
         <v>28.25</v>
@@ -16974,7 +16974,7 @@
         <v>21.5</v>
       </c>
       <c r="E555" t="n">
-        <v>355.5615539550781</v>
+        <v>355.5615844726562</v>
       </c>
       <c r="F555" t="n">
         <v>90.40000152587891</v>
@@ -16986,7 +16986,7 @@
         <v>268.6499938964844</v>
       </c>
       <c r="I555" t="n">
-        <v>1305.936279296875</v>
+        <v>1305.936401367188</v>
       </c>
       <c r="J555" t="n">
         <v>28.89999961853027</v>
@@ -17006,7 +17006,7 @@
         <v>21.5</v>
       </c>
       <c r="E556" t="n">
-        <v>355.7109985351562</v>
+        <v>355.7109680175781</v>
       </c>
       <c r="F556" t="n">
         <v>89.90000152587891</v>
@@ -17038,7 +17038,7 @@
         <v>21.95000076293945</v>
       </c>
       <c r="E557" t="n">
-        <v>355.7109985351562</v>
+        <v>355.7109680175781</v>
       </c>
       <c r="F557" t="n">
         <v>92.40000152587891</v>
@@ -17102,7 +17102,7 @@
         <v>22.10000038146973</v>
       </c>
       <c r="E559" t="n">
-        <v>371.7483520507812</v>
+        <v>371.7483825683594</v>
       </c>
       <c r="F559" t="n">
         <v>90.84999847412109</v>
@@ -17114,7 +17114,7 @@
         <v>298.8999938964844</v>
       </c>
       <c r="I559" t="n">
-        <v>1317.107543945312</v>
+        <v>1317.107666015625</v>
       </c>
       <c r="J559" t="n">
         <v>32.59999847412109</v>
@@ -17210,7 +17210,7 @@
         <v>227.6000061035156</v>
       </c>
       <c r="I562" t="n">
-        <v>1280.974365234375</v>
+        <v>1280.974243164062</v>
       </c>
       <c r="J562" t="n">
         <v>28.35000038146973</v>
@@ -17262,7 +17262,7 @@
         <v>20.75</v>
       </c>
       <c r="E564" t="n">
-        <v>352.9218444824219</v>
+        <v>352.921875</v>
       </c>
       <c r="F564" t="n">
         <v>85.90000152587891</v>
@@ -17326,7 +17326,7 @@
         <v>22</v>
       </c>
       <c r="E566" t="n">
-        <v>376.9281311035156</v>
+        <v>376.9281005859375</v>
       </c>
       <c r="F566" t="n">
         <v>89.5</v>
@@ -17338,7 +17338,7 @@
         <v>194.6999969482422</v>
       </c>
       <c r="I566" t="n">
-        <v>1236.8828125</v>
+        <v>1236.882934570312</v>
       </c>
       <c r="J566" t="n">
         <v>28.70000076293945</v>
@@ -17358,7 +17358,7 @@
         <v>22.10000038146973</v>
       </c>
       <c r="E567" t="n">
-        <v>368.660400390625</v>
+        <v>368.6604309082031</v>
       </c>
       <c r="F567" t="n">
         <v>87.59999847412109</v>
@@ -17370,7 +17370,7 @@
         <v>188.75</v>
       </c>
       <c r="I567" t="n">
-        <v>1248.350463867188</v>
+        <v>1248.3505859375</v>
       </c>
       <c r="J567" t="n">
         <v>28.04999923706055</v>
@@ -17390,7 +17390,7 @@
         <v>22.25</v>
       </c>
       <c r="E568" t="n">
-        <v>381.21142578125</v>
+        <v>381.2113952636719</v>
       </c>
       <c r="F568" t="n">
         <v>87.19999694824219</v>
@@ -17422,7 +17422,7 @@
         <v>22.64999961853027</v>
       </c>
       <c r="E569" t="n">
-        <v>386.4410095214844</v>
+        <v>386.4409790039062</v>
       </c>
       <c r="F569" t="n">
         <v>88.05000305175781</v>
@@ -17454,7 +17454,7 @@
         <v>22.75</v>
       </c>
       <c r="E570" t="n">
-        <v>380.3647155761719</v>
+        <v>380.3646850585938</v>
       </c>
       <c r="F570" t="n">
         <v>92.44999694824219</v>
@@ -17486,7 +17486,7 @@
         <v>22.35000038146973</v>
       </c>
       <c r="E571" t="n">
-        <v>380.8129272460938</v>
+        <v>380.8129577636719</v>
       </c>
       <c r="F571" t="n">
         <v>92.75</v>
@@ -17562,7 +17562,7 @@
         <v>185.8000030517578</v>
       </c>
       <c r="I573" t="n">
-        <v>1286.362060546875</v>
+        <v>1286.362182617188</v>
       </c>
       <c r="J573" t="n">
         <v>27.54999923706055</v>
@@ -17626,7 +17626,7 @@
         <v>175.4499969482422</v>
       </c>
       <c r="I575" t="n">
-        <v>1296.544677734375</v>
+        <v>1296.544555664062</v>
       </c>
       <c r="J575" t="n">
         <v>26.95000076293945</v>
@@ -17678,7 +17678,7 @@
         <v>21.45000076293945</v>
       </c>
       <c r="E577" t="n">
-        <v>368.8098449707031</v>
+        <v>368.809814453125</v>
       </c>
       <c r="F577" t="n">
         <v>80.65000152587891</v>
@@ -17690,7 +17690,7 @@
         <v>166.5500030517578</v>
       </c>
       <c r="I577" t="n">
-        <v>1268.073120117188</v>
+        <v>1268.072998046875</v>
       </c>
       <c r="J577" t="n">
         <v>25.85000038146973</v>
@@ -17710,7 +17710,7 @@
         <v>21.04999923706055</v>
       </c>
       <c r="E578" t="n">
-        <v>354.8642883300781</v>
+        <v>354.8642578125</v>
       </c>
       <c r="F578" t="n">
         <v>80</v>
@@ -17722,7 +17722,7 @@
         <v>170.75</v>
       </c>
       <c r="I578" t="n">
-        <v>1236.932250976562</v>
+        <v>1236.93212890625</v>
       </c>
       <c r="J578" t="n">
         <v>25.64999961853027</v>
@@ -17806,7 +17806,7 @@
         <v>20.79999923706055</v>
       </c>
       <c r="E581" t="n">
-        <v>346.4969787597656</v>
+        <v>346.4969482421875</v>
       </c>
       <c r="F581" t="n">
         <v>78</v>
@@ -17818,7 +17818,7 @@
         <v>162.9499969482422</v>
       </c>
       <c r="I581" t="n">
-        <v>1185.821899414062</v>
+        <v>1185.82177734375</v>
       </c>
       <c r="J581" t="n">
         <v>24.95000076293945</v>
@@ -17882,7 +17882,7 @@
         <v>171.4499969482422</v>
       </c>
       <c r="I583" t="n">
-        <v>1204.901977539062</v>
+        <v>1204.90185546875</v>
       </c>
       <c r="J583" t="n">
         <v>25.60000038146973</v>
@@ -17902,7 +17902,7 @@
         <v>20.85000038146973</v>
       </c>
       <c r="E584" t="n">
-        <v>352.4736022949219</v>
+        <v>352.4736328125</v>
       </c>
       <c r="F584" t="n">
         <v>80.5</v>
@@ -18030,7 +18030,7 @@
         <v>21.20000076293945</v>
       </c>
       <c r="E588" t="n">
-        <v>356.2588500976562</v>
+        <v>356.2588195800781</v>
       </c>
       <c r="F588" t="n">
         <v>82.25</v>
@@ -18094,7 +18094,7 @@
         <v>21.39999961853027</v>
       </c>
       <c r="E590" t="n">
-        <v>363.9786682128906</v>
+        <v>363.9786987304688</v>
       </c>
       <c r="F590" t="n">
         <v>82.19999694824219</v>
@@ -18190,7 +18190,7 @@
         <v>20.79999923706055</v>
       </c>
       <c r="E593" t="n">
-        <v>347.8417358398438</v>
+        <v>347.8417053222656</v>
       </c>
       <c r="F593" t="n">
         <v>77.80000305175781</v>
@@ -18222,7 +18222,7 @@
         <v>20.54999923706055</v>
       </c>
       <c r="E594" t="n">
-        <v>346.3973693847656</v>
+        <v>346.3973388671875</v>
       </c>
       <c r="F594" t="n">
         <v>80.94999694824219</v>
@@ -18234,7 +18234,7 @@
         <v>167.1000061035156</v>
       </c>
       <c r="I594" t="n">
-        <v>1165.160034179688</v>
+        <v>1165.16015625</v>
       </c>
       <c r="J594" t="n">
         <v>24.70000076293945</v>
@@ -18266,7 +18266,7 @@
         <v>166.3500061035156</v>
       </c>
       <c r="I595" t="n">
-        <v>1168.373168945312</v>
+        <v>1168.373046875</v>
       </c>
       <c r="J595" t="n">
         <v>24.54999923706055</v>
@@ -18298,7 +18298,7 @@
         <v>173.25</v>
       </c>
       <c r="I596" t="n">
-        <v>1223.042602539062</v>
+        <v>1223.04248046875</v>
       </c>
       <c r="J596" t="n">
         <v>25.75</v>
@@ -18318,7 +18318,7 @@
         <v>19.39999961853027</v>
       </c>
       <c r="E597" t="n">
-        <v>331.6549377441406</v>
+        <v>331.6549072265625</v>
       </c>
       <c r="F597" t="n">
         <v>75.59999847412109</v>
@@ -18350,7 +18350,7 @@
         <v>19.95000076293945</v>
       </c>
       <c r="E598" t="n">
-        <v>344.2557067871094</v>
+        <v>344.2557373046875</v>
       </c>
       <c r="F598" t="n">
         <v>76.09999847412109</v>
@@ -18382,7 +18382,7 @@
         <v>20.29999923706055</v>
       </c>
       <c r="E599" t="n">
-        <v>348.0408935546875</v>
+        <v>348.0409240722656</v>
       </c>
       <c r="F599" t="n">
         <v>79.84999847412109</v>
@@ -18478,7 +18478,7 @@
         <v>21.68000030517578</v>
       </c>
       <c r="E602" t="n">
-        <v>348.8876037597656</v>
+        <v>348.8876342773438</v>
       </c>
       <c r="F602" t="n">
         <v>79.94000244140625</v>
@@ -18670,7 +18670,7 @@
         <v>22.73999977111816</v>
       </c>
       <c r="E608" t="n">
-        <v>364.1281127929688</v>
+        <v>364.1280822753906</v>
       </c>
       <c r="F608" t="n">
         <v>84.08999633789062</v>
@@ -18734,7 +18734,7 @@
         <v>22.72999954223633</v>
       </c>
       <c r="E610" t="n">
-        <v>353.9678039550781</v>
+        <v>353.9677734375</v>
       </c>
       <c r="F610" t="n">
         <v>82.69999694824219</v>
@@ -18798,7 +18798,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="E612" t="n">
-        <v>354.8642883300781</v>
+        <v>354.8642578125</v>
       </c>
       <c r="F612" t="n">
         <v>81.08999633789062</v>
@@ -18958,7 +18958,7 @@
         <v>23.46999931335449</v>
       </c>
       <c r="E617" t="n">
-        <v>349.9335327148438</v>
+        <v>349.9335021972656</v>
       </c>
       <c r="F617" t="n">
         <v>88.41000366210938</v>
@@ -19118,7 +19118,7 @@
         <v>23.09000015258789</v>
       </c>
       <c r="E622" t="n">
-        <v>346.5965576171875</v>
+        <v>346.5965881347656</v>
       </c>
       <c r="F622" t="n">
         <v>82.37999725341797</v>
@@ -19438,7 +19438,7 @@
         <v>23.82999992370605</v>
       </c>
       <c r="E632" t="n">
-        <v>327.9195251464844</v>
+        <v>327.9194946289062</v>
       </c>
       <c r="F632" t="n">
         <v>84.30999755859375</v>
@@ -19470,7 +19470,7 @@
         <v>23.92000007629395</v>
       </c>
       <c r="E633" t="n">
-        <v>330.6089782714844</v>
+        <v>330.6090087890625</v>
       </c>
       <c r="F633" t="n">
         <v>91.58999633789062</v>
@@ -19534,7 +19534,7 @@
         <v>24.17000007629395</v>
       </c>
       <c r="E635" t="n">
-        <v>328.0689086914062</v>
+        <v>328.0689392089844</v>
       </c>
       <c r="F635" t="n">
         <v>90.97000122070312</v>
@@ -19630,7 +19630,7 @@
         <v>23.06999969482422</v>
       </c>
       <c r="E638" t="n">
-        <v>324.9809875488281</v>
+        <v>324.98095703125</v>
       </c>
       <c r="F638" t="n">
         <v>93.27999877929688</v>
@@ -19790,7 +19790,7 @@
         <v>21.71999931335449</v>
       </c>
       <c r="E643" t="n">
-        <v>324.3335266113281</v>
+        <v>324.33349609375</v>
       </c>
       <c r="F643" t="n">
         <v>99.91999816894531</v>
@@ -20014,7 +20014,7 @@
         <v>21.45999908447266</v>
       </c>
       <c r="E650" t="n">
-        <v>329.8121032714844</v>
+        <v>329.8121337890625</v>
       </c>
       <c r="F650" t="n">
         <v>98.65000152587891</v>
@@ -20142,7 +20142,7 @@
         <v>21.40999984741211</v>
       </c>
       <c r="E654" t="n">
-        <v>322.34130859375</v>
+        <v>322.3412780761719</v>
       </c>
       <c r="F654" t="n">
         <v>97.77999877929688</v>
@@ -20174,7 +20174,7 @@
         <v>21.23999977111816</v>
       </c>
       <c r="E655" t="n">
-        <v>320.9965515136719</v>
+        <v>320.9965209960938</v>
       </c>
       <c r="F655" t="n">
         <v>96.19000244140625</v>
@@ -20238,7 +20238,7 @@
         <v>21.11000061035156</v>
       </c>
       <c r="E657" t="n">
-        <v>320.4486999511719</v>
+        <v>320.4486694335938</v>
       </c>
       <c r="F657" t="n">
         <v>95.16000366210938</v>
@@ -20302,7 +20302,7 @@
         <v>20.65999984741211</v>
       </c>
       <c r="E659" t="n">
-        <v>348.8378295898438</v>
+        <v>348.8377990722656</v>
       </c>
       <c r="F659" t="n">
         <v>93.05999755859375</v>
@@ -20334,7 +20334,7 @@
         <v>20.5</v>
       </c>
       <c r="E660" t="n">
-        <v>345.8495178222656</v>
+        <v>345.8494873046875</v>
       </c>
       <c r="F660" t="n">
         <v>91.76000213623047</v>
@@ -20590,7 +20590,7 @@
         <v>21.73999977111816</v>
       </c>
       <c r="E668" t="n">
-        <v>347.4432373046875</v>
+        <v>347.4432678222656</v>
       </c>
       <c r="F668" t="n">
         <v>91.58000183105469</v>
@@ -20686,7 +20686,7 @@
         <v>20.45000076293945</v>
       </c>
       <c r="E671" t="n">
-        <v>345.3016357421875</v>
+        <v>345.3016052246094</v>
       </c>
       <c r="F671" t="n">
         <v>83.73999786376953</v>
@@ -20750,7 +20750,7 @@
         <v>20.71999931335449</v>
       </c>
       <c r="E673" t="n">
-        <v>352.8720703125</v>
+        <v>352.8720397949219</v>
       </c>
       <c r="F673" t="n">
         <v>83.36000061035156</v>
@@ -20974,7 +20974,7 @@
         <v>20.25</v>
       </c>
       <c r="E680" t="n">
-        <v>344.2557067871094</v>
+        <v>344.2557373046875</v>
       </c>
       <c r="F680" t="n">
         <v>80.34999847412109</v>
@@ -21070,7 +21070,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="E683" t="n">
-        <v>344.2557067871094</v>
+        <v>344.2557373046875</v>
       </c>
       <c r="F683" t="n">
         <v>75.75</v>
@@ -21166,7 +21166,7 @@
         <v>20.09000015258789</v>
       </c>
       <c r="E686" t="n">
-        <v>340.171630859375</v>
+        <v>340.1716613769531</v>
       </c>
       <c r="F686" t="n">
         <v>81.36000061035156</v>
@@ -21198,7 +21198,7 @@
         <v>20.72999954223633</v>
       </c>
       <c r="E687" t="n">
-        <v>338.7272644042969</v>
+        <v>338.727294921875</v>
       </c>
       <c r="F687" t="n">
         <v>79.09999847412109</v>
@@ -21262,7 +21262,7 @@
         <v>20.48999977111816</v>
       </c>
       <c r="E689" t="n">
-        <v>332.3521728515625</v>
+        <v>332.3522033691406</v>
       </c>
       <c r="F689" t="n">
         <v>85.95999908447266</v>
@@ -21390,7 +21390,7 @@
         <v>18.84000015258789</v>
       </c>
       <c r="E693" t="n">
-        <v>312.8284301757812</v>
+        <v>312.8283996582031</v>
       </c>
       <c r="F693" t="n">
         <v>76.08000183105469</v>
@@ -21422,7 +21422,7 @@
         <v>18.93000030517578</v>
       </c>
       <c r="E694" t="n">
-        <v>313.4759216308594</v>
+        <v>313.4758911132812</v>
       </c>
       <c r="F694" t="n">
         <v>79.12999725341797</v>
@@ -21582,7 +21582,7 @@
         <v>19.28000068664551</v>
       </c>
       <c r="E699" t="n">
-        <v>318.7055053710938</v>
+        <v>318.7054748535156</v>
       </c>
       <c r="F699" t="n">
         <v>81.11000061035156</v>
@@ -21774,7 +21774,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="E705" t="n">
-        <v>320.2992248535156</v>
+        <v>320.2992553710938</v>
       </c>
       <c r="F705" t="n">
         <v>83.80999755859375</v>
@@ -21902,7 +21902,7 @@
         <v>18.28000068664551</v>
       </c>
       <c r="E709" t="n">
-        <v>298.2353820800781</v>
+        <v>298.2354125976562</v>
       </c>
       <c r="F709" t="n">
         <v>77.97000122070312</v>
@@ -22030,7 +22030,7 @@
         <v>18.11000061035156</v>
       </c>
       <c r="E713" t="n">
-        <v>312.9778442382812</v>
+        <v>312.9778747558594</v>
       </c>
       <c r="F713" t="n">
         <v>84.30000305175781</v>
@@ -22062,7 +22062,7 @@
         <v>18.17000007629395</v>
       </c>
       <c r="E714" t="n">
-        <v>312.5794067382812</v>
+        <v>312.5793762207031</v>
       </c>
       <c r="F714" t="n">
         <v>79.55999755859375</v>
@@ -22158,7 +22158,7 @@
         <v>17.02000045776367</v>
       </c>
       <c r="E717" t="n">
-        <v>327.6206359863281</v>
+        <v>327.6206665039062</v>
       </c>
       <c r="F717" t="n">
         <v>79.70999908447266</v>
@@ -22222,7 +22222,7 @@
         <v>17.28000068664551</v>
       </c>
       <c r="E719" t="n">
-        <v>327.0727844238281</v>
+        <v>327.0728149414062</v>
       </c>
       <c r="F719" t="n">
         <v>78.83999633789062</v>
@@ -22286,7 +22286,7 @@
         <v>17.86000061035156</v>
       </c>
       <c r="E721" t="n">
-        <v>339.026123046875</v>
+        <v>339.0261535644531</v>
       </c>
       <c r="F721" t="n">
         <v>79.80999755859375</v>
@@ -22350,7 +22350,7 @@
         <v>17.93000030517578</v>
       </c>
       <c r="E723" t="n">
-        <v>340.171630859375</v>
+        <v>340.1716613769531</v>
       </c>
       <c r="F723" t="n">
         <v>79.20999908447266</v>
@@ -22382,7 +22382,7 @@
         <v>18.06999969482422</v>
       </c>
       <c r="E724" t="n">
-        <v>337.5817565917969</v>
+        <v>337.581787109375</v>
       </c>
       <c r="F724" t="n">
         <v>79.58999633789062</v>
@@ -22574,7 +22574,7 @@
         <v>17.80999946594238</v>
       </c>
       <c r="E730" t="n">
-        <v>339.026123046875</v>
+        <v>339.0261535644531</v>
       </c>
       <c r="F730" t="n">
         <v>74.36000061035156</v>
@@ -22606,7 +22606,7 @@
         <v>17.55999946594238</v>
       </c>
       <c r="E731" t="n">
-        <v>335.7887878417969</v>
+        <v>335.7887573242188</v>
       </c>
       <c r="F731" t="n">
         <v>73.54000091552734</v>
@@ -22638,7 +22638,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="E732" t="n">
-        <v>323.33740234375</v>
+        <v>323.3373718261719</v>
       </c>
       <c r="F732" t="n">
         <v>72.55999755859375</v>
@@ -22670,7 +22670,7 @@
         <v>17.13999938964844</v>
       </c>
       <c r="E733" t="n">
-        <v>311.7825012207031</v>
+        <v>311.7825317382812</v>
       </c>
       <c r="F733" t="n">
         <v>70.18000030517578</v>
@@ -22702,7 +22702,7 @@
         <v>16.61000061035156</v>
       </c>
       <c r="E734" t="n">
-        <v>303.1163330078125</v>
+        <v>303.1163635253906</v>
       </c>
       <c r="F734" t="n">
         <v>74.33999633789062</v>
@@ -22830,7 +22830,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="E738" t="n">
-        <v>303.7638244628906</v>
+        <v>303.7638549804688</v>
       </c>
       <c r="F738" t="n">
         <v>73.19000244140625</v>
@@ -22862,7 +22862,7 @@
         <v>15.19999980926514</v>
       </c>
       <c r="E739" t="n">
-        <v>305.0587768554688</v>
+        <v>305.0587463378906</v>
       </c>
       <c r="F739" t="n">
         <v>70.33999633789062</v>
@@ -22990,7 +22990,7 @@
         <v>16.32999992370605</v>
       </c>
       <c r="E743" t="n">
-        <v>306.2541198730469</v>
+        <v>306.2540893554688</v>
       </c>
       <c r="F743" t="n">
         <v>72.80000305175781</v>
@@ -23022,7 +23022,7 @@
         <v>15.73999977111816</v>
       </c>
       <c r="E744" t="n">
-        <v>295.5459289550781</v>
+        <v>295.5458984375</v>
       </c>
       <c r="F744" t="n">
         <v>68.94999694824219</v>
@@ -23118,7 +23118,7 @@
         <v>15.77999973297119</v>
       </c>
       <c r="E747" t="n">
-        <v>288.1248779296875</v>
+        <v>288.1249084472656</v>
       </c>
       <c r="F747" t="n">
         <v>66.61000061035156</v>
@@ -23182,7 +23182,7 @@
         <v>14.53999996185303</v>
       </c>
       <c r="E749" t="n">
-        <v>265.11474609375</v>
+        <v>265.1147155761719</v>
       </c>
       <c r="F749" t="n">
         <v>59.84000015258789</v>
@@ -23214,7 +23214,7 @@
         <v>15.23999977111816</v>
       </c>
       <c r="E750" t="n">
-        <v>271.7886962890625</v>
+        <v>271.7886657714844</v>
       </c>
       <c r="F750" t="n">
         <v>61.43999862670898</v>
@@ -23502,7 +23502,7 @@
         <v>14.88000011444092</v>
       </c>
       <c r="E759" t="n">
-        <v>232.3925170898438</v>
+        <v>232.3925323486328</v>
       </c>
       <c r="F759" t="n">
         <v>50.02999877929688</v>
@@ -23534,7 +23534,7 @@
         <v>14.77999973297119</v>
       </c>
       <c r="E760" t="n">
-        <v>232.4921264648438</v>
+        <v>232.4921417236328</v>
       </c>
       <c r="F760" t="n">
         <v>49.66999816894531</v>
@@ -23662,7 +23662,7 @@
         <v>15.10999965667725</v>
       </c>
       <c r="E764" t="n">
-        <v>240.5705718994141</v>
+        <v>240.5705871582031</v>
       </c>
       <c r="F764" t="n">
         <v>52.81999969482422</v>
@@ -23726,7 +23726,7 @@
         <v>14.75</v>
       </c>
       <c r="E766" t="n">
-        <v>244.1466217041016</v>
+        <v>244.1466369628906</v>
       </c>
       <c r="F766" t="n">
         <v>51.83000183105469</v>
@@ -23758,7 +23758,7 @@
         <v>14.84000015258789</v>
       </c>
       <c r="E767" t="n">
-        <v>248.8482818603516</v>
+        <v>248.8482666015625</v>
       </c>
       <c r="F767" t="n">
         <v>53.2599983215332</v>
@@ -23822,7 +23822,7 @@
         <v>14.69999980926514</v>
       </c>
       <c r="E769" t="n">
-        <v>248.4796905517578</v>
+        <v>248.4797058105469</v>
       </c>
       <c r="F769" t="n">
         <v>51.79000091552734</v>
@@ -23854,7 +23854,7 @@
         <v>14.82999992370605</v>
       </c>
       <c r="E770" t="n">
-        <v>242.0149688720703</v>
+        <v>242.0149536132812</v>
       </c>
       <c r="F770" t="n">
         <v>50.41999816894531</v>
@@ -23950,7 +23950,7 @@
         <v>14.34000015258789</v>
       </c>
       <c r="E773" t="n">
-        <v>227.1729125976562</v>
+        <v>227.1728973388672</v>
       </c>
       <c r="F773" t="n">
         <v>49.22999954223633</v>
@@ -24078,7 +24078,7 @@
         <v>14.14000034332275</v>
       </c>
       <c r="E777" t="n">
-        <v>228.0295562744141</v>
+        <v>228.0295715332031</v>
       </c>
       <c r="F777" t="n">
         <v>46.93000030517578</v>
@@ -24270,7 +24270,7 @@
         <v>13.22000026702881</v>
       </c>
       <c r="E783" t="n">
-        <v>206.8024444580078</v>
+        <v>206.8024597167969</v>
       </c>
       <c r="F783" t="n">
         <v>41.31999969482422</v>
@@ -24398,7 +24398,7 @@
         <v>13.89999961853027</v>
       </c>
       <c r="E787" t="n">
-        <v>219.0844879150391</v>
+        <v>219.0845031738281</v>
       </c>
       <c r="F787" t="n">
         <v>44.04999923706055</v>
@@ -24430,7 +24430,7 @@
         <v>14.17000007629395</v>
       </c>
       <c r="E788" t="n">
-        <v>220.9472198486328</v>
+        <v>220.9472045898438</v>
       </c>
       <c r="F788" t="n">
         <v>45.45000076293945</v>
@@ -24526,7 +24526,7 @@
         <v>13.38000011444092</v>
       </c>
       <c r="E791" t="n">
-        <v>224.6527404785156</v>
+        <v>224.6527557373047</v>
       </c>
       <c r="F791" t="n">
         <v>41.93000030517578</v>
@@ -24590,7 +24590,7 @@
         <v>13.01000022888184</v>
       </c>
       <c r="E793" t="n">
-        <v>218.6661224365234</v>
+        <v>218.6661376953125</v>
       </c>
       <c r="F793" t="n">
         <v>40.52999877929688</v>
@@ -24622,7 +24622,7 @@
         <v>13.01000022888184</v>
       </c>
       <c r="E794" t="n">
-        <v>218.6661224365234</v>
+        <v>218.6661376953125</v>
       </c>
       <c r="F794" t="n">
         <v>40.52999877929688</v>
@@ -24654,7 +24654,7 @@
         <v>13.55000019073486</v>
       </c>
       <c r="E795" t="n">
-        <v>227.9498596191406</v>
+        <v>227.9498748779297</v>
       </c>
       <c r="F795" t="n">
         <v>43.86999893188477</v>
@@ -24718,7 +24718,7 @@
         <v>13.71000003814697</v>
       </c>
       <c r="E797" t="n">
-        <v>228.2287902832031</v>
+        <v>228.2287750244141</v>
       </c>
       <c r="F797" t="n">
         <v>47.43999862670898</v>
@@ -24750,7 +24750,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="E798" t="n">
-        <v>231.7749176025391</v>
+        <v>231.7749328613281</v>
       </c>
       <c r="F798" t="n">
         <v>47.4900016784668</v>
@@ -24782,7 +24782,7 @@
         <v>13.32999992370605</v>
       </c>
       <c r="E799" t="n">
-        <v>226.6449737548828</v>
+        <v>226.6449584960938</v>
       </c>
       <c r="F799" t="n">
         <v>45.36000061035156</v>
@@ -24846,7 +24846,7 @@
         <v>13.07999992370605</v>
       </c>
       <c r="E801" t="n">
-        <v>224.9017791748047</v>
+        <v>224.9017639160156</v>
       </c>
       <c r="F801" t="n">
         <v>44.95999908447266</v>
@@ -24878,7 +24878,7 @@
         <v>13</v>
       </c>
       <c r="E802" t="n">
-        <v>226.6250457763672</v>
+        <v>226.6250305175781</v>
       </c>
       <c r="F802" t="n">
         <v>43.40999984741211</v>
@@ -25038,7 +25038,7 @@
         <v>12.46000003814697</v>
       </c>
       <c r="E807" t="n">
-        <v>212.689453125</v>
+        <v>212.6894683837891</v>
       </c>
       <c r="F807" t="n">
         <v>41.22999954223633</v>
@@ -25070,7 +25070,7 @@
         <v>12.98999977111816</v>
       </c>
       <c r="E808" t="n">
-        <v>223.9355316162109</v>
+        <v>223.935546875</v>
       </c>
       <c r="F808" t="n">
         <v>41.70999908447266</v>
@@ -25262,7 +25262,7 @@
         <v>14.10999965667725</v>
       </c>
       <c r="E814" t="n">
-        <v>245.4216613769531</v>
+        <v>245.4216461181641</v>
       </c>
       <c r="F814" t="n">
         <v>45.11000061035156</v>
@@ -25326,7 +25326,7 @@
         <v>14.72999954223633</v>
       </c>
       <c r="E816" t="n">
-        <v>257.1358947753906</v>
+        <v>257.1359252929688</v>
       </c>
       <c r="F816" t="n">
         <v>45.86999893188477</v>
@@ -25422,7 +25422,7 @@
         <v>14.02000045776367</v>
       </c>
       <c r="E819" t="n">
-        <v>256.8968505859375</v>
+        <v>256.8968200683594</v>
       </c>
       <c r="F819" t="n">
         <v>43.45000076293945</v>
@@ -25454,7 +25454,7 @@
         <v>13.90999984741211</v>
       </c>
       <c r="E820" t="n">
-        <v>256.6278686523438</v>
+        <v>256.6278991699219</v>
       </c>
       <c r="F820" t="n">
         <v>45.27000045776367</v>
@@ -25678,7 +25678,7 @@
         <v>13.15999984741211</v>
       </c>
       <c r="E827" t="n">
-        <v>247.3840026855469</v>
+        <v>247.3839874267578</v>
       </c>
       <c r="F827" t="n">
         <v>42.4900016784668</v>
@@ -25902,7 +25902,7 @@
         <v>15.01000022888184</v>
       </c>
       <c r="E834" t="n">
-        <v>270.3941345214844</v>
+        <v>270.3941650390625</v>
       </c>
       <c r="F834" t="n">
         <v>46.61999893188477</v>
@@ -25934,7 +25934,7 @@
         <v>15.14999961853027</v>
       </c>
       <c r="E835" t="n">
-        <v>273.2828369140625</v>
+        <v>273.2828674316406</v>
       </c>
       <c r="F835" t="n">
         <v>46.68999862670898</v>
@@ -25998,7 +25998,7 @@
         <v>15.3100004196167</v>
       </c>
       <c r="E837" t="n">
-        <v>280.6540832519531</v>
+        <v>280.654052734375</v>
       </c>
       <c r="F837" t="n">
         <v>48.81999969482422</v>
@@ -26030,7 +26030,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="E838" t="n">
-        <v>280.6540832519531</v>
+        <v>280.654052734375</v>
       </c>
       <c r="F838" t="n">
         <v>50.0099983215332</v>
@@ -26094,7 +26094,7 @@
         <v>15.52000045776367</v>
       </c>
       <c r="E840" t="n">
-        <v>289.2206115722656</v>
+        <v>289.2206420898438</v>
       </c>
       <c r="F840" t="n">
         <v>52.68999862670898</v>
@@ -26254,7 +26254,7 @@
         <v>15.72999954223633</v>
       </c>
       <c r="E845" t="n">
-        <v>289.2206115722656</v>
+        <v>289.2206420898438</v>
       </c>
       <c r="F845" t="n">
         <v>55.31999969482422</v>
@@ -26286,7 +26286,7 @@
         <v>15.75</v>
       </c>
       <c r="E846" t="n">
-        <v>290.3661193847656</v>
+        <v>290.3661499023438</v>
       </c>
       <c r="F846" t="n">
         <v>54.68999862670898</v>
@@ -26350,7 +26350,7 @@
         <v>15.80000019073486</v>
       </c>
       <c r="E848" t="n">
-        <v>303.0665588378906</v>
+        <v>303.0665283203125</v>
       </c>
       <c r="F848" t="n">
         <v>54.47999954223633</v>
@@ -26382,7 +26382,7 @@
         <v>15.98999977111816</v>
       </c>
       <c r="E849" t="n">
-        <v>301.6221923828125</v>
+        <v>301.6221618652344</v>
       </c>
       <c r="F849" t="n">
         <v>57.08000183105469</v>
@@ -26542,7 +26542,7 @@
         <v>15.03999996185303</v>
       </c>
       <c r="E854" t="n">
-        <v>288.6727294921875</v>
+        <v>288.6727600097656</v>
       </c>
       <c r="F854" t="n">
         <v>53.13999938964844</v>
@@ -26574,7 +26574,7 @@
         <v>14.89000034332275</v>
       </c>
       <c r="E855" t="n">
-        <v>287.0291442871094</v>
+        <v>287.0291748046875</v>
       </c>
       <c r="F855" t="n">
         <v>52.86999893188477</v>
@@ -26702,7 +26702,7 @@
         <v>15.15999984741211</v>
       </c>
       <c r="E859" t="n">
-        <v>299.6299438476562</v>
+        <v>299.6299743652344</v>
       </c>
       <c r="F859" t="n">
         <v>53.65999984741211</v>
@@ -26734,7 +26734,7 @@
         <v>16.04999923706055</v>
       </c>
       <c r="E860" t="n">
-        <v>302.1202087402344</v>
+        <v>302.1202392578125</v>
       </c>
       <c r="F860" t="n">
         <v>61.81999969482422</v>
@@ -26894,7 +26894,7 @@
         <v>15.85999965667725</v>
       </c>
       <c r="E865" t="n">
-        <v>325.4292602539062</v>
+        <v>325.4292297363281</v>
       </c>
       <c r="F865" t="n">
         <v>57.02000045776367</v>
@@ -26926,7 +26926,7 @@
         <v>15.96000003814697</v>
       </c>
       <c r="E866" t="n">
-        <v>323.78564453125</v>
+        <v>323.7856140136719</v>
       </c>
       <c r="F866" t="n">
         <v>58.11000061035156</v>
@@ -26958,7 +26958,7 @@
         <v>15.98999977111816</v>
       </c>
       <c r="E867" t="n">
-        <v>323.68603515625</v>
+        <v>323.6860656738281</v>
       </c>
       <c r="F867" t="n">
         <v>56.41999816894531</v>
@@ -27086,7 +27086,7 @@
         <v>15.57999992370605</v>
       </c>
       <c r="E871" t="n">
-        <v>330.3599548339844</v>
+        <v>330.3599853515625</v>
       </c>
       <c r="F871" t="n">
         <v>55.68000030517578</v>
@@ -27118,7 +27118,7 @@
         <v>15.35999965667725</v>
       </c>
       <c r="E872" t="n">
-        <v>324.5326843261719</v>
+        <v>324.53271484375</v>
       </c>
       <c r="F872" t="n">
         <v>54.81000137329102</v>
@@ -27310,7 +27310,7 @@
         <v>15.86999988555908</v>
       </c>
       <c r="E878" t="n">
-        <v>316.0159912109375</v>
+        <v>316.0159606933594</v>
       </c>
       <c r="F878" t="n">
         <v>59.61000061035156</v>
@@ -27470,7 +27470,7 @@
         <v>14.85999965667725</v>
       </c>
       <c r="E883" t="n">
-        <v>306.1545104980469</v>
+        <v>306.1544799804688</v>
       </c>
       <c r="F883" t="n">
         <v>56.25</v>
@@ -27598,7 +27598,7 @@
         <v>15.10000038146973</v>
       </c>
       <c r="E887" t="n">
-        <v>328.2183532714844</v>
+        <v>328.2183227539062</v>
       </c>
       <c r="F887" t="n">
         <v>57.47000122070312</v>
@@ -27726,7 +27726,7 @@
         <v>14.31999969482422</v>
       </c>
       <c r="E891" t="n">
-        <v>324.23388671875</v>
+        <v>324.2339172363281</v>
       </c>
       <c r="F891" t="n">
         <v>56.29000091552734</v>
@@ -37264,7 +37264,7 @@
         <v>3.846153846153855</v>
       </c>
       <c r="E19" t="n">
-        <v>14.46530217715354</v>
+        <v>14.46530988416585</v>
       </c>
       <c r="F19" t="n">
         <v>0.2994726297447459</v>
@@ -37296,7 +37296,7 @@
         <v>-1.664147220764423</v>
       </c>
       <c r="E20" t="n">
-        <v>9.585283854023508</v>
+        <v>9.585268389905522</v>
       </c>
       <c r="F20" t="n">
         <v>5.058083659302848</v>
@@ -37328,7 +37328,7 @@
         <v>-12.04257816433491</v>
       </c>
       <c r="E21" t="n">
-        <v>-14.08648894056502</v>
+        <v>-14.08648260149032</v>
       </c>
       <c r="F21" t="n">
         <v>-21.56416200558649</v>
@@ -37392,7 +37392,7 @@
         <v>-8.96991367371337</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.02998930442963</v>
+        <v>-9.029997792400145</v>
       </c>
       <c r="F23" t="n">
         <v>-9.284627137033763</v>
@@ -37424,7 +37424,7 @@
         <v>-10.92782976067592</v>
       </c>
       <c r="E24" t="n">
-        <v>1.877130575284558</v>
+        <v>1.877140080946416</v>
       </c>
       <c r="F24" t="n">
         <v>-8.750005850085408</v>
@@ -37488,7 +37488,7 @@
         <v>-2.652777627189706</v>
       </c>
       <c r="E26" t="n">
-        <v>8.983518155342285</v>
+        <v>8.983528534268292</v>
       </c>
       <c r="F26" t="n">
         <v>-13.86086794220902</v>
@@ -37520,7 +37520,7 @@
         <v>-12.37027614512571</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.070008835693593</v>
+        <v>-2.070018161948173</v>
       </c>
       <c r="F27" t="n">
         <v>-3.095716273530114</v>
@@ -37596,7 +37596,7 @@
         <v>20.18634526010754</v>
       </c>
       <c r="I29" t="n">
-        <v>14.89904258694705</v>
+        <v>14.89905459147085</v>
       </c>
       <c r="J29" t="n">
         <v>17.84114543475508</v>
@@ -37628,7 +37628,7 @@
         <v>-6.49240482812462</v>
       </c>
       <c r="I30" t="n">
-        <v>-10.79030161697194</v>
+        <v>-10.79031093750072</v>
       </c>
       <c r="J30" t="n">
         <v>-10.07326035477244</v>
@@ -37660,7 +37660,7 @@
         <v>-34.34213475489638</v>
       </c>
       <c r="I31" t="n">
-        <v>3.869231128923167</v>
+        <v>3.869221073176021</v>
       </c>
       <c r="J31" t="n">
         <v>-3.36283455907771</v>
@@ -37692,7 +37692,7 @@
         <v>22.65731991554547</v>
       </c>
       <c r="I32" t="n">
-        <v>-10.22068611256335</v>
+        <v>-10.22067742088289</v>
       </c>
       <c r="J32" t="n">
         <v>16.73553350982875</v>
@@ -37744,7 +37744,7 @@
         <v>12.97169764638586</v>
       </c>
       <c r="E34" t="n">
-        <v>6.567935984125439</v>
+        <v>6.56794299184198</v>
       </c>
       <c r="F34" t="n">
         <v>33.94390617495342</v>
@@ -37776,7 +37776,7 @@
         <v>5.735668676501682</v>
       </c>
       <c r="E35" t="n">
-        <v>1.547516340043864</v>
+        <v>1.547509662461577</v>
       </c>
       <c r="F35" t="n">
         <v>0.9243158800178009</v>
@@ -37788,7 +37788,7 @@
         <v>10.5665365226655</v>
       </c>
       <c r="I35" t="n">
-        <v>23.11872529727841</v>
+        <v>23.11871141371891</v>
       </c>
       <c r="J35" t="n">
         <v>10.16548301327902</v>
@@ -37820,7 +37820,7 @@
         <v>12.11225997045791</v>
       </c>
       <c r="I36" t="n">
-        <v>8.906449900509328</v>
+        <v>8.906468868764028</v>
       </c>
       <c r="J36" t="n">
         <v>23.68420553633026</v>
@@ -37852,7 +37852,7 @@
         <v>-2.336989602099571</v>
       </c>
       <c r="I37" t="n">
-        <v>4.51120543209822</v>
+        <v>4.51119901463739</v>
       </c>
       <c r="J37" t="n">
         <v>-11.16882918717025</v>
@@ -37872,7 +37872,7 @@
         <v>21.21212121212121</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9850140387806072</v>
+        <v>-0.9850075430692273</v>
       </c>
       <c r="F38" t="n">
         <v>-6.583760205501399</v>
@@ -37884,7 +37884,7 @@
         <v>-7.202140266796353</v>
       </c>
       <c r="I38" t="n">
-        <v>-5.426390322743146</v>
+        <v>-5.426396062627347</v>
       </c>
       <c r="J38" t="n">
         <v>0.5221952138994457</v>
@@ -37913,7 +37913,7 @@
         <v>-1.111996841749918</v>
       </c>
       <c r="I39" t="n">
-        <v>4.903569221099491</v>
+        <v>4.90358226696832</v>
       </c>
       <c r="J39" t="n">
         <v>16.41336614204727</v>
@@ -37936,13 +37936,13 @@
         <v>-7.245221803084723</v>
       </c>
       <c r="G40" t="n">
-        <v>8.299913357895106</v>
+        <v>8.299924766203226</v>
       </c>
       <c r="H40" t="n">
         <v>36.60036607849231</v>
       </c>
       <c r="I40" t="n">
-        <v>1.693675629957525</v>
+        <v>1.693669155291055</v>
       </c>
       <c r="J40" t="n">
         <v>17.08185437454475</v>
@@ -37965,13 +37965,13 @@
         <v>2.446982085920046</v>
       </c>
       <c r="G41" t="n">
-        <v>3.253172538244864</v>
+        <v>3.253161661561332</v>
       </c>
       <c r="H41" t="n">
         <v>2.635488591081314</v>
       </c>
       <c r="I41" t="n">
-        <v>5.350320191814273</v>
+        <v>5.350313005783192</v>
       </c>
       <c r="J41" t="n">
         <v>8.494211565028188</v>
@@ -37994,13 +37994,13 @@
         <v>5.598621951273208</v>
       </c>
       <c r="G42" t="n">
-        <v>2.040900359286013</v>
+        <v>2.040911684465785</v>
       </c>
       <c r="H42" t="n">
         <v>-14.50333586855534</v>
       </c>
       <c r="I42" t="n">
-        <v>7.789051998159846</v>
+        <v>7.789059350539329</v>
       </c>
       <c r="J42" t="n">
         <v>6.147541079717245</v>
@@ -38023,13 +38023,13 @@
         <v>7.004606888590881</v>
       </c>
       <c r="G43" t="n">
-        <v>3.837320273090516</v>
+        <v>3.837308748533363</v>
       </c>
       <c r="H43" t="n">
         <v>9.220106101738512</v>
       </c>
       <c r="I43" t="n">
-        <v>7.802001872916686</v>
+        <v>7.802010417317251</v>
       </c>
       <c r="J43" t="n">
         <v>22.61306576011055</v>
@@ -38058,7 +38058,7 @@
         <v>10.36725582872331</v>
       </c>
       <c r="I44" t="n">
-        <v>-2.506398442968916</v>
+        <v>-2.506406170323727</v>
       </c>
       <c r="J44" t="n">
         <v>1.53060832255989</v>
@@ -38081,13 +38081,13 @@
         <v>-5.117786759101961</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.329720456261541</v>
+        <v>-1.329742978595971</v>
       </c>
       <c r="H45" t="n">
         <v>4.476417699780821</v>
       </c>
       <c r="I45" t="n">
-        <v>-7.821829485785403</v>
+        <v>-7.82183605157546</v>
       </c>
       <c r="J45" t="n">
         <v>-23.13725340600107</v>
@@ -38110,13 +38110,13 @@
         <v>-6.883508838267105</v>
       </c>
       <c r="G46" t="n">
-        <v>-7.590690296697222</v>
+        <v>-7.590669203477852</v>
       </c>
       <c r="H46" t="n">
         <v>-9.150325892060184</v>
       </c>
       <c r="I46" t="n">
-        <v>-7.873144999173832</v>
+        <v>-7.873138437038474</v>
       </c>
       <c r="J46" t="n">
         <v>-11.14982814589901</v>
@@ -38145,7 +38145,7 @@
         <v>-12.68230842551258</v>
       </c>
       <c r="I47" t="n">
-        <v>-10.50510455831967</v>
+        <v>-10.50511506998821</v>
       </c>
       <c r="J47" t="n">
         <v>-10.59189368473866</v>
@@ -38168,13 +38168,13 @@
         <v>6.079503403138031</v>
       </c>
       <c r="G48" t="n">
-        <v>7.128570156643566</v>
+        <v>7.128558868849533</v>
       </c>
       <c r="H48" t="n">
         <v>11.48815860769938</v>
       </c>
       <c r="I48" t="n">
-        <v>-3.906760722347635</v>
+        <v>-3.906749435665913</v>
       </c>
       <c r="J48" t="n">
         <v>-0.3105661069842447</v>
@@ -38197,7 +38197,7 @@
         <v>-0.696589719615015</v>
       </c>
       <c r="G49" t="n">
-        <v>7.227420215142799</v>
+        <v>7.227431513353522</v>
       </c>
       <c r="H49" t="n">
         <v>3.474762330681291</v>
@@ -38226,13 +38226,13 @@
         <v>-8.498583753085121</v>
       </c>
       <c r="G50" t="n">
-        <v>-9.863720565037227</v>
+        <v>-9.863711385749763</v>
       </c>
       <c r="H50" t="n">
         <v>-15.6172858344184</v>
       </c>
       <c r="I50" t="n">
-        <v>5.378679965973343</v>
+        <v>5.378692749161718</v>
       </c>
       <c r="J50" t="n">
         <v>-2.380950218425493</v>
@@ -38255,13 +38255,13 @@
         <v>8.782737772308536</v>
       </c>
       <c r="G51" t="n">
-        <v>5.463620720061013</v>
+        <v>5.463621306864352</v>
       </c>
       <c r="H51" t="n">
         <v>38.34329813061588</v>
       </c>
       <c r="I51" t="n">
-        <v>4.312865298202651</v>
+        <v>4.312846044487295</v>
       </c>
       <c r="J51" t="n">
         <v>35.48386898298783</v>
@@ -38284,13 +38284,13 @@
         <v>-5.942026774088538</v>
       </c>
       <c r="G52" t="n">
-        <v>-3.32094891612208</v>
+        <v>-3.32094926095331</v>
       </c>
       <c r="H52" t="n">
         <v>29.24944861623748</v>
       </c>
       <c r="I52" t="n">
-        <v>3.064802510321041</v>
+        <v>3.064809031177451</v>
       </c>
       <c r="J52" t="n">
         <v>7.826083639393677</v>
@@ -38313,13 +38313,13 @@
         <v>-8.609271523178808</v>
       </c>
       <c r="G53" t="n">
-        <v>-1.405405239390534</v>
+        <v>-1.405425570676122</v>
       </c>
       <c r="H53" t="n">
         <v>-16.0722547147822</v>
       </c>
       <c r="I53" t="n">
-        <v>2.955485477722197</v>
+        <v>2.955478565724423</v>
       </c>
       <c r="J53" t="n">
         <v>-8.730161493387333</v>
@@ -38342,13 +38342,13 @@
         <v>-12.41298993858072</v>
       </c>
       <c r="G54" t="n">
-        <v>-5.648241217679606</v>
+        <v>-5.648240672096827</v>
       </c>
       <c r="H54" t="n">
         <v>-12.62647164563844</v>
       </c>
       <c r="I54" t="n">
-        <v>-16.35936670868768</v>
+        <v>-16.35936109340738</v>
       </c>
       <c r="J54" t="n">
         <v>-11.57894469144052</v>
@@ -38371,7 +38371,7 @@
         <v>1.233112628945943</v>
       </c>
       <c r="G55" t="n">
-        <v>5.901886326145522</v>
+        <v>5.901896555568986</v>
       </c>
       <c r="H55" t="n">
         <v>10.01780916676824</v>
@@ -38406,7 +38406,7 @@
         <v>7.361381156751889</v>
       </c>
       <c r="I56" t="n">
-        <v>11.44042835922838</v>
+        <v>11.44043827261805</v>
       </c>
       <c r="J56" t="n">
         <v>3.4482743501002</v>
@@ -38429,13 +38429,13 @@
         <v>-6.15854030702172</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.133426034140439</v>
+        <v>-1.133437199181664</v>
       </c>
       <c r="H57" t="n">
         <v>3.513107684464867</v>
       </c>
       <c r="I57" t="n">
-        <v>-20.63636310365917</v>
+        <v>-20.63637016359784</v>
       </c>
       <c r="J57" t="n">
         <v>-11.82432417193846</v>
@@ -38698,7 +38698,7 @@
         <v>22.99999823937049</v>
       </c>
       <c r="E7" t="n">
-        <v>43.62006339979285</v>
+        <v>43.62007306981142</v>
       </c>
       <c r="F7" t="n">
         <v>35.63695294881548</v>
@@ -38730,7 +38730,7 @@
         <v>-17.35536949575909</v>
       </c>
       <c r="E8" t="n">
-        <v>-23.83328051135775</v>
+        <v>-23.83328563970489</v>
       </c>
       <c r="F8" t="n">
         <v>-39.30368863961553</v>
@@ -38838,7 +38838,7 @@
         <v>-26.21148416003172</v>
       </c>
       <c r="I11" t="n">
-        <v>6.467093392907319</v>
+        <v>6.467083085656977</v>
       </c>
       <c r="J11" t="n">
         <v>2.407080726285948</v>
@@ -38858,7 +38858,7 @@
         <v>-7.547171339100844</v>
       </c>
       <c r="E12" t="n">
-        <v>51.85663028133727</v>
+        <v>51.8566402671572</v>
       </c>
       <c r="F12" t="n">
         <v>-1.316544414387844</v>
@@ -38870,7 +38870,7 @@
         <v>29.14681042220371</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.392583164828846</v>
+        <v>-5.392574005731943</v>
       </c>
       <c r="J12" t="n">
         <v>21.24463916318964</v>
@@ -38890,7 +38890,7 @@
         <v>6.000003814697275</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7569211287945299</v>
+        <v>0.7569145032003677</v>
       </c>
       <c r="F13" t="n">
         <v>36.80501262584171</v>
@@ -38925,7 +38925,7 @@
         <v>1.671973327733589</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.02533425681351398</v>
+        <v>-0.02532372548660344</v>
       </c>
       <c r="H14" t="n">
         <v>25.35262426890257</v>
@@ -38954,13 +38954,13 @@
         <v>15.76036725725447</v>
       </c>
       <c r="G15" t="n">
-        <v>9.403485464018434</v>
+        <v>9.403473939461261</v>
       </c>
       <c r="H15" t="n">
         <v>-4.159445407279028</v>
       </c>
       <c r="I15" t="n">
-        <v>22.41576135094123</v>
+        <v>22.41577105363026</v>
       </c>
       <c r="J15" t="n">
         <v>41.20603477451257</v>
@@ -38989,7 +38989,7 @@
         <v>4.756719823472322</v>
       </c>
       <c r="I16" t="n">
-        <v>-17.2076053573798</v>
+        <v>-17.20761191951514</v>
       </c>
       <c r="J16" t="n">
         <v>-30.66202407831533</v>
@@ -39041,7 +39041,7 @@
         <v>-6.376813805621606</v>
       </c>
       <c r="G18" t="n">
-        <v>-8.095942839170478</v>
+        <v>-8.095933296298796</v>
       </c>
       <c r="H18" t="n">
         <v>50.88300138028043</v>
@@ -39070,7 +39070,7 @@
         <v>-18.96653110566366</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.483992691281522</v>
+        <v>-1.484002920704985</v>
       </c>
       <c r="H19" t="n">
         <v>-19.32324486904549</v>
@@ -39179,7 +39179,7 @@
         <v>24.71641426655784</v>
       </c>
       <c r="E2" t="n">
-        <v>38.56971060642054</v>
+        <v>38.56970207824606</v>
       </c>
       <c r="F2" t="n">
         <v>48.02197768635678</v>
@@ -39211,7 +39211,7 @@
         <v>21.52941086713005</v>
       </c>
       <c r="E3" t="n">
-        <v>48.10742776232155</v>
+        <v>48.10741480535528</v>
       </c>
       <c r="F3" t="n">
         <v>37.25662738916504</v>
@@ -39243,7 +39243,7 @@
         <v>21.30177788597374</v>
       </c>
       <c r="E4" t="n">
-        <v>54.55154123022257</v>
+        <v>54.55153813119511</v>
       </c>
       <c r="F4" t="n">
         <v>35.23950508448274</v>
@@ -39275,7 +39275,7 @@
         <v>25.38921902642992</v>
       </c>
       <c r="E5" t="n">
-        <v>61.79433305581566</v>
+        <v>61.79434466708855</v>
       </c>
       <c r="F5" t="n">
         <v>37.43092805121666</v>
@@ -39307,7 +39307,7 @@
         <v>23.483483105072</v>
       </c>
       <c r="E6" t="n">
-        <v>57.03963895200328</v>
+        <v>57.03962773712359</v>
       </c>
       <c r="F6" t="n">
         <v>32.87407769097221</v>
@@ -39351,7 +39351,7 @@
         <v>19.02754764747889</v>
       </c>
       <c r="I7" t="n">
-        <v>14.23300996545445</v>
+        <v>14.23300300571448</v>
       </c>
       <c r="J7" t="n">
         <v>70.31517486505918</v>
@@ -39371,7 +39371,7 @@
         <v>28.34835632939052</v>
       </c>
       <c r="E8" t="n">
-        <v>59.59136353965761</v>
+        <v>59.59137463922708</v>
       </c>
       <c r="F8" t="n">
         <v>30.24495302920487</v>
@@ -39383,7 +39383,7 @@
         <v>17.59891665078761</v>
       </c>
       <c r="I8" t="n">
-        <v>16.76870935549983</v>
+        <v>16.76871654600964</v>
       </c>
       <c r="J8" t="n">
         <v>64.5479489679206</v>
@@ -39435,7 +39435,7 @@
         <v>27.15151237718987</v>
       </c>
       <c r="E10" t="n">
-        <v>49.80727387211014</v>
+        <v>49.80728369996403</v>
       </c>
       <c r="F10" t="n">
         <v>30.0219527879438</v>
@@ -39447,7 +39447,7 @@
         <v>14.29718712087935</v>
       </c>
       <c r="I10" t="n">
-        <v>15.13143815733493</v>
+        <v>15.13143116975007</v>
       </c>
       <c r="J10" t="n">
         <v>54.93472933327954</v>
@@ -39499,7 +39499,7 @@
         <v>17.83197220667512</v>
       </c>
       <c r="E12" t="n">
-        <v>37.62082597735093</v>
+        <v>37.62083806523711</v>
       </c>
       <c r="F12" t="n">
         <v>29.44169870113738</v>
@@ -39511,7 +39511,7 @@
         <v>12.00104193248259</v>
       </c>
       <c r="I12" t="n">
-        <v>16.53926699663837</v>
+        <v>16.53925992256591</v>
       </c>
       <c r="J12" t="n">
         <v>58.82353170735514</v>
@@ -39543,7 +39543,7 @@
         <v>23.48532329238919</v>
       </c>
       <c r="I13" t="n">
-        <v>16.79518332705205</v>
+        <v>16.79517617557025</v>
       </c>
       <c r="J13" t="n">
         <v>58.58586276992115</v>
@@ -39595,7 +39595,7 @@
         <v>10.24259624810628</v>
       </c>
       <c r="E15" t="n">
-        <v>37.66878574882724</v>
+        <v>37.66877358173188</v>
       </c>
       <c r="F15" t="n">
         <v>18.36042100886153</v>
@@ -39659,7 +39659,7 @@
         <v>11.39784348605077</v>
       </c>
       <c r="E17" t="n">
-        <v>41.61504102066482</v>
+        <v>41.61502010126967</v>
       </c>
       <c r="F17" t="n">
         <v>17.49119689344376</v>
@@ -39671,7 +39671,7 @@
         <v>80.21875186197276</v>
       </c>
       <c r="I17" t="n">
-        <v>38.57649706808945</v>
+        <v>38.57650560107664</v>
       </c>
       <c r="J17" t="n">
         <v>83.413475601984</v>
@@ -39723,7 +39723,7 @@
         <v>18.21325520423087</v>
       </c>
       <c r="E19" t="n">
-        <v>46.8775899976761</v>
+        <v>46.87759936456168</v>
       </c>
       <c r="F19" t="n">
         <v>18.99342970595615</v>
@@ -39735,7 +39735,7 @@
         <v>94.1268552045597</v>
       </c>
       <c r="I19" t="n">
-        <v>32.47950210002233</v>
+        <v>32.47951058552494</v>
       </c>
       <c r="J19" t="n">
         <v>121.3157854582134</v>
@@ -39799,7 +39799,7 @@
         <v>75.75510868409864</v>
       </c>
       <c r="I21" t="n">
-        <v>31.45755074527625</v>
+        <v>31.45755910332362</v>
       </c>
       <c r="J21" t="n">
         <v>142.036550378158</v>
@@ -39883,7 +39883,7 @@
         <v>1.75879592049748</v>
       </c>
       <c r="E24" t="n">
-        <v>51.81199574355784</v>
+        <v>51.81200920138686</v>
       </c>
       <c r="F24" t="n">
         <v>19.30215336975127</v>
@@ -39915,7 +39915,7 @@
         <v>4.647526447655226</v>
       </c>
       <c r="E25" t="n">
-        <v>48.72695435353167</v>
+        <v>48.72694435241242</v>
       </c>
       <c r="F25" t="n">
         <v>15.13592205797443</v>
@@ -39979,7 +39979,7 @@
         <v>-2.630266944568471</v>
       </c>
       <c r="E27" t="n">
-        <v>50.00000332429988</v>
+        <v>50.0000166214994</v>
       </c>
       <c r="F27" t="n">
         <v>17.44186046511629</v>
@@ -40011,7 +40011,7 @@
         <v>0.101012416840085</v>
       </c>
       <c r="E28" t="n">
-        <v>50.86871045504766</v>
+        <v>50.86870028982617</v>
       </c>
       <c r="F28" t="n">
         <v>21.00077612236952</v>
@@ -40055,7 +40055,7 @@
         <v>72.05968302788671</v>
       </c>
       <c r="I29" t="n">
-        <v>23.95292474688</v>
+        <v>23.95293274014536</v>
       </c>
       <c r="J29" t="n">
         <v>143.1331712833967</v>
@@ -40075,7 +40075,7 @@
         <v>0.450000762939462</v>
       </c>
       <c r="E30" t="n">
-        <v>47.70760404866208</v>
+        <v>47.7076172998504</v>
       </c>
       <c r="F30" t="n">
         <v>27.42365317882882</v>
@@ -40107,7 +40107,7 @@
         <v>0.1449216337739756</v>
       </c>
       <c r="E31" t="n">
-        <v>46.95331841391677</v>
+        <v>46.95333165365223</v>
       </c>
       <c r="F31" t="n">
         <v>15.39021874936699</v>
@@ -40139,7 +40139,7 @@
         <v>-1.052628312774884</v>
       </c>
       <c r="E32" t="n">
-        <v>49.89984245224899</v>
+        <v>49.89985267357972</v>
       </c>
       <c r="F32" t="n">
         <v>27.97941577115182</v>
@@ -40171,7 +40171,7 @@
         <v>-2.660330100898289</v>
       </c>
       <c r="E33" t="n">
-        <v>48.02573405358237</v>
+        <v>48.02573758579716</v>
       </c>
       <c r="F33" t="n">
         <v>17.99588316396285</v>
@@ -40183,7 +40183,7 @@
         <v>69.25088116850071</v>
       </c>
       <c r="I33" t="n">
-        <v>25.14076236892711</v>
+        <v>25.14077025349546</v>
       </c>
       <c r="J33" t="n">
         <v>132.4867699130986</v>
@@ -40247,7 +40247,7 @@
         <v>64.23357664233578</v>
       </c>
       <c r="I35" t="n">
-        <v>27.1980016778619</v>
+        <v>27.19799344911933</v>
       </c>
       <c r="J35" t="n">
         <v>137.8151252422787</v>
@@ -40267,7 +40267,7 @@
         <v>-0.4102560190054061</v>
       </c>
       <c r="E36" t="n">
-        <v>48.62593874181287</v>
+        <v>48.62594908343376</v>
       </c>
       <c r="F36" t="n">
         <v>11.65387061590668</v>
@@ -40299,7 +40299,7 @@
         <v>-5.088162264342754</v>
       </c>
       <c r="E37" t="n">
-        <v>39.51576792072717</v>
+        <v>39.51575431044456</v>
       </c>
       <c r="F37" t="n">
         <v>5.373968208882274</v>
@@ -40311,7 +40311,7 @@
         <v>49.29618947317174</v>
       </c>
       <c r="I37" t="n">
-        <v>15.74543228600769</v>
+        <v>15.74542504218792</v>
       </c>
       <c r="J37" t="n">
         <v>111.15383897912</v>
@@ -40331,7 +40331,7 @@
         <v>-9.425834207230599</v>
       </c>
       <c r="E38" t="n">
-        <v>39.77350033524889</v>
+        <v>39.77348672798779</v>
       </c>
       <c r="F38" t="n">
         <v>-1.762887330280316</v>
@@ -40343,7 +40343,7 @@
         <v>57.80926505349091</v>
       </c>
       <c r="I38" t="n">
-        <v>16.21145683918306</v>
+        <v>16.21146407658735</v>
       </c>
       <c r="J38" t="n">
         <v>124.1666581895616</v>
@@ -40363,7 +40363,7 @@
         <v>-7.586202295846512</v>
       </c>
       <c r="E39" t="n">
-        <v>40.77042925623107</v>
+        <v>40.77041965314101</v>
       </c>
       <c r="F39" t="n">
         <v>-0.3809562562003932</v>
@@ -40459,7 +40459,7 @@
         <v>-4.7715761302202</v>
       </c>
       <c r="E42" t="n">
-        <v>51.01853360181148</v>
+        <v>51.01852289181952</v>
       </c>
       <c r="F42" t="n">
         <v>0.8595328089425314</v>
@@ -40491,7 +40491,7 @@
         <v>-3.115572581757442</v>
       </c>
       <c r="E43" t="n">
-        <v>49.36975835587943</v>
+        <v>49.36975473509047</v>
       </c>
       <c r="F43" t="n">
         <v>4.18754296740822</v>
@@ -40523,7 +40523,7 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>50.46684566231154</v>
+        <v>50.46685642285065</v>
       </c>
       <c r="F44" t="n">
         <v>12.49999751647324</v>
@@ -40567,7 +40567,7 @@
         <v>71.45801931839102</v>
       </c>
       <c r="I45" t="n">
-        <v>12.16106151167788</v>
+        <v>12.1610683896405</v>
       </c>
       <c r="J45" t="n">
         <v>157.6646515776742</v>
@@ -40651,7 +40651,7 @@
         <v>6.467394340917232</v>
       </c>
       <c r="E48" t="n">
-        <v>46.2763635483981</v>
+        <v>46.27635349583639</v>
       </c>
       <c r="F48" t="n">
         <v>25.26545854048294</v>
@@ -40683,7 +40683,7 @@
         <v>8.154267621721157</v>
       </c>
       <c r="E49" t="n">
-        <v>46.82647017740005</v>
+        <v>46.82648416678226</v>
       </c>
       <c r="F49" t="n">
         <v>21.11271857609913</v>
@@ -40727,7 +40727,7 @@
         <v>62.06793961179837</v>
       </c>
       <c r="I50" t="n">
-        <v>10.18126922537272</v>
+        <v>10.18127599100154</v>
       </c>
       <c r="J50" t="n">
         <v>143.1579000203562</v>
@@ -40779,7 +40779,7 @@
         <v>3.767314869352423</v>
       </c>
       <c r="E52" t="n">
-        <v>42.7421148615067</v>
+        <v>42.74212492167262</v>
       </c>
       <c r="F52" t="n">
         <v>20.88757849896625</v>
@@ -40811,7 +40811,7 @@
         <v>-0.6521681215901576</v>
       </c>
       <c r="E53" t="n">
-        <v>36.68110950479731</v>
+        <v>36.68112349098636</v>
       </c>
       <c r="F53" t="n">
         <v>9.971790610249332</v>
@@ -40939,7 +40939,7 @@
         <v>-2.895437100396392</v>
       </c>
       <c r="E57" t="n">
-        <v>46.03765664399515</v>
+        <v>46.03767088371107</v>
       </c>
       <c r="F57" t="n">
         <v>17.16470691777749</v>
@@ -40971,7 +40971,7 @@
         <v>-4.116098444549698</v>
       </c>
       <c r="E58" t="n">
-        <v>41.38319910862871</v>
+        <v>41.38318530518315</v>
       </c>
       <c r="F58" t="n">
         <v>2.990288101739491</v>
@@ -41003,7 +41003,7 @@
         <v>-4.293192033753879</v>
       </c>
       <c r="E59" t="n">
-        <v>43.82646747624919</v>
+        <v>43.82647727908604</v>
       </c>
       <c r="F59" t="n">
         <v>5.94736400403475</v>
@@ -41067,7 +41067,7 @@
         <v>-16.15763006192025</v>
       </c>
       <c r="E61" t="n">
-        <v>44.92178179656079</v>
+        <v>44.92179529589908</v>
       </c>
       <c r="F61" t="n">
         <v>-6.880840531123522</v>
@@ -41131,7 +41131,7 @@
         <v>-13.16582403069547</v>
       </c>
       <c r="E63" t="n">
-        <v>52.36658211824747</v>
+        <v>52.36659633483563</v>
       </c>
       <c r="F63" t="n">
         <v>-4.954792961494691</v>
@@ -41143,7 +41143,7 @@
         <v>52.72230156143125</v>
       </c>
       <c r="I63" t="n">
-        <v>5.391828203771198</v>
+        <v>5.391816556919182</v>
       </c>
       <c r="J63" t="n">
         <v>75.11312260151992</v>
@@ -41175,7 +41175,7 @@
         <v>52.6315695544544</v>
       </c>
       <c r="I64" t="n">
-        <v>7.776534256813661</v>
+        <v>7.776546118368888</v>
       </c>
       <c r="J64" t="n">
         <v>82.06088167389984</v>
@@ -41195,7 +41195,7 @@
         <v>-9.5696171627769</v>
       </c>
       <c r="E65" t="n">
-        <v>53.37991067295851</v>
+        <v>53.37992447951525</v>
       </c>
       <c r="F65" t="n">
         <v>-2.789282531167381</v>
@@ -41227,7 +41227,7 @@
         <v>-11.31513063255917</v>
       </c>
       <c r="E66" t="n">
-        <v>56.02259572511812</v>
+        <v>56.02260652743436</v>
       </c>
       <c r="F66" t="n">
         <v>-3.191753439454137</v>
@@ -41259,7 +41259,7 @@
         <v>-11.01736652795241</v>
       </c>
       <c r="E67" t="n">
-        <v>50.77261751103143</v>
+        <v>50.77263103718916</v>
       </c>
       <c r="F67" t="n">
         <v>-5.080884384452744</v>
@@ -41291,7 +41291,7 @@
         <v>-9.423563890822795</v>
       </c>
       <c r="E68" t="n">
-        <v>49.7238733754217</v>
+        <v>49.72388691054292</v>
       </c>
       <c r="F68" t="n">
         <v>-3.992768548930603</v>
@@ -41303,7 +41303,7 @@
         <v>70.46093895677912</v>
       </c>
       <c r="I68" t="n">
-        <v>8.984565541660317</v>
+        <v>8.984577771064984</v>
       </c>
       <c r="J68" t="n">
         <v>112.8708253134189</v>
@@ -41367,7 +41367,7 @@
         <v>60.65876474493577</v>
       </c>
       <c r="I70" t="n">
-        <v>8.995201822292632</v>
+        <v>8.995189531381032</v>
       </c>
       <c r="J70" t="n">
         <v>112.1040256239442</v>
@@ -41483,7 +41483,7 @@
         <v>-10.50251353091357</v>
       </c>
       <c r="E74" t="n">
-        <v>37.76563551471814</v>
+        <v>37.76564791574937</v>
       </c>
       <c r="F74" t="n">
         <v>-24.46927078175064</v>
@@ -41515,7 +41515,7 @@
         <v>-11.97995591778075</v>
       </c>
       <c r="E75" t="n">
-        <v>35.3000326287824</v>
+        <v>35.300020332275</v>
       </c>
       <c r="F75" t="n">
         <v>-18.87479351610046</v>
@@ -41547,7 +41547,7 @@
         <v>-11.60304744813735</v>
       </c>
       <c r="E76" t="n">
-        <v>32.89662954383419</v>
+        <v>32.8966170006417</v>
       </c>
       <c r="F76" t="n">
         <v>-17.12165045191634</v>
@@ -41559,7 +41559,7 @@
         <v>29.75552684353173</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.790587515014507</v>
+        <v>-0.7905768063145135</v>
       </c>
       <c r="J76" t="n">
         <v>87.39039515006255</v>
@@ -41579,7 +41579,7 @@
         <v>-16.59367383947344</v>
       </c>
       <c r="E77" t="n">
-        <v>27.44299051570651</v>
+        <v>27.44300298995188</v>
       </c>
       <c r="F77" t="n">
         <v>-16.99586307263094</v>
@@ -41611,7 +41611,7 @@
         <v>-19.17274342085357</v>
       </c>
       <c r="E78" t="n">
-        <v>26.50176102394366</v>
+        <v>26.50176570435701</v>
       </c>
       <c r="F78" t="n">
         <v>-14.20658392523141</v>
@@ -41707,7 +41707,7 @@
         <v>-24.76658411486981</v>
       </c>
       <c r="E81" t="n">
-        <v>28.5714340963751</v>
+        <v>28.57142580895549</v>
       </c>
       <c r="F81" t="n">
         <v>-16.15832902940159</v>
@@ -41719,7 +41719,7 @@
         <v>44.05244047508194</v>
       </c>
       <c r="I81" t="n">
-        <v>-11.30205514714874</v>
+        <v>-11.30204587694931</v>
       </c>
       <c r="J81" t="n">
         <v>86.99152692711512</v>
@@ -41739,7 +41739,7 @@
         <v>-27.62790502503861</v>
       </c>
       <c r="E82" t="n">
-        <v>26.98314264407708</v>
+        <v>26.98314730158067</v>
       </c>
       <c r="F82" t="n">
         <v>-15.09280158634767</v>
@@ -41771,7 +41771,7 @@
         <v>-34.48276159737812</v>
       </c>
       <c r="E83" t="n">
-        <v>28.51448033045003</v>
+        <v>28.51446747407287</v>
       </c>
       <c r="F83" t="n">
         <v>-19.74900728652863</v>
@@ -41815,7 +41815,7 @@
         <v>59.40775106485634</v>
       </c>
       <c r="I84" t="n">
-        <v>-12.47748654563742</v>
+        <v>-12.47747784038312</v>
       </c>
       <c r="J84" t="n">
         <v>99.06541697895044</v>
@@ -41835,7 +41835,7 @@
         <v>-24.665128160175</v>
       </c>
       <c r="E85" t="n">
-        <v>27.92016784817664</v>
+        <v>27.92017608149169</v>
       </c>
       <c r="F85" t="n">
         <v>-16.67054649645153</v>
@@ -41867,7 +41867,7 @@
         <v>-26.6666637832975</v>
       </c>
       <c r="E86" t="n">
-        <v>28.70116495989465</v>
+        <v>28.70115663257717</v>
       </c>
       <c r="F86" t="n">
         <v>-17.14285992776975</v>
@@ -41899,7 +41899,7 @@
         <v>-26.10859890573426</v>
       </c>
       <c r="E87" t="n">
-        <v>30.99703429220788</v>
+        <v>30.99702123862926</v>
       </c>
       <c r="F87" t="n">
         <v>-18.06414822509883</v>
@@ -41931,7 +41931,7 @@
         <v>-27.29792125425134</v>
       </c>
       <c r="E88" t="n">
-        <v>26.79487970919705</v>
+        <v>26.79485831618089</v>
       </c>
       <c r="F88" t="n">
         <v>-22.44094964591114</v>
@@ -41943,7 +41943,7 @@
         <v>55.75244209203252</v>
       </c>
       <c r="I88" t="n">
-        <v>-20.06895592590158</v>
+        <v>-20.06894868868467</v>
       </c>
       <c r="J88" t="n">
         <v>92.52211321734347</v>
@@ -41995,7 +41995,7 @@
         <v>-25.66037895417199</v>
       </c>
       <c r="E90" t="n">
-        <v>28.1820197606033</v>
+        <v>28.18202818962325</v>
       </c>
       <c r="F90" t="n">
         <v>-21.60274235468711</v>
@@ -42027,7 +42027,7 @@
         <v>-27.11316392142076</v>
       </c>
       <c r="E91" t="n">
-        <v>23.32124539191589</v>
+        <v>23.32125845384157</v>
       </c>
       <c r="F91" t="n">
         <v>-24.73446258717338</v>
@@ -42071,7 +42071,7 @@
         <v>40.49050165131725</v>
       </c>
       <c r="I92" t="n">
-        <v>-26.51241816241978</v>
+        <v>-26.51242457432378</v>
       </c>
       <c r="J92" t="n">
         <v>61.74273412961313</v>
@@ -42091,7 +42091,7 @@
         <v>-33.75854461744496</v>
       </c>
       <c r="E93" t="n">
-        <v>13.49679986444057</v>
+        <v>13.49678679972988</v>
       </c>
       <c r="F93" t="n">
         <v>-33.28873780551388</v>
@@ -42103,7 +42103,7 @@
         <v>29.00301913394756</v>
       </c>
       <c r="I93" t="n">
-        <v>-29.45169627069456</v>
+        <v>-29.45170256490599</v>
       </c>
       <c r="J93" t="n">
         <v>42.69748628362795</v>
@@ -42123,7 +42123,7 @@
         <v>-32.86343938807552</v>
       </c>
       <c r="E94" t="n">
-        <v>13.02817533738021</v>
+        <v>13.0281626461012</v>
       </c>
       <c r="F94" t="n">
         <v>-31.92243919478229</v>
@@ -42167,7 +42167,7 @@
         <v>19.81707264392938</v>
       </c>
       <c r="I95" t="n">
-        <v>-26.00453059995175</v>
+        <v>-26.00453725848516</v>
       </c>
       <c r="J95" t="n">
         <v>24.96815972988056</v>
@@ -42187,7 +42187,7 @@
         <v>-39.19354682410292</v>
       </c>
       <c r="E96" t="n">
-        <v>14.19141167535614</v>
+        <v>14.19141889163848</v>
       </c>
       <c r="F96" t="n">
         <v>-43.65987090351605</v>
@@ -42199,7 +42199,7 @@
         <v>15.89211111741442</v>
       </c>
       <c r="I96" t="n">
-        <v>-23.5712605330649</v>
+        <v>-23.57126754833715</v>
       </c>
       <c r="J96" t="n">
         <v>28.54914740621408</v>
@@ -42219,7 +42219,7 @@
         <v>-37.38589247413267</v>
       </c>
       <c r="E97" t="n">
-        <v>15.21784828805857</v>
+        <v>15.21784099939436</v>
       </c>
       <c r="F97" t="n">
         <v>-43.28643185409469</v>
@@ -42231,7 +42231,7 @@
         <v>20.58264671468648</v>
       </c>
       <c r="I97" t="n">
-        <v>-25.00400219946962</v>
+        <v>-25.00399542027211</v>
       </c>
       <c r="J97" t="n">
         <v>34.37700446807093</v>
@@ -42251,7 +42251,7 @@
         <v>-36.22489816175252</v>
       </c>
       <c r="E98" t="n">
-        <v>14.42207519042114</v>
+        <v>14.42208246479413</v>
       </c>
       <c r="F98" t="n">
         <v>-52.13567772568902</v>
@@ -42411,7 +42411,7 @@
         <v>-37.47898911160345</v>
       </c>
       <c r="E103" t="n">
-        <v>-3.813646722865827</v>
+        <v>-3.813640407312757</v>
       </c>
       <c r="F103" t="n">
         <v>-61.42636857635259</v>
@@ -42423,7 +42423,7 @@
         <v>14.88724822383976</v>
       </c>
       <c r="I103" t="n">
-        <v>-32.84210154978727</v>
+        <v>-32.84210745784308</v>
       </c>
       <c r="J103" t="n">
         <v>22.98156990062044</v>
@@ -42443,7 +42443,7 @@
         <v>-38.02935221563132</v>
       </c>
       <c r="E104" t="n">
-        <v>-4.049334168701613</v>
+        <v>-4.049327871322895</v>
       </c>
       <c r="F104" t="n">
         <v>-60.6574271929146</v>
@@ -42571,7 +42571,7 @@
         <v>-34.87069327681005</v>
       </c>
       <c r="E108" t="n">
-        <v>0.6920890135108326</v>
+        <v>0.6920954001579327</v>
       </c>
       <c r="F108" t="n">
         <v>-56.18415731425067</v>
@@ -42603,7 +42603,7 @@
         <v>-38.2809222994163</v>
       </c>
       <c r="E109" t="n">
-        <v>-6.78485575492701</v>
+        <v>-6.784861443789014</v>
       </c>
       <c r="F109" t="n">
         <v>-56.1025635808961</v>
@@ -42615,7 +42615,7 @@
         <v>2.676028157570309</v>
       </c>
       <c r="I109" t="n">
-        <v>-34.05137407827211</v>
+        <v>-34.05136838470172</v>
       </c>
       <c r="J109" t="n">
         <v>26.24584557611403</v>
@@ -42635,7 +42635,7 @@
         <v>-38.41336313097599</v>
       </c>
       <c r="E110" t="n">
-        <v>-1.049657998912068</v>
+        <v>-1.049651814667596</v>
       </c>
       <c r="F110" t="n">
         <v>-55.1449584922653</v>
@@ -42667,7 +42667,7 @@
         <v>-38.03757962483449</v>
       </c>
       <c r="E111" t="n">
-        <v>0.632431300721481</v>
+        <v>0.6324251301784045</v>
       </c>
       <c r="F111" t="n">
         <v>-54.47863391321948</v>
@@ -42711,7 +42711,7 @@
         <v>21.10418192715375</v>
       </c>
       <c r="I112" t="n">
-        <v>-30.21470313468972</v>
+        <v>-30.21470932593397</v>
       </c>
       <c r="J112" t="n">
         <v>46.17241168844289</v>
@@ -42731,7 +42731,7 @@
         <v>-38.7500007947286</v>
       </c>
       <c r="E113" t="n">
-        <v>-1.713949824055983</v>
+        <v>-1.713949720608687</v>
       </c>
       <c r="F113" t="n">
         <v>-54.22889949879295</v>
@@ -42763,7 +42763,7 @@
         <v>-42.96153875497671</v>
       </c>
       <c r="E114" t="n">
-        <v>-15.95987381179289</v>
+        <v>-15.959870204464</v>
       </c>
       <c r="F114" t="n">
         <v>-55.92657561500155</v>
@@ -42807,7 +42807,7 @@
         <v>24.44754770776356</v>
       </c>
       <c r="I115" t="n">
-        <v>-34.41802113893922</v>
+        <v>-34.41802693935152</v>
       </c>
       <c r="J115" t="n">
         <v>50.05758655445842</v>
@@ -42859,7 +42859,7 @@
         <v>-44.84615325927734</v>
       </c>
       <c r="E117" t="n">
-        <v>-13.21917375442618</v>
+        <v>-13.21917958333557</v>
       </c>
       <c r="F117" t="n">
         <v>-55.92658828357197</v>
@@ -42871,7 +42871,7 @@
         <v>24.94730195367547</v>
       </c>
       <c r="I117" t="n">
-        <v>-36.19966175250494</v>
+        <v>-36.19966728478108</v>
       </c>
       <c r="J117" t="n">
         <v>38.56393145516608</v>
@@ -42903,7 +42903,7 @@
         <v>17.44131168849032</v>
       </c>
       <c r="I118" t="n">
-        <v>-36.78223083173312</v>
+        <v>-36.78223647824987</v>
       </c>
       <c r="J118" t="n">
         <v>35.52727439186789</v>
@@ -42923,7 +42923,7 @@
         <v>-41.87633402561816</v>
       </c>
       <c r="E119" t="n">
-        <v>-18.0512117287556</v>
+        <v>-18.05122097776638</v>
       </c>
       <c r="F119" t="n">
         <v>-56.31058995863971</v>
@@ -42955,7 +42955,7 @@
         <v>-42.79069788072998</v>
       </c>
       <c r="E120" t="n">
-        <v>-18.96608874513238</v>
+        <v>-18.96607964296703</v>
       </c>
       <c r="F120" t="n">
         <v>-56.69829342607511</v>
@@ -42967,7 +42967,7 @@
         <v>18.29646125327557</v>
       </c>
       <c r="I120" t="n">
-        <v>-38.547559258854</v>
+        <v>-38.54755360836089</v>
       </c>
       <c r="J120" t="n">
         <v>41.19001864296059</v>
@@ -42987,7 +42987,7 @@
         <v>-41.32780033399969</v>
       </c>
       <c r="E121" t="n">
-        <v>-16.14652467077281</v>
+        <v>-16.14651905964717</v>
       </c>
       <c r="F121" t="n">
         <v>-57.14155223271617</v>
@@ -43115,7 +43115,7 @@
         <v>-44.06438871165855</v>
       </c>
       <c r="E125" t="n">
-        <v>-19.65920559792231</v>
+        <v>-19.65921433551706</v>
       </c>
       <c r="F125" t="n">
         <v>-62.04201834542411</v>
@@ -43127,7 +43127,7 @@
         <v>-0.9950223577321893</v>
       </c>
       <c r="I125" t="n">
-        <v>-42.56499686306486</v>
+        <v>-42.56499198767874</v>
       </c>
       <c r="J125" t="n">
         <v>38.07183139644308</v>
@@ -43179,7 +43179,7 @@
         <v>-45.25879720144958</v>
       </c>
       <c r="E127" t="n">
-        <v>-31.44791479939482</v>
+        <v>-31.44790974132207</v>
       </c>
       <c r="F127" t="n">
         <v>-64.48646305395978</v>
@@ -43223,7 +43223,7 @@
         <v>-9.592997010479355</v>
       </c>
       <c r="I128" t="n">
-        <v>-49.59649089539933</v>
+        <v>-49.59648679341039</v>
       </c>
       <c r="J128" t="n">
         <v>28.59374093124656</v>
@@ -43255,7 +43255,7 @@
         <v>-9.914680971138623</v>
       </c>
       <c r="I129" t="n">
-        <v>-47.76542283989256</v>
+        <v>-47.76541850357405</v>
       </c>
       <c r="J129" t="n">
         <v>31.00990824180074</v>
@@ -43287,7 +43287,7 @@
         <v>-0.430739938833391</v>
       </c>
       <c r="I130" t="n">
-        <v>-44.80371006780727</v>
+        <v>-44.80370541333249</v>
       </c>
       <c r="J130" t="n">
         <v>40.60852082673853</v>
@@ -43307,7 +43307,7 @@
         <v>-38.22222391764323</v>
       </c>
       <c r="E131" t="n">
-        <v>-28.66039098574015</v>
+        <v>-28.66038601708145</v>
       </c>
       <c r="F131" t="n">
         <v>-60.87921861989671</v>
@@ -43319,7 +43319,7 @@
         <v>11.20226017119483</v>
       </c>
       <c r="I131" t="n">
-        <v>-41.57756135837645</v>
+        <v>-41.57756646105136</v>
       </c>
       <c r="J131" t="n">
         <v>50.06395514631925</v>
@@ -43339,7 +43339,7 @@
         <v>-37.71428537892771</v>
       </c>
       <c r="E132" t="n">
-        <v>-28.44838815136688</v>
+        <v>-28.44839309277756</v>
       </c>
       <c r="F132" t="n">
         <v>-57.52336377295379</v>
@@ -43371,7 +43371,7 @@
         <v>-39.29359721158256</v>
       </c>
       <c r="E133" t="n">
-        <v>-31.89682422506088</v>
+        <v>-31.89681766180208</v>
       </c>
       <c r="F133" t="n">
         <v>-56.86676433086298</v>
@@ -43435,7 +43435,7 @@
         <v>-39.18181766163219</v>
       </c>
       <c r="E135" t="n">
-        <v>-29.8943198980845</v>
+        <v>-29.89430845995157</v>
       </c>
       <c r="F135" t="n">
         <v>-55.97900230427739</v>
@@ -43447,7 +43447,7 @@
         <v>-2.809878783828057</v>
       </c>
       <c r="I135" t="n">
-        <v>-44.35211986444345</v>
+        <v>-44.35211507824253</v>
       </c>
       <c r="J135" t="n">
         <v>45.94360305036773</v>
@@ -43499,7 +43499,7 @@
         <v>-41.2641063072619</v>
       </c>
       <c r="E137" t="n">
-        <v>-34.25576189254548</v>
+        <v>-34.25575730483226</v>
       </c>
       <c r="F137" t="n">
         <v>-56.62921337306769</v>
@@ -43531,7 +43531,7 @@
         <v>-38.77646951114431</v>
       </c>
       <c r="E138" t="n">
-        <v>-38.27639900697836</v>
+        <v>-38.27638938277526</v>
       </c>
       <c r="F138" t="n">
         <v>-55.96958453493185</v>
@@ -43563,7 +43563,7 @@
         <v>-33.90243809397627</v>
       </c>
       <c r="E139" t="n">
-        <v>-36.75832996076532</v>
+        <v>-36.75832572741635</v>
       </c>
       <c r="F139" t="n">
         <v>-49.86285836356027</v>
@@ -43575,7 +43575,7 @@
         <v>11.39967947776015</v>
       </c>
       <c r="I139" t="n">
-        <v>-36.11916743903318</v>
+        <v>-36.11916133833199</v>
       </c>
       <c r="J139" t="n">
         <v>75.85081528702973</v>
@@ -43627,7 +43627,7 @@
         <v>-32.12871524589028</v>
       </c>
       <c r="E141" t="n">
-        <v>-32.28313624311352</v>
+        <v>-32.2831469020805</v>
       </c>
       <c r="F141" t="n">
         <v>-43.95747457582054</v>
@@ -43659,7 +43659,7 @@
         <v>-31.4987748448557</v>
       </c>
       <c r="E142" t="n">
-        <v>-32.50762230682122</v>
+        <v>-32.50761786349332</v>
       </c>
       <c r="F142" t="n">
         <v>-46.5503629780039</v>
@@ -43691,7 +43691,7 @@
         <v>-33.84615297239228</v>
       </c>
       <c r="E143" t="n">
-        <v>-35.46163637158381</v>
+        <v>-35.46164071660527</v>
       </c>
       <c r="F143" t="n">
         <v>-51.06795889575086</v>
@@ -43703,7 +43703,7 @@
         <v>-7.09122645551531</v>
       </c>
       <c r="I143" t="n">
-        <v>-32.10434891982889</v>
+        <v>-32.10435572998518</v>
       </c>
       <c r="J143" t="n">
         <v>60.56033954750786</v>
@@ -43723,7 +43723,7 @@
         <v>-33.90862967753029</v>
       </c>
       <c r="E144" t="n">
-        <v>-36.97423460587854</v>
+        <v>-36.97424007121808</v>
       </c>
       <c r="F144" t="n">
         <v>-49.50652575035288</v>
@@ -43755,7 +43755,7 @@
         <v>-32.57731865513828</v>
       </c>
       <c r="E145" t="n">
-        <v>-33.10222333815624</v>
+        <v>-33.10222787693342</v>
       </c>
       <c r="F145" t="n">
         <v>-47.72093129712481</v>
@@ -43787,7 +43787,7 @@
         <v>-32.98968940399975</v>
       </c>
       <c r="E146" t="n">
-        <v>-32.82846017281587</v>
+        <v>-32.82847077144174</v>
       </c>
       <c r="F146" t="n">
         <v>-50.13210990744989</v>
@@ -43831,7 +43831,7 @@
         <v>-8.328828410010559</v>
       </c>
       <c r="I147" t="n">
-        <v>-34.47114939719585</v>
+        <v>-34.47114291863736</v>
       </c>
       <c r="J147" t="n">
         <v>59.65780569033912</v>
@@ -43851,7 +43851,7 @@
         <v>-32.69521712881676</v>
       </c>
       <c r="E148" t="n">
-        <v>-33.61837206509205</v>
+        <v>-33.61837794033982</v>
       </c>
       <c r="F148" t="n">
         <v>-50.8521140595779</v>
@@ -43895,7 +43895,7 @@
         <v>-1.760633823603719</v>
       </c>
       <c r="I149" t="n">
-        <v>-34.87421557689749</v>
+        <v>-34.87420925337283</v>
       </c>
       <c r="J149" t="n">
         <v>56.09403415140542</v>
@@ -43927,7 +43927,7 @@
         <v>-7.602880670023849</v>
       </c>
       <c r="I150" t="n">
-        <v>-37.4569708671581</v>
+        <v>-37.45697692204924</v>
       </c>
       <c r="J150" t="n">
         <v>46.37167601458793</v>
@@ -43947,7 +43947,7 @@
         <v>-42.04651145047919</v>
       </c>
       <c r="E151" t="n">
-        <v>-40.1821004663875</v>
+        <v>-40.1821013090503</v>
       </c>
       <c r="F151" t="n">
         <v>-54.39159419656274</v>
@@ -43959,7 +43959,7 @@
         <v>-10.10608394316426</v>
       </c>
       <c r="I151" t="n">
-        <v>-43.26666186836514</v>
+        <v>-43.26666717142301</v>
       </c>
       <c r="J151" t="n">
         <v>35.01730440420005</v>
@@ -43979,7 +43979,7 @@
         <v>-39.58139641340389</v>
       </c>
       <c r="E152" t="n">
-        <v>-37.04565432657586</v>
+        <v>-37.04564463586239</v>
       </c>
       <c r="F152" t="n">
         <v>-53.60400625525475</v>
@@ -44011,7 +44011,7 @@
         <v>-41.59453644999592</v>
       </c>
       <c r="E153" t="n">
-        <v>-38.13498321627997</v>
+        <v>-38.13497790868293</v>
       </c>
       <c r="F153" t="n">
         <v>-55.56276981035423</v>
@@ -44075,7 +44075,7 @@
         <v>-39.45701410186536</v>
       </c>
       <c r="E155" t="n">
-        <v>-36.07449031108776</v>
+        <v>-36.07449555886241</v>
       </c>
       <c r="F155" t="n">
         <v>-51.83269228782829</v>
@@ -44087,7 +44087,7 @@
         <v>-14.68718460786851</v>
       </c>
       <c r="I155" t="n">
-        <v>-37.99085613237384</v>
+        <v>-37.99086187941774</v>
       </c>
       <c r="J155" t="n">
         <v>27.69939575660545</v>
@@ -44171,7 +44171,7 @@
         <v>-34.9769623935906</v>
       </c>
       <c r="E158" t="n">
-        <v>-33.49169830616715</v>
+        <v>-33.49170244123877</v>
       </c>
       <c r="F158" t="n">
         <v>-49.31460605578476</v>
@@ -44183,7 +44183,7 @@
         <v>19.17837993230622</v>
       </c>
       <c r="I158" t="n">
-        <v>-31.90961813240691</v>
+        <v>-31.90961164374077</v>
       </c>
       <c r="J158" t="n">
         <v>55.97883818585918</v>
@@ -44235,7 +44235,7 @@
         <v>-29.01205039886107</v>
       </c>
       <c r="E160" t="n">
-        <v>-27.14083902839913</v>
+        <v>-27.1408366814982</v>
       </c>
       <c r="F160" t="n">
         <v>-46.60070067860755</v>
@@ -44299,7 +44299,7 @@
         <v>-36.22727394104004</v>
       </c>
       <c r="E162" t="n">
-        <v>-33.12632209017097</v>
+        <v>-33.12631667581559</v>
       </c>
       <c r="F162" t="n">
         <v>-51.18435907630281</v>
@@ -44311,7 +44311,7 @@
         <v>31.94658342227763</v>
       </c>
       <c r="I162" t="n">
-        <v>-31.7316658087051</v>
+        <v>-31.73167254623591</v>
       </c>
       <c r="J162" t="n">
         <v>44.11149655354738</v>
@@ -44331,7 +44331,7 @@
         <v>-36.56108499654562</v>
       </c>
       <c r="E163" t="n">
-        <v>-30.31612554162724</v>
+        <v>-30.31613958799745</v>
       </c>
       <c r="F163" t="n">
         <v>-50.39954164408403</v>
@@ -44343,7 +44343,7 @@
         <v>35.25827976252069</v>
       </c>
       <c r="I163" t="n">
-        <v>-30.9723612810538</v>
+        <v>-30.97236803094082</v>
       </c>
       <c r="J163" t="n">
         <v>47.45098657865709</v>
@@ -44363,7 +44363,7 @@
         <v>-37.483146753204</v>
       </c>
       <c r="E164" t="n">
-        <v>-32.68096093226646</v>
+        <v>-32.68094753767251</v>
       </c>
       <c r="F164" t="n">
         <v>-48.08486004347705</v>
@@ -44395,7 +44395,7 @@
         <v>-40.39734998955379</v>
       </c>
       <c r="E165" t="n">
-        <v>-32.87279634781893</v>
+        <v>-32.87279104672564</v>
       </c>
       <c r="F165" t="n">
         <v>-50.55082406989408</v>
@@ -44427,7 +44427,7 @@
         <v>-40.43955960116543</v>
       </c>
       <c r="E166" t="n">
-        <v>-32.08065667981757</v>
+        <v>-32.08065123048447</v>
       </c>
       <c r="F166" t="n">
         <v>-53.59653548729015</v>
@@ -44459,7 +44459,7 @@
         <v>-38.52349200624654</v>
       </c>
       <c r="E167" t="n">
-        <v>-31.83363387746486</v>
+        <v>-31.8336393401792</v>
       </c>
       <c r="F167" t="n">
         <v>-53.46630744214328</v>
@@ -44535,7 +44535,7 @@
         <v>29.44025621625235</v>
       </c>
       <c r="I169" t="n">
-        <v>-35.44473564791697</v>
+        <v>-35.44474177393761</v>
       </c>
       <c r="J169" t="n">
         <v>41.96007874200003</v>
@@ -44587,7 +44587,7 @@
         <v>-40.04556086562169</v>
       </c>
       <c r="E171" t="n">
-        <v>-34.58447846232172</v>
+        <v>-34.58448249718911</v>
       </c>
       <c r="F171" t="n">
         <v>-51.04838688412199</v>
@@ -44599,7 +44599,7 @@
         <v>33.71331443951104</v>
       </c>
       <c r="I171" t="n">
-        <v>-37.94833755661033</v>
+        <v>-37.94833171441556</v>
       </c>
       <c r="J171" t="n">
         <v>43.41373072994053</v>
@@ -44651,7 +44651,7 @@
         <v>-32.91375369932255</v>
       </c>
       <c r="E173" t="n">
-        <v>-27.77852938823074</v>
+        <v>-27.77852341218486</v>
       </c>
       <c r="F173" t="n">
         <v>-43.44699349358814</v>
@@ -44663,7 +44663,7 @@
         <v>59.14138873392913</v>
       </c>
       <c r="I173" t="n">
-        <v>-31.15039340858322</v>
+        <v>-31.15038678081573</v>
       </c>
       <c r="J173" t="n">
         <v>68.31720572322637</v>
@@ -44683,7 +44683,7 @@
         <v>-30.59382334344727</v>
       </c>
       <c r="E174" t="n">
-        <v>-24.91228000773636</v>
+        <v>-24.91227355035074</v>
       </c>
       <c r="F174" t="n">
         <v>-41.76249980926514</v>
@@ -44695,7 +44695,7 @@
         <v>59.09223654259699</v>
       </c>
       <c r="I174" t="n">
-        <v>-27.84140135315001</v>
+        <v>-27.84139423196488</v>
       </c>
       <c r="J174" t="n">
         <v>72.74854593479307</v>
@@ -44779,7 +44779,7 @@
         <v>-26.87499713439198</v>
       </c>
       <c r="E177" t="n">
-        <v>-20.35360537283162</v>
+        <v>-20.35359835800773</v>
       </c>
       <c r="F177" t="n">
         <v>-38.99999765249399</v>
@@ -44791,7 +44791,7 @@
         <v>71.52501088341694</v>
       </c>
       <c r="I177" t="n">
-        <v>-22.33078549632175</v>
+        <v>-22.33077750093369</v>
       </c>
       <c r="J177" t="n">
         <v>83.1262414010687</v>
@@ -44811,7 +44811,7 @@
         <v>-27.66264949936464</v>
       </c>
       <c r="E178" t="n">
-        <v>-20.47751679276931</v>
+        <v>-20.47750781759832</v>
       </c>
       <c r="F178" t="n">
         <v>-39.01896560774591</v>
@@ -44843,7 +44843,7 @@
         <v>-28.19905523871372</v>
       </c>
       <c r="E179" t="n">
-        <v>-22.15917738967272</v>
+        <v>-22.15916869716422</v>
       </c>
       <c r="F179" t="n">
         <v>-41.81931635301061</v>
@@ -44855,7 +44855,7 @@
         <v>61.06736588618858</v>
       </c>
       <c r="I179" t="n">
-        <v>-24.21511774867416</v>
+        <v>-24.21511007080047</v>
       </c>
       <c r="J179" t="n">
         <v>75.58593786379788</v>
@@ -44875,7 +44875,7 @@
         <v>-27.29016992783636</v>
       </c>
       <c r="E180" t="n">
-        <v>-22.41062766588845</v>
+        <v>-22.41063438366677</v>
       </c>
       <c r="F180" t="n">
         <v>-39.6770169275888</v>
@@ -44907,7 +44907,7 @@
         <v>-26.03864804185331</v>
       </c>
       <c r="E181" t="n">
-        <v>-20.64497407201848</v>
+        <v>-20.64498270087283</v>
       </c>
       <c r="F181" t="n">
         <v>-39.39168486008041</v>
@@ -44939,7 +44939,7 @@
         <v>-27.65957226150498</v>
       </c>
       <c r="E182" t="n">
-        <v>-21.12262057043012</v>
+        <v>-21.12262914734645</v>
       </c>
       <c r="F182" t="n">
         <v>-38.78824946197358</v>
@@ -45003,7 +45003,7 @@
         <v>-26.79245330549804</v>
       </c>
       <c r="E184" t="n">
-        <v>-18.81728369892127</v>
+        <v>-18.81726817858214</v>
       </c>
       <c r="F184" t="n">
         <v>-35.9392113960985</v>
@@ -45067,7 +45067,7 @@
         <v>-25.23364352705133</v>
       </c>
       <c r="E186" t="n">
-        <v>-21.55172030710867</v>
+        <v>-21.55172688455815</v>
       </c>
       <c r="F186" t="n">
         <v>-33.64963145939185</v>
@@ -45163,7 +45163,7 @@
         <v>-24.3749994268784</v>
       </c>
       <c r="E189" t="n">
-        <v>-16.85281500968847</v>
+        <v>-16.85279894143548</v>
       </c>
       <c r="F189" t="n">
         <v>-28.89460472383064</v>
@@ -45195,7 +45195,7 @@
         <v>-23.35766138815261</v>
       </c>
       <c r="E190" t="n">
-        <v>-16.17542595647212</v>
+        <v>-16.1754097615417</v>
       </c>
       <c r="F190" t="n">
         <v>-32.43977679001436</v>
@@ -45207,7 +45207,7 @@
         <v>122.2920398799532</v>
       </c>
       <c r="I190" t="n">
-        <v>-17.22076008243486</v>
+        <v>-17.22076875496595</v>
       </c>
       <c r="J190" t="n">
         <v>146.51820853791</v>
@@ -45239,7 +45239,7 @@
         <v>123.5046433130916</v>
       </c>
       <c r="I191" t="n">
-        <v>-17.95775563916884</v>
+        <v>-17.95774706748667</v>
       </c>
       <c r="J191" t="n">
         <v>151.0794350518636</v>
@@ -45259,7 +45259,7 @@
         <v>-24.58234073821581</v>
       </c>
       <c r="E192" t="n">
-        <v>-14.56051583298611</v>
+        <v>-14.560524436397</v>
       </c>
       <c r="F192" t="n">
         <v>-31.51477378726198</v>
@@ -45271,7 +45271,7 @@
         <v>125.310248833198</v>
       </c>
       <c r="I192" t="n">
-        <v>-20.91946783988486</v>
+        <v>-20.91945994695765</v>
       </c>
       <c r="J192" t="n">
         <v>150.9514669770176</v>
@@ -45291,7 +45291,7 @@
         <v>-17.57731914672299</v>
       </c>
       <c r="E193" t="n">
-        <v>-9.055419336014003</v>
+        <v>-9.055420169258021</v>
       </c>
       <c r="F193" t="n">
         <v>-24.49735055141047</v>
@@ -45323,7 +45323,7 @@
         <v>-19.49875262272378</v>
       </c>
       <c r="E194" t="n">
-        <v>-12.4276599118963</v>
+        <v>-12.42766767500797</v>
       </c>
       <c r="F194" t="n">
         <v>-25.51905198204355</v>
@@ -45355,7 +45355,7 @@
         <v>-22.51231461369236</v>
       </c>
       <c r="E195" t="n">
-        <v>-15.28333644903409</v>
+        <v>-15.28334387731973</v>
       </c>
       <c r="F195" t="n">
         <v>-30.90795338358637</v>
@@ -45451,7 +45451,7 @@
         <v>-30.62730742553335</v>
       </c>
       <c r="E198" t="n">
-        <v>-17.25910396892187</v>
+        <v>-17.25910245924941</v>
       </c>
       <c r="F198" t="n">
         <v>-33.52514665157967</v>
@@ -45483,7 +45483,7 @@
         <v>-33.10871432964622</v>
       </c>
       <c r="E199" t="n">
-        <v>-20.16900416692024</v>
+        <v>-20.1689956791109</v>
       </c>
       <c r="F199" t="n">
         <v>-36.51537018870842</v>
@@ -45611,7 +45611,7 @@
         <v>-33.21586194762303</v>
       </c>
       <c r="E203" t="n">
-        <v>-16.04800469940202</v>
+        <v>-16.04799614881611</v>
       </c>
       <c r="F203" t="n">
         <v>-36.18741564478685</v>
@@ -45643,7 +45643,7 @@
         <v>-29.41952771061378</v>
       </c>
       <c r="E204" t="n">
-        <v>-17.02914492844722</v>
+        <v>-17.02912959365807</v>
       </c>
       <c r="F204" t="n">
         <v>-26.48352671295293</v>
@@ -45707,7 +45707,7 @@
         <v>-29.47645838329669</v>
       </c>
       <c r="E206" t="n">
-        <v>-8.977070678845955</v>
+        <v>-8.977062831240701</v>
       </c>
       <c r="F206" t="n">
         <v>-28.80289813678555</v>
@@ -45771,7 +45771,7 @@
         <v>-27.65476350642918</v>
       </c>
       <c r="E208" t="n">
-        <v>-7.480697989790852</v>
+        <v>-7.480690033325899</v>
       </c>
       <c r="F208" t="n">
         <v>-28.56085470297766</v>
@@ -45803,7 +45803,7 @@
         <v>-26.7097961922128</v>
       </c>
       <c r="E209" t="n">
-        <v>-7.607452804809</v>
+        <v>-7.60746146904766</v>
       </c>
       <c r="F209" t="n">
         <v>-28.01413821889418</v>
@@ -45835,7 +45835,7 @@
         <v>-26.72176522045333</v>
       </c>
       <c r="E210" t="n">
-        <v>-9.241938339858734</v>
+        <v>-9.241946894024998</v>
       </c>
       <c r="F210" t="n">
         <v>-27.03415236602241</v>
@@ -45867,7 +45867,7 @@
         <v>-27.28512988836156</v>
       </c>
       <c r="E211" t="n">
-        <v>-7.893982258126419</v>
+        <v>-7.893973574240542</v>
       </c>
       <c r="F211" t="n">
         <v>-31.35418360746799</v>
@@ -45931,7 +45931,7 @@
         <v>-32.08351066583373</v>
       </c>
       <c r="E213" t="n">
-        <v>-6.390548149228259</v>
+        <v>-6.390539985580757</v>
       </c>
       <c r="F213" t="n">
         <v>-36.81710406455739</v>
@@ -45995,7 +45995,7 @@
         <v>-31.69662302286084</v>
       </c>
       <c r="E215" t="n">
-        <v>-5.981578347866867</v>
+        <v>-5.981569662750863</v>
       </c>
       <c r="F215" t="n">
         <v>-35.00641823830535</v>
@@ -46027,7 +46027,7 @@
         <v>-33.33333747254461</v>
       </c>
       <c r="E216" t="n">
-        <v>-6.459955843676058</v>
+        <v>-6.459947047595593</v>
       </c>
       <c r="F216" t="n">
         <v>-35.39603519665386</v>
@@ -46091,7 +46091,7 @@
         <v>-31.83196333000435</v>
       </c>
       <c r="E218" t="n">
-        <v>-7.68788219992188</v>
+        <v>-7.687890327936886</v>
       </c>
       <c r="F218" t="n">
         <v>-32.37436156607637</v>
@@ -46219,7 +46219,7 @@
         <v>-36.29064639593801</v>
       </c>
       <c r="E222" t="n">
-        <v>-7.843132019864541</v>
+        <v>-7.84314091942816</v>
       </c>
       <c r="F222" t="n">
         <v>-28.89180566823137</v>
@@ -46379,7 +46379,7 @@
         <v>-34.85313456992967</v>
       </c>
       <c r="E227" t="n">
-        <v>-8.1714896278546</v>
+        <v>-8.171498781349463</v>
       </c>
       <c r="F227" t="n">
         <v>-32.55395806851909</v>
@@ -46411,7 +46411,7 @@
         <v>-36.55056678989862</v>
       </c>
       <c r="E228" t="n">
-        <v>-2.460515871778712</v>
+        <v>-2.460506794340878</v>
       </c>
       <c r="F228" t="n">
         <v>-33.03285408680733</v>
@@ -46443,7 +46443,7 @@
         <v>-37.24916312288149</v>
       </c>
       <c r="E229" t="n">
-        <v>-3.495026259081291</v>
+        <v>-3.495035167181182</v>
       </c>
       <c r="F229" t="n">
         <v>-38.67234368945173</v>
@@ -46507,7 +46507,7 @@
         <v>-37.52585712120092</v>
       </c>
       <c r="E231" t="n">
-        <v>0.04555280190197131</v>
+        <v>0.04553419329549335</v>
       </c>
       <c r="F231" t="n">
         <v>-36.82532653673968</v>
@@ -46603,7 +46603,7 @@
         <v>-37.23450483839871</v>
       </c>
       <c r="E234" t="n">
-        <v>0.09194310401834382</v>
+        <v>0.09195250322659998</v>
       </c>
       <c r="F234" t="n">
         <v>-38.63636103394656</v>
@@ -46635,7 +46635,7 @@
         <v>-34.25161045286568</v>
       </c>
       <c r="E235" t="n">
-        <v>2.665199040303001</v>
+        <v>2.665208703368349</v>
       </c>
       <c r="F235" t="n">
         <v>-35.84453808293154</v>
@@ -46763,7 +46763,7 @@
         <v>-33.56353240626703</v>
       </c>
       <c r="E239" t="n">
-        <v>1.693950400277155</v>
+        <v>1.693959968986869</v>
       </c>
       <c r="F239" t="n">
         <v>-43.07445745551136</v>
@@ -46987,7 +46987,7 @@
         <v>-31.36067022065163</v>
       </c>
       <c r="E246" t="n">
-        <v>-3.292492664437496</v>
+        <v>-3.292501612801146</v>
       </c>
       <c r="F246" t="n">
         <v>-44.01419291641084</v>
@@ -47115,7 +47115,7 @@
         <v>-32.32134575251007</v>
       </c>
       <c r="E250" t="n">
-        <v>-2.79985382220842</v>
+        <v>-2.799844619809422</v>
       </c>
       <c r="F250" t="n">
         <v>-45.22397009414632</v>
@@ -47147,7 +47147,7 @@
         <v>-31.40301388027185</v>
       </c>
       <c r="E251" t="n">
-        <v>-3.107492906488285</v>
+        <v>-3.107483694785163</v>
       </c>
       <c r="F251" t="n">
         <v>-44.10021926081409</v>
@@ -47211,7 +47211,7 @@
         <v>-30.50687043040482</v>
       </c>
       <c r="E253" t="n">
-        <v>-3.657905370458425</v>
+        <v>-3.657896195424548</v>
       </c>
       <c r="F253" t="n">
         <v>-43.2534700274485</v>
@@ -47275,7 +47275,7 @@
         <v>-28.36398693106126</v>
       </c>
       <c r="E255" t="n">
-        <v>-11.02652519290564</v>
+        <v>-11.0265174091879</v>
       </c>
       <c r="F255" t="n">
         <v>-40.86610764775907</v>
@@ -47307,7 +47307,7 @@
         <v>-28.43902401807832</v>
       </c>
       <c r="E256" t="n">
-        <v>-11.16642255217313</v>
+        <v>-11.16641471354466</v>
       </c>
       <c r="F256" t="n">
         <v>-40.68221552091195</v>
@@ -47563,7 +47563,7 @@
         <v>-30.63477422966672</v>
       </c>
       <c r="E264" t="n">
-        <v>-8.975249933684793</v>
+        <v>-8.975257928817172</v>
       </c>
       <c r="F264" t="n">
         <v>-39.47368508745812</v>
@@ -47659,7 +47659,7 @@
         <v>-29.24205512377247</v>
       </c>
       <c r="E267" t="n">
-        <v>-11.3721850694539</v>
+        <v>-11.37217723657323</v>
       </c>
       <c r="F267" t="n">
         <v>-35.66993037243454</v>
@@ -47723,7 +47723,7 @@
         <v>-31.51544377109349</v>
       </c>
       <c r="E269" t="n">
-        <v>-16.35530046410454</v>
+        <v>-16.3552932302255</v>
       </c>
       <c r="F269" t="n">
         <v>-38.0038388594275</v>
@@ -47947,7 +47947,7 @@
         <v>-30.96296522352431</v>
       </c>
       <c r="E276" t="n">
-        <v>-11.71149935583935</v>
+        <v>-11.7115071824372</v>
       </c>
       <c r="F276" t="n">
         <v>-34.97199627598184</v>
@@ -48043,7 +48043,7 @@
         <v>-28.54230449507224</v>
       </c>
       <c r="E279" t="n">
-        <v>-10.61024304532102</v>
+        <v>-10.61025096954303</v>
       </c>
       <c r="F279" t="n">
         <v>-31.85478688860097</v>
@@ -48139,7 +48139,7 @@
         <v>-31.95619725003812</v>
       </c>
       <c r="E282" t="n">
-        <v>-8.466562074090877</v>
+        <v>-8.466570285765041</v>
       </c>
       <c r="F282" t="n">
         <v>-36.50442544264273</v>
@@ -48171,7 +48171,7 @@
         <v>-34.78050768782048</v>
       </c>
       <c r="E283" t="n">
-        <v>-8.900946581418934</v>
+        <v>-8.900954788972681</v>
       </c>
       <c r="F283" t="n">
         <v>-36.51074312329671</v>
@@ -48235,7 +48235,7 @@
         <v>-33.6261564988414</v>
       </c>
       <c r="E285" t="n">
-        <v>-6.403057485981378</v>
+        <v>-6.403066080333931</v>
       </c>
       <c r="F285" t="n">
         <v>-43.19450633885003</v>
@@ -48363,7 +48363,7 @@
         <v>-27.07006549980937</v>
       </c>
       <c r="E289" t="n">
-        <v>-1.789457213034507</v>
+        <v>-1.789447632229446</v>
       </c>
       <c r="F289" t="n">
         <v>-36.1724497836834</v>
@@ -48395,7 +48395,7 @@
         <v>-26.88853708679655</v>
       </c>
       <c r="E290" t="n">
-        <v>-1.419453836500251</v>
+        <v>-1.419444239463907</v>
       </c>
       <c r="F290" t="n">
         <v>-38.08921600038258</v>
@@ -48555,7 +48555,7 @@
         <v>-30.8609987086815</v>
       </c>
       <c r="E295" t="n">
-        <v>-6.68391401909465</v>
+        <v>-6.683905083631759</v>
       </c>
       <c r="F295" t="n">
         <v>-41.6964609053498</v>
@@ -48747,7 +48747,7 @@
         <v>-32.60315788154286</v>
       </c>
       <c r="E301" t="n">
-        <v>-1.915389976623461</v>
+        <v>-1.915399321961297</v>
       </c>
       <c r="F301" t="n">
         <v>-44.79178880131202</v>
@@ -48875,7 +48875,7 @@
         <v>-27.57111994645234</v>
       </c>
       <c r="E305" t="n">
-        <v>3.14992657515003</v>
+        <v>3.149916020112609</v>
       </c>
       <c r="F305" t="n">
         <v>-41.52879384528914</v>
@@ -49003,7 +49003,7 @@
         <v>-27.55384073228704</v>
       </c>
       <c r="E309" t="n">
-        <v>-1.820409767954434</v>
+        <v>-1.820419341165691</v>
       </c>
       <c r="F309" t="n">
         <v>-46.45314619747551</v>
@@ -49035,7 +49035,7 @@
         <v>-28.12327812449581</v>
       </c>
       <c r="E310" t="n">
-        <v>-2.189970868730429</v>
+        <v>-2.189961319395339</v>
       </c>
       <c r="F310" t="n">
         <v>-43.11211700553351</v>
@@ -49131,7 +49131,7 @@
         <v>-23.67802924944825</v>
       </c>
       <c r="E313" t="n">
-        <v>-7.167704674027875</v>
+        <v>-7.167713321274871</v>
       </c>
       <c r="F313" t="n">
         <v>-43.89662309077295</v>
@@ -49195,7 +49195,7 @@
         <v>-25.69444651405009</v>
       </c>
       <c r="E315" t="n">
-        <v>-7.805284449640915</v>
+        <v>-7.8052930518827</v>
       </c>
       <c r="F315" t="n">
         <v>-44.86300958919328</v>
@@ -49259,7 +49259,7 @@
         <v>-30.79507707567796</v>
       </c>
       <c r="E317" t="n">
-        <v>-12.54195618625559</v>
+        <v>-12.54196405882723</v>
       </c>
       <c r="F317" t="n">
         <v>-47.19959819731769</v>
@@ -49323,7 +49323,7 @@
         <v>-28.38817660877887</v>
       </c>
       <c r="E319" t="n">
-        <v>-14.69881249627694</v>
+        <v>-14.69882014884166</v>
       </c>
       <c r="F319" t="n">
         <v>-46.19366314291567</v>
@@ -49355,7 +49355,7 @@
         <v>-30.04980322748305</v>
       </c>
       <c r="E320" t="n">
-        <v>-11.798339142925</v>
+        <v>-11.79834711640336</v>
       </c>
       <c r="F320" t="n">
         <v>-45.88515934593683</v>
@@ -49547,7 +49547,7 @@
         <v>-30.20774464959777</v>
       </c>
       <c r="E326" t="n">
-        <v>-12.61552578725684</v>
+        <v>-12.61553365320609</v>
       </c>
       <c r="F326" t="n">
         <v>-43.7062933475497</v>
@@ -49579,7 +49579,7 @@
         <v>-28.4168560528505</v>
       </c>
       <c r="E327" t="n">
-        <v>-11.2382507263617</v>
+        <v>-11.23824265940424</v>
       </c>
       <c r="F327" t="n">
         <v>-42.01795096708333</v>
@@ -49611,7 +49611,7 @@
         <v>-26.30973188082025</v>
       </c>
       <c r="E328" t="n">
-        <v>-7.835560144670373</v>
+        <v>-7.835551445906363</v>
       </c>
       <c r="F328" t="n">
         <v>-39.07111277288545</v>
@@ -49643,7 +49643,7 @@
         <v>-26.77945952370142</v>
       </c>
       <c r="E329" t="n">
-        <v>-4.35587998969117</v>
+        <v>-4.355889351430875</v>
       </c>
       <c r="F329" t="n">
         <v>-37.83128971446084</v>
@@ -49675,7 +49675,7 @@
         <v>-24.20228964506092</v>
       </c>
       <c r="E330" t="n">
-        <v>-2.263202999119251</v>
+        <v>-2.263212839202788</v>
       </c>
       <c r="F330" t="n">
         <v>-40.89319237117981</v>
@@ -49803,7 +49803,7 @@
         <v>-19.98714991312431</v>
       </c>
       <c r="E334" t="n">
-        <v>-2.88207449406167</v>
+        <v>-2.882084250995653</v>
       </c>
       <c r="F334" t="n">
         <v>-41.09851185636433</v>
@@ -49835,7 +49835,7 @@
         <v>-16.57894431388936</v>
       </c>
       <c r="E335" t="n">
-        <v>-1.332090723583423</v>
+        <v>-1.332080853007134</v>
       </c>
       <c r="F335" t="n">
         <v>-37.75945257518652</v>
@@ -49963,7 +49963,7 @@
         <v>-25.53582422398183</v>
       </c>
       <c r="E339" t="n">
-        <v>-4.37218089879411</v>
+        <v>-4.372171369682365</v>
       </c>
       <c r="F339" t="n">
         <v>-41.2774749891061</v>
@@ -49995,7 +49995,7 @@
         <v>-23.0622628159228</v>
       </c>
       <c r="E340" t="n">
-        <v>-3.034070394712185</v>
+        <v>-3.0340603821715</v>
       </c>
       <c r="F340" t="n">
         <v>-39.3328445504433</v>
@@ -50091,7 +50091,7 @@
         <v>-23.89099852905706</v>
       </c>
       <c r="E343" t="n">
-        <v>-0.6231467017805636</v>
+        <v>-0.6231572275657182</v>
       </c>
       <c r="F343" t="n">
         <v>-38.56778592704874</v>
@@ -50155,7 +50155,7 @@
         <v>-17.2627251407637</v>
       </c>
       <c r="E345" t="n">
-        <v>4.916302916447957</v>
+        <v>4.916314993451909</v>
       </c>
       <c r="F345" t="n">
         <v>-32.87099253590478</v>
@@ -50187,7 +50187,7 @@
         <v>-21.78477522759588</v>
       </c>
       <c r="E346" t="n">
-        <v>1.183733791213348</v>
+        <v>1.183745152549909</v>
       </c>
       <c r="F346" t="n">
         <v>-35.87239191644272</v>
@@ -50475,7 +50475,7 @@
         <v>-27.28494884671743</v>
       </c>
       <c r="E355" t="n">
-        <v>4.792392368889042</v>
+        <v>4.792385488267725</v>
       </c>
       <c r="F355" t="n">
         <v>-27.42354135671774</v>
@@ -50507,7 +50507,7 @@
         <v>-25.3721249509532</v>
       </c>
       <c r="E356" t="n">
-        <v>13.24401421734134</v>
+        <v>13.24400678497606</v>
       </c>
       <c r="F356" t="n">
         <v>-24.46144183427424</v>
@@ -50635,7 +50635,7 @@
         <v>-21.90601946492874</v>
       </c>
       <c r="E360" t="n">
-        <v>11.65992104672113</v>
+        <v>11.65991396441235</v>
       </c>
       <c r="F360" t="n">
         <v>-25.74782005433018</v>
@@ -50699,7 +50699,7 @@
         <v>-20.94915357686705</v>
       </c>
       <c r="E362" t="n">
-        <v>10.4534869862259</v>
+        <v>10.45348008305296</v>
       </c>
       <c r="F362" t="n">
         <v>-24.44530491228184</v>
@@ -50731,7 +50731,7 @@
         <v>-22.84366784680649</v>
       </c>
       <c r="E363" t="n">
-        <v>7.264098320135837</v>
+        <v>7.26410489731748</v>
       </c>
       <c r="F363" t="n">
         <v>-29.10251687659797</v>
@@ -50795,7 +50795,7 @@
         <v>-24.28571252479959</v>
       </c>
       <c r="E365" t="n">
-        <v>5.415679395542905</v>
+        <v>5.415672922114378</v>
       </c>
       <c r="F365" t="n">
         <v>-28.71211138002472</v>
@@ -50827,7 +50827,7 @@
         <v>-23.19622116035478</v>
       </c>
       <c r="E366" t="n">
-        <v>8.128490980816538</v>
+        <v>8.128497798204526</v>
       </c>
       <c r="F366" t="n">
         <v>-26.12058438561582</v>
@@ -50923,7 +50923,7 @@
         <v>-22.73361362756691</v>
       </c>
       <c r="E369" t="n">
-        <v>13.56802429660819</v>
+        <v>13.56803192476519</v>
       </c>
       <c r="F369" t="n">
         <v>-26.71135046405951</v>
@@ -51051,7 +51051,7 @@
         <v>-24.32815028665871</v>
       </c>
       <c r="E373" t="n">
-        <v>12.0694693473598</v>
+        <v>12.06946184813773</v>
       </c>
       <c r="F373" t="n">
         <v>-28.85148269226424</v>
@@ -51243,7 +51243,7 @@
         <v>-24.13010945252098</v>
       </c>
       <c r="E379" t="n">
-        <v>12.0428569162337</v>
+        <v>12.04284864922218</v>
       </c>
       <c r="F379" t="n">
         <v>-21.73281609041534</v>
@@ -51371,7 +51371,7 @@
         <v>-29.13668595833225</v>
       </c>
       <c r="E383" t="n">
-        <v>7.127779850578642</v>
+        <v>7.127772389347142</v>
       </c>
       <c r="F383" t="n">
         <v>-29.39840880790665</v>
@@ -51403,7 +51403,7 @@
         <v>-31.12208767584927</v>
       </c>
       <c r="E384" t="n">
-        <v>5.818240155712728</v>
+        <v>5.818247463604265</v>
       </c>
       <c r="F384" t="n">
         <v>-32.58526100040748</v>
@@ -51499,7 +51499,7 @@
         <v>-26.75635196626188</v>
       </c>
       <c r="E387" t="n">
-        <v>6.33768942164834</v>
+        <v>6.337682199015493</v>
       </c>
       <c r="F387" t="n">
         <v>-27.73670637603035</v>
@@ -51563,7 +51563,7 @@
         <v>-28.43965983222077</v>
       </c>
       <c r="E389" t="n">
-        <v>3.1580608161486</v>
+        <v>3.158053617653644</v>
       </c>
       <c r="F389" t="n">
         <v>-27.92992853630824</v>
@@ -51595,7 +51595,7 @@
         <v>-27.36356923125641</v>
       </c>
       <c r="E390" t="n">
-        <v>6.169308920977867</v>
+        <v>6.169301512354353</v>
       </c>
       <c r="F390" t="n">
         <v>-25.73402100163619</v>
@@ -51627,7 +51627,7 @@
         <v>-27.97047902954666</v>
       </c>
       <c r="E391" t="n">
-        <v>3.880500882192162</v>
+        <v>3.880493928511441</v>
       </c>
       <c r="F391" t="n">
         <v>-30.45361073235145</v>
@@ -51691,7 +51691,7 @@
         <v>-35.30269977477008</v>
       </c>
       <c r="E393" t="n">
-        <v>-2.038469494495021</v>
+        <v>-2.038462945038977</v>
       </c>
       <c r="F393" t="n">
         <v>-41.98987931194888</v>
@@ -51723,7 +51723,7 @@
         <v>-30.55953661004619</v>
       </c>
       <c r="E394" t="n">
-        <v>-0.1668904930419157</v>
+        <v>-0.1668970655057334</v>
       </c>
       <c r="F394" t="n">
         <v>-36.04969516561641</v>
@@ -51755,7 +51755,7 @@
         <v>-26.6316594977735</v>
       </c>
       <c r="E395" t="n">
-        <v>1.014299414847986</v>
+        <v>1.014306215598793</v>
       </c>
       <c r="F395" t="n">
         <v>-34.01675506515429</v>
@@ -51819,7 +51819,7 @@
         <v>-22.62996984260145</v>
       </c>
       <c r="E397" t="n">
-        <v>4.392311829375939</v>
+        <v>4.392318912024984</v>
       </c>
       <c r="F397" t="n">
         <v>-32.47330687594106</v>
@@ -51851,7 +51851,7 @@
         <v>-18.38461802555964</v>
       </c>
       <c r="E398" t="n">
-        <v>8.674322733776552</v>
+        <v>8.674330050879009</v>
       </c>
       <c r="F398" t="n">
         <v>-26.03086679746717</v>
@@ -52011,7 +52011,7 @@
         <v>-7.945423499897474</v>
       </c>
       <c r="E403" t="n">
-        <v>13.17264680156478</v>
+        <v>13.17263868232146</v>
       </c>
       <c r="F403" t="n">
         <v>-13.55808929093354</v>
@@ -52043,7 +52043,7 @@
         <v>-10.77751842338764</v>
       </c>
       <c r="E404" t="n">
-        <v>8.642981161077067</v>
+        <v>8.642973758231221</v>
       </c>
       <c r="F404" t="n">
         <v>-12.82665689655393</v>
@@ -52235,7 +52235,7 @@
         <v>-21.33238375936532</v>
       </c>
       <c r="E410" t="n">
-        <v>3.107189936007027</v>
+        <v>3.107196346569774</v>
       </c>
       <c r="F410" t="n">
         <v>-21.59166824801976</v>
@@ -52299,7 +52299,7 @@
         <v>-24.71146980834059</v>
       </c>
       <c r="E412" t="n">
-        <v>-2.726829609288295</v>
+        <v>-2.726841153927861</v>
       </c>
       <c r="F412" t="n">
         <v>-24.11161503408237</v>
@@ -52395,7 +52395,7 @@
         <v>-22.53923464985733</v>
       </c>
       <c r="E415" t="n">
-        <v>-1.847963577079392</v>
+        <v>-1.847951917291468</v>
       </c>
       <c r="F415" t="n">
         <v>-20.80552533209156</v>
@@ -52427,7 +52427,7 @@
         <v>-21.78288832645033</v>
       </c>
       <c r="E416" t="n">
-        <v>-3.412864651995873</v>
+        <v>-3.412876137907805</v>
       </c>
       <c r="F416" t="n">
         <v>-24.29865228356438</v>
@@ -52651,7 +52651,7 @@
         <v>-20.82066719519743</v>
       </c>
       <c r="E423" t="n">
-        <v>-5.578786518450696</v>
+        <v>-5.578780694495011</v>
       </c>
       <c r="F423" t="n">
         <v>-22.82890181163548</v>
@@ -52875,7 +52875,7 @@
         <v>-30.24650161641759</v>
       </c>
       <c r="E430" t="n">
-        <v>-10.80605285953314</v>
+        <v>-10.80606292625648</v>
       </c>
       <c r="F430" t="n">
         <v>-32.41098037149195</v>
@@ -52907,7 +52907,7 @@
         <v>-30.16501524682917</v>
       </c>
       <c r="E431" t="n">
-        <v>-12.13949474993221</v>
+        <v>-12.13950456134066</v>
       </c>
       <c r="F431" t="n">
         <v>-32.61940456242382</v>
@@ -52971,7 +52971,7 @@
         <v>-28.28217347291736</v>
       </c>
       <c r="E433" t="n">
-        <v>-13.65794799810753</v>
+        <v>-13.65793860950155</v>
       </c>
       <c r="F433" t="n">
         <v>-35.94838047268804</v>
@@ -53003,7 +53003,7 @@
         <v>-29.41176433922557</v>
       </c>
       <c r="E434" t="n">
-        <v>-15.05852841627437</v>
+        <v>-15.05851917996379</v>
       </c>
       <c r="F434" t="n">
         <v>-37.55248832154153</v>
@@ -53067,7 +53067,7 @@
         <v>-31.18556707365781</v>
       </c>
       <c r="E436" t="n">
-        <v>-18.02632554975999</v>
+        <v>-18.02633419934322</v>
       </c>
       <c r="F436" t="n">
         <v>-42.55076628068165</v>
@@ -53227,7 +53227,7 @@
         <v>-31.21424024348101</v>
       </c>
       <c r="E441" t="n">
-        <v>-19.20949383577247</v>
+        <v>-19.20950236051181</v>
       </c>
       <c r="F441" t="n">
         <v>-42.29934878455828</v>
@@ -53259,7 +53259,7 @@
         <v>-32.31746128627232</v>
       </c>
       <c r="E442" t="n">
-        <v>-20.91631837289538</v>
+        <v>-20.9163266846164</v>
       </c>
       <c r="F442" t="n">
         <v>-44.41396894882384</v>
@@ -53323,7 +53323,7 @@
         <v>-32.40506217564133</v>
       </c>
       <c r="E444" t="n">
-        <v>-22.34746953569596</v>
+        <v>-22.34746171639906</v>
       </c>
       <c r="F444" t="n">
         <v>-42.16226047422541</v>
@@ -53355,7 +53355,7 @@
         <v>-29.89368231014634</v>
       </c>
       <c r="E445" t="n">
-        <v>-20.7749366725903</v>
+        <v>-20.77492865674345</v>
       </c>
       <c r="F445" t="n">
         <v>-42.99229174547121</v>
@@ -53515,7 +53515,7 @@
         <v>-18.88297978584559</v>
       </c>
       <c r="E450" t="n">
-        <v>-15.88697830309197</v>
+        <v>-15.88698719525661</v>
       </c>
       <c r="F450" t="n">
         <v>-35.79224816752393</v>
@@ -53547,7 +53547,7 @@
         <v>-21.15514103139139</v>
       </c>
       <c r="E451" t="n">
-        <v>-17.34136803322271</v>
+        <v>-17.34137682167169</v>
       </c>
       <c r="F451" t="n">
         <v>-37.43143086937941</v>
@@ -53675,7 +53675,7 @@
         <v>-26.51714739149942</v>
       </c>
       <c r="E455" t="n">
-        <v>-21.18379462622453</v>
+        <v>-21.18380265372481</v>
       </c>
       <c r="F455" t="n">
         <v>-41.48341463321004</v>
@@ -53707,7 +53707,7 @@
         <v>-30.5295940900473</v>
       </c>
       <c r="E456" t="n">
-        <v>-21.92261013396634</v>
+        <v>-21.92261802067016</v>
       </c>
       <c r="F456" t="n">
         <v>-48.90003185290745</v>
@@ -53867,7 +53867,7 @@
         <v>-30.07565956712446</v>
       </c>
       <c r="E461" t="n">
-        <v>-25.4823950787656</v>
+        <v>-25.48238809077367</v>
       </c>
       <c r="F461" t="n">
         <v>-44.03718065374491</v>
@@ -53899,7 +53899,7 @@
         <v>-32.39348410987978</v>
       </c>
       <c r="E462" t="n">
-        <v>-29.13439621150543</v>
+        <v>-29.13438953225068</v>
       </c>
       <c r="F462" t="n">
         <v>-46.7217367763071</v>
@@ -53931,7 +53931,7 @@
         <v>-31.89493121198945</v>
       </c>
       <c r="E463" t="n">
-        <v>-28.07081175545964</v>
+        <v>-28.07081853704482</v>
       </c>
       <c r="F463" t="n">
         <v>-45.49804856795367</v>
@@ -54059,7 +54059,7 @@
         <v>-28.04877989062005</v>
       </c>
       <c r="E467" t="n">
-        <v>-28.551504886499</v>
+        <v>-28.55151148667798</v>
       </c>
       <c r="F467" t="n">
         <v>-42.95977001650706</v>
@@ -54091,7 +54091,7 @@
         <v>-27.86458221768647</v>
       </c>
       <c r="E468" t="n">
-        <v>-27.55755510454062</v>
+        <v>-27.55756191669814</v>
       </c>
       <c r="F468" t="n">
         <v>-44.69987464603042</v>
@@ -54283,7 +54283,7 @@
         <v>-32.19911590123635</v>
       </c>
       <c r="E474" t="n">
-        <v>-25.90197091088043</v>
+        <v>-25.90196375525328</v>
       </c>
       <c r="F474" t="n">
         <v>-51.98792057340895</v>
@@ -54443,7 +54443,7 @@
         <v>-27.52354840786123</v>
       </c>
       <c r="E479" t="n">
-        <v>-16.4275601717731</v>
+        <v>-16.42755184124513</v>
       </c>
       <c r="F479" t="n">
         <v>-47.64444308810764</v>
@@ -54571,7 +54571,7 @@
         <v>-28.27814801252383</v>
       </c>
       <c r="E483" t="n">
-        <v>-20.0272355549142</v>
+        <v>-20.02722811908593</v>
       </c>
       <c r="F483" t="n">
         <v>-47.95545639098183</v>
@@ -54699,7 +54699,7 @@
         <v>-25.48882469494409</v>
       </c>
       <c r="E487" t="n">
-        <v>-21.02923282196163</v>
+        <v>-21.0292402548563</v>
       </c>
       <c r="F487" t="n">
         <v>-48.99627177559144</v>

--- a/dashboards/Reliance Group.xlsx
+++ b/dashboards/Reliance Group.xlsx
@@ -528,7 +528,7 @@
         <v>97.5</v>
       </c>
       <c r="I3" t="n">
-        <v>857.11083984375</v>
+        <v>857.1109008789062</v>
       </c>
       <c r="J3" t="n">
         <v>13.89999961853027</v>
@@ -551,13 +551,13 @@
         <v>89.94999694824219</v>
       </c>
       <c r="G4" t="n">
-        <v>1118.526123046875</v>
+        <v>1118.526000976562</v>
       </c>
       <c r="H4" t="n">
         <v>97.05000305175781</v>
       </c>
       <c r="I4" t="n">
-        <v>844.1920776367188</v>
+        <v>844.1920166015625</v>
       </c>
       <c r="J4" t="n">
         <v>13.85000038146973</v>
@@ -580,7 +580,7 @@
         <v>89.90000152587891</v>
       </c>
       <c r="G5" t="n">
-        <v>1094.47607421875</v>
+        <v>1094.476196289062</v>
       </c>
       <c r="H5" t="n">
         <v>100.1500015258789</v>
@@ -609,13 +609,13 @@
         <v>91</v>
       </c>
       <c r="G6" t="n">
-        <v>1103.30810546875</v>
+        <v>1103.308227539062</v>
       </c>
       <c r="H6" t="n">
         <v>98.55000305175781</v>
       </c>
       <c r="I6" t="n">
-        <v>844.0447387695312</v>
+        <v>844.044677734375</v>
       </c>
       <c r="J6" t="n">
         <v>14.14999961853027</v>
@@ -638,7 +638,7 @@
         <v>91.5</v>
       </c>
       <c r="G7" t="n">
-        <v>1104.2138671875</v>
+        <v>1104.213745117188</v>
       </c>
       <c r="H7" t="n">
         <v>103.4499969482422</v>
@@ -667,7 +667,7 @@
         <v>89.34999847412109</v>
       </c>
       <c r="G8" t="n">
-        <v>1112.16259765625</v>
+        <v>1112.162719726562</v>
       </c>
       <c r="H8" t="n">
         <v>98.40000152587891</v>
@@ -696,13 +696,13 @@
         <v>88.09999847412109</v>
       </c>
       <c r="G9" t="n">
-        <v>1141.851318359375</v>
+        <v>1141.851196289062</v>
       </c>
       <c r="H9" t="n">
         <v>96.40000152587891</v>
       </c>
       <c r="I9" t="n">
-        <v>941.8934936523438</v>
+        <v>941.8935546875</v>
       </c>
       <c r="J9" t="n">
         <v>14.35000038146973</v>
@@ -725,7 +725,7 @@
         <v>90.09999847412109</v>
       </c>
       <c r="G10" t="n">
-        <v>1148.28271484375</v>
+        <v>1148.282836914062</v>
       </c>
       <c r="H10" t="n">
         <v>99.05000305175781</v>
@@ -754,7 +754,7 @@
         <v>89.59999847412109</v>
       </c>
       <c r="G11" t="n">
-        <v>1149.95849609375</v>
+        <v>1149.958618164062</v>
       </c>
       <c r="H11" t="n">
         <v>102.75</v>
@@ -783,13 +783,13 @@
         <v>91.40000152587891</v>
       </c>
       <c r="G12" t="n">
-        <v>1155.959716796875</v>
+        <v>1155.959594726562</v>
       </c>
       <c r="H12" t="n">
         <v>105.5500030517578</v>
       </c>
       <c r="I12" t="n">
-        <v>934.6728515625</v>
+        <v>934.6727905273438</v>
       </c>
       <c r="J12" t="n">
         <v>15.64999961853027</v>
@@ -812,13 +812,13 @@
         <v>89.80000305175781</v>
       </c>
       <c r="G13" t="n">
-        <v>1142.168334960938</v>
+        <v>1142.16845703125</v>
       </c>
       <c r="H13" t="n">
         <v>101.9499969482422</v>
       </c>
       <c r="I13" t="n">
-        <v>930.49755859375</v>
+        <v>930.4974975585938</v>
       </c>
       <c r="J13" t="n">
         <v>16.10000038146973</v>
@@ -841,7 +841,7 @@
         <v>90.69999694824219</v>
       </c>
       <c r="G14" t="n">
-        <v>1142.077758789062</v>
+        <v>1142.077880859375</v>
       </c>
       <c r="H14" t="n">
         <v>99.75</v>
@@ -870,7 +870,7 @@
         <v>88.75</v>
       </c>
       <c r="G15" t="n">
-        <v>1122.081420898438</v>
+        <v>1122.08154296875</v>
       </c>
       <c r="H15" t="n">
         <v>101.5500030517578</v>
@@ -899,7 +899,7 @@
         <v>86.40000152587891</v>
       </c>
       <c r="G16" t="n">
-        <v>1122.262573242188</v>
+        <v>1122.2626953125</v>
       </c>
       <c r="H16" t="n">
         <v>98.25</v>
@@ -934,7 +934,7 @@
         <v>93.55000305175781</v>
       </c>
       <c r="I17" t="n">
-        <v>835.7432861328125</v>
+        <v>835.7432250976562</v>
       </c>
       <c r="J17" t="n">
         <v>15.25</v>
@@ -963,7 +963,7 @@
         <v>98.05000305175781</v>
       </c>
       <c r="I18" t="n">
-        <v>835.7432861328125</v>
+        <v>835.7432250976562</v>
       </c>
       <c r="J18" t="n">
         <v>14.75</v>
@@ -986,7 +986,7 @@
         <v>81.90000152587891</v>
       </c>
       <c r="G19" t="n">
-        <v>1058.967407226562</v>
+        <v>1058.96728515625</v>
       </c>
       <c r="H19" t="n">
         <v>97.80000305175781</v>
@@ -1102,13 +1102,13 @@
         <v>85.90000152587891</v>
       </c>
       <c r="G23" t="n">
-        <v>1079.552368164062</v>
+        <v>1079.552490234375</v>
       </c>
       <c r="H23" t="n">
         <v>110.0999984741211</v>
       </c>
       <c r="I23" t="n">
-        <v>921.5574340820312</v>
+        <v>921.5574951171875</v>
       </c>
       <c r="J23" t="n">
         <v>16.04999923706055</v>
@@ -1137,7 +1137,7 @@
         <v>115.5999984741211</v>
       </c>
       <c r="I24" t="n">
-        <v>910.0140380859375</v>
+        <v>910.0140991210938</v>
       </c>
       <c r="J24" t="n">
         <v>16.85000038146973</v>
@@ -1160,13 +1160,13 @@
         <v>85.44999694824219</v>
       </c>
       <c r="G25" t="n">
-        <v>1055.887451171875</v>
+        <v>1055.8876953125</v>
       </c>
       <c r="H25" t="n">
         <v>121.3499984741211</v>
       </c>
       <c r="I25" t="n">
-        <v>898.3724975585938</v>
+        <v>898.3723754882812</v>
       </c>
       <c r="J25" t="n">
         <v>17.64999961853027</v>
@@ -1195,7 +1195,7 @@
         <v>133.4499969482422</v>
       </c>
       <c r="I26" t="n">
-        <v>874.7943115234375</v>
+        <v>874.7943725585938</v>
       </c>
       <c r="J26" t="n">
         <v>18.5</v>
@@ -1224,7 +1224,7 @@
         <v>134.4499969482422</v>
       </c>
       <c r="I27" t="n">
-        <v>865.2158813476562</v>
+        <v>865.2158203125</v>
       </c>
       <c r="J27" t="n">
         <v>17.60000038146973</v>
@@ -1253,7 +1253,7 @@
         <v>147.8500061035156</v>
       </c>
       <c r="I28" t="n">
-        <v>866.5419921875</v>
+        <v>866.5420532226562</v>
       </c>
       <c r="J28" t="n">
         <v>17</v>
@@ -1276,13 +1276,13 @@
         <v>92.09999847412109</v>
       </c>
       <c r="G29" t="n">
-        <v>1078.420288085938</v>
+        <v>1078.420166015625</v>
       </c>
       <c r="H29" t="n">
         <v>133.1000061035156</v>
       </c>
       <c r="I29" t="n">
-        <v>879.5099487304688</v>
+        <v>879.510009765625</v>
       </c>
       <c r="J29" t="n">
         <v>16.14999961853027</v>
@@ -1305,7 +1305,7 @@
         <v>91.44999694824219</v>
       </c>
       <c r="G30" t="n">
-        <v>1076.314208984375</v>
+        <v>1076.314086914062</v>
       </c>
       <c r="H30" t="n">
         <v>134</v>
@@ -1334,13 +1334,13 @@
         <v>86.90000152587891</v>
       </c>
       <c r="G31" t="n">
-        <v>1059.17138671875</v>
+        <v>1059.171142578125</v>
       </c>
       <c r="H31" t="n">
         <v>120.5999984741211</v>
       </c>
       <c r="I31" t="n">
-        <v>771.345703125</v>
+        <v>771.3457641601562</v>
       </c>
       <c r="J31" t="n">
         <v>15.19999980926514</v>
@@ -1392,7 +1392,7 @@
         <v>86.69999694824219</v>
       </c>
       <c r="G33" t="n">
-        <v>1092.868408203125</v>
+        <v>1092.868286132812</v>
       </c>
       <c r="H33" t="n">
         <v>122.5999984741211</v>
@@ -1421,7 +1421,7 @@
         <v>85.30000305175781</v>
       </c>
       <c r="G34" t="n">
-        <v>1106.704956054688</v>
+        <v>1106.704833984375</v>
       </c>
       <c r="H34" t="n">
         <v>113.3499984741211</v>
@@ -1456,7 +1456,7 @@
         <v>120.0999984741211</v>
       </c>
       <c r="I35" t="n">
-        <v>790.3063354492188</v>
+        <v>790.306396484375</v>
       </c>
       <c r="J35" t="n">
         <v>14.14999961853027</v>
@@ -1485,7 +1485,7 @@
         <v>112.6999969482422</v>
       </c>
       <c r="I36" t="n">
-        <v>750.4694213867188</v>
+        <v>750.4693603515625</v>
       </c>
       <c r="J36" t="n">
         <v>13.60000038146973</v>
@@ -1508,13 +1508,13 @@
         <v>78.05000305175781</v>
       </c>
       <c r="G37" t="n">
-        <v>1082.02099609375</v>
+        <v>1082.020874023438</v>
       </c>
       <c r="H37" t="n">
         <v>114.3499984741211</v>
       </c>
       <c r="I37" t="n">
-        <v>725.5650634765625</v>
+        <v>725.5651245117188</v>
       </c>
       <c r="J37" t="n">
         <v>12.94999980926514</v>
@@ -1630,7 +1630,7 @@
         <v>104.5999984741211</v>
       </c>
       <c r="I41" t="n">
-        <v>686.1209106445312</v>
+        <v>686.1209716796875</v>
       </c>
       <c r="J41" t="n">
         <v>13.05000019073486</v>
@@ -1653,13 +1653,13 @@
         <v>76.25</v>
       </c>
       <c r="G42" t="n">
-        <v>1086.346313476562</v>
+        <v>1086.346435546875</v>
       </c>
       <c r="H42" t="n">
         <v>107.5999984741211</v>
       </c>
       <c r="I42" t="n">
-        <v>692.8504638671875</v>
+        <v>692.8505249023438</v>
       </c>
       <c r="J42" t="n">
         <v>13.14999961853027</v>
@@ -1688,7 +1688,7 @@
         <v>106.4000015258789</v>
       </c>
       <c r="I43" t="n">
-        <v>688.6752319335938</v>
+        <v>688.6751708984375</v>
       </c>
       <c r="J43" t="n">
         <v>13.05000019073486</v>
@@ -1717,7 +1717,7 @@
         <v>103.5</v>
       </c>
       <c r="I44" t="n">
-        <v>674.7249755859375</v>
+        <v>674.7249145507812</v>
       </c>
       <c r="J44" t="n">
         <v>12.85000038146973</v>
@@ -1740,7 +1740,7 @@
         <v>73.65000152587891</v>
       </c>
       <c r="G45" t="n">
-        <v>1014.332458496094</v>
+        <v>1014.332336425781</v>
       </c>
       <c r="H45" t="n">
         <v>99.59999847412109</v>
@@ -1775,7 +1775,7 @@
         <v>101.75</v>
       </c>
       <c r="I46" t="n">
-        <v>667.504150390625</v>
+        <v>667.5040893554688</v>
       </c>
       <c r="J46" t="n">
         <v>12.80000019073486</v>
@@ -1856,7 +1856,7 @@
         <v>77.84999847412109</v>
       </c>
       <c r="G49" t="n">
-        <v>1086.617919921875</v>
+        <v>1086.618041992188</v>
       </c>
       <c r="H49" t="n">
         <v>122.5</v>
@@ -1914,13 +1914,13 @@
         <v>78.84999847412109</v>
       </c>
       <c r="G51" t="n">
-        <v>1070.448974609375</v>
+        <v>1070.44873046875</v>
       </c>
       <c r="H51" t="n">
         <v>115.5500030517578</v>
       </c>
       <c r="I51" t="n">
-        <v>747.32568359375</v>
+        <v>747.3256225585938</v>
       </c>
       <c r="J51" t="n">
         <v>13.44999980926514</v>
@@ -1943,7 +1943,7 @@
         <v>77.75</v>
       </c>
       <c r="G52" t="n">
-        <v>1088.520385742188</v>
+        <v>1088.520263671875</v>
       </c>
       <c r="H52" t="n">
         <v>118.9499969482422</v>
@@ -1972,13 +1972,13 @@
         <v>78.75</v>
       </c>
       <c r="G53" t="n">
-        <v>1124.00634765625</v>
+        <v>1124.006591796875</v>
       </c>
       <c r="H53" t="n">
         <v>116.8000030517578</v>
       </c>
       <c r="I53" t="n">
-        <v>758.7706909179688</v>
+        <v>758.770751953125</v>
       </c>
       <c r="J53" t="n">
         <v>13.75</v>
@@ -2007,7 +2007,7 @@
         <v>115.4000015258789</v>
       </c>
       <c r="I54" t="n">
-        <v>744.8695678710938</v>
+        <v>744.8695068359375</v>
       </c>
       <c r="J54" t="n">
         <v>13.64999961853027</v>
@@ -2065,7 +2065,7 @@
         <v>111.8000030517578</v>
       </c>
       <c r="I56" t="n">
-        <v>756.5111694335938</v>
+        <v>756.51123046875</v>
       </c>
       <c r="J56" t="n">
         <v>12.85000038146973</v>
@@ -2123,7 +2123,7 @@
         <v>109.1999969482422</v>
       </c>
       <c r="I58" t="n">
-        <v>755.5779418945312</v>
+        <v>755.577880859375</v>
       </c>
       <c r="J58" t="n">
         <v>13</v>
@@ -2152,7 +2152,7 @@
         <v>100.6999969482422</v>
       </c>
       <c r="I59" t="n">
-        <v>731.4595336914062</v>
+        <v>731.4595947265625</v>
       </c>
       <c r="J59" t="n">
         <v>12.35000038146973</v>
@@ -2175,13 +2175,13 @@
         <v>84.30000305175781</v>
       </c>
       <c r="G60" t="n">
-        <v>1187.7998046875</v>
+        <v>1187.799926757812</v>
       </c>
       <c r="H60" t="n">
         <v>110.75</v>
       </c>
       <c r="I60" t="n">
-        <v>735.4383544921875</v>
+        <v>735.438232421875</v>
       </c>
       <c r="J60" t="n">
         <v>12.94999980926514</v>
@@ -2239,7 +2239,7 @@
         <v>112.3000030517578</v>
       </c>
       <c r="I62" t="n">
-        <v>764.6162109375</v>
+        <v>764.6161499023438</v>
       </c>
       <c r="J62" t="n">
         <v>13.5</v>
@@ -2297,7 +2297,7 @@
         <v>124.6999969482422</v>
       </c>
       <c r="I64" t="n">
-        <v>794.3343505859375</v>
+        <v>794.3342895507812</v>
       </c>
       <c r="J64" t="n">
         <v>14.85000038146973</v>
@@ -2320,7 +2320,7 @@
         <v>93.05000305175781</v>
       </c>
       <c r="G65" t="n">
-        <v>1189.385131835938</v>
+        <v>1189.385009765625</v>
       </c>
       <c r="H65" t="n">
         <v>132.1499938964844</v>
@@ -2349,13 +2349,13 @@
         <v>94.5</v>
       </c>
       <c r="G66" t="n">
-        <v>1186.21484375</v>
+        <v>1186.214599609375</v>
       </c>
       <c r="H66" t="n">
         <v>136.1499938964844</v>
       </c>
       <c r="I66" t="n">
-        <v>822.1367797851562</v>
+        <v>822.13671875</v>
       </c>
       <c r="J66" t="n">
         <v>16.29999923706055</v>
@@ -2378,7 +2378,7 @@
         <v>96.30000305175781</v>
       </c>
       <c r="G67" t="n">
-        <v>1165.289916992188</v>
+        <v>1165.2900390625</v>
       </c>
       <c r="H67" t="n">
         <v>125.1500015258789</v>
@@ -2407,13 +2407,13 @@
         <v>97.19999694824219</v>
       </c>
       <c r="G68" t="n">
-        <v>1184.674682617188</v>
+        <v>1184.6748046875</v>
       </c>
       <c r="H68" t="n">
         <v>126.75</v>
       </c>
       <c r="I68" t="n">
-        <v>815.8491821289062</v>
+        <v>815.8493041992188</v>
       </c>
       <c r="J68" t="n">
         <v>15.60000038146973</v>
@@ -2442,7 +2442,7 @@
         <v>125.8499984741211</v>
       </c>
       <c r="I69" t="n">
-        <v>816.3896484375</v>
+        <v>816.3895874023438</v>
       </c>
       <c r="J69" t="n">
         <v>15.69999980926514</v>
@@ -2465,7 +2465,7 @@
         <v>94.84999847412109</v>
       </c>
       <c r="G70" t="n">
-        <v>1159.945556640625</v>
+        <v>1159.945434570312</v>
       </c>
       <c r="H70" t="n">
         <v>122.9499969482422</v>
@@ -2494,13 +2494,13 @@
         <v>93.80000305175781</v>
       </c>
       <c r="G71" t="n">
-        <v>1155.688110351562</v>
+        <v>1155.68798828125</v>
       </c>
       <c r="H71" t="n">
         <v>123.4000015258789</v>
       </c>
       <c r="I71" t="n">
-        <v>944.153076171875</v>
+        <v>944.1530151367188</v>
       </c>
       <c r="J71" t="n">
         <v>14.85000038146973</v>
@@ -2529,7 +2529,7 @@
         <v>119.5500030517578</v>
       </c>
       <c r="I72" t="n">
-        <v>982.61474609375</v>
+        <v>982.6148071289062</v>
       </c>
       <c r="J72" t="n">
         <v>14.39999961853027</v>
@@ -2558,7 +2558,7 @@
         <v>123.5999984741211</v>
       </c>
       <c r="I73" t="n">
-        <v>979.8148803710938</v>
+        <v>979.8148193359375</v>
       </c>
       <c r="J73" t="n">
         <v>14.39999961853027</v>
@@ -2587,7 +2587,7 @@
         <v>125.75</v>
       </c>
       <c r="I74" t="n">
-        <v>945.7249145507812</v>
+        <v>945.7249755859375</v>
       </c>
       <c r="J74" t="n">
         <v>14.75</v>
@@ -2616,7 +2616,7 @@
         <v>130.3000030517578</v>
       </c>
       <c r="I75" t="n">
-        <v>987.2322387695312</v>
+        <v>987.232177734375</v>
       </c>
       <c r="J75" t="n">
         <v>15.14999961853027</v>
@@ -2639,7 +2639,7 @@
         <v>98.90000152587891</v>
       </c>
       <c r="G76" t="n">
-        <v>1249.510131835938</v>
+        <v>1249.510009765625</v>
       </c>
       <c r="H76" t="n">
         <v>128.8999938964844</v>
@@ -2726,7 +2726,7 @@
         <v>113.6999969482422</v>
       </c>
       <c r="G79" t="n">
-        <v>1258.364624023438</v>
+        <v>1258.364501953125</v>
       </c>
       <c r="H79" t="n">
         <v>123</v>
@@ -2755,13 +2755,13 @@
         <v>91.34999847412109</v>
       </c>
       <c r="G80" t="n">
-        <v>1277.16064453125</v>
+        <v>1277.160766601562</v>
       </c>
       <c r="H80" t="n">
         <v>120.5999984741211</v>
       </c>
       <c r="I80" t="n">
-        <v>1080.660034179688</v>
+        <v>1080.66015625</v>
       </c>
       <c r="J80" t="n">
         <v>13.94999980926514</v>
@@ -2784,7 +2784,7 @@
         <v>86.19999694824219</v>
       </c>
       <c r="G81" t="n">
-        <v>1263.75439453125</v>
+        <v>1263.754272460938</v>
       </c>
       <c r="H81" t="n">
         <v>123.5500030517578</v>
@@ -2813,13 +2813,13 @@
         <v>85</v>
       </c>
       <c r="G82" t="n">
-        <v>1259.315551757812</v>
+        <v>1259.315795898438</v>
       </c>
       <c r="H82" t="n">
         <v>124.25</v>
       </c>
       <c r="I82" t="n">
-        <v>1096.47705078125</v>
+        <v>1096.476928710938</v>
       </c>
       <c r="J82" t="n">
         <v>14.19999980926514</v>
@@ -2842,13 +2842,13 @@
         <v>76.94999694824219</v>
       </c>
       <c r="G83" t="n">
-        <v>1220.002319335938</v>
+        <v>1220.00244140625</v>
       </c>
       <c r="H83" t="n">
         <v>116.0999984741211</v>
       </c>
       <c r="I83" t="n">
-        <v>1001.13330078125</v>
+        <v>1001.133422851562</v>
       </c>
       <c r="J83" t="n">
         <v>13.55000019073486</v>
@@ -2871,7 +2871,7 @@
         <v>80.30000305175781</v>
       </c>
       <c r="G84" t="n">
-        <v>1196.11083984375</v>
+        <v>1196.110961914062</v>
       </c>
       <c r="H84" t="n">
         <v>115.0999984741211</v>
@@ -2900,7 +2900,7 @@
         <v>78.34999847412109</v>
       </c>
       <c r="G85" t="n">
-        <v>1186.939453125</v>
+        <v>1186.939331054688</v>
       </c>
       <c r="H85" t="n">
         <v>111.3000030517578</v>
@@ -2935,7 +2935,7 @@
         <v>112.3000030517578</v>
       </c>
       <c r="I86" t="n">
-        <v>1002.950866699219</v>
+        <v>1002.950805664062</v>
       </c>
       <c r="J86" t="n">
         <v>13.69999980926514</v>
@@ -2958,13 +2958,13 @@
         <v>72.80000305175781</v>
       </c>
       <c r="G87" t="n">
-        <v>1120.813232421875</v>
+        <v>1120.813354492188</v>
       </c>
       <c r="H87" t="n">
         <v>108.1999969482422</v>
       </c>
       <c r="I87" t="n">
-        <v>953.9772338867188</v>
+        <v>953.977294921875</v>
       </c>
       <c r="J87" t="n">
         <v>13.10000038146973</v>
@@ -3016,7 +3016,7 @@
         <v>72.75</v>
       </c>
       <c r="G89" t="n">
-        <v>1086.731323242188</v>
+        <v>1086.731201171875</v>
       </c>
       <c r="H89" t="n">
         <v>100.9000015258789</v>
@@ -3051,7 +3051,7 @@
         <v>102.0500030517578</v>
       </c>
       <c r="I90" t="n">
-        <v>955.74560546875</v>
+        <v>955.7456665039062</v>
       </c>
       <c r="J90" t="n">
         <v>12.5</v>
@@ -3074,7 +3074,7 @@
         <v>74.59999847412109</v>
       </c>
       <c r="G91" t="n">
-        <v>1099.322387695312</v>
+        <v>1099.322509765625</v>
       </c>
       <c r="H91" t="n">
         <v>98.30000305175781</v>
@@ -3109,7 +3109,7 @@
         <v>107.0500030517578</v>
       </c>
       <c r="I92" t="n">
-        <v>1028.100708007812</v>
+        <v>1028.1005859375</v>
       </c>
       <c r="J92" t="n">
         <v>12.44999980926514</v>
@@ -3161,7 +3161,7 @@
         <v>75.65000152587891</v>
       </c>
       <c r="G94" t="n">
-        <v>1123.16845703125</v>
+        <v>1123.168334960938</v>
       </c>
       <c r="H94" t="n">
         <v>102.0999984741211</v>
@@ -3196,7 +3196,7 @@
         <v>104</v>
       </c>
       <c r="I95" t="n">
-        <v>1021.665893554688</v>
+        <v>1021.665771484375</v>
       </c>
       <c r="J95" t="n">
         <v>12.85000038146973</v>
@@ -3248,13 +3248,13 @@
         <v>78.94999694824219</v>
       </c>
       <c r="G97" t="n">
-        <v>1184.765258789062</v>
+        <v>1184.765380859375</v>
       </c>
       <c r="H97" t="n">
         <v>100.9000015258789</v>
       </c>
       <c r="I97" t="n">
-        <v>945.7249145507812</v>
+        <v>945.7249755859375</v>
       </c>
       <c r="J97" t="n">
         <v>12.55000019073486</v>
@@ -3277,13 +3277,13 @@
         <v>74.65000152587891</v>
       </c>
       <c r="G98" t="n">
-        <v>1183.021606445312</v>
+        <v>1183.021728515625</v>
       </c>
       <c r="H98" t="n">
         <v>100.6500015258789</v>
       </c>
       <c r="I98" t="n">
-        <v>869.98046875</v>
+        <v>869.9805297851562</v>
       </c>
       <c r="J98" t="n">
         <v>12.10000038146973</v>
@@ -3306,13 +3306,13 @@
         <v>71.59999847412109</v>
       </c>
       <c r="G99" t="n">
-        <v>1171.743896484375</v>
+        <v>1171.744018554688</v>
       </c>
       <c r="H99" t="n">
         <v>100.3499984741211</v>
       </c>
       <c r="I99" t="n">
-        <v>832.8450927734375</v>
+        <v>832.8451538085938</v>
       </c>
       <c r="J99" t="n">
         <v>11.89999961853027</v>
@@ -3335,13 +3335,13 @@
         <v>71.65000152587891</v>
       </c>
       <c r="G100" t="n">
-        <v>1166.308959960938</v>
+        <v>1166.308837890625</v>
       </c>
       <c r="H100" t="n">
         <v>99.84999847412109</v>
       </c>
       <c r="I100" t="n">
-        <v>871.9945068359375</v>
+        <v>871.9944458007812</v>
       </c>
       <c r="J100" t="n">
         <v>11.85000038146973</v>
@@ -3370,7 +3370,7 @@
         <v>102.5500030517578</v>
       </c>
       <c r="I101" t="n">
-        <v>914.9261474609375</v>
+        <v>914.9262084960938</v>
       </c>
       <c r="J101" t="n">
         <v>12</v>
@@ -3393,7 +3393,7 @@
         <v>75.5</v>
       </c>
       <c r="G102" t="n">
-        <v>1192.374389648438</v>
+        <v>1192.374267578125</v>
       </c>
       <c r="H102" t="n">
         <v>107.9499969482422</v>
@@ -3428,7 +3428,7 @@
         <v>108.0500030517578</v>
       </c>
       <c r="I103" t="n">
-        <v>929.4660034179688</v>
+        <v>929.4658813476562</v>
       </c>
       <c r="J103" t="n">
         <v>13.19999980926514</v>
@@ -3451,7 +3451,7 @@
         <v>76.5</v>
       </c>
       <c r="G104" t="n">
-        <v>1233.884399414062</v>
+        <v>1233.88427734375</v>
       </c>
       <c r="H104" t="n">
         <v>109.3000030517578</v>
@@ -3480,13 +3480,13 @@
         <v>76.59999847412109</v>
       </c>
       <c r="G105" t="n">
-        <v>1258.885375976562</v>
+        <v>1258.88525390625</v>
       </c>
       <c r="H105" t="n">
         <v>106.5999984741211</v>
       </c>
       <c r="I105" t="n">
-        <v>965.9136962890625</v>
+        <v>965.9136352539062</v>
       </c>
       <c r="J105" t="n">
         <v>13.25</v>
@@ -3538,7 +3538,7 @@
         <v>75.90000152587891</v>
       </c>
       <c r="G107" t="n">
-        <v>1255.828125</v>
+        <v>1255.828247070312</v>
       </c>
       <c r="H107" t="n">
         <v>105.5</v>
@@ -3573,7 +3573,7 @@
         <v>104.8499984741211</v>
       </c>
       <c r="I108" t="n">
-        <v>969.3521728515625</v>
+        <v>969.3521118164062</v>
       </c>
       <c r="J108" t="n">
         <v>13.85000038146973</v>
@@ -3596,13 +3596,13 @@
         <v>80.94999694824219</v>
       </c>
       <c r="G109" t="n">
-        <v>1267.60400390625</v>
+        <v>1267.604125976562</v>
       </c>
       <c r="H109" t="n">
         <v>104.4499969482422</v>
       </c>
       <c r="I109" t="n">
-        <v>974.75537109375</v>
+        <v>974.7554931640625</v>
       </c>
       <c r="J109" t="n">
         <v>13.94999980926514</v>
@@ -3631,7 +3631,7 @@
         <v>103.5999984741211</v>
       </c>
       <c r="I110" t="n">
-        <v>944.0548095703125</v>
+        <v>944.0548706054688</v>
       </c>
       <c r="J110" t="n">
         <v>13.55000019073486</v>
@@ -3660,7 +3660,7 @@
         <v>96.94999694824219</v>
       </c>
       <c r="I111" t="n">
-        <v>874.548828125</v>
+        <v>874.5487670898438</v>
       </c>
       <c r="J111" t="n">
         <v>12.89999961853027</v>
@@ -3683,13 +3683,13 @@
         <v>72.84999847412109</v>
       </c>
       <c r="G112" t="n">
-        <v>1190.313598632812</v>
+        <v>1190.3134765625</v>
       </c>
       <c r="H112" t="n">
         <v>95.75</v>
       </c>
       <c r="I112" t="n">
-        <v>879.7064819335938</v>
+        <v>879.7064208984375</v>
       </c>
       <c r="J112" t="n">
         <v>12.85000038146973</v>
@@ -3718,7 +3718,7 @@
         <v>95.5</v>
       </c>
       <c r="I113" t="n">
-        <v>876.5136108398438</v>
+        <v>876.513671875</v>
       </c>
       <c r="J113" t="n">
         <v>12.64999961853027</v>
@@ -3741,13 +3741,13 @@
         <v>67.25</v>
       </c>
       <c r="G114" t="n">
-        <v>1159.469848632812</v>
+        <v>1159.4697265625</v>
       </c>
       <c r="H114" t="n">
         <v>95.40000152587891</v>
       </c>
       <c r="I114" t="n">
-        <v>825.7225952148438</v>
+        <v>825.72265625</v>
       </c>
       <c r="J114" t="n">
         <v>12.05000019073486</v>
@@ -3770,13 +3770,13 @@
         <v>62.75</v>
       </c>
       <c r="G115" t="n">
-        <v>1173.057373046875</v>
+        <v>1173.057250976562</v>
       </c>
       <c r="H115" t="n">
         <v>95.59999847412109</v>
       </c>
       <c r="I115" t="n">
-        <v>833.4837646484375</v>
+        <v>833.4837036132812</v>
       </c>
       <c r="J115" t="n">
         <v>12.14999961853027</v>
@@ -3799,13 +3799,13 @@
         <v>58.90000152587891</v>
       </c>
       <c r="G116" t="n">
-        <v>1151.793090820312</v>
+        <v>1151.792846679688</v>
       </c>
       <c r="H116" t="n">
         <v>90.65000152587891</v>
       </c>
       <c r="I116" t="n">
-        <v>730.1824340820312</v>
+        <v>730.182373046875</v>
       </c>
       <c r="J116" t="n">
         <v>11.10000038146973</v>
@@ -3834,7 +3834,7 @@
         <v>94.5</v>
       </c>
       <c r="I117" t="n">
-        <v>770.3141479492188</v>
+        <v>770.314208984375</v>
       </c>
       <c r="J117" t="n">
         <v>11.44999980926514</v>
@@ -3857,13 +3857,13 @@
         <v>59.15000152587891</v>
       </c>
       <c r="G118" t="n">
-        <v>1134.831176757812</v>
+        <v>1134.831298828125</v>
       </c>
       <c r="H118" t="n">
         <v>91.19999694824219</v>
       </c>
       <c r="I118" t="n">
-        <v>743.8380126953125</v>
+        <v>743.8380737304688</v>
       </c>
       <c r="J118" t="n">
         <v>11.39999961853027</v>
@@ -3921,7 +3921,7 @@
         <v>90.69999694824219</v>
       </c>
       <c r="I120" t="n">
-        <v>775.570068359375</v>
+        <v>775.5701293945312</v>
       </c>
       <c r="J120" t="n">
         <v>11.85000038146973</v>
@@ -3944,13 +3944,13 @@
         <v>62.84999847412109</v>
       </c>
       <c r="G121" t="n">
-        <v>1128.9658203125</v>
+        <v>1128.965942382812</v>
       </c>
       <c r="H121" t="n">
         <v>93.09999847412109</v>
       </c>
       <c r="I121" t="n">
-        <v>801.5060424804688</v>
+        <v>801.5059814453125</v>
       </c>
       <c r="J121" t="n">
         <v>11.80000019073486</v>
@@ -4031,13 +4031,13 @@
         <v>69</v>
       </c>
       <c r="G124" t="n">
-        <v>1175.616455078125</v>
+        <v>1175.616333007812</v>
       </c>
       <c r="H124" t="n">
         <v>90.59999847412109</v>
       </c>
       <c r="I124" t="n">
-        <v>935.9990844726562</v>
+        <v>935.9990234375</v>
       </c>
       <c r="J124" t="n">
         <v>11.5</v>
@@ -4066,7 +4066,7 @@
         <v>91.09999847412109</v>
       </c>
       <c r="I125" t="n">
-        <v>920.820556640625</v>
+        <v>920.8206176757812</v>
       </c>
       <c r="J125" t="n">
         <v>11.39999961853027</v>
@@ -4089,7 +4089,7 @@
         <v>65.55000305175781</v>
       </c>
       <c r="G126" t="n">
-        <v>1093.207885742188</v>
+        <v>1093.2080078125</v>
       </c>
       <c r="H126" t="n">
         <v>94.5</v>
@@ -4124,7 +4124,7 @@
         <v>93.15000152587891</v>
       </c>
       <c r="I127" t="n">
-        <v>927.0098876953125</v>
+        <v>927.0098266601562</v>
       </c>
       <c r="J127" t="n">
         <v>11.35000038146973</v>
@@ -4153,7 +4153,7 @@
         <v>91.75</v>
       </c>
       <c r="I128" t="n">
-        <v>925.634521484375</v>
+        <v>925.6344604492188</v>
       </c>
       <c r="J128" t="n">
         <v>11.19999980926514</v>
@@ -4176,7 +4176,7 @@
         <v>67.25</v>
       </c>
       <c r="G129" t="n">
-        <v>1081.61328125</v>
+        <v>1081.613159179688</v>
       </c>
       <c r="H129" t="n">
         <v>94.90000152587891</v>
@@ -4205,7 +4205,7 @@
         <v>67.40000152587891</v>
       </c>
       <c r="G130" t="n">
-        <v>1083.108032226562</v>
+        <v>1083.10791015625</v>
       </c>
       <c r="H130" t="n">
         <v>94.80000305175781</v>
@@ -4234,13 +4234,13 @@
         <v>68.30000305175781</v>
       </c>
       <c r="G131" t="n">
-        <v>1097.827758789062</v>
+        <v>1097.82763671875</v>
       </c>
       <c r="H131" t="n">
         <v>101.3499984741211</v>
       </c>
       <c r="I131" t="n">
-        <v>940.5673217773438</v>
+        <v>940.5671997070312</v>
       </c>
       <c r="J131" t="n">
         <v>11.64999961853027</v>
@@ -4263,13 +4263,13 @@
         <v>69.19999694824219</v>
       </c>
       <c r="G132" t="n">
-        <v>1096.26513671875</v>
+        <v>1096.265014648438</v>
       </c>
       <c r="H132" t="n">
         <v>102.5999984741211</v>
       </c>
       <c r="I132" t="n">
-        <v>951.2264404296875</v>
+        <v>951.2265625</v>
       </c>
       <c r="J132" t="n">
         <v>11.5</v>
@@ -4292,13 +4292,13 @@
         <v>70.59999847412109</v>
       </c>
       <c r="G133" t="n">
-        <v>1076.8349609375</v>
+        <v>1076.834838867188</v>
       </c>
       <c r="H133" t="n">
         <v>101.6500015258789</v>
       </c>
       <c r="I133" t="n">
-        <v>945.1846313476562</v>
+        <v>945.1845703125</v>
       </c>
       <c r="J133" t="n">
         <v>11.5</v>
@@ -4350,13 +4350,13 @@
         <v>68.34999847412109</v>
       </c>
       <c r="G135" t="n">
-        <v>1087.818359375</v>
+        <v>1087.818115234375</v>
       </c>
       <c r="H135" t="n">
         <v>99.44999694824219</v>
       </c>
       <c r="I135" t="n">
-        <v>945.33203125</v>
+        <v>945.3319702148438</v>
       </c>
       <c r="J135" t="n">
         <v>11.30000019073486</v>
@@ -4379,7 +4379,7 @@
         <v>68.15000152587891</v>
       </c>
       <c r="G136" t="n">
-        <v>1097.080444335938</v>
+        <v>1097.080322265625</v>
       </c>
       <c r="H136" t="n">
         <v>102.25</v>
@@ -4437,13 +4437,13 @@
         <v>67</v>
       </c>
       <c r="G138" t="n">
-        <v>1133.653564453125</v>
+        <v>1133.653442382812</v>
       </c>
       <c r="H138" t="n">
         <v>104.4000015258789</v>
       </c>
       <c r="I138" t="n">
-        <v>959.67529296875</v>
+        <v>959.6753540039062</v>
       </c>
       <c r="J138" t="n">
         <v>11.85000038146973</v>
@@ -4466,13 +4466,13 @@
         <v>65</v>
       </c>
       <c r="G139" t="n">
-        <v>1126.089599609375</v>
+        <v>1126.089721679688</v>
       </c>
       <c r="H139" t="n">
         <v>105.8000030517578</v>
       </c>
       <c r="I139" t="n">
-        <v>961.9349365234375</v>
+        <v>961.9348754882812</v>
       </c>
       <c r="J139" t="n">
         <v>11.85000038146973</v>
@@ -4524,13 +4524,13 @@
         <v>62.95000076293945</v>
       </c>
       <c r="G141" t="n">
-        <v>1096.242553710938</v>
+        <v>1096.242431640625</v>
       </c>
       <c r="H141" t="n">
         <v>104.25</v>
       </c>
       <c r="I141" t="n">
-        <v>962.13134765625</v>
+        <v>962.1312866210938</v>
       </c>
       <c r="J141" t="n">
         <v>11.55000019073486</v>
@@ -4553,7 +4553,7 @@
         <v>62.90000152587891</v>
       </c>
       <c r="G142" t="n">
-        <v>1096.740844726562</v>
+        <v>1096.74072265625</v>
       </c>
       <c r="H142" t="n">
         <v>113.9000015258789</v>
@@ -4582,13 +4582,13 @@
         <v>64.90000152587891</v>
       </c>
       <c r="G143" t="n">
-        <v>1095.698974609375</v>
+        <v>1095.699096679688</v>
       </c>
       <c r="H143" t="n">
         <v>115.8499984741211</v>
       </c>
       <c r="I143" t="n">
-        <v>945.8231811523438</v>
+        <v>945.8232421875</v>
       </c>
       <c r="J143" t="n">
         <v>11.89999961853027</v>
@@ -4640,13 +4640,13 @@
         <v>64.90000152587891</v>
       </c>
       <c r="G145" t="n">
-        <v>1136.57470703125</v>
+        <v>1136.574951171875</v>
       </c>
       <c r="H145" t="n">
         <v>117.0999984741211</v>
       </c>
       <c r="I145" t="n">
-        <v>964.6856079101562</v>
+        <v>964.6856689453125</v>
       </c>
       <c r="J145" t="n">
         <v>12.39999961853027</v>
@@ -4669,7 +4669,7 @@
         <v>66.94999694824219</v>
       </c>
       <c r="G146" t="n">
-        <v>1166.19580078125</v>
+        <v>1166.195678710938</v>
       </c>
       <c r="H146" t="n">
         <v>123.25</v>
@@ -4733,7 +4733,7 @@
         <v>125.0500030517578</v>
       </c>
       <c r="I148" t="n">
-        <v>966.06103515625</v>
+        <v>966.0609741210938</v>
       </c>
       <c r="J148" t="n">
         <v>13</v>
@@ -4756,13 +4756,13 @@
         <v>67.90000152587891</v>
       </c>
       <c r="G149" t="n">
-        <v>1164.859619140625</v>
+        <v>1164.859497070312</v>
       </c>
       <c r="H149" t="n">
         <v>121.3499984741211</v>
       </c>
       <c r="I149" t="n">
-        <v>952.7492065429688</v>
+        <v>952.749267578125</v>
       </c>
       <c r="J149" t="n">
         <v>13.19999980926514</v>
@@ -4791,7 +4791,7 @@
         <v>120</v>
       </c>
       <c r="I150" t="n">
-        <v>942.0408325195312</v>
+        <v>942.0408935546875</v>
       </c>
       <c r="J150" t="n">
         <v>13.14999961853027</v>
@@ -4872,7 +4872,7 @@
         <v>67.19999694824219</v>
       </c>
       <c r="G153" t="n">
-        <v>1173.555541992188</v>
+        <v>1173.5556640625</v>
       </c>
       <c r="H153" t="n">
         <v>115.3499984741211</v>
@@ -4901,13 +4901,13 @@
         <v>68.34999847412109</v>
       </c>
       <c r="G154" t="n">
-        <v>1192.532836914062</v>
+        <v>1192.53271484375</v>
       </c>
       <c r="H154" t="n">
         <v>115.1500015258789</v>
       </c>
       <c r="I154" t="n">
-        <v>954.0263671875</v>
+        <v>954.0264282226562</v>
       </c>
       <c r="J154" t="n">
         <v>13.39999961853027</v>
@@ -4936,7 +4936,7 @@
         <v>116.5500030517578</v>
       </c>
       <c r="I155" t="n">
-        <v>979.5201416015625</v>
+        <v>979.5202026367188</v>
       </c>
       <c r="J155" t="n">
         <v>13.39999961853027</v>
@@ -4959,7 +4959,7 @@
         <v>72.55000305175781</v>
       </c>
       <c r="G156" t="n">
-        <v>1207.094116210938</v>
+        <v>1207.094360351562</v>
       </c>
       <c r="H156" t="n">
         <v>121.8000030517578</v>
@@ -4988,7 +4988,7 @@
         <v>71.44999694824219</v>
       </c>
       <c r="G157" t="n">
-        <v>1209.283325195312</v>
+        <v>1209.283447265625</v>
       </c>
       <c r="H157" t="n">
         <v>129.8999938964844</v>
@@ -5023,7 +5023,7 @@
         <v>135.6000061035156</v>
       </c>
       <c r="I158" t="n">
-        <v>1000.396484375</v>
+        <v>1000.396545410156</v>
       </c>
       <c r="J158" t="n">
         <v>14.94999980926514</v>
@@ -5075,7 +5075,7 @@
         <v>72.25</v>
       </c>
       <c r="G160" t="n">
-        <v>1202.694580078125</v>
+        <v>1202.694458007812</v>
       </c>
       <c r="H160" t="n">
         <v>138.6999969482422</v>
@@ -5104,13 +5104,13 @@
         <v>74.15000152587891</v>
       </c>
       <c r="G161" t="n">
-        <v>1199.490844726562</v>
+        <v>1199.491088867188</v>
       </c>
       <c r="H161" t="n">
         <v>139.6999969482422</v>
       </c>
       <c r="I161" t="n">
-        <v>1007.224426269531</v>
+        <v>1007.224365234375</v>
       </c>
       <c r="J161" t="n">
         <v>15.30000019073486</v>
@@ -5139,7 +5139,7 @@
         <v>139.75</v>
       </c>
       <c r="I162" t="n">
-        <v>1002.8525390625</v>
+        <v>1002.852600097656</v>
       </c>
       <c r="J162" t="n">
         <v>15.05000019073486</v>
@@ -5168,7 +5168,7 @@
         <v>157.3500061035156</v>
       </c>
       <c r="I163" t="n">
-        <v>997.10546875</v>
+        <v>997.1054077148438</v>
       </c>
       <c r="J163" t="n">
         <v>16.25</v>
@@ -5249,13 +5249,13 @@
         <v>73.30000305175781</v>
       </c>
       <c r="G166" t="n">
-        <v>1163.434814453125</v>
+        <v>1163.434692382812</v>
       </c>
       <c r="H166" t="n">
         <v>193.8500061035156</v>
       </c>
       <c r="I166" t="n">
-        <v>1039.644165039062</v>
+        <v>1039.644287109375</v>
       </c>
       <c r="J166" t="n">
         <v>20.14999961853027</v>
@@ -5284,7 +5284,7 @@
         <v>179.1499938964844</v>
       </c>
       <c r="I167" t="n">
-        <v>1082.084594726562</v>
+        <v>1082.08447265625</v>
       </c>
       <c r="J167" t="n">
         <v>21.20000076293945</v>
@@ -5307,13 +5307,13 @@
         <v>75.59999847412109</v>
       </c>
       <c r="G168" t="n">
-        <v>1167.7060546875</v>
+        <v>1167.705932617188</v>
       </c>
       <c r="H168" t="n">
         <v>182.6999969482422</v>
       </c>
       <c r="I168" t="n">
-        <v>1193.93310546875</v>
+        <v>1193.932983398438</v>
       </c>
       <c r="J168" t="n">
         <v>23.29999923706055</v>
@@ -5336,7 +5336,7 @@
         <v>73.94999694824219</v>
       </c>
       <c r="G169" t="n">
-        <v>1179.997314453125</v>
+        <v>1179.997436523438</v>
       </c>
       <c r="H169" t="n">
         <v>178.75</v>
@@ -5394,7 +5394,7 @@
         <v>73.65000152587891</v>
       </c>
       <c r="G171" t="n">
-        <v>1174.794555664062</v>
+        <v>1174.79443359375</v>
       </c>
       <c r="H171" t="n">
         <v>180.3000030517578</v>
@@ -5429,7 +5429,7 @@
         <v>162.4499969482422</v>
       </c>
       <c r="I172" t="n">
-        <v>1153.801147460938</v>
+        <v>1153.801025390625</v>
       </c>
       <c r="J172" t="n">
         <v>19.20000076293945</v>
@@ -5458,7 +5458,7 @@
         <v>174.1999969482422</v>
       </c>
       <c r="I173" t="n">
-        <v>1154.341430664062</v>
+        <v>1154.341552734375</v>
       </c>
       <c r="J173" t="n">
         <v>21.10000038146973</v>
@@ -5481,7 +5481,7 @@
         <v>74.15000152587891</v>
       </c>
       <c r="G174" t="n">
-        <v>1190.402954101562</v>
+        <v>1190.403076171875</v>
       </c>
       <c r="H174" t="n">
         <v>165.5</v>
@@ -5510,13 +5510,13 @@
         <v>73.25</v>
       </c>
       <c r="G175" t="n">
-        <v>1176.135009765625</v>
+        <v>1176.134887695312</v>
       </c>
       <c r="H175" t="n">
         <v>157.4499969482422</v>
       </c>
       <c r="I175" t="n">
-        <v>1151.19775390625</v>
+        <v>1151.197875976562</v>
       </c>
       <c r="J175" t="n">
         <v>19.04999923706055</v>
@@ -5545,7 +5545,7 @@
         <v>154.4499969482422</v>
       </c>
       <c r="I176" t="n">
-        <v>1170.551391601562</v>
+        <v>1170.55126953125</v>
       </c>
       <c r="J176" t="n">
         <v>18.10000038146973</v>
@@ -5568,13 +5568,13 @@
         <v>68.65000152587891</v>
       </c>
       <c r="G177" t="n">
-        <v>1135.625610351562</v>
+        <v>1135.625732421875</v>
       </c>
       <c r="H177" t="n">
         <v>156.3500061035156</v>
       </c>
       <c r="I177" t="n">
-        <v>1119.121826171875</v>
+        <v>1119.121704101562</v>
       </c>
       <c r="J177" t="n">
         <v>18.45000076293945</v>
@@ -5597,7 +5597,7 @@
         <v>67.05000305175781</v>
       </c>
       <c r="G178" t="n">
-        <v>1137.102416992188</v>
+        <v>1137.1025390625</v>
       </c>
       <c r="H178" t="n">
         <v>151.8000030517578</v>
@@ -5632,7 +5632,7 @@
         <v>154.4499969482422</v>
       </c>
       <c r="I179" t="n">
-        <v>1188.16064453125</v>
+        <v>1188.160766601562</v>
       </c>
       <c r="J179" t="n">
         <v>18.20000076293945</v>
@@ -5684,7 +5684,7 @@
         <v>70</v>
       </c>
       <c r="G181" t="n">
-        <v>1129.673095703125</v>
+        <v>1129.672973632812</v>
       </c>
       <c r="H181" t="n">
         <v>146.1499938964844</v>
@@ -5713,13 +5713,13 @@
         <v>67.69999694824219</v>
       </c>
       <c r="G182" t="n">
-        <v>1108.498291015625</v>
+        <v>1108.498168945312</v>
       </c>
       <c r="H182" t="n">
         <v>144.1499938964844</v>
       </c>
       <c r="I182" t="n">
-        <v>1157.628173828125</v>
+        <v>1157.628051757812</v>
       </c>
       <c r="J182" t="n">
         <v>16.89999961853027</v>
@@ -5742,13 +5742,13 @@
         <v>64</v>
       </c>
       <c r="G183" t="n">
-        <v>1080.257568359375</v>
+        <v>1080.257690429688</v>
       </c>
       <c r="H183" t="n">
         <v>137.1999969482422</v>
       </c>
       <c r="I183" t="n">
-        <v>1051.699951171875</v>
+        <v>1051.699829101562</v>
       </c>
       <c r="J183" t="n">
         <v>16.35000038146973</v>
@@ -5771,13 +5771,13 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G184" t="n">
-        <v>1088.845703125</v>
+        <v>1088.845581054688</v>
       </c>
       <c r="H184" t="n">
         <v>138.3500061035156</v>
       </c>
       <c r="I184" t="n">
-        <v>1044.90380859375</v>
+        <v>1044.903930664062</v>
       </c>
       <c r="J184" t="n">
         <v>16.20000076293945</v>
@@ -5800,7 +5800,7 @@
         <v>61.70000076293945</v>
       </c>
       <c r="G185" t="n">
-        <v>1059.855224609375</v>
+        <v>1059.855102539062</v>
       </c>
       <c r="H185" t="n">
         <v>136.3500061035156</v>
@@ -5858,13 +5858,13 @@
         <v>64.59999847412109</v>
       </c>
       <c r="G187" t="n">
-        <v>1080.439331054688</v>
+        <v>1080.439453125</v>
       </c>
       <c r="H187" t="n">
         <v>136.6999969482422</v>
       </c>
       <c r="I187" t="n">
-        <v>1060.416381835938</v>
+        <v>1060.41650390625</v>
       </c>
       <c r="J187" t="n">
         <v>16.39999961853027</v>
@@ -5945,13 +5945,13 @@
         <v>67.30000305175781</v>
       </c>
       <c r="G190" t="n">
-        <v>1100.591674804688</v>
+        <v>1100.591552734375</v>
       </c>
       <c r="H190" t="n">
         <v>144.3999938964844</v>
       </c>
       <c r="I190" t="n">
-        <v>1120.152099609375</v>
+        <v>1120.15185546875</v>
       </c>
       <c r="J190" t="n">
         <v>16.75</v>
@@ -5974,13 +5974,13 @@
         <v>68.19999694824219</v>
       </c>
       <c r="G191" t="n">
-        <v>1105.249389648438</v>
+        <v>1105.249267578125</v>
       </c>
       <c r="H191" t="n">
         <v>151.6000061035156</v>
       </c>
       <c r="I191" t="n">
-        <v>1158.268310546875</v>
+        <v>1158.268432617188</v>
       </c>
       <c r="J191" t="n">
         <v>17.54999923706055</v>
@@ -6003,7 +6003,7 @@
         <v>67.25</v>
       </c>
       <c r="G192" t="n">
-        <v>1093.185302734375</v>
+        <v>1093.185180664062</v>
       </c>
       <c r="H192" t="n">
         <v>157.6999969482422</v>
@@ -6038,7 +6038,7 @@
         <v>149.8500061035156</v>
       </c>
       <c r="I193" t="n">
-        <v>1184.811889648438</v>
+        <v>1184.81201171875</v>
       </c>
       <c r="J193" t="n">
         <v>16.89999961853027</v>
@@ -6061,13 +6061,13 @@
         <v>68.69999694824219</v>
       </c>
       <c r="G194" t="n">
-        <v>1079.30322265625</v>
+        <v>1079.303344726562</v>
       </c>
       <c r="H194" t="n">
         <v>142.6999969482422</v>
       </c>
       <c r="I194" t="n">
-        <v>1128.179077148438</v>
+        <v>1128.178955078125</v>
       </c>
       <c r="J194" t="n">
         <v>16.35000038146973</v>
@@ -6090,7 +6090,7 @@
         <v>67.59999847412109</v>
       </c>
       <c r="G195" t="n">
-        <v>1082.734130859375</v>
+        <v>1082.734008789062</v>
       </c>
       <c r="H195" t="n">
         <v>142.3500061035156</v>
@@ -6148,7 +6148,7 @@
         <v>66.40000152587891</v>
       </c>
       <c r="G197" t="n">
-        <v>1094.525634765625</v>
+        <v>1094.525512695312</v>
       </c>
       <c r="H197" t="n">
         <v>138.6999969482422</v>
@@ -6183,7 +6183,7 @@
         <v>143.6999969482422</v>
       </c>
       <c r="I198" t="n">
-        <v>1130.887573242188</v>
+        <v>1130.887451171875</v>
       </c>
       <c r="J198" t="n">
         <v>16.60000038146973</v>
@@ -6206,13 +6206,13 @@
         <v>65.59999847412109</v>
       </c>
       <c r="G199" t="n">
-        <v>1133.21728515625</v>
+        <v>1133.217407226562</v>
       </c>
       <c r="H199" t="n">
         <v>141.3500061035156</v>
       </c>
       <c r="I199" t="n">
-        <v>1121.087646484375</v>
+        <v>1121.087524414062</v>
       </c>
       <c r="J199" t="n">
         <v>16.35000038146973</v>
@@ -6241,7 +6241,7 @@
         <v>139.1000061035156</v>
       </c>
       <c r="I200" t="n">
-        <v>1117.492553710938</v>
+        <v>1117.492431640625</v>
       </c>
       <c r="J200" t="n">
         <v>16.10000038146973</v>
@@ -6264,7 +6264,7 @@
         <v>63.70000076293945</v>
       </c>
       <c r="G201" t="n">
-        <v>1123.084228515625</v>
+        <v>1123.084350585938</v>
       </c>
       <c r="H201" t="n">
         <v>139.1499938964844</v>
@@ -6328,7 +6328,7 @@
         <v>141.6000061035156</v>
       </c>
       <c r="I203" t="n">
-        <v>1089.7177734375</v>
+        <v>1089.717895507812</v>
       </c>
       <c r="J203" t="n">
         <v>16.29999923706055</v>
@@ -6386,7 +6386,7 @@
         <v>141.8999938964844</v>
       </c>
       <c r="I205" t="n">
-        <v>1081.690673828125</v>
+        <v>1081.690551757812</v>
       </c>
       <c r="J205" t="n">
         <v>16</v>
@@ -6415,7 +6415,7 @@
         <v>141.4499969482422</v>
       </c>
       <c r="I206" t="n">
-        <v>1081.542846679688</v>
+        <v>1081.54296875</v>
       </c>
       <c r="J206" t="n">
         <v>16.10000038146973</v>
@@ -6496,13 +6496,13 @@
         <v>62.75</v>
       </c>
       <c r="G209" t="n">
-        <v>1161.049072265625</v>
+        <v>1161.049194335938</v>
       </c>
       <c r="H209" t="n">
         <v>140.1499938964844</v>
       </c>
       <c r="I209" t="n">
-        <v>1067.310913085938</v>
+        <v>1067.310791015625</v>
       </c>
       <c r="J209" t="n">
         <v>16</v>
@@ -6560,7 +6560,7 @@
         <v>152.9499969482422</v>
       </c>
       <c r="I211" t="n">
-        <v>1081.936889648438</v>
+        <v>1081.93701171875</v>
       </c>
       <c r="J211" t="n">
         <v>16.85000038146973</v>
@@ -6583,7 +6583,7 @@
         <v>65.25</v>
       </c>
       <c r="G212" t="n">
-        <v>1183.246215820312</v>
+        <v>1183.246337890625</v>
       </c>
       <c r="H212" t="n">
         <v>146.6499938964844</v>
@@ -6618,7 +6618,7 @@
         <v>142.8500061035156</v>
       </c>
       <c r="I213" t="n">
-        <v>1053.669677734375</v>
+        <v>1053.669799804688</v>
       </c>
       <c r="J213" t="n">
         <v>16.10000038146973</v>
@@ -6670,7 +6670,7 @@
         <v>64.05000305175781</v>
       </c>
       <c r="G215" t="n">
-        <v>1190.085205078125</v>
+        <v>1190.085083007812</v>
       </c>
       <c r="H215" t="n">
         <v>153.3999938964844</v>
@@ -6728,7 +6728,7 @@
         <v>62.54999923706055</v>
       </c>
       <c r="G217" t="n">
-        <v>1177.952758789062</v>
+        <v>1177.95263671875</v>
       </c>
       <c r="H217" t="n">
         <v>148.6499938964844</v>
@@ -6757,7 +6757,7 @@
         <v>62.29999923706055</v>
       </c>
       <c r="G218" t="n">
-        <v>1180.997192382812</v>
+        <v>1180.9970703125</v>
       </c>
       <c r="H218" t="n">
         <v>146.0500030517578</v>
@@ -6844,7 +6844,7 @@
         <v>60.84999847412109</v>
       </c>
       <c r="G221" t="n">
-        <v>1165.547607421875</v>
+        <v>1165.547485351562</v>
       </c>
       <c r="H221" t="n">
         <v>141.3000030517578</v>
@@ -6902,7 +6902,7 @@
         <v>60.40000152587891</v>
       </c>
       <c r="G223" t="n">
-        <v>1171.932006835938</v>
+        <v>1171.931884765625</v>
       </c>
       <c r="H223" t="n">
         <v>147.0500030517578</v>
@@ -6931,13 +6931,13 @@
         <v>62.95000076293945</v>
       </c>
       <c r="G224" t="n">
-        <v>1189.426147460938</v>
+        <v>1189.426025390625</v>
       </c>
       <c r="H224" t="n">
         <v>154.3000030517578</v>
       </c>
       <c r="I224" t="n">
-        <v>1008.067810058594</v>
+        <v>1008.067749023438</v>
       </c>
       <c r="J224" t="n">
         <v>16</v>
@@ -7024,7 +7024,7 @@
         <v>157.6999969482422</v>
       </c>
       <c r="I227" t="n">
-        <v>1039.289672851562</v>
+        <v>1039.289794921875</v>
       </c>
       <c r="J227" t="n">
         <v>16.04999923706055</v>
@@ -7047,13 +7047,13 @@
         <v>73.40000152587891</v>
       </c>
       <c r="G228" t="n">
-        <v>1237.455810546875</v>
+        <v>1237.455932617188</v>
       </c>
       <c r="H228" t="n">
         <v>156.1000061035156</v>
       </c>
       <c r="I228" t="n">
-        <v>1040.225463867188</v>
+        <v>1040.2255859375</v>
       </c>
       <c r="J228" t="n">
         <v>16</v>
@@ -7082,7 +7082,7 @@
         <v>162.8999938964844</v>
       </c>
       <c r="I229" t="n">
-        <v>1033.67578125</v>
+        <v>1033.675903320312</v>
       </c>
       <c r="J229" t="n">
         <v>16.79999923706055</v>
@@ -7111,7 +7111,7 @@
         <v>157.8999938964844</v>
       </c>
       <c r="I230" t="n">
-        <v>1054.162109375</v>
+        <v>1054.162231445312</v>
       </c>
       <c r="J230" t="n">
         <v>16.04999923706055</v>
@@ -7140,7 +7140,7 @@
         <v>156.3999938964844</v>
       </c>
       <c r="I231" t="n">
-        <v>1050.419555664062</v>
+        <v>1050.41943359375</v>
       </c>
       <c r="J231" t="n">
         <v>15.85000038146973</v>
@@ -7192,13 +7192,13 @@
         <v>74.25</v>
       </c>
       <c r="G233" t="n">
-        <v>1203.807739257812</v>
+        <v>1203.807861328125</v>
       </c>
       <c r="H233" t="n">
         <v>154.0500030517578</v>
       </c>
       <c r="I233" t="n">
-        <v>1031.311889648438</v>
+        <v>1031.31201171875</v>
       </c>
       <c r="J233" t="n">
         <v>15.85000038146973</v>
@@ -7256,7 +7256,7 @@
         <v>161.8000030517578</v>
       </c>
       <c r="I235" t="n">
-        <v>1015.454711914062</v>
+        <v>1015.454772949219</v>
       </c>
       <c r="J235" t="n">
         <v>15.94999980926514</v>
@@ -7314,7 +7314,7 @@
         <v>156.6499938964844</v>
       </c>
       <c r="I237" t="n">
-        <v>1012.943054199219</v>
+        <v>1012.942993164062</v>
       </c>
       <c r="J237" t="n">
         <v>16.45000076293945</v>
@@ -7337,13 +7337,13 @@
         <v>73.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1171.591186523438</v>
+        <v>1171.591064453125</v>
       </c>
       <c r="H238" t="n">
         <v>148.8999938964844</v>
       </c>
       <c r="I238" t="n">
-        <v>1001.271850585938</v>
+        <v>1001.271789550781</v>
       </c>
       <c r="J238" t="n">
         <v>15.89999961853027</v>
@@ -7424,13 +7424,13 @@
         <v>71.34999847412109</v>
       </c>
       <c r="G241" t="n">
-        <v>1191.334594726562</v>
+        <v>1191.334716796875</v>
       </c>
       <c r="H241" t="n">
         <v>149.8000030517578</v>
       </c>
       <c r="I241" t="n">
-        <v>982.2135620117188</v>
+        <v>982.213623046875</v>
       </c>
       <c r="J241" t="n">
         <v>15.75</v>
@@ -7459,7 +7459,7 @@
         <v>142.5500030517578</v>
       </c>
       <c r="I242" t="n">
-        <v>939.5665283203125</v>
+        <v>939.5664672851562</v>
       </c>
       <c r="J242" t="n">
         <v>15</v>
@@ -7488,7 +7488,7 @@
         <v>135.4499969482422</v>
       </c>
       <c r="I243" t="n">
-        <v>898.8892211914062</v>
+        <v>898.88916015625</v>
       </c>
       <c r="J243" t="n">
         <v>14.25</v>
@@ -7540,13 +7540,13 @@
         <v>62.90000152587891</v>
       </c>
       <c r="G245" t="n">
-        <v>1146.917358398438</v>
+        <v>1146.91748046875</v>
       </c>
       <c r="H245" t="n">
         <v>128.1999969482422</v>
       </c>
       <c r="I245" t="n">
-        <v>858.0149536132812</v>
+        <v>858.014892578125</v>
       </c>
       <c r="J245" t="n">
         <v>14.14999961853027</v>
@@ -7569,7 +7569,7 @@
         <v>65.80000305175781</v>
       </c>
       <c r="G246" t="n">
-        <v>1156.30078125</v>
+        <v>1156.300659179688</v>
       </c>
       <c r="H246" t="n">
         <v>134.6000061035156</v>
@@ -7598,7 +7598,7 @@
         <v>67.05000305175781</v>
       </c>
       <c r="G247" t="n">
-        <v>1156.187133789062</v>
+        <v>1156.187255859375</v>
       </c>
       <c r="H247" t="n">
         <v>136.5</v>
@@ -7685,7 +7685,7 @@
         <v>67.55000305175781</v>
       </c>
       <c r="G250" t="n">
-        <v>1170.477905273438</v>
+        <v>1170.477783203125</v>
       </c>
       <c r="H250" t="n">
         <v>137.8500061035156</v>
@@ -7749,7 +7749,7 @@
         <v>136.4499969482422</v>
       </c>
       <c r="I252" t="n">
-        <v>901.9915771484375</v>
+        <v>901.9916381835938</v>
       </c>
       <c r="J252" t="n">
         <v>14.44999980926514</v>
@@ -7772,7 +7772,7 @@
         <v>65.75</v>
       </c>
       <c r="G253" t="n">
-        <v>1142.373413085938</v>
+        <v>1142.37353515625</v>
       </c>
       <c r="H253" t="n">
         <v>133.75</v>
@@ -7801,7 +7801,7 @@
         <v>65.40000152587891</v>
       </c>
       <c r="G254" t="n">
-        <v>1152.75634765625</v>
+        <v>1152.756469726562</v>
       </c>
       <c r="H254" t="n">
         <v>130.1999969482422</v>
@@ -7859,7 +7859,7 @@
         <v>63.75</v>
       </c>
       <c r="G256" t="n">
-        <v>1162.52587890625</v>
+        <v>1162.526000976562</v>
       </c>
       <c r="H256" t="n">
         <v>133</v>
@@ -7917,13 +7917,13 @@
         <v>63.59999847412109</v>
       </c>
       <c r="G258" t="n">
-        <v>1123.084228515625</v>
+        <v>1123.084350585938</v>
       </c>
       <c r="H258" t="n">
         <v>132.3000030517578</v>
       </c>
       <c r="I258" t="n">
-        <v>899.0369262695312</v>
+        <v>899.036865234375</v>
       </c>
       <c r="J258" t="n">
         <v>13.94999980926514</v>
@@ -7952,7 +7952,7 @@
         <v>132.6499938964844</v>
       </c>
       <c r="I259" t="n">
-        <v>899.3323364257812</v>
+        <v>899.3323974609375</v>
       </c>
       <c r="J259" t="n">
         <v>14.14999961853027</v>
@@ -8004,13 +8004,13 @@
         <v>63.34999847412109</v>
       </c>
       <c r="G261" t="n">
-        <v>1126.356079101562</v>
+        <v>1126.35595703125</v>
       </c>
       <c r="H261" t="n">
         <v>141.3000030517578</v>
       </c>
       <c r="I261" t="n">
-        <v>883.5242919921875</v>
+        <v>883.5243530273438</v>
       </c>
       <c r="J261" t="n">
         <v>14.14999961853027</v>
@@ -8062,13 +8062,13 @@
         <v>62.25</v>
       </c>
       <c r="G263" t="n">
-        <v>1123.288818359375</v>
+        <v>1123.288940429688</v>
       </c>
       <c r="H263" t="n">
         <v>137.5</v>
       </c>
       <c r="I263" t="n">
-        <v>901.8439331054688</v>
+        <v>901.8438720703125</v>
       </c>
       <c r="J263" t="n">
         <v>14</v>
@@ -8091,13 +8091,13 @@
         <v>61.34999847412109</v>
       </c>
       <c r="G264" t="n">
-        <v>1109.929565429688</v>
+        <v>1109.9296875</v>
       </c>
       <c r="H264" t="n">
         <v>136.25</v>
       </c>
       <c r="I264" t="n">
-        <v>895.3926391601562</v>
+        <v>895.3927001953125</v>
       </c>
       <c r="J264" t="n">
         <v>13.85000038146973</v>
@@ -8120,7 +8120,7 @@
         <v>61.5</v>
       </c>
       <c r="G265" t="n">
-        <v>1104.31787109375</v>
+        <v>1104.317749023438</v>
       </c>
       <c r="H265" t="n">
         <v>133.6999969482422</v>
@@ -8178,13 +8178,13 @@
         <v>60.90000152587891</v>
       </c>
       <c r="G267" t="n">
-        <v>1082.620239257812</v>
+        <v>1082.620361328125</v>
       </c>
       <c r="H267" t="n">
         <v>128.1499938964844</v>
       </c>
       <c r="I267" t="n">
-        <v>869.78466796875</v>
+        <v>869.7847290039062</v>
       </c>
       <c r="J267" t="n">
         <v>12.94999980926514</v>
@@ -8207,7 +8207,7 @@
         <v>59.04999923706055</v>
       </c>
       <c r="G268" t="n">
-        <v>1062.081787109375</v>
+        <v>1062.081665039062</v>
       </c>
       <c r="H268" t="n">
         <v>121.9000015258789</v>
@@ -8236,7 +8236,7 @@
         <v>58.45000076293945</v>
       </c>
       <c r="G269" t="n">
-        <v>1072.26025390625</v>
+        <v>1072.260375976562</v>
       </c>
       <c r="H269" t="n">
         <v>119.1500015258789</v>
@@ -8271,7 +8271,7 @@
         <v>125.0999984741211</v>
       </c>
       <c r="I270" t="n">
-        <v>856.8822631835938</v>
+        <v>856.8822021484375</v>
       </c>
       <c r="J270" t="n">
         <v>12.75</v>
@@ -8294,13 +8294,13 @@
         <v>59.25</v>
       </c>
       <c r="G271" t="n">
-        <v>1063.240600585938</v>
+        <v>1063.240478515625</v>
       </c>
       <c r="H271" t="n">
         <v>122.25</v>
       </c>
       <c r="I271" t="n">
-        <v>830.1415405273438</v>
+        <v>830.1414794921875</v>
       </c>
       <c r="J271" t="n">
         <v>12.25</v>
@@ -8323,7 +8323,7 @@
         <v>59.20000076293945</v>
       </c>
       <c r="G272" t="n">
-        <v>1057.356079101562</v>
+        <v>1057.35595703125</v>
       </c>
       <c r="H272" t="n">
         <v>121.3000030517578</v>
@@ -8352,13 +8352,13 @@
         <v>59.34999847412109</v>
       </c>
       <c r="G273" t="n">
-        <v>1058.287475585938</v>
+        <v>1058.28759765625</v>
       </c>
       <c r="H273" t="n">
         <v>121.4000015258789</v>
       </c>
       <c r="I273" t="n">
-        <v>817.8793334960938</v>
+        <v>817.87939453125</v>
       </c>
       <c r="J273" t="n">
         <v>11.75</v>
@@ -8381,7 +8381,7 @@
         <v>59.70000076293945</v>
       </c>
       <c r="G274" t="n">
-        <v>1050.312744140625</v>
+        <v>1050.312866210938</v>
       </c>
       <c r="H274" t="n">
         <v>124.4499969482422</v>
@@ -8445,7 +8445,7 @@
         <v>123.5500030517578</v>
       </c>
       <c r="I276" t="n">
-        <v>842.8471069335938</v>
+        <v>842.8470458984375</v>
       </c>
       <c r="J276" t="n">
         <v>11.69999980926514</v>
@@ -8497,13 +8497,13 @@
         <v>60.84999847412109</v>
       </c>
       <c r="G278" t="n">
-        <v>1061.763671875</v>
+        <v>1061.763793945312</v>
       </c>
       <c r="H278" t="n">
         <v>130.9499969482422</v>
       </c>
       <c r="I278" t="n">
-        <v>833.8350219726562</v>
+        <v>833.8350830078125</v>
       </c>
       <c r="J278" t="n">
         <v>11.64999961853027</v>
@@ -8526,7 +8526,7 @@
         <v>60.29999923706055</v>
       </c>
       <c r="G279" t="n">
-        <v>1055.720336914062</v>
+        <v>1055.72021484375</v>
       </c>
       <c r="H279" t="n">
         <v>127.5500030517578</v>
@@ -8590,7 +8590,7 @@
         <v>128.4499969482422</v>
       </c>
       <c r="I281" t="n">
-        <v>837.183837890625</v>
+        <v>837.1837768554688</v>
       </c>
       <c r="J281" t="n">
         <v>11.10000038146973</v>
@@ -8613,7 +8613,7 @@
         <v>60.40000152587891</v>
       </c>
       <c r="G282" t="n">
-        <v>1104.204223632812</v>
+        <v>1104.204345703125</v>
       </c>
       <c r="H282" t="n">
         <v>129.5500030517578</v>
@@ -8648,7 +8648,7 @@
         <v>127.0500030517578</v>
       </c>
       <c r="I283" t="n">
-        <v>853.6812133789062</v>
+        <v>853.6812744140625</v>
       </c>
       <c r="J283" t="n">
         <v>11.05000019073486</v>
@@ -8671,7 +8671,7 @@
         <v>60.45000076293945</v>
       </c>
       <c r="G284" t="n">
-        <v>1097.093017578125</v>
+        <v>1097.092895507812</v>
       </c>
       <c r="H284" t="n">
         <v>123.6500015258789</v>
@@ -8700,13 +8700,13 @@
         <v>60.40000152587891</v>
       </c>
       <c r="G285" t="n">
-        <v>1106.044677734375</v>
+        <v>1106.044555664062</v>
       </c>
       <c r="H285" t="n">
         <v>120.8000030517578</v>
       </c>
       <c r="I285" t="n">
-        <v>833.342529296875</v>
+        <v>833.3425903320312</v>
       </c>
       <c r="J285" t="n">
         <v>10.60000038146973</v>
@@ -8729,13 +8729,13 @@
         <v>59.34999847412109</v>
       </c>
       <c r="G286" t="n">
-        <v>1080.961791992188</v>
+        <v>1080.9619140625</v>
       </c>
       <c r="H286" t="n">
         <v>118.5500030517578</v>
       </c>
       <c r="I286" t="n">
-        <v>818.1256103515625</v>
+        <v>818.1255493164062</v>
       </c>
       <c r="J286" t="n">
         <v>10.39999961853027</v>
@@ -8787,13 +8787,13 @@
         <v>58.5</v>
       </c>
       <c r="G288" t="n">
-        <v>1083.142822265625</v>
+        <v>1083.142944335938</v>
       </c>
       <c r="H288" t="n">
         <v>126.9499969482422</v>
       </c>
       <c r="I288" t="n">
-        <v>802.1698608398438</v>
+        <v>802.1697998046875</v>
       </c>
       <c r="J288" t="n">
         <v>10.10000038146973</v>
@@ -8851,7 +8851,7 @@
         <v>130.6999969482422</v>
       </c>
       <c r="I290" t="n">
-        <v>789.8582763671875</v>
+        <v>789.8583374023438</v>
       </c>
       <c r="J290" t="n">
         <v>9.800000190734863</v>
@@ -8874,13 +8874,13 @@
         <v>58.90000152587891</v>
       </c>
       <c r="G291" t="n">
-        <v>1065.05810546875</v>
+        <v>1065.057861328125</v>
       </c>
       <c r="H291" t="n">
         <v>135.6999969482422</v>
       </c>
       <c r="I291" t="n">
-        <v>827.8270263671875</v>
+        <v>827.8270874023438</v>
       </c>
       <c r="J291" t="n">
         <v>10</v>
@@ -8903,7 +8903,7 @@
         <v>58.54999923706055</v>
       </c>
       <c r="G292" t="n">
-        <v>1056.947021484375</v>
+        <v>1056.947143554688</v>
       </c>
       <c r="H292" t="n">
         <v>135.8000030517578</v>
@@ -8932,7 +8932,7 @@
         <v>59.29999923706055</v>
       </c>
       <c r="G293" t="n">
-        <v>1083.91552734375</v>
+        <v>1083.915405273438</v>
       </c>
       <c r="H293" t="n">
         <v>143.25</v>
@@ -8990,13 +8990,13 @@
         <v>59.15000152587891</v>
       </c>
       <c r="G295" t="n">
-        <v>1098.433471679688</v>
+        <v>1098.433349609375</v>
       </c>
       <c r="H295" t="n">
         <v>153.8000030517578</v>
       </c>
       <c r="I295" t="n">
-        <v>869.341552734375</v>
+        <v>869.3414916992188</v>
       </c>
       <c r="J295" t="n">
         <v>11.69999980926514</v>
@@ -9019,13 +9019,13 @@
         <v>58.95000076293945</v>
       </c>
       <c r="G296" t="n">
-        <v>1072.033081054688</v>
+        <v>1072.032958984375</v>
       </c>
       <c r="H296" t="n">
         <v>146.3500061035156</v>
       </c>
       <c r="I296" t="n">
-        <v>854.5184326171875</v>
+        <v>854.5183715820312</v>
       </c>
       <c r="J296" t="n">
         <v>11.19999980926514</v>
@@ -9048,13 +9048,13 @@
         <v>58.25</v>
       </c>
       <c r="G297" t="n">
-        <v>1055.4248046875</v>
+        <v>1055.424926757812</v>
       </c>
       <c r="H297" t="n">
         <v>147.25</v>
       </c>
       <c r="I297" t="n">
-        <v>835.9033813476562</v>
+        <v>835.9034423828125</v>
       </c>
       <c r="J297" t="n">
         <v>11.44999980926514</v>
@@ -9077,13 +9077,13 @@
         <v>55.40000152587891</v>
       </c>
       <c r="G298" t="n">
-        <v>1038.067016601562</v>
+        <v>1038.06689453125</v>
       </c>
       <c r="H298" t="n">
         <v>139.6499938964844</v>
       </c>
       <c r="I298" t="n">
-        <v>793.7979736328125</v>
+        <v>793.7980346679688</v>
       </c>
       <c r="J298" t="n">
         <v>10.75</v>
@@ -9106,13 +9106,13 @@
         <v>53.70000076293945</v>
       </c>
       <c r="G299" t="n">
-        <v>1034.181762695312</v>
+        <v>1034.181884765625</v>
       </c>
       <c r="H299" t="n">
         <v>144.3000030517578</v>
       </c>
       <c r="I299" t="n">
-        <v>785.1306762695312</v>
+        <v>785.130615234375</v>
       </c>
       <c r="J299" t="n">
         <v>10.69999980926514</v>
@@ -9135,7 +9135,7 @@
         <v>50.95000076293945</v>
       </c>
       <c r="G300" t="n">
-        <v>1016.505859375</v>
+        <v>1016.505920410156</v>
       </c>
       <c r="H300" t="n">
         <v>146.6999969482422</v>
@@ -9164,13 +9164,13 @@
         <v>54.70000076293945</v>
       </c>
       <c r="G301" t="n">
-        <v>1011.439270019531</v>
+        <v>1011.439331054688</v>
       </c>
       <c r="H301" t="n">
         <v>141.25</v>
       </c>
       <c r="I301" t="n">
-        <v>772.7698974609375</v>
+        <v>772.7698364257812</v>
       </c>
       <c r="J301" t="n">
         <v>10.55000019073486</v>
@@ -9222,7 +9222,7 @@
         <v>59.20000076293945</v>
       </c>
       <c r="G303" t="n">
-        <v>1000.238464355469</v>
+        <v>1000.238525390625</v>
       </c>
       <c r="H303" t="n">
         <v>148.0500030517578</v>
@@ -9251,7 +9251,7 @@
         <v>59.59999847412109</v>
       </c>
       <c r="G304" t="n">
-        <v>1031.341796875</v>
+        <v>1031.341674804688</v>
       </c>
       <c r="H304" t="n">
         <v>146.8500061035156</v>
@@ -9309,13 +9309,13 @@
         <v>56.20000076293945</v>
       </c>
       <c r="G306" t="n">
-        <v>1021.390625</v>
+        <v>1021.390686035156</v>
       </c>
       <c r="H306" t="n">
         <v>148.1999969482422</v>
       </c>
       <c r="I306" t="n">
-        <v>773.0160522460938</v>
+        <v>773.01611328125</v>
       </c>
       <c r="J306" t="n">
         <v>9.949999809265137</v>
@@ -9338,13 +9338,13 @@
         <v>52.25</v>
       </c>
       <c r="G307" t="n">
-        <v>1001.170043945312</v>
+        <v>1001.169921875</v>
       </c>
       <c r="H307" t="n">
         <v>143.1000061035156</v>
       </c>
       <c r="I307" t="n">
-        <v>753.7608032226562</v>
+        <v>753.7608642578125</v>
       </c>
       <c r="J307" t="n">
         <v>9.850000381469727</v>
@@ -9367,7 +9367,7 @@
         <v>53.59999847412109</v>
       </c>
       <c r="G308" t="n">
-        <v>1016.732971191406</v>
+        <v>1016.73291015625</v>
       </c>
       <c r="H308" t="n">
         <v>142.1999969482422</v>
@@ -9396,13 +9396,13 @@
         <v>52.34999847412109</v>
       </c>
       <c r="G309" t="n">
-        <v>1021.481506347656</v>
+        <v>1021.481567382812</v>
       </c>
       <c r="H309" t="n">
         <v>137.5</v>
       </c>
       <c r="I309" t="n">
-        <v>721.9971923828125</v>
+        <v>721.9971313476562</v>
       </c>
       <c r="J309" t="n">
         <v>9.149999618530273</v>
@@ -9483,13 +9483,13 @@
         <v>56</v>
       </c>
       <c r="G312" t="n">
-        <v>1059.400756835938</v>
+        <v>1059.40087890625</v>
       </c>
       <c r="H312" t="n">
         <v>146.3999938964844</v>
       </c>
       <c r="I312" t="n">
-        <v>785.7708129882812</v>
+        <v>785.7708740234375</v>
       </c>
       <c r="J312" t="n">
         <v>10.39999961853027</v>
@@ -9541,7 +9541,7 @@
         <v>56.54999923706055</v>
       </c>
       <c r="G314" t="n">
-        <v>1063.944702148438</v>
+        <v>1063.94482421875</v>
       </c>
       <c r="H314" t="n">
         <v>151.3999938964844</v>
@@ -9605,7 +9605,7 @@
         <v>157.3500061035156</v>
       </c>
       <c r="I316" t="n">
-        <v>804.1396484375</v>
+        <v>804.1397094726562</v>
       </c>
       <c r="J316" t="n">
         <v>12.55000019073486</v>
@@ -9628,13 +9628,13 @@
         <v>55</v>
       </c>
       <c r="G317" t="n">
-        <v>1066.307495117188</v>
+        <v>1066.3076171875</v>
       </c>
       <c r="H317" t="n">
         <v>155.6999969482422</v>
       </c>
       <c r="I317" t="n">
-        <v>799.6090698242188</v>
+        <v>799.6090087890625</v>
       </c>
       <c r="J317" t="n">
         <v>12.14999961853027</v>
@@ -9715,7 +9715,7 @@
         <v>55.40000152587891</v>
       </c>
       <c r="G320" t="n">
-        <v>1063.444946289062</v>
+        <v>1063.44482421875</v>
       </c>
       <c r="H320" t="n">
         <v>159.6499938964844</v>
@@ -9808,7 +9808,7 @@
         <v>159.3500061035156</v>
       </c>
       <c r="I323" t="n">
-        <v>814.0873413085938</v>
+        <v>814.08740234375</v>
       </c>
       <c r="J323" t="n">
         <v>12</v>
@@ -9831,13 +9831,13 @@
         <v>54.25</v>
       </c>
       <c r="G324" t="n">
-        <v>1071.464965820312</v>
+        <v>1071.465087890625</v>
       </c>
       <c r="H324" t="n">
         <v>157.8500061035156</v>
       </c>
       <c r="I324" t="n">
-        <v>821.6712036132812</v>
+        <v>821.6712646484375</v>
       </c>
       <c r="J324" t="n">
         <v>11.80000019073486</v>
@@ -9860,7 +9860,7 @@
         <v>54.95000076293945</v>
       </c>
       <c r="G325" t="n">
-        <v>1079.666870117188</v>
+        <v>1079.666748046875</v>
       </c>
       <c r="H325" t="n">
         <v>157.8999938964844</v>
@@ -9889,13 +9889,13 @@
         <v>55</v>
       </c>
       <c r="G326" t="n">
-        <v>1073.328125</v>
+        <v>1073.328002929688</v>
       </c>
       <c r="H326" t="n">
         <v>153.6000061035156</v>
       </c>
       <c r="I326" t="n">
-        <v>816.9928588867188</v>
+        <v>816.992919921875</v>
       </c>
       <c r="J326" t="n">
         <v>11.89999961853027</v>
@@ -9924,7 +9924,7 @@
         <v>160.6999969482422</v>
       </c>
       <c r="I327" t="n">
-        <v>822.409912109375</v>
+        <v>822.4099731445312</v>
       </c>
       <c r="J327" t="n">
         <v>12.5</v>
@@ -9953,7 +9953,7 @@
         <v>157.5500030517578</v>
       </c>
       <c r="I328" t="n">
-        <v>830.1415405273438</v>
+        <v>830.1414794921875</v>
       </c>
       <c r="J328" t="n">
         <v>12.19999980926514</v>
@@ -10185,7 +10185,7 @@
         <v>147.8500061035156</v>
       </c>
       <c r="I336" t="n">
-        <v>878.6982421875</v>
+        <v>878.6983032226562</v>
       </c>
       <c r="J336" t="n">
         <v>11.85000038146973</v>
@@ -10208,7 +10208,7 @@
         <v>58.09999847412109</v>
       </c>
       <c r="G337" t="n">
-        <v>1128.877807617188</v>
+        <v>1128.8779296875</v>
       </c>
       <c r="H337" t="n">
         <v>146.6000061035156</v>
@@ -10237,13 +10237,13 @@
         <v>60.59999847412109</v>
       </c>
       <c r="G338" t="n">
-        <v>1131.104370117188</v>
+        <v>1131.1044921875</v>
       </c>
       <c r="H338" t="n">
         <v>144.1499938964844</v>
       </c>
       <c r="I338" t="n">
-        <v>873.1334838867188</v>
+        <v>873.1334228515625</v>
       </c>
       <c r="J338" t="n">
         <v>11.60000038146973</v>
@@ -10266,7 +10266,7 @@
         <v>59.54999923706055</v>
       </c>
       <c r="G339" t="n">
-        <v>1114.99609375</v>
+        <v>1114.996215820312</v>
       </c>
       <c r="H339" t="n">
         <v>140.8999938964844</v>
@@ -10295,13 +10295,13 @@
         <v>59.25</v>
       </c>
       <c r="G340" t="n">
-        <v>1108.407348632812</v>
+        <v>1108.4072265625</v>
       </c>
       <c r="H340" t="n">
         <v>137.1000061035156</v>
       </c>
       <c r="I340" t="n">
-        <v>869.3907470703125</v>
+        <v>869.3906860351562</v>
       </c>
       <c r="J340" t="n">
         <v>11.60000038146973</v>
@@ -10324,13 +10324,13 @@
         <v>57.75</v>
       </c>
       <c r="G341" t="n">
-        <v>1106.021850585938</v>
+        <v>1106.02197265625</v>
       </c>
       <c r="H341" t="n">
         <v>135.8999938964844</v>
       </c>
       <c r="I341" t="n">
-        <v>875.1525268554688</v>
+        <v>875.1524658203125</v>
       </c>
       <c r="J341" t="n">
         <v>11.39999961853027</v>
@@ -10353,7 +10353,7 @@
         <v>58.5</v>
       </c>
       <c r="G342" t="n">
-        <v>1109.611450195312</v>
+        <v>1109.611572265625</v>
       </c>
       <c r="H342" t="n">
         <v>137.4499969482422</v>
@@ -10417,7 +10417,7 @@
         <v>139.6499938964844</v>
       </c>
       <c r="I344" t="n">
-        <v>899.4308471679688</v>
+        <v>899.430908203125</v>
       </c>
       <c r="J344" t="n">
         <v>12.94999980926514</v>
@@ -10446,7 +10446,7 @@
         <v>138.6000061035156</v>
       </c>
       <c r="I345" t="n">
-        <v>881.3082885742188</v>
+        <v>881.308349609375</v>
       </c>
       <c r="J345" t="n">
         <v>12.10000038146973</v>
@@ -10498,7 +10498,7 @@
         <v>60.20000076293945</v>
       </c>
       <c r="G347" t="n">
-        <v>1138.942749023438</v>
+        <v>1138.94287109375</v>
       </c>
       <c r="H347" t="n">
         <v>138</v>
@@ -10556,13 +10556,13 @@
         <v>61.25</v>
       </c>
       <c r="G349" t="n">
-        <v>1145.054443359375</v>
+        <v>1145.054321289062</v>
       </c>
       <c r="H349" t="n">
         <v>138.6000061035156</v>
       </c>
       <c r="I349" t="n">
-        <v>902.0901489257812</v>
+        <v>902.0902099609375</v>
       </c>
       <c r="J349" t="n">
         <v>12.94999980926514</v>
@@ -10585,13 +10585,13 @@
         <v>61.29999923706055</v>
       </c>
       <c r="G350" t="n">
-        <v>1122.311889648438</v>
+        <v>1122.311767578125</v>
       </c>
       <c r="H350" t="n">
         <v>134.6999969482422</v>
       </c>
       <c r="I350" t="n">
-        <v>894.8017578125</v>
+        <v>894.8016967773438</v>
       </c>
       <c r="J350" t="n">
         <v>12.94999980926514</v>
@@ -10649,7 +10649,7 @@
         <v>134.6000061035156</v>
       </c>
       <c r="I352" t="n">
-        <v>931.1946411132812</v>
+        <v>931.194580078125</v>
       </c>
       <c r="J352" t="n">
         <v>13.14999961853027</v>
@@ -10707,7 +10707,7 @@
         <v>132.5</v>
       </c>
       <c r="I354" t="n">
-        <v>943.4075927734375</v>
+        <v>943.4076538085938</v>
       </c>
       <c r="J354" t="n">
         <v>13.60000038146973</v>
@@ -10736,7 +10736,7 @@
         <v>136.0500030517578</v>
       </c>
       <c r="I355" t="n">
-        <v>942.6196899414062</v>
+        <v>942.61962890625</v>
       </c>
       <c r="J355" t="n">
         <v>14.75</v>
@@ -10788,7 +10788,7 @@
         <v>63.75</v>
       </c>
       <c r="G357" t="n">
-        <v>1127.787353515625</v>
+        <v>1127.787231445312</v>
       </c>
       <c r="H357" t="n">
         <v>137.1999969482422</v>
@@ -10817,7 +10817,7 @@
         <v>63.54999923706055</v>
       </c>
       <c r="G358" t="n">
-        <v>1128.786987304688</v>
+        <v>1128.787109375</v>
       </c>
       <c r="H358" t="n">
         <v>139.3999938964844</v>
@@ -10852,7 +10852,7 @@
         <v>143.8500061035156</v>
       </c>
       <c r="I359" t="n">
-        <v>949.0528564453125</v>
+        <v>949.0529174804688</v>
       </c>
       <c r="J359" t="n">
         <v>16.04999923706055</v>
@@ -10875,13 +10875,13 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G360" t="n">
-        <v>1159.549560546875</v>
+        <v>1159.549438476562</v>
       </c>
       <c r="H360" t="n">
         <v>149.9499969482422</v>
       </c>
       <c r="I360" t="n">
-        <v>950.980712890625</v>
+        <v>950.9806518554688</v>
       </c>
       <c r="J360" t="n">
         <v>15.89999961853027</v>
@@ -10910,7 +10910,7 @@
         <v>149.4499969482422</v>
       </c>
       <c r="I361" t="n">
-        <v>938.8209838867188</v>
+        <v>938.8209228515625</v>
       </c>
       <c r="J361" t="n">
         <v>16.75</v>
@@ -10933,7 +10933,7 @@
         <v>65.59999847412109</v>
       </c>
       <c r="G362" t="n">
-        <v>1171.159423828125</v>
+        <v>1171.159545898438</v>
       </c>
       <c r="H362" t="n">
         <v>151.5500030517578</v>
@@ -10962,7 +10962,7 @@
         <v>66.5</v>
       </c>
       <c r="G363" t="n">
-        <v>1159.526977539062</v>
+        <v>1159.52685546875</v>
       </c>
       <c r="H363" t="n">
         <v>150.75</v>
@@ -11055,7 +11055,7 @@
         <v>145.1499938964844</v>
       </c>
       <c r="I366" t="n">
-        <v>939.5128784179688</v>
+        <v>939.512939453125</v>
       </c>
       <c r="J366" t="n">
         <v>14.75</v>
@@ -11084,7 +11084,7 @@
         <v>143.25</v>
       </c>
       <c r="I367" t="n">
-        <v>917.3683471679688</v>
+        <v>917.368408203125</v>
       </c>
       <c r="J367" t="n">
         <v>14.75</v>
@@ -11107,13 +11107,13 @@
         <v>63.29999923706055</v>
       </c>
       <c r="G368" t="n">
-        <v>1133.967163085938</v>
+        <v>1133.967041015625</v>
       </c>
       <c r="H368" t="n">
         <v>140.1999969482422</v>
       </c>
       <c r="I368" t="n">
-        <v>924.0413818359375</v>
+        <v>924.0414428710938</v>
       </c>
       <c r="J368" t="n">
         <v>14.10000038146973</v>
@@ -11252,13 +11252,13 @@
         <v>62.45000076293945</v>
       </c>
       <c r="G373" t="n">
-        <v>1176.31689453125</v>
+        <v>1176.316772460938</v>
       </c>
       <c r="H373" t="n">
         <v>137.1000061035156</v>
       </c>
       <c r="I373" t="n">
-        <v>939.61181640625</v>
+        <v>939.6118774414062</v>
       </c>
       <c r="J373" t="n">
         <v>14.64999961853027</v>
@@ -11316,7 +11316,7 @@
         <v>138.75</v>
       </c>
       <c r="I375" t="n">
-        <v>952.9085083007812</v>
+        <v>952.908447265625</v>
       </c>
       <c r="J375" t="n">
         <v>15.30000019073486</v>
@@ -11426,7 +11426,7 @@
         <v>63.45000076293945</v>
       </c>
       <c r="G379" t="n">
-        <v>1257.653564453125</v>
+        <v>1257.653686523438</v>
       </c>
       <c r="H379" t="n">
         <v>137.5500030517578</v>
@@ -11455,13 +11455,13 @@
         <v>62.79999923706055</v>
       </c>
       <c r="G380" t="n">
-        <v>1246.407470703125</v>
+        <v>1246.4072265625</v>
       </c>
       <c r="H380" t="n">
         <v>136.4499969482422</v>
       </c>
       <c r="I380" t="n">
-        <v>929.0338745117188</v>
+        <v>929.0338134765625</v>
       </c>
       <c r="J380" t="n">
         <v>15.19999980926514</v>
@@ -11484,7 +11484,7 @@
         <v>63.5</v>
       </c>
       <c r="G381" t="n">
-        <v>1245.362182617188</v>
+        <v>1245.3623046875</v>
       </c>
       <c r="H381" t="n">
         <v>136.1499938964844</v>
@@ -11513,7 +11513,7 @@
         <v>65</v>
       </c>
       <c r="G382" t="n">
-        <v>1270.808471679688</v>
+        <v>1270.808349609375</v>
       </c>
       <c r="H382" t="n">
         <v>135</v>
@@ -11542,7 +11542,7 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G383" t="n">
-        <v>1281.600219726562</v>
+        <v>1281.600341796875</v>
       </c>
       <c r="H383" t="n">
         <v>141.6999969482422</v>
@@ -11600,7 +11600,7 @@
         <v>59.70000076293945</v>
       </c>
       <c r="G385" t="n">
-        <v>1289.760620117188</v>
+        <v>1289.760498046875</v>
       </c>
       <c r="H385" t="n">
         <v>162.3999938964844</v>
@@ -11664,7 +11664,7 @@
         <v>162.6000061035156</v>
       </c>
       <c r="I387" t="n">
-        <v>949.4483642578125</v>
+        <v>949.4484252929688</v>
       </c>
       <c r="J387" t="n">
         <v>15.64999961853027</v>
@@ -11716,13 +11716,13 @@
         <v>58.29999923706055</v>
       </c>
       <c r="G389" t="n">
-        <v>1243.656127929688</v>
+        <v>1243.656372070312</v>
       </c>
       <c r="H389" t="n">
         <v>170.9499969482422</v>
       </c>
       <c r="I389" t="n">
-        <v>949.4483642578125</v>
+        <v>949.4484252929688</v>
       </c>
       <c r="J389" t="n">
         <v>15.75</v>
@@ -11751,7 +11751,7 @@
         <v>178.6000061035156</v>
       </c>
       <c r="I390" t="n">
-        <v>955.478759765625</v>
+        <v>955.4788208007812</v>
       </c>
       <c r="J390" t="n">
         <v>16.54999923706055</v>
@@ -11780,7 +11780,7 @@
         <v>184.8500061035156</v>
       </c>
       <c r="I391" t="n">
-        <v>947.7183227539062</v>
+        <v>947.7183837890625</v>
       </c>
       <c r="J391" t="n">
         <v>16.10000038146973</v>
@@ -11832,7 +11832,7 @@
         <v>58.04999923706055</v>
       </c>
       <c r="G393" t="n">
-        <v>1237.256469726562</v>
+        <v>1237.256225585938</v>
       </c>
       <c r="H393" t="n">
         <v>183.8000030517578</v>
@@ -11867,7 +11867,7 @@
         <v>181.1999969482422</v>
       </c>
       <c r="I394" t="n">
-        <v>977.1785278320312</v>
+        <v>977.178466796875</v>
       </c>
       <c r="J394" t="n">
         <v>18.14999961853027</v>
@@ -11919,13 +11919,13 @@
         <v>58.15000152587891</v>
       </c>
       <c r="G396" t="n">
-        <v>1235.459594726562</v>
+        <v>1235.45947265625</v>
       </c>
       <c r="H396" t="n">
         <v>199.1499938964844</v>
       </c>
       <c r="I396" t="n">
-        <v>968.0339965820312</v>
+        <v>968.033935546875</v>
       </c>
       <c r="J396" t="n">
         <v>19.04999923706055</v>
@@ -11954,7 +11954,7 @@
         <v>210.0500030517578</v>
       </c>
       <c r="I397" t="n">
-        <v>977.1785278320312</v>
+        <v>977.178466796875</v>
       </c>
       <c r="J397" t="n">
         <v>18.64999961853027</v>
@@ -11977,7 +11977,7 @@
         <v>60.20000076293945</v>
       </c>
       <c r="G398" t="n">
-        <v>1235.016235351562</v>
+        <v>1235.016357421875</v>
       </c>
       <c r="H398" t="n">
         <v>194.6999969482422</v>
@@ -12006,7 +12006,7 @@
         <v>60.04999923706055</v>
       </c>
       <c r="G399" t="n">
-        <v>1243.1640625</v>
+        <v>1243.163940429688</v>
       </c>
       <c r="H399" t="n">
         <v>191.4499969482422</v>
@@ -12035,7 +12035,7 @@
         <v>62</v>
       </c>
       <c r="G400" t="n">
-        <v>1248.702270507812</v>
+        <v>1248.702392578125</v>
       </c>
       <c r="H400" t="n">
         <v>175.8500061035156</v>
@@ -12093,7 +12093,7 @@
         <v>61.25</v>
       </c>
       <c r="G402" t="n">
-        <v>1268.788330078125</v>
+        <v>1268.788452148438</v>
       </c>
       <c r="H402" t="n">
         <v>166.9499969482422</v>
@@ -12151,13 +12151,13 @@
         <v>60.95000076293945</v>
       </c>
       <c r="G404" t="n">
-        <v>1249.465454101562</v>
+        <v>1249.465576171875</v>
       </c>
       <c r="H404" t="n">
         <v>158.0500030517578</v>
       </c>
       <c r="I404" t="n">
-        <v>1023.296569824219</v>
+        <v>1023.296447753906</v>
       </c>
       <c r="J404" t="n">
         <v>16.54999923706055</v>
@@ -12218,7 +12218,7 @@
         <v>162.3500061035156</v>
       </c>
       <c r="I406" t="n">
-        <v>1040.003662109375</v>
+        <v>1040.003784179688</v>
       </c>
       <c r="J406" t="n">
         <v>16.35000038146973</v>
@@ -12250,7 +12250,7 @@
         <v>170.4499969482422</v>
       </c>
       <c r="I407" t="n">
-        <v>1037.186279296875</v>
+        <v>1037.186401367188</v>
       </c>
       <c r="J407" t="n">
         <v>17.39999961853027</v>
@@ -12282,7 +12282,7 @@
         <v>178.9499969482422</v>
       </c>
       <c r="I408" t="n">
-        <v>1023.593200683594</v>
+        <v>1023.593078613281</v>
       </c>
       <c r="J408" t="n">
         <v>17.29999923706055</v>
@@ -12314,7 +12314,7 @@
         <v>177.3000030517578</v>
       </c>
       <c r="I409" t="n">
-        <v>1017.513244628906</v>
+        <v>1017.513305664062</v>
       </c>
       <c r="J409" t="n">
         <v>17.29999923706055</v>
@@ -12346,7 +12346,7 @@
         <v>177.25</v>
       </c>
       <c r="I410" t="n">
-        <v>988.15185546875</v>
+        <v>988.1519165039062</v>
       </c>
       <c r="J410" t="n">
         <v>17.35000038146973</v>
@@ -12378,7 +12378,7 @@
         <v>177.8999938964844</v>
       </c>
       <c r="I411" t="n">
-        <v>1001.794494628906</v>
+        <v>1001.794555664062</v>
       </c>
       <c r="J411" t="n">
         <v>17.45000076293945</v>
@@ -12410,7 +12410,7 @@
         <v>184.5</v>
       </c>
       <c r="I412" t="n">
-        <v>991.1671142578125</v>
+        <v>991.1670532226562</v>
       </c>
       <c r="J412" t="n">
         <v>18.25</v>
@@ -12506,7 +12506,7 @@
         <v>186.8999938964844</v>
       </c>
       <c r="I415" t="n">
-        <v>1000.114013671875</v>
+        <v>1000.113952636719</v>
       </c>
       <c r="J415" t="n">
         <v>19</v>
@@ -12634,7 +12634,7 @@
         <v>189.8000030517578</v>
       </c>
       <c r="I419" t="n">
-        <v>1005.304138183594</v>
+        <v>1005.304077148438</v>
       </c>
       <c r="J419" t="n">
         <v>21.20000076293945</v>
@@ -12666,7 +12666,7 @@
         <v>186.5</v>
       </c>
       <c r="I420" t="n">
-        <v>996.7527465820312</v>
+        <v>996.752685546875</v>
       </c>
       <c r="J420" t="n">
         <v>21.14999961853027</v>
@@ -12698,7 +12698,7 @@
         <v>182.8500061035156</v>
       </c>
       <c r="I421" t="n">
-        <v>991.2166137695312</v>
+        <v>991.216552734375</v>
       </c>
       <c r="J421" t="n">
         <v>20.79999923706055</v>
@@ -12730,7 +12730,7 @@
         <v>173.6999969482422</v>
       </c>
       <c r="I422" t="n">
-        <v>954.5890502929688</v>
+        <v>954.5889892578125</v>
       </c>
       <c r="J422" t="n">
         <v>18.39999961853027</v>
@@ -12762,7 +12762,7 @@
         <v>172.6499938964844</v>
       </c>
       <c r="I423" t="n">
-        <v>952.9085083007812</v>
+        <v>952.908447265625</v>
       </c>
       <c r="J423" t="n">
         <v>19</v>
@@ -12922,7 +12922,7 @@
         <v>175.1499938964844</v>
       </c>
       <c r="I428" t="n">
-        <v>941.0453491210938</v>
+        <v>941.0452880859375</v>
       </c>
       <c r="J428" t="n">
         <v>19</v>
@@ -12954,7 +12954,7 @@
         <v>175.75</v>
       </c>
       <c r="I429" t="n">
-        <v>936.1023559570312</v>
+        <v>936.102294921875</v>
       </c>
       <c r="J429" t="n">
         <v>18.89999961853027</v>
@@ -13050,7 +13050,7 @@
         <v>172.6499938964844</v>
       </c>
       <c r="I432" t="n">
-        <v>956.4180297851562</v>
+        <v>956.41796875</v>
       </c>
       <c r="J432" t="n">
         <v>19.20000076293945</v>
@@ -13210,7 +13210,7 @@
         <v>172.1999969482422</v>
       </c>
       <c r="I437" t="n">
-        <v>968.7260131835938</v>
+        <v>968.7259521484375</v>
       </c>
       <c r="J437" t="n">
         <v>18.89999961853027</v>
@@ -13274,7 +13274,7 @@
         <v>171.25</v>
       </c>
       <c r="I439" t="n">
-        <v>943.46728515625</v>
+        <v>943.4673461914062</v>
       </c>
       <c r="J439" t="n">
         <v>17.85000038146973</v>
@@ -13306,7 +13306,7 @@
         <v>170.8500061035156</v>
       </c>
       <c r="I440" t="n">
-        <v>970.3078002929688</v>
+        <v>970.3077392578125</v>
       </c>
       <c r="J440" t="n">
         <v>17.79999923706055</v>
@@ -13370,7 +13370,7 @@
         <v>169.3500061035156</v>
       </c>
       <c r="I442" t="n">
-        <v>980.04541015625</v>
+        <v>980.0453491210938</v>
       </c>
       <c r="J442" t="n">
         <v>18</v>
@@ -13498,7 +13498,7 @@
         <v>169.1999969482422</v>
       </c>
       <c r="I446" t="n">
-        <v>1029.079833984375</v>
+        <v>1029.079711914062</v>
       </c>
       <c r="J446" t="n">
         <v>18.14999961853027</v>
@@ -13594,7 +13594,7 @@
         <v>169.75</v>
       </c>
       <c r="I449" t="n">
-        <v>995.3192138671875</v>
+        <v>995.3191528320312</v>
       </c>
       <c r="J449" t="n">
         <v>16.70000076293945</v>
@@ -13626,7 +13626,7 @@
         <v>162.3000030517578</v>
       </c>
       <c r="I450" t="n">
-        <v>1000.262268066406</v>
+        <v>1000.26220703125</v>
       </c>
       <c r="J450" t="n">
         <v>16.29999923706055</v>
@@ -13658,7 +13658,7 @@
         <v>159.0500030517578</v>
       </c>
       <c r="I451" t="n">
-        <v>1007.726135253906</v>
+        <v>1007.72607421875</v>
       </c>
       <c r="J451" t="n">
         <v>16.5</v>
@@ -13722,7 +13722,7 @@
         <v>168</v>
       </c>
       <c r="I453" t="n">
-        <v>1007.577880859375</v>
+        <v>1007.577819824219</v>
       </c>
       <c r="J453" t="n">
         <v>16.95000076293945</v>
@@ -13786,7 +13786,7 @@
         <v>172.25</v>
       </c>
       <c r="I455" t="n">
-        <v>979.5511474609375</v>
+        <v>979.5510864257812</v>
       </c>
       <c r="J455" t="n">
         <v>17.39999961853027</v>
@@ -13818,7 +13818,7 @@
         <v>176.9499969482422</v>
       </c>
       <c r="I456" t="n">
-        <v>988.6956787109375</v>
+        <v>988.6956176757812</v>
       </c>
       <c r="J456" t="n">
         <v>18.25</v>
@@ -13882,7 +13882,7 @@
         <v>183.3500061035156</v>
       </c>
       <c r="I458" t="n">
-        <v>1032.3916015625</v>
+        <v>1032.391723632812</v>
       </c>
       <c r="J458" t="n">
         <v>19.29999923706055</v>
@@ -13914,7 +13914,7 @@
         <v>185.5500030517578</v>
       </c>
       <c r="I459" t="n">
-        <v>1038.817626953125</v>
+        <v>1038.817504882812</v>
       </c>
       <c r="J459" t="n">
         <v>20.70000076293945</v>
@@ -13946,7 +13946,7 @@
         <v>179.1000061035156</v>
       </c>
       <c r="I460" t="n">
-        <v>1039.509521484375</v>
+        <v>1039.509399414062</v>
       </c>
       <c r="J460" t="n">
         <v>20.45000076293945</v>
@@ -13978,7 +13978,7 @@
         <v>178.1000061035156</v>
       </c>
       <c r="I461" t="n">
-        <v>1038.175048828125</v>
+        <v>1038.1748046875</v>
       </c>
       <c r="J461" t="n">
         <v>21.20000076293945</v>
@@ -14042,7 +14042,7 @@
         <v>181.1499938964844</v>
       </c>
       <c r="I463" t="n">
-        <v>1030.216552734375</v>
+        <v>1030.216674804688</v>
       </c>
       <c r="J463" t="n">
         <v>22.5</v>
@@ -14074,7 +14074,7 @@
         <v>181.75</v>
       </c>
       <c r="I464" t="n">
-        <v>1070.156127929688</v>
+        <v>1070.156005859375</v>
       </c>
       <c r="J464" t="n">
         <v>22.29999923706055</v>
@@ -14170,7 +14170,7 @@
         <v>182.75</v>
       </c>
       <c r="I467" t="n">
-        <v>1104.608520507812</v>
+        <v>1104.608642578125</v>
       </c>
       <c r="J467" t="n">
         <v>22.10000038146973</v>
@@ -14202,7 +14202,7 @@
         <v>179.5500030517578</v>
       </c>
       <c r="I468" t="n">
-        <v>1109.156127929688</v>
+        <v>1109.156005859375</v>
       </c>
       <c r="J468" t="n">
         <v>21.35000038146973</v>
@@ -14234,7 +14234,7 @@
         <v>174.8500061035156</v>
       </c>
       <c r="I469" t="n">
-        <v>1108.315795898438</v>
+        <v>1108.31591796875</v>
       </c>
       <c r="J469" t="n">
         <v>20.89999961853027</v>
@@ -14298,7 +14298,7 @@
         <v>173.4499969482422</v>
       </c>
       <c r="I471" t="n">
-        <v>1078.55908203125</v>
+        <v>1078.558959960938</v>
       </c>
       <c r="J471" t="n">
         <v>20.89999961853027</v>
@@ -14330,7 +14330,7 @@
         <v>177.8999938964844</v>
       </c>
       <c r="I472" t="n">
-        <v>1087.851928710938</v>
+        <v>1087.851806640625</v>
       </c>
       <c r="J472" t="n">
         <v>20.89999961853027</v>
@@ -14426,7 +14426,7 @@
         <v>194.0500030517578</v>
       </c>
       <c r="I475" t="n">
-        <v>1081.030517578125</v>
+        <v>1081.030639648438</v>
       </c>
       <c r="J475" t="n">
         <v>20.85000038146973</v>
@@ -14490,7 +14490,7 @@
         <v>202.3000030517578</v>
       </c>
       <c r="I477" t="n">
-        <v>1095.16748046875</v>
+        <v>1095.167602539062</v>
       </c>
       <c r="J477" t="n">
         <v>22.29999923706055</v>
@@ -14522,7 +14522,7 @@
         <v>212.3999938964844</v>
       </c>
       <c r="I478" t="n">
-        <v>1103.867065429688</v>
+        <v>1103.8671875</v>
       </c>
       <c r="J478" t="n">
         <v>23.20000076293945</v>
@@ -14586,7 +14586,7 @@
         <v>214.75</v>
       </c>
       <c r="I480" t="n">
-        <v>1130.9052734375</v>
+        <v>1130.905151367188</v>
       </c>
       <c r="J480" t="n">
         <v>23.95000076293945</v>
@@ -14650,7 +14650,7 @@
         <v>211.6499938964844</v>
       </c>
       <c r="I482" t="n">
-        <v>1134.167602539062</v>
+        <v>1134.167724609375</v>
       </c>
       <c r="J482" t="n">
         <v>23.20000076293945</v>
@@ -14682,7 +14682,7 @@
         <v>215.8000030517578</v>
       </c>
       <c r="I483" t="n">
-        <v>1170.547973632812</v>
+        <v>1170.548095703125</v>
       </c>
       <c r="J483" t="n">
         <v>23.79999923706055</v>
@@ -14746,7 +14746,7 @@
         <v>209.75</v>
       </c>
       <c r="I485" t="n">
-        <v>1167.9775390625</v>
+        <v>1167.977661132812</v>
       </c>
       <c r="J485" t="n">
         <v>23.60000038146973</v>
@@ -14842,7 +14842,7 @@
         <v>190.8000030517578</v>
       </c>
       <c r="I488" t="n">
-        <v>1227.29345703125</v>
+        <v>1227.293334960938</v>
       </c>
       <c r="J488" t="n">
         <v>21.39999961853027</v>
@@ -14874,7 +14874,7 @@
         <v>193.3999938964844</v>
       </c>
       <c r="I489" t="n">
-        <v>1275.042602539062</v>
+        <v>1275.042724609375</v>
       </c>
       <c r="J489" t="n">
         <v>22.70000076293945</v>
@@ -15002,7 +15002,7 @@
         <v>190.8000030517578</v>
       </c>
       <c r="I493" t="n">
-        <v>1333.122802734375</v>
+        <v>1333.122680664062</v>
       </c>
       <c r="J493" t="n">
         <v>22.35000038146973</v>
@@ -15034,7 +15034,7 @@
         <v>209.8000030517578</v>
       </c>
       <c r="I494" t="n">
-        <v>1332.77685546875</v>
+        <v>1332.776733398438</v>
       </c>
       <c r="J494" t="n">
         <v>23.29999923706055</v>
@@ -15162,7 +15162,7 @@
         <v>231.5500030517578</v>
       </c>
       <c r="I498" t="n">
-        <v>1382.1572265625</v>
+        <v>1382.157104492188</v>
       </c>
       <c r="J498" t="n">
         <v>30.39999961853027</v>
@@ -15322,7 +15322,7 @@
         <v>239.8999938964844</v>
       </c>
       <c r="I503" t="n">
-        <v>1498.1689453125</v>
+        <v>1498.168823242188</v>
       </c>
       <c r="J503" t="n">
         <v>31.10000038146973</v>
@@ -15386,7 +15386,7 @@
         <v>232.6499938964844</v>
       </c>
       <c r="I505" t="n">
-        <v>1442.313232421875</v>
+        <v>1442.313354492188</v>
       </c>
       <c r="J505" t="n">
         <v>30.79999923706055</v>
@@ -15418,7 +15418,7 @@
         <v>221.8999938964844</v>
       </c>
       <c r="I506" t="n">
-        <v>1395.750244140625</v>
+        <v>1395.750366210938</v>
       </c>
       <c r="J506" t="n">
         <v>30.04999923706055</v>
@@ -15642,7 +15642,7 @@
         <v>227.9499969482422</v>
       </c>
       <c r="I513" t="n">
-        <v>1413.940551757812</v>
+        <v>1413.9404296875</v>
       </c>
       <c r="J513" t="n">
         <v>30.10000038146973</v>
@@ -15674,7 +15674,7 @@
         <v>231.5500030517578</v>
       </c>
       <c r="I514" t="n">
-        <v>1382.997436523438</v>
+        <v>1382.99755859375</v>
       </c>
       <c r="J514" t="n">
         <v>29.95000076293945</v>
@@ -15706,7 +15706,7 @@
         <v>231.0500030517578</v>
       </c>
       <c r="I515" t="n">
-        <v>1394.317016601562</v>
+        <v>1394.31689453125</v>
       </c>
       <c r="J515" t="n">
         <v>29.79999923706055</v>
@@ -15770,7 +15770,7 @@
         <v>221.9499969482422</v>
       </c>
       <c r="I517" t="n">
-        <v>1373.704833984375</v>
+        <v>1373.704711914062</v>
       </c>
       <c r="J517" t="n">
         <v>28.79999923706055</v>
@@ -15802,7 +15802,7 @@
         <v>214.5</v>
       </c>
       <c r="I518" t="n">
-        <v>1374.1494140625</v>
+        <v>1374.149536132812</v>
       </c>
       <c r="J518" t="n">
         <v>27.39999961853027</v>
@@ -16026,7 +16026,7 @@
         <v>229.1499938964844</v>
       </c>
       <c r="I525" t="n">
-        <v>1340.784301757812</v>
+        <v>1340.784423828125</v>
       </c>
       <c r="J525" t="n">
         <v>26.45000076293945</v>
@@ -16058,7 +16058,7 @@
         <v>234.3500061035156</v>
       </c>
       <c r="I526" t="n">
-        <v>1455.36279296875</v>
+        <v>1455.362670898438</v>
       </c>
       <c r="J526" t="n">
         <v>26.75</v>
@@ -16122,7 +16122,7 @@
         <v>242.8500061035156</v>
       </c>
       <c r="I528" t="n">
-        <v>1441.621215820312</v>
+        <v>1441.621337890625</v>
       </c>
       <c r="J528" t="n">
         <v>26.95000076293945</v>
@@ -16154,7 +16154,7 @@
         <v>241.1999969482422</v>
       </c>
       <c r="I529" t="n">
-        <v>1438.062377929688</v>
+        <v>1438.062255859375</v>
       </c>
       <c r="J529" t="n">
         <v>26.45000076293945</v>
@@ -16250,7 +16250,7 @@
         <v>228.5</v>
       </c>
       <c r="I532" t="n">
-        <v>1499.948364257812</v>
+        <v>1499.948486328125</v>
       </c>
       <c r="J532" t="n">
         <v>25.60000038146973</v>
@@ -16346,7 +16346,7 @@
         <v>212.1000061035156</v>
       </c>
       <c r="I535" t="n">
-        <v>1397.628662109375</v>
+        <v>1397.628784179688</v>
       </c>
       <c r="J535" t="n">
         <v>23.45000076293945</v>
@@ -16474,7 +16474,7 @@
         <v>226.6999969482422</v>
       </c>
       <c r="I539" t="n">
-        <v>1419.279052734375</v>
+        <v>1419.278930664062</v>
       </c>
       <c r="J539" t="n">
         <v>23.04999923706055</v>
@@ -16538,7 +16538,7 @@
         <v>221.1999969482422</v>
       </c>
       <c r="I541" t="n">
-        <v>1364.313110351562</v>
+        <v>1364.31298828125</v>
       </c>
       <c r="J541" t="n">
         <v>22.54999923706055</v>
@@ -16570,7 +16570,7 @@
         <v>223.6499938964844</v>
       </c>
       <c r="I542" t="n">
-        <v>1328.772827148438</v>
+        <v>1328.77294921875</v>
       </c>
       <c r="J542" t="n">
         <v>22.54999923706055</v>
@@ -16602,7 +16602,7 @@
         <v>217.5500030517578</v>
       </c>
       <c r="I543" t="n">
-        <v>1278.206176757812</v>
+        <v>1278.2060546875</v>
       </c>
       <c r="J543" t="n">
         <v>21.45000076293945</v>
@@ -16698,7 +16698,7 @@
         <v>237.5</v>
       </c>
       <c r="I546" t="n">
-        <v>1219.236328125</v>
+        <v>1219.236450195312</v>
       </c>
       <c r="J546" t="n">
         <v>22.10000038146973</v>
@@ -16730,7 +16730,7 @@
         <v>255.9499969482422</v>
       </c>
       <c r="I547" t="n">
-        <v>1217.012084960938</v>
+        <v>1217.01220703125</v>
       </c>
       <c r="J547" t="n">
         <v>23.20000076293945</v>
@@ -16794,7 +16794,7 @@
         <v>249.3000030517578</v>
       </c>
       <c r="I549" t="n">
-        <v>1200.205932617188</v>
+        <v>1200.2060546875</v>
       </c>
       <c r="J549" t="n">
         <v>23.89999961853027</v>
@@ -16922,7 +16922,7 @@
         <v>266.9500122070312</v>
       </c>
       <c r="I553" t="n">
-        <v>1257.198486328125</v>
+        <v>1257.198364257812</v>
       </c>
       <c r="J553" t="n">
         <v>27.64999961853027</v>
@@ -16986,7 +16986,7 @@
         <v>268.6499938964844</v>
       </c>
       <c r="I555" t="n">
-        <v>1305.936279296875</v>
+        <v>1305.936401367188</v>
       </c>
       <c r="J555" t="n">
         <v>28.89999961853027</v>
@@ -17050,7 +17050,7 @@
         <v>291.7999877929688</v>
       </c>
       <c r="I557" t="n">
-        <v>1334.457397460938</v>
+        <v>1334.457275390625</v>
       </c>
       <c r="J557" t="n">
         <v>31.79999923706055</v>
@@ -17082,7 +17082,7 @@
         <v>295</v>
       </c>
       <c r="I558" t="n">
-        <v>1325.807250976562</v>
+        <v>1325.80712890625</v>
       </c>
       <c r="J558" t="n">
         <v>33.34999847412109</v>
@@ -17114,7 +17114,7 @@
         <v>298.8999938964844</v>
       </c>
       <c r="I559" t="n">
-        <v>1317.107543945312</v>
+        <v>1317.107666015625</v>
       </c>
       <c r="J559" t="n">
         <v>32.59999847412109</v>
@@ -17466,7 +17466,7 @@
         <v>191.6999969482422</v>
       </c>
       <c r="I570" t="n">
-        <v>1292.491333007812</v>
+        <v>1292.491455078125</v>
       </c>
       <c r="J570" t="n">
         <v>27.60000038146973</v>
@@ -17498,7 +17498,7 @@
         <v>192.6499938964844</v>
       </c>
       <c r="I571" t="n">
-        <v>1290.761474609375</v>
+        <v>1290.761352539062</v>
       </c>
       <c r="J571" t="n">
         <v>27.5</v>
@@ -17562,7 +17562,7 @@
         <v>185.8000030517578</v>
       </c>
       <c r="I573" t="n">
-        <v>1286.362060546875</v>
+        <v>1286.362182617188</v>
       </c>
       <c r="J573" t="n">
         <v>27.54999923706055</v>
@@ -17594,7 +17594,7 @@
         <v>177.8999938964844</v>
       </c>
       <c r="I574" t="n">
-        <v>1309.693115234375</v>
+        <v>1309.692993164062</v>
       </c>
       <c r="J574" t="n">
         <v>27.29999923706055</v>
@@ -17658,7 +17658,7 @@
         <v>176.1999969482422</v>
       </c>
       <c r="I576" t="n">
-        <v>1283.791870117188</v>
+        <v>1283.791748046875</v>
       </c>
       <c r="J576" t="n">
         <v>26.79999923706055</v>
@@ -17722,7 +17722,7 @@
         <v>170.75</v>
       </c>
       <c r="I578" t="n">
-        <v>1236.932250976562</v>
+        <v>1236.93212890625</v>
       </c>
       <c r="J578" t="n">
         <v>25.64999961853027</v>
@@ -17818,7 +17818,7 @@
         <v>162.9499969482422</v>
       </c>
       <c r="I581" t="n">
-        <v>1185.821899414062</v>
+        <v>1185.82177734375</v>
       </c>
       <c r="J581" t="n">
         <v>24.95000076293945</v>
@@ -17882,7 +17882,7 @@
         <v>171.4499969482422</v>
       </c>
       <c r="I583" t="n">
-        <v>1204.901733398438</v>
+        <v>1204.90185546875</v>
       </c>
       <c r="J583" t="n">
         <v>25.60000038146973</v>
@@ -17914,7 +17914,7 @@
         <v>171.6000061035156</v>
       </c>
       <c r="I584" t="n">
-        <v>1211.426635742188</v>
+        <v>1211.426391601562</v>
       </c>
       <c r="J584" t="n">
         <v>25.79999923706055</v>
@@ -17978,7 +17978,7 @@
         <v>170.1000061035156</v>
       </c>
       <c r="I586" t="n">
-        <v>1220.47216796875</v>
+        <v>1220.472290039062</v>
       </c>
       <c r="J586" t="n">
         <v>26.14999961853027</v>
@@ -18138,7 +18138,7 @@
         <v>170</v>
       </c>
       <c r="I591" t="n">
-        <v>1222.053955078125</v>
+        <v>1222.053833007812</v>
       </c>
       <c r="J591" t="n">
         <v>25.29999923706055</v>
@@ -18266,7 +18266,7 @@
         <v>166.3500061035156</v>
       </c>
       <c r="I595" t="n">
-        <v>1168.373168945312</v>
+        <v>1168.373046875</v>
       </c>
       <c r="J595" t="n">
         <v>24.54999923706055</v>
@@ -18330,7 +18330,7 @@
         <v>155.9499969482422</v>
       </c>
       <c r="I597" t="n">
-        <v>1059.578125</v>
+        <v>1059.578002929688</v>
       </c>
       <c r="J597" t="n">
         <v>24.5</v>
@@ -18426,7 +18426,7 @@
         <v>167.8000030517578</v>
       </c>
       <c r="I600" t="n">
-        <v>1198.286376953125</v>
+        <v>1198.286254882812</v>
       </c>
       <c r="J600" t="n">
         <v>25</v>
@@ -18490,7 +18490,7 @@
         <v>189.3000030517578</v>
       </c>
       <c r="I602" t="n">
-        <v>1350.433959960938</v>
+        <v>1350.433837890625</v>
       </c>
       <c r="J602" t="n">
         <v>28.68000030517578</v>
@@ -18650,7 +18650,7 @@
         <v>209.8200073242188</v>
       </c>
       <c r="I607" t="n">
-        <v>1320.678833007812</v>
+        <v>1320.678955078125</v>
       </c>
       <c r="J607" t="n">
         <v>30.82999992370605</v>
@@ -18714,7 +18714,7 @@
         <v>214.8000030517578</v>
       </c>
       <c r="I609" t="n">
-        <v>1319.93505859375</v>
+        <v>1319.934936523438</v>
       </c>
       <c r="J609" t="n">
         <v>29.8700008392334</v>
@@ -18938,7 +18938,7 @@
         <v>187.5500030517578</v>
       </c>
       <c r="I616" t="n">
-        <v>1366.005737304688</v>
+        <v>1366.005615234375</v>
       </c>
       <c r="J616" t="n">
         <v>28.70999908447266</v>
@@ -18970,7 +18970,7 @@
         <v>185.7400054931641</v>
       </c>
       <c r="I617" t="n">
-        <v>1360.15380859375</v>
+        <v>1360.153930664062</v>
       </c>
       <c r="J617" t="n">
         <v>28.3799991607666</v>
@@ -19066,7 +19066,7 @@
         <v>199.9100036621094</v>
       </c>
       <c r="I620" t="n">
-        <v>1385.098510742188</v>
+        <v>1385.0986328125</v>
       </c>
       <c r="J620" t="n">
         <v>28.32999992370605</v>
@@ -19322,7 +19322,7 @@
         <v>181.7400054931641</v>
       </c>
       <c r="I628" t="n">
-        <v>1227.396728515625</v>
+        <v>1227.396606445312</v>
       </c>
       <c r="J628" t="n">
         <v>27.1200008392334</v>
@@ -19386,7 +19386,7 @@
         <v>175.1699981689453</v>
       </c>
       <c r="I630" t="n">
-        <v>1242.422973632812</v>
+        <v>1242.423095703125</v>
       </c>
       <c r="J630" t="n">
         <v>26.94000053405762</v>
@@ -19610,7 +19610,7 @@
         <v>214.4400024414062</v>
       </c>
       <c r="I637" t="n">
-        <v>1270.4423828125</v>
+        <v>1270.442260742188</v>
       </c>
       <c r="J637" t="n">
         <v>32.90000152587891</v>
@@ -19642,7 +19642,7 @@
         <v>215.7200012207031</v>
       </c>
       <c r="I638" t="n">
-        <v>1249.117797851562</v>
+        <v>1249.117919921875</v>
       </c>
       <c r="J638" t="n">
         <v>34.54000091552734</v>
@@ -19738,7 +19738,7 @@
         <v>214.0500030517578</v>
       </c>
       <c r="I641" t="n">
-        <v>1203.344604492188</v>
+        <v>1203.3447265625</v>
       </c>
       <c r="J641" t="n">
         <v>31.86000061035156</v>
@@ -19802,7 +19802,7 @@
         <v>230.0200042724609</v>
       </c>
       <c r="I643" t="n">
-        <v>1192.236083984375</v>
+        <v>1192.236206054688</v>
       </c>
       <c r="J643" t="n">
         <v>32.31999969482422</v>
@@ -19898,7 +19898,7 @@
         <v>220.2799987792969</v>
       </c>
       <c r="I646" t="n">
-        <v>1131.684448242188</v>
+        <v>1131.6845703125</v>
       </c>
       <c r="J646" t="n">
         <v>29.75</v>
@@ -19962,7 +19962,7 @@
         <v>225.7100067138672</v>
       </c>
       <c r="I648" t="n">
-        <v>1198.087890625</v>
+        <v>1198.087768554688</v>
       </c>
       <c r="J648" t="n">
         <v>32.79000091552734</v>
@@ -20026,7 +20026,7 @@
         <v>243.1000061035156</v>
       </c>
       <c r="I650" t="n">
-        <v>1205.47705078125</v>
+        <v>1205.477172851562</v>
       </c>
       <c r="J650" t="n">
         <v>36.13999938964844</v>
@@ -20122,7 +20122,7 @@
         <v>206.75</v>
       </c>
       <c r="I653" t="n">
-        <v>1203.344604492188</v>
+        <v>1203.3447265625</v>
       </c>
       <c r="J653" t="n">
         <v>32.75</v>
@@ -20218,7 +20218,7 @@
         <v>212.25</v>
       </c>
       <c r="I656" t="n">
-        <v>1204.435546875</v>
+        <v>1204.435668945312</v>
       </c>
       <c r="J656" t="n">
         <v>30.56999969482422</v>
@@ -20442,7 +20442,7 @@
         <v>211.75</v>
       </c>
       <c r="I663" t="n">
-        <v>1144.380126953125</v>
+        <v>1144.380004882812</v>
       </c>
       <c r="J663" t="n">
         <v>29.71999931335449</v>
@@ -20698,7 +20698,7 @@
         <v>284.8900146484375</v>
       </c>
       <c r="I671" t="n">
-        <v>1130.39501953125</v>
+        <v>1130.395141601562</v>
       </c>
       <c r="J671" t="n">
         <v>34.61000061035156</v>
@@ -20826,7 +20826,7 @@
         <v>335.1600036621094</v>
       </c>
       <c r="I675" t="n">
-        <v>1262.408569335938</v>
+        <v>1262.408447265625</v>
       </c>
       <c r="J675" t="n">
         <v>42.04999923706055</v>
@@ -20890,7 +20890,7 @@
         <v>322.9500122070312</v>
       </c>
       <c r="I677" t="n">
-        <v>1261.962036132812</v>
+        <v>1261.962158203125</v>
       </c>
       <c r="J677" t="n">
         <v>46.34999847412109</v>
@@ -20954,7 +20954,7 @@
         <v>332</v>
       </c>
       <c r="I679" t="n">
-        <v>1235.876831054688</v>
+        <v>1235.876953125</v>
       </c>
       <c r="J679" t="n">
         <v>51.09000015258789</v>
@@ -21082,7 +21082,7 @@
         <v>299.5</v>
       </c>
       <c r="I683" t="n">
-        <v>1158.860717773438</v>
+        <v>1158.86083984375</v>
       </c>
       <c r="J683" t="n">
         <v>45.97999954223633</v>
@@ -21306,7 +21306,7 @@
         <v>277.9500122070312</v>
       </c>
       <c r="I690" t="n">
-        <v>1192.781616210938</v>
+        <v>1192.781494140625</v>
       </c>
       <c r="J690" t="n">
         <v>41.7400016784668</v>
@@ -21402,7 +21402,7 @@
         <v>254.5500030517578</v>
       </c>
       <c r="I693" t="n">
-        <v>1128.808227539062</v>
+        <v>1128.80810546875</v>
       </c>
       <c r="J693" t="n">
         <v>38.43000030517578</v>
@@ -21434,7 +21434,7 @@
         <v>267.25</v>
       </c>
       <c r="I694" t="n">
-        <v>1138.924926757812</v>
+        <v>1138.925048828125</v>
       </c>
       <c r="J694" t="n">
         <v>40.34999847412109</v>
@@ -21658,7 +21658,7 @@
         <v>291.0499877929688</v>
       </c>
       <c r="I701" t="n">
-        <v>1116.360717773438</v>
+        <v>1116.360595703125</v>
       </c>
       <c r="J701" t="n">
         <v>43.02999877929688</v>
@@ -21786,7 +21786,7 @@
         <v>288.25</v>
       </c>
       <c r="I705" t="n">
-        <v>1128.4609375</v>
+        <v>1128.461059570312</v>
       </c>
       <c r="J705" t="n">
         <v>43.77000045776367</v>
@@ -21850,7 +21850,7 @@
         <v>260.6000061035156</v>
       </c>
       <c r="I707" t="n">
-        <v>1073.166137695312</v>
+        <v>1073.166259765625</v>
       </c>
       <c r="J707" t="n">
         <v>39.5</v>
@@ -22138,7 +22138,7 @@
         <v>271.75</v>
       </c>
       <c r="I716" t="n">
-        <v>1131.287719726562</v>
+        <v>1131.287841796875</v>
       </c>
       <c r="J716" t="n">
         <v>36.31000137329102</v>
@@ -22266,7 +22266,7 @@
         <v>274.0499877929688</v>
       </c>
       <c r="I720" t="n">
-        <v>1195.409912109375</v>
+        <v>1195.410034179688</v>
       </c>
       <c r="J720" t="n">
         <v>38.86999893188477</v>
@@ -22298,7 +22298,7 @@
         <v>281.3999938964844</v>
       </c>
       <c r="I721" t="n">
-        <v>1192.781616210938</v>
+        <v>1192.781494140625</v>
       </c>
       <c r="J721" t="n">
         <v>39.13999938964844</v>
@@ -22330,7 +22330,7 @@
         <v>295.4500122070312</v>
       </c>
       <c r="I722" t="n">
-        <v>1207.113647460938</v>
+        <v>1207.11376953125</v>
       </c>
       <c r="J722" t="n">
         <v>41.09000015258789</v>
@@ -22362,7 +22362,7 @@
         <v>302.1499938964844</v>
       </c>
       <c r="I723" t="n">
-        <v>1191.0458984375</v>
+        <v>1191.045776367188</v>
       </c>
       <c r="J723" t="n">
         <v>43.13999938964844</v>
@@ -22426,7 +22426,7 @@
         <v>298.3500061035156</v>
       </c>
       <c r="I725" t="n">
-        <v>1185.14453125</v>
+        <v>1185.144409179688</v>
       </c>
       <c r="J725" t="n">
         <v>44.38999938964844</v>
@@ -22618,7 +22618,7 @@
         <v>286.7000122070312</v>
       </c>
       <c r="I731" t="n">
-        <v>1144.231201171875</v>
+        <v>1144.231323242188</v>
       </c>
       <c r="J731" t="n">
         <v>46.70999908447266</v>
@@ -22714,7 +22714,7 @@
         <v>290.2999877929688</v>
       </c>
       <c r="I734" t="n">
-        <v>1070.240234375</v>
+        <v>1070.240356445312</v>
       </c>
       <c r="J734" t="n">
         <v>44.75</v>
@@ -22810,7 +22810,7 @@
         <v>302.1499938964844</v>
       </c>
       <c r="I737" t="n">
-        <v>1035.972412109375</v>
+        <v>1035.972290039062</v>
       </c>
       <c r="J737" t="n">
         <v>44.13000106811523</v>
@@ -22874,7 +22874,7 @@
         <v>297.0499877929688</v>
       </c>
       <c r="I739" t="n">
-        <v>1085.81201171875</v>
+        <v>1085.812133789062</v>
       </c>
       <c r="J739" t="n">
         <v>41.84999847412109</v>
@@ -22906,7 +22906,7 @@
         <v>304.1499938964844</v>
       </c>
       <c r="I740" t="n">
-        <v>1074.157958984375</v>
+        <v>1074.158081054688</v>
       </c>
       <c r="J740" t="n">
         <v>42.59999847412109</v>
@@ -22938,7 +22938,7 @@
         <v>319.2000122070312</v>
       </c>
       <c r="I741" t="n">
-        <v>1075.348266601562</v>
+        <v>1075.34814453125</v>
       </c>
       <c r="J741" t="n">
         <v>44.72999954223633</v>
@@ -23098,7 +23098,7 @@
         <v>302.1499938964844</v>
       </c>
       <c r="I746" t="n">
-        <v>1107.731689453125</v>
+        <v>1107.731567382812</v>
       </c>
       <c r="J746" t="n">
         <v>42.38000106811523</v>
@@ -23130,7 +23130,7 @@
         <v>287.0499877929688</v>
       </c>
       <c r="I747" t="n">
-        <v>1079.563598632812</v>
+        <v>1079.5634765625</v>
       </c>
       <c r="J747" t="n">
         <v>40.2599983215332</v>
@@ -23290,7 +23290,7 @@
         <v>279.2999877929688</v>
       </c>
       <c r="I752" t="n">
-        <v>1016.433227539062</v>
+        <v>1016.433288574219</v>
       </c>
       <c r="J752" t="n">
         <v>41.20000076293945</v>
@@ -23354,7 +23354,7 @@
         <v>280.9500122070312</v>
       </c>
       <c r="I754" t="n">
-        <v>1028.682495117188</v>
+        <v>1028.682373046875</v>
       </c>
       <c r="J754" t="n">
         <v>40.77999877929688</v>
@@ -23546,7 +23546,7 @@
         <v>240.6000061035156</v>
       </c>
       <c r="I760" t="n">
-        <v>913.7286376953125</v>
+        <v>913.7285766601562</v>
       </c>
       <c r="J760" t="n">
         <v>36.84999847412109</v>
@@ -23578,7 +23578,7 @@
         <v>248.25</v>
       </c>
       <c r="I761" t="n">
-        <v>942.98779296875</v>
+        <v>942.9877319335938</v>
       </c>
       <c r="J761" t="n">
         <v>38.65000152587891</v>
@@ -23706,7 +23706,7 @@
         <v>234.0500030517578</v>
       </c>
       <c r="I765" t="n">
-        <v>932.4743041992188</v>
+        <v>932.474365234375</v>
       </c>
       <c r="J765" t="n">
         <v>38</v>
@@ -23834,7 +23834,7 @@
         <v>286.5</v>
       </c>
       <c r="I769" t="n">
-        <v>945.6657104492188</v>
+        <v>945.665771484375</v>
       </c>
       <c r="J769" t="n">
         <v>41.84000015258789</v>
@@ -23866,7 +23866,7 @@
         <v>284.4500122070312</v>
       </c>
       <c r="I770" t="n">
-        <v>928.30859375</v>
+        <v>928.3086547851562</v>
       </c>
       <c r="J770" t="n">
         <v>41</v>
@@ -23930,7 +23930,7 @@
         <v>266.7999877929688</v>
       </c>
       <c r="I772" t="n">
-        <v>890.4204711914062</v>
+        <v>890.4205322265625</v>
       </c>
       <c r="J772" t="n">
         <v>39.45000076293945</v>
@@ -23962,7 +23962,7 @@
         <v>266.7000122070312</v>
       </c>
       <c r="I773" t="n">
-        <v>898.1567993164062</v>
+        <v>898.15673828125</v>
       </c>
       <c r="J773" t="n">
         <v>39.56000137329102</v>
@@ -24026,7 +24026,7 @@
         <v>244.3500061035156</v>
       </c>
       <c r="I775" t="n">
-        <v>836.2662353515625</v>
+        <v>836.2662963867188</v>
       </c>
       <c r="J775" t="n">
         <v>36.93999862670898</v>
@@ -24058,7 +24058,7 @@
         <v>248.6000061035156</v>
       </c>
       <c r="I776" t="n">
-        <v>815.83447265625</v>
+        <v>815.8344116210938</v>
       </c>
       <c r="J776" t="n">
         <v>36.77999877929688</v>
@@ -24186,7 +24186,7 @@
         <v>240.8000030517578</v>
       </c>
       <c r="I780" t="n">
-        <v>826.000732421875</v>
+        <v>826.0007934570312</v>
       </c>
       <c r="J780" t="n">
         <v>36.79999923706055</v>
@@ -24250,7 +24250,7 @@
         <v>222.9499969482422</v>
       </c>
       <c r="I782" t="n">
-        <v>815.884033203125</v>
+        <v>815.8839721679688</v>
       </c>
       <c r="J782" t="n">
         <v>34.75</v>
@@ -24282,7 +24282,7 @@
         <v>211.9499969482422</v>
       </c>
       <c r="I783" t="n">
-        <v>781.3681030273438</v>
+        <v>781.3681640625</v>
       </c>
       <c r="J783" t="n">
         <v>33.2599983215332</v>
@@ -24442,7 +24442,7 @@
         <v>239.3500061035156</v>
       </c>
       <c r="I788" t="n">
-        <v>835.6215209960938</v>
+        <v>835.62158203125</v>
       </c>
       <c r="J788" t="n">
         <v>36.04000091552734</v>
@@ -24570,7 +24570,7 @@
         <v>218.4400024414062</v>
       </c>
       <c r="I792" t="n">
-        <v>780.9217529296875</v>
+        <v>780.9218139648438</v>
       </c>
       <c r="J792" t="n">
         <v>33.38999938964844</v>
@@ -24602,7 +24602,7 @@
         <v>219.3800048828125</v>
       </c>
       <c r="I793" t="n">
-        <v>770.3588256835938</v>
+        <v>770.3587646484375</v>
       </c>
       <c r="J793" t="n">
         <v>33.02000045776367</v>
@@ -24634,7 +24634,7 @@
         <v>219.3800048828125</v>
       </c>
       <c r="I794" t="n">
-        <v>770.3588256835938</v>
+        <v>770.3587646484375</v>
       </c>
       <c r="J794" t="n">
         <v>33.02000045776367</v>
@@ -24826,7 +24826,7 @@
         <v>253.7799987792969</v>
       </c>
       <c r="I800" t="n">
-        <v>802.4942016601562</v>
+        <v>802.4942626953125</v>
       </c>
       <c r="J800" t="n">
         <v>39.47000122070312</v>
@@ -24954,7 +24954,7 @@
         <v>257.2000122070312</v>
       </c>
       <c r="I804" t="n">
-        <v>811.1231689453125</v>
+        <v>811.1232299804688</v>
       </c>
       <c r="J804" t="n">
         <v>42.31000137329102</v>
@@ -24986,7 +24986,7 @@
         <v>262.25</v>
       </c>
       <c r="I805" t="n">
-        <v>818.7603149414062</v>
+        <v>818.7603759765625</v>
       </c>
       <c r="J805" t="n">
         <v>43.15999984741211</v>
@@ -25018,7 +25018,7 @@
         <v>250.3500061035156</v>
       </c>
       <c r="I806" t="n">
-        <v>788.6085205078125</v>
+        <v>788.6085815429688</v>
       </c>
       <c r="J806" t="n">
         <v>41.34999847412109</v>
@@ -25114,7 +25114,7 @@
         <v>243.75</v>
       </c>
       <c r="I809" t="n">
-        <v>774.7228393554688</v>
+        <v>774.7227783203125</v>
       </c>
       <c r="J809" t="n">
         <v>39</v>
@@ -25210,7 +25210,7 @@
         <v>253.1999969482422</v>
       </c>
       <c r="I812" t="n">
-        <v>832.89404296875</v>
+        <v>832.8939819335938</v>
       </c>
       <c r="J812" t="n">
         <v>41.83000183105469</v>
@@ -25338,7 +25338,7 @@
         <v>266.25</v>
       </c>
       <c r="I816" t="n">
-        <v>866.1205444335938</v>
+        <v>866.1204833984375</v>
       </c>
       <c r="J816" t="n">
         <v>43.52999877929688</v>
@@ -25402,7 +25402,7 @@
         <v>256.8999938964844</v>
       </c>
       <c r="I818" t="n">
-        <v>844.3992309570312</v>
+        <v>844.3992919921875</v>
       </c>
       <c r="J818" t="n">
         <v>41.36000061035156</v>
@@ -25434,7 +25434,7 @@
         <v>255.3000030517578</v>
       </c>
       <c r="I819" t="n">
-        <v>861.706787109375</v>
+        <v>861.7068481445312</v>
       </c>
       <c r="J819" t="n">
         <v>41.36000061035156</v>
@@ -25466,7 +25466,7 @@
         <v>256.7000122070312</v>
       </c>
       <c r="I820" t="n">
-        <v>865.0294799804688</v>
+        <v>865.029541015625</v>
       </c>
       <c r="J820" t="n">
         <v>41.0099983215332</v>
@@ -25530,7 +25530,7 @@
         <v>251.75</v>
       </c>
       <c r="I822" t="n">
-        <v>849.7056884765625</v>
+        <v>849.7056274414062</v>
       </c>
       <c r="J822" t="n">
         <v>40.22999954223633</v>
@@ -25594,7 +25594,7 @@
         <v>236.3500061035156</v>
       </c>
       <c r="I824" t="n">
-        <v>841.027099609375</v>
+        <v>841.0270385742188</v>
       </c>
       <c r="J824" t="n">
         <v>38.25</v>
@@ -25882,7 +25882,7 @@
         <v>279.5</v>
       </c>
       <c r="I833" t="n">
-        <v>921.0186157226562</v>
+        <v>921.0185546875</v>
       </c>
       <c r="J833" t="n">
         <v>45.68999862670898</v>
@@ -25914,7 +25914,7 @@
         <v>274.6499938964844</v>
       </c>
       <c r="I834" t="n">
-        <v>912.092041015625</v>
+        <v>912.0921020507812</v>
       </c>
       <c r="J834" t="n">
         <v>44.72999954223633</v>
@@ -26106,7 +26106,7 @@
         <v>308.2999877929688</v>
       </c>
       <c r="I840" t="n">
-        <v>920.7705688476562</v>
+        <v>920.7706298828125</v>
       </c>
       <c r="J840" t="n">
         <v>50.43000030517578</v>
@@ -26266,7 +26266,7 @@
         <v>380.6000061035156</v>
       </c>
       <c r="I845" t="n">
-        <v>941.9464111328125</v>
+        <v>941.9463500976562</v>
       </c>
       <c r="J845" t="n">
         <v>60.93000030517578</v>
@@ -26458,7 +26458,7 @@
         <v>395.4500122070312</v>
       </c>
       <c r="I851" t="n">
-        <v>992.3811645507812</v>
+        <v>992.3812255859375</v>
       </c>
       <c r="J851" t="n">
         <v>69.72000122070312</v>
@@ -26490,7 +26490,7 @@
         <v>384.5499877929688</v>
       </c>
       <c r="I852" t="n">
-        <v>967.08935546875</v>
+        <v>967.0894165039062</v>
       </c>
       <c r="J852" t="n">
         <v>67.05000305175781</v>
@@ -36357,16 +36357,16 @@
         <v>46272</v>
       </c>
       <c r="B1161" t="n">
-        <v>7.829999923706055</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="C1161" t="n">
-        <v>27.96999931335449</v>
+        <v>27.89999961853027</v>
       </c>
       <c r="D1161" t="n">
         <v>10.38000011444092</v>
       </c>
       <c r="E1161" t="n">
-        <v>239.5</v>
+        <v>234.3999938964844</v>
       </c>
       <c r="F1161" t="n">
         <v>27.63999938964844</v>
@@ -36375,7 +36375,7 @@
         <v>1309.5</v>
       </c>
       <c r="H1161" t="n">
-        <v>57.02000045776367</v>
+        <v>58.15999984741211</v>
       </c>
       <c r="I1161" t="n">
         <v>732.4000244140625</v>
@@ -36648,25 +36648,25 @@
         <v>7.050000190734863</v>
       </c>
       <c r="C1170" t="n">
-        <v>26.60000038146973</v>
+        <v>26.6200008392334</v>
       </c>
       <c r="D1170" t="n">
-        <v>9.989999771118164</v>
+        <v>9.979999542236328</v>
       </c>
       <c r="E1170" t="n">
-        <v>231.5</v>
+        <v>229.8899993896484</v>
       </c>
       <c r="F1170" t="n">
-        <v>26.93000030517578</v>
+        <v>27</v>
       </c>
       <c r="G1170" t="n">
-        <v>1243.400024414062</v>
+        <v>1226.400024414062</v>
       </c>
       <c r="H1170" t="n">
         <v>49.9900016784668</v>
       </c>
       <c r="I1170" t="n">
-        <v>703</v>
+        <v>703.1500244140625</v>
       </c>
       <c r="J1170" t="n">
         <v>21.1299991607666</v>
@@ -36746,25 +36746,25 @@
         <v>-17.05882128547219</v>
       </c>
       <c r="C2" t="n">
-        <v>-5.90732242395603</v>
+        <v>-5.836574431597297</v>
       </c>
       <c r="D2" t="n">
-        <v>-6.109027737132589</v>
+        <v>-6.203014847650978</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.081212286893798</v>
+        <v>-4.748293525607772</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.101723254145559</v>
+        <v>-0.8446549618173038</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.631164885351411</v>
+        <v>-3.962409991067928</v>
       </c>
       <c r="H2" t="n">
         <v>-15.82757670952265</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.571866755904232</v>
+        <v>-6.551928632224435</v>
       </c>
       <c r="J2" t="n">
         <v>-4.345862314124171</v>
@@ -37340,7 +37340,7 @@
         <v>22.02878904102883</v>
       </c>
       <c r="I20" t="n">
-        <v>2.551418984708165</v>
+        <v>2.551410974090174</v>
       </c>
       <c r="J20" t="n">
         <v>29.22429859056908</v>
@@ -37372,7 +37372,7 @@
         <v>-15.42298811409775</v>
       </c>
       <c r="I21" t="n">
-        <v>-18.75000158667417</v>
+        <v>-18.74999523997749</v>
       </c>
       <c r="J21" t="n">
         <v>-17.03667200064552</v>
@@ -37404,7 +37404,7 @@
         <v>-17.60644052854861</v>
       </c>
       <c r="I22" t="n">
-        <v>-10.47091074017598</v>
+        <v>-10.47092091451074</v>
       </c>
       <c r="J22" t="n">
         <v>-5.892015050324451</v>
@@ -37436,7 +37436,7 @@
         <v>8.975273108262826</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.731635275646898</v>
+        <v>-7.731624790012059</v>
       </c>
       <c r="J23" t="n">
         <v>10.07751326691555</v>
@@ -37628,7 +37628,7 @@
         <v>20.18634526010754</v>
       </c>
       <c r="I29" t="n">
-        <v>14.89904258694705</v>
+        <v>14.89905459147085</v>
       </c>
       <c r="J29" t="n">
         <v>17.84114543475508</v>
@@ -37660,7 +37660,7 @@
         <v>-6.49240482812462</v>
       </c>
       <c r="I30" t="n">
-        <v>-10.79030993178678</v>
+        <v>-10.79031093750072</v>
       </c>
       <c r="J30" t="n">
         <v>-10.07326035477244</v>
@@ -37692,7 +37692,7 @@
         <v>-34.34213475489638</v>
       </c>
       <c r="I31" t="n">
-        <v>3.869230754336672</v>
+        <v>3.869221073176021</v>
       </c>
       <c r="J31" t="n">
         <v>-3.36283455907771</v>
@@ -37756,7 +37756,7 @@
         <v>-4.392992435061648</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7267397958982569</v>
+        <v>0.7267486143703428</v>
       </c>
       <c r="J33" t="n">
         <v>-18.79194166943702</v>
@@ -37788,7 +37788,7 @@
         <v>10.12869384694794</v>
       </c>
       <c r="I34" t="n">
-        <v>4.617439211995333</v>
+        <v>4.61743963491108</v>
       </c>
       <c r="J34" t="n">
         <v>27.89699662161886</v>
@@ -37820,7 +37820,7 @@
         <v>10.5665365226655</v>
       </c>
       <c r="I35" t="n">
-        <v>23.11872269028099</v>
+        <v>23.11871141371891</v>
       </c>
       <c r="J35" t="n">
         <v>10.16548301327902</v>
@@ -37997,13 +37997,13 @@
         <v>2.446982085920046</v>
       </c>
       <c r="G41" t="n">
-        <v>3.253172538244864</v>
+        <v>3.25318376876691</v>
       </c>
       <c r="H41" t="n">
         <v>2.635488591081314</v>
       </c>
       <c r="I41" t="n">
-        <v>5.350313005783192</v>
+        <v>5.350320191814273</v>
       </c>
       <c r="J41" t="n">
         <v>8.494211565028188</v>
@@ -38026,13 +38026,13 @@
         <v>5.598621951273208</v>
       </c>
       <c r="G42" t="n">
-        <v>2.040911684465785</v>
+        <v>2.040900585798755</v>
       </c>
       <c r="H42" t="n">
         <v>-14.50333586855534</v>
       </c>
       <c r="I42" t="n">
-        <v>7.789059350539329</v>
+        <v>7.789059923220565</v>
       </c>
       <c r="J42" t="n">
         <v>6.147541079717245</v>
@@ -38061,7 +38061,7 @@
         <v>9.220106101738512</v>
       </c>
       <c r="I43" t="n">
-        <v>7.802001872916686</v>
+        <v>7.80199394690444</v>
       </c>
       <c r="J43" t="n">
         <v>22.61306576011055</v>
@@ -38090,7 +38090,7 @@
         <v>10.36725582872331</v>
       </c>
       <c r="I44" t="n">
-        <v>-2.506390909291822</v>
+        <v>-2.506398442968916</v>
       </c>
       <c r="J44" t="n">
         <v>1.53060832255989</v>
@@ -38119,7 +38119,7 @@
         <v>4.476417699780821</v>
       </c>
       <c r="I45" t="n">
-        <v>-7.821843174509246</v>
+        <v>-7.821829485785403</v>
       </c>
       <c r="J45" t="n">
         <v>-23.13725340600107</v>
@@ -38148,7 +38148,7 @@
         <v>-9.150325892060184</v>
       </c>
       <c r="I46" t="n">
-        <v>-7.873144482527428</v>
+        <v>-7.873151044662352</v>
       </c>
       <c r="J46" t="n">
         <v>-11.14982814589901</v>
@@ -38177,7 +38177,7 @@
         <v>-12.68230842551258</v>
       </c>
       <c r="I47" t="n">
-        <v>-10.50509868554349</v>
+        <v>-10.50510919721274</v>
       </c>
       <c r="J47" t="n">
         <v>-10.59189368473866</v>
@@ -38206,7 +38206,7 @@
         <v>11.48815860769938</v>
       </c>
       <c r="I48" t="n">
-        <v>-3.90674987660834</v>
+        <v>-3.906749435665913</v>
       </c>
       <c r="J48" t="n">
         <v>-0.3105661069842447</v>
@@ -38229,13 +38229,13 @@
         <v>-0.696589719615015</v>
       </c>
       <c r="G49" t="n">
-        <v>7.227420215142799</v>
+        <v>7.227408100364263</v>
       </c>
       <c r="H49" t="n">
         <v>3.474762330681291</v>
       </c>
       <c r="I49" t="n">
-        <v>1.992280127469637</v>
+        <v>1.992279898127447</v>
       </c>
       <c r="J49" t="n">
         <v>-1.829263683162408</v>
@@ -38258,13 +38258,13 @@
         <v>-8.498583753085121</v>
       </c>
       <c r="G50" t="n">
-        <v>-9.863711385749763</v>
+        <v>-9.863701201961927</v>
       </c>
       <c r="H50" t="n">
         <v>-15.6172858344184</v>
       </c>
       <c r="I50" t="n">
-        <v>5.378686357567153</v>
+        <v>5.378698488282385</v>
       </c>
       <c r="J50" t="n">
         <v>-2.380950218425493</v>
@@ -38287,13 +38287,13 @@
         <v>8.782737772308536</v>
       </c>
       <c r="G51" t="n">
-        <v>5.463632633860382</v>
+        <v>5.463609979870743</v>
       </c>
       <c r="H51" t="n">
         <v>38.34329813061588</v>
       </c>
       <c r="I51" t="n">
-        <v>4.312858971254707</v>
+        <v>4.312852371434839</v>
       </c>
       <c r="J51" t="n">
         <v>35.48386898298783</v>
@@ -38316,13 +38316,13 @@
         <v>-5.942026774088538</v>
       </c>
       <c r="G52" t="n">
-        <v>-3.320959644468446</v>
+        <v>-3.320928838752191</v>
       </c>
       <c r="H52" t="n">
         <v>29.24944861623748</v>
       </c>
       <c r="I52" t="n">
-        <v>3.064802510321041</v>
+        <v>3.064815751886085</v>
       </c>
       <c r="J52" t="n">
         <v>7.826083639393677</v>
@@ -38345,13 +38345,13 @@
         <v>-8.609271523178808</v>
       </c>
       <c r="G53" t="n">
-        <v>-1.405425570676122</v>
+        <v>-1.40542571455774</v>
       </c>
       <c r="H53" t="n">
         <v>-16.0722547147822</v>
       </c>
       <c r="I53" t="n">
-        <v>2.955478565724423</v>
+        <v>2.955471852145508</v>
       </c>
       <c r="J53" t="n">
         <v>-8.730161493387333</v>
@@ -38374,7 +38374,7 @@
         <v>-12.41298993858072</v>
       </c>
       <c r="G54" t="n">
-        <v>-5.648249785852466</v>
+        <v>-5.648250331436078</v>
       </c>
       <c r="H54" t="n">
         <v>-12.62647164563844</v>
@@ -38403,13 +38403,13 @@
         <v>1.233112628945943</v>
       </c>
       <c r="G55" t="n">
-        <v>5.90190678499245</v>
+        <v>5.901896555568986</v>
       </c>
       <c r="H55" t="n">
         <v>10.01780916676824</v>
       </c>
       <c r="I55" t="n">
-        <v>42.15597528376036</v>
+        <v>42.15598663130014</v>
       </c>
       <c r="J55" t="n">
         <v>5.555555555555558</v>
@@ -38438,7 +38438,7 @@
         <v>7.361381156751889</v>
       </c>
       <c r="I56" t="n">
-        <v>11.44044716830326</v>
+        <v>11.44042835922838</v>
       </c>
       <c r="J56" t="n">
         <v>3.4482743501002</v>
@@ -38467,7 +38467,7 @@
         <v>3.513107684464867</v>
       </c>
       <c r="I57" t="n">
-        <v>-20.63636456057385</v>
+        <v>-20.63635750063468</v>
       </c>
       <c r="J57" t="n">
         <v>-11.82432417193846</v>
@@ -38564,25 +38564,25 @@
         <v>-44.53186333929624</v>
       </c>
       <c r="C2" t="n">
-        <v>-8.87290203905955</v>
+        <v>-8.80438385681307</v>
       </c>
       <c r="D2" t="n">
-        <v>-10.40358643137795</v>
+        <v>-10.49327458585302</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.860027292613142</v>
+        <v>-2.542556087251491</v>
       </c>
       <c r="F2" t="n">
-        <v>-14.75150308611301</v>
+        <v>-14.52991494275721</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.902929055347126</v>
+        <v>-5.216786361107539</v>
       </c>
       <c r="H2" t="n">
         <v>-32.08802980034638</v>
       </c>
       <c r="I2" t="n">
-        <v>-13.75820659450718</v>
+        <v>-13.73980207882673</v>
       </c>
       <c r="J2" t="n">
         <v>-14.93559166276724</v>
@@ -38774,7 +38774,7 @@
         <v>-14.96300514920803</v>
       </c>
       <c r="I8" t="n">
-        <v>-25.40165341174989</v>
+        <v>-25.40166188931352</v>
       </c>
       <c r="J8" t="n">
         <v>0.8920213186065729</v>
@@ -38806,7 +38806,7 @@
         <v>-9.514179193100469</v>
       </c>
       <c r="I9" t="n">
-        <v>-13.68454919940341</v>
+        <v>-13.68453939027434</v>
       </c>
       <c r="J9" t="n">
         <v>-12.45376365041914</v>
@@ -38902,7 +38902,7 @@
         <v>29.14681042220371</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.392582670916979</v>
+        <v>-5.392574005731943</v>
       </c>
       <c r="J12" t="n">
         <v>21.24463916318964</v>
@@ -38934,7 +38934,7 @@
         <v>21.06174227192534</v>
       </c>
       <c r="I13" t="n">
-        <v>40.1330609163993</v>
+        <v>40.13304808147762</v>
       </c>
       <c r="J13" t="n">
         <v>21.03895707563921</v>
@@ -39044,13 +39044,13 @@
         <v>2.321981478994783</v>
       </c>
       <c r="G17" t="n">
-        <v>7.12648200042505</v>
+        <v>7.126469897050725</v>
       </c>
       <c r="H17" t="n">
         <v>0.7315289117223678</v>
       </c>
       <c r="I17" t="n">
-        <v>-12.28810842402225</v>
+        <v>-12.28811852101525</v>
       </c>
       <c r="J17" t="n">
         <v>-12.49999563868442</v>
@@ -39073,13 +39073,13 @@
         <v>-6.376813805621606</v>
       </c>
       <c r="G18" t="n">
-        <v>-8.095933296298796</v>
+        <v>-8.095913369908924</v>
       </c>
       <c r="H18" t="n">
         <v>50.88300138028043</v>
       </c>
       <c r="I18" t="n">
-        <v>13.2924593012159</v>
+        <v>13.29247973056862</v>
       </c>
       <c r="J18" t="n">
         <v>42.60869233504585</v>
@@ -39102,13 +39102,13 @@
         <v>-18.96653110566366</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.484002920704985</v>
+        <v>-1.484013150128449</v>
       </c>
       <c r="H19" t="n">
         <v>-19.32324486904549</v>
       </c>
       <c r="I19" t="n">
-        <v>22.41423489112568</v>
+        <v>22.41423668033238</v>
       </c>
       <c r="J19" t="n">
         <v>-14.81481481481481</v>
@@ -39223,7 +39223,7 @@
         <v>26.11641041112731</v>
       </c>
       <c r="I2" t="n">
-        <v>13.54570754168862</v>
+        <v>13.54569421427558</v>
       </c>
       <c r="J2" t="n">
         <v>84.03669388711693</v>
@@ -39255,7 +39255,7 @@
         <v>16.15136360938538</v>
       </c>
       <c r="I3" t="n">
-        <v>13.18953514511048</v>
+        <v>13.18952182341448</v>
       </c>
       <c r="J3" t="n">
         <v>70.0000032885322</v>
@@ -39287,7 +39287,7 @@
         <v>18.55826056452661</v>
       </c>
       <c r="I4" t="n">
-        <v>15.84090469060915</v>
+        <v>15.84091850541089</v>
       </c>
       <c r="J4" t="n">
         <v>79.47977229122856</v>
@@ -39319,7 +39319,7 @@
         <v>18.42639458918014</v>
       </c>
       <c r="I5" t="n">
-        <v>15.59243490632829</v>
+        <v>15.5924279725592</v>
       </c>
       <c r="J5" t="n">
         <v>78.32370949116567</v>
@@ -39351,7 +39351,7 @@
         <v>20.42312944893776</v>
       </c>
       <c r="I6" t="n">
-        <v>16.8489945570937</v>
+        <v>16.84898733968458</v>
       </c>
       <c r="J6" t="n">
         <v>74.1786665643551</v>
@@ -39383,7 +39383,7 @@
         <v>19.02754764747889</v>
       </c>
       <c r="I7" t="n">
-        <v>14.23302215061948</v>
+        <v>14.23300300571448</v>
       </c>
       <c r="J7" t="n">
         <v>70.31517486505918</v>
@@ -39415,7 +39415,7 @@
         <v>17.59891665078761</v>
       </c>
       <c r="I8" t="n">
-        <v>16.76870935549983</v>
+        <v>16.76871654600964</v>
       </c>
       <c r="J8" t="n">
         <v>64.5479489679206</v>
@@ -39511,7 +39511,7 @@
         <v>13.73462507545713</v>
       </c>
       <c r="I11" t="n">
-        <v>16.10095968062235</v>
+        <v>16.10096676605517</v>
       </c>
       <c r="J11" t="n">
         <v>56.99999959845292</v>
@@ -39639,7 +39639,7 @@
         <v>50.10011067847504</v>
       </c>
       <c r="I15" t="n">
-        <v>12.4430882751237</v>
+        <v>12.44310724452127</v>
       </c>
       <c r="J15" t="n">
         <v>63.25471398498556</v>
@@ -39671,7 +39671,7 @@
         <v>69.59249787931468</v>
       </c>
       <c r="I16" t="n">
-        <v>15.68150654251597</v>
+        <v>15.6815136261576</v>
       </c>
       <c r="J16" t="n">
         <v>71.82033478974208</v>
@@ -39703,7 +39703,7 @@
         <v>80.21875186197276</v>
       </c>
       <c r="I17" t="n">
-        <v>38.57649706808945</v>
+        <v>38.57650560107664</v>
       </c>
       <c r="J17" t="n">
         <v>83.413475601984</v>
@@ -39735,7 +39735,7 @@
         <v>94.03570205320759</v>
       </c>
       <c r="I18" t="n">
-        <v>36.0335018181281</v>
+        <v>36.03351051593013</v>
       </c>
       <c r="J18" t="n">
         <v>117.663043844452</v>
@@ -39767,7 +39767,7 @@
         <v>94.1268552045597</v>
       </c>
       <c r="I19" t="n">
-        <v>32.47951491030909</v>
+        <v>32.47951058552494</v>
       </c>
       <c r="J19" t="n">
         <v>121.3157854582134</v>
@@ -39831,7 +39831,7 @@
         <v>75.75510868409864</v>
       </c>
       <c r="I21" t="n">
-        <v>31.45754638735967</v>
+        <v>31.45755910332362</v>
       </c>
       <c r="J21" t="n">
         <v>142.036550378158</v>
@@ -39895,7 +39895,7 @@
         <v>91.13414267872835</v>
       </c>
       <c r="I23" t="n">
-        <v>30.90391269316848</v>
+        <v>30.90392562284006</v>
       </c>
       <c r="J23" t="n">
         <v>168.1889879197244</v>
@@ -39927,7 +39927,7 @@
         <v>86.52584846797919</v>
       </c>
       <c r="I24" t="n">
-        <v>25.56498092143338</v>
+        <v>25.56498906543911</v>
       </c>
       <c r="J24" t="n">
         <v>182.3157862613076</v>
@@ -39959,7 +39959,7 @@
         <v>71.35134787851175</v>
       </c>
       <c r="I25" t="n">
-        <v>25.73532638273688</v>
+        <v>25.73533458085297</v>
       </c>
       <c r="J25" t="n">
         <v>169.5767290544607</v>
@@ -40023,7 +40023,7 @@
         <v>75.14619883040936</v>
       </c>
       <c r="I27" t="n">
-        <v>22.5987420097109</v>
+        <v>22.59875492383123</v>
       </c>
       <c r="J27" t="n">
         <v>141.9999975907175</v>
@@ -40055,7 +40055,7 @@
         <v>73.99363134446153</v>
       </c>
       <c r="I28" t="n">
-        <v>21.57638252010072</v>
+        <v>21.57639027866838</v>
       </c>
       <c r="J28" t="n">
         <v>151.4062423941993</v>
@@ -40215,7 +40215,7 @@
         <v>69.25088116850071</v>
       </c>
       <c r="I33" t="n">
-        <v>25.14076236892711</v>
+        <v>25.14077025349546</v>
       </c>
       <c r="J33" t="n">
         <v>132.4867699130986</v>
@@ -40247,7 +40247,7 @@
         <v>61.92835542694652</v>
       </c>
       <c r="I34" t="n">
-        <v>22.52247202740185</v>
+        <v>22.52245948834504</v>
       </c>
       <c r="J34" t="n">
         <v>121.4323651658852</v>
@@ -40279,7 +40279,7 @@
         <v>64.23357664233578</v>
       </c>
       <c r="I35" t="n">
-        <v>27.1980016778619</v>
+        <v>27.19799344911933</v>
       </c>
       <c r="J35" t="n">
         <v>137.8151252422787</v>
@@ -40311,7 +40311,7 @@
         <v>56.8334812026194</v>
       </c>
       <c r="I36" t="n">
-        <v>22.65728440839494</v>
+        <v>22.657292123892</v>
       </c>
       <c r="J36" t="n">
         <v>127.3033753857291</v>
@@ -40343,7 +40343,7 @@
         <v>49.29618947317174</v>
       </c>
       <c r="I37" t="n">
-        <v>15.74543755900113</v>
+        <v>15.74542504218792</v>
       </c>
       <c r="J37" t="n">
         <v>111.15383897912</v>
@@ -40375,7 +40375,7 @@
         <v>57.80926505349091</v>
       </c>
       <c r="I38" t="n">
-        <v>16.21144438360587</v>
+        <v>16.21146407658735</v>
       </c>
       <c r="J38" t="n">
         <v>124.1666581895616</v>
@@ -40503,7 +40503,7 @@
         <v>61.70213418337656</v>
       </c>
       <c r="I42" t="n">
-        <v>4.688856355146998</v>
+        <v>4.688868773428356</v>
       </c>
       <c r="J42" t="n">
         <v>126.3361029997708</v>
@@ -40599,7 +40599,7 @@
         <v>71.45801931839102</v>
       </c>
       <c r="I45" t="n">
-        <v>12.16107377611635</v>
+        <v>12.1610683896405</v>
       </c>
       <c r="J45" t="n">
         <v>157.6646515776742</v>
@@ -40631,7 +40631,7 @@
         <v>82.7479978598209</v>
       </c>
       <c r="I46" t="n">
-        <v>8.66180909462404</v>
+        <v>8.661815725075982</v>
       </c>
       <c r="J46" t="n">
         <v>157.8527653163028</v>
@@ -40663,7 +40663,7 @@
         <v>85.00471194850942</v>
       </c>
       <c r="I47" t="n">
-        <v>9.613838637455906</v>
+        <v>9.613845276460232</v>
       </c>
       <c r="J47" t="n">
         <v>151.6363664106889</v>
@@ -40727,7 +40727,7 @@
         <v>71.57738095238095</v>
       </c>
       <c r="I49" t="n">
-        <v>11.99739086546068</v>
+        <v>11.99740976505248</v>
       </c>
       <c r="J49" t="n">
         <v>158.230079573006</v>
@@ -40791,7 +40791,7 @@
         <v>51.29173068418904</v>
       </c>
       <c r="I51" t="n">
-        <v>9.556927218862565</v>
+        <v>9.55694650714236</v>
       </c>
       <c r="J51" t="n">
         <v>127.0114992297709</v>
@@ -40823,7 +40823,7 @@
         <v>48.54479267405647</v>
       </c>
       <c r="I52" t="n">
-        <v>8.042045115715425</v>
+        <v>8.042051785476056</v>
       </c>
       <c r="J52" t="n">
         <v>110.3013757156999</v>
@@ -40887,7 +40887,7 @@
         <v>41.15079311579386</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.52174699598645</v>
+        <v>-1.521758640085147</v>
       </c>
       <c r="J54" t="n">
         <v>86.16581204926534</v>
@@ -40919,7 +40919,7 @@
         <v>36.97116125920574</v>
       </c>
       <c r="I55" t="n">
-        <v>-4.102535207427882</v>
+        <v>-4.102523938621339</v>
       </c>
       <c r="J55" t="n">
         <v>64.87922613616699</v>
@@ -40951,7 +40951,7 @@
         <v>43.77442279436383</v>
       </c>
       <c r="I56" t="n">
-        <v>-3.550945305250486</v>
+        <v>-3.550933979170845</v>
       </c>
       <c r="J56" t="n">
         <v>74.76772784887457</v>
@@ -40983,7 +40983,7 @@
         <v>39.5845017315855</v>
       </c>
       <c r="I57" t="n">
-        <v>-4.840912057172886</v>
+        <v>-4.840889679246652</v>
       </c>
       <c r="J57" t="n">
         <v>61.69810163036917</v>
@@ -41047,7 +41047,7 @@
         <v>42.8926386006018</v>
       </c>
       <c r="I59" t="n">
-        <v>12.67965743132262</v>
+        <v>12.67964407991673</v>
       </c>
       <c r="J59" t="n">
         <v>53.73333401150173</v>
@@ -41079,7 +41079,7 @@
         <v>49.51856946354882</v>
       </c>
       <c r="I60" t="n">
-        <v>5.712399359441078</v>
+        <v>5.712422824596386</v>
       </c>
       <c r="J60" t="n">
         <v>62.82512383653869</v>
@@ -41175,7 +41175,7 @@
         <v>52.72230156143125</v>
       </c>
       <c r="I63" t="n">
-        <v>5.391828203771198</v>
+        <v>5.391816556919182</v>
       </c>
       <c r="J63" t="n">
         <v>75.11312260151992</v>
@@ -41207,7 +41207,7 @@
         <v>52.6315695544544</v>
       </c>
       <c r="I64" t="n">
-        <v>7.77652325112117</v>
+        <v>7.776546118368888</v>
       </c>
       <c r="J64" t="n">
         <v>82.06088167389984</v>
@@ -41239,7 +41239,7 @@
         <v>60.93793770295235</v>
       </c>
       <c r="I65" t="n">
-        <v>7.621096859314291</v>
+        <v>7.621073991852256</v>
       </c>
       <c r="J65" t="n">
         <v>87.27272777051292</v>
@@ -41271,7 +41271,7 @@
         <v>69.55524373430775</v>
       </c>
       <c r="I66" t="n">
-        <v>10.17209649828614</v>
+        <v>10.17210763952565</v>
       </c>
       <c r="J66" t="n">
         <v>92.45901366939118</v>
@@ -41303,7 +41303,7 @@
         <v>74.20005719956657</v>
       </c>
       <c r="I67" t="n">
-        <v>10.42936064238629</v>
+        <v>10.42936182277174</v>
       </c>
       <c r="J67" t="n">
         <v>106.4114841006974</v>
@@ -41335,7 +41335,7 @@
         <v>70.46093895677912</v>
       </c>
       <c r="I68" t="n">
-        <v>8.984565541660317</v>
+        <v>8.984577771064984</v>
       </c>
       <c r="J68" t="n">
         <v>112.8708253134189</v>
@@ -41367,7 +41367,7 @@
         <v>59.75903941285979</v>
       </c>
       <c r="I69" t="n">
-        <v>9.336032225438418</v>
+        <v>9.336020963787828</v>
       </c>
       <c r="J69" t="n">
         <v>106.4651134402253</v>
@@ -41431,7 +41431,7 @@
         <v>51.19813928486645</v>
       </c>
       <c r="I71" t="n">
-        <v>10.13101918945343</v>
+        <v>10.13100675342484</v>
       </c>
       <c r="J71" t="n">
         <v>111.2230221092348</v>
@@ -41495,7 +41495,7 @@
         <v>45.67474432100389</v>
       </c>
       <c r="I73" t="n">
-        <v>5.920006348914786</v>
+        <v>5.919994542787355</v>
       </c>
       <c r="J73" t="n">
         <v>112.7802797593012</v>
@@ -41527,7 +41527,7 @@
         <v>37.45292871774588</v>
       </c>
       <c r="I74" t="n">
-        <v>4.406870864909274</v>
+        <v>4.406859319154965</v>
       </c>
       <c r="J74" t="n">
         <v>103.5775775390632</v>
@@ -41559,7 +41559,7 @@
         <v>30.02268127303005</v>
       </c>
       <c r="I75" t="n">
-        <v>-2.413088070817371</v>
+        <v>-2.413077659927665</v>
       </c>
       <c r="J75" t="n">
         <v>100.9032218686996</v>
@@ -41591,7 +41591,7 @@
         <v>29.75552684353173</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.790587515014507</v>
+        <v>-0.7905768063145135</v>
       </c>
       <c r="J76" t="n">
         <v>87.39039515006255</v>
@@ -41655,7 +41655,7 @@
         <v>37.16040451905292</v>
       </c>
       <c r="I78" t="n">
-        <v>-5.63650099164782</v>
+        <v>-5.636500384992004</v>
       </c>
       <c r="J78" t="n">
         <v>92.88792469130138</v>
@@ -41687,7 +41687,7 @@
         <v>33.92029467705142</v>
       </c>
       <c r="I79" t="n">
-        <v>-10.19616067319565</v>
+        <v>-10.19617003836636</v>
       </c>
       <c r="J79" t="n">
         <v>83.99160638349537</v>
@@ -41751,7 +41751,7 @@
         <v>44.05244047508194</v>
       </c>
       <c r="I81" t="n">
-        <v>-11.30202615532158</v>
+        <v>-11.30204587694931</v>
       </c>
       <c r="J81" t="n">
         <v>86.99152692711512</v>
@@ -41815,7 +41815,7 @@
         <v>41.68852680226573</v>
       </c>
       <c r="I83" t="n">
-        <v>-18.32410639220786</v>
+        <v>-18.32409720995372</v>
       </c>
       <c r="J83" t="n">
         <v>76.21051989103617</v>
@@ -41847,7 +41847,7 @@
         <v>59.40775106485634</v>
       </c>
       <c r="I84" t="n">
-        <v>-12.47749649193932</v>
+        <v>-12.47747784038312</v>
       </c>
       <c r="J84" t="n">
         <v>99.06541697895044</v>
@@ -41879,7 +41879,7 @@
         <v>65.04654719786612</v>
       </c>
       <c r="I85" t="n">
-        <v>-15.66177753902792</v>
+        <v>-15.66179518724001</v>
       </c>
       <c r="J85" t="n">
         <v>97.04844951046681</v>
@@ -42007,7 +42007,7 @@
         <v>62.23793649992655</v>
       </c>
       <c r="I89" t="n">
-        <v>-15.4971246985837</v>
+        <v>-15.49711696089192</v>
       </c>
       <c r="J89" t="n">
         <v>94.18344870303281</v>
@@ -42039,7 +42039,7 @@
         <v>44.01810748398501</v>
       </c>
       <c r="I90" t="n">
-        <v>-16.88543472916736</v>
+        <v>-16.88543627572069</v>
       </c>
       <c r="J90" t="n">
         <v>81.88842255714064</v>
@@ -42071,7 +42071,7 @@
         <v>35.52879303916819</v>
       </c>
       <c r="I91" t="n">
-        <v>-23.03241385408457</v>
+        <v>-23.03242255709873</v>
       </c>
       <c r="J91" t="n">
         <v>68.10019640513771</v>
@@ -42167,7 +42167,7 @@
         <v>18.74325570428619</v>
       </c>
       <c r="I94" t="n">
-        <v>-28.0068053081651</v>
+        <v>-28.00679894982006</v>
       </c>
       <c r="J94" t="n">
         <v>27.89474196050972</v>
@@ -42231,7 +42231,7 @@
         <v>15.89211111741442</v>
       </c>
       <c r="I96" t="n">
-        <v>-23.57127213775751</v>
+        <v>-23.57126754833715</v>
       </c>
       <c r="J96" t="n">
         <v>28.54914740621408</v>
@@ -42295,7 +42295,7 @@
         <v>18.31965290286819</v>
       </c>
       <c r="I98" t="n">
-        <v>-26.40582069621047</v>
+        <v>-26.40582942938569</v>
       </c>
       <c r="J98" t="n">
         <v>32.4025967189887</v>
@@ -42327,7 +42327,7 @@
         <v>15.27719667733658</v>
       </c>
       <c r="I99" t="n">
-        <v>-33.24732339281348</v>
+        <v>-33.24731795382694</v>
       </c>
       <c r="J99" t="n">
         <v>28.97106147384567</v>
@@ -42391,7 +42391,7 @@
         <v>17.94541203322633</v>
       </c>
       <c r="I101" t="n">
-        <v>-31.17109576206706</v>
+        <v>-31.17110158740718</v>
       </c>
       <c r="J101" t="n">
         <v>28.66883782396286</v>
@@ -42423,7 +42423,7 @@
         <v>18.40919658725724</v>
       </c>
       <c r="I102" t="n">
-        <v>-29.82359782494049</v>
+        <v>-29.82360396246734</v>
       </c>
       <c r="J102" t="n">
         <v>28.18636085107484</v>
@@ -42487,7 +42487,7 @@
         <v>9.913208228453851</v>
       </c>
       <c r="I104" t="n">
-        <v>-35.85256845449841</v>
+        <v>-35.85257273941228</v>
       </c>
       <c r="J104" t="n">
         <v>23.86554108948267</v>
@@ -42519,7 +42519,7 @@
         <v>14.53287197231834</v>
       </c>
       <c r="I105" t="n">
-        <v>-33.59567417837825</v>
+        <v>-33.59567847641735</v>
       </c>
       <c r="J105" t="n">
         <v>30.79527080801228</v>
@@ -42647,7 +42647,7 @@
         <v>2.676028157570309</v>
       </c>
       <c r="I109" t="n">
-        <v>-34.05137839494272</v>
+        <v>-34.05136838470172</v>
       </c>
       <c r="J109" t="n">
         <v>26.24584557611403</v>
@@ -42679,7 +42679,7 @@
         <v>6.024615316080983</v>
       </c>
       <c r="I110" t="n">
-        <v>-31.27061043654561</v>
+        <v>-31.27061650294681</v>
       </c>
       <c r="J110" t="n">
         <v>33.22203842896631</v>
@@ -42711,7 +42711,7 @@
         <v>10.12767521636539</v>
       </c>
       <c r="I111" t="n">
-        <v>-30.90739167300298</v>
+        <v>-30.90738562405075</v>
       </c>
       <c r="J111" t="n">
         <v>33.95972882878166</v>
@@ -42775,7 +42775,7 @@
         <v>29.08312860522841</v>
       </c>
       <c r="I113" t="n">
-        <v>-31.15946839130254</v>
+        <v>-31.15945783088099</v>
       </c>
       <c r="J113" t="n">
         <v>45.27778215614377</v>
@@ -42807,7 +42807,7 @@
         <v>32.61072830164626</v>
       </c>
       <c r="I114" t="n">
-        <v>-32.44485757880052</v>
+        <v>-32.44485913828271</v>
       </c>
       <c r="J114" t="n">
         <v>49.6350385796072</v>
@@ -42871,7 +42871,7 @@
         <v>23.26171935995283</v>
       </c>
       <c r="I116" t="n">
-        <v>-36.4457180486654</v>
+        <v>-36.44571369224542</v>
       </c>
       <c r="J116" t="n">
         <v>44.24131704827239</v>
@@ -42903,7 +42903,7 @@
         <v>24.94730195367547</v>
       </c>
       <c r="I117" t="n">
-        <v>-36.19966294916446</v>
+        <v>-36.19966728478108</v>
       </c>
       <c r="J117" t="n">
         <v>38.56393145516608</v>
@@ -42967,7 +42967,7 @@
         <v>20.81582502027968</v>
       </c>
       <c r="I119" t="n">
-        <v>-36.06587516449706</v>
+        <v>-36.0658704982447</v>
       </c>
       <c r="J119" t="n">
         <v>41.26194709591032</v>
@@ -42999,7 +42999,7 @@
         <v>18.29646125327557</v>
       </c>
       <c r="I120" t="n">
-        <v>-38.54754901090875</v>
+        <v>-38.54755360836089</v>
       </c>
       <c r="J120" t="n">
         <v>41.19001864296059</v>
@@ -43031,7 +43031,7 @@
         <v>11.82631761961019</v>
       </c>
       <c r="I121" t="n">
-        <v>-37.32897961116035</v>
+        <v>-37.32898531697771</v>
       </c>
       <c r="J121" t="n">
         <v>43.47825961545257</v>
@@ -43063,7 +43063,7 @@
         <v>10.24109211646398</v>
       </c>
       <c r="I122" t="n">
-        <v>-41.40768769062964</v>
+        <v>-41.40768277612826</v>
       </c>
       <c r="J122" t="n">
         <v>42.65420503705462</v>
@@ -43127,7 +43127,7 @@
         <v>-0.8441437102060356</v>
       </c>
       <c r="I124" t="n">
-        <v>-42.70334513966879</v>
+        <v>-42.70334575751823</v>
       </c>
       <c r="J124" t="n">
         <v>36.54915842401909</v>
@@ -43159,7 +43159,7 @@
         <v>-0.9950223577321893</v>
       </c>
       <c r="I125" t="n">
-        <v>-42.56499686306486</v>
+        <v>-42.56499198767874</v>
       </c>
       <c r="J125" t="n">
         <v>38.07183139644308</v>
@@ -43191,7 +43191,7 @@
         <v>-4.313306030797348</v>
       </c>
       <c r="I126" t="n">
-        <v>-41.76579990753935</v>
+        <v>-41.76580426395932</v>
       </c>
       <c r="J126" t="n">
         <v>36.54223559239848</v>
@@ -43223,7 +43223,7 @@
         <v>-7.626934073983682</v>
       </c>
       <c r="I127" t="n">
-        <v>-45.25499703566405</v>
+        <v>-45.25499275935716</v>
       </c>
       <c r="J127" t="n">
         <v>29.66861136912165</v>
@@ -43255,7 +43255,7 @@
         <v>-9.592997010479355</v>
       </c>
       <c r="I128" t="n">
-        <v>-49.59648269142077</v>
+        <v>-49.59648679341039</v>
       </c>
       <c r="J128" t="n">
         <v>28.59374093124656</v>
@@ -43351,7 +43351,7 @@
         <v>11.20226017119483</v>
       </c>
       <c r="I131" t="n">
-        <v>-41.57756135837645</v>
+        <v>-41.57756646105136</v>
       </c>
       <c r="J131" t="n">
         <v>50.06395514631925</v>
@@ -43383,7 +43383,7 @@
         <v>8.352201320420626</v>
       </c>
       <c r="I132" t="n">
-        <v>-40.50187066692568</v>
+        <v>-40.50186632108546</v>
       </c>
       <c r="J132" t="n">
         <v>48.92561892278942</v>
@@ -43479,7 +43479,7 @@
         <v>-2.809878783828057</v>
       </c>
       <c r="I135" t="n">
-        <v>-44.35211986444345</v>
+        <v>-44.35211507824253</v>
       </c>
       <c r="J135" t="n">
         <v>45.94360305036773</v>
@@ -43511,7 +43511,7 @@
         <v>0.04121654929012397</v>
       </c>
       <c r="I136" t="n">
-        <v>-42.32407443970882</v>
+        <v>-42.32406993188314</v>
       </c>
       <c r="J136" t="n">
         <v>49.730944089708</v>
@@ -43543,7 +43543,7 @@
         <v>-0.8227812344208774</v>
       </c>
       <c r="I137" t="n">
-        <v>-43.53504193146073</v>
+        <v>-43.53504135301615</v>
       </c>
       <c r="J137" t="n">
         <v>46.43016219484324</v>
@@ -43575,7 +43575,7 @@
         <v>-1.909228316656353</v>
       </c>
       <c r="I138" t="n">
-        <v>-42.02479084880196</v>
+        <v>-42.02480076815466</v>
       </c>
       <c r="J138" t="n">
         <v>46.43016219484324</v>
@@ -43607,7 +43607,7 @@
         <v>11.39967947776015</v>
       </c>
       <c r="I139" t="n">
-        <v>-36.11916743903318</v>
+        <v>-36.11916133833199</v>
       </c>
       <c r="J139" t="n">
         <v>75.85081528702973</v>
@@ -43703,7 +43703,7 @@
         <v>2.585262900904595</v>
       </c>
       <c r="I142" t="n">
-        <v>-31.06491760499416</v>
+        <v>-31.06492450679491</v>
       </c>
       <c r="J142" t="n">
         <v>72.89592047478308</v>
@@ -43735,7 +43735,7 @@
         <v>-7.09122645551531</v>
       </c>
       <c r="I143" t="n">
-        <v>-32.10434891982889</v>
+        <v>-32.10435572998518</v>
       </c>
       <c r="J143" t="n">
         <v>60.56033954750786</v>
@@ -43767,7 +43767,7 @@
         <v>5.829856359310237</v>
       </c>
       <c r="I144" t="n">
-        <v>-32.77704585719886</v>
+        <v>-32.77704074443481</v>
       </c>
       <c r="J144" t="n">
         <v>73.11404623446703</v>
@@ -43799,7 +43799,7 @@
         <v>2.334533491450208</v>
       </c>
       <c r="I145" t="n">
-        <v>-33.51296118514819</v>
+        <v>-33.51296794739835</v>
       </c>
       <c r="J145" t="n">
         <v>79.7908029562787</v>
@@ -43895,7 +43895,7 @@
         <v>-6.028498086992817</v>
       </c>
       <c r="I148" t="n">
-        <v>-34.28806060348938</v>
+        <v>-34.28805565881679</v>
       </c>
       <c r="J148" t="n">
         <v>53.29710430619193</v>
@@ -43927,7 +43927,7 @@
         <v>-1.760633823603719</v>
       </c>
       <c r="I149" t="n">
-        <v>-34.87422043175192</v>
+        <v>-34.87420925337283</v>
       </c>
       <c r="J149" t="n">
         <v>56.09403415140542</v>
@@ -43959,7 +43959,7 @@
         <v>-7.602880670023849</v>
       </c>
       <c r="I150" t="n">
-        <v>-37.45698176262956</v>
+        <v>-37.45697692204924</v>
       </c>
       <c r="J150" t="n">
         <v>46.37167601458793</v>
@@ -43991,7 +43991,7 @@
         <v>-10.10608394316426</v>
       </c>
       <c r="I151" t="n">
-        <v>-43.26666186836514</v>
+        <v>-43.26666717142301</v>
       </c>
       <c r="J151" t="n">
         <v>35.01730440420005</v>
@@ -44055,7 +44055,7 @@
         <v>-16.46675455896869</v>
       </c>
       <c r="I153" t="n">
-        <v>-41.94473043279401</v>
+        <v>-41.94472969593319</v>
       </c>
       <c r="J153" t="n">
         <v>22.64151237635372</v>
@@ -44087,7 +44087,7 @@
         <v>-15.20339189949682</v>
       </c>
       <c r="I154" t="n">
-        <v>-40.56723806517864</v>
+        <v>-40.56723259305854</v>
       </c>
       <c r="J154" t="n">
         <v>20.02998683900788</v>
@@ -44119,7 +44119,7 @@
         <v>-14.68718460786851</v>
       </c>
       <c r="I155" t="n">
-        <v>-37.99085613237384</v>
+        <v>-37.99086187941774</v>
       </c>
       <c r="J155" t="n">
         <v>27.69939575660545</v>
@@ -44151,7 +44151,7 @@
         <v>-11.96105995313918</v>
       </c>
       <c r="I156" t="n">
-        <v>-35.97284968089498</v>
+        <v>-35.97285437285689</v>
       </c>
       <c r="J156" t="n">
         <v>34.93548977759578</v>
@@ -44279,7 +44279,7 @@
         <v>33.15829160473547</v>
       </c>
       <c r="I160" t="n">
-        <v>-29.84938784335838</v>
+        <v>-29.84939278684298</v>
       </c>
       <c r="J160" t="n">
         <v>67.10172765520876</v>
@@ -44343,7 +44343,7 @@
         <v>31.94658342227763</v>
       </c>
       <c r="I162" t="n">
-        <v>-31.73167748083034</v>
+        <v>-31.73167254623591</v>
       </c>
       <c r="J162" t="n">
         <v>44.11149655354738</v>
@@ -44375,7 +44375,7 @@
         <v>35.25827976252069</v>
       </c>
       <c r="I163" t="n">
-        <v>-30.97237292020486</v>
+        <v>-30.97236803094082</v>
       </c>
       <c r="J163" t="n">
         <v>47.45098657865709</v>
@@ -44407,7 +44407,7 @@
         <v>31.4724774427817</v>
       </c>
       <c r="I164" t="n">
-        <v>-33.50502602626197</v>
+        <v>-33.50502133447838</v>
       </c>
       <c r="J164" t="n">
         <v>45.68383260132476</v>
@@ -44471,7 +44471,7 @@
         <v>31.32498904941086</v>
       </c>
       <c r="I166" t="n">
-        <v>-34.25830666893714</v>
+        <v>-34.25831760024707</v>
       </c>
       <c r="J166" t="n">
         <v>45.76086589203896</v>
@@ -44503,7 +44503,7 @@
         <v>33.09109889422288</v>
       </c>
       <c r="I167" t="n">
-        <v>-32.89464226978117</v>
+        <v>-32.89463592347094</v>
       </c>
       <c r="J167" t="n">
         <v>48.14546064897016</v>
@@ -44535,7 +44535,7 @@
         <v>23.80828374026902</v>
       </c>
       <c r="I168" t="n">
-        <v>-34.9745393723056</v>
+        <v>-34.97454409134397</v>
       </c>
       <c r="J168" t="n">
         <v>38.0866387959659</v>
@@ -44567,7 +44567,7 @@
         <v>29.44025621625235</v>
       </c>
       <c r="I169" t="n">
-        <v>-35.44473564791697</v>
+        <v>-35.44474177393761</v>
       </c>
       <c r="J169" t="n">
         <v>41.96007874200003</v>
@@ -44599,7 +44599,7 @@
         <v>31.30973250029547</v>
       </c>
       <c r="I170" t="n">
-        <v>-37.60952319348129</v>
+        <v>-37.60951737835894</v>
       </c>
       <c r="J170" t="n">
         <v>40.14651791489481</v>
@@ -44663,7 +44663,7 @@
         <v>44.92055080938697</v>
       </c>
       <c r="I172" t="n">
-        <v>-32.8123236456485</v>
+        <v>-32.81231725705731</v>
       </c>
       <c r="J172" t="n">
         <v>59.58955849005739</v>
@@ -44727,7 +44727,7 @@
         <v>59.09223654259699</v>
       </c>
       <c r="I174" t="n">
-        <v>-27.84140135315001</v>
+        <v>-27.84139423196488</v>
       </c>
       <c r="J174" t="n">
         <v>72.74854593479307</v>
@@ -44823,7 +44823,7 @@
         <v>71.52501088341694</v>
       </c>
       <c r="I177" t="n">
-        <v>-22.33078034924558</v>
+        <v>-22.33077750093369</v>
       </c>
       <c r="J177" t="n">
         <v>83.1262414010687</v>
@@ -44855,7 +44855,7 @@
         <v>66.75774073195311</v>
       </c>
       <c r="I178" t="n">
-        <v>-21.79922553387539</v>
+        <v>-21.79922030085473</v>
       </c>
       <c r="J178" t="n">
         <v>83.31967312108763</v>
@@ -44887,7 +44887,7 @@
         <v>61.06736588618858</v>
       </c>
       <c r="I179" t="n">
-        <v>-24.21510239292522</v>
+        <v>-24.21511007080047</v>
       </c>
       <c r="J179" t="n">
         <v>75.58593786379788</v>
@@ -44919,7 +44919,7 @@
         <v>65.15150572053405</v>
       </c>
       <c r="I180" t="n">
-        <v>-25.31921329761254</v>
+        <v>-25.31919824707868</v>
       </c>
       <c r="J180" t="n">
         <v>72.82946306655833</v>
@@ -44983,7 +44983,7 @@
         <v>72.57494253958269</v>
       </c>
       <c r="I182" t="n">
-        <v>-25.49482362062903</v>
+        <v>-25.49483107255582</v>
       </c>
       <c r="J182" t="n">
         <v>93.80497531351087</v>
@@ -45047,7 +45047,7 @@
         <v>84.22466480357787</v>
       </c>
       <c r="I184" t="n">
-        <v>-25.14133965790279</v>
+        <v>-25.14133469574373</v>
       </c>
       <c r="J184" t="n">
         <v>90.30188794405956</v>
@@ -45143,7 +45143,7 @@
         <v>109.9117682961857</v>
       </c>
       <c r="I187" t="n">
-        <v>-23.41613770201895</v>
+        <v>-23.41613005209735</v>
       </c>
       <c r="J187" t="n">
         <v>144.9407236737255</v>
@@ -45207,7 +45207,7 @@
         <v>123.2258100313875</v>
       </c>
       <c r="I189" t="n">
-        <v>-21.52762332811739</v>
+        <v>-21.52762841287986</v>
       </c>
       <c r="J189" t="n">
         <v>141.7857081765763</v>
@@ -45271,7 +45271,7 @@
         <v>123.5046433130916</v>
       </c>
       <c r="I191" t="n">
-        <v>-17.95775563916884</v>
+        <v>-17.95774706748667</v>
       </c>
       <c r="J191" t="n">
         <v>151.0794350518636</v>
@@ -45335,7 +45335,7 @@
         <v>159.4421378782054</v>
       </c>
       <c r="I193" t="n">
-        <v>-7.811480422264172</v>
+        <v>-7.811469801544069</v>
       </c>
       <c r="J193" t="n">
         <v>190.7755014847736</v>
@@ -45399,7 +45399,7 @@
         <v>150.8404868487914</v>
       </c>
       <c r="I195" t="n">
-        <v>-14.28143416458211</v>
+        <v>-14.28142889256946</v>
       </c>
       <c r="J195" t="n">
         <v>183.9918671584078</v>
@@ -45431,7 +45431,7 @@
         <v>129.1716214536388</v>
       </c>
       <c r="I196" t="n">
-        <v>-19.293970617628</v>
+        <v>-19.29395730250751</v>
       </c>
       <c r="J196" t="n">
         <v>168.2000122070312</v>
@@ -45495,7 +45495,7 @@
         <v>94.45324890083117</v>
       </c>
       <c r="I198" t="n">
-        <v>-28.42349396691873</v>
+        <v>-28.42348749687464</v>
       </c>
       <c r="J198" t="n">
         <v>121.8619260496735</v>
@@ -45655,7 +45655,7 @@
         <v>83.68124127503025</v>
       </c>
       <c r="I203" t="n">
-        <v>-28.09563932936137</v>
+        <v>-28.09564597547907</v>
       </c>
       <c r="J203" t="n">
         <v>106.2277067414659</v>
@@ -45719,7 +45719,7 @@
         <v>94.32029234930152</v>
       </c>
       <c r="I205" t="n">
-        <v>-27.08600683553397</v>
+        <v>-27.0860000922971</v>
       </c>
       <c r="J205" t="n">
         <v>122.9661754366069</v>
@@ -45943,7 +45943,7 @@
         <v>98.29378184219588</v>
       </c>
       <c r="I212" t="n">
-        <v>-31.41072207146195</v>
+        <v>-31.41071594212068</v>
       </c>
       <c r="J212" t="n">
         <v>127.3423849684713</v>
@@ -45975,7 +45975,7 @@
         <v>101.0606230012067</v>
       </c>
       <c r="I213" t="n">
-        <v>-31.06073388270728</v>
+        <v>-31.06074006982888</v>
       </c>
       <c r="J213" t="n">
         <v>129.4573808043165</v>
@@ -46071,7 +46071,7 @@
         <v>88.96002855288734</v>
       </c>
       <c r="I216" t="n">
-        <v>-32.92036549394376</v>
+        <v>-32.92037140574799</v>
       </c>
       <c r="J216" t="n">
         <v>128.768082361913</v>
@@ -46327,7 +46327,7 @@
         <v>108.4021066095138</v>
       </c>
       <c r="I224" t="n">
-        <v>-23.58793790131195</v>
+        <v>-23.58793030177627</v>
       </c>
       <c r="J224" t="n">
         <v>132.0058857738733</v>
@@ -46391,7 +46391,7 @@
         <v>95.15328519545527</v>
       </c>
       <c r="I226" t="n">
-        <v>-27.24829383266478</v>
+        <v>-27.24830098065127</v>
       </c>
       <c r="J226" t="n">
         <v>110.7646535029406</v>
@@ -46615,7 +46615,7 @@
         <v>31.20220243440443</v>
       </c>
       <c r="I233" t="n">
-        <v>-32.79412256434421</v>
+        <v>-32.79411610687446</v>
       </c>
       <c r="J233" t="n">
         <v>37.38601418418006</v>
@@ -46647,7 +46647,7 @@
         <v>36.77451609649452</v>
       </c>
       <c r="I234" t="n">
-        <v>-32.68281725784399</v>
+        <v>-32.68282383642989</v>
       </c>
       <c r="J234" t="n">
         <v>37.40589990296488</v>
@@ -46743,7 +46743,7 @@
         <v>28.45130029759806</v>
       </c>
       <c r="I237" t="n">
-        <v>-30.34968049155801</v>
+        <v>-30.34968755706141</v>
       </c>
       <c r="J237" t="n">
         <v>37.53923055665842</v>
@@ -46807,7 +46807,7 @@
         <v>11.90330802341504</v>
       </c>
       <c r="I239" t="n">
-        <v>-29.36256590952326</v>
+        <v>-29.36257314192705</v>
       </c>
       <c r="J239" t="n">
         <v>30.84777634543028</v>
@@ -46903,7 +46903,7 @@
         <v>24.7957124658932</v>
       </c>
       <c r="I242" t="n">
-        <v>-20.23049029750423</v>
+        <v>-20.2304989019239</v>
       </c>
       <c r="J242" t="n">
         <v>52.73949118221508</v>
@@ -46967,7 +46967,7 @@
         <v>34.13228966130708</v>
       </c>
       <c r="I244" t="n">
-        <v>-23.2433353276135</v>
+        <v>-23.24332750705954</v>
       </c>
       <c r="J244" t="n">
         <v>52.75998400130671</v>
@@ -47031,7 +47031,7 @@
         <v>13.38954626727096</v>
       </c>
       <c r="I246" t="n">
-        <v>-26.33157398867555</v>
+        <v>-26.33158144856611</v>
       </c>
       <c r="J246" t="n">
         <v>28.55561668266151</v>
@@ -47127,7 +47127,7 @@
         <v>28.24667177580864</v>
       </c>
       <c r="I249" t="n">
-        <v>-27.19372245264892</v>
+        <v>-27.19372983830064</v>
       </c>
       <c r="J249" t="n">
         <v>34.10686463800094</v>
@@ -47223,7 +47223,7 @@
         <v>38.13899279483215</v>
       </c>
       <c r="I252" t="n">
-        <v>-22.31719283864492</v>
+        <v>-22.31720071184628</v>
       </c>
       <c r="J252" t="n">
         <v>56.19888935780564</v>
@@ -47447,7 +47447,7 @@
         <v>17.21369395430563</v>
       </c>
       <c r="I259" t="n">
-        <v>-20.11944409895419</v>
+        <v>-20.11943557814434</v>
       </c>
       <c r="J259" t="n">
         <v>54.07133907621559</v>
@@ -47703,7 +47703,7 @@
         <v>-9.789748048156266</v>
       </c>
       <c r="I267" t="n">
-        <v>-20.82639503526708</v>
+        <v>-20.82640358515051</v>
       </c>
       <c r="J267" t="n">
         <v>34.23865433442628</v>
@@ -47831,7 +47831,7 @@
         <v>-27.76584214756481</v>
       </c>
       <c r="I271" t="n">
-        <v>-32.16929289143484</v>
+        <v>-32.16928633245178</v>
       </c>
       <c r="J271" t="n">
         <v>5.493463531992426</v>
@@ -47895,7 +47895,7 @@
         <v>-22.71868945740797</v>
       </c>
       <c r="I273" t="n">
-        <v>-29.55400530838046</v>
+        <v>-29.55401212266132</v>
       </c>
       <c r="J273" t="n">
         <v>0.2804769630959436</v>
@@ -47959,7 +47959,7 @@
         <v>-29.18674514954349</v>
       </c>
       <c r="I275" t="n">
-        <v>-27.13680635595359</v>
+        <v>-27.13681355281311</v>
       </c>
       <c r="J275" t="n">
         <v>-12.78136378898818</v>
@@ -48087,7 +48087,7 @@
         <v>-20.91819495708994</v>
       </c>
       <c r="I279" t="n">
-        <v>-21.13047219079976</v>
+        <v>-21.13048049863758</v>
       </c>
       <c r="J279" t="n">
         <v>0.5219697278298963</v>
@@ -48311,7 +48311,7 @@
         <v>-17.3628377931779</v>
       </c>
       <c r="I286" t="n">
-        <v>-23.84494252383033</v>
+        <v>-23.84493473005442</v>
       </c>
       <c r="J286" t="n">
         <v>8.001916670527965</v>
@@ -48407,7 +48407,7 @@
         <v>-15.80435876850455</v>
       </c>
       <c r="I289" t="n">
-        <v>-19.52015837880386</v>
+        <v>-19.52014967564222</v>
       </c>
       <c r="J289" t="n">
         <v>13.66120207730763</v>
@@ -48439,7 +48439,7 @@
         <v>-18.49578771778532</v>
       </c>
       <c r="I290" t="n">
-        <v>-19.80675285177297</v>
+        <v>-19.80676144690814</v>
       </c>
       <c r="J290" t="n">
         <v>14.74597518697689</v>
@@ -48663,7 +48663,7 @@
         <v>-41.72135295266101</v>
       </c>
       <c r="I297" t="n">
-        <v>-22.88070596826082</v>
+        <v>-22.88069753552291</v>
       </c>
       <c r="J297" t="n">
         <v>-4.48524369027955</v>
@@ -48791,7 +48791,7 @@
         <v>-35.27146510631234</v>
       </c>
       <c r="I301" t="n">
-        <v>-23.42535204198196</v>
+        <v>-23.42536032537918</v>
       </c>
       <c r="J301" t="n">
         <v>-5.574591275281082</v>
@@ -48855,7 +48855,7 @@
         <v>-31.05525941638822</v>
       </c>
       <c r="I303" t="n">
-        <v>-20.082786803478</v>
+        <v>-20.08279589388603</v>
       </c>
       <c r="J303" t="n">
         <v>1.417724995673453</v>
@@ -49143,7 +49143,7 @@
         <v>-39.16467071785878</v>
       </c>
       <c r="I312" t="n">
-        <v>-23.67828830810955</v>
+        <v>-23.67829654351601</v>
       </c>
       <c r="J312" t="n">
         <v>7.188093354284919</v>
@@ -49271,7 +49271,7 @@
         <v>-43.54679306508746</v>
       </c>
       <c r="I316" t="n">
-        <v>-30.43281399248713</v>
+        <v>-30.43282109639951</v>
       </c>
       <c r="J316" t="n">
         <v>-3.061483559066525</v>
@@ -49303,7 +49303,7 @@
         <v>-47.77185344404541</v>
       </c>
       <c r="I317" t="n">
-        <v>-31.74837510836619</v>
+        <v>-31.74836812343457</v>
       </c>
       <c r="J317" t="n">
         <v>-9.555436694152498</v>
@@ -49335,7 +49335,7 @@
         <v>-52.72973501715575</v>
       </c>
       <c r="I318" t="n">
-        <v>-32.59171223647252</v>
+        <v>-32.59171905318771</v>
       </c>
       <c r="J318" t="n">
         <v>-13.31224434263872</v>
@@ -49367,7 +49367,7 @@
         <v>-55.27717768906935</v>
       </c>
       <c r="I319" t="n">
-        <v>-31.59040521272418</v>
+        <v>-31.59039820142303</v>
       </c>
       <c r="J319" t="n">
         <v>-21.23319419798155</v>
@@ -49431,7 +49431,7 @@
         <v>-54.49974954822018</v>
       </c>
       <c r="I321" t="n">
-        <v>-30.81718734034944</v>
+        <v>-30.81718021449415</v>
       </c>
       <c r="J321" t="n">
         <v>-22.21221163758537</v>
@@ -49623,7 +49623,7 @@
         <v>-39.58842358779834</v>
       </c>
       <c r="I327" t="n">
-        <v>-28.95246535407854</v>
+        <v>-28.9524729336602</v>
       </c>
       <c r="J327" t="n">
         <v>-24.47013600772119</v>
@@ -49719,7 +49719,7 @@
         <v>-40.33758035437396</v>
       </c>
       <c r="I330" t="n">
-        <v>-23.96618818241377</v>
+        <v>-23.96619685473781</v>
       </c>
       <c r="J330" t="n">
         <v>-18.34636666921264</v>
@@ -49815,7 +49815,7 @@
         <v>-45.54360529211075</v>
       </c>
       <c r="I333" t="n">
-        <v>-22.58020975443182</v>
+        <v>-22.58020063193108</v>
       </c>
       <c r="J333" t="n">
         <v>-21.02878397775322</v>
@@ -49879,7 +49879,7 @@
         <v>-44.60865172604881</v>
       </c>
       <c r="I335" t="n">
-        <v>-25.07035435299852</v>
+        <v>-25.07036277681787</v>
       </c>
       <c r="J335" t="n">
         <v>-14.14575480237133</v>
@@ -49911,7 +49911,7 @@
         <v>-48.60430364584478</v>
       </c>
       <c r="I336" t="n">
-        <v>-24.60030124432042</v>
+        <v>-24.60030981295194</v>
       </c>
       <c r="J336" t="n">
         <v>-15.84507099008591</v>
@@ -49943,7 +49943,7 @@
         <v>-51.0275685005831</v>
       </c>
       <c r="I337" t="n">
-        <v>-25.72519486044957</v>
+        <v>-25.72518642899533</v>
       </c>
       <c r="J337" t="n">
         <v>-21.41738903286038</v>
@@ -50103,7 +50103,7 @@
         <v>-50.84891692643389</v>
       </c>
       <c r="I342" t="n">
-        <v>-30.42624869717885</v>
+        <v>-30.42624103025863</v>
       </c>
       <c r="J342" t="n">
         <v>-21.04766814258902</v>
@@ -50135,7 +50135,7 @@
         <v>-48.263368464608</v>
       </c>
       <c r="I343" t="n">
-        <v>-29.51919907596125</v>
+        <v>-29.51919110643136</v>
       </c>
       <c r="J343" t="n">
         <v>-17.58568880160797</v>
@@ -50295,7 +50295,7 @@
         <v>-49.48442445243727</v>
       </c>
       <c r="I348" t="n">
-        <v>-31.66427293856655</v>
+        <v>-31.66427704201518</v>
       </c>
       <c r="J348" t="n">
         <v>-28.13106781059436</v>
@@ -50359,7 +50359,7 @@
         <v>-49.7811033252699</v>
       </c>
       <c r="I350" t="n">
-        <v>-32.73928211656697</v>
+        <v>-32.73927413496151</v>
       </c>
       <c r="J350" t="n">
         <v>-30.67679915646358</v>
@@ -50551,7 +50551,7 @@
         <v>-47.48545500046233</v>
       </c>
       <c r="I356" t="n">
-        <v>-19.94135144179933</v>
+        <v>-19.94134609404918</v>
       </c>
       <c r="J356" t="n">
         <v>-23.55494913771275</v>
@@ -50583,7 +50583,7 @@
         <v>-46.56193205957327</v>
       </c>
       <c r="I357" t="n">
-        <v>-21.40143581400335</v>
+        <v>-21.40143072668833</v>
       </c>
       <c r="J357" t="n">
         <v>-25.1228993751003</v>
@@ -50711,7 +50711,7 @@
         <v>-48.79726777384864</v>
       </c>
       <c r="I361" t="n">
-        <v>-16.44786678377885</v>
+        <v>-16.44787225268791</v>
       </c>
       <c r="J361" t="n">
         <v>-25.10526556717722</v>
@@ -50839,7 +50839,7 @@
         <v>-65.47643851235274</v>
       </c>
       <c r="I365" t="n">
-        <v>-22.14507660393162</v>
+        <v>-22.14508162884377</v>
       </c>
       <c r="J365" t="n">
         <v>-36.2810713427707</v>
@@ -50871,7 +50871,7 @@
         <v>-63.49094954563196</v>
       </c>
       <c r="I366" t="n">
-        <v>-20.31942334639192</v>
+        <v>-20.31942858529217</v>
       </c>
       <c r="J366" t="n">
         <v>-33.34146360071693</v>
@@ -50935,7 +50935,7 @@
         <v>-59.44152772284181</v>
       </c>
       <c r="I368" t="n">
-        <v>-19.10899357438787</v>
+        <v>-19.10899911917826</v>
       </c>
       <c r="J368" t="n">
         <v>-32.21799935619129</v>
@@ -50967,7 +50967,7 @@
         <v>-61.07611818254843</v>
       </c>
       <c r="I369" t="n">
-        <v>-19.0520801981543</v>
+        <v>-19.05207469725594</v>
       </c>
       <c r="J369" t="n">
         <v>-33.64509836007559</v>
@@ -51031,7 +51031,7 @@
         <v>-60.87988788615164</v>
       </c>
       <c r="I371" t="n">
-        <v>-15.5312900461311</v>
+        <v>-15.53129621110622</v>
       </c>
       <c r="J371" t="n">
         <v>-31.13156069349836</v>
@@ -51063,7 +51063,7 @@
         <v>-60.72807930150839</v>
       </c>
       <c r="I372" t="n">
-        <v>-13.58057886234917</v>
+        <v>-13.58057239703857</v>
       </c>
       <c r="J372" t="n">
         <v>-30.56008220994402</v>
@@ -51191,7 +51191,7 @@
         <v>-64.01993426427576</v>
       </c>
       <c r="I376" t="n">
-        <v>-19.42269217116194</v>
+        <v>-19.42269812521018</v>
       </c>
       <c r="J376" t="n">
         <v>-37.03804196560988</v>
@@ -51255,7 +51255,7 @@
         <v>-57.84704882559338</v>
       </c>
       <c r="I378" t="n">
-        <v>-16.06874881989406</v>
+        <v>-16.06874254111276</v>
       </c>
       <c r="J378" t="n">
         <v>-35.42445889479823</v>
@@ -51287,7 +51287,7 @@
         <v>-57.86270401296439</v>
       </c>
       <c r="I379" t="n">
-        <v>-14.80091095603907</v>
+        <v>-14.80091761121131</v>
       </c>
       <c r="J379" t="n">
         <v>-33.13288967690797</v>
@@ -51447,7 +51447,7 @@
         <v>-66.06225139522131</v>
       </c>
       <c r="I384" t="n">
-        <v>-24.65691069119804</v>
+        <v>-24.65691619437953</v>
       </c>
       <c r="J384" t="n">
         <v>-37.79134432087488</v>
@@ -51575,7 +51575,7 @@
         <v>-64.53946245251012</v>
       </c>
       <c r="I388" t="n">
-        <v>-8.856572706876376</v>
+        <v>-8.856579830449085</v>
       </c>
       <c r="J388" t="n">
         <v>-32.25516246566315</v>
@@ -51607,7 +51607,7 @@
         <v>-66.45546781840915</v>
       </c>
       <c r="I389" t="n">
-        <v>-14.83677254133186</v>
+        <v>-14.83676579389011</v>
       </c>
       <c r="J389" t="n">
         <v>-36.49303748442554</v>
@@ -51639,7 +51639,7 @@
         <v>-66.94776163626966</v>
       </c>
       <c r="I390" t="n">
-        <v>-13.80300167356505</v>
+        <v>-13.80299484421812</v>
       </c>
       <c r="J390" t="n">
         <v>-35.19079551224324</v>
@@ -51831,7 +51831,7 @@
         <v>-69.6705801911359</v>
       </c>
       <c r="I396" t="n">
-        <v>-15.75994642557669</v>
+        <v>-15.75995283260672</v>
       </c>
       <c r="J396" t="n">
         <v>-40.96782742221188</v>
@@ -51959,7 +51959,7 @@
         <v>-65.36158938197161</v>
       </c>
       <c r="I400" t="n">
-        <v>-10.88795150315567</v>
+        <v>-10.88795820863222</v>
       </c>
       <c r="J400" t="n">
         <v>-40.41598140815249</v>
@@ -51991,7 +51991,7 @@
         <v>-66.77216419841814</v>
       </c>
       <c r="I401" t="n">
-        <v>-12.15684976535586</v>
+        <v>-12.15685631369474</v>
       </c>
       <c r="J401" t="n">
         <v>-39.50416890022966</v>
@@ -52023,7 +52023,7 @@
         <v>-65.19273127014925</v>
       </c>
       <c r="I402" t="n">
-        <v>2.310069794177694</v>
+        <v>2.310061875786684</v>
       </c>
       <c r="J402" t="n">
         <v>-30.01208802421185</v>
@@ -52119,7 +52119,7 @@
         <v>-66.03487141927083</v>
       </c>
       <c r="I405" t="n">
-        <v>1.368362031563874</v>
+        <v>1.36837001768999</v>
       </c>
       <c r="J405" t="n">
         <v>-27.97435858310797</v>
@@ -52215,7 +52215,7 @@
         <v>-67.3025268904522</v>
       </c>
       <c r="I408" t="n">
-        <v>-5.191528209890328</v>
+        <v>-5.191521262247512</v>
       </c>
       <c r="J408" t="n">
         <v>-28.0659841371343</v>
@@ -52343,7 +52343,7 @@
         <v>-70.45633665272888</v>
       </c>
       <c r="I412" t="n">
-        <v>-8.24245399340221</v>
+        <v>-8.242447527285467</v>
       </c>
       <c r="J412" t="n">
         <v>-33.40224997914316</v>
@@ -52407,7 +52407,7 @@
         <v>-69.38107998017129</v>
       </c>
       <c r="I414" t="n">
-        <v>-7.644544630986704</v>
+        <v>-7.644551306655078</v>
       </c>
       <c r="J414" t="n">
         <v>-30.8268854251635</v>
@@ -52439,7 +52439,7 @@
         <v>-70.72855367660009</v>
       </c>
       <c r="I415" t="n">
-        <v>-8.69664441737773</v>
+        <v>-8.696650884443169</v>
       </c>
       <c r="J415" t="n">
         <v>-30.53675261541027</v>
@@ -52471,7 +52471,7 @@
         <v>-70.8881964147851</v>
       </c>
       <c r="I416" t="n">
-        <v>-5.721565130794593</v>
+        <v>-5.721571782936197</v>
       </c>
       <c r="J416" t="n">
         <v>-30.8217459147344</v>
@@ -52535,7 +52535,7 @@
         <v>-70.31578814024485</v>
       </c>
       <c r="I418" t="n">
-        <v>-6.077385767619159</v>
+        <v>-6.07737902106924</v>
       </c>
       <c r="J418" t="n">
         <v>-27.61620390111826</v>
@@ -52599,7 +52599,7 @@
         <v>-69.95980614914657</v>
       </c>
       <c r="I420" t="n">
-        <v>-8.179717415606557</v>
+        <v>-8.179710752009505</v>
       </c>
       <c r="J420" t="n">
         <v>-26.82353001014859</v>
@@ -52887,7 +52887,7 @@
         <v>-75.86762184320494</v>
       </c>
       <c r="I429" t="n">
-        <v>-18.76463099427176</v>
+        <v>-18.76462561086942</v>
       </c>
       <c r="J429" t="n">
         <v>-40.73101173639364</v>
@@ -52919,7 +52919,7 @@
         <v>-76.66848598030319</v>
       </c>
       <c r="I430" t="n">
-        <v>-17.167396650204</v>
+        <v>-17.1674021931759</v>
       </c>
       <c r="J430" t="n">
         <v>-40.24144910398108</v>
@@ -53111,7 +53111,7 @@
         <v>-77.08725196671594</v>
       </c>
       <c r="I436" t="n">
-        <v>-19.52655806860775</v>
+        <v>-19.52656340295372</v>
       </c>
       <c r="J436" t="n">
         <v>-46.51993029913489</v>
@@ -53271,7 +53271,7 @@
         <v>-77.44613900123169</v>
       </c>
       <c r="I441" t="n">
-        <v>-17.76891500921736</v>
+        <v>-17.76890968090208</v>
       </c>
       <c r="J441" t="n">
         <v>-54.40669531018253</v>
@@ -53463,7 +53463,7 @@
         <v>-79.37792374904173</v>
       </c>
       <c r="I447" t="n">
-        <v>-11.55112255709438</v>
+        <v>-11.5511279970311</v>
       </c>
       <c r="J447" t="n">
         <v>-61.48881251956044</v>
@@ -53495,7 +53495,7 @@
         <v>-78.79339341036149</v>
       </c>
       <c r="I448" t="n">
-        <v>-10.86656107571498</v>
+        <v>-10.86656670112384</v>
       </c>
       <c r="J448" t="n">
         <v>-60.23862992693305</v>
@@ -55298,16 +55298,16 @@
         <v>46272</v>
       </c>
       <c r="B505" t="n">
-        <v>-56.95437221650577</v>
+        <v>-58.21880329028639</v>
       </c>
       <c r="C505" t="n">
-        <v>-23.01129120933353</v>
+        <v>-23.20396858697237</v>
       </c>
       <c r="D505" t="n">
         <v>-29.24335337111192</v>
       </c>
       <c r="E505" t="n">
-        <v>-22.42336823321735</v>
+        <v>-24.07531518729157</v>
       </c>
       <c r="F505" t="n">
         <v>-48.81481594509549</v>
@@ -55316,7 +55316,7 @@
         <v>-3.218229799938421</v>
       </c>
       <c r="H505" t="n">
-        <v>-80.16005509091934</v>
+        <v>-79.76339558714112</v>
       </c>
       <c r="I505" t="n">
         <v>-19.90689967245617</v>
@@ -55589,25 +55589,25 @@
         <v>-62.73784269394243</v>
       </c>
       <c r="C514" t="n">
-        <v>-27.24289009216938</v>
+        <v>-27.18818424694947</v>
       </c>
       <c r="D514" t="n">
-        <v>-33.5329344736901</v>
+        <v>-33.59946959717316</v>
       </c>
       <c r="E514" t="n">
-        <v>-26.5340647329533</v>
+        <v>-27.04499432526428</v>
       </c>
       <c r="F514" t="n">
-        <v>-52.09889768686317</v>
+        <v>-51.97438738215965</v>
       </c>
       <c r="G514" t="n">
-        <v>-11.64599493761009</v>
+        <v>-12.85398758403813</v>
       </c>
       <c r="H514" t="n">
         <v>-81.5840856767617</v>
       </c>
       <c r="I514" t="n">
-        <v>-23.71576633057664</v>
+        <v>-23.69948681783345</v>
       </c>
       <c r="J514" t="n">
         <v>-56.72742500835124</v>

--- a/dashboards/Reliance Group.xlsx
+++ b/dashboards/Reliance Group.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1170"/>
+  <dimension ref="A1:J1171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,13 +493,13 @@
         <v>91.84999847412109</v>
       </c>
       <c r="G2" t="n">
-        <v>1088.746704101562</v>
+        <v>1088.74658203125</v>
       </c>
       <c r="H2" t="n">
         <v>100.8000030517578</v>
       </c>
       <c r="I2" t="n">
-        <v>850.6759643554688</v>
+        <v>850.676025390625</v>
       </c>
       <c r="J2" t="n">
         <v>14.25</v>
@@ -528,7 +528,7 @@
         <v>97.5</v>
       </c>
       <c r="I3" t="n">
-        <v>857.11083984375</v>
+        <v>857.1109008789062</v>
       </c>
       <c r="J3" t="n">
         <v>13.89999961853027</v>
@@ -580,7 +580,7 @@
         <v>89.90000152587891</v>
       </c>
       <c r="G5" t="n">
-        <v>1094.47607421875</v>
+        <v>1094.476196289062</v>
       </c>
       <c r="H5" t="n">
         <v>100.1500015258789</v>
@@ -609,13 +609,13 @@
         <v>91</v>
       </c>
       <c r="G6" t="n">
-        <v>1103.307983398438</v>
+        <v>1103.30810546875</v>
       </c>
       <c r="H6" t="n">
         <v>98.55000305175781</v>
       </c>
       <c r="I6" t="n">
-        <v>844.044677734375</v>
+        <v>844.0447387695312</v>
       </c>
       <c r="J6" t="n">
         <v>14.14999961853027</v>
@@ -667,13 +667,13 @@
         <v>89.34999847412109</v>
       </c>
       <c r="G8" t="n">
-        <v>1112.162719726562</v>
+        <v>1112.16259765625</v>
       </c>
       <c r="H8" t="n">
         <v>98.40000152587891</v>
       </c>
       <c r="I8" t="n">
-        <v>968.8118286132812</v>
+        <v>968.811767578125</v>
       </c>
       <c r="J8" t="n">
         <v>14.30000019073486</v>
@@ -702,7 +702,7 @@
         <v>96.40000152587891</v>
       </c>
       <c r="I9" t="n">
-        <v>941.8934936523438</v>
+        <v>941.8935546875</v>
       </c>
       <c r="J9" t="n">
         <v>14.35000038146973</v>
@@ -789,7 +789,7 @@
         <v>105.5500030517578</v>
       </c>
       <c r="I12" t="n">
-        <v>934.6728515625</v>
+        <v>934.6727905273438</v>
       </c>
       <c r="J12" t="n">
         <v>15.64999961853027</v>
@@ -818,7 +818,7 @@
         <v>101.9499969482422</v>
       </c>
       <c r="I13" t="n">
-        <v>930.49755859375</v>
+        <v>930.4974975585938</v>
       </c>
       <c r="J13" t="n">
         <v>16.10000038146973</v>
@@ -847,7 +847,7 @@
         <v>99.75</v>
       </c>
       <c r="I14" t="n">
-        <v>957.7103881835938</v>
+        <v>957.71044921875</v>
       </c>
       <c r="J14" t="n">
         <v>15.85000038146973</v>
@@ -870,13 +870,13 @@
         <v>88.75</v>
       </c>
       <c r="G15" t="n">
-        <v>1122.08154296875</v>
+        <v>1122.081420898438</v>
       </c>
       <c r="H15" t="n">
         <v>101.5500030517578</v>
       </c>
       <c r="I15" t="n">
-        <v>936.3429565429688</v>
+        <v>936.3428955078125</v>
       </c>
       <c r="J15" t="n">
         <v>16.54999923706055</v>
@@ -905,7 +905,7 @@
         <v>98.25</v>
       </c>
       <c r="I16" t="n">
-        <v>898.8636474609375</v>
+        <v>898.8637084960938</v>
       </c>
       <c r="J16" t="n">
         <v>16.04999923706055</v>
@@ -934,7 +934,7 @@
         <v>93.55000305175781</v>
       </c>
       <c r="I17" t="n">
-        <v>835.7432861328125</v>
+        <v>835.7432250976562</v>
       </c>
       <c r="J17" t="n">
         <v>15.25</v>
@@ -957,13 +957,13 @@
         <v>78</v>
       </c>
       <c r="G18" t="n">
-        <v>1074.887451171875</v>
+        <v>1074.887573242188</v>
       </c>
       <c r="H18" t="n">
         <v>98.05000305175781</v>
       </c>
       <c r="I18" t="n">
-        <v>835.7432861328125</v>
+        <v>835.7432250976562</v>
       </c>
       <c r="J18" t="n">
         <v>14.75</v>
@@ -992,7 +992,7 @@
         <v>97.80000305175781</v>
       </c>
       <c r="I19" t="n">
-        <v>855.3916625976562</v>
+        <v>855.3916015625</v>
       </c>
       <c r="J19" t="n">
         <v>14.80000019073486</v>
@@ -1021,7 +1021,7 @@
         <v>102.3000030517578</v>
       </c>
       <c r="I20" t="n">
-        <v>885.7974243164062</v>
+        <v>885.7974853515625</v>
       </c>
       <c r="J20" t="n">
         <v>15.19999980926514</v>
@@ -1050,7 +1050,7 @@
         <v>101.0500030517578</v>
       </c>
       <c r="I21" t="n">
-        <v>864.5281372070312</v>
+        <v>864.528076171875</v>
       </c>
       <c r="J21" t="n">
         <v>14.80000019073486</v>
@@ -1073,13 +1073,13 @@
         <v>82.55000305175781</v>
       </c>
       <c r="G22" t="n">
-        <v>1077.355712890625</v>
+        <v>1077.355834960938</v>
       </c>
       <c r="H22" t="n">
         <v>106.0999984741211</v>
       </c>
       <c r="I22" t="n">
-        <v>907.7545166015625</v>
+        <v>907.7544555664062</v>
       </c>
       <c r="J22" t="n">
         <v>15.5</v>
@@ -1102,7 +1102,7 @@
         <v>85.90000152587891</v>
       </c>
       <c r="G23" t="n">
-        <v>1079.552368164062</v>
+        <v>1079.552490234375</v>
       </c>
       <c r="H23" t="n">
         <v>110.0999984741211</v>
@@ -1137,7 +1137,7 @@
         <v>115.5999984741211</v>
       </c>
       <c r="I24" t="n">
-        <v>910.0140380859375</v>
+        <v>910.0140991210938</v>
       </c>
       <c r="J24" t="n">
         <v>16.85000038146973</v>
@@ -1160,7 +1160,7 @@
         <v>85.44999694824219</v>
       </c>
       <c r="G25" t="n">
-        <v>1055.887573242188</v>
+        <v>1055.887451171875</v>
       </c>
       <c r="H25" t="n">
         <v>121.3499984741211</v>
@@ -1195,7 +1195,7 @@
         <v>133.4499969482422</v>
       </c>
       <c r="I26" t="n">
-        <v>874.7943725585938</v>
+        <v>874.79443359375</v>
       </c>
       <c r="J26" t="n">
         <v>18.5</v>
@@ -1218,7 +1218,7 @@
         <v>83.59999847412109</v>
       </c>
       <c r="G27" t="n">
-        <v>1067.09716796875</v>
+        <v>1067.097290039062</v>
       </c>
       <c r="H27" t="n">
         <v>134.4499969482422</v>
@@ -1282,7 +1282,7 @@
         <v>133.1000061035156</v>
       </c>
       <c r="I29" t="n">
-        <v>879.510009765625</v>
+        <v>879.5099487304688</v>
       </c>
       <c r="J29" t="n">
         <v>16.14999961853027</v>
@@ -1305,13 +1305,13 @@
         <v>91.44999694824219</v>
       </c>
       <c r="G30" t="n">
-        <v>1076.314208984375</v>
+        <v>1076.314331054688</v>
       </c>
       <c r="H30" t="n">
         <v>134</v>
       </c>
       <c r="I30" t="n">
-        <v>853.6724243164062</v>
+        <v>853.6724853515625</v>
       </c>
       <c r="J30" t="n">
         <v>15.94999980926514</v>
@@ -1398,7 +1398,7 @@
         <v>122.5999984741211</v>
       </c>
       <c r="I33" t="n">
-        <v>794.4324951171875</v>
+        <v>794.4325561523438</v>
       </c>
       <c r="J33" t="n">
         <v>14.80000019073486</v>
@@ -1450,13 +1450,13 @@
         <v>83.09999847412109</v>
       </c>
       <c r="G35" t="n">
-        <v>1098.054321289062</v>
+        <v>1098.05419921875</v>
       </c>
       <c r="H35" t="n">
         <v>120.0999984741211</v>
       </c>
       <c r="I35" t="n">
-        <v>790.3063354492188</v>
+        <v>790.3064575195312</v>
       </c>
       <c r="J35" t="n">
         <v>14.14999961853027</v>
@@ -1485,7 +1485,7 @@
         <v>112.6999969482422</v>
       </c>
       <c r="I36" t="n">
-        <v>750.4694213867188</v>
+        <v>750.4693603515625</v>
       </c>
       <c r="J36" t="n">
         <v>13.60000038146973</v>
@@ -1514,7 +1514,7 @@
         <v>114.3499984741211</v>
       </c>
       <c r="I37" t="n">
-        <v>725.5650634765625</v>
+        <v>725.5650024414062</v>
       </c>
       <c r="J37" t="n">
         <v>12.94999980926514</v>
@@ -1543,7 +1543,7 @@
         <v>113.25</v>
       </c>
       <c r="I38" t="n">
-        <v>748.2589721679688</v>
+        <v>748.2588500976562</v>
       </c>
       <c r="J38" t="n">
         <v>13.55000019073486</v>
@@ -1566,7 +1566,7 @@
         <v>74.75</v>
       </c>
       <c r="G39" t="n">
-        <v>1021.669738769531</v>
+        <v>1021.669494628906</v>
       </c>
       <c r="H39" t="n">
         <v>101.9499969482422</v>
@@ -1601,7 +1601,7 @@
         <v>104.5999984741211</v>
       </c>
       <c r="I40" t="n">
-        <v>681.9456176757812</v>
+        <v>681.9456787109375</v>
       </c>
       <c r="J40" t="n">
         <v>13</v>
@@ -1624,13 +1624,13 @@
         <v>76.94999694824219</v>
       </c>
       <c r="G41" t="n">
-        <v>1068.682373046875</v>
+        <v>1068.682495117188</v>
       </c>
       <c r="H41" t="n">
         <v>104.5999984741211</v>
       </c>
       <c r="I41" t="n">
-        <v>686.1209716796875</v>
+        <v>686.1209106445312</v>
       </c>
       <c r="J41" t="n">
         <v>13.05000019073486</v>
@@ -1659,7 +1659,7 @@
         <v>107.5999984741211</v>
       </c>
       <c r="I42" t="n">
-        <v>692.8505249023438</v>
+        <v>692.8504638671875</v>
       </c>
       <c r="J42" t="n">
         <v>13.14999961853027</v>
@@ -1717,7 +1717,7 @@
         <v>103.5</v>
       </c>
       <c r="I44" t="n">
-        <v>674.7249145507812</v>
+        <v>674.7249755859375</v>
       </c>
       <c r="J44" t="n">
         <v>12.85000038146973</v>
@@ -1740,13 +1740,13 @@
         <v>73.65000152587891</v>
       </c>
       <c r="G45" t="n">
-        <v>1014.332458496094</v>
+        <v>1014.332397460938</v>
       </c>
       <c r="H45" t="n">
         <v>99.59999847412109</v>
       </c>
       <c r="I45" t="n">
-        <v>640.9788208007812</v>
+        <v>640.9788818359375</v>
       </c>
       <c r="J45" t="n">
         <v>12.64999961853027</v>
@@ -1775,7 +1775,7 @@
         <v>101.75</v>
       </c>
       <c r="I46" t="n">
-        <v>667.5040893554688</v>
+        <v>667.5040283203125</v>
       </c>
       <c r="J46" t="n">
         <v>12.80000019073486</v>
@@ -1827,7 +1827,7 @@
         <v>78</v>
       </c>
       <c r="G48" t="n">
-        <v>1083.492797851562</v>
+        <v>1083.492919921875</v>
       </c>
       <c r="H48" t="n">
         <v>111.4000015258789</v>
@@ -1856,7 +1856,7 @@
         <v>77.84999847412109</v>
       </c>
       <c r="G49" t="n">
-        <v>1086.617797851562</v>
+        <v>1086.617919921875</v>
       </c>
       <c r="H49" t="n">
         <v>122.5</v>
@@ -1914,13 +1914,13 @@
         <v>78.84999847412109</v>
       </c>
       <c r="G51" t="n">
-        <v>1070.448852539062</v>
+        <v>1070.44873046875</v>
       </c>
       <c r="H51" t="n">
         <v>115.5500030517578</v>
       </c>
       <c r="I51" t="n">
-        <v>747.3256225585938</v>
+        <v>747.3255615234375</v>
       </c>
       <c r="J51" t="n">
         <v>13.44999980926514</v>
@@ -1943,7 +1943,7 @@
         <v>77.75</v>
       </c>
       <c r="G52" t="n">
-        <v>1088.520263671875</v>
+        <v>1088.520141601562</v>
       </c>
       <c r="H52" t="n">
         <v>118.9499969482422</v>
@@ -1978,7 +1978,7 @@
         <v>116.8000030517578</v>
       </c>
       <c r="I53" t="n">
-        <v>758.7706909179688</v>
+        <v>758.770751953125</v>
       </c>
       <c r="J53" t="n">
         <v>13.75</v>
@@ -2036,7 +2036,7 @@
         <v>113.1500015258789</v>
       </c>
       <c r="I55" t="n">
-        <v>751.1078491210938</v>
+        <v>751.10791015625</v>
       </c>
       <c r="J55" t="n">
         <v>13</v>
@@ -2059,13 +2059,13 @@
         <v>81.65000152587891</v>
       </c>
       <c r="G56" t="n">
-        <v>1150.049072265625</v>
+        <v>1150.049194335938</v>
       </c>
       <c r="H56" t="n">
         <v>111.8000030517578</v>
       </c>
       <c r="I56" t="n">
-        <v>756.5111694335938</v>
+        <v>756.51123046875</v>
       </c>
       <c r="J56" t="n">
         <v>12.85000038146973</v>
@@ -2088,13 +2088,13 @@
         <v>85.55000305175781</v>
       </c>
       <c r="G57" t="n">
-        <v>1167.916625976562</v>
+        <v>1167.916748046875</v>
       </c>
       <c r="H57" t="n">
         <v>109.6999969482422</v>
       </c>
       <c r="I57" t="n">
-        <v>756.3638305664062</v>
+        <v>756.3638916015625</v>
       </c>
       <c r="J57" t="n">
         <v>13</v>
@@ -2117,13 +2117,13 @@
         <v>85.59999847412109</v>
       </c>
       <c r="G58" t="n">
-        <v>1175.706909179688</v>
+        <v>1175.70703125</v>
       </c>
       <c r="H58" t="n">
         <v>109.1999969482422</v>
       </c>
       <c r="I58" t="n">
-        <v>755.577880859375</v>
+        <v>755.5779418945312</v>
       </c>
       <c r="J58" t="n">
         <v>13</v>
@@ -2146,13 +2146,13 @@
         <v>87.59999847412109</v>
       </c>
       <c r="G59" t="n">
-        <v>1187.528198242188</v>
+        <v>1187.528076171875</v>
       </c>
       <c r="H59" t="n">
         <v>100.6999969482422</v>
       </c>
       <c r="I59" t="n">
-        <v>731.4595947265625</v>
+        <v>731.4595336914062</v>
       </c>
       <c r="J59" t="n">
         <v>12.35000038146973</v>
@@ -2181,7 +2181,7 @@
         <v>110.75</v>
       </c>
       <c r="I60" t="n">
-        <v>735.4382934570312</v>
+        <v>735.4383544921875</v>
       </c>
       <c r="J60" t="n">
         <v>12.94999980926514</v>
@@ -2204,7 +2204,7 @@
         <v>85.80000305175781</v>
       </c>
       <c r="G61" t="n">
-        <v>1210.627075195312</v>
+        <v>1210.627197265625</v>
       </c>
       <c r="H61" t="n">
         <v>114.8000030517578</v>
@@ -2233,13 +2233,13 @@
         <v>85.15000152587891</v>
       </c>
       <c r="G62" t="n">
-        <v>1193.325439453125</v>
+        <v>1193.325317382812</v>
       </c>
       <c r="H62" t="n">
         <v>112.3000030517578</v>
       </c>
       <c r="I62" t="n">
-        <v>764.6161499023438</v>
+        <v>764.6160888671875</v>
       </c>
       <c r="J62" t="n">
         <v>13.5</v>
@@ -2262,13 +2262,13 @@
         <v>87.84999847412109</v>
       </c>
       <c r="G63" t="n">
-        <v>1202.881958007812</v>
+        <v>1202.882080078125</v>
       </c>
       <c r="H63" t="n">
         <v>122.6500015258789</v>
       </c>
       <c r="I63" t="n">
-        <v>790.2572631835938</v>
+        <v>790.25732421875</v>
       </c>
       <c r="J63" t="n">
         <v>14.14999961853027</v>
@@ -2291,7 +2291,7 @@
         <v>92.19999694824219</v>
       </c>
       <c r="G64" t="n">
-        <v>1206.4375</v>
+        <v>1206.437377929688</v>
       </c>
       <c r="H64" t="n">
         <v>124.6999969482422</v>
@@ -2320,7 +2320,7 @@
         <v>93.05000305175781</v>
       </c>
       <c r="G65" t="n">
-        <v>1189.385009765625</v>
+        <v>1189.385131835938</v>
       </c>
       <c r="H65" t="n">
         <v>132.1499938964844</v>
@@ -2378,7 +2378,7 @@
         <v>96.30000305175781</v>
       </c>
       <c r="G67" t="n">
-        <v>1165.2900390625</v>
+        <v>1165.289916992188</v>
       </c>
       <c r="H67" t="n">
         <v>125.1500015258789</v>
@@ -2465,7 +2465,7 @@
         <v>94.84999847412109</v>
       </c>
       <c r="G70" t="n">
-        <v>1159.945556640625</v>
+        <v>1159.945434570312</v>
       </c>
       <c r="H70" t="n">
         <v>122.9499969482422</v>
@@ -2523,13 +2523,13 @@
         <v>103</v>
       </c>
       <c r="G72" t="n">
-        <v>1152.1552734375</v>
+        <v>1152.155151367188</v>
       </c>
       <c r="H72" t="n">
         <v>119.5500030517578</v>
       </c>
       <c r="I72" t="n">
-        <v>982.61474609375</v>
+        <v>982.6148071289062</v>
       </c>
       <c r="J72" t="n">
         <v>14.39999961853027</v>
@@ -2558,7 +2558,7 @@
         <v>123.5999984741211</v>
       </c>
       <c r="I73" t="n">
-        <v>979.8148803710938</v>
+        <v>979.8148193359375</v>
       </c>
       <c r="J73" t="n">
         <v>14.39999961853027</v>
@@ -2587,7 +2587,7 @@
         <v>125.75</v>
       </c>
       <c r="I74" t="n">
-        <v>945.7249145507812</v>
+        <v>945.7249755859375</v>
       </c>
       <c r="J74" t="n">
         <v>14.75</v>
@@ -2610,13 +2610,13 @@
         <v>103.4499969482422</v>
       </c>
       <c r="G75" t="n">
-        <v>1260.06298828125</v>
+        <v>1260.062866210938</v>
       </c>
       <c r="H75" t="n">
         <v>130.3000030517578</v>
       </c>
       <c r="I75" t="n">
-        <v>987.2322387695312</v>
+        <v>987.232177734375</v>
       </c>
       <c r="J75" t="n">
         <v>15.14999961853027</v>
@@ -2645,7 +2645,7 @@
         <v>128.8999938964844</v>
       </c>
       <c r="I76" t="n">
-        <v>962.5242309570312</v>
+        <v>962.5243530273438</v>
       </c>
       <c r="J76" t="n">
         <v>14.94999980926514</v>
@@ -2697,13 +2697,13 @@
         <v>114.1999969482422</v>
       </c>
       <c r="G78" t="n">
-        <v>1257.1416015625</v>
+        <v>1257.141479492188</v>
       </c>
       <c r="H78" t="n">
         <v>121.1999969482422</v>
       </c>
       <c r="I78" t="n">
-        <v>926.4695434570312</v>
+        <v>926.4696044921875</v>
       </c>
       <c r="J78" t="n">
         <v>14.5</v>
@@ -2732,7 +2732,7 @@
         <v>123</v>
       </c>
       <c r="I79" t="n">
-        <v>1111.753784179688</v>
+        <v>1111.753662109375</v>
       </c>
       <c r="J79" t="n">
         <v>14.39999961853027</v>
@@ -2755,7 +2755,7 @@
         <v>91.34999847412109</v>
       </c>
       <c r="G80" t="n">
-        <v>1277.16064453125</v>
+        <v>1277.160400390625</v>
       </c>
       <c r="H80" t="n">
         <v>120.5999984741211</v>
@@ -2784,13 +2784,13 @@
         <v>86.19999694824219</v>
       </c>
       <c r="G81" t="n">
-        <v>1263.75439453125</v>
+        <v>1263.754272460938</v>
       </c>
       <c r="H81" t="n">
         <v>123.5500030517578</v>
       </c>
       <c r="I81" t="n">
-        <v>1086.94775390625</v>
+        <v>1086.947509765625</v>
       </c>
       <c r="J81" t="n">
         <v>14.25</v>
@@ -2819,7 +2819,7 @@
         <v>124.25</v>
       </c>
       <c r="I82" t="n">
-        <v>1096.476928710938</v>
+        <v>1096.47705078125</v>
       </c>
       <c r="J82" t="n">
         <v>14.19999980926514</v>
@@ -2848,7 +2848,7 @@
         <v>116.0999984741211</v>
       </c>
       <c r="I83" t="n">
-        <v>1001.133361816406</v>
+        <v>1001.13330078125</v>
       </c>
       <c r="J83" t="n">
         <v>13.55000019073486</v>
@@ -2877,7 +2877,7 @@
         <v>115.0999984741211</v>
       </c>
       <c r="I84" t="n">
-        <v>980.3551635742188</v>
+        <v>980.355224609375</v>
       </c>
       <c r="J84" t="n">
         <v>13.39999961853027</v>
@@ -2900,13 +2900,13 @@
         <v>78.34999847412109</v>
       </c>
       <c r="G85" t="n">
-        <v>1186.939331054688</v>
+        <v>1186.939453125</v>
       </c>
       <c r="H85" t="n">
         <v>111.3000030517578</v>
       </c>
       <c r="I85" t="n">
-        <v>1049.320922851562</v>
+        <v>1049.32080078125</v>
       </c>
       <c r="J85" t="n">
         <v>13.10000038146973</v>
@@ -2964,7 +2964,7 @@
         <v>108.1999969482422</v>
       </c>
       <c r="I87" t="n">
-        <v>953.9773559570312</v>
+        <v>953.977294921875</v>
       </c>
       <c r="J87" t="n">
         <v>13.10000038146973</v>
@@ -2987,13 +2987,13 @@
         <v>68.44999694824219</v>
       </c>
       <c r="G88" t="n">
-        <v>1109.331909179688</v>
+        <v>1109.331787109375</v>
       </c>
       <c r="H88" t="n">
         <v>101</v>
       </c>
       <c r="I88" t="n">
-        <v>964.9312133789062</v>
+        <v>964.9312744140625</v>
       </c>
       <c r="J88" t="n">
         <v>13</v>
@@ -3022,7 +3022,7 @@
         <v>100.9000015258789</v>
       </c>
       <c r="I89" t="n">
-        <v>943.907470703125</v>
+        <v>943.9075317382812</v>
       </c>
       <c r="J89" t="n">
         <v>12.39999961853027</v>
@@ -3045,7 +3045,7 @@
         <v>76.65000152587891</v>
       </c>
       <c r="G90" t="n">
-        <v>1099.050659179688</v>
+        <v>1099.050537109375</v>
       </c>
       <c r="H90" t="n">
         <v>102.0500030517578</v>
@@ -3080,7 +3080,7 @@
         <v>98.30000305175781</v>
       </c>
       <c r="I91" t="n">
-        <v>964.9312133789062</v>
+        <v>964.9312744140625</v>
       </c>
       <c r="J91" t="n">
         <v>11.89999961853027</v>
@@ -3167,7 +3167,7 @@
         <v>102.0999984741211</v>
       </c>
       <c r="I94" t="n">
-        <v>977.5061645507812</v>
+        <v>977.5062255859375</v>
       </c>
       <c r="J94" t="n">
         <v>12.30000019073486</v>
@@ -3190,13 +3190,13 @@
         <v>80.75</v>
       </c>
       <c r="G95" t="n">
-        <v>1188.660522460938</v>
+        <v>1188.660400390625</v>
       </c>
       <c r="H95" t="n">
         <v>104</v>
       </c>
       <c r="I95" t="n">
-        <v>1021.665893554688</v>
+        <v>1021.665954589844</v>
       </c>
       <c r="J95" t="n">
         <v>12.85000038146973</v>
@@ -3219,7 +3219,7 @@
         <v>80.05000305175781</v>
       </c>
       <c r="G96" t="n">
-        <v>1180.711791992188</v>
+        <v>1180.711669921875</v>
       </c>
       <c r="H96" t="n">
         <v>101.6999969482422</v>
@@ -3254,7 +3254,7 @@
         <v>100.9000015258789</v>
       </c>
       <c r="I97" t="n">
-        <v>945.7249145507812</v>
+        <v>945.7249755859375</v>
       </c>
       <c r="J97" t="n">
         <v>12.55000019073486</v>
@@ -3283,7 +3283,7 @@
         <v>100.6500015258789</v>
       </c>
       <c r="I98" t="n">
-        <v>869.98046875</v>
+        <v>869.9805297851562</v>
       </c>
       <c r="J98" t="n">
         <v>12.10000038146973</v>
@@ -3306,7 +3306,7 @@
         <v>71.59999847412109</v>
       </c>
       <c r="G99" t="n">
-        <v>1171.743896484375</v>
+        <v>1171.744018554688</v>
       </c>
       <c r="H99" t="n">
         <v>100.3499984741211</v>
@@ -3341,7 +3341,7 @@
         <v>99.84999847412109</v>
       </c>
       <c r="I100" t="n">
-        <v>871.9944458007812</v>
+        <v>871.9945678710938</v>
       </c>
       <c r="J100" t="n">
         <v>11.85000038146973</v>
@@ -3364,13 +3364,13 @@
         <v>73.15000152587891</v>
       </c>
       <c r="G101" t="n">
-        <v>1206.935668945312</v>
+        <v>1206.935546875</v>
       </c>
       <c r="H101" t="n">
         <v>102.5500030517578</v>
       </c>
       <c r="I101" t="n">
-        <v>914.9261474609375</v>
+        <v>914.9260864257812</v>
       </c>
       <c r="J101" t="n">
         <v>12</v>
@@ -3422,7 +3422,7 @@
         <v>76.05000305175781</v>
       </c>
       <c r="G103" t="n">
-        <v>1192.75927734375</v>
+        <v>1192.759399414062</v>
       </c>
       <c r="H103" t="n">
         <v>108.0500030517578</v>
@@ -3480,13 +3480,13 @@
         <v>76.59999847412109</v>
       </c>
       <c r="G105" t="n">
-        <v>1258.885375976562</v>
+        <v>1258.88525390625</v>
       </c>
       <c r="H105" t="n">
         <v>106.5999984741211</v>
       </c>
       <c r="I105" t="n">
-        <v>965.9136352539062</v>
+        <v>965.9136962890625</v>
       </c>
       <c r="J105" t="n">
         <v>13.25</v>
@@ -3515,7 +3515,7 @@
         <v>105.1500015258789</v>
       </c>
       <c r="I106" t="n">
-        <v>990.7197875976562</v>
+        <v>990.7197265625</v>
       </c>
       <c r="J106" t="n">
         <v>13.80000019073486</v>
@@ -3538,13 +3538,13 @@
         <v>75.90000152587891</v>
       </c>
       <c r="G107" t="n">
-        <v>1255.828125</v>
+        <v>1255.828247070312</v>
       </c>
       <c r="H107" t="n">
         <v>105.5</v>
       </c>
       <c r="I107" t="n">
-        <v>978.3903198242188</v>
+        <v>978.390380859375</v>
       </c>
       <c r="J107" t="n">
         <v>14.30000019073486</v>
@@ -3596,13 +3596,13 @@
         <v>80.94999694824219</v>
       </c>
       <c r="G109" t="n">
-        <v>1267.60400390625</v>
+        <v>1267.604125976562</v>
       </c>
       <c r="H109" t="n">
         <v>104.4499969482422</v>
       </c>
       <c r="I109" t="n">
-        <v>974.7554931640625</v>
+        <v>974.7555541992188</v>
       </c>
       <c r="J109" t="n">
         <v>13.94999980926514</v>
@@ -3631,7 +3631,7 @@
         <v>103.5999984741211</v>
       </c>
       <c r="I110" t="n">
-        <v>944.0548095703125</v>
+        <v>944.054931640625</v>
       </c>
       <c r="J110" t="n">
         <v>13.55000019073486</v>
@@ -3654,13 +3654,13 @@
         <v>73.55000305175781</v>
       </c>
       <c r="G111" t="n">
-        <v>1206.074951171875</v>
+        <v>1206.075073242188</v>
       </c>
       <c r="H111" t="n">
         <v>96.94999694824219</v>
       </c>
       <c r="I111" t="n">
-        <v>874.548828125</v>
+        <v>874.5487670898438</v>
       </c>
       <c r="J111" t="n">
         <v>12.89999961853027</v>
@@ -3689,7 +3689,7 @@
         <v>95.75</v>
       </c>
       <c r="I112" t="n">
-        <v>879.7064208984375</v>
+        <v>879.7064819335938</v>
       </c>
       <c r="J112" t="n">
         <v>12.85000038146973</v>
@@ -3712,7 +3712,7 @@
         <v>74.59999847412109</v>
       </c>
       <c r="G113" t="n">
-        <v>1175.910888671875</v>
+        <v>1175.910766601562</v>
       </c>
       <c r="H113" t="n">
         <v>95.5</v>
@@ -3741,13 +3741,13 @@
         <v>67.25</v>
       </c>
       <c r="G114" t="n">
-        <v>1159.469848632812</v>
+        <v>1159.4697265625</v>
       </c>
       <c r="H114" t="n">
         <v>95.40000152587891</v>
       </c>
       <c r="I114" t="n">
-        <v>825.72265625</v>
+        <v>825.7225952148438</v>
       </c>
       <c r="J114" t="n">
         <v>12.05000019073486</v>
@@ -3776,7 +3776,7 @@
         <v>95.59999847412109</v>
       </c>
       <c r="I115" t="n">
-        <v>833.4837646484375</v>
+        <v>833.4837036132812</v>
       </c>
       <c r="J115" t="n">
         <v>12.14999961853027</v>
@@ -3799,13 +3799,13 @@
         <v>58.90000152587891</v>
       </c>
       <c r="G116" t="n">
-        <v>1151.79296875</v>
+        <v>1151.792846679688</v>
       </c>
       <c r="H116" t="n">
         <v>90.65000152587891</v>
       </c>
       <c r="I116" t="n">
-        <v>730.182373046875</v>
+        <v>730.1824340820312</v>
       </c>
       <c r="J116" t="n">
         <v>11.10000038146973</v>
@@ -3886,7 +3886,7 @@
         <v>61.40000152587891</v>
       </c>
       <c r="G119" t="n">
-        <v>1116.419921875</v>
+        <v>1116.420043945312</v>
       </c>
       <c r="H119" t="n">
         <v>90.30000305175781</v>
@@ -3944,7 +3944,7 @@
         <v>62.84999847412109</v>
       </c>
       <c r="G121" t="n">
-        <v>1128.965698242188</v>
+        <v>1128.9658203125</v>
       </c>
       <c r="H121" t="n">
         <v>93.09999847412109</v>
@@ -3979,7 +3979,7 @@
         <v>92.19999694824219</v>
       </c>
       <c r="I122" t="n">
-        <v>827.1961059570312</v>
+        <v>827.1961669921875</v>
       </c>
       <c r="J122" t="n">
         <v>11.80000019073486</v>
@@ -4008,7 +4008,7 @@
         <v>92.09999847412109</v>
       </c>
       <c r="I123" t="n">
-        <v>938.1112670898438</v>
+        <v>938.111328125</v>
       </c>
       <c r="J123" t="n">
         <v>11.75</v>
@@ -4066,7 +4066,7 @@
         <v>91.09999847412109</v>
       </c>
       <c r="I125" t="n">
-        <v>920.8206176757812</v>
+        <v>920.8206787109375</v>
       </c>
       <c r="J125" t="n">
         <v>11.39999961853027</v>
@@ -4089,7 +4089,7 @@
         <v>65.55000305175781</v>
       </c>
       <c r="G126" t="n">
-        <v>1093.207885742188</v>
+        <v>1093.2080078125</v>
       </c>
       <c r="H126" t="n">
         <v>94.5</v>
@@ -4118,13 +4118,13 @@
         <v>65.40000152587891</v>
       </c>
       <c r="G127" t="n">
-        <v>1102.0625</v>
+        <v>1102.062622070312</v>
       </c>
       <c r="H127" t="n">
         <v>93.15000152587891</v>
       </c>
       <c r="I127" t="n">
-        <v>927.0098876953125</v>
+        <v>927.0098266601562</v>
       </c>
       <c r="J127" t="n">
         <v>11.35000038146973</v>
@@ -4153,7 +4153,7 @@
         <v>91.75</v>
       </c>
       <c r="I128" t="n">
-        <v>925.6344604492188</v>
+        <v>925.634521484375</v>
       </c>
       <c r="J128" t="n">
         <v>11.19999980926514</v>
@@ -4182,7 +4182,7 @@
         <v>94.90000152587891</v>
       </c>
       <c r="I129" t="n">
-        <v>936.4903564453125</v>
+        <v>936.490234375</v>
       </c>
       <c r="J129" t="n">
         <v>11.44999980926514</v>
@@ -4205,13 +4205,13 @@
         <v>67.40000152587891</v>
       </c>
       <c r="G130" t="n">
-        <v>1083.108032226562</v>
+        <v>1083.10791015625</v>
       </c>
       <c r="H130" t="n">
         <v>94.80000305175781</v>
       </c>
       <c r="I130" t="n">
-        <v>933.3464965820312</v>
+        <v>933.3465576171875</v>
       </c>
       <c r="J130" t="n">
         <v>11.39999961853027</v>
@@ -4234,13 +4234,13 @@
         <v>68.30000305175781</v>
       </c>
       <c r="G131" t="n">
-        <v>1097.827758789062</v>
+        <v>1097.827880859375</v>
       </c>
       <c r="H131" t="n">
         <v>101.3499984741211</v>
       </c>
       <c r="I131" t="n">
-        <v>940.5673217773438</v>
+        <v>940.5672607421875</v>
       </c>
       <c r="J131" t="n">
         <v>11.64999961853027</v>
@@ -4263,13 +4263,13 @@
         <v>69.19999694824219</v>
       </c>
       <c r="G132" t="n">
-        <v>1096.265014648438</v>
+        <v>1096.26513671875</v>
       </c>
       <c r="H132" t="n">
         <v>102.5999984741211</v>
       </c>
       <c r="I132" t="n">
-        <v>951.2265625</v>
+        <v>951.2265014648438</v>
       </c>
       <c r="J132" t="n">
         <v>11.5</v>
@@ -4298,7 +4298,7 @@
         <v>101.6500015258789</v>
       </c>
       <c r="I133" t="n">
-        <v>945.1845703125</v>
+        <v>945.1846313476562</v>
       </c>
       <c r="J133" t="n">
         <v>11.5</v>
@@ -4327,7 +4327,7 @@
         <v>100.4000015258789</v>
       </c>
       <c r="I134" t="n">
-        <v>937.9638671875</v>
+        <v>937.9638061523438</v>
       </c>
       <c r="J134" t="n">
         <v>11.39999961853027</v>
@@ -4356,7 +4356,7 @@
         <v>99.44999694824219</v>
       </c>
       <c r="I135" t="n">
-        <v>945.3319702148438</v>
+        <v>945.33203125</v>
       </c>
       <c r="J135" t="n">
         <v>11.30000019073486</v>
@@ -4379,7 +4379,7 @@
         <v>68.15000152587891</v>
       </c>
       <c r="G136" t="n">
-        <v>1097.080444335938</v>
+        <v>1097.08056640625</v>
       </c>
       <c r="H136" t="n">
         <v>102.25</v>
@@ -4437,7 +4437,7 @@
         <v>67</v>
       </c>
       <c r="G138" t="n">
-        <v>1133.653442382812</v>
+        <v>1133.653564453125</v>
       </c>
       <c r="H138" t="n">
         <v>104.4000015258789</v>
@@ -4472,7 +4472,7 @@
         <v>105.8000030517578</v>
       </c>
       <c r="I139" t="n">
-        <v>961.9348754882812</v>
+        <v>961.934814453125</v>
       </c>
       <c r="J139" t="n">
         <v>11.85000038146973</v>
@@ -4501,7 +4501,7 @@
         <v>104.5</v>
       </c>
       <c r="I140" t="n">
-        <v>971.4152221679688</v>
+        <v>971.4151611328125</v>
       </c>
       <c r="J140" t="n">
         <v>11.75</v>
@@ -4524,7 +4524,7 @@
         <v>62.95000076293945</v>
       </c>
       <c r="G141" t="n">
-        <v>1096.242431640625</v>
+        <v>1096.242553710938</v>
       </c>
       <c r="H141" t="n">
         <v>104.25</v>
@@ -4553,13 +4553,13 @@
         <v>62.90000152587891</v>
       </c>
       <c r="G142" t="n">
-        <v>1096.740844726562</v>
+        <v>1096.74072265625</v>
       </c>
       <c r="H142" t="n">
         <v>113.9000015258789</v>
       </c>
       <c r="I142" t="n">
-        <v>945.135498046875</v>
+        <v>945.1355590820312</v>
       </c>
       <c r="J142" t="n">
         <v>11.89999961853027</v>
@@ -4582,13 +4582,13 @@
         <v>64.90000152587891</v>
       </c>
       <c r="G143" t="n">
-        <v>1095.698974609375</v>
+        <v>1095.699096679688</v>
       </c>
       <c r="H143" t="n">
         <v>115.8499984741211</v>
       </c>
       <c r="I143" t="n">
-        <v>945.8231811523438</v>
+        <v>945.8232421875</v>
       </c>
       <c r="J143" t="n">
         <v>11.89999961853027</v>
@@ -4617,7 +4617,7 @@
         <v>114.25</v>
       </c>
       <c r="I144" t="n">
-        <v>955.1070556640625</v>
+        <v>955.1071166992188</v>
       </c>
       <c r="J144" t="n">
         <v>11.75</v>
@@ -4640,13 +4640,13 @@
         <v>64.90000152587891</v>
       </c>
       <c r="G145" t="n">
-        <v>1136.57470703125</v>
+        <v>1136.574951171875</v>
       </c>
       <c r="H145" t="n">
         <v>117.0999984741211</v>
       </c>
       <c r="I145" t="n">
-        <v>964.6856689453125</v>
+        <v>964.6856079101562</v>
       </c>
       <c r="J145" t="n">
         <v>12.39999961853027</v>
@@ -4727,13 +4727,13 @@
         <v>69.19999694824219</v>
       </c>
       <c r="G148" t="n">
-        <v>1180.462524414062</v>
+        <v>1180.462646484375</v>
       </c>
       <c r="H148" t="n">
         <v>125.0500030517578</v>
       </c>
       <c r="I148" t="n">
-        <v>966.0609741210938</v>
+        <v>966.06103515625</v>
       </c>
       <c r="J148" t="n">
         <v>13</v>
@@ -4756,7 +4756,7 @@
         <v>67.90000152587891</v>
       </c>
       <c r="G149" t="n">
-        <v>1164.859497070312</v>
+        <v>1164.859619140625</v>
       </c>
       <c r="H149" t="n">
         <v>121.3499984741211</v>
@@ -4791,7 +4791,7 @@
         <v>120</v>
       </c>
       <c r="I150" t="n">
-        <v>942.0408935546875</v>
+        <v>942.041015625</v>
       </c>
       <c r="J150" t="n">
         <v>13.14999961853027</v>
@@ -4814,13 +4814,13 @@
         <v>67.5</v>
       </c>
       <c r="G151" t="n">
-        <v>1162.708129882812</v>
+        <v>1162.708251953125</v>
       </c>
       <c r="H151" t="n">
         <v>115.8499984741211</v>
       </c>
       <c r="I151" t="n">
-        <v>944.7916870117188</v>
+        <v>944.791748046875</v>
       </c>
       <c r="J151" t="n">
         <v>13.30000019073486</v>
@@ -4843,7 +4843,7 @@
         <v>66.65000152587891</v>
       </c>
       <c r="G152" t="n">
-        <v>1169.660522460938</v>
+        <v>1169.66064453125</v>
       </c>
       <c r="H152" t="n">
         <v>117.5500030517578</v>
@@ -4878,7 +4878,7 @@
         <v>115.3499984741211</v>
       </c>
       <c r="I153" t="n">
-        <v>953.8790893554688</v>
+        <v>953.8790283203125</v>
       </c>
       <c r="J153" t="n">
         <v>13.60000038146973</v>
@@ -4901,13 +4901,13 @@
         <v>68.34999847412109</v>
       </c>
       <c r="G154" t="n">
-        <v>1192.53271484375</v>
+        <v>1192.532836914062</v>
       </c>
       <c r="H154" t="n">
         <v>115.1500015258789</v>
       </c>
       <c r="I154" t="n">
-        <v>954.0264282226562</v>
+        <v>954.0263671875</v>
       </c>
       <c r="J154" t="n">
         <v>13.39999961853027</v>
@@ -4994,7 +4994,7 @@
         <v>129.8999938964844</v>
       </c>
       <c r="I157" t="n">
-        <v>1020.880004882812</v>
+        <v>1020.879943847656</v>
       </c>
       <c r="J157" t="n">
         <v>14.19999980926514</v>
@@ -5017,7 +5017,7 @@
         <v>73.75</v>
       </c>
       <c r="G158" t="n">
-        <v>1187.722045898438</v>
+        <v>1187.72216796875</v>
       </c>
       <c r="H158" t="n">
         <v>135.6000061035156</v>
@@ -5046,13 +5046,13 @@
         <v>72.15000152587891</v>
       </c>
       <c r="G159" t="n">
-        <v>1184.427734375</v>
+        <v>1184.427856445312</v>
       </c>
       <c r="H159" t="n">
         <v>140.6999969482422</v>
       </c>
       <c r="I159" t="n">
-        <v>973.0362548828125</v>
+        <v>973.0361328125</v>
       </c>
       <c r="J159" t="n">
         <v>15.64999961853027</v>
@@ -5081,7 +5081,7 @@
         <v>138.6999969482422</v>
       </c>
       <c r="I160" t="n">
-        <v>1004.915771484375</v>
+        <v>1004.915649414062</v>
       </c>
       <c r="J160" t="n">
         <v>15.39999961853027</v>
@@ -5104,7 +5104,7 @@
         <v>74.15000152587891</v>
       </c>
       <c r="G161" t="n">
-        <v>1199.490966796875</v>
+        <v>1199.490844726562</v>
       </c>
       <c r="H161" t="n">
         <v>139.6999969482422</v>
@@ -5133,13 +5133,13 @@
         <v>74.05000305175781</v>
       </c>
       <c r="G162" t="n">
-        <v>1195.992309570312</v>
+        <v>1195.9921875</v>
       </c>
       <c r="H162" t="n">
         <v>139.75</v>
       </c>
       <c r="I162" t="n">
-        <v>1002.852600097656</v>
+        <v>1002.8525390625</v>
       </c>
       <c r="J162" t="n">
         <v>15.05000019073486</v>
@@ -5168,7 +5168,7 @@
         <v>157.3500061035156</v>
       </c>
       <c r="I163" t="n">
-        <v>997.10546875</v>
+        <v>997.1054077148438</v>
       </c>
       <c r="J163" t="n">
         <v>16.25</v>
@@ -5191,7 +5191,7 @@
         <v>69.65000152587891</v>
       </c>
       <c r="G164" t="n">
-        <v>1180.36083984375</v>
+        <v>1180.360961914062</v>
       </c>
       <c r="H164" t="n">
         <v>158.75</v>
@@ -5226,7 +5226,7 @@
         <v>162</v>
       </c>
       <c r="I165" t="n">
-        <v>1006.291137695312</v>
+        <v>1006.291076660156</v>
       </c>
       <c r="J165" t="n">
         <v>16.79999923706055</v>
@@ -5284,7 +5284,7 @@
         <v>179.1499938964844</v>
       </c>
       <c r="I167" t="n">
-        <v>1082.08447265625</v>
+        <v>1082.084594726562</v>
       </c>
       <c r="J167" t="n">
         <v>21.20000076293945</v>
@@ -5307,13 +5307,13 @@
         <v>75.59999847412109</v>
       </c>
       <c r="G168" t="n">
-        <v>1167.7060546875</v>
+        <v>1167.705932617188</v>
       </c>
       <c r="H168" t="n">
         <v>182.6999969482422</v>
       </c>
       <c r="I168" t="n">
-        <v>1193.93310546875</v>
+        <v>1193.932983398438</v>
       </c>
       <c r="J168" t="n">
         <v>23.29999923706055</v>
@@ -5336,13 +5336,13 @@
         <v>73.94999694824219</v>
       </c>
       <c r="G169" t="n">
-        <v>1179.997436523438</v>
+        <v>1179.997314453125</v>
       </c>
       <c r="H169" t="n">
         <v>178.75</v>
       </c>
       <c r="I169" t="n">
-        <v>1173.302124023438</v>
+        <v>1173.302001953125</v>
       </c>
       <c r="J169" t="n">
         <v>21.95000076293945</v>
@@ -5365,7 +5365,7 @@
         <v>75.09999847412109</v>
       </c>
       <c r="G170" t="n">
-        <v>1173.136108398438</v>
+        <v>1173.135986328125</v>
       </c>
       <c r="H170" t="n">
         <v>180.6999969482422</v>
@@ -5423,13 +5423,13 @@
         <v>74.05000305175781</v>
       </c>
       <c r="G172" t="n">
-        <v>1167.478881835938</v>
+        <v>1167.47900390625</v>
       </c>
       <c r="H172" t="n">
         <v>162.4499969482422</v>
       </c>
       <c r="I172" t="n">
-        <v>1153.801147460938</v>
+        <v>1153.80126953125</v>
       </c>
       <c r="J172" t="n">
         <v>19.20000076293945</v>
@@ -5452,7 +5452,7 @@
         <v>73.90000152587891</v>
       </c>
       <c r="G173" t="n">
-        <v>1180.542602539062</v>
+        <v>1180.542724609375</v>
       </c>
       <c r="H173" t="n">
         <v>174.1999969482422</v>
@@ -5481,7 +5481,7 @@
         <v>74.15000152587891</v>
       </c>
       <c r="G174" t="n">
-        <v>1190.403076171875</v>
+        <v>1190.402954101562</v>
       </c>
       <c r="H174" t="n">
         <v>165.5</v>
@@ -5516,7 +5516,7 @@
         <v>157.4499969482422</v>
       </c>
       <c r="I175" t="n">
-        <v>1151.197875976562</v>
+        <v>1151.19775390625</v>
       </c>
       <c r="J175" t="n">
         <v>19.04999923706055</v>
@@ -5539,7 +5539,7 @@
         <v>71.75</v>
       </c>
       <c r="G176" t="n">
-        <v>1164.479858398438</v>
+        <v>1164.47998046875</v>
       </c>
       <c r="H176" t="n">
         <v>154.4499969482422</v>
@@ -5574,7 +5574,7 @@
         <v>156.3500061035156</v>
       </c>
       <c r="I177" t="n">
-        <v>1119.121704101562</v>
+        <v>1119.121948242188</v>
       </c>
       <c r="J177" t="n">
         <v>18.45000076293945</v>
@@ -5597,13 +5597,13 @@
         <v>67.05000305175781</v>
       </c>
       <c r="G178" t="n">
-        <v>1137.1025390625</v>
+        <v>1137.102416992188</v>
       </c>
       <c r="H178" t="n">
         <v>151.8000030517578</v>
       </c>
       <c r="I178" t="n">
-        <v>1159.351806640625</v>
+        <v>1159.351928710938</v>
       </c>
       <c r="J178" t="n">
         <v>17.64999961853027</v>
@@ -5632,7 +5632,7 @@
         <v>154.4499969482422</v>
       </c>
       <c r="I179" t="n">
-        <v>1188.160766601562</v>
+        <v>1188.16064453125</v>
       </c>
       <c r="J179" t="n">
         <v>18.20000076293945</v>
@@ -5655,7 +5655,7 @@
         <v>69.90000152587891</v>
       </c>
       <c r="G180" t="n">
-        <v>1140.419677734375</v>
+        <v>1140.419555664062</v>
       </c>
       <c r="H180" t="n">
         <v>146.75</v>
@@ -5748,7 +5748,7 @@
         <v>137.1999969482422</v>
       </c>
       <c r="I183" t="n">
-        <v>1051.699829101562</v>
+        <v>1051.69970703125</v>
       </c>
       <c r="J183" t="n">
         <v>16.35000038146973</v>
@@ -5800,13 +5800,13 @@
         <v>61.70000076293945</v>
       </c>
       <c r="G185" t="n">
-        <v>1059.855102539062</v>
+        <v>1059.855224609375</v>
       </c>
       <c r="H185" t="n">
         <v>136.3500061035156</v>
       </c>
       <c r="I185" t="n">
-        <v>1021.610412597656</v>
+        <v>1021.610595703125</v>
       </c>
       <c r="J185" t="n">
         <v>16.10000038146973</v>
@@ -5829,7 +5829,7 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G186" t="n">
-        <v>1056.606201171875</v>
+        <v>1056.606323242188</v>
       </c>
       <c r="H186" t="n">
         <v>137.6499938964844</v>
@@ -5858,7 +5858,7 @@
         <v>64.59999847412109</v>
       </c>
       <c r="G187" t="n">
-        <v>1080.439453125</v>
+        <v>1080.439208984375</v>
       </c>
       <c r="H187" t="n">
         <v>136.6999969482422</v>
@@ -5893,7 +5893,7 @@
         <v>135.4499969482422</v>
       </c>
       <c r="I188" t="n">
-        <v>1031.902709960938</v>
+        <v>1031.90283203125</v>
       </c>
       <c r="J188" t="n">
         <v>16.45000076293945</v>
@@ -5916,7 +5916,7 @@
         <v>66</v>
       </c>
       <c r="G189" t="n">
-        <v>1096.547729492188</v>
+        <v>1096.547607421875</v>
       </c>
       <c r="H189" t="n">
         <v>137.5500030517578</v>
@@ -6061,13 +6061,13 @@
         <v>68.69999694824219</v>
       </c>
       <c r="G194" t="n">
-        <v>1079.303344726562</v>
+        <v>1079.30322265625</v>
       </c>
       <c r="H194" t="n">
         <v>142.6999969482422</v>
       </c>
       <c r="I194" t="n">
-        <v>1128.178955078125</v>
+        <v>1128.179077148438</v>
       </c>
       <c r="J194" t="n">
         <v>16.35000038146973</v>
@@ -6090,13 +6090,13 @@
         <v>67.59999847412109</v>
       </c>
       <c r="G195" t="n">
-        <v>1082.734130859375</v>
+        <v>1082.734008789062</v>
       </c>
       <c r="H195" t="n">
         <v>142.3500061035156</v>
       </c>
       <c r="I195" t="n">
-        <v>1122.663330078125</v>
+        <v>1122.663452148438</v>
       </c>
       <c r="J195" t="n">
         <v>16.5</v>
@@ -6119,13 +6119,13 @@
         <v>67.19999694824219</v>
       </c>
       <c r="G196" t="n">
-        <v>1077.23583984375</v>
+        <v>1077.235717773438</v>
       </c>
       <c r="H196" t="n">
         <v>138.8500061035156</v>
       </c>
       <c r="I196" t="n">
-        <v>1100.404174804688</v>
+        <v>1100.404296875</v>
       </c>
       <c r="J196" t="n">
         <v>16.20000076293945</v>
@@ -6148,13 +6148,13 @@
         <v>66.40000152587891</v>
       </c>
       <c r="G197" t="n">
-        <v>1094.525512695312</v>
+        <v>1094.525634765625</v>
       </c>
       <c r="H197" t="n">
         <v>138.6999969482422</v>
       </c>
       <c r="I197" t="n">
-        <v>1122.56494140625</v>
+        <v>1122.564819335938</v>
       </c>
       <c r="J197" t="n">
         <v>16.20000076293945</v>
@@ -6177,7 +6177,7 @@
         <v>70</v>
       </c>
       <c r="G198" t="n">
-        <v>1113.837524414062</v>
+        <v>1113.83740234375</v>
       </c>
       <c r="H198" t="n">
         <v>143.6999969482422</v>
@@ -6206,13 +6206,13 @@
         <v>65.59999847412109</v>
       </c>
       <c r="G199" t="n">
-        <v>1133.217407226562</v>
+        <v>1133.21728515625</v>
       </c>
       <c r="H199" t="n">
         <v>141.3500061035156</v>
       </c>
       <c r="I199" t="n">
-        <v>1121.087646484375</v>
+        <v>1121.087524414062</v>
       </c>
       <c r="J199" t="n">
         <v>16.35000038146973</v>
@@ -6264,7 +6264,7 @@
         <v>63.70000076293945</v>
       </c>
       <c r="G201" t="n">
-        <v>1123.084350585938</v>
+        <v>1123.084228515625</v>
       </c>
       <c r="H201" t="n">
         <v>139.1499938964844</v>
@@ -6328,7 +6328,7 @@
         <v>141.6000061035156</v>
       </c>
       <c r="I203" t="n">
-        <v>1089.717895507812</v>
+        <v>1089.7177734375</v>
       </c>
       <c r="J203" t="n">
         <v>16.29999923706055</v>
@@ -6357,7 +6357,7 @@
         <v>141.8500061035156</v>
       </c>
       <c r="I204" t="n">
-        <v>1086.56591796875</v>
+        <v>1086.566040039062</v>
       </c>
       <c r="J204" t="n">
         <v>16.14999961853027</v>
@@ -6380,7 +6380,7 @@
         <v>63.25</v>
       </c>
       <c r="G205" t="n">
-        <v>1147.871826171875</v>
+        <v>1147.87158203125</v>
       </c>
       <c r="H205" t="n">
         <v>141.8999938964844</v>
@@ -6409,13 +6409,13 @@
         <v>64.15000152587891</v>
       </c>
       <c r="G206" t="n">
-        <v>1158.527221679688</v>
+        <v>1158.52734375</v>
       </c>
       <c r="H206" t="n">
         <v>141.4499969482422</v>
       </c>
       <c r="I206" t="n">
-        <v>1081.54296875</v>
+        <v>1081.542846679688</v>
       </c>
       <c r="J206" t="n">
         <v>16.10000038146973</v>
@@ -6438,13 +6438,13 @@
         <v>62.90000152587891</v>
       </c>
       <c r="G207" t="n">
-        <v>1149.552978515625</v>
+        <v>1149.552856445312</v>
       </c>
       <c r="H207" t="n">
         <v>140.6499938964844</v>
       </c>
       <c r="I207" t="n">
-        <v>1085.728881835938</v>
+        <v>1085.728759765625</v>
       </c>
       <c r="J207" t="n">
         <v>16.04999923706055</v>
@@ -6473,7 +6473,7 @@
         <v>140.5500030517578</v>
       </c>
       <c r="I208" t="n">
-        <v>1097.3017578125</v>
+        <v>1097.301513671875</v>
       </c>
       <c r="J208" t="n">
         <v>16.10000038146973</v>
@@ -6502,7 +6502,7 @@
         <v>140.1499938964844</v>
       </c>
       <c r="I209" t="n">
-        <v>1067.310791015625</v>
+        <v>1067.310913085938</v>
       </c>
       <c r="J209" t="n">
         <v>16</v>
@@ -6554,13 +6554,13 @@
         <v>65.40000152587891</v>
       </c>
       <c r="G211" t="n">
-        <v>1184.427734375</v>
+        <v>1184.427856445312</v>
       </c>
       <c r="H211" t="n">
         <v>152.9499969482422</v>
       </c>
       <c r="I211" t="n">
-        <v>1081.936889648438</v>
+        <v>1081.93701171875</v>
       </c>
       <c r="J211" t="n">
         <v>16.85000038146973</v>
@@ -6612,13 +6612,13 @@
         <v>64.5</v>
       </c>
       <c r="G213" t="n">
-        <v>1168.932861328125</v>
+        <v>1168.932983398438</v>
       </c>
       <c r="H213" t="n">
         <v>142.8500061035156</v>
       </c>
       <c r="I213" t="n">
-        <v>1053.669799804688</v>
+        <v>1053.669555664062</v>
       </c>
       <c r="J213" t="n">
         <v>16.10000038146973</v>
@@ -6641,7 +6641,7 @@
         <v>63.95000076293945</v>
       </c>
       <c r="G214" t="n">
-        <v>1195.878540039062</v>
+        <v>1195.878662109375</v>
       </c>
       <c r="H214" t="n">
         <v>146.1999969482422</v>
@@ -6676,7 +6676,7 @@
         <v>153.3999938964844</v>
       </c>
       <c r="I215" t="n">
-        <v>1071.693603515625</v>
+        <v>1071.693725585938</v>
       </c>
       <c r="J215" t="n">
         <v>16.04999923706055</v>
@@ -6699,13 +6699,13 @@
         <v>63.04999923706055</v>
       </c>
       <c r="G216" t="n">
-        <v>1184.745971679688</v>
+        <v>1184.745849609375</v>
       </c>
       <c r="H216" t="n">
         <v>151.3500061035156</v>
       </c>
       <c r="I216" t="n">
-        <v>1058.939086914062</v>
+        <v>1058.93896484375</v>
       </c>
       <c r="J216" t="n">
         <v>16.10000038146973</v>
@@ -6728,13 +6728,13 @@
         <v>62.54999923706055</v>
       </c>
       <c r="G217" t="n">
-        <v>1177.95263671875</v>
+        <v>1177.952758789062</v>
       </c>
       <c r="H217" t="n">
         <v>148.6499938964844</v>
       </c>
       <c r="I217" t="n">
-        <v>1012.499877929688</v>
+        <v>1012.499938964844</v>
       </c>
       <c r="J217" t="n">
         <v>16</v>
@@ -6786,13 +6786,13 @@
         <v>61.59999847412109</v>
       </c>
       <c r="G219" t="n">
-        <v>1180.36083984375</v>
+        <v>1180.360961914062</v>
       </c>
       <c r="H219" t="n">
         <v>147.6499938964844</v>
       </c>
       <c r="I219" t="n">
-        <v>990.683837890625</v>
+        <v>990.6838989257812</v>
       </c>
       <c r="J219" t="n">
         <v>15.5</v>
@@ -6879,7 +6879,7 @@
         <v>146.1499938964844</v>
       </c>
       <c r="I222" t="n">
-        <v>995.8055419921875</v>
+        <v>995.8054809570312</v>
       </c>
       <c r="J222" t="n">
         <v>15.19999980926514</v>
@@ -6902,7 +6902,7 @@
         <v>60.40000152587891</v>
       </c>
       <c r="G223" t="n">
-        <v>1171.931884765625</v>
+        <v>1171.932006835938</v>
       </c>
       <c r="H223" t="n">
         <v>147.0500030517578</v>
@@ -6931,13 +6931,13 @@
         <v>62.95000076293945</v>
       </c>
       <c r="G224" t="n">
-        <v>1189.426025390625</v>
+        <v>1189.42626953125</v>
       </c>
       <c r="H224" t="n">
         <v>154.3000030517578</v>
       </c>
       <c r="I224" t="n">
-        <v>1008.067749023438</v>
+        <v>1008.067810058594</v>
       </c>
       <c r="J224" t="n">
         <v>16</v>
@@ -7024,7 +7024,7 @@
         <v>157.6999969482422</v>
       </c>
       <c r="I227" t="n">
-        <v>1039.289672851562</v>
+        <v>1039.289794921875</v>
       </c>
       <c r="J227" t="n">
         <v>16.04999923706055</v>
@@ -7047,13 +7047,13 @@
         <v>73.40000152587891</v>
       </c>
       <c r="G228" t="n">
-        <v>1237.455810546875</v>
+        <v>1237.455688476562</v>
       </c>
       <c r="H228" t="n">
         <v>156.1000061035156</v>
       </c>
       <c r="I228" t="n">
-        <v>1040.2255859375</v>
+        <v>1040.225463867188</v>
       </c>
       <c r="J228" t="n">
         <v>16</v>
@@ -7076,13 +7076,13 @@
         <v>74.19999694824219</v>
       </c>
       <c r="G229" t="n">
-        <v>1236.932983398438</v>
+        <v>1236.933227539062</v>
       </c>
       <c r="H229" t="n">
         <v>162.8999938964844</v>
       </c>
       <c r="I229" t="n">
-        <v>1033.675903320312</v>
+        <v>1033.67578125</v>
       </c>
       <c r="J229" t="n">
         <v>16.79999923706055</v>
@@ -7105,13 +7105,13 @@
         <v>75.94999694824219</v>
       </c>
       <c r="G230" t="n">
-        <v>1218.893676757812</v>
+        <v>1218.893798828125</v>
       </c>
       <c r="H230" t="n">
         <v>157.8999938964844</v>
       </c>
       <c r="I230" t="n">
-        <v>1054.162231445312</v>
+        <v>1054.162109375</v>
       </c>
       <c r="J230" t="n">
         <v>16.04999923706055</v>
@@ -7134,13 +7134,13 @@
         <v>73.5</v>
       </c>
       <c r="G231" t="n">
-        <v>1222.415161132812</v>
+        <v>1222.415283203125</v>
       </c>
       <c r="H231" t="n">
         <v>156.3999938964844</v>
       </c>
       <c r="I231" t="n">
-        <v>1050.419311523438</v>
+        <v>1050.41943359375</v>
       </c>
       <c r="J231" t="n">
         <v>15.85000038146973</v>
@@ -7163,13 +7163,13 @@
         <v>71.19999694824219</v>
       </c>
       <c r="G232" t="n">
-        <v>1204.375732421875</v>
+        <v>1204.375610351562</v>
       </c>
       <c r="H232" t="n">
         <v>154.1999969482422</v>
       </c>
       <c r="I232" t="n">
-        <v>1031.902709960938</v>
+        <v>1031.90283203125</v>
       </c>
       <c r="J232" t="n">
         <v>15.69999980926514</v>
@@ -7192,13 +7192,13 @@
         <v>74.25</v>
       </c>
       <c r="G233" t="n">
-        <v>1203.807739257812</v>
+        <v>1203.8076171875</v>
       </c>
       <c r="H233" t="n">
         <v>154.0500030517578</v>
       </c>
       <c r="I233" t="n">
-        <v>1031.311889648438</v>
+        <v>1031.31201171875</v>
       </c>
       <c r="J233" t="n">
         <v>15.85000038146973</v>
@@ -7221,13 +7221,13 @@
         <v>72.90000152587891</v>
       </c>
       <c r="G234" t="n">
-        <v>1185.563842773438</v>
+        <v>1185.563720703125</v>
       </c>
       <c r="H234" t="n">
         <v>154.75</v>
       </c>
       <c r="I234" t="n">
-        <v>1009.98828125</v>
+        <v>1009.988342285156</v>
       </c>
       <c r="J234" t="n">
         <v>15.89999961853027</v>
@@ -7256,7 +7256,7 @@
         <v>161.8000030517578</v>
       </c>
       <c r="I235" t="n">
-        <v>1015.454772949219</v>
+        <v>1015.454711914062</v>
       </c>
       <c r="J235" t="n">
         <v>15.94999980926514</v>
@@ -7285,7 +7285,7 @@
         <v>157.25</v>
       </c>
       <c r="I236" t="n">
-        <v>1016.488891601562</v>
+        <v>1016.488952636719</v>
       </c>
       <c r="J236" t="n">
         <v>15.75</v>
@@ -7314,7 +7314,7 @@
         <v>156.6499938964844</v>
       </c>
       <c r="I237" t="n">
-        <v>1012.943054199219</v>
+        <v>1012.942993164062</v>
       </c>
       <c r="J237" t="n">
         <v>16.45000076293945</v>
@@ -7343,7 +7343,7 @@
         <v>148.8999938964844</v>
       </c>
       <c r="I238" t="n">
-        <v>1001.271850585938</v>
+        <v>1001.271789550781</v>
       </c>
       <c r="J238" t="n">
         <v>15.89999961853027</v>
@@ -7372,7 +7372,7 @@
         <v>151.1000061035156</v>
       </c>
       <c r="I239" t="n">
-        <v>982.7553100585938</v>
+        <v>982.7552490234375</v>
       </c>
       <c r="J239" t="n">
         <v>15.75</v>
@@ -7430,7 +7430,7 @@
         <v>149.8000030517578</v>
       </c>
       <c r="I241" t="n">
-        <v>982.213623046875</v>
+        <v>982.2135620117188</v>
       </c>
       <c r="J241" t="n">
         <v>15.75</v>
@@ -7459,7 +7459,7 @@
         <v>142.5500030517578</v>
       </c>
       <c r="I242" t="n">
-        <v>939.5665283203125</v>
+        <v>939.5664672851562</v>
       </c>
       <c r="J242" t="n">
         <v>15</v>
@@ -7517,7 +7517,7 @@
         <v>128.6999969482422</v>
       </c>
       <c r="I244" t="n">
-        <v>796.0140991210938</v>
+        <v>796.0140380859375</v>
       </c>
       <c r="J244" t="n">
         <v>13.55000019073486</v>
@@ -7546,7 +7546,7 @@
         <v>128.1999969482422</v>
       </c>
       <c r="I245" t="n">
-        <v>858.014892578125</v>
+        <v>858.0149536132812</v>
       </c>
       <c r="J245" t="n">
         <v>14.14999961853027</v>
@@ -7598,13 +7598,13 @@
         <v>67.05000305175781</v>
       </c>
       <c r="G247" t="n">
-        <v>1156.187255859375</v>
+        <v>1156.18701171875</v>
       </c>
       <c r="H247" t="n">
         <v>136.5</v>
       </c>
       <c r="I247" t="n">
-        <v>919.81884765625</v>
+        <v>919.8187866210938</v>
       </c>
       <c r="J247" t="n">
         <v>14.60000038146973</v>
@@ -7627,7 +7627,7 @@
         <v>66.15000152587891</v>
       </c>
       <c r="G248" t="n">
-        <v>1155.66455078125</v>
+        <v>1155.664672851562</v>
       </c>
       <c r="H248" t="n">
         <v>135.8000030517578</v>
@@ -7656,13 +7656,13 @@
         <v>66.09999847412109</v>
       </c>
       <c r="G249" t="n">
-        <v>1157.4365234375</v>
+        <v>1157.436645507812</v>
       </c>
       <c r="H249" t="n">
         <v>137.6999969482422</v>
       </c>
       <c r="I249" t="n">
-        <v>930.1112060546875</v>
+        <v>930.1111450195312</v>
       </c>
       <c r="J249" t="n">
         <v>14.35000038146973</v>
@@ -7685,7 +7685,7 @@
         <v>67.55000305175781</v>
       </c>
       <c r="G250" t="n">
-        <v>1170.477783203125</v>
+        <v>1170.477905273438</v>
       </c>
       <c r="H250" t="n">
         <v>137.8500061035156</v>
@@ -7772,13 +7772,13 @@
         <v>65.75</v>
       </c>
       <c r="G253" t="n">
-        <v>1142.373413085938</v>
+        <v>1142.373291015625</v>
       </c>
       <c r="H253" t="n">
         <v>133.75</v>
       </c>
       <c r="I253" t="n">
-        <v>905.3404541015625</v>
+        <v>905.3403930664062</v>
       </c>
       <c r="J253" t="n">
         <v>14.60000038146973</v>
@@ -7801,13 +7801,13 @@
         <v>65.40000152587891</v>
       </c>
       <c r="G254" t="n">
-        <v>1152.756469726562</v>
+        <v>1152.75634765625</v>
       </c>
       <c r="H254" t="n">
         <v>130.1999969482422</v>
       </c>
       <c r="I254" t="n">
-        <v>892.9302978515625</v>
+        <v>892.9303588867188</v>
       </c>
       <c r="J254" t="n">
         <v>14.44999980926514</v>
@@ -7836,7 +7836,7 @@
         <v>135.0500030517578</v>
       </c>
       <c r="I255" t="n">
-        <v>922.3302612304688</v>
+        <v>922.330322265625</v>
       </c>
       <c r="J255" t="n">
         <v>14.55000019073486</v>
@@ -7859,7 +7859,7 @@
         <v>63.75</v>
       </c>
       <c r="G256" t="n">
-        <v>1162.526000976562</v>
+        <v>1162.52587890625</v>
       </c>
       <c r="H256" t="n">
         <v>133</v>
@@ -7888,7 +7888,7 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G257" t="n">
-        <v>1147.871826171875</v>
+        <v>1147.87158203125</v>
       </c>
       <c r="H257" t="n">
         <v>134.3000030517578</v>
@@ -7917,7 +7917,7 @@
         <v>63.59999847412109</v>
       </c>
       <c r="G258" t="n">
-        <v>1123.084350585938</v>
+        <v>1123.084228515625</v>
       </c>
       <c r="H258" t="n">
         <v>132.3000030517578</v>
@@ -7946,7 +7946,7 @@
         <v>63.84999847412109</v>
       </c>
       <c r="G259" t="n">
-        <v>1121.266845703125</v>
+        <v>1121.266723632812</v>
       </c>
       <c r="H259" t="n">
         <v>132.6499938964844</v>
@@ -7975,7 +7975,7 @@
         <v>65.44999694824219</v>
       </c>
       <c r="G260" t="n">
-        <v>1110.588500976562</v>
+        <v>1110.58837890625</v>
       </c>
       <c r="H260" t="n">
         <v>139.25</v>
@@ -8033,7 +8033,7 @@
         <v>62.84999847412109</v>
       </c>
       <c r="G262" t="n">
-        <v>1124.492919921875</v>
+        <v>1124.493041992188</v>
       </c>
       <c r="H262" t="n">
         <v>139.5</v>
@@ -8062,13 +8062,13 @@
         <v>62.25</v>
       </c>
       <c r="G263" t="n">
-        <v>1123.288940429688</v>
+        <v>1123.288696289062</v>
       </c>
       <c r="H263" t="n">
         <v>137.5</v>
       </c>
       <c r="I263" t="n">
-        <v>901.8439331054688</v>
+        <v>901.843994140625</v>
       </c>
       <c r="J263" t="n">
         <v>14</v>
@@ -8091,13 +8091,13 @@
         <v>61.34999847412109</v>
       </c>
       <c r="G264" t="n">
-        <v>1109.9296875</v>
+        <v>1109.929565429688</v>
       </c>
       <c r="H264" t="n">
         <v>136.25</v>
       </c>
       <c r="I264" t="n">
-        <v>895.3927001953125</v>
+        <v>895.3926391601562</v>
       </c>
       <c r="J264" t="n">
         <v>13.85000038146973</v>
@@ -8120,13 +8120,13 @@
         <v>61.5</v>
       </c>
       <c r="G265" t="n">
-        <v>1104.31787109375</v>
+        <v>1104.317749023438</v>
       </c>
       <c r="H265" t="n">
         <v>133.6999969482422</v>
       </c>
       <c r="I265" t="n">
-        <v>892.0439453125</v>
+        <v>892.0440063476562</v>
       </c>
       <c r="J265" t="n">
         <v>13.19999980926514</v>
@@ -8155,7 +8155,7 @@
         <v>132.1000061035156</v>
       </c>
       <c r="I266" t="n">
-        <v>882.8842163085938</v>
+        <v>882.8841552734375</v>
       </c>
       <c r="J266" t="n">
         <v>13.19999980926514</v>
@@ -8184,7 +8184,7 @@
         <v>128.1499938964844</v>
       </c>
       <c r="I267" t="n">
-        <v>869.78466796875</v>
+        <v>869.7847290039062</v>
       </c>
       <c r="J267" t="n">
         <v>12.94999980926514</v>
@@ -8236,7 +8236,7 @@
         <v>58.45000076293945</v>
       </c>
       <c r="G269" t="n">
-        <v>1072.260375976562</v>
+        <v>1072.26025390625</v>
       </c>
       <c r="H269" t="n">
         <v>119.1500015258789</v>
@@ -8265,13 +8265,13 @@
         <v>61.54999923706055</v>
       </c>
       <c r="G270" t="n">
-        <v>1069.579223632812</v>
+        <v>1069.579345703125</v>
       </c>
       <c r="H270" t="n">
         <v>125.0999984741211</v>
       </c>
       <c r="I270" t="n">
-        <v>856.8822021484375</v>
+        <v>856.8822631835938</v>
       </c>
       <c r="J270" t="n">
         <v>12.75</v>
@@ -8352,7 +8352,7 @@
         <v>59.34999847412109</v>
       </c>
       <c r="G273" t="n">
-        <v>1058.28759765625</v>
+        <v>1058.287353515625</v>
       </c>
       <c r="H273" t="n">
         <v>121.4000015258789</v>
@@ -8381,7 +8381,7 @@
         <v>59.70000076293945</v>
       </c>
       <c r="G274" t="n">
-        <v>1050.312866210938</v>
+        <v>1050.312744140625</v>
       </c>
       <c r="H274" t="n">
         <v>124.4499969482422</v>
@@ -8410,13 +8410,13 @@
         <v>59.54999923706055</v>
       </c>
       <c r="G275" t="n">
-        <v>1047.790893554688</v>
+        <v>1047.791015625</v>
       </c>
       <c r="H275" t="n">
         <v>123.25</v>
       </c>
       <c r="I275" t="n">
-        <v>819.7998657226562</v>
+        <v>819.7999267578125</v>
       </c>
       <c r="J275" t="n">
         <v>11.64999961853027</v>
@@ -8445,7 +8445,7 @@
         <v>123.5500030517578</v>
       </c>
       <c r="I276" t="n">
-        <v>842.8471069335938</v>
+        <v>842.8469848632812</v>
       </c>
       <c r="J276" t="n">
         <v>11.69999980926514</v>
@@ -8468,13 +8468,13 @@
         <v>60.95000076293945</v>
       </c>
       <c r="G277" t="n">
-        <v>1070.578857421875</v>
+        <v>1070.578979492188</v>
       </c>
       <c r="H277" t="n">
         <v>127.3000030517578</v>
       </c>
       <c r="I277" t="n">
-        <v>831.4219970703125</v>
+        <v>831.4220581054688</v>
       </c>
       <c r="J277" t="n">
         <v>11.69999980926514</v>
@@ -8503,7 +8503,7 @@
         <v>130.9499969482422</v>
       </c>
       <c r="I278" t="n">
-        <v>833.8350830078125</v>
+        <v>833.8350219726562</v>
       </c>
       <c r="J278" t="n">
         <v>11.64999961853027</v>
@@ -8526,13 +8526,13 @@
         <v>60.29999923706055</v>
       </c>
       <c r="G279" t="n">
-        <v>1055.720336914062</v>
+        <v>1055.72021484375</v>
       </c>
       <c r="H279" t="n">
         <v>127.5500030517578</v>
       </c>
       <c r="I279" t="n">
-        <v>823.7888793945312</v>
+        <v>823.788818359375</v>
       </c>
       <c r="J279" t="n">
         <v>11.35000038146973</v>
@@ -8648,7 +8648,7 @@
         <v>127.0500030517578</v>
       </c>
       <c r="I283" t="n">
-        <v>853.6812744140625</v>
+        <v>853.6812133789062</v>
       </c>
       <c r="J283" t="n">
         <v>11.05000019073486</v>
@@ -8706,7 +8706,7 @@
         <v>120.8000030517578</v>
       </c>
       <c r="I285" t="n">
-        <v>833.3425903320312</v>
+        <v>833.342529296875</v>
       </c>
       <c r="J285" t="n">
         <v>10.60000038146973</v>
@@ -8729,13 +8729,13 @@
         <v>59.34999847412109</v>
       </c>
       <c r="G286" t="n">
-        <v>1080.9619140625</v>
+        <v>1080.961791992188</v>
       </c>
       <c r="H286" t="n">
         <v>118.5500030517578</v>
       </c>
       <c r="I286" t="n">
-        <v>818.1256103515625</v>
+        <v>818.1255493164062</v>
       </c>
       <c r="J286" t="n">
         <v>10.39999961853027</v>
@@ -8758,7 +8758,7 @@
         <v>59.04999923706055</v>
       </c>
       <c r="G287" t="n">
-        <v>1075.78173828125</v>
+        <v>1075.781616210938</v>
       </c>
       <c r="H287" t="n">
         <v>115.8000030517578</v>
@@ -8787,13 +8787,13 @@
         <v>58.5</v>
       </c>
       <c r="G288" t="n">
-        <v>1083.142822265625</v>
+        <v>1083.142944335938</v>
       </c>
       <c r="H288" t="n">
         <v>126.9499969482422</v>
       </c>
       <c r="I288" t="n">
-        <v>802.1697387695312</v>
+        <v>802.1697998046875</v>
       </c>
       <c r="J288" t="n">
         <v>10.10000038146973</v>
@@ -8822,7 +8822,7 @@
         <v>127.75</v>
       </c>
       <c r="I289" t="n">
-        <v>789.316650390625</v>
+        <v>789.3165893554688</v>
       </c>
       <c r="J289" t="n">
         <v>9.899999618530273</v>
@@ -8851,7 +8851,7 @@
         <v>130.6999969482422</v>
       </c>
       <c r="I290" t="n">
-        <v>789.8583374023438</v>
+        <v>789.8582763671875</v>
       </c>
       <c r="J290" t="n">
         <v>9.800000190734863</v>
@@ -8874,13 +8874,13 @@
         <v>58.90000152587891</v>
       </c>
       <c r="G291" t="n">
-        <v>1065.057983398438</v>
+        <v>1065.05810546875</v>
       </c>
       <c r="H291" t="n">
         <v>135.6999969482422</v>
       </c>
       <c r="I291" t="n">
-        <v>827.8270874023438</v>
+        <v>827.8270263671875</v>
       </c>
       <c r="J291" t="n">
         <v>10</v>
@@ -8903,7 +8903,7 @@
         <v>58.54999923706055</v>
       </c>
       <c r="G292" t="n">
-        <v>1056.947143554688</v>
+        <v>1056.947021484375</v>
       </c>
       <c r="H292" t="n">
         <v>135.8000030517578</v>
@@ -8932,7 +8932,7 @@
         <v>59.29999923706055</v>
       </c>
       <c r="G293" t="n">
-        <v>1083.91552734375</v>
+        <v>1083.915405273438</v>
       </c>
       <c r="H293" t="n">
         <v>143.25</v>
@@ -8967,7 +8967,7 @@
         <v>140.8000030517578</v>
       </c>
       <c r="I294" t="n">
-        <v>843.8320922851562</v>
+        <v>843.83203125</v>
       </c>
       <c r="J294" t="n">
         <v>10.69999980926514</v>
@@ -9019,7 +9019,7 @@
         <v>58.95000076293945</v>
       </c>
       <c r="G296" t="n">
-        <v>1072.032958984375</v>
+        <v>1072.033081054688</v>
       </c>
       <c r="H296" t="n">
         <v>146.3500061035156</v>
@@ -9054,7 +9054,7 @@
         <v>147.25</v>
       </c>
       <c r="I297" t="n">
-        <v>835.9034423828125</v>
+        <v>835.9033813476562</v>
       </c>
       <c r="J297" t="n">
         <v>11.44999980926514</v>
@@ -9083,7 +9083,7 @@
         <v>139.6499938964844</v>
       </c>
       <c r="I298" t="n">
-        <v>793.7979736328125</v>
+        <v>793.7979125976562</v>
       </c>
       <c r="J298" t="n">
         <v>10.75</v>
@@ -9106,7 +9106,7 @@
         <v>53.70000076293945</v>
       </c>
       <c r="G299" t="n">
-        <v>1034.181884765625</v>
+        <v>1034.181762695312</v>
       </c>
       <c r="H299" t="n">
         <v>144.3000030517578</v>
@@ -9141,7 +9141,7 @@
         <v>146.6999969482422</v>
       </c>
       <c r="I300" t="n">
-        <v>778.630126953125</v>
+        <v>778.6301879882812</v>
       </c>
       <c r="J300" t="n">
         <v>10.75</v>
@@ -9164,13 +9164,13 @@
         <v>54.70000076293945</v>
       </c>
       <c r="G301" t="n">
-        <v>1011.439331054688</v>
+        <v>1011.439270019531</v>
       </c>
       <c r="H301" t="n">
         <v>141.25</v>
       </c>
       <c r="I301" t="n">
-        <v>772.769775390625</v>
+        <v>772.7698974609375</v>
       </c>
       <c r="J301" t="n">
         <v>10.55000019073486</v>
@@ -9193,7 +9193,7 @@
         <v>52.54999923706055</v>
       </c>
       <c r="G302" t="n">
-        <v>1010.167053222656</v>
+        <v>1010.167114257812</v>
       </c>
       <c r="H302" t="n">
         <v>148.6499938964844</v>
@@ -9228,7 +9228,7 @@
         <v>148.0500030517578</v>
       </c>
       <c r="I303" t="n">
-        <v>771.5880126953125</v>
+        <v>771.5880737304688</v>
       </c>
       <c r="J303" t="n">
         <v>10.30000019073486</v>
@@ -9280,13 +9280,13 @@
         <v>58.09999847412109</v>
       </c>
       <c r="G305" t="n">
-        <v>1034.477172851562</v>
+        <v>1034.477294921875</v>
       </c>
       <c r="H305" t="n">
         <v>148.8999938964844</v>
       </c>
       <c r="I305" t="n">
-        <v>778.1376953125</v>
+        <v>778.1377563476562</v>
       </c>
       <c r="J305" t="n">
         <v>10.30000019073486</v>
@@ -9309,7 +9309,7 @@
         <v>56.20000076293945</v>
       </c>
       <c r="G306" t="n">
-        <v>1021.390686035156</v>
+        <v>1021.390747070312</v>
       </c>
       <c r="H306" t="n">
         <v>148.1999969482422</v>
@@ -9338,7 +9338,7 @@
         <v>52.25</v>
       </c>
       <c r="G307" t="n">
-        <v>1001.169982910156</v>
+        <v>1001.170043945312</v>
       </c>
       <c r="H307" t="n">
         <v>143.1000061035156</v>
@@ -9396,13 +9396,13 @@
         <v>52.34999847412109</v>
       </c>
       <c r="G309" t="n">
-        <v>1021.481567382812</v>
+        <v>1021.481506347656</v>
       </c>
       <c r="H309" t="n">
         <v>137.5</v>
       </c>
       <c r="I309" t="n">
-        <v>721.9971313476562</v>
+        <v>721.9970703125</v>
       </c>
       <c r="J309" t="n">
         <v>9.149999618530273</v>
@@ -9460,7 +9460,7 @@
         <v>144.25</v>
       </c>
       <c r="I311" t="n">
-        <v>770.0613403320312</v>
+        <v>770.061279296875</v>
       </c>
       <c r="J311" t="n">
         <v>9.949999809265137</v>
@@ -9483,13 +9483,13 @@
         <v>56</v>
       </c>
       <c r="G312" t="n">
-        <v>1059.40087890625</v>
+        <v>1059.400756835938</v>
       </c>
       <c r="H312" t="n">
         <v>146.3999938964844</v>
       </c>
       <c r="I312" t="n">
-        <v>785.7708740234375</v>
+        <v>785.7708129882812</v>
       </c>
       <c r="J312" t="n">
         <v>10.39999961853027</v>
@@ -9512,13 +9512,13 @@
         <v>56.65000152587891</v>
       </c>
       <c r="G313" t="n">
-        <v>1056.856201171875</v>
+        <v>1056.856323242188</v>
       </c>
       <c r="H313" t="n">
         <v>151.3999938964844</v>
       </c>
       <c r="I313" t="n">
-        <v>782.5697631835938</v>
+        <v>782.5698852539062</v>
       </c>
       <c r="J313" t="n">
         <v>10.80000019073486</v>
@@ -9547,7 +9547,7 @@
         <v>151.3999938964844</v>
       </c>
       <c r="I314" t="n">
-        <v>792.2220458984375</v>
+        <v>792.2221069335938</v>
       </c>
       <c r="J314" t="n">
         <v>11.14999961853027</v>
@@ -9634,7 +9634,7 @@
         <v>155.6999969482422</v>
       </c>
       <c r="I317" t="n">
-        <v>799.6089477539062</v>
+        <v>799.6090087890625</v>
       </c>
       <c r="J317" t="n">
         <v>12.14999961853027</v>
@@ -9692,7 +9692,7 @@
         <v>162</v>
       </c>
       <c r="I319" t="n">
-        <v>843.8320922851562</v>
+        <v>843.83203125</v>
       </c>
       <c r="J319" t="n">
         <v>12.69999980926514</v>
@@ -9721,7 +9721,7 @@
         <v>159.6499938964844</v>
       </c>
       <c r="I320" t="n">
-        <v>820.9818115234375</v>
+        <v>820.9817504882812</v>
       </c>
       <c r="J320" t="n">
         <v>12.39999961853027</v>
@@ -9802,7 +9802,7 @@
         <v>54.20000076293945</v>
       </c>
       <c r="G323" t="n">
-        <v>1067.37548828125</v>
+        <v>1067.375610351562</v>
       </c>
       <c r="H323" t="n">
         <v>159.3500061035156</v>
@@ -9831,7 +9831,7 @@
         <v>54.25</v>
       </c>
       <c r="G324" t="n">
-        <v>1071.465087890625</v>
+        <v>1071.464965820312</v>
       </c>
       <c r="H324" t="n">
         <v>157.8500061035156</v>
@@ -9860,7 +9860,7 @@
         <v>54.95000076293945</v>
       </c>
       <c r="G325" t="n">
-        <v>1079.666748046875</v>
+        <v>1079.666870117188</v>
       </c>
       <c r="H325" t="n">
         <v>157.8999938964844</v>
@@ -9895,7 +9895,7 @@
         <v>153.6000061035156</v>
       </c>
       <c r="I326" t="n">
-        <v>816.992919921875</v>
+        <v>816.9928588867188</v>
       </c>
       <c r="J326" t="n">
         <v>11.89999961853027</v>
@@ -9924,7 +9924,7 @@
         <v>160.6999969482422</v>
       </c>
       <c r="I327" t="n">
-        <v>822.4099731445312</v>
+        <v>822.409912109375</v>
       </c>
       <c r="J327" t="n">
         <v>12.5</v>
@@ -10005,7 +10005,7 @@
         <v>58.34999847412109</v>
       </c>
       <c r="G330" t="n">
-        <v>1099.682861328125</v>
+        <v>1099.682983398438</v>
       </c>
       <c r="H330" t="n">
         <v>153.75</v>
@@ -10034,13 +10034,13 @@
         <v>59.54999923706055</v>
       </c>
       <c r="G331" t="n">
-        <v>1112.360595703125</v>
+        <v>1112.360717773438</v>
       </c>
       <c r="H331" t="n">
         <v>154.5500030517578</v>
       </c>
       <c r="I331" t="n">
-        <v>882.3917846679688</v>
+        <v>882.3917236328125</v>
       </c>
       <c r="J331" t="n">
         <v>12.19999980926514</v>
@@ -10063,13 +10063,13 @@
         <v>57.5</v>
       </c>
       <c r="G332" t="n">
-        <v>1109.5205078125</v>
+        <v>1109.520629882812</v>
       </c>
       <c r="H332" t="n">
         <v>153.6000061035156</v>
       </c>
       <c r="I332" t="n">
-        <v>868.258056640625</v>
+        <v>868.2579956054688</v>
       </c>
       <c r="J332" t="n">
         <v>12.39999961853027</v>
@@ -10092,13 +10092,13 @@
         <v>57.09999847412109</v>
       </c>
       <c r="G333" t="n">
-        <v>1123.220703125</v>
+        <v>1123.220581054688</v>
       </c>
       <c r="H333" t="n">
         <v>152.4499969482422</v>
       </c>
       <c r="I333" t="n">
-        <v>868.3565063476562</v>
+        <v>868.3565673828125</v>
       </c>
       <c r="J333" t="n">
         <v>12.14999961853027</v>
@@ -10127,7 +10127,7 @@
         <v>150.3000030517578</v>
       </c>
       <c r="I334" t="n">
-        <v>860.8712158203125</v>
+        <v>860.8711547851562</v>
       </c>
       <c r="J334" t="n">
         <v>12</v>
@@ -10208,13 +10208,13 @@
         <v>58.09999847412109</v>
       </c>
       <c r="G337" t="n">
-        <v>1128.877807617188</v>
+        <v>1128.8779296875</v>
       </c>
       <c r="H337" t="n">
         <v>146.6000061035156</v>
       </c>
       <c r="I337" t="n">
-        <v>866.1405639648438</v>
+        <v>866.1405029296875</v>
       </c>
       <c r="J337" t="n">
         <v>11.80000019073486</v>
@@ -10237,13 +10237,13 @@
         <v>60.59999847412109</v>
       </c>
       <c r="G338" t="n">
-        <v>1131.1044921875</v>
+        <v>1131.104248046875</v>
       </c>
       <c r="H338" t="n">
         <v>144.1499938964844</v>
       </c>
       <c r="I338" t="n">
-        <v>873.1334228515625</v>
+        <v>873.1334838867188</v>
       </c>
       <c r="J338" t="n">
         <v>11.60000038146973</v>
@@ -10266,13 +10266,13 @@
         <v>59.54999923706055</v>
       </c>
       <c r="G339" t="n">
-        <v>1114.99609375</v>
+        <v>1114.996215820312</v>
       </c>
       <c r="H339" t="n">
         <v>140.8999938964844</v>
       </c>
       <c r="I339" t="n">
-        <v>886.9716186523438</v>
+        <v>886.9715576171875</v>
       </c>
       <c r="J339" t="n">
         <v>11.69999980926514</v>
@@ -10295,7 +10295,7 @@
         <v>59.25</v>
       </c>
       <c r="G340" t="n">
-        <v>1108.407348632812</v>
+        <v>1108.407470703125</v>
       </c>
       <c r="H340" t="n">
         <v>137.1000061035156</v>
@@ -10330,7 +10330,7 @@
         <v>135.8999938964844</v>
       </c>
       <c r="I341" t="n">
-        <v>875.1525268554688</v>
+        <v>875.1524658203125</v>
       </c>
       <c r="J341" t="n">
         <v>11.39999961853027</v>
@@ -10353,13 +10353,13 @@
         <v>58.5</v>
       </c>
       <c r="G342" t="n">
-        <v>1109.611572265625</v>
+        <v>1109.611450195312</v>
       </c>
       <c r="H342" t="n">
         <v>137.4499969482422</v>
       </c>
       <c r="I342" t="n">
-        <v>884.16455078125</v>
+        <v>884.1646118164062</v>
       </c>
       <c r="J342" t="n">
         <v>11.44999980926514</v>
@@ -10382,7 +10382,7 @@
         <v>58.29999923706055</v>
       </c>
       <c r="G343" t="n">
-        <v>1115.541259765625</v>
+        <v>1115.54150390625</v>
       </c>
       <c r="H343" t="n">
         <v>134.6499938964844</v>
@@ -10411,7 +10411,7 @@
         <v>59.79999923706055</v>
       </c>
       <c r="G344" t="n">
-        <v>1115.336791992188</v>
+        <v>1115.3369140625</v>
       </c>
       <c r="H344" t="n">
         <v>139.6499938964844</v>
@@ -10440,7 +10440,7 @@
         <v>60.65000152587891</v>
       </c>
       <c r="G345" t="n">
-        <v>1108.8388671875</v>
+        <v>1108.838989257812</v>
       </c>
       <c r="H345" t="n">
         <v>138.6000061035156</v>
@@ -10469,13 +10469,13 @@
         <v>60.34999847412109</v>
       </c>
       <c r="G346" t="n">
-        <v>1108.70263671875</v>
+        <v>1108.702758789062</v>
       </c>
       <c r="H346" t="n">
         <v>138.8999938964844</v>
       </c>
       <c r="I346" t="n">
-        <v>880.47119140625</v>
+        <v>880.4711303710938</v>
       </c>
       <c r="J346" t="n">
         <v>12.85000038146973</v>
@@ -10498,13 +10498,13 @@
         <v>60.20000076293945</v>
       </c>
       <c r="G347" t="n">
-        <v>1138.942749023438</v>
+        <v>1138.94287109375</v>
       </c>
       <c r="H347" t="n">
         <v>138</v>
       </c>
       <c r="I347" t="n">
-        <v>887.0208740234375</v>
+        <v>887.0208129882812</v>
       </c>
       <c r="J347" t="n">
         <v>13.05000019073486</v>
@@ -10533,7 +10533,7 @@
         <v>139.6499938964844</v>
       </c>
       <c r="I348" t="n">
-        <v>897.3624267578125</v>
+        <v>897.362548828125</v>
       </c>
       <c r="J348" t="n">
         <v>13.30000019073486</v>
@@ -10556,13 +10556,13 @@
         <v>61.25</v>
       </c>
       <c r="G349" t="n">
-        <v>1145.054321289062</v>
+        <v>1145.054443359375</v>
       </c>
       <c r="H349" t="n">
         <v>138.6000061035156</v>
       </c>
       <c r="I349" t="n">
-        <v>902.0902099609375</v>
+        <v>902.090087890625</v>
       </c>
       <c r="J349" t="n">
         <v>12.94999980926514</v>
@@ -10591,7 +10591,7 @@
         <v>134.6999969482422</v>
       </c>
       <c r="I350" t="n">
-        <v>894.8016967773438</v>
+        <v>894.8017578125</v>
       </c>
       <c r="J350" t="n">
         <v>12.94999980926514</v>
@@ -10614,13 +10614,13 @@
         <v>65.15000152587891</v>
       </c>
       <c r="G351" t="n">
-        <v>1119.2900390625</v>
+        <v>1119.289916992188</v>
       </c>
       <c r="H351" t="n">
         <v>133.9499969482422</v>
       </c>
       <c r="I351" t="n">
-        <v>904.7001953125</v>
+        <v>904.7001342773438</v>
       </c>
       <c r="J351" t="n">
         <v>12.94999980926514</v>
@@ -10788,7 +10788,7 @@
         <v>63.75</v>
       </c>
       <c r="G357" t="n">
-        <v>1127.787231445312</v>
+        <v>1127.787353515625</v>
       </c>
       <c r="H357" t="n">
         <v>137.1999969482422</v>
@@ -11020,7 +11020,7 @@
         <v>65.75</v>
       </c>
       <c r="G365" t="n">
-        <v>1165.206909179688</v>
+        <v>1165.206787109375</v>
       </c>
       <c r="H365" t="n">
         <v>147.75</v>
@@ -11194,7 +11194,7 @@
         <v>62.79999923706055</v>
       </c>
       <c r="G371" t="n">
-        <v>1158.822631835938</v>
+        <v>1158.822509765625</v>
       </c>
       <c r="H371" t="n">
         <v>138.25</v>
@@ -11368,7 +11368,7 @@
         <v>63.29999923706055</v>
       </c>
       <c r="G377" t="n">
-        <v>1242.794799804688</v>
+        <v>1242.794921875</v>
       </c>
       <c r="H377" t="n">
         <v>135.6499938964844</v>
@@ -11397,7 +11397,7 @@
         <v>63.04999923706055</v>
       </c>
       <c r="G378" t="n">
-        <v>1256.267578125</v>
+        <v>1256.267700195312</v>
       </c>
       <c r="H378" t="n">
         <v>136.8000030517578</v>
@@ -11426,7 +11426,7 @@
         <v>63.45000076293945</v>
       </c>
       <c r="G379" t="n">
-        <v>1257.653686523438</v>
+        <v>1257.653564453125</v>
       </c>
       <c r="H379" t="n">
         <v>137.5500030517578</v>
@@ -11484,7 +11484,7 @@
         <v>63.5</v>
       </c>
       <c r="G381" t="n">
-        <v>1245.362182617188</v>
+        <v>1245.3623046875</v>
       </c>
       <c r="H381" t="n">
         <v>136.1499938964844</v>
@@ -11542,7 +11542,7 @@
         <v>64.34999847412109</v>
       </c>
       <c r="G383" t="n">
-        <v>1281.600341796875</v>
+        <v>1281.600219726562</v>
       </c>
       <c r="H383" t="n">
         <v>141.6999969482422</v>
@@ -11600,7 +11600,7 @@
         <v>59.70000076293945</v>
       </c>
       <c r="G385" t="n">
-        <v>1289.760620117188</v>
+        <v>1289.760498046875</v>
       </c>
       <c r="H385" t="n">
         <v>162.3999938964844</v>
@@ -11658,7 +11658,7 @@
         <v>58.25</v>
       </c>
       <c r="G387" t="n">
-        <v>1224.554931640625</v>
+        <v>1224.554809570312</v>
       </c>
       <c r="H387" t="n">
         <v>162.6000061035156</v>
@@ -11716,7 +11716,7 @@
         <v>58.29999923706055</v>
       </c>
       <c r="G389" t="n">
-        <v>1243.65625</v>
+        <v>1243.656127929688</v>
       </c>
       <c r="H389" t="n">
         <v>170.9499969482422</v>
@@ -11832,7 +11832,7 @@
         <v>58.04999923706055</v>
       </c>
       <c r="G393" t="n">
-        <v>1237.25634765625</v>
+        <v>1237.256469726562</v>
       </c>
       <c r="H393" t="n">
         <v>183.8000030517578</v>
@@ -11890,7 +11890,7 @@
         <v>58.54999923706055</v>
       </c>
       <c r="G395" t="n">
-        <v>1218.893432617188</v>
+        <v>1218.8935546875</v>
       </c>
       <c r="H395" t="n">
         <v>187.0500030517578</v>
@@ -11919,7 +11919,7 @@
         <v>58.15000152587891</v>
       </c>
       <c r="G396" t="n">
-        <v>1235.45947265625</v>
+        <v>1235.459594726562</v>
       </c>
       <c r="H396" t="n">
         <v>199.1499938964844</v>
@@ -11948,7 +11948,7 @@
         <v>59.04999923706055</v>
       </c>
       <c r="G397" t="n">
-        <v>1242.499633789062</v>
+        <v>1242.49951171875</v>
       </c>
       <c r="H397" t="n">
         <v>210.0500030517578</v>
@@ -11977,7 +11977,7 @@
         <v>60.20000076293945</v>
       </c>
       <c r="G398" t="n">
-        <v>1235.016235351562</v>
+        <v>1235.016357421875</v>
       </c>
       <c r="H398" t="n">
         <v>194.6999969482422</v>
@@ -12006,7 +12006,7 @@
         <v>60.04999923706055</v>
       </c>
       <c r="G399" t="n">
-        <v>1243.163940429688</v>
+        <v>1243.1640625</v>
       </c>
       <c r="H399" t="n">
         <v>191.4499969482422</v>
@@ -12035,7 +12035,7 @@
         <v>62</v>
       </c>
       <c r="G400" t="n">
-        <v>1248.702392578125</v>
+        <v>1248.702270507812</v>
       </c>
       <c r="H400" t="n">
         <v>175.8500061035156</v>
@@ -12151,7 +12151,7 @@
         <v>60.95000076293945</v>
       </c>
       <c r="G404" t="n">
-        <v>1249.465576171875</v>
+        <v>1249.465454101562</v>
       </c>
       <c r="H404" t="n">
         <v>158.0500030517578</v>
@@ -12372,7 +12372,7 @@
         <v>68.65000152587891</v>
       </c>
       <c r="G411" t="n">
-        <v>1207.315551757812</v>
+        <v>1207.315673828125</v>
       </c>
       <c r="H411" t="n">
         <v>177.8999938964844</v>
@@ -12436,7 +12436,7 @@
         <v>68.75</v>
       </c>
       <c r="G413" t="n">
-        <v>1194.618896484375</v>
+        <v>1194.618774414062</v>
       </c>
       <c r="H413" t="n">
         <v>188.0500030517578</v>
@@ -12468,7 +12468,7 @@
         <v>68.34999847412109</v>
       </c>
       <c r="G414" t="n">
-        <v>1189.15966796875</v>
+        <v>1189.159545898438</v>
       </c>
       <c r="H414" t="n">
         <v>186.75</v>
@@ -12564,7 +12564,7 @@
         <v>74.44999694824219</v>
       </c>
       <c r="G417" t="n">
-        <v>1197.36083984375</v>
+        <v>1197.360717773438</v>
       </c>
       <c r="H417" t="n">
         <v>190.8000030517578</v>
@@ -12724,7 +12724,7 @@
         <v>65.84999847412109</v>
       </c>
       <c r="G422" t="n">
-        <v>1204.894897460938</v>
+        <v>1204.89501953125</v>
       </c>
       <c r="H422" t="n">
         <v>173.6999969482422</v>
@@ -12820,7 +12820,7 @@
         <v>66.15000152587891</v>
       </c>
       <c r="G425" t="n">
-        <v>1214.281616210938</v>
+        <v>1214.28173828125</v>
       </c>
       <c r="H425" t="n">
         <v>183.75</v>
@@ -12884,7 +12884,7 @@
         <v>66.65000152587891</v>
       </c>
       <c r="G427" t="n">
-        <v>1176.882690429688</v>
+        <v>1176.882568359375</v>
       </c>
       <c r="H427" t="n">
         <v>173.6999969482422</v>
@@ -12916,7 +12916,7 @@
         <v>67.34999847412109</v>
       </c>
       <c r="G428" t="n">
-        <v>1168.31103515625</v>
+        <v>1168.311157226562</v>
       </c>
       <c r="H428" t="n">
         <v>175.1499938964844</v>
@@ -12948,7 +12948,7 @@
         <v>68.05000305175781</v>
       </c>
       <c r="G429" t="n">
-        <v>1163.444702148438</v>
+        <v>1163.44482421875</v>
       </c>
       <c r="H429" t="n">
         <v>175.75</v>
@@ -13012,7 +13012,7 @@
         <v>64.5</v>
       </c>
       <c r="G431" t="n">
-        <v>1157.2939453125</v>
+        <v>1157.293823242188</v>
       </c>
       <c r="H431" t="n">
         <v>171</v>
@@ -13044,7 +13044,7 @@
         <v>63.95000076293945</v>
       </c>
       <c r="G432" t="n">
-        <v>1170.336669921875</v>
+        <v>1170.336547851562</v>
       </c>
       <c r="H432" t="n">
         <v>172.6499938964844</v>
@@ -13076,7 +13076,7 @@
         <v>63.20000076293945</v>
       </c>
       <c r="G433" t="n">
-        <v>1153.14404296875</v>
+        <v>1153.143920898438</v>
       </c>
       <c r="H433" t="n">
         <v>170.8999938964844</v>
@@ -13140,7 +13140,7 @@
         <v>68.55000305175781</v>
       </c>
       <c r="G435" t="n">
-        <v>1145.263916015625</v>
+        <v>1145.263793945312</v>
       </c>
       <c r="H435" t="n">
         <v>174.3500061035156</v>
@@ -13204,7 +13204,7 @@
         <v>72.84999847412109</v>
       </c>
       <c r="G437" t="n">
-        <v>1143.26318359375</v>
+        <v>1143.263061523438</v>
       </c>
       <c r="H437" t="n">
         <v>172.1999969482422</v>
@@ -13396,7 +13396,7 @@
         <v>78.75</v>
       </c>
       <c r="G443" t="n">
-        <v>1160.653442382812</v>
+        <v>1160.653564453125</v>
       </c>
       <c r="H443" t="n">
         <v>167.9499969482422</v>
@@ -13588,7 +13588,7 @@
         <v>70</v>
       </c>
       <c r="G449" t="n">
-        <v>1118.116333007812</v>
+        <v>1118.116455078125</v>
       </c>
       <c r="H449" t="n">
         <v>169.75</v>
@@ -13620,7 +13620,7 @@
         <v>68.59999847412109</v>
       </c>
       <c r="G450" t="n">
-        <v>1115.522705078125</v>
+        <v>1115.522583007812</v>
       </c>
       <c r="H450" t="n">
         <v>162.3000030517578</v>
@@ -13652,7 +13652,7 @@
         <v>68.19999694824219</v>
       </c>
       <c r="G451" t="n">
-        <v>1099.98486328125</v>
+        <v>1099.984985351562</v>
       </c>
       <c r="H451" t="n">
         <v>159.0500030517578</v>
@@ -13716,7 +13716,7 @@
         <v>69.19999694824219</v>
       </c>
       <c r="G453" t="n">
-        <v>1142.47265625</v>
+        <v>1142.472534179688</v>
       </c>
       <c r="H453" t="n">
         <v>168</v>
@@ -13940,7 +13940,7 @@
         <v>72</v>
       </c>
       <c r="G460" t="n">
-        <v>1154.033203125</v>
+        <v>1154.033081054688</v>
       </c>
       <c r="H460" t="n">
         <v>179.1000061035156</v>
@@ -14004,7 +14004,7 @@
         <v>77.25</v>
       </c>
       <c r="G462" t="n">
-        <v>1143.658325195312</v>
+        <v>1143.658203125</v>
       </c>
       <c r="H462" t="n">
         <v>177.3000030517578</v>
@@ -14036,7 +14036,7 @@
         <v>76</v>
       </c>
       <c r="G463" t="n">
-        <v>1143.51025390625</v>
+        <v>1143.510131835938</v>
       </c>
       <c r="H463" t="n">
         <v>181.1499938964844</v>
@@ -14164,7 +14164,7 @@
         <v>82.94999694824219</v>
       </c>
       <c r="G467" t="n">
-        <v>1160.678100585938</v>
+        <v>1160.67822265625</v>
       </c>
       <c r="H467" t="n">
         <v>182.75</v>
@@ -14228,7 +14228,7 @@
         <v>82.09999847412109</v>
       </c>
       <c r="G469" t="n">
-        <v>1179.87158203125</v>
+        <v>1179.871704101562</v>
       </c>
       <c r="H469" t="n">
         <v>174.8500061035156</v>
@@ -14452,7 +14452,7 @@
         <v>88.69999694824219</v>
       </c>
       <c r="G476" t="n">
-        <v>1195.681030273438</v>
+        <v>1195.680908203125</v>
       </c>
       <c r="H476" t="n">
         <v>192.6999969482422</v>
@@ -14484,7 +14484,7 @@
         <v>90.80000305175781</v>
       </c>
       <c r="G477" t="n">
-        <v>1204.351440429688</v>
+        <v>1204.351318359375</v>
       </c>
       <c r="H477" t="n">
         <v>202.3000030517578</v>
@@ -14548,7 +14548,7 @@
         <v>90.65000152587891</v>
       </c>
       <c r="G479" t="n">
-        <v>1213.886352539062</v>
+        <v>1213.886474609375</v>
       </c>
       <c r="H479" t="n">
         <v>220.5</v>
@@ -14580,7 +14580,7 @@
         <v>87.55000305175781</v>
       </c>
       <c r="G480" t="n">
-        <v>1213.244140625</v>
+        <v>1213.244262695312</v>
       </c>
       <c r="H480" t="n">
         <v>214.75</v>
@@ -14644,7 +14644,7 @@
         <v>86.65000152587891</v>
       </c>
       <c r="G482" t="n">
-        <v>1197.5830078125</v>
+        <v>1197.583129882812</v>
       </c>
       <c r="H482" t="n">
         <v>211.6499938964844</v>
@@ -14740,7 +14740,7 @@
         <v>85.90000152587891</v>
       </c>
       <c r="G485" t="n">
-        <v>1232.931762695312</v>
+        <v>1232.931884765625</v>
       </c>
       <c r="H485" t="n">
         <v>209.75</v>
@@ -14900,7 +14900,7 @@
         <v>86.09999847412109</v>
       </c>
       <c r="G490" t="n">
-        <v>1267.243041992188</v>
+        <v>1267.242919921875</v>
       </c>
       <c r="H490" t="n">
         <v>193.0500030517578</v>
@@ -14964,7 +14964,7 @@
         <v>88.90000152587891</v>
       </c>
       <c r="G492" t="n">
-        <v>1278.01318359375</v>
+        <v>1278.013061523438</v>
       </c>
       <c r="H492" t="n">
         <v>194.6999969482422</v>
@@ -14996,7 +14996,7 @@
         <v>88.05000305175781</v>
       </c>
       <c r="G493" t="n">
-        <v>1287.251708984375</v>
+        <v>1287.251586914062</v>
       </c>
       <c r="H493" t="n">
         <v>190.8000030517578</v>
@@ -15028,7 +15028,7 @@
         <v>87.34999847412109</v>
       </c>
       <c r="G494" t="n">
-        <v>1277.074340820312</v>
+        <v>1277.074462890625</v>
       </c>
       <c r="H494" t="n">
         <v>209.8000030517578</v>
@@ -15060,7 +15060,7 @@
         <v>88.5</v>
       </c>
       <c r="G495" t="n">
-        <v>1279.69287109375</v>
+        <v>1279.692993164062</v>
       </c>
       <c r="H495" t="n">
         <v>211.8000030517578</v>
@@ -15220,7 +15220,7 @@
         <v>100.5500030517578</v>
       </c>
       <c r="G500" t="n">
-        <v>1278.260131835938</v>
+        <v>1278.26025390625</v>
       </c>
       <c r="H500" t="n">
         <v>241</v>
@@ -15252,7 +15252,7 @@
         <v>99.5</v>
       </c>
       <c r="G501" t="n">
-        <v>1274.8759765625</v>
+        <v>1274.875854492188</v>
       </c>
       <c r="H501" t="n">
         <v>236.8500061035156</v>
@@ -15380,7 +15380,7 @@
         <v>122.8499984741211</v>
       </c>
       <c r="G505" t="n">
-        <v>1377.513305664062</v>
+        <v>1377.51318359375</v>
       </c>
       <c r="H505" t="n">
         <v>232.6499938964844</v>
@@ -15444,7 +15444,7 @@
         <v>129.6999969482422</v>
       </c>
       <c r="G507" t="n">
-        <v>1345.350952148438</v>
+        <v>1345.35107421875</v>
       </c>
       <c r="H507" t="n">
         <v>217.3000030517578</v>
@@ -15700,7 +15700,7 @@
         <v>117</v>
       </c>
       <c r="G515" t="n">
-        <v>1409.6259765625</v>
+        <v>1409.625854492188</v>
       </c>
       <c r="H515" t="n">
         <v>231.0500030517578</v>
@@ -15764,7 +15764,7 @@
         <v>113.1500015258789</v>
       </c>
       <c r="G517" t="n">
-        <v>1440.33056640625</v>
+        <v>1440.330688476562</v>
       </c>
       <c r="H517" t="n">
         <v>221.9499969482422</v>
@@ -15828,7 +15828,7 @@
         <v>113.6999969482422</v>
       </c>
       <c r="G519" t="n">
-        <v>1410.786865234375</v>
+        <v>1410.786987304688</v>
       </c>
       <c r="H519" t="n">
         <v>214.9499969482422</v>
@@ -15988,7 +15988,7 @@
         <v>105.4000015258789</v>
       </c>
       <c r="G524" t="n">
-        <v>1447.642456054688</v>
+        <v>1447.642333984375</v>
       </c>
       <c r="H524" t="n">
         <v>210.1499938964844</v>
@@ -16052,7 +16052,7 @@
         <v>112.6500015258789</v>
       </c>
       <c r="G526" t="n">
-        <v>1453.076904296875</v>
+        <v>1453.077026367188</v>
       </c>
       <c r="H526" t="n">
         <v>234.3500061035156</v>
@@ -16148,7 +16148,7 @@
         <v>119</v>
       </c>
       <c r="G529" t="n">
-        <v>1453.4970703125</v>
+        <v>1453.496948242188</v>
       </c>
       <c r="H529" t="n">
         <v>241.1999969482422</v>
@@ -16212,7 +16212,7 @@
         <v>116.3499984741211</v>
       </c>
       <c r="G531" t="n">
-        <v>1464.093994140625</v>
+        <v>1464.094116210938</v>
       </c>
       <c r="H531" t="n">
         <v>229.4499969482422</v>
@@ -16468,7 +16468,7 @@
         <v>95.25</v>
       </c>
       <c r="G539" t="n">
-        <v>1482.32421875</v>
+        <v>1482.324340820312</v>
       </c>
       <c r="H539" t="n">
         <v>226.6999969482422</v>
@@ -16500,7 +16500,7 @@
         <v>90.5</v>
       </c>
       <c r="G540" t="n">
-        <v>1485.090942382812</v>
+        <v>1485.0908203125</v>
       </c>
       <c r="H540" t="n">
         <v>218.3500061035156</v>
@@ -16564,7 +16564,7 @@
         <v>92.05000305175781</v>
       </c>
       <c r="G542" t="n">
-        <v>1449.12451171875</v>
+        <v>1449.124633789062</v>
       </c>
       <c r="H542" t="n">
         <v>223.6499938964844</v>
@@ -16596,7 +16596,7 @@
         <v>87.5</v>
       </c>
       <c r="G543" t="n">
-        <v>1457.844604492188</v>
+        <v>1457.844482421875</v>
       </c>
       <c r="H543" t="n">
         <v>217.5500030517578</v>
@@ -16660,7 +16660,7 @@
         <v>84.65000152587891</v>
       </c>
       <c r="G545" t="n">
-        <v>1414.418212890625</v>
+        <v>1414.418090820312</v>
       </c>
       <c r="H545" t="n">
         <v>214.25</v>
@@ -16724,7 +16724,7 @@
         <v>92.69999694824219</v>
       </c>
       <c r="G547" t="n">
-        <v>1422.32275390625</v>
+        <v>1422.322875976562</v>
       </c>
       <c r="H547" t="n">
         <v>255.9499969482422</v>
@@ -16788,7 +16788,7 @@
         <v>86</v>
       </c>
       <c r="G549" t="n">
-        <v>1426.546752929688</v>
+        <v>1426.546875</v>
       </c>
       <c r="H549" t="n">
         <v>249.3000030517578</v>
@@ -16916,7 +16916,7 @@
         <v>87.5</v>
       </c>
       <c r="G553" t="n">
-        <v>1475.061889648438</v>
+        <v>1475.061767578125</v>
       </c>
       <c r="H553" t="n">
         <v>266.9500122070312</v>
@@ -16980,7 +16980,7 @@
         <v>90.40000152587891</v>
       </c>
       <c r="G555" t="n">
-        <v>1467.083129882812</v>
+        <v>1467.0830078125</v>
       </c>
       <c r="H555" t="n">
         <v>268.6499938964844</v>
@@ -17076,7 +17076,7 @@
         <v>91.94999694824219</v>
       </c>
       <c r="G558" t="n">
-        <v>1445.493530273438</v>
+        <v>1445.493408203125</v>
       </c>
       <c r="H558" t="n">
         <v>295</v>
@@ -17236,7 +17236,7 @@
         <v>89.25</v>
       </c>
       <c r="G563" t="n">
-        <v>1449.668090820312</v>
+        <v>1449.668212890625</v>
       </c>
       <c r="H563" t="n">
         <v>197.75</v>
@@ -17300,7 +17300,7 @@
         <v>85.90000152587891</v>
       </c>
       <c r="G565" t="n">
-        <v>1448.284790039062</v>
+        <v>1448.28466796875</v>
       </c>
       <c r="H565" t="n">
         <v>194.1999969482422</v>
@@ -17332,7 +17332,7 @@
         <v>89.5</v>
       </c>
       <c r="G566" t="n">
-        <v>1446.876586914062</v>
+        <v>1446.876708984375</v>
       </c>
       <c r="H566" t="n">
         <v>194.6999969482422</v>
@@ -17524,7 +17524,7 @@
         <v>90.59999847412109</v>
       </c>
       <c r="G572" t="n">
-        <v>1435.2421875</v>
+        <v>1435.242065429688</v>
       </c>
       <c r="H572" t="n">
         <v>190.8999938964844</v>
@@ -17588,7 +17588,7 @@
         <v>88.90000152587891</v>
       </c>
       <c r="G574" t="n">
-        <v>1449.519775390625</v>
+        <v>1449.519897460938</v>
       </c>
       <c r="H574" t="n">
         <v>177.8999938964844</v>
@@ -17620,7 +17620,7 @@
         <v>86.80000305175781</v>
       </c>
       <c r="G575" t="n">
-        <v>1449.075317382812</v>
+        <v>1449.0751953125</v>
       </c>
       <c r="H575" t="n">
         <v>175.4499969482422</v>
@@ -17748,7 +17748,7 @@
         <v>80.59999847412109</v>
       </c>
       <c r="G579" t="n">
-        <v>1401.647338867188</v>
+        <v>1401.647216796875</v>
       </c>
       <c r="H579" t="n">
         <v>166.8000030517578</v>
@@ -17780,7 +17780,7 @@
         <v>77.55000305175781</v>
       </c>
       <c r="G580" t="n">
-        <v>1377.513305664062</v>
+        <v>1377.51318359375</v>
       </c>
       <c r="H580" t="n">
         <v>161.1999969482422</v>
@@ -17876,7 +17876,7 @@
         <v>80.25</v>
       </c>
       <c r="G583" t="n">
-        <v>1403.15380859375</v>
+        <v>1403.153930664062</v>
       </c>
       <c r="H583" t="n">
         <v>171.4499969482422</v>
@@ -18036,7 +18036,7 @@
         <v>82.25</v>
       </c>
       <c r="G588" t="n">
-        <v>1443.24560546875</v>
+        <v>1443.245483398438</v>
       </c>
       <c r="H588" t="n">
         <v>167.3500061035156</v>
@@ -18516,7 +18516,7 @@
         <v>83.27999877929688</v>
       </c>
       <c r="G603" t="n">
-        <v>1445.888671875</v>
+        <v>1445.888549804688</v>
       </c>
       <c r="H603" t="n">
         <v>190.3000030517578</v>
@@ -18676,7 +18676,7 @@
         <v>84.08999633789062</v>
       </c>
       <c r="G608" t="n">
-        <v>1456.14013671875</v>
+        <v>1456.140014648438</v>
       </c>
       <c r="H608" t="n">
         <v>213.25</v>
@@ -18836,7 +18836,7 @@
         <v>79.20999908447266</v>
       </c>
       <c r="G613" t="n">
-        <v>1512.312622070312</v>
+        <v>1512.312744140625</v>
       </c>
       <c r="H613" t="n">
         <v>197.6900024414062</v>
@@ -18932,7 +18932,7 @@
         <v>87.66999816894531</v>
       </c>
       <c r="G616" t="n">
-        <v>1546.525146484375</v>
+        <v>1546.525024414062</v>
       </c>
       <c r="H616" t="n">
         <v>187.5500030517578</v>
@@ -19060,7 +19060,7 @@
         <v>84.83999633789062</v>
       </c>
       <c r="G620" t="n">
-        <v>1581.824462890625</v>
+        <v>1581.824340820312</v>
       </c>
       <c r="H620" t="n">
         <v>199.9100036621094</v>
@@ -19444,7 +19444,7 @@
         <v>84.30999755859375</v>
       </c>
       <c r="G632" t="n">
-        <v>1474.6171875</v>
+        <v>1474.617309570312</v>
       </c>
       <c r="H632" t="n">
         <v>191.7799987792969</v>
@@ -19508,7 +19508,7 @@
         <v>93.55999755859375</v>
       </c>
       <c r="G634" t="n">
-        <v>1501.987182617188</v>
+        <v>1501.987060546875</v>
       </c>
       <c r="H634" t="n">
         <v>199.3699951171875</v>
@@ -19540,7 +19540,7 @@
         <v>90.97000122070312</v>
       </c>
       <c r="G635" t="n">
-        <v>1495.119873046875</v>
+        <v>1495.119995117188</v>
       </c>
       <c r="H635" t="n">
         <v>201.2599945068359</v>
@@ -19636,7 +19636,7 @@
         <v>93.27999877929688</v>
       </c>
       <c r="G638" t="n">
-        <v>1481.459594726562</v>
+        <v>1481.459716796875</v>
       </c>
       <c r="H638" t="n">
         <v>215.7200012207031</v>
@@ -19668,7 +19668,7 @@
         <v>87.73999786376953</v>
       </c>
       <c r="G639" t="n">
-        <v>1430.079223632812</v>
+        <v>1430.079345703125</v>
       </c>
       <c r="H639" t="n">
         <v>195.3300018310547</v>
@@ -19700,7 +19700,7 @@
         <v>93.98000335693359</v>
       </c>
       <c r="G640" t="n">
-        <v>1438.700439453125</v>
+        <v>1438.700317382812</v>
       </c>
       <c r="H640" t="n">
         <v>191.8899993896484</v>
@@ -19764,7 +19764,7 @@
         <v>96.30999755859375</v>
       </c>
       <c r="G642" t="n">
-        <v>1431.85791015625</v>
+        <v>1431.857788085938</v>
       </c>
       <c r="H642" t="n">
         <v>208.1999969482422</v>
@@ -19892,7 +19892,7 @@
         <v>93.84999847412109</v>
       </c>
       <c r="G646" t="n">
-        <v>1444.431274414062</v>
+        <v>1444.43115234375</v>
       </c>
       <c r="H646" t="n">
         <v>220.2799987792969</v>
@@ -36670,6 +36670,38 @@
       </c>
       <c r="J1170" t="n">
         <v>21.1299991607666</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1171" t="n">
+        <v>7.150000095367432</v>
+      </c>
+      <c r="C1171" t="n">
+        <v>26.68000030517578</v>
+      </c>
+      <c r="D1171" t="n">
+        <v>9.989999771118164</v>
+      </c>
+      <c r="E1171" t="n">
+        <v>230.2400054931641</v>
+      </c>
+      <c r="F1171" t="n">
+        <v>26.78000068664551</v>
+      </c>
+      <c r="G1171" t="n">
+        <v>1246.400024414062</v>
+      </c>
+      <c r="H1171" t="n">
+        <v>49</v>
+      </c>
+      <c r="I1171" t="n">
+        <v>704.2999877929688</v>
+      </c>
+      <c r="J1171" t="n">
+        <v>21.02000045776367</v>
       </c>
     </row>
   </sheetData>
@@ -36743,31 +36775,31 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-17.05882128547219</v>
+        <v>-15.88235181920669</v>
       </c>
       <c r="C2" t="n">
-        <v>-5.836574431597297</v>
+        <v>-5.624337201421003</v>
       </c>
       <c r="D2" t="n">
-        <v>-6.203014847650978</v>
+        <v>-6.109027737132589</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.748293525607772</v>
+        <v>-4.603273391087659</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8446549618173038</v>
+        <v>-1.652584881218333</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.962409991067928</v>
+        <v>-2.396239278460255</v>
       </c>
       <c r="H2" t="n">
-        <v>-15.82757670952265</v>
+        <v>-17.49452685035622</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.551928632224435</v>
+        <v>-6.399099426263866</v>
       </c>
       <c r="J2" t="n">
-        <v>-4.345862314124171</v>
+        <v>-4.84381931839356</v>
       </c>
     </row>
     <row r="3">
@@ -37654,7 +37686,7 @@
         <v>-10.12373435941966</v>
       </c>
       <c r="G30" t="n">
-        <v>-2.4948827172523</v>
+        <v>-2.494890928578097</v>
       </c>
       <c r="H30" t="n">
         <v>-6.49240482812462</v>
@@ -37686,7 +37718,7 @@
         <v>3.132256001421796</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.268640695312884</v>
+        <v>-1.268632380719259</v>
       </c>
       <c r="H31" t="n">
         <v>-34.34213475489638</v>
@@ -37750,7 +37782,7 @@
         <v>-8.54700854700855</v>
       </c>
       <c r="G33" t="n">
-        <v>2.395516458058666</v>
+        <v>2.395525325271675</v>
       </c>
       <c r="H33" t="n">
         <v>-4.392992435061648</v>
@@ -37782,7 +37814,7 @@
         <v>33.94390617495342</v>
       </c>
       <c r="G34" t="n">
-        <v>10.3793202560976</v>
+        <v>10.37930014680082</v>
       </c>
       <c r="H34" t="n">
         <v>10.12869384694794</v>
@@ -37814,7 +37846,7 @@
         <v>0.9243158800178009</v>
       </c>
       <c r="G35" t="n">
-        <v>8.72783114447817</v>
+        <v>8.727841537326796</v>
       </c>
       <c r="H35" t="n">
         <v>10.5665365226655</v>
@@ -37910,7 +37942,7 @@
         <v>-6.583760205501399</v>
       </c>
       <c r="G38" t="n">
-        <v>-2.57582022494055</v>
+        <v>-2.575810224095743</v>
       </c>
       <c r="H38" t="n">
         <v>-7.202140266796353</v>
@@ -37939,7 +37971,7 @@
         <v>17.33905317445681</v>
       </c>
       <c r="G39" t="n">
-        <v>-5.246536520989409</v>
+        <v>-5.246546247677264</v>
       </c>
       <c r="H39" t="n">
         <v>-1.111996841749918</v>
@@ -37968,7 +38000,7 @@
         <v>-7.245221803084723</v>
       </c>
       <c r="G40" t="n">
-        <v>8.299913357895106</v>
+        <v>8.299924766203226</v>
       </c>
       <c r="H40" t="n">
         <v>36.60036607849231</v>
@@ -37997,13 +38029,13 @@
         <v>2.446982085920046</v>
       </c>
       <c r="G41" t="n">
-        <v>3.253172538244864</v>
+        <v>3.253161661561332</v>
       </c>
       <c r="H41" t="n">
         <v>2.635488591081314</v>
       </c>
       <c r="I41" t="n">
-        <v>5.350320191814273</v>
+        <v>5.350313005783192</v>
       </c>
       <c r="J41" t="n">
         <v>8.494211565028188</v>
@@ -38032,7 +38064,7 @@
         <v>-14.50333586855534</v>
       </c>
       <c r="I42" t="n">
-        <v>7.789051998159846</v>
+        <v>7.789059350539329</v>
       </c>
       <c r="J42" t="n">
         <v>6.147541079717245</v>
@@ -38061,7 +38093,7 @@
         <v>9.220106101738512</v>
       </c>
       <c r="I43" t="n">
-        <v>7.802001872916686</v>
+        <v>7.802010417317251</v>
       </c>
       <c r="J43" t="n">
         <v>22.61306576011055</v>
@@ -38090,7 +38122,7 @@
         <v>10.36725582872331</v>
       </c>
       <c r="I44" t="n">
-        <v>-2.506398442968916</v>
+        <v>-2.506398636647234</v>
       </c>
       <c r="J44" t="n">
         <v>1.53060832255989</v>
@@ -38113,13 +38145,13 @@
         <v>-5.117786759101961</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.329731717430038</v>
+        <v>-1.329742978595971</v>
       </c>
       <c r="H45" t="n">
         <v>4.476417699780821</v>
       </c>
       <c r="I45" t="n">
-        <v>-7.821829485785403</v>
+        <v>-7.821843174509246</v>
       </c>
       <c r="J45" t="n">
         <v>-23.13725340600107</v>
@@ -38142,13 +38174,13 @@
         <v>-6.883508838267105</v>
       </c>
       <c r="G46" t="n">
-        <v>-7.590679750087537</v>
+        <v>-7.590678949528251</v>
       </c>
       <c r="H46" t="n">
         <v>-9.150325892060184</v>
       </c>
       <c r="I46" t="n">
-        <v>-7.873144999173832</v>
+        <v>-7.873132391548731</v>
       </c>
       <c r="J46" t="n">
         <v>-11.14982814589901</v>
@@ -38171,13 +38203,13 @@
         <v>-2.865546642449923</v>
       </c>
       <c r="G47" t="n">
-        <v>-6.742100064294965</v>
+        <v>-6.742090228748266</v>
       </c>
       <c r="H47" t="n">
         <v>-12.68230842551258</v>
       </c>
       <c r="I47" t="n">
-        <v>-10.50510455831967</v>
+        <v>-10.50512094276369</v>
       </c>
       <c r="J47" t="n">
         <v>-10.59189368473866</v>
@@ -38200,13 +38232,13 @@
         <v>6.079503403138031</v>
       </c>
       <c r="G48" t="n">
-        <v>7.128570156643566</v>
+        <v>7.128558868849533</v>
       </c>
       <c r="H48" t="n">
         <v>11.48815860769938</v>
       </c>
       <c r="I48" t="n">
-        <v>-3.906760722347635</v>
+        <v>-3.906738589925352</v>
       </c>
       <c r="J48" t="n">
         <v>-0.3105661069842447</v>
@@ -38229,13 +38261,13 @@
         <v>-0.696589719615015</v>
       </c>
       <c r="G49" t="n">
-        <v>7.227408100364263</v>
+        <v>7.227443628136077</v>
       </c>
       <c r="H49" t="n">
         <v>3.474762330681291</v>
       </c>
       <c r="I49" t="n">
-        <v>1.992291639014976</v>
+        <v>1.992280127469637</v>
       </c>
       <c r="J49" t="n">
         <v>-1.829263683162408</v>
@@ -38258,13 +38290,13 @@
         <v>-8.498583753085121</v>
       </c>
       <c r="G50" t="n">
-        <v>-9.863701201961927</v>
+        <v>-9.863721569537597</v>
       </c>
       <c r="H50" t="n">
         <v>-15.6172858344184</v>
       </c>
       <c r="I50" t="n">
-        <v>5.378686357567153</v>
+        <v>5.378692749161718</v>
       </c>
       <c r="J50" t="n">
         <v>-2.380950218425493</v>
@@ -38287,13 +38319,13 @@
         <v>8.782737772308536</v>
       </c>
       <c r="G51" t="n">
-        <v>5.463632633860382</v>
+        <v>5.463609979870743</v>
       </c>
       <c r="H51" t="n">
         <v>38.34329813061588</v>
       </c>
       <c r="I51" t="n">
-        <v>4.312852371434839</v>
+        <v>4.312852644306764</v>
       </c>
       <c r="J51" t="n">
         <v>35.48386898298783</v>
@@ -38316,13 +38348,13 @@
         <v>-5.942026774088538</v>
       </c>
       <c r="G52" t="n">
-        <v>-3.320959644468446</v>
+        <v>-3.320938877438184</v>
       </c>
       <c r="H52" t="n">
         <v>29.24944861623748</v>
       </c>
       <c r="I52" t="n">
-        <v>3.064815751886085</v>
+        <v>3.064809231029253</v>
       </c>
       <c r="J52" t="n">
         <v>7.826083639393677</v>
@@ -38374,13 +38406,13 @@
         <v>-12.41298993858072</v>
       </c>
       <c r="G54" t="n">
-        <v>-5.648240126514148</v>
+        <v>-5.648231012757576</v>
       </c>
       <c r="H54" t="n">
         <v>-12.62647164563844</v>
       </c>
       <c r="I54" t="n">
-        <v>-16.35937048671896</v>
+        <v>-16.35935170009368</v>
       </c>
       <c r="J54" t="n">
         <v>-11.57894469144052</v>
@@ -38403,13 +38435,13 @@
         <v>1.233112628945943</v>
       </c>
       <c r="G55" t="n">
-        <v>5.90190678499245</v>
+        <v>5.90190738872356</v>
       </c>
       <c r="H55" t="n">
         <v>10.01780916676824</v>
       </c>
       <c r="I55" t="n">
-        <v>42.15600259621435</v>
+        <v>42.15598201392618</v>
       </c>
       <c r="J55" t="n">
         <v>5.555555555555558</v>
@@ -38432,13 +38464,13 @@
         <v>10.65627667685571</v>
       </c>
       <c r="G56" t="n">
-        <v>11.66324714899951</v>
+        <v>11.6632229717543</v>
       </c>
       <c r="H56" t="n">
         <v>7.361381156751889</v>
       </c>
       <c r="I56" t="n">
-        <v>11.44042835922838</v>
+        <v>11.44042937693286</v>
       </c>
       <c r="J56" t="n">
         <v>3.4482743501002</v>
@@ -38461,13 +38493,13 @@
         <v>-6.15854030702172</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.133414869096705</v>
+        <v>-1.133403576054681</v>
       </c>
       <c r="H57" t="n">
         <v>3.513107684464867</v>
       </c>
       <c r="I57" t="n">
-        <v>-20.63636310365917</v>
+        <v>-20.63636456057385</v>
       </c>
       <c r="J57" t="n">
         <v>-11.82432417193846</v>
@@ -38561,31 +38593,31 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>-44.53186333929624</v>
+        <v>-43.74508203062247</v>
       </c>
       <c r="C2" t="n">
-        <v>-8.80438385681307</v>
+        <v>-8.598835844327157</v>
       </c>
       <c r="D2" t="n">
-        <v>-10.49327458585302</v>
+        <v>-10.40358643137795</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.542556087251491</v>
+        <v>-2.394177731111358</v>
       </c>
       <c r="F2" t="n">
-        <v>-14.52991494275721</v>
+        <v>-15.22633568442178</v>
       </c>
       <c r="G2" t="n">
-        <v>-5.216786361107539</v>
+        <v>-3.671071883742349</v>
       </c>
       <c r="H2" t="n">
-        <v>-32.08802980034638</v>
+        <v>-33.43295803055696</v>
       </c>
       <c r="I2" t="n">
-        <v>-13.73980207882673</v>
+        <v>-13.59872824646896</v>
       </c>
       <c r="J2" t="n">
-        <v>-14.93559166276724</v>
+        <v>-15.37842057712806</v>
       </c>
     </row>
     <row r="3">
@@ -38896,7 +38928,7 @@
         <v>-1.316544414387844</v>
       </c>
       <c r="G12" t="n">
-        <v>14.96161317663234</v>
+        <v>14.96160218792302</v>
       </c>
       <c r="H12" t="n">
         <v>29.14681042220371</v>
@@ -38928,7 +38960,7 @@
         <v>36.80501262584171</v>
       </c>
       <c r="G13" t="n">
-        <v>10.23239665903461</v>
+        <v>10.23240719569851</v>
       </c>
       <c r="H13" t="n">
         <v>21.06174227192534</v>
@@ -38957,7 +38989,7 @@
         <v>1.671973327733589</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.02533425681351398</v>
+        <v>-0.02532372548660344</v>
       </c>
       <c r="H14" t="n">
         <v>25.35262426890257</v>
@@ -38986,13 +39018,13 @@
         <v>15.76036725725447</v>
       </c>
       <c r="G15" t="n">
-        <v>9.403485464018434</v>
+        <v>9.403473939461261</v>
       </c>
       <c r="H15" t="n">
         <v>-4.159445407279028</v>
       </c>
       <c r="I15" t="n">
-        <v>22.41576135094123</v>
+        <v>22.41577105363026</v>
       </c>
       <c r="J15" t="n">
         <v>41.20603477451257</v>
@@ -39015,13 +39047,13 @@
         <v>-17.92738085880669</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.4857705142105</v>
+        <v>-8.485780165858081</v>
       </c>
       <c r="H16" t="n">
         <v>4.756719823472322</v>
       </c>
       <c r="I16" t="n">
-        <v>-17.2076053573798</v>
+        <v>-17.20760648656623</v>
       </c>
       <c r="J16" t="n">
         <v>-30.66202407831533</v>
@@ -39044,13 +39076,13 @@
         <v>2.321981478994783</v>
       </c>
       <c r="G17" t="n">
-        <v>7.126458598841245</v>
+        <v>7.126494103802106</v>
       </c>
       <c r="H17" t="n">
         <v>0.7315289117223678</v>
       </c>
       <c r="I17" t="n">
-        <v>-12.28811417979492</v>
+        <v>-12.28811993556758</v>
       </c>
       <c r="J17" t="n">
         <v>-12.49999563868442</v>
@@ -39073,7 +39105,7 @@
         <v>-6.376813805621606</v>
       </c>
       <c r="G18" t="n">
-        <v>-8.09592291278366</v>
+        <v>-8.095943679813933</v>
       </c>
       <c r="H18" t="n">
         <v>50.88300138028043</v>
@@ -39102,13 +39134,13 @@
         <v>-18.96653110566366</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.484002920704985</v>
+        <v>-1.483992843085435</v>
       </c>
       <c r="H19" t="n">
         <v>-19.32324486904549</v>
       </c>
       <c r="I19" t="n">
-        <v>22.41423668033238</v>
+        <v>22.4142464519971</v>
       </c>
       <c r="J19" t="n">
         <v>-14.81481481481481</v>
@@ -39142,7 +39174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J514"/>
+  <dimension ref="A1:J515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39377,7 +39409,7 @@
         <v>30.13837487565421</v>
       </c>
       <c r="G7" t="n">
-        <v>20.09523646786675</v>
+        <v>20.09522432517419</v>
       </c>
       <c r="H7" t="n">
         <v>19.02754764747889</v>
@@ -39441,7 +39473,7 @@
         <v>28.71272416548296</v>
       </c>
       <c r="G9" t="n">
-        <v>20.46287480132978</v>
+        <v>20.46288711064643</v>
       </c>
       <c r="H9" t="n">
         <v>12.19356144837187</v>
@@ -39473,7 +39505,7 @@
         <v>30.0219527879438</v>
       </c>
       <c r="G10" t="n">
-        <v>23.37534835154322</v>
+        <v>23.37536101634281</v>
       </c>
       <c r="H10" t="n">
         <v>14.29718712087935</v>
@@ -39569,7 +39601,7 @@
         <v>21.03425695637873</v>
       </c>
       <c r="G13" t="n">
-        <v>21.90929962747661</v>
+        <v>21.90931205606732</v>
       </c>
       <c r="H13" t="n">
         <v>23.48532329238919</v>
@@ -39729,7 +39761,7 @@
         <v>24.67729745868743</v>
       </c>
       <c r="G18" t="n">
-        <v>22.55201079499629</v>
+        <v>22.55199837900816</v>
       </c>
       <c r="H18" t="n">
         <v>94.03570205320759</v>
@@ -39825,7 +39857,7 @@
         <v>23.86999327483017</v>
       </c>
       <c r="G21" t="n">
-        <v>24.60930726084567</v>
+        <v>24.60929473401883</v>
       </c>
       <c r="H21" t="n">
         <v>75.75510868409864</v>
@@ -39889,7 +39921,7 @@
         <v>23.13578066904924</v>
       </c>
       <c r="G23" t="n">
-        <v>23.4008361975695</v>
+        <v>23.40084899712915</v>
       </c>
       <c r="H23" t="n">
         <v>91.13414267872835</v>
@@ -39921,7 +39953,7 @@
         <v>19.30215336975127</v>
       </c>
       <c r="G24" t="n">
-        <v>19.39701199606636</v>
+        <v>19.39699952093894</v>
       </c>
       <c r="H24" t="n">
         <v>86.52584846797919</v>
@@ -39953,7 +39985,7 @@
         <v>15.13592205797443</v>
       </c>
       <c r="G25" t="n">
-        <v>18.15375169225193</v>
+        <v>18.15373929538955</v>
       </c>
       <c r="H25" t="n">
         <v>71.35134787851175</v>
@@ -40017,7 +40049,7 @@
         <v>17.44186046511629</v>
       </c>
       <c r="G27" t="n">
-        <v>19.70906335411693</v>
+        <v>19.70907598092136</v>
       </c>
       <c r="H27" t="n">
         <v>75.14619883040936</v>
@@ -40049,7 +40081,7 @@
         <v>21.00077612236952</v>
       </c>
       <c r="G28" t="n">
-        <v>16.44774734500434</v>
+        <v>16.44775949092334</v>
       </c>
       <c r="H28" t="n">
         <v>73.99363134446153</v>
@@ -40081,7 +40113,7 @@
         <v>20.66455888549516</v>
       </c>
       <c r="G29" t="n">
-        <v>17.87868509962784</v>
+        <v>17.8786975781118</v>
       </c>
       <c r="H29" t="n">
         <v>72.05968302788671</v>
@@ -40145,7 +40177,7 @@
         <v>15.39021874936699</v>
       </c>
       <c r="G31" t="n">
-        <v>18.81745495257836</v>
+        <v>18.81746761698277</v>
       </c>
       <c r="H31" t="n">
         <v>65.98794595089427</v>
@@ -40209,7 +40241,7 @@
         <v>17.99588316396285</v>
       </c>
       <c r="G33" t="n">
-        <v>17.4254069034677</v>
+        <v>17.4254194414011</v>
       </c>
       <c r="H33" t="n">
         <v>69.25088116850071</v>
@@ -40401,7 +40433,7 @@
         <v>-0.3809562562003932</v>
       </c>
       <c r="G39" t="n">
-        <v>14.44662867018376</v>
+        <v>14.44661663340021</v>
       </c>
       <c r="H39" t="n">
         <v>67.07354045977698</v>
@@ -40593,7 +40625,7 @@
         <v>23.09999738420758</v>
       </c>
       <c r="G45" t="n">
-        <v>18.6986038377839</v>
+        <v>18.69859087886929</v>
       </c>
       <c r="H45" t="n">
         <v>71.45801931839102</v>
@@ -40625,7 +40657,7 @@
         <v>23.51312717433578</v>
       </c>
       <c r="G46" t="n">
-        <v>15.73058716649658</v>
+        <v>15.7305998307574</v>
       </c>
       <c r="H46" t="n">
         <v>82.7479978598209</v>
@@ -40657,7 +40689,7 @@
         <v>22.59531429862704</v>
       </c>
       <c r="G47" t="n">
-        <v>17.64925742497345</v>
+        <v>17.64924436890285</v>
       </c>
       <c r="H47" t="n">
         <v>85.00471194850942</v>
@@ -40721,7 +40753,7 @@
         <v>21.11271857609913</v>
       </c>
       <c r="G49" t="n">
-        <v>13.30433706701131</v>
+        <v>13.30434917329433</v>
       </c>
       <c r="H49" t="n">
         <v>71.57738095238095</v>
@@ -40945,7 +40977,7 @@
         <v>16.90277523464627</v>
       </c>
       <c r="G56" t="n">
-        <v>6.671014106437179</v>
+        <v>6.671025389791385</v>
       </c>
       <c r="H56" t="n">
         <v>43.77442279436383</v>
@@ -41009,7 +41041,7 @@
         <v>2.990288101739491</v>
       </c>
       <c r="G58" t="n">
-        <v>9.697583982835024</v>
+        <v>9.697595691594096</v>
       </c>
       <c r="H58" t="n">
         <v>45.31866297896825</v>
@@ -41041,7 +41073,7 @@
         <v>5.94736400403475</v>
       </c>
       <c r="G59" t="n">
-        <v>11.58453424108281</v>
+        <v>11.58454615279096</v>
       </c>
       <c r="H59" t="n">
         <v>42.8926386006018</v>
@@ -41169,7 +41201,7 @@
         <v>-4.954792961494691</v>
       </c>
       <c r="G63" t="n">
-        <v>10.3782442135929</v>
+        <v>10.3782326049433</v>
       </c>
       <c r="H63" t="n">
         <v>52.72230156143125</v>
@@ -41233,7 +41265,7 @@
         <v>-2.789282531167381</v>
       </c>
       <c r="G65" t="n">
-        <v>11.19598680172837</v>
+        <v>11.19597529731751</v>
       </c>
       <c r="H65" t="n">
         <v>60.93793770295235</v>
@@ -41457,7 +41489,7 @@
         <v>-16.35850620750612</v>
       </c>
       <c r="G72" t="n">
-        <v>4.717479363746002</v>
+        <v>4.717490054637974</v>
       </c>
       <c r="H72" t="n">
         <v>52.95796817224014</v>
@@ -41489,7 +41521,7 @@
         <v>-17.74229082477954</v>
       </c>
       <c r="G73" t="n">
-        <v>4.782695642945956</v>
+        <v>4.782706263481851</v>
       </c>
       <c r="H73" t="n">
         <v>45.67474432100389</v>
@@ -41553,7 +41585,7 @@
         <v>-18.87479351610046</v>
       </c>
       <c r="G75" t="n">
-        <v>1.709496340413774</v>
+        <v>1.709486112348579</v>
       </c>
       <c r="H75" t="n">
         <v>30.02268127303005</v>
@@ -41585,7 +41617,7 @@
         <v>-17.12165045191634</v>
       </c>
       <c r="G76" t="n">
-        <v>2.412994360741871</v>
+        <v>2.412984056480316</v>
       </c>
       <c r="H76" t="n">
         <v>29.75552684353173</v>
@@ -41649,7 +41681,7 @@
         <v>-14.20658392523141</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.217336350478059</v>
+        <v>-0.2173465213802905</v>
       </c>
       <c r="H78" t="n">
         <v>37.16040451905292</v>
@@ -41745,7 +41777,7 @@
         <v>-16.15832902940159</v>
       </c>
       <c r="G81" t="n">
-        <v>-2.173506464292652</v>
+        <v>-2.173516149913401</v>
       </c>
       <c r="H81" t="n">
         <v>44.05244047508194</v>
@@ -41905,7 +41937,7 @@
         <v>-17.14285992776975</v>
       </c>
       <c r="G86" t="n">
-        <v>-2.846756003970619</v>
+        <v>-2.846746645443798</v>
       </c>
       <c r="H86" t="n">
         <v>67.13286132918634</v>
@@ -41969,7 +42001,7 @@
         <v>-22.44094964591114</v>
       </c>
       <c r="G88" t="n">
-        <v>-5.51181892058864</v>
+        <v>-5.511809895483855</v>
       </c>
       <c r="H88" t="n">
         <v>55.75244209203252</v>
@@ -42001,7 +42033,7 @@
         <v>-21.64679673751331</v>
       </c>
       <c r="G89" t="n">
-        <v>-4.430058284525817</v>
+        <v>-4.430049221610089</v>
       </c>
       <c r="H89" t="n">
         <v>62.23793649992655</v>
@@ -42033,7 +42065,7 @@
         <v>-21.60274235468711</v>
       </c>
       <c r="G90" t="n">
-        <v>-1.754756569930216</v>
+        <v>-1.754765960790283</v>
       </c>
       <c r="H90" t="n">
         <v>44.01810748398501</v>
@@ -42065,7 +42097,7 @@
         <v>-24.73446258717338</v>
       </c>
       <c r="G91" t="n">
-        <v>-2.788650154475081</v>
+        <v>-2.788659427495976</v>
       </c>
       <c r="H91" t="n">
         <v>35.52879303916819</v>
@@ -42225,7 +42257,7 @@
         <v>-43.65987090351605</v>
       </c>
       <c r="G96" t="n">
-        <v>-1.77221865009497</v>
+        <v>-1.772228030575917</v>
       </c>
       <c r="H96" t="n">
         <v>15.89211111741442</v>
@@ -42257,7 +42289,7 @@
         <v>-43.28643185409469</v>
       </c>
       <c r="G97" t="n">
-        <v>1.280378835870222</v>
+        <v>1.28038853354191</v>
       </c>
       <c r="H97" t="n">
         <v>20.58264671468648</v>
@@ -42385,7 +42417,7 @@
         <v>-56.13349608547158</v>
       </c>
       <c r="G101" t="n">
-        <v>-9.051291101519077</v>
+        <v>-9.051283041968395</v>
       </c>
       <c r="H101" t="n">
         <v>17.94541203322633</v>
@@ -42449,7 +42481,7 @@
         <v>-61.42636857635259</v>
       </c>
       <c r="G103" t="n">
-        <v>-9.404738086845111</v>
+        <v>-9.404746306998312</v>
       </c>
       <c r="H103" t="n">
         <v>14.88724822383976</v>
@@ -42705,7 +42737,7 @@
         <v>-54.47863391321948</v>
       </c>
       <c r="G111" t="n">
-        <v>-10.09984190731003</v>
+        <v>-10.09983412216593</v>
       </c>
       <c r="H111" t="n">
         <v>10.12767521636539</v>
@@ -42769,7 +42801,7 @@
         <v>-54.22889949879295</v>
       </c>
       <c r="G113" t="n">
-        <v>-12.80789830622243</v>
+        <v>-12.80790569589147</v>
       </c>
       <c r="H113" t="n">
         <v>29.08312860522841</v>
@@ -42833,7 +42865,7 @@
         <v>-56.60509984441939</v>
       </c>
       <c r="G115" t="n">
-        <v>-13.22025659231684</v>
+        <v>-13.22026410105521</v>
       </c>
       <c r="H115" t="n">
         <v>24.44754770776356</v>
@@ -42993,7 +43025,7 @@
         <v>-56.69829342607511</v>
       </c>
       <c r="G120" t="n">
-        <v>-16.07677724263259</v>
+        <v>-16.07677016593015</v>
       </c>
       <c r="H120" t="n">
         <v>18.29646125327557</v>
@@ -43057,7 +43089,7 @@
         <v>-57.68309141301329</v>
       </c>
       <c r="G122" t="n">
-        <v>-15.87210631803505</v>
+        <v>-15.87211338546375</v>
       </c>
       <c r="H122" t="n">
         <v>10.24109211646398</v>
@@ -43153,7 +43185,7 @@
         <v>-62.04201834542411</v>
       </c>
       <c r="G125" t="n">
-        <v>-17.87453111804034</v>
+        <v>-17.87452422082486</v>
       </c>
       <c r="H125" t="n">
         <v>-0.9950223577321893</v>
@@ -43217,7 +43249,7 @@
         <v>-64.48646305395978</v>
       </c>
       <c r="G127" t="n">
-        <v>-18.73303819338198</v>
+        <v>-18.73304496909627</v>
       </c>
       <c r="H127" t="n">
         <v>-7.626934073983682</v>
@@ -43473,7 +43505,7 @@
         <v>-55.97900230427739</v>
       </c>
       <c r="G135" t="n">
-        <v>-15.92344686738257</v>
+        <v>-15.92345379113794</v>
       </c>
       <c r="H135" t="n">
         <v>-2.809878783828057</v>
@@ -43505,7 +43537,7 @@
         <v>-54.15469427793725</v>
       </c>
       <c r="G136" t="n">
-        <v>-16.69092168949762</v>
+        <v>-16.69091484172436</v>
       </c>
       <c r="H136" t="n">
         <v>0.04121654929012397</v>
@@ -43569,7 +43601,7 @@
         <v>-55.96958453493185</v>
       </c>
       <c r="G138" t="n">
-        <v>-15.24242479379555</v>
+        <v>-15.24243193354286</v>
       </c>
       <c r="H138" t="n">
         <v>-1.909228316656353</v>
@@ -43601,7 +43633,7 @@
         <v>-49.86285836356027</v>
       </c>
       <c r="G139" t="n">
-        <v>-15.18492986028326</v>
+        <v>-15.18492275842689</v>
       </c>
       <c r="H139" t="n">
         <v>11.39967947776015</v>
@@ -43665,7 +43697,7 @@
         <v>-43.95747457582054</v>
       </c>
       <c r="G141" t="n">
-        <v>-10.53411633157888</v>
+        <v>-10.53410861029163</v>
       </c>
       <c r="H141" t="n">
         <v>11.78529754959159</v>
@@ -43729,7 +43761,7 @@
         <v>-51.06795889575086</v>
       </c>
       <c r="G143" t="n">
-        <v>-10.39699208731316</v>
+        <v>-10.39699977745677</v>
       </c>
       <c r="H143" t="n">
         <v>-7.09122645551531</v>
@@ -43793,7 +43825,7 @@
         <v>-47.72093129712481</v>
       </c>
       <c r="G145" t="n">
-        <v>-11.16617952809754</v>
+        <v>-11.16618712965093</v>
       </c>
       <c r="H145" t="n">
         <v>2.334533491450208</v>
@@ -43921,7 +43953,7 @@
         <v>-48.09143066406249</v>
       </c>
       <c r="G149" t="n">
-        <v>-16.07073061271678</v>
+        <v>-16.07072366706042</v>
       </c>
       <c r="H149" t="n">
         <v>-1.760633823603719</v>
@@ -43985,7 +44017,7 @@
         <v>-54.39159419656274</v>
       </c>
       <c r="G151" t="n">
-        <v>-21.22333815512868</v>
+        <v>-21.22333160042681</v>
       </c>
       <c r="H151" t="n">
         <v>-10.10608394316426</v>
@@ -44081,7 +44113,7 @@
         <v>-54.55138411907664</v>
       </c>
       <c r="G154" t="n">
-        <v>-16.3944161385867</v>
+        <v>-16.39440907818802</v>
       </c>
       <c r="H154" t="n">
         <v>-15.20339189949682</v>
@@ -44241,7 +44273,7 @@
         <v>-48.69467684534752</v>
       </c>
       <c r="G159" t="n">
-        <v>-11.6939399096355</v>
+        <v>-11.69394734550824</v>
       </c>
       <c r="H159" t="n">
         <v>34.79139711401707</v>
@@ -44305,7 +44337,7 @@
         <v>-46.27473724552217</v>
       </c>
       <c r="G161" t="n">
-        <v>-10.89765650015858</v>
+        <v>-10.89764899006671</v>
       </c>
       <c r="H161" t="n">
         <v>38.5684914172453</v>
@@ -44337,7 +44369,7 @@
         <v>-51.18435907630281</v>
       </c>
       <c r="G162" t="n">
-        <v>-10.89316097368617</v>
+        <v>-10.8931684914654</v>
       </c>
       <c r="H162" t="n">
         <v>31.94658342227763</v>
@@ -44529,7 +44561,7 @@
         <v>-53.21192041547695</v>
       </c>
       <c r="G168" t="n">
-        <v>-1.846931117352801</v>
+        <v>-1.846922769230852</v>
       </c>
       <c r="H168" t="n">
         <v>23.80828374026902</v>
@@ -44593,7 +44625,7 @@
         <v>-52.14848123130358</v>
       </c>
       <c r="G170" t="n">
-        <v>-3.764455597413807</v>
+        <v>-3.764463701823417</v>
       </c>
       <c r="H170" t="n">
         <v>31.30973250029547</v>
@@ -44625,7 +44657,7 @@
         <v>-51.04838688412199</v>
       </c>
       <c r="G171" t="n">
-        <v>-5.77381942704066</v>
+        <v>-5.773811489413038</v>
       </c>
       <c r="H171" t="n">
         <v>33.71331443951104</v>
@@ -44753,7 +44785,7 @@
         <v>-42.28287675129394</v>
       </c>
       <c r="G175" t="n">
-        <v>2.861048248629738</v>
+        <v>2.861057206861273</v>
       </c>
       <c r="H175" t="n">
         <v>63.09951008127501</v>
@@ -44785,7 +44817,7 @@
         <v>-38.62024938625434</v>
       </c>
       <c r="G176" t="n">
-        <v>4.821513659026477</v>
+        <v>4.821522947935719</v>
       </c>
       <c r="H176" t="n">
         <v>73.38710005667144</v>
@@ -44881,7 +44913,7 @@
         <v>-41.81931635301061</v>
       </c>
       <c r="G179" t="n">
-        <v>0.9841546961556702</v>
+        <v>0.984145910827805</v>
       </c>
       <c r="H179" t="n">
         <v>61.06736588618858</v>
@@ -45041,7 +45073,7 @@
         <v>-35.9392113960985</v>
       </c>
       <c r="G184" t="n">
-        <v>-2.94078491301919</v>
+        <v>-2.940776703709791</v>
       </c>
       <c r="H184" t="n">
         <v>84.22466480357787</v>
@@ -45521,7 +45553,7 @@
         <v>-36.51537018870842</v>
       </c>
       <c r="G199" t="n">
-        <v>-1.938821685949521</v>
+        <v>-1.938813407055073</v>
       </c>
       <c r="H199" t="n">
         <v>103.1003645832206</v>
@@ -45681,7 +45713,7 @@
         <v>-26.48352671295293</v>
       </c>
       <c r="G204" t="n">
-        <v>-0.09635584766152228</v>
+        <v>-0.09634747259529286</v>
       </c>
       <c r="H204" t="n">
         <v>89.75380721992235</v>
@@ -45841,7 +45873,7 @@
         <v>-28.01413821889418</v>
       </c>
       <c r="G209" t="n">
-        <v>-0.4308950012773538</v>
+        <v>-0.4309030382603218</v>
       </c>
       <c r="H209" t="n">
         <v>100.6930017200002</v>
@@ -45937,7 +45969,7 @@
         <v>-35.74768677135886</v>
       </c>
       <c r="G212" t="n">
-        <v>-1.178352048372056</v>
+        <v>-1.178344248181784</v>
       </c>
       <c r="H212" t="n">
         <v>98.29378184219588</v>
@@ -46065,7 +46097,7 @@
         <v>-35.39603519665386</v>
       </c>
       <c r="G216" t="n">
-        <v>-6.28555152193504</v>
+        <v>-6.285544289936063</v>
       </c>
       <c r="H216" t="n">
         <v>88.96002855288734</v>
@@ -46449,7 +46481,7 @@
         <v>-33.03285408680733</v>
       </c>
       <c r="G228" t="n">
-        <v>-4.723286234245117</v>
+        <v>-4.723294121347854</v>
       </c>
       <c r="H228" t="n">
         <v>77.41683291570176</v>
@@ -46513,7 +46545,7 @@
         <v>-40.67977613483576</v>
       </c>
       <c r="G230" t="n">
-        <v>-8.235102601298294</v>
+        <v>-8.235095143331449</v>
       </c>
       <c r="H230" t="n">
         <v>64.56839752173443</v>
@@ -46545,7 +46577,7 @@
         <v>-36.82532653673968</v>
       </c>
       <c r="G231" t="n">
-        <v>-7.581518060630521</v>
+        <v>-7.581525606214157</v>
       </c>
       <c r="H231" t="n">
         <v>54.87430225307104</v>
@@ -46641,7 +46673,7 @@
         <v>-38.63636103394656</v>
       </c>
       <c r="G234" t="n">
-        <v>-6.78956868988656</v>
+        <v>-6.789576370302264</v>
       </c>
       <c r="H234" t="n">
         <v>36.77451609649452</v>
@@ -46673,7 +46705,7 @@
         <v>-35.84453808293154</v>
       </c>
       <c r="G235" t="n">
-        <v>-3.676391944864155</v>
+        <v>-3.676400166962435</v>
       </c>
       <c r="H235" t="n">
         <v>44.01268886295892</v>
@@ -46705,7 +46737,7 @@
         <v>-38.54011889937667</v>
       </c>
       <c r="G236" t="n">
-        <v>-5.742096825731635</v>
+        <v>-5.742088828171921</v>
       </c>
       <c r="H236" t="n">
         <v>42.47745831783718</v>
@@ -46769,7 +46801,7 @@
         <v>-41.6571487373118</v>
       </c>
       <c r="G238" t="n">
-        <v>-4.419213318578863</v>
+        <v>-4.419205170020679</v>
       </c>
       <c r="H238" t="n">
         <v>30.13929691573842</v>
@@ -46897,7 +46929,7 @@
         <v>-38.30580451011441</v>
       </c>
       <c r="G242" t="n">
-        <v>-2.136970167875163</v>
+        <v>-2.136961897373224</v>
       </c>
       <c r="H242" t="n">
         <v>24.7957124658932</v>
@@ -55611,6 +55643,38 @@
       </c>
       <c r="J514" t="n">
         <v>-56.72742500835124</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B515" t="n">
+        <v>-62.12923509962109</v>
+      </c>
+      <c r="C515" t="n">
+        <v>-27.10382126370712</v>
+      </c>
+      <c r="D515" t="n">
+        <v>-33.40000152587891</v>
+      </c>
+      <c r="E515" t="n">
+        <v>-27.27928391463444</v>
+      </c>
+      <c r="F515" t="n">
+        <v>-51.92963359048133</v>
+      </c>
+      <c r="G515" t="n">
+        <v>-11.50792085961132</v>
+      </c>
+      <c r="H515" t="n">
+        <v>-81.6719660066035</v>
+      </c>
+      <c r="I515" t="n">
+        <v>-23.43824279760223</v>
+      </c>
+      <c r="J515" t="n">
+        <v>-55.69139741515657</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/Reliance Group.xlsx
+++ b/dashboards/Reliance Group.xlsx
@@ -493,13 +493,13 @@
         <v>91.84999847412109</v>
       </c>
       <c r="G2" t="n">
-        <v>1088.74658203125</v>
+        <v>1088.746704101562</v>
       </c>
       <c r="H2" t="n">
         <v>100.8000030517578</v>
       </c>
       <c r="I2" t="n">
-        <v>850.676025390625</v>
+        <v>850.6760864257812</v>
       </c>
       <c r="J2" t="n">
         <v>14.25</v>
@@ -522,13 +522,13 @@
         <v>90.40000152587891</v>
       </c>
       <c r="G3" t="n">
-        <v>1113.317504882812</v>
+        <v>1113.3173828125</v>
       </c>
       <c r="H3" t="n">
         <v>97.5</v>
       </c>
       <c r="I3" t="n">
-        <v>857.1109008789062</v>
+        <v>857.11083984375</v>
       </c>
       <c r="J3" t="n">
         <v>13.89999961853027</v>
@@ -551,13 +551,13 @@
         <v>89.94999694824219</v>
       </c>
       <c r="G4" t="n">
-        <v>1118.526123046875</v>
+        <v>1118.526000976562</v>
       </c>
       <c r="H4" t="n">
         <v>97.05000305175781</v>
       </c>
       <c r="I4" t="n">
-        <v>844.1920166015625</v>
+        <v>844.1920776367188</v>
       </c>
       <c r="J4" t="n">
         <v>13.85000038146973</v>
@@ -580,13 +580,13 @@
         <v>89.90000152587891</v>
       </c>
       <c r="G5" t="n">
-        <v>1094.476196289062</v>
+        <v>1094.47607421875</v>
       </c>
       <c r="H5" t="n">
         <v>100.1500015258789</v>
       </c>
       <c r="I5" t="n">
-        <v>844.6340942382812</v>
+        <v>844.6341552734375</v>
       </c>
       <c r="J5" t="n">
         <v>14.30000019073486</v>
@@ -644,7 +644,7 @@
         <v>103.4499969482422</v>
       </c>
       <c r="I7" t="n">
-        <v>939.3392333984375</v>
+        <v>939.3392944335938</v>
       </c>
       <c r="J7" t="n">
         <v>14.85000038146973</v>
@@ -696,7 +696,7 @@
         <v>88.09999847412109</v>
       </c>
       <c r="G9" t="n">
-        <v>1141.851318359375</v>
+        <v>1141.851440429688</v>
       </c>
       <c r="H9" t="n">
         <v>96.40000152587891</v>
@@ -725,13 +725,13 @@
         <v>90.09999847412109</v>
       </c>
       <c r="G10" t="n">
-        <v>1148.282836914062</v>
+        <v>1148.28271484375</v>
       </c>
       <c r="H10" t="n">
         <v>99.05000305175781</v>
       </c>
       <c r="I10" t="n">
-        <v>931.4307861328125</v>
+        <v>931.4307250976562</v>
       </c>
       <c r="J10" t="n">
         <v>14.25</v>
@@ -754,7 +754,7 @@
         <v>89.59999847412109</v>
       </c>
       <c r="G11" t="n">
-        <v>1149.95849609375</v>
+        <v>1149.958618164062</v>
       </c>
       <c r="H11" t="n">
         <v>102.75</v>
@@ -783,13 +783,13 @@
         <v>91.40000152587891</v>
       </c>
       <c r="G12" t="n">
-        <v>1155.959716796875</v>
+        <v>1155.959594726562</v>
       </c>
       <c r="H12" t="n">
         <v>105.5500030517578</v>
       </c>
       <c r="I12" t="n">
-        <v>934.6727905273438</v>
+        <v>934.6728515625</v>
       </c>
       <c r="J12" t="n">
         <v>15.64999961853027</v>
@@ -812,13 +812,13 @@
         <v>89.80000305175781</v>
       </c>
       <c r="G13" t="n">
-        <v>1142.16845703125</v>
+        <v>1142.168334960938</v>
       </c>
       <c r="H13" t="n">
         <v>101.9499969482422</v>
       </c>
       <c r="I13" t="n">
-        <v>930.4974975585938</v>
+        <v>930.4976196289062</v>
       </c>
       <c r="J13" t="n">
         <v>16.10000038146973</v>
@@ -841,13 +841,13 @@
         <v>90.69999694824219</v>
       </c>
       <c r="G14" t="n">
-        <v>1142.077880859375</v>
+        <v>1142.077758789062</v>
       </c>
       <c r="H14" t="n">
         <v>99.75</v>
       </c>
       <c r="I14" t="n">
-        <v>957.71044921875</v>
+        <v>957.7103881835938</v>
       </c>
       <c r="J14" t="n">
         <v>15.85000038146973</v>
@@ -870,7 +870,7 @@
         <v>88.75</v>
       </c>
       <c r="G15" t="n">
-        <v>1122.081420898438</v>
+        <v>1122.081665039062</v>
       </c>
       <c r="H15" t="n">
         <v>101.5500030517578</v>
@@ -905,7 +905,7 @@
         <v>98.25</v>
       </c>
       <c r="I16" t="n">
-        <v>898.8637084960938</v>
+        <v>898.8635864257812</v>
       </c>
       <c r="J16" t="n">
         <v>16.04999923706055</v>
@@ -928,13 +928,13 @@
         <v>82.09999847412109</v>
       </c>
       <c r="G17" t="n">
-        <v>1076.99365234375</v>
+        <v>1076.993408203125</v>
       </c>
       <c r="H17" t="n">
         <v>93.55000305175781</v>
       </c>
       <c r="I17" t="n">
-        <v>835.7432250976562</v>
+        <v>835.7432861328125</v>
       </c>
       <c r="J17" t="n">
         <v>15.25</v>
@@ -957,13 +957,13 @@
         <v>78</v>
       </c>
       <c r="G18" t="n">
-        <v>1074.887573242188</v>
+        <v>1074.887451171875</v>
       </c>
       <c r="H18" t="n">
         <v>98.05000305175781</v>
       </c>
       <c r="I18" t="n">
-        <v>835.7432250976562</v>
+        <v>835.7432861328125</v>
       </c>
       <c r="J18" t="n">
         <v>14.75</v>
@@ -986,13 +986,13 @@
         <v>81.90000152587891</v>
       </c>
       <c r="G19" t="n">
-        <v>1058.967407226562</v>
+        <v>1058.967163085938</v>
       </c>
       <c r="H19" t="n">
         <v>97.80000305175781</v>
       </c>
       <c r="I19" t="n">
-        <v>855.3916015625</v>
+        <v>855.3916625976562</v>
       </c>
       <c r="J19" t="n">
         <v>14.80000019073486</v>
@@ -1015,7 +1015,7 @@
         <v>84.25</v>
       </c>
       <c r="G20" t="n">
-        <v>1057.9482421875</v>
+        <v>1057.948364257812</v>
       </c>
       <c r="H20" t="n">
         <v>102.3000030517578</v>
@@ -1044,13 +1044,13 @@
         <v>82</v>
       </c>
       <c r="G21" t="n">
-        <v>1080.933837890625</v>
+        <v>1080.93408203125</v>
       </c>
       <c r="H21" t="n">
         <v>101.0500030517578</v>
       </c>
       <c r="I21" t="n">
-        <v>864.528076171875</v>
+        <v>864.5281372070312</v>
       </c>
       <c r="J21" t="n">
         <v>14.80000019073486</v>
@@ -1073,13 +1073,13 @@
         <v>82.55000305175781</v>
       </c>
       <c r="G22" t="n">
-        <v>1077.355834960938</v>
+        <v>1077.35595703125</v>
       </c>
       <c r="H22" t="n">
         <v>106.0999984741211</v>
       </c>
       <c r="I22" t="n">
-        <v>907.7544555664062</v>
+        <v>907.7545166015625</v>
       </c>
       <c r="J22" t="n">
         <v>15.5</v>
@@ -1102,13 +1102,13 @@
         <v>85.90000152587891</v>
       </c>
       <c r="G23" t="n">
-        <v>1079.552490234375</v>
+        <v>1079.552368164062</v>
       </c>
       <c r="H23" t="n">
         <v>110.0999984741211</v>
       </c>
       <c r="I23" t="n">
-        <v>921.5574340820312</v>
+        <v>921.5574951171875</v>
       </c>
       <c r="J23" t="n">
         <v>16.04999923706055</v>
@@ -1137,7 +1137,7 @@
         <v>115.5999984741211</v>
       </c>
       <c r="I24" t="n">
-        <v>910.0140991210938</v>
+        <v>910.0139770507812</v>
       </c>
       <c r="J24" t="n">
         <v>16.85000038146973</v>
@@ -1160,13 +1160,13 @@
         <v>85.44999694824219</v>
       </c>
       <c r="G25" t="n">
-        <v>1055.887451171875</v>
+        <v>1055.887573242188</v>
       </c>
       <c r="H25" t="n">
         <v>121.3499984741211</v>
       </c>
       <c r="I25" t="n">
-        <v>898.3724365234375</v>
+        <v>898.3724975585938</v>
       </c>
       <c r="J25" t="n">
         <v>17.64999961853027</v>
@@ -1195,7 +1195,7 @@
         <v>133.4499969482422</v>
       </c>
       <c r="I26" t="n">
-        <v>874.79443359375</v>
+        <v>874.7943725585938</v>
       </c>
       <c r="J26" t="n">
         <v>18.5</v>
@@ -1218,7 +1218,7 @@
         <v>83.59999847412109</v>
       </c>
       <c r="G27" t="n">
-        <v>1067.097290039062</v>
+        <v>1067.09716796875</v>
       </c>
       <c r="H27" t="n">
         <v>134.4499969482422</v>
@@ -1247,13 +1247,13 @@
         <v>87.75</v>
       </c>
       <c r="G28" t="n">
-        <v>1079.529907226562</v>
+        <v>1079.52978515625</v>
       </c>
       <c r="H28" t="n">
         <v>147.8500061035156</v>
       </c>
       <c r="I28" t="n">
-        <v>866.5420532226562</v>
+        <v>866.5419921875</v>
       </c>
       <c r="J28" t="n">
         <v>17</v>
@@ -1276,7 +1276,7 @@
         <v>92.09999847412109</v>
       </c>
       <c r="G29" t="n">
-        <v>1078.420166015625</v>
+        <v>1078.420288085938</v>
       </c>
       <c r="H29" t="n">
         <v>133.1000061035156</v>
@@ -1305,13 +1305,13 @@
         <v>91.44999694824219</v>
       </c>
       <c r="G30" t="n">
-        <v>1076.314331054688</v>
+        <v>1076.314086914062</v>
       </c>
       <c r="H30" t="n">
         <v>134</v>
       </c>
       <c r="I30" t="n">
-        <v>853.6724853515625</v>
+        <v>853.6724243164062</v>
       </c>
       <c r="J30" t="n">
         <v>15.94999980926514</v>
@@ -1340,7 +1340,7 @@
         <v>120.5999984741211</v>
       </c>
       <c r="I31" t="n">
-        <v>771.345703125</v>
+        <v>771.3457641601562</v>
       </c>
       <c r="J31" t="n">
         <v>15.19999980926514</v>
@@ -1363,7 +1363,7 @@
         <v>87.05000305175781</v>
       </c>
       <c r="G32" t="n">
-        <v>1095.132934570312</v>
+        <v>1095.1328125</v>
       </c>
       <c r="H32" t="n">
         <v>111.8499984741211</v>
@@ -1398,7 +1398,7 @@
         <v>122.5999984741211</v>
       </c>
       <c r="I33" t="n">
-        <v>794.4325561523438</v>
+        <v>794.4324951171875</v>
       </c>
       <c r="J33" t="n">
         <v>14.80000019073486</v>
@@ -1421,7 +1421,7 @@
         <v>85.30000305175781</v>
       </c>
       <c r="G34" t="n">
-        <v>1106.704833984375</v>
+        <v>1106.704956054688</v>
       </c>
       <c r="H34" t="n">
         <v>113.3499984741211</v>
@@ -1450,7 +1450,7 @@
         <v>83.09999847412109</v>
       </c>
       <c r="G35" t="n">
-        <v>1098.05419921875</v>
+        <v>1098.054321289062</v>
       </c>
       <c r="H35" t="n">
         <v>120.0999984741211</v>
@@ -1479,7 +1479,7 @@
         <v>82.15000152587891</v>
       </c>
       <c r="G36" t="n">
-        <v>1086.957641601562</v>
+        <v>1086.957763671875</v>
       </c>
       <c r="H36" t="n">
         <v>112.6999969482422</v>
@@ -1514,7 +1514,7 @@
         <v>114.3499984741211</v>
       </c>
       <c r="I37" t="n">
-        <v>725.5650024414062</v>
+        <v>725.5650634765625</v>
       </c>
       <c r="J37" t="n">
         <v>12.94999980926514</v>
@@ -1543,7 +1543,7 @@
         <v>113.25</v>
       </c>
       <c r="I38" t="n">
-        <v>748.2588500976562</v>
+        <v>748.2589111328125</v>
       </c>
       <c r="J38" t="n">
         <v>13.55000019073486</v>
@@ -1566,7 +1566,7 @@
         <v>74.75</v>
       </c>
       <c r="G39" t="n">
-        <v>1021.669494628906</v>
+        <v>1021.669677734375</v>
       </c>
       <c r="H39" t="n">
         <v>101.9499969482422</v>
@@ -1595,7 +1595,7 @@
         <v>77.65000152587891</v>
       </c>
       <c r="G40" t="n">
-        <v>1034.44189453125</v>
+        <v>1034.442016601562</v>
       </c>
       <c r="H40" t="n">
         <v>104.5999984741211</v>
@@ -1630,7 +1630,7 @@
         <v>104.5999984741211</v>
       </c>
       <c r="I41" t="n">
-        <v>686.1209106445312</v>
+        <v>686.1209716796875</v>
       </c>
       <c r="J41" t="n">
         <v>13.05000019073486</v>
@@ -1653,13 +1653,13 @@
         <v>76.25</v>
       </c>
       <c r="G42" t="n">
-        <v>1086.346313476562</v>
+        <v>1086.34619140625</v>
       </c>
       <c r="H42" t="n">
         <v>107.5999984741211</v>
       </c>
       <c r="I42" t="n">
-        <v>692.8504638671875</v>
+        <v>692.8505249023438</v>
       </c>
       <c r="J42" t="n">
         <v>13.14999961853027</v>
@@ -1740,13 +1740,13 @@
         <v>73.65000152587891</v>
       </c>
       <c r="G45" t="n">
-        <v>1014.332397460938</v>
+        <v>1014.332336425781</v>
       </c>
       <c r="H45" t="n">
         <v>99.59999847412109</v>
       </c>
       <c r="I45" t="n">
-        <v>640.9788818359375</v>
+        <v>640.9788208007812</v>
       </c>
       <c r="J45" t="n">
         <v>12.64999961853027</v>
@@ -1769,13 +1769,13 @@
         <v>74.09999847412109</v>
       </c>
       <c r="G46" t="n">
-        <v>1012.497985839844</v>
+        <v>1012.497924804688</v>
       </c>
       <c r="H46" t="n">
         <v>101.75</v>
       </c>
       <c r="I46" t="n">
-        <v>667.5040283203125</v>
+        <v>667.504150390625</v>
       </c>
       <c r="J46" t="n">
         <v>12.80000019073486</v>
@@ -1804,7 +1804,7 @@
         <v>107.5</v>
       </c>
       <c r="I47" t="n">
-        <v>693.882080078125</v>
+        <v>693.8820190429688</v>
       </c>
       <c r="J47" t="n">
         <v>13.35000038146973</v>
@@ -1827,13 +1827,13 @@
         <v>78</v>
       </c>
       <c r="G48" t="n">
-        <v>1083.492919921875</v>
+        <v>1083.492797851562</v>
       </c>
       <c r="H48" t="n">
         <v>111.4000015258789</v>
       </c>
       <c r="I48" t="n">
-        <v>701.8396606445312</v>
+        <v>701.839599609375</v>
       </c>
       <c r="J48" t="n">
         <v>13.55000019073486</v>
@@ -1862,7 +1862,7 @@
         <v>122.5</v>
       </c>
       <c r="I49" t="n">
-        <v>746.5888061523438</v>
+        <v>746.5888671875</v>
       </c>
       <c r="J49" t="n">
         <v>14.19999980926514</v>
@@ -1885,13 +1885,13 @@
         <v>76.5</v>
       </c>
       <c r="G50" t="n">
-        <v>1095.540405273438</v>
+        <v>1095.540283203125</v>
       </c>
       <c r="H50" t="n">
         <v>117.25</v>
       </c>
       <c r="I50" t="n">
-        <v>737.84521484375</v>
+        <v>737.8451538085938</v>
       </c>
       <c r="J50" t="n">
         <v>13.85000038146973</v>
@@ -1914,13 +1914,13 @@
         <v>78.84999847412109</v>
       </c>
       <c r="G51" t="n">
-        <v>1070.44873046875</v>
+        <v>1070.448852539062</v>
       </c>
       <c r="H51" t="n">
         <v>115.5500030517578</v>
       </c>
       <c r="I51" t="n">
-        <v>747.3255615234375</v>
+        <v>747.32568359375</v>
       </c>
       <c r="J51" t="n">
         <v>13.44999980926514</v>
@@ -1943,13 +1943,13 @@
         <v>77.75</v>
       </c>
       <c r="G52" t="n">
-        <v>1088.520141601562</v>
+        <v>1088.520385742188</v>
       </c>
       <c r="H52" t="n">
         <v>118.9499969482422</v>
       </c>
       <c r="I52" t="n">
-        <v>750.5184936523438</v>
+        <v>750.5184326171875</v>
       </c>
       <c r="J52" t="n">
         <v>14.10000038146973</v>
@@ -1978,7 +1978,7 @@
         <v>116.8000030517578</v>
       </c>
       <c r="I53" t="n">
-        <v>758.770751953125</v>
+        <v>758.7706909179688</v>
       </c>
       <c r="J53" t="n">
         <v>13.75</v>
@@ -2001,7 +2001,7 @@
         <v>79.15000152587891</v>
       </c>
       <c r="G54" t="n">
-        <v>1117.52978515625</v>
+        <v>1117.529663085938</v>
       </c>
       <c r="H54" t="n">
         <v>115.4000015258789</v>
@@ -2036,7 +2036,7 @@
         <v>113.1500015258789</v>
       </c>
       <c r="I55" t="n">
-        <v>751.10791015625</v>
+        <v>751.1078491210938</v>
       </c>
       <c r="J55" t="n">
         <v>13</v>
@@ -2065,7 +2065,7 @@
         <v>111.8000030517578</v>
       </c>
       <c r="I56" t="n">
-        <v>756.51123046875</v>
+        <v>756.5111694335938</v>
       </c>
       <c r="J56" t="n">
         <v>12.85000038146973</v>
@@ -2088,13 +2088,13 @@
         <v>85.55000305175781</v>
       </c>
       <c r="G57" t="n">
-        <v>1167.916748046875</v>
+        <v>1167.916625976562</v>
       </c>
       <c r="H57" t="n">
         <v>109.6999969482422</v>
       </c>
       <c r="I57" t="n">
-        <v>756.3638916015625</v>
+        <v>756.3638305664062</v>
       </c>
       <c r="J57" t="n">
         <v>13</v>
@@ -2146,7 +2146,7 @@
         <v>87.59999847412109</v>
       </c>
       <c r="G59" t="n">
-        <v>1187.528076171875</v>
+        <v>1187.528198242188</v>
       </c>
       <c r="H59" t="n">
         <v>100.6999969482422</v>
@@ -2204,13 +2204,13 @@
         <v>85.80000305175781</v>
       </c>
       <c r="G61" t="n">
-        <v>1210.627197265625</v>
+        <v>1210.626953125</v>
       </c>
       <c r="H61" t="n">
         <v>114.8000030517578</v>
       </c>
       <c r="I61" t="n">
-        <v>769.7738647460938</v>
+        <v>769.7738037109375</v>
       </c>
       <c r="J61" t="n">
         <v>13.55000019073486</v>
@@ -2233,13 +2233,13 @@
         <v>85.15000152587891</v>
       </c>
       <c r="G62" t="n">
-        <v>1193.325317382812</v>
+        <v>1193.325439453125</v>
       </c>
       <c r="H62" t="n">
         <v>112.3000030517578</v>
       </c>
       <c r="I62" t="n">
-        <v>764.6160888671875</v>
+        <v>764.6162109375</v>
       </c>
       <c r="J62" t="n">
         <v>13.5</v>
@@ -2262,7 +2262,7 @@
         <v>87.84999847412109</v>
       </c>
       <c r="G63" t="n">
-        <v>1202.882080078125</v>
+        <v>1202.881958007812</v>
       </c>
       <c r="H63" t="n">
         <v>122.6500015258789</v>
@@ -2291,7 +2291,7 @@
         <v>92.19999694824219</v>
       </c>
       <c r="G64" t="n">
-        <v>1206.437377929688</v>
+        <v>1206.4375</v>
       </c>
       <c r="H64" t="n">
         <v>124.6999969482422</v>
@@ -2349,13 +2349,13 @@
         <v>94.5</v>
       </c>
       <c r="G66" t="n">
-        <v>1186.214721679688</v>
+        <v>1186.214599609375</v>
       </c>
       <c r="H66" t="n">
         <v>136.1499938964844</v>
       </c>
       <c r="I66" t="n">
-        <v>822.1367797851562</v>
+        <v>822.13671875</v>
       </c>
       <c r="J66" t="n">
         <v>16.29999923706055</v>
@@ -2384,7 +2384,7 @@
         <v>125.1500015258789</v>
       </c>
       <c r="I67" t="n">
-        <v>798.9517211914062</v>
+        <v>798.95166015625</v>
       </c>
       <c r="J67" t="n">
         <v>15.5</v>
@@ -2407,13 +2407,13 @@
         <v>97.19999694824219</v>
       </c>
       <c r="G68" t="n">
-        <v>1184.674560546875</v>
+        <v>1184.674926757812</v>
       </c>
       <c r="H68" t="n">
         <v>126.75</v>
       </c>
       <c r="I68" t="n">
-        <v>815.8492431640625</v>
+        <v>815.8493041992188</v>
       </c>
       <c r="J68" t="n">
         <v>15.60000038146973</v>
@@ -2436,7 +2436,7 @@
         <v>98.40000152587891</v>
       </c>
       <c r="G69" t="n">
-        <v>1182.206298828125</v>
+        <v>1182.206420898438</v>
       </c>
       <c r="H69" t="n">
         <v>125.8499984741211</v>
@@ -2494,7 +2494,7 @@
         <v>93.80000305175781</v>
       </c>
       <c r="G71" t="n">
-        <v>1155.688110351562</v>
+        <v>1155.68798828125</v>
       </c>
       <c r="H71" t="n">
         <v>123.4000015258789</v>
@@ -2529,7 +2529,7 @@
         <v>119.5500030517578</v>
       </c>
       <c r="I72" t="n">
-        <v>982.6148071289062</v>
+        <v>982.6146850585938</v>
       </c>
       <c r="J72" t="n">
         <v>14.39999961853027</v>
@@ -2552,13 +2552,13 @@
         <v>99.09999847412109</v>
       </c>
       <c r="G73" t="n">
-        <v>1196.065673828125</v>
+        <v>1196.065551757812</v>
       </c>
       <c r="H73" t="n">
         <v>123.5999984741211</v>
       </c>
       <c r="I73" t="n">
-        <v>979.8148193359375</v>
+        <v>979.8148803710938</v>
       </c>
       <c r="J73" t="n">
         <v>14.39999961853027</v>
@@ -2581,13 +2581,13 @@
         <v>101.5500030517578</v>
       </c>
       <c r="G74" t="n">
-        <v>1231.234741210938</v>
+        <v>1231.234619140625</v>
       </c>
       <c r="H74" t="n">
         <v>125.75</v>
       </c>
       <c r="I74" t="n">
-        <v>945.7249755859375</v>
+        <v>945.7249145507812</v>
       </c>
       <c r="J74" t="n">
         <v>14.75</v>
@@ -2645,7 +2645,7 @@
         <v>128.8999938964844</v>
       </c>
       <c r="I76" t="n">
-        <v>962.5243530273438</v>
+        <v>962.5242919921875</v>
       </c>
       <c r="J76" t="n">
         <v>14.94999980926514</v>
@@ -2668,7 +2668,7 @@
         <v>105.6999969482422</v>
       </c>
       <c r="G77" t="n">
-        <v>1220.613891601562</v>
+        <v>1220.61376953125</v>
       </c>
       <c r="H77" t="n">
         <v>123.25</v>
@@ -2697,13 +2697,13 @@
         <v>114.1999969482422</v>
       </c>
       <c r="G78" t="n">
-        <v>1257.141479492188</v>
+        <v>1257.1416015625</v>
       </c>
       <c r="H78" t="n">
         <v>121.1999969482422</v>
       </c>
       <c r="I78" t="n">
-        <v>926.4696044921875</v>
+        <v>926.4695434570312</v>
       </c>
       <c r="J78" t="n">
         <v>14.5</v>
@@ -2732,7 +2732,7 @@
         <v>123</v>
       </c>
       <c r="I79" t="n">
-        <v>1111.753662109375</v>
+        <v>1111.753784179688</v>
       </c>
       <c r="J79" t="n">
         <v>14.39999961853027</v>
@@ -2755,13 +2755,13 @@
         <v>91.34999847412109</v>
       </c>
       <c r="G80" t="n">
-        <v>1277.160400390625</v>
+        <v>1277.160766601562</v>
       </c>
       <c r="H80" t="n">
         <v>120.5999984741211</v>
       </c>
       <c r="I80" t="n">
-        <v>1080.66015625</v>
+        <v>1080.660034179688</v>
       </c>
       <c r="J80" t="n">
         <v>13.94999980926514</v>
@@ -2790,7 +2790,7 @@
         <v>123.5500030517578</v>
       </c>
       <c r="I81" t="n">
-        <v>1086.947509765625</v>
+        <v>1086.947631835938</v>
       </c>
       <c r="J81" t="n">
         <v>14.25</v>
@@ -2813,13 +2813,13 @@
         <v>85</v>
       </c>
       <c r="G82" t="n">
-        <v>1259.315551757812</v>
+        <v>1259.315673828125</v>
       </c>
       <c r="H82" t="n">
         <v>124.25</v>
       </c>
       <c r="I82" t="n">
-        <v>1096.47705078125</v>
+        <v>1096.477172851562</v>
       </c>
       <c r="J82" t="n">
         <v>14.19999980926514</v>
@@ -2848,7 +2848,7 @@
         <v>116.0999984741211</v>
       </c>
       <c r="I83" t="n">
-        <v>1001.13330078125</v>
+        <v>1001.133361816406</v>
       </c>
       <c r="J83" t="n">
         <v>13.55000019073486</v>
@@ -2877,7 +2877,7 @@
         <v>115.0999984741211</v>
       </c>
       <c r="I84" t="n">
-        <v>980.355224609375</v>
+        <v>980.3552856445312</v>
       </c>
       <c r="J84" t="n">
         <v>13.39999961853027</v>
@@ -2900,13 +2900,13 @@
         <v>78.34999847412109</v>
       </c>
       <c r="G85" t="n">
-        <v>1186.939453125</v>
+        <v>1186.939331054688</v>
       </c>
       <c r="H85" t="n">
         <v>111.3000030517578</v>
       </c>
       <c r="I85" t="n">
-        <v>1049.32080078125</v>
+        <v>1049.321044921875</v>
       </c>
       <c r="J85" t="n">
         <v>13.10000038146973</v>
@@ -2935,7 +2935,7 @@
         <v>112.3000030517578</v>
       </c>
       <c r="I86" t="n">
-        <v>1002.950866699219</v>
+        <v>1002.950927734375</v>
       </c>
       <c r="J86" t="n">
         <v>13.69999980926514</v>
@@ -2958,13 +2958,13 @@
         <v>72.80000305175781</v>
       </c>
       <c r="G87" t="n">
-        <v>1120.813232421875</v>
+        <v>1120.813354492188</v>
       </c>
       <c r="H87" t="n">
         <v>108.1999969482422</v>
       </c>
       <c r="I87" t="n">
-        <v>953.977294921875</v>
+        <v>953.9772338867188</v>
       </c>
       <c r="J87" t="n">
         <v>13.10000038146973</v>
@@ -3016,13 +3016,13 @@
         <v>72.75</v>
       </c>
       <c r="G89" t="n">
-        <v>1086.731323242188</v>
+        <v>1086.731201171875</v>
       </c>
       <c r="H89" t="n">
         <v>100.9000015258789</v>
       </c>
       <c r="I89" t="n">
-        <v>943.9075317382812</v>
+        <v>943.907470703125</v>
       </c>
       <c r="J89" t="n">
         <v>12.39999961853027</v>
@@ -3051,7 +3051,7 @@
         <v>102.0500030517578</v>
       </c>
       <c r="I90" t="n">
-        <v>955.7456665039062</v>
+        <v>955.74560546875</v>
       </c>
       <c r="J90" t="n">
         <v>12.5</v>
@@ -3074,7 +3074,7 @@
         <v>74.59999847412109</v>
       </c>
       <c r="G91" t="n">
-        <v>1099.322509765625</v>
+        <v>1099.322387695312</v>
       </c>
       <c r="H91" t="n">
         <v>98.30000305175781</v>
@@ -3109,7 +3109,7 @@
         <v>107.0500030517578</v>
       </c>
       <c r="I92" t="n">
-        <v>1028.100708007812</v>
+        <v>1028.1005859375</v>
       </c>
       <c r="J92" t="n">
         <v>12.44999980926514</v>
@@ -3138,7 +3138,7 @@
         <v>104.0999984741211</v>
       </c>
       <c r="I93" t="n">
-        <v>1021.715026855469</v>
+        <v>1021.715087890625</v>
       </c>
       <c r="J93" t="n">
         <v>12.44999980926514</v>
@@ -3167,7 +3167,7 @@
         <v>102.0999984741211</v>
       </c>
       <c r="I94" t="n">
-        <v>977.5062255859375</v>
+        <v>977.5062866210938</v>
       </c>
       <c r="J94" t="n">
         <v>12.30000019073486</v>
@@ -3196,7 +3196,7 @@
         <v>104</v>
       </c>
       <c r="I95" t="n">
-        <v>1021.665954589844</v>
+        <v>1021.665832519531</v>
       </c>
       <c r="J95" t="n">
         <v>12.85000038146973</v>
@@ -3219,13 +3219,13 @@
         <v>80.05000305175781</v>
       </c>
       <c r="G96" t="n">
-        <v>1180.711669921875</v>
+        <v>1180.711791992188</v>
       </c>
       <c r="H96" t="n">
         <v>101.6999969482422</v>
       </c>
       <c r="I96" t="n">
-        <v>979.0289916992188</v>
+        <v>979.0288696289062</v>
       </c>
       <c r="J96" t="n">
         <v>12.39999961853027</v>
@@ -3254,7 +3254,7 @@
         <v>100.9000015258789</v>
       </c>
       <c r="I97" t="n">
-        <v>945.7249755859375</v>
+        <v>945.7249145507812</v>
       </c>
       <c r="J97" t="n">
         <v>12.55000019073486</v>
@@ -3283,7 +3283,7 @@
         <v>100.6500015258789</v>
       </c>
       <c r="I98" t="n">
-        <v>869.9805297851562</v>
+        <v>869.98046875</v>
       </c>
       <c r="J98" t="n">
         <v>12.10000038146973</v>
@@ -3306,7 +3306,7 @@
         <v>71.59999847412109</v>
       </c>
       <c r="G99" t="n">
-        <v>1171.744018554688</v>
+        <v>1171.743896484375</v>
       </c>
       <c r="H99" t="n">
         <v>100.3499984741211</v>
@@ -3341,7 +3341,7 @@
         <v>99.84999847412109</v>
       </c>
       <c r="I100" t="n">
-        <v>871.9945678710938</v>
+        <v>871.9944458007812</v>
       </c>
       <c r="J100" t="n">
         <v>11.85000038146973</v>
@@ -3364,13 +3364,13 @@
         <v>73.15000152587891</v>
       </c>
       <c r="G101" t="n">
-        <v>1206.935546875</v>
+        <v>1206.935668945312</v>
       </c>
       <c r="H101" t="n">
         <v>102.5500030517578</v>
       </c>
       <c r="I101" t="n">
-        <v>914.9260864257812</v>
+        <v>914.9262084960938</v>
       </c>
       <c r="J101" t="n">
         <v>12</v>
@@ -3393,7 +3393,7 @@
         <v>75.5</v>
       </c>
       <c r="G102" t="n">
-        <v>1192.37451171875</v>
+        <v>1192.374267578125</v>
       </c>
       <c r="H102" t="n">
         <v>107.9499969482422</v>
@@ -3422,13 +3422,13 @@
         <v>76.05000305175781</v>
       </c>
       <c r="G103" t="n">
-        <v>1192.759399414062</v>
+        <v>1192.75927734375</v>
       </c>
       <c r="H103" t="n">
         <v>108.0500030517578</v>
       </c>
       <c r="I103" t="n">
-        <v>929.4659423828125</v>
+        <v>929.4658813476562</v>
       </c>
       <c r="J103" t="n">
         <v>13.19999980926514</v>
@@ -3451,7 +3451,7 @@
         <v>76.5</v>
       </c>
       <c r="G104" t="n">
-        <v>1233.88427734375</v>
+        <v>1233.884521484375</v>
       </c>
       <c r="H104" t="n">
         <v>109.3000030517578</v>
@@ -3509,7 +3509,7 @@
         <v>74.65000152587891</v>
       </c>
       <c r="G106" t="n">
-        <v>1253.47314453125</v>
+        <v>1253.473022460938</v>
       </c>
       <c r="H106" t="n">
         <v>105.1500015258789</v>
@@ -3573,7 +3573,7 @@
         <v>104.8499984741211</v>
       </c>
       <c r="I108" t="n">
-        <v>969.3521728515625</v>
+        <v>969.3522338867188</v>
       </c>
       <c r="J108" t="n">
         <v>13.85000038146973</v>
@@ -3602,7 +3602,7 @@
         <v>104.4499969482422</v>
       </c>
       <c r="I109" t="n">
-        <v>974.7555541992188</v>
+        <v>974.75537109375</v>
       </c>
       <c r="J109" t="n">
         <v>13.94999980926514</v>
@@ -3625,13 +3625,13 @@
         <v>78.59999847412109</v>
       </c>
       <c r="G110" t="n">
-        <v>1229.33251953125</v>
+        <v>1229.332397460938</v>
       </c>
       <c r="H110" t="n">
         <v>103.5999984741211</v>
       </c>
       <c r="I110" t="n">
-        <v>944.054931640625</v>
+        <v>944.0548706054688</v>
       </c>
       <c r="J110" t="n">
         <v>13.55000019073486</v>
@@ -3718,7 +3718,7 @@
         <v>95.5</v>
       </c>
       <c r="I113" t="n">
-        <v>876.5136108398438</v>
+        <v>876.513671875</v>
       </c>
       <c r="J113" t="n">
         <v>12.64999961853027</v>
@@ -3741,13 +3741,13 @@
         <v>67.25</v>
       </c>
       <c r="G114" t="n">
-        <v>1159.4697265625</v>
+        <v>1159.469848632812</v>
       </c>
       <c r="H114" t="n">
         <v>95.40000152587891</v>
       </c>
       <c r="I114" t="n">
-        <v>825.7225952148438</v>
+        <v>825.7225341796875</v>
       </c>
       <c r="J114" t="n">
         <v>12.05000019073486</v>
@@ -3776,7 +3776,7 @@
         <v>95.59999847412109</v>
       </c>
       <c r="I115" t="n">
-        <v>833.4837036132812</v>
+        <v>833.4837646484375</v>
       </c>
       <c r="J115" t="n">
         <v>12.14999961853027</v>
@@ -3799,13 +3799,13 @@
         <v>58.90000152587891</v>
       </c>
       <c r="G116" t="n">
-        <v>1151.792846679688</v>
+        <v>1151.79296875</v>
       </c>
       <c r="H116" t="n">
         <v>90.65000152587891</v>
       </c>
       <c r="I116" t="n">
-        <v>730.1824340820312</v>
+        <v>730.182373046875</v>
       </c>
       <c r="J116" t="n">
         <v>11.10000038146973</v>
@@ -3828,13 +3828,13 @@
         <v>62.29999923706055</v>
       </c>
       <c r="G117" t="n">
-        <v>1170.385131835938</v>
+        <v>1170.38525390625</v>
       </c>
       <c r="H117" t="n">
         <v>94.5</v>
       </c>
       <c r="I117" t="n">
-        <v>770.3141479492188</v>
+        <v>770.314208984375</v>
       </c>
       <c r="J117" t="n">
         <v>11.44999980926514</v>
@@ -3857,13 +3857,13 @@
         <v>59.15000152587891</v>
       </c>
       <c r="G118" t="n">
-        <v>1134.831176757812</v>
+        <v>1134.8310546875</v>
       </c>
       <c r="H118" t="n">
         <v>91.19999694824219</v>
       </c>
       <c r="I118" t="n">
-        <v>743.8380126953125</v>
+        <v>743.8379516601562</v>
       </c>
       <c r="J118" t="n">
         <v>11.39999961853027</v>
@@ -3886,7 +3886,7 @@
         <v>61.40000152587891</v>
       </c>
       <c r="G119" t="n">
-        <v>1116.420043945312</v>
+        <v>1116.419921875</v>
       </c>
       <c r="H119" t="n">
         <v>90.30000305175781</v>
@@ -4002,13 +4002,13 @@
         <v>68.19999694824219</v>
       </c>
       <c r="G123" t="n">
-        <v>1168.596069335938</v>
+        <v>1168.59619140625</v>
       </c>
       <c r="H123" t="n">
         <v>92.09999847412109</v>
       </c>
       <c r="I123" t="n">
-        <v>938.111328125</v>
+        <v>938.1112670898438</v>
       </c>
       <c r="J123" t="n">
         <v>11.75</v>
@@ -4037,7 +4037,7 @@
         <v>90.59999847412109</v>
       </c>
       <c r="I124" t="n">
-        <v>935.9990234375</v>
+        <v>935.9990844726562</v>
       </c>
       <c r="J124" t="n">
         <v>11.5</v>
@@ -4066,7 +4066,7 @@
         <v>91.09999847412109</v>
       </c>
       <c r="I125" t="n">
-        <v>920.8206787109375</v>
+        <v>920.8206176757812</v>
       </c>
       <c r="J125" t="n">
         <v>11.39999961853027</v>
@@ -4089,7 +4089,7 @@
         <v>65.55000305175781</v>
       </c>
       <c r="G126" t="n">
-        <v>1093.2080078125</v>
+        <v>1093.207885742188</v>
       </c>
       <c r="H126" t="n">
         <v>94.5</v>
@@ -4118,13 +4118,13 @@
         <v>65.40000152587891</v>
       </c>
       <c r="G127" t="n">
-        <v>1102.062622070312</v>
+        <v>1102.0625</v>
       </c>
       <c r="H127" t="n">
         <v>93.15000152587891</v>
       </c>
       <c r="I127" t="n">
-        <v>927.0098266601562</v>
+        <v>927.0099487304688</v>
       </c>
       <c r="J127" t="n">
         <v>11.35000038146973</v>
@@ -4147,7 +4147,7 @@
         <v>65.30000305175781</v>
       </c>
       <c r="G128" t="n">
-        <v>1092.369995117188</v>
+        <v>1092.3701171875</v>
       </c>
       <c r="H128" t="n">
         <v>91.75</v>
@@ -4182,7 +4182,7 @@
         <v>94.90000152587891</v>
       </c>
       <c r="I129" t="n">
-        <v>936.490234375</v>
+        <v>936.4902954101562</v>
       </c>
       <c r="J129" t="n">
         <v>11.44999980926514</v>
@@ -4205,7 +4205,7 @@
         <v>67.40000152587891</v>
       </c>
       <c r="G130" t="n">
-        <v>1083.10791015625</v>
+        <v>1083.108032226562</v>
       </c>
       <c r="H130" t="n">
         <v>94.80000305175781</v>
@@ -4234,13 +4234,13 @@
         <v>68.30000305175781</v>
       </c>
       <c r="G131" t="n">
-        <v>1097.827880859375</v>
+        <v>1097.827758789062</v>
       </c>
       <c r="H131" t="n">
         <v>101.3499984741211</v>
       </c>
       <c r="I131" t="n">
-        <v>940.5672607421875</v>
+        <v>940.5673217773438</v>
       </c>
       <c r="J131" t="n">
         <v>11.64999961853027</v>
@@ -4263,7 +4263,7 @@
         <v>69.19999694824219</v>
       </c>
       <c r="G132" t="n">
-        <v>1096.26513671875</v>
+        <v>1096.265014648438</v>
       </c>
       <c r="H132" t="n">
         <v>102.5999984741211</v>
@@ -4321,13 +4321,13 @@
         <v>69.75</v>
       </c>
       <c r="G134" t="n">
-        <v>1085.712158203125</v>
+        <v>1085.712036132812</v>
       </c>
       <c r="H134" t="n">
         <v>100.4000015258789</v>
       </c>
       <c r="I134" t="n">
-        <v>937.9638061523438</v>
+        <v>937.9638671875</v>
       </c>
       <c r="J134" t="n">
         <v>11.39999961853027</v>
@@ -4379,7 +4379,7 @@
         <v>68.15000152587891</v>
       </c>
       <c r="G136" t="n">
-        <v>1097.08056640625</v>
+        <v>1097.080322265625</v>
       </c>
       <c r="H136" t="n">
         <v>102.25</v>
@@ -4437,7 +4437,7 @@
         <v>67</v>
       </c>
       <c r="G138" t="n">
-        <v>1133.653564453125</v>
+        <v>1133.653442382812</v>
       </c>
       <c r="H138" t="n">
         <v>104.4000015258789</v>
@@ -4472,7 +4472,7 @@
         <v>105.8000030517578</v>
       </c>
       <c r="I139" t="n">
-        <v>961.934814453125</v>
+        <v>961.9349365234375</v>
       </c>
       <c r="J139" t="n">
         <v>11.85000038146973</v>
@@ -4588,7 +4588,7 @@
         <v>115.8499984741211</v>
       </c>
       <c r="I143" t="n">
-        <v>945.8232421875</v>
+        <v>945.8231811523438</v>
       </c>
       <c r="J143" t="n">
         <v>11.89999961853027</v>
@@ -4611,13 +4611,13 @@
         <v>65.15000152587891</v>
       </c>
       <c r="G144" t="n">
-        <v>1112.86474609375</v>
+        <v>1112.864624023438</v>
       </c>
       <c r="H144" t="n">
         <v>114.25</v>
       </c>
       <c r="I144" t="n">
-        <v>955.1071166992188</v>
+        <v>955.1070556640625</v>
       </c>
       <c r="J144" t="n">
         <v>11.75</v>
@@ -4669,13 +4669,13 @@
         <v>66.94999694824219</v>
       </c>
       <c r="G146" t="n">
-        <v>1166.195678710938</v>
+        <v>1166.195556640625</v>
       </c>
       <c r="H146" t="n">
         <v>123.25</v>
       </c>
       <c r="I146" t="n">
-        <v>1014.592529296875</v>
+        <v>1014.592468261719</v>
       </c>
       <c r="J146" t="n">
         <v>13</v>
@@ -4698,13 +4698,13 @@
         <v>68.05000305175781</v>
       </c>
       <c r="G147" t="n">
-        <v>1170.634399414062</v>
+        <v>1170.63427734375</v>
       </c>
       <c r="H147" t="n">
         <v>128.6999969482422</v>
       </c>
       <c r="I147" t="n">
-        <v>994.7967529296875</v>
+        <v>994.7968139648438</v>
       </c>
       <c r="J147" t="n">
         <v>13.30000019073486</v>
@@ -4727,7 +4727,7 @@
         <v>69.19999694824219</v>
       </c>
       <c r="G148" t="n">
-        <v>1180.462646484375</v>
+        <v>1180.462524414062</v>
       </c>
       <c r="H148" t="n">
         <v>125.0500030517578</v>
@@ -4762,7 +4762,7 @@
         <v>121.3499984741211</v>
       </c>
       <c r="I149" t="n">
-        <v>952.7492065429688</v>
+        <v>952.749267578125</v>
       </c>
       <c r="J149" t="n">
         <v>13.19999980926514</v>
@@ -4791,7 +4791,7 @@
         <v>120</v>
       </c>
       <c r="I150" t="n">
-        <v>942.041015625</v>
+        <v>942.0408325195312</v>
       </c>
       <c r="J150" t="n">
         <v>13.14999961853027</v>
@@ -4843,13 +4843,13 @@
         <v>66.65000152587891</v>
       </c>
       <c r="G152" t="n">
-        <v>1169.66064453125</v>
+        <v>1169.660522460938</v>
       </c>
       <c r="H152" t="n">
         <v>117.5500030517578</v>
       </c>
       <c r="I152" t="n">
-        <v>944.4969482421875</v>
+        <v>944.4970092773438</v>
       </c>
       <c r="J152" t="n">
         <v>14.14999961853027</v>
@@ -4907,7 +4907,7 @@
         <v>115.1500015258789</v>
       </c>
       <c r="I154" t="n">
-        <v>954.0263671875</v>
+        <v>954.0263061523438</v>
       </c>
       <c r="J154" t="n">
         <v>13.39999961853027</v>
@@ -4959,13 +4959,13 @@
         <v>72.55000305175781</v>
       </c>
       <c r="G156" t="n">
-        <v>1207.094116210938</v>
+        <v>1207.09423828125</v>
       </c>
       <c r="H156" t="n">
         <v>121.8000030517578</v>
       </c>
       <c r="I156" t="n">
-        <v>975.4922485351562</v>
+        <v>975.4923095703125</v>
       </c>
       <c r="J156" t="n">
         <v>13.64999961853027</v>
@@ -4994,7 +4994,7 @@
         <v>129.8999938964844</v>
       </c>
       <c r="I157" t="n">
-        <v>1020.879943847656</v>
+        <v>1020.880004882812</v>
       </c>
       <c r="J157" t="n">
         <v>14.19999980926514</v>
@@ -5017,7 +5017,7 @@
         <v>73.75</v>
       </c>
       <c r="G158" t="n">
-        <v>1187.72216796875</v>
+        <v>1187.722045898438</v>
       </c>
       <c r="H158" t="n">
         <v>135.6000061035156</v>
@@ -5046,13 +5046,13 @@
         <v>72.15000152587891</v>
       </c>
       <c r="G159" t="n">
-        <v>1184.427856445312</v>
+        <v>1184.427734375</v>
       </c>
       <c r="H159" t="n">
         <v>140.6999969482422</v>
       </c>
       <c r="I159" t="n">
-        <v>973.0361328125</v>
+        <v>973.0361938476562</v>
       </c>
       <c r="J159" t="n">
         <v>15.64999961853027</v>
@@ -5075,13 +5075,13 @@
         <v>72.25</v>
       </c>
       <c r="G160" t="n">
-        <v>1202.694580078125</v>
+        <v>1202.694458007812</v>
       </c>
       <c r="H160" t="n">
         <v>138.6999969482422</v>
       </c>
       <c r="I160" t="n">
-        <v>1004.915649414062</v>
+        <v>1004.915710449219</v>
       </c>
       <c r="J160" t="n">
         <v>15.39999961853027</v>
@@ -5104,7 +5104,7 @@
         <v>74.15000152587891</v>
       </c>
       <c r="G161" t="n">
-        <v>1199.490844726562</v>
+        <v>1199.491088867188</v>
       </c>
       <c r="H161" t="n">
         <v>139.6999969482422</v>
@@ -5133,7 +5133,7 @@
         <v>74.05000305175781</v>
       </c>
       <c r="G162" t="n">
-        <v>1195.9921875</v>
+        <v>1195.992065429688</v>
       </c>
       <c r="H162" t="n">
         <v>139.75</v>
@@ -5162,13 +5162,13 @@
         <v>74</v>
       </c>
       <c r="G163" t="n">
-        <v>1189.607788085938</v>
+        <v>1189.60791015625</v>
       </c>
       <c r="H163" t="n">
         <v>157.3500061035156</v>
       </c>
       <c r="I163" t="n">
-        <v>997.1054077148438</v>
+        <v>997.10546875</v>
       </c>
       <c r="J163" t="n">
         <v>16.25</v>
@@ -5220,13 +5220,13 @@
         <v>70.59999847412109</v>
       </c>
       <c r="G165" t="n">
-        <v>1198.672973632812</v>
+        <v>1198.673095703125</v>
       </c>
       <c r="H165" t="n">
         <v>162</v>
       </c>
       <c r="I165" t="n">
-       